--- a/public/worldcup.xlsx
+++ b/public/worldcup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rylanpaul/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D9BE58A-1EB0-544F-AA37-CD1BAFF9E9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01B6D0D5-8BEF-0744-A445-2947AF29247D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T" sheetId="1" state="hidden" r:id="rId1"/>
@@ -12746,7 +12746,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="51" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="200">
+  <cellXfs count="196">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
@@ -13280,60 +13280,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="11" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="11" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -13341,10 +13311,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -13427,23 +13393,49 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection hidden="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -38576,60 +38568,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" s="131" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="154" t="s">
+      <c r="A1" s="158" t="s">
         <v>3698</v>
       </c>
-      <c r="B1" s="157" t="s">
+      <c r="B1" s="155" t="s">
         <v>3705</v>
       </c>
       <c r="C1" s="156"/>
       <c r="D1" s="156"/>
-      <c r="E1" s="158"/>
+      <c r="E1" s="157"/>
       <c r="F1" s="156" t="s">
         <v>3706</v>
       </c>
       <c r="G1" s="156"/>
       <c r="H1" s="156"/>
       <c r="I1" s="156"/>
-      <c r="J1" s="157" t="s">
+      <c r="J1" s="155" t="s">
         <v>3707</v>
       </c>
       <c r="K1" s="156"/>
       <c r="L1" s="156"/>
       <c r="M1" s="156"/>
-      <c r="N1" s="157" t="s">
+      <c r="N1" s="155" t="s">
         <v>3708</v>
       </c>
       <c r="O1" s="156"/>
       <c r="P1" s="156"/>
-      <c r="Q1" s="158"/>
+      <c r="Q1" s="157"/>
       <c r="R1" s="156" t="s">
         <v>3709</v>
       </c>
       <c r="S1" s="156"/>
       <c r="T1" s="156"/>
       <c r="U1" s="156"/>
-      <c r="V1" s="157" t="s">
+      <c r="V1" s="155" t="s">
         <v>3710</v>
       </c>
       <c r="W1" s="156"/>
       <c r="X1" s="156"/>
-      <c r="Y1" s="158"/>
+      <c r="Y1" s="157"/>
       <c r="Z1" s="156" t="s">
         <v>3711</v>
       </c>
       <c r="AA1" s="156"/>
       <c r="AB1" s="156"/>
       <c r="AC1" s="156"/>
-      <c r="AD1" s="157" t="s">
+      <c r="AD1" s="155" t="s">
         <v>3712</v>
       </c>
       <c r="AE1" s="156"/>
       <c r="AF1" s="156"/>
-      <c r="AG1" s="158"/>
+      <c r="AG1" s="157"/>
     </row>
     <row r="2" spans="1:33" s="131" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="155"/>
+      <c r="A2" s="159"/>
       <c r="B2" s="137" t="s">
         <v>3713</v>
       </c>
@@ -38714,7 +38706,7 @@
         <f>IFERROR(_xlfn.XLOOKUP(B3,Rounds!A$2:A$25,Rounds!D$2:D$25), _xlfn.XLOOKUP(B3,Rounds!D$2:D$25,Rounds!A$2:A$25))</f>
         <v>Tunisia</v>
       </c>
-      <c r="F3" s="195"/>
+      <c r="F3" s="154"/>
       <c r="G3" s="142" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(F3,Rounds!E$2:E$25,Rounds!F$2:F$25), _xlfn.XLOOKUP(F3,Rounds!H$2:H$25,Rounds!G$2:G$25))</f>
         <v>#N/A</v>
@@ -38807,11 +38799,11 @@
       <c r="B4" s="145" t="s">
         <v>1798</v>
       </c>
-      <c r="C4" s="199" t="e">
+      <c r="C4" s="146" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(B4,Rounds!A$2:A$25,Rounds!B$2:B$25), _xlfn.XLOOKUP(B4,Rounds!D$2:D$25,Rounds!C$2:C$25))</f>
         <v>#N/A</v>
       </c>
-      <c r="D4" s="199" t="e">
+      <c r="D4" s="146" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(B4,Rounds!A$2:A$25,Rounds!C$2:C$25), _xlfn.XLOOKUP(B4,Rounds!D$2:D$25,Rounds!B$2:B$25))</f>
         <v>#N/A</v>
       </c>
@@ -38819,12 +38811,11 @@
         <f>IFERROR(_xlfn.XLOOKUP(B4,Rounds!A$2:A$25,Rounds!D$2:D$25), _xlfn.XLOOKUP(B4,Rounds!D$2:D$25,Rounds!A$2:A$25))</f>
         <v>Qatar</v>
       </c>
-      <c r="F4" s="196"/>
-      <c r="G4" s="199" t="e">
+      <c r="G4" s="146" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(F4,Rounds!E$2:E$25,Rounds!F$2:F$25), _xlfn.XLOOKUP(F4,Rounds!H$2:H$25,Rounds!G$2:G$25))</f>
         <v>#N/A</v>
       </c>
-      <c r="H4" s="199" t="e">
+      <c r="H4" s="146" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(F4,Rounds!E$2:E$25,Rounds!G$2:G$25), _xlfn.XLOOKUP(F4,Rounds!H$2:H$25,Rounds!F$2:F$25))</f>
         <v>#N/A</v>
       </c>
@@ -38832,11 +38823,11 @@
         <f>IFERROR(_xlfn.XLOOKUP(F4,Rounds!E$2:E$25,Rounds!H$2:H$25), _xlfn.XLOOKUP(F4,Rounds!H$2:H$25,Rounds!E$2:E$25))</f>
         <v>#N/A</v>
       </c>
-      <c r="K4" s="199" t="e">
+      <c r="K4" s="146" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(J4,Rounds!I$2:I$25,Rounds!J$2:J$25), _xlfn.XLOOKUP(J4,Rounds!L$2:L$25,Rounds!K$2:K$25))</f>
         <v>#N/A</v>
       </c>
-      <c r="L4" s="199" t="e">
+      <c r="L4" s="146" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(J4,Rounds!I$2:I$25,Rounds!K$2:K$25), _xlfn.XLOOKUP(J4,Rounds!L$2:L$25,Rounds!J$2:J$25))</f>
         <v>#N/A</v>
       </c>
@@ -38844,11 +38835,11 @@
         <f>IFERROR(_xlfn.XLOOKUP(J4,Rounds!I$2:I$25,Rounds!L$2:L$25), _xlfn.XLOOKUP(J4,Rounds!L$2:L$25,Rounds!I$2:I$25))</f>
         <v>#N/A</v>
       </c>
-      <c r="O4" s="199" t="e">
+      <c r="O4" s="146" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(N4,Rounds!M$2:M$17,Rounds!N$2:N$17), _xlfn.XLOOKUP(N4,Rounds!P$2:P$17,Rounds!O$2:O$17))</f>
         <v>#N/A</v>
       </c>
-      <c r="P4" s="199" t="e">
+      <c r="P4" s="146" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(N4,Rounds!M$2:M$17,Rounds!O$2:O$17), _xlfn.XLOOKUP(N4,Rounds!P$2:P$17,Rounds!N$2:N$17))</f>
         <v>#N/A</v>
       </c>
@@ -38856,11 +38847,11 @@
         <f>IFERROR(_xlfn.XLOOKUP(N4,Rounds!M$2:M$17,Rounds!P$2:P$17), _xlfn.XLOOKUP(N4,Rounds!P$2:P$17,Rounds!M$2:M$17))</f>
         <v>#N/A</v>
       </c>
-      <c r="S4" s="199" t="e">
+      <c r="S4" s="146" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(R4,Rounds!Q$2:Q$9,Rounds!R$2:R$9), _xlfn.XLOOKUP(R4,Rounds!T$2:T$9,Rounds!S$2:S$9))</f>
         <v>#N/A</v>
       </c>
-      <c r="T4" s="199" t="e">
+      <c r="T4" s="146" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(R4,Rounds!Q$2:Q$9,Rounds!S$2:S$9), _xlfn.XLOOKUP(R4,Rounds!T$2:T$9,Rounds!R$2:R$9))</f>
         <v>#N/A</v>
       </c>
@@ -38912,11 +38903,11 @@
       <c r="B5" s="132" t="s">
         <v>2573</v>
       </c>
-      <c r="C5" s="198" t="e">
+      <c r="C5" s="82" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(B5,Rounds!A$2:A$25,Rounds!B$2:B$25), _xlfn.XLOOKUP(B5,Rounds!D$2:D$25,Rounds!C$2:C$25))</f>
         <v>#N/A</v>
       </c>
-      <c r="D5" s="198" t="e">
+      <c r="D5" s="82" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(B5,Rounds!A$2:A$25,Rounds!C$2:C$25), _xlfn.XLOOKUP(B5,Rounds!D$2:D$25,Rounds!B$2:B$25))</f>
         <v>#N/A</v>
       </c>
@@ -38924,12 +38915,11 @@
         <f>IFERROR(_xlfn.XLOOKUP(B5,Rounds!A$2:A$25,Rounds!D$2:D$25), _xlfn.XLOOKUP(B5,Rounds!D$2:D$25,Rounds!A$2:A$25))</f>
         <v>Uzbekistan</v>
       </c>
-      <c r="F5" s="197"/>
-      <c r="G5" s="198" t="e">
+      <c r="G5" s="82" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(F5,Rounds!E$2:E$25,Rounds!F$2:F$25), _xlfn.XLOOKUP(F5,Rounds!H$2:H$25,Rounds!G$2:G$25))</f>
         <v>#N/A</v>
       </c>
-      <c r="H5" s="198" t="e">
+      <c r="H5" s="82" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(F5,Rounds!E$2:E$25,Rounds!G$2:G$25), _xlfn.XLOOKUP(F5,Rounds!H$2:H$25,Rounds!F$2:F$25))</f>
         <v>#N/A</v>
       </c>
@@ -38937,11 +38927,11 @@
         <f>IFERROR(_xlfn.XLOOKUP(F5,Rounds!E$2:E$25,Rounds!H$2:H$25), _xlfn.XLOOKUP(F5,Rounds!H$2:H$25,Rounds!E$2:E$25))</f>
         <v>#N/A</v>
       </c>
-      <c r="K5" s="198" t="e">
+      <c r="K5" s="82" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(J5,Rounds!I$2:I$25,Rounds!J$2:J$25), _xlfn.XLOOKUP(J5,Rounds!L$2:L$25,Rounds!K$2:K$25))</f>
         <v>#N/A</v>
       </c>
-      <c r="L5" s="198" t="e">
+      <c r="L5" s="82" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(J5,Rounds!I$2:I$25,Rounds!K$2:K$25), _xlfn.XLOOKUP(J5,Rounds!L$2:L$25,Rounds!J$2:J$25))</f>
         <v>#N/A</v>
       </c>
@@ -38949,11 +38939,11 @@
         <f>IFERROR(_xlfn.XLOOKUP(J5,Rounds!I$2:I$25,Rounds!L$2:L$25), _xlfn.XLOOKUP(J5,Rounds!L$2:L$25,Rounds!I$2:I$25))</f>
         <v>#N/A</v>
       </c>
-      <c r="O5" s="198" t="e">
+      <c r="O5" s="82" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(N5,Rounds!M$2:M$17,Rounds!N$2:N$17), _xlfn.XLOOKUP(N5,Rounds!P$2:P$17,Rounds!O$2:O$17))</f>
         <v>#N/A</v>
       </c>
-      <c r="P5" s="198" t="e">
+      <c r="P5" s="82" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(N5,Rounds!M$2:M$17,Rounds!O$2:O$17), _xlfn.XLOOKUP(N5,Rounds!P$2:P$17,Rounds!N$2:N$17))</f>
         <v>#N/A</v>
       </c>
@@ -38961,11 +38951,11 @@
         <f>IFERROR(_xlfn.XLOOKUP(N5,Rounds!M$2:M$17,Rounds!P$2:P$17), _xlfn.XLOOKUP(N5,Rounds!P$2:P$17,Rounds!M$2:M$17))</f>
         <v>#N/A</v>
       </c>
-      <c r="S5" s="198" t="e">
+      <c r="S5" s="82" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(R5,Rounds!Q$2:Q$9,Rounds!R$2:R$9), _xlfn.XLOOKUP(R5,Rounds!T$2:T$9,Rounds!S$2:S$9))</f>
         <v>#N/A</v>
       </c>
-      <c r="T5" s="198" t="e">
+      <c r="T5" s="82" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(R5,Rounds!Q$2:Q$9,Rounds!S$2:S$9), _xlfn.XLOOKUP(R5,Rounds!T$2:T$9,Rounds!R$2:R$9))</f>
         <v>#N/A</v>
       </c>
@@ -39017,11 +39007,11 @@
       <c r="B6" s="145" t="s">
         <v>2395</v>
       </c>
-      <c r="C6" s="199" t="e">
+      <c r="C6" s="146" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(B6,Rounds!A$2:A$25,Rounds!B$2:B$25), _xlfn.XLOOKUP(B6,Rounds!D$2:D$25,Rounds!C$2:C$25))</f>
         <v>#N/A</v>
       </c>
-      <c r="D6" s="199" t="e">
+      <c r="D6" s="146" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(B6,Rounds!A$2:A$25,Rounds!C$2:C$25), _xlfn.XLOOKUP(B6,Rounds!D$2:D$25,Rounds!B$2:B$25))</f>
         <v>#N/A</v>
       </c>
@@ -39029,12 +39019,11 @@
         <f>IFERROR(_xlfn.XLOOKUP(B6,Rounds!A$2:A$25,Rounds!D$2:D$25), _xlfn.XLOOKUP(B6,Rounds!D$2:D$25,Rounds!A$2:A$25))</f>
         <v>Iraq</v>
       </c>
-      <c r="F6" s="196"/>
-      <c r="G6" s="199" t="e">
+      <c r="G6" s="146" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(F6,Rounds!E$2:E$25,Rounds!F$2:F$25), _xlfn.XLOOKUP(F6,Rounds!H$2:H$25,Rounds!G$2:G$25))</f>
         <v>#N/A</v>
       </c>
-      <c r="H6" s="199" t="e">
+      <c r="H6" s="146" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(F6,Rounds!E$2:E$25,Rounds!G$2:G$25), _xlfn.XLOOKUP(F6,Rounds!H$2:H$25,Rounds!F$2:F$25))</f>
         <v>#N/A</v>
       </c>
@@ -39042,11 +39031,11 @@
         <f>IFERROR(_xlfn.XLOOKUP(F6,Rounds!E$2:E$25,Rounds!H$2:H$25), _xlfn.XLOOKUP(F6,Rounds!H$2:H$25,Rounds!E$2:E$25))</f>
         <v>#N/A</v>
       </c>
-      <c r="K6" s="199" t="e">
+      <c r="K6" s="146" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(J6,Rounds!I$2:I$25,Rounds!J$2:J$25), _xlfn.XLOOKUP(J6,Rounds!L$2:L$25,Rounds!K$2:K$25))</f>
         <v>#N/A</v>
       </c>
-      <c r="L6" s="199" t="e">
+      <c r="L6" s="146" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(J6,Rounds!I$2:I$25,Rounds!K$2:K$25), _xlfn.XLOOKUP(J6,Rounds!L$2:L$25,Rounds!J$2:J$25))</f>
         <v>#N/A</v>
       </c>
@@ -39054,11 +39043,11 @@
         <f>IFERROR(_xlfn.XLOOKUP(J6,Rounds!I$2:I$25,Rounds!L$2:L$25), _xlfn.XLOOKUP(J6,Rounds!L$2:L$25,Rounds!I$2:I$25))</f>
         <v>#N/A</v>
       </c>
-      <c r="O6" s="199" t="e">
+      <c r="O6" s="146" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(N6,Rounds!M$2:M$17,Rounds!N$2:N$17), _xlfn.XLOOKUP(N6,Rounds!P$2:P$17,Rounds!O$2:O$17))</f>
         <v>#N/A</v>
       </c>
-      <c r="P6" s="199" t="e">
+      <c r="P6" s="146" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(N6,Rounds!M$2:M$17,Rounds!O$2:O$17), _xlfn.XLOOKUP(N6,Rounds!P$2:P$17,Rounds!N$2:N$17))</f>
         <v>#N/A</v>
       </c>
@@ -39066,11 +39055,11 @@
         <f>IFERROR(_xlfn.XLOOKUP(N6,Rounds!M$2:M$17,Rounds!P$2:P$17), _xlfn.XLOOKUP(N6,Rounds!P$2:P$17,Rounds!M$2:M$17))</f>
         <v>#N/A</v>
       </c>
-      <c r="S6" s="199" t="e">
+      <c r="S6" s="146" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(R6,Rounds!Q$2:Q$9,Rounds!R$2:R$9), _xlfn.XLOOKUP(R6,Rounds!T$2:T$9,Rounds!S$2:S$9))</f>
         <v>#N/A</v>
       </c>
-      <c r="T6" s="199" t="e">
+      <c r="T6" s="146" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(R6,Rounds!Q$2:Q$9,Rounds!S$2:S$9), _xlfn.XLOOKUP(R6,Rounds!T$2:T$9,Rounds!R$2:R$9))</f>
         <v>#N/A</v>
       </c>
@@ -39122,11 +39111,11 @@
       <c r="B7" s="132" t="s">
         <v>1798</v>
       </c>
-      <c r="C7" s="198" t="e">
+      <c r="C7" s="82" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(B7,Rounds!A$2:A$25,Rounds!B$2:B$25), _xlfn.XLOOKUP(B7,Rounds!D$2:D$25,Rounds!C$2:C$25))</f>
         <v>#N/A</v>
       </c>
-      <c r="D7" s="198" t="e">
+      <c r="D7" s="82" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(B7,Rounds!A$2:A$25,Rounds!C$2:C$25), _xlfn.XLOOKUP(B7,Rounds!D$2:D$25,Rounds!B$2:B$25))</f>
         <v>#N/A</v>
       </c>
@@ -39134,12 +39123,11 @@
         <f>IFERROR(_xlfn.XLOOKUP(B7,Rounds!A$2:A$25,Rounds!D$2:D$25), _xlfn.XLOOKUP(B7,Rounds!D$2:D$25,Rounds!A$2:A$25))</f>
         <v>Qatar</v>
       </c>
-      <c r="F7" s="197"/>
-      <c r="G7" s="198" t="e">
+      <c r="G7" s="82" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(F7,Rounds!E$2:E$25,Rounds!F$2:F$25), _xlfn.XLOOKUP(F7,Rounds!H$2:H$25,Rounds!G$2:G$25))</f>
         <v>#N/A</v>
       </c>
-      <c r="H7" s="198" t="e">
+      <c r="H7" s="82" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(F7,Rounds!E$2:E$25,Rounds!G$2:G$25), _xlfn.XLOOKUP(F7,Rounds!H$2:H$25,Rounds!F$2:F$25))</f>
         <v>#N/A</v>
       </c>
@@ -39147,11 +39135,11 @@
         <f>IFERROR(_xlfn.XLOOKUP(F7,Rounds!E$2:E$25,Rounds!H$2:H$25), _xlfn.XLOOKUP(F7,Rounds!H$2:H$25,Rounds!E$2:E$25))</f>
         <v>#N/A</v>
       </c>
-      <c r="K7" s="198" t="e">
+      <c r="K7" s="82" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(J7,Rounds!I$2:I$25,Rounds!J$2:J$25), _xlfn.XLOOKUP(J7,Rounds!L$2:L$25,Rounds!K$2:K$25))</f>
         <v>#N/A</v>
       </c>
-      <c r="L7" s="198" t="e">
+      <c r="L7" s="82" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(J7,Rounds!I$2:I$25,Rounds!K$2:K$25), _xlfn.XLOOKUP(J7,Rounds!L$2:L$25,Rounds!J$2:J$25))</f>
         <v>#N/A</v>
       </c>
@@ -39159,11 +39147,11 @@
         <f>IFERROR(_xlfn.XLOOKUP(J7,Rounds!I$2:I$25,Rounds!L$2:L$25), _xlfn.XLOOKUP(J7,Rounds!L$2:L$25,Rounds!I$2:I$25))</f>
         <v>#N/A</v>
       </c>
-      <c r="O7" s="198" t="e">
+      <c r="O7" s="82" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(N7,Rounds!M$2:M$17,Rounds!N$2:N$17), _xlfn.XLOOKUP(N7,Rounds!P$2:P$17,Rounds!O$2:O$17))</f>
         <v>#N/A</v>
       </c>
-      <c r="P7" s="198" t="e">
+      <c r="P7" s="82" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(N7,Rounds!M$2:M$17,Rounds!O$2:O$17), _xlfn.XLOOKUP(N7,Rounds!P$2:P$17,Rounds!N$2:N$17))</f>
         <v>#N/A</v>
       </c>
@@ -39171,11 +39159,11 @@
         <f>IFERROR(_xlfn.XLOOKUP(N7,Rounds!M$2:M$17,Rounds!P$2:P$17), _xlfn.XLOOKUP(N7,Rounds!P$2:P$17,Rounds!M$2:M$17))</f>
         <v>#N/A</v>
       </c>
-      <c r="S7" s="198" t="e">
+      <c r="S7" s="82" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(R7,Rounds!Q$2:Q$9,Rounds!R$2:R$9), _xlfn.XLOOKUP(R7,Rounds!T$2:T$9,Rounds!S$2:S$9))</f>
         <v>#N/A</v>
       </c>
-      <c r="T7" s="198" t="e">
+      <c r="T7" s="82" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(R7,Rounds!Q$2:Q$9,Rounds!S$2:S$9), _xlfn.XLOOKUP(R7,Rounds!T$2:T$9,Rounds!R$2:R$9))</f>
         <v>#N/A</v>
       </c>
@@ -39403,65 +39391,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A1" s="192" t="s">
+      <c r="A1" s="160" t="s">
         <v>3705</v>
       </c>
-      <c r="B1" s="193"/>
-      <c r="C1" s="193"/>
-      <c r="D1" s="194"/>
-      <c r="E1" s="192" t="s">
+      <c r="B1" s="161"/>
+      <c r="C1" s="161"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="160" t="s">
         <v>3706</v>
       </c>
-      <c r="F1" s="193"/>
-      <c r="G1" s="193"/>
-      <c r="H1" s="194"/>
-      <c r="I1" s="192" t="s">
+      <c r="F1" s="161"/>
+      <c r="G1" s="161"/>
+      <c r="H1" s="162"/>
+      <c r="I1" s="160" t="s">
         <v>3707</v>
       </c>
-      <c r="J1" s="193"/>
-      <c r="K1" s="193"/>
-      <c r="L1" s="194"/>
-      <c r="M1" s="192" t="s">
+      <c r="J1" s="161"/>
+      <c r="K1" s="161"/>
+      <c r="L1" s="162"/>
+      <c r="M1" s="160" t="s">
         <v>3708</v>
       </c>
-      <c r="N1" s="193"/>
-      <c r="O1" s="193"/>
-      <c r="P1" s="194"/>
-      <c r="Q1" s="192" t="s">
+      <c r="N1" s="161"/>
+      <c r="O1" s="161"/>
+      <c r="P1" s="162"/>
+      <c r="Q1" s="160" t="s">
         <v>3709</v>
       </c>
-      <c r="R1" s="193"/>
-      <c r="S1" s="193"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="192" t="s">
+      <c r="R1" s="161"/>
+      <c r="S1" s="161"/>
+      <c r="T1" s="162"/>
+      <c r="U1" s="160" t="s">
         <v>3710</v>
       </c>
-      <c r="V1" s="193"/>
-      <c r="W1" s="193"/>
-      <c r="X1" s="194"/>
-      <c r="Y1" s="192" t="s">
+      <c r="V1" s="161"/>
+      <c r="W1" s="161"/>
+      <c r="X1" s="162"/>
+      <c r="Y1" s="160" t="s">
         <v>3711</v>
       </c>
-      <c r="Z1" s="193"/>
-      <c r="AA1" s="193"/>
-      <c r="AB1" s="194"/>
-      <c r="AC1" s="192" t="s">
+      <c r="Z1" s="161"/>
+      <c r="AA1" s="161"/>
+      <c r="AB1" s="162"/>
+      <c r="AC1" s="160" t="s">
         <v>3712</v>
       </c>
-      <c r="AD1" s="193"/>
-      <c r="AE1" s="193"/>
-      <c r="AF1" s="194"/>
+      <c r="AD1" s="161"/>
+      <c r="AE1" s="161"/>
+      <c r="AF1" s="162"/>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A2" s="132" t="str" cm="1">
         <f t="array" ref="A2:D25">IF('2026 World Cup'!E7:H30="",NA(),'2026 World Cup'!E7:H30)</f>
         <v>Mexico</v>
       </c>
-      <c r="B2" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C2" s="81" t="e">
-        <v>#N/A</v>
+      <c r="B2" s="81">
+        <v>2</v>
+      </c>
+      <c r="C2" s="81">
+        <v>0</v>
       </c>
       <c r="D2" s="134" t="str">
         <v>South Africa</v>
@@ -39577,11 +39565,11 @@
       <c r="A3" s="132" t="str">
         <v>Korea Republic</v>
       </c>
-      <c r="B3" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C3" s="81" t="e">
-        <v>#N/A</v>
+      <c r="B3" s="81">
+        <v>2</v>
+      </c>
+      <c r="C3" s="81">
+        <v>1</v>
       </c>
       <c r="D3" s="134" t="str">
         <v>Czech Republic</v>
@@ -40943,25 +40931,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:95" ht="47" x14ac:dyDescent="0.2">
-      <c r="A1" s="178" t="str" cm="1">
+      <c r="A1" s="171" t="str" cm="1">
         <f t="array" ref="A1">INDEX(T,2,lang)</f>
         <v>2026 World Cup Final Tournament Schedule</v>
       </c>
-      <c r="B1" s="178"/>
-      <c r="C1" s="178"/>
-      <c r="D1" s="178"/>
-      <c r="E1" s="178"/>
-      <c r="F1" s="178"/>
-      <c r="G1" s="178"/>
-      <c r="H1" s="178"/>
-      <c r="I1" s="178"/>
-      <c r="J1" s="178"/>
-      <c r="K1" s="178"/>
-      <c r="L1" s="178"/>
-      <c r="M1" s="178"/>
-      <c r="N1" s="178"/>
-      <c r="O1" s="178"/>
-      <c r="P1" s="178"/>
+      <c r="B1" s="171"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="171"/>
+      <c r="F1" s="171"/>
+      <c r="G1" s="171"/>
+      <c r="H1" s="171"/>
+      <c r="I1" s="171"/>
+      <c r="J1" s="171"/>
+      <c r="K1" s="171"/>
+      <c r="L1" s="171"/>
+      <c r="M1" s="171"/>
+      <c r="N1" s="171"/>
+      <c r="O1" s="171"/>
+      <c r="P1" s="171"/>
       <c r="S1" s="123"/>
       <c r="T1" s="123"/>
       <c r="AC1" s="123"/>
@@ -41008,11 +40996,11 @@
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
-      <c r="O3" s="179" t="str">
+      <c r="O3" s="172" t="str">
         <f>"Language: " &amp; Settings!C4</f>
         <v>Language: English</v>
       </c>
-      <c r="P3" s="179"/>
+      <c r="P3" s="172"/>
       <c r="S3" s="123"/>
       <c r="T3" s="123"/>
       <c r="AC3" s="123"/>
@@ -41030,43 +41018,43 @@
     </row>
     <row r="4" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:95" x14ac:dyDescent="0.2">
-      <c r="A5" s="180" t="str" cm="1">
+      <c r="A5" s="173" t="str" cm="1">
         <f t="array" ref="A5">INDEX(T,3,lang)</f>
         <v>Group Stage</v>
       </c>
-      <c r="B5" s="181"/>
-      <c r="C5" s="181"/>
-      <c r="D5" s="181"/>
-      <c r="E5" s="181"/>
-      <c r="F5" s="181"/>
-      <c r="G5" s="181"/>
-      <c r="H5" s="182"/>
-      <c r="J5" s="186" t="s">
+      <c r="B5" s="174"/>
+      <c r="C5" s="174"/>
+      <c r="D5" s="174"/>
+      <c r="E5" s="174"/>
+      <c r="F5" s="174"/>
+      <c r="G5" s="174"/>
+      <c r="H5" s="175"/>
+      <c r="J5" s="179" t="s">
         <v>3166</v>
       </c>
-      <c r="K5" s="187"/>
-      <c r="L5" s="187"/>
-      <c r="M5" s="187"/>
-      <c r="N5" s="187"/>
-      <c r="O5" s="187"/>
-      <c r="P5" s="188"/>
+      <c r="K5" s="180"/>
+      <c r="L5" s="180"/>
+      <c r="M5" s="180"/>
+      <c r="N5" s="180"/>
+      <c r="O5" s="180"/>
+      <c r="P5" s="181"/>
     </row>
     <row r="6" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="183"/>
-      <c r="B6" s="184"/>
-      <c r="C6" s="184"/>
-      <c r="D6" s="184"/>
-      <c r="E6" s="184"/>
-      <c r="F6" s="184"/>
-      <c r="G6" s="184"/>
-      <c r="H6" s="185"/>
-      <c r="J6" s="189"/>
-      <c r="K6" s="190"/>
-      <c r="L6" s="190"/>
-      <c r="M6" s="190"/>
-      <c r="N6" s="190"/>
-      <c r="O6" s="190"/>
-      <c r="P6" s="191"/>
+      <c r="A6" s="176"/>
+      <c r="B6" s="177"/>
+      <c r="C6" s="177"/>
+      <c r="D6" s="177"/>
+      <c r="E6" s="177"/>
+      <c r="F6" s="177"/>
+      <c r="G6" s="177"/>
+      <c r="H6" s="178"/>
+      <c r="J6" s="182"/>
+      <c r="K6" s="183"/>
+      <c r="L6" s="183"/>
+      <c r="M6" s="183"/>
+      <c r="N6" s="183"/>
+      <c r="O6" s="183"/>
+      <c r="P6" s="184"/>
       <c r="R6" s="123" t="s">
         <v>3167</v>
       </c>
@@ -41176,37 +41164,37 @@
       <c r="BI6" s="128" t="s">
         <v>3178</v>
       </c>
-      <c r="BK6" s="172" t="s">
+      <c r="BK6" s="165" t="s">
         <v>3179</v>
       </c>
-      <c r="BL6" s="173"/>
-      <c r="BM6" s="173"/>
-      <c r="BN6" s="173"/>
-      <c r="BO6" s="174"/>
-      <c r="BR6" s="172" t="str" cm="1">
+      <c r="BL6" s="166"/>
+      <c r="BM6" s="166"/>
+      <c r="BN6" s="166"/>
+      <c r="BO6" s="167"/>
+      <c r="BR6" s="165" t="str" cm="1">
         <f t="array" ref="BR6">INDEX(T,4,lang)</f>
         <v>Round of 16</v>
       </c>
-      <c r="BS6" s="173"/>
-      <c r="BT6" s="173"/>
-      <c r="BU6" s="173"/>
-      <c r="BV6" s="174"/>
-      <c r="BY6" s="172" t="str" cm="1">
+      <c r="BS6" s="166"/>
+      <c r="BT6" s="166"/>
+      <c r="BU6" s="166"/>
+      <c r="BV6" s="167"/>
+      <c r="BY6" s="165" t="str" cm="1">
         <f t="array" ref="BY6">INDEX(T,5,lang)</f>
         <v>Quarterfinals</v>
       </c>
-      <c r="BZ6" s="173"/>
-      <c r="CA6" s="173"/>
-      <c r="CB6" s="173"/>
-      <c r="CC6" s="174"/>
-      <c r="CF6" s="172" t="str" cm="1">
+      <c r="BZ6" s="166"/>
+      <c r="CA6" s="166"/>
+      <c r="CB6" s="166"/>
+      <c r="CC6" s="167"/>
+      <c r="CF6" s="165" t="str" cm="1">
         <f t="array" ref="CF6">INDEX(T,6,lang)</f>
         <v>Semi-Finals</v>
       </c>
-      <c r="CG6" s="173"/>
-      <c r="CH6" s="173"/>
-      <c r="CI6" s="173"/>
-      <c r="CJ6" s="174"/>
+      <c r="CG6" s="166"/>
+      <c r="CH6" s="166"/>
+      <c r="CI6" s="166"/>
+      <c r="CJ6" s="167"/>
     </row>
     <row r="7" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="11">
@@ -41228,8 +41216,12 @@
         <f>AE8</f>
         <v>Mexico</v>
       </c>
-      <c r="F7" s="14"/>
-      <c r="G7" s="15"/>
+      <c r="F7" s="14">
+        <v>2</v>
+      </c>
+      <c r="G7" s="15">
+        <v>0</v>
+      </c>
       <c r="H7" s="79" t="str">
         <f>AE9</f>
         <v>South Africa</v>
@@ -41240,11 +41232,11 @@
       </c>
       <c r="S7" s="127" t="str">
         <f t="shared" ref="S7:S46" si="1">IF(OR(F7="",G7=""),"",IF(F7&gt;G7,E7&amp;"_win",IF(F7&lt;G7,E7&amp;"_lose",E7&amp;"_draw")))</f>
-        <v/>
+        <v>Mexico_win</v>
       </c>
       <c r="T7" s="127" t="str">
         <f t="shared" ref="T7:T46" si="2">IF(S7="","",IF(F7&lt;G7,H7&amp;"_win",IF(F7&gt;G7,H7&amp;"_lose",H7&amp;"_draw")))</f>
-        <v/>
+        <v>South Africa_lose</v>
       </c>
       <c r="U7" s="123">
         <f>IF(S7="",0,IF(VLOOKUP(E7,$AE$8:$AN$77,10,FALSE)=VLOOKUP(H7,$AE$8:$AN$77,10,FALSE),1,0))</f>
@@ -41274,31 +41266,31 @@
         <f t="shared" ref="AA7:AA38" si="5">IF(OR(E7=my_team,H7=my_team),1,IF(INT(MATCH(E7,$AE$8:$AE$78,0)/6)=$AA$6,1,0))</f>
         <v>0</v>
       </c>
-      <c r="AB7" s="123" t="str">
+      <c r="AB7" s="123">
         <f t="shared" ref="AB7:AB46" si="6">IF(OR(F7="",G7=""),"",IF(F7&gt;G7,1,IF(F7&lt;G7,-1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AY7" s="126"/>
-      <c r="BK7" s="175"/>
-      <c r="BL7" s="176"/>
-      <c r="BM7" s="176"/>
-      <c r="BN7" s="176"/>
-      <c r="BO7" s="177"/>
-      <c r="BR7" s="175"/>
-      <c r="BS7" s="176"/>
-      <c r="BT7" s="176"/>
-      <c r="BU7" s="176"/>
-      <c r="BV7" s="177"/>
-      <c r="BY7" s="175"/>
-      <c r="BZ7" s="176"/>
-      <c r="CA7" s="176"/>
-      <c r="CB7" s="176"/>
-      <c r="CC7" s="177"/>
-      <c r="CF7" s="175"/>
-      <c r="CG7" s="176"/>
-      <c r="CH7" s="176"/>
-      <c r="CI7" s="176"/>
-      <c r="CJ7" s="177"/>
+      <c r="BK7" s="168"/>
+      <c r="BL7" s="169"/>
+      <c r="BM7" s="169"/>
+      <c r="BN7" s="169"/>
+      <c r="BO7" s="170"/>
+      <c r="BR7" s="168"/>
+      <c r="BS7" s="169"/>
+      <c r="BT7" s="169"/>
+      <c r="BU7" s="169"/>
+      <c r="BV7" s="170"/>
+      <c r="BY7" s="168"/>
+      <c r="BZ7" s="169"/>
+      <c r="CA7" s="169"/>
+      <c r="CB7" s="169"/>
+      <c r="CC7" s="170"/>
+      <c r="CF7" s="168"/>
+      <c r="CG7" s="169"/>
+      <c r="CH7" s="169"/>
+      <c r="CI7" s="169"/>
+      <c r="CJ7" s="170"/>
     </row>
     <row r="8" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A8" s="16">
@@ -41320,8 +41312,12 @@
         <f>AE10</f>
         <v>Korea Republic</v>
       </c>
-      <c r="F8" s="19"/>
-      <c r="G8" s="20"/>
+      <c r="F8" s="19">
+        <v>2</v>
+      </c>
+      <c r="G8" s="20">
+        <v>1</v>
+      </c>
       <c r="H8" s="80" t="str">
         <f>AE11</f>
         <v>Czech Republic</v>
@@ -41360,11 +41356,11 @@
       </c>
       <c r="S8" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Korea Republic_win</v>
       </c>
       <c r="T8" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Czech Republic_lose</v>
       </c>
       <c r="U8" s="123">
         <f t="shared" ref="U8:U71" si="8">IF(S8="",0,IF(VLOOKUP(E8,$AE$8:$AN$77,10,FALSE)=VLOOKUP(H8,$AE$8:$AN$77,10,FALSE),1,0))</f>
@@ -41394,9 +41390,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB8" s="123" t="str">
+      <c r="AB8" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD8" s="123">
         <f>COUNTIF(AR8:AR11,CONCATENATE("&gt;=",AR8))</f>
@@ -41408,7 +41404,7 @@
       </c>
       <c r="AF8" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE8 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG8" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE8 &amp; "_draw")</f>
@@ -41420,7 +41416,7 @@
       </c>
       <c r="AI8" s="123">
         <f>SUMIF($E$7:$E$78,$AE8,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE8,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ8" s="123">
         <f>SUMIF($E$7:$E$78,$AE8,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE8,$F$7:$F$78)</f>
@@ -41428,23 +41424,23 @@
       </c>
       <c r="AL8" s="123">
         <f>AI8-AJ8</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM8" s="123">
         <f>AL8-AL12</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN8" s="123">
         <f>AF8*3+AG8</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO8" s="123">
         <f>AN8/AN12*10+BA8</f>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AP8" s="123">
         <f>AO8*10000000+BI8*100+AM8/AM12*10+AI8/AI12*1++IF(AQ8=0,ROW(),AQ8)/2000000</f>
-        <v>8.4051500000000001E-4</v>
+        <v>75000008.667507187</v>
       </c>
       <c r="AQ8" s="126">
         <f>VLOOKUP(AE8,db_fifarank,2,FALSE)</f>
@@ -41452,7 +41448,7 @@
       </c>
       <c r="AR8" s="125">
         <f>AP8/AP12</f>
-        <v>8.3980912783092126E-4</v>
+        <v>0.99999998666666834</v>
       </c>
       <c r="AS8" s="125" t="str">
         <f>IF(SUM(AF8:AH11)=12,J9,"1A")</f>
@@ -41575,11 +41571,11 @@
       </c>
       <c r="K9" s="31">
         <f>L9+M9+N9</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="31">
         <f>VLOOKUP(1,AD8:AN11,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="31">
         <f>VLOOKUP(1,AD8:AN11,4,FALSE)</f>
@@ -41591,11 +41587,11 @@
       </c>
       <c r="O9" s="31" t="str">
         <f>VLOOKUP(1,AD8:AN11,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD8:AN11,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>2 - 0</v>
       </c>
       <c r="P9" s="32">
         <f>L9*3+M9</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R9" s="123">
         <f>DATE(2026,6,12)+TIME(8,0,0)+gmt_delta</f>
@@ -41659,7 +41655,7 @@
       </c>
       <c r="AH9" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE9 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI9" s="123">
         <f>SUMIF($E$7:$E$78,$AE9,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE9,$G$7:$G$78)</f>
@@ -41667,11 +41663,11 @@
       </c>
       <c r="AJ9" s="123">
         <f>SUMIF($E$7:$E$78,$AE9,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE9,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL9" s="123">
         <f>AI9-AJ9</f>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AM9" s="123">
         <f>AL9-AL12</f>
@@ -41695,7 +41691,7 @@
       </c>
       <c r="AR9" s="125">
         <f>AP9/AP12</f>
-        <v>7.1426464984783314E-4</v>
+        <v>9.5315321047179319E-12</v>
       </c>
       <c r="AS9" s="125" t="str">
         <f>IF(SUM(AF8:AH11)=12,J10,"2A")</f>
@@ -41836,11 +41832,11 @@
       </c>
       <c r="K10" s="23">
         <f>L10+M10+N10</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="23">
         <f>VLOOKUP(2,AD8:AN11,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="23">
         <f>VLOOKUP(2,AD8:AN11,4,FALSE)</f>
@@ -41852,11 +41848,11 @@
       </c>
       <c r="O10" s="23" t="str">
         <f>VLOOKUP(2,AD8:AN11,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD8:AN11,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>2 - 1</v>
       </c>
       <c r="P10" s="34">
         <f>L10*3+M10</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R10" s="123">
         <f>DATE(2026,6,12)+TIME(14,0,0)+gmt_delta</f>
@@ -41912,7 +41908,7 @@
       </c>
       <c r="AF10" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE10 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG10" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE10 &amp; "_draw")</f>
@@ -41924,31 +41920,31 @@
       </c>
       <c r="AI10" s="123">
         <f>SUMIF($E$7:$E$78,$AE10,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE10,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ10" s="123">
         <f>SUMIF($E$7:$E$78,$AE10,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE10,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL10" s="123">
         <f>AI10-AJ10</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM10" s="123">
         <f>AL10-AL12</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN10" s="123">
         <f>AF10*3+AG10</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO10" s="123">
         <f>AN10/AN12*10+BA10</f>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AP10" s="123">
         <f>AO10*10000000+BI10*100+AM10/AM12*10+AI10/AI12*1++IF(AQ10=0,ROW(),AQ10)/2000000</f>
-        <v>7.9432999999999999E-4</v>
+        <v>75000006.667461008</v>
       </c>
       <c r="AQ10" s="126">
         <f>VLOOKUP(AE10,db_fifarank,2,FALSE)</f>
@@ -41956,7 +41952,7 @@
       </c>
       <c r="AR10" s="125">
         <f>AP10/AP12</f>
-        <v>7.9366291441549015E-4</v>
+        <v>0.9999999599993894</v>
       </c>
       <c r="AT10" s="126" cm="1">
         <f t="array" ref="AT10">SUMPRODUCT(($S$7:$S$78=AE10&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE10&amp;"_win")*($U$7:$U$78))</f>
@@ -42022,7 +42018,7 @@
         <f>BH10/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK10" s="169">
+      <c r="BK10" s="163">
         <v>74</v>
       </c>
       <c r="BL10" s="24" t="str">
@@ -42095,7 +42091,7 @@
       </c>
       <c r="K11" s="23">
         <f>L11+M11+N11</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="23">
         <f>VLOOKUP(3,AD8:AN11,3,FALSE)</f>
@@ -42107,11 +42103,11 @@
       </c>
       <c r="N11" s="23">
         <f>VLOOKUP(3,AD8:AN11,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" s="23" t="str">
         <f>VLOOKUP(3,AD8:AN11,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD8:AN11,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 2</v>
       </c>
       <c r="P11" s="34">
         <f>L11*3+M11</f>
@@ -42179,23 +42175,23 @@
       </c>
       <c r="AH11" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE11 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI11" s="123">
         <f>SUMIF($E$7:$E$78,$AE11,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE11,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ11" s="123">
         <f>SUMIF($E$7:$E$78,$AE11,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE11,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL11" s="123">
         <f>AI11-AJ11</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM11" s="123">
         <f>AL11-AL12</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN11" s="123">
         <f>AF11*3+AG11</f>
@@ -42207,7 +42203,7 @@
       </c>
       <c r="AP11" s="123">
         <f>AO11*10000000+BI11*100+AM11/AM12*10+AI11/AI12*1++IF(AQ11=0,ROW(),AQ11)/2000000</f>
-        <v>7.5069000000000004E-4</v>
+        <v>2.3340840233333333</v>
       </c>
       <c r="AQ11" s="126">
         <f>VLOOKUP(AE11,db_fifarank,2,FALSE)</f>
@@ -42215,7 +42211,7 @@
       </c>
       <c r="AR11" s="125">
         <f>AP11/AP12</f>
-        <v>7.5005956368582867E-4</v>
+        <v>3.1121116299596237E-8</v>
       </c>
       <c r="AT11" s="126" cm="1">
         <f t="array" ref="AT11">SUMPRODUCT(($S$7:$S$78=AE11&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE11&amp;"_win")*($U$7:$U$78))</f>
@@ -42281,7 +42277,7 @@
         <f>BH11/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK11" s="170"/>
+      <c r="BK11" s="164"/>
       <c r="BL11" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!G3,AK80:AS91,9,FALSE),"3rd Group A/B/C/D/F")</f>
         <v>3rd Group A/B/C/D/F</v>
@@ -42358,7 +42354,7 @@
       </c>
       <c r="K12" s="36">
         <f>L12+M12+N12</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="36">
         <f>VLOOKUP(4,AD8:AN11,3,FALSE)</f>
@@ -42370,11 +42366,11 @@
       </c>
       <c r="N12" s="36">
         <f>VLOOKUP(4,AD8:AN11,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" s="36" t="str">
         <f>VLOOKUP(4,AD8:AN11,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD8:AN11,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>0 - 2</v>
       </c>
       <c r="P12" s="37">
         <f>L12*3+M12</f>
@@ -42426,7 +42422,7 @@
       </c>
       <c r="AF12" s="123">
         <f t="shared" ref="AF12:AH12" si="12">MAX(AF8:AF11)-MIN(AF8:AF11)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG12" s="123">
         <f t="shared" si="12"/>
@@ -42434,31 +42430,31 @@
       </c>
       <c r="AH12" s="123">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI12" s="123">
         <f>MAX(AI8:AI11)+1</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AL12" s="123">
         <f>MIN(AL8:AL11)</f>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AM12" s="123">
         <f>MAX(AM8:AM11)+1</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AN12" s="123">
         <f>MAX(AN8:AN11)+1</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AO12" s="123">
         <f>MAX(AO8:AO11)+1</f>
-        <v>1</v>
+        <v>8.5</v>
       </c>
       <c r="AP12" s="123">
         <f>MAX(AP8:AP11)+1</f>
-        <v>1.0008405149999999</v>
+        <v>75000009.667507187</v>
       </c>
       <c r="AT12" s="126">
         <f>MAX(AT8:AT11)-MIN(AT8:AT11)+1</f>
@@ -42515,7 +42511,7 @@
       <c r="BO12" s="21"/>
       <c r="BP12" s="114"/>
       <c r="BQ12" s="112"/>
-      <c r="BR12" s="169">
+      <c r="BR12" s="163">
         <v>89</v>
       </c>
       <c r="BS12" s="24" t="str">
@@ -42632,7 +42628,7 @@
         <v>46203.875</v>
       </c>
       <c r="BQ13" s="115"/>
-      <c r="BR13" s="170"/>
+      <c r="BR13" s="164"/>
       <c r="BS13" s="26" t="str">
         <f>IF(BP14&gt;BP15,BL14,IF(BP14&lt;BP15,BL15,""))</f>
         <v/>
@@ -42886,7 +42882,7 @@
         <f>BH14/BH18</f>
         <v>0</v>
       </c>
-      <c r="BK14" s="169">
+      <c r="BK14" s="163">
         <v>77</v>
       </c>
       <c r="BL14" s="24" t="str">
@@ -43149,7 +43145,7 @@
         <f>BH15/BH18</f>
         <v>0</v>
       </c>
-      <c r="BK15" s="170"/>
+      <c r="BK15" s="164"/>
       <c r="BL15" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!I3,AK80:AS91,9,FALSE),"3rd Group C/D/F/G/H")</f>
         <v>3rd Group C/D/F/G/H</v>
@@ -43419,7 +43415,7 @@
       <c r="BV16" s="21"/>
       <c r="BW16" s="114"/>
       <c r="BX16" s="112"/>
-      <c r="BY16" s="169">
+      <c r="BY16" s="163">
         <v>97</v>
       </c>
       <c r="BZ16" s="24" t="str">
@@ -43677,7 +43673,7 @@
       <c r="BV17" s="21"/>
       <c r="BW17" s="114"/>
       <c r="BX17" s="115"/>
-      <c r="BY17" s="170"/>
+      <c r="BY17" s="164"/>
       <c r="BZ17" s="26" t="str">
         <f>IF(BW20&gt;BW21,BS20,IF(BW20&lt;BW21,BS21,""))</f>
         <v/>
@@ -43877,7 +43873,7 @@
         <f>MAX(BH14:BH17)+1</f>
         <v>1</v>
       </c>
-      <c r="BK18" s="169">
+      <c r="BK18" s="163">
         <v>73</v>
       </c>
       <c r="BL18" s="24" t="str">
@@ -43981,7 +43977,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK19" s="170"/>
+      <c r="BK19" s="164"/>
       <c r="BL19" s="26" t="str">
         <f>AS15</f>
         <v>2B</v>
@@ -44255,7 +44251,7 @@
       <c r="BO20" s="21"/>
       <c r="BP20" s="114"/>
       <c r="BQ20" s="112"/>
-      <c r="BR20" s="169">
+      <c r="BR20" s="163">
         <v>90</v>
       </c>
       <c r="BS20" s="24" t="str">
@@ -44524,7 +44520,7 @@
         <v>46203.041666666672</v>
       </c>
       <c r="BQ21" s="115"/>
-      <c r="BR21" s="170"/>
+      <c r="BR21" s="164"/>
       <c r="BS21" s="26" t="str">
         <f>IF(BP22&gt;BP23,BL22,IF(BP22&lt;BP23,BL23,""))</f>
         <v/>
@@ -44774,7 +44770,7 @@
         <f>BH22/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK22" s="169">
+      <c r="BK22" s="163">
         <v>75</v>
       </c>
       <c r="BL22" s="24" t="str">
@@ -45034,7 +45030,7 @@
         <f>BH23/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK23" s="170"/>
+      <c r="BK23" s="164"/>
       <c r="BL23" s="26" t="str">
         <f>AS21</f>
         <v>2C</v>
@@ -45061,7 +45057,7 @@
       <c r="CC23" s="21"/>
       <c r="CD23" s="114"/>
       <c r="CE23" s="112"/>
-      <c r="CF23" s="169">
+      <c r="CF23" s="163">
         <v>101</v>
       </c>
       <c r="CG23" s="24" t="str">
@@ -45278,7 +45274,7 @@
       <c r="CC24" s="21"/>
       <c r="CD24" s="114"/>
       <c r="CE24" s="115"/>
-      <c r="CF24" s="170"/>
+      <c r="CF24" s="164"/>
       <c r="CG24" s="26" t="str">
         <f>IF(CD32&gt;CD33,BZ32,IF(CD32&lt;CD33,BZ33,""))</f>
         <v/>
@@ -45623,7 +45619,7 @@
         <f>BH26/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK26" s="169">
+      <c r="BK26" s="163">
         <v>83</v>
       </c>
       <c r="BL26" s="24" t="str">
@@ -45887,7 +45883,7 @@
         <f>BH27/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK27" s="170"/>
+      <c r="BK27" s="164"/>
       <c r="BL27" s="26" t="str">
         <f>AS75</f>
         <v>2L</v>
@@ -46158,7 +46154,7 @@
       <c r="BO28" s="21"/>
       <c r="BP28" s="114"/>
       <c r="BQ28" s="112"/>
-      <c r="BR28" s="169">
+      <c r="BR28" s="163">
         <v>93</v>
       </c>
       <c r="BS28" s="24" t="str">
@@ -46419,7 +46415,7 @@
         <v>46205.791666666672</v>
       </c>
       <c r="BQ29" s="115"/>
-      <c r="BR29" s="170"/>
+      <c r="BR29" s="164"/>
       <c r="BS29" s="26" t="str">
         <f>IF(BP30&gt;BP31,BL30,IF(BP30&lt;BP31,BL31,""))</f>
         <v/>
@@ -46629,7 +46625,7 @@
         <f>MAX(BH26:BH29)+1</f>
         <v>1</v>
       </c>
-      <c r="BK30" s="169">
+      <c r="BK30" s="163">
         <v>84</v>
       </c>
       <c r="BL30" s="24" t="str">
@@ -46736,7 +46732,7 @@
         <f>IF(OR(F31="",G31=""),"",IF(F31&gt;G31,1,IF(F31&lt;G31,-1,0)))</f>
         <v/>
       </c>
-      <c r="BK31" s="170"/>
+      <c r="BK31" s="164"/>
       <c r="BL31" s="26" t="str">
         <f>AS63</f>
         <v>2J</v>
@@ -47008,7 +47004,7 @@
       <c r="BV32" s="21"/>
       <c r="BW32" s="114"/>
       <c r="BX32" s="112"/>
-      <c r="BY32" s="169">
+      <c r="BY32" s="163">
         <v>98</v>
       </c>
       <c r="BZ32" s="24" t="str">
@@ -47268,7 +47264,7 @@
       <c r="BV33" s="21"/>
       <c r="BW33" s="114"/>
       <c r="BX33" s="115"/>
-      <c r="BY33" s="170"/>
+      <c r="BY33" s="164"/>
       <c r="BZ33" s="26" t="str">
         <f>IF(BW36&gt;BW37,BS36,IF(BW36&lt;BW37,BS37,""))</f>
         <v/>
@@ -47283,14 +47279,14 @@
       <c r="CE33" s="112"/>
       <c r="CK33" s="114"/>
       <c r="CL33" s="112"/>
-      <c r="CM33" s="172" t="str" cm="1">
+      <c r="CM33" s="165" t="str" cm="1">
         <f t="array" ref="CM33">INDEX(T,8,lang)</f>
         <v>Final</v>
       </c>
-      <c r="CN33" s="173"/>
-      <c r="CO33" s="173"/>
-      <c r="CP33" s="173"/>
-      <c r="CQ33" s="174"/>
+      <c r="CN33" s="166"/>
+      <c r="CO33" s="166"/>
+      <c r="CP33" s="166"/>
+      <c r="CQ33" s="167"/>
     </row>
     <row r="34" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A34" s="16">
@@ -47510,7 +47506,7 @@
         <f>BH34/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK34" s="169">
+      <c r="BK34" s="163">
         <v>81</v>
       </c>
       <c r="BL34" s="24" t="str">
@@ -47541,11 +47537,11 @@
       <c r="CE34" s="112"/>
       <c r="CK34" s="114"/>
       <c r="CL34" s="112"/>
-      <c r="CM34" s="175"/>
-      <c r="CN34" s="176"/>
-      <c r="CO34" s="176"/>
-      <c r="CP34" s="176"/>
-      <c r="CQ34" s="177"/>
+      <c r="CM34" s="168"/>
+      <c r="CN34" s="169"/>
+      <c r="CO34" s="169"/>
+      <c r="CP34" s="169"/>
+      <c r="CQ34" s="170"/>
     </row>
     <row r="35" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A35" s="16">
@@ -47765,7 +47761,7 @@
         <f>BH35/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK35" s="170"/>
+      <c r="BK35" s="164"/>
       <c r="BL35" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!F3,AK80:AS91,9,FALSE),"3rd Group B/E/F/I/J")</f>
         <v>3rd Group B/E/F/I/J</v>
@@ -47990,7 +47986,7 @@
       <c r="BO36" s="21"/>
       <c r="BP36" s="114"/>
       <c r="BQ36" s="112"/>
-      <c r="BR36" s="169">
+      <c r="BR36" s="163">
         <v>94</v>
       </c>
       <c r="BS36" s="24" t="str">
@@ -48110,7 +48106,7 @@
         <v>46204.833333333336</v>
       </c>
       <c r="BQ37" s="115"/>
-      <c r="BR37" s="170"/>
+      <c r="BR37" s="164"/>
       <c r="BS37" s="26" t="str">
         <f>IF(BP38&gt;BP39,BL38,IF(BP38&lt;BP39,BL39,""))</f>
         <v/>
@@ -48137,7 +48133,7 @@
       <c r="CJ37" s="21"/>
       <c r="CK37" s="114"/>
       <c r="CL37" s="112"/>
-      <c r="CM37" s="169">
+      <c r="CM37" s="163">
         <v>104</v>
       </c>
       <c r="CN37" s="24" t="str">
@@ -48374,7 +48370,7 @@
         <f>BH38/BH42</f>
         <v>0</v>
       </c>
-      <c r="BK38" s="169">
+      <c r="BK38" s="163">
         <v>82</v>
       </c>
       <c r="BL38" s="24" t="str">
@@ -48404,7 +48400,7 @@
       <c r="CI38" s="21"/>
       <c r="CJ38" s="21"/>
       <c r="CL38" s="115"/>
-      <c r="CM38" s="170"/>
+      <c r="CM38" s="164"/>
       <c r="CN38" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG55,IF(CK55&lt;CK56,CG56,""))</f>
         <v/>
@@ -48639,7 +48635,7 @@
         <f>BH39/BH42</f>
         <v>0</v>
       </c>
-      <c r="BK39" s="170"/>
+      <c r="BK39" s="164"/>
       <c r="BL39" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!H3,AK80:AS91,9,FALSE),"3rd Group A/E/H/I/J")</f>
         <v>3rd Group A/E/H/I/J</v>
@@ -49315,7 +49311,7 @@
         <f>MAX(BH38:BH41)+1</f>
         <v>1</v>
       </c>
-      <c r="BK42" s="169">
+      <c r="BK42" s="163">
         <v>76</v>
       </c>
       <c r="BL42" s="24" t="str">
@@ -49408,7 +49404,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK43" s="170"/>
+      <c r="BK43" s="164"/>
       <c r="BL43" s="26" t="str">
         <f>AS39</f>
         <v>2F</v>
@@ -49664,7 +49660,7 @@
       <c r="BO44" s="21"/>
       <c r="BP44" s="114"/>
       <c r="BQ44" s="112"/>
-      <c r="BR44" s="169">
+      <c r="BR44" s="163">
         <v>91</v>
       </c>
       <c r="BS44" s="24" t="str">
@@ -49679,14 +49675,14 @@
         <v/>
       </c>
       <c r="CK44" s="114"/>
-      <c r="CM44" s="172" t="str" cm="1">
+      <c r="CM44" s="165" t="str" cm="1">
         <f t="array" ref="CM44">INDEX(T,7,lang)</f>
         <v>Third-Place Play-Off</v>
       </c>
-      <c r="CN44" s="173"/>
-      <c r="CO44" s="173"/>
-      <c r="CP44" s="173"/>
-      <c r="CQ44" s="174"/>
+      <c r="CN44" s="166"/>
+      <c r="CO44" s="166"/>
+      <c r="CP44" s="166"/>
+      <c r="CQ44" s="167"/>
     </row>
     <row r="45" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="16">
@@ -49923,7 +49919,7 @@
         <v>46203.708333333336</v>
       </c>
       <c r="BQ45" s="115"/>
-      <c r="BR45" s="170"/>
+      <c r="BR45" s="164"/>
       <c r="BS45" s="26" t="str">
         <f>IF(BP46&gt;BP47,BL46,IF(BP46&lt;BP47,BL47,""))</f>
         <v/>
@@ -49936,11 +49932,11 @@
         <v/>
       </c>
       <c r="CK45" s="114"/>
-      <c r="CM45" s="175"/>
-      <c r="CN45" s="176"/>
-      <c r="CO45" s="176"/>
-      <c r="CP45" s="176"/>
-      <c r="CQ45" s="177"/>
+      <c r="CM45" s="168"/>
+      <c r="CN45" s="169"/>
+      <c r="CO45" s="169"/>
+      <c r="CP45" s="169"/>
+      <c r="CQ45" s="170"/>
     </row>
     <row r="46" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A46" s="16">
@@ -50160,7 +50156,7 @@
         <f>BH46/BH48</f>
         <v>0</v>
       </c>
-      <c r="BK46" s="169">
+      <c r="BK46" s="163">
         <v>78</v>
       </c>
       <c r="BL46" s="24" t="str">
@@ -50402,7 +50398,7 @@
         <f>BH47/BH48</f>
         <v>0</v>
       </c>
-      <c r="BK47" s="170"/>
+      <c r="BK47" s="164"/>
       <c r="BL47" s="26" t="str">
         <f>AS57</f>
         <v>2I</v>
@@ -50645,7 +50641,7 @@
       <c r="BV48" s="21"/>
       <c r="BW48" s="114"/>
       <c r="BX48" s="112"/>
-      <c r="BY48" s="169">
+      <c r="BY48" s="163">
         <v>99</v>
       </c>
       <c r="BZ48" s="24" t="str">
@@ -50661,7 +50657,7 @@
       </c>
       <c r="CK48" s="114"/>
       <c r="CL48" s="112"/>
-      <c r="CM48" s="169">
+      <c r="CM48" s="163">
         <v>103</v>
       </c>
       <c r="CN48" s="24" t="str">
@@ -50766,7 +50762,7 @@
       <c r="BV49" s="21"/>
       <c r="BW49" s="114"/>
       <c r="BX49" s="115"/>
-      <c r="BY49" s="170"/>
+      <c r="BY49" s="164"/>
       <c r="BZ49" s="26" t="str">
         <f>IF(BW52&gt;BW53,BS52,IF(BW52&lt;BW53,BS53,""))</f>
         <v/>
@@ -50780,7 +50776,7 @@
       </c>
       <c r="CK49" s="114"/>
       <c r="CL49" s="115"/>
-      <c r="CM49" s="170"/>
+      <c r="CM49" s="164"/>
       <c r="CN49" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG56,IF(CK55&lt;CK56,CG55,""))</f>
         <v/>
@@ -51015,7 +51011,7 @@
         <f>BH50/BH54</f>
         <v>0</v>
       </c>
-      <c r="BK50" s="169">
+      <c r="BK50" s="163">
         <v>79</v>
       </c>
       <c r="BL50" s="24" t="str">
@@ -51268,7 +51264,7 @@
         <f>BH51/BH54</f>
         <v>0</v>
       </c>
-      <c r="BK51" s="170"/>
+      <c r="BK51" s="164"/>
       <c r="BL51" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!D3,AK80:AS91,9,FALSE),"3rd Group C/E/F/H/I")</f>
         <v>3rd Group C/E/F/H/I</v>
@@ -51528,7 +51524,7 @@
       <c r="BO52" s="21"/>
       <c r="BP52" s="114"/>
       <c r="BQ52" s="112"/>
-      <c r="BR52" s="169">
+      <c r="BR52" s="163">
         <v>92</v>
       </c>
       <c r="BS52" s="24" t="str">
@@ -51783,7 +51779,7 @@
         <v>46204.666666666672</v>
       </c>
       <c r="BQ53" s="115"/>
-      <c r="BR53" s="170"/>
+      <c r="BR53" s="164"/>
       <c r="BS53" s="26" t="str">
         <f>IF(BP54&gt;BP55,BL54,IF(BP54&lt;BP55,BL55,""))</f>
         <v/>
@@ -51987,7 +51983,7 @@
         <f>MAX(BH50:BH53)+1</f>
         <v>1</v>
       </c>
-      <c r="BK54" s="169">
+      <c r="BK54" s="163">
         <v>80</v>
       </c>
       <c r="BL54" s="24" t="str">
@@ -52108,7 +52104,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK55" s="170"/>
+      <c r="BK55" s="164"/>
       <c r="BL55" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!K3,AK80:AS91,9,FALSE),"3rd Group E/H/I/J/K")</f>
         <v>3rd Group E/H/I/J/K</v>
@@ -52135,7 +52131,7 @@
       <c r="CC55" s="21"/>
       <c r="CD55" s="114"/>
       <c r="CE55" s="112"/>
-      <c r="CF55" s="169">
+      <c r="CF55" s="163">
         <v>102</v>
       </c>
       <c r="CG55" s="24" t="str">
@@ -52394,7 +52390,7 @@
       <c r="CC56" s="21"/>
       <c r="CD56" s="114"/>
       <c r="CE56" s="115"/>
-      <c r="CF56" s="170"/>
+      <c r="CF56" s="164"/>
       <c r="CG56" s="26" t="str">
         <f>IF(CD64&gt;CD65,BZ64,IF(CD64&lt;CD65,BZ65,""))</f>
         <v/>
@@ -52877,7 +52873,7 @@
         <f>BH58/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK58" s="169">
+      <c r="BK58" s="163">
         <v>86</v>
       </c>
       <c r="BL58" s="24" t="str">
@@ -53125,7 +53121,7 @@
         <f>BH59/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK59" s="170"/>
+      <c r="BK59" s="164"/>
       <c r="BL59" s="26" t="str">
         <f>AS51</f>
         <v>2H</v>
@@ -53348,7 +53344,7 @@
       <c r="BO60" s="21"/>
       <c r="BP60" s="114"/>
       <c r="BQ60" s="112"/>
-      <c r="BR60" s="169">
+      <c r="BR60" s="163">
         <v>95</v>
       </c>
       <c r="BS60" s="24" t="str">
@@ -53461,7 +53457,7 @@
         <v>46206.75</v>
       </c>
       <c r="BQ61" s="115"/>
-      <c r="BR61" s="170"/>
+      <c r="BR61" s="164"/>
       <c r="BS61" s="26" t="str">
         <f>IF(BP62&gt;BP63,BL62,IF(BP62&lt;BP63,BL63,""))</f>
         <v/>
@@ -53704,7 +53700,7 @@
         <f>BH62/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK62" s="169">
+      <c r="BK62" s="163">
         <v>88</v>
       </c>
       <c r="BL62" s="24" t="str">
@@ -53956,7 +53952,7 @@
         <f>BH63/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK63" s="170"/>
+      <c r="BK63" s="164"/>
       <c r="BL63" s="26" t="str">
         <f>AS45</f>
         <v>2G</v>
@@ -54222,7 +54218,7 @@
       <c r="BV64" s="21"/>
       <c r="BW64" s="114"/>
       <c r="BX64" s="112"/>
-      <c r="BY64" s="169">
+      <c r="BY64" s="163">
         <v>100</v>
       </c>
       <c r="BZ64" s="24" t="str">
@@ -54476,7 +54472,7 @@
       <c r="BV65" s="21"/>
       <c r="BW65" s="114"/>
       <c r="BX65" s="115"/>
-      <c r="BY65" s="170"/>
+      <c r="BY65" s="164"/>
       <c r="BZ65" s="26" t="str">
         <f>IF(BW68&gt;BW69,BS68,IF(BW68&lt;BW69,BS69,""))</f>
         <v/>
@@ -54672,7 +54668,7 @@
         <f>MAX(BH62:BH65)+1</f>
         <v>1</v>
       </c>
-      <c r="BK66" s="169">
+      <c r="BK66" s="163">
         <v>85</v>
       </c>
       <c r="BL66" s="24" t="str">
@@ -54772,7 +54768,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK67" s="170"/>
+      <c r="BK67" s="164"/>
       <c r="BL67" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!E3,AK80:AS91,9,FALSE),"3rd Group E/F/G/I/J")</f>
         <v>3rd Group E/F/G/I/J</v>
@@ -55028,7 +55024,7 @@
       <c r="BO68" s="21"/>
       <c r="BP68" s="114"/>
       <c r="BQ68" s="112"/>
-      <c r="BR68" s="169">
+      <c r="BR68" s="163">
         <v>96</v>
       </c>
       <c r="BS68" s="24" t="str">
@@ -55042,25 +55038,25 @@
         <f>IF(OR(BT68="",BT69="",AND(BU68="",BU69&lt;&gt;""),AND(BU69="",BU68&lt;&gt;""),AND(BV68="",BV69&lt;&gt;""),AND(BV69="",BV68&lt;&gt;"")),"",BT68*1000+BU68*10+BV68)</f>
         <v/>
       </c>
-      <c r="CE68" s="171" t="str">
+      <c r="CE68" s="195" t="str">
         <f>INDEX(T,144,lang)</f>
         <v>World Champion 2026</v>
       </c>
-      <c r="CF68" s="171"/>
-      <c r="CG68" s="171"/>
-      <c r="CH68" s="171"/>
-      <c r="CI68" s="171"/>
-      <c r="CJ68" s="171"/>
-      <c r="CK68" s="159" t="str">
+      <c r="CF68" s="195"/>
+      <c r="CG68" s="195"/>
+      <c r="CH68" s="195"/>
+      <c r="CI68" s="195"/>
+      <c r="CJ68" s="195"/>
+      <c r="CK68" s="185" t="str">
         <f>IF(CR37&gt;CR38,CN37,IF(CR37&lt;CR38,CN38,""))</f>
         <v/>
       </c>
-      <c r="CL68" s="159"/>
-      <c r="CM68" s="159"/>
-      <c r="CN68" s="159"/>
-      <c r="CO68" s="159"/>
-      <c r="CP68" s="159"/>
-      <c r="CQ68" s="159"/>
+      <c r="CL68" s="185"/>
+      <c r="CM68" s="185"/>
+      <c r="CN68" s="185"/>
+      <c r="CO68" s="185"/>
+      <c r="CP68" s="185"/>
+      <c r="CQ68" s="185"/>
     </row>
     <row r="69" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A69" s="16">
@@ -55298,7 +55294,7 @@
         <v>46207.0625</v>
       </c>
       <c r="BQ69" s="115"/>
-      <c r="BR69" s="170"/>
+      <c r="BR69" s="164"/>
       <c r="BS69" s="26" t="str">
         <f>IF(BP70&gt;BP71,BL70,IF(BP70&lt;BP71,BL71,""))</f>
         <v/>
@@ -55310,19 +55306,19 @@
         <f>IF(BW68="","",BT69*1000+BU69*10+BV69)</f>
         <v/>
       </c>
-      <c r="CE69" s="171"/>
-      <c r="CF69" s="171"/>
-      <c r="CG69" s="171"/>
-      <c r="CH69" s="171"/>
-      <c r="CI69" s="171"/>
-      <c r="CJ69" s="171"/>
-      <c r="CK69" s="159"/>
-      <c r="CL69" s="159"/>
-      <c r="CM69" s="159"/>
-      <c r="CN69" s="159"/>
-      <c r="CO69" s="159"/>
-      <c r="CP69" s="159"/>
-      <c r="CQ69" s="159"/>
+      <c r="CE69" s="195"/>
+      <c r="CF69" s="195"/>
+      <c r="CG69" s="195"/>
+      <c r="CH69" s="195"/>
+      <c r="CI69" s="195"/>
+      <c r="CJ69" s="195"/>
+      <c r="CK69" s="185"/>
+      <c r="CL69" s="185"/>
+      <c r="CM69" s="185"/>
+      <c r="CN69" s="185"/>
+      <c r="CO69" s="185"/>
+      <c r="CP69" s="185"/>
+      <c r="CQ69" s="185"/>
     </row>
     <row r="70" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A70" s="16">
@@ -55543,7 +55539,7 @@
         <f>BH70/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK70" s="169">
+      <c r="BK70" s="163">
         <v>87</v>
       </c>
       <c r="BL70" s="24" t="str">
@@ -55779,7 +55775,7 @@
         <f>BH71/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK71" s="170"/>
+      <c r="BK71" s="164"/>
       <c r="BL71" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!J3,AK80:AS91,9,FALSE),"3rd Group D/E/I/J/L")</f>
         <v>3rd Group D/E/I/J/L</v>
@@ -57186,7 +57182,7 @@
       </c>
       <c r="AD80" s="123">
         <f>COUNTIF($AP$80:$AP$91,CONCATENATE("&gt;=",AP80))</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE80" s="124" t="str">
         <f>J11</f>
@@ -57202,22 +57198,22 @@
       </c>
       <c r="AH80" s="123">
         <f>VLOOKUP($AE80,$AE$8:$AQ$78,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI80" s="123">
         <f>VLOOKUP($AE80,$AE$8:$AQ$78,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ80" s="123">
         <f>VLOOKUP($AE80,$AE$8:$AQ$78,6,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK80" s="123" t="s">
         <v>3180</v>
       </c>
       <c r="AL80" s="123">
         <f>VLOOKUP($AE80,$AE$8:$AQ$78,8,FALSE)</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM80" s="123">
         <f>AL80-$AL$92</f>
@@ -57229,7 +57225,7 @@
       </c>
       <c r="AP80" s="123">
         <f>AN80/AN92*10000+AM80/AM92*1000+AI80/AI92*100+IF(AQ80=0,ROW(),AQ80)/2000000</f>
-        <v>7.5069000000000004E-4</v>
+        <v>50.000750689999997</v>
       </c>
       <c r="AQ80" s="126">
         <f t="shared" ref="AQ80:AQ91" si="37">VLOOKUP($AE80,$AE$8:$AQ$78,13,FALSE)</f>
@@ -57237,11 +57233,11 @@
       </c>
       <c r="AR80" s="125" t="str">
         <f>IF(AD80&lt;=8,RIGHT(AK80,1),"")</f>
-        <v>A</v>
+        <v/>
       </c>
       <c r="AS80" s="129" t="str">
         <f>IF(AD80&lt;=8,AE80,"")</f>
-        <v>Czech Republic</v>
+        <v/>
       </c>
       <c r="AT80" s="130" t="str">
         <f>"Ⓐ "&amp;AE80</f>
@@ -57288,7 +57284,7 @@
       </c>
       <c r="AD81" s="123">
         <f t="shared" ref="AD81:AD91" si="38">COUNTIF($AP$80:$AP$91,CONCATENATE("&gt;=",AP81))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE81" s="124" t="str">
         <f>J17</f>
@@ -57323,7 +57319,7 @@
       </c>
       <c r="AM81" s="123">
         <f t="shared" ref="AM81:AM91" si="44">AL81-$AL$92</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN81" s="123">
         <f t="shared" ref="AN81:AN90" si="45">VLOOKUP($AE81,$AE$8:$AQ$78,10,FALSE)</f>
@@ -57331,7 +57327,7 @@
       </c>
       <c r="AP81" s="123">
         <f>AN81/AN92*10000+AM81/AM92*1000+AI81/AI92*100+IF(AQ81=0,ROW(),AQ81)/2000000</f>
-        <v>7.2747999999999997E-4</v>
+        <v>500.00072748000002</v>
       </c>
       <c r="AQ81" s="126">
         <f t="shared" si="37"/>
@@ -57339,7 +57335,7 @@
       </c>
       <c r="AR81" s="125" t="str">
         <f>AR80&amp;IF(AD81&lt;=8,RIGHT(AK81,1),"")</f>
-        <v>A</v>
+        <v/>
       </c>
       <c r="AS81" s="129" t="str">
         <f t="shared" ref="AS81:AS91" si="46">IF(AD81&lt;=8,AE81,"")</f>
@@ -57390,7 +57386,7 @@
       </c>
       <c r="AD82" s="123">
         <f t="shared" si="38"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE82" s="124" t="str">
         <f>J23</f>
@@ -57425,7 +57421,7 @@
       </c>
       <c r="AM82" s="123">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN82" s="123">
         <f t="shared" si="45"/>
@@ -57433,7 +57429,7 @@
       </c>
       <c r="AP82" s="123">
         <f>AN82/AN92*10000+AM82/AM92*1000+AI82/AI92*100+IF(AQ82=0,ROW(),AQ82)/2000000</f>
-        <v>7.4917499999999993E-4</v>
+        <v>500.00074917500001</v>
       </c>
       <c r="AQ82" s="126">
         <f t="shared" si="37"/>
@@ -57441,11 +57437,11 @@
       </c>
       <c r="AR82" s="125" t="str">
         <f t="shared" ref="AR82:AR91" si="50">AR81&amp;IF(AD82&lt;=8,RIGHT(AK82,1),"")</f>
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="AS82" s="129" t="str">
         <f t="shared" si="46"/>
-        <v/>
+        <v>Scotland</v>
       </c>
       <c r="AT82" s="130" t="str">
         <f>"Ⓒ "&amp;AE82</f>
@@ -57455,13 +57451,13 @@
     <row r="83" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="73"/>
       <c r="B83" s="73"/>
-      <c r="C83" s="160" t="s">
+      <c r="C83" s="186" t="s">
         <v>3183</v>
       </c>
-      <c r="D83" s="161"/>
-      <c r="E83" s="161"/>
-      <c r="F83" s="161"/>
-      <c r="G83" s="162"/>
+      <c r="D83" s="187"/>
+      <c r="E83" s="187"/>
+      <c r="F83" s="187"/>
+      <c r="G83" s="188"/>
       <c r="H83" s="75"/>
       <c r="I83" s="69"/>
       <c r="J83" s="99" t="str">
@@ -57529,7 +57525,7 @@
       </c>
       <c r="AM83" s="123">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN83" s="123">
         <f t="shared" si="45"/>
@@ -57537,7 +57533,7 @@
       </c>
       <c r="AP83" s="123">
         <f>AN83/AN92*10000+AM83/AM92*1000+AI83/AI92*100+IF(AQ83=0,ROW(),AQ83)/2000000</f>
-        <v>7.9033500000000008E-4</v>
+        <v>500.00079033499998</v>
       </c>
       <c r="AQ83" s="126">
         <f t="shared" si="37"/>
@@ -57545,7 +57541,7 @@
       </c>
       <c r="AR83" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>AD</v>
+        <v>CD</v>
       </c>
       <c r="AS83" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57559,11 +57555,11 @@
     <row r="84" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="73"/>
       <c r="B84" s="73"/>
-      <c r="C84" s="163"/>
-      <c r="D84" s="164"/>
-      <c r="E84" s="164"/>
-      <c r="F84" s="164"/>
-      <c r="G84" s="165"/>
+      <c r="C84" s="189"/>
+      <c r="D84" s="190"/>
+      <c r="E84" s="190"/>
+      <c r="F84" s="190"/>
+      <c r="G84" s="191"/>
       <c r="H84" s="75"/>
       <c r="I84" s="69"/>
       <c r="J84" s="99" t="str">
@@ -57643,7 +57639,7 @@
       </c>
       <c r="AM84" s="123">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN84" s="123">
         <f t="shared" si="45"/>
@@ -57651,7 +57647,7 @@
       </c>
       <c r="AP84" s="123">
         <f>AN84/AN92*10000+AM84/AM92*1000+AI84/AI92*100+IF(AQ84=0,ROW(),AQ84)/2000000</f>
-        <v>7.6648999999999999E-4</v>
+        <v>500.00076648999999</v>
       </c>
       <c r="AQ84" s="126">
         <f t="shared" si="37"/>
@@ -57659,7 +57655,7 @@
       </c>
       <c r="AR84" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ADE</v>
+        <v>CDE</v>
       </c>
       <c r="AS84" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57673,11 +57669,11 @@
     <row r="85" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="73"/>
       <c r="B85" s="73"/>
-      <c r="C85" s="163"/>
-      <c r="D85" s="164"/>
-      <c r="E85" s="164"/>
-      <c r="F85" s="164"/>
-      <c r="G85" s="165"/>
+      <c r="C85" s="189"/>
+      <c r="D85" s="190"/>
+      <c r="E85" s="190"/>
+      <c r="F85" s="190"/>
+      <c r="G85" s="191"/>
       <c r="H85" s="75"/>
       <c r="I85" s="69"/>
       <c r="J85" s="99" t="str">
@@ -57757,7 +57753,7 @@
       </c>
       <c r="AM85" s="123">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN85" s="123">
         <f t="shared" si="45"/>
@@ -57765,7 +57761,7 @@
       </c>
       <c r="AP85" s="123">
         <f>AN85/AN92*10000+AM85/AM92*1000+AI85/AI92*100+IF(AQ85=0,ROW(),AQ85)/2000000</f>
-        <v>7.5738499999999996E-4</v>
+        <v>500.00075738499999</v>
       </c>
       <c r="AQ85" s="126">
         <f t="shared" si="37"/>
@@ -57773,7 +57769,7 @@
       </c>
       <c r="AR85" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ADEF</v>
+        <v>CDEF</v>
       </c>
       <c r="AS85" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57787,11 +57783,11 @@
     <row r="86" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="73"/>
       <c r="B86" s="73"/>
-      <c r="C86" s="163"/>
-      <c r="D86" s="164"/>
-      <c r="E86" s="164"/>
-      <c r="F86" s="164"/>
-      <c r="G86" s="165"/>
+      <c r="C86" s="189"/>
+      <c r="D86" s="190"/>
+      <c r="E86" s="190"/>
+      <c r="F86" s="190"/>
+      <c r="G86" s="191"/>
       <c r="H86" s="75"/>
       <c r="I86" s="69"/>
       <c r="J86" s="99" t="str">
@@ -57871,7 +57867,7 @@
       </c>
       <c r="AM86" s="123">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN86" s="123">
         <f t="shared" si="45"/>
@@ -57879,7 +57875,7 @@
       </c>
       <c r="AP86" s="123">
         <f>AN86/AN92*10000+AM86/AM92*1000+AI86/AI92*100+IF(AQ86=0,ROW(),AQ86)/2000000</f>
-        <v>7.8162000000000001E-4</v>
+        <v>500.00078162</v>
       </c>
       <c r="AQ86" s="126">
         <f t="shared" si="37"/>
@@ -57887,7 +57883,7 @@
       </c>
       <c r="AR86" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ADEFG</v>
+        <v>CDEFG</v>
       </c>
       <c r="AS86" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57901,11 +57897,11 @@
     <row r="87" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="73"/>
       <c r="B87" s="73"/>
-      <c r="C87" s="163"/>
-      <c r="D87" s="164"/>
-      <c r="E87" s="164"/>
-      <c r="F87" s="164"/>
-      <c r="G87" s="165"/>
+      <c r="C87" s="189"/>
+      <c r="D87" s="190"/>
+      <c r="E87" s="190"/>
+      <c r="F87" s="190"/>
+      <c r="G87" s="191"/>
       <c r="H87" s="75"/>
       <c r="I87" s="69"/>
       <c r="J87" s="99" t="str">
@@ -57950,7 +57946,7 @@
       </c>
       <c r="AD87" s="123">
         <f t="shared" si="38"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE87" s="124" t="str">
         <f>J53</f>
@@ -57985,7 +57981,7 @@
       </c>
       <c r="AM87" s="123">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN87" s="123">
         <f t="shared" si="45"/>
@@ -57993,7 +57989,7 @@
       </c>
       <c r="AP87" s="123">
         <f>AN87/AN92*10000+AM87/AM92*1000+AI87/AI92*100+IF(AQ87=0,ROW(),AQ87)/2000000</f>
-        <v>7.10715E-4</v>
+        <v>500.00071071500003</v>
       </c>
       <c r="AQ87" s="126">
         <f t="shared" si="37"/>
@@ -58001,7 +57997,7 @@
       </c>
       <c r="AR87" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ADEFG</v>
+        <v>CDEFG</v>
       </c>
       <c r="AS87" s="129" t="str">
         <f t="shared" si="46"/>
@@ -58015,16 +58011,16 @@
     <row r="88" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="73"/>
       <c r="B88" s="73"/>
-      <c r="C88" s="166"/>
-      <c r="D88" s="167"/>
-      <c r="E88" s="167"/>
-      <c r="F88" s="167"/>
-      <c r="G88" s="168"/>
+      <c r="C88" s="192"/>
+      <c r="D88" s="193"/>
+      <c r="E88" s="193"/>
+      <c r="F88" s="193"/>
+      <c r="G88" s="194"/>
       <c r="H88" s="75"/>
       <c r="I88" s="69"/>
       <c r="J88" s="99" t="str">
         <f>VLOOKUP(8,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓐ Czech Republic</v>
+        <v>Ⓒ Scotland</v>
       </c>
       <c r="K88" s="100">
         <f t="shared" si="47"/>
@@ -58099,7 +58095,7 @@
       </c>
       <c r="AM88" s="123">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN88" s="123">
         <f t="shared" si="45"/>
@@ -58107,7 +58103,7 @@
       </c>
       <c r="AP88" s="123">
         <f>AN88/AN92*10000+AM88/AM92*1000+AI88/AI92*100+IF(AQ88=0,ROW(),AQ88)/2000000</f>
-        <v>7.7547E-4</v>
+        <v>500.00077547000001</v>
       </c>
       <c r="AQ88" s="126">
         <f t="shared" si="37"/>
@@ -58115,7 +58111,7 @@
       </c>
       <c r="AR88" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ADEFGI</v>
+        <v>CDEFGI</v>
       </c>
       <c r="AS88" s="129" t="str">
         <f t="shared" si="46"/>
@@ -58138,7 +58134,7 @@
       <c r="I89" s="69"/>
       <c r="J89" s="102" t="str">
         <f>VLOOKUP(9,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓒ Scotland</v>
+        <v>Ⓚ DR Congo</v>
       </c>
       <c r="K89" s="103">
         <f t="shared" si="47"/>
@@ -58213,7 +58209,7 @@
       </c>
       <c r="AM89" s="123">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN89" s="123">
         <f t="shared" si="45"/>
@@ -58221,7 +58217,7 @@
       </c>
       <c r="AP89" s="123">
         <f>AN89/AN92*10000+AM89/AM92*1000+AI89/AI92*100+IF(AQ89=0,ROW(),AQ89)/2000000</f>
-        <v>7.8213000000000002E-4</v>
+        <v>500.00078213</v>
       </c>
       <c r="AQ89" s="126">
         <f t="shared" si="37"/>
@@ -58229,7 +58225,7 @@
       </c>
       <c r="AR89" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ADEFGIJ</v>
+        <v>CDEFGIJ</v>
       </c>
       <c r="AS89" s="129" t="str">
         <f t="shared" si="46"/>
@@ -58252,7 +58248,7 @@
       <c r="I90" s="69"/>
       <c r="J90" s="102" t="str">
         <f>VLOOKUP(10,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓚ DR Congo</v>
+        <v>Ⓑ Qatar</v>
       </c>
       <c r="K90" s="103">
         <f t="shared" si="47"/>
@@ -58292,7 +58288,7 @@
       </c>
       <c r="AD90" s="123">
         <f t="shared" si="38"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE90" s="124" t="str">
         <f>J71</f>
@@ -58327,7 +58323,7 @@
       </c>
       <c r="AM90" s="123">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN90" s="123">
         <f t="shared" si="45"/>
@@ -58335,7 +58331,7 @@
       </c>
       <c r="AP90" s="123">
         <f>AN90/AN92*10000+AM90/AM92*1000+AI90/AI92*100+IF(AQ90=0,ROW(),AQ90)/2000000</f>
-        <v>7.391749999999999E-4</v>
+        <v>500.00073917499998</v>
       </c>
       <c r="AQ90" s="126">
         <f t="shared" si="37"/>
@@ -58343,7 +58339,7 @@
       </c>
       <c r="AR90" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ADEFGIJ</v>
+        <v>CDEFGIJ</v>
       </c>
       <c r="AS90" s="129" t="str">
         <f t="shared" si="46"/>
@@ -58366,7 +58362,7 @@
       <c r="I91" s="69"/>
       <c r="J91" s="102" t="str">
         <f>VLOOKUP(11,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓑ Qatar</v>
+        <v>Ⓗ Saudi Arabia</v>
       </c>
       <c r="K91" s="103">
         <f t="shared" si="47"/>
@@ -58441,7 +58437,7 @@
       </c>
       <c r="AM91" s="123">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN91" s="123">
         <f>VLOOKUP($AE91,$AE$8:$AQ$78,10,FALSE)</f>
@@ -58449,7 +58445,7 @@
       </c>
       <c r="AP91" s="123">
         <f>AN91/AN92*10000+AM91/AM92*1000+AI91/AI92*100+IF(AQ91=0,ROW(),AQ91)/2000000</f>
-        <v>7.7032000000000001E-4</v>
+        <v>500.00077032000002</v>
       </c>
       <c r="AQ91" s="126">
         <f t="shared" si="37"/>
@@ -58457,7 +58453,7 @@
       </c>
       <c r="AR91" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ADEFGIJL</v>
+        <v>CDEFGIJL</v>
       </c>
       <c r="AS91" s="129" t="str">
         <f t="shared" si="46"/>
@@ -58480,11 +58476,11 @@
       <c r="I92" s="69"/>
       <c r="J92" s="105" t="str">
         <f>VLOOKUP(12,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓗ Saudi Arabia</v>
+        <v>Ⓐ Czech Republic</v>
       </c>
       <c r="K92" s="106">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" s="106">
         <f>VLOOKUP(12,$AD$80:$AN$91,3,FALSE)</f>
@@ -58496,11 +58492,11 @@
       </c>
       <c r="N92" s="106">
         <f>VLOOKUP(12,$AD$80:$AN$91,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O92" s="106" t="str">
         <f>VLOOKUP(12,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(12,$AD$80:$AN$91,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 2</v>
       </c>
       <c r="P92" s="107">
         <f t="shared" si="48"/>
@@ -58516,23 +58512,23 @@
       </c>
       <c r="AH92" s="123">
         <f>MAX(AH80:AH91)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI92" s="123">
         <f>MAX(AI80:AI91)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ92" s="123">
         <f>MAX(AJ80:AJ91)+1</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AL92" s="123">
         <f>MIN(AL80:AL91)</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM92" s="123">
         <f>MAX(AM80:AM91)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN92" s="123">
         <f>MAX(AN80:AN91)+1</f>
@@ -58697,11 +58693,31 @@
   <sheetProtection algorithmName="SHA-512" hashValue="7nWuIQAsd0NKRlhwUK3tOeNHpTch5B5FULy2gxNNaIdJM5RfhFSMzPcx55y+pmM3d73guUy+p5Y+SvIjJZQRaA==" saltValue="Uw23KnM8csnTioq5H8upCA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <dataConsolidate/>
   <mergeCells count="45">
-    <mergeCell ref="BK14:BK15"/>
-    <mergeCell ref="BY16:BY17"/>
-    <mergeCell ref="BK26:BK27"/>
-    <mergeCell ref="BR28:BR29"/>
-    <mergeCell ref="BK22:BK23"/>
+    <mergeCell ref="CK68:CQ69"/>
+    <mergeCell ref="C83:G88"/>
+    <mergeCell ref="BK70:BK71"/>
+    <mergeCell ref="BY48:BY49"/>
+    <mergeCell ref="BY64:BY65"/>
+    <mergeCell ref="CF55:CF56"/>
+    <mergeCell ref="BK58:BK59"/>
+    <mergeCell ref="BR60:BR61"/>
+    <mergeCell ref="BK62:BK63"/>
+    <mergeCell ref="BK66:BK67"/>
+    <mergeCell ref="BR68:BR69"/>
+    <mergeCell ref="BK50:BK51"/>
+    <mergeCell ref="BR52:BR53"/>
+    <mergeCell ref="BK54:BK55"/>
+    <mergeCell ref="CE68:CJ69"/>
+    <mergeCell ref="CF6:CJ7"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="A5:H6"/>
+    <mergeCell ref="J5:P6"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="BR12:BR13"/>
+    <mergeCell ref="BK6:BO7"/>
+    <mergeCell ref="BR6:BV7"/>
+    <mergeCell ref="BY6:CC7"/>
     <mergeCell ref="CF23:CF24"/>
     <mergeCell ref="BK18:BK19"/>
     <mergeCell ref="BR20:BR21"/>
@@ -58717,31 +58733,11 @@
     <mergeCell ref="BK42:BK43"/>
     <mergeCell ref="CM33:CQ34"/>
     <mergeCell ref="CM37:CM38"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="BR12:BR13"/>
-    <mergeCell ref="BK6:BO7"/>
-    <mergeCell ref="BR6:BV7"/>
-    <mergeCell ref="BY6:CC7"/>
-    <mergeCell ref="CF6:CJ7"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="A5:H6"/>
-    <mergeCell ref="J5:P6"/>
-    <mergeCell ref="CK68:CQ69"/>
-    <mergeCell ref="C83:G88"/>
-    <mergeCell ref="BK70:BK71"/>
-    <mergeCell ref="BY48:BY49"/>
-    <mergeCell ref="BY64:BY65"/>
-    <mergeCell ref="CF55:CF56"/>
-    <mergeCell ref="BK58:BK59"/>
-    <mergeCell ref="BR60:BR61"/>
-    <mergeCell ref="BK62:BK63"/>
-    <mergeCell ref="BK66:BK67"/>
-    <mergeCell ref="BR68:BR69"/>
-    <mergeCell ref="BK50:BK51"/>
-    <mergeCell ref="BR52:BR53"/>
-    <mergeCell ref="BK54:BK55"/>
-    <mergeCell ref="CE68:CJ69"/>
+    <mergeCell ref="BK14:BK15"/>
+    <mergeCell ref="BY16:BY17"/>
+    <mergeCell ref="BK26:BK27"/>
+    <mergeCell ref="BR28:BR29"/>
+    <mergeCell ref="BK22:BK23"/>
   </mergeCells>
   <conditionalFormatting sqref="A7:E78">
     <cfRule type="expression" dxfId="228" priority="339">
@@ -60038,15 +60034,15 @@
     <row r="3" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B3" s="109">
         <f>MATCH(C3,C6:C500,0)</f>
-        <v>194</v>
+        <v>38</v>
       </c>
       <c r="C3" s="121" t="str">
         <f>'2026 World Cup'!AR91</f>
-        <v>ADEFGIJL</v>
+        <v>CDEFGIJL</v>
       </c>
       <c r="D3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,2,FALSE)</f>
-        <v>3E</v>
+        <v>3C</v>
       </c>
       <c r="E3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,3,FALSE)</f>
@@ -60054,7 +60050,7 @@
       </c>
       <c r="F3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,4,FALSE)</f>
-        <v>3J</v>
+        <v>3E</v>
       </c>
       <c r="G3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,5,FALSE)</f>
@@ -60062,7 +60058,7 @@
       </c>
       <c r="H3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,6,FALSE)</f>
-        <v>3A</v>
+        <v>3J</v>
       </c>
       <c r="I3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,7,FALSE)</f>

--- a/public/worldcup.xlsx
+++ b/public/worldcup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rylanpaul/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01B6D0D5-8BEF-0744-A445-2947AF29247D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0F3F4DC-2D43-3E4A-B6B1-89FC2F43EA69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T" sheetId="1" state="hidden" r:id="rId1"/>
@@ -13305,12 +13305,56 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -13391,50 +13435,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -38799,13 +38799,13 @@
       <c r="B4" s="145" t="s">
         <v>1798</v>
       </c>
-      <c r="C4" s="146" t="e">
+      <c r="C4" s="146">
         <f>IFERROR(_xlfn.XLOOKUP(B4,Rounds!A$2:A$25,Rounds!B$2:B$25), _xlfn.XLOOKUP(B4,Rounds!D$2:D$25,Rounds!C$2:C$25))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D4" s="146" t="e">
+        <v>1</v>
+      </c>
+      <c r="D4" s="146">
         <f>IFERROR(_xlfn.XLOOKUP(B4,Rounds!A$2:A$25,Rounds!C$2:C$25), _xlfn.XLOOKUP(B4,Rounds!D$2:D$25,Rounds!B$2:B$25))</f>
-        <v>#N/A</v>
+        <v>1</v>
       </c>
       <c r="E4" s="147" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(B4,Rounds!A$2:A$25,Rounds!D$2:D$25), _xlfn.XLOOKUP(B4,Rounds!D$2:D$25,Rounds!A$2:A$25))</f>
@@ -39111,13 +39111,13 @@
       <c r="B7" s="132" t="s">
         <v>1798</v>
       </c>
-      <c r="C7" s="82" t="e">
+      <c r="C7" s="82">
         <f>IFERROR(_xlfn.XLOOKUP(B7,Rounds!A$2:A$25,Rounds!B$2:B$25), _xlfn.XLOOKUP(B7,Rounds!D$2:D$25,Rounds!C$2:C$25))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D7" s="82" t="e">
+        <v>1</v>
+      </c>
+      <c r="D7" s="82">
         <f>IFERROR(_xlfn.XLOOKUP(B7,Rounds!A$2:A$25,Rounds!C$2:C$25), _xlfn.XLOOKUP(B7,Rounds!D$2:D$25,Rounds!B$2:B$25))</f>
-        <v>#N/A</v>
+        <v>1</v>
       </c>
       <c r="E7" s="134" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(B7,Rounds!A$2:A$25,Rounds!D$2:D$25), _xlfn.XLOOKUP(B7,Rounds!D$2:D$25,Rounds!A$2:A$25))</f>
@@ -39215,13 +39215,13 @@
       <c r="B8" s="149" t="s">
         <v>1798</v>
       </c>
-      <c r="C8" s="150" t="e">
+      <c r="C8" s="150">
         <f>IFERROR(_xlfn.XLOOKUP(B8,Rounds!A$2:A$25,Rounds!B$2:B$25), _xlfn.XLOOKUP(B8,Rounds!D$2:D$25,Rounds!C$2:C$25))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D8" s="150" t="e">
+        <v>1</v>
+      </c>
+      <c r="D8" s="150">
         <f>IFERROR(_xlfn.XLOOKUP(B8,Rounds!A$2:A$25,Rounds!C$2:C$25), _xlfn.XLOOKUP(B8,Rounds!D$2:D$25,Rounds!B$2:B$25))</f>
-        <v>#N/A</v>
+        <v>1</v>
       </c>
       <c r="E8" s="151" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(B8,Rounds!A$2:A$25,Rounds!D$2:D$25), _xlfn.XLOOKUP(B8,Rounds!D$2:D$25,Rounds!A$2:A$25))</f>
@@ -39667,11 +39667,11 @@
       <c r="A4" s="132" t="str">
         <v>Canada</v>
       </c>
-      <c r="B4" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C4" s="81" t="e">
-        <v>#N/A</v>
+      <c r="B4" s="81">
+        <v>1</v>
+      </c>
+      <c r="C4" s="81">
+        <v>1</v>
       </c>
       <c r="D4" s="134" t="str">
         <v>Bosnia and Herzegovina</v>
@@ -39753,11 +39753,11 @@
       <c r="A5" s="132" t="str">
         <v>United States</v>
       </c>
-      <c r="B5" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C5" s="81" t="e">
-        <v>#N/A</v>
+      <c r="B5" s="81">
+        <v>4</v>
+      </c>
+      <c r="C5" s="81">
+        <v>1</v>
       </c>
       <c r="D5" s="134" t="str">
         <v>Paraguay</v>
@@ -39839,11 +39839,11 @@
       <c r="A6" s="132" t="str">
         <v>Haiti</v>
       </c>
-      <c r="B6" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C6" s="81" t="e">
-        <v>#N/A</v>
+      <c r="B6" s="81">
+        <v>0</v>
+      </c>
+      <c r="C6" s="81">
+        <v>1</v>
       </c>
       <c r="D6" s="134" t="str">
         <v>Scotland</v>
@@ -39909,11 +39909,11 @@
       <c r="A7" s="132" t="str">
         <v>Australia</v>
       </c>
-      <c r="B7" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C7" s="81" t="e">
-        <v>#N/A</v>
+      <c r="B7" s="81">
+        <v>2</v>
+      </c>
+      <c r="C7" s="81">
+        <v>0</v>
       </c>
       <c r="D7" s="134" t="str">
         <v>Turkey</v>
@@ -39979,11 +39979,11 @@
       <c r="A8" s="132" t="str">
         <v>Brazil</v>
       </c>
-      <c r="B8" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C8" s="81" t="e">
-        <v>#N/A</v>
+      <c r="B8" s="81">
+        <v>1</v>
+      </c>
+      <c r="C8" s="81">
+        <v>1</v>
       </c>
       <c r="D8" s="134" t="str">
         <v>Morocco</v>
@@ -40049,11 +40049,11 @@
       <c r="A9" s="132" t="str">
         <v>Qatar</v>
       </c>
-      <c r="B9" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C9" s="81" t="e">
-        <v>#N/A</v>
+      <c r="B9" s="81">
+        <v>1</v>
+      </c>
+      <c r="C9" s="81">
+        <v>1</v>
       </c>
       <c r="D9" s="134" t="str">
         <v>Switzerland</v>
@@ -40173,11 +40173,11 @@
       <c r="A11" s="132" t="str">
         <v>Germany</v>
       </c>
-      <c r="B11" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C11" s="81" t="e">
-        <v>#N/A</v>
+      <c r="B11" s="81">
+        <v>7</v>
+      </c>
+      <c r="C11" s="81">
+        <v>1</v>
       </c>
       <c r="D11" s="134" t="str">
         <v>Curaçao</v>
@@ -40227,11 +40227,11 @@
       <c r="A12" s="132" t="str">
         <v>Netherlands</v>
       </c>
-      <c r="B12" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C12" s="81" t="e">
-        <v>#N/A</v>
+      <c r="B12" s="81">
+        <v>2</v>
+      </c>
+      <c r="C12" s="81">
+        <v>2</v>
       </c>
       <c r="D12" s="134" t="str">
         <v>Japan</v>
@@ -40931,25 +40931,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:95" ht="47" x14ac:dyDescent="0.2">
-      <c r="A1" s="171" t="str" cm="1">
+      <c r="A1" s="182" t="str" cm="1">
         <f t="array" ref="A1">INDEX(T,2,lang)</f>
         <v>2026 World Cup Final Tournament Schedule</v>
       </c>
-      <c r="B1" s="171"/>
-      <c r="C1" s="171"/>
-      <c r="D1" s="171"/>
-      <c r="E1" s="171"/>
-      <c r="F1" s="171"/>
-      <c r="G1" s="171"/>
-      <c r="H1" s="171"/>
-      <c r="I1" s="171"/>
-      <c r="J1" s="171"/>
-      <c r="K1" s="171"/>
-      <c r="L1" s="171"/>
-      <c r="M1" s="171"/>
-      <c r="N1" s="171"/>
-      <c r="O1" s="171"/>
-      <c r="P1" s="171"/>
+      <c r="B1" s="182"/>
+      <c r="C1" s="182"/>
+      <c r="D1" s="182"/>
+      <c r="E1" s="182"/>
+      <c r="F1" s="182"/>
+      <c r="G1" s="182"/>
+      <c r="H1" s="182"/>
+      <c r="I1" s="182"/>
+      <c r="J1" s="182"/>
+      <c r="K1" s="182"/>
+      <c r="L1" s="182"/>
+      <c r="M1" s="182"/>
+      <c r="N1" s="182"/>
+      <c r="O1" s="182"/>
+      <c r="P1" s="182"/>
       <c r="S1" s="123"/>
       <c r="T1" s="123"/>
       <c r="AC1" s="123"/>
@@ -40996,11 +40996,11 @@
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
-      <c r="O3" s="172" t="str">
+      <c r="O3" s="183" t="str">
         <f>"Language: " &amp; Settings!C4</f>
         <v>Language: English</v>
       </c>
-      <c r="P3" s="172"/>
+      <c r="P3" s="183"/>
       <c r="S3" s="123"/>
       <c r="T3" s="123"/>
       <c r="AC3" s="123"/>
@@ -41018,43 +41018,43 @@
     </row>
     <row r="4" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:95" x14ac:dyDescent="0.2">
-      <c r="A5" s="173" t="str" cm="1">
+      <c r="A5" s="184" t="str" cm="1">
         <f t="array" ref="A5">INDEX(T,3,lang)</f>
         <v>Group Stage</v>
       </c>
-      <c r="B5" s="174"/>
-      <c r="C5" s="174"/>
-      <c r="D5" s="174"/>
-      <c r="E5" s="174"/>
-      <c r="F5" s="174"/>
-      <c r="G5" s="174"/>
-      <c r="H5" s="175"/>
-      <c r="J5" s="179" t="s">
+      <c r="B5" s="185"/>
+      <c r="C5" s="185"/>
+      <c r="D5" s="185"/>
+      <c r="E5" s="185"/>
+      <c r="F5" s="185"/>
+      <c r="G5" s="185"/>
+      <c r="H5" s="186"/>
+      <c r="J5" s="190" t="s">
         <v>3166</v>
       </c>
-      <c r="K5" s="180"/>
-      <c r="L5" s="180"/>
-      <c r="M5" s="180"/>
-      <c r="N5" s="180"/>
-      <c r="O5" s="180"/>
-      <c r="P5" s="181"/>
+      <c r="K5" s="191"/>
+      <c r="L5" s="191"/>
+      <c r="M5" s="191"/>
+      <c r="N5" s="191"/>
+      <c r="O5" s="191"/>
+      <c r="P5" s="192"/>
     </row>
     <row r="6" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="176"/>
-      <c r="B6" s="177"/>
-      <c r="C6" s="177"/>
-      <c r="D6" s="177"/>
-      <c r="E6" s="177"/>
-      <c r="F6" s="177"/>
-      <c r="G6" s="177"/>
-      <c r="H6" s="178"/>
-      <c r="J6" s="182"/>
-      <c r="K6" s="183"/>
-      <c r="L6" s="183"/>
-      <c r="M6" s="183"/>
-      <c r="N6" s="183"/>
-      <c r="O6" s="183"/>
-      <c r="P6" s="184"/>
+      <c r="A6" s="187"/>
+      <c r="B6" s="188"/>
+      <c r="C6" s="188"/>
+      <c r="D6" s="188"/>
+      <c r="E6" s="188"/>
+      <c r="F6" s="188"/>
+      <c r="G6" s="188"/>
+      <c r="H6" s="189"/>
+      <c r="J6" s="193"/>
+      <c r="K6" s="194"/>
+      <c r="L6" s="194"/>
+      <c r="M6" s="194"/>
+      <c r="N6" s="194"/>
+      <c r="O6" s="194"/>
+      <c r="P6" s="195"/>
       <c r="R6" s="123" t="s">
         <v>3167</v>
       </c>
@@ -41164,37 +41164,37 @@
       <c r="BI6" s="128" t="s">
         <v>3178</v>
       </c>
-      <c r="BK6" s="165" t="s">
+      <c r="BK6" s="176" t="s">
         <v>3179</v>
       </c>
-      <c r="BL6" s="166"/>
-      <c r="BM6" s="166"/>
-      <c r="BN6" s="166"/>
-      <c r="BO6" s="167"/>
-      <c r="BR6" s="165" t="str" cm="1">
+      <c r="BL6" s="177"/>
+      <c r="BM6" s="177"/>
+      <c r="BN6" s="177"/>
+      <c r="BO6" s="178"/>
+      <c r="BR6" s="176" t="str" cm="1">
         <f t="array" ref="BR6">INDEX(T,4,lang)</f>
         <v>Round of 16</v>
       </c>
-      <c r="BS6" s="166"/>
-      <c r="BT6" s="166"/>
-      <c r="BU6" s="166"/>
-      <c r="BV6" s="167"/>
-      <c r="BY6" s="165" t="str" cm="1">
+      <c r="BS6" s="177"/>
+      <c r="BT6" s="177"/>
+      <c r="BU6" s="177"/>
+      <c r="BV6" s="178"/>
+      <c r="BY6" s="176" t="str" cm="1">
         <f t="array" ref="BY6">INDEX(T,5,lang)</f>
         <v>Quarterfinals</v>
       </c>
-      <c r="BZ6" s="166"/>
-      <c r="CA6" s="166"/>
-      <c r="CB6" s="166"/>
-      <c r="CC6" s="167"/>
-      <c r="CF6" s="165" t="str" cm="1">
+      <c r="BZ6" s="177"/>
+      <c r="CA6" s="177"/>
+      <c r="CB6" s="177"/>
+      <c r="CC6" s="178"/>
+      <c r="CF6" s="176" t="str" cm="1">
         <f t="array" ref="CF6">INDEX(T,6,lang)</f>
         <v>Semi-Finals</v>
       </c>
-      <c r="CG6" s="166"/>
-      <c r="CH6" s="166"/>
-      <c r="CI6" s="166"/>
-      <c r="CJ6" s="167"/>
+      <c r="CG6" s="177"/>
+      <c r="CH6" s="177"/>
+      <c r="CI6" s="177"/>
+      <c r="CJ6" s="178"/>
     </row>
     <row r="7" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="11">
@@ -41271,26 +41271,26 @@
         <v>1</v>
       </c>
       <c r="AY7" s="126"/>
-      <c r="BK7" s="168"/>
-      <c r="BL7" s="169"/>
-      <c r="BM7" s="169"/>
-      <c r="BN7" s="169"/>
-      <c r="BO7" s="170"/>
-      <c r="BR7" s="168"/>
-      <c r="BS7" s="169"/>
-      <c r="BT7" s="169"/>
-      <c r="BU7" s="169"/>
-      <c r="BV7" s="170"/>
-      <c r="BY7" s="168"/>
-      <c r="BZ7" s="169"/>
-      <c r="CA7" s="169"/>
-      <c r="CB7" s="169"/>
-      <c r="CC7" s="170"/>
-      <c r="CF7" s="168"/>
-      <c r="CG7" s="169"/>
-      <c r="CH7" s="169"/>
-      <c r="CI7" s="169"/>
-      <c r="CJ7" s="170"/>
+      <c r="BK7" s="179"/>
+      <c r="BL7" s="180"/>
+      <c r="BM7" s="180"/>
+      <c r="BN7" s="180"/>
+      <c r="BO7" s="181"/>
+      <c r="BR7" s="179"/>
+      <c r="BS7" s="180"/>
+      <c r="BT7" s="180"/>
+      <c r="BU7" s="180"/>
+      <c r="BV7" s="181"/>
+      <c r="BY7" s="179"/>
+      <c r="BZ7" s="180"/>
+      <c r="CA7" s="180"/>
+      <c r="CB7" s="180"/>
+      <c r="CC7" s="181"/>
+      <c r="CF7" s="179"/>
+      <c r="CG7" s="180"/>
+      <c r="CH7" s="180"/>
+      <c r="CI7" s="180"/>
+      <c r="CJ7" s="181"/>
     </row>
     <row r="8" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A8" s="16">
@@ -41559,8 +41559,12 @@
         <f>AE14</f>
         <v>Canada</v>
       </c>
-      <c r="F9" s="19"/>
-      <c r="G9" s="20"/>
+      <c r="F9" s="19">
+        <v>1</v>
+      </c>
+      <c r="G9" s="20">
+        <v>1</v>
+      </c>
       <c r="H9" s="80" t="str">
         <f>AE15</f>
         <v>Bosnia and Herzegovina</v>
@@ -41599,43 +41603,43 @@
       </c>
       <c r="S9" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Canada_draw</v>
       </c>
       <c r="T9" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Bosnia and Herzegovina_draw</v>
       </c>
       <c r="U9" s="123">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="123">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" s="123">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9" s="123">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9" s="123">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z9" s="123">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA9" s="123">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB9" s="123" t="str">
+      <c r="AB9" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AD9" s="123">
         <f>COUNTIF(AR8:AR11,CONCATENATE("&gt;=",AR9))</f>
@@ -41820,8 +41824,12 @@
         <f>AE26</f>
         <v>United States</v>
       </c>
-      <c r="F10" s="19"/>
-      <c r="G10" s="20"/>
+      <c r="F10" s="19">
+        <v>4</v>
+      </c>
+      <c r="G10" s="20">
+        <v>1</v>
+      </c>
       <c r="H10" s="80" t="str">
         <f>AE27</f>
         <v>Paraguay</v>
@@ -41860,11 +41868,11 @@
       </c>
       <c r="S10" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>United States_win</v>
       </c>
       <c r="T10" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Paraguay_lose</v>
       </c>
       <c r="U10" s="123">
         <f t="shared" si="8"/>
@@ -41894,9 +41902,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB10" s="123" t="str">
+      <c r="AB10" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD10" s="123">
         <f>COUNTIF(AR8:AR11,CONCATENATE("&gt;=",AR10))</f>
@@ -42018,7 +42026,7 @@
         <f>BH10/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK10" s="163">
+      <c r="BK10" s="173">
         <v>74</v>
       </c>
       <c r="BL10" s="24" t="str">
@@ -42079,8 +42087,12 @@
         <f>AE22</f>
         <v>Haiti</v>
       </c>
-      <c r="F11" s="19"/>
-      <c r="G11" s="20"/>
+      <c r="F11" s="19">
+        <v>0</v>
+      </c>
+      <c r="G11" s="20">
+        <v>1</v>
+      </c>
       <c r="H11" s="80" t="str">
         <f>AE23</f>
         <v>Scotland</v>
@@ -42119,11 +42131,11 @@
       </c>
       <c r="S11" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Haiti_lose</v>
       </c>
       <c r="T11" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Scotland_win</v>
       </c>
       <c r="U11" s="123">
         <f t="shared" si="8"/>
@@ -42153,9 +42165,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB11" s="123" t="str">
+      <c r="AB11" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>-1</v>
       </c>
       <c r="AD11" s="123">
         <f>COUNTIF(AR8:AR11,CONCATENATE("&gt;=",AR11))</f>
@@ -42277,7 +42289,7 @@
         <f>BH11/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK11" s="164"/>
+      <c r="BK11" s="174"/>
       <c r="BL11" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!G3,AK80:AS91,9,FALSE),"3rd Group A/B/C/D/F")</f>
         <v>3rd Group A/B/C/D/F</v>
@@ -42342,8 +42354,12 @@
         <f>AE28</f>
         <v>Australia</v>
       </c>
-      <c r="F12" s="19"/>
-      <c r="G12" s="20"/>
+      <c r="F12" s="19">
+        <v>2</v>
+      </c>
+      <c r="G12" s="20">
+        <v>0</v>
+      </c>
       <c r="H12" s="80" t="str">
         <f>AE29</f>
         <v>Turkey</v>
@@ -42382,11 +42398,11 @@
       </c>
       <c r="S12" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Australia_win</v>
       </c>
       <c r="T12" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Turkey_lose</v>
       </c>
       <c r="U12" s="123">
         <f t="shared" si="8"/>
@@ -42416,9 +42432,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB12" s="123" t="str">
+      <c r="AB12" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AF12" s="123">
         <f t="shared" ref="AF12:AH12" si="12">MAX(AF8:AF11)-MIN(AF8:AF11)+1</f>
@@ -42511,7 +42527,7 @@
       <c r="BO12" s="21"/>
       <c r="BP12" s="114"/>
       <c r="BQ12" s="112"/>
-      <c r="BR12" s="163">
+      <c r="BR12" s="173">
         <v>89</v>
       </c>
       <c r="BS12" s="24" t="str">
@@ -42565,8 +42581,12 @@
         <f>AE20</f>
         <v>Brazil</v>
       </c>
-      <c r="F13" s="19"/>
-      <c r="G13" s="20"/>
+      <c r="F13" s="19">
+        <v>1</v>
+      </c>
+      <c r="G13" s="20">
+        <v>1</v>
+      </c>
       <c r="H13" s="80" t="str">
         <f>AE21</f>
         <v>Morocco</v>
@@ -42577,43 +42597,43 @@
       </c>
       <c r="S13" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Brazil_draw</v>
       </c>
       <c r="T13" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Morocco_draw</v>
       </c>
       <c r="U13" s="123">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="123">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W13" s="123">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X13" s="123">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y13" s="123">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z13" s="123">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA13" s="123">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB13" s="123" t="str">
+      <c r="AB13" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BK13" s="21" t="str" cm="1">
         <f t="array" ref="BK13">INDEX(T,24+MONTH(BP13),lang) &amp; " " &amp; DAY(BP13) &amp; ", " &amp; YEAR(BP13) &amp; "   " &amp; (IF(HOUR(BP13)&lt;10,0,"")&amp;HOUR(BP13)) &amp; ":" &amp;  (IF(MINUTE(BP13)&lt;10,0,"")&amp;MINUTE(BP13))</f>
@@ -42628,7 +42648,7 @@
         <v>46203.875</v>
       </c>
       <c r="BQ13" s="115"/>
-      <c r="BR13" s="164"/>
+      <c r="BR13" s="174"/>
       <c r="BS13" s="26" t="str">
         <f>IF(BP14&gt;BP15,BL14,IF(BP14&lt;BP15,BL15,""))</f>
         <v/>
@@ -42680,8 +42700,12 @@
         <f>AE16</f>
         <v>Qatar</v>
       </c>
-      <c r="F14" s="19"/>
-      <c r="G14" s="20"/>
+      <c r="F14" s="19">
+        <v>1</v>
+      </c>
+      <c r="G14" s="20">
+        <v>1</v>
+      </c>
       <c r="H14" s="80" t="str">
         <f>AE17</f>
         <v>Switzerland</v>
@@ -42720,43 +42744,43 @@
       </c>
       <c r="S14" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Qatar_draw</v>
       </c>
       <c r="T14" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Switzerland_draw</v>
       </c>
       <c r="U14" s="123">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="123">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W14" s="123">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X14" s="123">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14" s="123">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z14" s="123">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA14" s="123">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB14" s="123" t="str">
+      <c r="AB14" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AD14" s="123">
         <f>COUNTIF(AR14:AR17,CONCATENATE("&gt;=",AR14))</f>
@@ -42772,7 +42796,7 @@
       </c>
       <c r="AG14" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE14 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH14" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE14 &amp; "_lose")</f>
@@ -42780,11 +42804,11 @@
       </c>
       <c r="AI14" s="123">
         <f>SUMIF($E$7:$E$78,$AE14,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE14,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ14" s="123">
         <f>SUMIF($E$7:$E$78,$AE14,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE14,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL14" s="123">
         <f>AI14-AJ14</f>
@@ -42796,15 +42820,15 @@
       </c>
       <c r="AN14" s="123">
         <f>AF14*3+AG14</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO14" s="123">
         <f>AN14/AN18*10+BA14</f>
-        <v>0</v>
+        <v>5.9901960784313726</v>
       </c>
       <c r="AP14" s="123">
         <f>AO14*10000000+BI14*100+AM14/AM18*10+AI14/AI18*1++IF(AQ14=0,ROW(),AQ14)/2000000</f>
-        <v>7.7824000000000003E-4</v>
+        <v>59902060.304699808</v>
       </c>
       <c r="AQ14" s="126">
         <f>VLOOKUP(AE14,db_fifarank,2,FALSE)</f>
@@ -42812,7 +42836,7 @@
       </c>
       <c r="AR14" s="125">
         <f>AP14/AP18</f>
-        <v>7.7759871434028365E-4</v>
+        <v>0.99999998330530815</v>
       </c>
       <c r="AS14" s="125" t="str">
         <f>IF(SUM(AF14:AH17)=12,J15,"1B")</f>
@@ -42824,15 +42848,15 @@
       </c>
       <c r="AU14" s="126" cm="1">
         <f t="array" ref="AU14">SUMPRODUCT(($S$7:$S$78=AE14&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE14&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV14" s="126" cm="1">
         <f t="array" ref="AV14">SUMPRODUCT(($E$7:$E$78=AE14)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE14)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW14" s="126" cm="1">
         <f t="array" ref="AW14">SUMPRODUCT(($E$7:$E$78=AE14)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE14)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX14" s="126">
         <f>AV14-AW14</f>
@@ -42844,11 +42868,11 @@
       </c>
       <c r="AZ14" s="126">
         <f>AT14/AT18*1000+AU14/AU18*100+AY14/AY18*10+AV14/AV18</f>
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="BA14" s="126">
         <f>AZ14/AZ18</f>
-        <v>0</v>
+        <v>0.99019607843137258</v>
       </c>
       <c r="BB14" s="126" cm="1">
         <f t="array" ref="BB14">SUMPRODUCT(($S$7:$S$78=AE14&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE14&amp;"_win")*($X$7:$X$78))</f>
@@ -42856,15 +42880,15 @@
       </c>
       <c r="BC14" s="126" cm="1">
         <f t="array" ref="BC14">SUMPRODUCT(($S$7:$S$78=AE14&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE14&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD14" s="126" cm="1">
         <f t="array" ref="BD14">SUMPRODUCT(($E$7:$E$78=AE14)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE14)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE14" s="126" cm="1">
         <f t="array" ref="BE14">SUMPRODUCT(($E$7:$E$78=AE14)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE14)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF14" s="126">
         <f>BD14-BE14</f>
@@ -42876,13 +42900,13 @@
       </c>
       <c r="BH14" s="126">
         <f>BB14/BB18*1000+BC14/BC18*100+BG14/BG18*10+BD14/BD18</f>
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="BI14" s="126">
         <f>BH14/BH18</f>
-        <v>0</v>
-      </c>
-      <c r="BK14" s="163">
+        <v>0.99019607843137258</v>
+      </c>
+      <c r="BK14" s="173">
         <v>77</v>
       </c>
       <c r="BL14" s="24" t="str">
@@ -42955,7 +42979,7 @@
       </c>
       <c r="K15" s="31">
         <f>L15+M15+N15</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="31">
         <f>VLOOKUP(1,AD14:AN17,3,FALSE)</f>
@@ -42963,7 +42987,7 @@
       </c>
       <c r="M15" s="31">
         <f>VLOOKUP(1,AD14:AN17,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" s="31">
         <f>VLOOKUP(1,AD14:AN17,5,FALSE)</f>
@@ -42971,11 +42995,11 @@
       </c>
       <c r="O15" s="31" t="str">
         <f>VLOOKUP(1,AD14:AN17,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD14:AN17,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 1</v>
       </c>
       <c r="P15" s="32">
         <f>L15*3+M15</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" s="123">
         <f>DATE(2026,6,14)+TIME(12,0,0)+gmt_delta</f>
@@ -43035,7 +43059,7 @@
       </c>
       <c r="AG15" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE15 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH15" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE15 &amp; "_lose")</f>
@@ -43043,11 +43067,11 @@
       </c>
       <c r="AI15" s="123">
         <f>SUMIF($E$7:$E$78,$AE15,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE15,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ15" s="123">
         <f>SUMIF($E$7:$E$78,$AE15,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE15,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL15" s="123">
         <f>AI15-AJ15</f>
@@ -43059,15 +43083,15 @@
       </c>
       <c r="AN15" s="123">
         <f>AF15*3+AG15</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO15" s="123">
         <f>AN15/AN18*10+BA15</f>
-        <v>0</v>
+        <v>5.9901960784313726</v>
       </c>
       <c r="AP15" s="123">
         <f>AO15*10000000+BI15*100+AM15/AM18*10+AI15/AI18*1++IF(AQ15=0,ROW(),AQ15)/2000000</f>
-        <v>6.9291999999999997E-4</v>
+        <v>59902060.304614484</v>
       </c>
       <c r="AQ15" s="126">
         <f>VLOOKUP(AE15,db_fifarank,2,FALSE)</f>
@@ -43075,7 +43099,7 @@
       </c>
       <c r="AR15" s="125">
         <f>AP15/AP18</f>
-        <v>6.9234901976340118E-4</v>
+        <v>0.99999998330388373</v>
       </c>
       <c r="AS15" s="125" t="str">
         <f>IF(SUM(AF14:AH17)=12,J16,"2B")</f>
@@ -43087,15 +43111,15 @@
       </c>
       <c r="AU15" s="126" cm="1">
         <f t="array" ref="AU15">SUMPRODUCT(($S$7:$S$78=AE15&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE15&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV15" s="126" cm="1">
         <f t="array" ref="AV15">SUMPRODUCT(($E$7:$E$78=AE15)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE15)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW15" s="126" cm="1">
         <f t="array" ref="AW15">SUMPRODUCT(($E$7:$E$78=AE15)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE15)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX15" s="126">
         <f>AV15-AW15</f>
@@ -43107,11 +43131,11 @@
       </c>
       <c r="AZ15" s="126">
         <f>AT15/AT18*1000+AU15/AU18*100+AY15/AY18*10+AV15/AV18</f>
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="BA15" s="126">
         <f>AZ15/AZ18</f>
-        <v>0</v>
+        <v>0.99019607843137258</v>
       </c>
       <c r="BB15" s="126" cm="1">
         <f t="array" ref="BB15">SUMPRODUCT(($S$7:$S$78=AE15&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE15&amp;"_win")*($X$7:$X$78))</f>
@@ -43119,15 +43143,15 @@
       </c>
       <c r="BC15" s="126" cm="1">
         <f t="array" ref="BC15">SUMPRODUCT(($S$7:$S$78=AE15&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE15&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD15" s="126" cm="1">
         <f t="array" ref="BD15">SUMPRODUCT(($E$7:$E$78=AE15)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE15)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE15" s="126" cm="1">
         <f t="array" ref="BE15">SUMPRODUCT(($E$7:$E$78=AE15)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE15)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF15" s="126">
         <f>BD15-BE15</f>
@@ -43139,13 +43163,13 @@
       </c>
       <c r="BH15" s="126">
         <f>BB15/BB18*1000+BC15/BC18*100+BG15/BG18*10+BD15/BD18</f>
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="BI15" s="126">
         <f>BH15/BH18</f>
-        <v>0</v>
-      </c>
-      <c r="BK15" s="164"/>
+        <v>0.99019607843137258</v>
+      </c>
+      <c r="BK15" s="174"/>
       <c r="BL15" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!I3,AK80:AS91,9,FALSE),"3rd Group C/D/F/G/H")</f>
         <v>3rd Group C/D/F/G/H</v>
@@ -43203,8 +43227,12 @@
         <f>AE32</f>
         <v>Germany</v>
       </c>
-      <c r="F16" s="19"/>
-      <c r="G16" s="20"/>
+      <c r="F16" s="19">
+        <v>7</v>
+      </c>
+      <c r="G16" s="20">
+        <v>1</v>
+      </c>
       <c r="H16" s="80" t="str">
         <f>AE33</f>
         <v>Curaçao</v>
@@ -43215,7 +43243,7 @@
       </c>
       <c r="K16" s="23">
         <f>L16+M16+N16</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="23">
         <f>VLOOKUP(2,AD14:AN17,3,FALSE)</f>
@@ -43223,7 +43251,7 @@
       </c>
       <c r="M16" s="23">
         <f>VLOOKUP(2,AD14:AN17,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" s="23">
         <f>VLOOKUP(2,AD14:AN17,5,FALSE)</f>
@@ -43231,11 +43259,11 @@
       </c>
       <c r="O16" s="23" t="str">
         <f>VLOOKUP(2,AD14:AN17,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD14:AN17,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 1</v>
       </c>
       <c r="P16" s="34">
         <f>L16*3+M16</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" s="123">
         <f>DATE(2026,6,14)+TIME(6,0,0)+gmt_delta</f>
@@ -43243,11 +43271,11 @@
       </c>
       <c r="S16" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Germany_win</v>
       </c>
       <c r="T16" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Curaçao_lose</v>
       </c>
       <c r="U16" s="123">
         <f t="shared" si="8"/>
@@ -43277,9 +43305,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB16" s="123" t="str">
+      <c r="AB16" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD16" s="123">
         <f>COUNTIF(AR14:AR17,CONCATENATE("&gt;=",AR16))</f>
@@ -43295,7 +43323,7 @@
       </c>
       <c r="AG16" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE16 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH16" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE16 &amp; "_lose")</f>
@@ -43303,11 +43331,11 @@
       </c>
       <c r="AI16" s="123">
         <f>SUMIF($E$7:$E$78,$AE16,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE16,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ16" s="123">
         <f>SUMIF($E$7:$E$78,$AE16,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE16,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL16" s="123">
         <f>AI16-AJ16</f>
@@ -43319,15 +43347,15 @@
       </c>
       <c r="AN16" s="123">
         <f>AF16*3+AG16</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO16" s="123">
         <f>AN16/AN18*10+BA16</f>
-        <v>0</v>
+        <v>5.9901960784313726</v>
       </c>
       <c r="AP16" s="123">
         <f>AO16*10000000+BI16*100+AM16/AM18*10+AI16/AI18*1++IF(AQ16=0,ROW(),AQ16)/2000000</f>
-        <v>7.2747999999999997E-4</v>
+        <v>59902060.304649048</v>
       </c>
       <c r="AQ16" s="126">
         <f>VLOOKUP(AE16,db_fifarank,2,FALSE)</f>
@@ -43335,7 +43363,7 @@
       </c>
       <c r="AR16" s="125">
         <f>AP16/AP18</f>
-        <v>7.268805416173282E-4</v>
+        <v>0.99999998330446072</v>
       </c>
       <c r="AT16" s="126" cm="1">
         <f t="array" ref="AT16">SUMPRODUCT(($S$7:$S$78=AE16&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE16&amp;"_win")*($U$7:$U$78))</f>
@@ -43343,15 +43371,15 @@
       </c>
       <c r="AU16" s="126" cm="1">
         <f t="array" ref="AU16">SUMPRODUCT(($S$7:$S$78=AE16&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE16&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV16" s="126" cm="1">
         <f t="array" ref="AV16">SUMPRODUCT(($E$7:$E$78=AE16)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE16)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW16" s="126" cm="1">
         <f t="array" ref="AW16">SUMPRODUCT(($E$7:$E$78=AE16)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE16)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX16" s="126">
         <f>AV16-AW16</f>
@@ -43363,11 +43391,11 @@
       </c>
       <c r="AZ16" s="126">
         <f>AT16/AT18*1000+AU16/AU18*100+AY16/AY18*10+AV16/AV18</f>
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="BA16" s="126">
         <f>AZ16/AZ18</f>
-        <v>0</v>
+        <v>0.99019607843137258</v>
       </c>
       <c r="BB16" s="126" cm="1">
         <f t="array" ref="BB16">SUMPRODUCT(($S$7:$S$78=AE16&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE16&amp;"_win")*($X$7:$X$78))</f>
@@ -43375,15 +43403,15 @@
       </c>
       <c r="BC16" s="126" cm="1">
         <f t="array" ref="BC16">SUMPRODUCT(($S$7:$S$78=AE16&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE16&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD16" s="126" cm="1">
         <f t="array" ref="BD16">SUMPRODUCT(($E$7:$E$78=AE16)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE16)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE16" s="126" cm="1">
         <f t="array" ref="BE16">SUMPRODUCT(($E$7:$E$78=AE16)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE16)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF16" s="126">
         <f>BD16-BE16</f>
@@ -43395,11 +43423,11 @@
       </c>
       <c r="BH16" s="126">
         <f>BB16/BB18*1000+BC16/BC18*100+BG16/BG18*10+BD16/BD18</f>
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="BI16" s="126">
         <f>BH16/BH18</f>
-        <v>0</v>
+        <v>0.99019607843137258</v>
       </c>
       <c r="BK16" s="21"/>
       <c r="BL16" s="21"/>
@@ -43415,7 +43443,7 @@
       <c r="BV16" s="21"/>
       <c r="BW16" s="114"/>
       <c r="BX16" s="112"/>
-      <c r="BY16" s="163">
+      <c r="BY16" s="173">
         <v>97</v>
       </c>
       <c r="BZ16" s="24" t="str">
@@ -43455,8 +43483,12 @@
         <f>AE38</f>
         <v>Netherlands</v>
       </c>
-      <c r="F17" s="19"/>
-      <c r="G17" s="20"/>
+      <c r="F17" s="19">
+        <v>2</v>
+      </c>
+      <c r="G17" s="20">
+        <v>2</v>
+      </c>
       <c r="H17" s="80" t="str">
         <f>AE39</f>
         <v>Japan</v>
@@ -43467,7 +43499,7 @@
       </c>
       <c r="K17" s="23">
         <f>L17+M17+N17</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="23">
         <f>VLOOKUP(3,AD14:AN17,3,FALSE)</f>
@@ -43475,7 +43507,7 @@
       </c>
       <c r="M17" s="23">
         <f>VLOOKUP(3,AD14:AN17,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" s="23">
         <f>VLOOKUP(3,AD14:AN17,5,FALSE)</f>
@@ -43483,11 +43515,11 @@
       </c>
       <c r="O17" s="23" t="str">
         <f>VLOOKUP(3,AD14:AN17,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD14:AN17,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 1</v>
       </c>
       <c r="P17" s="34">
         <f>L17*3+M17</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" s="123">
         <f>DATE(2026,6,14)+TIME(9,0,0)+gmt_delta</f>
@@ -43495,43 +43527,43 @@
       </c>
       <c r="S17" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Netherlands_draw</v>
       </c>
       <c r="T17" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Japan_draw</v>
       </c>
       <c r="U17" s="123">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="123">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W17" s="123">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X17" s="123">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17" s="123">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z17" s="123">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA17" s="123">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB17" s="123" t="str">
+      <c r="AB17" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AD17" s="123">
         <f>COUNTIF(AR14:AR17,CONCATENATE("&gt;=",AR17))</f>
@@ -43547,7 +43579,7 @@
       </c>
       <c r="AG17" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE17 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH17" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE17 &amp; "_lose")</f>
@@ -43555,11 +43587,11 @@
       </c>
       <c r="AI17" s="123">
         <f>SUMIF($E$7:$E$78,$AE17,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE17,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ17" s="123">
         <f>SUMIF($E$7:$E$78,$AE17,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE17,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL17" s="123">
         <f>AI17-AJ17</f>
@@ -43571,15 +43603,15 @@
       </c>
       <c r="AN17" s="123">
         <f>AF17*3+AG17</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO17" s="123">
         <f>AN17/AN18*10+BA17</f>
-        <v>0</v>
+        <v>5.9901960784313726</v>
       </c>
       <c r="AP17" s="123">
         <f>AO17*10000000+BI17*100+AM17/AM18*10+AI17/AI18*1++IF(AQ17=0,ROW(),AQ17)/2000000</f>
-        <v>8.2470000000000004E-4</v>
+        <v>59902060.304746263</v>
       </c>
       <c r="AQ17" s="126">
         <f>VLOOKUP(AE17,db_fifarank,2,FALSE)</f>
@@ -43587,7 +43619,7 @@
       </c>
       <c r="AR17" s="125">
         <f>AP17/AP18</f>
-        <v>8.2402043035108958E-4</v>
+        <v>0.99999998330608364</v>
       </c>
       <c r="AT17" s="126" cm="1">
         <f t="array" ref="AT17">SUMPRODUCT(($S$7:$S$78=AE17&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE17&amp;"_win")*($U$7:$U$78))</f>
@@ -43595,15 +43627,15 @@
       </c>
       <c r="AU17" s="126" cm="1">
         <f t="array" ref="AU17">SUMPRODUCT(($S$7:$S$78=AE17&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE17&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV17" s="126" cm="1">
         <f t="array" ref="AV17">SUMPRODUCT(($E$7:$E$78=AE17)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE17)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW17" s="126" cm="1">
         <f t="array" ref="AW17">SUMPRODUCT(($E$7:$E$78=AE17)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE17)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX17" s="126">
         <f>AV17-AW17</f>
@@ -43615,11 +43647,11 @@
       </c>
       <c r="AZ17" s="126">
         <f>AT17/AT18*1000+AU17/AU18*100+AY17/AY18*10+AV17/AV18</f>
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="BA17" s="126">
         <f>AZ17/AZ18</f>
-        <v>0</v>
+        <v>0.99019607843137258</v>
       </c>
       <c r="BB17" s="126" cm="1">
         <f t="array" ref="BB17">SUMPRODUCT(($S$7:$S$78=AE17&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE17&amp;"_win")*($X$7:$X$78))</f>
@@ -43627,15 +43659,15 @@
       </c>
       <c r="BC17" s="126" cm="1">
         <f t="array" ref="BC17">SUMPRODUCT(($S$7:$S$78=AE17&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE17&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD17" s="126" cm="1">
         <f t="array" ref="BD17">SUMPRODUCT(($E$7:$E$78=AE17)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE17)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE17" s="126" cm="1">
         <f t="array" ref="BE17">SUMPRODUCT(($E$7:$E$78=AE17)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE17)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF17" s="126">
         <f>BD17-BE17</f>
@@ -43647,11 +43679,11 @@
       </c>
       <c r="BH17" s="126">
         <f>BB17/BB18*1000+BC17/BC18*100+BG17/BG18*10+BD17/BD18</f>
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="BI17" s="126">
         <f>BH17/BH18</f>
-        <v>0</v>
+        <v>0.99019607843137258</v>
       </c>
       <c r="BK17" s="21" t="str" cm="1">
         <f t="array" ref="BK17">INDEX(T,24+MONTH(BP17),lang) &amp; " " &amp; DAY(BP17) &amp; ", " &amp; YEAR(BP17) &amp; "   " &amp; (IF(HOUR(BP17)&lt;10,0,"")&amp;HOUR(BP17)) &amp; ":" &amp;  (IF(MINUTE(BP17)&lt;10,0,"")&amp;MINUTE(BP17))</f>
@@ -43673,7 +43705,7 @@
       <c r="BV17" s="21"/>
       <c r="BW17" s="114"/>
       <c r="BX17" s="115"/>
-      <c r="BY17" s="164"/>
+      <c r="BY17" s="174"/>
       <c r="BZ17" s="26" t="str">
         <f>IF(BW20&gt;BW21,BS20,IF(BW20&lt;BW21,BS21,""))</f>
         <v/>
@@ -43723,7 +43755,7 @@
       </c>
       <c r="K18" s="36">
         <f>L18+M18+N18</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="36">
         <f>VLOOKUP(4,AD14:AN17,3,FALSE)</f>
@@ -43731,7 +43763,7 @@
       </c>
       <c r="M18" s="36">
         <f>VLOOKUP(4,AD14:AN17,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" s="36">
         <f>VLOOKUP(4,AD14:AN17,5,FALSE)</f>
@@ -43739,11 +43771,11 @@
       </c>
       <c r="O18" s="36" t="str">
         <f>VLOOKUP(4,AD14:AN17,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD14:AN17,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 1</v>
       </c>
       <c r="P18" s="37">
         <f>L18*3+M18</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" s="123">
         <f>DATE(2026,6,14)+TIME(15,0,0)+gmt_delta</f>
@@ -43803,7 +43835,7 @@
       </c>
       <c r="AI18" s="123">
         <f>MAX(AI14:AI17)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL18" s="123">
         <f>MIN(AL14:AL17)</f>
@@ -43815,15 +43847,15 @@
       </c>
       <c r="AN18" s="123">
         <f>MAX(AN14:AN17)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO18" s="123">
         <f>MAX(AO14:AO17)+1</f>
-        <v>1</v>
+        <v>6.9901960784313726</v>
       </c>
       <c r="AP18" s="123">
         <f>MAX(AP14:AP17)+1</f>
-        <v>1.0008246999999999</v>
+        <v>59902061.304746263</v>
       </c>
       <c r="AT18" s="126">
         <f>MAX(AT14:AT17)-MIN(AT14:AT17)+1</f>
@@ -43847,7 +43879,7 @@
       </c>
       <c r="AZ18" s="126">
         <f>MAX(AZ14:AZ17)+1</f>
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="BB18" s="126">
         <f>MAX(BB14:BB17)-MIN(BB14:BB17)+1</f>
@@ -43871,9 +43903,9 @@
       </c>
       <c r="BH18" s="126">
         <f>MAX(BH14:BH17)+1</f>
-        <v>1</v>
-      </c>
-      <c r="BK18" s="163">
+        <v>102</v>
+      </c>
+      <c r="BK18" s="173">
         <v>73</v>
       </c>
       <c r="BL18" s="24" t="str">
@@ -43977,7 +44009,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK19" s="164"/>
+      <c r="BK19" s="174"/>
       <c r="BL19" s="26" t="str">
         <f>AS15</f>
         <v>2B</v>
@@ -44122,7 +44154,7 @@
       </c>
       <c r="AD20" s="123">
         <f>COUNTIF(AR20:AR23,CONCATENATE("&gt;=",AR20))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE20" s="124" t="str">
         <f>VLOOKUP("Brazil",T,lang,FALSE)</f>
@@ -44134,7 +44166,7 @@
       </c>
       <c r="AG20" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE20 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH20" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE20 &amp; "_lose")</f>
@@ -44142,11 +44174,11 @@
       </c>
       <c r="AI20" s="123">
         <f>SUMIF($E$7:$E$78,$AE20,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE20,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ20" s="123">
         <f>SUMIF($E$7:$E$78,$AE20,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE20,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL20" s="123">
         <f>AI20-AJ20</f>
@@ -44154,19 +44186,19 @@
       </c>
       <c r="AM20" s="123">
         <f>AL20-AL24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN20" s="123">
         <f>AF20*3+AG20</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO20" s="123">
         <f>AN20/AN24*10+BA20</f>
-        <v>0</v>
+        <v>3.4805825242718447</v>
       </c>
       <c r="AP20" s="123">
         <f>AO20*10000000+BI20*100+AM20/AM24*10+AI20/AI24*1++IF(AQ20=0,ROW(),AQ20)/2000000</f>
-        <v>8.8058000000000006E-4</v>
+        <v>34805927.13518478</v>
       </c>
       <c r="AQ20" s="126">
         <f>VLOOKUP(AE20,db_fifarank,2,FALSE)</f>
@@ -44174,7 +44206,7 @@
       </c>
       <c r="AR20" s="125">
         <f>AP20/AP24</f>
-        <v>8.7980526108319542E-4</v>
+        <v>0.46407897793145042</v>
       </c>
       <c r="AS20" s="125" t="str">
         <f>IF(SUM(AF20:AH23)=12,J21,"1C")</f>
@@ -44186,15 +44218,15 @@
       </c>
       <c r="AU20" s="126" cm="1">
         <f t="array" ref="AU20">SUMPRODUCT(($S$7:$S$78=AE20&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE20&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV20" s="126" cm="1">
         <f t="array" ref="AV20">SUMPRODUCT(($E$7:$E$78=AE20)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE20)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW20" s="126" cm="1">
         <f t="array" ref="AW20">SUMPRODUCT(($E$7:$E$78=AE20)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE20)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX20" s="126">
         <f>AV20-AW20</f>
@@ -44206,11 +44238,11 @@
       </c>
       <c r="AZ20" s="126">
         <f>AT20/AT24*1000+AU20/AU24*100+AY20/AY24*10+AV20/AV24</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BA20" s="126">
         <f>AZ20/AZ24</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BB20" s="126" cm="1">
         <f t="array" ref="BB20">SUMPRODUCT(($S$7:$S$78=AE20&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE20&amp;"_win")*($X$7:$X$78))</f>
@@ -44218,15 +44250,15 @@
       </c>
       <c r="BC20" s="126" cm="1">
         <f t="array" ref="BC20">SUMPRODUCT(($S$7:$S$78=AE20&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE20&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD20" s="126" cm="1">
         <f t="array" ref="BD20">SUMPRODUCT(($E$7:$E$78=AE20)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE20)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE20" s="126" cm="1">
         <f t="array" ref="BE20">SUMPRODUCT(($E$7:$E$78=AE20)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE20)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF20" s="126">
         <f>BD20-BE20</f>
@@ -44238,11 +44270,11 @@
       </c>
       <c r="BH20" s="126">
         <f>BB20/BB24*1000+BC20/BC24*100+BG20/BG24*10+BD20/BD24</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BI20" s="126">
         <f>BH20/BH24</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BK20" s="21"/>
       <c r="BL20" s="21"/>
@@ -44251,7 +44283,7 @@
       <c r="BO20" s="21"/>
       <c r="BP20" s="114"/>
       <c r="BQ20" s="112"/>
-      <c r="BR20" s="163">
+      <c r="BR20" s="173">
         <v>90</v>
       </c>
       <c r="BS20" s="24" t="str">
@@ -44313,15 +44345,15 @@
       </c>
       <c r="J21" s="30" t="str">
         <f>VLOOKUP(1,AD20:AN23,2,FALSE)</f>
-        <v>Brazil</v>
+        <v>Scotland</v>
       </c>
       <c r="K21" s="31">
         <f>L21+M21+N21</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="31">
         <f>VLOOKUP(1,AD20:AN23,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="31">
         <f>VLOOKUP(1,AD20:AN23,4,FALSE)</f>
@@ -44333,11 +44365,11 @@
       </c>
       <c r="O21" s="31" t="str">
         <f>VLOOKUP(1,AD20:AN23,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD20:AN23,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 0</v>
       </c>
       <c r="P21" s="32">
         <f>L21*3+M21</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R21" s="123">
         <f>DATE(2026,6,15)+TIME(14,0,0)+gmt_delta</f>
@@ -44385,7 +44417,7 @@
       </c>
       <c r="AD21" s="123">
         <f>COUNTIF(AR20:AR23,CONCATENATE("&gt;=",AR21))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE21" s="124" t="str">
         <f>VLOOKUP("Morocco",T,lang,FALSE)</f>
@@ -44397,7 +44429,7 @@
       </c>
       <c r="AG21" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE21 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH21" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE21 &amp; "_lose")</f>
@@ -44405,11 +44437,11 @@
       </c>
       <c r="AI21" s="123">
         <f>SUMIF($E$7:$E$78,$AE21,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE21,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ21" s="123">
         <f>SUMIF($E$7:$E$78,$AE21,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE21,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL21" s="123">
         <f>AI21-AJ21</f>
@@ -44417,19 +44449,19 @@
       </c>
       <c r="AM21" s="123">
         <f>AL21-AL24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN21" s="123">
         <f>AF21*3+AG21</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO21" s="123">
         <f>AN21/AN24*10+BA21</f>
-        <v>0</v>
+        <v>3.4805825242718447</v>
       </c>
       <c r="AP21" s="123">
         <f>AO21*10000000+BI21*100+AM21/AM24*10+AI21/AI24*1++IF(AQ21=0,ROW(),AQ21)/2000000</f>
-        <v>8.7793499999999994E-4</v>
+        <v>34805927.135182135</v>
       </c>
       <c r="AQ21" s="126">
         <f>VLOOKUP(AE21,db_fifarank,2,FALSE)</f>
@@ -44437,7 +44469,7 @@
       </c>
       <c r="AR21" s="125">
         <f>AP21/AP24</f>
-        <v>8.771625881681108E-4</v>
+        <v>0.46407897793141517</v>
       </c>
       <c r="AS21" s="125" t="str">
         <f>IF(SUM(AF20:AH23)=12,J22,"2C")</f>
@@ -44449,15 +44481,15 @@
       </c>
       <c r="AU21" s="126" cm="1">
         <f t="array" ref="AU21">SUMPRODUCT(($S$7:$S$78=AE21&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE21&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV21" s="126" cm="1">
         <f t="array" ref="AV21">SUMPRODUCT(($E$7:$E$78=AE21)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE21)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW21" s="126" cm="1">
         <f t="array" ref="AW21">SUMPRODUCT(($E$7:$E$78=AE21)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE21)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX21" s="126">
         <f>AV21-AW21</f>
@@ -44469,11 +44501,11 @@
       </c>
       <c r="AZ21" s="126">
         <f>AT21/AT24*1000+AU21/AU24*100+AY21/AY24*10+AV21/AV24</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BA21" s="126">
         <f>AZ21/AZ24</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BB21" s="126" cm="1">
         <f t="array" ref="BB21">SUMPRODUCT(($S$7:$S$78=AE21&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE21&amp;"_win")*($X$7:$X$78))</f>
@@ -44481,15 +44513,15 @@
       </c>
       <c r="BC21" s="126" cm="1">
         <f t="array" ref="BC21">SUMPRODUCT(($S$7:$S$78=AE21&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE21&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD21" s="126" cm="1">
         <f t="array" ref="BD21">SUMPRODUCT(($E$7:$E$78=AE21)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE21)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE21" s="126" cm="1">
         <f t="array" ref="BE21">SUMPRODUCT(($E$7:$E$78=AE21)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE21)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF21" s="126">
         <f>BD21-BE21</f>
@@ -44501,11 +44533,11 @@
       </c>
       <c r="BH21" s="126">
         <f>BB21/BB24*1000+BC21/BC24*100+BG21/BG24*10+BD21/BD24</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BI21" s="126">
         <f>BH21/BH24</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BK21" s="21" t="str" cm="1">
         <f t="array" ref="BK21">INDEX(T,24+MONTH(BP21),lang) &amp; " " &amp; DAY(BP21) &amp; ", " &amp; YEAR(BP21) &amp; "   " &amp; (IF(HOUR(BP21)&lt;10,0,"")&amp;HOUR(BP21)) &amp; ":" &amp;  (IF(MINUTE(BP21)&lt;10,0,"")&amp;MINUTE(BP21))</f>
@@ -44520,7 +44552,7 @@
         <v>46203.041666666672</v>
       </c>
       <c r="BQ21" s="115"/>
-      <c r="BR21" s="164"/>
+      <c r="BR21" s="174"/>
       <c r="BS21" s="26" t="str">
         <f>IF(BP22&gt;BP23,BL22,IF(BP22&lt;BP23,BL23,""))</f>
         <v/>
@@ -44580,11 +44612,11 @@
       </c>
       <c r="J22" s="33" t="str">
         <f>VLOOKUP(2,AD20:AN23,2,FALSE)</f>
-        <v>Morocco</v>
+        <v>Brazil</v>
       </c>
       <c r="K22" s="23">
         <f>L22+M22+N22</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="23">
         <f>VLOOKUP(2,AD20:AN23,3,FALSE)</f>
@@ -44592,7 +44624,7 @@
       </c>
       <c r="M22" s="23">
         <f>VLOOKUP(2,AD20:AN23,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" s="23">
         <f>VLOOKUP(2,AD20:AN23,5,FALSE)</f>
@@ -44600,11 +44632,11 @@
       </c>
       <c r="O22" s="23" t="str">
         <f>VLOOKUP(2,AD20:AN23,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD20:AN23,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 1</v>
       </c>
       <c r="P22" s="34">
         <f>L22*3+M22</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" s="123">
         <f>DATE(2026,6,15)+TIME(8,0,0)+gmt_delta</f>
@@ -44668,7 +44700,7 @@
       </c>
       <c r="AH22" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE22 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI22" s="123">
         <f>SUMIF($E$7:$E$78,$AE22,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE22,$G$7:$G$78)</f>
@@ -44676,11 +44708,11 @@
       </c>
       <c r="AJ22" s="123">
         <f>SUMIF($E$7:$E$78,$AE22,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE22,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL22" s="123">
         <f>AI22-AJ22</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM22" s="123">
         <f>AL22-AL24</f>
@@ -44704,7 +44736,7 @@
       </c>
       <c r="AR22" s="125">
         <f>AP22/AP24</f>
-        <v>6.4528677337310309E-4</v>
+        <v>8.6113990622283044E-12</v>
       </c>
       <c r="AT22" s="126" cm="1">
         <f t="array" ref="AT22">SUMPRODUCT(($S$7:$S$78=AE22&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE22&amp;"_win")*($U$7:$U$78))</f>
@@ -44770,7 +44802,7 @@
         <f>BH22/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK22" s="163">
+      <c r="BK22" s="173">
         <v>75</v>
       </c>
       <c r="BL22" s="24" t="str">
@@ -44840,11 +44872,11 @@
       </c>
       <c r="J23" s="33" t="str">
         <f>VLOOKUP(3,AD20:AN23,2,FALSE)</f>
-        <v>Scotland</v>
+        <v>Morocco</v>
       </c>
       <c r="K23" s="23">
         <f>L23+M23+N23</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="23">
         <f>VLOOKUP(3,AD20:AN23,3,FALSE)</f>
@@ -44852,7 +44884,7 @@
       </c>
       <c r="M23" s="23">
         <f>VLOOKUP(3,AD20:AN23,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" s="23">
         <f>VLOOKUP(3,AD20:AN23,5,FALSE)</f>
@@ -44860,11 +44892,11 @@
       </c>
       <c r="O23" s="23" t="str">
         <f>VLOOKUP(3,AD20:AN23,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD20:AN23,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 1</v>
       </c>
       <c r="P23" s="34">
         <f>L23*3+M23</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" s="123">
         <f>DATE(2026,6,16)+TIME(8,0,0)+gmt_delta</f>
@@ -44912,7 +44944,7 @@
       </c>
       <c r="AD23" s="123">
         <f>COUNTIF(AR20:AR23,CONCATENATE("&gt;=",AR23))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE23" s="124" t="str">
         <f>VLOOKUP("Scotland",T,lang,FALSE)</f>
@@ -44920,7 +44952,7 @@
       </c>
       <c r="AF23" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE23 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG23" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE23 &amp; "_draw")</f>
@@ -44932,7 +44964,7 @@
       </c>
       <c r="AI23" s="123">
         <f>SUMIF($E$7:$E$78,$AE23,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE23,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ23" s="123">
         <f>SUMIF($E$7:$E$78,$AE23,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE23,$F$7:$F$78)</f>
@@ -44940,23 +44972,23 @@
       </c>
       <c r="AL23" s="123">
         <f>AI23-AJ23</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM23" s="123">
         <f>AL23-AL24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN23" s="123">
         <f>AF23*3+AG23</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO23" s="123">
         <f>AN23/AN24*10+BA23</f>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AP23" s="123">
         <f>AO23*10000000+BI23*100+AM23/AM24*10+AI23/AI24*1++IF(AQ23=0,ROW(),AQ23)/2000000</f>
-        <v>7.4917499999999993E-4</v>
+        <v>75000007.167415842</v>
       </c>
       <c r="AQ23" s="126">
         <f>VLOOKUP(AE23,db_fifarank,2,FALSE)</f>
@@ -44964,7 +44996,7 @@
       </c>
       <c r="AR23" s="125">
         <f>AP23/AP24</f>
-        <v>7.4851587189352792E-4</v>
+        <v>0.99999998666666812</v>
       </c>
       <c r="AT23" s="126" cm="1">
         <f t="array" ref="AT23">SUMPRODUCT(($S$7:$S$78=AE23&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE23&amp;"_win")*($U$7:$U$78))</f>
@@ -45030,7 +45062,7 @@
         <f>BH23/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK23" s="164"/>
+      <c r="BK23" s="174"/>
       <c r="BL23" s="26" t="str">
         <f>AS21</f>
         <v>2C</v>
@@ -45057,7 +45089,7 @@
       <c r="CC23" s="21"/>
       <c r="CD23" s="114"/>
       <c r="CE23" s="112"/>
-      <c r="CF23" s="163">
+      <c r="CF23" s="173">
         <v>101</v>
       </c>
       <c r="CG23" s="24" t="str">
@@ -45104,7 +45136,7 @@
       </c>
       <c r="K24" s="36">
         <f>L24+M24+N24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="36">
         <f>VLOOKUP(4,AD20:AN23,3,FALSE)</f>
@@ -45116,11 +45148,11 @@
       </c>
       <c r="N24" s="36">
         <f>VLOOKUP(4,AD20:AN23,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24" s="36" t="str">
         <f>VLOOKUP(4,AD20:AN23,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD20:AN23,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>0 - 1</v>
       </c>
       <c r="P24" s="37">
         <f>L24*3+M24</f>
@@ -45172,39 +45204,39 @@
       </c>
       <c r="AF24" s="123">
         <f t="shared" ref="AF24:AH24" si="14">MAX(AF20:AF23)-MIN(AF20:AF23)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG24" s="123">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH24" s="123">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI24" s="123">
         <f>MAX(AI20:AI23)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL24" s="123">
         <f>MIN(AL20:AL23)</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM24" s="123">
         <f>MAX(AM20:AM23)+1</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AN24" s="123">
         <f>MAX(AN20:AN23)+1</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AO24" s="123">
         <f>MAX(AO20:AO23)+1</f>
-        <v>1</v>
+        <v>8.5</v>
       </c>
       <c r="AP24" s="123">
         <f>MAX(AP20:AP23)+1</f>
-        <v>1.00088058</v>
+        <v>75000008.167415842</v>
       </c>
       <c r="AT24" s="126">
         <f>MAX(AT20:AT23)-MIN(AT20:AT23)+1</f>
@@ -45212,15 +45244,15 @@
       </c>
       <c r="AU24" s="126">
         <f>MAX(AU20:AU23)-MIN(AU20:AU23)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV24" s="126">
         <f>MAX(AV20:AV23)-MIN(AV20:AV23)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW24" s="126">
         <f>MAX(AW20:AW23)-MIN(AW20:AW23)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY24" s="126">
         <f>MAX(AY20:AY23)-MIN(AY20:AY23)+1</f>
@@ -45228,7 +45260,7 @@
       </c>
       <c r="AZ24" s="126">
         <f>MAX(AZ20:AZ23)+1</f>
-        <v>1</v>
+        <v>51.5</v>
       </c>
       <c r="BB24" s="126">
         <f>MAX(BB20:BB23)-MIN(BB20:BB23)+1</f>
@@ -45236,15 +45268,15 @@
       </c>
       <c r="BC24" s="126">
         <f>MAX(BC20:BC23)-MIN(BC20:BC23)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD24" s="126">
         <f>MAX(BD20:BD23)-MIN(BD20:BD23)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BE24" s="126">
         <f>MAX(BE20:BE23)-MIN(BE20:BE23)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BG24" s="126">
         <f>MAX(BG20:BG23)-MIN(BG20:BG23)+1</f>
@@ -45252,7 +45284,7 @@
       </c>
       <c r="BH24" s="126">
         <f>MAX(BH20:BH23)+1</f>
-        <v>1</v>
+        <v>51.5</v>
       </c>
       <c r="BL24" s="21"/>
       <c r="BM24" s="21"/>
@@ -45274,7 +45306,7 @@
       <c r="CC24" s="21"/>
       <c r="CD24" s="114"/>
       <c r="CE24" s="115"/>
-      <c r="CF24" s="164"/>
+      <c r="CF24" s="174"/>
       <c r="CG24" s="26" t="str">
         <f>IF(CD32&gt;CD33,BZ32,IF(CD32&lt;CD33,BZ33,""))</f>
         <v/>
@@ -45505,7 +45537,7 @@
       </c>
       <c r="AF26" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE26 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG26" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE26 &amp; "_draw")</f>
@@ -45517,31 +45549,31 @@
       </c>
       <c r="AI26" s="123">
         <f>SUMIF($E$7:$E$78,$AE26,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE26,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ26" s="123">
         <f>SUMIF($E$7:$E$78,$AE26,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE26,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL26" s="123">
         <f>AI26-AJ26</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AM26" s="123">
         <f>AL26-AL30</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AN26" s="123">
         <f>AF26*3+AG26</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO26" s="123">
         <f>AN26/AN30*10+BA26</f>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AP26" s="123">
         <f>AO26*10000000+BI26*100+AM26/AM30*10+AI26/AI30*1++IF(AQ26=0,ROW(),AQ26)/2000000</f>
-        <v>8.3656500000000005E-4</v>
+        <v>75000009.37226513</v>
       </c>
       <c r="AQ26" s="126">
         <f>VLOOKUP(AE26,db_fifarank,2,FALSE)</f>
@@ -45549,7 +45581,7 @@
       </c>
       <c r="AR26" s="125">
         <f>AP26/AP30</f>
-        <v>8.3586574397389256E-4</v>
+        <v>0.99999998666666856</v>
       </c>
       <c r="AS26" s="125" t="str">
         <f>IF(SUM(AF26:AH29)=12,J27,"1D")</f>
@@ -45619,7 +45651,7 @@
         <f>BH26/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK26" s="163">
+      <c r="BK26" s="173">
         <v>83</v>
       </c>
       <c r="BL26" s="24" t="str">
@@ -45693,11 +45725,11 @@
       </c>
       <c r="K27" s="31">
         <f>L27+M27+N27</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="31">
         <f>VLOOKUP(1,AD26:AN29,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" s="31">
         <f>VLOOKUP(1,AD26:AN29,4,FALSE)</f>
@@ -45709,11 +45741,11 @@
       </c>
       <c r="O27" s="31" t="str">
         <f>VLOOKUP(1,AD26:AN29,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD26:AN29,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>4 - 1</v>
       </c>
       <c r="P27" s="32">
         <f>L27*3+M27</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R27" s="123">
         <f>DATE(2026,6,17)+TIME(12,0,0)+gmt_delta</f>
@@ -45777,19 +45809,19 @@
       </c>
       <c r="AH27" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE27 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI27" s="123">
         <f>SUMIF($E$7:$E$78,$AE27,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE27,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ27" s="123">
         <f>SUMIF($E$7:$E$78,$AE27,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE27,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL27" s="123">
         <f>AI27-AJ27</f>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AM27" s="123">
         <f>AL27-AL30</f>
@@ -45805,7 +45837,7 @@
       </c>
       <c r="AP27" s="123">
         <f>AO27*10000000+BI27*100+AM27/AM30*10+AI27/AI30*1++IF(AQ27=0,ROW(),AQ27)/2000000</f>
-        <v>7.5175000000000003E-4</v>
+        <v>0.20075175000000001</v>
       </c>
       <c r="AQ27" s="126">
         <f>VLOOKUP(AE27,db_fifarank,2,FALSE)</f>
@@ -45813,7 +45845,7 @@
       </c>
       <c r="AR27" s="125">
         <f>AP27/AP30</f>
-        <v>7.5112163792696765E-4</v>
+        <v>2.6766896298222066E-9</v>
       </c>
       <c r="AS27" s="125" t="str">
         <f>IF(SUM(AF26:AH29)=12,J28,"2D")</f>
@@ -45883,7 +45915,7 @@
         <f>BH27/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK27" s="164"/>
+      <c r="BK27" s="174"/>
       <c r="BL27" s="26" t="str">
         <f>AS75</f>
         <v>2L</v>
@@ -45957,15 +45989,15 @@
       </c>
       <c r="J28" s="33" t="str">
         <f>VLOOKUP(2,AD26:AN29,2,FALSE)</f>
-        <v>Turkey</v>
+        <v>Australia</v>
       </c>
       <c r="K28" s="23">
         <f>L28+M28+N28</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="23">
         <f>VLOOKUP(2,AD26:AN29,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="23">
         <f>VLOOKUP(2,AD26:AN29,4,FALSE)</f>
@@ -45977,11 +46009,11 @@
       </c>
       <c r="O28" s="23" t="str">
         <f>VLOOKUP(2,AD26:AN29,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD26:AN29,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>2 - 0</v>
       </c>
       <c r="P28" s="34">
         <f>L28*3+M28</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R28" s="123">
         <f>DATE(2026,6,17)+TIME(9,0,0)+gmt_delta</f>
@@ -46029,7 +46061,7 @@
       </c>
       <c r="AD28" s="123">
         <f>COUNTIF(AR26:AR29,CONCATENATE("&gt;=",AR28))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE28" s="124" t="str">
         <f>VLOOKUP("Australia",T,lang,FALSE)</f>
@@ -46037,7 +46069,7 @@
       </c>
       <c r="AF28" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE28 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG28" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE28 &amp; "_draw")</f>
@@ -46049,7 +46081,7 @@
       </c>
       <c r="AI28" s="123">
         <f>SUMIF($E$7:$E$78,$AE28,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE28,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ28" s="123">
         <f>SUMIF($E$7:$E$78,$AE28,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE28,$F$7:$F$78)</f>
@@ -46057,23 +46089,23 @@
       </c>
       <c r="AL28" s="123">
         <f>AI28-AJ28</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM28" s="123">
         <f>AL28-AL30</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AN28" s="123">
         <f>AF28*3+AG28</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO28" s="123">
         <f>AN28/AN30*10+BA28</f>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AP28" s="123">
         <f>AO28*10000000+BI28*100+AM28/AM30*10+AI28/AI30*1++IF(AQ28=0,ROW(),AQ28)/2000000</f>
-        <v>7.9033500000000008E-4</v>
+        <v>75000007.543647483</v>
       </c>
       <c r="AQ28" s="126">
         <f>VLOOKUP(AE28,db_fifarank,2,FALSE)</f>
@@ -46081,7 +46113,7 @@
       </c>
       <c r="AR28" s="125">
         <f>AP28/AP30</f>
-        <v>7.8967438604723647E-4</v>
+        <v>0.99999996228510324</v>
       </c>
       <c r="AT28" s="126" cm="1">
         <f t="array" ref="AT28">SUMPRODUCT(($S$7:$S$78=AE28&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE28&amp;"_win")*($U$7:$U$78))</f>
@@ -46154,7 +46186,7 @@
       <c r="BO28" s="21"/>
       <c r="BP28" s="114"/>
       <c r="BQ28" s="112"/>
-      <c r="BR28" s="163">
+      <c r="BR28" s="173">
         <v>93</v>
       </c>
       <c r="BS28" s="24" t="str">
@@ -46212,11 +46244,11 @@
       </c>
       <c r="J29" s="33" t="str">
         <f>VLOOKUP(3,AD26:AN29,2,FALSE)</f>
-        <v>Australia</v>
+        <v>Turkey</v>
       </c>
       <c r="K29" s="23">
         <f>L29+M29+N29</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="23">
         <f>VLOOKUP(3,AD26:AN29,3,FALSE)</f>
@@ -46228,11 +46260,11 @@
       </c>
       <c r="N29" s="23">
         <f>VLOOKUP(3,AD26:AN29,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O29" s="23" t="str">
         <f>VLOOKUP(3,AD26:AN29,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD26:AN29,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>0 - 2</v>
       </c>
       <c r="P29" s="34">
         <f>L29*3+M29</f>
@@ -46284,7 +46316,7 @@
       </c>
       <c r="AD29" s="123">
         <f>COUNTIF(AR26:AR29,CONCATENATE("&gt;=",AR29))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE29" s="124" t="str">
         <f>VLOOKUP("Turkey",T,lang,FALSE)</f>
@@ -46300,7 +46332,7 @@
       </c>
       <c r="AH29" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE29 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI29" s="123">
         <f>SUMIF($E$7:$E$78,$AE29,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE29,$G$7:$G$78)</f>
@@ -46308,15 +46340,15 @@
       </c>
       <c r="AJ29" s="123">
         <f>SUMIF($E$7:$E$78,$AE29,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE29,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL29" s="123">
         <f>AI29-AJ29</f>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AM29" s="123">
         <f>AL29-AL30</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN29" s="123">
         <f>AF29*3+AG29</f>
@@ -46328,7 +46360,7 @@
       </c>
       <c r="AP29" s="123">
         <f>AO29*10000000+BI29*100+AM29/AM30*10+AI29/AI30*1++IF(AQ29=0,ROW(),AQ29)/2000000</f>
-        <v>7.9951999999999996E-4</v>
+        <v>1.4293709485714283</v>
       </c>
       <c r="AQ29" s="126">
         <f>VLOOKUP(AE29,db_fifarank,2,FALSE)</f>
@@ -46336,7 +46368,7 @@
       </c>
       <c r="AR29" s="125">
         <f>AP29/AP30</f>
-        <v>7.9885170862037803E-4</v>
+        <v>1.9058276678585728E-8</v>
       </c>
       <c r="AT29" s="126" cm="1">
         <f t="array" ref="AT29">SUMPRODUCT(($S$7:$S$78=AE29&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE29&amp;"_win")*($U$7:$U$78))</f>
@@ -46415,7 +46447,7 @@
         <v>46205.791666666672</v>
       </c>
       <c r="BQ29" s="115"/>
-      <c r="BR29" s="164"/>
+      <c r="BR29" s="174"/>
       <c r="BS29" s="26" t="str">
         <f>IF(BP30&gt;BP31,BL30,IF(BP30&lt;BP31,BL31,""))</f>
         <v/>
@@ -46475,7 +46507,7 @@
       </c>
       <c r="K30" s="36">
         <f>L30+M30+N30</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="36">
         <f>VLOOKUP(4,AD26:AN29,3,FALSE)</f>
@@ -46487,11 +46519,11 @@
       </c>
       <c r="N30" s="36">
         <f>VLOOKUP(4,AD26:AN29,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O30" s="36" t="str">
         <f>VLOOKUP(4,AD26:AN29,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD26:AN29,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 4</v>
       </c>
       <c r="P30" s="37">
         <f>L30*3+M30</f>
@@ -46543,7 +46575,7 @@
       </c>
       <c r="AF30" s="123">
         <f t="shared" ref="AF30:AH30" si="15">MAX(AF26:AF29)-MIN(AF26:AF29)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG30" s="123">
         <f t="shared" si="15"/>
@@ -46551,31 +46583,31 @@
       </c>
       <c r="AH30" s="123">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI30" s="123">
         <f>MAX(AI26:AI29)+1</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AL30" s="123">
         <f>MIN(AL26:AL29)</f>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AM30" s="123">
         <f>MAX(AM26:AM29)+1</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AN30" s="123">
         <f>MAX(AN26:AN29)+1</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AO30" s="123">
         <f>MAX(AO26:AO29)+1</f>
-        <v>1</v>
+        <v>8.5</v>
       </c>
       <c r="AP30" s="123">
         <f>MAX(AP26:AP29)+1</f>
-        <v>1.000836565</v>
+        <v>75000010.37226513</v>
       </c>
       <c r="AT30" s="126">
         <f>MAX(AT26:AT29)-MIN(AT26:AT29)+1</f>
@@ -46625,7 +46657,7 @@
         <f>MAX(BH26:BH29)+1</f>
         <v>1</v>
       </c>
-      <c r="BK30" s="163">
+      <c r="BK30" s="173">
         <v>84</v>
       </c>
       <c r="BL30" s="24" t="str">
@@ -46732,7 +46764,7 @@
         <f>IF(OR(F31="",G31=""),"",IF(F31&gt;G31,1,IF(F31&lt;G31,-1,0)))</f>
         <v/>
       </c>
-      <c r="BK31" s="164"/>
+      <c r="BK31" s="174"/>
       <c r="BL31" s="26" t="str">
         <f>AS63</f>
         <v>2J</v>
@@ -46876,7 +46908,7 @@
       </c>
       <c r="AF32" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE32 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG32" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE32 &amp; "_draw")</f>
@@ -46888,31 +46920,31 @@
       </c>
       <c r="AI32" s="123">
         <f>SUMIF($E$7:$E$78,$AE32,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE32,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ32" s="123">
         <f>SUMIF($E$7:$E$78,$AE32,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE32,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL32" s="123">
         <f>AI32-AJ32</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AM32" s="123">
         <f>AL32-AL36</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AN32" s="123">
         <f>AF32*3+AG32</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO32" s="123">
         <f>AN32/AN36*10+BA32</f>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AP32" s="123">
         <f>AO32*10000000+BI32*100+AM32/AM36*10+AI32/AI36*1++IF(AQ32=0,ROW(),AQ32)/2000000</f>
-        <v>8.6518499999999998E-4</v>
+        <v>75000010.106634423</v>
       </c>
       <c r="AQ32" s="126">
         <f>VLOOKUP(AE32,db_fifarank,2,FALSE)</f>
@@ -46920,7 +46952,7 @@
       </c>
       <c r="AR32" s="125">
         <f>AP32/AP36</f>
-        <v>8.6443710198591821E-4</v>
+        <v>0.99999998666666867</v>
       </c>
       <c r="AS32" s="125" t="str">
         <f>IF(SUM(AF32:AH35)=12,J33,"1E")</f>
@@ -47004,7 +47036,7 @@
       <c r="BV32" s="21"/>
       <c r="BW32" s="114"/>
       <c r="BX32" s="112"/>
-      <c r="BY32" s="163">
+      <c r="BY32" s="173">
         <v>98</v>
       </c>
       <c r="BZ32" s="24" t="str">
@@ -47054,11 +47086,11 @@
       </c>
       <c r="K33" s="31">
         <f>L33+M33+N33</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="31">
         <f>VLOOKUP(1,AD32:AN35,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" s="31">
         <f>VLOOKUP(1,AD32:AN35,4,FALSE)</f>
@@ -47070,11 +47102,11 @@
       </c>
       <c r="O33" s="31" t="str">
         <f>VLOOKUP(1,AD32:AN35,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD32:AN35,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>7 - 1</v>
       </c>
       <c r="P33" s="32">
         <f>L33*3+M33</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R33" s="123">
         <f>DATE(2026,6,18)+TIME(11,0,0)+gmt_delta</f>
@@ -47138,19 +47170,19 @@
       </c>
       <c r="AH33" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE33 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI33" s="123">
         <f>SUMIF($E$7:$E$78,$AE33,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE33,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ33" s="123">
         <f>SUMIF($E$7:$E$78,$AE33,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE33,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AL33" s="123">
         <f>AI33-AJ33</f>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AM33" s="123">
         <f>AL33-AL36</f>
@@ -47166,7 +47198,7 @@
       </c>
       <c r="AP33" s="123">
         <f>AO33*10000000+BI33*100+AM33/AM36*10+AI33/AI36*1++IF(AQ33=0,ROW(),AQ33)/2000000</f>
-        <v>6.4732500000000003E-4</v>
+        <v>0.125647325</v>
       </c>
       <c r="AQ33" s="126">
         <f>VLOOKUP(AE33,db_fifarank,2,FALSE)</f>
@@ -47174,7 +47206,7 @@
       </c>
       <c r="AR33" s="125">
         <f>AP33/AP36</f>
-        <v>6.4676542825295696E-4</v>
+        <v>1.6752974185744538E-9</v>
       </c>
       <c r="AS33" s="125" t="str">
         <f>IF(SUM(AF32:AH35)=12,J34,"2E")</f>
@@ -47264,7 +47296,7 @@
       <c r="BV33" s="21"/>
       <c r="BW33" s="114"/>
       <c r="BX33" s="115"/>
-      <c r="BY33" s="164"/>
+      <c r="BY33" s="174"/>
       <c r="BZ33" s="26" t="str">
         <f>IF(BW36&gt;BW37,BS36,IF(BW36&lt;BW37,BS37,""))</f>
         <v/>
@@ -47279,14 +47311,14 @@
       <c r="CE33" s="112"/>
       <c r="CK33" s="114"/>
       <c r="CL33" s="112"/>
-      <c r="CM33" s="165" t="str" cm="1">
+      <c r="CM33" s="176" t="str" cm="1">
         <f t="array" ref="CM33">INDEX(T,8,lang)</f>
         <v>Final</v>
       </c>
-      <c r="CN33" s="166"/>
-      <c r="CO33" s="166"/>
-      <c r="CP33" s="166"/>
-      <c r="CQ33" s="167"/>
+      <c r="CN33" s="177"/>
+      <c r="CO33" s="177"/>
+      <c r="CP33" s="177"/>
+      <c r="CQ33" s="178"/>
     </row>
     <row r="34" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A34" s="16">
@@ -47420,7 +47452,7 @@
       </c>
       <c r="AM34" s="123">
         <f>AL34-AL36</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AN34" s="123">
         <f>AF34*3+AG34</f>
@@ -47432,7 +47464,7 @@
       </c>
       <c r="AP34" s="123">
         <f>AO34*10000000+BI34*100+AM34/AM36*10+AI34/AI36*1++IF(AQ34=0,ROW(),AQ34)/2000000</f>
-        <v>7.6648999999999999E-4</v>
+        <v>4.616151105384616</v>
       </c>
       <c r="AQ34" s="126">
         <f>VLOOKUP(AE34,db_fifarank,2,FALSE)</f>
@@ -47440,7 +47472,7 @@
       </c>
       <c r="AR34" s="125">
         <f>AP34/AP36</f>
-        <v>7.6582741760569868E-4</v>
+        <v>6.1548672290480187E-8</v>
       </c>
       <c r="AT34" s="126" cm="1">
         <f t="array" ref="AT34">SUMPRODUCT(($S$7:$S$78=AE34&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE34&amp;"_win")*($U$7:$U$78))</f>
@@ -47506,7 +47538,7 @@
         <f>BH34/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK34" s="163">
+      <c r="BK34" s="173">
         <v>81</v>
       </c>
       <c r="BL34" s="24" t="str">
@@ -47537,11 +47569,11 @@
       <c r="CE34" s="112"/>
       <c r="CK34" s="114"/>
       <c r="CL34" s="112"/>
-      <c r="CM34" s="168"/>
-      <c r="CN34" s="169"/>
-      <c r="CO34" s="169"/>
-      <c r="CP34" s="169"/>
-      <c r="CQ34" s="170"/>
+      <c r="CM34" s="179"/>
+      <c r="CN34" s="180"/>
+      <c r="CO34" s="180"/>
+      <c r="CP34" s="180"/>
+      <c r="CQ34" s="181"/>
     </row>
     <row r="35" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A35" s="16">
@@ -47675,7 +47707,7 @@
       </c>
       <c r="AM35" s="123">
         <f>AL35-AL36</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AN35" s="123">
         <f>AF35*3+AG35</f>
@@ -47687,7 +47719,7 @@
       </c>
       <c r="AP35" s="123">
         <f>AO35*10000000+BI35*100+AM35/AM36*10+AI35/AI36*1++IF(AQ35=0,ROW(),AQ35)/2000000</f>
-        <v>7.9739000000000003E-4</v>
+        <v>4.6161820053846156</v>
       </c>
       <c r="AQ35" s="126">
         <f>VLOOKUP(AE35,db_fifarank,2,FALSE)</f>
@@ -47695,7 +47727,7 @@
       </c>
       <c r="AR35" s="125">
         <f>AP35/AP36</f>
-        <v>7.9670070649924736E-4</v>
+        <v>6.154908429041916E-8</v>
       </c>
       <c r="AT35" s="126" cm="1">
         <f t="array" ref="AT35">SUMPRODUCT(($S$7:$S$78=AE35&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE35&amp;"_win")*($U$7:$U$78))</f>
@@ -47761,7 +47793,7 @@
         <f>BH35/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK35" s="164"/>
+      <c r="BK35" s="174"/>
       <c r="BL35" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!F3,AK80:AS91,9,FALSE),"3rd Group B/E/F/I/J")</f>
         <v>3rd Group B/E/F/I/J</v>
@@ -47829,7 +47861,7 @@
       </c>
       <c r="K36" s="36">
         <f>L36+M36+N36</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="36">
         <f>VLOOKUP(4,AD32:AN35,3,FALSE)</f>
@@ -47841,11 +47873,11 @@
       </c>
       <c r="N36" s="36">
         <f>VLOOKUP(4,AD32:AN35,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O36" s="36" t="str">
         <f>VLOOKUP(4,AD32:AN35,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD32:AN35,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 7</v>
       </c>
       <c r="P36" s="37">
         <f>L36*3+M36</f>
@@ -47897,7 +47929,7 @@
       </c>
       <c r="AF36" s="123">
         <f t="shared" ref="AF36:AH36" si="16">MAX(AF32:AF35)-MIN(AF32:AF35)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG36" s="123">
         <f t="shared" si="16"/>
@@ -47905,31 +47937,31 @@
       </c>
       <c r="AH36" s="123">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI36" s="123">
         <f>MAX(AI32:AI35)+1</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AL36" s="123">
         <f>MIN(AL32:AL35)</f>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AM36" s="123">
         <f>MAX(AM32:AM35)+1</f>
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="AN36" s="123">
         <f>MAX(AN32:AN35)+1</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AO36" s="123">
         <f>MAX(AO32:AO35)+1</f>
-        <v>1</v>
+        <v>8.5</v>
       </c>
       <c r="AP36" s="123">
         <f>MAX(AP32:AP35)+1</f>
-        <v>1.0008651850000001</v>
+        <v>75000011.106634423</v>
       </c>
       <c r="AT36" s="126">
         <f>MAX(AT32:AT35)-MIN(AT32:AT35)+1</f>
@@ -47986,7 +48018,7 @@
       <c r="BO36" s="21"/>
       <c r="BP36" s="114"/>
       <c r="BQ36" s="112"/>
-      <c r="BR36" s="163">
+      <c r="BR36" s="173">
         <v>94</v>
       </c>
       <c r="BS36" s="24" t="str">
@@ -48106,7 +48138,7 @@
         <v>46204.833333333336</v>
       </c>
       <c r="BQ37" s="115"/>
-      <c r="BR37" s="164"/>
+      <c r="BR37" s="174"/>
       <c r="BS37" s="26" t="str">
         <f>IF(BP38&gt;BP39,BL38,IF(BP38&lt;BP39,BL39,""))</f>
         <v/>
@@ -48133,7 +48165,7 @@
       <c r="CJ37" s="21"/>
       <c r="CK37" s="114"/>
       <c r="CL37" s="112"/>
-      <c r="CM37" s="163">
+      <c r="CM37" s="173">
         <v>104</v>
       </c>
       <c r="CN37" s="24" t="str">
@@ -48260,7 +48292,7 @@
       </c>
       <c r="AG38" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE38 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH38" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE38 &amp; "_lose")</f>
@@ -48268,11 +48300,11 @@
       </c>
       <c r="AI38" s="123">
         <f>SUMIF($E$7:$E$78,$AE38,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE38,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ38" s="123">
         <f>SUMIF($E$7:$E$78,$AE38,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE38,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL38" s="123">
         <f>AI38-AJ38</f>
@@ -48284,15 +48316,15 @@
       </c>
       <c r="AN38" s="123">
         <f>AF38*3+AG38</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO38" s="123">
         <f>AN38/AN42*10+BA38</f>
-        <v>0</v>
+        <v>5.9806451612903224</v>
       </c>
       <c r="AP38" s="123">
         <f>AO38*10000000+BI38*100+AM38/AM42*10+AI38/AI42*1++IF(AQ38=0,ROW(),AQ38)/2000000</f>
-        <v>8.7893499999999996E-4</v>
+        <v>59806550.344964951</v>
       </c>
       <c r="AQ38" s="126">
         <f>VLOOKUP(AE38,db_fifarank,2,FALSE)</f>
@@ -48300,7 +48332,7 @@
       </c>
       <c r="AR38" s="125">
         <f>AP38/AP42</f>
-        <v>8.7816315167028663E-4</v>
+        <v>0.99999998327942374</v>
       </c>
       <c r="AS38" s="125" t="str">
         <f>IF(SUM(AF38:AH41)=12,J39,"1F")</f>
@@ -48312,15 +48344,15 @@
       </c>
       <c r="AU38" s="126" cm="1">
         <f t="array" ref="AU38">SUMPRODUCT(($S$7:$S$78=AE38&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE38&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV38" s="126" cm="1">
         <f t="array" ref="AV38">SUMPRODUCT(($E$7:$E$78=AE38)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE38)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW38" s="126" cm="1">
         <f t="array" ref="AW38">SUMPRODUCT(($E$7:$E$78=AE38)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE38)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX38" s="126">
         <f>AV38-AW38</f>
@@ -48332,11 +48364,11 @@
       </c>
       <c r="AZ38" s="126">
         <f>AT38/AT42*1000+AU38/AU42*100+AY38/AY42*10+AV38/AV42</f>
-        <v>0</v>
+        <v>50.666666666666664</v>
       </c>
       <c r="BA38" s="126">
         <f>AZ38/AZ42</f>
-        <v>0</v>
+        <v>0.98064516129032253</v>
       </c>
       <c r="BB38" s="126" cm="1">
         <f t="array" ref="BB38">SUMPRODUCT(($S$7:$S$78=AE38&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE38&amp;"_win")*($X$7:$X$78))</f>
@@ -48344,15 +48376,15 @@
       </c>
       <c r="BC38" s="126" cm="1">
         <f t="array" ref="BC38">SUMPRODUCT(($S$7:$S$78=AE38&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE38&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD38" s="126" cm="1">
         <f t="array" ref="BD38">SUMPRODUCT(($E$7:$E$78=AE38)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE38)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BE38" s="126" cm="1">
         <f t="array" ref="BE38">SUMPRODUCT(($E$7:$E$78=AE38)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE38)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF38" s="126">
         <f>BD38-BE38</f>
@@ -48364,13 +48396,13 @@
       </c>
       <c r="BH38" s="126">
         <f>BB38/BB42*1000+BC38/BC42*100+BG38/BG42*10+BD38/BD42</f>
-        <v>0</v>
+        <v>50.666666666666664</v>
       </c>
       <c r="BI38" s="126">
         <f>BH38/BH42</f>
-        <v>0</v>
-      </c>
-      <c r="BK38" s="163">
+        <v>0.98064516129032253</v>
+      </c>
+      <c r="BK38" s="173">
         <v>82</v>
       </c>
       <c r="BL38" s="24" t="str">
@@ -48400,7 +48432,7 @@
       <c r="CI38" s="21"/>
       <c r="CJ38" s="21"/>
       <c r="CL38" s="115"/>
-      <c r="CM38" s="164"/>
+      <c r="CM38" s="174"/>
       <c r="CN38" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG55,IF(CK55&lt;CK56,CG56,""))</f>
         <v/>
@@ -48445,7 +48477,7 @@
       </c>
       <c r="K39" s="31">
         <f>L39+M39+N39</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="31">
         <f>VLOOKUP(1,AD38:AN41,3,FALSE)</f>
@@ -48453,7 +48485,7 @@
       </c>
       <c r="M39" s="31">
         <f>VLOOKUP(1,AD38:AN41,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N39" s="31">
         <f>VLOOKUP(1,AD38:AN41,5,FALSE)</f>
@@ -48461,11 +48493,11 @@
       </c>
       <c r="O39" s="31" t="str">
         <f>VLOOKUP(1,AD38:AN41,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD38:AN41,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>2 - 2</v>
       </c>
       <c r="P39" s="32">
         <f>L39*3+M39</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R39" s="123">
         <f>DATE(2026,6,20)+TIME(9,0,0)+gmt_delta</f>
@@ -48525,7 +48557,7 @@
       </c>
       <c r="AG39" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE39 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH39" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE39 &amp; "_lose")</f>
@@ -48533,11 +48565,11 @@
       </c>
       <c r="AI39" s="123">
         <f>SUMIF($E$7:$E$78,$AE39,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE39,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ39" s="123">
         <f>SUMIF($E$7:$E$78,$AE39,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE39,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL39" s="123">
         <f>AI39-AJ39</f>
@@ -48549,15 +48581,15 @@
       </c>
       <c r="AN39" s="123">
         <f>AF39*3+AG39</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO39" s="123">
         <f>AN39/AN42*10+BA39</f>
-        <v>0</v>
+        <v>5.9806451612903224</v>
       </c>
       <c r="AP39" s="123">
         <f>AO39*10000000+BI39*100+AM39/AM42*10+AI39/AI42*1++IF(AQ39=0,ROW(),AQ39)/2000000</f>
-        <v>8.3021500000000003E-4</v>
+        <v>59806550.344916232</v>
       </c>
       <c r="AQ39" s="126">
         <f>VLOOKUP(AE39,db_fifarank,2,FALSE)</f>
@@ -48565,7 +48597,7 @@
       </c>
       <c r="AR39" s="125">
         <f>AP39/AP42</f>
-        <v>8.2948593577903611E-4</v>
+        <v>0.99999998327860917</v>
       </c>
       <c r="AS39" s="125" t="str">
         <f>IF(SUM(AF38:AH41)=12,J40,"2F")</f>
@@ -48577,15 +48609,15 @@
       </c>
       <c r="AU39" s="126" cm="1">
         <f t="array" ref="AU39">SUMPRODUCT(($S$7:$S$78=AE39&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE39&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV39" s="126" cm="1">
         <f t="array" ref="AV39">SUMPRODUCT(($E$7:$E$78=AE39)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE39)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW39" s="126" cm="1">
         <f t="array" ref="AW39">SUMPRODUCT(($E$7:$E$78=AE39)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE39)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX39" s="126">
         <f>AV39-AW39</f>
@@ -48597,11 +48629,11 @@
       </c>
       <c r="AZ39" s="126">
         <f>AT39/AT42*1000+AU39/AU42*100+AY39/AY42*10+AV39/AV42</f>
-        <v>0</v>
+        <v>50.666666666666664</v>
       </c>
       <c r="BA39" s="126">
         <f>AZ39/AZ42</f>
-        <v>0</v>
+        <v>0.98064516129032253</v>
       </c>
       <c r="BB39" s="126" cm="1">
         <f t="array" ref="BB39">SUMPRODUCT(($S$7:$S$78=AE39&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE39&amp;"_win")*($X$7:$X$78))</f>
@@ -48609,15 +48641,15 @@
       </c>
       <c r="BC39" s="126" cm="1">
         <f t="array" ref="BC39">SUMPRODUCT(($S$7:$S$78=AE39&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE39&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD39" s="126" cm="1">
         <f t="array" ref="BD39">SUMPRODUCT(($E$7:$E$78=AE39)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE39)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BE39" s="126" cm="1">
         <f t="array" ref="BE39">SUMPRODUCT(($E$7:$E$78=AE39)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE39)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF39" s="126">
         <f>BD39-BE39</f>
@@ -48629,13 +48661,13 @@
       </c>
       <c r="BH39" s="126">
         <f>BB39/BB42*1000+BC39/BC42*100+BG39/BG42*10+BD39/BD42</f>
-        <v>0</v>
+        <v>50.666666666666664</v>
       </c>
       <c r="BI39" s="126">
         <f>BH39/BH42</f>
-        <v>0</v>
-      </c>
-      <c r="BK39" s="164"/>
+        <v>0.98064516129032253</v>
+      </c>
+      <c r="BK39" s="174"/>
       <c r="BL39" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!H3,AK80:AS91,9,FALSE),"3rd Group A/E/H/I/J")</f>
         <v>3rd Group A/E/H/I/J</v>
@@ -48700,7 +48732,7 @@
       </c>
       <c r="K40" s="23">
         <f>L40+M40+N40</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="23">
         <f>VLOOKUP(2,AD38:AN41,3,FALSE)</f>
@@ -48708,7 +48740,7 @@
       </c>
       <c r="M40" s="23">
         <f>VLOOKUP(2,AD38:AN41,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N40" s="23">
         <f>VLOOKUP(2,AD38:AN41,5,FALSE)</f>
@@ -48716,11 +48748,11 @@
       </c>
       <c r="O40" s="23" t="str">
         <f>VLOOKUP(2,AD38:AN41,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD38:AN41,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>2 - 2</v>
       </c>
       <c r="P40" s="34">
         <f>L40*3+M40</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40" s="123">
         <f>DATE(2026,6,20)+TIME(13,0,0)+gmt_delta</f>
@@ -48820,7 +48852,7 @@
       </c>
       <c r="AR40" s="125">
         <f>AP40/AP42</f>
-        <v>7.5671989240137219E-4</v>
+        <v>1.2663913617613456E-11</v>
       </c>
       <c r="AT40" s="126" cm="1">
         <f t="array" ref="AT40">SUMPRODUCT(($S$7:$S$78=AE40&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE40&amp;"_win")*($U$7:$U$78))</f>
@@ -49041,7 +49073,7 @@
       </c>
       <c r="AR41" s="125">
         <f>AP41/AP42</f>
-        <v>7.4087382006895759E-4</v>
+        <v>1.2398725278822286E-11</v>
       </c>
       <c r="AT41" s="126" cm="1">
         <f t="array" ref="AT41">SUMPRODUCT(($S$7:$S$78=AE41&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE41&amp;"_win")*($U$7:$U$78))</f>
@@ -49233,7 +49265,7 @@
       </c>
       <c r="AG42" s="123">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH42" s="123">
         <f t="shared" si="18"/>
@@ -49241,7 +49273,7 @@
       </c>
       <c r="AI42" s="123">
         <f>MAX(AI38:AI41)+1</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AL42" s="123">
         <f>MIN(AL38:AL41)</f>
@@ -49253,15 +49285,15 @@
       </c>
       <c r="AN42" s="123">
         <f>MAX(AN38:AN41)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO42" s="123">
         <f>MAX(AO38:AO41)+1</f>
-        <v>1</v>
+        <v>6.9806451612903224</v>
       </c>
       <c r="AP42" s="123">
         <f>MAX(AP38:AP41)+1</f>
-        <v>1.000878935</v>
+        <v>59806551.344964951</v>
       </c>
       <c r="AT42" s="126">
         <f>MAX(AT38:AT41)-MIN(AT38:AT41)+1</f>
@@ -49269,15 +49301,15 @@
       </c>
       <c r="AU42" s="126">
         <f>MAX(AU38:AU41)-MIN(AU38:AU41)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV42" s="126">
         <f>MAX(AV38:AV41)-MIN(AV38:AV41)+1</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW42" s="126">
         <f>MAX(AW38:AW41)-MIN(AW38:AW41)+1</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AY42" s="126">
         <f>MAX(AY38:AY41)-MIN(AY38:AY41)+1</f>
@@ -49285,7 +49317,7 @@
       </c>
       <c r="AZ42" s="126">
         <f>MAX(AZ38:AZ41)+1</f>
-        <v>1</v>
+        <v>51.666666666666664</v>
       </c>
       <c r="BB42" s="126">
         <f>MAX(BB38:BB41)-MIN(BB38:BB41)+1</f>
@@ -49293,15 +49325,15 @@
       </c>
       <c r="BC42" s="126">
         <f>MAX(BC38:BC41)-MIN(BC38:BC41)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD42" s="126">
         <f>MAX(BD38:BD41)-MIN(BD38:BD41)+1</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BE42" s="126">
         <f>MAX(BE38:BE41)-MIN(BE38:BE41)+1</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BG42" s="126">
         <f>MAX(BG38:BG41)-MIN(BG38:BG41)+1</f>
@@ -49309,9 +49341,9 @@
       </c>
       <c r="BH42" s="126">
         <f>MAX(BH38:BH41)+1</f>
-        <v>1</v>
-      </c>
-      <c r="BK42" s="163">
+        <v>51.666666666666664</v>
+      </c>
+      <c r="BK42" s="173">
         <v>76</v>
       </c>
       <c r="BL42" s="24" t="str">
@@ -49404,7 +49436,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK43" s="164"/>
+      <c r="BK43" s="174"/>
       <c r="BL43" s="26" t="str">
         <f>AS39</f>
         <v>2F</v>
@@ -49660,7 +49692,7 @@
       <c r="BO44" s="21"/>
       <c r="BP44" s="114"/>
       <c r="BQ44" s="112"/>
-      <c r="BR44" s="163">
+      <c r="BR44" s="173">
         <v>91</v>
       </c>
       <c r="BS44" s="24" t="str">
@@ -49675,14 +49707,14 @@
         <v/>
       </c>
       <c r="CK44" s="114"/>
-      <c r="CM44" s="165" t="str" cm="1">
+      <c r="CM44" s="176" t="str" cm="1">
         <f t="array" ref="CM44">INDEX(T,7,lang)</f>
         <v>Third-Place Play-Off</v>
       </c>
-      <c r="CN44" s="166"/>
-      <c r="CO44" s="166"/>
-      <c r="CP44" s="166"/>
-      <c r="CQ44" s="167"/>
+      <c r="CN44" s="177"/>
+      <c r="CO44" s="177"/>
+      <c r="CP44" s="177"/>
+      <c r="CQ44" s="178"/>
     </row>
     <row r="45" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="16">
@@ -49919,7 +49951,7 @@
         <v>46203.708333333336</v>
       </c>
       <c r="BQ45" s="115"/>
-      <c r="BR45" s="164"/>
+      <c r="BR45" s="174"/>
       <c r="BS45" s="26" t="str">
         <f>IF(BP46&gt;BP47,BL46,IF(BP46&lt;BP47,BL47,""))</f>
         <v/>
@@ -49932,11 +49964,11 @@
         <v/>
       </c>
       <c r="CK45" s="114"/>
-      <c r="CM45" s="168"/>
-      <c r="CN45" s="169"/>
-      <c r="CO45" s="169"/>
-      <c r="CP45" s="169"/>
-      <c r="CQ45" s="170"/>
+      <c r="CM45" s="179"/>
+      <c r="CN45" s="180"/>
+      <c r="CO45" s="180"/>
+      <c r="CP45" s="180"/>
+      <c r="CQ45" s="181"/>
     </row>
     <row r="46" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A46" s="16">
@@ -50156,7 +50188,7 @@
         <f>BH46/BH48</f>
         <v>0</v>
       </c>
-      <c r="BK46" s="163">
+      <c r="BK46" s="173">
         <v>78</v>
       </c>
       <c r="BL46" s="24" t="str">
@@ -50398,7 +50430,7 @@
         <f>BH47/BH48</f>
         <v>0</v>
       </c>
-      <c r="BK47" s="164"/>
+      <c r="BK47" s="174"/>
       <c r="BL47" s="26" t="str">
         <f>AS57</f>
         <v>2I</v>
@@ -50641,7 +50673,7 @@
       <c r="BV48" s="21"/>
       <c r="BW48" s="114"/>
       <c r="BX48" s="112"/>
-      <c r="BY48" s="163">
+      <c r="BY48" s="173">
         <v>99</v>
       </c>
       <c r="BZ48" s="24" t="str">
@@ -50657,7 +50689,7 @@
       </c>
       <c r="CK48" s="114"/>
       <c r="CL48" s="112"/>
-      <c r="CM48" s="163">
+      <c r="CM48" s="173">
         <v>103</v>
       </c>
       <c r="CN48" s="24" t="str">
@@ -50762,7 +50794,7 @@
       <c r="BV49" s="21"/>
       <c r="BW49" s="114"/>
       <c r="BX49" s="115"/>
-      <c r="BY49" s="164"/>
+      <c r="BY49" s="174"/>
       <c r="BZ49" s="26" t="str">
         <f>IF(BW52&gt;BW53,BS52,IF(BW52&lt;BW53,BS53,""))</f>
         <v/>
@@ -50776,7 +50808,7 @@
       </c>
       <c r="CK49" s="114"/>
       <c r="CL49" s="115"/>
-      <c r="CM49" s="164"/>
+      <c r="CM49" s="174"/>
       <c r="CN49" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG56,IF(CK55&lt;CK56,CG55,""))</f>
         <v/>
@@ -51011,7 +51043,7 @@
         <f>BH50/BH54</f>
         <v>0</v>
       </c>
-      <c r="BK50" s="163">
+      <c r="BK50" s="173">
         <v>79</v>
       </c>
       <c r="BL50" s="24" t="str">
@@ -51264,7 +51296,7 @@
         <f>BH51/BH54</f>
         <v>0</v>
       </c>
-      <c r="BK51" s="164"/>
+      <c r="BK51" s="174"/>
       <c r="BL51" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!D3,AK80:AS91,9,FALSE),"3rd Group C/E/F/H/I")</f>
         <v>3rd Group C/E/F/H/I</v>
@@ -51524,7 +51556,7 @@
       <c r="BO52" s="21"/>
       <c r="BP52" s="114"/>
       <c r="BQ52" s="112"/>
-      <c r="BR52" s="163">
+      <c r="BR52" s="173">
         <v>92</v>
       </c>
       <c r="BS52" s="24" t="str">
@@ -51779,7 +51811,7 @@
         <v>46204.666666666672</v>
       </c>
       <c r="BQ53" s="115"/>
-      <c r="BR53" s="164"/>
+      <c r="BR53" s="174"/>
       <c r="BS53" s="26" t="str">
         <f>IF(BP54&gt;BP55,BL54,IF(BP54&lt;BP55,BL55,""))</f>
         <v/>
@@ -51983,7 +52015,7 @@
         <f>MAX(BH50:BH53)+1</f>
         <v>1</v>
       </c>
-      <c r="BK54" s="163">
+      <c r="BK54" s="173">
         <v>80</v>
       </c>
       <c r="BL54" s="24" t="str">
@@ -52104,7 +52136,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK55" s="164"/>
+      <c r="BK55" s="174"/>
       <c r="BL55" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!K3,AK80:AS91,9,FALSE),"3rd Group E/H/I/J/K")</f>
         <v>3rd Group E/H/I/J/K</v>
@@ -52131,7 +52163,7 @@
       <c r="CC55" s="21"/>
       <c r="CD55" s="114"/>
       <c r="CE55" s="112"/>
-      <c r="CF55" s="163">
+      <c r="CF55" s="173">
         <v>102</v>
       </c>
       <c r="CG55" s="24" t="str">
@@ -52390,7 +52422,7 @@
       <c r="CC56" s="21"/>
       <c r="CD56" s="114"/>
       <c r="CE56" s="115"/>
-      <c r="CF56" s="164"/>
+      <c r="CF56" s="174"/>
       <c r="CG56" s="26" t="str">
         <f>IF(CD64&gt;CD65,BZ64,IF(CD64&lt;CD65,BZ65,""))</f>
         <v/>
@@ -52873,7 +52905,7 @@
         <f>BH58/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK58" s="163">
+      <c r="BK58" s="173">
         <v>86</v>
       </c>
       <c r="BL58" s="24" t="str">
@@ -53121,7 +53153,7 @@
         <f>BH59/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK59" s="164"/>
+      <c r="BK59" s="174"/>
       <c r="BL59" s="26" t="str">
         <f>AS51</f>
         <v>2H</v>
@@ -53344,7 +53376,7 @@
       <c r="BO60" s="21"/>
       <c r="BP60" s="114"/>
       <c r="BQ60" s="112"/>
-      <c r="BR60" s="163">
+      <c r="BR60" s="173">
         <v>95</v>
       </c>
       <c r="BS60" s="24" t="str">
@@ -53457,7 +53489,7 @@
         <v>46206.75</v>
       </c>
       <c r="BQ61" s="115"/>
-      <c r="BR61" s="164"/>
+      <c r="BR61" s="174"/>
       <c r="BS61" s="26" t="str">
         <f>IF(BP62&gt;BP63,BL62,IF(BP62&lt;BP63,BL63,""))</f>
         <v/>
@@ -53700,7 +53732,7 @@
         <f>BH62/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK62" s="163">
+      <c r="BK62" s="173">
         <v>88</v>
       </c>
       <c r="BL62" s="24" t="str">
@@ -53952,7 +53984,7 @@
         <f>BH63/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK63" s="164"/>
+      <c r="BK63" s="174"/>
       <c r="BL63" s="26" t="str">
         <f>AS45</f>
         <v>2G</v>
@@ -54218,7 +54250,7 @@
       <c r="BV64" s="21"/>
       <c r="BW64" s="114"/>
       <c r="BX64" s="112"/>
-      <c r="BY64" s="163">
+      <c r="BY64" s="173">
         <v>100</v>
       </c>
       <c r="BZ64" s="24" t="str">
@@ -54472,7 +54504,7 @@
       <c r="BV65" s="21"/>
       <c r="BW65" s="114"/>
       <c r="BX65" s="115"/>
-      <c r="BY65" s="164"/>
+      <c r="BY65" s="174"/>
       <c r="BZ65" s="26" t="str">
         <f>IF(BW68&gt;BW69,BS68,IF(BW68&lt;BW69,BS69,""))</f>
         <v/>
@@ -54668,7 +54700,7 @@
         <f>MAX(BH62:BH65)+1</f>
         <v>1</v>
       </c>
-      <c r="BK66" s="163">
+      <c r="BK66" s="173">
         <v>85</v>
       </c>
       <c r="BL66" s="24" t="str">
@@ -54768,7 +54800,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK67" s="164"/>
+      <c r="BK67" s="174"/>
       <c r="BL67" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!E3,AK80:AS91,9,FALSE),"3rd Group E/F/G/I/J")</f>
         <v>3rd Group E/F/G/I/J</v>
@@ -55024,7 +55056,7 @@
       <c r="BO68" s="21"/>
       <c r="BP68" s="114"/>
       <c r="BQ68" s="112"/>
-      <c r="BR68" s="163">
+      <c r="BR68" s="173">
         <v>96</v>
       </c>
       <c r="BS68" s="24" t="str">
@@ -55038,25 +55070,25 @@
         <f>IF(OR(BT68="",BT69="",AND(BU68="",BU69&lt;&gt;""),AND(BU69="",BU68&lt;&gt;""),AND(BV68="",BV69&lt;&gt;""),AND(BV69="",BV68&lt;&gt;"")),"",BT68*1000+BU68*10+BV68)</f>
         <v/>
       </c>
-      <c r="CE68" s="195" t="str">
+      <c r="CE68" s="175" t="str">
         <f>INDEX(T,144,lang)</f>
         <v>World Champion 2026</v>
       </c>
-      <c r="CF68" s="195"/>
-      <c r="CG68" s="195"/>
-      <c r="CH68" s="195"/>
-      <c r="CI68" s="195"/>
-      <c r="CJ68" s="195"/>
-      <c r="CK68" s="185" t="str">
+      <c r="CF68" s="175"/>
+      <c r="CG68" s="175"/>
+      <c r="CH68" s="175"/>
+      <c r="CI68" s="175"/>
+      <c r="CJ68" s="175"/>
+      <c r="CK68" s="163" t="str">
         <f>IF(CR37&gt;CR38,CN37,IF(CR37&lt;CR38,CN38,""))</f>
         <v/>
       </c>
-      <c r="CL68" s="185"/>
-      <c r="CM68" s="185"/>
-      <c r="CN68" s="185"/>
-      <c r="CO68" s="185"/>
-      <c r="CP68" s="185"/>
-      <c r="CQ68" s="185"/>
+      <c r="CL68" s="163"/>
+      <c r="CM68" s="163"/>
+      <c r="CN68" s="163"/>
+      <c r="CO68" s="163"/>
+      <c r="CP68" s="163"/>
+      <c r="CQ68" s="163"/>
     </row>
     <row r="69" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A69" s="16">
@@ -55294,7 +55326,7 @@
         <v>46207.0625</v>
       </c>
       <c r="BQ69" s="115"/>
-      <c r="BR69" s="164"/>
+      <c r="BR69" s="174"/>
       <c r="BS69" s="26" t="str">
         <f>IF(BP70&gt;BP71,BL70,IF(BP70&lt;BP71,BL71,""))</f>
         <v/>
@@ -55306,19 +55338,19 @@
         <f>IF(BW68="","",BT69*1000+BU69*10+BV69)</f>
         <v/>
       </c>
-      <c r="CE69" s="195"/>
-      <c r="CF69" s="195"/>
-      <c r="CG69" s="195"/>
-      <c r="CH69" s="195"/>
-      <c r="CI69" s="195"/>
-      <c r="CJ69" s="195"/>
-      <c r="CK69" s="185"/>
-      <c r="CL69" s="185"/>
-      <c r="CM69" s="185"/>
-      <c r="CN69" s="185"/>
-      <c r="CO69" s="185"/>
-      <c r="CP69" s="185"/>
-      <c r="CQ69" s="185"/>
+      <c r="CE69" s="175"/>
+      <c r="CF69" s="175"/>
+      <c r="CG69" s="175"/>
+      <c r="CH69" s="175"/>
+      <c r="CI69" s="175"/>
+      <c r="CJ69" s="175"/>
+      <c r="CK69" s="163"/>
+      <c r="CL69" s="163"/>
+      <c r="CM69" s="163"/>
+      <c r="CN69" s="163"/>
+      <c r="CO69" s="163"/>
+      <c r="CP69" s="163"/>
+      <c r="CQ69" s="163"/>
     </row>
     <row r="70" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A70" s="16">
@@ -55539,7 +55571,7 @@
         <f>BH70/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK70" s="163">
+      <c r="BK70" s="173">
         <v>87</v>
       </c>
       <c r="BL70" s="24" t="str">
@@ -55775,7 +55807,7 @@
         <f>BH71/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK71" s="164"/>
+      <c r="BK71" s="174"/>
       <c r="BL71" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!J3,AK80:AS91,9,FALSE),"3rd Group D/E/I/J/L")</f>
         <v>3rd Group D/E/I/J/L</v>
@@ -57182,7 +57214,7 @@
       </c>
       <c r="AD80" s="123">
         <f>COUNTIF($AP$80:$AP$91,CONCATENATE("&gt;=",AP80))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE80" s="124" t="str">
         <f>J11</f>
@@ -57217,7 +57249,7 @@
       </c>
       <c r="AM80" s="123">
         <f>AL80-$AL$92</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN80" s="123">
         <f>VLOOKUP($AE80,$AE$8:$AQ$78,10,FALSE)</f>
@@ -57225,7 +57257,7 @@
       </c>
       <c r="AP80" s="123">
         <f>AN80/AN92*10000+AM80/AM92*1000+AI80/AI92*100+IF(AQ80=0,ROW(),AQ80)/2000000</f>
-        <v>50.000750689999997</v>
+        <v>383.33408402333333</v>
       </c>
       <c r="AQ80" s="126">
         <f t="shared" ref="AQ80:AQ91" si="37">VLOOKUP($AE80,$AE$8:$AQ$78,13,FALSE)</f>
@@ -57256,11 +57288,11 @@
       <c r="I81" s="69"/>
       <c r="J81" s="96" t="str">
         <f>VLOOKUP(1,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓓ Australia</v>
+        <v>Ⓒ Morocco</v>
       </c>
       <c r="K81" s="97">
         <f>L81+M81+N81</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" s="97">
         <f>VLOOKUP(1,$AD$80:$AN$91,3,FALSE)</f>
@@ -57268,7 +57300,7 @@
       </c>
       <c r="M81" s="97">
         <f>VLOOKUP(1,$AD$80:$AN$91,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N81" s="97">
         <f>VLOOKUP(1,$AD$80:$AN$91,5,FALSE)</f>
@@ -57276,15 +57308,15 @@
       </c>
       <c r="O81" s="97" t="str">
         <f>VLOOKUP(1,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(1,$AD$80:$AN$91,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 1</v>
       </c>
       <c r="P81" s="98">
         <f>L81*3+M81</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD81" s="123">
         <f t="shared" ref="AD81:AD91" si="38">COUNTIF($AP$80:$AP$91,CONCATENATE("&gt;=",AP81))</f>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AE81" s="124" t="str">
         <f>J17</f>
@@ -57296,7 +57328,7 @@
       </c>
       <c r="AG81" s="123">
         <f>VLOOKUP($AE81,$AE$8:$AQ$78,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH81" s="123">
         <f t="shared" ref="AH81:AH90" si="40">VLOOKUP($AE81,$AE$8:$AQ$78,4,FALSE)</f>
@@ -57304,11 +57336,11 @@
       </c>
       <c r="AI81" s="123">
         <f t="shared" ref="AI81:AI90" si="41">VLOOKUP($AE81,$AE$8:$AQ$78,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ81" s="123">
         <f t="shared" ref="AJ81:AJ90" si="42">VLOOKUP($AE81,$AE$8:$AQ$78,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK81" s="123" t="s">
         <v>3181</v>
@@ -57319,15 +57351,15 @@
       </c>
       <c r="AM81" s="123">
         <f t="shared" ref="AM81:AM91" si="44">AL81-$AL$92</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN81" s="123">
         <f t="shared" ref="AN81:AN90" si="45">VLOOKUP($AE81,$AE$8:$AQ$78,10,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP81" s="123">
         <f>AN81/AN92*10000+AM81/AM92*1000+AI81/AI92*100+IF(AQ81=0,ROW(),AQ81)/2000000</f>
-        <v>500.00072748000002</v>
+        <v>5716.667394146667</v>
       </c>
       <c r="AQ81" s="126">
         <f t="shared" si="37"/>
@@ -57335,11 +57367,11 @@
       </c>
       <c r="AR81" s="125" t="str">
         <f>AR80&amp;IF(AD81&lt;=8,RIGHT(AK81,1),"")</f>
-        <v/>
+        <v>B</v>
       </c>
       <c r="AS81" s="129" t="str">
         <f t="shared" ref="AS81:AS91" si="46">IF(AD81&lt;=8,AE81,"")</f>
-        <v/>
+        <v>Qatar</v>
       </c>
       <c r="AT81" s="130" t="str">
         <f>"Ⓑ "&amp;AE81</f>
@@ -57358,11 +57390,11 @@
       <c r="I82" s="69"/>
       <c r="J82" s="99" t="str">
         <f>VLOOKUP(2,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓙ Algeria</v>
+        <v>Ⓑ Qatar</v>
       </c>
       <c r="K82" s="100">
         <f t="shared" ref="K82:K92" si="47">L82+M82+N82</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" s="100">
         <f>VLOOKUP(2,$AD$80:$AN$91,3,FALSE)</f>
@@ -57370,7 +57402,7 @@
       </c>
       <c r="M82" s="100">
         <f>VLOOKUP(2,$AD$80:$AN$91,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N82" s="100">
         <f>VLOOKUP(2,$AD$80:$AN$91,5,FALSE)</f>
@@ -57378,19 +57410,19 @@
       </c>
       <c r="O82" s="100" t="str">
         <f>VLOOKUP(2,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(2,$AD$80:$AN$91,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 1</v>
       </c>
       <c r="P82" s="101">
         <f t="shared" ref="P82:P92" si="48">L82*3+M82</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD82" s="123">
         <f t="shared" si="38"/>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AE82" s="124" t="str">
         <f>J23</f>
-        <v>Scotland</v>
+        <v>Morocco</v>
       </c>
       <c r="AF82" s="123">
         <f t="shared" si="39"/>
@@ -57398,7 +57430,7 @@
       </c>
       <c r="AG82" s="123">
         <f t="shared" ref="AG82:AG91" si="49">VLOOKUP($AE82,$AE$8:$AQ$78,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH82" s="123">
         <f t="shared" si="40"/>
@@ -57406,11 +57438,11 @@
       </c>
       <c r="AI82" s="123">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ82" s="123">
         <f t="shared" si="42"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK82" s="123" t="s">
         <v>3182</v>
@@ -57421,48 +57453,48 @@
       </c>
       <c r="AM82" s="123">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN82" s="123">
         <f t="shared" si="45"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP82" s="123">
         <f>AN82/AN92*10000+AM82/AM92*1000+AI82/AI92*100+IF(AQ82=0,ROW(),AQ82)/2000000</f>
-        <v>500.00074917500001</v>
+        <v>5716.667544601667</v>
       </c>
       <c r="AQ82" s="126">
         <f t="shared" si="37"/>
-        <v>1498.35</v>
+        <v>1755.87</v>
       </c>
       <c r="AR82" s="125" t="str">
         <f t="shared" ref="AR82:AR91" si="50">AR81&amp;IF(AD82&lt;=8,RIGHT(AK82,1),"")</f>
-        <v>C</v>
+        <v>BC</v>
       </c>
       <c r="AS82" s="129" t="str">
         <f t="shared" si="46"/>
-        <v>Scotland</v>
+        <v>Morocco</v>
       </c>
       <c r="AT82" s="130" t="str">
         <f>"Ⓒ "&amp;AE82</f>
-        <v>Ⓒ Scotland</v>
+        <v>Ⓒ Morocco</v>
       </c>
     </row>
     <row r="83" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="73"/>
       <c r="B83" s="73"/>
-      <c r="C83" s="186" t="s">
+      <c r="C83" s="164" t="s">
         <v>3183</v>
       </c>
-      <c r="D83" s="187"/>
-      <c r="E83" s="187"/>
-      <c r="F83" s="187"/>
-      <c r="G83" s="188"/>
+      <c r="D83" s="165"/>
+      <c r="E83" s="165"/>
+      <c r="F83" s="165"/>
+      <c r="G83" s="166"/>
       <c r="H83" s="75"/>
       <c r="I83" s="69"/>
       <c r="J83" s="99" t="str">
         <f>VLOOKUP(3,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓖ Egypt</v>
+        <v>Ⓙ Algeria</v>
       </c>
       <c r="K83" s="100">
         <f t="shared" si="47"/>
@@ -57490,11 +57522,11 @@
       </c>
       <c r="AD83" s="123">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AE83" s="124" t="str">
         <f>J29</f>
-        <v>Australia</v>
+        <v>Turkey</v>
       </c>
       <c r="AF83" s="123">
         <f t="shared" si="39"/>
@@ -57506,7 +57538,7 @@
       </c>
       <c r="AH83" s="123">
         <f t="shared" si="40"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI83" s="123">
         <f t="shared" si="41"/>
@@ -57514,18 +57546,18 @@
       </c>
       <c r="AJ83" s="123">
         <f t="shared" si="42"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK83" s="123" t="s">
         <v>3184</v>
       </c>
       <c r="AL83" s="123">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AM83" s="123">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN83" s="123">
         <f t="shared" si="45"/>
@@ -57533,38 +57565,38 @@
       </c>
       <c r="AP83" s="123">
         <f>AN83/AN92*10000+AM83/AM92*1000+AI83/AI92*100+IF(AQ83=0,ROW(),AQ83)/2000000</f>
-        <v>500.00079033499998</v>
+        <v>7.9951999999999996E-4</v>
       </c>
       <c r="AQ83" s="126">
         <f t="shared" si="37"/>
-        <v>1580.67</v>
+        <v>1599.04</v>
       </c>
       <c r="AR83" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>CD</v>
+        <v>BC</v>
       </c>
       <c r="AS83" s="129" t="str">
         <f t="shared" si="46"/>
-        <v>Australia</v>
+        <v/>
       </c>
       <c r="AT83" s="130" t="str">
         <f>"Ⓓ "&amp;AE83</f>
-        <v>Ⓓ Australia</v>
+        <v>Ⓓ Turkey</v>
       </c>
     </row>
     <row r="84" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="73"/>
       <c r="B84" s="73"/>
-      <c r="C84" s="189"/>
-      <c r="D84" s="190"/>
-      <c r="E84" s="190"/>
-      <c r="F84" s="190"/>
-      <c r="G84" s="191"/>
+      <c r="C84" s="167"/>
+      <c r="D84" s="168"/>
+      <c r="E84" s="168"/>
+      <c r="F84" s="168"/>
+      <c r="G84" s="169"/>
       <c r="H84" s="75"/>
       <c r="I84" s="69"/>
       <c r="J84" s="99" t="str">
         <f>VLOOKUP(4,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓘ Norway</v>
+        <v>Ⓖ Egypt</v>
       </c>
       <c r="K84" s="100">
         <f t="shared" si="47"/>
@@ -57604,7 +57636,7 @@
       </c>
       <c r="AD84" s="123">
         <f t="shared" si="38"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE84" s="124" t="str">
         <f>J35</f>
@@ -57639,7 +57671,7 @@
       </c>
       <c r="AM84" s="123">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN84" s="123">
         <f t="shared" si="45"/>
@@ -57647,7 +57679,7 @@
       </c>
       <c r="AP84" s="123">
         <f>AN84/AN92*10000+AM84/AM92*1000+AI84/AI92*100+IF(AQ84=0,ROW(),AQ84)/2000000</f>
-        <v>500.00076648999999</v>
+        <v>666.66743315666668</v>
       </c>
       <c r="AQ84" s="126">
         <f t="shared" si="37"/>
@@ -57655,7 +57687,7 @@
       </c>
       <c r="AR84" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>CDE</v>
+        <v>BCE</v>
       </c>
       <c r="AS84" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57669,16 +57701,16 @@
     <row r="85" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="73"/>
       <c r="B85" s="73"/>
-      <c r="C85" s="189"/>
-      <c r="D85" s="190"/>
-      <c r="E85" s="190"/>
-      <c r="F85" s="190"/>
-      <c r="G85" s="191"/>
+      <c r="C85" s="167"/>
+      <c r="D85" s="168"/>
+      <c r="E85" s="168"/>
+      <c r="F85" s="168"/>
+      <c r="G85" s="169"/>
       <c r="H85" s="75"/>
       <c r="I85" s="69"/>
       <c r="J85" s="99" t="str">
         <f>VLOOKUP(5,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓛ Panama</v>
+        <v>Ⓘ Norway</v>
       </c>
       <c r="K85" s="100">
         <f t="shared" si="47"/>
@@ -57718,7 +57750,7 @@
       </c>
       <c r="AD85" s="123">
         <f t="shared" si="38"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE85" s="124" t="str">
         <f>J41</f>
@@ -57753,7 +57785,7 @@
       </c>
       <c r="AM85" s="123">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN85" s="123">
         <f t="shared" si="45"/>
@@ -57761,7 +57793,7 @@
       </c>
       <c r="AP85" s="123">
         <f>AN85/AN92*10000+AM85/AM92*1000+AI85/AI92*100+IF(AQ85=0,ROW(),AQ85)/2000000</f>
-        <v>500.00075738499999</v>
+        <v>666.66742405166667</v>
       </c>
       <c r="AQ85" s="126">
         <f t="shared" si="37"/>
@@ -57769,7 +57801,7 @@
       </c>
       <c r="AR85" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>CDEF</v>
+        <v>BCEF</v>
       </c>
       <c r="AS85" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57783,16 +57815,16 @@
     <row r="86" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="73"/>
       <c r="B86" s="73"/>
-      <c r="C86" s="189"/>
-      <c r="D86" s="190"/>
-      <c r="E86" s="190"/>
-      <c r="F86" s="190"/>
-      <c r="G86" s="191"/>
+      <c r="C86" s="167"/>
+      <c r="D86" s="168"/>
+      <c r="E86" s="168"/>
+      <c r="F86" s="168"/>
+      <c r="G86" s="169"/>
       <c r="H86" s="75"/>
       <c r="I86" s="69"/>
       <c r="J86" s="99" t="str">
         <f>VLOOKUP(6,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓔ Ivory Coast</v>
+        <v>Ⓛ Panama</v>
       </c>
       <c r="K86" s="100">
         <f t="shared" si="47"/>
@@ -57832,7 +57864,7 @@
       </c>
       <c r="AD86" s="123">
         <f t="shared" si="38"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE86" s="124" t="str">
         <f>J47</f>
@@ -57867,7 +57899,7 @@
       </c>
       <c r="AM86" s="123">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN86" s="123">
         <f t="shared" si="45"/>
@@ -57875,7 +57907,7 @@
       </c>
       <c r="AP86" s="123">
         <f>AN86/AN92*10000+AM86/AM92*1000+AI86/AI92*100+IF(AQ86=0,ROW(),AQ86)/2000000</f>
-        <v>500.00078162</v>
+        <v>666.66744828666663</v>
       </c>
       <c r="AQ86" s="126">
         <f t="shared" si="37"/>
@@ -57883,7 +57915,7 @@
       </c>
       <c r="AR86" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>CDEFG</v>
+        <v>BCEFG</v>
       </c>
       <c r="AS86" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57897,16 +57929,16 @@
     <row r="87" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="73"/>
       <c r="B87" s="73"/>
-      <c r="C87" s="189"/>
-      <c r="D87" s="190"/>
-      <c r="E87" s="190"/>
-      <c r="F87" s="190"/>
-      <c r="G87" s="191"/>
+      <c r="C87" s="167"/>
+      <c r="D87" s="168"/>
+      <c r="E87" s="168"/>
+      <c r="F87" s="168"/>
+      <c r="G87" s="169"/>
       <c r="H87" s="75"/>
       <c r="I87" s="69"/>
       <c r="J87" s="99" t="str">
         <f>VLOOKUP(7,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓕ Sweden</v>
+        <v>Ⓔ Ivory Coast</v>
       </c>
       <c r="K87" s="100">
         <f t="shared" si="47"/>
@@ -57946,7 +57978,7 @@
       </c>
       <c r="AD87" s="123">
         <f t="shared" si="38"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE87" s="124" t="str">
         <f>J53</f>
@@ -57981,7 +58013,7 @@
       </c>
       <c r="AM87" s="123">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN87" s="123">
         <f t="shared" si="45"/>
@@ -57989,7 +58021,7 @@
       </c>
       <c r="AP87" s="123">
         <f>AN87/AN92*10000+AM87/AM92*1000+AI87/AI92*100+IF(AQ87=0,ROW(),AQ87)/2000000</f>
-        <v>500.00071071500003</v>
+        <v>666.6673773816666</v>
       </c>
       <c r="AQ87" s="126">
         <f t="shared" si="37"/>
@@ -57997,7 +58029,7 @@
       </c>
       <c r="AR87" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>CDEFG</v>
+        <v>BCEFG</v>
       </c>
       <c r="AS87" s="129" t="str">
         <f t="shared" si="46"/>
@@ -58011,16 +58043,16 @@
     <row r="88" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="73"/>
       <c r="B88" s="73"/>
-      <c r="C88" s="192"/>
-      <c r="D88" s="193"/>
-      <c r="E88" s="193"/>
-      <c r="F88" s="193"/>
-      <c r="G88" s="194"/>
+      <c r="C88" s="170"/>
+      <c r="D88" s="171"/>
+      <c r="E88" s="171"/>
+      <c r="F88" s="171"/>
+      <c r="G88" s="172"/>
       <c r="H88" s="75"/>
       <c r="I88" s="69"/>
       <c r="J88" s="99" t="str">
         <f>VLOOKUP(8,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓒ Scotland</v>
+        <v>Ⓕ Sweden</v>
       </c>
       <c r="K88" s="100">
         <f t="shared" si="47"/>
@@ -58060,7 +58092,7 @@
       </c>
       <c r="AD88" s="123">
         <f t="shared" si="38"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE88" s="124" t="str">
         <f>J59</f>
@@ -58095,7 +58127,7 @@
       </c>
       <c r="AM88" s="123">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN88" s="123">
         <f t="shared" si="45"/>
@@ -58103,7 +58135,7 @@
       </c>
       <c r="AP88" s="123">
         <f>AN88/AN92*10000+AM88/AM92*1000+AI88/AI92*100+IF(AQ88=0,ROW(),AQ88)/2000000</f>
-        <v>500.00077547000001</v>
+        <v>666.66744213666664</v>
       </c>
       <c r="AQ88" s="126">
         <f t="shared" si="37"/>
@@ -58111,7 +58143,7 @@
       </c>
       <c r="AR88" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>CDEFGI</v>
+        <v>BCEFGI</v>
       </c>
       <c r="AS88" s="129" t="str">
         <f t="shared" si="46"/>
@@ -58174,7 +58206,7 @@
       </c>
       <c r="AD89" s="123">
         <f t="shared" si="38"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE89" s="124" t="str">
         <f>J65</f>
@@ -58209,7 +58241,7 @@
       </c>
       <c r="AM89" s="123">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN89" s="123">
         <f t="shared" si="45"/>
@@ -58217,7 +58249,7 @@
       </c>
       <c r="AP89" s="123">
         <f>AN89/AN92*10000+AM89/AM92*1000+AI89/AI92*100+IF(AQ89=0,ROW(),AQ89)/2000000</f>
-        <v>500.00078213</v>
+        <v>666.66744879666658</v>
       </c>
       <c r="AQ89" s="126">
         <f t="shared" si="37"/>
@@ -58225,7 +58257,7 @@
       </c>
       <c r="AR89" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>CDEFGIJ</v>
+        <v>BCEFGIJ</v>
       </c>
       <c r="AS89" s="129" t="str">
         <f t="shared" si="46"/>
@@ -58248,7 +58280,7 @@
       <c r="I90" s="69"/>
       <c r="J90" s="102" t="str">
         <f>VLOOKUP(10,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓑ Qatar</v>
+        <v>Ⓗ Saudi Arabia</v>
       </c>
       <c r="K90" s="103">
         <f t="shared" si="47"/>
@@ -58323,7 +58355,7 @@
       </c>
       <c r="AM90" s="123">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN90" s="123">
         <f t="shared" si="45"/>
@@ -58331,7 +58363,7 @@
       </c>
       <c r="AP90" s="123">
         <f>AN90/AN92*10000+AM90/AM92*1000+AI90/AI92*100+IF(AQ90=0,ROW(),AQ90)/2000000</f>
-        <v>500.00073917499998</v>
+        <v>666.66740584166666</v>
       </c>
       <c r="AQ90" s="126">
         <f t="shared" si="37"/>
@@ -58339,7 +58371,7 @@
       </c>
       <c r="AR90" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>CDEFGIJ</v>
+        <v>BCEFGIJ</v>
       </c>
       <c r="AS90" s="129" t="str">
         <f t="shared" si="46"/>
@@ -58362,11 +58394,11 @@
       <c r="I91" s="69"/>
       <c r="J91" s="102" t="str">
         <f>VLOOKUP(11,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓗ Saudi Arabia</v>
+        <v>Ⓐ Czech Republic</v>
       </c>
       <c r="K91" s="103">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="103">
         <f>VLOOKUP(11,$AD$80:$AN$91,3,FALSE)</f>
@@ -58378,11 +58410,11 @@
       </c>
       <c r="N91" s="103">
         <f>VLOOKUP(11,$AD$80:$AN$91,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O91" s="103" t="str">
         <f>VLOOKUP(11,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(11,$AD$80:$AN$91,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 2</v>
       </c>
       <c r="P91" s="104">
         <f t="shared" si="48"/>
@@ -58402,7 +58434,7 @@
       </c>
       <c r="AD91" s="123">
         <f t="shared" si="38"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE91" s="124" t="str">
         <f>J77</f>
@@ -58437,7 +58469,7 @@
       </c>
       <c r="AM91" s="123">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN91" s="123">
         <f>VLOOKUP($AE91,$AE$8:$AQ$78,10,FALSE)</f>
@@ -58445,7 +58477,7 @@
       </c>
       <c r="AP91" s="123">
         <f>AN91/AN92*10000+AM91/AM92*1000+AI91/AI92*100+IF(AQ91=0,ROW(),AQ91)/2000000</f>
-        <v>500.00077032000002</v>
+        <v>666.66743698666664</v>
       </c>
       <c r="AQ91" s="126">
         <f t="shared" si="37"/>
@@ -58453,7 +58485,7 @@
       </c>
       <c r="AR91" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>CDEFGIJL</v>
+        <v>BCEFGIJL</v>
       </c>
       <c r="AS91" s="129" t="str">
         <f t="shared" si="46"/>
@@ -58476,7 +58508,7 @@
       <c r="I92" s="69"/>
       <c r="J92" s="105" t="str">
         <f>VLOOKUP(12,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓐ Czech Republic</v>
+        <v>Ⓓ Turkey</v>
       </c>
       <c r="K92" s="106">
         <f t="shared" si="47"/>
@@ -58496,7 +58528,7 @@
       </c>
       <c r="O92" s="106" t="str">
         <f>VLOOKUP(12,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(12,$AD$80:$AN$91,7,FALSE)</f>
-        <v>1 - 2</v>
+        <v>0 - 2</v>
       </c>
       <c r="P92" s="107">
         <f t="shared" si="48"/>
@@ -58508,7 +58540,7 @@
       </c>
       <c r="AG92" s="123">
         <f>MAX(AG80:AG91)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH92" s="123">
         <f>MAX(AH80:AH91)+1</f>
@@ -58524,15 +58556,15 @@
       </c>
       <c r="AL92" s="123">
         <f>MIN(AL80:AL91)</f>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AM92" s="123">
         <f>MAX(AM80:AM91)+1</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN92" s="123">
         <f>MAX(AN80:AN91)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS92" s="126" t="b">
         <f>SUM(K9:K78)=144</f>
@@ -58693,6 +58725,36 @@
   <sheetProtection algorithmName="SHA-512" hashValue="7nWuIQAsd0NKRlhwUK3tOeNHpTch5B5FULy2gxNNaIdJM5RfhFSMzPcx55y+pmM3d73guUy+p5Y+SvIjJZQRaA==" saltValue="Uw23KnM8csnTioq5H8upCA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <dataConsolidate/>
   <mergeCells count="45">
+    <mergeCell ref="BK14:BK15"/>
+    <mergeCell ref="BY16:BY17"/>
+    <mergeCell ref="BK26:BK27"/>
+    <mergeCell ref="BR28:BR29"/>
+    <mergeCell ref="BK22:BK23"/>
+    <mergeCell ref="CF23:CF24"/>
+    <mergeCell ref="BK18:BK19"/>
+    <mergeCell ref="BR20:BR21"/>
+    <mergeCell ref="CM48:CM49"/>
+    <mergeCell ref="BR44:BR45"/>
+    <mergeCell ref="BK46:BK47"/>
+    <mergeCell ref="BK30:BK31"/>
+    <mergeCell ref="CM44:CQ45"/>
+    <mergeCell ref="BY32:BY33"/>
+    <mergeCell ref="BK38:BK39"/>
+    <mergeCell ref="BK34:BK35"/>
+    <mergeCell ref="BR36:BR37"/>
+    <mergeCell ref="BK42:BK43"/>
+    <mergeCell ref="CM33:CQ34"/>
+    <mergeCell ref="CM37:CM38"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="BR12:BR13"/>
+    <mergeCell ref="BK6:BO7"/>
+    <mergeCell ref="BR6:BV7"/>
+    <mergeCell ref="BY6:CC7"/>
+    <mergeCell ref="CF6:CJ7"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="A5:H6"/>
+    <mergeCell ref="J5:P6"/>
     <mergeCell ref="CK68:CQ69"/>
     <mergeCell ref="C83:G88"/>
     <mergeCell ref="BK70:BK71"/>
@@ -58708,36 +58770,6 @@
     <mergeCell ref="BR52:BR53"/>
     <mergeCell ref="BK54:BK55"/>
     <mergeCell ref="CE68:CJ69"/>
-    <mergeCell ref="CF6:CJ7"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="A5:H6"/>
-    <mergeCell ref="J5:P6"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="BR12:BR13"/>
-    <mergeCell ref="BK6:BO7"/>
-    <mergeCell ref="BR6:BV7"/>
-    <mergeCell ref="BY6:CC7"/>
-    <mergeCell ref="CF23:CF24"/>
-    <mergeCell ref="BK18:BK19"/>
-    <mergeCell ref="BR20:BR21"/>
-    <mergeCell ref="CM48:CM49"/>
-    <mergeCell ref="BR44:BR45"/>
-    <mergeCell ref="BK46:BK47"/>
-    <mergeCell ref="BK30:BK31"/>
-    <mergeCell ref="CM44:CQ45"/>
-    <mergeCell ref="BY32:BY33"/>
-    <mergeCell ref="BK38:BK39"/>
-    <mergeCell ref="BK34:BK35"/>
-    <mergeCell ref="BR36:BR37"/>
-    <mergeCell ref="BK42:BK43"/>
-    <mergeCell ref="CM33:CQ34"/>
-    <mergeCell ref="CM37:CM38"/>
-    <mergeCell ref="BK14:BK15"/>
-    <mergeCell ref="BY16:BY17"/>
-    <mergeCell ref="BK26:BK27"/>
-    <mergeCell ref="BR28:BR29"/>
-    <mergeCell ref="BK22:BK23"/>
   </mergeCells>
   <conditionalFormatting sqref="A7:E78">
     <cfRule type="expression" dxfId="228" priority="339">
@@ -60034,15 +60066,15 @@
     <row r="3" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B3" s="109">
         <f>MATCH(C3,C6:C500,0)</f>
-        <v>38</v>
+        <v>102</v>
       </c>
       <c r="C3" s="121" t="str">
         <f>'2026 World Cup'!AR91</f>
-        <v>CDEFGIJL</v>
+        <v>BCEFGIJL</v>
       </c>
       <c r="D3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,2,FALSE)</f>
-        <v>3C</v>
+        <v>3E</v>
       </c>
       <c r="E3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,3,FALSE)</f>
@@ -60050,11 +60082,11 @@
       </c>
       <c r="F3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,4,FALSE)</f>
-        <v>3E</v>
+        <v>3B</v>
       </c>
       <c r="G3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,5,FALSE)</f>
-        <v>3D</v>
+        <v>3C</v>
       </c>
       <c r="H3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,6,FALSE)</f>

--- a/public/worldcup.xlsx
+++ b/public/worldcup.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rylanpaul/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0F3F4DC-2D43-3E4A-B6B1-89FC2F43EA69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C29F59D-1C50-534C-8905-E307811F3961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9879" uniqueCount="3715">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9880" uniqueCount="3715">
   <si>
     <t>English</t>
   </si>
@@ -13305,56 +13305,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -13435,6 +13391,50 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -38694,13 +38694,13 @@
       <c r="B3" s="141" t="s">
         <v>2240</v>
       </c>
-      <c r="C3" s="142" t="e">
+      <c r="C3" s="142">
         <f>IFERROR(_xlfn.XLOOKUP(B3,Rounds!A$2:A$25,Rounds!B$2:B$25), _xlfn.XLOOKUP(B3,Rounds!D$2:D$25,Rounds!C$2:C$25))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D3" s="142" t="e">
+        <v>5</v>
+      </c>
+      <c r="D3" s="142">
         <f>IFERROR(_xlfn.XLOOKUP(B3,Rounds!A$2:A$25,Rounds!C$2:C$25), _xlfn.XLOOKUP(B3,Rounds!D$2:D$25,Rounds!B$2:B$25))</f>
-        <v>#N/A</v>
+        <v>1</v>
       </c>
       <c r="E3" s="140" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(B3,Rounds!A$2:A$25,Rounds!D$2:D$25), _xlfn.XLOOKUP(B3,Rounds!D$2:D$25,Rounds!A$2:A$25))</f>
@@ -38811,6 +38811,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(B4,Rounds!A$2:A$25,Rounds!D$2:D$25), _xlfn.XLOOKUP(B4,Rounds!D$2:D$25,Rounds!A$2:A$25))</f>
         <v>Qatar</v>
       </c>
+      <c r="F4" s="148" t="s">
+        <v>2274</v>
+      </c>
       <c r="G4" s="146" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(F4,Rounds!E$2:E$25,Rounds!F$2:F$25), _xlfn.XLOOKUP(F4,Rounds!H$2:H$25,Rounds!G$2:G$25))</f>
         <v>#N/A</v>
@@ -38819,9 +38822,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(F4,Rounds!E$2:E$25,Rounds!G$2:G$25), _xlfn.XLOOKUP(F4,Rounds!H$2:H$25,Rounds!F$2:F$25))</f>
         <v>#N/A</v>
       </c>
-      <c r="I4" s="147" t="e">
+      <c r="I4" s="147" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F4,Rounds!E$2:E$25,Rounds!H$2:H$25), _xlfn.XLOOKUP(F4,Rounds!H$2:H$25,Rounds!E$2:E$25))</f>
-        <v>#N/A</v>
+        <v>New Zealand</v>
       </c>
       <c r="K4" s="146" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(J4,Rounds!I$2:I$25,Rounds!J$2:J$25), _xlfn.XLOOKUP(J4,Rounds!L$2:L$25,Rounds!K$2:K$25))</f>
@@ -40119,11 +40122,11 @@
       <c r="A10" s="132" t="str">
         <v>Ivory Coast</v>
       </c>
-      <c r="B10" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C10" s="81" t="e">
-        <v>#N/A</v>
+      <c r="B10" s="81">
+        <v>1</v>
+      </c>
+      <c r="C10" s="81">
+        <v>0</v>
       </c>
       <c r="D10" s="134" t="str">
         <v>Ecuador</v>
@@ -40281,11 +40284,11 @@
       <c r="A13" s="132" t="str">
         <v>Sweden</v>
       </c>
-      <c r="B13" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C13" s="81" t="e">
-        <v>#N/A</v>
+      <c r="B13" s="81">
+        <v>5</v>
+      </c>
+      <c r="C13" s="81">
+        <v>1</v>
       </c>
       <c r="D13" s="134" t="str">
         <v>Tunisia</v>
@@ -40335,11 +40338,11 @@
       <c r="A14" s="132" t="str">
         <v>Saudi Arabia</v>
       </c>
-      <c r="B14" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C14" s="81" t="e">
-        <v>#N/A</v>
+      <c r="B14" s="81">
+        <v>1</v>
+      </c>
+      <c r="C14" s="81">
+        <v>1</v>
       </c>
       <c r="D14" s="134" t="str">
         <v>Uruguay</v>
@@ -40389,11 +40392,11 @@
       <c r="A15" s="132" t="str">
         <v>Spain</v>
       </c>
-      <c r="B15" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C15" s="81" t="e">
-        <v>#N/A</v>
+      <c r="B15" s="81">
+        <v>0</v>
+      </c>
+      <c r="C15" s="81">
+        <v>0</v>
       </c>
       <c r="D15" s="134" t="str">
         <v>Cape Verde</v>
@@ -40443,11 +40446,11 @@
       <c r="A16" s="132" t="str">
         <v>Iran</v>
       </c>
-      <c r="B16" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C16" s="81" t="e">
-        <v>#N/A</v>
+      <c r="B16" s="81">
+        <v>2</v>
+      </c>
+      <c r="C16" s="81">
+        <v>2</v>
       </c>
       <c r="D16" s="134" t="str">
         <v>New Zealand</v>
@@ -40497,11 +40500,11 @@
       <c r="A17" s="132" t="str">
         <v>Belgium</v>
       </c>
-      <c r="B17" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C17" s="81" t="e">
-        <v>#N/A</v>
+      <c r="B17" s="81">
+        <v>1</v>
+      </c>
+      <c r="C17" s="81">
+        <v>1</v>
       </c>
       <c r="D17" s="134" t="str">
         <v>Egypt</v>
@@ -40931,25 +40934,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:95" ht="47" x14ac:dyDescent="0.2">
-      <c r="A1" s="182" t="str" cm="1">
+      <c r="A1" s="171" t="str" cm="1">
         <f t="array" ref="A1">INDEX(T,2,lang)</f>
         <v>2026 World Cup Final Tournament Schedule</v>
       </c>
-      <c r="B1" s="182"/>
-      <c r="C1" s="182"/>
-      <c r="D1" s="182"/>
-      <c r="E1" s="182"/>
-      <c r="F1" s="182"/>
-      <c r="G1" s="182"/>
-      <c r="H1" s="182"/>
-      <c r="I1" s="182"/>
-      <c r="J1" s="182"/>
-      <c r="K1" s="182"/>
-      <c r="L1" s="182"/>
-      <c r="M1" s="182"/>
-      <c r="N1" s="182"/>
-      <c r="O1" s="182"/>
-      <c r="P1" s="182"/>
+      <c r="B1" s="171"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="171"/>
+      <c r="F1" s="171"/>
+      <c r="G1" s="171"/>
+      <c r="H1" s="171"/>
+      <c r="I1" s="171"/>
+      <c r="J1" s="171"/>
+      <c r="K1" s="171"/>
+      <c r="L1" s="171"/>
+      <c r="M1" s="171"/>
+      <c r="N1" s="171"/>
+      <c r="O1" s="171"/>
+      <c r="P1" s="171"/>
       <c r="S1" s="123"/>
       <c r="T1" s="123"/>
       <c r="AC1" s="123"/>
@@ -40996,11 +40999,11 @@
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
-      <c r="O3" s="183" t="str">
+      <c r="O3" s="172" t="str">
         <f>"Language: " &amp; Settings!C4</f>
         <v>Language: English</v>
       </c>
-      <c r="P3" s="183"/>
+      <c r="P3" s="172"/>
       <c r="S3" s="123"/>
       <c r="T3" s="123"/>
       <c r="AC3" s="123"/>
@@ -41018,43 +41021,43 @@
     </row>
     <row r="4" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:95" x14ac:dyDescent="0.2">
-      <c r="A5" s="184" t="str" cm="1">
+      <c r="A5" s="173" t="str" cm="1">
         <f t="array" ref="A5">INDEX(T,3,lang)</f>
         <v>Group Stage</v>
       </c>
-      <c r="B5" s="185"/>
-      <c r="C5" s="185"/>
-      <c r="D5" s="185"/>
-      <c r="E5" s="185"/>
-      <c r="F5" s="185"/>
-      <c r="G5" s="185"/>
-      <c r="H5" s="186"/>
-      <c r="J5" s="190" t="s">
+      <c r="B5" s="174"/>
+      <c r="C5" s="174"/>
+      <c r="D5" s="174"/>
+      <c r="E5" s="174"/>
+      <c r="F5" s="174"/>
+      <c r="G5" s="174"/>
+      <c r="H5" s="175"/>
+      <c r="J5" s="179" t="s">
         <v>3166</v>
       </c>
-      <c r="K5" s="191"/>
-      <c r="L5" s="191"/>
-      <c r="M5" s="191"/>
-      <c r="N5" s="191"/>
-      <c r="O5" s="191"/>
-      <c r="P5" s="192"/>
+      <c r="K5" s="180"/>
+      <c r="L5" s="180"/>
+      <c r="M5" s="180"/>
+      <c r="N5" s="180"/>
+      <c r="O5" s="180"/>
+      <c r="P5" s="181"/>
     </row>
     <row r="6" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="187"/>
-      <c r="B6" s="188"/>
-      <c r="C6" s="188"/>
-      <c r="D6" s="188"/>
-      <c r="E6" s="188"/>
-      <c r="F6" s="188"/>
-      <c r="G6" s="188"/>
-      <c r="H6" s="189"/>
-      <c r="J6" s="193"/>
-      <c r="K6" s="194"/>
-      <c r="L6" s="194"/>
-      <c r="M6" s="194"/>
-      <c r="N6" s="194"/>
-      <c r="O6" s="194"/>
-      <c r="P6" s="195"/>
+      <c r="A6" s="176"/>
+      <c r="B6" s="177"/>
+      <c r="C6" s="177"/>
+      <c r="D6" s="177"/>
+      <c r="E6" s="177"/>
+      <c r="F6" s="177"/>
+      <c r="G6" s="177"/>
+      <c r="H6" s="178"/>
+      <c r="J6" s="182"/>
+      <c r="K6" s="183"/>
+      <c r="L6" s="183"/>
+      <c r="M6" s="183"/>
+      <c r="N6" s="183"/>
+      <c r="O6" s="183"/>
+      <c r="P6" s="184"/>
       <c r="R6" s="123" t="s">
         <v>3167</v>
       </c>
@@ -41164,37 +41167,37 @@
       <c r="BI6" s="128" t="s">
         <v>3178</v>
       </c>
-      <c r="BK6" s="176" t="s">
+      <c r="BK6" s="165" t="s">
         <v>3179</v>
       </c>
-      <c r="BL6" s="177"/>
-      <c r="BM6" s="177"/>
-      <c r="BN6" s="177"/>
-      <c r="BO6" s="178"/>
-      <c r="BR6" s="176" t="str" cm="1">
+      <c r="BL6" s="166"/>
+      <c r="BM6" s="166"/>
+      <c r="BN6" s="166"/>
+      <c r="BO6" s="167"/>
+      <c r="BR6" s="165" t="str" cm="1">
         <f t="array" ref="BR6">INDEX(T,4,lang)</f>
         <v>Round of 16</v>
       </c>
-      <c r="BS6" s="177"/>
-      <c r="BT6" s="177"/>
-      <c r="BU6" s="177"/>
-      <c r="BV6" s="178"/>
-      <c r="BY6" s="176" t="str" cm="1">
+      <c r="BS6" s="166"/>
+      <c r="BT6" s="166"/>
+      <c r="BU6" s="166"/>
+      <c r="BV6" s="167"/>
+      <c r="BY6" s="165" t="str" cm="1">
         <f t="array" ref="BY6">INDEX(T,5,lang)</f>
         <v>Quarterfinals</v>
       </c>
-      <c r="BZ6" s="177"/>
-      <c r="CA6" s="177"/>
-      <c r="CB6" s="177"/>
-      <c r="CC6" s="178"/>
-      <c r="CF6" s="176" t="str" cm="1">
+      <c r="BZ6" s="166"/>
+      <c r="CA6" s="166"/>
+      <c r="CB6" s="166"/>
+      <c r="CC6" s="167"/>
+      <c r="CF6" s="165" t="str" cm="1">
         <f t="array" ref="CF6">INDEX(T,6,lang)</f>
         <v>Semi-Finals</v>
       </c>
-      <c r="CG6" s="177"/>
-      <c r="CH6" s="177"/>
-      <c r="CI6" s="177"/>
-      <c r="CJ6" s="178"/>
+      <c r="CG6" s="166"/>
+      <c r="CH6" s="166"/>
+      <c r="CI6" s="166"/>
+      <c r="CJ6" s="167"/>
     </row>
     <row r="7" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="11">
@@ -41271,26 +41274,26 @@
         <v>1</v>
       </c>
       <c r="AY7" s="126"/>
-      <c r="BK7" s="179"/>
-      <c r="BL7" s="180"/>
-      <c r="BM7" s="180"/>
-      <c r="BN7" s="180"/>
-      <c r="BO7" s="181"/>
-      <c r="BR7" s="179"/>
-      <c r="BS7" s="180"/>
-      <c r="BT7" s="180"/>
-      <c r="BU7" s="180"/>
-      <c r="BV7" s="181"/>
-      <c r="BY7" s="179"/>
-      <c r="BZ7" s="180"/>
-      <c r="CA7" s="180"/>
-      <c r="CB7" s="180"/>
-      <c r="CC7" s="181"/>
-      <c r="CF7" s="179"/>
-      <c r="CG7" s="180"/>
-      <c r="CH7" s="180"/>
-      <c r="CI7" s="180"/>
-      <c r="CJ7" s="181"/>
+      <c r="BK7" s="168"/>
+      <c r="BL7" s="169"/>
+      <c r="BM7" s="169"/>
+      <c r="BN7" s="169"/>
+      <c r="BO7" s="170"/>
+      <c r="BR7" s="168"/>
+      <c r="BS7" s="169"/>
+      <c r="BT7" s="169"/>
+      <c r="BU7" s="169"/>
+      <c r="BV7" s="170"/>
+      <c r="BY7" s="168"/>
+      <c r="BZ7" s="169"/>
+      <c r="CA7" s="169"/>
+      <c r="CB7" s="169"/>
+      <c r="CC7" s="170"/>
+      <c r="CF7" s="168"/>
+      <c r="CG7" s="169"/>
+      <c r="CH7" s="169"/>
+      <c r="CI7" s="169"/>
+      <c r="CJ7" s="170"/>
     </row>
     <row r="8" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A8" s="16">
@@ -42026,7 +42029,7 @@
         <f>BH10/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK10" s="173">
+      <c r="BK10" s="163">
         <v>74</v>
       </c>
       <c r="BL10" s="24" t="str">
@@ -42289,7 +42292,7 @@
         <f>BH11/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK11" s="174"/>
+      <c r="BK11" s="164"/>
       <c r="BL11" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!G3,AK80:AS91,9,FALSE),"3rd Group A/B/C/D/F")</f>
         <v>3rd Group A/B/C/D/F</v>
@@ -42527,7 +42530,7 @@
       <c r="BO12" s="21"/>
       <c r="BP12" s="114"/>
       <c r="BQ12" s="112"/>
-      <c r="BR12" s="173">
+      <c r="BR12" s="163">
         <v>89</v>
       </c>
       <c r="BS12" s="24" t="str">
@@ -42648,7 +42651,7 @@
         <v>46203.875</v>
       </c>
       <c r="BQ13" s="115"/>
-      <c r="BR13" s="174"/>
+      <c r="BR13" s="164"/>
       <c r="BS13" s="26" t="str">
         <f>IF(BP14&gt;BP15,BL14,IF(BP14&lt;BP15,BL15,""))</f>
         <v/>
@@ -42906,7 +42909,7 @@
         <f>BH14/BH18</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK14" s="173">
+      <c r="BK14" s="163">
         <v>77</v>
       </c>
       <c r="BL14" s="24" t="str">
@@ -42967,8 +42970,12 @@
         <f>AE34</f>
         <v>Ivory Coast</v>
       </c>
-      <c r="F15" s="19"/>
-      <c r="G15" s="20"/>
+      <c r="F15" s="19">
+        <v>1</v>
+      </c>
+      <c r="G15" s="20">
+        <v>0</v>
+      </c>
       <c r="H15" s="80" t="str">
         <f>AE35</f>
         <v>Ecuador</v>
@@ -43007,11 +43014,11 @@
       </c>
       <c r="S15" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Ivory Coast_win</v>
       </c>
       <c r="T15" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Ecuador_lose</v>
       </c>
       <c r="U15" s="123">
         <f t="shared" si="8"/>
@@ -43041,9 +43048,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB15" s="123" t="str">
+      <c r="AB15" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD15" s="123">
         <f>COUNTIF(AR14:AR17,CONCATENATE("&gt;=",AR15))</f>
@@ -43169,7 +43176,7 @@
         <f>BH15/BH18</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK15" s="174"/>
+      <c r="BK15" s="164"/>
       <c r="BL15" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!I3,AK80:AS91,9,FALSE),"3rd Group C/D/F/G/H")</f>
         <v>3rd Group C/D/F/G/H</v>
@@ -43443,7 +43450,7 @@
       <c r="BV16" s="21"/>
       <c r="BW16" s="114"/>
       <c r="BX16" s="112"/>
-      <c r="BY16" s="173">
+      <c r="BY16" s="163">
         <v>97</v>
       </c>
       <c r="BZ16" s="24" t="str">
@@ -43705,7 +43712,7 @@
       <c r="BV17" s="21"/>
       <c r="BW17" s="114"/>
       <c r="BX17" s="115"/>
-      <c r="BY17" s="174"/>
+      <c r="BY17" s="164"/>
       <c r="BZ17" s="26" t="str">
         <f>IF(BW20&gt;BW21,BS20,IF(BW20&lt;BW21,BS21,""))</f>
         <v/>
@@ -43743,8 +43750,12 @@
         <f>AE40</f>
         <v>Sweden</v>
       </c>
-      <c r="F18" s="19"/>
-      <c r="G18" s="20"/>
+      <c r="F18" s="19">
+        <v>5</v>
+      </c>
+      <c r="G18" s="20">
+        <v>1</v>
+      </c>
       <c r="H18" s="80" t="str">
         <f>AE41</f>
         <v>Tunisia</v>
@@ -43783,11 +43794,11 @@
       </c>
       <c r="S18" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Sweden_win</v>
       </c>
       <c r="T18" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Tunisia_lose</v>
       </c>
       <c r="U18" s="123">
         <f t="shared" si="8"/>
@@ -43817,9 +43828,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB18" s="123" t="str">
+      <c r="AB18" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AF18" s="123">
         <f t="shared" ref="AF18:AH18" si="13">MAX(AF14:AF17)-MIN(AF14:AF17)+1</f>
@@ -43905,7 +43916,7 @@
         <f>MAX(BH14:BH17)+1</f>
         <v>102</v>
       </c>
-      <c r="BK18" s="173">
+      <c r="BK18" s="163">
         <v>73</v>
       </c>
       <c r="BL18" s="24" t="str">
@@ -43959,8 +43970,12 @@
         <f>AE52</f>
         <v>Saudi Arabia</v>
       </c>
-      <c r="F19" s="19"/>
-      <c r="G19" s="20"/>
+      <c r="F19" s="19">
+        <v>1</v>
+      </c>
+      <c r="G19" s="20">
+        <v>1</v>
+      </c>
       <c r="H19" s="80" t="str">
         <f>AE53</f>
         <v>Uruguay</v>
@@ -43971,45 +43986,45 @@
       </c>
       <c r="S19" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Saudi Arabia_draw</v>
       </c>
       <c r="T19" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Uruguay_draw</v>
       </c>
       <c r="U19" s="123">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="123">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19" s="123">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" s="123">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19" s="123">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z19" s="123">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA19" s="123">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB19" s="123" t="str">
+      <c r="AB19" s="123">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="BK19" s="174"/>
+        <v>0</v>
+      </c>
+      <c r="BK19" s="164"/>
       <c r="BL19" s="26" t="str">
         <f>AS15</f>
         <v>2B</v>
@@ -44074,8 +44089,12 @@
         <f>AE50</f>
         <v>Spain</v>
       </c>
-      <c r="F20" s="19"/>
-      <c r="G20" s="20"/>
+      <c r="F20" s="19">
+        <v>0</v>
+      </c>
+      <c r="G20" s="20">
+        <v>0</v>
+      </c>
       <c r="H20" s="80" t="str">
         <f>AE51</f>
         <v>Cape Verde</v>
@@ -44114,15 +44133,15 @@
       </c>
       <c r="S20" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Spain_draw</v>
       </c>
       <c r="T20" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Cape Verde_draw</v>
       </c>
       <c r="U20" s="123">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="123">
         <f t="shared" si="3"/>
@@ -44134,7 +44153,7 @@
       </c>
       <c r="X20" s="123">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y20" s="123">
         <f t="shared" si="10"/>
@@ -44148,9 +44167,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB20" s="123" t="str">
+      <c r="AB20" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AD20" s="123">
         <f>COUNTIF(AR20:AR23,CONCATENATE("&gt;=",AR20))</f>
@@ -44283,7 +44302,7 @@
       <c r="BO20" s="21"/>
       <c r="BP20" s="114"/>
       <c r="BQ20" s="112"/>
-      <c r="BR20" s="173">
+      <c r="BR20" s="163">
         <v>90</v>
       </c>
       <c r="BS20" s="24" t="str">
@@ -44337,8 +44356,12 @@
         <f>AE46</f>
         <v>Iran</v>
       </c>
-      <c r="F21" s="19"/>
-      <c r="G21" s="20"/>
+      <c r="F21" s="19">
+        <v>2</v>
+      </c>
+      <c r="G21" s="20">
+        <v>2</v>
+      </c>
       <c r="H21" s="80" t="str">
         <f>AE47</f>
         <v>New Zealand</v>
@@ -44377,43 +44400,43 @@
       </c>
       <c r="S21" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Iran_draw</v>
       </c>
       <c r="T21" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>New Zealand_draw</v>
       </c>
       <c r="U21" s="123">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="123">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W21" s="123">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X21" s="123">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y21" s="123">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z21" s="123">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA21" s="123">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB21" s="123" t="str">
+      <c r="AB21" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AD21" s="123">
         <f>COUNTIF(AR20:AR23,CONCATENATE("&gt;=",AR21))</f>
@@ -44552,7 +44575,7 @@
         <v>46203.041666666672</v>
       </c>
       <c r="BQ21" s="115"/>
-      <c r="BR21" s="174"/>
+      <c r="BR21" s="164"/>
       <c r="BS21" s="26" t="str">
         <f>IF(BP22&gt;BP23,BL22,IF(BP22&lt;BP23,BL23,""))</f>
         <v/>
@@ -44604,8 +44627,12 @@
         <f>AE44</f>
         <v>Belgium</v>
       </c>
-      <c r="F22" s="19"/>
-      <c r="G22" s="20"/>
+      <c r="F22" s="19">
+        <v>1</v>
+      </c>
+      <c r="G22" s="20">
+        <v>1</v>
+      </c>
       <c r="H22" s="80" t="str">
         <f>AE45</f>
         <v>Egypt</v>
@@ -44644,43 +44671,43 @@
       </c>
       <c r="S22" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Belgium_draw</v>
       </c>
       <c r="T22" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Egypt_draw</v>
       </c>
       <c r="U22" s="123">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="123">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W22" s="123">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22" s="123">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y22" s="123">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z22" s="123">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA22" s="123">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB22" s="123" t="str">
+      <c r="AB22" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AD22" s="123">
         <f>COUNTIF(AR20:AR23,CONCATENATE("&gt;=",AR22))</f>
@@ -44802,7 +44829,7 @@
         <f>BH22/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK22" s="173">
+      <c r="BK22" s="163">
         <v>75</v>
       </c>
       <c r="BL22" s="24" t="str">
@@ -45062,7 +45089,7 @@
         <f>BH23/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK23" s="174"/>
+      <c r="BK23" s="164"/>
       <c r="BL23" s="26" t="str">
         <f>AS21</f>
         <v>2C</v>
@@ -45089,7 +45116,7 @@
       <c r="CC23" s="21"/>
       <c r="CD23" s="114"/>
       <c r="CE23" s="112"/>
-      <c r="CF23" s="173">
+      <c r="CF23" s="163">
         <v>101</v>
       </c>
       <c r="CG23" s="24" t="str">
@@ -45306,7 +45333,7 @@
       <c r="CC24" s="21"/>
       <c r="CD24" s="114"/>
       <c r="CE24" s="115"/>
-      <c r="CF24" s="174"/>
+      <c r="CF24" s="164"/>
       <c r="CG24" s="26" t="str">
         <f>IF(CD32&gt;CD33,BZ32,IF(CD32&lt;CD33,BZ33,""))</f>
         <v/>
@@ -45651,7 +45678,7 @@
         <f>BH26/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK26" s="173">
+      <c r="BK26" s="163">
         <v>83</v>
       </c>
       <c r="BL26" s="24" t="str">
@@ -45915,7 +45942,7 @@
         <f>BH27/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK27" s="174"/>
+      <c r="BK27" s="164"/>
       <c r="BL27" s="26" t="str">
         <f>AS75</f>
         <v>2L</v>
@@ -46186,7 +46213,7 @@
       <c r="BO28" s="21"/>
       <c r="BP28" s="114"/>
       <c r="BQ28" s="112"/>
-      <c r="BR28" s="173">
+      <c r="BR28" s="163">
         <v>93</v>
       </c>
       <c r="BS28" s="24" t="str">
@@ -46447,7 +46474,7 @@
         <v>46205.791666666672</v>
       </c>
       <c r="BQ29" s="115"/>
-      <c r="BR29" s="174"/>
+      <c r="BR29" s="164"/>
       <c r="BS29" s="26" t="str">
         <f>IF(BP30&gt;BP31,BL30,IF(BP30&lt;BP31,BL31,""))</f>
         <v/>
@@ -46657,7 +46684,7 @@
         <f>MAX(BH26:BH29)+1</f>
         <v>1</v>
       </c>
-      <c r="BK30" s="173">
+      <c r="BK30" s="163">
         <v>84</v>
       </c>
       <c r="BL30" s="24" t="str">
@@ -46764,7 +46791,7 @@
         <f>IF(OR(F31="",G31=""),"",IF(F31&gt;G31,1,IF(F31&lt;G31,-1,0)))</f>
         <v/>
       </c>
-      <c r="BK31" s="174"/>
+      <c r="BK31" s="164"/>
       <c r="BL31" s="26" t="str">
         <f>AS63</f>
         <v>2J</v>
@@ -47036,7 +47063,7 @@
       <c r="BV32" s="21"/>
       <c r="BW32" s="114"/>
       <c r="BX32" s="112"/>
-      <c r="BY32" s="173">
+      <c r="BY32" s="163">
         <v>98</v>
       </c>
       <c r="BZ32" s="24" t="str">
@@ -47296,7 +47323,7 @@
       <c r="BV33" s="21"/>
       <c r="BW33" s="114"/>
       <c r="BX33" s="115"/>
-      <c r="BY33" s="174"/>
+      <c r="BY33" s="164"/>
       <c r="BZ33" s="26" t="str">
         <f>IF(BW36&gt;BW37,BS36,IF(BW36&lt;BW37,BS37,""))</f>
         <v/>
@@ -47311,14 +47338,14 @@
       <c r="CE33" s="112"/>
       <c r="CK33" s="114"/>
       <c r="CL33" s="112"/>
-      <c r="CM33" s="176" t="str" cm="1">
+      <c r="CM33" s="165" t="str" cm="1">
         <f t="array" ref="CM33">INDEX(T,8,lang)</f>
         <v>Final</v>
       </c>
-      <c r="CN33" s="177"/>
-      <c r="CO33" s="177"/>
-      <c r="CP33" s="177"/>
-      <c r="CQ33" s="178"/>
+      <c r="CN33" s="166"/>
+      <c r="CO33" s="166"/>
+      <c r="CP33" s="166"/>
+      <c r="CQ33" s="167"/>
     </row>
     <row r="34" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A34" s="16">
@@ -47348,15 +47375,15 @@
       </c>
       <c r="J34" s="33" t="str">
         <f>VLOOKUP(2,AD32:AN35,2,FALSE)</f>
-        <v>Ecuador</v>
+        <v>Ivory Coast</v>
       </c>
       <c r="K34" s="23">
         <f>L34+M34+N34</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="23">
         <f>VLOOKUP(2,AD32:AN35,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="23">
         <f>VLOOKUP(2,AD32:AN35,4,FALSE)</f>
@@ -47368,11 +47395,11 @@
       </c>
       <c r="O34" s="23" t="str">
         <f>VLOOKUP(2,AD32:AN35,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD32:AN35,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 0</v>
       </c>
       <c r="P34" s="34">
         <f>L34*3+M34</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R34" s="123">
         <f>DATE(2026,6,18)+TIME(14,0,0)+gmt_delta</f>
@@ -47420,7 +47447,7 @@
       </c>
       <c r="AD34" s="123">
         <f>COUNTIF(AR32:AR35,CONCATENATE("&gt;=",AR34))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE34" s="124" t="str">
         <f>VLOOKUP("Ivory Coast",T,lang,FALSE)</f>
@@ -47428,7 +47455,7 @@
       </c>
       <c r="AF34" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE34 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG34" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE34 &amp; "_draw")</f>
@@ -47440,7 +47467,7 @@
       </c>
       <c r="AI34" s="123">
         <f>SUMIF($E$7:$E$78,$AE34,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE34,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ34" s="123">
         <f>SUMIF($E$7:$E$78,$AE34,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE34,$F$7:$F$78)</f>
@@ -47448,23 +47475,23 @@
       </c>
       <c r="AL34" s="123">
         <f>AI34-AJ34</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM34" s="123">
         <f>AL34-AL36</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AN34" s="123">
         <f>AF34*3+AG34</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO34" s="123">
         <f>AN34/AN36*10+BA34</f>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AP34" s="123">
         <f>AO34*10000000+BI34*100+AM34/AM36*10+AI34/AI36*1++IF(AQ34=0,ROW(),AQ34)/2000000</f>
-        <v>4.616151105384616</v>
+        <v>75000005.510381877</v>
       </c>
       <c r="AQ34" s="126">
         <f>VLOOKUP(AE34,db_fifarank,2,FALSE)</f>
@@ -47472,7 +47499,7 @@
       </c>
       <c r="AR34" s="125">
         <f>AP34/AP36</f>
-        <v>6.1548672290480187E-8</v>
+        <v>0.9999999253833104</v>
       </c>
       <c r="AT34" s="126" cm="1">
         <f t="array" ref="AT34">SUMPRODUCT(($S$7:$S$78=AE34&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE34&amp;"_win")*($U$7:$U$78))</f>
@@ -47538,7 +47565,7 @@
         <f>BH34/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK34" s="173">
+      <c r="BK34" s="163">
         <v>81</v>
       </c>
       <c r="BL34" s="24" t="str">
@@ -47569,11 +47596,11 @@
       <c r="CE34" s="112"/>
       <c r="CK34" s="114"/>
       <c r="CL34" s="112"/>
-      <c r="CM34" s="179"/>
-      <c r="CN34" s="180"/>
-      <c r="CO34" s="180"/>
-      <c r="CP34" s="180"/>
-      <c r="CQ34" s="181"/>
+      <c r="CM34" s="168"/>
+      <c r="CN34" s="169"/>
+      <c r="CO34" s="169"/>
+      <c r="CP34" s="169"/>
+      <c r="CQ34" s="170"/>
     </row>
     <row r="35" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A35" s="16">
@@ -47603,11 +47630,11 @@
       </c>
       <c r="J35" s="33" t="str">
         <f>VLOOKUP(3,AD32:AN35,2,FALSE)</f>
-        <v>Ivory Coast</v>
+        <v>Ecuador</v>
       </c>
       <c r="K35" s="23">
         <f>L35+M35+N35</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="23">
         <f>VLOOKUP(3,AD32:AN35,3,FALSE)</f>
@@ -47619,11 +47646,11 @@
       </c>
       <c r="N35" s="23">
         <f>VLOOKUP(3,AD32:AN35,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O35" s="23" t="str">
         <f>VLOOKUP(3,AD32:AN35,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD32:AN35,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>0 - 1</v>
       </c>
       <c r="P35" s="34">
         <f>L35*3+M35</f>
@@ -47675,7 +47702,7 @@
       </c>
       <c r="AD35" s="123">
         <f>COUNTIF(AR32:AR35,CONCATENATE("&gt;=",AR35))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE35" s="124" t="str">
         <f>VLOOKUP("Ecuador",T,lang,FALSE)</f>
@@ -47691,7 +47718,7 @@
       </c>
       <c r="AH35" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE35 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI35" s="123">
         <f>SUMIF($E$7:$E$78,$AE35,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE35,$G$7:$G$78)</f>
@@ -47699,15 +47726,15 @@
       </c>
       <c r="AJ35" s="123">
         <f>SUMIF($E$7:$E$78,$AE35,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE35,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL35" s="123">
         <f>AI35-AJ35</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM35" s="123">
         <f>AL35-AL36</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN35" s="123">
         <f>AF35*3+AG35</f>
@@ -47719,7 +47746,7 @@
       </c>
       <c r="AP35" s="123">
         <f>AO35*10000000+BI35*100+AM35/AM36*10+AI35/AI36*1++IF(AQ35=0,ROW(),AQ35)/2000000</f>
-        <v>4.6161820053846156</v>
+        <v>3.846951236153846</v>
       </c>
       <c r="AQ35" s="126">
         <f>VLOOKUP(AE35,db_fifarank,2,FALSE)</f>
@@ -47727,7 +47754,7 @@
       </c>
       <c r="AR35" s="125">
         <f>AP35/AP36</f>
-        <v>6.154908429041916E-8</v>
+        <v>5.1292675552864665E-8</v>
       </c>
       <c r="AT35" s="126" cm="1">
         <f t="array" ref="AT35">SUMPRODUCT(($S$7:$S$78=AE35&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE35&amp;"_win")*($U$7:$U$78))</f>
@@ -47793,7 +47820,7 @@
         <f>BH35/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK35" s="174"/>
+      <c r="BK35" s="164"/>
       <c r="BL35" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!F3,AK80:AS91,9,FALSE),"3rd Group B/E/F/I/J")</f>
         <v>3rd Group B/E/F/I/J</v>
@@ -48018,7 +48045,7 @@
       <c r="BO36" s="21"/>
       <c r="BP36" s="114"/>
       <c r="BQ36" s="112"/>
-      <c r="BR36" s="173">
+      <c r="BR36" s="163">
         <v>94</v>
       </c>
       <c r="BS36" s="24" t="str">
@@ -48138,7 +48165,7 @@
         <v>46204.833333333336</v>
       </c>
       <c r="BQ37" s="115"/>
-      <c r="BR37" s="174"/>
+      <c r="BR37" s="164"/>
       <c r="BS37" s="26" t="str">
         <f>IF(BP38&gt;BP39,BL38,IF(BP38&lt;BP39,BL39,""))</f>
         <v/>
@@ -48165,7 +48192,7 @@
       <c r="CJ37" s="21"/>
       <c r="CK37" s="114"/>
       <c r="CL37" s="112"/>
-      <c r="CM37" s="173">
+      <c r="CM37" s="163">
         <v>104</v>
       </c>
       <c r="CN37" s="24" t="str">
@@ -48280,7 +48307,7 @@
       </c>
       <c r="AD38" s="123">
         <f>COUNTIF(AR38:AR41,CONCATENATE("&gt;=",AR38))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE38" s="124" t="str">
         <f>VLOOKUP("Netherlands",T,lang,FALSE)</f>
@@ -48312,7 +48339,7 @@
       </c>
       <c r="AM38" s="123">
         <f>AL38-AL42</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN38" s="123">
         <f>AF38*3+AG38</f>
@@ -48320,11 +48347,11 @@
       </c>
       <c r="AO38" s="123">
         <f>AN38/AN42*10+BA38</f>
-        <v>5.9806451612903224</v>
+        <v>3.4806451612903224</v>
       </c>
       <c r="AP38" s="123">
         <f>AO38*10000000+BI38*100+AM38/AM42*10+AI38/AI42*1++IF(AQ38=0,ROW(),AQ38)/2000000</f>
-        <v>59806550.344964951</v>
+        <v>34806554.456076071</v>
       </c>
       <c r="AQ38" s="126">
         <f>VLOOKUP(AE38,db_fifarank,2,FALSE)</f>
@@ -48332,7 +48359,7 @@
       </c>
       <c r="AR38" s="125">
         <f>AP38/AP42</f>
-        <v>0.99999998327942374</v>
+        <v>0.46408732639569511</v>
       </c>
       <c r="AS38" s="125" t="str">
         <f>IF(SUM(AF38:AH41)=12,J39,"1F")</f>
@@ -48402,7 +48429,7 @@
         <f>BH38/BH42</f>
         <v>0.98064516129032253</v>
       </c>
-      <c r="BK38" s="173">
+      <c r="BK38" s="163">
         <v>82</v>
       </c>
       <c r="BL38" s="24" t="str">
@@ -48432,7 +48459,7 @@
       <c r="CI38" s="21"/>
       <c r="CJ38" s="21"/>
       <c r="CL38" s="115"/>
-      <c r="CM38" s="174"/>
+      <c r="CM38" s="164"/>
       <c r="CN38" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG55,IF(CK55&lt;CK56,CG56,""))</f>
         <v/>
@@ -48473,7 +48500,7 @@
       </c>
       <c r="J39" s="30" t="str">
         <f>VLOOKUP(1,AD38:AN41,2,FALSE)</f>
-        <v>Netherlands</v>
+        <v>Sweden</v>
       </c>
       <c r="K39" s="31">
         <f>L39+M39+N39</f>
@@ -48481,11 +48508,11 @@
       </c>
       <c r="L39" s="31">
         <f>VLOOKUP(1,AD38:AN41,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" s="31">
         <f>VLOOKUP(1,AD38:AN41,4,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N39" s="31">
         <f>VLOOKUP(1,AD38:AN41,5,FALSE)</f>
@@ -48493,11 +48520,11 @@
       </c>
       <c r="O39" s="31" t="str">
         <f>VLOOKUP(1,AD38:AN41,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD38:AN41,7,FALSE)</f>
-        <v>2 - 2</v>
+        <v>5 - 1</v>
       </c>
       <c r="P39" s="32">
         <f>L39*3+M39</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R39" s="123">
         <f>DATE(2026,6,20)+TIME(9,0,0)+gmt_delta</f>
@@ -48545,7 +48572,7 @@
       </c>
       <c r="AD39" s="123">
         <f>COUNTIF(AR38:AR41,CONCATENATE("&gt;=",AR39))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE39" s="124" t="str">
         <f>VLOOKUP("Japan",T,lang,FALSE)</f>
@@ -48577,7 +48604,7 @@
       </c>
       <c r="AM39" s="123">
         <f>AL39-AL42</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN39" s="123">
         <f>AF39*3+AG39</f>
@@ -48585,11 +48612,11 @@
       </c>
       <c r="AO39" s="123">
         <f>AN39/AN42*10+BA39</f>
-        <v>5.9806451612903224</v>
+        <v>3.4806451612903224</v>
       </c>
       <c r="AP39" s="123">
         <f>AO39*10000000+BI39*100+AM39/AM42*10+AI39/AI42*1++IF(AQ39=0,ROW(),AQ39)/2000000</f>
-        <v>59806550.344916232</v>
+        <v>34806554.456027351</v>
       </c>
       <c r="AQ39" s="126">
         <f>VLOOKUP(AE39,db_fifarank,2,FALSE)</f>
@@ -48597,7 +48624,7 @@
       </c>
       <c r="AR39" s="125">
         <f>AP39/AP42</f>
-        <v>0.99999998327860917</v>
+        <v>0.46408732639504552</v>
       </c>
       <c r="AS39" s="125" t="str">
         <f>IF(SUM(AF38:AH41)=12,J40,"2F")</f>
@@ -48667,7 +48694,7 @@
         <f>BH39/BH42</f>
         <v>0.98064516129032253</v>
       </c>
-      <c r="BK39" s="174"/>
+      <c r="BK39" s="164"/>
       <c r="BL39" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!H3,AK80:AS91,9,FALSE),"3rd Group A/E/H/I/J")</f>
         <v>3rd Group A/E/H/I/J</v>
@@ -48728,7 +48755,7 @@
       </c>
       <c r="J40" s="33" t="str">
         <f>VLOOKUP(2,AD38:AN41,2,FALSE)</f>
-        <v>Japan</v>
+        <v>Netherlands</v>
       </c>
       <c r="K40" s="23">
         <f>L40+M40+N40</f>
@@ -48800,7 +48827,7 @@
       </c>
       <c r="AD40" s="123">
         <f>COUNTIF(AR38:AR41,CONCATENATE("&gt;=",AR40))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE40" s="124" t="str">
         <f>VLOOKUP("Sweden",T,lang,FALSE)</f>
@@ -48808,7 +48835,7 @@
       </c>
       <c r="AF40" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE40 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG40" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE40 &amp; "_draw")</f>
@@ -48820,31 +48847,31 @@
       </c>
       <c r="AI40" s="123">
         <f>SUMIF($E$7:$E$78,$AE40,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE40,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ40" s="123">
         <f>SUMIF($E$7:$E$78,$AE40,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE40,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL40" s="123">
         <f>AI40-AJ40</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AM40" s="123">
         <f>AL40-AL42</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AN40" s="123">
         <f>AF40*3+AG40</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO40" s="123">
         <f>AN40/AN42*10+BA40</f>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AP40" s="123">
         <f>AO40*10000000+BI40*100+AM40/AM42*10+AI40/AI42*1++IF(AQ40=0,ROW(),AQ40)/2000000</f>
-        <v>7.5738499999999996E-4</v>
+        <v>75000009.722979605</v>
       </c>
       <c r="AQ40" s="126">
         <f>VLOOKUP(AE40,db_fifarank,2,FALSE)</f>
@@ -48852,7 +48879,7 @@
       </c>
       <c r="AR40" s="125">
         <f>AP40/AP42</f>
-        <v>1.2663913617613456E-11</v>
+        <v>0.99999998666666856</v>
       </c>
       <c r="AT40" s="126" cm="1">
         <f t="array" ref="AT40">SUMPRODUCT(($S$7:$S$78=AE40&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE40&amp;"_win")*($U$7:$U$78))</f>
@@ -48949,11 +48976,11 @@
       </c>
       <c r="J41" s="33" t="str">
         <f>VLOOKUP(3,AD38:AN41,2,FALSE)</f>
-        <v>Sweden</v>
+        <v>Japan</v>
       </c>
       <c r="K41" s="23">
         <f>L41+M41+N41</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="23">
         <f>VLOOKUP(3,AD38:AN41,3,FALSE)</f>
@@ -48961,7 +48988,7 @@
       </c>
       <c r="M41" s="23">
         <f>VLOOKUP(3,AD38:AN41,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N41" s="23">
         <f>VLOOKUP(3,AD38:AN41,5,FALSE)</f>
@@ -48969,11 +48996,11 @@
       </c>
       <c r="O41" s="23" t="str">
         <f>VLOOKUP(3,AD38:AN41,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD38:AN41,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>2 - 2</v>
       </c>
       <c r="P41" s="34">
         <f>L41*3+M41</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" s="123">
         <f>DATE(2026,6,20)+TIME(6,0,0)+gmt_delta</f>
@@ -49037,19 +49064,19 @@
       </c>
       <c r="AH41" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE41 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI41" s="123">
         <f>SUMIF($E$7:$E$78,$AE41,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE41,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ41" s="123">
         <f>SUMIF($E$7:$E$78,$AE41,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE41,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL41" s="123">
         <f>AI41-AJ41</f>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AM41" s="123">
         <f>AL41-AL42</f>
@@ -49065,7 +49092,7 @@
       </c>
       <c r="AP41" s="123">
         <f>AO41*10000000+BI41*100+AM41/AM42*10+AI41/AI42*1++IF(AQ41=0,ROW(),AQ41)/2000000</f>
-        <v>7.4152499999999993E-4</v>
+        <v>0.16740819166666665</v>
       </c>
       <c r="AQ41" s="126">
         <f>VLOOKUP(AE41,db_fifarank,2,FALSE)</f>
@@ -49073,7 +49100,7 @@
       </c>
       <c r="AR41" s="125">
         <f>AP41/AP42</f>
-        <v>1.2398725278822286E-11</v>
+        <v>2.2321089030907787E-9</v>
       </c>
       <c r="AT41" s="126" cm="1">
         <f t="array" ref="AT41">SUMPRODUCT(($S$7:$S$78=AE41&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE41&amp;"_win")*($U$7:$U$78))</f>
@@ -49193,7 +49220,7 @@
       </c>
       <c r="K42" s="36">
         <f>L42+M42+N42</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="36">
         <f>VLOOKUP(4,AD38:AN41,3,FALSE)</f>
@@ -49205,11 +49232,11 @@
       </c>
       <c r="N42" s="36">
         <f>VLOOKUP(4,AD38:AN41,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O42" s="36" t="str">
         <f>VLOOKUP(4,AD38:AN41,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD38:AN41,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 5</v>
       </c>
       <c r="P42" s="37">
         <f>L42*3+M42</f>
@@ -49261,7 +49288,7 @@
       </c>
       <c r="AF42" s="123">
         <f t="shared" ref="AF42:AH42" si="18">MAX(AF38:AF41)-MIN(AF38:AF41)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG42" s="123">
         <f t="shared" si="18"/>
@@ -49269,31 +49296,31 @@
       </c>
       <c r="AH42" s="123">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI42" s="123">
         <f>MAX(AI38:AI41)+1</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AL42" s="123">
         <f>MIN(AL38:AL41)</f>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AM42" s="123">
         <f>MAX(AM38:AM41)+1</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AN42" s="123">
         <f>MAX(AN38:AN41)+1</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AO42" s="123">
         <f>MAX(AO38:AO41)+1</f>
-        <v>6.9806451612903224</v>
+        <v>8.5</v>
       </c>
       <c r="AP42" s="123">
         <f>MAX(AP38:AP41)+1</f>
-        <v>59806551.344964951</v>
+        <v>75000010.722979605</v>
       </c>
       <c r="AT42" s="126">
         <f>MAX(AT38:AT41)-MIN(AT38:AT41)+1</f>
@@ -49343,7 +49370,7 @@
         <f>MAX(BH38:BH41)+1</f>
         <v>51.666666666666664</v>
       </c>
-      <c r="BK42" s="173">
+      <c r="BK42" s="163">
         <v>76</v>
       </c>
       <c r="BL42" s="24" t="str">
@@ -49436,7 +49463,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK43" s="174"/>
+      <c r="BK43" s="164"/>
       <c r="BL43" s="26" t="str">
         <f>AS39</f>
         <v>2F</v>
@@ -49563,7 +49590,7 @@
       </c>
       <c r="AD44" s="123">
         <f>COUNTIF(AR44:AR47,CONCATENATE("&gt;=",AR44))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE44" s="124" t="str">
         <f>VLOOKUP("Belgium",T,lang,FALSE)</f>
@@ -49575,7 +49602,7 @@
       </c>
       <c r="AG44" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE44 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH44" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE44 &amp; "_lose")</f>
@@ -49583,11 +49610,11 @@
       </c>
       <c r="AI44" s="123">
         <f>SUMIF($E$7:$E$78,$AE44,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE44,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ44" s="123">
         <f>SUMIF($E$7:$E$78,$AE44,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE44,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL44" s="123">
         <f>AI44-AJ44</f>
@@ -49599,15 +49626,15 @@
       </c>
       <c r="AN44" s="123">
         <f>AF44*3+AG44</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO44" s="123">
         <f>AN44/AN48*10+BA44</f>
-        <v>0</v>
+        <v>5.9852941176470589</v>
       </c>
       <c r="AP44" s="123">
         <f>AO44*10000000+BI44*100+AM44/AM48*10+AI44/AI48*1++IF(AQ44=0,ROW(),AQ44)/2000000</f>
-        <v>8.6735499999999999E-4</v>
+        <v>59853040.040083036</v>
       </c>
       <c r="AQ44" s="126">
         <f>VLOOKUP(AE44,db_fifarank,2,FALSE)</f>
@@ -49615,7 +49642,7 @@
       </c>
       <c r="AR44" s="125">
         <f>AP44/AP48</f>
-        <v>8.6660334725374266E-4</v>
+        <v>0.9991816403290853</v>
       </c>
       <c r="AS44" s="125" t="str">
         <f>IF(SUM(AF44:AH47)=12,J45,"1G")</f>
@@ -49627,15 +49654,15 @@
       </c>
       <c r="AU44" s="126" cm="1">
         <f t="array" ref="AU44">SUMPRODUCT(($S$7:$S$78=AE44&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE44&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV44" s="126" cm="1">
         <f t="array" ref="AV44">SUMPRODUCT(($E$7:$E$78=AE44)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE44)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW44" s="126" cm="1">
         <f t="array" ref="AW44">SUMPRODUCT(($E$7:$E$78=AE44)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE44)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX44" s="126">
         <f>AV44-AW44</f>
@@ -49647,11 +49674,11 @@
       </c>
       <c r="AZ44" s="126">
         <f>AT44/AT48*1000+AU44/AU48*100+AY44/AY48*10+AV44/AV48</f>
-        <v>0</v>
+        <v>100.5</v>
       </c>
       <c r="BA44" s="126">
         <f>AZ44/AZ48</f>
-        <v>0</v>
+        <v>0.98529411764705888</v>
       </c>
       <c r="BB44" s="126" cm="1">
         <f t="array" ref="BB44">SUMPRODUCT(($S$7:$S$78=AE44&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE44&amp;"_win")*($X$7:$X$78))</f>
@@ -49659,15 +49686,15 @@
       </c>
       <c r="BC44" s="126" cm="1">
         <f t="array" ref="BC44">SUMPRODUCT(($S$7:$S$78=AE44&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE44&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD44" s="126" cm="1">
         <f t="array" ref="BD44">SUMPRODUCT(($E$7:$E$78=AE44)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE44)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE44" s="126" cm="1">
         <f t="array" ref="BE44">SUMPRODUCT(($E$7:$E$78=AE44)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE44)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF44" s="126">
         <f>BD44-BE44</f>
@@ -49679,11 +49706,11 @@
       </c>
       <c r="BH44" s="126">
         <f>BB44/BB48*1000+BC44/BC48*100+BG44/BG48*10+BD44/BD48</f>
-        <v>0</v>
+        <v>100.5</v>
       </c>
       <c r="BI44" s="126">
         <f>BH44/BH48</f>
-        <v>0</v>
+        <v>0.98529411764705888</v>
       </c>
       <c r="BK44" s="21"/>
       <c r="BL44" s="21"/>
@@ -49692,7 +49719,7 @@
       <c r="BO44" s="21"/>
       <c r="BP44" s="114"/>
       <c r="BQ44" s="112"/>
-      <c r="BR44" s="173">
+      <c r="BR44" s="163">
         <v>91</v>
       </c>
       <c r="BS44" s="24" t="str">
@@ -49707,14 +49734,14 @@
         <v/>
       </c>
       <c r="CK44" s="114"/>
-      <c r="CM44" s="176" t="str" cm="1">
+      <c r="CM44" s="165" t="str" cm="1">
         <f t="array" ref="CM44">INDEX(T,7,lang)</f>
         <v>Third-Place Play-Off</v>
       </c>
-      <c r="CN44" s="177"/>
-      <c r="CO44" s="177"/>
-      <c r="CP44" s="177"/>
-      <c r="CQ44" s="178"/>
+      <c r="CN44" s="166"/>
+      <c r="CO44" s="166"/>
+      <c r="CP44" s="166"/>
+      <c r="CQ44" s="167"/>
     </row>
     <row r="45" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="16">
@@ -49744,11 +49771,11 @@
       </c>
       <c r="J45" s="30" t="str">
         <f>VLOOKUP(1,AD44:AN47,2,FALSE)</f>
-        <v>Belgium</v>
+        <v>Iran</v>
       </c>
       <c r="K45" s="31">
         <f>L45+M45+N45</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="31">
         <f>VLOOKUP(1,AD44:AN47,3,FALSE)</f>
@@ -49756,7 +49783,7 @@
       </c>
       <c r="M45" s="31">
         <f>VLOOKUP(1,AD44:AN47,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N45" s="31">
         <f>VLOOKUP(1,AD44:AN47,5,FALSE)</f>
@@ -49764,11 +49791,11 @@
       </c>
       <c r="O45" s="31" t="str">
         <f>VLOOKUP(1,AD44:AN47,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD44:AN47,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>2 - 2</v>
       </c>
       <c r="P45" s="32">
         <f>L45*3+M45</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R45" s="123">
         <f>DATE(2026,6,21)+TIME(8,0,0)+gmt_delta</f>
@@ -49816,7 +49843,7 @@
       </c>
       <c r="AD45" s="123">
         <f>COUNTIF(AR44:AR47,CONCATENATE("&gt;=",AR45))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE45" s="124" t="str">
         <f>VLOOKUP("Egypt",T,lang,FALSE)</f>
@@ -49828,7 +49855,7 @@
       </c>
       <c r="AG45" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE45 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH45" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE45 &amp; "_lose")</f>
@@ -49836,11 +49863,11 @@
       </c>
       <c r="AI45" s="123">
         <f>SUMIF($E$7:$E$78,$AE45,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE45,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ45" s="123">
         <f>SUMIF($E$7:$E$78,$AE45,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE45,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL45" s="123">
         <f>AI45-AJ45</f>
@@ -49852,15 +49879,15 @@
       </c>
       <c r="AN45" s="123">
         <f>AF45*3+AG45</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO45" s="123">
         <f>AN45/AN48*10+BA45</f>
-        <v>0</v>
+        <v>5.9852941176470589</v>
       </c>
       <c r="AP45" s="123">
         <f>AO45*10000000+BI45*100+AM45/AM48*10+AI45/AI48*1++IF(AQ45=0,ROW(),AQ45)/2000000</f>
-        <v>7.8162000000000001E-4</v>
+        <v>59853040.039997302</v>
       </c>
       <c r="AQ45" s="126">
         <f>VLOOKUP(AE45,db_fifarank,2,FALSE)</f>
@@ -49868,7 +49895,7 @@
       </c>
       <c r="AR45" s="125">
         <f>AP45/AP48</f>
-        <v>7.809426454917195E-4</v>
+        <v>0.99918164032765411</v>
       </c>
       <c r="AS45" s="125" t="str">
         <f>IF(SUM(AF44:AH47)=12,J46,"2G")</f>
@@ -49880,15 +49907,15 @@
       </c>
       <c r="AU45" s="126" cm="1">
         <f t="array" ref="AU45">SUMPRODUCT(($S$7:$S$78=AE45&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE45&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV45" s="126" cm="1">
         <f t="array" ref="AV45">SUMPRODUCT(($E$7:$E$78=AE45)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE45)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW45" s="126" cm="1">
         <f t="array" ref="AW45">SUMPRODUCT(($E$7:$E$78=AE45)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE45)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX45" s="126">
         <f>AV45-AW45</f>
@@ -49900,11 +49927,11 @@
       </c>
       <c r="AZ45" s="126">
         <f>AT45/AT48*1000+AU45/AU48*100+AY45/AY48*10+AV45/AV48</f>
-        <v>0</v>
+        <v>100.5</v>
       </c>
       <c r="BA45" s="126">
         <f>AZ45/AZ48</f>
-        <v>0</v>
+        <v>0.98529411764705888</v>
       </c>
       <c r="BB45" s="126" cm="1">
         <f t="array" ref="BB45">SUMPRODUCT(($S$7:$S$78=AE45&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE45&amp;"_win")*($X$7:$X$78))</f>
@@ -49912,15 +49939,15 @@
       </c>
       <c r="BC45" s="126" cm="1">
         <f t="array" ref="BC45">SUMPRODUCT(($S$7:$S$78=AE45&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE45&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD45" s="126" cm="1">
         <f t="array" ref="BD45">SUMPRODUCT(($E$7:$E$78=AE45)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE45)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE45" s="126" cm="1">
         <f t="array" ref="BE45">SUMPRODUCT(($E$7:$E$78=AE45)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE45)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF45" s="126">
         <f>BD45-BE45</f>
@@ -49932,11 +49959,11 @@
       </c>
       <c r="BH45" s="126">
         <f>BB45/BB48*1000+BC45/BC48*100+BG45/BG48*10+BD45/BD48</f>
-        <v>0</v>
+        <v>100.5</v>
       </c>
       <c r="BI45" s="126">
         <f>BH45/BH48</f>
-        <v>0</v>
+        <v>0.98529411764705888</v>
       </c>
       <c r="BK45" s="21" t="str" cm="1">
         <f t="array" ref="BK45">INDEX(T,24+MONTH(BP45),lang) &amp; " " &amp; DAY(BP45) &amp; ", " &amp; YEAR(BP45) &amp; "   " &amp; (IF(HOUR(BP45)&lt;10,0,"")&amp;HOUR(BP45)) &amp; ":" &amp;  (IF(MINUTE(BP45)&lt;10,0,"")&amp;MINUTE(BP45))</f>
@@ -49951,7 +49978,7 @@
         <v>46203.708333333336</v>
       </c>
       <c r="BQ45" s="115"/>
-      <c r="BR45" s="174"/>
+      <c r="BR45" s="164"/>
       <c r="BS45" s="26" t="str">
         <f>IF(BP46&gt;BP47,BL46,IF(BP46&lt;BP47,BL47,""))</f>
         <v/>
@@ -49964,11 +49991,11 @@
         <v/>
       </c>
       <c r="CK45" s="114"/>
-      <c r="CM45" s="179"/>
-      <c r="CN45" s="180"/>
-      <c r="CO45" s="180"/>
-      <c r="CP45" s="180"/>
-      <c r="CQ45" s="181"/>
+      <c r="CM45" s="168"/>
+      <c r="CN45" s="169"/>
+      <c r="CO45" s="169"/>
+      <c r="CP45" s="169"/>
+      <c r="CQ45" s="170"/>
     </row>
     <row r="46" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A46" s="16">
@@ -49998,11 +50025,11 @@
       </c>
       <c r="J46" s="33" t="str">
         <f>VLOOKUP(2,AD44:AN47,2,FALSE)</f>
-        <v>Iran</v>
+        <v>New Zealand</v>
       </c>
       <c r="K46" s="23">
         <f>L46+M46+N46</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" s="23">
         <f>VLOOKUP(2,AD44:AN47,3,FALSE)</f>
@@ -50010,7 +50037,7 @@
       </c>
       <c r="M46" s="23">
         <f>VLOOKUP(2,AD44:AN47,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N46" s="23">
         <f>VLOOKUP(2,AD44:AN47,5,FALSE)</f>
@@ -50018,11 +50045,11 @@
       </c>
       <c r="O46" s="23" t="str">
         <f>VLOOKUP(2,AD44:AN47,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD44:AN47,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>2 - 2</v>
       </c>
       <c r="P46" s="34">
         <f>L46*3+M46</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R46" s="123">
         <f>DATE(2026,6,21)+TIME(14,0,0)+gmt_delta</f>
@@ -50070,7 +50097,7 @@
       </c>
       <c r="AD46" s="123">
         <f>COUNTIF(AR44:AR47,CONCATENATE("&gt;=",AR46))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE46" s="124" t="str">
         <f>VLOOKUP("Iran",T,lang,FALSE)</f>
@@ -50082,7 +50109,7 @@
       </c>
       <c r="AG46" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE46 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH46" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE46 &amp; "_lose")</f>
@@ -50090,11 +50117,11 @@
       </c>
       <c r="AI46" s="123">
         <f>SUMIF($E$7:$E$78,$AE46,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE46,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ46" s="123">
         <f>SUMIF($E$7:$E$78,$AE46,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE46,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL46" s="123">
         <f>AI46-AJ46</f>
@@ -50106,15 +50133,15 @@
       </c>
       <c r="AN46" s="123">
         <f>AF46*3+AG46</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO46" s="123">
         <f>AN46/AN48*10+BA46</f>
-        <v>0</v>
+        <v>5.9901960784313726</v>
       </c>
       <c r="AP46" s="123">
         <f>AO46*10000000+BI46*100+AM46/AM48*10+AI46/AI48*1++IF(AQ46=0,ROW(),AQ46)/2000000</f>
-        <v>8.0764999999999993E-4</v>
+        <v>59902060.47139588</v>
       </c>
       <c r="AQ46" s="126">
         <f>VLOOKUP(AE46,db_fifarank,2,FALSE)</f>
@@ -50122,7 +50149,7 @@
       </c>
       <c r="AR46" s="125">
         <f>AP46/AP48</f>
-        <v>8.0695008780659041E-4</v>
+        <v>0.99999998330608375</v>
       </c>
       <c r="AT46" s="126" cm="1">
         <f t="array" ref="AT46">SUMPRODUCT(($S$7:$S$78=AE46&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE46&amp;"_win")*($U$7:$U$78))</f>
@@ -50130,15 +50157,15 @@
       </c>
       <c r="AU46" s="126" cm="1">
         <f t="array" ref="AU46">SUMPRODUCT(($S$7:$S$78=AE46&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE46&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV46" s="126" cm="1">
         <f t="array" ref="AV46">SUMPRODUCT(($E$7:$E$78=AE46)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE46)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW46" s="126" cm="1">
         <f t="array" ref="AW46">SUMPRODUCT(($E$7:$E$78=AE46)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE46)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX46" s="126">
         <f>AV46-AW46</f>
@@ -50150,11 +50177,11 @@
       </c>
       <c r="AZ46" s="126">
         <f>AT46/AT48*1000+AU46/AU48*100+AY46/AY48*10+AV46/AV48</f>
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="BA46" s="126">
         <f>AZ46/AZ48</f>
-        <v>0</v>
+        <v>0.99019607843137258</v>
       </c>
       <c r="BB46" s="126" cm="1">
         <f t="array" ref="BB46">SUMPRODUCT(($S$7:$S$78=AE46&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE46&amp;"_win")*($X$7:$X$78))</f>
@@ -50162,15 +50189,15 @@
       </c>
       <c r="BC46" s="126" cm="1">
         <f t="array" ref="BC46">SUMPRODUCT(($S$7:$S$78=AE46&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE46&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD46" s="126" cm="1">
         <f t="array" ref="BD46">SUMPRODUCT(($E$7:$E$78=AE46)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE46)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BE46" s="126" cm="1">
         <f t="array" ref="BE46">SUMPRODUCT(($E$7:$E$78=AE46)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE46)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF46" s="126">
         <f>BD46-BE46</f>
@@ -50182,13 +50209,13 @@
       </c>
       <c r="BH46" s="126">
         <f>BB46/BB48*1000+BC46/BC48*100+BG46/BG48*10+BD46/BD48</f>
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="BI46" s="126">
         <f>BH46/BH48</f>
-        <v>0</v>
-      </c>
-      <c r="BK46" s="173">
+        <v>0.99019607843137258</v>
+      </c>
+      <c r="BK46" s="163">
         <v>78</v>
       </c>
       <c r="BL46" s="24" t="str">
@@ -50240,11 +50267,11 @@
       </c>
       <c r="J47" s="33" t="str">
         <f>VLOOKUP(3,AD44:AN47,2,FALSE)</f>
-        <v>Egypt</v>
+        <v>Belgium</v>
       </c>
       <c r="K47" s="23">
         <f>L47+M47+N47</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="23">
         <f>VLOOKUP(3,AD44:AN47,3,FALSE)</f>
@@ -50252,7 +50279,7 @@
       </c>
       <c r="M47" s="23">
         <f>VLOOKUP(3,AD44:AN47,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N47" s="23">
         <f>VLOOKUP(3,AD44:AN47,5,FALSE)</f>
@@ -50260,11 +50287,11 @@
       </c>
       <c r="O47" s="23" t="str">
         <f>VLOOKUP(3,AD44:AN47,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD44:AN47,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 1</v>
       </c>
       <c r="P47" s="34">
         <f>L47*3+M47</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R47" s="123">
         <f>DATE(2026,6,22)+TIME(13,0,0)+gmt_delta</f>
@@ -50312,7 +50339,7 @@
       </c>
       <c r="AD47" s="123">
         <f>COUNTIF(AR44:AR47,CONCATENATE("&gt;=",AR47))</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE47" s="124" t="str">
         <f>VLOOKUP("New Zealand",T,lang,FALSE)</f>
@@ -50324,7 +50351,7 @@
       </c>
       <c r="AG47" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE47 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH47" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE47 &amp; "_lose")</f>
@@ -50332,11 +50359,11 @@
       </c>
       <c r="AI47" s="123">
         <f>SUMIF($E$7:$E$78,$AE47,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE47,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ47" s="123">
         <f>SUMIF($E$7:$E$78,$AE47,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE47,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL47" s="123">
         <f>AI47-AJ47</f>
@@ -50348,15 +50375,15 @@
       </c>
       <c r="AN47" s="123">
         <f>AF47*3+AG47</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO47" s="123">
         <f>AN47/AN48*10+BA47</f>
-        <v>0</v>
+        <v>5.9901960784313726</v>
       </c>
       <c r="AP47" s="123">
         <f>AO47*10000000+BI47*100+AM47/AM48*10+AI47/AI48*1++IF(AQ47=0,ROW(),AQ47)/2000000</f>
-        <v>6.4078499999999994E-4</v>
+        <v>59902060.471229017</v>
       </c>
       <c r="AQ47" s="126">
         <f>VLOOKUP(AE47,db_fifarank,2,FALSE)</f>
@@ -50364,7 +50391,7 @@
       </c>
       <c r="AR47" s="125">
         <f>AP47/AP48</f>
-        <v>6.4022969357412996E-4</v>
+        <v>0.99999998330329809</v>
       </c>
       <c r="AT47" s="126" cm="1">
         <f t="array" ref="AT47">SUMPRODUCT(($S$7:$S$78=AE47&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE47&amp;"_win")*($U$7:$U$78))</f>
@@ -50372,15 +50399,15 @@
       </c>
       <c r="AU47" s="126" cm="1">
         <f t="array" ref="AU47">SUMPRODUCT(($S$7:$S$78=AE47&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE47&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV47" s="126" cm="1">
         <f t="array" ref="AV47">SUMPRODUCT(($E$7:$E$78=AE47)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE47)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW47" s="126" cm="1">
         <f t="array" ref="AW47">SUMPRODUCT(($E$7:$E$78=AE47)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE47)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX47" s="126">
         <f>AV47-AW47</f>
@@ -50392,11 +50419,11 @@
       </c>
       <c r="AZ47" s="126">
         <f>AT47/AT48*1000+AU47/AU48*100+AY47/AY48*10+AV47/AV48</f>
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="BA47" s="126">
         <f>AZ47/AZ48</f>
-        <v>0</v>
+        <v>0.99019607843137258</v>
       </c>
       <c r="BB47" s="126" cm="1">
         <f t="array" ref="BB47">SUMPRODUCT(($S$7:$S$78=AE47&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE47&amp;"_win")*($X$7:$X$78))</f>
@@ -50404,15 +50431,15 @@
       </c>
       <c r="BC47" s="126" cm="1">
         <f t="array" ref="BC47">SUMPRODUCT(($S$7:$S$78=AE47&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE47&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD47" s="126" cm="1">
         <f t="array" ref="BD47">SUMPRODUCT(($E$7:$E$78=AE47)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE47)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BE47" s="126" cm="1">
         <f t="array" ref="BE47">SUMPRODUCT(($E$7:$E$78=AE47)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE47)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF47" s="126">
         <f>BD47-BE47</f>
@@ -50424,13 +50451,13 @@
       </c>
       <c r="BH47" s="126">
         <f>BB47/BB48*1000+BC47/BC48*100+BG47/BG48*10+BD47/BD48</f>
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="BI47" s="126">
         <f>BH47/BH48</f>
-        <v>0</v>
-      </c>
-      <c r="BK47" s="174"/>
+        <v>0.99019607843137258</v>
+      </c>
+      <c r="BK47" s="164"/>
       <c r="BL47" s="26" t="str">
         <f>AS57</f>
         <v>2I</v>
@@ -50505,11 +50532,11 @@
       </c>
       <c r="J48" s="35" t="str">
         <f>VLOOKUP(4,AD44:AN47,2,FALSE)</f>
-        <v>New Zealand</v>
+        <v>Egypt</v>
       </c>
       <c r="K48" s="36">
         <f>L48+M48+N48</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="36">
         <f>VLOOKUP(4,AD44:AN47,3,FALSE)</f>
@@ -50517,7 +50544,7 @@
       </c>
       <c r="M48" s="36">
         <f>VLOOKUP(4,AD44:AN47,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N48" s="36">
         <f>VLOOKUP(4,AD44:AN47,5,FALSE)</f>
@@ -50525,11 +50552,11 @@
       </c>
       <c r="O48" s="36" t="str">
         <f>VLOOKUP(4,AD44:AN47,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD44:AN47,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 1</v>
       </c>
       <c r="P48" s="37">
         <f>L48*3+M48</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48" s="123">
         <f>DATE(2026,6,22)+TIME(105,0,0)+gmt_delta</f>
@@ -50589,7 +50616,7 @@
       </c>
       <c r="AI48" s="123">
         <f>MAX(AI44:AI47)+1</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AL48" s="123">
         <f>MIN(AL44:AL47)</f>
@@ -50601,15 +50628,15 @@
       </c>
       <c r="AN48" s="123">
         <f>MAX(AN44:AN47)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO48" s="123">
         <f>MAX(AO44:AO47)+1</f>
-        <v>1</v>
+        <v>6.9901960784313726</v>
       </c>
       <c r="AP48" s="123">
         <f>MAX(AP44:AP47)+1</f>
-        <v>1.000867355</v>
+        <v>59902061.47139588</v>
       </c>
       <c r="AT48" s="126">
         <f>MAX(AT44:AT47)-MIN(AT44:AT47)+1</f>
@@ -50621,11 +50648,11 @@
       </c>
       <c r="AV48" s="126">
         <f>MAX(AV44:AV47)-MIN(AV44:AV47)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW48" s="126">
         <f>MAX(AW44:AW47)-MIN(AW44:AW47)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY48" s="126">
         <f>MAX(AY44:AY47)-MIN(AY44:AY47)+1</f>
@@ -50633,7 +50660,7 @@
       </c>
       <c r="AZ48" s="126">
         <f>MAX(AZ44:AZ47)+1</f>
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="BB48" s="126">
         <f>MAX(BB44:BB47)-MIN(BB44:BB47)+1</f>
@@ -50645,11 +50672,11 @@
       </c>
       <c r="BD48" s="126">
         <f>MAX(BD44:BD47)-MIN(BD44:BD47)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BE48" s="126">
         <f>MAX(BE44:BE47)-MIN(BE44:BE47)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BG48" s="126">
         <f>MAX(BG44:BG47)-MIN(BG44:BG47)+1</f>
@@ -50657,7 +50684,7 @@
       </c>
       <c r="BH48" s="126">
         <f>MAX(BH44:BH47)+1</f>
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="BK48" s="21"/>
       <c r="BL48" s="21"/>
@@ -50673,7 +50700,7 @@
       <c r="BV48" s="21"/>
       <c r="BW48" s="114"/>
       <c r="BX48" s="112"/>
-      <c r="BY48" s="173">
+      <c r="BY48" s="163">
         <v>99</v>
       </c>
       <c r="BZ48" s="24" t="str">
@@ -50689,7 +50716,7 @@
       </c>
       <c r="CK48" s="114"/>
       <c r="CL48" s="112"/>
-      <c r="CM48" s="173">
+      <c r="CM48" s="163">
         <v>103</v>
       </c>
       <c r="CN48" s="24" t="str">
@@ -50794,7 +50821,7 @@
       <c r="BV49" s="21"/>
       <c r="BW49" s="114"/>
       <c r="BX49" s="115"/>
-      <c r="BY49" s="174"/>
+      <c r="BY49" s="164"/>
       <c r="BZ49" s="26" t="str">
         <f>IF(BW52&gt;BW53,BS52,IF(BW52&lt;BW53,BS53,""))</f>
         <v/>
@@ -50808,7 +50835,7 @@
       </c>
       <c r="CK49" s="114"/>
       <c r="CL49" s="115"/>
-      <c r="CM49" s="174"/>
+      <c r="CM49" s="164"/>
       <c r="CN49" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG56,IF(CK55&lt;CK56,CG55,""))</f>
         <v/>
@@ -50921,7 +50948,7 @@
       </c>
       <c r="AD50" s="123">
         <f>COUNTIF(AR50:AR53,CONCATENATE("&gt;=",AR50))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE50" s="124" t="str">
         <f>VLOOKUP("Spain",T,lang,FALSE)</f>
@@ -50933,7 +50960,7 @@
       </c>
       <c r="AG50" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE50 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH50" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE50 &amp; "_lose")</f>
@@ -50957,15 +50984,15 @@
       </c>
       <c r="AN50" s="123">
         <f>AF50*3+AG50</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO50" s="123">
         <f>AN50/AN54*10+BA50</f>
-        <v>0</v>
+        <v>5.985221674876847</v>
       </c>
       <c r="AP50" s="123">
         <f>AO50*10000000+BI50*100+AM50/AM54*10+AI50/AI54*1++IF(AQ50=0,ROW(),AQ50)/2000000</f>
-        <v>9.3820000000000004E-4</v>
+        <v>59852315.27187416</v>
       </c>
       <c r="AQ50" s="126">
         <f>VLOOKUP(AE50,db_fifarank,2,FALSE)</f>
@@ -50973,7 +51000,7 @@
       </c>
       <c r="AR50" s="125">
         <f>AP50/AP54</f>
-        <v>9.3732060580763133E-4</v>
+        <v>0.99917759969584252</v>
       </c>
       <c r="AS50" s="125" t="str">
         <f>IF(SUM(AF50:AH53)=12,J51,"1H")</f>
@@ -50985,7 +51012,7 @@
       </c>
       <c r="AU50" s="126" cm="1">
         <f t="array" ref="AU50">SUMPRODUCT(($S$7:$S$78=AE50&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE50&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV50" s="126" cm="1">
         <f t="array" ref="AV50">SUMPRODUCT(($E$7:$E$78=AE50)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE50)*($U$7:$U$78)*($G$7:$G$78))</f>
@@ -51005,11 +51032,11 @@
       </c>
       <c r="AZ50" s="126">
         <f>AT50/AT54*1000+AU50/AU54*100+AY50/AY54*10+AV50/AV54</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BA50" s="126">
         <f>AZ50/AZ54</f>
-        <v>0</v>
+        <v>0.98522167487684731</v>
       </c>
       <c r="BB50" s="126" cm="1">
         <f t="array" ref="BB50">SUMPRODUCT(($S$7:$S$78=AE50&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE50&amp;"_win")*($X$7:$X$78))</f>
@@ -51017,7 +51044,7 @@
       </c>
       <c r="BC50" s="126" cm="1">
         <f t="array" ref="BC50">SUMPRODUCT(($S$7:$S$78=AE50&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE50&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD50" s="126" cm="1">
         <f t="array" ref="BD50">SUMPRODUCT(($E$7:$E$78=AE50)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE50)*($X$7:$X$78)*($G$7:$G$78))</f>
@@ -51037,13 +51064,13 @@
       </c>
       <c r="BH50" s="126">
         <f>BB50/BB54*1000+BC50/BC54*100+BG50/BG54*10+BD50/BD54</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BI50" s="126">
         <f>BH50/BH54</f>
-        <v>0</v>
-      </c>
-      <c r="BK50" s="173">
+        <v>0.98522167487684731</v>
+      </c>
+      <c r="BK50" s="163">
         <v>79</v>
       </c>
       <c r="BL50" s="24" t="str">
@@ -51102,11 +51129,11 @@
       </c>
       <c r="J51" s="30" t="str">
         <f>VLOOKUP(1,AD50:AN53,2,FALSE)</f>
-        <v>Spain</v>
+        <v>Uruguay</v>
       </c>
       <c r="K51" s="31">
         <f>L51+M51+N51</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" s="31">
         <f>VLOOKUP(1,AD50:AN53,3,FALSE)</f>
@@ -51114,7 +51141,7 @@
       </c>
       <c r="M51" s="31">
         <f>VLOOKUP(1,AD50:AN53,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N51" s="31">
         <f>VLOOKUP(1,AD50:AN53,5,FALSE)</f>
@@ -51122,11 +51149,11 @@
       </c>
       <c r="O51" s="31" t="str">
         <f>VLOOKUP(1,AD50:AN53,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD50:AN53,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 1</v>
       </c>
       <c r="P51" s="32">
         <f>L51*3+M51</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R51" s="123">
         <f>DATE(2026,6,23)+TIME(9,0,0)+gmt_delta</f>
@@ -51186,7 +51213,7 @@
       </c>
       <c r="AG51" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE51 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH51" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE51 &amp; "_lose")</f>
@@ -51210,15 +51237,15 @@
       </c>
       <c r="AN51" s="123">
         <f>AF51*3+AG51</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO51" s="123">
         <f>AN51/AN54*10+BA51</f>
-        <v>0</v>
+        <v>5.985221674876847</v>
       </c>
       <c r="AP51" s="123">
         <f>AO51*10000000+BI51*100+AM51/AM54*10+AI51/AI54*1++IF(AQ51=0,ROW(),AQ51)/2000000</f>
-        <v>6.8306500000000006E-4</v>
+        <v>59852315.271619022</v>
       </c>
       <c r="AQ51" s="126">
         <f>VLOOKUP(AE51,db_fifarank,2,FALSE)</f>
@@ -51226,7 +51253,7 @@
       </c>
       <c r="AR51" s="125">
         <f>AP51/AP54</f>
-        <v>6.8242474910039407E-4</v>
+        <v>0.99917759969158326</v>
       </c>
       <c r="AS51" s="125" t="str">
         <f>IF(SUM(AF50:AH53)=12,J52,"2H")</f>
@@ -51238,7 +51265,7 @@
       </c>
       <c r="AU51" s="126" cm="1">
         <f t="array" ref="AU51">SUMPRODUCT(($S$7:$S$78=AE51&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE51&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV51" s="126" cm="1">
         <f t="array" ref="AV51">SUMPRODUCT(($E$7:$E$78=AE51)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE51)*($U$7:$U$78)*($G$7:$G$78))</f>
@@ -51258,11 +51285,11 @@
       </c>
       <c r="AZ51" s="126">
         <f>AT51/AT54*1000+AU51/AU54*100+AY51/AY54*10+AV51/AV54</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BA51" s="126">
         <f>AZ51/AZ54</f>
-        <v>0</v>
+        <v>0.98522167487684731</v>
       </c>
       <c r="BB51" s="126" cm="1">
         <f t="array" ref="BB51">SUMPRODUCT(($S$7:$S$78=AE51&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE51&amp;"_win")*($X$7:$X$78))</f>
@@ -51270,7 +51297,7 @@
       </c>
       <c r="BC51" s="126" cm="1">
         <f t="array" ref="BC51">SUMPRODUCT(($S$7:$S$78=AE51&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE51&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD51" s="126" cm="1">
         <f t="array" ref="BD51">SUMPRODUCT(($E$7:$E$78=AE51)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE51)*($X$7:$X$78)*($G$7:$G$78))</f>
@@ -51290,13 +51317,13 @@
       </c>
       <c r="BH51" s="126">
         <f>BB51/BB54*1000+BC51/BC54*100+BG51/BG54*10+BD51/BD54</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BI51" s="126">
         <f>BH51/BH54</f>
-        <v>0</v>
-      </c>
-      <c r="BK51" s="174"/>
+        <v>0.98522167487684731</v>
+      </c>
+      <c r="BK51" s="164"/>
       <c r="BL51" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!D3,AK80:AS91,9,FALSE),"3rd Group C/E/F/H/I")</f>
         <v>3rd Group C/E/F/H/I</v>
@@ -51359,11 +51386,11 @@
       </c>
       <c r="J52" s="33" t="str">
         <f>VLOOKUP(2,AD50:AN53,2,FALSE)</f>
-        <v>Uruguay</v>
+        <v>Saudi Arabia</v>
       </c>
       <c r="K52" s="23">
         <f>L52+M52+N52</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="23">
         <f>VLOOKUP(2,AD50:AN53,3,FALSE)</f>
@@ -51371,7 +51398,7 @@
       </c>
       <c r="M52" s="23">
         <f>VLOOKUP(2,AD50:AN53,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N52" s="23">
         <f>VLOOKUP(2,AD50:AN53,5,FALSE)</f>
@@ -51379,11 +51406,11 @@
       </c>
       <c r="O52" s="23" t="str">
         <f>VLOOKUP(2,AD50:AN53,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD50:AN53,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 1</v>
       </c>
       <c r="P52" s="34">
         <f>L52*3+M52</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R52" s="123">
         <f>DATE(2026,6,23)+TIME(12,0,0)+gmt_delta</f>
@@ -51431,7 +51458,7 @@
       </c>
       <c r="AD52" s="123">
         <f>COUNTIF(AR50:AR53,CONCATENATE("&gt;=",AR52))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE52" s="124" t="str">
         <f>VLOOKUP("Saudi Arabia",T,lang,FALSE)</f>
@@ -51443,7 +51470,7 @@
       </c>
       <c r="AG52" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE52 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH52" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE52 &amp; "_lose")</f>
@@ -51451,11 +51478,11 @@
       </c>
       <c r="AI52" s="123">
         <f>SUMIF($E$7:$E$78,$AE52,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE52,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ52" s="123">
         <f>SUMIF($E$7:$E$78,$AE52,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE52,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL52" s="123">
         <f>AI52-AJ52</f>
@@ -51467,15 +51494,15 @@
       </c>
       <c r="AN52" s="123">
         <f>AF52*3+AG52</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO52" s="123">
         <f>AN52/AN54*10+BA52</f>
-        <v>0</v>
+        <v>5.9901477832512313</v>
       </c>
       <c r="AP52" s="123">
         <f>AO52*10000000+BI52*100+AM52/AM54*10+AI52/AI54*1++IF(AQ52=0,ROW(),AQ52)/2000000</f>
-        <v>7.10715E-4</v>
+        <v>59901577.348001353</v>
       </c>
       <c r="AQ52" s="126">
         <f>VLOOKUP(AE52,db_fifarank,2,FALSE)</f>
@@ -51483,7 +51510,7 @@
       </c>
       <c r="AR52" s="125">
         <f>AP52/AP54</f>
-        <v>7.1004883218564344E-4</v>
+        <v>0.99999998330384865</v>
       </c>
       <c r="AT52" s="126" cm="1">
         <f t="array" ref="AT52">SUMPRODUCT(($S$7:$S$78=AE52&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE52&amp;"_win")*($U$7:$U$78))</f>
@@ -51491,15 +51518,15 @@
       </c>
       <c r="AU52" s="126" cm="1">
         <f t="array" ref="AU52">SUMPRODUCT(($S$7:$S$78=AE52&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE52&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV52" s="126" cm="1">
         <f t="array" ref="AV52">SUMPRODUCT(($E$7:$E$78=AE52)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE52)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW52" s="126" cm="1">
         <f t="array" ref="AW52">SUMPRODUCT(($E$7:$E$78=AE52)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE52)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX52" s="126">
         <f>AV52-AW52</f>
@@ -51511,11 +51538,11 @@
       </c>
       <c r="AZ52" s="126">
         <f>AT52/AT54*1000+AU52/AU54*100+AY52/AY54*10+AV52/AV54</f>
-        <v>0</v>
+        <v>100.5</v>
       </c>
       <c r="BA52" s="126">
         <f>AZ52/AZ54</f>
-        <v>0</v>
+        <v>0.99014778325123154</v>
       </c>
       <c r="BB52" s="126" cm="1">
         <f t="array" ref="BB52">SUMPRODUCT(($S$7:$S$78=AE52&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE52&amp;"_win")*($X$7:$X$78))</f>
@@ -51523,15 +51550,15 @@
       </c>
       <c r="BC52" s="126" cm="1">
         <f t="array" ref="BC52">SUMPRODUCT(($S$7:$S$78=AE52&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE52&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD52" s="126" cm="1">
         <f t="array" ref="BD52">SUMPRODUCT(($E$7:$E$78=AE52)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE52)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE52" s="126" cm="1">
         <f t="array" ref="BE52">SUMPRODUCT(($E$7:$E$78=AE52)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE52)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF52" s="126">
         <f>BD52-BE52</f>
@@ -51543,11 +51570,11 @@
       </c>
       <c r="BH52" s="126">
         <f>BB52/BB54*1000+BC52/BC54*100+BG52/BG54*10+BD52/BD54</f>
-        <v>0</v>
+        <v>100.5</v>
       </c>
       <c r="BI52" s="126">
         <f>BH52/BH54</f>
-        <v>0</v>
+        <v>0.99014778325123154</v>
       </c>
       <c r="BK52" s="21"/>
       <c r="BL52" s="21"/>
@@ -51556,7 +51583,7 @@
       <c r="BO52" s="21"/>
       <c r="BP52" s="114"/>
       <c r="BQ52" s="112"/>
-      <c r="BR52" s="173">
+      <c r="BR52" s="163">
         <v>92</v>
       </c>
       <c r="BS52" s="24" t="str">
@@ -51608,11 +51635,11 @@
       </c>
       <c r="J53" s="33" t="str">
         <f>VLOOKUP(3,AD50:AN53,2,FALSE)</f>
-        <v>Saudi Arabia</v>
+        <v>Spain</v>
       </c>
       <c r="K53" s="23">
         <f>L53+M53+N53</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="23">
         <f>VLOOKUP(3,AD50:AN53,3,FALSE)</f>
@@ -51620,7 +51647,7 @@
       </c>
       <c r="M53" s="23">
         <f>VLOOKUP(3,AD50:AN53,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N53" s="23">
         <f>VLOOKUP(3,AD50:AN53,5,FALSE)</f>
@@ -51632,7 +51659,7 @@
       </c>
       <c r="P53" s="34">
         <f>L53*3+M53</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R53" s="123">
         <f>DATE(2026,6,23)+TIME(6,0,0)+gmt_delta</f>
@@ -51680,7 +51707,7 @@
       </c>
       <c r="AD53" s="123">
         <f>COUNTIF(AR50:AR53,CONCATENATE("&gt;=",AR53))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE53" s="124" t="str">
         <f>VLOOKUP("Uruguay",T,lang,FALSE)</f>
@@ -51692,7 +51719,7 @@
       </c>
       <c r="AG53" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE53 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH53" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE53 &amp; "_lose")</f>
@@ -51700,11 +51727,11 @@
       </c>
       <c r="AI53" s="123">
         <f>SUMIF($E$7:$E$78,$AE53,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE53,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ53" s="123">
         <f>SUMIF($E$7:$E$78,$AE53,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE53,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL53" s="123">
         <f>AI53-AJ53</f>
@@ -51716,15 +51743,15 @@
       </c>
       <c r="AN53" s="123">
         <f>AF53*3+AG53</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO53" s="123">
         <f>AN53/AN54*10+BA53</f>
-        <v>0</v>
+        <v>5.9901477832512313</v>
       </c>
       <c r="AP53" s="123">
         <f>AO53*10000000+BI53*100+AM53/AM54*10+AI53/AI54*1++IF(AQ53=0,ROW(),AQ53)/2000000</f>
-        <v>8.3653500000000001E-4</v>
+        <v>59901577.348127171</v>
       </c>
       <c r="AQ53" s="126">
         <f>VLOOKUP(AE53,db_fifarank,2,FALSE)</f>
@@ -51732,7 +51759,7 @@
       </c>
       <c r="AR53" s="125">
         <f>AP53/AP54</f>
-        <v>8.3575089850702075E-4</v>
+        <v>0.99999998330594908</v>
       </c>
       <c r="AT53" s="126" cm="1">
         <f t="array" ref="AT53">SUMPRODUCT(($S$7:$S$78=AE53&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE53&amp;"_win")*($U$7:$U$78))</f>
@@ -51740,15 +51767,15 @@
       </c>
       <c r="AU53" s="126" cm="1">
         <f t="array" ref="AU53">SUMPRODUCT(($S$7:$S$78=AE53&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE53&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV53" s="126" cm="1">
         <f t="array" ref="AV53">SUMPRODUCT(($E$7:$E$78=AE53)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE53)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW53" s="126" cm="1">
         <f t="array" ref="AW53">SUMPRODUCT(($E$7:$E$78=AE53)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE53)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX53" s="126">
         <f>AV53-AW53</f>
@@ -51760,11 +51787,11 @@
       </c>
       <c r="AZ53" s="126">
         <f>AT53/AT54*1000+AU53/AU54*100+AY53/AY54*10+AV53/AV54</f>
-        <v>0</v>
+        <v>100.5</v>
       </c>
       <c r="BA53" s="126">
         <f>AZ53/AZ54</f>
-        <v>0</v>
+        <v>0.99014778325123154</v>
       </c>
       <c r="BB53" s="126" cm="1">
         <f t="array" ref="BB53">SUMPRODUCT(($S$7:$S$78=AE53&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE53&amp;"_win")*($X$7:$X$78))</f>
@@ -51772,15 +51799,15 @@
       </c>
       <c r="BC53" s="126" cm="1">
         <f t="array" ref="BC53">SUMPRODUCT(($S$7:$S$78=AE53&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE53&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD53" s="126" cm="1">
         <f t="array" ref="BD53">SUMPRODUCT(($E$7:$E$78=AE53)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE53)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE53" s="126" cm="1">
         <f t="array" ref="BE53">SUMPRODUCT(($E$7:$E$78=AE53)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE53)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF53" s="126">
         <f>BD53-BE53</f>
@@ -51792,11 +51819,11 @@
       </c>
       <c r="BH53" s="126">
         <f>BB53/BB54*1000+BC53/BC54*100+BG53/BG54*10+BD53/BD54</f>
-        <v>0</v>
+        <v>100.5</v>
       </c>
       <c r="BI53" s="126">
         <f>BH53/BH54</f>
-        <v>0</v>
+        <v>0.99014778325123154</v>
       </c>
       <c r="BK53" s="21" t="str" cm="1">
         <f t="array" ref="BK53">INDEX(T,24+MONTH(BP53),lang) &amp; " " &amp; DAY(BP53) &amp; ", " &amp; YEAR(BP53) &amp; "   " &amp; (IF(HOUR(BP53)&lt;10,0,"")&amp;HOUR(BP53)) &amp; ":" &amp;  (IF(MINUTE(BP53)&lt;10,0,"")&amp;MINUTE(BP53))</f>
@@ -51811,7 +51838,7 @@
         <v>46204.666666666672</v>
       </c>
       <c r="BQ53" s="115"/>
-      <c r="BR53" s="174"/>
+      <c r="BR53" s="164"/>
       <c r="BS53" s="26" t="str">
         <f>IF(BP54&gt;BP55,BL54,IF(BP54&lt;BP55,BL55,""))</f>
         <v/>
@@ -51865,7 +51892,7 @@
       </c>
       <c r="K54" s="36">
         <f>L54+M54+N54</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="36">
         <f>VLOOKUP(4,AD50:AN53,3,FALSE)</f>
@@ -51873,7 +51900,7 @@
       </c>
       <c r="M54" s="36">
         <f>VLOOKUP(4,AD50:AN53,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N54" s="36">
         <f>VLOOKUP(4,AD50:AN53,5,FALSE)</f>
@@ -51885,7 +51912,7 @@
       </c>
       <c r="P54" s="37">
         <f>L54*3+M54</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R54" s="123">
         <f>DATE(2026,6,23)+TIME(15,0,0)+gmt_delta</f>
@@ -51945,7 +51972,7 @@
       </c>
       <c r="AI54" s="123">
         <f>MAX(AI50:AI53)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL54" s="123">
         <f>MIN(AL50:AL53)</f>
@@ -51957,15 +51984,15 @@
       </c>
       <c r="AN54" s="123">
         <f>MAX(AN50:AN53)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO54" s="123">
         <f>MAX(AO50:AO53)+1</f>
-        <v>1</v>
+        <v>6.9901477832512313</v>
       </c>
       <c r="AP54" s="123">
         <f>MAX(AP50:AP53)+1</f>
-        <v>1.0009382</v>
+        <v>59901578.348127171</v>
       </c>
       <c r="AT54" s="126">
         <f>MAX(AT50:AT53)-MIN(AT50:AT53)+1</f>
@@ -51977,11 +52004,11 @@
       </c>
       <c r="AV54" s="126">
         <f>MAX(AV50:AV53)-MIN(AV50:AV53)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW54" s="126">
         <f>MAX(AW50:AW53)-MIN(AW50:AW53)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY54" s="126">
         <f>MAX(AY50:AY53)-MIN(AY50:AY53)+1</f>
@@ -51989,7 +52016,7 @@
       </c>
       <c r="AZ54" s="126">
         <f>MAX(AZ50:AZ53)+1</f>
-        <v>1</v>
+        <v>101.5</v>
       </c>
       <c r="BB54" s="126">
         <f>MAX(BB50:BB53)-MIN(BB50:BB53)+1</f>
@@ -52001,11 +52028,11 @@
       </c>
       <c r="BD54" s="126">
         <f>MAX(BD50:BD53)-MIN(BD50:BD53)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BE54" s="126">
         <f>MAX(BE50:BE53)-MIN(BE50:BE53)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BG54" s="126">
         <f>MAX(BG50:BG53)-MIN(BG50:BG53)+1</f>
@@ -52013,9 +52040,9 @@
       </c>
       <c r="BH54" s="126">
         <f>MAX(BH50:BH53)+1</f>
-        <v>1</v>
-      </c>
-      <c r="BK54" s="173">
+        <v>101.5</v>
+      </c>
+      <c r="BK54" s="163">
         <v>80</v>
       </c>
       <c r="BL54" s="24" t="str">
@@ -52136,7 +52163,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK55" s="174"/>
+      <c r="BK55" s="164"/>
       <c r="BL55" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!K3,AK80:AS91,9,FALSE),"3rd Group E/H/I/J/K")</f>
         <v>3rd Group E/H/I/J/K</v>
@@ -52163,7 +52190,7 @@
       <c r="CC55" s="21"/>
       <c r="CD55" s="114"/>
       <c r="CE55" s="112"/>
-      <c r="CF55" s="173">
+      <c r="CF55" s="163">
         <v>102</v>
       </c>
       <c r="CG55" s="24" t="str">
@@ -52422,7 +52449,7 @@
       <c r="CC56" s="21"/>
       <c r="CD56" s="114"/>
       <c r="CE56" s="115"/>
-      <c r="CF56" s="174"/>
+      <c r="CF56" s="164"/>
       <c r="CG56" s="26" t="str">
         <f>IF(CD64&gt;CD65,BZ64,IF(CD64&lt;CD65,BZ65,""))</f>
         <v/>
@@ -52905,7 +52932,7 @@
         <f>BH58/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK58" s="173">
+      <c r="BK58" s="163">
         <v>86</v>
       </c>
       <c r="BL58" s="24" t="str">
@@ -53153,7 +53180,7 @@
         <f>BH59/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK59" s="174"/>
+      <c r="BK59" s="164"/>
       <c r="BL59" s="26" t="str">
         <f>AS51</f>
         <v>2H</v>
@@ -53376,7 +53403,7 @@
       <c r="BO60" s="21"/>
       <c r="BP60" s="114"/>
       <c r="BQ60" s="112"/>
-      <c r="BR60" s="173">
+      <c r="BR60" s="163">
         <v>95</v>
       </c>
       <c r="BS60" s="24" t="str">
@@ -53489,7 +53516,7 @@
         <v>46206.75</v>
       </c>
       <c r="BQ61" s="115"/>
-      <c r="BR61" s="174"/>
+      <c r="BR61" s="164"/>
       <c r="BS61" s="26" t="str">
         <f>IF(BP62&gt;BP63,BL62,IF(BP62&lt;BP63,BL63,""))</f>
         <v/>
@@ -53732,7 +53759,7 @@
         <f>BH62/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK62" s="173">
+      <c r="BK62" s="163">
         <v>88</v>
       </c>
       <c r="BL62" s="24" t="str">
@@ -53984,7 +54011,7 @@
         <f>BH63/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK63" s="174"/>
+      <c r="BK63" s="164"/>
       <c r="BL63" s="26" t="str">
         <f>AS45</f>
         <v>2G</v>
@@ -54250,7 +54277,7 @@
       <c r="BV64" s="21"/>
       <c r="BW64" s="114"/>
       <c r="BX64" s="112"/>
-      <c r="BY64" s="173">
+      <c r="BY64" s="163">
         <v>100</v>
       </c>
       <c r="BZ64" s="24" t="str">
@@ -54504,7 +54531,7 @@
       <c r="BV65" s="21"/>
       <c r="BW65" s="114"/>
       <c r="BX65" s="115"/>
-      <c r="BY65" s="174"/>
+      <c r="BY65" s="164"/>
       <c r="BZ65" s="26" t="str">
         <f>IF(BW68&gt;BW69,BS68,IF(BW68&lt;BW69,BS69,""))</f>
         <v/>
@@ -54700,7 +54727,7 @@
         <f>MAX(BH62:BH65)+1</f>
         <v>1</v>
       </c>
-      <c r="BK66" s="173">
+      <c r="BK66" s="163">
         <v>85</v>
       </c>
       <c r="BL66" s="24" t="str">
@@ -54800,7 +54827,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK67" s="174"/>
+      <c r="BK67" s="164"/>
       <c r="BL67" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!E3,AK80:AS91,9,FALSE),"3rd Group E/F/G/I/J")</f>
         <v>3rd Group E/F/G/I/J</v>
@@ -55056,7 +55083,7 @@
       <c r="BO68" s="21"/>
       <c r="BP68" s="114"/>
       <c r="BQ68" s="112"/>
-      <c r="BR68" s="173">
+      <c r="BR68" s="163">
         <v>96</v>
       </c>
       <c r="BS68" s="24" t="str">
@@ -55070,25 +55097,25 @@
         <f>IF(OR(BT68="",BT69="",AND(BU68="",BU69&lt;&gt;""),AND(BU69="",BU68&lt;&gt;""),AND(BV68="",BV69&lt;&gt;""),AND(BV69="",BV68&lt;&gt;"")),"",BT68*1000+BU68*10+BV68)</f>
         <v/>
       </c>
-      <c r="CE68" s="175" t="str">
+      <c r="CE68" s="195" t="str">
         <f>INDEX(T,144,lang)</f>
         <v>World Champion 2026</v>
       </c>
-      <c r="CF68" s="175"/>
-      <c r="CG68" s="175"/>
-      <c r="CH68" s="175"/>
-      <c r="CI68" s="175"/>
-      <c r="CJ68" s="175"/>
-      <c r="CK68" s="163" t="str">
+      <c r="CF68" s="195"/>
+      <c r="CG68" s="195"/>
+      <c r="CH68" s="195"/>
+      <c r="CI68" s="195"/>
+      <c r="CJ68" s="195"/>
+      <c r="CK68" s="185" t="str">
         <f>IF(CR37&gt;CR38,CN37,IF(CR37&lt;CR38,CN38,""))</f>
         <v/>
       </c>
-      <c r="CL68" s="163"/>
-      <c r="CM68" s="163"/>
-      <c r="CN68" s="163"/>
-      <c r="CO68" s="163"/>
-      <c r="CP68" s="163"/>
-      <c r="CQ68" s="163"/>
+      <c r="CL68" s="185"/>
+      <c r="CM68" s="185"/>
+      <c r="CN68" s="185"/>
+      <c r="CO68" s="185"/>
+      <c r="CP68" s="185"/>
+      <c r="CQ68" s="185"/>
     </row>
     <row r="69" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A69" s="16">
@@ -55326,7 +55353,7 @@
         <v>46207.0625</v>
       </c>
       <c r="BQ69" s="115"/>
-      <c r="BR69" s="174"/>
+      <c r="BR69" s="164"/>
       <c r="BS69" s="26" t="str">
         <f>IF(BP70&gt;BP71,BL70,IF(BP70&lt;BP71,BL71,""))</f>
         <v/>
@@ -55338,19 +55365,19 @@
         <f>IF(BW68="","",BT69*1000+BU69*10+BV69)</f>
         <v/>
       </c>
-      <c r="CE69" s="175"/>
-      <c r="CF69" s="175"/>
-      <c r="CG69" s="175"/>
-      <c r="CH69" s="175"/>
-      <c r="CI69" s="175"/>
-      <c r="CJ69" s="175"/>
-      <c r="CK69" s="163"/>
-      <c r="CL69" s="163"/>
-      <c r="CM69" s="163"/>
-      <c r="CN69" s="163"/>
-      <c r="CO69" s="163"/>
-      <c r="CP69" s="163"/>
-      <c r="CQ69" s="163"/>
+      <c r="CE69" s="195"/>
+      <c r="CF69" s="195"/>
+      <c r="CG69" s="195"/>
+      <c r="CH69" s="195"/>
+      <c r="CI69" s="195"/>
+      <c r="CJ69" s="195"/>
+      <c r="CK69" s="185"/>
+      <c r="CL69" s="185"/>
+      <c r="CM69" s="185"/>
+      <c r="CN69" s="185"/>
+      <c r="CO69" s="185"/>
+      <c r="CP69" s="185"/>
+      <c r="CQ69" s="185"/>
     </row>
     <row r="70" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A70" s="16">
@@ -55571,7 +55598,7 @@
         <f>BH70/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK70" s="173">
+      <c r="BK70" s="163">
         <v>87</v>
       </c>
       <c r="BL70" s="24" t="str">
@@ -55807,7 +55834,7 @@
         <f>BH71/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK71" s="174"/>
+      <c r="BK71" s="164"/>
       <c r="BL71" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!J3,AK80:AS91,9,FALSE),"3rd Group D/E/I/J/L")</f>
         <v>3rd Group D/E/I/J/L</v>
@@ -57214,7 +57241,7 @@
       </c>
       <c r="AD80" s="123">
         <f>COUNTIF($AP$80:$AP$91,CONCATENATE("&gt;=",AP80))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE80" s="124" t="str">
         <f>J11</f>
@@ -57257,7 +57284,7 @@
       </c>
       <c r="AP80" s="123">
         <f>AN80/AN92*10000+AM80/AM92*1000+AI80/AI92*100+IF(AQ80=0,ROW(),AQ80)/2000000</f>
-        <v>383.33408402333333</v>
+        <v>366.66741735666665</v>
       </c>
       <c r="AQ80" s="126">
         <f t="shared" ref="AQ80:AQ91" si="37">VLOOKUP($AE80,$AE$8:$AQ$78,13,FALSE)</f>
@@ -57288,7 +57315,7 @@
       <c r="I81" s="69"/>
       <c r="J81" s="96" t="str">
         <f>VLOOKUP(1,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓒ Morocco</v>
+        <v>Ⓕ Japan</v>
       </c>
       <c r="K81" s="97">
         <f>L81+M81+N81</f>
@@ -57308,7 +57335,7 @@
       </c>
       <c r="O81" s="97" t="str">
         <f>VLOOKUP(1,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(1,$AD$80:$AN$91,7,FALSE)</f>
-        <v>1 - 1</v>
+        <v>2 - 2</v>
       </c>
       <c r="P81" s="98">
         <f>L81*3+M81</f>
@@ -57316,7 +57343,7 @@
       </c>
       <c r="AD81" s="123">
         <f t="shared" ref="AD81:AD91" si="38">COUNTIF($AP$80:$AP$91,CONCATENATE("&gt;=",AP81))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE81" s="124" t="str">
         <f>J17</f>
@@ -57359,7 +57386,7 @@
       </c>
       <c r="AP81" s="123">
         <f>AN81/AN92*10000+AM81/AM92*1000+AI81/AI92*100+IF(AQ81=0,ROW(),AQ81)/2000000</f>
-        <v>5716.667394146667</v>
+        <v>5700.00072748</v>
       </c>
       <c r="AQ81" s="126">
         <f t="shared" si="37"/>
@@ -57390,7 +57417,7 @@
       <c r="I82" s="69"/>
       <c r="J82" s="99" t="str">
         <f>VLOOKUP(2,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓑ Qatar</v>
+        <v>Ⓒ Morocco</v>
       </c>
       <c r="K82" s="100">
         <f t="shared" ref="K82:K92" si="47">L82+M82+N82</f>
@@ -57418,7 +57445,7 @@
       </c>
       <c r="AD82" s="123">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE82" s="124" t="str">
         <f>J23</f>
@@ -57461,7 +57488,7 @@
       </c>
       <c r="AP82" s="123">
         <f>AN82/AN92*10000+AM82/AM92*1000+AI82/AI92*100+IF(AQ82=0,ROW(),AQ82)/2000000</f>
-        <v>5716.667544601667</v>
+        <v>5700.0008779350001</v>
       </c>
       <c r="AQ82" s="126">
         <f t="shared" si="37"/>
@@ -57483,22 +57510,22 @@
     <row r="83" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="73"/>
       <c r="B83" s="73"/>
-      <c r="C83" s="164" t="s">
+      <c r="C83" s="186" t="s">
         <v>3183</v>
       </c>
-      <c r="D83" s="165"/>
-      <c r="E83" s="165"/>
-      <c r="F83" s="165"/>
-      <c r="G83" s="166"/>
+      <c r="D83" s="187"/>
+      <c r="E83" s="187"/>
+      <c r="F83" s="187"/>
+      <c r="G83" s="188"/>
       <c r="H83" s="75"/>
       <c r="I83" s="69"/>
       <c r="J83" s="99" t="str">
         <f>VLOOKUP(3,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓙ Algeria</v>
+        <v>Ⓖ Belgium</v>
       </c>
       <c r="K83" s="100">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" s="100">
         <f>VLOOKUP(3,$AD$80:$AN$91,3,FALSE)</f>
@@ -57506,7 +57533,7 @@
       </c>
       <c r="M83" s="100">
         <f>VLOOKUP(3,$AD$80:$AN$91,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N83" s="100">
         <f>VLOOKUP(3,$AD$80:$AN$91,5,FALSE)</f>
@@ -57514,11 +57541,11 @@
       </c>
       <c r="O83" s="100" t="str">
         <f>VLOOKUP(3,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(3,$AD$80:$AN$91,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 1</v>
       </c>
       <c r="P83" s="101">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD83" s="123">
         <f t="shared" si="38"/>
@@ -57587,20 +57614,20 @@
     <row r="84" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="73"/>
       <c r="B84" s="73"/>
-      <c r="C84" s="167"/>
-      <c r="D84" s="168"/>
-      <c r="E84" s="168"/>
-      <c r="F84" s="168"/>
-      <c r="G84" s="169"/>
+      <c r="C84" s="189"/>
+      <c r="D84" s="190"/>
+      <c r="E84" s="190"/>
+      <c r="F84" s="190"/>
+      <c r="G84" s="191"/>
       <c r="H84" s="75"/>
       <c r="I84" s="69"/>
       <c r="J84" s="99" t="str">
         <f>VLOOKUP(4,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓖ Egypt</v>
+        <v>Ⓑ Qatar</v>
       </c>
       <c r="K84" s="100">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="100">
         <f>VLOOKUP(4,$AD$80:$AN$91,3,FALSE)</f>
@@ -57608,7 +57635,7 @@
       </c>
       <c r="M84" s="100">
         <f>VLOOKUP(4,$AD$80:$AN$91,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N84" s="100">
         <f>VLOOKUP(4,$AD$80:$AN$91,5,FALSE)</f>
@@ -57616,11 +57643,11 @@
       </c>
       <c r="O84" s="100" t="str">
         <f>VLOOKUP(4,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(4,$AD$80:$AN$91,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 1</v>
       </c>
       <c r="P84" s="101">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R84" s="123">
         <f>DATE(2026,12,3)+TIME(4,0,0)+gmt_delta</f>
@@ -57636,11 +57663,11 @@
       </c>
       <c r="AD84" s="123">
         <f t="shared" si="38"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE84" s="124" t="str">
         <f>J35</f>
-        <v>Ivory Coast</v>
+        <v>Ecuador</v>
       </c>
       <c r="AF84" s="123">
         <f t="shared" si="39"/>
@@ -57652,7 +57679,7 @@
       </c>
       <c r="AH84" s="123">
         <f t="shared" si="40"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI84" s="123">
         <f t="shared" si="41"/>
@@ -57660,18 +57687,18 @@
       </c>
       <c r="AJ84" s="123">
         <f t="shared" si="42"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK84" s="123" t="s">
         <v>3185</v>
       </c>
       <c r="AL84" s="123">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM84" s="123">
         <f t="shared" si="44"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN84" s="123">
         <f t="shared" si="45"/>
@@ -57679,42 +57706,42 @@
       </c>
       <c r="AP84" s="123">
         <f>AN84/AN92*10000+AM84/AM92*1000+AI84/AI92*100+IF(AQ84=0,ROW(),AQ84)/2000000</f>
-        <v>666.66743315666668</v>
+        <v>333.33413072333332</v>
       </c>
       <c r="AQ84" s="126">
         <f t="shared" si="37"/>
-        <v>1532.98</v>
+        <v>1594.78</v>
       </c>
       <c r="AR84" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCE</v>
+        <v>BC</v>
       </c>
       <c r="AS84" s="129" t="str">
         <f t="shared" si="46"/>
-        <v>Ivory Coast</v>
+        <v/>
       </c>
       <c r="AT84" s="130" t="str">
         <f>"Ⓔ "&amp;AE84</f>
-        <v>Ⓔ Ivory Coast</v>
+        <v>Ⓔ Ecuador</v>
       </c>
     </row>
     <row r="85" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="73"/>
       <c r="B85" s="73"/>
-      <c r="C85" s="167"/>
-      <c r="D85" s="168"/>
-      <c r="E85" s="168"/>
-      <c r="F85" s="168"/>
-      <c r="G85" s="169"/>
+      <c r="C85" s="189"/>
+      <c r="D85" s="190"/>
+      <c r="E85" s="190"/>
+      <c r="F85" s="190"/>
+      <c r="G85" s="191"/>
       <c r="H85" s="75"/>
       <c r="I85" s="69"/>
       <c r="J85" s="99" t="str">
         <f>VLOOKUP(5,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓘ Norway</v>
+        <v>Ⓗ Spain</v>
       </c>
       <c r="K85" s="100">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="100">
         <f>VLOOKUP(5,$AD$80:$AN$91,3,FALSE)</f>
@@ -57722,7 +57749,7 @@
       </c>
       <c r="M85" s="100">
         <f>VLOOKUP(5,$AD$80:$AN$91,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N85" s="100">
         <f>VLOOKUP(5,$AD$80:$AN$91,5,FALSE)</f>
@@ -57734,7 +57761,7 @@
       </c>
       <c r="P85" s="101">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R85" s="123">
         <f>DATE(2026,12,3)+TIME(8,0,0)+gmt_delta</f>
@@ -57750,11 +57777,11 @@
       </c>
       <c r="AD85" s="123">
         <f t="shared" si="38"/>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AE85" s="124" t="str">
         <f>J41</f>
-        <v>Sweden</v>
+        <v>Japan</v>
       </c>
       <c r="AF85" s="123">
         <f t="shared" si="39"/>
@@ -57762,7 +57789,7 @@
       </c>
       <c r="AG85" s="123">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH85" s="123">
         <f t="shared" si="40"/>
@@ -57770,11 +57797,11 @@
       </c>
       <c r="AI85" s="123">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ85" s="123">
         <f t="shared" si="42"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK85" s="123" t="s">
         <v>3186</v>
@@ -57789,42 +57816,42 @@
       </c>
       <c r="AN85" s="123">
         <f t="shared" si="45"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP85" s="123">
         <f>AN85/AN92*10000+AM85/AM92*1000+AI85/AI92*100+IF(AQ85=0,ROW(),AQ85)/2000000</f>
-        <v>666.66742405166667</v>
+        <v>5733.3341635483339</v>
       </c>
       <c r="AQ85" s="126">
         <f t="shared" si="37"/>
-        <v>1514.77</v>
+        <v>1660.43</v>
       </c>
       <c r="AR85" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCEF</v>
+        <v>BCF</v>
       </c>
       <c r="AS85" s="129" t="str">
         <f t="shared" si="46"/>
-        <v>Sweden</v>
+        <v>Japan</v>
       </c>
       <c r="AT85" s="130" t="str">
         <f>"Ⓕ "&amp;AE85</f>
-        <v>Ⓕ Sweden</v>
+        <v>Ⓕ Japan</v>
       </c>
     </row>
     <row r="86" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="73"/>
       <c r="B86" s="73"/>
-      <c r="C86" s="167"/>
-      <c r="D86" s="168"/>
-      <c r="E86" s="168"/>
-      <c r="F86" s="168"/>
-      <c r="G86" s="169"/>
+      <c r="C86" s="189"/>
+      <c r="D86" s="190"/>
+      <c r="E86" s="190"/>
+      <c r="F86" s="190"/>
+      <c r="G86" s="191"/>
       <c r="H86" s="75"/>
       <c r="I86" s="69"/>
       <c r="J86" s="99" t="str">
         <f>VLOOKUP(6,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓛ Panama</v>
+        <v>Ⓙ Algeria</v>
       </c>
       <c r="K86" s="100">
         <f t="shared" si="47"/>
@@ -57864,11 +57891,11 @@
       </c>
       <c r="AD86" s="123">
         <f t="shared" si="38"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE86" s="124" t="str">
         <f>J47</f>
-        <v>Egypt</v>
+        <v>Belgium</v>
       </c>
       <c r="AF86" s="123">
         <f t="shared" si="39"/>
@@ -57876,7 +57903,7 @@
       </c>
       <c r="AG86" s="123">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH86" s="123">
         <f t="shared" si="40"/>
@@ -57884,11 +57911,11 @@
       </c>
       <c r="AI86" s="123">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ86" s="123">
         <f t="shared" si="42"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK86" s="123" t="s">
         <v>3187</v>
@@ -57903,42 +57930,42 @@
       </c>
       <c r="AN86" s="123">
         <f t="shared" si="45"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP86" s="123">
         <f>AN86/AN92*10000+AM86/AM92*1000+AI86/AI92*100+IF(AQ86=0,ROW(),AQ86)/2000000</f>
-        <v>666.66744828666663</v>
+        <v>5700.0008673550001</v>
       </c>
       <c r="AQ86" s="126">
         <f t="shared" si="37"/>
-        <v>1563.24</v>
+        <v>1734.71</v>
       </c>
       <c r="AR86" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCEFG</v>
+        <v>BCFG</v>
       </c>
       <c r="AS86" s="129" t="str">
         <f t="shared" si="46"/>
-        <v>Egypt</v>
+        <v>Belgium</v>
       </c>
       <c r="AT86" s="130" t="str">
         <f>"Ⓖ "&amp;AE86</f>
-        <v>Ⓖ Egypt</v>
+        <v>Ⓖ Belgium</v>
       </c>
     </row>
     <row r="87" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="73"/>
       <c r="B87" s="73"/>
-      <c r="C87" s="167"/>
-      <c r="D87" s="168"/>
-      <c r="E87" s="168"/>
-      <c r="F87" s="168"/>
-      <c r="G87" s="169"/>
+      <c r="C87" s="189"/>
+      <c r="D87" s="190"/>
+      <c r="E87" s="190"/>
+      <c r="F87" s="190"/>
+      <c r="G87" s="191"/>
       <c r="H87" s="75"/>
       <c r="I87" s="69"/>
       <c r="J87" s="99" t="str">
         <f>VLOOKUP(7,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓔ Ivory Coast</v>
+        <v>Ⓘ Norway</v>
       </c>
       <c r="K87" s="100">
         <f t="shared" si="47"/>
@@ -57978,11 +58005,11 @@
       </c>
       <c r="AD87" s="123">
         <f t="shared" si="38"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AE87" s="124" t="str">
         <f>J53</f>
-        <v>Saudi Arabia</v>
+        <v>Spain</v>
       </c>
       <c r="AF87" s="123">
         <f t="shared" si="39"/>
@@ -57990,7 +58017,7 @@
       </c>
       <c r="AG87" s="123">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH87" s="123">
         <f t="shared" si="40"/>
@@ -58017,42 +58044,42 @@
       </c>
       <c r="AN87" s="123">
         <f t="shared" si="45"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP87" s="123">
         <f>AN87/AN92*10000+AM87/AM92*1000+AI87/AI92*100+IF(AQ87=0,ROW(),AQ87)/2000000</f>
-        <v>666.6673773816666</v>
+        <v>5666.6676048666668</v>
       </c>
       <c r="AQ87" s="126">
         <f t="shared" si="37"/>
-        <v>1421.43</v>
+        <v>1876.4</v>
       </c>
       <c r="AR87" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCEFG</v>
+        <v>BCFGH</v>
       </c>
       <c r="AS87" s="129" t="str">
         <f t="shared" si="46"/>
-        <v/>
+        <v>Spain</v>
       </c>
       <c r="AT87" s="130" t="str">
         <f>"Ⓗ "&amp;AE87</f>
-        <v>Ⓗ Saudi Arabia</v>
+        <v>Ⓗ Spain</v>
       </c>
     </row>
     <row r="88" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="73"/>
       <c r="B88" s="73"/>
-      <c r="C88" s="170"/>
-      <c r="D88" s="171"/>
-      <c r="E88" s="171"/>
-      <c r="F88" s="171"/>
-      <c r="G88" s="172"/>
+      <c r="C88" s="192"/>
+      <c r="D88" s="193"/>
+      <c r="E88" s="193"/>
+      <c r="F88" s="193"/>
+      <c r="G88" s="194"/>
       <c r="H88" s="75"/>
       <c r="I88" s="69"/>
       <c r="J88" s="99" t="str">
         <f>VLOOKUP(8,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓕ Sweden</v>
+        <v>Ⓛ Panama</v>
       </c>
       <c r="K88" s="100">
         <f t="shared" si="47"/>
@@ -58092,7 +58119,7 @@
       </c>
       <c r="AD88" s="123">
         <f t="shared" si="38"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE88" s="124" t="str">
         <f>J59</f>
@@ -58143,7 +58170,7 @@
       </c>
       <c r="AR88" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCEFGI</v>
+        <v>BCFGHI</v>
       </c>
       <c r="AS88" s="129" t="str">
         <f t="shared" si="46"/>
@@ -58206,7 +58233,7 @@
       </c>
       <c r="AD89" s="123">
         <f t="shared" si="38"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE89" s="124" t="str">
         <f>J65</f>
@@ -58257,7 +58284,7 @@
       </c>
       <c r="AR89" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCEFGIJ</v>
+        <v>BCFGHIJ</v>
       </c>
       <c r="AS89" s="129" t="str">
         <f t="shared" si="46"/>
@@ -58280,11 +58307,11 @@
       <c r="I90" s="69"/>
       <c r="J90" s="102" t="str">
         <f>VLOOKUP(10,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓗ Saudi Arabia</v>
+        <v>Ⓐ Czech Republic</v>
       </c>
       <c r="K90" s="103">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" s="103">
         <f>VLOOKUP(10,$AD$80:$AN$91,3,FALSE)</f>
@@ -58296,11 +58323,11 @@
       </c>
       <c r="N90" s="103">
         <f>VLOOKUP(10,$AD$80:$AN$91,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O90" s="103" t="str">
         <f>VLOOKUP(10,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(10,$AD$80:$AN$91,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 2</v>
       </c>
       <c r="P90" s="104">
         <f t="shared" si="48"/>
@@ -58371,7 +58398,7 @@
       </c>
       <c r="AR90" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCEFGIJ</v>
+        <v>BCFGHIJ</v>
       </c>
       <c r="AS90" s="129" t="str">
         <f t="shared" si="46"/>
@@ -58394,7 +58421,7 @@
       <c r="I91" s="69"/>
       <c r="J91" s="102" t="str">
         <f>VLOOKUP(11,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓐ Czech Republic</v>
+        <v>Ⓔ Ecuador</v>
       </c>
       <c r="K91" s="103">
         <f t="shared" si="47"/>
@@ -58414,7 +58441,7 @@
       </c>
       <c r="O91" s="103" t="str">
         <f>VLOOKUP(11,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(11,$AD$80:$AN$91,7,FALSE)</f>
-        <v>1 - 2</v>
+        <v>0 - 1</v>
       </c>
       <c r="P91" s="104">
         <f t="shared" si="48"/>
@@ -58434,7 +58461,7 @@
       </c>
       <c r="AD91" s="123">
         <f t="shared" si="38"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE91" s="124" t="str">
         <f>J77</f>
@@ -58485,7 +58512,7 @@
       </c>
       <c r="AR91" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCEFGIJL</v>
+        <v>BCFGHIJL</v>
       </c>
       <c r="AS91" s="129" t="str">
         <f t="shared" si="46"/>
@@ -58548,7 +58575,7 @@
       </c>
       <c r="AI92" s="123">
         <f>MAX(AI80:AI91)+1</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ92" s="123">
         <f>MAX(AJ80:AJ91)+1</f>
@@ -58725,11 +58752,31 @@
   <sheetProtection algorithmName="SHA-512" hashValue="7nWuIQAsd0NKRlhwUK3tOeNHpTch5B5FULy2gxNNaIdJM5RfhFSMzPcx55y+pmM3d73guUy+p5Y+SvIjJZQRaA==" saltValue="Uw23KnM8csnTioq5H8upCA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <dataConsolidate/>
   <mergeCells count="45">
-    <mergeCell ref="BK14:BK15"/>
-    <mergeCell ref="BY16:BY17"/>
-    <mergeCell ref="BK26:BK27"/>
-    <mergeCell ref="BR28:BR29"/>
-    <mergeCell ref="BK22:BK23"/>
+    <mergeCell ref="CK68:CQ69"/>
+    <mergeCell ref="C83:G88"/>
+    <mergeCell ref="BK70:BK71"/>
+    <mergeCell ref="BY48:BY49"/>
+    <mergeCell ref="BY64:BY65"/>
+    <mergeCell ref="CF55:CF56"/>
+    <mergeCell ref="BK58:BK59"/>
+    <mergeCell ref="BR60:BR61"/>
+    <mergeCell ref="BK62:BK63"/>
+    <mergeCell ref="BK66:BK67"/>
+    <mergeCell ref="BR68:BR69"/>
+    <mergeCell ref="BK50:BK51"/>
+    <mergeCell ref="BR52:BR53"/>
+    <mergeCell ref="BK54:BK55"/>
+    <mergeCell ref="CE68:CJ69"/>
+    <mergeCell ref="CF6:CJ7"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="A5:H6"/>
+    <mergeCell ref="J5:P6"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="BR12:BR13"/>
+    <mergeCell ref="BK6:BO7"/>
+    <mergeCell ref="BR6:BV7"/>
+    <mergeCell ref="BY6:CC7"/>
     <mergeCell ref="CF23:CF24"/>
     <mergeCell ref="BK18:BK19"/>
     <mergeCell ref="BR20:BR21"/>
@@ -58745,31 +58792,11 @@
     <mergeCell ref="BK42:BK43"/>
     <mergeCell ref="CM33:CQ34"/>
     <mergeCell ref="CM37:CM38"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="BR12:BR13"/>
-    <mergeCell ref="BK6:BO7"/>
-    <mergeCell ref="BR6:BV7"/>
-    <mergeCell ref="BY6:CC7"/>
-    <mergeCell ref="CF6:CJ7"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="A5:H6"/>
-    <mergeCell ref="J5:P6"/>
-    <mergeCell ref="CK68:CQ69"/>
-    <mergeCell ref="C83:G88"/>
-    <mergeCell ref="BK70:BK71"/>
-    <mergeCell ref="BY48:BY49"/>
-    <mergeCell ref="BY64:BY65"/>
-    <mergeCell ref="CF55:CF56"/>
-    <mergeCell ref="BK58:BK59"/>
-    <mergeCell ref="BR60:BR61"/>
-    <mergeCell ref="BK62:BK63"/>
-    <mergeCell ref="BK66:BK67"/>
-    <mergeCell ref="BR68:BR69"/>
-    <mergeCell ref="BK50:BK51"/>
-    <mergeCell ref="BR52:BR53"/>
-    <mergeCell ref="BK54:BK55"/>
-    <mergeCell ref="CE68:CJ69"/>
+    <mergeCell ref="BK14:BK15"/>
+    <mergeCell ref="BY16:BY17"/>
+    <mergeCell ref="BK26:BK27"/>
+    <mergeCell ref="BR28:BR29"/>
+    <mergeCell ref="BK22:BK23"/>
   </mergeCells>
   <conditionalFormatting sqref="A7:E78">
     <cfRule type="expression" dxfId="228" priority="339">
@@ -60066,15 +60093,15 @@
     <row r="3" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B3" s="109">
         <f>MATCH(C3,C6:C500,0)</f>
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="C3" s="121" t="str">
         <f>'2026 World Cup'!AR91</f>
-        <v>BCEFGIJL</v>
+        <v>BCFGHIJL</v>
       </c>
       <c r="D3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,2,FALSE)</f>
-        <v>3E</v>
+        <v>3H</v>
       </c>
       <c r="E3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,3,FALSE)</f>

--- a/public/worldcup.xlsx
+++ b/public/worldcup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rylanpaul/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C29F59D-1C50-534C-8905-E307811F3961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E9FCAB3-1F0B-9447-9030-EF88896AC3FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T" sheetId="1" state="hidden" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9880" uniqueCount="3715">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9881" uniqueCount="3715">
   <si>
     <t>English</t>
   </si>
@@ -13305,12 +13305,56 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -13391,50 +13435,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -39010,13 +39010,13 @@
       <c r="B6" s="145" t="s">
         <v>2395</v>
       </c>
-      <c r="C6" s="146" t="e">
+      <c r="C6" s="146">
         <f>IFERROR(_xlfn.XLOOKUP(B6,Rounds!A$2:A$25,Rounds!B$2:B$25), _xlfn.XLOOKUP(B6,Rounds!D$2:D$25,Rounds!C$2:C$25))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D6" s="146" t="e">
+        <v>4</v>
+      </c>
+      <c r="D6" s="146">
         <f>IFERROR(_xlfn.XLOOKUP(B6,Rounds!A$2:A$25,Rounds!C$2:C$25), _xlfn.XLOOKUP(B6,Rounds!D$2:D$25,Rounds!B$2:B$25))</f>
-        <v>#N/A</v>
+        <v>1</v>
       </c>
       <c r="E6" s="147" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(B6,Rounds!A$2:A$25,Rounds!D$2:D$25), _xlfn.XLOOKUP(B6,Rounds!D$2:D$25,Rounds!A$2:A$25))</f>
@@ -39230,7 +39230,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(B8,Rounds!A$2:A$25,Rounds!D$2:D$25), _xlfn.XLOOKUP(B8,Rounds!D$2:D$25,Rounds!A$2:A$25))</f>
         <v>Qatar</v>
       </c>
-      <c r="F8" s="152"/>
+      <c r="F8" s="152" t="s">
+        <v>1093</v>
+      </c>
       <c r="G8" s="150" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(F8,Rounds!E$2:E$25,Rounds!F$2:F$25), _xlfn.XLOOKUP(F8,Rounds!H$2:H$25,Rounds!G$2:G$25))</f>
         <v>#N/A</v>
@@ -39239,9 +39241,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(F8,Rounds!E$2:E$25,Rounds!G$2:G$25), _xlfn.XLOOKUP(F8,Rounds!H$2:H$25,Rounds!F$2:F$25))</f>
         <v>#N/A</v>
       </c>
-      <c r="I8" s="151" t="e">
+      <c r="I8" s="151" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F8,Rounds!E$2:E$25,Rounds!H$2:H$25), _xlfn.XLOOKUP(F8,Rounds!H$2:H$25,Rounds!E$2:E$25))</f>
-        <v>#N/A</v>
+        <v>Curaçao</v>
       </c>
       <c r="J8" s="152"/>
       <c r="K8" s="150" t="e">
@@ -40554,11 +40556,11 @@
       <c r="A18" s="132" t="str">
         <v>France</v>
       </c>
-      <c r="B18" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C18" s="81" t="e">
-        <v>#N/A</v>
+      <c r="B18" s="81">
+        <v>3</v>
+      </c>
+      <c r="C18" s="81">
+        <v>1</v>
       </c>
       <c r="D18" s="134" t="str">
         <v>Senegal</v>
@@ -40592,11 +40594,11 @@
       <c r="A19" s="132" t="str">
         <v>Iraq</v>
       </c>
-      <c r="B19" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C19" s="81" t="e">
-        <v>#N/A</v>
+      <c r="B19" s="81">
+        <v>1</v>
+      </c>
+      <c r="C19" s="81">
+        <v>4</v>
       </c>
       <c r="D19" s="134" t="str">
         <v>Norway</v>
@@ -40934,25 +40936,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:95" ht="47" x14ac:dyDescent="0.2">
-      <c r="A1" s="171" t="str" cm="1">
+      <c r="A1" s="182" t="str" cm="1">
         <f t="array" ref="A1">INDEX(T,2,lang)</f>
         <v>2026 World Cup Final Tournament Schedule</v>
       </c>
-      <c r="B1" s="171"/>
-      <c r="C1" s="171"/>
-      <c r="D1" s="171"/>
-      <c r="E1" s="171"/>
-      <c r="F1" s="171"/>
-      <c r="G1" s="171"/>
-      <c r="H1" s="171"/>
-      <c r="I1" s="171"/>
-      <c r="J1" s="171"/>
-      <c r="K1" s="171"/>
-      <c r="L1" s="171"/>
-      <c r="M1" s="171"/>
-      <c r="N1" s="171"/>
-      <c r="O1" s="171"/>
-      <c r="P1" s="171"/>
+      <c r="B1" s="182"/>
+      <c r="C1" s="182"/>
+      <c r="D1" s="182"/>
+      <c r="E1" s="182"/>
+      <c r="F1" s="182"/>
+      <c r="G1" s="182"/>
+      <c r="H1" s="182"/>
+      <c r="I1" s="182"/>
+      <c r="J1" s="182"/>
+      <c r="K1" s="182"/>
+      <c r="L1" s="182"/>
+      <c r="M1" s="182"/>
+      <c r="N1" s="182"/>
+      <c r="O1" s="182"/>
+      <c r="P1" s="182"/>
       <c r="S1" s="123"/>
       <c r="T1" s="123"/>
       <c r="AC1" s="123"/>
@@ -40999,11 +41001,11 @@
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
-      <c r="O3" s="172" t="str">
+      <c r="O3" s="183" t="str">
         <f>"Language: " &amp; Settings!C4</f>
         <v>Language: English</v>
       </c>
-      <c r="P3" s="172"/>
+      <c r="P3" s="183"/>
       <c r="S3" s="123"/>
       <c r="T3" s="123"/>
       <c r="AC3" s="123"/>
@@ -41021,43 +41023,43 @@
     </row>
     <row r="4" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:95" x14ac:dyDescent="0.2">
-      <c r="A5" s="173" t="str" cm="1">
+      <c r="A5" s="184" t="str" cm="1">
         <f t="array" ref="A5">INDEX(T,3,lang)</f>
         <v>Group Stage</v>
       </c>
-      <c r="B5" s="174"/>
-      <c r="C5" s="174"/>
-      <c r="D5" s="174"/>
-      <c r="E5" s="174"/>
-      <c r="F5" s="174"/>
-      <c r="G5" s="174"/>
-      <c r="H5" s="175"/>
-      <c r="J5" s="179" t="s">
+      <c r="B5" s="185"/>
+      <c r="C5" s="185"/>
+      <c r="D5" s="185"/>
+      <c r="E5" s="185"/>
+      <c r="F5" s="185"/>
+      <c r="G5" s="185"/>
+      <c r="H5" s="186"/>
+      <c r="J5" s="190" t="s">
         <v>3166</v>
       </c>
-      <c r="K5" s="180"/>
-      <c r="L5" s="180"/>
-      <c r="M5" s="180"/>
-      <c r="N5" s="180"/>
-      <c r="O5" s="180"/>
-      <c r="P5" s="181"/>
+      <c r="K5" s="191"/>
+      <c r="L5" s="191"/>
+      <c r="M5" s="191"/>
+      <c r="N5" s="191"/>
+      <c r="O5" s="191"/>
+      <c r="P5" s="192"/>
     </row>
     <row r="6" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="176"/>
-      <c r="B6" s="177"/>
-      <c r="C6" s="177"/>
-      <c r="D6" s="177"/>
-      <c r="E6" s="177"/>
-      <c r="F6" s="177"/>
-      <c r="G6" s="177"/>
-      <c r="H6" s="178"/>
-      <c r="J6" s="182"/>
-      <c r="K6" s="183"/>
-      <c r="L6" s="183"/>
-      <c r="M6" s="183"/>
-      <c r="N6" s="183"/>
-      <c r="O6" s="183"/>
-      <c r="P6" s="184"/>
+      <c r="A6" s="187"/>
+      <c r="B6" s="188"/>
+      <c r="C6" s="188"/>
+      <c r="D6" s="188"/>
+      <c r="E6" s="188"/>
+      <c r="F6" s="188"/>
+      <c r="G6" s="188"/>
+      <c r="H6" s="189"/>
+      <c r="J6" s="193"/>
+      <c r="K6" s="194"/>
+      <c r="L6" s="194"/>
+      <c r="M6" s="194"/>
+      <c r="N6" s="194"/>
+      <c r="O6" s="194"/>
+      <c r="P6" s="195"/>
       <c r="R6" s="123" t="s">
         <v>3167</v>
       </c>
@@ -41167,37 +41169,37 @@
       <c r="BI6" s="128" t="s">
         <v>3178</v>
       </c>
-      <c r="BK6" s="165" t="s">
+      <c r="BK6" s="176" t="s">
         <v>3179</v>
       </c>
-      <c r="BL6" s="166"/>
-      <c r="BM6" s="166"/>
-      <c r="BN6" s="166"/>
-      <c r="BO6" s="167"/>
-      <c r="BR6" s="165" t="str" cm="1">
+      <c r="BL6" s="177"/>
+      <c r="BM6" s="177"/>
+      <c r="BN6" s="177"/>
+      <c r="BO6" s="178"/>
+      <c r="BR6" s="176" t="str" cm="1">
         <f t="array" ref="BR6">INDEX(T,4,lang)</f>
         <v>Round of 16</v>
       </c>
-      <c r="BS6" s="166"/>
-      <c r="BT6" s="166"/>
-      <c r="BU6" s="166"/>
-      <c r="BV6" s="167"/>
-      <c r="BY6" s="165" t="str" cm="1">
+      <c r="BS6" s="177"/>
+      <c r="BT6" s="177"/>
+      <c r="BU6" s="177"/>
+      <c r="BV6" s="178"/>
+      <c r="BY6" s="176" t="str" cm="1">
         <f t="array" ref="BY6">INDEX(T,5,lang)</f>
         <v>Quarterfinals</v>
       </c>
-      <c r="BZ6" s="166"/>
-      <c r="CA6" s="166"/>
-      <c r="CB6" s="166"/>
-      <c r="CC6" s="167"/>
-      <c r="CF6" s="165" t="str" cm="1">
+      <c r="BZ6" s="177"/>
+      <c r="CA6" s="177"/>
+      <c r="CB6" s="177"/>
+      <c r="CC6" s="178"/>
+      <c r="CF6" s="176" t="str" cm="1">
         <f t="array" ref="CF6">INDEX(T,6,lang)</f>
         <v>Semi-Finals</v>
       </c>
-      <c r="CG6" s="166"/>
-      <c r="CH6" s="166"/>
-      <c r="CI6" s="166"/>
-      <c r="CJ6" s="167"/>
+      <c r="CG6" s="177"/>
+      <c r="CH6" s="177"/>
+      <c r="CI6" s="177"/>
+      <c r="CJ6" s="178"/>
     </row>
     <row r="7" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="11">
@@ -41274,26 +41276,26 @@
         <v>1</v>
       </c>
       <c r="AY7" s="126"/>
-      <c r="BK7" s="168"/>
-      <c r="BL7" s="169"/>
-      <c r="BM7" s="169"/>
-      <c r="BN7" s="169"/>
-      <c r="BO7" s="170"/>
-      <c r="BR7" s="168"/>
-      <c r="BS7" s="169"/>
-      <c r="BT7" s="169"/>
-      <c r="BU7" s="169"/>
-      <c r="BV7" s="170"/>
-      <c r="BY7" s="168"/>
-      <c r="BZ7" s="169"/>
-      <c r="CA7" s="169"/>
-      <c r="CB7" s="169"/>
-      <c r="CC7" s="170"/>
-      <c r="CF7" s="168"/>
-      <c r="CG7" s="169"/>
-      <c r="CH7" s="169"/>
-      <c r="CI7" s="169"/>
-      <c r="CJ7" s="170"/>
+      <c r="BK7" s="179"/>
+      <c r="BL7" s="180"/>
+      <c r="BM7" s="180"/>
+      <c r="BN7" s="180"/>
+      <c r="BO7" s="181"/>
+      <c r="BR7" s="179"/>
+      <c r="BS7" s="180"/>
+      <c r="BT7" s="180"/>
+      <c r="BU7" s="180"/>
+      <c r="BV7" s="181"/>
+      <c r="BY7" s="179"/>
+      <c r="BZ7" s="180"/>
+      <c r="CA7" s="180"/>
+      <c r="CB7" s="180"/>
+      <c r="CC7" s="181"/>
+      <c r="CF7" s="179"/>
+      <c r="CG7" s="180"/>
+      <c r="CH7" s="180"/>
+      <c r="CI7" s="180"/>
+      <c r="CJ7" s="181"/>
     </row>
     <row r="8" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A8" s="16">
@@ -42029,7 +42031,7 @@
         <f>BH10/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK10" s="163">
+      <c r="BK10" s="173">
         <v>74</v>
       </c>
       <c r="BL10" s="24" t="str">
@@ -42292,7 +42294,7 @@
         <f>BH11/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK11" s="164"/>
+      <c r="BK11" s="174"/>
       <c r="BL11" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!G3,AK80:AS91,9,FALSE),"3rd Group A/B/C/D/F")</f>
         <v>3rd Group A/B/C/D/F</v>
@@ -42530,7 +42532,7 @@
       <c r="BO12" s="21"/>
       <c r="BP12" s="114"/>
       <c r="BQ12" s="112"/>
-      <c r="BR12" s="163">
+      <c r="BR12" s="173">
         <v>89</v>
       </c>
       <c r="BS12" s="24" t="str">
@@ -42651,7 +42653,7 @@
         <v>46203.875</v>
       </c>
       <c r="BQ13" s="115"/>
-      <c r="BR13" s="164"/>
+      <c r="BR13" s="174"/>
       <c r="BS13" s="26" t="str">
         <f>IF(BP14&gt;BP15,BL14,IF(BP14&lt;BP15,BL15,""))</f>
         <v/>
@@ -42909,7 +42911,7 @@
         <f>BH14/BH18</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK14" s="163">
+      <c r="BK14" s="173">
         <v>77</v>
       </c>
       <c r="BL14" s="24" t="str">
@@ -43176,7 +43178,7 @@
         <f>BH15/BH18</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK15" s="164"/>
+      <c r="BK15" s="174"/>
       <c r="BL15" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!I3,AK80:AS91,9,FALSE),"3rd Group C/D/F/G/H")</f>
         <v>3rd Group C/D/F/G/H</v>
@@ -43450,7 +43452,7 @@
       <c r="BV16" s="21"/>
       <c r="BW16" s="114"/>
       <c r="BX16" s="112"/>
-      <c r="BY16" s="163">
+      <c r="BY16" s="173">
         <v>97</v>
       </c>
       <c r="BZ16" s="24" t="str">
@@ -43712,7 +43714,7 @@
       <c r="BV17" s="21"/>
       <c r="BW17" s="114"/>
       <c r="BX17" s="115"/>
-      <c r="BY17" s="164"/>
+      <c r="BY17" s="174"/>
       <c r="BZ17" s="26" t="str">
         <f>IF(BW20&gt;BW21,BS20,IF(BW20&lt;BW21,BS21,""))</f>
         <v/>
@@ -43916,7 +43918,7 @@
         <f>MAX(BH14:BH17)+1</f>
         <v>102</v>
       </c>
-      <c r="BK18" s="163">
+      <c r="BK18" s="173">
         <v>73</v>
       </c>
       <c r="BL18" s="24" t="str">
@@ -44024,7 +44026,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BK19" s="164"/>
+      <c r="BK19" s="174"/>
       <c r="BL19" s="26" t="str">
         <f>AS15</f>
         <v>2B</v>
@@ -44302,7 +44304,7 @@
       <c r="BO20" s="21"/>
       <c r="BP20" s="114"/>
       <c r="BQ20" s="112"/>
-      <c r="BR20" s="163">
+      <c r="BR20" s="173">
         <v>90</v>
       </c>
       <c r="BS20" s="24" t="str">
@@ -44575,7 +44577,7 @@
         <v>46203.041666666672</v>
       </c>
       <c r="BQ21" s="115"/>
-      <c r="BR21" s="164"/>
+      <c r="BR21" s="174"/>
       <c r="BS21" s="26" t="str">
         <f>IF(BP22&gt;BP23,BL22,IF(BP22&lt;BP23,BL23,""))</f>
         <v/>
@@ -44829,7 +44831,7 @@
         <f>BH22/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK22" s="163">
+      <c r="BK22" s="173">
         <v>75</v>
       </c>
       <c r="BL22" s="24" t="str">
@@ -44891,8 +44893,12 @@
         <f>AE56</f>
         <v>France</v>
       </c>
-      <c r="F23" s="19"/>
-      <c r="G23" s="20"/>
+      <c r="F23" s="19">
+        <v>3</v>
+      </c>
+      <c r="G23" s="20">
+        <v>1</v>
+      </c>
       <c r="H23" s="80" t="str">
         <f>AE57</f>
         <v>Senegal</v>
@@ -44931,11 +44937,11 @@
       </c>
       <c r="S23" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>France_win</v>
       </c>
       <c r="T23" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Senegal_lose</v>
       </c>
       <c r="U23" s="123">
         <f t="shared" si="8"/>
@@ -44965,9 +44971,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB23" s="123" t="str">
+      <c r="AB23" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD23" s="123">
         <f>COUNTIF(AR20:AR23,CONCATENATE("&gt;=",AR23))</f>
@@ -45089,7 +45095,7 @@
         <f>BH23/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK23" s="164"/>
+      <c r="BK23" s="174"/>
       <c r="BL23" s="26" t="str">
         <f>AS21</f>
         <v>2C</v>
@@ -45116,7 +45122,7 @@
       <c r="CC23" s="21"/>
       <c r="CD23" s="114"/>
       <c r="CE23" s="112"/>
-      <c r="CF23" s="163">
+      <c r="CF23" s="173">
         <v>101</v>
       </c>
       <c r="CG23" s="24" t="str">
@@ -45151,8 +45157,12 @@
         <f>AE58</f>
         <v>Iraq</v>
       </c>
-      <c r="F24" s="19"/>
-      <c r="G24" s="20"/>
+      <c r="F24" s="19">
+        <v>1</v>
+      </c>
+      <c r="G24" s="20">
+        <v>4</v>
+      </c>
       <c r="H24" s="80" t="str">
         <f>AE59</f>
         <v>Norway</v>
@@ -45191,11 +45201,11 @@
       </c>
       <c r="S24" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Iraq_lose</v>
       </c>
       <c r="T24" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Norway_win</v>
       </c>
       <c r="U24" s="123">
         <f t="shared" si="8"/>
@@ -45225,9 +45235,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB24" s="123" t="str">
+      <c r="AB24" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>-1</v>
       </c>
       <c r="AF24" s="123">
         <f t="shared" ref="AF24:AH24" si="14">MAX(AF20:AF23)-MIN(AF20:AF23)+1</f>
@@ -45333,7 +45343,7 @@
       <c r="CC24" s="21"/>
       <c r="CD24" s="114"/>
       <c r="CE24" s="115"/>
-      <c r="CF24" s="164"/>
+      <c r="CF24" s="174"/>
       <c r="CG24" s="26" t="str">
         <f>IF(CD32&gt;CD33,BZ32,IF(CD32&lt;CD33,BZ33,""))</f>
         <v/>
@@ -45678,7 +45688,7 @@
         <f>BH26/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK26" s="163">
+      <c r="BK26" s="173">
         <v>83</v>
       </c>
       <c r="BL26" s="24" t="str">
@@ -45942,7 +45952,7 @@
         <f>BH27/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK27" s="164"/>
+      <c r="BK27" s="174"/>
       <c r="BL27" s="26" t="str">
         <f>AS75</f>
         <v>2L</v>
@@ -46213,7 +46223,7 @@
       <c r="BO28" s="21"/>
       <c r="BP28" s="114"/>
       <c r="BQ28" s="112"/>
-      <c r="BR28" s="163">
+      <c r="BR28" s="173">
         <v>93</v>
       </c>
       <c r="BS28" s="24" t="str">
@@ -46474,7 +46484,7 @@
         <v>46205.791666666672</v>
       </c>
       <c r="BQ29" s="115"/>
-      <c r="BR29" s="164"/>
+      <c r="BR29" s="174"/>
       <c r="BS29" s="26" t="str">
         <f>IF(BP30&gt;BP31,BL30,IF(BP30&lt;BP31,BL31,""))</f>
         <v/>
@@ -46684,7 +46694,7 @@
         <f>MAX(BH26:BH29)+1</f>
         <v>1</v>
       </c>
-      <c r="BK30" s="163">
+      <c r="BK30" s="173">
         <v>84</v>
       </c>
       <c r="BL30" s="24" t="str">
@@ -46791,7 +46801,7 @@
         <f>IF(OR(F31="",G31=""),"",IF(F31&gt;G31,1,IF(F31&lt;G31,-1,0)))</f>
         <v/>
       </c>
-      <c r="BK31" s="164"/>
+      <c r="BK31" s="174"/>
       <c r="BL31" s="26" t="str">
         <f>AS63</f>
         <v>2J</v>
@@ -47063,7 +47073,7 @@
       <c r="BV32" s="21"/>
       <c r="BW32" s="114"/>
       <c r="BX32" s="112"/>
-      <c r="BY32" s="163">
+      <c r="BY32" s="173">
         <v>98</v>
       </c>
       <c r="BZ32" s="24" t="str">
@@ -47323,7 +47333,7 @@
       <c r="BV33" s="21"/>
       <c r="BW33" s="114"/>
       <c r="BX33" s="115"/>
-      <c r="BY33" s="164"/>
+      <c r="BY33" s="174"/>
       <c r="BZ33" s="26" t="str">
         <f>IF(BW36&gt;BW37,BS36,IF(BW36&lt;BW37,BS37,""))</f>
         <v/>
@@ -47338,14 +47348,14 @@
       <c r="CE33" s="112"/>
       <c r="CK33" s="114"/>
       <c r="CL33" s="112"/>
-      <c r="CM33" s="165" t="str" cm="1">
+      <c r="CM33" s="176" t="str" cm="1">
         <f t="array" ref="CM33">INDEX(T,8,lang)</f>
         <v>Final</v>
       </c>
-      <c r="CN33" s="166"/>
-      <c r="CO33" s="166"/>
-      <c r="CP33" s="166"/>
-      <c r="CQ33" s="167"/>
+      <c r="CN33" s="177"/>
+      <c r="CO33" s="177"/>
+      <c r="CP33" s="177"/>
+      <c r="CQ33" s="178"/>
     </row>
     <row r="34" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A34" s="16">
@@ -47565,7 +47575,7 @@
         <f>BH34/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK34" s="163">
+      <c r="BK34" s="173">
         <v>81</v>
       </c>
       <c r="BL34" s="24" t="str">
@@ -47596,11 +47606,11 @@
       <c r="CE34" s="112"/>
       <c r="CK34" s="114"/>
       <c r="CL34" s="112"/>
-      <c r="CM34" s="168"/>
-      <c r="CN34" s="169"/>
-      <c r="CO34" s="169"/>
-      <c r="CP34" s="169"/>
-      <c r="CQ34" s="170"/>
+      <c r="CM34" s="179"/>
+      <c r="CN34" s="180"/>
+      <c r="CO34" s="180"/>
+      <c r="CP34" s="180"/>
+      <c r="CQ34" s="181"/>
     </row>
     <row r="35" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A35" s="16">
@@ -47820,7 +47830,7 @@
         <f>BH35/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK35" s="164"/>
+      <c r="BK35" s="174"/>
       <c r="BL35" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!F3,AK80:AS91,9,FALSE),"3rd Group B/E/F/I/J")</f>
         <v>3rd Group B/E/F/I/J</v>
@@ -48045,7 +48055,7 @@
       <c r="BO36" s="21"/>
       <c r="BP36" s="114"/>
       <c r="BQ36" s="112"/>
-      <c r="BR36" s="163">
+      <c r="BR36" s="173">
         <v>94</v>
       </c>
       <c r="BS36" s="24" t="str">
@@ -48165,7 +48175,7 @@
         <v>46204.833333333336</v>
       </c>
       <c r="BQ37" s="115"/>
-      <c r="BR37" s="164"/>
+      <c r="BR37" s="174"/>
       <c r="BS37" s="26" t="str">
         <f>IF(BP38&gt;BP39,BL38,IF(BP38&lt;BP39,BL39,""))</f>
         <v/>
@@ -48192,7 +48202,7 @@
       <c r="CJ37" s="21"/>
       <c r="CK37" s="114"/>
       <c r="CL37" s="112"/>
-      <c r="CM37" s="163">
+      <c r="CM37" s="173">
         <v>104</v>
       </c>
       <c r="CN37" s="24" t="str">
@@ -48429,7 +48439,7 @@
         <f>BH38/BH42</f>
         <v>0.98064516129032253</v>
       </c>
-      <c r="BK38" s="163">
+      <c r="BK38" s="173">
         <v>82</v>
       </c>
       <c r="BL38" s="24" t="str">
@@ -48459,7 +48469,7 @@
       <c r="CI38" s="21"/>
       <c r="CJ38" s="21"/>
       <c r="CL38" s="115"/>
-      <c r="CM38" s="164"/>
+      <c r="CM38" s="174"/>
       <c r="CN38" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG55,IF(CK55&lt;CK56,CG56,""))</f>
         <v/>
@@ -48694,7 +48704,7 @@
         <f>BH39/BH42</f>
         <v>0.98064516129032253</v>
       </c>
-      <c r="BK39" s="164"/>
+      <c r="BK39" s="174"/>
       <c r="BL39" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!H3,AK80:AS91,9,FALSE),"3rd Group A/E/H/I/J")</f>
         <v>3rd Group A/E/H/I/J</v>
@@ -49370,7 +49380,7 @@
         <f>MAX(BH38:BH41)+1</f>
         <v>51.666666666666664</v>
       </c>
-      <c r="BK42" s="163">
+      <c r="BK42" s="173">
         <v>76</v>
       </c>
       <c r="BL42" s="24" t="str">
@@ -49463,7 +49473,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK43" s="164"/>
+      <c r="BK43" s="174"/>
       <c r="BL43" s="26" t="str">
         <f>AS39</f>
         <v>2F</v>
@@ -49719,7 +49729,7 @@
       <c r="BO44" s="21"/>
       <c r="BP44" s="114"/>
       <c r="BQ44" s="112"/>
-      <c r="BR44" s="163">
+      <c r="BR44" s="173">
         <v>91</v>
       </c>
       <c r="BS44" s="24" t="str">
@@ -49734,14 +49744,14 @@
         <v/>
       </c>
       <c r="CK44" s="114"/>
-      <c r="CM44" s="165" t="str" cm="1">
+      <c r="CM44" s="176" t="str" cm="1">
         <f t="array" ref="CM44">INDEX(T,7,lang)</f>
         <v>Third-Place Play-Off</v>
       </c>
-      <c r="CN44" s="166"/>
-      <c r="CO44" s="166"/>
-      <c r="CP44" s="166"/>
-      <c r="CQ44" s="167"/>
+      <c r="CN44" s="177"/>
+      <c r="CO44" s="177"/>
+      <c r="CP44" s="177"/>
+      <c r="CQ44" s="178"/>
     </row>
     <row r="45" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="16">
@@ -49978,7 +49988,7 @@
         <v>46203.708333333336</v>
       </c>
       <c r="BQ45" s="115"/>
-      <c r="BR45" s="164"/>
+      <c r="BR45" s="174"/>
       <c r="BS45" s="26" t="str">
         <f>IF(BP46&gt;BP47,BL46,IF(BP46&lt;BP47,BL47,""))</f>
         <v/>
@@ -49991,11 +50001,11 @@
         <v/>
       </c>
       <c r="CK45" s="114"/>
-      <c r="CM45" s="168"/>
-      <c r="CN45" s="169"/>
-      <c r="CO45" s="169"/>
-      <c r="CP45" s="169"/>
-      <c r="CQ45" s="170"/>
+      <c r="CM45" s="179"/>
+      <c r="CN45" s="180"/>
+      <c r="CO45" s="180"/>
+      <c r="CP45" s="180"/>
+      <c r="CQ45" s="181"/>
     </row>
     <row r="46" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A46" s="16">
@@ -50215,7 +50225,7 @@
         <f>BH46/BH48</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK46" s="163">
+      <c r="BK46" s="173">
         <v>78</v>
       </c>
       <c r="BL46" s="24" t="str">
@@ -50457,7 +50467,7 @@
         <f>BH47/BH48</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK47" s="164"/>
+      <c r="BK47" s="174"/>
       <c r="BL47" s="26" t="str">
         <f>AS57</f>
         <v>2I</v>
@@ -50700,7 +50710,7 @@
       <c r="BV48" s="21"/>
       <c r="BW48" s="114"/>
       <c r="BX48" s="112"/>
-      <c r="BY48" s="163">
+      <c r="BY48" s="173">
         <v>99</v>
       </c>
       <c r="BZ48" s="24" t="str">
@@ -50716,7 +50726,7 @@
       </c>
       <c r="CK48" s="114"/>
       <c r="CL48" s="112"/>
-      <c r="CM48" s="163">
+      <c r="CM48" s="173">
         <v>103</v>
       </c>
       <c r="CN48" s="24" t="str">
@@ -50821,7 +50831,7 @@
       <c r="BV49" s="21"/>
       <c r="BW49" s="114"/>
       <c r="BX49" s="115"/>
-      <c r="BY49" s="164"/>
+      <c r="BY49" s="174"/>
       <c r="BZ49" s="26" t="str">
         <f>IF(BW52&gt;BW53,BS52,IF(BW52&lt;BW53,BS53,""))</f>
         <v/>
@@ -50835,7 +50845,7 @@
       </c>
       <c r="CK49" s="114"/>
       <c r="CL49" s="115"/>
-      <c r="CM49" s="164"/>
+      <c r="CM49" s="174"/>
       <c r="CN49" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG56,IF(CK55&lt;CK56,CG55,""))</f>
         <v/>
@@ -51070,7 +51080,7 @@
         <f>BH50/BH54</f>
         <v>0.98522167487684731</v>
       </c>
-      <c r="BK50" s="163">
+      <c r="BK50" s="173">
         <v>79</v>
       </c>
       <c r="BL50" s="24" t="str">
@@ -51323,7 +51333,7 @@
         <f>BH51/BH54</f>
         <v>0.98522167487684731</v>
       </c>
-      <c r="BK51" s="164"/>
+      <c r="BK51" s="174"/>
       <c r="BL51" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!D3,AK80:AS91,9,FALSE),"3rd Group C/E/F/H/I")</f>
         <v>3rd Group C/E/F/H/I</v>
@@ -51583,7 +51593,7 @@
       <c r="BO52" s="21"/>
       <c r="BP52" s="114"/>
       <c r="BQ52" s="112"/>
-      <c r="BR52" s="163">
+      <c r="BR52" s="173">
         <v>92</v>
       </c>
       <c r="BS52" s="24" t="str">
@@ -51838,7 +51848,7 @@
         <v>46204.666666666672</v>
       </c>
       <c r="BQ53" s="115"/>
-      <c r="BR53" s="164"/>
+      <c r="BR53" s="174"/>
       <c r="BS53" s="26" t="str">
         <f>IF(BP54&gt;BP55,BL54,IF(BP54&lt;BP55,BL55,""))</f>
         <v/>
@@ -52042,7 +52052,7 @@
         <f>MAX(BH50:BH53)+1</f>
         <v>101.5</v>
       </c>
-      <c r="BK54" s="163">
+      <c r="BK54" s="173">
         <v>80</v>
       </c>
       <c r="BL54" s="24" t="str">
@@ -52163,7 +52173,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK55" s="164"/>
+      <c r="BK55" s="174"/>
       <c r="BL55" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!K3,AK80:AS91,9,FALSE),"3rd Group E/H/I/J/K")</f>
         <v>3rd Group E/H/I/J/K</v>
@@ -52190,7 +52200,7 @@
       <c r="CC55" s="21"/>
       <c r="CD55" s="114"/>
       <c r="CE55" s="112"/>
-      <c r="CF55" s="163">
+      <c r="CF55" s="173">
         <v>102</v>
       </c>
       <c r="CG55" s="24" t="str">
@@ -52307,7 +52317,7 @@
       </c>
       <c r="AD56" s="123">
         <f>COUNTIF(AR56:AR59,CONCATENATE("&gt;=",AR56))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE56" s="124" t="str">
         <f>VLOOKUP("France",T,lang,FALSE)</f>
@@ -52315,7 +52325,7 @@
       </c>
       <c r="AF56" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE56 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG56" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE56 &amp; "_draw")</f>
@@ -52327,31 +52337,31 @@
       </c>
       <c r="AI56" s="123">
         <f>SUMIF($E$7:$E$78,$AE56,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE56,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AJ56" s="123">
         <f>SUMIF($E$7:$E$78,$AE56,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE56,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL56" s="123">
         <f>AI56-AJ56</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM56" s="123">
         <f>AL56-AL60</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AN56" s="123">
         <f>AF56*3+AG56</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO56" s="123">
         <f>AN56/AN60*10+BA56</f>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AP56" s="123">
         <f>AO56*10000000+BI56*100+AM56/AM60*10+AI56/AI60*1++IF(AQ56=0,ROW(),AQ56)/2000000</f>
-        <v>9.3866000000000002E-4</v>
+        <v>75000007.743795797</v>
       </c>
       <c r="AQ56" s="126">
         <f>VLOOKUP(AE56,db_fifarank,2,FALSE)</f>
@@ -52359,7 +52369,7 @@
       </c>
       <c r="AR56" s="125">
         <f>AP56/AP60</f>
-        <v>9.3777974366581059E-4</v>
+        <v>0.99999996495456167</v>
       </c>
       <c r="AS56" s="125" t="str">
         <f>IF(SUM(AF56:AH59)=12,J57,"1I")</f>
@@ -52449,7 +52459,7 @@
       <c r="CC56" s="21"/>
       <c r="CD56" s="114"/>
       <c r="CE56" s="115"/>
-      <c r="CF56" s="164"/>
+      <c r="CF56" s="174"/>
       <c r="CG56" s="26" t="str">
         <f>IF(CD64&gt;CD65,BZ64,IF(CD64&lt;CD65,BZ65,""))</f>
         <v/>
@@ -52492,15 +52502,15 @@
       <c r="I57" s="69"/>
       <c r="J57" s="30" t="str">
         <f>VLOOKUP(1,AD56:AN59,2,FALSE)</f>
-        <v>France</v>
+        <v>Norway</v>
       </c>
       <c r="K57" s="31">
         <f>L57+M57+N57</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" s="31">
         <f>VLOOKUP(1,AD56:AN59,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" s="31">
         <f>VLOOKUP(1,AD56:AN59,4,FALSE)</f>
@@ -52512,11 +52522,11 @@
       </c>
       <c r="O57" s="31" t="str">
         <f>VLOOKUP(1,AD56:AN59,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD56:AN59,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>4 - 1</v>
       </c>
       <c r="P57" s="32">
         <f>L57*3+M57</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R57" s="123">
         <f>DATE(2026,6,24)+TIME(8,0,0)+gmt_delta</f>
@@ -52564,7 +52574,7 @@
       </c>
       <c r="AD57" s="123">
         <f>COUNTIF(AR56:AR59,CONCATENATE("&gt;=",AR57))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE57" s="124" t="str">
         <f>VLOOKUP("Senegal",T,lang,FALSE)</f>
@@ -52580,23 +52590,23 @@
       </c>
       <c r="AH57" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE57 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI57" s="123">
         <f>SUMIF($E$7:$E$78,$AE57,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE57,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ57" s="123">
         <f>SUMIF($E$7:$E$78,$AE57,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE57,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL57" s="123">
         <f>AI57-AJ57</f>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AM57" s="123">
         <f>AL57-AL60</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN57" s="123">
         <f>AF57*3+AG57</f>
@@ -52608,7 +52618,7 @@
       </c>
       <c r="AP57" s="123">
         <f>AO57*10000000+BI57*100+AM57/AM60*10+AI57/AI60*1++IF(AQ57=0,ROW(),AQ57)/2000000</f>
-        <v>8.4449500000000001E-4</v>
+        <v>1.6294159235714283</v>
       </c>
       <c r="AQ57" s="126">
         <f>VLOOKUP(AE57,db_fifarank,2,FALSE)</f>
@@ -52616,7 +52626,7 @@
       </c>
       <c r="AR57" s="125">
         <f>AP57/AP60</f>
-        <v>8.4370304969537283E-4</v>
+        <v>2.172554264306223E-8</v>
       </c>
       <c r="AS57" s="125" t="str">
         <f>IF(SUM(AF56:AH59)=12,J58,"2I")</f>
@@ -52742,15 +52752,15 @@
       <c r="I58" s="69"/>
       <c r="J58" s="33" t="str">
         <f>VLOOKUP(2,AD56:AN59,2,FALSE)</f>
-        <v>Senegal</v>
+        <v>France</v>
       </c>
       <c r="K58" s="23">
         <f>L58+M58+N58</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="23">
         <f>VLOOKUP(2,AD56:AN59,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" s="23">
         <f>VLOOKUP(2,AD56:AN59,4,FALSE)</f>
@@ -52762,11 +52772,11 @@
       </c>
       <c r="O58" s="23" t="str">
         <f>VLOOKUP(2,AD56:AN59,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD56:AN59,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>3 - 1</v>
       </c>
       <c r="P58" s="34">
         <f>L58*3+M58</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R58" s="123">
         <f>DATE(2026,6,24)+TIME(8,0,0)+gmt_delta</f>
@@ -52830,19 +52840,19 @@
       </c>
       <c r="AH58" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE58 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI58" s="123">
         <f>SUMIF($E$7:$E$78,$AE58,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE58,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ58" s="123">
         <f>SUMIF($E$7:$E$78,$AE58,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE58,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL58" s="123">
         <f>AI58-AJ58</f>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AM58" s="123">
         <f>AL58-AL60</f>
@@ -52858,7 +52868,7 @@
       </c>
       <c r="AP58" s="123">
         <f>AO58*10000000+BI58*100+AM58/AM60*10+AI58/AI60*1++IF(AQ58=0,ROW(),AQ58)/2000000</f>
-        <v>7.2357000000000009E-4</v>
+        <v>0.20072357000000002</v>
       </c>
       <c r="AQ58" s="126">
         <f>VLOOKUP(AE58,db_fifarank,2,FALSE)</f>
@@ -52866,7 +52876,7 @@
       </c>
       <c r="AR58" s="125">
         <f>AP58/AP60</f>
-        <v>7.2289145071087577E-4</v>
+        <v>2.6763138965430164E-9</v>
       </c>
       <c r="AT58" s="126" cm="1">
         <f t="array" ref="AT58">SUMPRODUCT(($S$7:$S$78=AE58&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE58&amp;"_win")*($U$7:$U$78))</f>
@@ -52932,7 +52942,7 @@
         <f>BH58/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK58" s="163">
+      <c r="BK58" s="173">
         <v>86</v>
       </c>
       <c r="BL58" s="24" t="str">
@@ -52990,11 +53000,11 @@
       <c r="I59" s="69"/>
       <c r="J59" s="33" t="str">
         <f>VLOOKUP(3,AD56:AN59,2,FALSE)</f>
-        <v>Norway</v>
+        <v>Senegal</v>
       </c>
       <c r="K59" s="23">
         <f>L59+M59+N59</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="23">
         <f>VLOOKUP(3,AD56:AN59,3,FALSE)</f>
@@ -53006,11 +53016,11 @@
       </c>
       <c r="N59" s="23">
         <f>VLOOKUP(3,AD56:AN59,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O59" s="23" t="str">
         <f>VLOOKUP(3,AD56:AN59,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD56:AN59,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 3</v>
       </c>
       <c r="P59" s="34">
         <f>L59*3+M59</f>
@@ -53062,7 +53072,7 @@
       </c>
       <c r="AD59" s="123">
         <f>COUNTIF(AR56:AR59,CONCATENATE("&gt;=",AR59))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE59" s="124" t="str">
         <f>VLOOKUP("Norway",T,lang,FALSE)</f>
@@ -53070,7 +53080,7 @@
       </c>
       <c r="AF59" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE59 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG59" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE59 &amp; "_draw")</f>
@@ -53082,31 +53092,31 @@
       </c>
       <c r="AI59" s="123">
         <f>SUMIF($E$7:$E$78,$AE59,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE59,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ59" s="123">
         <f>SUMIF($E$7:$E$78,$AE59,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE59,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL59" s="123">
         <f>AI59-AJ59</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AM59" s="123">
         <f>AL59-AL60</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AN59" s="123">
         <f>AF59*3+AG59</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO59" s="123">
         <f>AN59/AN60*10+BA59</f>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AP59" s="123">
         <f>AO59*10000000+BI59*100+AM59/AM60*10+AI59/AI60*1++IF(AQ59=0,ROW(),AQ59)/2000000</f>
-        <v>7.7547E-4</v>
+        <v>75000009.372204036</v>
       </c>
       <c r="AQ59" s="126">
         <f>VLOOKUP(AE59,db_fifarank,2,FALSE)</f>
@@ -53114,7 +53124,7 @@
       </c>
       <c r="AR59" s="125">
         <f>AP59/AP60</f>
-        <v>7.7474277994217945E-4</v>
+        <v>0.99999998666666856</v>
       </c>
       <c r="AT59" s="126" cm="1">
         <f t="array" ref="AT59">SUMPRODUCT(($S$7:$S$78=AE59&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE59&amp;"_win")*($U$7:$U$78))</f>
@@ -53180,7 +53190,7 @@
         <f>BH59/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK59" s="164"/>
+      <c r="BK59" s="174"/>
       <c r="BL59" s="26" t="str">
         <f>AS51</f>
         <v>2H</v>
@@ -53246,7 +53256,7 @@
       </c>
       <c r="K60" s="36">
         <f>L60+M60+N60</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" s="36">
         <f>VLOOKUP(4,AD56:AN59,3,FALSE)</f>
@@ -53258,11 +53268,11 @@
       </c>
       <c r="N60" s="36">
         <f>VLOOKUP(4,AD56:AN59,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O60" s="36" t="str">
         <f>VLOOKUP(4,AD56:AN59,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD56:AN59,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 4</v>
       </c>
       <c r="P60" s="37">
         <f>L60*3+M60</f>
@@ -53314,7 +53324,7 @@
       </c>
       <c r="AF60" s="123">
         <f t="shared" ref="AF60:AH60" si="27">MAX(AF56:AF59)-MIN(AF56:AF59)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG60" s="123">
         <f t="shared" si="27"/>
@@ -53322,31 +53332,31 @@
       </c>
       <c r="AH60" s="123">
         <f t="shared" si="27"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI60" s="123">
         <f>MAX(AI56:AI59)+1</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AL60" s="123">
         <f>MIN(AL56:AL59)</f>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AM60" s="123">
         <f>MAX(AM56:AM59)+1</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AN60" s="123">
         <f>MAX(AN56:AN59)+1</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AO60" s="123">
         <f>MAX(AO56:AO59)+1</f>
-        <v>1</v>
+        <v>8.5</v>
       </c>
       <c r="AP60" s="123">
         <f>MAX(AP56:AP59)+1</f>
-        <v>1.0009386600000001</v>
+        <v>75000010.372204036</v>
       </c>
       <c r="AT60" s="126">
         <f>MAX(AT56:AT59)-MIN(AT56:AT59)+1</f>
@@ -53403,7 +53413,7 @@
       <c r="BO60" s="21"/>
       <c r="BP60" s="114"/>
       <c r="BQ60" s="112"/>
-      <c r="BR60" s="163">
+      <c r="BR60" s="173">
         <v>95</v>
       </c>
       <c r="BS60" s="24" t="str">
@@ -53516,7 +53526,7 @@
         <v>46206.75</v>
       </c>
       <c r="BQ61" s="115"/>
-      <c r="BR61" s="164"/>
+      <c r="BR61" s="174"/>
       <c r="BS61" s="26" t="str">
         <f>IF(BP62&gt;BP63,BL62,IF(BP62&lt;BP63,BL63,""))</f>
         <v/>
@@ -53759,7 +53769,7 @@
         <f>BH62/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK62" s="163">
+      <c r="BK62" s="173">
         <v>88</v>
       </c>
       <c r="BL62" s="24" t="str">
@@ -54011,7 +54021,7 @@
         <f>BH63/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK63" s="164"/>
+      <c r="BK63" s="174"/>
       <c r="BL63" s="26" t="str">
         <f>AS45</f>
         <v>2G</v>
@@ -54277,7 +54287,7 @@
       <c r="BV64" s="21"/>
       <c r="BW64" s="114"/>
       <c r="BX64" s="112"/>
-      <c r="BY64" s="163">
+      <c r="BY64" s="173">
         <v>100</v>
       </c>
       <c r="BZ64" s="24" t="str">
@@ -54531,7 +54541,7 @@
       <c r="BV65" s="21"/>
       <c r="BW65" s="114"/>
       <c r="BX65" s="115"/>
-      <c r="BY65" s="164"/>
+      <c r="BY65" s="174"/>
       <c r="BZ65" s="26" t="str">
         <f>IF(BW68&gt;BW69,BS68,IF(BW68&lt;BW69,BS69,""))</f>
         <v/>
@@ -54727,7 +54737,7 @@
         <f>MAX(BH62:BH65)+1</f>
         <v>1</v>
       </c>
-      <c r="BK66" s="163">
+      <c r="BK66" s="173">
         <v>85</v>
       </c>
       <c r="BL66" s="24" t="str">
@@ -54827,7 +54837,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK67" s="164"/>
+      <c r="BK67" s="174"/>
       <c r="BL67" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!E3,AK80:AS91,9,FALSE),"3rd Group E/F/G/I/J")</f>
         <v>3rd Group E/F/G/I/J</v>
@@ -55083,7 +55093,7 @@
       <c r="BO68" s="21"/>
       <c r="BP68" s="114"/>
       <c r="BQ68" s="112"/>
-      <c r="BR68" s="163">
+      <c r="BR68" s="173">
         <v>96</v>
       </c>
       <c r="BS68" s="24" t="str">
@@ -55097,25 +55107,25 @@
         <f>IF(OR(BT68="",BT69="",AND(BU68="",BU69&lt;&gt;""),AND(BU69="",BU68&lt;&gt;""),AND(BV68="",BV69&lt;&gt;""),AND(BV69="",BV68&lt;&gt;"")),"",BT68*1000+BU68*10+BV68)</f>
         <v/>
       </c>
-      <c r="CE68" s="195" t="str">
+      <c r="CE68" s="175" t="str">
         <f>INDEX(T,144,lang)</f>
         <v>World Champion 2026</v>
       </c>
-      <c r="CF68" s="195"/>
-      <c r="CG68" s="195"/>
-      <c r="CH68" s="195"/>
-      <c r="CI68" s="195"/>
-      <c r="CJ68" s="195"/>
-      <c r="CK68" s="185" t="str">
+      <c r="CF68" s="175"/>
+      <c r="CG68" s="175"/>
+      <c r="CH68" s="175"/>
+      <c r="CI68" s="175"/>
+      <c r="CJ68" s="175"/>
+      <c r="CK68" s="163" t="str">
         <f>IF(CR37&gt;CR38,CN37,IF(CR37&lt;CR38,CN38,""))</f>
         <v/>
       </c>
-      <c r="CL68" s="185"/>
-      <c r="CM68" s="185"/>
-      <c r="CN68" s="185"/>
-      <c r="CO68" s="185"/>
-      <c r="CP68" s="185"/>
-      <c r="CQ68" s="185"/>
+      <c r="CL68" s="163"/>
+      <c r="CM68" s="163"/>
+      <c r="CN68" s="163"/>
+      <c r="CO68" s="163"/>
+      <c r="CP68" s="163"/>
+      <c r="CQ68" s="163"/>
     </row>
     <row r="69" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A69" s="16">
@@ -55353,7 +55363,7 @@
         <v>46207.0625</v>
       </c>
       <c r="BQ69" s="115"/>
-      <c r="BR69" s="164"/>
+      <c r="BR69" s="174"/>
       <c r="BS69" s="26" t="str">
         <f>IF(BP70&gt;BP71,BL70,IF(BP70&lt;BP71,BL71,""))</f>
         <v/>
@@ -55365,19 +55375,19 @@
         <f>IF(BW68="","",BT69*1000+BU69*10+BV69)</f>
         <v/>
       </c>
-      <c r="CE69" s="195"/>
-      <c r="CF69" s="195"/>
-      <c r="CG69" s="195"/>
-      <c r="CH69" s="195"/>
-      <c r="CI69" s="195"/>
-      <c r="CJ69" s="195"/>
-      <c r="CK69" s="185"/>
-      <c r="CL69" s="185"/>
-      <c r="CM69" s="185"/>
-      <c r="CN69" s="185"/>
-      <c r="CO69" s="185"/>
-      <c r="CP69" s="185"/>
-      <c r="CQ69" s="185"/>
+      <c r="CE69" s="175"/>
+      <c r="CF69" s="175"/>
+      <c r="CG69" s="175"/>
+      <c r="CH69" s="175"/>
+      <c r="CI69" s="175"/>
+      <c r="CJ69" s="175"/>
+      <c r="CK69" s="163"/>
+      <c r="CL69" s="163"/>
+      <c r="CM69" s="163"/>
+      <c r="CN69" s="163"/>
+      <c r="CO69" s="163"/>
+      <c r="CP69" s="163"/>
+      <c r="CQ69" s="163"/>
     </row>
     <row r="70" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A70" s="16">
@@ -55598,7 +55608,7 @@
         <f>BH70/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK70" s="163">
+      <c r="BK70" s="173">
         <v>87</v>
       </c>
       <c r="BL70" s="24" t="str">
@@ -55834,7 +55844,7 @@
         <f>BH71/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK71" s="164"/>
+      <c r="BK71" s="174"/>
       <c r="BL71" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!J3,AK80:AS91,9,FALSE),"3rd Group D/E/I/J/L")</f>
         <v>3rd Group D/E/I/J/L</v>
@@ -57241,7 +57251,7 @@
       </c>
       <c r="AD80" s="123">
         <f>COUNTIF($AP$80:$AP$91,CONCATENATE("&gt;=",AP80))</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE80" s="124" t="str">
         <f>J11</f>
@@ -57510,13 +57520,13 @@
     <row r="83" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="73"/>
       <c r="B83" s="73"/>
-      <c r="C83" s="186" t="s">
+      <c r="C83" s="164" t="s">
         <v>3183</v>
       </c>
-      <c r="D83" s="187"/>
-      <c r="E83" s="187"/>
-      <c r="F83" s="187"/>
-      <c r="G83" s="188"/>
+      <c r="D83" s="165"/>
+      <c r="E83" s="165"/>
+      <c r="F83" s="165"/>
+      <c r="G83" s="166"/>
       <c r="H83" s="75"/>
       <c r="I83" s="69"/>
       <c r="J83" s="99" t="str">
@@ -57614,11 +57624,11 @@
     <row r="84" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="73"/>
       <c r="B84" s="73"/>
-      <c r="C84" s="189"/>
-      <c r="D84" s="190"/>
-      <c r="E84" s="190"/>
-      <c r="F84" s="190"/>
-      <c r="G84" s="191"/>
+      <c r="C84" s="167"/>
+      <c r="D84" s="168"/>
+      <c r="E84" s="168"/>
+      <c r="F84" s="168"/>
+      <c r="G84" s="169"/>
       <c r="H84" s="75"/>
       <c r="I84" s="69"/>
       <c r="J84" s="99" t="str">
@@ -57663,7 +57673,7 @@
       </c>
       <c r="AD84" s="123">
         <f t="shared" si="38"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE84" s="124" t="str">
         <f>J35</f>
@@ -57728,11 +57738,11 @@
     <row r="85" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="73"/>
       <c r="B85" s="73"/>
-      <c r="C85" s="189"/>
-      <c r="D85" s="190"/>
-      <c r="E85" s="190"/>
-      <c r="F85" s="190"/>
-      <c r="G85" s="191"/>
+      <c r="C85" s="167"/>
+      <c r="D85" s="168"/>
+      <c r="E85" s="168"/>
+      <c r="F85" s="168"/>
+      <c r="G85" s="169"/>
       <c r="H85" s="75"/>
       <c r="I85" s="69"/>
       <c r="J85" s="99" t="str">
@@ -57842,11 +57852,11 @@
     <row r="86" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="73"/>
       <c r="B86" s="73"/>
-      <c r="C86" s="189"/>
-      <c r="D86" s="190"/>
-      <c r="E86" s="190"/>
-      <c r="F86" s="190"/>
-      <c r="G86" s="191"/>
+      <c r="C86" s="167"/>
+      <c r="D86" s="168"/>
+      <c r="E86" s="168"/>
+      <c r="F86" s="168"/>
+      <c r="G86" s="169"/>
       <c r="H86" s="75"/>
       <c r="I86" s="69"/>
       <c r="J86" s="99" t="str">
@@ -57956,16 +57966,16 @@
     <row r="87" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="73"/>
       <c r="B87" s="73"/>
-      <c r="C87" s="189"/>
-      <c r="D87" s="190"/>
-      <c r="E87" s="190"/>
-      <c r="F87" s="190"/>
-      <c r="G87" s="191"/>
+      <c r="C87" s="167"/>
+      <c r="D87" s="168"/>
+      <c r="E87" s="168"/>
+      <c r="F87" s="168"/>
+      <c r="G87" s="169"/>
       <c r="H87" s="75"/>
       <c r="I87" s="69"/>
       <c r="J87" s="99" t="str">
         <f>VLOOKUP(7,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓘ Norway</v>
+        <v>Ⓛ Panama</v>
       </c>
       <c r="K87" s="100">
         <f t="shared" si="47"/>
@@ -58070,16 +58080,16 @@
     <row r="88" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="73"/>
       <c r="B88" s="73"/>
-      <c r="C88" s="192"/>
-      <c r="D88" s="193"/>
-      <c r="E88" s="193"/>
-      <c r="F88" s="193"/>
-      <c r="G88" s="194"/>
+      <c r="C88" s="170"/>
+      <c r="D88" s="171"/>
+      <c r="E88" s="171"/>
+      <c r="F88" s="171"/>
+      <c r="G88" s="172"/>
       <c r="H88" s="75"/>
       <c r="I88" s="69"/>
       <c r="J88" s="99" t="str">
         <f>VLOOKUP(8,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓛ Panama</v>
+        <v>Ⓚ DR Congo</v>
       </c>
       <c r="K88" s="100">
         <f t="shared" si="47"/>
@@ -58119,11 +58129,11 @@
       </c>
       <c r="AD88" s="123">
         <f t="shared" si="38"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE88" s="124" t="str">
         <f>J59</f>
-        <v>Norway</v>
+        <v>Senegal</v>
       </c>
       <c r="AF88" s="123">
         <f t="shared" si="39"/>
@@ -58135,26 +58145,26 @@
       </c>
       <c r="AH88" s="123">
         <f t="shared" si="40"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI88" s="123">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ88" s="123">
         <f t="shared" si="42"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK88" s="123" t="s">
         <v>3189</v>
       </c>
       <c r="AL88" s="123">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AM88" s="123">
         <f t="shared" si="44"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN88" s="123">
         <f t="shared" si="45"/>
@@ -58162,23 +58172,23 @@
       </c>
       <c r="AP88" s="123">
         <f>AN88/AN92*10000+AM88/AM92*1000+AI88/AI92*100+IF(AQ88=0,ROW(),AQ88)/2000000</f>
-        <v>666.66744213666664</v>
+        <v>33.334177828333331</v>
       </c>
       <c r="AQ88" s="126">
         <f t="shared" si="37"/>
-        <v>1550.94</v>
+        <v>1688.99</v>
       </c>
       <c r="AR88" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCFGHI</v>
+        <v>BCFGH</v>
       </c>
       <c r="AS88" s="129" t="str">
         <f t="shared" si="46"/>
-        <v>Norway</v>
+        <v/>
       </c>
       <c r="AT88" s="130" t="str">
         <f>"Ⓘ "&amp;AE88</f>
-        <v>Ⓘ Norway</v>
+        <v>Ⓘ Senegal</v>
       </c>
     </row>
     <row r="89" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -58193,11 +58203,11 @@
       <c r="I89" s="69"/>
       <c r="J89" s="102" t="str">
         <f>VLOOKUP(9,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓚ DR Congo</v>
+        <v>Ⓐ Czech Republic</v>
       </c>
       <c r="K89" s="103">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="103">
         <f>VLOOKUP(9,$AD$80:$AN$91,3,FALSE)</f>
@@ -58209,11 +58219,11 @@
       </c>
       <c r="N89" s="103">
         <f>VLOOKUP(9,$AD$80:$AN$91,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O89" s="103" t="str">
         <f>VLOOKUP(9,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(9,$AD$80:$AN$91,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 2</v>
       </c>
       <c r="P89" s="104">
         <f t="shared" si="48"/>
@@ -58284,7 +58294,7 @@
       </c>
       <c r="AR89" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCFGHIJ</v>
+        <v>BCFGHJ</v>
       </c>
       <c r="AS89" s="129" t="str">
         <f t="shared" si="46"/>
@@ -58307,7 +58317,7 @@
       <c r="I90" s="69"/>
       <c r="J90" s="102" t="str">
         <f>VLOOKUP(10,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓐ Czech Republic</v>
+        <v>Ⓔ Ecuador</v>
       </c>
       <c r="K90" s="103">
         <f t="shared" si="47"/>
@@ -58327,7 +58337,7 @@
       </c>
       <c r="O90" s="103" t="str">
         <f>VLOOKUP(10,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(10,$AD$80:$AN$91,7,FALSE)</f>
-        <v>1 - 2</v>
+        <v>0 - 1</v>
       </c>
       <c r="P90" s="104">
         <f t="shared" si="48"/>
@@ -58347,7 +58357,7 @@
       </c>
       <c r="AD90" s="123">
         <f t="shared" si="38"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE90" s="124" t="str">
         <f>J71</f>
@@ -58398,11 +58408,11 @@
       </c>
       <c r="AR90" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCFGHIJ</v>
+        <v>BCFGHJK</v>
       </c>
       <c r="AS90" s="129" t="str">
         <f t="shared" si="46"/>
-        <v/>
+        <v>DR Congo</v>
       </c>
       <c r="AT90" s="130" t="str">
         <f>"Ⓚ "&amp;AE90</f>
@@ -58421,7 +58431,7 @@
       <c r="I91" s="69"/>
       <c r="J91" s="102" t="str">
         <f>VLOOKUP(11,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓔ Ecuador</v>
+        <v>Ⓘ Senegal</v>
       </c>
       <c r="K91" s="103">
         <f t="shared" si="47"/>
@@ -58441,7 +58451,7 @@
       </c>
       <c r="O91" s="103" t="str">
         <f>VLOOKUP(11,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(11,$AD$80:$AN$91,7,FALSE)</f>
-        <v>0 - 1</v>
+        <v>1 - 3</v>
       </c>
       <c r="P91" s="104">
         <f t="shared" si="48"/>
@@ -58461,7 +58471,7 @@
       </c>
       <c r="AD91" s="123">
         <f t="shared" si="38"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE91" s="124" t="str">
         <f>J77</f>
@@ -58512,7 +58522,7 @@
       </c>
       <c r="AR91" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCFGHIJL</v>
+        <v>BCFGHJKL</v>
       </c>
       <c r="AS91" s="129" t="str">
         <f t="shared" si="46"/>
@@ -58579,7 +58589,7 @@
       </c>
       <c r="AJ92" s="123">
         <f>MAX(AJ80:AJ91)+1</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL92" s="123">
         <f>MIN(AL80:AL91)</f>
@@ -58752,6 +58762,36 @@
   <sheetProtection algorithmName="SHA-512" hashValue="7nWuIQAsd0NKRlhwUK3tOeNHpTch5B5FULy2gxNNaIdJM5RfhFSMzPcx55y+pmM3d73guUy+p5Y+SvIjJZQRaA==" saltValue="Uw23KnM8csnTioq5H8upCA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <dataConsolidate/>
   <mergeCells count="45">
+    <mergeCell ref="BK14:BK15"/>
+    <mergeCell ref="BY16:BY17"/>
+    <mergeCell ref="BK26:BK27"/>
+    <mergeCell ref="BR28:BR29"/>
+    <mergeCell ref="BK22:BK23"/>
+    <mergeCell ref="CF23:CF24"/>
+    <mergeCell ref="BK18:BK19"/>
+    <mergeCell ref="BR20:BR21"/>
+    <mergeCell ref="CM48:CM49"/>
+    <mergeCell ref="BR44:BR45"/>
+    <mergeCell ref="BK46:BK47"/>
+    <mergeCell ref="BK30:BK31"/>
+    <mergeCell ref="CM44:CQ45"/>
+    <mergeCell ref="BY32:BY33"/>
+    <mergeCell ref="BK38:BK39"/>
+    <mergeCell ref="BK34:BK35"/>
+    <mergeCell ref="BR36:BR37"/>
+    <mergeCell ref="BK42:BK43"/>
+    <mergeCell ref="CM33:CQ34"/>
+    <mergeCell ref="CM37:CM38"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="BR12:BR13"/>
+    <mergeCell ref="BK6:BO7"/>
+    <mergeCell ref="BR6:BV7"/>
+    <mergeCell ref="BY6:CC7"/>
+    <mergeCell ref="CF6:CJ7"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="A5:H6"/>
+    <mergeCell ref="J5:P6"/>
     <mergeCell ref="CK68:CQ69"/>
     <mergeCell ref="C83:G88"/>
     <mergeCell ref="BK70:BK71"/>
@@ -58767,36 +58807,6 @@
     <mergeCell ref="BR52:BR53"/>
     <mergeCell ref="BK54:BK55"/>
     <mergeCell ref="CE68:CJ69"/>
-    <mergeCell ref="CF6:CJ7"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="A5:H6"/>
-    <mergeCell ref="J5:P6"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="BR12:BR13"/>
-    <mergeCell ref="BK6:BO7"/>
-    <mergeCell ref="BR6:BV7"/>
-    <mergeCell ref="BY6:CC7"/>
-    <mergeCell ref="CF23:CF24"/>
-    <mergeCell ref="BK18:BK19"/>
-    <mergeCell ref="BR20:BR21"/>
-    <mergeCell ref="CM48:CM49"/>
-    <mergeCell ref="BR44:BR45"/>
-    <mergeCell ref="BK46:BK47"/>
-    <mergeCell ref="BK30:BK31"/>
-    <mergeCell ref="CM44:CQ45"/>
-    <mergeCell ref="BY32:BY33"/>
-    <mergeCell ref="BK38:BK39"/>
-    <mergeCell ref="BK34:BK35"/>
-    <mergeCell ref="BR36:BR37"/>
-    <mergeCell ref="BK42:BK43"/>
-    <mergeCell ref="CM33:CQ34"/>
-    <mergeCell ref="CM37:CM38"/>
-    <mergeCell ref="BK14:BK15"/>
-    <mergeCell ref="BY16:BY17"/>
-    <mergeCell ref="BK26:BK27"/>
-    <mergeCell ref="BR28:BR29"/>
-    <mergeCell ref="BK22:BK23"/>
   </mergeCells>
   <conditionalFormatting sqref="A7:E78">
     <cfRule type="expression" dxfId="228" priority="339">
@@ -60093,11 +60103,11 @@
     <row r="3" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B3" s="109">
         <f>MATCH(C3,C6:C500,0)</f>
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C3" s="121" t="str">
         <f>'2026 World Cup'!AR91</f>
-        <v>BCFGHIJL</v>
+        <v>BCFGHJKL</v>
       </c>
       <c r="D3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,2,FALSE)</f>
@@ -60129,7 +60139,7 @@
       </c>
       <c r="K3" s="122" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,9,FALSE)</f>
-        <v>3I</v>
+        <v>3K</v>
       </c>
     </row>
     <row r="5" spans="2:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">

--- a/public/worldcup.xlsx
+++ b/public/worldcup.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rylanpaul/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E9FCAB3-1F0B-9447-9030-EF88896AC3FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F971ACF6-796A-0B45-8B26-AA3E7C735F48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13305,56 +13305,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -13435,6 +13391,50 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -40632,11 +40632,11 @@
       <c r="A20" s="132" t="str">
         <v>Argentina</v>
       </c>
-      <c r="B20" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C20" s="81" t="e">
-        <v>#N/A</v>
+      <c r="B20" s="81">
+        <v>3</v>
+      </c>
+      <c r="C20" s="81">
+        <v>0</v>
       </c>
       <c r="D20" s="134" t="str">
         <v>Algeria</v>
@@ -40936,25 +40936,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:95" ht="47" x14ac:dyDescent="0.2">
-      <c r="A1" s="182" t="str" cm="1">
+      <c r="A1" s="171" t="str" cm="1">
         <f t="array" ref="A1">INDEX(T,2,lang)</f>
         <v>2026 World Cup Final Tournament Schedule</v>
       </c>
-      <c r="B1" s="182"/>
-      <c r="C1" s="182"/>
-      <c r="D1" s="182"/>
-      <c r="E1" s="182"/>
-      <c r="F1" s="182"/>
-      <c r="G1" s="182"/>
-      <c r="H1" s="182"/>
-      <c r="I1" s="182"/>
-      <c r="J1" s="182"/>
-      <c r="K1" s="182"/>
-      <c r="L1" s="182"/>
-      <c r="M1" s="182"/>
-      <c r="N1" s="182"/>
-      <c r="O1" s="182"/>
-      <c r="P1" s="182"/>
+      <c r="B1" s="171"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="171"/>
+      <c r="F1" s="171"/>
+      <c r="G1" s="171"/>
+      <c r="H1" s="171"/>
+      <c r="I1" s="171"/>
+      <c r="J1" s="171"/>
+      <c r="K1" s="171"/>
+      <c r="L1" s="171"/>
+      <c r="M1" s="171"/>
+      <c r="N1" s="171"/>
+      <c r="O1" s="171"/>
+      <c r="P1" s="171"/>
       <c r="S1" s="123"/>
       <c r="T1" s="123"/>
       <c r="AC1" s="123"/>
@@ -41001,11 +41001,11 @@
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
-      <c r="O3" s="183" t="str">
+      <c r="O3" s="172" t="str">
         <f>"Language: " &amp; Settings!C4</f>
         <v>Language: English</v>
       </c>
-      <c r="P3" s="183"/>
+      <c r="P3" s="172"/>
       <c r="S3" s="123"/>
       <c r="T3" s="123"/>
       <c r="AC3" s="123"/>
@@ -41023,43 +41023,43 @@
     </row>
     <row r="4" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:95" x14ac:dyDescent="0.2">
-      <c r="A5" s="184" t="str" cm="1">
+      <c r="A5" s="173" t="str" cm="1">
         <f t="array" ref="A5">INDEX(T,3,lang)</f>
         <v>Group Stage</v>
       </c>
-      <c r="B5" s="185"/>
-      <c r="C5" s="185"/>
-      <c r="D5" s="185"/>
-      <c r="E5" s="185"/>
-      <c r="F5" s="185"/>
-      <c r="G5" s="185"/>
-      <c r="H5" s="186"/>
-      <c r="J5" s="190" t="s">
+      <c r="B5" s="174"/>
+      <c r="C5" s="174"/>
+      <c r="D5" s="174"/>
+      <c r="E5" s="174"/>
+      <c r="F5" s="174"/>
+      <c r="G5" s="174"/>
+      <c r="H5" s="175"/>
+      <c r="J5" s="179" t="s">
         <v>3166</v>
       </c>
-      <c r="K5" s="191"/>
-      <c r="L5" s="191"/>
-      <c r="M5" s="191"/>
-      <c r="N5" s="191"/>
-      <c r="O5" s="191"/>
-      <c r="P5" s="192"/>
+      <c r="K5" s="180"/>
+      <c r="L5" s="180"/>
+      <c r="M5" s="180"/>
+      <c r="N5" s="180"/>
+      <c r="O5" s="180"/>
+      <c r="P5" s="181"/>
     </row>
     <row r="6" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="187"/>
-      <c r="B6" s="188"/>
-      <c r="C6" s="188"/>
-      <c r="D6" s="188"/>
-      <c r="E6" s="188"/>
-      <c r="F6" s="188"/>
-      <c r="G6" s="188"/>
-      <c r="H6" s="189"/>
-      <c r="J6" s="193"/>
-      <c r="K6" s="194"/>
-      <c r="L6" s="194"/>
-      <c r="M6" s="194"/>
-      <c r="N6" s="194"/>
-      <c r="O6" s="194"/>
-      <c r="P6" s="195"/>
+      <c r="A6" s="176"/>
+      <c r="B6" s="177"/>
+      <c r="C6" s="177"/>
+      <c r="D6" s="177"/>
+      <c r="E6" s="177"/>
+      <c r="F6" s="177"/>
+      <c r="G6" s="177"/>
+      <c r="H6" s="178"/>
+      <c r="J6" s="182"/>
+      <c r="K6" s="183"/>
+      <c r="L6" s="183"/>
+      <c r="M6" s="183"/>
+      <c r="N6" s="183"/>
+      <c r="O6" s="183"/>
+      <c r="P6" s="184"/>
       <c r="R6" s="123" t="s">
         <v>3167</v>
       </c>
@@ -41169,37 +41169,37 @@
       <c r="BI6" s="128" t="s">
         <v>3178</v>
       </c>
-      <c r="BK6" s="176" t="s">
+      <c r="BK6" s="165" t="s">
         <v>3179</v>
       </c>
-      <c r="BL6" s="177"/>
-      <c r="BM6" s="177"/>
-      <c r="BN6" s="177"/>
-      <c r="BO6" s="178"/>
-      <c r="BR6" s="176" t="str" cm="1">
+      <c r="BL6" s="166"/>
+      <c r="BM6" s="166"/>
+      <c r="BN6" s="166"/>
+      <c r="BO6" s="167"/>
+      <c r="BR6" s="165" t="str" cm="1">
         <f t="array" ref="BR6">INDEX(T,4,lang)</f>
         <v>Round of 16</v>
       </c>
-      <c r="BS6" s="177"/>
-      <c r="BT6" s="177"/>
-      <c r="BU6" s="177"/>
-      <c r="BV6" s="178"/>
-      <c r="BY6" s="176" t="str" cm="1">
+      <c r="BS6" s="166"/>
+      <c r="BT6" s="166"/>
+      <c r="BU6" s="166"/>
+      <c r="BV6" s="167"/>
+      <c r="BY6" s="165" t="str" cm="1">
         <f t="array" ref="BY6">INDEX(T,5,lang)</f>
         <v>Quarterfinals</v>
       </c>
-      <c r="BZ6" s="177"/>
-      <c r="CA6" s="177"/>
-      <c r="CB6" s="177"/>
-      <c r="CC6" s="178"/>
-      <c r="CF6" s="176" t="str" cm="1">
+      <c r="BZ6" s="166"/>
+      <c r="CA6" s="166"/>
+      <c r="CB6" s="166"/>
+      <c r="CC6" s="167"/>
+      <c r="CF6" s="165" t="str" cm="1">
         <f t="array" ref="CF6">INDEX(T,6,lang)</f>
         <v>Semi-Finals</v>
       </c>
-      <c r="CG6" s="177"/>
-      <c r="CH6" s="177"/>
-      <c r="CI6" s="177"/>
-      <c r="CJ6" s="178"/>
+      <c r="CG6" s="166"/>
+      <c r="CH6" s="166"/>
+      <c r="CI6" s="166"/>
+      <c r="CJ6" s="167"/>
     </row>
     <row r="7" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="11">
@@ -41276,26 +41276,26 @@
         <v>1</v>
       </c>
       <c r="AY7" s="126"/>
-      <c r="BK7" s="179"/>
-      <c r="BL7" s="180"/>
-      <c r="BM7" s="180"/>
-      <c r="BN7" s="180"/>
-      <c r="BO7" s="181"/>
-      <c r="BR7" s="179"/>
-      <c r="BS7" s="180"/>
-      <c r="BT7" s="180"/>
-      <c r="BU7" s="180"/>
-      <c r="BV7" s="181"/>
-      <c r="BY7" s="179"/>
-      <c r="BZ7" s="180"/>
-      <c r="CA7" s="180"/>
-      <c r="CB7" s="180"/>
-      <c r="CC7" s="181"/>
-      <c r="CF7" s="179"/>
-      <c r="CG7" s="180"/>
-      <c r="CH7" s="180"/>
-      <c r="CI7" s="180"/>
-      <c r="CJ7" s="181"/>
+      <c r="BK7" s="168"/>
+      <c r="BL7" s="169"/>
+      <c r="BM7" s="169"/>
+      <c r="BN7" s="169"/>
+      <c r="BO7" s="170"/>
+      <c r="BR7" s="168"/>
+      <c r="BS7" s="169"/>
+      <c r="BT7" s="169"/>
+      <c r="BU7" s="169"/>
+      <c r="BV7" s="170"/>
+      <c r="BY7" s="168"/>
+      <c r="BZ7" s="169"/>
+      <c r="CA7" s="169"/>
+      <c r="CB7" s="169"/>
+      <c r="CC7" s="170"/>
+      <c r="CF7" s="168"/>
+      <c r="CG7" s="169"/>
+      <c r="CH7" s="169"/>
+      <c r="CI7" s="169"/>
+      <c r="CJ7" s="170"/>
     </row>
     <row r="8" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A8" s="16">
@@ -42031,7 +42031,7 @@
         <f>BH10/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK10" s="173">
+      <c r="BK10" s="163">
         <v>74</v>
       </c>
       <c r="BL10" s="24" t="str">
@@ -42294,7 +42294,7 @@
         <f>BH11/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK11" s="174"/>
+      <c r="BK11" s="164"/>
       <c r="BL11" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!G3,AK80:AS91,9,FALSE),"3rd Group A/B/C/D/F")</f>
         <v>3rd Group A/B/C/D/F</v>
@@ -42532,7 +42532,7 @@
       <c r="BO12" s="21"/>
       <c r="BP12" s="114"/>
       <c r="BQ12" s="112"/>
-      <c r="BR12" s="173">
+      <c r="BR12" s="163">
         <v>89</v>
       </c>
       <c r="BS12" s="24" t="str">
@@ -42653,7 +42653,7 @@
         <v>46203.875</v>
       </c>
       <c r="BQ13" s="115"/>
-      <c r="BR13" s="174"/>
+      <c r="BR13" s="164"/>
       <c r="BS13" s="26" t="str">
         <f>IF(BP14&gt;BP15,BL14,IF(BP14&lt;BP15,BL15,""))</f>
         <v/>
@@ -42911,7 +42911,7 @@
         <f>BH14/BH18</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK14" s="173">
+      <c r="BK14" s="163">
         <v>77</v>
       </c>
       <c r="BL14" s="24" t="str">
@@ -43178,7 +43178,7 @@
         <f>BH15/BH18</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK15" s="174"/>
+      <c r="BK15" s="164"/>
       <c r="BL15" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!I3,AK80:AS91,9,FALSE),"3rd Group C/D/F/G/H")</f>
         <v>3rd Group C/D/F/G/H</v>
@@ -43452,7 +43452,7 @@
       <c r="BV16" s="21"/>
       <c r="BW16" s="114"/>
       <c r="BX16" s="112"/>
-      <c r="BY16" s="173">
+      <c r="BY16" s="163">
         <v>97</v>
       </c>
       <c r="BZ16" s="24" t="str">
@@ -43714,7 +43714,7 @@
       <c r="BV17" s="21"/>
       <c r="BW17" s="114"/>
       <c r="BX17" s="115"/>
-      <c r="BY17" s="174"/>
+      <c r="BY17" s="164"/>
       <c r="BZ17" s="26" t="str">
         <f>IF(BW20&gt;BW21,BS20,IF(BW20&lt;BW21,BS21,""))</f>
         <v/>
@@ -43918,7 +43918,7 @@
         <f>MAX(BH14:BH17)+1</f>
         <v>102</v>
       </c>
-      <c r="BK18" s="173">
+      <c r="BK18" s="163">
         <v>73</v>
       </c>
       <c r="BL18" s="24" t="str">
@@ -44026,7 +44026,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BK19" s="174"/>
+      <c r="BK19" s="164"/>
       <c r="BL19" s="26" t="str">
         <f>AS15</f>
         <v>2B</v>
@@ -44304,7 +44304,7 @@
       <c r="BO20" s="21"/>
       <c r="BP20" s="114"/>
       <c r="BQ20" s="112"/>
-      <c r="BR20" s="173">
+      <c r="BR20" s="163">
         <v>90</v>
       </c>
       <c r="BS20" s="24" t="str">
@@ -44577,7 +44577,7 @@
         <v>46203.041666666672</v>
       </c>
       <c r="BQ21" s="115"/>
-      <c r="BR21" s="174"/>
+      <c r="BR21" s="164"/>
       <c r="BS21" s="26" t="str">
         <f>IF(BP22&gt;BP23,BL22,IF(BP22&lt;BP23,BL23,""))</f>
         <v/>
@@ -44831,7 +44831,7 @@
         <f>BH22/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK22" s="173">
+      <c r="BK22" s="163">
         <v>75</v>
       </c>
       <c r="BL22" s="24" t="str">
@@ -45095,7 +45095,7 @@
         <f>BH23/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK23" s="174"/>
+      <c r="BK23" s="164"/>
       <c r="BL23" s="26" t="str">
         <f>AS21</f>
         <v>2C</v>
@@ -45122,7 +45122,7 @@
       <c r="CC23" s="21"/>
       <c r="CD23" s="114"/>
       <c r="CE23" s="112"/>
-      <c r="CF23" s="173">
+      <c r="CF23" s="163">
         <v>101</v>
       </c>
       <c r="CG23" s="24" t="str">
@@ -45343,7 +45343,7 @@
       <c r="CC24" s="21"/>
       <c r="CD24" s="114"/>
       <c r="CE24" s="115"/>
-      <c r="CF24" s="174"/>
+      <c r="CF24" s="164"/>
       <c r="CG24" s="26" t="str">
         <f>IF(CD32&gt;CD33,BZ32,IF(CD32&lt;CD33,BZ33,""))</f>
         <v/>
@@ -45376,8 +45376,12 @@
         <f>AE62</f>
         <v>Argentina</v>
       </c>
-      <c r="F25" s="19"/>
-      <c r="G25" s="20"/>
+      <c r="F25" s="19">
+        <v>3</v>
+      </c>
+      <c r="G25" s="20">
+        <v>0</v>
+      </c>
       <c r="H25" s="80" t="str">
         <f>AE63</f>
         <v>Algeria</v>
@@ -45388,11 +45392,11 @@
       </c>
       <c r="S25" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Argentina_win</v>
       </c>
       <c r="T25" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Algeria_lose</v>
       </c>
       <c r="U25" s="123">
         <f t="shared" si="8"/>
@@ -45422,9 +45426,9 @@
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="AB25" s="123" t="str">
+      <c r="AB25" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="BK25" s="21" t="str" cm="1">
         <f t="array" ref="BK25">INDEX(T,24+MONTH(BP25),lang) &amp; " " &amp; DAY(BP25) &amp; ", " &amp; YEAR(BP25) &amp; "   " &amp; (IF(HOUR(BP25)&lt;10,0,"")&amp;HOUR(BP25)) &amp; ":" &amp;  (IF(MINUTE(BP25)&lt;10,0,"")&amp;MINUTE(BP25))</f>
@@ -45688,7 +45692,7 @@
         <f>BH26/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK26" s="173">
+      <c r="BK26" s="163">
         <v>83</v>
       </c>
       <c r="BL26" s="24" t="str">
@@ -45952,7 +45956,7 @@
         <f>BH27/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK27" s="174"/>
+      <c r="BK27" s="164"/>
       <c r="BL27" s="26" t="str">
         <f>AS75</f>
         <v>2L</v>
@@ -46223,7 +46227,7 @@
       <c r="BO28" s="21"/>
       <c r="BP28" s="114"/>
       <c r="BQ28" s="112"/>
-      <c r="BR28" s="173">
+      <c r="BR28" s="163">
         <v>93</v>
       </c>
       <c r="BS28" s="24" t="str">
@@ -46484,7 +46488,7 @@
         <v>46205.791666666672</v>
       </c>
       <c r="BQ29" s="115"/>
-      <c r="BR29" s="174"/>
+      <c r="BR29" s="164"/>
       <c r="BS29" s="26" t="str">
         <f>IF(BP30&gt;BP31,BL30,IF(BP30&lt;BP31,BL31,""))</f>
         <v/>
@@ -46694,7 +46698,7 @@
         <f>MAX(BH26:BH29)+1</f>
         <v>1</v>
       </c>
-      <c r="BK30" s="173">
+      <c r="BK30" s="163">
         <v>84</v>
       </c>
       <c r="BL30" s="24" t="str">
@@ -46801,7 +46805,7 @@
         <f>IF(OR(F31="",G31=""),"",IF(F31&gt;G31,1,IF(F31&lt;G31,-1,0)))</f>
         <v/>
       </c>
-      <c r="BK31" s="174"/>
+      <c r="BK31" s="164"/>
       <c r="BL31" s="26" t="str">
         <f>AS63</f>
         <v>2J</v>
@@ -47073,7 +47077,7 @@
       <c r="BV32" s="21"/>
       <c r="BW32" s="114"/>
       <c r="BX32" s="112"/>
-      <c r="BY32" s="173">
+      <c r="BY32" s="163">
         <v>98</v>
       </c>
       <c r="BZ32" s="24" t="str">
@@ -47333,7 +47337,7 @@
       <c r="BV33" s="21"/>
       <c r="BW33" s="114"/>
       <c r="BX33" s="115"/>
-      <c r="BY33" s="174"/>
+      <c r="BY33" s="164"/>
       <c r="BZ33" s="26" t="str">
         <f>IF(BW36&gt;BW37,BS36,IF(BW36&lt;BW37,BS37,""))</f>
         <v/>
@@ -47348,14 +47352,14 @@
       <c r="CE33" s="112"/>
       <c r="CK33" s="114"/>
       <c r="CL33" s="112"/>
-      <c r="CM33" s="176" t="str" cm="1">
+      <c r="CM33" s="165" t="str" cm="1">
         <f t="array" ref="CM33">INDEX(T,8,lang)</f>
         <v>Final</v>
       </c>
-      <c r="CN33" s="177"/>
-      <c r="CO33" s="177"/>
-      <c r="CP33" s="177"/>
-      <c r="CQ33" s="178"/>
+      <c r="CN33" s="166"/>
+      <c r="CO33" s="166"/>
+      <c r="CP33" s="166"/>
+      <c r="CQ33" s="167"/>
     </row>
     <row r="34" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A34" s="16">
@@ -47575,7 +47579,7 @@
         <f>BH34/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK34" s="173">
+      <c r="BK34" s="163">
         <v>81</v>
       </c>
       <c r="BL34" s="24" t="str">
@@ -47606,11 +47610,11 @@
       <c r="CE34" s="112"/>
       <c r="CK34" s="114"/>
       <c r="CL34" s="112"/>
-      <c r="CM34" s="179"/>
-      <c r="CN34" s="180"/>
-      <c r="CO34" s="180"/>
-      <c r="CP34" s="180"/>
-      <c r="CQ34" s="181"/>
+      <c r="CM34" s="168"/>
+      <c r="CN34" s="169"/>
+      <c r="CO34" s="169"/>
+      <c r="CP34" s="169"/>
+      <c r="CQ34" s="170"/>
     </row>
     <row r="35" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A35" s="16">
@@ -47830,7 +47834,7 @@
         <f>BH35/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK35" s="174"/>
+      <c r="BK35" s="164"/>
       <c r="BL35" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!F3,AK80:AS91,9,FALSE),"3rd Group B/E/F/I/J")</f>
         <v>3rd Group B/E/F/I/J</v>
@@ -48055,7 +48059,7 @@
       <c r="BO36" s="21"/>
       <c r="BP36" s="114"/>
       <c r="BQ36" s="112"/>
-      <c r="BR36" s="173">
+      <c r="BR36" s="163">
         <v>94</v>
       </c>
       <c r="BS36" s="24" t="str">
@@ -48175,7 +48179,7 @@
         <v>46204.833333333336</v>
       </c>
       <c r="BQ37" s="115"/>
-      <c r="BR37" s="174"/>
+      <c r="BR37" s="164"/>
       <c r="BS37" s="26" t="str">
         <f>IF(BP38&gt;BP39,BL38,IF(BP38&lt;BP39,BL39,""))</f>
         <v/>
@@ -48202,7 +48206,7 @@
       <c r="CJ37" s="21"/>
       <c r="CK37" s="114"/>
       <c r="CL37" s="112"/>
-      <c r="CM37" s="173">
+      <c r="CM37" s="163">
         <v>104</v>
       </c>
       <c r="CN37" s="24" t="str">
@@ -48439,7 +48443,7 @@
         <f>BH38/BH42</f>
         <v>0.98064516129032253</v>
       </c>
-      <c r="BK38" s="173">
+      <c r="BK38" s="163">
         <v>82</v>
       </c>
       <c r="BL38" s="24" t="str">
@@ -48469,7 +48473,7 @@
       <c r="CI38" s="21"/>
       <c r="CJ38" s="21"/>
       <c r="CL38" s="115"/>
-      <c r="CM38" s="174"/>
+      <c r="CM38" s="164"/>
       <c r="CN38" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG55,IF(CK55&lt;CK56,CG56,""))</f>
         <v/>
@@ -48704,7 +48708,7 @@
         <f>BH39/BH42</f>
         <v>0.98064516129032253</v>
       </c>
-      <c r="BK39" s="174"/>
+      <c r="BK39" s="164"/>
       <c r="BL39" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!H3,AK80:AS91,9,FALSE),"3rd Group A/E/H/I/J")</f>
         <v>3rd Group A/E/H/I/J</v>
@@ -49380,7 +49384,7 @@
         <f>MAX(BH38:BH41)+1</f>
         <v>51.666666666666664</v>
       </c>
-      <c r="BK42" s="173">
+      <c r="BK42" s="163">
         <v>76</v>
       </c>
       <c r="BL42" s="24" t="str">
@@ -49473,7 +49477,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK43" s="174"/>
+      <c r="BK43" s="164"/>
       <c r="BL43" s="26" t="str">
         <f>AS39</f>
         <v>2F</v>
@@ -49729,7 +49733,7 @@
       <c r="BO44" s="21"/>
       <c r="BP44" s="114"/>
       <c r="BQ44" s="112"/>
-      <c r="BR44" s="173">
+      <c r="BR44" s="163">
         <v>91</v>
       </c>
       <c r="BS44" s="24" t="str">
@@ -49744,14 +49748,14 @@
         <v/>
       </c>
       <c r="CK44" s="114"/>
-      <c r="CM44" s="176" t="str" cm="1">
+      <c r="CM44" s="165" t="str" cm="1">
         <f t="array" ref="CM44">INDEX(T,7,lang)</f>
         <v>Third-Place Play-Off</v>
       </c>
-      <c r="CN44" s="177"/>
-      <c r="CO44" s="177"/>
-      <c r="CP44" s="177"/>
-      <c r="CQ44" s="178"/>
+      <c r="CN44" s="166"/>
+      <c r="CO44" s="166"/>
+      <c r="CP44" s="166"/>
+      <c r="CQ44" s="167"/>
     </row>
     <row r="45" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="16">
@@ -49988,7 +49992,7 @@
         <v>46203.708333333336</v>
       </c>
       <c r="BQ45" s="115"/>
-      <c r="BR45" s="174"/>
+      <c r="BR45" s="164"/>
       <c r="BS45" s="26" t="str">
         <f>IF(BP46&gt;BP47,BL46,IF(BP46&lt;BP47,BL47,""))</f>
         <v/>
@@ -50001,11 +50005,11 @@
         <v/>
       </c>
       <c r="CK45" s="114"/>
-      <c r="CM45" s="179"/>
-      <c r="CN45" s="180"/>
-      <c r="CO45" s="180"/>
-      <c r="CP45" s="180"/>
-      <c r="CQ45" s="181"/>
+      <c r="CM45" s="168"/>
+      <c r="CN45" s="169"/>
+      <c r="CO45" s="169"/>
+      <c r="CP45" s="169"/>
+      <c r="CQ45" s="170"/>
     </row>
     <row r="46" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A46" s="16">
@@ -50225,7 +50229,7 @@
         <f>BH46/BH48</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK46" s="173">
+      <c r="BK46" s="163">
         <v>78</v>
       </c>
       <c r="BL46" s="24" t="str">
@@ -50467,7 +50471,7 @@
         <f>BH47/BH48</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK47" s="174"/>
+      <c r="BK47" s="164"/>
       <c r="BL47" s="26" t="str">
         <f>AS57</f>
         <v>2I</v>
@@ -50710,7 +50714,7 @@
       <c r="BV48" s="21"/>
       <c r="BW48" s="114"/>
       <c r="BX48" s="112"/>
-      <c r="BY48" s="173">
+      <c r="BY48" s="163">
         <v>99</v>
       </c>
       <c r="BZ48" s="24" t="str">
@@ -50726,7 +50730,7 @@
       </c>
       <c r="CK48" s="114"/>
       <c r="CL48" s="112"/>
-      <c r="CM48" s="173">
+      <c r="CM48" s="163">
         <v>103</v>
       </c>
       <c r="CN48" s="24" t="str">
@@ -50831,7 +50835,7 @@
       <c r="BV49" s="21"/>
       <c r="BW49" s="114"/>
       <c r="BX49" s="115"/>
-      <c r="BY49" s="174"/>
+      <c r="BY49" s="164"/>
       <c r="BZ49" s="26" t="str">
         <f>IF(BW52&gt;BW53,BS52,IF(BW52&lt;BW53,BS53,""))</f>
         <v/>
@@ -50845,7 +50849,7 @@
       </c>
       <c r="CK49" s="114"/>
       <c r="CL49" s="115"/>
-      <c r="CM49" s="174"/>
+      <c r="CM49" s="164"/>
       <c r="CN49" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG56,IF(CK55&lt;CK56,CG55,""))</f>
         <v/>
@@ -51080,7 +51084,7 @@
         <f>BH50/BH54</f>
         <v>0.98522167487684731</v>
       </c>
-      <c r="BK50" s="173">
+      <c r="BK50" s="163">
         <v>79</v>
       </c>
       <c r="BL50" s="24" t="str">
@@ -51333,7 +51337,7 @@
         <f>BH51/BH54</f>
         <v>0.98522167487684731</v>
       </c>
-      <c r="BK51" s="174"/>
+      <c r="BK51" s="164"/>
       <c r="BL51" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!D3,AK80:AS91,9,FALSE),"3rd Group C/E/F/H/I")</f>
         <v>3rd Group C/E/F/H/I</v>
@@ -51593,7 +51597,7 @@
       <c r="BO52" s="21"/>
       <c r="BP52" s="114"/>
       <c r="BQ52" s="112"/>
-      <c r="BR52" s="173">
+      <c r="BR52" s="163">
         <v>92</v>
       </c>
       <c r="BS52" s="24" t="str">
@@ -51848,7 +51852,7 @@
         <v>46204.666666666672</v>
       </c>
       <c r="BQ53" s="115"/>
-      <c r="BR53" s="174"/>
+      <c r="BR53" s="164"/>
       <c r="BS53" s="26" t="str">
         <f>IF(BP54&gt;BP55,BL54,IF(BP54&lt;BP55,BL55,""))</f>
         <v/>
@@ -52052,7 +52056,7 @@
         <f>MAX(BH50:BH53)+1</f>
         <v>101.5</v>
       </c>
-      <c r="BK54" s="173">
+      <c r="BK54" s="163">
         <v>80</v>
       </c>
       <c r="BL54" s="24" t="str">
@@ -52173,7 +52177,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK55" s="174"/>
+      <c r="BK55" s="164"/>
       <c r="BL55" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!K3,AK80:AS91,9,FALSE),"3rd Group E/H/I/J/K")</f>
         <v>3rd Group E/H/I/J/K</v>
@@ -52200,7 +52204,7 @@
       <c r="CC55" s="21"/>
       <c r="CD55" s="114"/>
       <c r="CE55" s="112"/>
-      <c r="CF55" s="173">
+      <c r="CF55" s="163">
         <v>102</v>
       </c>
       <c r="CG55" s="24" t="str">
@@ -52459,7 +52463,7 @@
       <c r="CC56" s="21"/>
       <c r="CD56" s="114"/>
       <c r="CE56" s="115"/>
-      <c r="CF56" s="174"/>
+      <c r="CF56" s="164"/>
       <c r="CG56" s="26" t="str">
         <f>IF(CD64&gt;CD65,BZ64,IF(CD64&lt;CD65,BZ65,""))</f>
         <v/>
@@ -52942,7 +52946,7 @@
         <f>BH58/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK58" s="173">
+      <c r="BK58" s="163">
         <v>86</v>
       </c>
       <c r="BL58" s="24" t="str">
@@ -53190,7 +53194,7 @@
         <f>BH59/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK59" s="174"/>
+      <c r="BK59" s="164"/>
       <c r="BL59" s="26" t="str">
         <f>AS51</f>
         <v>2H</v>
@@ -53413,7 +53417,7 @@
       <c r="BO60" s="21"/>
       <c r="BP60" s="114"/>
       <c r="BQ60" s="112"/>
-      <c r="BR60" s="173">
+      <c r="BR60" s="163">
         <v>95</v>
       </c>
       <c r="BS60" s="24" t="str">
@@ -53526,7 +53530,7 @@
         <v>46206.75</v>
       </c>
       <c r="BQ61" s="115"/>
-      <c r="BR61" s="174"/>
+      <c r="BR61" s="164"/>
       <c r="BS61" s="26" t="str">
         <f>IF(BP62&gt;BP63,BL62,IF(BP62&lt;BP63,BL63,""))</f>
         <v/>
@@ -53655,7 +53659,7 @@
       </c>
       <c r="AF62" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE62 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG62" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE62 &amp; "_draw")</f>
@@ -53667,7 +53671,7 @@
       </c>
       <c r="AI62" s="123">
         <f>SUMIF($E$7:$E$78,$AE62,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE62,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AJ62" s="123">
         <f>SUMIF($E$7:$E$78,$AE62,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE62,$F$7:$F$78)</f>
@@ -53675,23 +53679,23 @@
       </c>
       <c r="AL62" s="123">
         <f>AI62-AJ62</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AM62" s="123">
         <f>AL62-AL66</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AN62" s="123">
         <f>AF62*3+AG62</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO62" s="123">
         <f>AN62/AN66*10+BA62</f>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AP62" s="123">
         <f>AO62*10000000+BI62*100+AM62/AM66*10+AI62/AI66*1++IF(AQ62=0,ROW(),AQ62)/2000000</f>
-        <v>9.3740999999999996E-4</v>
+        <v>75000009.322365984</v>
       </c>
       <c r="AQ62" s="126">
         <f>VLOOKUP(AE62,db_fifarank,2,FALSE)</f>
@@ -53699,7 +53703,7 @@
       </c>
       <c r="AR62" s="125">
         <f>AP62/AP66</f>
-        <v>9.3653208545777108E-4</v>
+        <v>0.99999998666666845</v>
       </c>
       <c r="AS62" s="125" t="str">
         <f>IF(SUM(AF62:AH65)=12,J63,"1J")</f>
@@ -53769,7 +53773,7 @@
         <f>BH62/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK62" s="173">
+      <c r="BK62" s="163">
         <v>88</v>
       </c>
       <c r="BL62" s="24" t="str">
@@ -53831,11 +53835,11 @@
       </c>
       <c r="K63" s="31">
         <f>L63+M63+N63</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" s="31">
         <f>VLOOKUP(1,AD62:AN65,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" s="31">
         <f>VLOOKUP(1,AD62:AN65,4,FALSE)</f>
@@ -53847,11 +53851,11 @@
       </c>
       <c r="O63" s="31" t="str">
         <f>VLOOKUP(1,AD62:AN65,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD62:AN65,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>3 - 0</v>
       </c>
       <c r="P63" s="32">
         <f>L63*3+M63</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R63" s="123">
         <f>DATE(2026,6,25)+TIME(12,0,0)+gmt_delta</f>
@@ -53899,7 +53903,7 @@
       </c>
       <c r="AD63" s="123">
         <f>COUNTIF(AR62:AR65,CONCATENATE("&gt;=",AR63))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE63" s="124" t="str">
         <f>VLOOKUP("Algeria",T,lang,FALSE)</f>
@@ -53915,7 +53919,7 @@
       </c>
       <c r="AH63" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE63 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI63" s="123">
         <f>SUMIF($E$7:$E$78,$AE63,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE63,$G$7:$G$78)</f>
@@ -53923,11 +53927,11 @@
       </c>
       <c r="AJ63" s="123">
         <f>SUMIF($E$7:$E$78,$AE63,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE63,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL63" s="123">
         <f>AI63-AJ63</f>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AM63" s="123">
         <f>AL63-AL66</f>
@@ -53951,7 +53955,7 @@
       </c>
       <c r="AR63" s="125">
         <f>AP63/AP66</f>
-        <v>7.8139751016000102E-4</v>
+        <v>1.0428398564723378E-11</v>
       </c>
       <c r="AS63" s="125" t="str">
         <f>IF(SUM(AF62:AH65)=12,J64,"2J")</f>
@@ -54021,7 +54025,7 @@
         <f>BH63/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK63" s="174"/>
+      <c r="BK63" s="164"/>
       <c r="BL63" s="26" t="str">
         <f>AS45</f>
         <v>2G</v>
@@ -54187,7 +54191,7 @@
       </c>
       <c r="AM64" s="123">
         <f>AL64-AL66</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN64" s="123">
         <f>AF64*3+AG64</f>
@@ -54199,7 +54203,7 @@
       </c>
       <c r="AP64" s="123">
         <f>AO64*10000000+BI64*100+AM64/AM66*10+AI64/AI66*1++IF(AQ64=0,ROW(),AQ64)/2000000</f>
-        <v>7.9672499999999997E-4</v>
+        <v>4.2865110107142854</v>
       </c>
       <c r="AQ64" s="126">
         <f>VLOOKUP(AE64,db_fifarank,2,FALSE)</f>
@@ -54207,7 +54211,7 @@
       </c>
       <c r="AR64" s="125">
         <f>AP64/AP66</f>
-        <v>7.9597884147421369E-4</v>
+        <v>5.7153472276736365E-8</v>
       </c>
       <c r="AT64" s="126" cm="1">
         <f t="array" ref="AT64">SUMPRODUCT(($S$7:$S$78=AE64&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE64&amp;"_win")*($U$7:$U$78))</f>
@@ -54287,7 +54291,7 @@
       <c r="BV64" s="21"/>
       <c r="BW64" s="114"/>
       <c r="BX64" s="112"/>
-      <c r="BY64" s="173">
+      <c r="BY64" s="163">
         <v>100</v>
       </c>
       <c r="BZ64" s="24" t="str">
@@ -54331,7 +54335,7 @@
       <c r="I65" s="69"/>
       <c r="J65" s="33" t="str">
         <f>VLOOKUP(3,AD62:AN65,2,FALSE)</f>
-        <v>Algeria</v>
+        <v>Jordan</v>
       </c>
       <c r="K65" s="23">
         <f>L65+M65+N65</f>
@@ -54403,7 +54407,7 @@
       </c>
       <c r="AD65" s="123">
         <f>COUNTIF(AR62:AR65,CONCATENATE("&gt;=",AR65))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE65" s="124" t="str">
         <f>VLOOKUP("Jordan",T,lang,FALSE)</f>
@@ -54435,7 +54439,7 @@
       </c>
       <c r="AM65" s="123">
         <f>AL65-AL66</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN65" s="123">
         <f>AF65*3+AG65</f>
@@ -54447,7 +54451,7 @@
       </c>
       <c r="AP65" s="123">
         <f>AO65*10000000+BI65*100+AM65/AM66*10+AI65/AI66*1++IF(AQ65=0,ROW(),AQ65)/2000000</f>
-        <v>6.9572500000000001E-4</v>
+        <v>4.2864100107142855</v>
       </c>
       <c r="AQ65" s="126">
         <f>VLOOKUP(AE65,db_fifarank,2,FALSE)</f>
@@ -54455,7 +54459,7 @@
       </c>
       <c r="AR65" s="125">
         <f>AP65/AP66</f>
-        <v>6.9507343121484491E-4</v>
+        <v>5.7152125610255043E-8</v>
       </c>
       <c r="AT65" s="126" cm="1">
         <f t="array" ref="AT65">SUMPRODUCT(($S$7:$S$78=AE65&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE65&amp;"_win")*($U$7:$U$78))</f>
@@ -54541,7 +54545,7 @@
       <c r="BV65" s="21"/>
       <c r="BW65" s="114"/>
       <c r="BX65" s="115"/>
-      <c r="BY65" s="174"/>
+      <c r="BY65" s="164"/>
       <c r="BZ65" s="26" t="str">
         <f>IF(BW68&gt;BW69,BS68,IF(BW68&lt;BW69,BS69,""))</f>
         <v/>
@@ -54583,11 +54587,11 @@
       <c r="I66" s="69"/>
       <c r="J66" s="35" t="str">
         <f>VLOOKUP(4,AD62:AN65,2,FALSE)</f>
-        <v>Jordan</v>
+        <v>Algeria</v>
       </c>
       <c r="K66" s="36">
         <f>L66+M66+N66</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="36">
         <f>VLOOKUP(4,AD62:AN65,3,FALSE)</f>
@@ -54599,11 +54603,11 @@
       </c>
       <c r="N66" s="36">
         <f>VLOOKUP(4,AD62:AN65,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O66" s="36" t="str">
         <f>VLOOKUP(4,AD62:AN65,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD62:AN65,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>0 - 3</v>
       </c>
       <c r="P66" s="37">
         <f>L66*3+M66</f>
@@ -54655,7 +54659,7 @@
       </c>
       <c r="AF66" s="123">
         <f t="shared" ref="AF66:AH66" si="28">MAX(AF62:AF65)-MIN(AF62:AF65)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG66" s="123">
         <f t="shared" si="28"/>
@@ -54663,31 +54667,31 @@
       </c>
       <c r="AH66" s="123">
         <f t="shared" si="28"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI66" s="123">
         <f>MAX(AI62:AI65)+1</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AL66" s="123">
         <f>MIN(AL62:AL65)</f>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AM66" s="123">
         <f>MAX(AM62:AM65)+1</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AN66" s="123">
         <f>MAX(AN62:AN65)+1</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AO66" s="123">
         <f>MAX(AO62:AO65)+1</f>
-        <v>1</v>
+        <v>8.5</v>
       </c>
       <c r="AP66" s="123">
         <f>MAX(AP62:AP65)+1</f>
-        <v>1.0009374099999999</v>
+        <v>75000010.322365984</v>
       </c>
       <c r="AT66" s="126">
         <f>MAX(AT62:AT65)-MIN(AT62:AT65)+1</f>
@@ -54737,7 +54741,7 @@
         <f>MAX(BH62:BH65)+1</f>
         <v>1</v>
       </c>
-      <c r="BK66" s="173">
+      <c r="BK66" s="163">
         <v>85</v>
       </c>
       <c r="BL66" s="24" t="str">
@@ -54837,7 +54841,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK67" s="174"/>
+      <c r="BK67" s="164"/>
       <c r="BL67" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!E3,AK80:AS91,9,FALSE),"3rd Group E/F/G/I/J")</f>
         <v>3rd Group E/F/G/I/J</v>
@@ -55093,7 +55097,7 @@
       <c r="BO68" s="21"/>
       <c r="BP68" s="114"/>
       <c r="BQ68" s="112"/>
-      <c r="BR68" s="173">
+      <c r="BR68" s="163">
         <v>96</v>
       </c>
       <c r="BS68" s="24" t="str">
@@ -55107,25 +55111,25 @@
         <f>IF(OR(BT68="",BT69="",AND(BU68="",BU69&lt;&gt;""),AND(BU69="",BU68&lt;&gt;""),AND(BV68="",BV69&lt;&gt;""),AND(BV69="",BV68&lt;&gt;"")),"",BT68*1000+BU68*10+BV68)</f>
         <v/>
       </c>
-      <c r="CE68" s="175" t="str">
+      <c r="CE68" s="195" t="str">
         <f>INDEX(T,144,lang)</f>
         <v>World Champion 2026</v>
       </c>
-      <c r="CF68" s="175"/>
-      <c r="CG68" s="175"/>
-      <c r="CH68" s="175"/>
-      <c r="CI68" s="175"/>
-      <c r="CJ68" s="175"/>
-      <c r="CK68" s="163" t="str">
+      <c r="CF68" s="195"/>
+      <c r="CG68" s="195"/>
+      <c r="CH68" s="195"/>
+      <c r="CI68" s="195"/>
+      <c r="CJ68" s="195"/>
+      <c r="CK68" s="185" t="str">
         <f>IF(CR37&gt;CR38,CN37,IF(CR37&lt;CR38,CN38,""))</f>
         <v/>
       </c>
-      <c r="CL68" s="163"/>
-      <c r="CM68" s="163"/>
-      <c r="CN68" s="163"/>
-      <c r="CO68" s="163"/>
-      <c r="CP68" s="163"/>
-      <c r="CQ68" s="163"/>
+      <c r="CL68" s="185"/>
+      <c r="CM68" s="185"/>
+      <c r="CN68" s="185"/>
+      <c r="CO68" s="185"/>
+      <c r="CP68" s="185"/>
+      <c r="CQ68" s="185"/>
     </row>
     <row r="69" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A69" s="16">
@@ -55363,7 +55367,7 @@
         <v>46207.0625</v>
       </c>
       <c r="BQ69" s="115"/>
-      <c r="BR69" s="174"/>
+      <c r="BR69" s="164"/>
       <c r="BS69" s="26" t="str">
         <f>IF(BP70&gt;BP71,BL70,IF(BP70&lt;BP71,BL71,""))</f>
         <v/>
@@ -55375,19 +55379,19 @@
         <f>IF(BW68="","",BT69*1000+BU69*10+BV69)</f>
         <v/>
       </c>
-      <c r="CE69" s="175"/>
-      <c r="CF69" s="175"/>
-      <c r="CG69" s="175"/>
-      <c r="CH69" s="175"/>
-      <c r="CI69" s="175"/>
-      <c r="CJ69" s="175"/>
-      <c r="CK69" s="163"/>
-      <c r="CL69" s="163"/>
-      <c r="CM69" s="163"/>
-      <c r="CN69" s="163"/>
-      <c r="CO69" s="163"/>
-      <c r="CP69" s="163"/>
-      <c r="CQ69" s="163"/>
+      <c r="CE69" s="195"/>
+      <c r="CF69" s="195"/>
+      <c r="CG69" s="195"/>
+      <c r="CH69" s="195"/>
+      <c r="CI69" s="195"/>
+      <c r="CJ69" s="195"/>
+      <c r="CK69" s="185"/>
+      <c r="CL69" s="185"/>
+      <c r="CM69" s="185"/>
+      <c r="CN69" s="185"/>
+      <c r="CO69" s="185"/>
+      <c r="CP69" s="185"/>
+      <c r="CQ69" s="185"/>
     </row>
     <row r="70" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A70" s="16">
@@ -55608,7 +55612,7 @@
         <f>BH70/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK70" s="173">
+      <c r="BK70" s="163">
         <v>87</v>
       </c>
       <c r="BL70" s="24" t="str">
@@ -55844,7 +55848,7 @@
         <f>BH71/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK71" s="174"/>
+      <c r="BK71" s="164"/>
       <c r="BL71" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!J3,AK80:AS91,9,FALSE),"3rd Group D/E/I/J/L")</f>
         <v>3rd Group D/E/I/J/L</v>
@@ -57520,13 +57524,13 @@
     <row r="83" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="73"/>
       <c r="B83" s="73"/>
-      <c r="C83" s="164" t="s">
+      <c r="C83" s="186" t="s">
         <v>3183</v>
       </c>
-      <c r="D83" s="165"/>
-      <c r="E83" s="165"/>
-      <c r="F83" s="165"/>
-      <c r="G83" s="166"/>
+      <c r="D83" s="187"/>
+      <c r="E83" s="187"/>
+      <c r="F83" s="187"/>
+      <c r="G83" s="188"/>
       <c r="H83" s="75"/>
       <c r="I83" s="69"/>
       <c r="J83" s="99" t="str">
@@ -57624,11 +57628,11 @@
     <row r="84" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="73"/>
       <c r="B84" s="73"/>
-      <c r="C84" s="167"/>
-      <c r="D84" s="168"/>
-      <c r="E84" s="168"/>
-      <c r="F84" s="168"/>
-      <c r="G84" s="169"/>
+      <c r="C84" s="189"/>
+      <c r="D84" s="190"/>
+      <c r="E84" s="190"/>
+      <c r="F84" s="190"/>
+      <c r="G84" s="191"/>
       <c r="H84" s="75"/>
       <c r="I84" s="69"/>
       <c r="J84" s="99" t="str">
@@ -57738,11 +57742,11 @@
     <row r="85" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="73"/>
       <c r="B85" s="73"/>
-      <c r="C85" s="167"/>
-      <c r="D85" s="168"/>
-      <c r="E85" s="168"/>
-      <c r="F85" s="168"/>
-      <c r="G85" s="169"/>
+      <c r="C85" s="189"/>
+      <c r="D85" s="190"/>
+      <c r="E85" s="190"/>
+      <c r="F85" s="190"/>
+      <c r="G85" s="191"/>
       <c r="H85" s="75"/>
       <c r="I85" s="69"/>
       <c r="J85" s="99" t="str">
@@ -57852,16 +57856,16 @@
     <row r="86" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="73"/>
       <c r="B86" s="73"/>
-      <c r="C86" s="167"/>
-      <c r="D86" s="168"/>
-      <c r="E86" s="168"/>
-      <c r="F86" s="168"/>
-      <c r="G86" s="169"/>
+      <c r="C86" s="189"/>
+      <c r="D86" s="190"/>
+      <c r="E86" s="190"/>
+      <c r="F86" s="190"/>
+      <c r="G86" s="191"/>
       <c r="H86" s="75"/>
       <c r="I86" s="69"/>
       <c r="J86" s="99" t="str">
         <f>VLOOKUP(6,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓙ Algeria</v>
+        <v>Ⓛ Panama</v>
       </c>
       <c r="K86" s="100">
         <f t="shared" si="47"/>
@@ -57966,16 +57970,16 @@
     <row r="87" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="73"/>
       <c r="B87" s="73"/>
-      <c r="C87" s="167"/>
-      <c r="D87" s="168"/>
-      <c r="E87" s="168"/>
-      <c r="F87" s="168"/>
-      <c r="G87" s="169"/>
+      <c r="C87" s="189"/>
+      <c r="D87" s="190"/>
+      <c r="E87" s="190"/>
+      <c r="F87" s="190"/>
+      <c r="G87" s="191"/>
       <c r="H87" s="75"/>
       <c r="I87" s="69"/>
       <c r="J87" s="99" t="str">
         <f>VLOOKUP(7,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓛ Panama</v>
+        <v>Ⓚ DR Congo</v>
       </c>
       <c r="K87" s="100">
         <f t="shared" si="47"/>
@@ -58080,16 +58084,16 @@
     <row r="88" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="73"/>
       <c r="B88" s="73"/>
-      <c r="C88" s="170"/>
-      <c r="D88" s="171"/>
-      <c r="E88" s="171"/>
-      <c r="F88" s="171"/>
-      <c r="G88" s="172"/>
+      <c r="C88" s="192"/>
+      <c r="D88" s="193"/>
+      <c r="E88" s="193"/>
+      <c r="F88" s="193"/>
+      <c r="G88" s="194"/>
       <c r="H88" s="75"/>
       <c r="I88" s="69"/>
       <c r="J88" s="99" t="str">
         <f>VLOOKUP(8,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓚ DR Congo</v>
+        <v>Ⓙ Jordan</v>
       </c>
       <c r="K88" s="100">
         <f t="shared" si="47"/>
@@ -58243,11 +58247,11 @@
       </c>
       <c r="AD89" s="123">
         <f t="shared" si="38"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE89" s="124" t="str">
         <f>J65</f>
-        <v>Algeria</v>
+        <v>Jordan</v>
       </c>
       <c r="AF89" s="123">
         <f t="shared" si="39"/>
@@ -58286,11 +58290,11 @@
       </c>
       <c r="AP89" s="123">
         <f>AN89/AN92*10000+AM89/AM92*1000+AI89/AI92*100+IF(AQ89=0,ROW(),AQ89)/2000000</f>
-        <v>666.66744879666658</v>
+        <v>666.66736239166664</v>
       </c>
       <c r="AQ89" s="126">
         <f t="shared" si="37"/>
-        <v>1564.26</v>
+        <v>1391.45</v>
       </c>
       <c r="AR89" s="125" t="str">
         <f t="shared" si="50"/>
@@ -58298,11 +58302,11 @@
       </c>
       <c r="AS89" s="129" t="str">
         <f t="shared" si="46"/>
-        <v>Algeria</v>
+        <v>Jordan</v>
       </c>
       <c r="AT89" s="130" t="str">
         <f>"Ⓙ "&amp;AE89</f>
-        <v>Ⓙ Algeria</v>
+        <v>Ⓙ Jordan</v>
       </c>
     </row>
     <row r="90" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -58357,7 +58361,7 @@
       </c>
       <c r="AD90" s="123">
         <f t="shared" si="38"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE90" s="124" t="str">
         <f>J71</f>
@@ -58471,7 +58475,7 @@
       </c>
       <c r="AD91" s="123">
         <f t="shared" si="38"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE91" s="124" t="str">
         <f>J77</f>
@@ -58762,11 +58766,31 @@
   <sheetProtection algorithmName="SHA-512" hashValue="7nWuIQAsd0NKRlhwUK3tOeNHpTch5B5FULy2gxNNaIdJM5RfhFSMzPcx55y+pmM3d73guUy+p5Y+SvIjJZQRaA==" saltValue="Uw23KnM8csnTioq5H8upCA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <dataConsolidate/>
   <mergeCells count="45">
-    <mergeCell ref="BK14:BK15"/>
-    <mergeCell ref="BY16:BY17"/>
-    <mergeCell ref="BK26:BK27"/>
-    <mergeCell ref="BR28:BR29"/>
-    <mergeCell ref="BK22:BK23"/>
+    <mergeCell ref="CK68:CQ69"/>
+    <mergeCell ref="C83:G88"/>
+    <mergeCell ref="BK70:BK71"/>
+    <mergeCell ref="BY48:BY49"/>
+    <mergeCell ref="BY64:BY65"/>
+    <mergeCell ref="CF55:CF56"/>
+    <mergeCell ref="BK58:BK59"/>
+    <mergeCell ref="BR60:BR61"/>
+    <mergeCell ref="BK62:BK63"/>
+    <mergeCell ref="BK66:BK67"/>
+    <mergeCell ref="BR68:BR69"/>
+    <mergeCell ref="BK50:BK51"/>
+    <mergeCell ref="BR52:BR53"/>
+    <mergeCell ref="BK54:BK55"/>
+    <mergeCell ref="CE68:CJ69"/>
+    <mergeCell ref="CF6:CJ7"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="A5:H6"/>
+    <mergeCell ref="J5:P6"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="BR12:BR13"/>
+    <mergeCell ref="BK6:BO7"/>
+    <mergeCell ref="BR6:BV7"/>
+    <mergeCell ref="BY6:CC7"/>
     <mergeCell ref="CF23:CF24"/>
     <mergeCell ref="BK18:BK19"/>
     <mergeCell ref="BR20:BR21"/>
@@ -58782,31 +58806,11 @@
     <mergeCell ref="BK42:BK43"/>
     <mergeCell ref="CM33:CQ34"/>
     <mergeCell ref="CM37:CM38"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="BR12:BR13"/>
-    <mergeCell ref="BK6:BO7"/>
-    <mergeCell ref="BR6:BV7"/>
-    <mergeCell ref="BY6:CC7"/>
-    <mergeCell ref="CF6:CJ7"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="A5:H6"/>
-    <mergeCell ref="J5:P6"/>
-    <mergeCell ref="CK68:CQ69"/>
-    <mergeCell ref="C83:G88"/>
-    <mergeCell ref="BK70:BK71"/>
-    <mergeCell ref="BY48:BY49"/>
-    <mergeCell ref="BY64:BY65"/>
-    <mergeCell ref="CF55:CF56"/>
-    <mergeCell ref="BK58:BK59"/>
-    <mergeCell ref="BR60:BR61"/>
-    <mergeCell ref="BK62:BK63"/>
-    <mergeCell ref="BK66:BK67"/>
-    <mergeCell ref="BR68:BR69"/>
-    <mergeCell ref="BK50:BK51"/>
-    <mergeCell ref="BR52:BR53"/>
-    <mergeCell ref="BK54:BK55"/>
-    <mergeCell ref="CE68:CJ69"/>
+    <mergeCell ref="BK14:BK15"/>
+    <mergeCell ref="BY16:BY17"/>
+    <mergeCell ref="BK26:BK27"/>
+    <mergeCell ref="BR28:BR29"/>
+    <mergeCell ref="BK22:BK23"/>
   </mergeCells>
   <conditionalFormatting sqref="A7:E78">
     <cfRule type="expression" dxfId="228" priority="339">

--- a/public/worldcup.xlsx
+++ b/public/worldcup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rylanpaul/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F971ACF6-796A-0B45-8B26-AA3E7C735F48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{810ABDFC-956F-EC4A-BFF4-8F0FB6CD876C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T" sheetId="1" state="hidden" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9881" uniqueCount="3715">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9885" uniqueCount="3715">
   <si>
     <t>English</t>
   </si>
@@ -13305,12 +13305,56 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -13391,50 +13435,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -38706,7 +38706,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(B3,Rounds!A$2:A$25,Rounds!D$2:D$25), _xlfn.XLOOKUP(B3,Rounds!D$2:D$25,Rounds!A$2:A$25))</f>
         <v>Tunisia</v>
       </c>
-      <c r="F3" s="154"/>
+      <c r="F3" s="154" t="s">
+        <v>2183</v>
+      </c>
       <c r="G3" s="142" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(F3,Rounds!E$2:E$25,Rounds!F$2:F$25), _xlfn.XLOOKUP(F3,Rounds!H$2:H$25,Rounds!G$2:G$25))</f>
         <v>#N/A</v>
@@ -38715,9 +38717,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(F3,Rounds!E$2:E$25,Rounds!G$2:G$25), _xlfn.XLOOKUP(F3,Rounds!H$2:H$25,Rounds!F$2:F$25))</f>
         <v>#N/A</v>
       </c>
-      <c r="I3" s="140" t="e">
+      <c r="I3" s="140" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F3,Rounds!E$2:E$25,Rounds!H$2:H$25), _xlfn.XLOOKUP(F3,Rounds!H$2:H$25,Rounds!E$2:E$25))</f>
-        <v>#N/A</v>
+        <v>Ecuador</v>
       </c>
       <c r="K3" s="142" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(J3,Rounds!I$2:I$25,Rounds!J$2:J$25), _xlfn.XLOOKUP(J3,Rounds!L$2:L$25,Rounds!K$2:K$25))</f>
@@ -38918,6 +38920,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(B5,Rounds!A$2:A$25,Rounds!D$2:D$25), _xlfn.XLOOKUP(B5,Rounds!D$2:D$25,Rounds!A$2:A$25))</f>
         <v>Uzbekistan</v>
       </c>
+      <c r="F5" t="s">
+        <v>1093</v>
+      </c>
       <c r="G5" s="82" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(F5,Rounds!E$2:E$25,Rounds!F$2:F$25), _xlfn.XLOOKUP(F5,Rounds!H$2:H$25,Rounds!G$2:G$25))</f>
         <v>#N/A</v>
@@ -38926,9 +38931,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(F5,Rounds!E$2:E$25,Rounds!G$2:G$25), _xlfn.XLOOKUP(F5,Rounds!H$2:H$25,Rounds!F$2:F$25))</f>
         <v>#N/A</v>
       </c>
-      <c r="I5" s="134" t="e">
+      <c r="I5" s="134" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F5,Rounds!E$2:E$25,Rounds!H$2:H$25), _xlfn.XLOOKUP(F5,Rounds!H$2:H$25,Rounds!E$2:E$25))</f>
-        <v>#N/A</v>
+        <v>Curaçao</v>
       </c>
       <c r="K5" s="82" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(J5,Rounds!I$2:I$25,Rounds!J$2:J$25), _xlfn.XLOOKUP(J5,Rounds!L$2:L$25,Rounds!K$2:K$25))</f>
@@ -39022,6 +39027,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(B6,Rounds!A$2:A$25,Rounds!D$2:D$25), _xlfn.XLOOKUP(B6,Rounds!D$2:D$25,Rounds!A$2:A$25))</f>
         <v>Iraq</v>
       </c>
+      <c r="F6" s="148" t="s">
+        <v>1604</v>
+      </c>
       <c r="G6" s="146" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(F6,Rounds!E$2:E$25,Rounds!F$2:F$25), _xlfn.XLOOKUP(F6,Rounds!H$2:H$25,Rounds!G$2:G$25))</f>
         <v>#N/A</v>
@@ -39030,9 +39038,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(F6,Rounds!E$2:E$25,Rounds!G$2:G$25), _xlfn.XLOOKUP(F6,Rounds!H$2:H$25,Rounds!F$2:F$25))</f>
         <v>#N/A</v>
       </c>
-      <c r="I6" s="147" t="e">
+      <c r="I6" s="147" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F6,Rounds!E$2:E$25,Rounds!H$2:H$25), _xlfn.XLOOKUP(F6,Rounds!H$2:H$25,Rounds!E$2:E$25))</f>
-        <v>#N/A</v>
+        <v>Tunisia</v>
       </c>
       <c r="K6" s="146" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(J6,Rounds!I$2:I$25,Rounds!J$2:J$25), _xlfn.XLOOKUP(J6,Rounds!L$2:L$25,Rounds!K$2:K$25))</f>
@@ -39126,6 +39134,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(B7,Rounds!A$2:A$25,Rounds!D$2:D$25), _xlfn.XLOOKUP(B7,Rounds!D$2:D$25,Rounds!A$2:A$25))</f>
         <v>Qatar</v>
       </c>
+      <c r="F7" t="s">
+        <v>2274</v>
+      </c>
       <c r="G7" s="82" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(F7,Rounds!E$2:E$25,Rounds!F$2:F$25), _xlfn.XLOOKUP(F7,Rounds!H$2:H$25,Rounds!G$2:G$25))</f>
         <v>#N/A</v>
@@ -39134,9 +39145,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(F7,Rounds!E$2:E$25,Rounds!G$2:G$25), _xlfn.XLOOKUP(F7,Rounds!H$2:H$25,Rounds!F$2:F$25))</f>
         <v>#N/A</v>
       </c>
-      <c r="I7" s="134" t="e">
+      <c r="I7" s="134" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F7,Rounds!E$2:E$25,Rounds!H$2:H$25), _xlfn.XLOOKUP(F7,Rounds!H$2:H$25,Rounds!E$2:E$25))</f>
-        <v>#N/A</v>
+        <v>New Zealand</v>
       </c>
       <c r="K7" s="82" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(J7,Rounds!I$2:I$25,Rounds!J$2:J$25), _xlfn.XLOOKUP(J7,Rounds!L$2:L$25,Rounds!K$2:K$25))</f>
@@ -40670,11 +40681,11 @@
       <c r="A21" s="132" t="str">
         <v>Austria</v>
       </c>
-      <c r="B21" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C21" s="81" t="e">
-        <v>#N/A</v>
+      <c r="B21" s="81">
+        <v>3</v>
+      </c>
+      <c r="C21" s="81">
+        <v>1</v>
       </c>
       <c r="D21" s="134" t="str">
         <v>Jordan</v>
@@ -40784,11 +40795,11 @@
       <c r="A24" s="132" t="str">
         <v>Portugal</v>
       </c>
-      <c r="B24" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C24" s="81" t="e">
-        <v>#N/A</v>
+      <c r="B24" s="81">
+        <v>1</v>
+      </c>
+      <c r="C24" s="81">
+        <v>1</v>
       </c>
       <c r="D24" s="134" t="str">
         <v>DR Congo</v>
@@ -40936,25 +40947,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:95" ht="47" x14ac:dyDescent="0.2">
-      <c r="A1" s="171" t="str" cm="1">
+      <c r="A1" s="182" t="str" cm="1">
         <f t="array" ref="A1">INDEX(T,2,lang)</f>
         <v>2026 World Cup Final Tournament Schedule</v>
       </c>
-      <c r="B1" s="171"/>
-      <c r="C1" s="171"/>
-      <c r="D1" s="171"/>
-      <c r="E1" s="171"/>
-      <c r="F1" s="171"/>
-      <c r="G1" s="171"/>
-      <c r="H1" s="171"/>
-      <c r="I1" s="171"/>
-      <c r="J1" s="171"/>
-      <c r="K1" s="171"/>
-      <c r="L1" s="171"/>
-      <c r="M1" s="171"/>
-      <c r="N1" s="171"/>
-      <c r="O1" s="171"/>
-      <c r="P1" s="171"/>
+      <c r="B1" s="182"/>
+      <c r="C1" s="182"/>
+      <c r="D1" s="182"/>
+      <c r="E1" s="182"/>
+      <c r="F1" s="182"/>
+      <c r="G1" s="182"/>
+      <c r="H1" s="182"/>
+      <c r="I1" s="182"/>
+      <c r="J1" s="182"/>
+      <c r="K1" s="182"/>
+      <c r="L1" s="182"/>
+      <c r="M1" s="182"/>
+      <c r="N1" s="182"/>
+      <c r="O1" s="182"/>
+      <c r="P1" s="182"/>
       <c r="S1" s="123"/>
       <c r="T1" s="123"/>
       <c r="AC1" s="123"/>
@@ -41001,11 +41012,11 @@
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
-      <c r="O3" s="172" t="str">
+      <c r="O3" s="183" t="str">
         <f>"Language: " &amp; Settings!C4</f>
         <v>Language: English</v>
       </c>
-      <c r="P3" s="172"/>
+      <c r="P3" s="183"/>
       <c r="S3" s="123"/>
       <c r="T3" s="123"/>
       <c r="AC3" s="123"/>
@@ -41023,43 +41034,43 @@
     </row>
     <row r="4" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:95" x14ac:dyDescent="0.2">
-      <c r="A5" s="173" t="str" cm="1">
+      <c r="A5" s="184" t="str" cm="1">
         <f t="array" ref="A5">INDEX(T,3,lang)</f>
         <v>Group Stage</v>
       </c>
-      <c r="B5" s="174"/>
-      <c r="C5" s="174"/>
-      <c r="D5" s="174"/>
-      <c r="E5" s="174"/>
-      <c r="F5" s="174"/>
-      <c r="G5" s="174"/>
-      <c r="H5" s="175"/>
-      <c r="J5" s="179" t="s">
+      <c r="B5" s="185"/>
+      <c r="C5" s="185"/>
+      <c r="D5" s="185"/>
+      <c r="E5" s="185"/>
+      <c r="F5" s="185"/>
+      <c r="G5" s="185"/>
+      <c r="H5" s="186"/>
+      <c r="J5" s="190" t="s">
         <v>3166</v>
       </c>
-      <c r="K5" s="180"/>
-      <c r="L5" s="180"/>
-      <c r="M5" s="180"/>
-      <c r="N5" s="180"/>
-      <c r="O5" s="180"/>
-      <c r="P5" s="181"/>
+      <c r="K5" s="191"/>
+      <c r="L5" s="191"/>
+      <c r="M5" s="191"/>
+      <c r="N5" s="191"/>
+      <c r="O5" s="191"/>
+      <c r="P5" s="192"/>
     </row>
     <row r="6" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="176"/>
-      <c r="B6" s="177"/>
-      <c r="C6" s="177"/>
-      <c r="D6" s="177"/>
-      <c r="E6" s="177"/>
-      <c r="F6" s="177"/>
-      <c r="G6" s="177"/>
-      <c r="H6" s="178"/>
-      <c r="J6" s="182"/>
-      <c r="K6" s="183"/>
-      <c r="L6" s="183"/>
-      <c r="M6" s="183"/>
-      <c r="N6" s="183"/>
-      <c r="O6" s="183"/>
-      <c r="P6" s="184"/>
+      <c r="A6" s="187"/>
+      <c r="B6" s="188"/>
+      <c r="C6" s="188"/>
+      <c r="D6" s="188"/>
+      <c r="E6" s="188"/>
+      <c r="F6" s="188"/>
+      <c r="G6" s="188"/>
+      <c r="H6" s="189"/>
+      <c r="J6" s="193"/>
+      <c r="K6" s="194"/>
+      <c r="L6" s="194"/>
+      <c r="M6" s="194"/>
+      <c r="N6" s="194"/>
+      <c r="O6" s="194"/>
+      <c r="P6" s="195"/>
       <c r="R6" s="123" t="s">
         <v>3167</v>
       </c>
@@ -41169,37 +41180,37 @@
       <c r="BI6" s="128" t="s">
         <v>3178</v>
       </c>
-      <c r="BK6" s="165" t="s">
+      <c r="BK6" s="176" t="s">
         <v>3179</v>
       </c>
-      <c r="BL6" s="166"/>
-      <c r="BM6" s="166"/>
-      <c r="BN6" s="166"/>
-      <c r="BO6" s="167"/>
-      <c r="BR6" s="165" t="str" cm="1">
+      <c r="BL6" s="177"/>
+      <c r="BM6" s="177"/>
+      <c r="BN6" s="177"/>
+      <c r="BO6" s="178"/>
+      <c r="BR6" s="176" t="str" cm="1">
         <f t="array" ref="BR6">INDEX(T,4,lang)</f>
         <v>Round of 16</v>
       </c>
-      <c r="BS6" s="166"/>
-      <c r="BT6" s="166"/>
-      <c r="BU6" s="166"/>
-      <c r="BV6" s="167"/>
-      <c r="BY6" s="165" t="str" cm="1">
+      <c r="BS6" s="177"/>
+      <c r="BT6" s="177"/>
+      <c r="BU6" s="177"/>
+      <c r="BV6" s="178"/>
+      <c r="BY6" s="176" t="str" cm="1">
         <f t="array" ref="BY6">INDEX(T,5,lang)</f>
         <v>Quarterfinals</v>
       </c>
-      <c r="BZ6" s="166"/>
-      <c r="CA6" s="166"/>
-      <c r="CB6" s="166"/>
-      <c r="CC6" s="167"/>
-      <c r="CF6" s="165" t="str" cm="1">
+      <c r="BZ6" s="177"/>
+      <c r="CA6" s="177"/>
+      <c r="CB6" s="177"/>
+      <c r="CC6" s="178"/>
+      <c r="CF6" s="176" t="str" cm="1">
         <f t="array" ref="CF6">INDEX(T,6,lang)</f>
         <v>Semi-Finals</v>
       </c>
-      <c r="CG6" s="166"/>
-      <c r="CH6" s="166"/>
-      <c r="CI6" s="166"/>
-      <c r="CJ6" s="167"/>
+      <c r="CG6" s="177"/>
+      <c r="CH6" s="177"/>
+      <c r="CI6" s="177"/>
+      <c r="CJ6" s="178"/>
     </row>
     <row r="7" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="11">
@@ -41276,26 +41287,26 @@
         <v>1</v>
       </c>
       <c r="AY7" s="126"/>
-      <c r="BK7" s="168"/>
-      <c r="BL7" s="169"/>
-      <c r="BM7" s="169"/>
-      <c r="BN7" s="169"/>
-      <c r="BO7" s="170"/>
-      <c r="BR7" s="168"/>
-      <c r="BS7" s="169"/>
-      <c r="BT7" s="169"/>
-      <c r="BU7" s="169"/>
-      <c r="BV7" s="170"/>
-      <c r="BY7" s="168"/>
-      <c r="BZ7" s="169"/>
-      <c r="CA7" s="169"/>
-      <c r="CB7" s="169"/>
-      <c r="CC7" s="170"/>
-      <c r="CF7" s="168"/>
-      <c r="CG7" s="169"/>
-      <c r="CH7" s="169"/>
-      <c r="CI7" s="169"/>
-      <c r="CJ7" s="170"/>
+      <c r="BK7" s="179"/>
+      <c r="BL7" s="180"/>
+      <c r="BM7" s="180"/>
+      <c r="BN7" s="180"/>
+      <c r="BO7" s="181"/>
+      <c r="BR7" s="179"/>
+      <c r="BS7" s="180"/>
+      <c r="BT7" s="180"/>
+      <c r="BU7" s="180"/>
+      <c r="BV7" s="181"/>
+      <c r="BY7" s="179"/>
+      <c r="BZ7" s="180"/>
+      <c r="CA7" s="180"/>
+      <c r="CB7" s="180"/>
+      <c r="CC7" s="181"/>
+      <c r="CF7" s="179"/>
+      <c r="CG7" s="180"/>
+      <c r="CH7" s="180"/>
+      <c r="CI7" s="180"/>
+      <c r="CJ7" s="181"/>
     </row>
     <row r="8" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A8" s="16">
@@ -42031,7 +42042,7 @@
         <f>BH10/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK10" s="163">
+      <c r="BK10" s="173">
         <v>74</v>
       </c>
       <c r="BL10" s="24" t="str">
@@ -42294,7 +42305,7 @@
         <f>BH11/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK11" s="164"/>
+      <c r="BK11" s="174"/>
       <c r="BL11" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!G3,AK80:AS91,9,FALSE),"3rd Group A/B/C/D/F")</f>
         <v>3rd Group A/B/C/D/F</v>
@@ -42532,7 +42543,7 @@
       <c r="BO12" s="21"/>
       <c r="BP12" s="114"/>
       <c r="BQ12" s="112"/>
-      <c r="BR12" s="163">
+      <c r="BR12" s="173">
         <v>89</v>
       </c>
       <c r="BS12" s="24" t="str">
@@ -42653,7 +42664,7 @@
         <v>46203.875</v>
       </c>
       <c r="BQ13" s="115"/>
-      <c r="BR13" s="164"/>
+      <c r="BR13" s="174"/>
       <c r="BS13" s="26" t="str">
         <f>IF(BP14&gt;BP15,BL14,IF(BP14&lt;BP15,BL15,""))</f>
         <v/>
@@ -42911,7 +42922,7 @@
         <f>BH14/BH18</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK14" s="163">
+      <c r="BK14" s="173">
         <v>77</v>
       </c>
       <c r="BL14" s="24" t="str">
@@ -43178,7 +43189,7 @@
         <f>BH15/BH18</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK15" s="164"/>
+      <c r="BK15" s="174"/>
       <c r="BL15" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!I3,AK80:AS91,9,FALSE),"3rd Group C/D/F/G/H")</f>
         <v>3rd Group C/D/F/G/H</v>
@@ -43452,7 +43463,7 @@
       <c r="BV16" s="21"/>
       <c r="BW16" s="114"/>
       <c r="BX16" s="112"/>
-      <c r="BY16" s="163">
+      <c r="BY16" s="173">
         <v>97</v>
       </c>
       <c r="BZ16" s="24" t="str">
@@ -43714,7 +43725,7 @@
       <c r="BV17" s="21"/>
       <c r="BW17" s="114"/>
       <c r="BX17" s="115"/>
-      <c r="BY17" s="164"/>
+      <c r="BY17" s="174"/>
       <c r="BZ17" s="26" t="str">
         <f>IF(BW20&gt;BW21,BS20,IF(BW20&lt;BW21,BS21,""))</f>
         <v/>
@@ -43918,7 +43929,7 @@
         <f>MAX(BH14:BH17)+1</f>
         <v>102</v>
       </c>
-      <c r="BK18" s="163">
+      <c r="BK18" s="173">
         <v>73</v>
       </c>
       <c r="BL18" s="24" t="str">
@@ -44026,7 +44037,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BK19" s="164"/>
+      <c r="BK19" s="174"/>
       <c r="BL19" s="26" t="str">
         <f>AS15</f>
         <v>2B</v>
@@ -44304,7 +44315,7 @@
       <c r="BO20" s="21"/>
       <c r="BP20" s="114"/>
       <c r="BQ20" s="112"/>
-      <c r="BR20" s="163">
+      <c r="BR20" s="173">
         <v>90</v>
       </c>
       <c r="BS20" s="24" t="str">
@@ -44577,7 +44588,7 @@
         <v>46203.041666666672</v>
       </c>
       <c r="BQ21" s="115"/>
-      <c r="BR21" s="164"/>
+      <c r="BR21" s="174"/>
       <c r="BS21" s="26" t="str">
         <f>IF(BP22&gt;BP23,BL22,IF(BP22&lt;BP23,BL23,""))</f>
         <v/>
@@ -44831,7 +44842,7 @@
         <f>BH22/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK22" s="163">
+      <c r="BK22" s="173">
         <v>75</v>
       </c>
       <c r="BL22" s="24" t="str">
@@ -45095,7 +45106,7 @@
         <f>BH23/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK23" s="164"/>
+      <c r="BK23" s="174"/>
       <c r="BL23" s="26" t="str">
         <f>AS21</f>
         <v>2C</v>
@@ -45122,7 +45133,7 @@
       <c r="CC23" s="21"/>
       <c r="CD23" s="114"/>
       <c r="CE23" s="112"/>
-      <c r="CF23" s="163">
+      <c r="CF23" s="173">
         <v>101</v>
       </c>
       <c r="CG23" s="24" t="str">
@@ -45343,7 +45354,7 @@
       <c r="CC24" s="21"/>
       <c r="CD24" s="114"/>
       <c r="CE24" s="115"/>
-      <c r="CF24" s="164"/>
+      <c r="CF24" s="174"/>
       <c r="CG24" s="26" t="str">
         <f>IF(CD32&gt;CD33,BZ32,IF(CD32&lt;CD33,BZ33,""))</f>
         <v/>
@@ -45490,8 +45501,12 @@
         <f>AE64</f>
         <v>Austria</v>
       </c>
-      <c r="F26" s="19"/>
-      <c r="G26" s="20"/>
+      <c r="F26" s="19">
+        <v>3</v>
+      </c>
+      <c r="G26" s="20">
+        <v>1</v>
+      </c>
       <c r="H26" s="80" t="str">
         <f>AE65</f>
         <v>Jordan</v>
@@ -45530,11 +45545,11 @@
       </c>
       <c r="S26" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Austria_win</v>
       </c>
       <c r="T26" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Jordan_lose</v>
       </c>
       <c r="U26" s="123">
         <f t="shared" si="8"/>
@@ -45564,9 +45579,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB26" s="123" t="str">
+      <c r="AB26" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD26" s="123">
         <f>COUNTIF(AR26:AR29,CONCATENATE("&gt;=",AR26))</f>
@@ -45692,7 +45707,7 @@
         <f>BH26/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK26" s="163">
+      <c r="BK26" s="173">
         <v>83</v>
       </c>
       <c r="BL26" s="24" t="str">
@@ -45956,7 +45971,7 @@
         <f>BH27/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK27" s="164"/>
+      <c r="BK27" s="174"/>
       <c r="BL27" s="26" t="str">
         <f>AS75</f>
         <v>2L</v>
@@ -46227,7 +46242,7 @@
       <c r="BO28" s="21"/>
       <c r="BP28" s="114"/>
       <c r="BQ28" s="112"/>
-      <c r="BR28" s="163">
+      <c r="BR28" s="173">
         <v>93</v>
       </c>
       <c r="BS28" s="24" t="str">
@@ -46277,8 +46292,12 @@
         <f>AE68</f>
         <v>Portugal</v>
       </c>
-      <c r="F29" s="19"/>
-      <c r="G29" s="20"/>
+      <c r="F29" s="19">
+        <v>1</v>
+      </c>
+      <c r="G29" s="20">
+        <v>1</v>
+      </c>
       <c r="H29" s="80" t="str">
         <f>AE69</f>
         <v>DR Congo</v>
@@ -46317,43 +46336,43 @@
       </c>
       <c r="S29" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Portugal_draw</v>
       </c>
       <c r="T29" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>DR Congo_draw</v>
       </c>
       <c r="U29" s="123">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V29" s="123">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W29" s="123">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X29" s="123">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y29" s="123">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z29" s="123">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA29" s="123">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB29" s="123" t="str">
+      <c r="AB29" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AD29" s="123">
         <f>COUNTIF(AR26:AR29,CONCATENATE("&gt;=",AR29))</f>
@@ -46488,7 +46507,7 @@
         <v>46205.791666666672</v>
       </c>
       <c r="BQ29" s="115"/>
-      <c r="BR29" s="164"/>
+      <c r="BR29" s="174"/>
       <c r="BS29" s="26" t="str">
         <f>IF(BP30&gt;BP31,BL30,IF(BP30&lt;BP31,BL31,""))</f>
         <v/>
@@ -46698,7 +46717,7 @@
         <f>MAX(BH26:BH29)+1</f>
         <v>1</v>
       </c>
-      <c r="BK30" s="163">
+      <c r="BK30" s="173">
         <v>84</v>
       </c>
       <c r="BL30" s="24" t="str">
@@ -46805,7 +46824,7 @@
         <f>IF(OR(F31="",G31=""),"",IF(F31&gt;G31,1,IF(F31&lt;G31,-1,0)))</f>
         <v/>
       </c>
-      <c r="BK31" s="164"/>
+      <c r="BK31" s="174"/>
       <c r="BL31" s="26" t="str">
         <f>AS63</f>
         <v>2J</v>
@@ -47077,7 +47096,7 @@
       <c r="BV32" s="21"/>
       <c r="BW32" s="114"/>
       <c r="BX32" s="112"/>
-      <c r="BY32" s="163">
+      <c r="BY32" s="173">
         <v>98</v>
       </c>
       <c r="BZ32" s="24" t="str">
@@ -47337,7 +47356,7 @@
       <c r="BV33" s="21"/>
       <c r="BW33" s="114"/>
       <c r="BX33" s="115"/>
-      <c r="BY33" s="164"/>
+      <c r="BY33" s="174"/>
       <c r="BZ33" s="26" t="str">
         <f>IF(BW36&gt;BW37,BS36,IF(BW36&lt;BW37,BS37,""))</f>
         <v/>
@@ -47352,14 +47371,14 @@
       <c r="CE33" s="112"/>
       <c r="CK33" s="114"/>
       <c r="CL33" s="112"/>
-      <c r="CM33" s="165" t="str" cm="1">
+      <c r="CM33" s="176" t="str" cm="1">
         <f t="array" ref="CM33">INDEX(T,8,lang)</f>
         <v>Final</v>
       </c>
-      <c r="CN33" s="166"/>
-      <c r="CO33" s="166"/>
-      <c r="CP33" s="166"/>
-      <c r="CQ33" s="167"/>
+      <c r="CN33" s="177"/>
+      <c r="CO33" s="177"/>
+      <c r="CP33" s="177"/>
+      <c r="CQ33" s="178"/>
     </row>
     <row r="34" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A34" s="16">
@@ -47579,7 +47598,7 @@
         <f>BH34/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK34" s="163">
+      <c r="BK34" s="173">
         <v>81</v>
       </c>
       <c r="BL34" s="24" t="str">
@@ -47610,11 +47629,11 @@
       <c r="CE34" s="112"/>
       <c r="CK34" s="114"/>
       <c r="CL34" s="112"/>
-      <c r="CM34" s="168"/>
-      <c r="CN34" s="169"/>
-      <c r="CO34" s="169"/>
-      <c r="CP34" s="169"/>
-      <c r="CQ34" s="170"/>
+      <c r="CM34" s="179"/>
+      <c r="CN34" s="180"/>
+      <c r="CO34" s="180"/>
+      <c r="CP34" s="180"/>
+      <c r="CQ34" s="181"/>
     </row>
     <row r="35" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A35" s="16">
@@ -47834,7 +47853,7 @@
         <f>BH35/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK35" s="164"/>
+      <c r="BK35" s="174"/>
       <c r="BL35" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!F3,AK80:AS91,9,FALSE),"3rd Group B/E/F/I/J")</f>
         <v>3rd Group B/E/F/I/J</v>
@@ -48059,7 +48078,7 @@
       <c r="BO36" s="21"/>
       <c r="BP36" s="114"/>
       <c r="BQ36" s="112"/>
-      <c r="BR36" s="163">
+      <c r="BR36" s="173">
         <v>94</v>
       </c>
       <c r="BS36" s="24" t="str">
@@ -48179,7 +48198,7 @@
         <v>46204.833333333336</v>
       </c>
       <c r="BQ37" s="115"/>
-      <c r="BR37" s="164"/>
+      <c r="BR37" s="174"/>
       <c r="BS37" s="26" t="str">
         <f>IF(BP38&gt;BP39,BL38,IF(BP38&lt;BP39,BL39,""))</f>
         <v/>
@@ -48206,7 +48225,7 @@
       <c r="CJ37" s="21"/>
       <c r="CK37" s="114"/>
       <c r="CL37" s="112"/>
-      <c r="CM37" s="163">
+      <c r="CM37" s="173">
         <v>104</v>
       </c>
       <c r="CN37" s="24" t="str">
@@ -48443,7 +48462,7 @@
         <f>BH38/BH42</f>
         <v>0.98064516129032253</v>
       </c>
-      <c r="BK38" s="163">
+      <c r="BK38" s="173">
         <v>82</v>
       </c>
       <c r="BL38" s="24" t="str">
@@ -48473,7 +48492,7 @@
       <c r="CI38" s="21"/>
       <c r="CJ38" s="21"/>
       <c r="CL38" s="115"/>
-      <c r="CM38" s="164"/>
+      <c r="CM38" s="174"/>
       <c r="CN38" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG55,IF(CK55&lt;CK56,CG56,""))</f>
         <v/>
@@ -48708,7 +48727,7 @@
         <f>BH39/BH42</f>
         <v>0.98064516129032253</v>
       </c>
-      <c r="BK39" s="164"/>
+      <c r="BK39" s="174"/>
       <c r="BL39" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!H3,AK80:AS91,9,FALSE),"3rd Group A/E/H/I/J")</f>
         <v>3rd Group A/E/H/I/J</v>
@@ -49384,7 +49403,7 @@
         <f>MAX(BH38:BH41)+1</f>
         <v>51.666666666666664</v>
       </c>
-      <c r="BK42" s="163">
+      <c r="BK42" s="173">
         <v>76</v>
       </c>
       <c r="BL42" s="24" t="str">
@@ -49477,7 +49496,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BK43" s="164"/>
+      <c r="BK43" s="174"/>
       <c r="BL43" s="26" t="str">
         <f>AS39</f>
         <v>2F</v>
@@ -49733,7 +49752,7 @@
       <c r="BO44" s="21"/>
       <c r="BP44" s="114"/>
       <c r="BQ44" s="112"/>
-      <c r="BR44" s="163">
+      <c r="BR44" s="173">
         <v>91</v>
       </c>
       <c r="BS44" s="24" t="str">
@@ -49748,14 +49767,14 @@
         <v/>
       </c>
       <c r="CK44" s="114"/>
-      <c r="CM44" s="165" t="str" cm="1">
+      <c r="CM44" s="176" t="str" cm="1">
         <f t="array" ref="CM44">INDEX(T,7,lang)</f>
         <v>Third-Place Play-Off</v>
       </c>
-      <c r="CN44" s="166"/>
-      <c r="CO44" s="166"/>
-      <c r="CP44" s="166"/>
-      <c r="CQ44" s="167"/>
+      <c r="CN44" s="177"/>
+      <c r="CO44" s="177"/>
+      <c r="CP44" s="177"/>
+      <c r="CQ44" s="178"/>
     </row>
     <row r="45" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="16">
@@ -49992,7 +50011,7 @@
         <v>46203.708333333336</v>
       </c>
       <c r="BQ45" s="115"/>
-      <c r="BR45" s="164"/>
+      <c r="BR45" s="174"/>
       <c r="BS45" s="26" t="str">
         <f>IF(BP46&gt;BP47,BL46,IF(BP46&lt;BP47,BL47,""))</f>
         <v/>
@@ -50005,11 +50024,11 @@
         <v/>
       </c>
       <c r="CK45" s="114"/>
-      <c r="CM45" s="168"/>
-      <c r="CN45" s="169"/>
-      <c r="CO45" s="169"/>
-      <c r="CP45" s="169"/>
-      <c r="CQ45" s="170"/>
+      <c r="CM45" s="179"/>
+      <c r="CN45" s="180"/>
+      <c r="CO45" s="180"/>
+      <c r="CP45" s="180"/>
+      <c r="CQ45" s="181"/>
     </row>
     <row r="46" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A46" s="16">
@@ -50229,7 +50248,7 @@
         <f>BH46/BH48</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK46" s="163">
+      <c r="BK46" s="173">
         <v>78</v>
       </c>
       <c r="BL46" s="24" t="str">
@@ -50471,7 +50490,7 @@
         <f>BH47/BH48</f>
         <v>0.99019607843137258</v>
       </c>
-      <c r="BK47" s="164"/>
+      <c r="BK47" s="174"/>
       <c r="BL47" s="26" t="str">
         <f>AS57</f>
         <v>2I</v>
@@ -50714,7 +50733,7 @@
       <c r="BV48" s="21"/>
       <c r="BW48" s="114"/>
       <c r="BX48" s="112"/>
-      <c r="BY48" s="163">
+      <c r="BY48" s="173">
         <v>99</v>
       </c>
       <c r="BZ48" s="24" t="str">
@@ -50730,7 +50749,7 @@
       </c>
       <c r="CK48" s="114"/>
       <c r="CL48" s="112"/>
-      <c r="CM48" s="163">
+      <c r="CM48" s="173">
         <v>103</v>
       </c>
       <c r="CN48" s="24" t="str">
@@ -50835,7 +50854,7 @@
       <c r="BV49" s="21"/>
       <c r="BW49" s="114"/>
       <c r="BX49" s="115"/>
-      <c r="BY49" s="164"/>
+      <c r="BY49" s="174"/>
       <c r="BZ49" s="26" t="str">
         <f>IF(BW52&gt;BW53,BS52,IF(BW52&lt;BW53,BS53,""))</f>
         <v/>
@@ -50849,7 +50868,7 @@
       </c>
       <c r="CK49" s="114"/>
       <c r="CL49" s="115"/>
-      <c r="CM49" s="164"/>
+      <c r="CM49" s="174"/>
       <c r="CN49" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG56,IF(CK55&lt;CK56,CG55,""))</f>
         <v/>
@@ -51084,7 +51103,7 @@
         <f>BH50/BH54</f>
         <v>0.98522167487684731</v>
       </c>
-      <c r="BK50" s="163">
+      <c r="BK50" s="173">
         <v>79</v>
       </c>
       <c r="BL50" s="24" t="str">
@@ -51337,7 +51356,7 @@
         <f>BH51/BH54</f>
         <v>0.98522167487684731</v>
       </c>
-      <c r="BK51" s="164"/>
+      <c r="BK51" s="174"/>
       <c r="BL51" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!D3,AK80:AS91,9,FALSE),"3rd Group C/E/F/H/I")</f>
         <v>3rd Group C/E/F/H/I</v>
@@ -51597,7 +51616,7 @@
       <c r="BO52" s="21"/>
       <c r="BP52" s="114"/>
       <c r="BQ52" s="112"/>
-      <c r="BR52" s="163">
+      <c r="BR52" s="173">
         <v>92</v>
       </c>
       <c r="BS52" s="24" t="str">
@@ -51852,7 +51871,7 @@
         <v>46204.666666666672</v>
       </c>
       <c r="BQ53" s="115"/>
-      <c r="BR53" s="164"/>
+      <c r="BR53" s="174"/>
       <c r="BS53" s="26" t="str">
         <f>IF(BP54&gt;BP55,BL54,IF(BP54&lt;BP55,BL55,""))</f>
         <v/>
@@ -52056,7 +52075,7 @@
         <f>MAX(BH50:BH53)+1</f>
         <v>101.5</v>
       </c>
-      <c r="BK54" s="163">
+      <c r="BK54" s="173">
         <v>80</v>
       </c>
       <c r="BL54" s="24" t="str">
@@ -52177,7 +52196,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK55" s="164"/>
+      <c r="BK55" s="174"/>
       <c r="BL55" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!K3,AK80:AS91,9,FALSE),"3rd Group E/H/I/J/K")</f>
         <v>3rd Group E/H/I/J/K</v>
@@ -52204,7 +52223,7 @@
       <c r="CC55" s="21"/>
       <c r="CD55" s="114"/>
       <c r="CE55" s="112"/>
-      <c r="CF55" s="163">
+      <c r="CF55" s="173">
         <v>102</v>
       </c>
       <c r="CG55" s="24" t="str">
@@ -52463,7 +52482,7 @@
       <c r="CC56" s="21"/>
       <c r="CD56" s="114"/>
       <c r="CE56" s="115"/>
-      <c r="CF56" s="164"/>
+      <c r="CF56" s="174"/>
       <c r="CG56" s="26" t="str">
         <f>IF(CD64&gt;CD65,BZ64,IF(CD64&lt;CD65,BZ65,""))</f>
         <v/>
@@ -52946,7 +52965,7 @@
         <f>BH58/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK58" s="163">
+      <c r="BK58" s="173">
         <v>86</v>
       </c>
       <c r="BL58" s="24" t="str">
@@ -53194,7 +53213,7 @@
         <f>BH59/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK59" s="164"/>
+      <c r="BK59" s="174"/>
       <c r="BL59" s="26" t="str">
         <f>AS51</f>
         <v>2H</v>
@@ -53417,7 +53436,7 @@
       <c r="BO60" s="21"/>
       <c r="BP60" s="114"/>
       <c r="BQ60" s="112"/>
-      <c r="BR60" s="163">
+      <c r="BR60" s="173">
         <v>95</v>
       </c>
       <c r="BS60" s="24" t="str">
@@ -53530,7 +53549,7 @@
         <v>46206.75</v>
       </c>
       <c r="BQ61" s="115"/>
-      <c r="BR61" s="164"/>
+      <c r="BR61" s="174"/>
       <c r="BS61" s="26" t="str">
         <f>IF(BP62&gt;BP63,BL62,IF(BP62&lt;BP63,BL63,""))</f>
         <v/>
@@ -53773,7 +53792,7 @@
         <f>BH62/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK62" s="163">
+      <c r="BK62" s="173">
         <v>88</v>
       </c>
       <c r="BL62" s="24" t="str">
@@ -54025,7 +54044,7 @@
         <f>BH63/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK63" s="164"/>
+      <c r="BK63" s="174"/>
       <c r="BL63" s="26" t="str">
         <f>AS45</f>
         <v>2G</v>
@@ -54091,11 +54110,11 @@
       </c>
       <c r="K64" s="23">
         <f>L64+M64+N64</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" s="23">
         <f>VLOOKUP(2,AD62:AN65,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" s="23">
         <f>VLOOKUP(2,AD62:AN65,4,FALSE)</f>
@@ -54107,11 +54126,11 @@
       </c>
       <c r="O64" s="23" t="str">
         <f>VLOOKUP(2,AD62:AN65,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD62:AN65,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>3 - 1</v>
       </c>
       <c r="P64" s="34">
         <f>L64*3+M64</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R64" s="123">
         <f>DATE(2026,6,25)+TIME(12,0,0)+gmt_delta</f>
@@ -54167,7 +54186,7 @@
       </c>
       <c r="AF64" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE64 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG64" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE64 &amp; "_draw")</f>
@@ -54179,31 +54198,31 @@
       </c>
       <c r="AI64" s="123">
         <f>SUMIF($E$7:$E$78,$AE64,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE64,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AJ64" s="123">
         <f>SUMIF($E$7:$E$78,$AE64,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE64,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL64" s="123">
         <f>AI64-AJ64</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM64" s="123">
         <f>AL64-AL66</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AN64" s="123">
         <f>AF64*3+AG64</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO64" s="123">
         <f>AN64/AN66*10+BA64</f>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AP64" s="123">
         <f>AO64*10000000+BI64*100+AM64/AM66*10+AI64/AI66*1++IF(AQ64=0,ROW(),AQ64)/2000000</f>
-        <v>4.2865110107142854</v>
+        <v>75000007.89365387</v>
       </c>
       <c r="AQ64" s="126">
         <f>VLOOKUP(AE64,db_fifarank,2,FALSE)</f>
@@ -54211,7 +54230,7 @@
       </c>
       <c r="AR64" s="125">
         <f>AP64/AP66</f>
-        <v>5.7153472276736365E-8</v>
+        <v>0.99999996761717624</v>
       </c>
       <c r="AT64" s="126" cm="1">
         <f t="array" ref="AT64">SUMPRODUCT(($S$7:$S$78=AE64&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE64&amp;"_win")*($U$7:$U$78))</f>
@@ -54291,7 +54310,7 @@
       <c r="BV64" s="21"/>
       <c r="BW64" s="114"/>
       <c r="BX64" s="112"/>
-      <c r="BY64" s="163">
+      <c r="BY64" s="173">
         <v>100</v>
       </c>
       <c r="BZ64" s="24" t="str">
@@ -54339,7 +54358,7 @@
       </c>
       <c r="K65" s="23">
         <f>L65+M65+N65</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" s="23">
         <f>VLOOKUP(3,AD62:AN65,3,FALSE)</f>
@@ -54351,11 +54370,11 @@
       </c>
       <c r="N65" s="23">
         <f>VLOOKUP(3,AD62:AN65,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O65" s="23" t="str">
         <f>VLOOKUP(3,AD62:AN65,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD62:AN65,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 3</v>
       </c>
       <c r="P65" s="34">
         <f>L65*3+M65</f>
@@ -54423,23 +54442,23 @@
       </c>
       <c r="AH65" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE65 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI65" s="123">
         <f>SUMIF($E$7:$E$78,$AE65,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE65,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ65" s="123">
         <f>SUMIF($E$7:$E$78,$AE65,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE65,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL65" s="123">
         <f>AI65-AJ65</f>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AM65" s="123">
         <f>AL65-AL66</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AN65" s="123">
         <f>AF65*3+AG65</f>
@@ -54451,7 +54470,7 @@
       </c>
       <c r="AP65" s="123">
         <f>AO65*10000000+BI65*100+AM65/AM66*10+AI65/AI66*1++IF(AQ65=0,ROW(),AQ65)/2000000</f>
-        <v>4.2864100107142855</v>
+        <v>1.6792671535714283</v>
       </c>
       <c r="AQ65" s="126">
         <f>VLOOKUP(AE65,db_fifarank,2,FALSE)</f>
@@ -54459,7 +54478,7 @@
       </c>
       <c r="AR65" s="125">
         <f>AP65/AP66</f>
-        <v>5.7152125610255043E-8</v>
+        <v>2.2390225632684331E-8</v>
       </c>
       <c r="AT65" s="126" cm="1">
         <f t="array" ref="AT65">SUMPRODUCT(($S$7:$S$78=AE65&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE65&amp;"_win")*($U$7:$U$78))</f>
@@ -54545,7 +54564,7 @@
       <c r="BV65" s="21"/>
       <c r="BW65" s="114"/>
       <c r="BX65" s="115"/>
-      <c r="BY65" s="164"/>
+      <c r="BY65" s="174"/>
       <c r="BZ65" s="26" t="str">
         <f>IF(BW68&gt;BW69,BS68,IF(BW68&lt;BW69,BS69,""))</f>
         <v/>
@@ -54741,7 +54760,7 @@
         <f>MAX(BH62:BH65)+1</f>
         <v>1</v>
       </c>
-      <c r="BK66" s="163">
+      <c r="BK66" s="173">
         <v>85</v>
       </c>
       <c r="BL66" s="24" t="str">
@@ -54841,7 +54860,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK67" s="164"/>
+      <c r="BK67" s="174"/>
       <c r="BL67" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!E3,AK80:AS91,9,FALSE),"3rd Group E/F/G/I/J")</f>
         <v>3rd Group E/F/G/I/J</v>
@@ -54980,7 +54999,7 @@
       </c>
       <c r="AG68" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE68 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH68" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE68 &amp; "_lose")</f>
@@ -54988,11 +55007,11 @@
       </c>
       <c r="AI68" s="123">
         <f>SUMIF($E$7:$E$78,$AE68,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE68,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ68" s="123">
         <f>SUMIF($E$7:$E$78,$AE68,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE68,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL68" s="123">
         <f>AI68-AJ68</f>
@@ -55004,15 +55023,15 @@
       </c>
       <c r="AN68" s="123">
         <f>AF68*3+AG68</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO68" s="123">
         <f>AN68/AN72*10+BA68</f>
-        <v>0</v>
+        <v>5.9805825242718447</v>
       </c>
       <c r="AP68" s="123">
         <f>AO68*10000000+BI68*100+AM68/AM72*10+AI68/AI72*1++IF(AQ68=0,ROW(),AQ68)/2000000</f>
-        <v>8.8191499999999993E-4</v>
+        <v>59805923.801852785</v>
       </c>
       <c r="AQ68" s="126">
         <f>VLOOKUP(AE68,db_fifarank,2,FALSE)</f>
@@ -55020,7 +55039,7 @@
       </c>
       <c r="AR68" s="125">
         <f>AP68/AP72</f>
-        <v>8.8113791125899203E-4</v>
+        <v>0.99999998327924866</v>
       </c>
       <c r="AS68" s="125" t="str">
         <f>IF(SUM(AF68:AH71)=12,J69,"1K")</f>
@@ -55032,15 +55051,15 @@
       </c>
       <c r="AU68" s="126" cm="1">
         <f t="array" ref="AU68">SUMPRODUCT(($S$7:$S$78=AE68&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE68&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV68" s="126" cm="1">
         <f t="array" ref="AV68">SUMPRODUCT(($E$7:$E$78=AE68)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE68)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW68" s="126" cm="1">
         <f t="array" ref="AW68">SUMPRODUCT(($E$7:$E$78=AE68)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE68)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX68" s="126">
         <f>AV68-AW68</f>
@@ -55052,11 +55071,11 @@
       </c>
       <c r="AZ68" s="126">
         <f>AT68/AT72*1000+AU68/AU72*100+AY68/AY72*10+AV68/AV72</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BA68" s="126">
         <f>AZ68/AZ72</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BB68" s="126" cm="1">
         <f t="array" ref="BB68">SUMPRODUCT(($S$7:$S$78=AE68&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE68&amp;"_win")*($X$7:$X$78))</f>
@@ -55064,15 +55083,15 @@
       </c>
       <c r="BC68" s="126" cm="1">
         <f t="array" ref="BC68">SUMPRODUCT(($S$7:$S$78=AE68&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE68&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD68" s="126" cm="1">
         <f t="array" ref="BD68">SUMPRODUCT(($E$7:$E$78=AE68)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE68)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE68" s="126" cm="1">
         <f t="array" ref="BE68">SUMPRODUCT(($E$7:$E$78=AE68)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE68)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF68" s="126">
         <f>BD68-BE68</f>
@@ -55084,11 +55103,11 @@
       </c>
       <c r="BH68" s="126">
         <f>BB68/BB72*1000+BC68/BC72*100+BG68/BG72*10+BD68/BD72</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BI68" s="126">
         <f>BH68/BH72</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BK68" s="21"/>
       <c r="BL68" s="21"/>
@@ -55097,7 +55116,7 @@
       <c r="BO68" s="21"/>
       <c r="BP68" s="114"/>
       <c r="BQ68" s="112"/>
-      <c r="BR68" s="163">
+      <c r="BR68" s="173">
         <v>96</v>
       </c>
       <c r="BS68" s="24" t="str">
@@ -55111,25 +55130,25 @@
         <f>IF(OR(BT68="",BT69="",AND(BU68="",BU69&lt;&gt;""),AND(BU69="",BU68&lt;&gt;""),AND(BV68="",BV69&lt;&gt;""),AND(BV69="",BV68&lt;&gt;"")),"",BT68*1000+BU68*10+BV68)</f>
         <v/>
       </c>
-      <c r="CE68" s="195" t="str">
+      <c r="CE68" s="175" t="str">
         <f>INDEX(T,144,lang)</f>
         <v>World Champion 2026</v>
       </c>
-      <c r="CF68" s="195"/>
-      <c r="CG68" s="195"/>
-      <c r="CH68" s="195"/>
-      <c r="CI68" s="195"/>
-      <c r="CJ68" s="195"/>
-      <c r="CK68" s="185" t="str">
+      <c r="CF68" s="175"/>
+      <c r="CG68" s="175"/>
+      <c r="CH68" s="175"/>
+      <c r="CI68" s="175"/>
+      <c r="CJ68" s="175"/>
+      <c r="CK68" s="163" t="str">
         <f>IF(CR37&gt;CR38,CN37,IF(CR37&lt;CR38,CN38,""))</f>
         <v/>
       </c>
-      <c r="CL68" s="185"/>
-      <c r="CM68" s="185"/>
-      <c r="CN68" s="185"/>
-      <c r="CO68" s="185"/>
-      <c r="CP68" s="185"/>
-      <c r="CQ68" s="185"/>
+      <c r="CL68" s="163"/>
+      <c r="CM68" s="163"/>
+      <c r="CN68" s="163"/>
+      <c r="CO68" s="163"/>
+      <c r="CP68" s="163"/>
+      <c r="CQ68" s="163"/>
     </row>
     <row r="69" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A69" s="16">
@@ -55164,7 +55183,7 @@
       </c>
       <c r="K69" s="31">
         <f>L69+M69+N69</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" s="31">
         <f>VLOOKUP(1,AD68:AN71,3,FALSE)</f>
@@ -55172,7 +55191,7 @@
       </c>
       <c r="M69" s="31">
         <f>VLOOKUP(1,AD68:AN71,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N69" s="31">
         <f>VLOOKUP(1,AD68:AN71,5,FALSE)</f>
@@ -55180,11 +55199,11 @@
       </c>
       <c r="O69" s="31" t="str">
         <f>VLOOKUP(1,AD68:AN71,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD68:AN71,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 1</v>
       </c>
       <c r="P69" s="32">
         <f>L69*3+M69</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R69" s="123">
         <f>DATE(2026,6,26)+TIME(16,0,0)+gmt_delta</f>
@@ -55232,7 +55251,7 @@
       </c>
       <c r="AD69" s="123">
         <f>COUNTIF(AR68:AR71,CONCATENATE("&gt;=",AR69))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE69" s="124" t="str">
         <f>VLOOKUP("DR Congo",T,lang,FALSE)</f>
@@ -55244,7 +55263,7 @@
       </c>
       <c r="AG69" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE69 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH69" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE69 &amp; "_lose")</f>
@@ -55252,11 +55271,11 @@
       </c>
       <c r="AI69" s="123">
         <f>SUMIF($E$7:$E$78,$AE69,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE69,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ69" s="123">
         <f>SUMIF($E$7:$E$78,$AE69,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE69,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL69" s="123">
         <f>AI69-AJ69</f>
@@ -55268,15 +55287,15 @@
       </c>
       <c r="AN69" s="123">
         <f>AF69*3+AG69</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO69" s="123">
         <f>AN69/AN72*10+BA69</f>
-        <v>0</v>
+        <v>5.9805825242718447</v>
       </c>
       <c r="AP69" s="123">
         <f>AO69*10000000+BI69*100+AM69/AM72*10+AI69/AI72*1++IF(AQ69=0,ROW(),AQ69)/2000000</f>
-        <v>7.391749999999999E-4</v>
+        <v>59805923.801710039</v>
       </c>
       <c r="AQ69" s="126">
         <f>VLOOKUP(AE69,db_fifarank,2,FALSE)</f>
@@ -55284,7 +55303,7 @@
       </c>
       <c r="AR69" s="125">
         <f>AP69/AP72</f>
-        <v>7.385236848844451E-4</v>
+        <v>0.99999998327686179</v>
       </c>
       <c r="AS69" s="125" t="str">
         <f>IF(SUM(AF68:AH71)=12,J70,"2K")</f>
@@ -55296,15 +55315,15 @@
       </c>
       <c r="AU69" s="126" cm="1">
         <f t="array" ref="AU69">SUMPRODUCT(($S$7:$S$78=AE69&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE69&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV69" s="126" cm="1">
         <f t="array" ref="AV69">SUMPRODUCT(($E$7:$E$78=AE69)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE69)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW69" s="126" cm="1">
         <f t="array" ref="AW69">SUMPRODUCT(($E$7:$E$78=AE69)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE69)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX69" s="126">
         <f>AV69-AW69</f>
@@ -55316,11 +55335,11 @@
       </c>
       <c r="AZ69" s="126">
         <f>AT69/AT72*1000+AU69/AU72*100+AY69/AY72*10+AV69/AV72</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BA69" s="126">
         <f>AZ69/AZ72</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BB69" s="126" cm="1">
         <f t="array" ref="BB69">SUMPRODUCT(($S$7:$S$78=AE69&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE69&amp;"_win")*($X$7:$X$78))</f>
@@ -55328,15 +55347,15 @@
       </c>
       <c r="BC69" s="126" cm="1">
         <f t="array" ref="BC69">SUMPRODUCT(($S$7:$S$78=AE69&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE69&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD69" s="126" cm="1">
         <f t="array" ref="BD69">SUMPRODUCT(($E$7:$E$78=AE69)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE69)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE69" s="126" cm="1">
         <f t="array" ref="BE69">SUMPRODUCT(($E$7:$E$78=AE69)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE69)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF69" s="126">
         <f>BD69-BE69</f>
@@ -55348,11 +55367,11 @@
       </c>
       <c r="BH69" s="126">
         <f>BB69/BB72*1000+BC69/BC72*100+BG69/BG72*10+BD69/BD72</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BI69" s="126">
         <f>BH69/BH72</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BK69" s="21" t="str" cm="1">
         <f t="array" ref="BK69">INDEX(T,24+MONTH(BP69),lang) &amp; " " &amp; DAY(BP69) &amp; ", " &amp; YEAR(BP69) &amp; "   " &amp; (IF(HOUR(BP69)&lt;10,0,"")&amp;HOUR(BP69)) &amp; ":" &amp;  (IF(MINUTE(BP69)&lt;10,0,"")&amp;MINUTE(BP69))</f>
@@ -55367,7 +55386,7 @@
         <v>46207.0625</v>
       </c>
       <c r="BQ69" s="115"/>
-      <c r="BR69" s="164"/>
+      <c r="BR69" s="174"/>
       <c r="BS69" s="26" t="str">
         <f>IF(BP70&gt;BP71,BL70,IF(BP70&lt;BP71,BL71,""))</f>
         <v/>
@@ -55379,19 +55398,19 @@
         <f>IF(BW68="","",BT69*1000+BU69*10+BV69)</f>
         <v/>
       </c>
-      <c r="CE69" s="195"/>
-      <c r="CF69" s="195"/>
-      <c r="CG69" s="195"/>
-      <c r="CH69" s="195"/>
-      <c r="CI69" s="195"/>
-      <c r="CJ69" s="195"/>
-      <c r="CK69" s="185"/>
-      <c r="CL69" s="185"/>
-      <c r="CM69" s="185"/>
-      <c r="CN69" s="185"/>
-      <c r="CO69" s="185"/>
-      <c r="CP69" s="185"/>
-      <c r="CQ69" s="185"/>
+      <c r="CE69" s="175"/>
+      <c r="CF69" s="175"/>
+      <c r="CG69" s="175"/>
+      <c r="CH69" s="175"/>
+      <c r="CI69" s="175"/>
+      <c r="CJ69" s="175"/>
+      <c r="CK69" s="163"/>
+      <c r="CL69" s="163"/>
+      <c r="CM69" s="163"/>
+      <c r="CN69" s="163"/>
+      <c r="CO69" s="163"/>
+      <c r="CP69" s="163"/>
+      <c r="CQ69" s="163"/>
     </row>
     <row r="70" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A70" s="16">
@@ -55422,11 +55441,11 @@
       <c r="I70" s="69"/>
       <c r="J70" s="33" t="str">
         <f>VLOOKUP(2,AD68:AN71,2,FALSE)</f>
-        <v>Colombia</v>
+        <v>DR Congo</v>
       </c>
       <c r="K70" s="23">
         <f>L70+M70+N70</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="23">
         <f>VLOOKUP(2,AD68:AN71,3,FALSE)</f>
@@ -55434,7 +55453,7 @@
       </c>
       <c r="M70" s="23">
         <f>VLOOKUP(2,AD68:AN71,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N70" s="23">
         <f>VLOOKUP(2,AD68:AN71,5,FALSE)</f>
@@ -55442,11 +55461,11 @@
       </c>
       <c r="O70" s="23" t="str">
         <f>VLOOKUP(2,AD68:AN71,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD68:AN71,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 1</v>
       </c>
       <c r="P70" s="34">
         <f>L70*3+M70</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R70" s="123">
         <f>DATE(2026,6,26)+TIME(16,0,0)+gmt_delta</f>
@@ -55546,7 +55565,7 @@
       </c>
       <c r="AR70" s="125">
         <f>AP70/AP72</f>
-        <v>7.3202441668655794E-4</v>
+        <v>1.2250792917716104E-11</v>
       </c>
       <c r="AT70" s="126" cm="1">
         <f t="array" ref="AT70">SUMPRODUCT(($S$7:$S$78=AE70&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE70&amp;"_win")*($U$7:$U$78))</f>
@@ -55612,7 +55631,7 @@
         <f>BH70/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK70" s="163">
+      <c r="BK70" s="173">
         <v>87</v>
       </c>
       <c r="BL70" s="24" t="str">
@@ -55658,7 +55677,7 @@
       <c r="I71" s="69"/>
       <c r="J71" s="33" t="str">
         <f>VLOOKUP(3,AD68:AN71,2,FALSE)</f>
-        <v>DR Congo</v>
+        <v>Colombia</v>
       </c>
       <c r="K71" s="23">
         <f>L71+M71+N71</f>
@@ -55730,7 +55749,7 @@
       </c>
       <c r="AD71" s="123">
         <f>COUNTIF(AR68:AR71,CONCATENATE("&gt;=",AR71))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE71" s="124" t="str">
         <f>VLOOKUP("Colombia",T,lang,FALSE)</f>
@@ -55782,7 +55801,7 @@
       </c>
       <c r="AR71" s="125">
         <f>AP71/AP72</f>
-        <v>8.4579907710691335E-4</v>
+        <v>1.4154868481755742E-11</v>
       </c>
       <c r="AT71" s="126" cm="1">
         <f t="array" ref="AT71">SUMPRODUCT(($S$7:$S$78=AE71&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE71&amp;"_win")*($U$7:$U$78))</f>
@@ -55848,7 +55867,7 @@
         <f>BH71/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK71" s="164"/>
+      <c r="BK71" s="174"/>
       <c r="BL71" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!J3,AK80:AS91,9,FALSE),"3rd Group D/E/I/J/L")</f>
         <v>3rd Group D/E/I/J/L</v>
@@ -55967,7 +55986,7 @@
       </c>
       <c r="AG72" s="123">
         <f t="shared" si="35"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH72" s="123">
         <f t="shared" si="35"/>
@@ -55975,7 +55994,7 @@
       </c>
       <c r="AI72" s="123">
         <f>MAX(AI68:AI71)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL72" s="123">
         <f>MIN(AL68:AL71)</f>
@@ -55987,15 +56006,15 @@
       </c>
       <c r="AN72" s="123">
         <f>MAX(AN68:AN71)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO72" s="123">
         <f>MAX(AO68:AO71)+1</f>
-        <v>1</v>
+        <v>6.9805825242718447</v>
       </c>
       <c r="AP72" s="123">
         <f>MAX(AP68:AP71)+1</f>
-        <v>1.0008819149999999</v>
+        <v>59805924.801852785</v>
       </c>
       <c r="AT72" s="126">
         <f>MAX(AT68:AT71)-MIN(AT68:AT71)+1</f>
@@ -56003,15 +56022,15 @@
       </c>
       <c r="AU72" s="126">
         <f>MAX(AU68:AU71)-MIN(AU68:AU71)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV72" s="126">
         <f>MAX(AV68:AV71)-MIN(AV68:AV71)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW72" s="126">
         <f>MAX(AW68:AW71)-MIN(AW68:AW71)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY72" s="126">
         <f>MAX(AY68:AY71)-MIN(AY68:AY71)+1</f>
@@ -56019,7 +56038,7 @@
       </c>
       <c r="AZ72" s="126">
         <f>MAX(AZ68:AZ71)+1</f>
-        <v>1</v>
+        <v>51.5</v>
       </c>
       <c r="BB72" s="126">
         <f>MAX(BB68:BB71)-MIN(BB68:BB71)+1</f>
@@ -56027,15 +56046,15 @@
       </c>
       <c r="BC72" s="126">
         <f>MAX(BC68:BC71)-MIN(BC68:BC71)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD72" s="126">
         <f>MAX(BD68:BD71)-MIN(BD68:BD71)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BE72" s="126">
         <f>MAX(BE68:BE71)-MIN(BE68:BE71)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BG72" s="126">
         <f>MAX(BG68:BG71)-MIN(BG68:BG71)+1</f>
@@ -56043,7 +56062,7 @@
       </c>
       <c r="BH72" s="126">
         <f>MAX(BH68:BH71)+1</f>
-        <v>1</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="73" spans="1:95" x14ac:dyDescent="0.2">
@@ -57255,7 +57274,7 @@
       </c>
       <c r="AD80" s="123">
         <f>COUNTIF($AP$80:$AP$91,CONCATENATE("&gt;=",AP80))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE80" s="124" t="str">
         <f>J11</f>
@@ -57306,11 +57325,11 @@
       </c>
       <c r="AR80" s="125" t="str">
         <f>IF(AD80&lt;=8,RIGHT(AK80,1),"")</f>
-        <v/>
+        <v>A</v>
       </c>
       <c r="AS80" s="129" t="str">
         <f>IF(AD80&lt;=8,AE80,"")</f>
-        <v/>
+        <v>Czech Republic</v>
       </c>
       <c r="AT80" s="130" t="str">
         <f>"Ⓐ "&amp;AE80</f>
@@ -57408,7 +57427,7 @@
       </c>
       <c r="AR81" s="125" t="str">
         <f>AR80&amp;IF(AD81&lt;=8,RIGHT(AK81,1),"")</f>
-        <v>B</v>
+        <v>AB</v>
       </c>
       <c r="AS81" s="129" t="str">
         <f t="shared" ref="AS81:AS91" si="46">IF(AD81&lt;=8,AE81,"")</f>
@@ -57510,7 +57529,7 @@
       </c>
       <c r="AR82" s="125" t="str">
         <f t="shared" ref="AR82:AR91" si="50">AR81&amp;IF(AD82&lt;=8,RIGHT(AK82,1),"")</f>
-        <v>BC</v>
+        <v>ABC</v>
       </c>
       <c r="AS82" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57524,13 +57543,13 @@
     <row r="83" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="73"/>
       <c r="B83" s="73"/>
-      <c r="C83" s="186" t="s">
+      <c r="C83" s="164" t="s">
         <v>3183</v>
       </c>
-      <c r="D83" s="187"/>
-      <c r="E83" s="187"/>
-      <c r="F83" s="187"/>
-      <c r="G83" s="188"/>
+      <c r="D83" s="165"/>
+      <c r="E83" s="165"/>
+      <c r="F83" s="165"/>
+      <c r="G83" s="166"/>
       <c r="H83" s="75"/>
       <c r="I83" s="69"/>
       <c r="J83" s="99" t="str">
@@ -57614,7 +57633,7 @@
       </c>
       <c r="AR83" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BC</v>
+        <v>ABC</v>
       </c>
       <c r="AS83" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57628,11 +57647,11 @@
     <row r="84" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="73"/>
       <c r="B84" s="73"/>
-      <c r="C84" s="189"/>
-      <c r="D84" s="190"/>
-      <c r="E84" s="190"/>
-      <c r="F84" s="190"/>
-      <c r="G84" s="191"/>
+      <c r="C84" s="167"/>
+      <c r="D84" s="168"/>
+      <c r="E84" s="168"/>
+      <c r="F84" s="168"/>
+      <c r="G84" s="169"/>
       <c r="H84" s="75"/>
       <c r="I84" s="69"/>
       <c r="J84" s="99" t="str">
@@ -57677,7 +57696,7 @@
       </c>
       <c r="AD84" s="123">
         <f t="shared" si="38"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE84" s="124" t="str">
         <f>J35</f>
@@ -57728,7 +57747,7 @@
       </c>
       <c r="AR84" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BC</v>
+        <v>ABC</v>
       </c>
       <c r="AS84" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57742,11 +57761,11 @@
     <row r="85" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="73"/>
       <c r="B85" s="73"/>
-      <c r="C85" s="189"/>
-      <c r="D85" s="190"/>
-      <c r="E85" s="190"/>
-      <c r="F85" s="190"/>
-      <c r="G85" s="191"/>
+      <c r="C85" s="167"/>
+      <c r="D85" s="168"/>
+      <c r="E85" s="168"/>
+      <c r="F85" s="168"/>
+      <c r="G85" s="169"/>
       <c r="H85" s="75"/>
       <c r="I85" s="69"/>
       <c r="J85" s="99" t="str">
@@ -57842,7 +57861,7 @@
       </c>
       <c r="AR85" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCF</v>
+        <v>ABCF</v>
       </c>
       <c r="AS85" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57856,16 +57875,16 @@
     <row r="86" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="73"/>
       <c r="B86" s="73"/>
-      <c r="C86" s="189"/>
-      <c r="D86" s="190"/>
-      <c r="E86" s="190"/>
-      <c r="F86" s="190"/>
-      <c r="G86" s="191"/>
+      <c r="C86" s="167"/>
+      <c r="D86" s="168"/>
+      <c r="E86" s="168"/>
+      <c r="F86" s="168"/>
+      <c r="G86" s="169"/>
       <c r="H86" s="75"/>
       <c r="I86" s="69"/>
       <c r="J86" s="99" t="str">
         <f>VLOOKUP(6,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓛ Panama</v>
+        <v>Ⓚ Colombia</v>
       </c>
       <c r="K86" s="100">
         <f t="shared" si="47"/>
@@ -57956,7 +57975,7 @@
       </c>
       <c r="AR86" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCFG</v>
+        <v>ABCFG</v>
       </c>
       <c r="AS86" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57970,16 +57989,16 @@
     <row r="87" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="73"/>
       <c r="B87" s="73"/>
-      <c r="C87" s="189"/>
-      <c r="D87" s="190"/>
-      <c r="E87" s="190"/>
-      <c r="F87" s="190"/>
-      <c r="G87" s="191"/>
+      <c r="C87" s="167"/>
+      <c r="D87" s="168"/>
+      <c r="E87" s="168"/>
+      <c r="F87" s="168"/>
+      <c r="G87" s="169"/>
       <c r="H87" s="75"/>
       <c r="I87" s="69"/>
       <c r="J87" s="99" t="str">
         <f>VLOOKUP(7,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓚ DR Congo</v>
+        <v>Ⓛ Panama</v>
       </c>
       <c r="K87" s="100">
         <f t="shared" si="47"/>
@@ -58070,7 +58089,7 @@
       </c>
       <c r="AR87" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCFGH</v>
+        <v>ABCFGH</v>
       </c>
       <c r="AS87" s="129" t="str">
         <f t="shared" si="46"/>
@@ -58084,20 +58103,20 @@
     <row r="88" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="73"/>
       <c r="B88" s="73"/>
-      <c r="C88" s="192"/>
-      <c r="D88" s="193"/>
-      <c r="E88" s="193"/>
-      <c r="F88" s="193"/>
-      <c r="G88" s="194"/>
+      <c r="C88" s="170"/>
+      <c r="D88" s="171"/>
+      <c r="E88" s="171"/>
+      <c r="F88" s="171"/>
+      <c r="G88" s="172"/>
       <c r="H88" s="75"/>
       <c r="I88" s="69"/>
       <c r="J88" s="99" t="str">
         <f>VLOOKUP(8,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓙ Jordan</v>
+        <v>Ⓐ Czech Republic</v>
       </c>
       <c r="K88" s="100">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="100">
         <f>VLOOKUP(8,$AD$80:$AN$91,3,FALSE)</f>
@@ -58109,11 +58128,11 @@
       </c>
       <c r="N88" s="100">
         <f>VLOOKUP(8,$AD$80:$AN$91,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O88" s="100" t="str">
         <f>VLOOKUP(8,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(8,$AD$80:$AN$91,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 2</v>
       </c>
       <c r="P88" s="101">
         <f t="shared" si="48"/>
@@ -58133,7 +58152,7 @@
       </c>
       <c r="AD88" s="123">
         <f t="shared" si="38"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE88" s="124" t="str">
         <f>J59</f>
@@ -58184,7 +58203,7 @@
       </c>
       <c r="AR88" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCFGH</v>
+        <v>ABCFGH</v>
       </c>
       <c r="AS88" s="129" t="str">
         <f t="shared" si="46"/>
@@ -58207,7 +58226,7 @@
       <c r="I89" s="69"/>
       <c r="J89" s="102" t="str">
         <f>VLOOKUP(9,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓐ Czech Republic</v>
+        <v>Ⓔ Ecuador</v>
       </c>
       <c r="K89" s="103">
         <f t="shared" si="47"/>
@@ -58227,7 +58246,7 @@
       </c>
       <c r="O89" s="103" t="str">
         <f>VLOOKUP(9,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(9,$AD$80:$AN$91,7,FALSE)</f>
-        <v>1 - 2</v>
+        <v>0 - 1</v>
       </c>
       <c r="P89" s="104">
         <f t="shared" si="48"/>
@@ -58247,7 +58266,7 @@
       </c>
       <c r="AD89" s="123">
         <f t="shared" si="38"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AE89" s="124" t="str">
         <f>J65</f>
@@ -58263,26 +58282,26 @@
       </c>
       <c r="AH89" s="123">
         <f t="shared" si="40"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI89" s="123">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ89" s="123">
         <f t="shared" si="42"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK89" s="123" t="s">
         <v>3190</v>
       </c>
       <c r="AL89" s="123">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AM89" s="123">
         <f t="shared" si="44"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN89" s="123">
         <f t="shared" si="45"/>
@@ -58290,7 +58309,7 @@
       </c>
       <c r="AP89" s="123">
         <f>AN89/AN92*10000+AM89/AM92*1000+AI89/AI92*100+IF(AQ89=0,ROW(),AQ89)/2000000</f>
-        <v>666.66736239166664</v>
+        <v>33.334029058333329</v>
       </c>
       <c r="AQ89" s="126">
         <f t="shared" si="37"/>
@@ -58298,11 +58317,11 @@
       </c>
       <c r="AR89" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCFGHJ</v>
+        <v>ABCFGH</v>
       </c>
       <c r="AS89" s="129" t="str">
         <f t="shared" si="46"/>
-        <v>Jordan</v>
+        <v/>
       </c>
       <c r="AT89" s="130" t="str">
         <f>"Ⓙ "&amp;AE89</f>
@@ -58321,7 +58340,7 @@
       <c r="I90" s="69"/>
       <c r="J90" s="102" t="str">
         <f>VLOOKUP(10,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓔ Ecuador</v>
+        <v>Ⓘ Senegal</v>
       </c>
       <c r="K90" s="103">
         <f t="shared" si="47"/>
@@ -58341,7 +58360,7 @@
       </c>
       <c r="O90" s="103" t="str">
         <f>VLOOKUP(10,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(10,$AD$80:$AN$91,7,FALSE)</f>
-        <v>0 - 1</v>
+        <v>1 - 3</v>
       </c>
       <c r="P90" s="104">
         <f t="shared" si="48"/>
@@ -58361,11 +58380,11 @@
       </c>
       <c r="AD90" s="123">
         <f t="shared" si="38"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE90" s="124" t="str">
         <f>J71</f>
-        <v>DR Congo</v>
+        <v>Colombia</v>
       </c>
       <c r="AF90" s="123">
         <f t="shared" si="39"/>
@@ -58404,23 +58423,23 @@
       </c>
       <c r="AP90" s="123">
         <f>AN90/AN92*10000+AM90/AM92*1000+AI90/AI92*100+IF(AQ90=0,ROW(),AQ90)/2000000</f>
-        <v>666.66740584166666</v>
+        <v>666.66751321166657</v>
       </c>
       <c r="AQ90" s="126">
         <f t="shared" si="37"/>
-        <v>1478.35</v>
+        <v>1693.09</v>
       </c>
       <c r="AR90" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCFGHJK</v>
+        <v>ABCFGHK</v>
       </c>
       <c r="AS90" s="129" t="str">
         <f t="shared" si="46"/>
-        <v>DR Congo</v>
+        <v>Colombia</v>
       </c>
       <c r="AT90" s="130" t="str">
         <f>"Ⓚ "&amp;AE90</f>
-        <v>Ⓚ DR Congo</v>
+        <v>Ⓚ Colombia</v>
       </c>
     </row>
     <row r="91" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -58435,7 +58454,7 @@
       <c r="I91" s="69"/>
       <c r="J91" s="102" t="str">
         <f>VLOOKUP(11,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓘ Senegal</v>
+        <v>Ⓙ Jordan</v>
       </c>
       <c r="K91" s="103">
         <f t="shared" si="47"/>
@@ -58475,7 +58494,7 @@
       </c>
       <c r="AD91" s="123">
         <f t="shared" si="38"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE91" s="124" t="str">
         <f>J77</f>
@@ -58526,7 +58545,7 @@
       </c>
       <c r="AR91" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCFGHJKL</v>
+        <v>ABCFGHKL</v>
       </c>
       <c r="AS91" s="129" t="str">
         <f t="shared" si="46"/>
@@ -58766,6 +58785,36 @@
   <sheetProtection algorithmName="SHA-512" hashValue="7nWuIQAsd0NKRlhwUK3tOeNHpTch5B5FULy2gxNNaIdJM5RfhFSMzPcx55y+pmM3d73guUy+p5Y+SvIjJZQRaA==" saltValue="Uw23KnM8csnTioq5H8upCA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <dataConsolidate/>
   <mergeCells count="45">
+    <mergeCell ref="BK14:BK15"/>
+    <mergeCell ref="BY16:BY17"/>
+    <mergeCell ref="BK26:BK27"/>
+    <mergeCell ref="BR28:BR29"/>
+    <mergeCell ref="BK22:BK23"/>
+    <mergeCell ref="CF23:CF24"/>
+    <mergeCell ref="BK18:BK19"/>
+    <mergeCell ref="BR20:BR21"/>
+    <mergeCell ref="CM48:CM49"/>
+    <mergeCell ref="BR44:BR45"/>
+    <mergeCell ref="BK46:BK47"/>
+    <mergeCell ref="BK30:BK31"/>
+    <mergeCell ref="CM44:CQ45"/>
+    <mergeCell ref="BY32:BY33"/>
+    <mergeCell ref="BK38:BK39"/>
+    <mergeCell ref="BK34:BK35"/>
+    <mergeCell ref="BR36:BR37"/>
+    <mergeCell ref="BK42:BK43"/>
+    <mergeCell ref="CM33:CQ34"/>
+    <mergeCell ref="CM37:CM38"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="BR12:BR13"/>
+    <mergeCell ref="BK6:BO7"/>
+    <mergeCell ref="BR6:BV7"/>
+    <mergeCell ref="BY6:CC7"/>
+    <mergeCell ref="CF6:CJ7"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="A5:H6"/>
+    <mergeCell ref="J5:P6"/>
     <mergeCell ref="CK68:CQ69"/>
     <mergeCell ref="C83:G88"/>
     <mergeCell ref="BK70:BK71"/>
@@ -58781,36 +58830,6 @@
     <mergeCell ref="BR52:BR53"/>
     <mergeCell ref="BK54:BK55"/>
     <mergeCell ref="CE68:CJ69"/>
-    <mergeCell ref="CF6:CJ7"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="A5:H6"/>
-    <mergeCell ref="J5:P6"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="BR12:BR13"/>
-    <mergeCell ref="BK6:BO7"/>
-    <mergeCell ref="BR6:BV7"/>
-    <mergeCell ref="BY6:CC7"/>
-    <mergeCell ref="CF23:CF24"/>
-    <mergeCell ref="BK18:BK19"/>
-    <mergeCell ref="BR20:BR21"/>
-    <mergeCell ref="CM48:CM49"/>
-    <mergeCell ref="BR44:BR45"/>
-    <mergeCell ref="BK46:BK47"/>
-    <mergeCell ref="BK30:BK31"/>
-    <mergeCell ref="CM44:CQ45"/>
-    <mergeCell ref="BY32:BY33"/>
-    <mergeCell ref="BK38:BK39"/>
-    <mergeCell ref="BK34:BK35"/>
-    <mergeCell ref="BR36:BR37"/>
-    <mergeCell ref="BK42:BK43"/>
-    <mergeCell ref="CM33:CQ34"/>
-    <mergeCell ref="CM37:CM38"/>
-    <mergeCell ref="BK14:BK15"/>
-    <mergeCell ref="BY16:BY17"/>
-    <mergeCell ref="BK26:BK27"/>
-    <mergeCell ref="BR28:BR29"/>
-    <mergeCell ref="BK22:BK23"/>
   </mergeCells>
   <conditionalFormatting sqref="A7:E78">
     <cfRule type="expression" dxfId="228" priority="339">
@@ -60107,11 +60126,11 @@
     <row r="3" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B3" s="109">
         <f>MATCH(C3,C6:C500,0)</f>
-        <v>85</v>
+        <v>385</v>
       </c>
       <c r="C3" s="121" t="str">
         <f>'2026 World Cup'!AR91</f>
-        <v>BCFGHJKL</v>
+        <v>ABCFGHKL</v>
       </c>
       <c r="D3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,2,FALSE)</f>
@@ -60131,7 +60150,7 @@
       </c>
       <c r="H3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,6,FALSE)</f>
-        <v>3J</v>
+        <v>3A</v>
       </c>
       <c r="I3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,7,FALSE)</f>

--- a/public/worldcup.xlsx
+++ b/public/worldcup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rylanpaul/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{810ABDFC-956F-EC4A-BFF4-8F0FB6CD876C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A30D9966-6EF5-6047-AE09-950073088213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T" sheetId="1" state="hidden" r:id="rId1"/>
@@ -13305,56 +13305,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -13435,6 +13391,50 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -38707,19 +38707,19 @@
         <v>Tunisia</v>
       </c>
       <c r="F3" s="154" t="s">
-        <v>2183</v>
-      </c>
-      <c r="G3" s="142" t="e">
+        <v>1198</v>
+      </c>
+      <c r="G3" s="142">
         <f>IFERROR(_xlfn.XLOOKUP(F3,Rounds!E$2:E$25,Rounds!F$2:F$25), _xlfn.XLOOKUP(F3,Rounds!H$2:H$25,Rounds!G$2:G$25))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H3" s="142" t="e">
+        <v>2</v>
+      </c>
+      <c r="H3" s="142">
         <f>IFERROR(_xlfn.XLOOKUP(F3,Rounds!E$2:E$25,Rounds!G$2:G$25), _xlfn.XLOOKUP(F3,Rounds!H$2:H$25,Rounds!F$2:F$25))</f>
-        <v>#N/A</v>
+        <v>0</v>
       </c>
       <c r="I3" s="140" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F3,Rounds!E$2:E$25,Rounds!H$2:H$25), _xlfn.XLOOKUP(F3,Rounds!H$2:H$25,Rounds!E$2:E$25))</f>
-        <v>Ecuador</v>
+        <v>Australia</v>
       </c>
       <c r="K3" s="142" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(J3,Rounds!I$2:I$25,Rounds!J$2:J$25), _xlfn.XLOOKUP(J3,Rounds!L$2:L$25,Rounds!K$2:K$25))</f>
@@ -38816,13 +38816,13 @@
       <c r="F4" s="148" t="s">
         <v>2274</v>
       </c>
-      <c r="G4" s="146" t="e">
+      <c r="G4" s="146">
         <f>IFERROR(_xlfn.XLOOKUP(F4,Rounds!E$2:E$25,Rounds!F$2:F$25), _xlfn.XLOOKUP(F4,Rounds!H$2:H$25,Rounds!G$2:G$25))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H4" s="146" t="e">
+        <v>3</v>
+      </c>
+      <c r="H4" s="146">
         <f>IFERROR(_xlfn.XLOOKUP(F4,Rounds!E$2:E$25,Rounds!G$2:G$25), _xlfn.XLOOKUP(F4,Rounds!H$2:H$25,Rounds!F$2:F$25))</f>
-        <v>#N/A</v>
+        <v>1</v>
       </c>
       <c r="I4" s="147" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F4,Rounds!E$2:E$25,Rounds!H$2:H$25), _xlfn.XLOOKUP(F4,Rounds!H$2:H$25,Rounds!E$2:E$25))</f>
@@ -38908,13 +38908,13 @@
       <c r="B5" s="132" t="s">
         <v>2573</v>
       </c>
-      <c r="C5" s="82" t="e">
+      <c r="C5" s="82">
         <f>IFERROR(_xlfn.XLOOKUP(B5,Rounds!A$2:A$25,Rounds!B$2:B$25), _xlfn.XLOOKUP(B5,Rounds!D$2:D$25,Rounds!C$2:C$25))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D5" s="82" t="e">
+        <v>3</v>
+      </c>
+      <c r="D5" s="82">
         <f>IFERROR(_xlfn.XLOOKUP(B5,Rounds!A$2:A$25,Rounds!C$2:C$25), _xlfn.XLOOKUP(B5,Rounds!D$2:D$25,Rounds!B$2:B$25))</f>
-        <v>#N/A</v>
+        <v>1</v>
       </c>
       <c r="E5" s="134" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(B5,Rounds!A$2:A$25,Rounds!D$2:D$25), _xlfn.XLOOKUP(B5,Rounds!D$2:D$25,Rounds!A$2:A$25))</f>
@@ -38923,13 +38923,13 @@
       <c r="F5" t="s">
         <v>1093</v>
       </c>
-      <c r="G5" s="82" t="e">
+      <c r="G5" s="82">
         <f>IFERROR(_xlfn.XLOOKUP(F5,Rounds!E$2:E$25,Rounds!F$2:F$25), _xlfn.XLOOKUP(F5,Rounds!H$2:H$25,Rounds!G$2:G$25))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H5" s="82" t="e">
+        <v>0</v>
+      </c>
+      <c r="H5" s="82">
         <f>IFERROR(_xlfn.XLOOKUP(F5,Rounds!E$2:E$25,Rounds!G$2:G$25), _xlfn.XLOOKUP(F5,Rounds!H$2:H$25,Rounds!F$2:F$25))</f>
-        <v>#N/A</v>
+        <v>0</v>
       </c>
       <c r="I5" s="134" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F5,Rounds!E$2:E$25,Rounds!H$2:H$25), _xlfn.XLOOKUP(F5,Rounds!H$2:H$25,Rounds!E$2:E$25))</f>
@@ -39030,13 +39030,13 @@
       <c r="F6" s="148" t="s">
         <v>1604</v>
       </c>
-      <c r="G6" s="146" t="e">
+      <c r="G6" s="146">
         <f>IFERROR(_xlfn.XLOOKUP(F6,Rounds!E$2:E$25,Rounds!F$2:F$25), _xlfn.XLOOKUP(F6,Rounds!H$2:H$25,Rounds!G$2:G$25))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H6" s="146" t="e">
+        <v>4</v>
+      </c>
+      <c r="H6" s="146">
         <f>IFERROR(_xlfn.XLOOKUP(F6,Rounds!E$2:E$25,Rounds!G$2:G$25), _xlfn.XLOOKUP(F6,Rounds!H$2:H$25,Rounds!F$2:F$25))</f>
-        <v>#N/A</v>
+        <v>0</v>
       </c>
       <c r="I6" s="147" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F6,Rounds!E$2:E$25,Rounds!H$2:H$25), _xlfn.XLOOKUP(F6,Rounds!H$2:H$25,Rounds!E$2:E$25))</f>
@@ -39137,13 +39137,13 @@
       <c r="F7" t="s">
         <v>2274</v>
       </c>
-      <c r="G7" s="82" t="e">
+      <c r="G7" s="82">
         <f>IFERROR(_xlfn.XLOOKUP(F7,Rounds!E$2:E$25,Rounds!F$2:F$25), _xlfn.XLOOKUP(F7,Rounds!H$2:H$25,Rounds!G$2:G$25))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H7" s="82" t="e">
+        <v>3</v>
+      </c>
+      <c r="H7" s="82">
         <f>IFERROR(_xlfn.XLOOKUP(F7,Rounds!E$2:E$25,Rounds!G$2:G$25), _xlfn.XLOOKUP(F7,Rounds!H$2:H$25,Rounds!F$2:F$25))</f>
-        <v>#N/A</v>
+        <v>1</v>
       </c>
       <c r="I7" s="134" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F7,Rounds!E$2:E$25,Rounds!H$2:H$25), _xlfn.XLOOKUP(F7,Rounds!H$2:H$25,Rounds!E$2:E$25))</f>
@@ -39244,13 +39244,13 @@
       <c r="F8" s="152" t="s">
         <v>1093</v>
       </c>
-      <c r="G8" s="150" t="e">
+      <c r="G8" s="150">
         <f>IFERROR(_xlfn.XLOOKUP(F8,Rounds!E$2:E$25,Rounds!F$2:F$25), _xlfn.XLOOKUP(F8,Rounds!H$2:H$25,Rounds!G$2:G$25))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H8" s="150" t="e">
+        <v>0</v>
+      </c>
+      <c r="H8" s="150">
         <f>IFERROR(_xlfn.XLOOKUP(F8,Rounds!E$2:E$25,Rounds!G$2:G$25), _xlfn.XLOOKUP(F8,Rounds!H$2:H$25,Rounds!F$2:F$25))</f>
-        <v>#N/A</v>
+        <v>0</v>
       </c>
       <c r="I8" s="151" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F8,Rounds!E$2:E$25,Rounds!H$2:H$25), _xlfn.XLOOKUP(F8,Rounds!H$2:H$25,Rounds!E$2:E$25))</f>
@@ -39474,11 +39474,11 @@
         <f t="array" ref="E2:H25">IF('2026 World Cup'!E31:H54="",NA(),'2026 World Cup'!E31:H54)</f>
         <v>Czech Republic</v>
       </c>
-      <c r="F2" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G2" s="81" t="e">
-        <v>#N/A</v>
+      <c r="F2" s="81">
+        <v>1</v>
+      </c>
+      <c r="G2" s="81">
+        <v>1</v>
       </c>
       <c r="H2" s="134" t="str">
         <v>South Africa</v>
@@ -39593,11 +39593,11 @@
       <c r="E3" s="132" t="str">
         <v>Switzerland</v>
       </c>
-      <c r="F3" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G3" s="81" t="e">
-        <v>#N/A</v>
+      <c r="F3" s="81">
+        <v>4</v>
+      </c>
+      <c r="G3" s="81">
+        <v>1</v>
       </c>
       <c r="H3" s="134" t="str">
         <v>Bosnia and Herzegovina</v>
@@ -39695,11 +39695,11 @@
       <c r="E4" s="132" t="str">
         <v>Canada</v>
       </c>
-      <c r="F4" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G4" s="81" t="e">
-        <v>#N/A</v>
+      <c r="F4" s="81">
+        <v>6</v>
+      </c>
+      <c r="G4" s="81">
+        <v>0</v>
       </c>
       <c r="H4" s="134" t="str">
         <v>Qatar</v>
@@ -39781,11 +39781,11 @@
       <c r="E5" s="132" t="str">
         <v>Mexico</v>
       </c>
-      <c r="F5" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G5" s="81" t="e">
-        <v>#N/A</v>
+      <c r="F5" s="81">
+        <v>1</v>
+      </c>
+      <c r="G5" s="81">
+        <v>0</v>
       </c>
       <c r="H5" s="134" t="str">
         <v>Korea Republic</v>
@@ -39867,11 +39867,11 @@
       <c r="E6" s="132" t="str">
         <v>Brazil</v>
       </c>
-      <c r="F6" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G6" s="81" t="e">
-        <v>#N/A</v>
+      <c r="F6" s="81">
+        <v>3</v>
+      </c>
+      <c r="G6" s="81">
+        <v>0</v>
       </c>
       <c r="H6" s="134" t="str">
         <v>Haiti</v>
@@ -39937,11 +39937,11 @@
       <c r="E7" s="132" t="str">
         <v>Scotland</v>
       </c>
-      <c r="F7" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G7" s="81" t="e">
-        <v>#N/A</v>
+      <c r="F7" s="81">
+        <v>0</v>
+      </c>
+      <c r="G7" s="81">
+        <v>1</v>
       </c>
       <c r="H7" s="134" t="str">
         <v>Morocco</v>
@@ -40007,11 +40007,11 @@
       <c r="E8" s="132" t="str">
         <v>United States</v>
       </c>
-      <c r="F8" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G8" s="81" t="e">
-        <v>#N/A</v>
+      <c r="F8" s="81">
+        <v>2</v>
+      </c>
+      <c r="G8" s="81">
+        <v>0</v>
       </c>
       <c r="H8" s="134" t="str">
         <v>Australia</v>
@@ -40077,11 +40077,11 @@
       <c r="E9" s="132" t="str">
         <v>Turkey</v>
       </c>
-      <c r="F9" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G9" s="81" t="e">
-        <v>#N/A</v>
+      <c r="F9" s="81">
+        <v>0</v>
+      </c>
+      <c r="G9" s="81">
+        <v>1</v>
       </c>
       <c r="H9" s="134" t="str">
         <v>Paraguay</v>
@@ -40147,11 +40147,11 @@
       <c r="E10" s="132" t="str">
         <v>Germany</v>
       </c>
-      <c r="F10" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G10" s="81" t="e">
-        <v>#N/A</v>
+      <c r="F10" s="81">
+        <v>2</v>
+      </c>
+      <c r="G10" s="81">
+        <v>1</v>
       </c>
       <c r="H10" s="134" t="str">
         <v>Ivory Coast</v>
@@ -40201,11 +40201,11 @@
       <c r="E11" s="132" t="str">
         <v>Ecuador</v>
       </c>
-      <c r="F11" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G11" s="81" t="e">
-        <v>#N/A</v>
+      <c r="F11" s="81">
+        <v>0</v>
+      </c>
+      <c r="G11" s="81">
+        <v>0</v>
       </c>
       <c r="H11" s="134" t="str">
         <v>Curaçao</v>
@@ -40255,11 +40255,11 @@
       <c r="E12" s="132" t="str">
         <v>Netherlands</v>
       </c>
-      <c r="F12" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G12" s="81" t="e">
-        <v>#N/A</v>
+      <c r="F12" s="81">
+        <v>5</v>
+      </c>
+      <c r="G12" s="81">
+        <v>1</v>
       </c>
       <c r="H12" s="134" t="str">
         <v>Sweden</v>
@@ -40309,11 +40309,11 @@
       <c r="E13" s="132" t="str">
         <v>Tunisia</v>
       </c>
-      <c r="F13" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G13" s="81" t="e">
-        <v>#N/A</v>
+      <c r="F13" s="81">
+        <v>0</v>
+      </c>
+      <c r="G13" s="81">
+        <v>4</v>
       </c>
       <c r="H13" s="134" t="str">
         <v>Japan</v>
@@ -40363,11 +40363,11 @@
       <c r="E14" s="132" t="str">
         <v>Uruguay</v>
       </c>
-      <c r="F14" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G14" s="81" t="e">
-        <v>#N/A</v>
+      <c r="F14" s="81">
+        <v>2</v>
+      </c>
+      <c r="G14" s="81">
+        <v>2</v>
       </c>
       <c r="H14" s="134" t="str">
         <v>Cape Verde</v>
@@ -40417,11 +40417,11 @@
       <c r="E15" s="132" t="str">
         <v>Spain</v>
       </c>
-      <c r="F15" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G15" s="81" t="e">
-        <v>#N/A</v>
+      <c r="F15" s="81">
+        <v>4</v>
+      </c>
+      <c r="G15" s="81">
+        <v>0</v>
       </c>
       <c r="H15" s="134" t="str">
         <v>Saudi Arabia</v>
@@ -40471,11 +40471,11 @@
       <c r="E16" s="132" t="str">
         <v>Belgium</v>
       </c>
-      <c r="F16" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G16" s="81" t="e">
-        <v>#N/A</v>
+      <c r="F16" s="81">
+        <v>0</v>
+      </c>
+      <c r="G16" s="81">
+        <v>0</v>
       </c>
       <c r="H16" s="134" t="str">
         <v>Iran</v>
@@ -40525,11 +40525,11 @@
       <c r="E17" s="132" t="str">
         <v>New Zealand</v>
       </c>
-      <c r="F17" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G17" s="81" t="e">
-        <v>#N/A</v>
+      <c r="F17" s="81">
+        <v>1</v>
+      </c>
+      <c r="G17" s="81">
+        <v>3</v>
       </c>
       <c r="H17" s="134" t="str">
         <v>Egypt</v>
@@ -40719,11 +40719,11 @@
       <c r="A22" s="132" t="str">
         <v>Ghana</v>
       </c>
-      <c r="B22" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C22" s="81" t="e">
-        <v>#N/A</v>
+      <c r="B22" s="81">
+        <v>1</v>
+      </c>
+      <c r="C22" s="81">
+        <v>0</v>
       </c>
       <c r="D22" s="134" t="str">
         <v>Panama</v>
@@ -40757,11 +40757,11 @@
       <c r="A23" s="132" t="str">
         <v>England</v>
       </c>
-      <c r="B23" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C23" s="81" t="e">
-        <v>#N/A</v>
+      <c r="B23" s="81">
+        <v>4</v>
+      </c>
+      <c r="C23" s="81">
+        <v>2</v>
       </c>
       <c r="D23" s="134" t="str">
         <v>Croatia</v>
@@ -40833,11 +40833,11 @@
       <c r="A25" s="135" t="str">
         <v>Uzbekistan</v>
       </c>
-      <c r="B25" s="153" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C25" s="153" t="e">
-        <v>#N/A</v>
+      <c r="B25" s="153">
+        <v>1</v>
+      </c>
+      <c r="C25" s="153">
+        <v>3</v>
       </c>
       <c r="D25" s="136" t="str">
         <v>Colombia</v>
@@ -40947,25 +40947,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:95" ht="47" x14ac:dyDescent="0.2">
-      <c r="A1" s="182" t="str" cm="1">
+      <c r="A1" s="171" t="str" cm="1">
         <f t="array" ref="A1">INDEX(T,2,lang)</f>
         <v>2026 World Cup Final Tournament Schedule</v>
       </c>
-      <c r="B1" s="182"/>
-      <c r="C1" s="182"/>
-      <c r="D1" s="182"/>
-      <c r="E1" s="182"/>
-      <c r="F1" s="182"/>
-      <c r="G1" s="182"/>
-      <c r="H1" s="182"/>
-      <c r="I1" s="182"/>
-      <c r="J1" s="182"/>
-      <c r="K1" s="182"/>
-      <c r="L1" s="182"/>
-      <c r="M1" s="182"/>
-      <c r="N1" s="182"/>
-      <c r="O1" s="182"/>
-      <c r="P1" s="182"/>
+      <c r="B1" s="171"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="171"/>
+      <c r="F1" s="171"/>
+      <c r="G1" s="171"/>
+      <c r="H1" s="171"/>
+      <c r="I1" s="171"/>
+      <c r="J1" s="171"/>
+      <c r="K1" s="171"/>
+      <c r="L1" s="171"/>
+      <c r="M1" s="171"/>
+      <c r="N1" s="171"/>
+      <c r="O1" s="171"/>
+      <c r="P1" s="171"/>
       <c r="S1" s="123"/>
       <c r="T1" s="123"/>
       <c r="AC1" s="123"/>
@@ -41012,11 +41012,11 @@
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
-      <c r="O3" s="183" t="str">
+      <c r="O3" s="172" t="str">
         <f>"Language: " &amp; Settings!C4</f>
         <v>Language: English</v>
       </c>
-      <c r="P3" s="183"/>
+      <c r="P3" s="172"/>
       <c r="S3" s="123"/>
       <c r="T3" s="123"/>
       <c r="AC3" s="123"/>
@@ -41034,43 +41034,43 @@
     </row>
     <row r="4" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:95" x14ac:dyDescent="0.2">
-      <c r="A5" s="184" t="str" cm="1">
+      <c r="A5" s="173" t="str" cm="1">
         <f t="array" ref="A5">INDEX(T,3,lang)</f>
         <v>Group Stage</v>
       </c>
-      <c r="B5" s="185"/>
-      <c r="C5" s="185"/>
-      <c r="D5" s="185"/>
-      <c r="E5" s="185"/>
-      <c r="F5" s="185"/>
-      <c r="G5" s="185"/>
-      <c r="H5" s="186"/>
-      <c r="J5" s="190" t="s">
+      <c r="B5" s="174"/>
+      <c r="C5" s="174"/>
+      <c r="D5" s="174"/>
+      <c r="E5" s="174"/>
+      <c r="F5" s="174"/>
+      <c r="G5" s="174"/>
+      <c r="H5" s="175"/>
+      <c r="J5" s="179" t="s">
         <v>3166</v>
       </c>
-      <c r="K5" s="191"/>
-      <c r="L5" s="191"/>
-      <c r="M5" s="191"/>
-      <c r="N5" s="191"/>
-      <c r="O5" s="191"/>
-      <c r="P5" s="192"/>
+      <c r="K5" s="180"/>
+      <c r="L5" s="180"/>
+      <c r="M5" s="180"/>
+      <c r="N5" s="180"/>
+      <c r="O5" s="180"/>
+      <c r="P5" s="181"/>
     </row>
     <row r="6" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="187"/>
-      <c r="B6" s="188"/>
-      <c r="C6" s="188"/>
-      <c r="D6" s="188"/>
-      <c r="E6" s="188"/>
-      <c r="F6" s="188"/>
-      <c r="G6" s="188"/>
-      <c r="H6" s="189"/>
-      <c r="J6" s="193"/>
-      <c r="K6" s="194"/>
-      <c r="L6" s="194"/>
-      <c r="M6" s="194"/>
-      <c r="N6" s="194"/>
-      <c r="O6" s="194"/>
-      <c r="P6" s="195"/>
+      <c r="A6" s="176"/>
+      <c r="B6" s="177"/>
+      <c r="C6" s="177"/>
+      <c r="D6" s="177"/>
+      <c r="E6" s="177"/>
+      <c r="F6" s="177"/>
+      <c r="G6" s="177"/>
+      <c r="H6" s="178"/>
+      <c r="J6" s="182"/>
+      <c r="K6" s="183"/>
+      <c r="L6" s="183"/>
+      <c r="M6" s="183"/>
+      <c r="N6" s="183"/>
+      <c r="O6" s="183"/>
+      <c r="P6" s="184"/>
       <c r="R6" s="123" t="s">
         <v>3167</v>
       </c>
@@ -41180,37 +41180,37 @@
       <c r="BI6" s="128" t="s">
         <v>3178</v>
       </c>
-      <c r="BK6" s="176" t="s">
+      <c r="BK6" s="165" t="s">
         <v>3179</v>
       </c>
-      <c r="BL6" s="177"/>
-      <c r="BM6" s="177"/>
-      <c r="BN6" s="177"/>
-      <c r="BO6" s="178"/>
-      <c r="BR6" s="176" t="str" cm="1">
+      <c r="BL6" s="166"/>
+      <c r="BM6" s="166"/>
+      <c r="BN6" s="166"/>
+      <c r="BO6" s="167"/>
+      <c r="BR6" s="165" t="str" cm="1">
         <f t="array" ref="BR6">INDEX(T,4,lang)</f>
         <v>Round of 16</v>
       </c>
-      <c r="BS6" s="177"/>
-      <c r="BT6" s="177"/>
-      <c r="BU6" s="177"/>
-      <c r="BV6" s="178"/>
-      <c r="BY6" s="176" t="str" cm="1">
+      <c r="BS6" s="166"/>
+      <c r="BT6" s="166"/>
+      <c r="BU6" s="166"/>
+      <c r="BV6" s="167"/>
+      <c r="BY6" s="165" t="str" cm="1">
         <f t="array" ref="BY6">INDEX(T,5,lang)</f>
         <v>Quarterfinals</v>
       </c>
-      <c r="BZ6" s="177"/>
-      <c r="CA6" s="177"/>
-      <c r="CB6" s="177"/>
-      <c r="CC6" s="178"/>
-      <c r="CF6" s="176" t="str" cm="1">
+      <c r="BZ6" s="166"/>
+      <c r="CA6" s="166"/>
+      <c r="CB6" s="166"/>
+      <c r="CC6" s="167"/>
+      <c r="CF6" s="165" t="str" cm="1">
         <f t="array" ref="CF6">INDEX(T,6,lang)</f>
         <v>Semi-Finals</v>
       </c>
-      <c r="CG6" s="177"/>
-      <c r="CH6" s="177"/>
-      <c r="CI6" s="177"/>
-      <c r="CJ6" s="178"/>
+      <c r="CG6" s="166"/>
+      <c r="CH6" s="166"/>
+      <c r="CI6" s="166"/>
+      <c r="CJ6" s="167"/>
     </row>
     <row r="7" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="11">
@@ -41287,26 +41287,26 @@
         <v>1</v>
       </c>
       <c r="AY7" s="126"/>
-      <c r="BK7" s="179"/>
-      <c r="BL7" s="180"/>
-      <c r="BM7" s="180"/>
-      <c r="BN7" s="180"/>
-      <c r="BO7" s="181"/>
-      <c r="BR7" s="179"/>
-      <c r="BS7" s="180"/>
-      <c r="BT7" s="180"/>
-      <c r="BU7" s="180"/>
-      <c r="BV7" s="181"/>
-      <c r="BY7" s="179"/>
-      <c r="BZ7" s="180"/>
-      <c r="CA7" s="180"/>
-      <c r="CB7" s="180"/>
-      <c r="CC7" s="181"/>
-      <c r="CF7" s="179"/>
-      <c r="CG7" s="180"/>
-      <c r="CH7" s="180"/>
-      <c r="CI7" s="180"/>
-      <c r="CJ7" s="181"/>
+      <c r="BK7" s="168"/>
+      <c r="BL7" s="169"/>
+      <c r="BM7" s="169"/>
+      <c r="BN7" s="169"/>
+      <c r="BO7" s="170"/>
+      <c r="BR7" s="168"/>
+      <c r="BS7" s="169"/>
+      <c r="BT7" s="169"/>
+      <c r="BU7" s="169"/>
+      <c r="BV7" s="170"/>
+      <c r="BY7" s="168"/>
+      <c r="BZ7" s="169"/>
+      <c r="CA7" s="169"/>
+      <c r="CB7" s="169"/>
+      <c r="CC7" s="170"/>
+      <c r="CF7" s="168"/>
+      <c r="CG7" s="169"/>
+      <c r="CH7" s="169"/>
+      <c r="CI7" s="169"/>
+      <c r="CJ7" s="170"/>
     </row>
     <row r="8" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A8" s="16">
@@ -41420,7 +41420,7 @@
       </c>
       <c r="AF8" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE8 &amp; "_win")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG8" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE8 &amp; "_draw")</f>
@@ -41432,7 +41432,7 @@
       </c>
       <c r="AI8" s="123">
         <f>SUMIF($E$7:$E$78,$AE8,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE8,$G$7:$G$78)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ8" s="123">
         <f>SUMIF($E$7:$E$78,$AE8,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE8,$F$7:$F$78)</f>
@@ -41440,23 +41440,23 @@
       </c>
       <c r="AL8" s="123">
         <f>AI8-AJ8</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM8" s="123">
         <f>AL8-AL12</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN8" s="123">
         <f>AF8*3+AG8</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AO8" s="123">
         <f>AN8/AN12*10+BA8</f>
-        <v>7.5</v>
+        <v>8.5714285714285712</v>
       </c>
       <c r="AP8" s="123">
         <f>AO8*10000000+BI8*100+AM8/AM12*10+AI8/AI12*1++IF(AQ8=0,ROW(),AQ8)/2000000</f>
-        <v>75000008.667507187</v>
+        <v>85714294.79845956</v>
       </c>
       <c r="AQ8" s="126">
         <f>VLOOKUP(AE8,db_fifarank,2,FALSE)</f>
@@ -41464,7 +41464,7 @@
       </c>
       <c r="AR8" s="125">
         <f>AP8/AP12</f>
-        <v>0.99999998666666834</v>
+        <v>0.9999999883333347</v>
       </c>
       <c r="AS8" s="125" t="str">
         <f>IF(SUM(AF8:AH11)=12,J9,"1A")</f>
@@ -41591,11 +41591,11 @@
       </c>
       <c r="K9" s="31">
         <f>L9+M9+N9</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L9" s="31">
         <f>VLOOKUP(1,AD8:AN11,3,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M9" s="31">
         <f>VLOOKUP(1,AD8:AN11,4,FALSE)</f>
@@ -41607,11 +41607,11 @@
       </c>
       <c r="O9" s="31" t="str">
         <f>VLOOKUP(1,AD8:AN11,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD8:AN11,7,FALSE)</f>
-        <v>2 - 0</v>
+        <v>3 - 0</v>
       </c>
       <c r="P9" s="32">
         <f>L9*3+M9</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R9" s="123">
         <f>DATE(2026,6,12)+TIME(8,0,0)+gmt_delta</f>
@@ -41627,27 +41627,27 @@
       </c>
       <c r="U9" s="123">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="123">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W9" s="123">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X9" s="123">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="123">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="123">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA9" s="123">
         <f t="shared" si="5"/>
@@ -41671,7 +41671,7 @@
       </c>
       <c r="AG9" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE9 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH9" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE9 &amp; "_lose")</f>
@@ -41679,11 +41679,11 @@
       </c>
       <c r="AI9" s="123">
         <f>SUMIF($E$7:$E$78,$AE9,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE9,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ9" s="123">
         <f>SUMIF($E$7:$E$78,$AE9,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE9,$F$7:$F$78)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL9" s="123">
         <f>AI9-AJ9</f>
@@ -41695,15 +41695,15 @@
       </c>
       <c r="AN9" s="123">
         <f>AF9*3+AG9</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO9" s="123">
         <f>AN9/AN12*10+BA9</f>
-        <v>0</v>
+        <v>2.409153952843273</v>
       </c>
       <c r="AP9" s="123">
         <f>AO9*10000000+BI9*100+AM9/AM12*10+AI9/AI12*1++IF(AQ9=0,ROW(),AQ9)/2000000</f>
-        <v>7.1486499999999997E-4</v>
+        <v>24091637.837400023</v>
       </c>
       <c r="AQ9" s="126">
         <f>VLOOKUP(AE9,db_fifarank,2,FALSE)</f>
@@ -41711,7 +41711,7 @@
       </c>
       <c r="AR9" s="125">
         <f>AP9/AP12</f>
-        <v>9.5315321047179319E-12</v>
+        <v>0.28106907503559042</v>
       </c>
       <c r="AS9" s="125" t="str">
         <f>IF(SUM(AF8:AH11)=12,J10,"2A")</f>
@@ -41723,15 +41723,15 @@
       </c>
       <c r="AU9" s="126" cm="1">
         <f t="array" ref="AU9">SUMPRODUCT(($S$7:$S$78=AE9&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE9&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV9" s="126" cm="1">
         <f t="array" ref="AV9">SUMPRODUCT(($E$7:$E$78=AE9)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE9)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW9" s="126" cm="1">
         <f t="array" ref="AW9">SUMPRODUCT(($E$7:$E$78=AE9)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE9)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX9" s="126">
         <f>AV9-AW9</f>
@@ -41743,11 +41743,11 @@
       </c>
       <c r="AZ9" s="126">
         <f>AT9/AT12*1000+AU9/AU12*100+AY9/AY12*10+AV9/AV12</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BA9" s="126">
         <f>AZ9/AZ12</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BB9" s="126" cm="1">
         <f t="array" ref="BB9">SUMPRODUCT(($S$7:$S$78=AE9&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE9&amp;"_win")*($X$7:$X$78))</f>
@@ -41755,15 +41755,15 @@
       </c>
       <c r="BC9" s="126" cm="1">
         <f t="array" ref="BC9">SUMPRODUCT(($S$7:$S$78=AE9&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE9&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD9" s="126" cm="1">
         <f t="array" ref="BD9">SUMPRODUCT(($E$7:$E$78=AE9)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE9)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE9" s="126" cm="1">
         <f t="array" ref="BE9">SUMPRODUCT(($E$7:$E$78=AE9)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE9)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF9" s="126">
         <f>BD9-BE9</f>
@@ -41775,11 +41775,11 @@
       </c>
       <c r="BH9" s="126">
         <f>BB9/BB12*1000+BC9/BC12*100+BG9/BG12*10+BD9/BD12</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BI9" s="126">
         <f>BH9/BH12</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BK9" s="21" t="str" cm="1">
         <f t="array" ref="BK9">INDEX(T,24+MONTH(BP9),lang) &amp; " " &amp; DAY(BP9) &amp; ", " &amp; YEAR(BP9) &amp; "   " &amp; (IF(HOUR(BP9)&lt;10,0,"")&amp;HOUR(BP9)) &amp; ":" &amp;  (IF(MINUTE(BP9)&lt;10,0,"")&amp;MINUTE(BP9))</f>
@@ -41856,7 +41856,7 @@
       </c>
       <c r="K10" s="23">
         <f>L10+M10+N10</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L10" s="23">
         <f>VLOOKUP(2,AD8:AN11,3,FALSE)</f>
@@ -41868,11 +41868,11 @@
       </c>
       <c r="N10" s="23">
         <f>VLOOKUP(2,AD8:AN11,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" s="23" t="str">
         <f>VLOOKUP(2,AD8:AN11,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD8:AN11,7,FALSE)</f>
-        <v>2 - 1</v>
+        <v>2 - 2</v>
       </c>
       <c r="P10" s="34">
         <f>L10*3+M10</f>
@@ -41940,7 +41940,7 @@
       </c>
       <c r="AH10" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE10 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI10" s="123">
         <f>SUMIF($E$7:$E$78,$AE10,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE10,$G$7:$G$78)</f>
@@ -41948,15 +41948,15 @@
       </c>
       <c r="AJ10" s="123">
         <f>SUMIF($E$7:$E$78,$AE10,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE10,$F$7:$F$78)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL10" s="123">
         <f>AI10-AJ10</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM10" s="123">
         <f>AL10-AL12</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN10" s="123">
         <f>AF10*3+AG10</f>
@@ -41964,11 +41964,11 @@
       </c>
       <c r="AO10" s="123">
         <f>AN10/AN12*10+BA10</f>
-        <v>7.5</v>
+        <v>4.2857142857142856</v>
       </c>
       <c r="AP10" s="123">
         <f>AO10*10000000+BI10*100+AM10/AM12*10+AI10/AI12*1++IF(AQ10=0,ROW(),AQ10)/2000000</f>
-        <v>75000006.667461008</v>
+        <v>42857146.691270523</v>
       </c>
       <c r="AQ10" s="126">
         <f>VLOOKUP(AE10,db_fifarank,2,FALSE)</f>
@@ -41976,7 +41976,7 @@
       </c>
       <c r="AR10" s="125">
         <f>AP10/AP12</f>
-        <v>0.9999999599993894</v>
+        <v>0.49999998590714367</v>
       </c>
       <c r="AT10" s="126" cm="1">
         <f t="array" ref="AT10">SUMPRODUCT(($S$7:$S$78=AE10&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE10&amp;"_win")*($U$7:$U$78))</f>
@@ -42042,7 +42042,7 @@
         <f>BH10/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK10" s="173">
+      <c r="BK10" s="163">
         <v>74</v>
       </c>
       <c r="BL10" s="24" t="str">
@@ -42119,7 +42119,7 @@
       </c>
       <c r="K11" s="23">
         <f>L11+M11+N11</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L11" s="23">
         <f>VLOOKUP(3,AD8:AN11,3,FALSE)</f>
@@ -42127,7 +42127,7 @@
       </c>
       <c r="M11" s="23">
         <f>VLOOKUP(3,AD8:AN11,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" s="23">
         <f>VLOOKUP(3,AD8:AN11,5,FALSE)</f>
@@ -42135,11 +42135,11 @@
       </c>
       <c r="O11" s="23" t="str">
         <f>VLOOKUP(3,AD8:AN11,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD8:AN11,7,FALSE)</f>
-        <v>1 - 2</v>
+        <v>2 - 3</v>
       </c>
       <c r="P11" s="34">
         <f>L11*3+M11</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" s="123">
         <f>DATE(2026,6,13)+TIME(14,0,0)+gmt_delta</f>
@@ -42199,7 +42199,7 @@
       </c>
       <c r="AG11" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE11 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH11" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE11 &amp; "_lose")</f>
@@ -42207,11 +42207,11 @@
       </c>
       <c r="AI11" s="123">
         <f>SUMIF($E$7:$E$78,$AE11,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE11,$G$7:$G$78)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ11" s="123">
         <f>SUMIF($E$7:$E$78,$AE11,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE11,$F$7:$F$78)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL11" s="123">
         <f>AI11-AJ11</f>
@@ -42223,15 +42223,15 @@
       </c>
       <c r="AN11" s="123">
         <f>AF11*3+AG11</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO11" s="123">
         <f>AN11/AN12*10+BA11</f>
-        <v>0</v>
+        <v>2.409153952843273</v>
       </c>
       <c r="AP11" s="123">
         <f>AO11*10000000+BI11*100+AM11/AM12*10+AI11/AI12*1++IF(AQ11=0,ROW(),AQ11)/2000000</f>
-        <v>2.3340840233333333</v>
+        <v>24091639.754102517</v>
       </c>
       <c r="AQ11" s="126">
         <f>VLOOKUP(AE11,db_fifarank,2,FALSE)</f>
@@ -42239,7 +42239,7 @@
       </c>
       <c r="AR11" s="125">
         <f>AP11/AP12</f>
-        <v>3.1121116299596237E-8</v>
+        <v>0.28106909739711688</v>
       </c>
       <c r="AT11" s="126" cm="1">
         <f t="array" ref="AT11">SUMPRODUCT(($S$7:$S$78=AE11&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE11&amp;"_win")*($U$7:$U$78))</f>
@@ -42247,15 +42247,15 @@
       </c>
       <c r="AU11" s="126" cm="1">
         <f t="array" ref="AU11">SUMPRODUCT(($S$7:$S$78=AE11&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE11&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV11" s="126" cm="1">
         <f t="array" ref="AV11">SUMPRODUCT(($E$7:$E$78=AE11)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE11)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW11" s="126" cm="1">
         <f t="array" ref="AW11">SUMPRODUCT(($E$7:$E$78=AE11)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE11)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX11" s="126">
         <f>AV11-AW11</f>
@@ -42267,11 +42267,11 @@
       </c>
       <c r="AZ11" s="126">
         <f>AT11/AT12*1000+AU11/AU12*100+AY11/AY12*10+AV11/AV12</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BA11" s="126">
         <f>AZ11/AZ12</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BB11" s="126" cm="1">
         <f t="array" ref="BB11">SUMPRODUCT(($S$7:$S$78=AE11&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE11&amp;"_win")*($X$7:$X$78))</f>
@@ -42279,15 +42279,15 @@
       </c>
       <c r="BC11" s="126" cm="1">
         <f t="array" ref="BC11">SUMPRODUCT(($S$7:$S$78=AE11&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE11&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD11" s="126" cm="1">
         <f t="array" ref="BD11">SUMPRODUCT(($E$7:$E$78=AE11)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE11)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE11" s="126" cm="1">
         <f t="array" ref="BE11">SUMPRODUCT(($E$7:$E$78=AE11)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE11)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF11" s="126">
         <f>BD11-BE11</f>
@@ -42299,13 +42299,13 @@
       </c>
       <c r="BH11" s="126">
         <f>BB11/BB12*1000+BC11/BC12*100+BG11/BG12*10+BD11/BD12</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BI11" s="126">
         <f>BH11/BH12</f>
-        <v>0</v>
-      </c>
-      <c r="BK11" s="174"/>
+        <v>0.98058252427184467</v>
+      </c>
+      <c r="BK11" s="164"/>
       <c r="BL11" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!G3,AK80:AS91,9,FALSE),"3rd Group A/B/C/D/F")</f>
         <v>3rd Group A/B/C/D/F</v>
@@ -42386,7 +42386,7 @@
       </c>
       <c r="K12" s="36">
         <f>L12+M12+N12</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L12" s="36">
         <f>VLOOKUP(4,AD8:AN11,3,FALSE)</f>
@@ -42394,7 +42394,7 @@
       </c>
       <c r="M12" s="36">
         <f>VLOOKUP(4,AD8:AN11,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" s="36">
         <f>VLOOKUP(4,AD8:AN11,5,FALSE)</f>
@@ -42402,11 +42402,11 @@
       </c>
       <c r="O12" s="36" t="str">
         <f>VLOOKUP(4,AD8:AN11,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD8:AN11,7,FALSE)</f>
-        <v>0 - 2</v>
+        <v>1 - 3</v>
       </c>
       <c r="P12" s="37">
         <f>L12*3+M12</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" s="123">
         <f>DATE(2026,6,13)+TIME(17,0,0)+gmt_delta</f>
@@ -42454,11 +42454,11 @@
       </c>
       <c r="AF12" s="123">
         <f t="shared" ref="AF12:AH12" si="12">MAX(AF8:AF11)-MIN(AF8:AF11)+1</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG12" s="123">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH12" s="123">
         <f t="shared" si="12"/>
@@ -42466,7 +42466,7 @@
       </c>
       <c r="AI12" s="123">
         <f>MAX(AI8:AI11)+1</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL12" s="123">
         <f>MIN(AL8:AL11)</f>
@@ -42474,19 +42474,19 @@
       </c>
       <c r="AM12" s="123">
         <f>MAX(AM8:AM11)+1</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN12" s="123">
         <f>MAX(AN8:AN11)+1</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AO12" s="123">
         <f>MAX(AO8:AO11)+1</f>
-        <v>8.5</v>
+        <v>9.5714285714285712</v>
       </c>
       <c r="AP12" s="123">
         <f>MAX(AP8:AP11)+1</f>
-        <v>75000009.667507187</v>
+        <v>85714295.79845956</v>
       </c>
       <c r="AT12" s="126">
         <f>MAX(AT8:AT11)-MIN(AT8:AT11)+1</f>
@@ -42494,15 +42494,15 @@
       </c>
       <c r="AU12" s="126">
         <f>MAX(AU8:AU11)-MIN(AU8:AU11)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV12" s="126">
         <f>MAX(AV8:AV11)-MIN(AV8:AV11)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW12" s="126">
         <f>MAX(AW8:AW11)-MIN(AW8:AW11)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY12" s="126">
         <f>MAX(AY8:AY11)-MIN(AY8:AY11)+1</f>
@@ -42510,7 +42510,7 @@
       </c>
       <c r="AZ12" s="126">
         <f>MAX(AZ8:AZ11)+1</f>
-        <v>1</v>
+        <v>51.5</v>
       </c>
       <c r="BB12" s="126">
         <f>MAX(BB8:BB11)-MIN(BB8:BB11)+1</f>
@@ -42518,15 +42518,15 @@
       </c>
       <c r="BC12" s="126">
         <f>MAX(BC8:BC11)-MIN(BC8:BC11)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD12" s="126">
         <f>MAX(BD8:BD11)-MIN(BD8:BD11)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BE12" s="126">
         <f>MAX(BE8:BE11)-MIN(BE8:BE11)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BG12" s="126">
         <f>MAX(BG8:BG11)-MIN(BG8:BG11)+1</f>
@@ -42534,7 +42534,7 @@
       </c>
       <c r="BH12" s="126">
         <f>MAX(BH8:BH11)+1</f>
-        <v>1</v>
+        <v>51.5</v>
       </c>
       <c r="BK12" s="21"/>
       <c r="BL12" s="21"/>
@@ -42543,7 +42543,7 @@
       <c r="BO12" s="21"/>
       <c r="BP12" s="114"/>
       <c r="BQ12" s="112"/>
-      <c r="BR12" s="173">
+      <c r="BR12" s="163">
         <v>89</v>
       </c>
       <c r="BS12" s="24" t="str">
@@ -42664,7 +42664,7 @@
         <v>46203.875</v>
       </c>
       <c r="BQ13" s="115"/>
-      <c r="BR13" s="174"/>
+      <c r="BR13" s="164"/>
       <c r="BS13" s="26" t="str">
         <f>IF(BP14&gt;BP15,BL14,IF(BP14&lt;BP15,BL15,""))</f>
         <v/>
@@ -42768,27 +42768,27 @@
       </c>
       <c r="U14" s="123">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="123">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W14" s="123">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X14" s="123">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y14" s="123">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z14" s="123">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA14" s="123">
         <f t="shared" si="5"/>
@@ -42800,7 +42800,7 @@
       </c>
       <c r="AD14" s="123">
         <f>COUNTIF(AR14:AR17,CONCATENATE("&gt;=",AR14))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE14" s="124" t="str">
         <f>VLOOKUP("Canada",T,lang,FALSE)</f>
@@ -42808,7 +42808,7 @@
       </c>
       <c r="AF14" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE14 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG14" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE14 &amp; "_draw")</f>
@@ -42820,7 +42820,7 @@
       </c>
       <c r="AI14" s="123">
         <f>SUMIF($E$7:$E$78,$AE14,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE14,$G$7:$G$78)</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AJ14" s="123">
         <f>SUMIF($E$7:$E$78,$AE14,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE14,$F$7:$F$78)</f>
@@ -42828,23 +42828,23 @@
       </c>
       <c r="AL14" s="123">
         <f>AI14-AJ14</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AM14" s="123">
         <f>AL14-AL18</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AN14" s="123">
         <f>AF14*3+AG14</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AO14" s="123">
         <f>AN14/AN18*10+BA14</f>
-        <v>5.9901960784313726</v>
+        <v>8</v>
       </c>
       <c r="AP14" s="123">
         <f>AO14*10000000+BI14*100+AM14/AM18*10+AI14/AI18*1++IF(AQ14=0,ROW(),AQ14)/2000000</f>
-        <v>59902060.304699808</v>
+        <v>80000010.106547475</v>
       </c>
       <c r="AQ14" s="126">
         <f>VLOOKUP(AE14,db_fifarank,2,FALSE)</f>
@@ -42852,7 +42852,7 @@
       </c>
       <c r="AR14" s="125">
         <f>AP14/AP18</f>
-        <v>0.99999998330530815</v>
+        <v>0.99999998750000174</v>
       </c>
       <c r="AS14" s="125" t="str">
         <f>IF(SUM(AF14:AH17)=12,J15,"1B")</f>
@@ -42864,15 +42864,15 @@
       </c>
       <c r="AU14" s="126" cm="1">
         <f t="array" ref="AU14">SUMPRODUCT(($S$7:$S$78=AE14&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE14&amp;"_draw")*($U$7:$U$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV14" s="126" cm="1">
         <f t="array" ref="AV14">SUMPRODUCT(($E$7:$E$78=AE14)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE14)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW14" s="126" cm="1">
         <f t="array" ref="AW14">SUMPRODUCT(($E$7:$E$78=AE14)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE14)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX14" s="126">
         <f>AV14-AW14</f>
@@ -42884,11 +42884,11 @@
       </c>
       <c r="AZ14" s="126">
         <f>AT14/AT18*1000+AU14/AU18*100+AY14/AY18*10+AV14/AV18</f>
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="BA14" s="126">
         <f>AZ14/AZ18</f>
-        <v>0.99019607843137258</v>
+        <v>0</v>
       </c>
       <c r="BB14" s="126" cm="1">
         <f t="array" ref="BB14">SUMPRODUCT(($S$7:$S$78=AE14&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE14&amp;"_win")*($X$7:$X$78))</f>
@@ -42896,15 +42896,15 @@
       </c>
       <c r="BC14" s="126" cm="1">
         <f t="array" ref="BC14">SUMPRODUCT(($S$7:$S$78=AE14&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE14&amp;"_draw")*($X$7:$X$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD14" s="126" cm="1">
         <f t="array" ref="BD14">SUMPRODUCT(($E$7:$E$78=AE14)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE14)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE14" s="126" cm="1">
         <f t="array" ref="BE14">SUMPRODUCT(($E$7:$E$78=AE14)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE14)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF14" s="126">
         <f>BD14-BE14</f>
@@ -42916,13 +42916,13 @@
       </c>
       <c r="BH14" s="126">
         <f>BB14/BB18*1000+BC14/BC18*100+BG14/BG18*10+BD14/BD18</f>
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="BI14" s="126">
         <f>BH14/BH18</f>
-        <v>0.99019607843137258</v>
-      </c>
-      <c r="BK14" s="173">
+        <v>0</v>
+      </c>
+      <c r="BK14" s="163">
         <v>77</v>
       </c>
       <c r="BL14" s="24" t="str">
@@ -42995,15 +42995,15 @@
       </c>
       <c r="J15" s="30" t="str">
         <f>VLOOKUP(1,AD14:AN17,2,FALSE)</f>
-        <v>Switzerland</v>
+        <v>Canada</v>
       </c>
       <c r="K15" s="31">
         <f>L15+M15+N15</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L15" s="31">
         <f>VLOOKUP(1,AD14:AN17,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="31">
         <f>VLOOKUP(1,AD14:AN17,4,FALSE)</f>
@@ -43015,11 +43015,11 @@
       </c>
       <c r="O15" s="31" t="str">
         <f>VLOOKUP(1,AD14:AN17,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD14:AN17,7,FALSE)</f>
-        <v>1 - 1</v>
+        <v>7 - 1</v>
       </c>
       <c r="P15" s="32">
         <f>L15*3+M15</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R15" s="123">
         <f>DATE(2026,6,14)+TIME(12,0,0)+gmt_delta</f>
@@ -43067,7 +43067,7 @@
       </c>
       <c r="AD15" s="123">
         <f>COUNTIF(AR14:AR17,CONCATENATE("&gt;=",AR15))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE15" s="124" t="str">
         <f>VLOOKUP("Bosnia and Herzegovina",T,lang,FALSE)</f>
@@ -43083,23 +43083,23 @@
       </c>
       <c r="AH15" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE15 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI15" s="123">
         <f>SUMIF($E$7:$E$78,$AE15,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE15,$G$7:$G$78)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ15" s="123">
         <f>SUMIF($E$7:$E$78,$AE15,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE15,$F$7:$F$78)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AL15" s="123">
         <f>AI15-AJ15</f>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AM15" s="123">
         <f>AL15-AL18</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN15" s="123">
         <f>AF15*3+AG15</f>
@@ -43107,11 +43107,11 @@
       </c>
       <c r="AO15" s="123">
         <f>AN15/AN18*10+BA15</f>
-        <v>5.9901960784313726</v>
+        <v>2</v>
       </c>
       <c r="AP15" s="123">
         <f>AO15*10000000+BI15*100+AM15/AM18*10+AI15/AI18*1++IF(AQ15=0,ROW(),AQ15)/2000000</f>
-        <v>59902060.304614484</v>
+        <v>20000002.558385227</v>
       </c>
       <c r="AQ15" s="126">
         <f>VLOOKUP(AE15,db_fifarank,2,FALSE)</f>
@@ -43119,7 +43119,7 @@
       </c>
       <c r="AR15" s="125">
         <f>AP15/AP18</f>
-        <v>0.99999998330388373</v>
+        <v>0.24999999727185485</v>
       </c>
       <c r="AS15" s="125" t="str">
         <f>IF(SUM(AF14:AH17)=12,J16,"2B")</f>
@@ -43131,15 +43131,15 @@
       </c>
       <c r="AU15" s="126" cm="1">
         <f t="array" ref="AU15">SUMPRODUCT(($S$7:$S$78=AE15&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE15&amp;"_draw")*($U$7:$U$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV15" s="126" cm="1">
         <f t="array" ref="AV15">SUMPRODUCT(($E$7:$E$78=AE15)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE15)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW15" s="126" cm="1">
         <f t="array" ref="AW15">SUMPRODUCT(($E$7:$E$78=AE15)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE15)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX15" s="126">
         <f>AV15-AW15</f>
@@ -43151,11 +43151,11 @@
       </c>
       <c r="AZ15" s="126">
         <f>AT15/AT18*1000+AU15/AU18*100+AY15/AY18*10+AV15/AV18</f>
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="BA15" s="126">
         <f>AZ15/AZ18</f>
-        <v>0.99019607843137258</v>
+        <v>0</v>
       </c>
       <c r="BB15" s="126" cm="1">
         <f t="array" ref="BB15">SUMPRODUCT(($S$7:$S$78=AE15&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE15&amp;"_win")*($X$7:$X$78))</f>
@@ -43163,15 +43163,15 @@
       </c>
       <c r="BC15" s="126" cm="1">
         <f t="array" ref="BC15">SUMPRODUCT(($S$7:$S$78=AE15&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE15&amp;"_draw")*($X$7:$X$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD15" s="126" cm="1">
         <f t="array" ref="BD15">SUMPRODUCT(($E$7:$E$78=AE15)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE15)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE15" s="126" cm="1">
         <f t="array" ref="BE15">SUMPRODUCT(($E$7:$E$78=AE15)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE15)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF15" s="126">
         <f>BD15-BE15</f>
@@ -43183,13 +43183,13 @@
       </c>
       <c r="BH15" s="126">
         <f>BB15/BB18*1000+BC15/BC18*100+BG15/BG18*10+BD15/BD18</f>
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="BI15" s="126">
         <f>BH15/BH18</f>
-        <v>0.99019607843137258</v>
-      </c>
-      <c r="BK15" s="174"/>
+        <v>0</v>
+      </c>
+      <c r="BK15" s="164"/>
       <c r="BL15" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!I3,AK80:AS91,9,FALSE),"3rd Group C/D/F/G/H")</f>
         <v>3rd Group C/D/F/G/H</v>
@@ -43259,15 +43259,15 @@
       </c>
       <c r="J16" s="33" t="str">
         <f>VLOOKUP(2,AD14:AN17,2,FALSE)</f>
-        <v>Canada</v>
+        <v>Switzerland</v>
       </c>
       <c r="K16" s="23">
         <f>L16+M16+N16</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L16" s="23">
         <f>VLOOKUP(2,AD14:AN17,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="23">
         <f>VLOOKUP(2,AD14:AN17,4,FALSE)</f>
@@ -43279,11 +43279,11 @@
       </c>
       <c r="O16" s="23" t="str">
         <f>VLOOKUP(2,AD14:AN17,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD14:AN17,7,FALSE)</f>
-        <v>1 - 1</v>
+        <v>5 - 2</v>
       </c>
       <c r="P16" s="34">
         <f>L16*3+M16</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R16" s="123">
         <f>DATE(2026,6,14)+TIME(6,0,0)+gmt_delta</f>
@@ -43331,7 +43331,7 @@
       </c>
       <c r="AD16" s="123">
         <f>COUNTIF(AR14:AR17,CONCATENATE("&gt;=",AR16))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE16" s="124" t="str">
         <f>VLOOKUP("Qatar",T,lang,FALSE)</f>
@@ -43347,7 +43347,7 @@
       </c>
       <c r="AH16" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE16 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI16" s="123">
         <f>SUMIF($E$7:$E$78,$AE16,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE16,$G$7:$G$78)</f>
@@ -43355,11 +43355,11 @@
       </c>
       <c r="AJ16" s="123">
         <f>SUMIF($E$7:$E$78,$AE16,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE16,$F$7:$F$78)</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AL16" s="123">
         <f>AI16-AJ16</f>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AM16" s="123">
         <f>AL16-AL18</f>
@@ -43371,11 +43371,11 @@
       </c>
       <c r="AO16" s="123">
         <f>AN16/AN18*10+BA16</f>
-        <v>5.9901960784313726</v>
+        <v>2</v>
       </c>
       <c r="AP16" s="123">
         <f>AO16*10000000+BI16*100+AM16/AM18*10+AI16/AI18*1++IF(AQ16=0,ROW(),AQ16)/2000000</f>
-        <v>59902060.304649048</v>
+        <v>20000000.125727478</v>
       </c>
       <c r="AQ16" s="126">
         <f>VLOOKUP(AE16,db_fifarank,2,FALSE)</f>
@@ -43383,7 +43383,7 @@
       </c>
       <c r="AR16" s="125">
         <f>AP16/AP18</f>
-        <v>0.99999998330446072</v>
+        <v>0.24999996686363724</v>
       </c>
       <c r="AT16" s="126" cm="1">
         <f t="array" ref="AT16">SUMPRODUCT(($S$7:$S$78=AE16&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE16&amp;"_win")*($U$7:$U$78))</f>
@@ -43391,15 +43391,15 @@
       </c>
       <c r="AU16" s="126" cm="1">
         <f t="array" ref="AU16">SUMPRODUCT(($S$7:$S$78=AE16&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE16&amp;"_draw")*($U$7:$U$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV16" s="126" cm="1">
         <f t="array" ref="AV16">SUMPRODUCT(($E$7:$E$78=AE16)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE16)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW16" s="126" cm="1">
         <f t="array" ref="AW16">SUMPRODUCT(($E$7:$E$78=AE16)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE16)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX16" s="126">
         <f>AV16-AW16</f>
@@ -43411,11 +43411,11 @@
       </c>
       <c r="AZ16" s="126">
         <f>AT16/AT18*1000+AU16/AU18*100+AY16/AY18*10+AV16/AV18</f>
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="BA16" s="126">
         <f>AZ16/AZ18</f>
-        <v>0.99019607843137258</v>
+        <v>0</v>
       </c>
       <c r="BB16" s="126" cm="1">
         <f t="array" ref="BB16">SUMPRODUCT(($S$7:$S$78=AE16&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE16&amp;"_win")*($X$7:$X$78))</f>
@@ -43423,15 +43423,15 @@
       </c>
       <c r="BC16" s="126" cm="1">
         <f t="array" ref="BC16">SUMPRODUCT(($S$7:$S$78=AE16&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE16&amp;"_draw")*($X$7:$X$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD16" s="126" cm="1">
         <f t="array" ref="BD16">SUMPRODUCT(($E$7:$E$78=AE16)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE16)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE16" s="126" cm="1">
         <f t="array" ref="BE16">SUMPRODUCT(($E$7:$E$78=AE16)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE16)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF16" s="126">
         <f>BD16-BE16</f>
@@ -43443,11 +43443,11 @@
       </c>
       <c r="BH16" s="126">
         <f>BB16/BB18*1000+BC16/BC18*100+BG16/BG18*10+BD16/BD18</f>
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="BI16" s="126">
         <f>BH16/BH18</f>
-        <v>0.99019607843137258</v>
+        <v>0</v>
       </c>
       <c r="BK16" s="21"/>
       <c r="BL16" s="21"/>
@@ -43463,7 +43463,7 @@
       <c r="BV16" s="21"/>
       <c r="BW16" s="114"/>
       <c r="BX16" s="112"/>
-      <c r="BY16" s="173">
+      <c r="BY16" s="163">
         <v>97</v>
       </c>
       <c r="BZ16" s="24" t="str">
@@ -43515,11 +43515,11 @@
       </c>
       <c r="J17" s="33" t="str">
         <f>VLOOKUP(3,AD14:AN17,2,FALSE)</f>
-        <v>Qatar</v>
+        <v>Bosnia and Herzegovina</v>
       </c>
       <c r="K17" s="23">
         <f>L17+M17+N17</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L17" s="23">
         <f>VLOOKUP(3,AD14:AN17,3,FALSE)</f>
@@ -43531,11 +43531,11 @@
       </c>
       <c r="N17" s="23">
         <f>VLOOKUP(3,AD14:AN17,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" s="23" t="str">
         <f>VLOOKUP(3,AD14:AN17,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD14:AN17,7,FALSE)</f>
-        <v>1 - 1</v>
+        <v>2 - 5</v>
       </c>
       <c r="P17" s="34">
         <f>L17*3+M17</f>
@@ -43587,7 +43587,7 @@
       </c>
       <c r="AD17" s="123">
         <f>COUNTIF(AR14:AR17,CONCATENATE("&gt;=",AR17))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE17" s="124" t="str">
         <f>VLOOKUP("Switzerland",T,lang,FALSE)</f>
@@ -43595,7 +43595,7 @@
       </c>
       <c r="AF17" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE17 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG17" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE17 &amp; "_draw")</f>
@@ -43607,31 +43607,31 @@
       </c>
       <c r="AI17" s="123">
         <f>SUMIF($E$7:$E$78,$AE17,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE17,$G$7:$G$78)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AJ17" s="123">
         <f>SUMIF($E$7:$E$78,$AE17,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE17,$F$7:$F$78)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL17" s="123">
         <f>AI17-AJ17</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AM17" s="123">
         <f>AL17-AL18</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AN17" s="123">
         <f>AF17*3+AG17</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AO17" s="123">
         <f>AN17/AN18*10+BA17</f>
-        <v>5.9901960784313726</v>
+        <v>8</v>
       </c>
       <c r="AP17" s="123">
         <f>AO17*10000000+BI17*100+AM17/AM18*10+AI17/AI18*1++IF(AQ17=0,ROW(),AQ17)/2000000</f>
-        <v>59902060.304746263</v>
+        <v>80000007.548901632</v>
       </c>
       <c r="AQ17" s="126">
         <f>VLOOKUP(AE17,db_fifarank,2,FALSE)</f>
@@ -43639,7 +43639,7 @@
       </c>
       <c r="AR17" s="125">
         <f>AP17/AP18</f>
-        <v>0.99999998330608364</v>
+        <v>0.9999999555294331</v>
       </c>
       <c r="AT17" s="126" cm="1">
         <f t="array" ref="AT17">SUMPRODUCT(($S$7:$S$78=AE17&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE17&amp;"_win")*($U$7:$U$78))</f>
@@ -43647,15 +43647,15 @@
       </c>
       <c r="AU17" s="126" cm="1">
         <f t="array" ref="AU17">SUMPRODUCT(($S$7:$S$78=AE17&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE17&amp;"_draw")*($U$7:$U$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV17" s="126" cm="1">
         <f t="array" ref="AV17">SUMPRODUCT(($E$7:$E$78=AE17)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE17)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW17" s="126" cm="1">
         <f t="array" ref="AW17">SUMPRODUCT(($E$7:$E$78=AE17)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE17)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX17" s="126">
         <f>AV17-AW17</f>
@@ -43667,11 +43667,11 @@
       </c>
       <c r="AZ17" s="126">
         <f>AT17/AT18*1000+AU17/AU18*100+AY17/AY18*10+AV17/AV18</f>
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="BA17" s="126">
         <f>AZ17/AZ18</f>
-        <v>0.99019607843137258</v>
+        <v>0</v>
       </c>
       <c r="BB17" s="126" cm="1">
         <f t="array" ref="BB17">SUMPRODUCT(($S$7:$S$78=AE17&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE17&amp;"_win")*($X$7:$X$78))</f>
@@ -43679,15 +43679,15 @@
       </c>
       <c r="BC17" s="126" cm="1">
         <f t="array" ref="BC17">SUMPRODUCT(($S$7:$S$78=AE17&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE17&amp;"_draw")*($X$7:$X$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD17" s="126" cm="1">
         <f t="array" ref="BD17">SUMPRODUCT(($E$7:$E$78=AE17)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE17)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE17" s="126" cm="1">
         <f t="array" ref="BE17">SUMPRODUCT(($E$7:$E$78=AE17)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE17)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF17" s="126">
         <f>BD17-BE17</f>
@@ -43699,11 +43699,11 @@
       </c>
       <c r="BH17" s="126">
         <f>BB17/BB18*1000+BC17/BC18*100+BG17/BG18*10+BD17/BD18</f>
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="BI17" s="126">
         <f>BH17/BH18</f>
-        <v>0.99019607843137258</v>
+        <v>0</v>
       </c>
       <c r="BK17" s="21" t="str" cm="1">
         <f t="array" ref="BK17">INDEX(T,24+MONTH(BP17),lang) &amp; " " &amp; DAY(BP17) &amp; ", " &amp; YEAR(BP17) &amp; "   " &amp; (IF(HOUR(BP17)&lt;10,0,"")&amp;HOUR(BP17)) &amp; ":" &amp;  (IF(MINUTE(BP17)&lt;10,0,"")&amp;MINUTE(BP17))</f>
@@ -43725,7 +43725,7 @@
       <c r="BV17" s="21"/>
       <c r="BW17" s="114"/>
       <c r="BX17" s="115"/>
-      <c r="BY17" s="174"/>
+      <c r="BY17" s="164"/>
       <c r="BZ17" s="26" t="str">
         <f>IF(BW20&gt;BW21,BS20,IF(BW20&lt;BW21,BS21,""))</f>
         <v/>
@@ -43775,11 +43775,11 @@
       </c>
       <c r="J18" s="35" t="str">
         <f>VLOOKUP(4,AD14:AN17,2,FALSE)</f>
-        <v>Bosnia and Herzegovina</v>
+        <v>Qatar</v>
       </c>
       <c r="K18" s="36">
         <f>L18+M18+N18</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L18" s="36">
         <f>VLOOKUP(4,AD14:AN17,3,FALSE)</f>
@@ -43791,11 +43791,11 @@
       </c>
       <c r="N18" s="36">
         <f>VLOOKUP(4,AD14:AN17,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" s="36" t="str">
         <f>VLOOKUP(4,AD14:AN17,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD14:AN17,7,FALSE)</f>
-        <v>1 - 1</v>
+        <v>1 - 7</v>
       </c>
       <c r="P18" s="37">
         <f>L18*3+M18</f>
@@ -43847,7 +43847,7 @@
       </c>
       <c r="AF18" s="123">
         <f t="shared" ref="AF18:AH18" si="13">MAX(AF14:AF17)-MIN(AF14:AF17)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG18" s="123">
         <f t="shared" si="13"/>
@@ -43855,31 +43855,31 @@
       </c>
       <c r="AH18" s="123">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI18" s="123">
         <f>MAX(AI14:AI17)+1</f>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AL18" s="123">
         <f>MIN(AL14:AL17)</f>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AM18" s="123">
         <f>MAX(AM14:AM17)+1</f>
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="AN18" s="123">
         <f>MAX(AN14:AN17)+1</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AO18" s="123">
         <f>MAX(AO14:AO17)+1</f>
-        <v>6.9901960784313726</v>
+        <v>9</v>
       </c>
       <c r="AP18" s="123">
         <f>MAX(AP14:AP17)+1</f>
-        <v>59902061.304746263</v>
+        <v>80000011.106547475</v>
       </c>
       <c r="AT18" s="126">
         <f>MAX(AT14:AT17)-MIN(AT14:AT17)+1</f>
@@ -43903,7 +43903,7 @@
       </c>
       <c r="AZ18" s="126">
         <f>MAX(AZ14:AZ17)+1</f>
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="BB18" s="126">
         <f>MAX(BB14:BB17)-MIN(BB14:BB17)+1</f>
@@ -43927,9 +43927,9 @@
       </c>
       <c r="BH18" s="126">
         <f>MAX(BH14:BH17)+1</f>
-        <v>102</v>
-      </c>
-      <c r="BK18" s="173">
+        <v>1</v>
+      </c>
+      <c r="BK18" s="163">
         <v>73</v>
       </c>
       <c r="BL18" s="24" t="str">
@@ -44007,27 +44007,27 @@
       </c>
       <c r="U19" s="123">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="123">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W19" s="123">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X19" s="123">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y19" s="123">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z19" s="123">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA19" s="123">
         <f t="shared" si="5"/>
@@ -44037,7 +44037,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BK19" s="174"/>
+      <c r="BK19" s="164"/>
       <c r="BL19" s="26" t="str">
         <f>AS15</f>
         <v>2B</v>
@@ -44154,7 +44154,7 @@
       </c>
       <c r="U20" s="123">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="123">
         <f t="shared" si="3"/>
@@ -44166,7 +44166,7 @@
       </c>
       <c r="X20" s="123">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y20" s="123">
         <f t="shared" si="10"/>
@@ -44186,7 +44186,7 @@
       </c>
       <c r="AD20" s="123">
         <f>COUNTIF(AR20:AR23,CONCATENATE("&gt;=",AR20))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE20" s="124" t="str">
         <f>VLOOKUP("Brazil",T,lang,FALSE)</f>
@@ -44194,7 +44194,7 @@
       </c>
       <c r="AF20" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE20 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG20" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE20 &amp; "_draw")</f>
@@ -44206,7 +44206,7 @@
       </c>
       <c r="AI20" s="123">
         <f>SUMIF($E$7:$E$78,$AE20,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE20,$G$7:$G$78)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AJ20" s="123">
         <f>SUMIF($E$7:$E$78,$AE20,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE20,$F$7:$F$78)</f>
@@ -44214,23 +44214,23 @@
       </c>
       <c r="AL20" s="123">
         <f>AI20-AJ20</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AM20" s="123">
         <f>AL20-AL24</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AN20" s="123">
         <f>AF20*3+AG20</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AO20" s="123">
         <f>AN20/AN24*10+BA20</f>
-        <v>3.4805825242718447</v>
+        <v>8.9805825242718456</v>
       </c>
       <c r="AP20" s="123">
         <f>AO20*10000000+BI20*100+AM20/AM24*10+AI20/AI24*1++IF(AQ20=0,ROW(),AQ20)/2000000</f>
-        <v>34805927.13518478</v>
+        <v>89805932.851851463</v>
       </c>
       <c r="AQ20" s="126">
         <f>VLOOKUP(AE20,db_fifarank,2,FALSE)</f>
@@ -44238,7 +44238,7 @@
       </c>
       <c r="AR20" s="125">
         <f>AP20/AP24</f>
-        <v>0.46407897793145042</v>
+        <v>0.99999998886487829</v>
       </c>
       <c r="AS20" s="125" t="str">
         <f>IF(SUM(AF20:AH23)=12,J21,"1C")</f>
@@ -44315,7 +44315,7 @@
       <c r="BO20" s="21"/>
       <c r="BP20" s="114"/>
       <c r="BQ20" s="112"/>
-      <c r="BR20" s="173">
+      <c r="BR20" s="163">
         <v>90</v>
       </c>
       <c r="BS20" s="24" t="str">
@@ -44381,11 +44381,11 @@
       </c>
       <c r="J21" s="30" t="str">
         <f>VLOOKUP(1,AD20:AN23,2,FALSE)</f>
-        <v>Scotland</v>
+        <v>Brazil</v>
       </c>
       <c r="K21" s="31">
         <f>L21+M21+N21</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L21" s="31">
         <f>VLOOKUP(1,AD20:AN23,3,FALSE)</f>
@@ -44393,7 +44393,7 @@
       </c>
       <c r="M21" s="31">
         <f>VLOOKUP(1,AD20:AN23,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21" s="31">
         <f>VLOOKUP(1,AD20:AN23,5,FALSE)</f>
@@ -44401,11 +44401,11 @@
       </c>
       <c r="O21" s="31" t="str">
         <f>VLOOKUP(1,AD20:AN23,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD20:AN23,7,FALSE)</f>
-        <v>1 - 0</v>
+        <v>4 - 1</v>
       </c>
       <c r="P21" s="32">
         <f>L21*3+M21</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R21" s="123">
         <f>DATE(2026,6,15)+TIME(14,0,0)+gmt_delta</f>
@@ -44421,27 +44421,27 @@
       </c>
       <c r="U21" s="123">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="123">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W21" s="123">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X21" s="123">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y21" s="123">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z21" s="123">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA21" s="123">
         <f t="shared" si="5"/>
@@ -44453,7 +44453,7 @@
       </c>
       <c r="AD21" s="123">
         <f>COUNTIF(AR20:AR23,CONCATENATE("&gt;=",AR21))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE21" s="124" t="str">
         <f>VLOOKUP("Morocco",T,lang,FALSE)</f>
@@ -44461,7 +44461,7 @@
       </c>
       <c r="AF21" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE21 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG21" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE21 &amp; "_draw")</f>
@@ -44473,7 +44473,7 @@
       </c>
       <c r="AI21" s="123">
         <f>SUMIF($E$7:$E$78,$AE21,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE21,$G$7:$G$78)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ21" s="123">
         <f>SUMIF($E$7:$E$78,$AE21,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE21,$F$7:$F$78)</f>
@@ -44481,23 +44481,23 @@
       </c>
       <c r="AL21" s="123">
         <f>AI21-AJ21</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM21" s="123">
         <f>AL21-AL24</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AN21" s="123">
         <f>AF21*3+AG21</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AO21" s="123">
         <f>AN21/AN24*10+BA21</f>
-        <v>3.4805825242718447</v>
+        <v>8.9805825242718456</v>
       </c>
       <c r="AP21" s="123">
         <f>AO21*10000000+BI21*100+AM21/AM24*10+AI21/AI24*1++IF(AQ21=0,ROW(),AQ21)/2000000</f>
-        <v>34805927.135182135</v>
+        <v>89805929.95184882</v>
       </c>
       <c r="AQ21" s="126">
         <f>VLOOKUP(AE21,db_fifarank,2,FALSE)</f>
@@ -44505,7 +44505,7 @@
       </c>
       <c r="AR21" s="125">
         <f>AP21/AP24</f>
-        <v>0.46407897793141517</v>
+        <v>0.99999995657299601</v>
       </c>
       <c r="AS21" s="125" t="str">
         <f>IF(SUM(AF20:AH23)=12,J22,"2C")</f>
@@ -44588,7 +44588,7 @@
         <v>46203.041666666672</v>
       </c>
       <c r="BQ21" s="115"/>
-      <c r="BR21" s="174"/>
+      <c r="BR21" s="164"/>
       <c r="BS21" s="26" t="str">
         <f>IF(BP22&gt;BP23,BL22,IF(BP22&lt;BP23,BL23,""))</f>
         <v/>
@@ -44652,15 +44652,15 @@
       </c>
       <c r="J22" s="33" t="str">
         <f>VLOOKUP(2,AD20:AN23,2,FALSE)</f>
-        <v>Brazil</v>
+        <v>Morocco</v>
       </c>
       <c r="K22" s="23">
         <f>L22+M22+N22</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L22" s="23">
         <f>VLOOKUP(2,AD20:AN23,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="23">
         <f>VLOOKUP(2,AD20:AN23,4,FALSE)</f>
@@ -44672,11 +44672,11 @@
       </c>
       <c r="O22" s="23" t="str">
         <f>VLOOKUP(2,AD20:AN23,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD20:AN23,7,FALSE)</f>
-        <v>1 - 1</v>
+        <v>2 - 1</v>
       </c>
       <c r="P22" s="34">
         <f>L22*3+M22</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R22" s="123">
         <f>DATE(2026,6,15)+TIME(8,0,0)+gmt_delta</f>
@@ -44692,27 +44692,27 @@
       </c>
       <c r="U22" s="123">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="123">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W22" s="123">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X22" s="123">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y22" s="123">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z22" s="123">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA22" s="123">
         <f t="shared" si="5"/>
@@ -44740,7 +44740,7 @@
       </c>
       <c r="AH22" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE22 &amp; "_lose")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI22" s="123">
         <f>SUMIF($E$7:$E$78,$AE22,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE22,$G$7:$G$78)</f>
@@ -44748,11 +44748,11 @@
       </c>
       <c r="AJ22" s="123">
         <f>SUMIF($E$7:$E$78,$AE22,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE22,$F$7:$F$78)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AL22" s="123">
         <f>AI22-AJ22</f>
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="AM22" s="123">
         <f>AL22-AL24</f>
@@ -44776,7 +44776,7 @@
       </c>
       <c r="AR22" s="125">
         <f>AP22/AP24</f>
-        <v>8.6113990622283044E-12</v>
+        <v>7.1916740052548863E-12</v>
       </c>
       <c r="AT22" s="126" cm="1">
         <f t="array" ref="AT22">SUMPRODUCT(($S$7:$S$78=AE22&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE22&amp;"_win")*($U$7:$U$78))</f>
@@ -44842,7 +44842,7 @@
         <f>BH22/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK22" s="173">
+      <c r="BK22" s="163">
         <v>75</v>
       </c>
       <c r="BL22" s="24" t="str">
@@ -44916,23 +44916,23 @@
       </c>
       <c r="J23" s="33" t="str">
         <f>VLOOKUP(3,AD20:AN23,2,FALSE)</f>
-        <v>Morocco</v>
+        <v>Scotland</v>
       </c>
       <c r="K23" s="23">
         <f>L23+M23+N23</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L23" s="23">
         <f>VLOOKUP(3,AD20:AN23,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" s="23">
         <f>VLOOKUP(3,AD20:AN23,4,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" s="23">
         <f>VLOOKUP(3,AD20:AN23,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23" s="23" t="str">
         <f>VLOOKUP(3,AD20:AN23,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD20:AN23,7,FALSE)</f>
@@ -44940,7 +44940,7 @@
       </c>
       <c r="P23" s="34">
         <f>L23*3+M23</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R23" s="123">
         <f>DATE(2026,6,16)+TIME(8,0,0)+gmt_delta</f>
@@ -44988,7 +44988,7 @@
       </c>
       <c r="AD23" s="123">
         <f>COUNTIF(AR20:AR23,CONCATENATE("&gt;=",AR23))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE23" s="124" t="str">
         <f>VLOOKUP("Scotland",T,lang,FALSE)</f>
@@ -45004,7 +45004,7 @@
       </c>
       <c r="AH23" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE23 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI23" s="123">
         <f>SUMIF($E$7:$E$78,$AE23,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE23,$G$7:$G$78)</f>
@@ -45012,15 +45012,15 @@
       </c>
       <c r="AJ23" s="123">
         <f>SUMIF($E$7:$E$78,$AE23,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE23,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL23" s="123">
         <f>AI23-AJ23</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM23" s="123">
         <f>AL23-AL24</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AN23" s="123">
         <f>AF23*3+AG23</f>
@@ -45028,11 +45028,11 @@
       </c>
       <c r="AO23" s="123">
         <f>AN23/AN24*10+BA23</f>
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="AP23" s="123">
         <f>AO23*10000000+BI23*100+AM23/AM24*10+AI23/AI24*1++IF(AQ23=0,ROW(),AQ23)/2000000</f>
-        <v>75000007.167415842</v>
+        <v>60000005.200749181</v>
       </c>
       <c r="AQ23" s="126">
         <f>VLOOKUP(AE23,db_fifarank,2,FALSE)</f>
@@ -45040,7 +45040,7 @@
       </c>
       <c r="AR23" s="125">
         <f>AP23/AP24</f>
-        <v>0.99999998666666812</v>
+        <v>0.66810735802523147</v>
       </c>
       <c r="AT23" s="126" cm="1">
         <f t="array" ref="AT23">SUMPRODUCT(($S$7:$S$78=AE23&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE23&amp;"_win")*($U$7:$U$78))</f>
@@ -45106,7 +45106,7 @@
         <f>BH23/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK23" s="174"/>
+      <c r="BK23" s="164"/>
       <c r="BL23" s="26" t="str">
         <f>AS21</f>
         <v>2C</v>
@@ -45133,7 +45133,7 @@
       <c r="CC23" s="21"/>
       <c r="CD23" s="114"/>
       <c r="CE23" s="112"/>
-      <c r="CF23" s="173">
+      <c r="CF23" s="163">
         <v>101</v>
       </c>
       <c r="CG23" s="24" t="str">
@@ -45184,7 +45184,7 @@
       </c>
       <c r="K24" s="36">
         <f>L24+M24+N24</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L24" s="36">
         <f>VLOOKUP(4,AD20:AN23,3,FALSE)</f>
@@ -45196,11 +45196,11 @@
       </c>
       <c r="N24" s="36">
         <f>VLOOKUP(4,AD20:AN23,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O24" s="36" t="str">
         <f>VLOOKUP(4,AD20:AN23,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD20:AN23,7,FALSE)</f>
-        <v>0 - 1</v>
+        <v>0 - 4</v>
       </c>
       <c r="P24" s="37">
         <f>L24*3+M24</f>
@@ -45260,31 +45260,31 @@
       </c>
       <c r="AH24" s="123">
         <f t="shared" si="14"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI24" s="123">
         <f>MAX(AI20:AI23)+1</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AL24" s="123">
         <f>MIN(AL20:AL23)</f>
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="AM24" s="123">
         <f>MAX(AM20:AM23)+1</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AN24" s="123">
         <f>MAX(AN20:AN23)+1</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO24" s="123">
         <f>MAX(AO20:AO23)+1</f>
-        <v>8.5</v>
+        <v>9.9805825242718456</v>
       </c>
       <c r="AP24" s="123">
         <f>MAX(AP20:AP23)+1</f>
-        <v>75000008.167415842</v>
+        <v>89805933.851851463</v>
       </c>
       <c r="AT24" s="126">
         <f>MAX(AT20:AT23)-MIN(AT20:AT23)+1</f>
@@ -45354,7 +45354,7 @@
       <c r="CC24" s="21"/>
       <c r="CD24" s="114"/>
       <c r="CE24" s="115"/>
-      <c r="CF24" s="174"/>
+      <c r="CF24" s="164"/>
       <c r="CG24" s="26" t="str">
         <f>IF(CD32&gt;CD33,BZ32,IF(CD32&lt;CD33,BZ33,""))</f>
         <v/>
@@ -45593,7 +45593,7 @@
       </c>
       <c r="AF26" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE26 &amp; "_win")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG26" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE26 &amp; "_draw")</f>
@@ -45605,7 +45605,7 @@
       </c>
       <c r="AI26" s="123">
         <f>SUMIF($E$7:$E$78,$AE26,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE26,$G$7:$G$78)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AJ26" s="123">
         <f>SUMIF($E$7:$E$78,$AE26,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE26,$F$7:$F$78)</f>
@@ -45613,23 +45613,23 @@
       </c>
       <c r="AL26" s="123">
         <f>AI26-AJ26</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AM26" s="123">
         <f>AL26-AL30</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AN26" s="123">
         <f>AF26*3+AG26</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AO26" s="123">
         <f>AN26/AN30*10+BA26</f>
-        <v>7.5</v>
+        <v>8.5714285714285712</v>
       </c>
       <c r="AP26" s="123">
         <f>AO26*10000000+BI26*100+AM26/AM30*10+AI26/AI30*1++IF(AQ26=0,ROW(),AQ26)/2000000</f>
-        <v>75000009.37226513</v>
+        <v>85714295.461154029</v>
       </c>
       <c r="AQ26" s="126">
         <f>VLOOKUP(AE26,db_fifarank,2,FALSE)</f>
@@ -45637,7 +45637,7 @@
       </c>
       <c r="AR26" s="125">
         <f>AP26/AP30</f>
-        <v>0.99999998666666856</v>
+        <v>0.99999998833333481</v>
       </c>
       <c r="AS26" s="125" t="str">
         <f>IF(SUM(AF26:AH29)=12,J27,"1D")</f>
@@ -45707,7 +45707,7 @@
         <f>BH26/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK26" s="173">
+      <c r="BK26" s="163">
         <v>83</v>
       </c>
       <c r="BL26" s="24" t="str">
@@ -45769,8 +45769,12 @@
         <f>AE76</f>
         <v>Ghana</v>
       </c>
-      <c r="F27" s="19"/>
-      <c r="G27" s="20"/>
+      <c r="F27" s="19">
+        <v>1</v>
+      </c>
+      <c r="G27" s="20">
+        <v>0</v>
+      </c>
       <c r="H27" s="80" t="str">
         <f>AE77</f>
         <v>Panama</v>
@@ -45781,11 +45785,11 @@
       </c>
       <c r="K27" s="31">
         <f>L27+M27+N27</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L27" s="31">
         <f>VLOOKUP(1,AD26:AN29,3,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M27" s="31">
         <f>VLOOKUP(1,AD26:AN29,4,FALSE)</f>
@@ -45797,11 +45801,11 @@
       </c>
       <c r="O27" s="31" t="str">
         <f>VLOOKUP(1,AD26:AN29,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD26:AN29,7,FALSE)</f>
-        <v>4 - 1</v>
+        <v>6 - 1</v>
       </c>
       <c r="P27" s="32">
         <f>L27*3+M27</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R27" s="123">
         <f>DATE(2026,6,17)+TIME(12,0,0)+gmt_delta</f>
@@ -45809,11 +45813,11 @@
       </c>
       <c r="S27" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Ghana_win</v>
       </c>
       <c r="T27" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Panama_lose</v>
       </c>
       <c r="U27" s="123">
         <f t="shared" si="8"/>
@@ -45843,13 +45847,13 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB27" s="123" t="str">
+      <c r="AB27" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD27" s="123">
         <f>COUNTIF(AR26:AR29,CONCATENATE("&gt;=",AR27))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE27" s="124" t="str">
         <f>VLOOKUP("Paraguay",T,lang,FALSE)</f>
@@ -45857,7 +45861,7 @@
       </c>
       <c r="AF27" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE27 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG27" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE27 &amp; "_draw")</f>
@@ -45869,7 +45873,7 @@
       </c>
       <c r="AI27" s="123">
         <f>SUMIF($E$7:$E$78,$AE27,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE27,$G$7:$G$78)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ27" s="123">
         <f>SUMIF($E$7:$E$78,$AE27,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE27,$F$7:$F$78)</f>
@@ -45877,23 +45881,23 @@
       </c>
       <c r="AL27" s="123">
         <f>AI27-AJ27</f>
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="AM27" s="123">
         <f>AL27-AL30</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN27" s="123">
         <f>AF27*3+AG27</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO27" s="123">
         <f>AN27/AN30*10+BA27</f>
-        <v>0</v>
+        <v>4.2857142857142856</v>
       </c>
       <c r="AP27" s="123">
         <f>AO27*10000000+BI27*100+AM27/AM30*10+AI27/AI30*1++IF(AQ27=0,ROW(),AQ27)/2000000</f>
-        <v>0.20075175000000001</v>
+        <v>42857144.254720002</v>
       </c>
       <c r="AQ27" s="126">
         <f>VLOOKUP(AE27,db_fifarank,2,FALSE)</f>
@@ -45901,7 +45905,7 @@
       </c>
       <c r="AR27" s="125">
         <f>AP27/AP30</f>
-        <v>2.6766896298222066E-9</v>
+        <v>0.49999995361500732</v>
       </c>
       <c r="AS27" s="125" t="str">
         <f>IF(SUM(AF26:AH29)=12,J28,"2D")</f>
@@ -45971,7 +45975,7 @@
         <f>BH27/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK27" s="174"/>
+      <c r="BK27" s="164"/>
       <c r="BL27" s="26" t="str">
         <f>AS75</f>
         <v>2L</v>
@@ -46037,8 +46041,12 @@
         <f>AE74</f>
         <v>England</v>
       </c>
-      <c r="F28" s="19"/>
-      <c r="G28" s="20"/>
+      <c r="F28" s="19">
+        <v>4</v>
+      </c>
+      <c r="G28" s="20">
+        <v>2</v>
+      </c>
       <c r="H28" s="80" t="str">
         <f>AE75</f>
         <v>Croatia</v>
@@ -46049,7 +46057,7 @@
       </c>
       <c r="K28" s="23">
         <f>L28+M28+N28</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L28" s="23">
         <f>VLOOKUP(2,AD26:AN29,3,FALSE)</f>
@@ -46061,11 +46069,11 @@
       </c>
       <c r="N28" s="23">
         <f>VLOOKUP(2,AD26:AN29,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O28" s="23" t="str">
         <f>VLOOKUP(2,AD26:AN29,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD26:AN29,7,FALSE)</f>
-        <v>2 - 0</v>
+        <v>2 - 2</v>
       </c>
       <c r="P28" s="34">
         <f>L28*3+M28</f>
@@ -46077,11 +46085,11 @@
       </c>
       <c r="S28" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>England_win</v>
       </c>
       <c r="T28" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Croatia_lose</v>
       </c>
       <c r="U28" s="123">
         <f t="shared" si="8"/>
@@ -46111,9 +46119,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB28" s="123" t="str">
+      <c r="AB28" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD28" s="123">
         <f>COUNTIF(AR26:AR29,CONCATENATE("&gt;=",AR28))</f>
@@ -46133,7 +46141,7 @@
       </c>
       <c r="AH28" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE28 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI28" s="123">
         <f>SUMIF($E$7:$E$78,$AE28,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE28,$G$7:$G$78)</f>
@@ -46141,15 +46149,15 @@
       </c>
       <c r="AJ28" s="123">
         <f>SUMIF($E$7:$E$78,$AE28,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE28,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL28" s="123">
         <f>AI28-AJ28</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM28" s="123">
         <f>AL28-AL30</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AN28" s="123">
         <f>AF28*3+AG28</f>
@@ -46157,11 +46165,11 @@
       </c>
       <c r="AO28" s="123">
         <f>AN28/AN30*10+BA28</f>
-        <v>7.5</v>
+        <v>4.2857142857142856</v>
       </c>
       <c r="AP28" s="123">
         <f>AO28*10000000+BI28*100+AM28/AM30*10+AI28/AI30*1++IF(AQ28=0,ROW(),AQ28)/2000000</f>
-        <v>75000007.543647483</v>
+        <v>42857146.476980813</v>
       </c>
       <c r="AQ28" s="126">
         <f>VLOOKUP(AE28,db_fifarank,2,FALSE)</f>
@@ -46169,7 +46177,7 @@
       </c>
       <c r="AR28" s="125">
         <f>AP28/AP30</f>
-        <v>0.99999996228510324</v>
+        <v>0.4999999795413802</v>
       </c>
       <c r="AT28" s="126" cm="1">
         <f t="array" ref="AT28">SUMPRODUCT(($S$7:$S$78=AE28&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE28&amp;"_win")*($U$7:$U$78))</f>
@@ -46242,7 +46250,7 @@
       <c r="BO28" s="21"/>
       <c r="BP28" s="114"/>
       <c r="BQ28" s="112"/>
-      <c r="BR28" s="173">
+      <c r="BR28" s="163">
         <v>93</v>
       </c>
       <c r="BS28" s="24" t="str">
@@ -46304,15 +46312,15 @@
       </c>
       <c r="J29" s="33" t="str">
         <f>VLOOKUP(3,AD26:AN29,2,FALSE)</f>
-        <v>Turkey</v>
+        <v>Paraguay</v>
       </c>
       <c r="K29" s="23">
         <f>L29+M29+N29</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L29" s="23">
         <f>VLOOKUP(3,AD26:AN29,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" s="23">
         <f>VLOOKUP(3,AD26:AN29,4,FALSE)</f>
@@ -46324,11 +46332,11 @@
       </c>
       <c r="O29" s="23" t="str">
         <f>VLOOKUP(3,AD26:AN29,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD26:AN29,7,FALSE)</f>
-        <v>0 - 2</v>
+        <v>2 - 4</v>
       </c>
       <c r="P29" s="34">
         <f>L29*3+M29</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R29" s="123">
         <f>DATE(2026,6,17)+TIME(6,0,0)+gmt_delta</f>
@@ -46376,7 +46384,7 @@
       </c>
       <c r="AD29" s="123">
         <f>COUNTIF(AR26:AR29,CONCATENATE("&gt;=",AR29))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE29" s="124" t="str">
         <f>VLOOKUP("Turkey",T,lang,FALSE)</f>
@@ -46392,7 +46400,7 @@
       </c>
       <c r="AH29" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE29 &amp; "_lose")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI29" s="123">
         <f>SUMIF($E$7:$E$78,$AE29,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE29,$G$7:$G$78)</f>
@@ -46400,15 +46408,15 @@
       </c>
       <c r="AJ29" s="123">
         <f>SUMIF($E$7:$E$78,$AE29,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE29,$F$7:$F$78)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL29" s="123">
         <f>AI29-AJ29</f>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AM29" s="123">
         <f>AL29-AL30</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN29" s="123">
         <f>AF29*3+AG29</f>
@@ -46420,7 +46428,7 @@
       </c>
       <c r="AP29" s="123">
         <f>AO29*10000000+BI29*100+AM29/AM30*10+AI29/AI30*1++IF(AQ29=0,ROW(),AQ29)/2000000</f>
-        <v>1.4293709485714283</v>
+        <v>7.9951999999999996E-4</v>
       </c>
       <c r="AQ29" s="126">
         <f>VLOOKUP(AE29,db_fifarank,2,FALSE)</f>
@@ -46428,7 +46436,7 @@
       </c>
       <c r="AR29" s="125">
         <f>AP29/AP30</f>
-        <v>1.9058276678585728E-8</v>
+        <v>9.3277321638210582E-12</v>
       </c>
       <c r="AT29" s="126" cm="1">
         <f t="array" ref="AT29">SUMPRODUCT(($S$7:$S$78=AE29&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE29&amp;"_win")*($U$7:$U$78))</f>
@@ -46507,7 +46515,7 @@
         <v>46205.791666666672</v>
       </c>
       <c r="BQ29" s="115"/>
-      <c r="BR29" s="174"/>
+      <c r="BR29" s="164"/>
       <c r="BS29" s="26" t="str">
         <f>IF(BP30&gt;BP31,BL30,IF(BP30&lt;BP31,BL31,""))</f>
         <v/>
@@ -46555,19 +46563,23 @@
         <f>AE70</f>
         <v>Uzbekistan</v>
       </c>
-      <c r="F30" s="19"/>
-      <c r="G30" s="20"/>
+      <c r="F30" s="19">
+        <v>1</v>
+      </c>
+      <c r="G30" s="20">
+        <v>3</v>
+      </c>
       <c r="H30" s="80" t="str">
         <f>AE71</f>
         <v>Colombia</v>
       </c>
       <c r="J30" s="35" t="str">
         <f>VLOOKUP(4,AD26:AN29,2,FALSE)</f>
-        <v>Paraguay</v>
+        <v>Turkey</v>
       </c>
       <c r="K30" s="36">
         <f>L30+M30+N30</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L30" s="36">
         <f>VLOOKUP(4,AD26:AN29,3,FALSE)</f>
@@ -46579,11 +46591,11 @@
       </c>
       <c r="N30" s="36">
         <f>VLOOKUP(4,AD26:AN29,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O30" s="36" t="str">
         <f>VLOOKUP(4,AD26:AN29,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD26:AN29,7,FALSE)</f>
-        <v>1 - 4</v>
+        <v>0 - 3</v>
       </c>
       <c r="P30" s="37">
         <f>L30*3+M30</f>
@@ -46595,11 +46607,11 @@
       </c>
       <c r="S30" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Uzbekistan_lose</v>
       </c>
       <c r="T30" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Colombia_win</v>
       </c>
       <c r="U30" s="123">
         <f t="shared" si="8"/>
@@ -46629,13 +46641,13 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB30" s="123" t="str">
+      <c r="AB30" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>-1</v>
       </c>
       <c r="AF30" s="123">
         <f t="shared" ref="AF30:AH30" si="15">MAX(AF26:AF29)-MIN(AF26:AF29)+1</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG30" s="123">
         <f t="shared" si="15"/>
@@ -46643,11 +46655,11 @@
       </c>
       <c r="AH30" s="123">
         <f t="shared" si="15"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI30" s="123">
         <f>MAX(AI26:AI29)+1</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AL30" s="123">
         <f>MIN(AL26:AL29)</f>
@@ -46655,19 +46667,19 @@
       </c>
       <c r="AM30" s="123">
         <f>MAX(AM26:AM29)+1</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AN30" s="123">
         <f>MAX(AN26:AN29)+1</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AO30" s="123">
         <f>MAX(AO26:AO29)+1</f>
-        <v>8.5</v>
+        <v>9.5714285714285712</v>
       </c>
       <c r="AP30" s="123">
         <f>MAX(AP26:AP29)+1</f>
-        <v>75000010.37226513</v>
+        <v>85714296.461154029</v>
       </c>
       <c r="AT30" s="126">
         <f>MAX(AT26:AT29)-MIN(AT26:AT29)+1</f>
@@ -46717,7 +46729,7 @@
         <f>MAX(BH26:BH29)+1</f>
         <v>1</v>
       </c>
-      <c r="BK30" s="173">
+      <c r="BK30" s="163">
         <v>84</v>
       </c>
       <c r="BL30" s="24" t="str">
@@ -46774,8 +46786,12 @@
         <f>AE11</f>
         <v>Czech Republic</v>
       </c>
-      <c r="F31" s="19"/>
-      <c r="G31" s="20"/>
+      <c r="F31" s="19">
+        <v>1</v>
+      </c>
+      <c r="G31" s="20">
+        <v>1</v>
+      </c>
       <c r="H31" s="80" t="str">
         <f>AE9</f>
         <v>South Africa</v>
@@ -46786,45 +46802,45 @@
       </c>
       <c r="S31" s="127" t="str">
         <f>IF(OR(F31="",G31=""),"",IF(F31&gt;G31,E31&amp;"_win",IF(F31&lt;G31,E31&amp;"_lose",E31&amp;"_draw")))</f>
-        <v/>
+        <v>Czech Republic_draw</v>
       </c>
       <c r="T31" s="127" t="str">
         <f>IF(S31="","",IF(F31&lt;G31,H31&amp;"_win",IF(F31&gt;G31,H31&amp;"_lose",H31&amp;"_draw")))</f>
-        <v/>
+        <v>South Africa_draw</v>
       </c>
       <c r="U31" s="123">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V31" s="123">
         <f>U31*F31</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W31" s="123">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X31" s="123">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y31" s="123">
         <f>X31*F31</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z31" s="123">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA31" s="123">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB31" s="123" t="str">
+      <c r="AB31" s="123">
         <f>IF(OR(F31="",G31=""),"",IF(F31&gt;G31,1,IF(F31&lt;G31,-1,0)))</f>
-        <v/>
-      </c>
-      <c r="BK31" s="174"/>
+        <v>0</v>
+      </c>
+      <c r="BK31" s="164"/>
       <c r="BL31" s="26" t="str">
         <f>AS63</f>
         <v>2J</v>
@@ -46880,8 +46896,12 @@
         <f>AE17</f>
         <v>Switzerland</v>
       </c>
-      <c r="F32" s="19"/>
-      <c r="G32" s="20"/>
+      <c r="F32" s="19">
+        <v>4</v>
+      </c>
+      <c r="G32" s="20">
+        <v>1</v>
+      </c>
       <c r="H32" s="80" t="str">
         <f>AE15</f>
         <v>Bosnia and Herzegovina</v>
@@ -46920,11 +46940,11 @@
       </c>
       <c r="S32" s="127" t="str">
         <f>IF(OR(F32="",G32=""),"",IF(F32&gt;G32,E32&amp;"_win",IF(F32&lt;G32,E32&amp;"_lose",E32&amp;"_draw")))</f>
-        <v/>
+        <v>Switzerland_win</v>
       </c>
       <c r="T32" s="127" t="str">
         <f>IF(S32="","",IF(F32&lt;G32,H32&amp;"_win",IF(F32&gt;G32,H32&amp;"_lose",H32&amp;"_draw")))</f>
-        <v/>
+        <v>Bosnia and Herzegovina_lose</v>
       </c>
       <c r="U32" s="123">
         <f t="shared" si="8"/>
@@ -46954,9 +46974,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB32" s="123" t="str">
+      <c r="AB32" s="123">
         <f>IF(OR(F32="",G32=""),"",IF(F32&gt;G32,1,IF(F32&lt;G32,-1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD32" s="123">
         <f>COUNTIF(AR32:AR35,CONCATENATE("&gt;=",AR32))</f>
@@ -46968,7 +46988,7 @@
       </c>
       <c r="AF32" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE32 &amp; "_win")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG32" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE32 &amp; "_draw")</f>
@@ -46980,31 +47000,31 @@
       </c>
       <c r="AI32" s="123">
         <f>SUMIF($E$7:$E$78,$AE32,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE32,$G$7:$G$78)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AJ32" s="123">
         <f>SUMIF($E$7:$E$78,$AE32,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE32,$F$7:$F$78)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL32" s="123">
         <f>AI32-AJ32</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM32" s="123">
         <f>AL32-AL36</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN32" s="123">
         <f>AF32*3+AG32</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AO32" s="123">
         <f>AN32/AN36*10+BA32</f>
-        <v>7.5</v>
+        <v>8.5714285714285712</v>
       </c>
       <c r="AP32" s="123">
         <f>AO32*10000000+BI32*100+AM32/AM36*10+AI32/AI36*1++IF(AQ32=0,ROW(),AQ32)/2000000</f>
-        <v>75000010.106634423</v>
+        <v>85714295.900865197</v>
       </c>
       <c r="AQ32" s="126">
         <f>VLOOKUP(AE32,db_fifarank,2,FALSE)</f>
@@ -47012,7 +47032,7 @@
       </c>
       <c r="AR32" s="125">
         <f>AP32/AP36</f>
-        <v>0.99999998666666867</v>
+        <v>0.99999998833333481</v>
       </c>
       <c r="AS32" s="125" t="str">
         <f>IF(SUM(AF32:AH35)=12,J33,"1E")</f>
@@ -47096,7 +47116,7 @@
       <c r="BV32" s="21"/>
       <c r="BW32" s="114"/>
       <c r="BX32" s="112"/>
-      <c r="BY32" s="173">
+      <c r="BY32" s="163">
         <v>98</v>
       </c>
       <c r="BZ32" s="24" t="str">
@@ -47134,8 +47154,12 @@
         <f>AE14</f>
         <v>Canada</v>
       </c>
-      <c r="F33" s="19"/>
-      <c r="G33" s="20"/>
+      <c r="F33" s="19">
+        <v>6</v>
+      </c>
+      <c r="G33" s="20">
+        <v>0</v>
+      </c>
       <c r="H33" s="80" t="str">
         <f>AE16</f>
         <v>Qatar</v>
@@ -47146,11 +47170,11 @@
       </c>
       <c r="K33" s="31">
         <f>L33+M33+N33</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L33" s="31">
         <f>VLOOKUP(1,AD32:AN35,3,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M33" s="31">
         <f>VLOOKUP(1,AD32:AN35,4,FALSE)</f>
@@ -47162,11 +47186,11 @@
       </c>
       <c r="O33" s="31" t="str">
         <f>VLOOKUP(1,AD32:AN35,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD32:AN35,7,FALSE)</f>
-        <v>7 - 1</v>
+        <v>9 - 2</v>
       </c>
       <c r="P33" s="32">
         <f>L33*3+M33</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R33" s="123">
         <f>DATE(2026,6,18)+TIME(11,0,0)+gmt_delta</f>
@@ -47174,11 +47198,11 @@
       </c>
       <c r="S33" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Canada_win</v>
       </c>
       <c r="T33" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Qatar_lose</v>
       </c>
       <c r="U33" s="123">
         <f t="shared" si="8"/>
@@ -47208,9 +47232,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB33" s="123" t="str">
+      <c r="AB33" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD33" s="123">
         <f>COUNTIF(AR32:AR35,CONCATENATE("&gt;=",AR33))</f>
@@ -47226,7 +47250,7 @@
       </c>
       <c r="AG33" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE33 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH33" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE33 &amp; "_lose")</f>
@@ -47250,15 +47274,15 @@
       </c>
       <c r="AN33" s="123">
         <f>AF33*3+AG33</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO33" s="123">
         <f>AN33/AN36*10+BA33</f>
-        <v>0</v>
+        <v>2.4089635854341735</v>
       </c>
       <c r="AP33" s="123">
         <f>AO33*10000000+BI33*100+AM33/AM36*10+AI33/AI36*1++IF(AQ33=0,ROW(),AQ33)/2000000</f>
-        <v>0.125647325</v>
+        <v>24089733.994204748</v>
       </c>
       <c r="AQ33" s="126">
         <f>VLOOKUP(AE33,db_fifarank,2,FALSE)</f>
@@ -47266,7 +47290,7 @@
       </c>
       <c r="AR33" s="125">
         <f>AP33/AP36</f>
-        <v>1.6752974185744538E-9</v>
+        <v>0.28104685991960332</v>
       </c>
       <c r="AS33" s="125" t="str">
         <f>IF(SUM(AF32:AH35)=12,J34,"2E")</f>
@@ -47278,7 +47302,7 @@
       </c>
       <c r="AU33" s="126" cm="1">
         <f t="array" ref="AU33">SUMPRODUCT(($S$7:$S$78=AE33&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE33&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV33" s="126" cm="1">
         <f t="array" ref="AV33">SUMPRODUCT(($E$7:$E$78=AE33)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE33)*($U$7:$U$78)*($G$7:$G$78))</f>
@@ -47298,11 +47322,11 @@
       </c>
       <c r="AZ33" s="126">
         <f>AT33/AT36*1000+AU33/AU36*100+AY33/AY36*10+AV33/AV36</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BA33" s="126">
         <f>AZ33/AZ36</f>
-        <v>0</v>
+        <v>0.98039215686274506</v>
       </c>
       <c r="BB33" s="126" cm="1">
         <f t="array" ref="BB33">SUMPRODUCT(($S$7:$S$78=AE33&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE33&amp;"_win")*($X$7:$X$78))</f>
@@ -47310,7 +47334,7 @@
       </c>
       <c r="BC33" s="126" cm="1">
         <f t="array" ref="BC33">SUMPRODUCT(($S$7:$S$78=AE33&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE33&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD33" s="126" cm="1">
         <f t="array" ref="BD33">SUMPRODUCT(($E$7:$E$78=AE33)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE33)*($X$7:$X$78)*($G$7:$G$78))</f>
@@ -47330,11 +47354,11 @@
       </c>
       <c r="BH33" s="126">
         <f>BB33/BB36*1000+BC33/BC36*100+BG33/BG36*10+BD33/BD36</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BI33" s="126">
         <f>BH33/BH36</f>
-        <v>0</v>
+        <v>0.98039215686274506</v>
       </c>
       <c r="BK33" s="21" t="str" cm="1">
         <f t="array" ref="BK33">INDEX(T,24+MONTH(BP33),lang) &amp; " " &amp; DAY(BP33) &amp; ", " &amp; YEAR(BP33) &amp; "   " &amp; (IF(HOUR(BP33)&lt;10,0,"")&amp;HOUR(BP33)) &amp; ":" &amp;  (IF(MINUTE(BP33)&lt;10,0,"")&amp;MINUTE(BP33))</f>
@@ -47356,7 +47380,7 @@
       <c r="BV33" s="21"/>
       <c r="BW33" s="114"/>
       <c r="BX33" s="115"/>
-      <c r="BY33" s="174"/>
+      <c r="BY33" s="164"/>
       <c r="BZ33" s="26" t="str">
         <f>IF(BW36&gt;BW37,BS36,IF(BW36&lt;BW37,BS37,""))</f>
         <v/>
@@ -47371,14 +47395,14 @@
       <c r="CE33" s="112"/>
       <c r="CK33" s="114"/>
       <c r="CL33" s="112"/>
-      <c r="CM33" s="176" t="str" cm="1">
+      <c r="CM33" s="165" t="str" cm="1">
         <f t="array" ref="CM33">INDEX(T,8,lang)</f>
         <v>Final</v>
       </c>
-      <c r="CN33" s="177"/>
-      <c r="CO33" s="177"/>
-      <c r="CP33" s="177"/>
-      <c r="CQ33" s="178"/>
+      <c r="CN33" s="166"/>
+      <c r="CO33" s="166"/>
+      <c r="CP33" s="166"/>
+      <c r="CQ33" s="167"/>
     </row>
     <row r="34" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A34" s="16">
@@ -47400,8 +47424,12 @@
         <f>AE8</f>
         <v>Mexico</v>
       </c>
-      <c r="F34" s="19"/>
-      <c r="G34" s="20"/>
+      <c r="F34" s="19">
+        <v>1</v>
+      </c>
+      <c r="G34" s="20">
+        <v>0</v>
+      </c>
       <c r="H34" s="80" t="str">
         <f>AE10</f>
         <v>Korea Republic</v>
@@ -47412,7 +47440,7 @@
       </c>
       <c r="K34" s="23">
         <f>L34+M34+N34</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L34" s="23">
         <f>VLOOKUP(2,AD32:AN35,3,FALSE)</f>
@@ -47424,11 +47452,11 @@
       </c>
       <c r="N34" s="23">
         <f>VLOOKUP(2,AD32:AN35,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O34" s="23" t="str">
         <f>VLOOKUP(2,AD32:AN35,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD32:AN35,7,FALSE)</f>
-        <v>1 - 0</v>
+        <v>2 - 2</v>
       </c>
       <c r="P34" s="34">
         <f>L34*3+M34</f>
@@ -47440,11 +47468,11 @@
       </c>
       <c r="S34" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Mexico_win</v>
       </c>
       <c r="T34" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Korea Republic_lose</v>
       </c>
       <c r="U34" s="123">
         <f t="shared" si="8"/>
@@ -47474,9 +47502,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB34" s="123" t="str">
+      <c r="AB34" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD34" s="123">
         <f>COUNTIF(AR32:AR35,CONCATENATE("&gt;=",AR34))</f>
@@ -47496,23 +47524,23 @@
       </c>
       <c r="AH34" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE34 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI34" s="123">
         <f>SUMIF($E$7:$E$78,$AE34,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE34,$G$7:$G$78)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ34" s="123">
         <f>SUMIF($E$7:$E$78,$AE34,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE34,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL34" s="123">
         <f>AI34-AJ34</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM34" s="123">
         <f>AL34-AL36</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN34" s="123">
         <f>AF34*3+AG34</f>
@@ -47520,11 +47548,11 @@
       </c>
       <c r="AO34" s="123">
         <f>AN34/AN36*10+BA34</f>
-        <v>7.5</v>
+        <v>4.2857142857142856</v>
       </c>
       <c r="AP34" s="123">
         <f>AO34*10000000+BI34*100+AM34/AM36*10+AI34/AI36*1++IF(AQ34=0,ROW(),AQ34)/2000000</f>
-        <v>75000005.510381877</v>
+        <v>42857147.343623638</v>
       </c>
       <c r="AQ34" s="126">
         <f>VLOOKUP(AE34,db_fifarank,2,FALSE)</f>
@@ -47532,7 +47560,7 @@
       </c>
       <c r="AR34" s="125">
         <f>AP34/AP36</f>
-        <v>0.9999999253833104</v>
+        <v>0.49999998708723048</v>
       </c>
       <c r="AT34" s="126" cm="1">
         <f t="array" ref="AT34">SUMPRODUCT(($S$7:$S$78=AE34&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE34&amp;"_win")*($U$7:$U$78))</f>
@@ -47598,7 +47626,7 @@
         <f>BH34/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK34" s="173">
+      <c r="BK34" s="163">
         <v>81</v>
       </c>
       <c r="BL34" s="24" t="str">
@@ -47629,11 +47657,11 @@
       <c r="CE34" s="112"/>
       <c r="CK34" s="114"/>
       <c r="CL34" s="112"/>
-      <c r="CM34" s="179"/>
-      <c r="CN34" s="180"/>
-      <c r="CO34" s="180"/>
-      <c r="CP34" s="180"/>
-      <c r="CQ34" s="181"/>
+      <c r="CM34" s="168"/>
+      <c r="CN34" s="169"/>
+      <c r="CO34" s="169"/>
+      <c r="CP34" s="169"/>
+      <c r="CQ34" s="170"/>
     </row>
     <row r="35" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A35" s="16">
@@ -47655,8 +47683,12 @@
         <f>AE20</f>
         <v>Brazil</v>
       </c>
-      <c r="F35" s="19"/>
-      <c r="G35" s="20"/>
+      <c r="F35" s="19">
+        <v>3</v>
+      </c>
+      <c r="G35" s="20">
+        <v>0</v>
+      </c>
       <c r="H35" s="80" t="str">
         <f>AE22</f>
         <v>Haiti</v>
@@ -47667,7 +47699,7 @@
       </c>
       <c r="K35" s="23">
         <f>L35+M35+N35</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L35" s="23">
         <f>VLOOKUP(3,AD32:AN35,3,FALSE)</f>
@@ -47675,7 +47707,7 @@
       </c>
       <c r="M35" s="23">
         <f>VLOOKUP(3,AD32:AN35,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" s="23">
         <f>VLOOKUP(3,AD32:AN35,5,FALSE)</f>
@@ -47687,7 +47719,7 @@
       </c>
       <c r="P35" s="34">
         <f>L35*3+M35</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" s="123">
         <f>DATE(2026,6,19)+TIME(13,30,0)+gmt_delta</f>
@@ -47695,11 +47727,11 @@
       </c>
       <c r="S35" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Brazil_win</v>
       </c>
       <c r="T35" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Haiti_lose</v>
       </c>
       <c r="U35" s="123">
         <f t="shared" si="8"/>
@@ -47729,9 +47761,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB35" s="123" t="str">
+      <c r="AB35" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD35" s="123">
         <f>COUNTIF(AR32:AR35,CONCATENATE("&gt;=",AR35))</f>
@@ -47747,7 +47779,7 @@
       </c>
       <c r="AG35" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE35 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH35" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE35 &amp; "_lose")</f>
@@ -47771,15 +47803,15 @@
       </c>
       <c r="AN35" s="123">
         <f>AF35*3+AG35</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO35" s="123">
         <f>AN35/AN36*10+BA35</f>
-        <v>0</v>
+        <v>2.4089635854341735</v>
       </c>
       <c r="AP35" s="123">
         <f>AO35*10000000+BI35*100+AM35/AM36*10+AI35/AI36*1++IF(AQ35=0,ROW(),AQ35)/2000000</f>
-        <v>3.846951236153846</v>
+        <v>24089737.465783384</v>
       </c>
       <c r="AQ35" s="126">
         <f>VLOOKUP(AE35,db_fifarank,2,FALSE)</f>
@@ -47787,7 +47819,7 @@
       </c>
       <c r="AR35" s="125">
         <f>AP35/AP36</f>
-        <v>5.1292675552864665E-8</v>
+        <v>0.28104690042134878</v>
       </c>
       <c r="AT35" s="126" cm="1">
         <f t="array" ref="AT35">SUMPRODUCT(($S$7:$S$78=AE35&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE35&amp;"_win")*($U$7:$U$78))</f>
@@ -47795,7 +47827,7 @@
       </c>
       <c r="AU35" s="126" cm="1">
         <f t="array" ref="AU35">SUMPRODUCT(($S$7:$S$78=AE35&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE35&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV35" s="126" cm="1">
         <f t="array" ref="AV35">SUMPRODUCT(($E$7:$E$78=AE35)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE35)*($U$7:$U$78)*($G$7:$G$78))</f>
@@ -47815,11 +47847,11 @@
       </c>
       <c r="AZ35" s="126">
         <f>AT35/AT36*1000+AU35/AU36*100+AY35/AY36*10+AV35/AV36</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BA35" s="126">
         <f>AZ35/AZ36</f>
-        <v>0</v>
+        <v>0.98039215686274506</v>
       </c>
       <c r="BB35" s="126" cm="1">
         <f t="array" ref="BB35">SUMPRODUCT(($S$7:$S$78=AE35&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE35&amp;"_win")*($X$7:$X$78))</f>
@@ -47827,7 +47859,7 @@
       </c>
       <c r="BC35" s="126" cm="1">
         <f t="array" ref="BC35">SUMPRODUCT(($S$7:$S$78=AE35&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE35&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD35" s="126" cm="1">
         <f t="array" ref="BD35">SUMPRODUCT(($E$7:$E$78=AE35)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE35)*($X$7:$X$78)*($G$7:$G$78))</f>
@@ -47847,13 +47879,13 @@
       </c>
       <c r="BH35" s="126">
         <f>BB35/BB36*1000+BC35/BC36*100+BG35/BG36*10+BD35/BD36</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BI35" s="126">
         <f>BH35/BH36</f>
-        <v>0</v>
-      </c>
-      <c r="BK35" s="174"/>
+        <v>0.98039215686274506</v>
+      </c>
+      <c r="BK35" s="164"/>
       <c r="BL35" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!F3,AK80:AS91,9,FALSE),"3rd Group B/E/F/I/J")</f>
         <v>3rd Group B/E/F/I/J</v>
@@ -47909,8 +47941,12 @@
         <f>AE23</f>
         <v>Scotland</v>
       </c>
-      <c r="F36" s="19"/>
-      <c r="G36" s="20"/>
+      <c r="F36" s="19">
+        <v>0</v>
+      </c>
+      <c r="G36" s="20">
+        <v>1</v>
+      </c>
       <c r="H36" s="80" t="str">
         <f>AE21</f>
         <v>Morocco</v>
@@ -47921,7 +47957,7 @@
       </c>
       <c r="K36" s="36">
         <f>L36+M36+N36</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L36" s="36">
         <f>VLOOKUP(4,AD32:AN35,3,FALSE)</f>
@@ -47929,7 +47965,7 @@
       </c>
       <c r="M36" s="36">
         <f>VLOOKUP(4,AD32:AN35,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N36" s="36">
         <f>VLOOKUP(4,AD32:AN35,5,FALSE)</f>
@@ -47941,7 +47977,7 @@
       </c>
       <c r="P36" s="37">
         <f>L36*3+M36</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" s="123">
         <f>DATE(2026,6,19)+TIME(11,0,0)+gmt_delta</f>
@@ -47949,11 +47985,11 @@
       </c>
       <c r="S36" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Scotland_lose</v>
       </c>
       <c r="T36" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Morocco_win</v>
       </c>
       <c r="U36" s="123">
         <f t="shared" si="8"/>
@@ -47983,17 +48019,17 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB36" s="123" t="str">
+      <c r="AB36" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>-1</v>
       </c>
       <c r="AF36" s="123">
         <f t="shared" ref="AF36:AH36" si="16">MAX(AF32:AF35)-MIN(AF32:AF35)+1</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG36" s="123">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH36" s="123">
         <f t="shared" si="16"/>
@@ -48001,7 +48037,7 @@
       </c>
       <c r="AI36" s="123">
         <f>MAX(AI32:AI35)+1</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AL36" s="123">
         <f>MIN(AL32:AL35)</f>
@@ -48009,19 +48045,19 @@
       </c>
       <c r="AM36" s="123">
         <f>MAX(AM32:AM35)+1</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AN36" s="123">
         <f>MAX(AN32:AN35)+1</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AO36" s="123">
         <f>MAX(AO32:AO35)+1</f>
-        <v>8.5</v>
+        <v>9.5714285714285712</v>
       </c>
       <c r="AP36" s="123">
         <f>MAX(AP32:AP35)+1</f>
-        <v>75000011.106634423</v>
+        <v>85714296.900865197</v>
       </c>
       <c r="AT36" s="126">
         <f>MAX(AT32:AT35)-MIN(AT32:AT35)+1</f>
@@ -48029,7 +48065,7 @@
       </c>
       <c r="AU36" s="126">
         <f>MAX(AU32:AU35)-MIN(AU32:AU35)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV36" s="126">
         <f>MAX(AV32:AV35)-MIN(AV32:AV35)+1</f>
@@ -48045,7 +48081,7 @@
       </c>
       <c r="AZ36" s="126">
         <f>MAX(AZ32:AZ35)+1</f>
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="BB36" s="126">
         <f>MAX(BB32:BB35)-MIN(BB32:BB35)+1</f>
@@ -48053,7 +48089,7 @@
       </c>
       <c r="BC36" s="126">
         <f>MAX(BC32:BC35)-MIN(BC32:BC35)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD36" s="126">
         <f>MAX(BD32:BD35)-MIN(BD32:BD35)+1</f>
@@ -48069,7 +48105,7 @@
       </c>
       <c r="BH36" s="126">
         <f>MAX(BH32:BH35)+1</f>
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="BK36" s="21"/>
       <c r="BL36" s="21"/>
@@ -48078,7 +48114,7 @@
       <c r="BO36" s="21"/>
       <c r="BP36" s="114"/>
       <c r="BQ36" s="112"/>
-      <c r="BR36" s="173">
+      <c r="BR36" s="163">
         <v>94</v>
       </c>
       <c r="BS36" s="24" t="str">
@@ -48135,8 +48171,12 @@
         <f>AE26</f>
         <v>United States</v>
       </c>
-      <c r="F37" s="19"/>
-      <c r="G37" s="20"/>
+      <c r="F37" s="19">
+        <v>2</v>
+      </c>
+      <c r="G37" s="20">
+        <v>0</v>
+      </c>
       <c r="H37" s="80" t="str">
         <f>AE28</f>
         <v>Australia</v>
@@ -48147,11 +48187,11 @@
       </c>
       <c r="S37" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>United States_win</v>
       </c>
       <c r="T37" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Australia_lose</v>
       </c>
       <c r="U37" s="123">
         <f t="shared" si="8"/>
@@ -48181,9 +48221,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB37" s="123" t="str">
+      <c r="AB37" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="BK37" s="21" t="str" cm="1">
         <f t="array" ref="BK37">INDEX(T,24+MONTH(BP37),lang) &amp; " " &amp; DAY(BP37) &amp; ", " &amp; YEAR(BP37) &amp; "   " &amp; (IF(HOUR(BP37)&lt;10,0,"")&amp;HOUR(BP37)) &amp; ":" &amp;  (IF(MINUTE(BP37)&lt;10,0,"")&amp;MINUTE(BP37))</f>
@@ -48198,7 +48238,7 @@
         <v>46204.833333333336</v>
       </c>
       <c r="BQ37" s="115"/>
-      <c r="BR37" s="174"/>
+      <c r="BR37" s="164"/>
       <c r="BS37" s="26" t="str">
         <f>IF(BP38&gt;BP39,BL38,IF(BP38&lt;BP39,BL39,""))</f>
         <v/>
@@ -48225,7 +48265,7 @@
       <c r="CJ37" s="21"/>
       <c r="CK37" s="114"/>
       <c r="CL37" s="112"/>
-      <c r="CM37" s="173">
+      <c r="CM37" s="163">
         <v>104</v>
       </c>
       <c r="CN37" s="24" t="str">
@@ -48260,8 +48300,12 @@
         <f>AE29</f>
         <v>Turkey</v>
       </c>
-      <c r="F38" s="19"/>
-      <c r="G38" s="20"/>
+      <c r="F38" s="19">
+        <v>0</v>
+      </c>
+      <c r="G38" s="20">
+        <v>1</v>
+      </c>
       <c r="H38" s="80" t="str">
         <f>AE27</f>
         <v>Paraguay</v>
@@ -48300,11 +48344,11 @@
       </c>
       <c r="S38" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Turkey_lose</v>
       </c>
       <c r="T38" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Paraguay_win</v>
       </c>
       <c r="U38" s="123">
         <f t="shared" si="8"/>
@@ -48334,13 +48378,13 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB38" s="123" t="str">
+      <c r="AB38" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>-1</v>
       </c>
       <c r="AD38" s="123">
         <f>COUNTIF(AR38:AR41,CONCATENATE("&gt;=",AR38))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE38" s="124" t="str">
         <f>VLOOKUP("Netherlands",T,lang,FALSE)</f>
@@ -48348,7 +48392,7 @@
       </c>
       <c r="AF38" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE38 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG38" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE38 &amp; "_draw")</f>
@@ -48360,31 +48404,31 @@
       </c>
       <c r="AI38" s="123">
         <f>SUMIF($E$7:$E$78,$AE38,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE38,$G$7:$G$78)</f>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AJ38" s="123">
         <f>SUMIF($E$7:$E$78,$AE38,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE38,$F$7:$F$78)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL38" s="123">
         <f>AI38-AJ38</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AM38" s="123">
         <f>AL38-AL42</f>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AN38" s="123">
         <f>AF38*3+AG38</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AO38" s="123">
         <f>AN38/AN42*10+BA38</f>
-        <v>3.4806451612903224</v>
+        <v>8.9806451612903224</v>
       </c>
       <c r="AP38" s="123">
         <f>AO38*10000000+BI38*100+AM38/AM42*10+AI38/AI42*1++IF(AQ38=0,ROW(),AQ38)/2000000</f>
-        <v>34806554.456076071</v>
+        <v>89806559.784067512</v>
       </c>
       <c r="AQ38" s="126">
         <f>VLOOKUP(AE38,db_fifarank,2,FALSE)</f>
@@ -48392,7 +48436,7 @@
       </c>
       <c r="AR38" s="125">
         <f>AP38/AP42</f>
-        <v>0.46408732639569511</v>
+        <v>0.99999998886495611</v>
       </c>
       <c r="AS38" s="125" t="str">
         <f>IF(SUM(AF38:AH41)=12,J39,"1F")</f>
@@ -48462,7 +48506,7 @@
         <f>BH38/BH42</f>
         <v>0.98064516129032253</v>
       </c>
-      <c r="BK38" s="173">
+      <c r="BK38" s="163">
         <v>82</v>
       </c>
       <c r="BL38" s="24" t="str">
@@ -48492,7 +48536,7 @@
       <c r="CI38" s="21"/>
       <c r="CJ38" s="21"/>
       <c r="CL38" s="115"/>
-      <c r="CM38" s="174"/>
+      <c r="CM38" s="164"/>
       <c r="CN38" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG55,IF(CK55&lt;CK56,CG56,""))</f>
         <v/>
@@ -48525,19 +48569,23 @@
         <f>AE32</f>
         <v>Germany</v>
       </c>
-      <c r="F39" s="19"/>
-      <c r="G39" s="20"/>
+      <c r="F39" s="19">
+        <v>2</v>
+      </c>
+      <c r="G39" s="20">
+        <v>1</v>
+      </c>
       <c r="H39" s="80" t="str">
         <f>AE34</f>
         <v>Ivory Coast</v>
       </c>
       <c r="J39" s="30" t="str">
         <f>VLOOKUP(1,AD38:AN41,2,FALSE)</f>
-        <v>Sweden</v>
+        <v>Netherlands</v>
       </c>
       <c r="K39" s="31">
         <f>L39+M39+N39</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L39" s="31">
         <f>VLOOKUP(1,AD38:AN41,3,FALSE)</f>
@@ -48545,7 +48593,7 @@
       </c>
       <c r="M39" s="31">
         <f>VLOOKUP(1,AD38:AN41,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N39" s="31">
         <f>VLOOKUP(1,AD38:AN41,5,FALSE)</f>
@@ -48553,11 +48601,11 @@
       </c>
       <c r="O39" s="31" t="str">
         <f>VLOOKUP(1,AD38:AN41,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD38:AN41,7,FALSE)</f>
-        <v>5 - 1</v>
+        <v>7 - 3</v>
       </c>
       <c r="P39" s="32">
         <f>L39*3+M39</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R39" s="123">
         <f>DATE(2026,6,20)+TIME(9,0,0)+gmt_delta</f>
@@ -48565,11 +48613,11 @@
       </c>
       <c r="S39" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Germany_win</v>
       </c>
       <c r="T39" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Ivory Coast_lose</v>
       </c>
       <c r="U39" s="123">
         <f t="shared" si="8"/>
@@ -48599,13 +48647,13 @@
         <f t="shared" ref="AA39:AA70" si="17">IF(OR(E39=my_team,H39=my_team),1,IF(INT(MATCH(E39,$AE$8:$AE$78,0)/6)=$AA$6,1,0))</f>
         <v>0</v>
       </c>
-      <c r="AB39" s="123" t="str">
+      <c r="AB39" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD39" s="123">
         <f>COUNTIF(AR38:AR41,CONCATENATE("&gt;=",AR39))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE39" s="124" t="str">
         <f>VLOOKUP("Japan",T,lang,FALSE)</f>
@@ -48613,7 +48661,7 @@
       </c>
       <c r="AF39" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE39 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG39" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE39 &amp; "_draw")</f>
@@ -48625,7 +48673,7 @@
       </c>
       <c r="AI39" s="123">
         <f>SUMIF($E$7:$E$78,$AE39,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE39,$G$7:$G$78)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AJ39" s="123">
         <f>SUMIF($E$7:$E$78,$AE39,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE39,$F$7:$F$78)</f>
@@ -48633,23 +48681,23 @@
       </c>
       <c r="AL39" s="123">
         <f>AI39-AJ39</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AM39" s="123">
         <f>AL39-AL42</f>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AN39" s="123">
         <f>AF39*3+AG39</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AO39" s="123">
         <f>AN39/AN42*10+BA39</f>
-        <v>3.4806451612903224</v>
+        <v>8.9806451612903224</v>
       </c>
       <c r="AP39" s="123">
         <f>AO39*10000000+BI39*100+AM39/AM42*10+AI39/AI42*1++IF(AQ39=0,ROW(),AQ39)/2000000</f>
-        <v>34806554.456027351</v>
+        <v>89806559.6590188</v>
       </c>
       <c r="AQ39" s="126">
         <f>VLOOKUP(AE39,db_fifarank,2,FALSE)</f>
@@ -48657,7 +48705,7 @@
       </c>
       <c r="AR39" s="125">
         <f>AP39/AP42</f>
-        <v>0.46408732639504552</v>
+        <v>0.99999998747253316</v>
       </c>
       <c r="AS39" s="125" t="str">
         <f>IF(SUM(AF38:AH41)=12,J40,"2F")</f>
@@ -48727,7 +48775,7 @@
         <f>BH39/BH42</f>
         <v>0.98064516129032253</v>
       </c>
-      <c r="BK39" s="174"/>
+      <c r="BK39" s="164"/>
       <c r="BL39" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!H3,AK80:AS91,9,FALSE),"3rd Group A/E/H/I/J")</f>
         <v>3rd Group A/E/H/I/J</v>
@@ -48780,23 +48828,27 @@
         <f>AE35</f>
         <v>Ecuador</v>
       </c>
-      <c r="F40" s="19"/>
-      <c r="G40" s="20"/>
+      <c r="F40" s="19">
+        <v>0</v>
+      </c>
+      <c r="G40" s="20">
+        <v>0</v>
+      </c>
       <c r="H40" s="80" t="str">
         <f>AE33</f>
         <v>Curaçao</v>
       </c>
       <c r="J40" s="33" t="str">
         <f>VLOOKUP(2,AD38:AN41,2,FALSE)</f>
-        <v>Netherlands</v>
+        <v>Japan</v>
       </c>
       <c r="K40" s="23">
         <f>L40+M40+N40</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L40" s="23">
         <f>VLOOKUP(2,AD38:AN41,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" s="23">
         <f>VLOOKUP(2,AD38:AN41,4,FALSE)</f>
@@ -48808,11 +48860,11 @@
       </c>
       <c r="O40" s="23" t="str">
         <f>VLOOKUP(2,AD38:AN41,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD38:AN41,7,FALSE)</f>
-        <v>2 - 2</v>
+        <v>6 - 2</v>
       </c>
       <c r="P40" s="34">
         <f>L40*3+M40</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R40" s="123">
         <f>DATE(2026,6,20)+TIME(13,0,0)+gmt_delta</f>
@@ -48820,15 +48872,15 @@
       </c>
       <c r="S40" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Ecuador_draw</v>
       </c>
       <c r="T40" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Curaçao_draw</v>
       </c>
       <c r="U40" s="123">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V40" s="123">
         <f t="shared" si="3"/>
@@ -48840,7 +48892,7 @@
       </c>
       <c r="X40" s="123">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y40" s="123">
         <f t="shared" si="10"/>
@@ -48854,13 +48906,13 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB40" s="123" t="str">
+      <c r="AB40" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AD40" s="123">
         <f>COUNTIF(AR38:AR41,CONCATENATE("&gt;=",AR40))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE40" s="124" t="str">
         <f>VLOOKUP("Sweden",T,lang,FALSE)</f>
@@ -48876,19 +48928,19 @@
       </c>
       <c r="AH40" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE40 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI40" s="123">
         <f>SUMIF($E$7:$E$78,$AE40,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE40,$G$7:$G$78)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ40" s="123">
         <f>SUMIF($E$7:$E$78,$AE40,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE40,$F$7:$F$78)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AL40" s="123">
         <f>AI40-AJ40</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AM40" s="123">
         <f>AL40-AL42</f>
@@ -48900,11 +48952,11 @@
       </c>
       <c r="AO40" s="123">
         <f>AN40/AN42*10+BA40</f>
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="AP40" s="123">
         <f>AO40*10000000+BI40*100+AM40/AM42*10+AI40/AI42*1++IF(AQ40=0,ROW(),AQ40)/2000000</f>
-        <v>75000009.722979605</v>
+        <v>60000006.904603533</v>
       </c>
       <c r="AQ40" s="126">
         <f>VLOOKUP(AE40,db_fifarank,2,FALSE)</f>
@@ -48912,7 +48964,7 @@
       </c>
       <c r="AR40" s="125">
         <f>AP40/AP42</f>
-        <v>0.99999998666666856</v>
+        <v>0.66810271299519663</v>
       </c>
       <c r="AT40" s="126" cm="1">
         <f t="array" ref="AT40">SUMPRODUCT(($S$7:$S$78=AE40&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE40&amp;"_win")*($U$7:$U$78))</f>
@@ -49001,39 +49053,43 @@
         <f>AE38</f>
         <v>Netherlands</v>
       </c>
-      <c r="F41" s="19"/>
-      <c r="G41" s="20"/>
+      <c r="F41" s="19">
+        <v>5</v>
+      </c>
+      <c r="G41" s="20">
+        <v>1</v>
+      </c>
       <c r="H41" s="80" t="str">
         <f>AE40</f>
         <v>Sweden</v>
       </c>
       <c r="J41" s="33" t="str">
         <f>VLOOKUP(3,AD38:AN41,2,FALSE)</f>
-        <v>Japan</v>
+        <v>Sweden</v>
       </c>
       <c r="K41" s="23">
         <f>L41+M41+N41</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L41" s="23">
         <f>VLOOKUP(3,AD38:AN41,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" s="23">
         <f>VLOOKUP(3,AD38:AN41,4,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N41" s="23">
         <f>VLOOKUP(3,AD38:AN41,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O41" s="23" t="str">
         <f>VLOOKUP(3,AD38:AN41,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD38:AN41,7,FALSE)</f>
-        <v>2 - 2</v>
+        <v>6 - 6</v>
       </c>
       <c r="P41" s="34">
         <f>L41*3+M41</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R41" s="123">
         <f>DATE(2026,6,20)+TIME(6,0,0)+gmt_delta</f>
@@ -49041,11 +49097,11 @@
       </c>
       <c r="S41" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Netherlands_win</v>
       </c>
       <c r="T41" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Sweden_lose</v>
       </c>
       <c r="U41" s="123">
         <f t="shared" si="8"/>
@@ -49075,9 +49131,9 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB41" s="123" t="str">
+      <c r="AB41" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD41" s="123">
         <f>COUNTIF(AR38:AR41,CONCATENATE("&gt;=",AR41))</f>
@@ -49097,7 +49153,7 @@
       </c>
       <c r="AH41" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE41 &amp; "_lose")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI41" s="123">
         <f>SUMIF($E$7:$E$78,$AE41,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE41,$G$7:$G$78)</f>
@@ -49105,11 +49161,11 @@
       </c>
       <c r="AJ41" s="123">
         <f>SUMIF($E$7:$E$78,$AE41,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE41,$F$7:$F$78)</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AL41" s="123">
         <f>AI41-AJ41</f>
-        <v>-4</v>
+        <v>-8</v>
       </c>
       <c r="AM41" s="123">
         <f>AL41-AL42</f>
@@ -49125,7 +49181,7 @@
       </c>
       <c r="AP41" s="123">
         <f>AO41*10000000+BI41*100+AM41/AM42*10+AI41/AI42*1++IF(AQ41=0,ROW(),AQ41)/2000000</f>
-        <v>0.16740819166666665</v>
+        <v>0.12574152499999999</v>
       </c>
       <c r="AQ41" s="126">
         <f>VLOOKUP(AE41,db_fifarank,2,FALSE)</f>
@@ -49133,7 +49189,7 @@
       </c>
       <c r="AR41" s="125">
         <f>AP41/AP42</f>
-        <v>2.2321089030907787E-9</v>
+        <v>1.4001374053543276E-9</v>
       </c>
       <c r="AT41" s="126" cm="1">
         <f t="array" ref="AT41">SUMPRODUCT(($S$7:$S$78=AE41&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE41&amp;"_win")*($U$7:$U$78))</f>
@@ -49241,8 +49297,12 @@
         <f>AE41</f>
         <v>Tunisia</v>
       </c>
-      <c r="F42" s="19"/>
-      <c r="G42" s="20"/>
+      <c r="F42" s="19">
+        <v>0</v>
+      </c>
+      <c r="G42" s="20">
+        <v>4</v>
+      </c>
       <c r="H42" s="80" t="str">
         <f>AE39</f>
         <v>Japan</v>
@@ -49253,7 +49313,7 @@
       </c>
       <c r="K42" s="36">
         <f>L42+M42+N42</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L42" s="36">
         <f>VLOOKUP(4,AD38:AN41,3,FALSE)</f>
@@ -49265,11 +49325,11 @@
       </c>
       <c r="N42" s="36">
         <f>VLOOKUP(4,AD38:AN41,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O42" s="36" t="str">
         <f>VLOOKUP(4,AD38:AN41,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD38:AN41,7,FALSE)</f>
-        <v>1 - 5</v>
+        <v>1 - 9</v>
       </c>
       <c r="P42" s="37">
         <f>L42*3+M42</f>
@@ -49281,11 +49341,11 @@
       </c>
       <c r="S42" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Tunisia_lose</v>
       </c>
       <c r="T42" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Japan_win</v>
       </c>
       <c r="U42" s="123">
         <f t="shared" si="8"/>
@@ -49315,9 +49375,9 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB42" s="123" t="str">
+      <c r="AB42" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>-1</v>
       </c>
       <c r="AF42" s="123">
         <f t="shared" ref="AF42:AH42" si="18">MAX(AF38:AF41)-MIN(AF38:AF41)+1</f>
@@ -49329,31 +49389,31 @@
       </c>
       <c r="AH42" s="123">
         <f t="shared" si="18"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI42" s="123">
         <f>MAX(AI38:AI41)+1</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AL42" s="123">
         <f>MIN(AL38:AL41)</f>
-        <v>-4</v>
+        <v>-8</v>
       </c>
       <c r="AM42" s="123">
         <f>MAX(AM38:AM41)+1</f>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AN42" s="123">
         <f>MAX(AN38:AN41)+1</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO42" s="123">
         <f>MAX(AO38:AO41)+1</f>
-        <v>8.5</v>
+        <v>9.9806451612903224</v>
       </c>
       <c r="AP42" s="123">
         <f>MAX(AP38:AP41)+1</f>
-        <v>75000010.722979605</v>
+        <v>89806560.784067512</v>
       </c>
       <c r="AT42" s="126">
         <f>MAX(AT38:AT41)-MIN(AT38:AT41)+1</f>
@@ -49403,7 +49463,7 @@
         <f>MAX(BH38:BH41)+1</f>
         <v>51.666666666666664</v>
       </c>
-      <c r="BK42" s="173">
+      <c r="BK42" s="163">
         <v>76</v>
       </c>
       <c r="BL42" s="24" t="str">
@@ -49446,8 +49506,12 @@
         <f>AE53</f>
         <v>Uruguay</v>
       </c>
-      <c r="F43" s="19"/>
-      <c r="G43" s="20"/>
+      <c r="F43" s="19">
+        <v>2</v>
+      </c>
+      <c r="G43" s="20">
+        <v>2</v>
+      </c>
       <c r="H43" s="80" t="str">
         <f>AE51</f>
         <v>Cape Verde</v>
@@ -49458,45 +49522,45 @@
       </c>
       <c r="S43" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Uruguay_draw</v>
       </c>
       <c r="T43" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Cape Verde_draw</v>
       </c>
       <c r="U43" s="123">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V43" s="123">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W43" s="123">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X43" s="123">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y43" s="123">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z43" s="123">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA43" s="123">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB43" s="123" t="str">
+      <c r="AB43" s="123">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="BK43" s="174"/>
+        <v>0</v>
+      </c>
+      <c r="BK43" s="164"/>
       <c r="BL43" s="26" t="str">
         <f>AS39</f>
         <v>2F</v>
@@ -49543,8 +49607,12 @@
         <f>AE50</f>
         <v>Spain</v>
       </c>
-      <c r="F44" s="19"/>
-      <c r="G44" s="20"/>
+      <c r="F44" s="19">
+        <v>4</v>
+      </c>
+      <c r="G44" s="20">
+        <v>0</v>
+      </c>
       <c r="H44" s="80" t="str">
         <f>AE52</f>
         <v>Saudi Arabia</v>
@@ -49583,11 +49651,11 @@
       </c>
       <c r="S44" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Spain_win</v>
       </c>
       <c r="T44" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Saudi Arabia_lose</v>
       </c>
       <c r="U44" s="123">
         <f t="shared" si="8"/>
@@ -49617,9 +49685,9 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB44" s="123" t="str">
+      <c r="AB44" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD44" s="123">
         <f>COUNTIF(AR44:AR47,CONCATENATE("&gt;=",AR44))</f>
@@ -49635,7 +49703,7 @@
       </c>
       <c r="AG44" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE44 &amp; "_draw")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH44" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE44 &amp; "_lose")</f>
@@ -49655,19 +49723,19 @@
       </c>
       <c r="AM44" s="123">
         <f>AL44-AL48</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN44" s="123">
         <f>AF44*3+AG44</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO44" s="123">
         <f>AN44/AN48*10+BA44</f>
-        <v>5.9852941176470589</v>
+        <v>4.9803921568627452</v>
       </c>
       <c r="AP44" s="123">
         <f>AO44*10000000+BI44*100+AM44/AM48*10+AI44/AI48*1++IF(AQ44=0,ROW(),AQ44)/2000000</f>
-        <v>59853040.040083036</v>
+        <v>49804023.808710493</v>
       </c>
       <c r="AQ44" s="126">
         <f>VLOOKUP(AE44,db_fifarank,2,FALSE)</f>
@@ -49675,7 +49743,7 @@
       </c>
       <c r="AR44" s="125">
         <f>AP44/AP48</f>
-        <v>0.9991816403290853</v>
+        <v>0.62255022134039661</v>
       </c>
       <c r="AS44" s="125" t="str">
         <f>IF(SUM(AF44:AH47)=12,J45,"1G")</f>
@@ -49691,11 +49759,11 @@
       </c>
       <c r="AV44" s="126" cm="1">
         <f t="array" ref="AV44">SUMPRODUCT(($E$7:$E$78=AE44)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE44)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW44" s="126" cm="1">
         <f t="array" ref="AW44">SUMPRODUCT(($E$7:$E$78=AE44)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE44)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX44" s="126">
         <f>AV44-AW44</f>
@@ -49707,11 +49775,11 @@
       </c>
       <c r="AZ44" s="126">
         <f>AT44/AT48*1000+AU44/AU48*100+AY44/AY48*10+AV44/AV48</f>
-        <v>100.5</v>
+        <v>50</v>
       </c>
       <c r="BA44" s="126">
         <f>AZ44/AZ48</f>
-        <v>0.98529411764705888</v>
+        <v>0.98039215686274506</v>
       </c>
       <c r="BB44" s="126" cm="1">
         <f t="array" ref="BB44">SUMPRODUCT(($S$7:$S$78=AE44&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE44&amp;"_win")*($X$7:$X$78))</f>
@@ -49723,11 +49791,11 @@
       </c>
       <c r="BD44" s="126" cm="1">
         <f t="array" ref="BD44">SUMPRODUCT(($E$7:$E$78=AE44)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE44)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE44" s="126" cm="1">
         <f t="array" ref="BE44">SUMPRODUCT(($E$7:$E$78=AE44)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE44)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF44" s="126">
         <f>BD44-BE44</f>
@@ -49739,11 +49807,11 @@
       </c>
       <c r="BH44" s="126">
         <f>BB44/BB48*1000+BC44/BC48*100+BG44/BG48*10+BD44/BD48</f>
-        <v>100.5</v>
+        <v>50</v>
       </c>
       <c r="BI44" s="126">
         <f>BH44/BH48</f>
-        <v>0.98529411764705888</v>
+        <v>0.98039215686274506</v>
       </c>
       <c r="BK44" s="21"/>
       <c r="BL44" s="21"/>
@@ -49752,7 +49820,7 @@
       <c r="BO44" s="21"/>
       <c r="BP44" s="114"/>
       <c r="BQ44" s="112"/>
-      <c r="BR44" s="173">
+      <c r="BR44" s="163">
         <v>91</v>
       </c>
       <c r="BS44" s="24" t="str">
@@ -49767,14 +49835,14 @@
         <v/>
       </c>
       <c r="CK44" s="114"/>
-      <c r="CM44" s="176" t="str" cm="1">
+      <c r="CM44" s="165" t="str" cm="1">
         <f t="array" ref="CM44">INDEX(T,7,lang)</f>
         <v>Third-Place Play-Off</v>
       </c>
-      <c r="CN44" s="177"/>
-      <c r="CO44" s="177"/>
-      <c r="CP44" s="177"/>
-      <c r="CQ44" s="178"/>
+      <c r="CN44" s="166"/>
+      <c r="CO44" s="166"/>
+      <c r="CP44" s="166"/>
+      <c r="CQ44" s="167"/>
     </row>
     <row r="45" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="16">
@@ -49796,23 +49864,27 @@
         <f>AE44</f>
         <v>Belgium</v>
       </c>
-      <c r="F45" s="19"/>
-      <c r="G45" s="20"/>
+      <c r="F45" s="19">
+        <v>0</v>
+      </c>
+      <c r="G45" s="20">
+        <v>0</v>
+      </c>
       <c r="H45" s="80" t="str">
         <f>AE46</f>
         <v>Iran</v>
       </c>
       <c r="J45" s="30" t="str">
         <f>VLOOKUP(1,AD44:AN47,2,FALSE)</f>
-        <v>Iran</v>
+        <v>Egypt</v>
       </c>
       <c r="K45" s="31">
         <f>L45+M45+N45</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L45" s="31">
         <f>VLOOKUP(1,AD44:AN47,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" s="31">
         <f>VLOOKUP(1,AD44:AN47,4,FALSE)</f>
@@ -49824,11 +49896,11 @@
       </c>
       <c r="O45" s="31" t="str">
         <f>VLOOKUP(1,AD44:AN47,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD44:AN47,7,FALSE)</f>
-        <v>2 - 2</v>
+        <v>4 - 2</v>
       </c>
       <c r="P45" s="32">
         <f>L45*3+M45</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R45" s="123">
         <f>DATE(2026,6,21)+TIME(8,0,0)+gmt_delta</f>
@@ -49836,15 +49908,15 @@
       </c>
       <c r="S45" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Belgium_draw</v>
       </c>
       <c r="T45" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Iran_draw</v>
       </c>
       <c r="U45" s="123">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V45" s="123">
         <f t="shared" si="3"/>
@@ -49856,7 +49928,7 @@
       </c>
       <c r="X45" s="123">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y45" s="123">
         <f t="shared" si="10"/>
@@ -49870,13 +49942,13 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB45" s="123" t="str">
+      <c r="AB45" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AD45" s="123">
         <f>COUNTIF(AR44:AR47,CONCATENATE("&gt;=",AR45))</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE45" s="124" t="str">
         <f>VLOOKUP("Egypt",T,lang,FALSE)</f>
@@ -49884,7 +49956,7 @@
       </c>
       <c r="AF45" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE45 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG45" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE45 &amp; "_draw")</f>
@@ -49896,31 +49968,31 @@
       </c>
       <c r="AI45" s="123">
         <f>SUMIF($E$7:$E$78,$AE45,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE45,$G$7:$G$78)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AJ45" s="123">
         <f>SUMIF($E$7:$E$78,$AE45,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE45,$F$7:$F$78)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL45" s="123">
         <f>AI45-AJ45</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM45" s="123">
         <f>AL45-AL48</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN45" s="123">
         <f>AF45*3+AG45</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AO45" s="123">
         <f>AN45/AN48*10+BA45</f>
-        <v>5.9852941176470589</v>
+        <v>8</v>
       </c>
       <c r="AP45" s="123">
         <f>AO45*10000000+BI45*100+AM45/AM48*10+AI45/AI48*1++IF(AQ45=0,ROW(),AQ45)/2000000</f>
-        <v>59853040.039997302</v>
+        <v>80000008.800781623</v>
       </c>
       <c r="AQ45" s="126">
         <f>VLOOKUP(AE45,db_fifarank,2,FALSE)</f>
@@ -49928,7 +50000,7 @@
       </c>
       <c r="AR45" s="125">
         <f>AP45/AP48</f>
-        <v>0.99918164032765411</v>
+        <v>0.99999998750000152</v>
       </c>
       <c r="AS45" s="125" t="str">
         <f>IF(SUM(AF44:AH47)=12,J46,"2G")</f>
@@ -49940,15 +50012,15 @@
       </c>
       <c r="AU45" s="126" cm="1">
         <f t="array" ref="AU45">SUMPRODUCT(($S$7:$S$78=AE45&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE45&amp;"_draw")*($U$7:$U$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV45" s="126" cm="1">
         <f t="array" ref="AV45">SUMPRODUCT(($E$7:$E$78=AE45)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE45)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW45" s="126" cm="1">
         <f t="array" ref="AW45">SUMPRODUCT(($E$7:$E$78=AE45)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE45)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX45" s="126">
         <f>AV45-AW45</f>
@@ -49960,11 +50032,11 @@
       </c>
       <c r="AZ45" s="126">
         <f>AT45/AT48*1000+AU45/AU48*100+AY45/AY48*10+AV45/AV48</f>
-        <v>100.5</v>
+        <v>0</v>
       </c>
       <c r="BA45" s="126">
         <f>AZ45/AZ48</f>
-        <v>0.98529411764705888</v>
+        <v>0</v>
       </c>
       <c r="BB45" s="126" cm="1">
         <f t="array" ref="BB45">SUMPRODUCT(($S$7:$S$78=AE45&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE45&amp;"_win")*($X$7:$X$78))</f>
@@ -49972,15 +50044,15 @@
       </c>
       <c r="BC45" s="126" cm="1">
         <f t="array" ref="BC45">SUMPRODUCT(($S$7:$S$78=AE45&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE45&amp;"_draw")*($X$7:$X$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD45" s="126" cm="1">
         <f t="array" ref="BD45">SUMPRODUCT(($E$7:$E$78=AE45)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE45)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE45" s="126" cm="1">
         <f t="array" ref="BE45">SUMPRODUCT(($E$7:$E$78=AE45)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE45)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF45" s="126">
         <f>BD45-BE45</f>
@@ -49992,11 +50064,11 @@
       </c>
       <c r="BH45" s="126">
         <f>BB45/BB48*1000+BC45/BC48*100+BG45/BG48*10+BD45/BD48</f>
-        <v>100.5</v>
+        <v>0</v>
       </c>
       <c r="BI45" s="126">
         <f>BH45/BH48</f>
-        <v>0.98529411764705888</v>
+        <v>0</v>
       </c>
       <c r="BK45" s="21" t="str" cm="1">
         <f t="array" ref="BK45">INDEX(T,24+MONTH(BP45),lang) &amp; " " &amp; DAY(BP45) &amp; ", " &amp; YEAR(BP45) &amp; "   " &amp; (IF(HOUR(BP45)&lt;10,0,"")&amp;HOUR(BP45)) &amp; ":" &amp;  (IF(MINUTE(BP45)&lt;10,0,"")&amp;MINUTE(BP45))</f>
@@ -50011,7 +50083,7 @@
         <v>46203.708333333336</v>
       </c>
       <c r="BQ45" s="115"/>
-      <c r="BR45" s="174"/>
+      <c r="BR45" s="164"/>
       <c r="BS45" s="26" t="str">
         <f>IF(BP46&gt;BP47,BL46,IF(BP46&lt;BP47,BL47,""))</f>
         <v/>
@@ -50024,11 +50096,11 @@
         <v/>
       </c>
       <c r="CK45" s="114"/>
-      <c r="CM45" s="179"/>
-      <c r="CN45" s="180"/>
-      <c r="CO45" s="180"/>
-      <c r="CP45" s="180"/>
-      <c r="CQ45" s="181"/>
+      <c r="CM45" s="168"/>
+      <c r="CN45" s="169"/>
+      <c r="CO45" s="169"/>
+      <c r="CP45" s="169"/>
+      <c r="CQ45" s="170"/>
     </row>
     <row r="46" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A46" s="16">
@@ -50050,19 +50122,23 @@
         <f>AE47</f>
         <v>New Zealand</v>
       </c>
-      <c r="F46" s="19"/>
-      <c r="G46" s="20"/>
+      <c r="F46" s="19">
+        <v>1</v>
+      </c>
+      <c r="G46" s="20">
+        <v>3</v>
+      </c>
       <c r="H46" s="80" t="str">
         <f>AE45</f>
         <v>Egypt</v>
       </c>
       <c r="J46" s="33" t="str">
         <f>VLOOKUP(2,AD44:AN47,2,FALSE)</f>
-        <v>New Zealand</v>
+        <v>Iran</v>
       </c>
       <c r="K46" s="23">
         <f>L46+M46+N46</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L46" s="23">
         <f>VLOOKUP(2,AD44:AN47,3,FALSE)</f>
@@ -50070,7 +50146,7 @@
       </c>
       <c r="M46" s="23">
         <f>VLOOKUP(2,AD44:AN47,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N46" s="23">
         <f>VLOOKUP(2,AD44:AN47,5,FALSE)</f>
@@ -50082,7 +50158,7 @@
       </c>
       <c r="P46" s="34">
         <f>L46*3+M46</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R46" s="123">
         <f>DATE(2026,6,21)+TIME(14,0,0)+gmt_delta</f>
@@ -50090,11 +50166,11 @@
       </c>
       <c r="S46" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>New Zealand_lose</v>
       </c>
       <c r="T46" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Egypt_win</v>
       </c>
       <c r="U46" s="123">
         <f t="shared" si="8"/>
@@ -50124,13 +50200,13 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB46" s="123" t="str">
+      <c r="AB46" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>-1</v>
       </c>
       <c r="AD46" s="123">
         <f>COUNTIF(AR44:AR47,CONCATENATE("&gt;=",AR46))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE46" s="124" t="str">
         <f>VLOOKUP("Iran",T,lang,FALSE)</f>
@@ -50142,7 +50218,7 @@
       </c>
       <c r="AG46" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE46 &amp; "_draw")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH46" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE46 &amp; "_lose")</f>
@@ -50162,19 +50238,19 @@
       </c>
       <c r="AM46" s="123">
         <f>AL46-AL48</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN46" s="123">
         <f>AF46*3+AG46</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO46" s="123">
         <f>AN46/AN48*10+BA46</f>
-        <v>5.9901960784313726</v>
+        <v>4.9803921568627452</v>
       </c>
       <c r="AP46" s="123">
         <f>AO46*10000000+BI46*100+AM46/AM48*10+AI46/AI48*1++IF(AQ46=0,ROW(),AQ46)/2000000</f>
-        <v>59902060.47139588</v>
+        <v>49804024.008650787</v>
       </c>
       <c r="AQ46" s="126">
         <f>VLOOKUP(AE46,db_fifarank,2,FALSE)</f>
@@ -50182,7 +50258,7 @@
       </c>
       <c r="AR46" s="125">
         <f>AP46/AP48</f>
-        <v>0.99999998330608375</v>
+        <v>0.62255022383964997</v>
       </c>
       <c r="AT46" s="126" cm="1">
         <f t="array" ref="AT46">SUMPRODUCT(($S$7:$S$78=AE46&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE46&amp;"_win")*($U$7:$U$78))</f>
@@ -50194,11 +50270,11 @@
       </c>
       <c r="AV46" s="126" cm="1">
         <f t="array" ref="AV46">SUMPRODUCT(($E$7:$E$78=AE46)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE46)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW46" s="126" cm="1">
         <f t="array" ref="AW46">SUMPRODUCT(($E$7:$E$78=AE46)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE46)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX46" s="126">
         <f>AV46-AW46</f>
@@ -50210,11 +50286,11 @@
       </c>
       <c r="AZ46" s="126">
         <f>AT46/AT48*1000+AU46/AU48*100+AY46/AY48*10+AV46/AV48</f>
-        <v>101</v>
+        <v>50</v>
       </c>
       <c r="BA46" s="126">
         <f>AZ46/AZ48</f>
-        <v>0.99019607843137258</v>
+        <v>0.98039215686274506</v>
       </c>
       <c r="BB46" s="126" cm="1">
         <f t="array" ref="BB46">SUMPRODUCT(($S$7:$S$78=AE46&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE46&amp;"_win")*($X$7:$X$78))</f>
@@ -50226,11 +50302,11 @@
       </c>
       <c r="BD46" s="126" cm="1">
         <f t="array" ref="BD46">SUMPRODUCT(($E$7:$E$78=AE46)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE46)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BE46" s="126" cm="1">
         <f t="array" ref="BE46">SUMPRODUCT(($E$7:$E$78=AE46)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE46)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF46" s="126">
         <f>BD46-BE46</f>
@@ -50242,13 +50318,13 @@
       </c>
       <c r="BH46" s="126">
         <f>BB46/BB48*1000+BC46/BC48*100+BG46/BG48*10+BD46/BD48</f>
-        <v>101</v>
+        <v>50</v>
       </c>
       <c r="BI46" s="126">
         <f>BH46/BH48</f>
-        <v>0.99019607843137258</v>
-      </c>
-      <c r="BK46" s="173">
+        <v>0.98039215686274506</v>
+      </c>
+      <c r="BK46" s="163">
         <v>78</v>
       </c>
       <c r="BL46" s="24" t="str">
@@ -50304,7 +50380,7 @@
       </c>
       <c r="K47" s="23">
         <f>L47+M47+N47</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L47" s="23">
         <f>VLOOKUP(3,AD44:AN47,3,FALSE)</f>
@@ -50312,7 +50388,7 @@
       </c>
       <c r="M47" s="23">
         <f>VLOOKUP(3,AD44:AN47,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N47" s="23">
         <f>VLOOKUP(3,AD44:AN47,5,FALSE)</f>
@@ -50324,7 +50400,7 @@
       </c>
       <c r="P47" s="34">
         <f>L47*3+M47</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R47" s="123">
         <f>DATE(2026,6,22)+TIME(13,0,0)+gmt_delta</f>
@@ -50372,7 +50448,7 @@
       </c>
       <c r="AD47" s="123">
         <f>COUNTIF(AR44:AR47,CONCATENATE("&gt;=",AR47))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE47" s="124" t="str">
         <f>VLOOKUP("New Zealand",T,lang,FALSE)</f>
@@ -50388,19 +50464,19 @@
       </c>
       <c r="AH47" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE47 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI47" s="123">
         <f>SUMIF($E$7:$E$78,$AE47,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE47,$G$7:$G$78)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ47" s="123">
         <f>SUMIF($E$7:$E$78,$AE47,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE47,$F$7:$F$78)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AL47" s="123">
         <f>AI47-AJ47</f>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AM47" s="123">
         <f>AL47-AL48</f>
@@ -50412,11 +50488,11 @@
       </c>
       <c r="AO47" s="123">
         <f>AN47/AN48*10+BA47</f>
-        <v>5.9901960784313726</v>
+        <v>2</v>
       </c>
       <c r="AP47" s="123">
         <f>AO47*10000000+BI47*100+AM47/AM48*10+AI47/AI48*1++IF(AQ47=0,ROW(),AQ47)/2000000</f>
-        <v>59902060.471229017</v>
+        <v>20000000.600640785</v>
       </c>
       <c r="AQ47" s="126">
         <f>VLOOKUP(AE47,db_fifarank,2,FALSE)</f>
@@ -50424,7 +50500,7 @@
       </c>
       <c r="AR47" s="125">
         <f>AP47/AP48</f>
-        <v>0.99999998330329809</v>
+        <v>0.24999997688057007</v>
       </c>
       <c r="AT47" s="126" cm="1">
         <f t="array" ref="AT47">SUMPRODUCT(($S$7:$S$78=AE47&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE47&amp;"_win")*($U$7:$U$78))</f>
@@ -50432,15 +50508,15 @@
       </c>
       <c r="AU47" s="126" cm="1">
         <f t="array" ref="AU47">SUMPRODUCT(($S$7:$S$78=AE47&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE47&amp;"_draw")*($U$7:$U$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV47" s="126" cm="1">
         <f t="array" ref="AV47">SUMPRODUCT(($E$7:$E$78=AE47)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE47)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW47" s="126" cm="1">
         <f t="array" ref="AW47">SUMPRODUCT(($E$7:$E$78=AE47)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE47)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX47" s="126">
         <f>AV47-AW47</f>
@@ -50452,11 +50528,11 @@
       </c>
       <c r="AZ47" s="126">
         <f>AT47/AT48*1000+AU47/AU48*100+AY47/AY48*10+AV47/AV48</f>
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="BA47" s="126">
         <f>AZ47/AZ48</f>
-        <v>0.99019607843137258</v>
+        <v>0</v>
       </c>
       <c r="BB47" s="126" cm="1">
         <f t="array" ref="BB47">SUMPRODUCT(($S$7:$S$78=AE47&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE47&amp;"_win")*($X$7:$X$78))</f>
@@ -50464,15 +50540,15 @@
       </c>
       <c r="BC47" s="126" cm="1">
         <f t="array" ref="BC47">SUMPRODUCT(($S$7:$S$78=AE47&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE47&amp;"_draw")*($X$7:$X$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD47" s="126" cm="1">
         <f t="array" ref="BD47">SUMPRODUCT(($E$7:$E$78=AE47)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE47)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BE47" s="126" cm="1">
         <f t="array" ref="BE47">SUMPRODUCT(($E$7:$E$78=AE47)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE47)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF47" s="126">
         <f>BD47-BE47</f>
@@ -50484,13 +50560,13 @@
       </c>
       <c r="BH47" s="126">
         <f>BB47/BB48*1000+BC47/BC48*100+BG47/BG48*10+BD47/BD48</f>
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="BI47" s="126">
         <f>BH47/BH48</f>
-        <v>0.99019607843137258</v>
-      </c>
-      <c r="BK47" s="174"/>
+        <v>0</v>
+      </c>
+      <c r="BK47" s="164"/>
       <c r="BL47" s="26" t="str">
         <f>AS57</f>
         <v>2I</v>
@@ -50565,11 +50641,11 @@
       </c>
       <c r="J48" s="35" t="str">
         <f>VLOOKUP(4,AD44:AN47,2,FALSE)</f>
-        <v>Egypt</v>
+        <v>New Zealand</v>
       </c>
       <c r="K48" s="36">
         <f>L48+M48+N48</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L48" s="36">
         <f>VLOOKUP(4,AD44:AN47,3,FALSE)</f>
@@ -50581,11 +50657,11 @@
       </c>
       <c r="N48" s="36">
         <f>VLOOKUP(4,AD44:AN47,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O48" s="36" t="str">
         <f>VLOOKUP(4,AD44:AN47,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD44:AN47,7,FALSE)</f>
-        <v>1 - 1</v>
+        <v>3 - 5</v>
       </c>
       <c r="P48" s="37">
         <f>L48*3+M48</f>
@@ -50637,39 +50713,39 @@
       </c>
       <c r="AF48" s="123">
         <f t="shared" ref="AF48:AH48" si="24">MAX(AF44:AF47)-MIN(AF44:AF47)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG48" s="123">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH48" s="123">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI48" s="123">
         <f>MAX(AI44:AI47)+1</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AL48" s="123">
         <f>MIN(AL44:AL47)</f>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AM48" s="123">
         <f>MAX(AM44:AM47)+1</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AN48" s="123">
         <f>MAX(AN44:AN47)+1</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AO48" s="123">
         <f>MAX(AO44:AO47)+1</f>
-        <v>6.9901960784313726</v>
+        <v>9</v>
       </c>
       <c r="AP48" s="123">
         <f>MAX(AP44:AP47)+1</f>
-        <v>59902061.47139588</v>
+        <v>80000009.800781623</v>
       </c>
       <c r="AT48" s="126">
         <f>MAX(AT44:AT47)-MIN(AT44:AT47)+1</f>
@@ -50677,15 +50753,15 @@
       </c>
       <c r="AU48" s="126">
         <f>MAX(AU44:AU47)-MIN(AU44:AU47)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV48" s="126">
         <f>MAX(AV44:AV47)-MIN(AV44:AV47)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW48" s="126">
         <f>MAX(AW44:AW47)-MIN(AW44:AW47)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY48" s="126">
         <f>MAX(AY44:AY47)-MIN(AY44:AY47)+1</f>
@@ -50693,7 +50769,7 @@
       </c>
       <c r="AZ48" s="126">
         <f>MAX(AZ44:AZ47)+1</f>
-        <v>102</v>
+        <v>51</v>
       </c>
       <c r="BB48" s="126">
         <f>MAX(BB44:BB47)-MIN(BB44:BB47)+1</f>
@@ -50701,15 +50777,15 @@
       </c>
       <c r="BC48" s="126">
         <f>MAX(BC44:BC47)-MIN(BC44:BC47)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD48" s="126">
         <f>MAX(BD44:BD47)-MIN(BD44:BD47)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BE48" s="126">
         <f>MAX(BE44:BE47)-MIN(BE44:BE47)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BG48" s="126">
         <f>MAX(BG44:BG47)-MIN(BG44:BG47)+1</f>
@@ -50717,7 +50793,7 @@
       </c>
       <c r="BH48" s="126">
         <f>MAX(BH44:BH47)+1</f>
-        <v>102</v>
+        <v>51</v>
       </c>
       <c r="BK48" s="21"/>
       <c r="BL48" s="21"/>
@@ -50733,7 +50809,7 @@
       <c r="BV48" s="21"/>
       <c r="BW48" s="114"/>
       <c r="BX48" s="112"/>
-      <c r="BY48" s="173">
+      <c r="BY48" s="163">
         <v>99</v>
       </c>
       <c r="BZ48" s="24" t="str">
@@ -50749,7 +50825,7 @@
       </c>
       <c r="CK48" s="114"/>
       <c r="CL48" s="112"/>
-      <c r="CM48" s="173">
+      <c r="CM48" s="163">
         <v>103</v>
       </c>
       <c r="CN48" s="24" t="str">
@@ -50854,7 +50930,7 @@
       <c r="BV49" s="21"/>
       <c r="BW49" s="114"/>
       <c r="BX49" s="115"/>
-      <c r="BY49" s="174"/>
+      <c r="BY49" s="164"/>
       <c r="BZ49" s="26" t="str">
         <f>IF(BW52&gt;BW53,BS52,IF(BW52&lt;BW53,BS53,""))</f>
         <v/>
@@ -50868,7 +50944,7 @@
       </c>
       <c r="CK49" s="114"/>
       <c r="CL49" s="115"/>
-      <c r="CM49" s="174"/>
+      <c r="CM49" s="164"/>
       <c r="CN49" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG56,IF(CK55&lt;CK56,CG55,""))</f>
         <v/>
@@ -50981,7 +51057,7 @@
       </c>
       <c r="AD50" s="123">
         <f>COUNTIF(AR50:AR53,CONCATENATE("&gt;=",AR50))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE50" s="124" t="str">
         <f>VLOOKUP("Spain",T,lang,FALSE)</f>
@@ -50989,7 +51065,7 @@
       </c>
       <c r="AF50" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE50 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG50" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE50 &amp; "_draw")</f>
@@ -51001,7 +51077,7 @@
       </c>
       <c r="AI50" s="123">
         <f>SUMIF($E$7:$E$78,$AE50,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE50,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ50" s="123">
         <f>SUMIF($E$7:$E$78,$AE50,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE50,$F$7:$F$78)</f>
@@ -51009,23 +51085,23 @@
       </c>
       <c r="AL50" s="123">
         <f>AI50-AJ50</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AM50" s="123">
         <f>AL50-AL54</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AN50" s="123">
         <f>AF50*3+AG50</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AO50" s="123">
         <f>AN50/AN54*10+BA50</f>
-        <v>5.985221674876847</v>
+        <v>8</v>
       </c>
       <c r="AP50" s="123">
         <f>AO50*10000000+BI50*100+AM50/AM54*10+AI50/AI54*1++IF(AQ50=0,ROW(),AQ50)/2000000</f>
-        <v>59852315.27187416</v>
+        <v>80000009.689827099</v>
       </c>
       <c r="AQ50" s="126">
         <f>VLOOKUP(AE50,db_fifarank,2,FALSE)</f>
@@ -51033,7 +51109,7 @@
       </c>
       <c r="AR50" s="125">
         <f>AP50/AP54</f>
-        <v>0.99917759969584252</v>
+        <v>0.99999998750000163</v>
       </c>
       <c r="AS50" s="125" t="str">
         <f>IF(SUM(AF50:AH53)=12,J51,"1H")</f>
@@ -51045,7 +51121,7 @@
       </c>
       <c r="AU50" s="126" cm="1">
         <f t="array" ref="AU50">SUMPRODUCT(($S$7:$S$78=AE50&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE50&amp;"_draw")*($U$7:$U$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV50" s="126" cm="1">
         <f t="array" ref="AV50">SUMPRODUCT(($E$7:$E$78=AE50)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE50)*($U$7:$U$78)*($G$7:$G$78))</f>
@@ -51065,11 +51141,11 @@
       </c>
       <c r="AZ50" s="126">
         <f>AT50/AT54*1000+AU50/AU54*100+AY50/AY54*10+AV50/AV54</f>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BA50" s="126">
         <f>AZ50/AZ54</f>
-        <v>0.98522167487684731</v>
+        <v>0</v>
       </c>
       <c r="BB50" s="126" cm="1">
         <f t="array" ref="BB50">SUMPRODUCT(($S$7:$S$78=AE50&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE50&amp;"_win")*($X$7:$X$78))</f>
@@ -51077,7 +51153,7 @@
       </c>
       <c r="BC50" s="126" cm="1">
         <f t="array" ref="BC50">SUMPRODUCT(($S$7:$S$78=AE50&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE50&amp;"_draw")*($X$7:$X$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD50" s="126" cm="1">
         <f t="array" ref="BD50">SUMPRODUCT(($E$7:$E$78=AE50)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE50)*($X$7:$X$78)*($G$7:$G$78))</f>
@@ -51097,13 +51173,13 @@
       </c>
       <c r="BH50" s="126">
         <f>BB50/BB54*1000+BC50/BC54*100+BG50/BG54*10+BD50/BD54</f>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BI50" s="126">
         <f>BH50/BH54</f>
-        <v>0.98522167487684731</v>
-      </c>
-      <c r="BK50" s="173">
+        <v>0</v>
+      </c>
+      <c r="BK50" s="163">
         <v>79</v>
       </c>
       <c r="BL50" s="24" t="str">
@@ -51162,15 +51238,15 @@
       </c>
       <c r="J51" s="30" t="str">
         <f>VLOOKUP(1,AD50:AN53,2,FALSE)</f>
-        <v>Uruguay</v>
+        <v>Spain</v>
       </c>
       <c r="K51" s="31">
         <f>L51+M51+N51</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L51" s="31">
         <f>VLOOKUP(1,AD50:AN53,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" s="31">
         <f>VLOOKUP(1,AD50:AN53,4,FALSE)</f>
@@ -51182,11 +51258,11 @@
       </c>
       <c r="O51" s="31" t="str">
         <f>VLOOKUP(1,AD50:AN53,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD50:AN53,7,FALSE)</f>
-        <v>1 - 1</v>
+        <v>4 - 0</v>
       </c>
       <c r="P51" s="32">
         <f>L51*3+M51</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R51" s="123">
         <f>DATE(2026,6,23)+TIME(9,0,0)+gmt_delta</f>
@@ -51234,7 +51310,7 @@
       </c>
       <c r="AD51" s="123">
         <f>COUNTIF(AR50:AR53,CONCATENATE("&gt;=",AR51))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE51" s="124" t="str">
         <f>VLOOKUP("Cape Verde",T,lang,FALSE)</f>
@@ -51246,7 +51322,7 @@
       </c>
       <c r="AG51" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE51 &amp; "_draw")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH51" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE51 &amp; "_lose")</f>
@@ -51254,11 +51330,11 @@
       </c>
       <c r="AI51" s="123">
         <f>SUMIF($E$7:$E$78,$AE51,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE51,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ51" s="123">
         <f>SUMIF($E$7:$E$78,$AE51,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE51,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL51" s="123">
         <f>AI51-AJ51</f>
@@ -51266,19 +51342,19 @@
       </c>
       <c r="AM51" s="123">
         <f>AL51-AL54</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN51" s="123">
         <f>AF51*3+AG51</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO51" s="123">
         <f>AN51/AN54*10+BA51</f>
-        <v>5.985221674876847</v>
+        <v>4.9806451612903224</v>
       </c>
       <c r="AP51" s="123">
         <f>AO51*10000000+BI51*100+AM51/AM54*10+AI51/AI54*1++IF(AQ51=0,ROW(),AQ51)/2000000</f>
-        <v>59852315.271619022</v>
+        <v>49806554.522546858</v>
       </c>
       <c r="AQ51" s="126">
         <f>VLOOKUP(AE51,db_fifarank,2,FALSE)</f>
@@ -51286,7 +51362,7 @@
       </c>
       <c r="AR51" s="125">
         <f>AP51/AP54</f>
-        <v>0.99917759969158326</v>
+        <v>0.62258184834068175</v>
       </c>
       <c r="AS51" s="125" t="str">
         <f>IF(SUM(AF50:AH53)=12,J52,"2H")</f>
@@ -51302,11 +51378,11 @@
       </c>
       <c r="AV51" s="126" cm="1">
         <f t="array" ref="AV51">SUMPRODUCT(($E$7:$E$78=AE51)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE51)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW51" s="126" cm="1">
         <f t="array" ref="AW51">SUMPRODUCT(($E$7:$E$78=AE51)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE51)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX51" s="126">
         <f>AV51-AW51</f>
@@ -51318,11 +51394,11 @@
       </c>
       <c r="AZ51" s="126">
         <f>AT51/AT54*1000+AU51/AU54*100+AY51/AY54*10+AV51/AV54</f>
-        <v>100</v>
+        <v>50.666666666666664</v>
       </c>
       <c r="BA51" s="126">
         <f>AZ51/AZ54</f>
-        <v>0.98522167487684731</v>
+        <v>0.98064516129032253</v>
       </c>
       <c r="BB51" s="126" cm="1">
         <f t="array" ref="BB51">SUMPRODUCT(($S$7:$S$78=AE51&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE51&amp;"_win")*($X$7:$X$78))</f>
@@ -51334,11 +51410,11 @@
       </c>
       <c r="BD51" s="126" cm="1">
         <f t="array" ref="BD51">SUMPRODUCT(($E$7:$E$78=AE51)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE51)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BE51" s="126" cm="1">
         <f t="array" ref="BE51">SUMPRODUCT(($E$7:$E$78=AE51)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE51)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF51" s="126">
         <f>BD51-BE51</f>
@@ -51350,13 +51426,13 @@
       </c>
       <c r="BH51" s="126">
         <f>BB51/BB54*1000+BC51/BC54*100+BG51/BG54*10+BD51/BD54</f>
-        <v>100</v>
+        <v>50.666666666666664</v>
       </c>
       <c r="BI51" s="126">
         <f>BH51/BH54</f>
-        <v>0.98522167487684731</v>
-      </c>
-      <c r="BK51" s="174"/>
+        <v>0.98064516129032253</v>
+      </c>
+      <c r="BK51" s="164"/>
       <c r="BL51" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!D3,AK80:AS91,9,FALSE),"3rd Group C/E/F/H/I")</f>
         <v>3rd Group C/E/F/H/I</v>
@@ -51419,11 +51495,11 @@
       </c>
       <c r="J52" s="33" t="str">
         <f>VLOOKUP(2,AD50:AN53,2,FALSE)</f>
-        <v>Saudi Arabia</v>
+        <v>Uruguay</v>
       </c>
       <c r="K52" s="23">
         <f>L52+M52+N52</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L52" s="23">
         <f>VLOOKUP(2,AD50:AN53,3,FALSE)</f>
@@ -51431,7 +51507,7 @@
       </c>
       <c r="M52" s="23">
         <f>VLOOKUP(2,AD50:AN53,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N52" s="23">
         <f>VLOOKUP(2,AD50:AN53,5,FALSE)</f>
@@ -51439,11 +51515,11 @@
       </c>
       <c r="O52" s="23" t="str">
         <f>VLOOKUP(2,AD50:AN53,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD50:AN53,7,FALSE)</f>
-        <v>1 - 1</v>
+        <v>3 - 3</v>
       </c>
       <c r="P52" s="34">
         <f>L52*3+M52</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R52" s="123">
         <f>DATE(2026,6,23)+TIME(12,0,0)+gmt_delta</f>
@@ -51491,7 +51567,7 @@
       </c>
       <c r="AD52" s="123">
         <f>COUNTIF(AR50:AR53,CONCATENATE("&gt;=",AR52))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE52" s="124" t="str">
         <f>VLOOKUP("Saudi Arabia",T,lang,FALSE)</f>
@@ -51507,7 +51583,7 @@
       </c>
       <c r="AH52" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE52 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI52" s="123">
         <f>SUMIF($E$7:$E$78,$AE52,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE52,$G$7:$G$78)</f>
@@ -51515,11 +51591,11 @@
       </c>
       <c r="AJ52" s="123">
         <f>SUMIF($E$7:$E$78,$AE52,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE52,$F$7:$F$78)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AL52" s="123">
         <f>AI52-AJ52</f>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AM52" s="123">
         <f>AL52-AL54</f>
@@ -51531,11 +51607,11 @@
       </c>
       <c r="AO52" s="123">
         <f>AN52/AN54*10+BA52</f>
-        <v>5.9901477832512313</v>
+        <v>2</v>
       </c>
       <c r="AP52" s="123">
         <f>AO52*10000000+BI52*100+AM52/AM54*10+AI52/AI54*1++IF(AQ52=0,ROW(),AQ52)/2000000</f>
-        <v>59901577.348001353</v>
+        <v>20000000.200710714</v>
       </c>
       <c r="AQ52" s="126">
         <f>VLOOKUP(AE52,db_fifarank,2,FALSE)</f>
@@ -51543,7 +51619,7 @@
       </c>
       <c r="AR52" s="125">
         <f>AP52/AP54</f>
-        <v>0.99999998330384865</v>
+        <v>0.24999996910317837</v>
       </c>
       <c r="AT52" s="126" cm="1">
         <f t="array" ref="AT52">SUMPRODUCT(($S$7:$S$78=AE52&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE52&amp;"_win")*($U$7:$U$78))</f>
@@ -51551,15 +51627,15 @@
       </c>
       <c r="AU52" s="126" cm="1">
         <f t="array" ref="AU52">SUMPRODUCT(($S$7:$S$78=AE52&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE52&amp;"_draw")*($U$7:$U$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV52" s="126" cm="1">
         <f t="array" ref="AV52">SUMPRODUCT(($E$7:$E$78=AE52)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE52)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW52" s="126" cm="1">
         <f t="array" ref="AW52">SUMPRODUCT(($E$7:$E$78=AE52)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE52)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX52" s="126">
         <f>AV52-AW52</f>
@@ -51571,11 +51647,11 @@
       </c>
       <c r="AZ52" s="126">
         <f>AT52/AT54*1000+AU52/AU54*100+AY52/AY54*10+AV52/AV54</f>
-        <v>100.5</v>
+        <v>0</v>
       </c>
       <c r="BA52" s="126">
         <f>AZ52/AZ54</f>
-        <v>0.99014778325123154</v>
+        <v>0</v>
       </c>
       <c r="BB52" s="126" cm="1">
         <f t="array" ref="BB52">SUMPRODUCT(($S$7:$S$78=AE52&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE52&amp;"_win")*($X$7:$X$78))</f>
@@ -51583,15 +51659,15 @@
       </c>
       <c r="BC52" s="126" cm="1">
         <f t="array" ref="BC52">SUMPRODUCT(($S$7:$S$78=AE52&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE52&amp;"_draw")*($X$7:$X$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD52" s="126" cm="1">
         <f t="array" ref="BD52">SUMPRODUCT(($E$7:$E$78=AE52)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE52)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE52" s="126" cm="1">
         <f t="array" ref="BE52">SUMPRODUCT(($E$7:$E$78=AE52)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE52)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF52" s="126">
         <f>BD52-BE52</f>
@@ -51603,11 +51679,11 @@
       </c>
       <c r="BH52" s="126">
         <f>BB52/BB54*1000+BC52/BC54*100+BG52/BG54*10+BD52/BD54</f>
-        <v>100.5</v>
+        <v>0</v>
       </c>
       <c r="BI52" s="126">
         <f>BH52/BH54</f>
-        <v>0.99014778325123154</v>
+        <v>0</v>
       </c>
       <c r="BK52" s="21"/>
       <c r="BL52" s="21"/>
@@ -51616,7 +51692,7 @@
       <c r="BO52" s="21"/>
       <c r="BP52" s="114"/>
       <c r="BQ52" s="112"/>
-      <c r="BR52" s="173">
+      <c r="BR52" s="163">
         <v>92</v>
       </c>
       <c r="BS52" s="24" t="str">
@@ -51668,11 +51744,11 @@
       </c>
       <c r="J53" s="33" t="str">
         <f>VLOOKUP(3,AD50:AN53,2,FALSE)</f>
-        <v>Spain</v>
+        <v>Cape Verde</v>
       </c>
       <c r="K53" s="23">
         <f>L53+M53+N53</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L53" s="23">
         <f>VLOOKUP(3,AD50:AN53,3,FALSE)</f>
@@ -51680,7 +51756,7 @@
       </c>
       <c r="M53" s="23">
         <f>VLOOKUP(3,AD50:AN53,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N53" s="23">
         <f>VLOOKUP(3,AD50:AN53,5,FALSE)</f>
@@ -51688,11 +51764,11 @@
       </c>
       <c r="O53" s="23" t="str">
         <f>VLOOKUP(3,AD50:AN53,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD50:AN53,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>2 - 2</v>
       </c>
       <c r="P53" s="34">
         <f>L53*3+M53</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R53" s="123">
         <f>DATE(2026,6,23)+TIME(6,0,0)+gmt_delta</f>
@@ -51740,7 +51816,7 @@
       </c>
       <c r="AD53" s="123">
         <f>COUNTIF(AR50:AR53,CONCATENATE("&gt;=",AR53))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE53" s="124" t="str">
         <f>VLOOKUP("Uruguay",T,lang,FALSE)</f>
@@ -51752,7 +51828,7 @@
       </c>
       <c r="AG53" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE53 &amp; "_draw")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH53" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE53 &amp; "_lose")</f>
@@ -51760,11 +51836,11 @@
       </c>
       <c r="AI53" s="123">
         <f>SUMIF($E$7:$E$78,$AE53,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE53,$G$7:$G$78)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AJ53" s="123">
         <f>SUMIF($E$7:$E$78,$AE53,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE53,$F$7:$F$78)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AL53" s="123">
         <f>AI53-AJ53</f>
@@ -51772,19 +51848,19 @@
       </c>
       <c r="AM53" s="123">
         <f>AL53-AL54</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN53" s="123">
         <f>AF53*3+AG53</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO53" s="123">
         <f>AN53/AN54*10+BA53</f>
-        <v>5.9901477832512313</v>
+        <v>4.9806451612903224</v>
       </c>
       <c r="AP53" s="123">
         <f>AO53*10000000+BI53*100+AM53/AM54*10+AI53/AI54*1++IF(AQ53=0,ROW(),AQ53)/2000000</f>
-        <v>59901577.348127171</v>
+        <v>49806554.722700335</v>
       </c>
       <c r="AQ53" s="126">
         <f>VLOOKUP(AE53,db_fifarank,2,FALSE)</f>
@@ -51792,7 +51868,7 @@
       </c>
       <c r="AR53" s="125">
         <f>AP53/AP54</f>
-        <v>0.99999998330594908</v>
+        <v>0.62258185084259998</v>
       </c>
       <c r="AT53" s="126" cm="1">
         <f t="array" ref="AT53">SUMPRODUCT(($S$7:$S$78=AE53&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE53&amp;"_win")*($U$7:$U$78))</f>
@@ -51804,11 +51880,11 @@
       </c>
       <c r="AV53" s="126" cm="1">
         <f t="array" ref="AV53">SUMPRODUCT(($E$7:$E$78=AE53)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE53)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW53" s="126" cm="1">
         <f t="array" ref="AW53">SUMPRODUCT(($E$7:$E$78=AE53)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE53)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX53" s="126">
         <f>AV53-AW53</f>
@@ -51820,11 +51896,11 @@
       </c>
       <c r="AZ53" s="126">
         <f>AT53/AT54*1000+AU53/AU54*100+AY53/AY54*10+AV53/AV54</f>
-        <v>100.5</v>
+        <v>50.666666666666664</v>
       </c>
       <c r="BA53" s="126">
         <f>AZ53/AZ54</f>
-        <v>0.99014778325123154</v>
+        <v>0.98064516129032253</v>
       </c>
       <c r="BB53" s="126" cm="1">
         <f t="array" ref="BB53">SUMPRODUCT(($S$7:$S$78=AE53&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE53&amp;"_win")*($X$7:$X$78))</f>
@@ -51836,11 +51912,11 @@
       </c>
       <c r="BD53" s="126" cm="1">
         <f t="array" ref="BD53">SUMPRODUCT(($E$7:$E$78=AE53)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE53)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BE53" s="126" cm="1">
         <f t="array" ref="BE53">SUMPRODUCT(($E$7:$E$78=AE53)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE53)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BF53" s="126">
         <f>BD53-BE53</f>
@@ -51852,11 +51928,11 @@
       </c>
       <c r="BH53" s="126">
         <f>BB53/BB54*1000+BC53/BC54*100+BG53/BG54*10+BD53/BD54</f>
-        <v>100.5</v>
+        <v>50.666666666666664</v>
       </c>
       <c r="BI53" s="126">
         <f>BH53/BH54</f>
-        <v>0.99014778325123154</v>
+        <v>0.98064516129032253</v>
       </c>
       <c r="BK53" s="21" t="str" cm="1">
         <f t="array" ref="BK53">INDEX(T,24+MONTH(BP53),lang) &amp; " " &amp; DAY(BP53) &amp; ", " &amp; YEAR(BP53) &amp; "   " &amp; (IF(HOUR(BP53)&lt;10,0,"")&amp;HOUR(BP53)) &amp; ":" &amp;  (IF(MINUTE(BP53)&lt;10,0,"")&amp;MINUTE(BP53))</f>
@@ -51871,7 +51947,7 @@
         <v>46204.666666666672</v>
       </c>
       <c r="BQ53" s="115"/>
-      <c r="BR53" s="174"/>
+      <c r="BR53" s="164"/>
       <c r="BS53" s="26" t="str">
         <f>IF(BP54&gt;BP55,BL54,IF(BP54&lt;BP55,BL55,""))</f>
         <v/>
@@ -51921,11 +51997,11 @@
       </c>
       <c r="J54" s="35" t="str">
         <f>VLOOKUP(4,AD50:AN53,2,FALSE)</f>
-        <v>Cape Verde</v>
+        <v>Saudi Arabia</v>
       </c>
       <c r="K54" s="36">
         <f>L54+M54+N54</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L54" s="36">
         <f>VLOOKUP(4,AD50:AN53,3,FALSE)</f>
@@ -51937,11 +52013,11 @@
       </c>
       <c r="N54" s="36">
         <f>VLOOKUP(4,AD50:AN53,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O54" s="36" t="str">
         <f>VLOOKUP(4,AD50:AN53,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD50:AN53,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 5</v>
       </c>
       <c r="P54" s="37">
         <f>L54*3+M54</f>
@@ -51993,39 +52069,39 @@
       </c>
       <c r="AF54" s="123">
         <f t="shared" ref="AF54:AH54" si="25">MAX(AF50:AF53)-MIN(AF50:AF53)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG54" s="123">
         <f t="shared" si="25"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH54" s="123">
         <f t="shared" si="25"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI54" s="123">
         <f>MAX(AI50:AI53)+1</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AL54" s="123">
         <f>MIN(AL50:AL53)</f>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AM54" s="123">
         <f>MAX(AM50:AM53)+1</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AN54" s="123">
         <f>MAX(AN50:AN53)+1</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AO54" s="123">
         <f>MAX(AO50:AO53)+1</f>
-        <v>6.9901477832512313</v>
+        <v>9</v>
       </c>
       <c r="AP54" s="123">
         <f>MAX(AP50:AP53)+1</f>
-        <v>59901578.348127171</v>
+        <v>80000010.689827099</v>
       </c>
       <c r="AT54" s="126">
         <f>MAX(AT50:AT53)-MIN(AT50:AT53)+1</f>
@@ -52033,15 +52109,15 @@
       </c>
       <c r="AU54" s="126">
         <f>MAX(AU50:AU53)-MIN(AU50:AU53)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV54" s="126">
         <f>MAX(AV50:AV53)-MIN(AV50:AV53)+1</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW54" s="126">
         <f>MAX(AW50:AW53)-MIN(AW50:AW53)+1</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY54" s="126">
         <f>MAX(AY50:AY53)-MIN(AY50:AY53)+1</f>
@@ -52049,7 +52125,7 @@
       </c>
       <c r="AZ54" s="126">
         <f>MAX(AZ50:AZ53)+1</f>
-        <v>101.5</v>
+        <v>51.666666666666664</v>
       </c>
       <c r="BB54" s="126">
         <f>MAX(BB50:BB53)-MIN(BB50:BB53)+1</f>
@@ -52057,15 +52133,15 @@
       </c>
       <c r="BC54" s="126">
         <f>MAX(BC50:BC53)-MIN(BC50:BC53)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD54" s="126">
         <f>MAX(BD50:BD53)-MIN(BD50:BD53)+1</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BE54" s="126">
         <f>MAX(BE50:BE53)-MIN(BE50:BE53)+1</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BG54" s="126">
         <f>MAX(BG50:BG53)-MIN(BG50:BG53)+1</f>
@@ -52073,9 +52149,9 @@
       </c>
       <c r="BH54" s="126">
         <f>MAX(BH50:BH53)+1</f>
-        <v>101.5</v>
-      </c>
-      <c r="BK54" s="173">
+        <v>51.666666666666664</v>
+      </c>
+      <c r="BK54" s="163">
         <v>80</v>
       </c>
       <c r="BL54" s="24" t="str">
@@ -52196,7 +52272,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK55" s="174"/>
+      <c r="BK55" s="164"/>
       <c r="BL55" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!K3,AK80:AS91,9,FALSE),"3rd Group E/H/I/J/K")</f>
         <v>3rd Group E/H/I/J/K</v>
@@ -52223,7 +52299,7 @@
       <c r="CC55" s="21"/>
       <c r="CD55" s="114"/>
       <c r="CE55" s="112"/>
-      <c r="CF55" s="173">
+      <c r="CF55" s="163">
         <v>102</v>
       </c>
       <c r="CG55" s="24" t="str">
@@ -52482,7 +52558,7 @@
       <c r="CC56" s="21"/>
       <c r="CD56" s="114"/>
       <c r="CE56" s="115"/>
-      <c r="CF56" s="174"/>
+      <c r="CF56" s="164"/>
       <c r="CG56" s="26" t="str">
         <f>IF(CD64&gt;CD65,BZ64,IF(CD64&lt;CD65,BZ65,""))</f>
         <v/>
@@ -52965,7 +53041,7 @@
         <f>BH58/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK58" s="173">
+      <c r="BK58" s="163">
         <v>86</v>
       </c>
       <c r="BL58" s="24" t="str">
@@ -53213,7 +53289,7 @@
         <f>BH59/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK59" s="174"/>
+      <c r="BK59" s="164"/>
       <c r="BL59" s="26" t="str">
         <f>AS51</f>
         <v>2H</v>
@@ -53436,7 +53512,7 @@
       <c r="BO60" s="21"/>
       <c r="BP60" s="114"/>
       <c r="BQ60" s="112"/>
-      <c r="BR60" s="173">
+      <c r="BR60" s="163">
         <v>95</v>
       </c>
       <c r="BS60" s="24" t="str">
@@ -53549,7 +53625,7 @@
         <v>46206.75</v>
       </c>
       <c r="BQ61" s="115"/>
-      <c r="BR61" s="174"/>
+      <c r="BR61" s="164"/>
       <c r="BS61" s="26" t="str">
         <f>IF(BP62&gt;BP63,BL62,IF(BP62&lt;BP63,BL63,""))</f>
         <v/>
@@ -53792,7 +53868,7 @@
         <f>BH62/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK62" s="173">
+      <c r="BK62" s="163">
         <v>88</v>
       </c>
       <c r="BL62" s="24" t="str">
@@ -54044,7 +54120,7 @@
         <f>BH63/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK63" s="174"/>
+      <c r="BK63" s="164"/>
       <c r="BL63" s="26" t="str">
         <f>AS45</f>
         <v>2G</v>
@@ -54310,7 +54386,7 @@
       <c r="BV64" s="21"/>
       <c r="BW64" s="114"/>
       <c r="BX64" s="112"/>
-      <c r="BY64" s="173">
+      <c r="BY64" s="163">
         <v>100</v>
       </c>
       <c r="BZ64" s="24" t="str">
@@ -54564,7 +54640,7 @@
       <c r="BV65" s="21"/>
       <c r="BW65" s="114"/>
       <c r="BX65" s="115"/>
-      <c r="BY65" s="174"/>
+      <c r="BY65" s="164"/>
       <c r="BZ65" s="26" t="str">
         <f>IF(BW68&gt;BW69,BS68,IF(BW68&lt;BW69,BS69,""))</f>
         <v/>
@@ -54760,7 +54836,7 @@
         <f>MAX(BH62:BH65)+1</f>
         <v>1</v>
       </c>
-      <c r="BK66" s="173">
+      <c r="BK66" s="163">
         <v>85</v>
       </c>
       <c r="BL66" s="24" t="str">
@@ -54860,7 +54936,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK67" s="174"/>
+      <c r="BK67" s="164"/>
       <c r="BL67" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!E3,AK80:AS91,9,FALSE),"3rd Group E/F/G/I/J")</f>
         <v>3rd Group E/F/G/I/J</v>
@@ -54987,7 +55063,7 @@
       </c>
       <c r="AD68" s="123">
         <f>COUNTIF(AR68:AR71,CONCATENATE("&gt;=",AR68))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE68" s="124" t="str">
         <f>VLOOKUP("Portugal",T,lang,FALSE)</f>
@@ -55019,7 +55095,7 @@
       </c>
       <c r="AM68" s="123">
         <f>AL68-AL72</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN68" s="123">
         <f>AF68*3+AG68</f>
@@ -55027,11 +55103,11 @@
       </c>
       <c r="AO68" s="123">
         <f>AN68/AN72*10+BA68</f>
-        <v>5.9805825242718447</v>
+        <v>3.4805825242718447</v>
       </c>
       <c r="AP68" s="123">
         <f>AO68*10000000+BI68*100+AM68/AM72*10+AI68/AI72*1++IF(AQ68=0,ROW(),AQ68)/2000000</f>
-        <v>59805923.801852785</v>
+        <v>34805927.551852785</v>
       </c>
       <c r="AQ68" s="126">
         <f>VLOOKUP(AE68,db_fifarank,2,FALSE)</f>
@@ -55039,7 +55115,7 @@
       </c>
       <c r="AR68" s="125">
         <f>AP68/AP72</f>
-        <v>0.99999998327924866</v>
+        <v>0.46407897368919898</v>
       </c>
       <c r="AS68" s="125" t="str">
         <f>IF(SUM(AF68:AH71)=12,J69,"1K")</f>
@@ -55116,7 +55192,7 @@
       <c r="BO68" s="21"/>
       <c r="BP68" s="114"/>
       <c r="BQ68" s="112"/>
-      <c r="BR68" s="173">
+      <c r="BR68" s="163">
         <v>96</v>
       </c>
       <c r="BS68" s="24" t="str">
@@ -55130,25 +55206,25 @@
         <f>IF(OR(BT68="",BT69="",AND(BU68="",BU69&lt;&gt;""),AND(BU69="",BU68&lt;&gt;""),AND(BV68="",BV69&lt;&gt;""),AND(BV69="",BV68&lt;&gt;"")),"",BT68*1000+BU68*10+BV68)</f>
         <v/>
       </c>
-      <c r="CE68" s="175" t="str">
+      <c r="CE68" s="195" t="str">
         <f>INDEX(T,144,lang)</f>
         <v>World Champion 2026</v>
       </c>
-      <c r="CF68" s="175"/>
-      <c r="CG68" s="175"/>
-      <c r="CH68" s="175"/>
-      <c r="CI68" s="175"/>
-      <c r="CJ68" s="175"/>
-      <c r="CK68" s="163" t="str">
+      <c r="CF68" s="195"/>
+      <c r="CG68" s="195"/>
+      <c r="CH68" s="195"/>
+      <c r="CI68" s="195"/>
+      <c r="CJ68" s="195"/>
+      <c r="CK68" s="185" t="str">
         <f>IF(CR37&gt;CR38,CN37,IF(CR37&lt;CR38,CN38,""))</f>
         <v/>
       </c>
-      <c r="CL68" s="163"/>
-      <c r="CM68" s="163"/>
-      <c r="CN68" s="163"/>
-      <c r="CO68" s="163"/>
-      <c r="CP68" s="163"/>
-      <c r="CQ68" s="163"/>
+      <c r="CL68" s="185"/>
+      <c r="CM68" s="185"/>
+      <c r="CN68" s="185"/>
+      <c r="CO68" s="185"/>
+      <c r="CP68" s="185"/>
+      <c r="CQ68" s="185"/>
     </row>
     <row r="69" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A69" s="16">
@@ -55179,7 +55255,7 @@
       <c r="I69" s="69"/>
       <c r="J69" s="30" t="str">
         <f>VLOOKUP(1,AD68:AN71,2,FALSE)</f>
-        <v>Portugal</v>
+        <v>Colombia</v>
       </c>
       <c r="K69" s="31">
         <f>L69+M69+N69</f>
@@ -55187,11 +55263,11 @@
       </c>
       <c r="L69" s="31">
         <f>VLOOKUP(1,AD68:AN71,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" s="31">
         <f>VLOOKUP(1,AD68:AN71,4,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N69" s="31">
         <f>VLOOKUP(1,AD68:AN71,5,FALSE)</f>
@@ -55199,11 +55275,11 @@
       </c>
       <c r="O69" s="31" t="str">
         <f>VLOOKUP(1,AD68:AN71,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD68:AN71,7,FALSE)</f>
-        <v>1 - 1</v>
+        <v>3 - 1</v>
       </c>
       <c r="P69" s="32">
         <f>L69*3+M69</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R69" s="123">
         <f>DATE(2026,6,26)+TIME(16,0,0)+gmt_delta</f>
@@ -55251,7 +55327,7 @@
       </c>
       <c r="AD69" s="123">
         <f>COUNTIF(AR68:AR71,CONCATENATE("&gt;=",AR69))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE69" s="124" t="str">
         <f>VLOOKUP("DR Congo",T,lang,FALSE)</f>
@@ -55283,7 +55359,7 @@
       </c>
       <c r="AM69" s="123">
         <f>AL69-AL72</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN69" s="123">
         <f>AF69*3+AG69</f>
@@ -55291,11 +55367,11 @@
       </c>
       <c r="AO69" s="123">
         <f>AN69/AN72*10+BA69</f>
-        <v>5.9805825242718447</v>
+        <v>3.4805825242718447</v>
       </c>
       <c r="AP69" s="123">
         <f>AO69*10000000+BI69*100+AM69/AM72*10+AI69/AI72*1++IF(AQ69=0,ROW(),AQ69)/2000000</f>
-        <v>59805923.801710039</v>
+        <v>34805927.551710039</v>
       </c>
       <c r="AQ69" s="126">
         <f>VLOOKUP(AE69,db_fifarank,2,FALSE)</f>
@@ -55303,7 +55379,7 @@
       </c>
       <c r="AR69" s="125">
         <f>AP69/AP72</f>
-        <v>0.99999998327686179</v>
+        <v>0.46407897368729573</v>
       </c>
       <c r="AS69" s="125" t="str">
         <f>IF(SUM(AF68:AH71)=12,J70,"2K")</f>
@@ -55386,7 +55462,7 @@
         <v>46207.0625</v>
       </c>
       <c r="BQ69" s="115"/>
-      <c r="BR69" s="174"/>
+      <c r="BR69" s="164"/>
       <c r="BS69" s="26" t="str">
         <f>IF(BP70&gt;BP71,BL70,IF(BP70&lt;BP71,BL71,""))</f>
         <v/>
@@ -55398,19 +55474,19 @@
         <f>IF(BW68="","",BT69*1000+BU69*10+BV69)</f>
         <v/>
       </c>
-      <c r="CE69" s="175"/>
-      <c r="CF69" s="175"/>
-      <c r="CG69" s="175"/>
-      <c r="CH69" s="175"/>
-      <c r="CI69" s="175"/>
-      <c r="CJ69" s="175"/>
-      <c r="CK69" s="163"/>
-      <c r="CL69" s="163"/>
-      <c r="CM69" s="163"/>
-      <c r="CN69" s="163"/>
-      <c r="CO69" s="163"/>
-      <c r="CP69" s="163"/>
-      <c r="CQ69" s="163"/>
+      <c r="CE69" s="195"/>
+      <c r="CF69" s="195"/>
+      <c r="CG69" s="195"/>
+      <c r="CH69" s="195"/>
+      <c r="CI69" s="195"/>
+      <c r="CJ69" s="195"/>
+      <c r="CK69" s="185"/>
+      <c r="CL69" s="185"/>
+      <c r="CM69" s="185"/>
+      <c r="CN69" s="185"/>
+      <c r="CO69" s="185"/>
+      <c r="CP69" s="185"/>
+      <c r="CQ69" s="185"/>
     </row>
     <row r="70" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A70" s="16">
@@ -55441,7 +55517,7 @@
       <c r="I70" s="69"/>
       <c r="J70" s="33" t="str">
         <f>VLOOKUP(2,AD68:AN71,2,FALSE)</f>
-        <v>DR Congo</v>
+        <v>Portugal</v>
       </c>
       <c r="K70" s="23">
         <f>L70+M70+N70</f>
@@ -55529,19 +55605,19 @@
       </c>
       <c r="AH70" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE70 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI70" s="123">
         <f>SUMIF($E$7:$E$78,$AE70,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE70,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ70" s="123">
         <f>SUMIF($E$7:$E$78,$AE70,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE70,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL70" s="123">
         <f>AI70-AJ70</f>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AM70" s="123">
         <f>AL70-AL72</f>
@@ -55557,7 +55633,7 @@
       </c>
       <c r="AP70" s="123">
         <f>AO70*10000000+BI70*100+AM70/AM72*10+AI70/AI72*1++IF(AQ70=0,ROW(),AQ70)/2000000</f>
-        <v>7.3266999999999994E-4</v>
+        <v>0.25073266999999999</v>
       </c>
       <c r="AQ70" s="126">
         <f>VLOOKUP(AE70,db_fifarank,2,FALSE)</f>
@@ -55565,7 +55641,7 @@
       </c>
       <c r="AR70" s="125">
         <f>AP70/AP72</f>
-        <v>1.2250792917716104E-11</v>
+        <v>3.3431018320256936E-9</v>
       </c>
       <c r="AT70" s="126" cm="1">
         <f t="array" ref="AT70">SUMPRODUCT(($S$7:$S$78=AE70&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE70&amp;"_win")*($U$7:$U$78))</f>
@@ -55631,7 +55707,7 @@
         <f>BH70/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK70" s="173">
+      <c r="BK70" s="163">
         <v>87</v>
       </c>
       <c r="BL70" s="24" t="str">
@@ -55677,11 +55753,11 @@
       <c r="I71" s="69"/>
       <c r="J71" s="33" t="str">
         <f>VLOOKUP(3,AD68:AN71,2,FALSE)</f>
-        <v>Colombia</v>
+        <v>DR Congo</v>
       </c>
       <c r="K71" s="23">
         <f>L71+M71+N71</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" s="23">
         <f>VLOOKUP(3,AD68:AN71,3,FALSE)</f>
@@ -55689,7 +55765,7 @@
       </c>
       <c r="M71" s="23">
         <f>VLOOKUP(3,AD68:AN71,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N71" s="23">
         <f>VLOOKUP(3,AD68:AN71,5,FALSE)</f>
@@ -55697,11 +55773,11 @@
       </c>
       <c r="O71" s="23" t="str">
         <f>VLOOKUP(3,AD68:AN71,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD68:AN71,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 1</v>
       </c>
       <c r="P71" s="34">
         <f>L71*3+M71</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R71" s="123">
         <f>DATE(2026,6,26)+TIME(13,0,0)+gmt_delta</f>
@@ -55749,7 +55825,7 @@
       </c>
       <c r="AD71" s="123">
         <f>COUNTIF(AR68:AR71,CONCATENATE("&gt;=",AR71))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE71" s="124" t="str">
         <f>VLOOKUP("Colombia",T,lang,FALSE)</f>
@@ -55757,7 +55833,7 @@
       </c>
       <c r="AF71" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE71 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG71" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE71 &amp; "_draw")</f>
@@ -55769,31 +55845,31 @@
       </c>
       <c r="AI71" s="123">
         <f>SUMIF($E$7:$E$78,$AE71,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE71,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AJ71" s="123">
         <f>SUMIF($E$7:$E$78,$AE71,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE71,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL71" s="123">
         <f>AI71-AJ71</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM71" s="123">
         <f>AL71-AL72</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN71" s="123">
         <f>AF71*3+AG71</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO71" s="123">
         <f>AN71/AN72*10+BA71</f>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AP71" s="123">
         <f>AO71*10000000+BI71*100+AM71/AM72*10+AI71/AI72*1++IF(AQ71=0,ROW(),AQ71)/2000000</f>
-        <v>8.4654499999999998E-4</v>
+        <v>75000008.75084655</v>
       </c>
       <c r="AQ71" s="126">
         <f>VLOOKUP(AE71,db_fifarank,2,FALSE)</f>
@@ -55801,7 +55877,7 @@
       </c>
       <c r="AR71" s="125">
         <f>AP71/AP72</f>
-        <v>1.4154868481755742E-11</v>
+        <v>0.99999998666666845</v>
       </c>
       <c r="AT71" s="126" cm="1">
         <f t="array" ref="AT71">SUMPRODUCT(($S$7:$S$78=AE71&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE71&amp;"_win")*($U$7:$U$78))</f>
@@ -55867,7 +55943,7 @@
         <f>BH71/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK71" s="174"/>
+      <c r="BK71" s="164"/>
       <c r="BL71" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!J3,AK80:AS91,9,FALSE),"3rd Group D/E/I/J/L")</f>
         <v>3rd Group D/E/I/J/L</v>
@@ -55914,7 +55990,7 @@
       </c>
       <c r="K72" s="36">
         <f>L72+M72+N72</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="36">
         <f>VLOOKUP(4,AD68:AN71,3,FALSE)</f>
@@ -55926,11 +56002,11 @@
       </c>
       <c r="N72" s="36">
         <f>VLOOKUP(4,AD68:AN71,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O72" s="36" t="str">
         <f>VLOOKUP(4,AD68:AN71,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD68:AN71,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 3</v>
       </c>
       <c r="P72" s="37">
         <f>L72*3+M72</f>
@@ -55982,7 +56058,7 @@
       </c>
       <c r="AF72" s="123">
         <f t="shared" ref="AF72:AH72" si="35">MAX(AF68:AF71)-MIN(AF68:AF71)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG72" s="123">
         <f t="shared" si="35"/>
@@ -55990,31 +56066,31 @@
       </c>
       <c r="AH72" s="123">
         <f t="shared" si="35"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI72" s="123">
         <f>MAX(AI68:AI71)+1</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AL72" s="123">
         <f>MIN(AL68:AL71)</f>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AM72" s="123">
         <f>MAX(AM68:AM71)+1</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AN72" s="123">
         <f>MAX(AN68:AN71)+1</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AO72" s="123">
         <f>MAX(AO68:AO71)+1</f>
-        <v>6.9805825242718447</v>
+        <v>8.5</v>
       </c>
       <c r="AP72" s="123">
         <f>MAX(AP68:AP71)+1</f>
-        <v>59805924.801852785</v>
+        <v>75000009.75084655</v>
       </c>
       <c r="AT72" s="126">
         <f>MAX(AT68:AT71)-MIN(AT68:AT71)+1</f>
@@ -56253,7 +56329,7 @@
       </c>
       <c r="AF74" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE74 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG74" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE74 &amp; "_draw")</f>
@@ -56265,31 +56341,31 @@
       </c>
       <c r="AI74" s="123">
         <f>SUMIF($E$7:$E$78,$AE74,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE74,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ74" s="123">
         <f>SUMIF($E$7:$E$78,$AE74,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE74,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL74" s="123">
         <f>AI74-AJ74</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM74" s="123">
         <f>AL74-AL78</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN74" s="123">
         <f>AF74*3+AG74</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO74" s="123">
         <f>AN74/AN78*10+BA74</f>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AP74" s="123">
         <f>AO74*10000000+BI74*100+AM74/AM78*10+AI74/AI78*1++IF(AQ74=0,ROW(),AQ74)/2000000</f>
-        <v>9.1298500000000006E-4</v>
+        <v>75000008.800912976</v>
       </c>
       <c r="AQ74" s="126">
         <f>VLOOKUP(AE74,db_fifarank,2,FALSE)</f>
@@ -56297,7 +56373,7 @@
       </c>
       <c r="AR74" s="125">
         <f>AP74/AP78</f>
-        <v>9.1215221870660421E-4</v>
+        <v>0.99999998666666845</v>
       </c>
       <c r="AS74" s="125" t="str">
         <f>IF(SUM(AF74:AH77)=12,J75,"1L")</f>
@@ -56401,11 +56477,11 @@
       </c>
       <c r="K75" s="31">
         <f>L75+M75+N75</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="31">
         <f>VLOOKUP(1,AD74:AN77,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" s="31">
         <f>VLOOKUP(1,AD74:AN77,4,FALSE)</f>
@@ -56417,11 +56493,11 @@
       </c>
       <c r="O75" s="31" t="str">
         <f>VLOOKUP(1,AD74:AN77,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD74:AN77,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>4 - 2</v>
       </c>
       <c r="P75" s="32">
         <f>L75*3+M75</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R75" s="123">
         <f>DATE(2026,6,27)+TIME(15,0,0)+gmt_delta</f>
@@ -56469,7 +56545,7 @@
       </c>
       <c r="AD75" s="123">
         <f>COUNTIF(AR74:AR77,CONCATENATE("&gt;=",AR75))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE75" s="124" t="str">
         <f>VLOOKUP("Croatia",T,lang,FALSE)</f>
@@ -56485,19 +56561,19 @@
       </c>
       <c r="AH75" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE75 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI75" s="123">
         <f>SUMIF($E$7:$E$78,$AE75,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE75,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ75" s="123">
         <f>SUMIF($E$7:$E$78,$AE75,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE75,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL75" s="123">
         <f>AI75-AJ75</f>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AM75" s="123">
         <f>AL75-AL78</f>
@@ -56513,7 +56589,7 @@
       </c>
       <c r="AP75" s="123">
         <f>AO75*10000000+BI75*100+AM75/AM78*10+AI75/AI78*1++IF(AQ75=0,ROW(),AQ75)/2000000</f>
-        <v>8.5853500000000001E-4</v>
+        <v>0.40085853500000002</v>
       </c>
       <c r="AQ75" s="126">
         <f>VLOOKUP(AE75,db_fifarank,2,FALSE)</f>
@@ -56521,7 +56597,7 @@
       </c>
       <c r="AR75" s="125">
         <f>AP75/AP78</f>
-        <v>8.5775188539491268E-4</v>
+        <v>5.3447797682170484E-9</v>
       </c>
       <c r="AS75" s="125" t="str">
         <f>IF(SUM(AF74:AH77)=12,J76,"2L")</f>
@@ -56621,15 +56697,15 @@
       <c r="I76" s="69"/>
       <c r="J76" s="33" t="str">
         <f>VLOOKUP(2,AD74:AN77,2,FALSE)</f>
-        <v>Croatia</v>
+        <v>Ghana</v>
       </c>
       <c r="K76" s="23">
         <f>L76+M76+N76</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="23">
         <f>VLOOKUP(2,AD74:AN77,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76" s="23">
         <f>VLOOKUP(2,AD74:AN77,4,FALSE)</f>
@@ -56641,11 +56717,11 @@
       </c>
       <c r="O76" s="23" t="str">
         <f>VLOOKUP(2,AD74:AN77,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD74:AN77,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 0</v>
       </c>
       <c r="P76" s="34">
         <f>L76*3+M76</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R76" s="123">
         <f>DATE(2026,6,27)+TIME(15,0,0)+gmt_delta</f>
@@ -56693,7 +56769,7 @@
       </c>
       <c r="AD76" s="123">
         <f>COUNTIF(AR74:AR77,CONCATENATE("&gt;=",AR76))</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE76" s="124" t="str">
         <f>VLOOKUP("Ghana",T,lang,FALSE)</f>
@@ -56701,7 +56777,7 @@
       </c>
       <c r="AF76" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE76 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG76" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE76 &amp; "_draw")</f>
@@ -56713,7 +56789,7 @@
       </c>
       <c r="AI76" s="123">
         <f>SUMIF($E$7:$E$78,$AE76,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE76,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ76" s="123">
         <f>SUMIF($E$7:$E$78,$AE76,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE76,$F$7:$F$78)</f>
@@ -56721,23 +56797,23 @@
       </c>
       <c r="AL76" s="123">
         <f>AI76-AJ76</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM76" s="123">
         <f>AL76-AL78</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN76" s="123">
         <f>AF76*3+AG76</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO76" s="123">
         <f>AN76/AN78*10+BA76</f>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AP76" s="123">
         <f>AO76*10000000+BI76*100+AM76/AM78*10+AI76/AI78*1++IF(AQ76=0,ROW(),AQ76)/2000000</f>
-        <v>6.7315499999999993E-4</v>
+        <v>75000006.200673163</v>
       </c>
       <c r="AQ76" s="126">
         <f>VLOOKUP(AE76,db_fifarank,2,FALSE)</f>
@@ -56745,7 +56821,7 @@
       </c>
       <c r="AR76" s="125">
         <f>AP76/AP78</f>
-        <v>6.7254098017321647E-4</v>
+        <v>0.9999999519968088</v>
       </c>
       <c r="AT76" s="126" cm="1">
         <f t="array" ref="AT76">SUMPRODUCT(($S$7:$S$78=AE76&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE76&amp;"_win")*($U$7:$U$78))</f>
@@ -56845,7 +56921,7 @@
       </c>
       <c r="K77" s="23">
         <f>L77+M77+N77</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="23">
         <f>VLOOKUP(3,AD74:AN77,3,FALSE)</f>
@@ -56857,11 +56933,11 @@
       </c>
       <c r="N77" s="23">
         <f>VLOOKUP(3,AD74:AN77,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O77" s="23" t="str">
         <f>VLOOKUP(3,AD74:AN77,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD74:AN77,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>0 - 1</v>
       </c>
       <c r="P77" s="34">
         <f>L77*3+M77</f>
@@ -56929,7 +57005,7 @@
       </c>
       <c r="AH77" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE77 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI77" s="123">
         <f>SUMIF($E$7:$E$78,$AE77,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE77,$G$7:$G$78)</f>
@@ -56937,15 +57013,15 @@
       </c>
       <c r="AJ77" s="123">
         <f>SUMIF($E$7:$E$78,$AE77,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE77,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL77" s="123">
         <f>AI77-AJ77</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM77" s="123">
         <f>AL77-AL78</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN77" s="123">
         <f>AF77*3+AG77</f>
@@ -56957,7 +57033,7 @@
       </c>
       <c r="AP77" s="123">
         <f>AO77*10000000+BI77*100+AM77/AM78*10+AI77/AI78*1++IF(AQ77=0,ROW(),AQ77)/2000000</f>
-        <v>7.7032000000000001E-4</v>
+        <v>2.00077032</v>
       </c>
       <c r="AQ77" s="126">
         <f>VLOOKUP(AE77,db_fifarank,2,FALSE)</f>
@@ -56965,7 +57041,7 @@
       </c>
       <c r="AR77" s="125">
         <f>AP77/AP78</f>
-        <v>7.6961735090288596E-4</v>
+        <v>2.6676934113889205E-8</v>
       </c>
       <c r="AT77" s="126" cm="1">
         <f t="array" ref="AT77">SUMPRODUCT(($S$7:$S$78=AE77&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE77&amp;"_win")*($U$7:$U$78))</f>
@@ -57061,11 +57137,11 @@
       <c r="I78" s="69"/>
       <c r="J78" s="35" t="str">
         <f>VLOOKUP(4,AD74:AN77,2,FALSE)</f>
-        <v>Ghana</v>
+        <v>Croatia</v>
       </c>
       <c r="K78" s="36">
         <f>L78+M78+N78</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="36">
         <f>VLOOKUP(4,AD74:AN77,3,FALSE)</f>
@@ -57077,11 +57153,11 @@
       </c>
       <c r="N78" s="36">
         <f>VLOOKUP(4,AD74:AN77,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O78" s="36" t="str">
         <f>VLOOKUP(4,AD74:AN77,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD74:AN77,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>2 - 4</v>
       </c>
       <c r="P78" s="37">
         <f>L78*3+M78</f>
@@ -57133,7 +57209,7 @@
       </c>
       <c r="AF78" s="123">
         <f t="shared" ref="AF78:AH78" si="36">MAX(AF74:AF77)-MIN(AF74:AF77)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG78" s="123">
         <f t="shared" si="36"/>
@@ -57141,31 +57217,31 @@
       </c>
       <c r="AH78" s="123">
         <f t="shared" si="36"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI78" s="123">
         <f>MAX(AI74:AI77)+1</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AL78" s="123">
         <f>MIN(AL74:AL77)</f>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AM78" s="123">
         <f>MAX(AM74:AM77)+1</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AN78" s="123">
         <f>MAX(AN74:AN77)+1</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AO78" s="123">
         <f>MAX(AO74:AO77)+1</f>
-        <v>1</v>
+        <v>8.5</v>
       </c>
       <c r="AP78" s="123">
         <f>MAX(AP74:AP77)+1</f>
-        <v>1.000912985</v>
+        <v>75000009.800912976</v>
       </c>
       <c r="AT78" s="126">
         <f>MAX(AT74:AT77)-MIN(AT74:AT77)+1</f>
@@ -57274,7 +57350,7 @@
       </c>
       <c r="AD80" s="123">
         <f>COUNTIF($AP$80:$AP$91,CONCATENATE("&gt;=",AP80))</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE80" s="124" t="str">
         <f>J11</f>
@@ -57286,7 +57362,7 @@
       </c>
       <c r="AG80" s="123">
         <f>VLOOKUP($AE80,$AE$8:$AQ$78,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH80" s="123">
         <f>VLOOKUP($AE80,$AE$8:$AQ$78,4,FALSE)</f>
@@ -57294,11 +57370,11 @@
       </c>
       <c r="AI80" s="123">
         <f>VLOOKUP($AE80,$AE$8:$AQ$78,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ80" s="123">
         <f>VLOOKUP($AE80,$AE$8:$AQ$78,6,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK80" s="123" t="s">
         <v>3180</v>
@@ -57309,15 +57385,15 @@
       </c>
       <c r="AM80" s="123">
         <f>AL80-$AL$92</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN80" s="123">
         <f>VLOOKUP($AE80,$AE$8:$AQ$78,10,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP80" s="123">
         <f>AN80/AN92*10000+AM80/AM92*1000+AI80/AI92*100+IF(AQ80=0,ROW(),AQ80)/2000000</f>
-        <v>366.66741735666665</v>
+        <v>3028.5721792614286</v>
       </c>
       <c r="AQ80" s="126">
         <f t="shared" ref="AQ80:AQ91" si="37">VLOOKUP($AE80,$AE$8:$AQ$78,13,FALSE)</f>
@@ -57348,39 +57424,39 @@
       <c r="I81" s="69"/>
       <c r="J81" s="96" t="str">
         <f>VLOOKUP(1,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓕ Japan</v>
+        <v>Ⓕ Sweden</v>
       </c>
       <c r="K81" s="97">
         <f>L81+M81+N81</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L81" s="97">
         <f>VLOOKUP(1,$AD$80:$AN$91,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M81" s="97">
         <f>VLOOKUP(1,$AD$80:$AN$91,4,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N81" s="97">
         <f>VLOOKUP(1,$AD$80:$AN$91,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O81" s="97" t="str">
         <f>VLOOKUP(1,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(1,$AD$80:$AN$91,7,FALSE)</f>
-        <v>2 - 2</v>
+        <v>6 - 6</v>
       </c>
       <c r="P81" s="98">
         <f>L81*3+M81</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD81" s="123">
         <f t="shared" ref="AD81:AD91" si="38">COUNTIF($AP$80:$AP$91,CONCATENATE("&gt;=",AP81))</f>
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AE81" s="124" t="str">
         <f>J17</f>
-        <v>Qatar</v>
+        <v>Bosnia and Herzegovina</v>
       </c>
       <c r="AF81" s="123">
         <f t="shared" ref="AF81:AF91" si="39">VLOOKUP($AE81,$AE$8:$AQ$78,2,FALSE)</f>
@@ -57392,26 +57468,26 @@
       </c>
       <c r="AH81" s="123">
         <f t="shared" ref="AH81:AH90" si="40">VLOOKUP($AE81,$AE$8:$AQ$78,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI81" s="123">
         <f t="shared" ref="AI81:AI90" si="41">VLOOKUP($AE81,$AE$8:$AQ$78,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ81" s="123">
         <f t="shared" ref="AJ81:AJ90" si="42">VLOOKUP($AE81,$AE$8:$AQ$78,6,FALSE)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AK81" s="123" t="s">
         <v>3181</v>
       </c>
       <c r="AL81" s="123">
         <f t="shared" ref="AL81:AL90" si="43">VLOOKUP($AE81,$AE$8:$AQ$78,8,FALSE)</f>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AM81" s="123">
         <f t="shared" ref="AM81:AM91" si="44">AL81-$AL$92</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN81" s="123">
         <f t="shared" ref="AN81:AN90" si="45">VLOOKUP($AE81,$AE$8:$AQ$78,10,FALSE)</f>
@@ -57419,23 +57495,23 @@
       </c>
       <c r="AP81" s="123">
         <f>AN81/AN92*10000+AM81/AM92*1000+AI81/AI92*100+IF(AQ81=0,ROW(),AQ81)/2000000</f>
-        <v>5700.00072748</v>
+        <v>2528.5721214914283</v>
       </c>
       <c r="AQ81" s="126">
         <f t="shared" si="37"/>
-        <v>1454.96</v>
+        <v>1385.84</v>
       </c>
       <c r="AR81" s="125" t="str">
         <f>AR80&amp;IF(AD81&lt;=8,RIGHT(AK81,1),"")</f>
-        <v>AB</v>
+        <v>A</v>
       </c>
       <c r="AS81" s="129" t="str">
         <f t="shared" ref="AS81:AS91" si="46">IF(AD81&lt;=8,AE81,"")</f>
-        <v>Qatar</v>
+        <v/>
       </c>
       <c r="AT81" s="130" t="str">
         <f>"Ⓑ "&amp;AE81</f>
-        <v>Ⓑ Qatar</v>
+        <v>Ⓑ Bosnia and Herzegovina</v>
       </c>
     </row>
     <row r="82" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -57450,23 +57526,23 @@
       <c r="I82" s="69"/>
       <c r="J82" s="99" t="str">
         <f>VLOOKUP(2,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓒ Morocco</v>
+        <v>Ⓒ Scotland</v>
       </c>
       <c r="K82" s="100">
         <f t="shared" ref="K82:K92" si="47">L82+M82+N82</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L82" s="100">
         <f>VLOOKUP(2,$AD$80:$AN$91,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M82" s="100">
         <f>VLOOKUP(2,$AD$80:$AN$91,4,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N82" s="100">
         <f>VLOOKUP(2,$AD$80:$AN$91,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O82" s="100" t="str">
         <f>VLOOKUP(2,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(2,$AD$80:$AN$91,7,FALSE)</f>
@@ -57474,7 +57550,7 @@
       </c>
       <c r="P82" s="101">
         <f t="shared" ref="P82:P92" si="48">L82*3+M82</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD82" s="123">
         <f t="shared" si="38"/>
@@ -57482,19 +57558,19 @@
       </c>
       <c r="AE82" s="124" t="str">
         <f>J23</f>
-        <v>Morocco</v>
+        <v>Scotland</v>
       </c>
       <c r="AF82" s="123">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG82" s="123">
         <f t="shared" ref="AG82:AG91" si="49">VLOOKUP($AE82,$AE$8:$AQ$78,3,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH82" s="123">
         <f t="shared" si="40"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI82" s="123">
         <f t="shared" si="41"/>
@@ -57513,84 +57589,84 @@
       </c>
       <c r="AM82" s="123">
         <f t="shared" si="44"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN82" s="123">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AP82" s="123">
         <f>AN82/AN92*10000+AM82/AM92*1000+AI82/AI92*100+IF(AQ82=0,ROW(),AQ82)/2000000</f>
-        <v>5700.0008779350001</v>
+        <v>8264.286463460714</v>
       </c>
       <c r="AQ82" s="126">
         <f t="shared" si="37"/>
-        <v>1755.87</v>
+        <v>1498.35</v>
       </c>
       <c r="AR82" s="125" t="str">
         <f t="shared" ref="AR82:AR91" si="50">AR81&amp;IF(AD82&lt;=8,RIGHT(AK82,1),"")</f>
-        <v>ABC</v>
+        <v>AC</v>
       </c>
       <c r="AS82" s="129" t="str">
         <f t="shared" si="46"/>
-        <v>Morocco</v>
+        <v>Scotland</v>
       </c>
       <c r="AT82" s="130" t="str">
         <f>"Ⓒ "&amp;AE82</f>
-        <v>Ⓒ Morocco</v>
+        <v>Ⓒ Scotland</v>
       </c>
     </row>
     <row r="83" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="73"/>
       <c r="B83" s="73"/>
-      <c r="C83" s="164" t="s">
+      <c r="C83" s="186" t="s">
         <v>3183</v>
       </c>
-      <c r="D83" s="165"/>
-      <c r="E83" s="165"/>
-      <c r="F83" s="165"/>
-      <c r="G83" s="166"/>
+      <c r="D83" s="187"/>
+      <c r="E83" s="187"/>
+      <c r="F83" s="187"/>
+      <c r="G83" s="188"/>
       <c r="H83" s="75"/>
       <c r="I83" s="69"/>
       <c r="J83" s="99" t="str">
         <f>VLOOKUP(3,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓖ Belgium</v>
+        <v>Ⓓ Paraguay</v>
       </c>
       <c r="K83" s="100">
         <f t="shared" si="47"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L83" s="100">
         <f>VLOOKUP(3,$AD$80:$AN$91,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83" s="100">
         <f>VLOOKUP(3,$AD$80:$AN$91,4,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N83" s="100">
         <f>VLOOKUP(3,$AD$80:$AN$91,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O83" s="100" t="str">
         <f>VLOOKUP(3,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(3,$AD$80:$AN$91,7,FALSE)</f>
-        <v>1 - 1</v>
+        <v>2 - 4</v>
       </c>
       <c r="P83" s="101">
         <f t="shared" si="48"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD83" s="123">
         <f t="shared" si="38"/>
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AE83" s="124" t="str">
         <f>J29</f>
-        <v>Turkey</v>
+        <v>Paraguay</v>
       </c>
       <c r="AF83" s="123">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG83" s="123">
         <f t="shared" si="49"/>
@@ -57602,11 +57678,11 @@
       </c>
       <c r="AI83" s="123">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ83" s="123">
         <f t="shared" si="42"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AK83" s="123" t="s">
         <v>3184</v>
@@ -57617,50 +57693,50 @@
       </c>
       <c r="AM83" s="123">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN83" s="123">
         <f t="shared" si="45"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP83" s="123">
         <f>AN83/AN92*10000+AM83/AM92*1000+AI83/AI92*100+IF(AQ83=0,ROW(),AQ83)/2000000</f>
-        <v>7.9951999999999996E-4</v>
+        <v>7778.5721803214283</v>
       </c>
       <c r="AQ83" s="126">
         <f t="shared" si="37"/>
-        <v>1599.04</v>
+        <v>1503.5</v>
       </c>
       <c r="AR83" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABC</v>
+        <v>ACD</v>
       </c>
       <c r="AS83" s="129" t="str">
         <f t="shared" si="46"/>
-        <v/>
+        <v>Paraguay</v>
       </c>
       <c r="AT83" s="130" t="str">
         <f>"Ⓓ "&amp;AE83</f>
-        <v>Ⓓ Turkey</v>
+        <v>Ⓓ Paraguay</v>
       </c>
     </row>
     <row r="84" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="73"/>
       <c r="B84" s="73"/>
-      <c r="C84" s="167"/>
-      <c r="D84" s="168"/>
-      <c r="E84" s="168"/>
-      <c r="F84" s="168"/>
-      <c r="G84" s="169"/>
+      <c r="C84" s="189"/>
+      <c r="D84" s="190"/>
+      <c r="E84" s="190"/>
+      <c r="F84" s="190"/>
+      <c r="G84" s="191"/>
       <c r="H84" s="75"/>
       <c r="I84" s="69"/>
       <c r="J84" s="99" t="str">
         <f>VLOOKUP(4,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓑ Qatar</v>
+        <v>Ⓗ Cape Verde</v>
       </c>
       <c r="K84" s="100">
         <f t="shared" si="47"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L84" s="100">
         <f>VLOOKUP(4,$AD$80:$AN$91,3,FALSE)</f>
@@ -57668,7 +57744,7 @@
       </c>
       <c r="M84" s="100">
         <f>VLOOKUP(4,$AD$80:$AN$91,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N84" s="100">
         <f>VLOOKUP(4,$AD$80:$AN$91,5,FALSE)</f>
@@ -57676,11 +57752,11 @@
       </c>
       <c r="O84" s="100" t="str">
         <f>VLOOKUP(4,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(4,$AD$80:$AN$91,7,FALSE)</f>
-        <v>1 - 1</v>
+        <v>2 - 2</v>
       </c>
       <c r="P84" s="101">
         <f t="shared" si="48"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R84" s="123">
         <f>DATE(2026,12,3)+TIME(4,0,0)+gmt_delta</f>
@@ -57696,7 +57772,7 @@
       </c>
       <c r="AD84" s="123">
         <f t="shared" si="38"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE84" s="124" t="str">
         <f>J35</f>
@@ -57708,7 +57784,7 @@
       </c>
       <c r="AG84" s="123">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH84" s="123">
         <f t="shared" si="40"/>
@@ -57731,15 +57807,15 @@
       </c>
       <c r="AM84" s="123">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN84" s="123">
         <f t="shared" si="45"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP84" s="123">
         <f>AN84/AN92*10000+AM84/AM92*1000+AI84/AI92*100+IF(AQ84=0,ROW(),AQ84)/2000000</f>
-        <v>333.33413072333332</v>
+        <v>3000.0007973900001</v>
       </c>
       <c r="AQ84" s="126">
         <f t="shared" si="37"/>
@@ -57747,11 +57823,11 @@
       </c>
       <c r="AR84" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABC</v>
+        <v>ACDE</v>
       </c>
       <c r="AS84" s="129" t="str">
         <f t="shared" si="46"/>
-        <v/>
+        <v>Ecuador</v>
       </c>
       <c r="AT84" s="130" t="str">
         <f>"Ⓔ "&amp;AE84</f>
@@ -57761,20 +57837,20 @@
     <row r="85" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="73"/>
       <c r="B85" s="73"/>
-      <c r="C85" s="167"/>
-      <c r="D85" s="168"/>
-      <c r="E85" s="168"/>
-      <c r="F85" s="168"/>
-      <c r="G85" s="169"/>
+      <c r="C85" s="189"/>
+      <c r="D85" s="190"/>
+      <c r="E85" s="190"/>
+      <c r="F85" s="190"/>
+      <c r="G85" s="191"/>
       <c r="H85" s="75"/>
       <c r="I85" s="69"/>
       <c r="J85" s="99" t="str">
         <f>VLOOKUP(5,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓗ Spain</v>
+        <v>Ⓖ Belgium</v>
       </c>
       <c r="K85" s="100">
         <f t="shared" si="47"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L85" s="100">
         <f>VLOOKUP(5,$AD$80:$AN$91,3,FALSE)</f>
@@ -57782,7 +57858,7 @@
       </c>
       <c r="M85" s="100">
         <f>VLOOKUP(5,$AD$80:$AN$91,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N85" s="100">
         <f>VLOOKUP(5,$AD$80:$AN$91,5,FALSE)</f>
@@ -57790,11 +57866,11 @@
       </c>
       <c r="O85" s="100" t="str">
         <f>VLOOKUP(5,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(5,$AD$80:$AN$91,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 1</v>
       </c>
       <c r="P85" s="101">
         <f t="shared" si="48"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R85" s="123">
         <f>DATE(2026,12,3)+TIME(8,0,0)+gmt_delta</f>
@@ -57814,27 +57890,27 @@
       </c>
       <c r="AE85" s="124" t="str">
         <f>J41</f>
-        <v>Japan</v>
+        <v>Sweden</v>
       </c>
       <c r="AF85" s="123">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG85" s="123">
         <f t="shared" si="49"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH85" s="123">
         <f t="shared" si="40"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI85" s="123">
         <f t="shared" si="41"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AJ85" s="123">
         <f t="shared" si="42"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AK85" s="123" t="s">
         <v>3186</v>
@@ -57845,50 +57921,50 @@
       </c>
       <c r="AM85" s="123">
         <f t="shared" si="44"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN85" s="123">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AP85" s="123">
         <f>AN85/AN92*10000+AM85/AM92*1000+AI85/AI92*100+IF(AQ85=0,ROW(),AQ85)/2000000</f>
-        <v>5733.3341635483339</v>
+        <v>8335.715043099286</v>
       </c>
       <c r="AQ85" s="126">
         <f t="shared" si="37"/>
-        <v>1660.43</v>
+        <v>1514.77</v>
       </c>
       <c r="AR85" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABCF</v>
+        <v>ACDEF</v>
       </c>
       <c r="AS85" s="129" t="str">
         <f t="shared" si="46"/>
-        <v>Japan</v>
+        <v>Sweden</v>
       </c>
       <c r="AT85" s="130" t="str">
         <f>"Ⓕ "&amp;AE85</f>
-        <v>Ⓕ Japan</v>
+        <v>Ⓕ Sweden</v>
       </c>
     </row>
     <row r="86" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="73"/>
       <c r="B86" s="73"/>
-      <c r="C86" s="167"/>
-      <c r="D86" s="168"/>
-      <c r="E86" s="168"/>
-      <c r="F86" s="168"/>
-      <c r="G86" s="169"/>
+      <c r="C86" s="189"/>
+      <c r="D86" s="190"/>
+      <c r="E86" s="190"/>
+      <c r="F86" s="190"/>
+      <c r="G86" s="191"/>
       <c r="H86" s="75"/>
       <c r="I86" s="69"/>
       <c r="J86" s="99" t="str">
         <f>VLOOKUP(6,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓚ Colombia</v>
+        <v>Ⓚ DR Congo</v>
       </c>
       <c r="K86" s="100">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="100">
         <f>VLOOKUP(6,$AD$80:$AN$91,3,FALSE)</f>
@@ -57896,7 +57972,7 @@
       </c>
       <c r="M86" s="100">
         <f>VLOOKUP(6,$AD$80:$AN$91,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N86" s="100">
         <f>VLOOKUP(6,$AD$80:$AN$91,5,FALSE)</f>
@@ -57904,11 +57980,11 @@
       </c>
       <c r="O86" s="100" t="str">
         <f>VLOOKUP(6,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(6,$AD$80:$AN$91,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>1 - 1</v>
       </c>
       <c r="P86" s="101">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R86" s="123">
         <f>DATE(2026,12,4)+TIME(8,0,0)+gmt_delta</f>
@@ -57924,7 +58000,7 @@
       </c>
       <c r="AD86" s="123">
         <f t="shared" si="38"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE86" s="124" t="str">
         <f>J47</f>
@@ -57936,7 +58012,7 @@
       </c>
       <c r="AG86" s="123">
         <f t="shared" si="49"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH86" s="123">
         <f t="shared" si="40"/>
@@ -57959,15 +58035,15 @@
       </c>
       <c r="AM86" s="123">
         <f t="shared" si="44"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN86" s="123">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP86" s="123">
         <f>AN86/AN92*10000+AM86/AM92*1000+AI86/AI92*100+IF(AQ86=0,ROW(),AQ86)/2000000</f>
-        <v>5700.0008673550001</v>
+        <v>5764.2865816407148</v>
       </c>
       <c r="AQ86" s="126">
         <f t="shared" si="37"/>
@@ -57975,7 +58051,7 @@
       </c>
       <c r="AR86" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABCFG</v>
+        <v>ACDEFG</v>
       </c>
       <c r="AS86" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57989,20 +58065,20 @@
     <row r="87" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="73"/>
       <c r="B87" s="73"/>
-      <c r="C87" s="167"/>
-      <c r="D87" s="168"/>
-      <c r="E87" s="168"/>
-      <c r="F87" s="168"/>
-      <c r="G87" s="169"/>
+      <c r="C87" s="189"/>
+      <c r="D87" s="190"/>
+      <c r="E87" s="190"/>
+      <c r="F87" s="190"/>
+      <c r="G87" s="191"/>
       <c r="H87" s="75"/>
       <c r="I87" s="69"/>
       <c r="J87" s="99" t="str">
         <f>VLOOKUP(7,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓛ Panama</v>
+        <v>Ⓐ Czech Republic</v>
       </c>
       <c r="K87" s="100">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L87" s="100">
         <f>VLOOKUP(7,$AD$80:$AN$91,3,FALSE)</f>
@@ -58010,19 +58086,19 @@
       </c>
       <c r="M87" s="100">
         <f>VLOOKUP(7,$AD$80:$AN$91,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N87" s="100">
         <f>VLOOKUP(7,$AD$80:$AN$91,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O87" s="100" t="str">
         <f>VLOOKUP(7,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(7,$AD$80:$AN$91,7,FALSE)</f>
-        <v>0 - 0</v>
+        <v>2 - 3</v>
       </c>
       <c r="P87" s="101">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R87" s="123">
         <f>DATE(2026,12,4)+TIME(4,0,0)+gmt_delta</f>
@@ -58038,11 +58114,11 @@
       </c>
       <c r="AD87" s="123">
         <f t="shared" si="38"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE87" s="124" t="str">
         <f>J53</f>
-        <v>Spain</v>
+        <v>Cape Verde</v>
       </c>
       <c r="AF87" s="123">
         <f t="shared" si="39"/>
@@ -58050,7 +58126,7 @@
       </c>
       <c r="AG87" s="123">
         <f t="shared" si="49"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH87" s="123">
         <f t="shared" si="40"/>
@@ -58058,11 +58134,11 @@
       </c>
       <c r="AI87" s="123">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ87" s="123">
         <f t="shared" si="42"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK87" s="123" t="s">
         <v>3188</v>
@@ -58073,50 +58149,50 @@
       </c>
       <c r="AM87" s="123">
         <f t="shared" si="44"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN87" s="123">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP87" s="123">
         <f>AN87/AN92*10000+AM87/AM92*1000+AI87/AI92*100+IF(AQ87=0,ROW(),AQ87)/2000000</f>
-        <v>5666.6676048666668</v>
+        <v>5778.5721116364284</v>
       </c>
       <c r="AQ87" s="126">
         <f t="shared" si="37"/>
-        <v>1876.4</v>
+        <v>1366.13</v>
       </c>
       <c r="AR87" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABCFGH</v>
+        <v>ACDEFGH</v>
       </c>
       <c r="AS87" s="129" t="str">
         <f t="shared" si="46"/>
-        <v>Spain</v>
+        <v>Cape Verde</v>
       </c>
       <c r="AT87" s="130" t="str">
         <f>"Ⓗ "&amp;AE87</f>
-        <v>Ⓗ Spain</v>
+        <v>Ⓗ Cape Verde</v>
       </c>
     </row>
     <row r="88" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="73"/>
       <c r="B88" s="73"/>
-      <c r="C88" s="170"/>
-      <c r="D88" s="171"/>
-      <c r="E88" s="171"/>
-      <c r="F88" s="171"/>
-      <c r="G88" s="172"/>
+      <c r="C88" s="192"/>
+      <c r="D88" s="193"/>
+      <c r="E88" s="193"/>
+      <c r="F88" s="193"/>
+      <c r="G88" s="194"/>
       <c r="H88" s="75"/>
       <c r="I88" s="69"/>
       <c r="J88" s="99" t="str">
         <f>VLOOKUP(8,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓐ Czech Republic</v>
+        <v>Ⓔ Ecuador</v>
       </c>
       <c r="K88" s="100">
         <f t="shared" si="47"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L88" s="100">
         <f>VLOOKUP(8,$AD$80:$AN$91,3,FALSE)</f>
@@ -58124,7 +58200,7 @@
       </c>
       <c r="M88" s="100">
         <f>VLOOKUP(8,$AD$80:$AN$91,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N88" s="100">
         <f>VLOOKUP(8,$AD$80:$AN$91,5,FALSE)</f>
@@ -58132,11 +58208,11 @@
       </c>
       <c r="O88" s="100" t="str">
         <f>VLOOKUP(8,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(8,$AD$80:$AN$91,7,FALSE)</f>
-        <v>1 - 2</v>
+        <v>0 - 1</v>
       </c>
       <c r="P88" s="101">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R88" s="123">
         <f>DATE(2026,12,5)+TIME(4,0,0)+gmt_delta</f>
@@ -58152,7 +58228,7 @@
       </c>
       <c r="AD88" s="123">
         <f t="shared" si="38"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AE88" s="124" t="str">
         <f>J59</f>
@@ -58187,7 +58263,7 @@
       </c>
       <c r="AM88" s="123">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN88" s="123">
         <f t="shared" si="45"/>
@@ -58195,7 +58271,7 @@
       </c>
       <c r="AP88" s="123">
         <f>AN88/AN92*10000+AM88/AM92*1000+AI88/AI92*100+IF(AQ88=0,ROW(),AQ88)/2000000</f>
-        <v>33.334177828333331</v>
+        <v>264.2865587807143</v>
       </c>
       <c r="AQ88" s="126">
         <f t="shared" si="37"/>
@@ -58203,7 +58279,7 @@
       </c>
       <c r="AR88" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABCFGH</v>
+        <v>ACDEFGH</v>
       </c>
       <c r="AS88" s="129" t="str">
         <f t="shared" si="46"/>
@@ -58226,11 +58302,11 @@
       <c r="I89" s="69"/>
       <c r="J89" s="102" t="str">
         <f>VLOOKUP(9,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓔ Ecuador</v>
+        <v>Ⓑ Bosnia and Herzegovina</v>
       </c>
       <c r="K89" s="103">
         <f t="shared" si="47"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L89" s="103">
         <f>VLOOKUP(9,$AD$80:$AN$91,3,FALSE)</f>
@@ -58238,7 +58314,7 @@
       </c>
       <c r="M89" s="103">
         <f>VLOOKUP(9,$AD$80:$AN$91,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N89" s="103">
         <f>VLOOKUP(9,$AD$80:$AN$91,5,FALSE)</f>
@@ -58246,11 +58322,11 @@
       </c>
       <c r="O89" s="103" t="str">
         <f>VLOOKUP(9,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(9,$AD$80:$AN$91,7,FALSE)</f>
-        <v>0 - 1</v>
+        <v>2 - 5</v>
       </c>
       <c r="P89" s="104">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R89" s="123">
         <f>DATE(2026,12,5)+TIME(8,0,0)+gmt_delta</f>
@@ -58266,7 +58342,7 @@
       </c>
       <c r="AD89" s="123">
         <f t="shared" si="38"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AE89" s="124" t="str">
         <f>J65</f>
@@ -58301,7 +58377,7 @@
       </c>
       <c r="AM89" s="123">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN89" s="123">
         <f t="shared" si="45"/>
@@ -58309,7 +58385,7 @@
       </c>
       <c r="AP89" s="123">
         <f>AN89/AN92*10000+AM89/AM92*1000+AI89/AI92*100+IF(AQ89=0,ROW(),AQ89)/2000000</f>
-        <v>33.334029058333329</v>
+        <v>264.28641001071429</v>
       </c>
       <c r="AQ89" s="126">
         <f t="shared" si="37"/>
@@ -58317,7 +58393,7 @@
       </c>
       <c r="AR89" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABCFGH</v>
+        <v>ACDEFGH</v>
       </c>
       <c r="AS89" s="129" t="str">
         <f t="shared" si="46"/>
@@ -58340,7 +58416,7 @@
       <c r="I90" s="69"/>
       <c r="J90" s="102" t="str">
         <f>VLOOKUP(10,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓘ Senegal</v>
+        <v>Ⓛ Panama</v>
       </c>
       <c r="K90" s="103">
         <f t="shared" si="47"/>
@@ -58360,7 +58436,7 @@
       </c>
       <c r="O90" s="103" t="str">
         <f>VLOOKUP(10,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(10,$AD$80:$AN$91,7,FALSE)</f>
-        <v>1 - 3</v>
+        <v>0 - 1</v>
       </c>
       <c r="P90" s="104">
         <f t="shared" si="48"/>
@@ -58384,7 +58460,7 @@
       </c>
       <c r="AE90" s="124" t="str">
         <f>J71</f>
-        <v>Colombia</v>
+        <v>DR Congo</v>
       </c>
       <c r="AF90" s="123">
         <f t="shared" si="39"/>
@@ -58392,7 +58468,7 @@
       </c>
       <c r="AG90" s="123">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH90" s="123">
         <f t="shared" si="40"/>
@@ -58400,11 +58476,11 @@
       </c>
       <c r="AI90" s="123">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ90" s="123">
         <f t="shared" si="42"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK90" s="123" t="s">
         <v>3191</v>
@@ -58415,31 +58491,31 @@
       </c>
       <c r="AM90" s="123">
         <f t="shared" si="44"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN90" s="123">
         <f t="shared" si="45"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP90" s="123">
         <f>AN90/AN92*10000+AM90/AM92*1000+AI90/AI92*100+IF(AQ90=0,ROW(),AQ90)/2000000</f>
-        <v>666.66751321166657</v>
+        <v>3264.2864534607143</v>
       </c>
       <c r="AQ90" s="126">
         <f t="shared" si="37"/>
-        <v>1693.09</v>
+        <v>1478.35</v>
       </c>
       <c r="AR90" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABCFGHK</v>
+        <v>ACDEFGHK</v>
       </c>
       <c r="AS90" s="129" t="str">
         <f t="shared" si="46"/>
-        <v>Colombia</v>
+        <v>DR Congo</v>
       </c>
       <c r="AT90" s="130" t="str">
         <f>"Ⓚ "&amp;AE90</f>
-        <v>Ⓚ Colombia</v>
+        <v>Ⓚ DR Congo</v>
       </c>
     </row>
     <row r="91" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -58454,7 +58530,7 @@
       <c r="I91" s="69"/>
       <c r="J91" s="102" t="str">
         <f>VLOOKUP(11,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓙ Jordan</v>
+        <v>Ⓘ Senegal</v>
       </c>
       <c r="K91" s="103">
         <f t="shared" si="47"/>
@@ -58494,7 +58570,7 @@
       </c>
       <c r="AD91" s="123">
         <f t="shared" si="38"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE91" s="124" t="str">
         <f>J77</f>
@@ -58510,7 +58586,7 @@
       </c>
       <c r="AH91" s="123">
         <f>VLOOKUP($AE91,$AE$8:$AQ$78,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI91" s="123">
         <f>VLOOKUP($AE91,$AE$8:$AQ$78,5,FALSE)</f>
@@ -58518,14 +58594,14 @@
       </c>
       <c r="AJ91" s="123">
         <f>VLOOKUP($AE91,$AE$8:$AQ$78,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK91" s="123" t="s">
         <v>3192</v>
       </c>
       <c r="AL91" s="123">
         <f>VLOOKUP($AE91,$AE$8:$AQ$78,8,FALSE)</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM91" s="123">
         <f t="shared" si="44"/>
@@ -58537,7 +58613,7 @@
       </c>
       <c r="AP91" s="123">
         <f>AN91/AN92*10000+AM91/AM92*1000+AI91/AI92*100+IF(AQ91=0,ROW(),AQ91)/2000000</f>
-        <v>666.66743698666664</v>
+        <v>500.00077032000002</v>
       </c>
       <c r="AQ91" s="126">
         <f t="shared" si="37"/>
@@ -58545,11 +58621,11 @@
       </c>
       <c r="AR91" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABCFGHKL</v>
+        <v>ACDEFGHK</v>
       </c>
       <c r="AS91" s="129" t="str">
         <f t="shared" si="46"/>
-        <v>Panama</v>
+        <v/>
       </c>
       <c r="AT91" s="130" t="str">
         <f>"Ⓛ "&amp;AE91</f>
@@ -58568,7 +58644,7 @@
       <c r="I92" s="69"/>
       <c r="J92" s="105" t="str">
         <f>VLOOKUP(12,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓓ Turkey</v>
+        <v>Ⓙ Jordan</v>
       </c>
       <c r="K92" s="106">
         <f t="shared" si="47"/>
@@ -58588,7 +58664,7 @@
       </c>
       <c r="O92" s="106" t="str">
         <f>VLOOKUP(12,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(12,$AD$80:$AN$91,7,FALSE)</f>
-        <v>0 - 2</v>
+        <v>1 - 3</v>
       </c>
       <c r="P92" s="107">
         <f t="shared" si="48"/>
@@ -58596,11 +58672,11 @@
       </c>
       <c r="AF92" s="123">
         <f>MAX(AF80:AF91)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG92" s="123">
         <f>MAX(AG80:AG91)+1</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH92" s="123">
         <f>MAX(AH80:AH91)+1</f>
@@ -58608,23 +58684,23 @@
       </c>
       <c r="AI92" s="123">
         <f>MAX(AI80:AI91)+1</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AJ92" s="123">
         <f>MAX(AJ80:AJ91)+1</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AL92" s="123">
         <f>MIN(AL80:AL91)</f>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AM92" s="123">
         <f>MAX(AM80:AM91)+1</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN92" s="123">
         <f>MAX(AN80:AN91)+1</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AS92" s="126" t="b">
         <f>SUM(K9:K78)=144</f>
@@ -58785,11 +58861,31 @@
   <sheetProtection algorithmName="SHA-512" hashValue="7nWuIQAsd0NKRlhwUK3tOeNHpTch5B5FULy2gxNNaIdJM5RfhFSMzPcx55y+pmM3d73guUy+p5Y+SvIjJZQRaA==" saltValue="Uw23KnM8csnTioq5H8upCA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <dataConsolidate/>
   <mergeCells count="45">
-    <mergeCell ref="BK14:BK15"/>
-    <mergeCell ref="BY16:BY17"/>
-    <mergeCell ref="BK26:BK27"/>
-    <mergeCell ref="BR28:BR29"/>
-    <mergeCell ref="BK22:BK23"/>
+    <mergeCell ref="CK68:CQ69"/>
+    <mergeCell ref="C83:G88"/>
+    <mergeCell ref="BK70:BK71"/>
+    <mergeCell ref="BY48:BY49"/>
+    <mergeCell ref="BY64:BY65"/>
+    <mergeCell ref="CF55:CF56"/>
+    <mergeCell ref="BK58:BK59"/>
+    <mergeCell ref="BR60:BR61"/>
+    <mergeCell ref="BK62:BK63"/>
+    <mergeCell ref="BK66:BK67"/>
+    <mergeCell ref="BR68:BR69"/>
+    <mergeCell ref="BK50:BK51"/>
+    <mergeCell ref="BR52:BR53"/>
+    <mergeCell ref="BK54:BK55"/>
+    <mergeCell ref="CE68:CJ69"/>
+    <mergeCell ref="CF6:CJ7"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="A5:H6"/>
+    <mergeCell ref="J5:P6"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="BR12:BR13"/>
+    <mergeCell ref="BK6:BO7"/>
+    <mergeCell ref="BR6:BV7"/>
+    <mergeCell ref="BY6:CC7"/>
     <mergeCell ref="CF23:CF24"/>
     <mergeCell ref="BK18:BK19"/>
     <mergeCell ref="BR20:BR21"/>
@@ -58805,31 +58901,11 @@
     <mergeCell ref="BK42:BK43"/>
     <mergeCell ref="CM33:CQ34"/>
     <mergeCell ref="CM37:CM38"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="BR12:BR13"/>
-    <mergeCell ref="BK6:BO7"/>
-    <mergeCell ref="BR6:BV7"/>
-    <mergeCell ref="BY6:CC7"/>
-    <mergeCell ref="CF6:CJ7"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="A5:H6"/>
-    <mergeCell ref="J5:P6"/>
-    <mergeCell ref="CK68:CQ69"/>
-    <mergeCell ref="C83:G88"/>
-    <mergeCell ref="BK70:BK71"/>
-    <mergeCell ref="BY48:BY49"/>
-    <mergeCell ref="BY64:BY65"/>
-    <mergeCell ref="CF55:CF56"/>
-    <mergeCell ref="BK58:BK59"/>
-    <mergeCell ref="BR60:BR61"/>
-    <mergeCell ref="BK62:BK63"/>
-    <mergeCell ref="BK66:BK67"/>
-    <mergeCell ref="BR68:BR69"/>
-    <mergeCell ref="BK50:BK51"/>
-    <mergeCell ref="BR52:BR53"/>
-    <mergeCell ref="BK54:BK55"/>
-    <mergeCell ref="CE68:CJ69"/>
+    <mergeCell ref="BK14:BK15"/>
+    <mergeCell ref="BY16:BY17"/>
+    <mergeCell ref="BK26:BK27"/>
+    <mergeCell ref="BR28:BR29"/>
+    <mergeCell ref="BK22:BK23"/>
   </mergeCells>
   <conditionalFormatting sqref="A7:E78">
     <cfRule type="expression" dxfId="228" priority="339">
@@ -60126,11 +60202,11 @@
     <row r="3" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B3" s="109">
         <f>MATCH(C3,C6:C500,0)</f>
-        <v>385</v>
+        <v>283</v>
       </c>
       <c r="C3" s="121" t="str">
         <f>'2026 World Cup'!AR91</f>
-        <v>ABCFGHKL</v>
+        <v>ACDEFGHK</v>
       </c>
       <c r="D3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,2,FALSE)</f>
@@ -60142,7 +60218,7 @@
       </c>
       <c r="F3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,4,FALSE)</f>
-        <v>3B</v>
+        <v>3E</v>
       </c>
       <c r="G3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,5,FALSE)</f>
@@ -60158,7 +60234,7 @@
       </c>
       <c r="J3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,8,FALSE)</f>
-        <v>3L</v>
+        <v>3D</v>
       </c>
       <c r="K3" s="122" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,9,FALSE)</f>

--- a/public/worldcup.xlsx
+++ b/public/worldcup.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rylanpaul/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A30D9966-6EF5-6047-AE09-950073088213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6B4F149-D3DA-2E43-B83F-DAD8DE8EE622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13305,12 +13305,56 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -13391,50 +13435,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -40579,11 +40579,11 @@
       <c r="E18" s="132" t="str">
         <v>Norway</v>
       </c>
-      <c r="F18" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G18" s="81" t="e">
-        <v>#N/A</v>
+      <c r="F18" s="81">
+        <v>3</v>
+      </c>
+      <c r="G18" s="81">
+        <v>2</v>
       </c>
       <c r="H18" s="134" t="str">
         <v>Senegal</v>
@@ -40617,11 +40617,11 @@
       <c r="E19" s="132" t="str">
         <v>France</v>
       </c>
-      <c r="F19" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G19" s="81" t="e">
-        <v>#N/A</v>
+      <c r="F19" s="81">
+        <v>3</v>
+      </c>
+      <c r="G19" s="81">
+        <v>0</v>
       </c>
       <c r="H19" s="134" t="str">
         <v>Iraq</v>
@@ -40655,11 +40655,11 @@
       <c r="E20" s="132" t="str">
         <v>Argentina</v>
       </c>
-      <c r="F20" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G20" s="81" t="e">
-        <v>#N/A</v>
+      <c r="F20" s="81">
+        <v>2</v>
+      </c>
+      <c r="G20" s="81">
+        <v>0</v>
       </c>
       <c r="H20" s="134" t="str">
         <v>Austria</v>
@@ -40693,11 +40693,11 @@
       <c r="E21" s="132" t="str">
         <v>Jordan</v>
       </c>
-      <c r="F21" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G21" s="81" t="e">
-        <v>#N/A</v>
+      <c r="F21" s="81">
+        <v>1</v>
+      </c>
+      <c r="G21" s="81">
+        <v>2</v>
       </c>
       <c r="H21" s="134" t="str">
         <v>Algeria</v>
@@ -40947,25 +40947,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:95" ht="47" x14ac:dyDescent="0.2">
-      <c r="A1" s="171" t="str" cm="1">
+      <c r="A1" s="182" t="str" cm="1">
         <f t="array" ref="A1">INDEX(T,2,lang)</f>
         <v>2026 World Cup Final Tournament Schedule</v>
       </c>
-      <c r="B1" s="171"/>
-      <c r="C1" s="171"/>
-      <c r="D1" s="171"/>
-      <c r="E1" s="171"/>
-      <c r="F1" s="171"/>
-      <c r="G1" s="171"/>
-      <c r="H1" s="171"/>
-      <c r="I1" s="171"/>
-      <c r="J1" s="171"/>
-      <c r="K1" s="171"/>
-      <c r="L1" s="171"/>
-      <c r="M1" s="171"/>
-      <c r="N1" s="171"/>
-      <c r="O1" s="171"/>
-      <c r="P1" s="171"/>
+      <c r="B1" s="182"/>
+      <c r="C1" s="182"/>
+      <c r="D1" s="182"/>
+      <c r="E1" s="182"/>
+      <c r="F1" s="182"/>
+      <c r="G1" s="182"/>
+      <c r="H1" s="182"/>
+      <c r="I1" s="182"/>
+      <c r="J1" s="182"/>
+      <c r="K1" s="182"/>
+      <c r="L1" s="182"/>
+      <c r="M1" s="182"/>
+      <c r="N1" s="182"/>
+      <c r="O1" s="182"/>
+      <c r="P1" s="182"/>
       <c r="S1" s="123"/>
       <c r="T1" s="123"/>
       <c r="AC1" s="123"/>
@@ -41012,11 +41012,11 @@
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
-      <c r="O3" s="172" t="str">
+      <c r="O3" s="183" t="str">
         <f>"Language: " &amp; Settings!C4</f>
         <v>Language: English</v>
       </c>
-      <c r="P3" s="172"/>
+      <c r="P3" s="183"/>
       <c r="S3" s="123"/>
       <c r="T3" s="123"/>
       <c r="AC3" s="123"/>
@@ -41034,43 +41034,43 @@
     </row>
     <row r="4" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:95" x14ac:dyDescent="0.2">
-      <c r="A5" s="173" t="str" cm="1">
+      <c r="A5" s="184" t="str" cm="1">
         <f t="array" ref="A5">INDEX(T,3,lang)</f>
         <v>Group Stage</v>
       </c>
-      <c r="B5" s="174"/>
-      <c r="C5" s="174"/>
-      <c r="D5" s="174"/>
-      <c r="E5" s="174"/>
-      <c r="F5" s="174"/>
-      <c r="G5" s="174"/>
-      <c r="H5" s="175"/>
-      <c r="J5" s="179" t="s">
+      <c r="B5" s="185"/>
+      <c r="C5" s="185"/>
+      <c r="D5" s="185"/>
+      <c r="E5" s="185"/>
+      <c r="F5" s="185"/>
+      <c r="G5" s="185"/>
+      <c r="H5" s="186"/>
+      <c r="J5" s="190" t="s">
         <v>3166</v>
       </c>
-      <c r="K5" s="180"/>
-      <c r="L5" s="180"/>
-      <c r="M5" s="180"/>
-      <c r="N5" s="180"/>
-      <c r="O5" s="180"/>
-      <c r="P5" s="181"/>
+      <c r="K5" s="191"/>
+      <c r="L5" s="191"/>
+      <c r="M5" s="191"/>
+      <c r="N5" s="191"/>
+      <c r="O5" s="191"/>
+      <c r="P5" s="192"/>
     </row>
     <row r="6" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="176"/>
-      <c r="B6" s="177"/>
-      <c r="C6" s="177"/>
-      <c r="D6" s="177"/>
-      <c r="E6" s="177"/>
-      <c r="F6" s="177"/>
-      <c r="G6" s="177"/>
-      <c r="H6" s="178"/>
-      <c r="J6" s="182"/>
-      <c r="K6" s="183"/>
-      <c r="L6" s="183"/>
-      <c r="M6" s="183"/>
-      <c r="N6" s="183"/>
-      <c r="O6" s="183"/>
-      <c r="P6" s="184"/>
+      <c r="A6" s="187"/>
+      <c r="B6" s="188"/>
+      <c r="C6" s="188"/>
+      <c r="D6" s="188"/>
+      <c r="E6" s="188"/>
+      <c r="F6" s="188"/>
+      <c r="G6" s="188"/>
+      <c r="H6" s="189"/>
+      <c r="J6" s="193"/>
+      <c r="K6" s="194"/>
+      <c r="L6" s="194"/>
+      <c r="M6" s="194"/>
+      <c r="N6" s="194"/>
+      <c r="O6" s="194"/>
+      <c r="P6" s="195"/>
       <c r="R6" s="123" t="s">
         <v>3167</v>
       </c>
@@ -41180,37 +41180,37 @@
       <c r="BI6" s="128" t="s">
         <v>3178</v>
       </c>
-      <c r="BK6" s="165" t="s">
+      <c r="BK6" s="176" t="s">
         <v>3179</v>
       </c>
-      <c r="BL6" s="166"/>
-      <c r="BM6" s="166"/>
-      <c r="BN6" s="166"/>
-      <c r="BO6" s="167"/>
-      <c r="BR6" s="165" t="str" cm="1">
+      <c r="BL6" s="177"/>
+      <c r="BM6" s="177"/>
+      <c r="BN6" s="177"/>
+      <c r="BO6" s="178"/>
+      <c r="BR6" s="176" t="str" cm="1">
         <f t="array" ref="BR6">INDEX(T,4,lang)</f>
         <v>Round of 16</v>
       </c>
-      <c r="BS6" s="166"/>
-      <c r="BT6" s="166"/>
-      <c r="BU6" s="166"/>
-      <c r="BV6" s="167"/>
-      <c r="BY6" s="165" t="str" cm="1">
+      <c r="BS6" s="177"/>
+      <c r="BT6" s="177"/>
+      <c r="BU6" s="177"/>
+      <c r="BV6" s="178"/>
+      <c r="BY6" s="176" t="str" cm="1">
         <f t="array" ref="BY6">INDEX(T,5,lang)</f>
         <v>Quarterfinals</v>
       </c>
-      <c r="BZ6" s="166"/>
-      <c r="CA6" s="166"/>
-      <c r="CB6" s="166"/>
-      <c r="CC6" s="167"/>
-      <c r="CF6" s="165" t="str" cm="1">
+      <c r="BZ6" s="177"/>
+      <c r="CA6" s="177"/>
+      <c r="CB6" s="177"/>
+      <c r="CC6" s="178"/>
+      <c r="CF6" s="176" t="str" cm="1">
         <f t="array" ref="CF6">INDEX(T,6,lang)</f>
         <v>Semi-Finals</v>
       </c>
-      <c r="CG6" s="166"/>
-      <c r="CH6" s="166"/>
-      <c r="CI6" s="166"/>
-      <c r="CJ6" s="167"/>
+      <c r="CG6" s="177"/>
+      <c r="CH6" s="177"/>
+      <c r="CI6" s="177"/>
+      <c r="CJ6" s="178"/>
     </row>
     <row r="7" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="11">
@@ -41287,26 +41287,26 @@
         <v>1</v>
       </c>
       <c r="AY7" s="126"/>
-      <c r="BK7" s="168"/>
-      <c r="BL7" s="169"/>
-      <c r="BM7" s="169"/>
-      <c r="BN7" s="169"/>
-      <c r="BO7" s="170"/>
-      <c r="BR7" s="168"/>
-      <c r="BS7" s="169"/>
-      <c r="BT7" s="169"/>
-      <c r="BU7" s="169"/>
-      <c r="BV7" s="170"/>
-      <c r="BY7" s="168"/>
-      <c r="BZ7" s="169"/>
-      <c r="CA7" s="169"/>
-      <c r="CB7" s="169"/>
-      <c r="CC7" s="170"/>
-      <c r="CF7" s="168"/>
-      <c r="CG7" s="169"/>
-      <c r="CH7" s="169"/>
-      <c r="CI7" s="169"/>
-      <c r="CJ7" s="170"/>
+      <c r="BK7" s="179"/>
+      <c r="BL7" s="180"/>
+      <c r="BM7" s="180"/>
+      <c r="BN7" s="180"/>
+      <c r="BO7" s="181"/>
+      <c r="BR7" s="179"/>
+      <c r="BS7" s="180"/>
+      <c r="BT7" s="180"/>
+      <c r="BU7" s="180"/>
+      <c r="BV7" s="181"/>
+      <c r="BY7" s="179"/>
+      <c r="BZ7" s="180"/>
+      <c r="CA7" s="180"/>
+      <c r="CB7" s="180"/>
+      <c r="CC7" s="181"/>
+      <c r="CF7" s="179"/>
+      <c r="CG7" s="180"/>
+      <c r="CH7" s="180"/>
+      <c r="CI7" s="180"/>
+      <c r="CJ7" s="181"/>
     </row>
     <row r="8" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A8" s="16">
@@ -42042,7 +42042,7 @@
         <f>BH10/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK10" s="163">
+      <c r="BK10" s="173">
         <v>74</v>
       </c>
       <c r="BL10" s="24" t="str">
@@ -42305,7 +42305,7 @@
         <f>BH11/BH12</f>
         <v>0.98058252427184467</v>
       </c>
-      <c r="BK11" s="164"/>
+      <c r="BK11" s="174"/>
       <c r="BL11" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!G3,AK80:AS91,9,FALSE),"3rd Group A/B/C/D/F")</f>
         <v>3rd Group A/B/C/D/F</v>
@@ -42543,7 +42543,7 @@
       <c r="BO12" s="21"/>
       <c r="BP12" s="114"/>
       <c r="BQ12" s="112"/>
-      <c r="BR12" s="163">
+      <c r="BR12" s="173">
         <v>89</v>
       </c>
       <c r="BS12" s="24" t="str">
@@ -42664,7 +42664,7 @@
         <v>46203.875</v>
       </c>
       <c r="BQ13" s="115"/>
-      <c r="BR13" s="164"/>
+      <c r="BR13" s="174"/>
       <c r="BS13" s="26" t="str">
         <f>IF(BP14&gt;BP15,BL14,IF(BP14&lt;BP15,BL15,""))</f>
         <v/>
@@ -42922,7 +42922,7 @@
         <f>BH14/BH18</f>
         <v>0</v>
       </c>
-      <c r="BK14" s="163">
+      <c r="BK14" s="173">
         <v>77</v>
       </c>
       <c r="BL14" s="24" t="str">
@@ -43189,7 +43189,7 @@
         <f>BH15/BH18</f>
         <v>0</v>
       </c>
-      <c r="BK15" s="164"/>
+      <c r="BK15" s="174"/>
       <c r="BL15" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!I3,AK80:AS91,9,FALSE),"3rd Group C/D/F/G/H")</f>
         <v>3rd Group C/D/F/G/H</v>
@@ -43463,7 +43463,7 @@
       <c r="BV16" s="21"/>
       <c r="BW16" s="114"/>
       <c r="BX16" s="112"/>
-      <c r="BY16" s="163">
+      <c r="BY16" s="173">
         <v>97</v>
       </c>
       <c r="BZ16" s="24" t="str">
@@ -43725,7 +43725,7 @@
       <c r="BV17" s="21"/>
       <c r="BW17" s="114"/>
       <c r="BX17" s="115"/>
-      <c r="BY17" s="164"/>
+      <c r="BY17" s="174"/>
       <c r="BZ17" s="26" t="str">
         <f>IF(BW20&gt;BW21,BS20,IF(BW20&lt;BW21,BS21,""))</f>
         <v/>
@@ -43929,7 +43929,7 @@
         <f>MAX(BH14:BH17)+1</f>
         <v>1</v>
       </c>
-      <c r="BK18" s="163">
+      <c r="BK18" s="173">
         <v>73</v>
       </c>
       <c r="BL18" s="24" t="str">
@@ -44037,7 +44037,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BK19" s="164"/>
+      <c r="BK19" s="174"/>
       <c r="BL19" s="26" t="str">
         <f>AS15</f>
         <v>2B</v>
@@ -44315,7 +44315,7 @@
       <c r="BO20" s="21"/>
       <c r="BP20" s="114"/>
       <c r="BQ20" s="112"/>
-      <c r="BR20" s="163">
+      <c r="BR20" s="173">
         <v>90</v>
       </c>
       <c r="BS20" s="24" t="str">
@@ -44588,7 +44588,7 @@
         <v>46203.041666666672</v>
       </c>
       <c r="BQ21" s="115"/>
-      <c r="BR21" s="164"/>
+      <c r="BR21" s="174"/>
       <c r="BS21" s="26" t="str">
         <f>IF(BP22&gt;BP23,BL22,IF(BP22&lt;BP23,BL23,""))</f>
         <v/>
@@ -44842,7 +44842,7 @@
         <f>BH22/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK22" s="163">
+      <c r="BK22" s="173">
         <v>75</v>
       </c>
       <c r="BL22" s="24" t="str">
@@ -45106,7 +45106,7 @@
         <f>BH23/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK23" s="164"/>
+      <c r="BK23" s="174"/>
       <c r="BL23" s="26" t="str">
         <f>AS21</f>
         <v>2C</v>
@@ -45133,7 +45133,7 @@
       <c r="CC23" s="21"/>
       <c r="CD23" s="114"/>
       <c r="CE23" s="112"/>
-      <c r="CF23" s="163">
+      <c r="CF23" s="173">
         <v>101</v>
       </c>
       <c r="CG23" s="24" t="str">
@@ -45354,7 +45354,7 @@
       <c r="CC24" s="21"/>
       <c r="CD24" s="114"/>
       <c r="CE24" s="115"/>
-      <c r="CF24" s="164"/>
+      <c r="CF24" s="174"/>
       <c r="CG24" s="26" t="str">
         <f>IF(CD32&gt;CD33,BZ32,IF(CD32&lt;CD33,BZ33,""))</f>
         <v/>
@@ -45707,7 +45707,7 @@
         <f>BH26/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK26" s="163">
+      <c r="BK26" s="173">
         <v>83</v>
       </c>
       <c r="BL26" s="24" t="str">
@@ -45975,7 +45975,7 @@
         <f>BH27/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK27" s="164"/>
+      <c r="BK27" s="174"/>
       <c r="BL27" s="26" t="str">
         <f>AS75</f>
         <v>2L</v>
@@ -46250,7 +46250,7 @@
       <c r="BO28" s="21"/>
       <c r="BP28" s="114"/>
       <c r="BQ28" s="112"/>
-      <c r="BR28" s="163">
+      <c r="BR28" s="173">
         <v>93</v>
       </c>
       <c r="BS28" s="24" t="str">
@@ -46515,7 +46515,7 @@
         <v>46205.791666666672</v>
       </c>
       <c r="BQ29" s="115"/>
-      <c r="BR29" s="164"/>
+      <c r="BR29" s="174"/>
       <c r="BS29" s="26" t="str">
         <f>IF(BP30&gt;BP31,BL30,IF(BP30&lt;BP31,BL31,""))</f>
         <v/>
@@ -46729,7 +46729,7 @@
         <f>MAX(BH26:BH29)+1</f>
         <v>1</v>
       </c>
-      <c r="BK30" s="163">
+      <c r="BK30" s="173">
         <v>84</v>
       </c>
       <c r="BL30" s="24" t="str">
@@ -46840,7 +46840,7 @@
         <f>IF(OR(F31="",G31=""),"",IF(F31&gt;G31,1,IF(F31&lt;G31,-1,0)))</f>
         <v>0</v>
       </c>
-      <c r="BK31" s="164"/>
+      <c r="BK31" s="174"/>
       <c r="BL31" s="26" t="str">
         <f>AS63</f>
         <v>2J</v>
@@ -47116,7 +47116,7 @@
       <c r="BV32" s="21"/>
       <c r="BW32" s="114"/>
       <c r="BX32" s="112"/>
-      <c r="BY32" s="163">
+      <c r="BY32" s="173">
         <v>98</v>
       </c>
       <c r="BZ32" s="24" t="str">
@@ -47380,7 +47380,7 @@
       <c r="BV33" s="21"/>
       <c r="BW33" s="114"/>
       <c r="BX33" s="115"/>
-      <c r="BY33" s="164"/>
+      <c r="BY33" s="174"/>
       <c r="BZ33" s="26" t="str">
         <f>IF(BW36&gt;BW37,BS36,IF(BW36&lt;BW37,BS37,""))</f>
         <v/>
@@ -47395,14 +47395,14 @@
       <c r="CE33" s="112"/>
       <c r="CK33" s="114"/>
       <c r="CL33" s="112"/>
-      <c r="CM33" s="165" t="str" cm="1">
+      <c r="CM33" s="176" t="str" cm="1">
         <f t="array" ref="CM33">INDEX(T,8,lang)</f>
         <v>Final</v>
       </c>
-      <c r="CN33" s="166"/>
-      <c r="CO33" s="166"/>
-      <c r="CP33" s="166"/>
-      <c r="CQ33" s="167"/>
+      <c r="CN33" s="177"/>
+      <c r="CO33" s="177"/>
+      <c r="CP33" s="177"/>
+      <c r="CQ33" s="178"/>
     </row>
     <row r="34" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A34" s="16">
@@ -47626,7 +47626,7 @@
         <f>BH34/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK34" s="163">
+      <c r="BK34" s="173">
         <v>81</v>
       </c>
       <c r="BL34" s="24" t="str">
@@ -47657,11 +47657,11 @@
       <c r="CE34" s="112"/>
       <c r="CK34" s="114"/>
       <c r="CL34" s="112"/>
-      <c r="CM34" s="168"/>
-      <c r="CN34" s="169"/>
-      <c r="CO34" s="169"/>
-      <c r="CP34" s="169"/>
-      <c r="CQ34" s="170"/>
+      <c r="CM34" s="179"/>
+      <c r="CN34" s="180"/>
+      <c r="CO34" s="180"/>
+      <c r="CP34" s="180"/>
+      <c r="CQ34" s="181"/>
     </row>
     <row r="35" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A35" s="16">
@@ -47885,7 +47885,7 @@
         <f>BH35/BH36</f>
         <v>0.98039215686274506</v>
       </c>
-      <c r="BK35" s="164"/>
+      <c r="BK35" s="174"/>
       <c r="BL35" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!F3,AK80:AS91,9,FALSE),"3rd Group B/E/F/I/J")</f>
         <v>3rd Group B/E/F/I/J</v>
@@ -48114,7 +48114,7 @@
       <c r="BO36" s="21"/>
       <c r="BP36" s="114"/>
       <c r="BQ36" s="112"/>
-      <c r="BR36" s="163">
+      <c r="BR36" s="173">
         <v>94</v>
       </c>
       <c r="BS36" s="24" t="str">
@@ -48238,7 +48238,7 @@
         <v>46204.833333333336</v>
       </c>
       <c r="BQ37" s="115"/>
-      <c r="BR37" s="164"/>
+      <c r="BR37" s="174"/>
       <c r="BS37" s="26" t="str">
         <f>IF(BP38&gt;BP39,BL38,IF(BP38&lt;BP39,BL39,""))</f>
         <v/>
@@ -48265,7 +48265,7 @@
       <c r="CJ37" s="21"/>
       <c r="CK37" s="114"/>
       <c r="CL37" s="112"/>
-      <c r="CM37" s="163">
+      <c r="CM37" s="173">
         <v>104</v>
       </c>
       <c r="CN37" s="24" t="str">
@@ -48506,7 +48506,7 @@
         <f>BH38/BH42</f>
         <v>0.98064516129032253</v>
       </c>
-      <c r="BK38" s="163">
+      <c r="BK38" s="173">
         <v>82</v>
       </c>
       <c r="BL38" s="24" t="str">
@@ -48536,7 +48536,7 @@
       <c r="CI38" s="21"/>
       <c r="CJ38" s="21"/>
       <c r="CL38" s="115"/>
-      <c r="CM38" s="164"/>
+      <c r="CM38" s="174"/>
       <c r="CN38" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG55,IF(CK55&lt;CK56,CG56,""))</f>
         <v/>
@@ -48775,7 +48775,7 @@
         <f>BH39/BH42</f>
         <v>0.98064516129032253</v>
       </c>
-      <c r="BK39" s="164"/>
+      <c r="BK39" s="174"/>
       <c r="BL39" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!H3,AK80:AS91,9,FALSE),"3rd Group A/E/H/I/J")</f>
         <v>3rd Group A/E/H/I/J</v>
@@ -49463,7 +49463,7 @@
         <f>MAX(BH38:BH41)+1</f>
         <v>51.666666666666664</v>
       </c>
-      <c r="BK42" s="163">
+      <c r="BK42" s="173">
         <v>76</v>
       </c>
       <c r="BL42" s="24" t="str">
@@ -49560,7 +49560,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BK43" s="164"/>
+      <c r="BK43" s="174"/>
       <c r="BL43" s="26" t="str">
         <f>AS39</f>
         <v>2F</v>
@@ -49820,7 +49820,7 @@
       <c r="BO44" s="21"/>
       <c r="BP44" s="114"/>
       <c r="BQ44" s="112"/>
-      <c r="BR44" s="163">
+      <c r="BR44" s="173">
         <v>91</v>
       </c>
       <c r="BS44" s="24" t="str">
@@ -49835,14 +49835,14 @@
         <v/>
       </c>
       <c r="CK44" s="114"/>
-      <c r="CM44" s="165" t="str" cm="1">
+      <c r="CM44" s="176" t="str" cm="1">
         <f t="array" ref="CM44">INDEX(T,7,lang)</f>
         <v>Third-Place Play-Off</v>
       </c>
-      <c r="CN44" s="166"/>
-      <c r="CO44" s="166"/>
-      <c r="CP44" s="166"/>
-      <c r="CQ44" s="167"/>
+      <c r="CN44" s="177"/>
+      <c r="CO44" s="177"/>
+      <c r="CP44" s="177"/>
+      <c r="CQ44" s="178"/>
     </row>
     <row r="45" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="16">
@@ -50083,7 +50083,7 @@
         <v>46203.708333333336</v>
       </c>
       <c r="BQ45" s="115"/>
-      <c r="BR45" s="164"/>
+      <c r="BR45" s="174"/>
       <c r="BS45" s="26" t="str">
         <f>IF(BP46&gt;BP47,BL46,IF(BP46&lt;BP47,BL47,""))</f>
         <v/>
@@ -50096,11 +50096,11 @@
         <v/>
       </c>
       <c r="CK45" s="114"/>
-      <c r="CM45" s="168"/>
-      <c r="CN45" s="169"/>
-      <c r="CO45" s="169"/>
-      <c r="CP45" s="169"/>
-      <c r="CQ45" s="170"/>
+      <c r="CM45" s="179"/>
+      <c r="CN45" s="180"/>
+      <c r="CO45" s="180"/>
+      <c r="CP45" s="180"/>
+      <c r="CQ45" s="181"/>
     </row>
     <row r="46" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A46" s="16">
@@ -50324,7 +50324,7 @@
         <f>BH46/BH48</f>
         <v>0.98039215686274506</v>
       </c>
-      <c r="BK46" s="163">
+      <c r="BK46" s="173">
         <v>78</v>
       </c>
       <c r="BL46" s="24" t="str">
@@ -50368,8 +50368,12 @@
         <f>AE59</f>
         <v>Norway</v>
       </c>
-      <c r="F47" s="19"/>
-      <c r="G47" s="20"/>
+      <c r="F47" s="19">
+        <v>3</v>
+      </c>
+      <c r="G47" s="20">
+        <v>2</v>
+      </c>
       <c r="H47" s="80" t="str">
         <f>AE57</f>
         <v>Senegal</v>
@@ -50408,11 +50412,11 @@
       </c>
       <c r="S47" s="127" t="str">
         <f t="shared" ref="S47:S78" si="19">IF(OR(F47="",G47=""),"",IF(F47&gt;G47,E47&amp;"_win",IF(F47&lt;G47,E47&amp;"_lose",E47&amp;"_draw")))</f>
-        <v/>
+        <v>Norway_win</v>
       </c>
       <c r="T47" s="127" t="str">
         <f t="shared" ref="T47:T78" si="20">IF(S47="","",IF(F47&lt;G47,H47&amp;"_win",IF(F47&gt;G47,H47&amp;"_lose",H47&amp;"_draw")))</f>
-        <v/>
+        <v>Senegal_lose</v>
       </c>
       <c r="U47" s="123">
         <f t="shared" si="8"/>
@@ -50442,9 +50446,9 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB47" s="123" t="str">
+      <c r="AB47" s="123">
         <f t="shared" ref="AB47:AB78" si="23">IF(OR(F47="",G47=""),"",IF(F47&gt;G47,1,IF(F47&lt;G47,-1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD47" s="123">
         <f>COUNTIF(AR44:AR47,CONCATENATE("&gt;=",AR47))</f>
@@ -50566,7 +50570,7 @@
         <f>BH47/BH48</f>
         <v>0</v>
       </c>
-      <c r="BK47" s="164"/>
+      <c r="BK47" s="174"/>
       <c r="BL47" s="26" t="str">
         <f>AS57</f>
         <v>2I</v>
@@ -50633,8 +50637,12 @@
         <f>AE56</f>
         <v>France</v>
       </c>
-      <c r="F48" s="19"/>
-      <c r="G48" s="20"/>
+      <c r="F48" s="19">
+        <v>3</v>
+      </c>
+      <c r="G48" s="20">
+        <v>0</v>
+      </c>
       <c r="H48" s="80" t="str">
         <f>AE58</f>
         <v>Iraq</v>
@@ -50673,11 +50681,11 @@
       </c>
       <c r="S48" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>France_win</v>
       </c>
       <c r="T48" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Iraq_lose</v>
       </c>
       <c r="U48" s="123">
         <f t="shared" si="8"/>
@@ -50707,9 +50715,9 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB48" s="123" t="str">
+      <c r="AB48" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AF48" s="123">
         <f t="shared" ref="AF48:AH48" si="24">MAX(AF44:AF47)-MIN(AF44:AF47)+1</f>
@@ -50809,7 +50817,7 @@
       <c r="BV48" s="21"/>
       <c r="BW48" s="114"/>
       <c r="BX48" s="112"/>
-      <c r="BY48" s="163">
+      <c r="BY48" s="173">
         <v>99</v>
       </c>
       <c r="BZ48" s="24" t="str">
@@ -50825,7 +50833,7 @@
       </c>
       <c r="CK48" s="114"/>
       <c r="CL48" s="112"/>
-      <c r="CM48" s="163">
+      <c r="CM48" s="173">
         <v>103</v>
       </c>
       <c r="CN48" s="24" t="str">
@@ -50860,8 +50868,12 @@
         <f>AE62</f>
         <v>Argentina</v>
       </c>
-      <c r="F49" s="19"/>
-      <c r="G49" s="20"/>
+      <c r="F49" s="19">
+        <v>2</v>
+      </c>
+      <c r="G49" s="20">
+        <v>0</v>
+      </c>
       <c r="H49" s="80" t="str">
         <f>AE64</f>
         <v>Austria</v>
@@ -50872,11 +50884,11 @@
       </c>
       <c r="S49" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Argentina_win</v>
       </c>
       <c r="T49" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Austria_lose</v>
       </c>
       <c r="U49" s="123">
         <f t="shared" si="8"/>
@@ -50906,9 +50918,9 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB49" s="123" t="str">
+      <c r="AB49" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="BK49" s="21" t="str" cm="1">
         <f t="array" ref="BK49">INDEX(T,24+MONTH(BP49),lang) &amp; " " &amp; DAY(BP49) &amp; ", " &amp; YEAR(BP49) &amp; "   " &amp; (IF(HOUR(BP49)&lt;10,0,"")&amp;HOUR(BP49)) &amp; ":" &amp;  (IF(MINUTE(BP49)&lt;10,0,"")&amp;MINUTE(BP49))</f>
@@ -50930,7 +50942,7 @@
       <c r="BV49" s="21"/>
       <c r="BW49" s="114"/>
       <c r="BX49" s="115"/>
-      <c r="BY49" s="164"/>
+      <c r="BY49" s="174"/>
       <c r="BZ49" s="26" t="str">
         <f>IF(BW52&gt;BW53,BS52,IF(BW52&lt;BW53,BS53,""))</f>
         <v/>
@@ -50944,7 +50956,7 @@
       </c>
       <c r="CK49" s="114"/>
       <c r="CL49" s="115"/>
-      <c r="CM49" s="164"/>
+      <c r="CM49" s="174"/>
       <c r="CN49" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG56,IF(CK55&lt;CK56,CG55,""))</f>
         <v/>
@@ -50977,8 +50989,12 @@
         <f>AE65</f>
         <v>Jordan</v>
       </c>
-      <c r="F50" s="19"/>
-      <c r="G50" s="20"/>
+      <c r="F50" s="19">
+        <v>1</v>
+      </c>
+      <c r="G50" s="20">
+        <v>2</v>
+      </c>
       <c r="H50" s="80" t="str">
         <f>AE63</f>
         <v>Algeria</v>
@@ -51017,11 +51033,11 @@
       </c>
       <c r="S50" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Jordan_lose</v>
       </c>
       <c r="T50" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Algeria_win</v>
       </c>
       <c r="U50" s="123">
         <f t="shared" si="8"/>
@@ -51051,9 +51067,9 @@
         <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="AB50" s="123" t="str">
+      <c r="AB50" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>-1</v>
       </c>
       <c r="AD50" s="123">
         <f>COUNTIF(AR50:AR53,CONCATENATE("&gt;=",AR50))</f>
@@ -51179,7 +51195,7 @@
         <f>BH50/BH54</f>
         <v>0</v>
       </c>
-      <c r="BK50" s="163">
+      <c r="BK50" s="173">
         <v>79</v>
       </c>
       <c r="BL50" s="24" t="str">
@@ -51432,7 +51448,7 @@
         <f>BH51/BH54</f>
         <v>0.98064516129032253</v>
       </c>
-      <c r="BK51" s="164"/>
+      <c r="BK51" s="174"/>
       <c r="BL51" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!D3,AK80:AS91,9,FALSE),"3rd Group C/E/F/H/I")</f>
         <v>3rd Group C/E/F/H/I</v>
@@ -51692,7 +51708,7 @@
       <c r="BO52" s="21"/>
       <c r="BP52" s="114"/>
       <c r="BQ52" s="112"/>
-      <c r="BR52" s="163">
+      <c r="BR52" s="173">
         <v>92</v>
       </c>
       <c r="BS52" s="24" t="str">
@@ -51947,7 +51963,7 @@
         <v>46204.666666666672</v>
       </c>
       <c r="BQ53" s="115"/>
-      <c r="BR53" s="164"/>
+      <c r="BR53" s="174"/>
       <c r="BS53" s="26" t="str">
         <f>IF(BP54&gt;BP55,BL54,IF(BP54&lt;BP55,BL55,""))</f>
         <v/>
@@ -52151,7 +52167,7 @@
         <f>MAX(BH50:BH53)+1</f>
         <v>51.666666666666664</v>
       </c>
-      <c r="BK54" s="163">
+      <c r="BK54" s="173">
         <v>80</v>
       </c>
       <c r="BL54" s="24" t="str">
@@ -52272,7 +52288,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK55" s="164"/>
+      <c r="BK55" s="174"/>
       <c r="BL55" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!K3,AK80:AS91,9,FALSE),"3rd Group E/H/I/J/K")</f>
         <v>3rd Group E/H/I/J/K</v>
@@ -52299,7 +52315,7 @@
       <c r="CC55" s="21"/>
       <c r="CD55" s="114"/>
       <c r="CE55" s="112"/>
-      <c r="CF55" s="163">
+      <c r="CF55" s="173">
         <v>102</v>
       </c>
       <c r="CG55" s="24" t="str">
@@ -52416,7 +52432,7 @@
       </c>
       <c r="AD56" s="123">
         <f>COUNTIF(AR56:AR59,CONCATENATE("&gt;=",AR56))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE56" s="124" t="str">
         <f>VLOOKUP("France",T,lang,FALSE)</f>
@@ -52424,7 +52440,7 @@
       </c>
       <c r="AF56" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE56 &amp; "_win")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG56" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE56 &amp; "_draw")</f>
@@ -52436,7 +52452,7 @@
       </c>
       <c r="AI56" s="123">
         <f>SUMIF($E$7:$E$78,$AE56,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE56,$G$7:$G$78)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AJ56" s="123">
         <f>SUMIF($E$7:$E$78,$AE56,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE56,$F$7:$F$78)</f>
@@ -52444,23 +52460,23 @@
       </c>
       <c r="AL56" s="123">
         <f>AI56-AJ56</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AM56" s="123">
         <f>AL56-AL60</f>
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AN56" s="123">
         <f>AF56*3+AG56</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AO56" s="123">
         <f>AN56/AN60*10+BA56</f>
-        <v>7.5</v>
+        <v>8.5714285714285712</v>
       </c>
       <c r="AP56" s="123">
         <f>AO56*10000000+BI56*100+AM56/AM60*10+AI56/AI60*1++IF(AQ56=0,ROW(),AQ56)/2000000</f>
-        <v>75000007.743795797</v>
+        <v>85714295.631891042</v>
       </c>
       <c r="AQ56" s="126">
         <f>VLOOKUP(AE56,db_fifarank,2,FALSE)</f>
@@ -52468,7 +52484,7 @@
       </c>
       <c r="AR56" s="125">
         <f>AP56/AP60</f>
-        <v>0.99999996495456167</v>
+        <v>0.99999998833333481</v>
       </c>
       <c r="AS56" s="125" t="str">
         <f>IF(SUM(AF56:AH59)=12,J57,"1I")</f>
@@ -52558,7 +52574,7 @@
       <c r="CC56" s="21"/>
       <c r="CD56" s="114"/>
       <c r="CE56" s="115"/>
-      <c r="CF56" s="164"/>
+      <c r="CF56" s="174"/>
       <c r="CG56" s="26" t="str">
         <f>IF(CD64&gt;CD65,BZ64,IF(CD64&lt;CD65,BZ65,""))</f>
         <v/>
@@ -52601,15 +52617,15 @@
       <c r="I57" s="69"/>
       <c r="J57" s="30" t="str">
         <f>VLOOKUP(1,AD56:AN59,2,FALSE)</f>
-        <v>Norway</v>
+        <v>France</v>
       </c>
       <c r="K57" s="31">
         <f>L57+M57+N57</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L57" s="31">
         <f>VLOOKUP(1,AD56:AN59,3,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M57" s="31">
         <f>VLOOKUP(1,AD56:AN59,4,FALSE)</f>
@@ -52621,11 +52637,11 @@
       </c>
       <c r="O57" s="31" t="str">
         <f>VLOOKUP(1,AD56:AN59,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD56:AN59,7,FALSE)</f>
-        <v>4 - 1</v>
+        <v>6 - 1</v>
       </c>
       <c r="P57" s="32">
         <f>L57*3+M57</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R57" s="123">
         <f>DATE(2026,6,24)+TIME(8,0,0)+gmt_delta</f>
@@ -52689,23 +52705,23 @@
       </c>
       <c r="AH57" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE57 &amp; "_lose")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI57" s="123">
         <f>SUMIF($E$7:$E$78,$AE57,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE57,$G$7:$G$78)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AJ57" s="123">
         <f>SUMIF($E$7:$E$78,$AE57,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE57,$F$7:$F$78)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AL57" s="123">
         <f>AI57-AJ57</f>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AM57" s="123">
         <f>AL57-AL60</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AN57" s="123">
         <f>AF57*3+AG57</f>
@@ -52717,7 +52733,7 @@
       </c>
       <c r="AP57" s="123">
         <f>AO57*10000000+BI57*100+AM57/AM60*10+AI57/AI60*1++IF(AQ57=0,ROW(),AQ57)/2000000</f>
-        <v>1.6294159235714283</v>
+        <v>2.8758444949999999</v>
       </c>
       <c r="AQ57" s="126">
         <f>VLOOKUP(AE57,db_fifarank,2,FALSE)</f>
@@ -52725,7 +52741,7 @@
       </c>
       <c r="AR57" s="125">
         <f>AP57/AP60</f>
-        <v>2.172554264306223E-8</v>
+        <v>3.35515148348077E-8</v>
       </c>
       <c r="AS57" s="125" t="str">
         <f>IF(SUM(AF56:AH59)=12,J58,"2I")</f>
@@ -52851,15 +52867,15 @@
       <c r="I58" s="69"/>
       <c r="J58" s="33" t="str">
         <f>VLOOKUP(2,AD56:AN59,2,FALSE)</f>
-        <v>France</v>
+        <v>Norway</v>
       </c>
       <c r="K58" s="23">
         <f>L58+M58+N58</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L58" s="23">
         <f>VLOOKUP(2,AD56:AN59,3,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M58" s="23">
         <f>VLOOKUP(2,AD56:AN59,4,FALSE)</f>
@@ -52871,11 +52887,11 @@
       </c>
       <c r="O58" s="23" t="str">
         <f>VLOOKUP(2,AD56:AN59,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD56:AN59,7,FALSE)</f>
-        <v>3 - 1</v>
+        <v>7 - 3</v>
       </c>
       <c r="P58" s="34">
         <f>L58*3+M58</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R58" s="123">
         <f>DATE(2026,6,24)+TIME(8,0,0)+gmt_delta</f>
@@ -52939,7 +52955,7 @@
       </c>
       <c r="AH58" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE58 &amp; "_lose")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI58" s="123">
         <f>SUMIF($E$7:$E$78,$AE58,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE58,$G$7:$G$78)</f>
@@ -52947,11 +52963,11 @@
       </c>
       <c r="AJ58" s="123">
         <f>SUMIF($E$7:$E$78,$AE58,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE58,$F$7:$F$78)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AL58" s="123">
         <f>AI58-AJ58</f>
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="AM58" s="123">
         <f>AL58-AL60</f>
@@ -52967,7 +52983,7 @@
       </c>
       <c r="AP58" s="123">
         <f>AO58*10000000+BI58*100+AM58/AM60*10+AI58/AI60*1++IF(AQ58=0,ROW(),AQ58)/2000000</f>
-        <v>0.20072357000000002</v>
+        <v>0.12572357000000001</v>
       </c>
       <c r="AQ58" s="126">
         <f>VLOOKUP(AE58,db_fifarank,2,FALSE)</f>
@@ -52975,7 +52991,7 @@
       </c>
       <c r="AR58" s="125">
         <f>AP58/AP60</f>
-        <v>2.6763138965430164E-9</v>
+        <v>1.466774796507203E-9</v>
       </c>
       <c r="AT58" s="126" cm="1">
         <f t="array" ref="AT58">SUMPRODUCT(($S$7:$S$78=AE58&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE58&amp;"_win")*($U$7:$U$78))</f>
@@ -53041,7 +53057,7 @@
         <f>BH58/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK58" s="163">
+      <c r="BK58" s="173">
         <v>86</v>
       </c>
       <c r="BL58" s="24" t="str">
@@ -53103,7 +53119,7 @@
       </c>
       <c r="K59" s="23">
         <f>L59+M59+N59</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L59" s="23">
         <f>VLOOKUP(3,AD56:AN59,3,FALSE)</f>
@@ -53115,11 +53131,11 @@
       </c>
       <c r="N59" s="23">
         <f>VLOOKUP(3,AD56:AN59,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O59" s="23" t="str">
         <f>VLOOKUP(3,AD56:AN59,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD56:AN59,7,FALSE)</f>
-        <v>1 - 3</v>
+        <v>3 - 6</v>
       </c>
       <c r="P59" s="34">
         <f>L59*3+M59</f>
@@ -53171,7 +53187,7 @@
       </c>
       <c r="AD59" s="123">
         <f>COUNTIF(AR56:AR59,CONCATENATE("&gt;=",AR59))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE59" s="124" t="str">
         <f>VLOOKUP("Norway",T,lang,FALSE)</f>
@@ -53179,7 +53195,7 @@
       </c>
       <c r="AF59" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE59 &amp; "_win")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG59" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE59 &amp; "_draw")</f>
@@ -53191,31 +53207,31 @@
       </c>
       <c r="AI59" s="123">
         <f>SUMIF($E$7:$E$78,$AE59,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE59,$G$7:$G$78)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AJ59" s="123">
         <f>SUMIF($E$7:$E$78,$AE59,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE59,$F$7:$F$78)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AL59" s="123">
         <f>AI59-AJ59</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM59" s="123">
         <f>AL59-AL60</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AN59" s="123">
         <f>AF59*3+AG59</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AO59" s="123">
         <f>AN59/AN60*10+BA59</f>
-        <v>7.5</v>
+        <v>8.5714285714285712</v>
       </c>
       <c r="AP59" s="123">
         <f>AO59*10000000+BI59*100+AM59/AM60*10+AI59/AI60*1++IF(AQ59=0,ROW(),AQ59)/2000000</f>
-        <v>75000009.372204036</v>
+        <v>85714294.923394516</v>
       </c>
       <c r="AQ59" s="126">
         <f>VLOOKUP(AE59,db_fifarank,2,FALSE)</f>
@@ -53223,7 +53239,7 @@
       </c>
       <c r="AR59" s="125">
         <f>AP59/AP60</f>
-        <v>0.99999998666666856</v>
+        <v>0.99999998006754309</v>
       </c>
       <c r="AT59" s="126" cm="1">
         <f t="array" ref="AT59">SUMPRODUCT(($S$7:$S$78=AE59&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE59&amp;"_win")*($U$7:$U$78))</f>
@@ -53289,7 +53305,7 @@
         <f>BH59/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK59" s="164"/>
+      <c r="BK59" s="174"/>
       <c r="BL59" s="26" t="str">
         <f>AS51</f>
         <v>2H</v>
@@ -53355,7 +53371,7 @@
       </c>
       <c r="K60" s="36">
         <f>L60+M60+N60</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L60" s="36">
         <f>VLOOKUP(4,AD56:AN59,3,FALSE)</f>
@@ -53367,11 +53383,11 @@
       </c>
       <c r="N60" s="36">
         <f>VLOOKUP(4,AD56:AN59,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O60" s="36" t="str">
         <f>VLOOKUP(4,AD56:AN59,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD56:AN59,7,FALSE)</f>
-        <v>1 - 4</v>
+        <v>1 - 7</v>
       </c>
       <c r="P60" s="37">
         <f>L60*3+M60</f>
@@ -53423,7 +53439,7 @@
       </c>
       <c r="AF60" s="123">
         <f t="shared" ref="AF60:AH60" si="27">MAX(AF56:AF59)-MIN(AF56:AF59)+1</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG60" s="123">
         <f t="shared" si="27"/>
@@ -53431,31 +53447,31 @@
       </c>
       <c r="AH60" s="123">
         <f t="shared" si="27"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI60" s="123">
         <f>MAX(AI56:AI59)+1</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AL60" s="123">
         <f>MIN(AL56:AL59)</f>
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="AM60" s="123">
         <f>MAX(AM56:AM59)+1</f>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AN60" s="123">
         <f>MAX(AN56:AN59)+1</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AO60" s="123">
         <f>MAX(AO56:AO59)+1</f>
-        <v>8.5</v>
+        <v>9.5714285714285712</v>
       </c>
       <c r="AP60" s="123">
         <f>MAX(AP56:AP59)+1</f>
-        <v>75000010.372204036</v>
+        <v>85714296.631891042</v>
       </c>
       <c r="AT60" s="126">
         <f>MAX(AT56:AT59)-MIN(AT56:AT59)+1</f>
@@ -53512,7 +53528,7 @@
       <c r="BO60" s="21"/>
       <c r="BP60" s="114"/>
       <c r="BQ60" s="112"/>
-      <c r="BR60" s="163">
+      <c r="BR60" s="173">
         <v>95</v>
       </c>
       <c r="BS60" s="24" t="str">
@@ -53625,7 +53641,7 @@
         <v>46206.75</v>
       </c>
       <c r="BQ61" s="115"/>
-      <c r="BR61" s="164"/>
+      <c r="BR61" s="174"/>
       <c r="BS61" s="26" t="str">
         <f>IF(BP62&gt;BP63,BL62,IF(BP62&lt;BP63,BL63,""))</f>
         <v/>
@@ -53754,7 +53770,7 @@
       </c>
       <c r="AF62" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE62 &amp; "_win")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG62" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE62 &amp; "_draw")</f>
@@ -53766,7 +53782,7 @@
       </c>
       <c r="AI62" s="123">
         <f>SUMIF($E$7:$E$78,$AE62,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE62,$G$7:$G$78)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AJ62" s="123">
         <f>SUMIF($E$7:$E$78,$AE62,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE62,$F$7:$F$78)</f>
@@ -53774,23 +53790,23 @@
       </c>
       <c r="AL62" s="123">
         <f>AI62-AJ62</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AM62" s="123">
         <f>AL62-AL66</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AN62" s="123">
         <f>AF62*3+AG62</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AO62" s="123">
         <f>AN62/AN66*10+BA62</f>
-        <v>7.5</v>
+        <v>8.5714285714285712</v>
       </c>
       <c r="AP62" s="123">
         <f>AO62*10000000+BI62*100+AM62/AM66*10+AI62/AI66*1++IF(AQ62=0,ROW(),AQ62)/2000000</f>
-        <v>75000009.322365984</v>
+        <v>85714295.437445357</v>
       </c>
       <c r="AQ62" s="126">
         <f>VLOOKUP(AE62,db_fifarank,2,FALSE)</f>
@@ -53798,7 +53814,7 @@
       </c>
       <c r="AR62" s="125">
         <f>AP62/AP66</f>
-        <v>0.99999998666666845</v>
+        <v>0.99999998833333481</v>
       </c>
       <c r="AS62" s="125" t="str">
         <f>IF(SUM(AF62:AH65)=12,J63,"1J")</f>
@@ -53868,7 +53884,7 @@
         <f>BH62/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK62" s="163">
+      <c r="BK62" s="173">
         <v>88</v>
       </c>
       <c r="BL62" s="24" t="str">
@@ -53930,11 +53946,11 @@
       </c>
       <c r="K63" s="31">
         <f>L63+M63+N63</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L63" s="31">
         <f>VLOOKUP(1,AD62:AN65,3,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M63" s="31">
         <f>VLOOKUP(1,AD62:AN65,4,FALSE)</f>
@@ -53946,11 +53962,11 @@
       </c>
       <c r="O63" s="31" t="str">
         <f>VLOOKUP(1,AD62:AN65,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD62:AN65,7,FALSE)</f>
-        <v>3 - 0</v>
+        <v>5 - 0</v>
       </c>
       <c r="P63" s="32">
         <f>L63*3+M63</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R63" s="123">
         <f>DATE(2026,6,25)+TIME(12,0,0)+gmt_delta</f>
@@ -53998,7 +54014,7 @@
       </c>
       <c r="AD63" s="123">
         <f>COUNTIF(AR62:AR65,CONCATENATE("&gt;=",AR63))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE63" s="124" t="str">
         <f>VLOOKUP("Algeria",T,lang,FALSE)</f>
@@ -54006,7 +54022,7 @@
       </c>
       <c r="AF63" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE63 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG63" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE63 &amp; "_draw")</f>
@@ -54018,31 +54034,31 @@
       </c>
       <c r="AI63" s="123">
         <f>SUMIF($E$7:$E$78,$AE63,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE63,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ63" s="123">
         <f>SUMIF($E$7:$E$78,$AE63,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE63,$F$7:$F$78)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL63" s="123">
         <f>AI63-AJ63</f>
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="AM63" s="123">
         <f>AL63-AL66</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN63" s="123">
         <f>AF63*3+AG63</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO63" s="123">
         <f>AN63/AN66*10+BA63</f>
-        <v>0</v>
+        <v>4.2857142857142856</v>
       </c>
       <c r="AP63" s="123">
         <f>AO63*10000000+BI63*100+AM63/AM66*10+AI63/AI66*1++IF(AQ63=0,ROW(),AQ63)/2000000</f>
-        <v>7.8213000000000002E-4</v>
+        <v>42857144.302369438</v>
       </c>
       <c r="AQ63" s="126">
         <f>VLOOKUP(AE63,db_fifarank,2,FALSE)</f>
@@ -54050,7 +54066,7 @@
       </c>
       <c r="AR63" s="125">
         <f>AP63/AP66</f>
-        <v>1.0428398564723378E-11</v>
+        <v>0.4999999543092179</v>
       </c>
       <c r="AS63" s="125" t="str">
         <f>IF(SUM(AF62:AH65)=12,J64,"2J")</f>
@@ -54120,7 +54136,7 @@
         <f>BH63/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK63" s="164"/>
+      <c r="BK63" s="174"/>
       <c r="BL63" s="26" t="str">
         <f>AS45</f>
         <v>2G</v>
@@ -54186,7 +54202,7 @@
       </c>
       <c r="K64" s="23">
         <f>L64+M64+N64</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L64" s="23">
         <f>VLOOKUP(2,AD62:AN65,3,FALSE)</f>
@@ -54198,11 +54214,11 @@
       </c>
       <c r="N64" s="23">
         <f>VLOOKUP(2,AD62:AN65,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O64" s="23" t="str">
         <f>VLOOKUP(2,AD62:AN65,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD62:AN65,7,FALSE)</f>
-        <v>3 - 1</v>
+        <v>3 - 3</v>
       </c>
       <c r="P64" s="34">
         <f>L64*3+M64</f>
@@ -54270,7 +54286,7 @@
       </c>
       <c r="AH64" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE64 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI64" s="123">
         <f>SUMIF($E$7:$E$78,$AE64,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE64,$G$7:$G$78)</f>
@@ -54278,15 +54294,15 @@
       </c>
       <c r="AJ64" s="123">
         <f>SUMIF($E$7:$E$78,$AE64,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE64,$F$7:$F$78)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AL64" s="123">
         <f>AI64-AJ64</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM64" s="123">
         <f>AL64-AL66</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AN64" s="123">
         <f>AF64*3+AG64</f>
@@ -54294,11 +54310,11 @@
       </c>
       <c r="AO64" s="123">
         <f>AN64/AN66*10+BA64</f>
-        <v>7.5</v>
+        <v>4.2857142857142856</v>
       </c>
       <c r="AP64" s="123">
         <f>AO64*10000000+BI64*100+AM64/AM66*10+AI64/AI66*1++IF(AQ64=0,ROW(),AQ64)/2000000</f>
-        <v>75000007.89365387</v>
+        <v>42857146.691272922</v>
       </c>
       <c r="AQ64" s="126">
         <f>VLOOKUP(AE64,db_fifarank,2,FALSE)</f>
@@ -54306,7 +54322,7 @@
       </c>
       <c r="AR64" s="125">
         <f>AP64/AP66</f>
-        <v>0.99999996761717624</v>
+        <v>0.49999998217975505</v>
       </c>
       <c r="AT64" s="126" cm="1">
         <f t="array" ref="AT64">SUMPRODUCT(($S$7:$S$78=AE64&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE64&amp;"_win")*($U$7:$U$78))</f>
@@ -54386,7 +54402,7 @@
       <c r="BV64" s="21"/>
       <c r="BW64" s="114"/>
       <c r="BX64" s="112"/>
-      <c r="BY64" s="163">
+      <c r="BY64" s="173">
         <v>100</v>
       </c>
       <c r="BZ64" s="24" t="str">
@@ -54430,15 +54446,15 @@
       <c r="I65" s="69"/>
       <c r="J65" s="33" t="str">
         <f>VLOOKUP(3,AD62:AN65,2,FALSE)</f>
-        <v>Jordan</v>
+        <v>Algeria</v>
       </c>
       <c r="K65" s="23">
         <f>L65+M65+N65</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L65" s="23">
         <f>VLOOKUP(3,AD62:AN65,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" s="23">
         <f>VLOOKUP(3,AD62:AN65,4,FALSE)</f>
@@ -54450,11 +54466,11 @@
       </c>
       <c r="O65" s="23" t="str">
         <f>VLOOKUP(3,AD62:AN65,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD62:AN65,7,FALSE)</f>
-        <v>1 - 3</v>
+        <v>2 - 4</v>
       </c>
       <c r="P65" s="34">
         <f>L65*3+M65</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R65" s="123">
         <f>DATE(2026,6,25)+TIME(15,0,0)+gmt_delta</f>
@@ -54502,7 +54518,7 @@
       </c>
       <c r="AD65" s="123">
         <f>COUNTIF(AR62:AR65,CONCATENATE("&gt;=",AR65))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE65" s="124" t="str">
         <f>VLOOKUP("Jordan",T,lang,FALSE)</f>
@@ -54518,23 +54534,23 @@
       </c>
       <c r="AH65" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE65 &amp; "_lose")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI65" s="123">
         <f>SUMIF($E$7:$E$78,$AE65,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE65,$G$7:$G$78)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ65" s="123">
         <f>SUMIF($E$7:$E$78,$AE65,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE65,$F$7:$F$78)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AL65" s="123">
         <f>AI65-AJ65</f>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AM65" s="123">
         <f>AL65-AL66</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN65" s="123">
         <f>AF65*3+AG65</f>
@@ -54546,7 +54562,7 @@
       </c>
       <c r="AP65" s="123">
         <f>AO65*10000000+BI65*100+AM65/AM66*10+AI65/AI66*1++IF(AQ65=0,ROW(),AQ65)/2000000</f>
-        <v>1.6792671535714283</v>
+        <v>0.3340290583333333</v>
       </c>
       <c r="AQ65" s="126">
         <f>VLOOKUP(AE65,db_fifarank,2,FALSE)</f>
@@ -54554,7 +54570,7 @@
       </c>
       <c r="AR65" s="125">
         <f>AP65/AP66</f>
-        <v>2.2390225632684331E-8</v>
+        <v>3.8970051930264523E-9</v>
       </c>
       <c r="AT65" s="126" cm="1">
         <f t="array" ref="AT65">SUMPRODUCT(($S$7:$S$78=AE65&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE65&amp;"_win")*($U$7:$U$78))</f>
@@ -54640,7 +54656,7 @@
       <c r="BV65" s="21"/>
       <c r="BW65" s="114"/>
       <c r="BX65" s="115"/>
-      <c r="BY65" s="164"/>
+      <c r="BY65" s="174"/>
       <c r="BZ65" s="26" t="str">
         <f>IF(BW68&gt;BW69,BS68,IF(BW68&lt;BW69,BS69,""))</f>
         <v/>
@@ -54682,11 +54698,11 @@
       <c r="I66" s="69"/>
       <c r="J66" s="35" t="str">
         <f>VLOOKUP(4,AD62:AN65,2,FALSE)</f>
-        <v>Algeria</v>
+        <v>Jordan</v>
       </c>
       <c r="K66" s="36">
         <f>L66+M66+N66</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L66" s="36">
         <f>VLOOKUP(4,AD62:AN65,3,FALSE)</f>
@@ -54698,11 +54714,11 @@
       </c>
       <c r="N66" s="36">
         <f>VLOOKUP(4,AD62:AN65,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O66" s="36" t="str">
         <f>VLOOKUP(4,AD62:AN65,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD62:AN65,7,FALSE)</f>
-        <v>0 - 3</v>
+        <v>2 - 5</v>
       </c>
       <c r="P66" s="37">
         <f>L66*3+M66</f>
@@ -54754,7 +54770,7 @@
       </c>
       <c r="AF66" s="123">
         <f t="shared" ref="AF66:AH66" si="28">MAX(AF62:AF65)-MIN(AF62:AF65)+1</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG66" s="123">
         <f t="shared" si="28"/>
@@ -54762,11 +54778,11 @@
       </c>
       <c r="AH66" s="123">
         <f t="shared" si="28"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI66" s="123">
         <f>MAX(AI62:AI65)+1</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AL66" s="123">
         <f>MIN(AL62:AL65)</f>
@@ -54774,19 +54790,19 @@
       </c>
       <c r="AM66" s="123">
         <f>MAX(AM62:AM65)+1</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AN66" s="123">
         <f>MAX(AN62:AN65)+1</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AO66" s="123">
         <f>MAX(AO62:AO65)+1</f>
-        <v>8.5</v>
+        <v>9.5714285714285712</v>
       </c>
       <c r="AP66" s="123">
         <f>MAX(AP62:AP65)+1</f>
-        <v>75000010.322365984</v>
+        <v>85714296.437445357</v>
       </c>
       <c r="AT66" s="126">
         <f>MAX(AT62:AT65)-MIN(AT62:AT65)+1</f>
@@ -54836,7 +54852,7 @@
         <f>MAX(BH62:BH65)+1</f>
         <v>1</v>
       </c>
-      <c r="BK66" s="163">
+      <c r="BK66" s="173">
         <v>85</v>
       </c>
       <c r="BL66" s="24" t="str">
@@ -54936,7 +54952,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BK67" s="164"/>
+      <c r="BK67" s="174"/>
       <c r="BL67" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!E3,AK80:AS91,9,FALSE),"3rd Group E/F/G/I/J")</f>
         <v>3rd Group E/F/G/I/J</v>
@@ -55192,7 +55208,7 @@
       <c r="BO68" s="21"/>
       <c r="BP68" s="114"/>
       <c r="BQ68" s="112"/>
-      <c r="BR68" s="163">
+      <c r="BR68" s="173">
         <v>96</v>
       </c>
       <c r="BS68" s="24" t="str">
@@ -55206,25 +55222,25 @@
         <f>IF(OR(BT68="",BT69="",AND(BU68="",BU69&lt;&gt;""),AND(BU69="",BU68&lt;&gt;""),AND(BV68="",BV69&lt;&gt;""),AND(BV69="",BV68&lt;&gt;"")),"",BT68*1000+BU68*10+BV68)</f>
         <v/>
       </c>
-      <c r="CE68" s="195" t="str">
+      <c r="CE68" s="175" t="str">
         <f>INDEX(T,144,lang)</f>
         <v>World Champion 2026</v>
       </c>
-      <c r="CF68" s="195"/>
-      <c r="CG68" s="195"/>
-      <c r="CH68" s="195"/>
-      <c r="CI68" s="195"/>
-      <c r="CJ68" s="195"/>
-      <c r="CK68" s="185" t="str">
+      <c r="CF68" s="175"/>
+      <c r="CG68" s="175"/>
+      <c r="CH68" s="175"/>
+      <c r="CI68" s="175"/>
+      <c r="CJ68" s="175"/>
+      <c r="CK68" s="163" t="str">
         <f>IF(CR37&gt;CR38,CN37,IF(CR37&lt;CR38,CN38,""))</f>
         <v/>
       </c>
-      <c r="CL68" s="185"/>
-      <c r="CM68" s="185"/>
-      <c r="CN68" s="185"/>
-      <c r="CO68" s="185"/>
-      <c r="CP68" s="185"/>
-      <c r="CQ68" s="185"/>
+      <c r="CL68" s="163"/>
+      <c r="CM68" s="163"/>
+      <c r="CN68" s="163"/>
+      <c r="CO68" s="163"/>
+      <c r="CP68" s="163"/>
+      <c r="CQ68" s="163"/>
     </row>
     <row r="69" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A69" s="16">
@@ -55462,7 +55478,7 @@
         <v>46207.0625</v>
       </c>
       <c r="BQ69" s="115"/>
-      <c r="BR69" s="164"/>
+      <c r="BR69" s="174"/>
       <c r="BS69" s="26" t="str">
         <f>IF(BP70&gt;BP71,BL70,IF(BP70&lt;BP71,BL71,""))</f>
         <v/>
@@ -55474,19 +55490,19 @@
         <f>IF(BW68="","",BT69*1000+BU69*10+BV69)</f>
         <v/>
       </c>
-      <c r="CE69" s="195"/>
-      <c r="CF69" s="195"/>
-      <c r="CG69" s="195"/>
-      <c r="CH69" s="195"/>
-      <c r="CI69" s="195"/>
-      <c r="CJ69" s="195"/>
-      <c r="CK69" s="185"/>
-      <c r="CL69" s="185"/>
-      <c r="CM69" s="185"/>
-      <c r="CN69" s="185"/>
-      <c r="CO69" s="185"/>
-      <c r="CP69" s="185"/>
-      <c r="CQ69" s="185"/>
+      <c r="CE69" s="175"/>
+      <c r="CF69" s="175"/>
+      <c r="CG69" s="175"/>
+      <c r="CH69" s="175"/>
+      <c r="CI69" s="175"/>
+      <c r="CJ69" s="175"/>
+      <c r="CK69" s="163"/>
+      <c r="CL69" s="163"/>
+      <c r="CM69" s="163"/>
+      <c r="CN69" s="163"/>
+      <c r="CO69" s="163"/>
+      <c r="CP69" s="163"/>
+      <c r="CQ69" s="163"/>
     </row>
     <row r="70" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A70" s="16">
@@ -55707,7 +55723,7 @@
         <f>BH70/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK70" s="163">
+      <c r="BK70" s="173">
         <v>87</v>
       </c>
       <c r="BL70" s="24" t="str">
@@ -55943,7 +55959,7 @@
         <f>BH71/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK71" s="164"/>
+      <c r="BK71" s="174"/>
       <c r="BL71" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!J3,AK80:AS91,9,FALSE),"3rd Group D/E/I/J/L")</f>
         <v>3rd Group D/E/I/J/L</v>
@@ -57350,7 +57366,7 @@
       </c>
       <c r="AD80" s="123">
         <f>COUNTIF($AP$80:$AP$91,CONCATENATE("&gt;=",AP80))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE80" s="124" t="str">
         <f>J11</f>
@@ -57452,7 +57468,7 @@
       </c>
       <c r="AD81" s="123">
         <f t="shared" ref="AD81:AD91" si="38">COUNTIF($AP$80:$AP$91,CONCATENATE("&gt;=",AP81))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE81" s="124" t="str">
         <f>J17</f>
@@ -57619,18 +57635,18 @@
     <row r="83" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="73"/>
       <c r="B83" s="73"/>
-      <c r="C83" s="186" t="s">
+      <c r="C83" s="164" t="s">
         <v>3183</v>
       </c>
-      <c r="D83" s="187"/>
-      <c r="E83" s="187"/>
-      <c r="F83" s="187"/>
-      <c r="G83" s="188"/>
+      <c r="D83" s="165"/>
+      <c r="E83" s="165"/>
+      <c r="F83" s="165"/>
+      <c r="G83" s="166"/>
       <c r="H83" s="75"/>
       <c r="I83" s="69"/>
       <c r="J83" s="99" t="str">
         <f>VLOOKUP(3,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓓ Paraguay</v>
+        <v>Ⓙ Algeria</v>
       </c>
       <c r="K83" s="100">
         <f t="shared" si="47"/>
@@ -57658,7 +57674,7 @@
       </c>
       <c r="AD83" s="123">
         <f t="shared" si="38"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE83" s="124" t="str">
         <f>J29</f>
@@ -57723,16 +57739,16 @@
     <row r="84" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="73"/>
       <c r="B84" s="73"/>
-      <c r="C84" s="189"/>
-      <c r="D84" s="190"/>
-      <c r="E84" s="190"/>
-      <c r="F84" s="190"/>
-      <c r="G84" s="191"/>
+      <c r="C84" s="167"/>
+      <c r="D84" s="168"/>
+      <c r="E84" s="168"/>
+      <c r="F84" s="168"/>
+      <c r="G84" s="169"/>
       <c r="H84" s="75"/>
       <c r="I84" s="69"/>
       <c r="J84" s="99" t="str">
         <f>VLOOKUP(4,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓗ Cape Verde</v>
+        <v>Ⓓ Paraguay</v>
       </c>
       <c r="K84" s="100">
         <f t="shared" si="47"/>
@@ -57740,23 +57756,23 @@
       </c>
       <c r="L84" s="100">
         <f>VLOOKUP(4,$AD$80:$AN$91,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M84" s="100">
         <f>VLOOKUP(4,$AD$80:$AN$91,4,FALSE)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N84" s="100">
         <f>VLOOKUP(4,$AD$80:$AN$91,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O84" s="100" t="str">
         <f>VLOOKUP(4,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(4,$AD$80:$AN$91,7,FALSE)</f>
-        <v>2 - 2</v>
+        <v>2 - 4</v>
       </c>
       <c r="P84" s="101">
         <f t="shared" si="48"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R84" s="123">
         <f>DATE(2026,12,3)+TIME(4,0,0)+gmt_delta</f>
@@ -57772,7 +57788,7 @@
       </c>
       <c r="AD84" s="123">
         <f t="shared" si="38"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE84" s="124" t="str">
         <f>J35</f>
@@ -57823,11 +57839,11 @@
       </c>
       <c r="AR84" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ACDE</v>
+        <v>ACD</v>
       </c>
       <c r="AS84" s="129" t="str">
         <f t="shared" si="46"/>
-        <v>Ecuador</v>
+        <v/>
       </c>
       <c r="AT84" s="130" t="str">
         <f>"Ⓔ "&amp;AE84</f>
@@ -57837,16 +57853,16 @@
     <row r="85" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="73"/>
       <c r="B85" s="73"/>
-      <c r="C85" s="189"/>
-      <c r="D85" s="190"/>
-      <c r="E85" s="190"/>
-      <c r="F85" s="190"/>
-      <c r="G85" s="191"/>
+      <c r="C85" s="167"/>
+      <c r="D85" s="168"/>
+      <c r="E85" s="168"/>
+      <c r="F85" s="168"/>
+      <c r="G85" s="169"/>
       <c r="H85" s="75"/>
       <c r="I85" s="69"/>
       <c r="J85" s="99" t="str">
         <f>VLOOKUP(5,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓖ Belgium</v>
+        <v>Ⓗ Cape Verde</v>
       </c>
       <c r="K85" s="100">
         <f t="shared" si="47"/>
@@ -57866,7 +57882,7 @@
       </c>
       <c r="O85" s="100" t="str">
         <f>VLOOKUP(5,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(5,$AD$80:$AN$91,7,FALSE)</f>
-        <v>1 - 1</v>
+        <v>2 - 2</v>
       </c>
       <c r="P85" s="101">
         <f t="shared" si="48"/>
@@ -57937,7 +57953,7 @@
       </c>
       <c r="AR85" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ACDEF</v>
+        <v>ACDF</v>
       </c>
       <c r="AS85" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57951,20 +57967,20 @@
     <row r="86" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="73"/>
       <c r="B86" s="73"/>
-      <c r="C86" s="189"/>
-      <c r="D86" s="190"/>
-      <c r="E86" s="190"/>
-      <c r="F86" s="190"/>
-      <c r="G86" s="191"/>
+      <c r="C86" s="167"/>
+      <c r="D86" s="168"/>
+      <c r="E86" s="168"/>
+      <c r="F86" s="168"/>
+      <c r="G86" s="169"/>
       <c r="H86" s="75"/>
       <c r="I86" s="69"/>
       <c r="J86" s="99" t="str">
         <f>VLOOKUP(6,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓚ DR Congo</v>
+        <v>Ⓖ Belgium</v>
       </c>
       <c r="K86" s="100">
         <f t="shared" si="47"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L86" s="100">
         <f>VLOOKUP(6,$AD$80:$AN$91,3,FALSE)</f>
@@ -57972,7 +57988,7 @@
       </c>
       <c r="M86" s="100">
         <f>VLOOKUP(6,$AD$80:$AN$91,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N86" s="100">
         <f>VLOOKUP(6,$AD$80:$AN$91,5,FALSE)</f>
@@ -57984,7 +58000,7 @@
       </c>
       <c r="P86" s="101">
         <f t="shared" si="48"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R86" s="123">
         <f>DATE(2026,12,4)+TIME(8,0,0)+gmt_delta</f>
@@ -58000,7 +58016,7 @@
       </c>
       <c r="AD86" s="123">
         <f t="shared" si="38"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE86" s="124" t="str">
         <f>J47</f>
@@ -58051,7 +58067,7 @@
       </c>
       <c r="AR86" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ACDEFG</v>
+        <v>ACDFG</v>
       </c>
       <c r="AS86" s="129" t="str">
         <f t="shared" si="46"/>
@@ -58065,20 +58081,20 @@
     <row r="87" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="73"/>
       <c r="B87" s="73"/>
-      <c r="C87" s="189"/>
-      <c r="D87" s="190"/>
-      <c r="E87" s="190"/>
-      <c r="F87" s="190"/>
-      <c r="G87" s="191"/>
+      <c r="C87" s="167"/>
+      <c r="D87" s="168"/>
+      <c r="E87" s="168"/>
+      <c r="F87" s="168"/>
+      <c r="G87" s="169"/>
       <c r="H87" s="75"/>
       <c r="I87" s="69"/>
       <c r="J87" s="99" t="str">
         <f>VLOOKUP(7,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓐ Czech Republic</v>
+        <v>Ⓚ DR Congo</v>
       </c>
       <c r="K87" s="100">
         <f t="shared" si="47"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L87" s="100">
         <f>VLOOKUP(7,$AD$80:$AN$91,3,FALSE)</f>
@@ -58090,11 +58106,11 @@
       </c>
       <c r="N87" s="100">
         <f>VLOOKUP(7,$AD$80:$AN$91,5,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O87" s="100" t="str">
         <f>VLOOKUP(7,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(7,$AD$80:$AN$91,7,FALSE)</f>
-        <v>2 - 3</v>
+        <v>1 - 1</v>
       </c>
       <c r="P87" s="101">
         <f t="shared" si="48"/>
@@ -58114,7 +58130,7 @@
       </c>
       <c r="AD87" s="123">
         <f t="shared" si="38"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE87" s="124" t="str">
         <f>J53</f>
@@ -58165,7 +58181,7 @@
       </c>
       <c r="AR87" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ACDEFGH</v>
+        <v>ACDFGH</v>
       </c>
       <c r="AS87" s="129" t="str">
         <f t="shared" si="46"/>
@@ -58179,16 +58195,16 @@
     <row r="88" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="73"/>
       <c r="B88" s="73"/>
-      <c r="C88" s="192"/>
-      <c r="D88" s="193"/>
-      <c r="E88" s="193"/>
-      <c r="F88" s="193"/>
-      <c r="G88" s="194"/>
+      <c r="C88" s="170"/>
+      <c r="D88" s="171"/>
+      <c r="E88" s="171"/>
+      <c r="F88" s="171"/>
+      <c r="G88" s="172"/>
       <c r="H88" s="75"/>
       <c r="I88" s="69"/>
       <c r="J88" s="99" t="str">
         <f>VLOOKUP(8,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓔ Ecuador</v>
+        <v>Ⓐ Czech Republic</v>
       </c>
       <c r="K88" s="100">
         <f t="shared" si="47"/>
@@ -58208,7 +58224,7 @@
       </c>
       <c r="O88" s="100" t="str">
         <f>VLOOKUP(8,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(8,$AD$80:$AN$91,7,FALSE)</f>
-        <v>0 - 1</v>
+        <v>2 - 3</v>
       </c>
       <c r="P88" s="101">
         <f t="shared" si="48"/>
@@ -58228,7 +58244,7 @@
       </c>
       <c r="AD88" s="123">
         <f t="shared" si="38"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AE88" s="124" t="str">
         <f>J59</f>
@@ -58244,26 +58260,26 @@
       </c>
       <c r="AH88" s="123">
         <f t="shared" si="40"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI88" s="123">
         <f t="shared" si="41"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AJ88" s="123">
         <f t="shared" si="42"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AK88" s="123" t="s">
         <v>3189</v>
       </c>
       <c r="AL88" s="123">
         <f t="shared" si="43"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AM88" s="123">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN88" s="123">
         <f t="shared" si="45"/>
@@ -58271,7 +58287,7 @@
       </c>
       <c r="AP88" s="123">
         <f>AN88/AN92*10000+AM88/AM92*1000+AI88/AI92*100+IF(AQ88=0,ROW(),AQ88)/2000000</f>
-        <v>264.2865587807143</v>
+        <v>42.857987352142857</v>
       </c>
       <c r="AQ88" s="126">
         <f t="shared" si="37"/>
@@ -58279,7 +58295,7 @@
       </c>
       <c r="AR88" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ACDEFGH</v>
+        <v>ACDFGH</v>
       </c>
       <c r="AS88" s="129" t="str">
         <f t="shared" si="46"/>
@@ -58302,7 +58318,7 @@
       <c r="I89" s="69"/>
       <c r="J89" s="102" t="str">
         <f>VLOOKUP(9,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓑ Bosnia and Herzegovina</v>
+        <v>Ⓔ Ecuador</v>
       </c>
       <c r="K89" s="103">
         <f t="shared" si="47"/>
@@ -58322,7 +58338,7 @@
       </c>
       <c r="O89" s="103" t="str">
         <f>VLOOKUP(9,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(9,$AD$80:$AN$91,7,FALSE)</f>
-        <v>2 - 5</v>
+        <v>0 - 1</v>
       </c>
       <c r="P89" s="104">
         <f t="shared" si="48"/>
@@ -58342,15 +58358,15 @@
       </c>
       <c r="AD89" s="123">
         <f t="shared" si="38"/>
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AE89" s="124" t="str">
         <f>J65</f>
-        <v>Jordan</v>
+        <v>Algeria</v>
       </c>
       <c r="AF89" s="123">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG89" s="123">
         <f t="shared" si="49"/>
@@ -58362,11 +58378,11 @@
       </c>
       <c r="AI89" s="123">
         <f t="shared" si="41"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ89" s="123">
         <f t="shared" si="42"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK89" s="123" t="s">
         <v>3190</v>
@@ -58381,27 +58397,27 @@
       </c>
       <c r="AN89" s="123">
         <f t="shared" si="45"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP89" s="123">
         <f>AN89/AN92*10000+AM89/AM92*1000+AI89/AI92*100+IF(AQ89=0,ROW(),AQ89)/2000000</f>
-        <v>264.28641001071429</v>
+        <v>7778.572210701428</v>
       </c>
       <c r="AQ89" s="126">
         <f t="shared" si="37"/>
-        <v>1391.45</v>
+        <v>1564.26</v>
       </c>
       <c r="AR89" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ACDEFGH</v>
+        <v>ACDFGHJ</v>
       </c>
       <c r="AS89" s="129" t="str">
         <f t="shared" si="46"/>
-        <v/>
+        <v>Algeria</v>
       </c>
       <c r="AT89" s="130" t="str">
         <f>"Ⓙ "&amp;AE89</f>
-        <v>Ⓙ Jordan</v>
+        <v>Ⓙ Algeria</v>
       </c>
     </row>
     <row r="90" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -58416,11 +58432,11 @@
       <c r="I90" s="69"/>
       <c r="J90" s="102" t="str">
         <f>VLOOKUP(10,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓛ Panama</v>
+        <v>Ⓑ Bosnia and Herzegovina</v>
       </c>
       <c r="K90" s="103">
         <f t="shared" si="47"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L90" s="103">
         <f>VLOOKUP(10,$AD$80:$AN$91,3,FALSE)</f>
@@ -58428,7 +58444,7 @@
       </c>
       <c r="M90" s="103">
         <f>VLOOKUP(10,$AD$80:$AN$91,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N90" s="103">
         <f>VLOOKUP(10,$AD$80:$AN$91,5,FALSE)</f>
@@ -58436,11 +58452,11 @@
       </c>
       <c r="O90" s="103" t="str">
         <f>VLOOKUP(10,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(10,$AD$80:$AN$91,7,FALSE)</f>
-        <v>0 - 1</v>
+        <v>2 - 5</v>
       </c>
       <c r="P90" s="104">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R90" s="123">
         <f>DATE(2026,12,6)+TIME(4,0,0)+gmt_delta</f>
@@ -58456,7 +58472,7 @@
       </c>
       <c r="AD90" s="123">
         <f t="shared" si="38"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE90" s="124" t="str">
         <f>J71</f>
@@ -58507,7 +58523,7 @@
       </c>
       <c r="AR90" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ACDEFGHK</v>
+        <v>ACDFGHJK</v>
       </c>
       <c r="AS90" s="129" t="str">
         <f t="shared" si="46"/>
@@ -58530,7 +58546,7 @@
       <c r="I91" s="69"/>
       <c r="J91" s="102" t="str">
         <f>VLOOKUP(11,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓘ Senegal</v>
+        <v>Ⓛ Panama</v>
       </c>
       <c r="K91" s="103">
         <f t="shared" si="47"/>
@@ -58550,7 +58566,7 @@
       </c>
       <c r="O91" s="103" t="str">
         <f>VLOOKUP(11,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(11,$AD$80:$AN$91,7,FALSE)</f>
-        <v>1 - 3</v>
+        <v>0 - 1</v>
       </c>
       <c r="P91" s="104">
         <f t="shared" si="48"/>
@@ -58570,7 +58586,7 @@
       </c>
       <c r="AD91" s="123">
         <f t="shared" si="38"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AE91" s="124" t="str">
         <f>J77</f>
@@ -58621,7 +58637,7 @@
       </c>
       <c r="AR91" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ACDEFGHK</v>
+        <v>ACDFGHJK</v>
       </c>
       <c r="AS91" s="129" t="str">
         <f t="shared" si="46"/>
@@ -58644,11 +58660,11 @@
       <c r="I92" s="69"/>
       <c r="J92" s="105" t="str">
         <f>VLOOKUP(12,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓙ Jordan</v>
+        <v>Ⓘ Senegal</v>
       </c>
       <c r="K92" s="106">
         <f t="shared" si="47"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L92" s="106">
         <f>VLOOKUP(12,$AD$80:$AN$91,3,FALSE)</f>
@@ -58660,11 +58676,11 @@
       </c>
       <c r="N92" s="106">
         <f>VLOOKUP(12,$AD$80:$AN$91,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O92" s="106" t="str">
         <f>VLOOKUP(12,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(12,$AD$80:$AN$91,7,FALSE)</f>
-        <v>1 - 3</v>
+        <v>3 - 6</v>
       </c>
       <c r="P92" s="107">
         <f t="shared" si="48"/>
@@ -58680,7 +58696,7 @@
       </c>
       <c r="AH92" s="123">
         <f>MAX(AH80:AH91)+1</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI92" s="123">
         <f>MAX(AI80:AI91)+1</f>
@@ -58861,6 +58877,36 @@
   <sheetProtection algorithmName="SHA-512" hashValue="7nWuIQAsd0NKRlhwUK3tOeNHpTch5B5FULy2gxNNaIdJM5RfhFSMzPcx55y+pmM3d73guUy+p5Y+SvIjJZQRaA==" saltValue="Uw23KnM8csnTioq5H8upCA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <dataConsolidate/>
   <mergeCells count="45">
+    <mergeCell ref="BK14:BK15"/>
+    <mergeCell ref="BY16:BY17"/>
+    <mergeCell ref="BK26:BK27"/>
+    <mergeCell ref="BR28:BR29"/>
+    <mergeCell ref="BK22:BK23"/>
+    <mergeCell ref="CF23:CF24"/>
+    <mergeCell ref="BK18:BK19"/>
+    <mergeCell ref="BR20:BR21"/>
+    <mergeCell ref="CM48:CM49"/>
+    <mergeCell ref="BR44:BR45"/>
+    <mergeCell ref="BK46:BK47"/>
+    <mergeCell ref="BK30:BK31"/>
+    <mergeCell ref="CM44:CQ45"/>
+    <mergeCell ref="BY32:BY33"/>
+    <mergeCell ref="BK38:BK39"/>
+    <mergeCell ref="BK34:BK35"/>
+    <mergeCell ref="BR36:BR37"/>
+    <mergeCell ref="BK42:BK43"/>
+    <mergeCell ref="CM33:CQ34"/>
+    <mergeCell ref="CM37:CM38"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="BR12:BR13"/>
+    <mergeCell ref="BK6:BO7"/>
+    <mergeCell ref="BR6:BV7"/>
+    <mergeCell ref="BY6:CC7"/>
+    <mergeCell ref="CF6:CJ7"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="A5:H6"/>
+    <mergeCell ref="J5:P6"/>
     <mergeCell ref="CK68:CQ69"/>
     <mergeCell ref="C83:G88"/>
     <mergeCell ref="BK70:BK71"/>
@@ -58876,36 +58922,6 @@
     <mergeCell ref="BR52:BR53"/>
     <mergeCell ref="BK54:BK55"/>
     <mergeCell ref="CE68:CJ69"/>
-    <mergeCell ref="CF6:CJ7"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="A5:H6"/>
-    <mergeCell ref="J5:P6"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="BR12:BR13"/>
-    <mergeCell ref="BK6:BO7"/>
-    <mergeCell ref="BR6:BV7"/>
-    <mergeCell ref="BY6:CC7"/>
-    <mergeCell ref="CF23:CF24"/>
-    <mergeCell ref="BK18:BK19"/>
-    <mergeCell ref="BR20:BR21"/>
-    <mergeCell ref="CM48:CM49"/>
-    <mergeCell ref="BR44:BR45"/>
-    <mergeCell ref="BK46:BK47"/>
-    <mergeCell ref="BK30:BK31"/>
-    <mergeCell ref="CM44:CQ45"/>
-    <mergeCell ref="BY32:BY33"/>
-    <mergeCell ref="BK38:BK39"/>
-    <mergeCell ref="BK34:BK35"/>
-    <mergeCell ref="BR36:BR37"/>
-    <mergeCell ref="BK42:BK43"/>
-    <mergeCell ref="CM33:CQ34"/>
-    <mergeCell ref="CM37:CM38"/>
-    <mergeCell ref="BK14:BK15"/>
-    <mergeCell ref="BY16:BY17"/>
-    <mergeCell ref="BK26:BK27"/>
-    <mergeCell ref="BR28:BR29"/>
-    <mergeCell ref="BK22:BK23"/>
   </mergeCells>
   <conditionalFormatting sqref="A7:E78">
     <cfRule type="expression" dxfId="228" priority="339">
@@ -60202,11 +60218,11 @@
     <row r="3" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B3" s="109">
         <f>MATCH(C3,C6:C500,0)</f>
-        <v>283</v>
+        <v>247</v>
       </c>
       <c r="C3" s="121" t="str">
         <f>'2026 World Cup'!AR91</f>
-        <v>ACDEFGHK</v>
+        <v>ACDFGHJK</v>
       </c>
       <c r="D3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,2,FALSE)</f>
@@ -60218,7 +60234,7 @@
       </c>
       <c r="F3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,4,FALSE)</f>
-        <v>3E</v>
+        <v>3J</v>
       </c>
       <c r="G3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,5,FALSE)</f>

--- a/public/worldcup.xlsx
+++ b/public/worldcup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rylanpaul/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6B4F149-D3DA-2E43-B83F-DAD8DE8EE622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E563C63E-6689-6045-B8E5-33FA7CF8C24B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T" sheetId="1" state="hidden" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9885" uniqueCount="3715">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9891" uniqueCount="3715">
   <si>
     <t>English</t>
   </si>
@@ -38721,6 +38721,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(F3,Rounds!E$2:E$25,Rounds!H$2:H$25), _xlfn.XLOOKUP(F3,Rounds!H$2:H$25,Rounds!E$2:E$25))</f>
         <v>Australia</v>
       </c>
+      <c r="J3" t="s">
+        <v>2201</v>
+      </c>
       <c r="K3" s="142" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(J3,Rounds!I$2:I$25,Rounds!J$2:J$25), _xlfn.XLOOKUP(J3,Rounds!L$2:L$25,Rounds!K$2:K$25))</f>
         <v>#N/A</v>
@@ -38729,9 +38732,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(J3,Rounds!I$2:I$25,Rounds!K$2:K$25), _xlfn.XLOOKUP(J3,Rounds!L$2:L$25,Rounds!J$2:J$25))</f>
         <v>#N/A</v>
       </c>
-      <c r="M3" s="140" t="e">
+      <c r="M3" s="140" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(J3,Rounds!I$2:I$25,Rounds!L$2:L$25), _xlfn.XLOOKUP(J3,Rounds!L$2:L$25,Rounds!I$2:I$25))</f>
-        <v>#N/A</v>
+        <v>Curaçao</v>
       </c>
       <c r="O3" s="142" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(N3,Rounds!M$2:M$17,Rounds!N$2:N$17), _xlfn.XLOOKUP(N3,Rounds!P$2:P$17,Rounds!O$2:O$17))</f>
@@ -38828,6 +38831,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(F4,Rounds!E$2:E$25,Rounds!H$2:H$25), _xlfn.XLOOKUP(F4,Rounds!H$2:H$25,Rounds!E$2:E$25))</f>
         <v>New Zealand</v>
       </c>
+      <c r="J4" s="148" t="s">
+        <v>1677</v>
+      </c>
       <c r="K4" s="146" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(J4,Rounds!I$2:I$25,Rounds!J$2:J$25), _xlfn.XLOOKUP(J4,Rounds!L$2:L$25,Rounds!K$2:K$25))</f>
         <v>#N/A</v>
@@ -38836,9 +38842,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(J4,Rounds!I$2:I$25,Rounds!K$2:K$25), _xlfn.XLOOKUP(J4,Rounds!L$2:L$25,Rounds!J$2:J$25))</f>
         <v>#N/A</v>
       </c>
-      <c r="M4" s="147" t="e">
+      <c r="M4" s="147" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(J4,Rounds!I$2:I$25,Rounds!L$2:L$25), _xlfn.XLOOKUP(J4,Rounds!L$2:L$25,Rounds!I$2:I$25))</f>
-        <v>#N/A</v>
+        <v>Haiti</v>
       </c>
       <c r="O4" s="146" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(N4,Rounds!M$2:M$17,Rounds!N$2:N$17), _xlfn.XLOOKUP(N4,Rounds!P$2:P$17,Rounds!O$2:O$17))</f>
@@ -38935,6 +38941,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(F5,Rounds!E$2:E$25,Rounds!H$2:H$25), _xlfn.XLOOKUP(F5,Rounds!H$2:H$25,Rounds!E$2:E$25))</f>
         <v>Curaçao</v>
       </c>
+      <c r="J5" t="s">
+        <v>1323</v>
+      </c>
       <c r="K5" s="82" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(J5,Rounds!I$2:I$25,Rounds!J$2:J$25), _xlfn.XLOOKUP(J5,Rounds!L$2:L$25,Rounds!K$2:K$25))</f>
         <v>#N/A</v>
@@ -38943,9 +38952,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(J5,Rounds!I$2:I$25,Rounds!K$2:K$25), _xlfn.XLOOKUP(J5,Rounds!L$2:L$25,Rounds!J$2:J$25))</f>
         <v>#N/A</v>
       </c>
-      <c r="M5" s="134" t="e">
+      <c r="M5" s="134" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(J5,Rounds!I$2:I$25,Rounds!L$2:L$25), _xlfn.XLOOKUP(J5,Rounds!L$2:L$25,Rounds!I$2:I$25))</f>
-        <v>#N/A</v>
+        <v>Czech Republic</v>
       </c>
       <c r="O5" s="82" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(N5,Rounds!M$2:M$17,Rounds!N$2:N$17), _xlfn.XLOOKUP(N5,Rounds!P$2:P$17,Rounds!O$2:O$17))</f>
@@ -39042,6 +39051,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(F6,Rounds!E$2:E$25,Rounds!H$2:H$25), _xlfn.XLOOKUP(F6,Rounds!H$2:H$25,Rounds!E$2:E$25))</f>
         <v>Tunisia</v>
       </c>
+      <c r="J6" s="148" t="s">
+        <v>2201</v>
+      </c>
       <c r="K6" s="146" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(J6,Rounds!I$2:I$25,Rounds!J$2:J$25), _xlfn.XLOOKUP(J6,Rounds!L$2:L$25,Rounds!K$2:K$25))</f>
         <v>#N/A</v>
@@ -39050,9 +39062,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(J6,Rounds!I$2:I$25,Rounds!K$2:K$25), _xlfn.XLOOKUP(J6,Rounds!L$2:L$25,Rounds!J$2:J$25))</f>
         <v>#N/A</v>
       </c>
-      <c r="M6" s="147" t="e">
+      <c r="M6" s="147" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(J6,Rounds!I$2:I$25,Rounds!L$2:L$25), _xlfn.XLOOKUP(J6,Rounds!L$2:L$25,Rounds!I$2:I$25))</f>
-        <v>#N/A</v>
+        <v>Curaçao</v>
       </c>
       <c r="O6" s="146" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(N6,Rounds!M$2:M$17,Rounds!N$2:N$17), _xlfn.XLOOKUP(N6,Rounds!P$2:P$17,Rounds!O$2:O$17))</f>
@@ -39149,6 +39161,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(F7,Rounds!E$2:E$25,Rounds!H$2:H$25), _xlfn.XLOOKUP(F7,Rounds!H$2:H$25,Rounds!E$2:E$25))</f>
         <v>New Zealand</v>
       </c>
+      <c r="J7" t="s">
+        <v>1995</v>
+      </c>
       <c r="K7" s="82" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(J7,Rounds!I$2:I$25,Rounds!J$2:J$25), _xlfn.XLOOKUP(J7,Rounds!L$2:L$25,Rounds!K$2:K$25))</f>
         <v>#N/A</v>
@@ -39157,9 +39172,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(J7,Rounds!I$2:I$25,Rounds!K$2:K$25), _xlfn.XLOOKUP(J7,Rounds!L$2:L$25,Rounds!J$2:J$25))</f>
         <v>#N/A</v>
       </c>
-      <c r="M7" s="134" t="e">
+      <c r="M7" s="134" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(J7,Rounds!I$2:I$25,Rounds!L$2:L$25), _xlfn.XLOOKUP(J7,Rounds!L$2:L$25,Rounds!I$2:I$25))</f>
-        <v>#N/A</v>
+        <v>Qatar</v>
       </c>
       <c r="O7" s="82" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(N7,Rounds!M$2:M$17,Rounds!N$2:N$17), _xlfn.XLOOKUP(N7,Rounds!P$2:P$17,Rounds!O$2:O$17))</f>
@@ -39256,7 +39271,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(F8,Rounds!E$2:E$25,Rounds!H$2:H$25), _xlfn.XLOOKUP(F8,Rounds!H$2:H$25,Rounds!E$2:E$25))</f>
         <v>Curaçao</v>
       </c>
-      <c r="J8" s="152"/>
+      <c r="J8" s="152" t="s">
+        <v>1677</v>
+      </c>
       <c r="K8" s="150" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(J8,Rounds!I$2:I$25,Rounds!J$2:J$25), _xlfn.XLOOKUP(J8,Rounds!L$2:L$25,Rounds!K$2:K$25))</f>
         <v>#N/A</v>
@@ -39265,9 +39282,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(J8,Rounds!I$2:I$25,Rounds!K$2:K$25), _xlfn.XLOOKUP(J8,Rounds!L$2:L$25,Rounds!J$2:J$25))</f>
         <v>#N/A</v>
       </c>
-      <c r="M8" s="151" t="e">
+      <c r="M8" s="151" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(J8,Rounds!I$2:I$25,Rounds!L$2:L$25), _xlfn.XLOOKUP(J8,Rounds!L$2:L$25,Rounds!I$2:I$25))</f>
-        <v>#N/A</v>
+        <v>Haiti</v>
       </c>
       <c r="N8" s="152"/>
       <c r="O8" s="150" t="e">
@@ -40731,11 +40748,11 @@
       <c r="E22" s="132" t="str">
         <v>England</v>
       </c>
-      <c r="F22" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G22" s="81" t="e">
-        <v>#N/A</v>
+      <c r="F22" s="81">
+        <v>0</v>
+      </c>
+      <c r="G22" s="81">
+        <v>0</v>
       </c>
       <c r="H22" s="134" t="str">
         <v>Ghana</v>
@@ -40769,11 +40786,11 @@
       <c r="E23" s="132" t="str">
         <v>Panama</v>
       </c>
-      <c r="F23" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G23" s="81" t="e">
-        <v>#N/A</v>
+      <c r="F23" s="81">
+        <v>0</v>
+      </c>
+      <c r="G23" s="81">
+        <v>1</v>
       </c>
       <c r="H23" s="134" t="str">
         <v>Croatia</v>
@@ -40807,11 +40824,11 @@
       <c r="E24" s="132" t="str">
         <v>Portugal</v>
       </c>
-      <c r="F24" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G24" s="81" t="e">
-        <v>#N/A</v>
+      <c r="F24" s="81">
+        <v>5</v>
+      </c>
+      <c r="G24" s="81">
+        <v>0</v>
       </c>
       <c r="H24" s="134" t="str">
         <v>Uzbekistan</v>
@@ -40845,11 +40862,11 @@
       <c r="E25" s="135" t="str">
         <v>Colombia</v>
       </c>
-      <c r="F25" s="153" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G25" s="153" t="e">
-        <v>#N/A</v>
+      <c r="F25" s="153">
+        <v>1</v>
+      </c>
+      <c r="G25" s="153">
+        <v>0</v>
       </c>
       <c r="H25" s="136" t="str">
         <v>DR Congo</v>
@@ -46352,27 +46369,27 @@
       </c>
       <c r="U29" s="123">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" s="123">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W29" s="123">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X29" s="123">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y29" s="123">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z29" s="123">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA29" s="123">
         <f t="shared" si="5"/>
@@ -51246,8 +51263,12 @@
         <f>AE74</f>
         <v>England</v>
       </c>
-      <c r="F51" s="19"/>
-      <c r="G51" s="20"/>
+      <c r="F51" s="19">
+        <v>0</v>
+      </c>
+      <c r="G51" s="20">
+        <v>0</v>
+      </c>
       <c r="H51" s="80" t="str">
         <f>AE76</f>
         <v>Ghana</v>
@@ -51286,15 +51307,15 @@
       </c>
       <c r="S51" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>England_draw</v>
       </c>
       <c r="T51" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Ghana_draw</v>
       </c>
       <c r="U51" s="123">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V51" s="123">
         <f t="shared" si="21"/>
@@ -51306,7 +51327,7 @@
       </c>
       <c r="X51" s="123">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y51" s="123">
         <f t="shared" si="10"/>
@@ -51320,9 +51341,9 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB51" s="123" t="str">
+      <c r="AB51" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AD51" s="123">
         <f>COUNTIF(AR50:AR53,CONCATENATE("&gt;=",AR51))</f>
@@ -51503,8 +51524,12 @@
         <f>AE77</f>
         <v>Panama</v>
       </c>
-      <c r="F52" s="19"/>
-      <c r="G52" s="20"/>
+      <c r="F52" s="19">
+        <v>0</v>
+      </c>
+      <c r="G52" s="20">
+        <v>1</v>
+      </c>
       <c r="H52" s="80" t="str">
         <f>AE75</f>
         <v>Croatia</v>
@@ -51543,11 +51568,11 @@
       </c>
       <c r="S52" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Panama_lose</v>
       </c>
       <c r="T52" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Croatia_win</v>
       </c>
       <c r="U52" s="123">
         <f t="shared" si="8"/>
@@ -51577,9 +51602,9 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB52" s="123" t="str">
+      <c r="AB52" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>-1</v>
       </c>
       <c r="AD52" s="123">
         <f>COUNTIF(AR50:AR53,CONCATENATE("&gt;=",AR52))</f>
@@ -51752,8 +51777,12 @@
         <f>AE68</f>
         <v>Portugal</v>
       </c>
-      <c r="F53" s="19"/>
-      <c r="G53" s="20"/>
+      <c r="F53" s="19">
+        <v>5</v>
+      </c>
+      <c r="G53" s="20">
+        <v>0</v>
+      </c>
       <c r="H53" s="80" t="str">
         <f>AE70</f>
         <v>Uzbekistan</v>
@@ -51792,11 +51821,11 @@
       </c>
       <c r="S53" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Portugal_win</v>
       </c>
       <c r="T53" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Uzbekistan_lose</v>
       </c>
       <c r="U53" s="123">
         <f t="shared" si="8"/>
@@ -51826,9 +51855,9 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB53" s="123" t="str">
+      <c r="AB53" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD53" s="123">
         <f>COUNTIF(AR50:AR53,CONCATENATE("&gt;=",AR53))</f>
@@ -52005,8 +52034,12 @@
         <f>AE71</f>
         <v>Colombia</v>
       </c>
-      <c r="F54" s="19"/>
-      <c r="G54" s="20"/>
+      <c r="F54" s="19">
+        <v>1</v>
+      </c>
+      <c r="G54" s="20">
+        <v>0</v>
+      </c>
       <c r="H54" s="80" t="str">
         <f>AE69</f>
         <v>DR Congo</v>
@@ -52045,11 +52078,11 @@
       </c>
       <c r="S54" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Colombia_win</v>
       </c>
       <c r="T54" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>DR Congo_lose</v>
       </c>
       <c r="U54" s="123">
         <f t="shared" si="8"/>
@@ -52079,9 +52112,9 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB54" s="123" t="str">
+      <c r="AB54" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AF54" s="123">
         <f t="shared" ref="AF54:AH54" si="25">MAX(AF50:AF53)-MIN(AF50:AF53)+1</f>
@@ -55087,7 +55120,7 @@
       </c>
       <c r="AF68" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE68 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG68" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE68 &amp; "_draw")</f>
@@ -55099,7 +55132,7 @@
       </c>
       <c r="AI68" s="123">
         <f>SUMIF($E$7:$E$78,$AE68,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE68,$G$7:$G$78)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AJ68" s="123">
         <f>SUMIF($E$7:$E$78,$AE68,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE68,$F$7:$F$78)</f>
@@ -55107,23 +55140,23 @@
       </c>
       <c r="AL68" s="123">
         <f>AI68-AJ68</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AM68" s="123">
         <f>AL68-AL72</f>
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AN68" s="123">
         <f>AF68*3+AG68</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AO68" s="123">
         <f>AN68/AN72*10+BA68</f>
-        <v>3.4805825242718447</v>
+        <v>5.7142857142857135</v>
       </c>
       <c r="AP68" s="123">
         <f>AO68*10000000+BI68*100+AM68/AM72*10+AI68/AI72*1++IF(AQ68=0,ROW(),AQ68)/2000000</f>
-        <v>34805927.551852785</v>
+        <v>57142867.231651142</v>
       </c>
       <c r="AQ68" s="126">
         <f>VLOOKUP(AE68,db_fifarank,2,FALSE)</f>
@@ -55131,7 +55164,7 @@
       </c>
       <c r="AR68" s="125">
         <f>AP68/AP72</f>
-        <v>0.46407897368919898</v>
+        <v>0.66666671231139207</v>
       </c>
       <c r="AS68" s="125" t="str">
         <f>IF(SUM(AF68:AH71)=12,J69,"1K")</f>
@@ -55143,15 +55176,15 @@
       </c>
       <c r="AU68" s="126" cm="1">
         <f t="array" ref="AU68">SUMPRODUCT(($S$7:$S$78=AE68&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE68&amp;"_draw")*($U$7:$U$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV68" s="126" cm="1">
         <f t="array" ref="AV68">SUMPRODUCT(($E$7:$E$78=AE68)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE68)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW68" s="126" cm="1">
         <f t="array" ref="AW68">SUMPRODUCT(($E$7:$E$78=AE68)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE68)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX68" s="126">
         <f>AV68-AW68</f>
@@ -55163,11 +55196,11 @@
       </c>
       <c r="AZ68" s="126">
         <f>AT68/AT72*1000+AU68/AU72*100+AY68/AY72*10+AV68/AV72</f>
-        <v>50.5</v>
+        <v>0</v>
       </c>
       <c r="BA68" s="126">
         <f>AZ68/AZ72</f>
-        <v>0.98058252427184467</v>
+        <v>0</v>
       </c>
       <c r="BB68" s="126" cm="1">
         <f t="array" ref="BB68">SUMPRODUCT(($S$7:$S$78=AE68&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE68&amp;"_win")*($X$7:$X$78))</f>
@@ -55175,15 +55208,15 @@
       </c>
       <c r="BC68" s="126" cm="1">
         <f t="array" ref="BC68">SUMPRODUCT(($S$7:$S$78=AE68&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE68&amp;"_draw")*($X$7:$X$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD68" s="126" cm="1">
         <f t="array" ref="BD68">SUMPRODUCT(($E$7:$E$78=AE68)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE68)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE68" s="126" cm="1">
         <f t="array" ref="BE68">SUMPRODUCT(($E$7:$E$78=AE68)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE68)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF68" s="126">
         <f>BD68-BE68</f>
@@ -55195,11 +55228,11 @@
       </c>
       <c r="BH68" s="126">
         <f>BB68/BB72*1000+BC68/BC72*100+BG68/BG72*10+BD68/BD72</f>
-        <v>50.5</v>
+        <v>0</v>
       </c>
       <c r="BI68" s="126">
         <f>BH68/BH72</f>
-        <v>0.98058252427184467</v>
+        <v>0</v>
       </c>
       <c r="BK68" s="21"/>
       <c r="BL68" s="21"/>
@@ -55275,11 +55308,11 @@
       </c>
       <c r="K69" s="31">
         <f>L69+M69+N69</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L69" s="31">
         <f>VLOOKUP(1,AD68:AN71,3,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M69" s="31">
         <f>VLOOKUP(1,AD68:AN71,4,FALSE)</f>
@@ -55291,11 +55324,11 @@
       </c>
       <c r="O69" s="31" t="str">
         <f>VLOOKUP(1,AD68:AN71,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD68:AN71,7,FALSE)</f>
-        <v>3 - 1</v>
+        <v>4 - 1</v>
       </c>
       <c r="P69" s="32">
         <f>L69*3+M69</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R69" s="123">
         <f>DATE(2026,6,26)+TIME(16,0,0)+gmt_delta</f>
@@ -55359,7 +55392,7 @@
       </c>
       <c r="AH69" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE69 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI69" s="123">
         <f>SUMIF($E$7:$E$78,$AE69,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE69,$G$7:$G$78)</f>
@@ -55367,15 +55400,15 @@
       </c>
       <c r="AJ69" s="123">
         <f>SUMIF($E$7:$E$78,$AE69,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE69,$F$7:$F$78)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL69" s="123">
         <f>AI69-AJ69</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM69" s="123">
         <f>AL69-AL72</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AN69" s="123">
         <f>AF69*3+AG69</f>
@@ -55383,11 +55416,11 @@
       </c>
       <c r="AO69" s="123">
         <f>AN69/AN72*10+BA69</f>
-        <v>3.4805825242718447</v>
+        <v>1.4285714285714284</v>
       </c>
       <c r="AP69" s="123">
         <f>AO69*10000000+BI69*100+AM69/AM72*10+AI69/AI72*1++IF(AQ69=0,ROW(),AQ69)/2000000</f>
-        <v>34805927.551710039</v>
+        <v>14285719.044695219</v>
       </c>
       <c r="AQ69" s="126">
         <f>VLOOKUP(AE69,db_fifarank,2,FALSE)</f>
@@ -55395,7 +55428,7 @@
       </c>
       <c r="AR69" s="125">
         <f>AP69/AP72</f>
-        <v>0.46407897368729573</v>
+        <v>0.16666670417364024</v>
       </c>
       <c r="AS69" s="125" t="str">
         <f>IF(SUM(AF68:AH71)=12,J70,"2K")</f>
@@ -55407,15 +55440,15 @@
       </c>
       <c r="AU69" s="126" cm="1">
         <f t="array" ref="AU69">SUMPRODUCT(($S$7:$S$78=AE69&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE69&amp;"_draw")*($U$7:$U$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV69" s="126" cm="1">
         <f t="array" ref="AV69">SUMPRODUCT(($E$7:$E$78=AE69)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE69)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW69" s="126" cm="1">
         <f t="array" ref="AW69">SUMPRODUCT(($E$7:$E$78=AE69)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE69)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX69" s="126">
         <f>AV69-AW69</f>
@@ -55427,11 +55460,11 @@
       </c>
       <c r="AZ69" s="126">
         <f>AT69/AT72*1000+AU69/AU72*100+AY69/AY72*10+AV69/AV72</f>
-        <v>50.5</v>
+        <v>0</v>
       </c>
       <c r="BA69" s="126">
         <f>AZ69/AZ72</f>
-        <v>0.98058252427184467</v>
+        <v>0</v>
       </c>
       <c r="BB69" s="126" cm="1">
         <f t="array" ref="BB69">SUMPRODUCT(($S$7:$S$78=AE69&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE69&amp;"_win")*($X$7:$X$78))</f>
@@ -55439,15 +55472,15 @@
       </c>
       <c r="BC69" s="126" cm="1">
         <f t="array" ref="BC69">SUMPRODUCT(($S$7:$S$78=AE69&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE69&amp;"_draw")*($X$7:$X$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD69" s="126" cm="1">
         <f t="array" ref="BD69">SUMPRODUCT(($E$7:$E$78=AE69)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE69)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE69" s="126" cm="1">
         <f t="array" ref="BE69">SUMPRODUCT(($E$7:$E$78=AE69)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE69)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF69" s="126">
         <f>BD69-BE69</f>
@@ -55459,11 +55492,11 @@
       </c>
       <c r="BH69" s="126">
         <f>BB69/BB72*1000+BC69/BC72*100+BG69/BG72*10+BD69/BD72</f>
-        <v>50.5</v>
+        <v>0</v>
       </c>
       <c r="BI69" s="126">
         <f>BH69/BH72</f>
-        <v>0.98058252427184467</v>
+        <v>0</v>
       </c>
       <c r="BK69" s="21" t="str" cm="1">
         <f t="array" ref="BK69">INDEX(T,24+MONTH(BP69),lang) &amp; " " &amp; DAY(BP69) &amp; ", " &amp; YEAR(BP69) &amp; "   " &amp; (IF(HOUR(BP69)&lt;10,0,"")&amp;HOUR(BP69)) &amp; ":" &amp;  (IF(MINUTE(BP69)&lt;10,0,"")&amp;MINUTE(BP69))</f>
@@ -55537,11 +55570,11 @@
       </c>
       <c r="K70" s="23">
         <f>L70+M70+N70</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L70" s="23">
         <f>VLOOKUP(2,AD68:AN71,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" s="23">
         <f>VLOOKUP(2,AD68:AN71,4,FALSE)</f>
@@ -55553,11 +55586,11 @@
       </c>
       <c r="O70" s="23" t="str">
         <f>VLOOKUP(2,AD68:AN71,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD68:AN71,7,FALSE)</f>
-        <v>1 - 1</v>
+        <v>6 - 1</v>
       </c>
       <c r="P70" s="34">
         <f>L70*3+M70</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R70" s="123">
         <f>DATE(2026,6,26)+TIME(16,0,0)+gmt_delta</f>
@@ -55621,7 +55654,7 @@
       </c>
       <c r="AH70" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE70 &amp; "_lose")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI70" s="123">
         <f>SUMIF($E$7:$E$78,$AE70,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE70,$G$7:$G$78)</f>
@@ -55629,11 +55662,11 @@
       </c>
       <c r="AJ70" s="123">
         <f>SUMIF($E$7:$E$78,$AE70,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE70,$F$7:$F$78)</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AL70" s="123">
         <f>AI70-AJ70</f>
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="AM70" s="123">
         <f>AL70-AL72</f>
@@ -55649,7 +55682,7 @@
       </c>
       <c r="AP70" s="123">
         <f>AO70*10000000+BI70*100+AM70/AM72*10+AI70/AI72*1++IF(AQ70=0,ROW(),AQ70)/2000000</f>
-        <v>0.25073266999999999</v>
+        <v>0.14358981285714284</v>
       </c>
       <c r="AQ70" s="126">
         <f>VLOOKUP(AE70,db_fifarank,2,FALSE)</f>
@@ -55657,7 +55690,7 @@
       </c>
       <c r="AR70" s="125">
         <f>AP70/AP72</f>
-        <v>3.3431018320256936E-9</v>
+        <v>1.6752143022647808E-9</v>
       </c>
       <c r="AT70" s="126" cm="1">
         <f t="array" ref="AT70">SUMPRODUCT(($S$7:$S$78=AE70&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE70&amp;"_win")*($U$7:$U$78))</f>
@@ -55773,7 +55806,7 @@
       </c>
       <c r="K71" s="23">
         <f>L71+M71+N71</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L71" s="23">
         <f>VLOOKUP(3,AD68:AN71,3,FALSE)</f>
@@ -55785,11 +55818,11 @@
       </c>
       <c r="N71" s="23">
         <f>VLOOKUP(3,AD68:AN71,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O71" s="23" t="str">
         <f>VLOOKUP(3,AD68:AN71,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD68:AN71,7,FALSE)</f>
-        <v>1 - 1</v>
+        <v>1 - 2</v>
       </c>
       <c r="P71" s="34">
         <f>L71*3+M71</f>
@@ -55849,7 +55882,7 @@
       </c>
       <c r="AF71" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE71 &amp; "_win")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG71" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE71 &amp; "_draw")</f>
@@ -55861,7 +55894,7 @@
       </c>
       <c r="AI71" s="123">
         <f>SUMIF($E$7:$E$78,$AE71,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE71,$G$7:$G$78)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ71" s="123">
         <f>SUMIF($E$7:$E$78,$AE71,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE71,$F$7:$F$78)</f>
@@ -55869,23 +55902,23 @@
       </c>
       <c r="AL71" s="123">
         <f>AI71-AJ71</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM71" s="123">
         <f>AL71-AL72</f>
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AN71" s="123">
         <f>AF71*3+AG71</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AO71" s="123">
         <f>AN71/AN72*10+BA71</f>
-        <v>7.5</v>
+        <v>8.5714285714285712</v>
       </c>
       <c r="AP71" s="123">
         <f>AO71*10000000+BI71*100+AM71/AM72*10+AI71/AI72*1++IF(AQ71=0,ROW(),AQ71)/2000000</f>
-        <v>75000008.75084655</v>
+        <v>85714293.978868529</v>
       </c>
       <c r="AQ71" s="126">
         <f>VLOOKUP(AE71,db_fifarank,2,FALSE)</f>
@@ -55893,7 +55926,7 @@
       </c>
       <c r="AR71" s="125">
         <f>AP71/AP72</f>
-        <v>0.99999998666666845</v>
+        <v>0.99999998833333459</v>
       </c>
       <c r="AT71" s="126" cm="1">
         <f t="array" ref="AT71">SUMPRODUCT(($S$7:$S$78=AE71&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE71&amp;"_win")*($U$7:$U$78))</f>
@@ -56006,7 +56039,7 @@
       </c>
       <c r="K72" s="36">
         <f>L72+M72+N72</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L72" s="36">
         <f>VLOOKUP(4,AD68:AN71,3,FALSE)</f>
@@ -56018,11 +56051,11 @@
       </c>
       <c r="N72" s="36">
         <f>VLOOKUP(4,AD68:AN71,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O72" s="36" t="str">
         <f>VLOOKUP(4,AD68:AN71,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD68:AN71,7,FALSE)</f>
-        <v>1 - 3</v>
+        <v>1 - 8</v>
       </c>
       <c r="P72" s="37">
         <f>L72*3+M72</f>
@@ -56074,7 +56107,7 @@
       </c>
       <c r="AF72" s="123">
         <f t="shared" ref="AF72:AH72" si="35">MAX(AF68:AF71)-MIN(AF68:AF71)+1</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG72" s="123">
         <f t="shared" si="35"/>
@@ -56082,31 +56115,31 @@
       </c>
       <c r="AH72" s="123">
         <f t="shared" si="35"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI72" s="123">
         <f>MAX(AI68:AI71)+1</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AL72" s="123">
         <f>MIN(AL68:AL71)</f>
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="AM72" s="123">
         <f>MAX(AM68:AM71)+1</f>
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AN72" s="123">
         <f>MAX(AN68:AN71)+1</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AO72" s="123">
         <f>MAX(AO68:AO71)+1</f>
-        <v>8.5</v>
+        <v>9.5714285714285712</v>
       </c>
       <c r="AP72" s="123">
         <f>MAX(AP68:AP71)+1</f>
-        <v>75000009.75084655</v>
+        <v>85714294.978868529</v>
       </c>
       <c r="AT72" s="126">
         <f>MAX(AT68:AT71)-MIN(AT68:AT71)+1</f>
@@ -56114,15 +56147,15 @@
       </c>
       <c r="AU72" s="126">
         <f>MAX(AU68:AU71)-MIN(AU68:AU71)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV72" s="126">
         <f>MAX(AV68:AV71)-MIN(AV68:AV71)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW72" s="126">
         <f>MAX(AW68:AW71)-MIN(AW68:AW71)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY72" s="126">
         <f>MAX(AY68:AY71)-MIN(AY68:AY71)+1</f>
@@ -56130,7 +56163,7 @@
       </c>
       <c r="AZ72" s="126">
         <f>MAX(AZ68:AZ71)+1</f>
-        <v>51.5</v>
+        <v>1</v>
       </c>
       <c r="BB72" s="126">
         <f>MAX(BB68:BB71)-MIN(BB68:BB71)+1</f>
@@ -56138,15 +56171,15 @@
       </c>
       <c r="BC72" s="126">
         <f>MAX(BC68:BC71)-MIN(BC68:BC71)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BD72" s="126">
         <f>MAX(BD68:BD71)-MIN(BD68:BD71)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BE72" s="126">
         <f>MAX(BE68:BE71)-MIN(BE68:BE71)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BG72" s="126">
         <f>MAX(BG68:BG71)-MIN(BG68:BG71)+1</f>
@@ -56154,7 +56187,7 @@
       </c>
       <c r="BH72" s="126">
         <f>MAX(BH68:BH71)+1</f>
-        <v>51.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:95" x14ac:dyDescent="0.2">
@@ -56349,7 +56382,7 @@
       </c>
       <c r="AG74" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE74 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH74" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE74 &amp; "_lose")</f>
@@ -56373,15 +56406,15 @@
       </c>
       <c r="AN74" s="123">
         <f>AF74*3+AG74</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO74" s="123">
         <f>AN74/AN78*10+BA74</f>
-        <v>7.5</v>
+        <v>8.9803921568627452</v>
       </c>
       <c r="AP74" s="123">
         <f>AO74*10000000+BI74*100+AM74/AM78*10+AI74/AI78*1++IF(AQ74=0,ROW(),AQ74)/2000000</f>
-        <v>75000008.800912976</v>
+        <v>89804028.408756107</v>
       </c>
       <c r="AQ74" s="126">
         <f>VLOOKUP(AE74,db_fifarank,2,FALSE)</f>
@@ -56389,7 +56422,7 @@
       </c>
       <c r="AR74" s="125">
         <f>AP74/AP78</f>
-        <v>0.99999998666666845</v>
+        <v>0.99999998886464214</v>
       </c>
       <c r="AS74" s="125" t="str">
         <f>IF(SUM(AF74:AH77)=12,J75,"1L")</f>
@@ -56401,7 +56434,7 @@
       </c>
       <c r="AU74" s="126" cm="1">
         <f t="array" ref="AU74">SUMPRODUCT(($S$7:$S$78=AE74&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE74&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV74" s="126" cm="1">
         <f t="array" ref="AV74">SUMPRODUCT(($E$7:$E$78=AE74)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE74)*($U$7:$U$78)*($G$7:$G$78))</f>
@@ -56421,11 +56454,11 @@
       </c>
       <c r="AZ74" s="126">
         <f>AT74/AT78*1000+AU74/AU78*100+AY74/AY78*10+AV74/AV78</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BA74" s="126">
         <f>AZ74/AZ78</f>
-        <v>0</v>
+        <v>0.98039215686274506</v>
       </c>
       <c r="BB74" s="126" cm="1">
         <f t="array" ref="BB74">SUMPRODUCT(($S$7:$S$78=AE74&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE74&amp;"_win")*($X$7:$X$78))</f>
@@ -56433,7 +56466,7 @@
       </c>
       <c r="BC74" s="126" cm="1">
         <f t="array" ref="BC74">SUMPRODUCT(($S$7:$S$78=AE74&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE74&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD74" s="126" cm="1">
         <f t="array" ref="BD74">SUMPRODUCT(($E$7:$E$78=AE74)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE74)*($X$7:$X$78)*($G$7:$G$78))</f>
@@ -56453,11 +56486,11 @@
       </c>
       <c r="BH74" s="126">
         <f>BB74/BB78*1000+BC74/BC78*100+BG74/BG78*10+BD74/BD78</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BI74" s="126">
         <f>BH74/BH78</f>
-        <v>0</v>
+        <v>0.98039215686274506</v>
       </c>
     </row>
     <row r="75" spans="1:95" x14ac:dyDescent="0.2">
@@ -56493,7 +56526,7 @@
       </c>
       <c r="K75" s="31">
         <f>L75+M75+N75</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L75" s="31">
         <f>VLOOKUP(1,AD74:AN77,3,FALSE)</f>
@@ -56501,7 +56534,7 @@
       </c>
       <c r="M75" s="31">
         <f>VLOOKUP(1,AD74:AN77,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N75" s="31">
         <f>VLOOKUP(1,AD74:AN77,5,FALSE)</f>
@@ -56513,7 +56546,7 @@
       </c>
       <c r="P75" s="32">
         <f>L75*3+M75</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R75" s="123">
         <f>DATE(2026,6,27)+TIME(15,0,0)+gmt_delta</f>
@@ -56561,7 +56594,7 @@
       </c>
       <c r="AD75" s="123">
         <f>COUNTIF(AR74:AR77,CONCATENATE("&gt;=",AR75))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE75" s="124" t="str">
         <f>VLOOKUP("Croatia",T,lang,FALSE)</f>
@@ -56569,7 +56602,7 @@
       </c>
       <c r="AF75" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE75 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG75" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE75 &amp; "_draw")</f>
@@ -56581,7 +56614,7 @@
       </c>
       <c r="AI75" s="123">
         <f>SUMIF($E$7:$E$78,$AE75,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE75,$G$7:$G$78)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ75" s="123">
         <f>SUMIF($E$7:$E$78,$AE75,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE75,$F$7:$F$78)</f>
@@ -56589,23 +56622,23 @@
       </c>
       <c r="AL75" s="123">
         <f>AI75-AJ75</f>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AM75" s="123">
         <f>AL75-AL78</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN75" s="123">
         <f>AF75*3+AG75</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO75" s="123">
         <f>AN75/AN78*10+BA75</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AP75" s="123">
         <f>AO75*10000000+BI75*100+AM75/AM78*10+AI75/AI78*1++IF(AQ75=0,ROW(),AQ75)/2000000</f>
-        <v>0.40085853500000002</v>
+        <v>60000002.600858539</v>
       </c>
       <c r="AQ75" s="126">
         <f>VLOOKUP(AE75,db_fifarank,2,FALSE)</f>
@@ -56613,7 +56646,7 @@
       </c>
       <c r="AR75" s="125">
         <f>AP75/AP78</f>
-        <v>5.3447797682170484E-9</v>
+        <v>0.66812149739695748</v>
       </c>
       <c r="AS75" s="125" t="str">
         <f>IF(SUM(AF74:AH77)=12,J76,"2L")</f>
@@ -56717,7 +56750,7 @@
       </c>
       <c r="K76" s="23">
         <f>L76+M76+N76</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L76" s="23">
         <f>VLOOKUP(2,AD74:AN77,3,FALSE)</f>
@@ -56725,7 +56758,7 @@
       </c>
       <c r="M76" s="23">
         <f>VLOOKUP(2,AD74:AN77,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N76" s="23">
         <f>VLOOKUP(2,AD74:AN77,5,FALSE)</f>
@@ -56737,7 +56770,7 @@
       </c>
       <c r="P76" s="34">
         <f>L76*3+M76</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R76" s="123">
         <f>DATE(2026,6,27)+TIME(15,0,0)+gmt_delta</f>
@@ -56797,7 +56830,7 @@
       </c>
       <c r="AG76" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE76 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH76" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE76 &amp; "_lose")</f>
@@ -56821,15 +56854,15 @@
       </c>
       <c r="AN76" s="123">
         <f>AF76*3+AG76</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO76" s="123">
         <f>AN76/AN78*10+BA76</f>
-        <v>7.5</v>
+        <v>8.9803921568627452</v>
       </c>
       <c r="AP76" s="123">
         <f>AO76*10000000+BI76*100+AM76/AM78*10+AI76/AI78*1++IF(AQ76=0,ROW(),AQ76)/2000000</f>
-        <v>75000006.200673163</v>
+        <v>89804025.808516294</v>
       </c>
       <c r="AQ76" s="126">
         <f>VLOOKUP(AE76,db_fifarank,2,FALSE)</f>
@@ -56837,7 +56870,7 @@
       </c>
       <c r="AR76" s="125">
         <f>AP76/AP78</f>
-        <v>0.9999999519968088</v>
+        <v>0.99999995991004154</v>
       </c>
       <c r="AT76" s="126" cm="1">
         <f t="array" ref="AT76">SUMPRODUCT(($S$7:$S$78=AE76&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE76&amp;"_win")*($U$7:$U$78))</f>
@@ -56845,7 +56878,7 @@
       </c>
       <c r="AU76" s="126" cm="1">
         <f t="array" ref="AU76">SUMPRODUCT(($S$7:$S$78=AE76&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE76&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV76" s="126" cm="1">
         <f t="array" ref="AV76">SUMPRODUCT(($E$7:$E$78=AE76)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE76)*($U$7:$U$78)*($G$7:$G$78))</f>
@@ -56865,11 +56898,11 @@
       </c>
       <c r="AZ76" s="126">
         <f>AT76/AT78*1000+AU76/AU78*100+AY76/AY78*10+AV76/AV78</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BA76" s="126">
         <f>AZ76/AZ78</f>
-        <v>0</v>
+        <v>0.98039215686274506</v>
       </c>
       <c r="BB76" s="126" cm="1">
         <f t="array" ref="BB76">SUMPRODUCT(($S$7:$S$78=AE76&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE76&amp;"_win")*($X$7:$X$78))</f>
@@ -56877,7 +56910,7 @@
       </c>
       <c r="BC76" s="126" cm="1">
         <f t="array" ref="BC76">SUMPRODUCT(($S$7:$S$78=AE76&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE76&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD76" s="126" cm="1">
         <f t="array" ref="BD76">SUMPRODUCT(($E$7:$E$78=AE76)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE76)*($X$7:$X$78)*($G$7:$G$78))</f>
@@ -56897,11 +56930,11 @@
       </c>
       <c r="BH76" s="126">
         <f>BB76/BB78*1000+BC76/BC78*100+BG76/BG78*10+BD76/BD78</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BI76" s="126">
         <f>BH76/BH78</f>
-        <v>0</v>
+        <v>0.98039215686274506</v>
       </c>
     </row>
     <row r="77" spans="1:95" x14ac:dyDescent="0.2">
@@ -56933,15 +56966,15 @@
       <c r="I77" s="69"/>
       <c r="J77" s="33" t="str">
         <f>VLOOKUP(3,AD74:AN77,2,FALSE)</f>
-        <v>Panama</v>
+        <v>Croatia</v>
       </c>
       <c r="K77" s="23">
         <f>L77+M77+N77</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L77" s="23">
         <f>VLOOKUP(3,AD74:AN77,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" s="23">
         <f>VLOOKUP(3,AD74:AN77,4,FALSE)</f>
@@ -56953,11 +56986,11 @@
       </c>
       <c r="O77" s="23" t="str">
         <f>VLOOKUP(3,AD74:AN77,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD74:AN77,7,FALSE)</f>
-        <v>0 - 1</v>
+        <v>3 - 4</v>
       </c>
       <c r="P77" s="34">
         <f>L77*3+M77</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R77" s="123">
         <f>DATE(2026,6,27)+TIME(12,30,0)+gmt_delta</f>
@@ -57005,7 +57038,7 @@
       </c>
       <c r="AD77" s="123">
         <f>COUNTIF(AR74:AR77,CONCATENATE("&gt;=",AR77))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE77" s="124" t="str">
         <f>VLOOKUP("Panama",T,lang,FALSE)</f>
@@ -57021,7 +57054,7 @@
       </c>
       <c r="AH77" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE77 &amp; "_lose")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI77" s="123">
         <f>SUMIF($E$7:$E$78,$AE77,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE77,$G$7:$G$78)</f>
@@ -57029,15 +57062,15 @@
       </c>
       <c r="AJ77" s="123">
         <f>SUMIF($E$7:$E$78,$AE77,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE77,$F$7:$F$78)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL77" s="123">
         <f>AI77-AJ77</f>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AM77" s="123">
         <f>AL77-AL78</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN77" s="123">
         <f>AF77*3+AG77</f>
@@ -57049,7 +57082,7 @@
       </c>
       <c r="AP77" s="123">
         <f>AO77*10000000+BI77*100+AM77/AM78*10+AI77/AI78*1++IF(AQ77=0,ROW(),AQ77)/2000000</f>
-        <v>2.00077032</v>
+        <v>7.7032000000000001E-4</v>
       </c>
       <c r="AQ77" s="126">
         <f>VLOOKUP(AE77,db_fifarank,2,FALSE)</f>
@@ -57057,7 +57090,7 @@
       </c>
       <c r="AR77" s="125">
         <f>AP77/AP78</f>
-        <v>2.6676934113889205E-8</v>
+        <v>8.5777888260868168E-12</v>
       </c>
       <c r="AT77" s="126" cm="1">
         <f t="array" ref="AT77">SUMPRODUCT(($S$7:$S$78=AE77&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE77&amp;"_win")*($U$7:$U$78))</f>
@@ -57153,11 +57186,11 @@
       <c r="I78" s="69"/>
       <c r="J78" s="35" t="str">
         <f>VLOOKUP(4,AD74:AN77,2,FALSE)</f>
-        <v>Croatia</v>
+        <v>Panama</v>
       </c>
       <c r="K78" s="36">
         <f>L78+M78+N78</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L78" s="36">
         <f>VLOOKUP(4,AD74:AN77,3,FALSE)</f>
@@ -57169,11 +57202,11 @@
       </c>
       <c r="N78" s="36">
         <f>VLOOKUP(4,AD74:AN77,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O78" s="36" t="str">
         <f>VLOOKUP(4,AD74:AN77,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD74:AN77,7,FALSE)</f>
-        <v>2 - 4</v>
+        <v>0 - 2</v>
       </c>
       <c r="P78" s="37">
         <f>L78*3+M78</f>
@@ -57229,11 +57262,11 @@
       </c>
       <c r="AG78" s="123">
         <f t="shared" si="36"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH78" s="123">
         <f t="shared" si="36"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI78" s="123">
         <f>MAX(AI74:AI77)+1</f>
@@ -57249,15 +57282,15 @@
       </c>
       <c r="AN78" s="123">
         <f>MAX(AN74:AN77)+1</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO78" s="123">
         <f>MAX(AO74:AO77)+1</f>
-        <v>8.5</v>
+        <v>9.9803921568627452</v>
       </c>
       <c r="AP78" s="123">
         <f>MAX(AP74:AP77)+1</f>
-        <v>75000009.800912976</v>
+        <v>89804029.408756107</v>
       </c>
       <c r="AT78" s="126">
         <f>MAX(AT74:AT77)-MIN(AT74:AT77)+1</f>
@@ -57265,7 +57298,7 @@
       </c>
       <c r="AU78" s="126">
         <f>MAX(AU74:AU77)-MIN(AU74:AU77)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV78" s="126">
         <f>MAX(AV74:AV77)-MIN(AV74:AV77)+1</f>
@@ -57281,7 +57314,7 @@
       </c>
       <c r="AZ78" s="126">
         <f>MAX(AZ74:AZ77)+1</f>
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="BB78" s="126">
         <f>MAX(BB74:BB77)-MIN(BB74:BB77)+1</f>
@@ -57289,7 +57322,7 @@
       </c>
       <c r="BC78" s="126">
         <f>MAX(BC74:BC77)-MIN(BC74:BC77)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD78" s="126">
         <f>MAX(BD74:BD77)-MIN(BD74:BD77)+1</f>
@@ -57305,7 +57338,7 @@
       </c>
       <c r="BH78" s="126">
         <f>MAX(BH74:BH77)+1</f>
-        <v>1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="79" spans="1:95" x14ac:dyDescent="0.2">
@@ -57468,7 +57501,7 @@
       </c>
       <c r="AD81" s="123">
         <f t="shared" ref="AD81:AD91" si="38">COUNTIF($AP$80:$AP$91,CONCATENATE("&gt;=",AP81))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AE81" s="124" t="str">
         <f>J17</f>
@@ -57646,7 +57679,7 @@
       <c r="I83" s="69"/>
       <c r="J83" s="99" t="str">
         <f>VLOOKUP(3,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓙ Algeria</v>
+        <v>Ⓛ Croatia</v>
       </c>
       <c r="K83" s="100">
         <f t="shared" si="47"/>
@@ -57666,7 +57699,7 @@
       </c>
       <c r="O83" s="100" t="str">
         <f>VLOOKUP(3,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(3,$AD$80:$AN$91,7,FALSE)</f>
-        <v>2 - 4</v>
+        <v>3 - 4</v>
       </c>
       <c r="P83" s="101">
         <f t="shared" si="48"/>
@@ -57674,7 +57707,7 @@
       </c>
       <c r="AD83" s="123">
         <f t="shared" si="38"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE83" s="124" t="str">
         <f>J29</f>
@@ -57748,7 +57781,7 @@
       <c r="I84" s="69"/>
       <c r="J84" s="99" t="str">
         <f>VLOOKUP(4,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓓ Paraguay</v>
+        <v>Ⓙ Algeria</v>
       </c>
       <c r="K84" s="100">
         <f t="shared" si="47"/>
@@ -57788,7 +57821,7 @@
       </c>
       <c r="AD84" s="123">
         <f t="shared" si="38"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE84" s="124" t="str">
         <f>J35</f>
@@ -57862,7 +57895,7 @@
       <c r="I85" s="69"/>
       <c r="J85" s="99" t="str">
         <f>VLOOKUP(5,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓗ Cape Verde</v>
+        <v>Ⓓ Paraguay</v>
       </c>
       <c r="K85" s="100">
         <f t="shared" si="47"/>
@@ -57870,23 +57903,23 @@
       </c>
       <c r="L85" s="100">
         <f>VLOOKUP(5,$AD$80:$AN$91,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M85" s="100">
         <f>VLOOKUP(5,$AD$80:$AN$91,4,FALSE)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N85" s="100">
         <f>VLOOKUP(5,$AD$80:$AN$91,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O85" s="100" t="str">
         <f>VLOOKUP(5,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(5,$AD$80:$AN$91,7,FALSE)</f>
-        <v>2 - 2</v>
+        <v>2 - 4</v>
       </c>
       <c r="P85" s="101">
         <f t="shared" si="48"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R85" s="123">
         <f>DATE(2026,12,3)+TIME(8,0,0)+gmt_delta</f>
@@ -57976,7 +58009,7 @@
       <c r="I86" s="69"/>
       <c r="J86" s="99" t="str">
         <f>VLOOKUP(6,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓖ Belgium</v>
+        <v>Ⓗ Cape Verde</v>
       </c>
       <c r="K86" s="100">
         <f t="shared" si="47"/>
@@ -57996,7 +58029,7 @@
       </c>
       <c r="O86" s="100" t="str">
         <f>VLOOKUP(6,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(6,$AD$80:$AN$91,7,FALSE)</f>
-        <v>1 - 1</v>
+        <v>2 - 2</v>
       </c>
       <c r="P86" s="101">
         <f t="shared" si="48"/>
@@ -58016,7 +58049,7 @@
       </c>
       <c r="AD86" s="123">
         <f t="shared" si="38"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE86" s="124" t="str">
         <f>J47</f>
@@ -58090,11 +58123,11 @@
       <c r="I87" s="69"/>
       <c r="J87" s="99" t="str">
         <f>VLOOKUP(7,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓚ DR Congo</v>
+        <v>Ⓖ Belgium</v>
       </c>
       <c r="K87" s="100">
         <f t="shared" si="47"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L87" s="100">
         <f>VLOOKUP(7,$AD$80:$AN$91,3,FALSE)</f>
@@ -58102,7 +58135,7 @@
       </c>
       <c r="M87" s="100">
         <f>VLOOKUP(7,$AD$80:$AN$91,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N87" s="100">
         <f>VLOOKUP(7,$AD$80:$AN$91,5,FALSE)</f>
@@ -58114,7 +58147,7 @@
       </c>
       <c r="P87" s="101">
         <f t="shared" si="48"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R87" s="123">
         <f>DATE(2026,12,4)+TIME(4,0,0)+gmt_delta</f>
@@ -58130,7 +58163,7 @@
       </c>
       <c r="AD87" s="123">
         <f t="shared" si="38"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE87" s="124" t="str">
         <f>J53</f>
@@ -58318,7 +58351,7 @@
       <c r="I89" s="69"/>
       <c r="J89" s="102" t="str">
         <f>VLOOKUP(9,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓔ Ecuador</v>
+        <v>Ⓚ DR Congo</v>
       </c>
       <c r="K89" s="103">
         <f t="shared" si="47"/>
@@ -58338,7 +58371,7 @@
       </c>
       <c r="O89" s="103" t="str">
         <f>VLOOKUP(9,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(9,$AD$80:$AN$91,7,FALSE)</f>
-        <v>0 - 1</v>
+        <v>1 - 2</v>
       </c>
       <c r="P89" s="104">
         <f t="shared" si="48"/>
@@ -58358,7 +58391,7 @@
       </c>
       <c r="AD89" s="123">
         <f t="shared" si="38"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE89" s="124" t="str">
         <f>J65</f>
@@ -58432,7 +58465,7 @@
       <c r="I90" s="69"/>
       <c r="J90" s="102" t="str">
         <f>VLOOKUP(10,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓑ Bosnia and Herzegovina</v>
+        <v>Ⓔ Ecuador</v>
       </c>
       <c r="K90" s="103">
         <f t="shared" si="47"/>
@@ -58452,7 +58485,7 @@
       </c>
       <c r="O90" s="103" t="str">
         <f>VLOOKUP(10,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(10,$AD$80:$AN$91,7,FALSE)</f>
-        <v>2 - 5</v>
+        <v>0 - 1</v>
       </c>
       <c r="P90" s="104">
         <f t="shared" si="48"/>
@@ -58472,7 +58505,7 @@
       </c>
       <c r="AD90" s="123">
         <f t="shared" si="38"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE90" s="124" t="str">
         <f>J71</f>
@@ -58488,7 +58521,7 @@
       </c>
       <c r="AH90" s="123">
         <f t="shared" si="40"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI90" s="123">
         <f t="shared" si="41"/>
@@ -58496,18 +58529,18 @@
       </c>
       <c r="AJ90" s="123">
         <f t="shared" si="42"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK90" s="123" t="s">
         <v>3191</v>
       </c>
       <c r="AL90" s="123">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM90" s="123">
         <f t="shared" si="44"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN90" s="123">
         <f t="shared" si="45"/>
@@ -58515,7 +58548,7 @@
       </c>
       <c r="AP90" s="123">
         <f>AN90/AN92*10000+AM90/AM92*1000+AI90/AI92*100+IF(AQ90=0,ROW(),AQ90)/2000000</f>
-        <v>3264.2864534607143</v>
+        <v>3014.2864534607143</v>
       </c>
       <c r="AQ90" s="126">
         <f t="shared" si="37"/>
@@ -58523,11 +58556,11 @@
       </c>
       <c r="AR90" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ACDFGHJK</v>
+        <v>ACDFGHJ</v>
       </c>
       <c r="AS90" s="129" t="str">
         <f t="shared" si="46"/>
-        <v>DR Congo</v>
+        <v/>
       </c>
       <c r="AT90" s="130" t="str">
         <f>"Ⓚ "&amp;AE90</f>
@@ -58546,11 +58579,11 @@
       <c r="I91" s="69"/>
       <c r="J91" s="102" t="str">
         <f>VLOOKUP(11,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓛ Panama</v>
+        <v>Ⓑ Bosnia and Herzegovina</v>
       </c>
       <c r="K91" s="103">
         <f t="shared" si="47"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L91" s="103">
         <f>VLOOKUP(11,$AD$80:$AN$91,3,FALSE)</f>
@@ -58558,7 +58591,7 @@
       </c>
       <c r="M91" s="103">
         <f>VLOOKUP(11,$AD$80:$AN$91,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N91" s="103">
         <f>VLOOKUP(11,$AD$80:$AN$91,5,FALSE)</f>
@@ -58566,11 +58599,11 @@
       </c>
       <c r="O91" s="103" t="str">
         <f>VLOOKUP(11,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(11,$AD$80:$AN$91,7,FALSE)</f>
-        <v>0 - 1</v>
+        <v>2 - 5</v>
       </c>
       <c r="P91" s="104">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R91" s="123">
         <f>DATE(2026,12,6)+TIME(8,0,0)+gmt_delta</f>
@@ -58586,15 +58619,15 @@
       </c>
       <c r="AD91" s="123">
         <f t="shared" si="38"/>
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AE91" s="124" t="str">
         <f>J77</f>
-        <v>Panama</v>
+        <v>Croatia</v>
       </c>
       <c r="AF91" s="123">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG91" s="123">
         <f t="shared" si="49"/>
@@ -58606,11 +58639,11 @@
       </c>
       <c r="AI91" s="123">
         <f>VLOOKUP($AE91,$AE$8:$AQ$78,5,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AJ91" s="123">
         <f>VLOOKUP($AE91,$AE$8:$AQ$78,6,FALSE)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AK91" s="123" t="s">
         <v>3192</v>
@@ -58625,27 +58658,27 @@
       </c>
       <c r="AN91" s="123">
         <f>VLOOKUP($AE91,$AE$8:$AQ$78,10,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP91" s="123">
         <f>AN91/AN92*10000+AM91/AM92*1000+AI91/AI92*100+IF(AQ91=0,ROW(),AQ91)/2000000</f>
-        <v>500.00077032000002</v>
+        <v>8042.8580013921428</v>
       </c>
       <c r="AQ91" s="126">
         <f t="shared" si="37"/>
-        <v>1540.64</v>
+        <v>1717.07</v>
       </c>
       <c r="AR91" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ACDFGHJK</v>
+        <v>ACDFGHJL</v>
       </c>
       <c r="AS91" s="129" t="str">
         <f t="shared" si="46"/>
-        <v/>
+        <v>Croatia</v>
       </c>
       <c r="AT91" s="130" t="str">
         <f>"Ⓛ "&amp;AE91</f>
-        <v>Ⓛ Panama</v>
+        <v>Ⓛ Croatia</v>
       </c>
     </row>
     <row r="92" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -60218,15 +60251,15 @@
     <row r="3" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B3" s="109">
         <f>MATCH(C3,C6:C500,0)</f>
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C3" s="121" t="str">
         <f>'2026 World Cup'!AR91</f>
-        <v>ACDFGHJK</v>
+        <v>ACDFGHJL</v>
       </c>
       <c r="D3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,2,FALSE)</f>
-        <v>3H</v>
+        <v>3C</v>
       </c>
       <c r="E3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,3,FALSE)</f>
@@ -60238,7 +60271,7 @@
       </c>
       <c r="G3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,5,FALSE)</f>
-        <v>3C</v>
+        <v>3D</v>
       </c>
       <c r="H3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,6,FALSE)</f>
@@ -60250,11 +60283,11 @@
       </c>
       <c r="J3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,8,FALSE)</f>
-        <v>3D</v>
+        <v>3L</v>
       </c>
       <c r="K3" s="122" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,9,FALSE)</f>
-        <v>3K</v>
+        <v>3H</v>
       </c>
     </row>
     <row r="5" spans="2:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">

--- a/public/worldcup.xlsx
+++ b/public/worldcup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rylanpaul/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E563C63E-6689-6045-B8E5-33FA7CF8C24B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{890E4366-911D-7E45-82FF-2F002A696F7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T" sheetId="1" state="hidden" r:id="rId1"/>
@@ -13305,56 +13305,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -13435,6 +13391,50 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -38724,13 +38724,13 @@
       <c r="J3" t="s">
         <v>2201</v>
       </c>
-      <c r="K3" s="142" t="e">
+      <c r="K3" s="142">
         <f>IFERROR(_xlfn.XLOOKUP(J3,Rounds!I$2:I$25,Rounds!J$2:J$25), _xlfn.XLOOKUP(J3,Rounds!L$2:L$25,Rounds!K$2:K$25))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L3" s="142" t="e">
+        <v>2</v>
+      </c>
+      <c r="L3" s="142">
         <f>IFERROR(_xlfn.XLOOKUP(J3,Rounds!I$2:I$25,Rounds!K$2:K$25), _xlfn.XLOOKUP(J3,Rounds!L$2:L$25,Rounds!J$2:J$25))</f>
-        <v>#N/A</v>
+        <v>0</v>
       </c>
       <c r="M3" s="140" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(J3,Rounds!I$2:I$25,Rounds!L$2:L$25), _xlfn.XLOOKUP(J3,Rounds!L$2:L$25,Rounds!I$2:I$25))</f>
@@ -38834,13 +38834,13 @@
       <c r="J4" s="148" t="s">
         <v>1677</v>
       </c>
-      <c r="K4" s="146" t="e">
+      <c r="K4" s="146">
         <f>IFERROR(_xlfn.XLOOKUP(J4,Rounds!I$2:I$25,Rounds!J$2:J$25), _xlfn.XLOOKUP(J4,Rounds!L$2:L$25,Rounds!K$2:K$25))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L4" s="146" t="e">
+        <v>4</v>
+      </c>
+      <c r="L4" s="146">
         <f>IFERROR(_xlfn.XLOOKUP(J4,Rounds!I$2:I$25,Rounds!K$2:K$25), _xlfn.XLOOKUP(J4,Rounds!L$2:L$25,Rounds!J$2:J$25))</f>
-        <v>#N/A</v>
+        <v>2</v>
       </c>
       <c r="M4" s="147" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(J4,Rounds!I$2:I$25,Rounds!L$2:L$25), _xlfn.XLOOKUP(J4,Rounds!L$2:L$25,Rounds!I$2:I$25))</f>
@@ -38944,13 +38944,13 @@
       <c r="J5" t="s">
         <v>1323</v>
       </c>
-      <c r="K5" s="82" t="e">
+      <c r="K5" s="82">
         <f>IFERROR(_xlfn.XLOOKUP(J5,Rounds!I$2:I$25,Rounds!J$2:J$25), _xlfn.XLOOKUP(J5,Rounds!L$2:L$25,Rounds!K$2:K$25))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L5" s="82" t="e">
+        <v>3</v>
+      </c>
+      <c r="L5" s="82">
         <f>IFERROR(_xlfn.XLOOKUP(J5,Rounds!I$2:I$25,Rounds!K$2:K$25), _xlfn.XLOOKUP(J5,Rounds!L$2:L$25,Rounds!J$2:J$25))</f>
-        <v>#N/A</v>
+        <v>0</v>
       </c>
       <c r="M5" s="134" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(J5,Rounds!I$2:I$25,Rounds!L$2:L$25), _xlfn.XLOOKUP(J5,Rounds!L$2:L$25,Rounds!I$2:I$25))</f>
@@ -39054,13 +39054,13 @@
       <c r="J6" s="148" t="s">
         <v>2201</v>
       </c>
-      <c r="K6" s="146" t="e">
+      <c r="K6" s="146">
         <f>IFERROR(_xlfn.XLOOKUP(J6,Rounds!I$2:I$25,Rounds!J$2:J$25), _xlfn.XLOOKUP(J6,Rounds!L$2:L$25,Rounds!K$2:K$25))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L6" s="146" t="e">
+        <v>2</v>
+      </c>
+      <c r="L6" s="146">
         <f>IFERROR(_xlfn.XLOOKUP(J6,Rounds!I$2:I$25,Rounds!K$2:K$25), _xlfn.XLOOKUP(J6,Rounds!L$2:L$25,Rounds!J$2:J$25))</f>
-        <v>#N/A</v>
+        <v>0</v>
       </c>
       <c r="M6" s="147" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(J6,Rounds!I$2:I$25,Rounds!L$2:L$25), _xlfn.XLOOKUP(J6,Rounds!L$2:L$25,Rounds!I$2:I$25))</f>
@@ -39164,13 +39164,13 @@
       <c r="J7" t="s">
         <v>1995</v>
       </c>
-      <c r="K7" s="82" t="e">
+      <c r="K7" s="82">
         <f>IFERROR(_xlfn.XLOOKUP(J7,Rounds!I$2:I$25,Rounds!J$2:J$25), _xlfn.XLOOKUP(J7,Rounds!L$2:L$25,Rounds!K$2:K$25))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L7" s="82" t="e">
+        <v>3</v>
+      </c>
+      <c r="L7" s="82">
         <f>IFERROR(_xlfn.XLOOKUP(J7,Rounds!I$2:I$25,Rounds!K$2:K$25), _xlfn.XLOOKUP(J7,Rounds!L$2:L$25,Rounds!J$2:J$25))</f>
-        <v>#N/A</v>
+        <v>1</v>
       </c>
       <c r="M7" s="134" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(J7,Rounds!I$2:I$25,Rounds!L$2:L$25), _xlfn.XLOOKUP(J7,Rounds!L$2:L$25,Rounds!I$2:I$25))</f>
@@ -39274,13 +39274,13 @@
       <c r="J8" s="152" t="s">
         <v>1677</v>
       </c>
-      <c r="K8" s="150" t="e">
+      <c r="K8" s="150">
         <f>IFERROR(_xlfn.XLOOKUP(J8,Rounds!I$2:I$25,Rounds!J$2:J$25), _xlfn.XLOOKUP(J8,Rounds!L$2:L$25,Rounds!K$2:K$25))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L8" s="150" t="e">
+        <v>4</v>
+      </c>
+      <c r="L8" s="150">
         <f>IFERROR(_xlfn.XLOOKUP(J8,Rounds!I$2:I$25,Rounds!K$2:K$25), _xlfn.XLOOKUP(J8,Rounds!L$2:L$25,Rounds!J$2:J$25))</f>
-        <v>#N/A</v>
+        <v>2</v>
       </c>
       <c r="M8" s="151" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(J8,Rounds!I$2:I$25,Rounds!L$2:L$25), _xlfn.XLOOKUP(J8,Rounds!L$2:L$25,Rounds!I$2:I$25))</f>
@@ -39504,18 +39504,18 @@
         <f t="array" ref="I2:L25">IF('2026 World Cup'!E55:H78="",NA(),'2026 World Cup'!E55:H78)</f>
         <v>Scotland</v>
       </c>
-      <c r="J2" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K2" s="81" t="e">
-        <v>#N/A</v>
+      <c r="J2" s="81">
+        <v>0</v>
+      </c>
+      <c r="K2" s="81">
+        <v>3</v>
       </c>
       <c r="L2" s="134" t="str">
         <v>Brazil</v>
       </c>
       <c r="M2" s="132" t="str">
         <f>IF('2026 World Cup'!BL10="",NA(),'2026 World Cup'!BL10)</f>
-        <v>1E</v>
+        <v>Germany</v>
       </c>
       <c r="N2" s="81" t="e">
         <f>IF('2026 World Cup'!$BM10="",NA(),'2026 World Cup'!$BM10)</f>
@@ -39622,18 +39622,18 @@
       <c r="I3" s="132" t="str">
         <v>Morocco</v>
       </c>
-      <c r="J3" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K3" s="81" t="e">
-        <v>#N/A</v>
+      <c r="J3" s="81">
+        <v>4</v>
+      </c>
+      <c r="K3" s="81">
+        <v>2</v>
       </c>
       <c r="L3" s="134" t="str">
         <v>Haiti</v>
       </c>
       <c r="M3" s="132" t="str">
         <f>'2026 World Cup'!BL14</f>
-        <v>1I</v>
+        <v>France</v>
       </c>
       <c r="N3" s="81" t="e">
         <f>IF('2026 World Cup'!$BM14="",NA(),'2026 World Cup'!$BM14)</f>
@@ -39724,18 +39724,18 @@
       <c r="I4" s="132" t="str">
         <v>Switzerland</v>
       </c>
-      <c r="J4" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K4" s="81" t="e">
-        <v>#N/A</v>
+      <c r="J4" s="81">
+        <v>2</v>
+      </c>
+      <c r="K4" s="81">
+        <v>1</v>
       </c>
       <c r="L4" s="134" t="str">
         <v>Canada</v>
       </c>
       <c r="M4" s="132" t="str">
         <f>'2026 World Cup'!BL18</f>
-        <v>2A</v>
+        <v>South Africa</v>
       </c>
       <c r="N4" s="81" t="e">
         <f>IF('2026 World Cup'!$BM18="",NA(),'2026 World Cup'!$BM18)</f>
@@ -39747,7 +39747,7 @@
       </c>
       <c r="P4" s="134" t="str">
         <f>'2026 World Cup'!BL19</f>
-        <v>2B</v>
+        <v>Canada</v>
       </c>
       <c r="Q4" s="132" t="str">
         <f>'2026 World Cup'!BS28</f>
@@ -39810,18 +39810,18 @@
       <c r="I5" s="132" t="str">
         <v>Bosnia and Herzegovina</v>
       </c>
-      <c r="J5" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K5" s="81" t="e">
-        <v>#N/A</v>
+      <c r="J5" s="81">
+        <v>3</v>
+      </c>
+      <c r="K5" s="81">
+        <v>1</v>
       </c>
       <c r="L5" s="134" t="str">
         <v>Qatar</v>
       </c>
       <c r="M5" s="132" t="str">
         <f>'2026 World Cup'!BL22</f>
-        <v>1F</v>
+        <v>Netherlands</v>
       </c>
       <c r="N5" s="81" t="e">
         <f>IF('2026 World Cup'!$BM22="",NA(),'2026 World Cup'!$BM22)</f>
@@ -39833,7 +39833,7 @@
       </c>
       <c r="P5" s="134" t="str">
         <f>'2026 World Cup'!BL23</f>
-        <v>2C</v>
+        <v>Morocco</v>
       </c>
       <c r="Q5" s="132" t="str">
         <f>'2026 World Cup'!BS36</f>
@@ -39896,11 +39896,11 @@
       <c r="I6" s="132" t="str">
         <v>Czech Republic</v>
       </c>
-      <c r="J6" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K6" s="81" t="e">
-        <v>#N/A</v>
+      <c r="J6" s="81">
+        <v>0</v>
+      </c>
+      <c r="K6" s="81">
+        <v>3</v>
       </c>
       <c r="L6" s="134" t="str">
         <v>Mexico</v>
@@ -39966,11 +39966,11 @@
       <c r="I7" s="132" t="str">
         <v>South Africa</v>
       </c>
-      <c r="J7" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K7" s="81" t="e">
-        <v>#N/A</v>
+      <c r="J7" s="81">
+        <v>1</v>
+      </c>
+      <c r="K7" s="81">
+        <v>0</v>
       </c>
       <c r="L7" s="134" t="str">
         <v>Korea Republic</v>
@@ -40036,18 +40036,18 @@
       <c r="I8" s="132" t="str">
         <v>Curaçao</v>
       </c>
-      <c r="J8" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K8" s="81" t="e">
-        <v>#N/A</v>
+      <c r="J8" s="81">
+        <v>0</v>
+      </c>
+      <c r="K8" s="81">
+        <v>2</v>
       </c>
       <c r="L8" s="134" t="str">
         <v>Ivory Coast</v>
       </c>
       <c r="M8" s="132" t="str">
         <f>'2026 World Cup'!BL34</f>
-        <v>1D</v>
+        <v>United States</v>
       </c>
       <c r="N8" s="81" t="e">
         <f>IF('2026 World Cup'!$BM34="",NA(),'2026 World Cup'!$BM34)</f>
@@ -40106,11 +40106,11 @@
       <c r="I9" s="132" t="str">
         <v>Ecuador</v>
       </c>
-      <c r="J9" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K9" s="81" t="e">
-        <v>#N/A</v>
+      <c r="J9" s="81">
+        <v>2</v>
+      </c>
+      <c r="K9" s="81">
+        <v>1</v>
       </c>
       <c r="L9" s="134" t="str">
         <v>Germany</v>
@@ -40176,18 +40176,18 @@
       <c r="I10" s="132" t="str">
         <v>Japan</v>
       </c>
-      <c r="J10" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K10" s="81" t="e">
-        <v>#N/A</v>
+      <c r="J10" s="81">
+        <v>1</v>
+      </c>
+      <c r="K10" s="81">
+        <v>1</v>
       </c>
       <c r="L10" s="134" t="str">
         <v>Sweden</v>
       </c>
       <c r="M10" s="132" t="str">
         <f>'2026 World Cup'!BL42</f>
-        <v>1C</v>
+        <v>Brazil</v>
       </c>
       <c r="N10" s="81" t="e">
         <f>IF('2026 World Cup'!$BM42="",NA(),'2026 World Cup'!$BM42)</f>
@@ -40199,7 +40199,7 @@
       </c>
       <c r="P10" s="134" t="str">
         <f>'2026 World Cup'!BL43</f>
-        <v>2F</v>
+        <v>Japan</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.2">
@@ -40230,18 +40230,18 @@
       <c r="I11" s="132" t="str">
         <v>Tunisia</v>
       </c>
-      <c r="J11" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K11" s="81" t="e">
-        <v>#N/A</v>
+      <c r="J11" s="81">
+        <v>1</v>
+      </c>
+      <c r="K11" s="81">
+        <v>3</v>
       </c>
       <c r="L11" s="134" t="str">
         <v>Netherlands</v>
       </c>
       <c r="M11" s="132" t="str">
         <f>'2026 World Cup'!BL46</f>
-        <v>2E</v>
+        <v>Ivory Coast</v>
       </c>
       <c r="N11" s="81" t="e">
         <f>IF('2026 World Cup'!$BM46="",NA(),'2026 World Cup'!$BM46)</f>
@@ -40253,7 +40253,7 @@
       </c>
       <c r="P11" s="134" t="str">
         <f>'2026 World Cup'!BL47</f>
-        <v>2I</v>
+        <v>Norway</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.2">
@@ -40284,18 +40284,18 @@
       <c r="I12" s="132" t="str">
         <v>Turkey</v>
       </c>
-      <c r="J12" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K12" s="81" t="e">
-        <v>#N/A</v>
+      <c r="J12" s="81">
+        <v>3</v>
+      </c>
+      <c r="K12" s="81">
+        <v>2</v>
       </c>
       <c r="L12" s="134" t="str">
         <v>United States</v>
       </c>
       <c r="M12" s="132" t="str">
         <f>'2026 World Cup'!BL50</f>
-        <v>1A</v>
+        <v>Mexico</v>
       </c>
       <c r="N12" s="81" t="e">
         <f>IF('2026 World Cup'!$BM40="",NA(),'2026 World Cup'!$BM40)</f>
@@ -40338,11 +40338,11 @@
       <c r="I13" s="132" t="str">
         <v>Paraguay</v>
       </c>
-      <c r="J13" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K13" s="81" t="e">
-        <v>#N/A</v>
+      <c r="J13" s="81">
+        <v>0</v>
+      </c>
+      <c r="K13" s="81">
+        <v>0</v>
       </c>
       <c r="L13" s="134" t="str">
         <v>Australia</v>
@@ -40392,11 +40392,11 @@
       <c r="I14" s="132" t="str">
         <v>Norway</v>
       </c>
-      <c r="J14" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K14" s="81" t="e">
-        <v>#N/A</v>
+      <c r="J14" s="81">
+        <v>1</v>
+      </c>
+      <c r="K14" s="81">
+        <v>4</v>
       </c>
       <c r="L14" s="134" t="str">
         <v>France</v>
@@ -40446,18 +40446,18 @@
       <c r="I15" s="132" t="str">
         <v>Senegal</v>
       </c>
-      <c r="J15" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K15" s="81" t="e">
-        <v>#N/A</v>
+      <c r="J15" s="81">
+        <v>5</v>
+      </c>
+      <c r="K15" s="81">
+        <v>0</v>
       </c>
       <c r="L15" s="134" t="str">
         <v>Iraq</v>
       </c>
       <c r="M15" s="132" t="str">
         <f>'2026 World Cup'!BL62</f>
-        <v>2D</v>
+        <v>Australia</v>
       </c>
       <c r="N15" s="81" t="e">
         <f>IF('2026 World Cup'!$BM62="",NA(),'2026 World Cup'!$BM62)</f>
@@ -40511,7 +40511,7 @@
       </c>
       <c r="M16" s="132" t="str">
         <f>'2026 World Cup'!BL66</f>
-        <v>1B</v>
+        <v>Switzerland</v>
       </c>
       <c r="N16" s="81" t="e">
         <f>IF('2026 World Cup'!$BM66="",NA(),'2026 World Cup'!$BM66)</f>
@@ -40964,25 +40964,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:95" ht="47" x14ac:dyDescent="0.2">
-      <c r="A1" s="182" t="str" cm="1">
+      <c r="A1" s="171" t="str" cm="1">
         <f t="array" ref="A1">INDEX(T,2,lang)</f>
         <v>2026 World Cup Final Tournament Schedule</v>
       </c>
-      <c r="B1" s="182"/>
-      <c r="C1" s="182"/>
-      <c r="D1" s="182"/>
-      <c r="E1" s="182"/>
-      <c r="F1" s="182"/>
-      <c r="G1" s="182"/>
-      <c r="H1" s="182"/>
-      <c r="I1" s="182"/>
-      <c r="J1" s="182"/>
-      <c r="K1" s="182"/>
-      <c r="L1" s="182"/>
-      <c r="M1" s="182"/>
-      <c r="N1" s="182"/>
-      <c r="O1" s="182"/>
-      <c r="P1" s="182"/>
+      <c r="B1" s="171"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="171"/>
+      <c r="F1" s="171"/>
+      <c r="G1" s="171"/>
+      <c r="H1" s="171"/>
+      <c r="I1" s="171"/>
+      <c r="J1" s="171"/>
+      <c r="K1" s="171"/>
+      <c r="L1" s="171"/>
+      <c r="M1" s="171"/>
+      <c r="N1" s="171"/>
+      <c r="O1" s="171"/>
+      <c r="P1" s="171"/>
       <c r="S1" s="123"/>
       <c r="T1" s="123"/>
       <c r="AC1" s="123"/>
@@ -41029,11 +41029,11 @@
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
-      <c r="O3" s="183" t="str">
+      <c r="O3" s="172" t="str">
         <f>"Language: " &amp; Settings!C4</f>
         <v>Language: English</v>
       </c>
-      <c r="P3" s="183"/>
+      <c r="P3" s="172"/>
       <c r="S3" s="123"/>
       <c r="T3" s="123"/>
       <c r="AC3" s="123"/>
@@ -41051,43 +41051,43 @@
     </row>
     <row r="4" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:95" x14ac:dyDescent="0.2">
-      <c r="A5" s="184" t="str" cm="1">
+      <c r="A5" s="173" t="str" cm="1">
         <f t="array" ref="A5">INDEX(T,3,lang)</f>
         <v>Group Stage</v>
       </c>
-      <c r="B5" s="185"/>
-      <c r="C5" s="185"/>
-      <c r="D5" s="185"/>
-      <c r="E5" s="185"/>
-      <c r="F5" s="185"/>
-      <c r="G5" s="185"/>
-      <c r="H5" s="186"/>
-      <c r="J5" s="190" t="s">
+      <c r="B5" s="174"/>
+      <c r="C5" s="174"/>
+      <c r="D5" s="174"/>
+      <c r="E5" s="174"/>
+      <c r="F5" s="174"/>
+      <c r="G5" s="174"/>
+      <c r="H5" s="175"/>
+      <c r="J5" s="179" t="s">
         <v>3166</v>
       </c>
-      <c r="K5" s="191"/>
-      <c r="L5" s="191"/>
-      <c r="M5" s="191"/>
-      <c r="N5" s="191"/>
-      <c r="O5" s="191"/>
-      <c r="P5" s="192"/>
+      <c r="K5" s="180"/>
+      <c r="L5" s="180"/>
+      <c r="M5" s="180"/>
+      <c r="N5" s="180"/>
+      <c r="O5" s="180"/>
+      <c r="P5" s="181"/>
     </row>
     <row r="6" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="187"/>
-      <c r="B6" s="188"/>
-      <c r="C6" s="188"/>
-      <c r="D6" s="188"/>
-      <c r="E6" s="188"/>
-      <c r="F6" s="188"/>
-      <c r="G6" s="188"/>
-      <c r="H6" s="189"/>
-      <c r="J6" s="193"/>
-      <c r="K6" s="194"/>
-      <c r="L6" s="194"/>
-      <c r="M6" s="194"/>
-      <c r="N6" s="194"/>
-      <c r="O6" s="194"/>
-      <c r="P6" s="195"/>
+      <c r="A6" s="176"/>
+      <c r="B6" s="177"/>
+      <c r="C6" s="177"/>
+      <c r="D6" s="177"/>
+      <c r="E6" s="177"/>
+      <c r="F6" s="177"/>
+      <c r="G6" s="177"/>
+      <c r="H6" s="178"/>
+      <c r="J6" s="182"/>
+      <c r="K6" s="183"/>
+      <c r="L6" s="183"/>
+      <c r="M6" s="183"/>
+      <c r="N6" s="183"/>
+      <c r="O6" s="183"/>
+      <c r="P6" s="184"/>
       <c r="R6" s="123" t="s">
         <v>3167</v>
       </c>
@@ -41197,37 +41197,37 @@
       <c r="BI6" s="128" t="s">
         <v>3178</v>
       </c>
-      <c r="BK6" s="176" t="s">
+      <c r="BK6" s="165" t="s">
         <v>3179</v>
       </c>
-      <c r="BL6" s="177"/>
-      <c r="BM6" s="177"/>
-      <c r="BN6" s="177"/>
-      <c r="BO6" s="178"/>
-      <c r="BR6" s="176" t="str" cm="1">
+      <c r="BL6" s="166"/>
+      <c r="BM6" s="166"/>
+      <c r="BN6" s="166"/>
+      <c r="BO6" s="167"/>
+      <c r="BR6" s="165" t="str" cm="1">
         <f t="array" ref="BR6">INDEX(T,4,lang)</f>
         <v>Round of 16</v>
       </c>
-      <c r="BS6" s="177"/>
-      <c r="BT6" s="177"/>
-      <c r="BU6" s="177"/>
-      <c r="BV6" s="178"/>
-      <c r="BY6" s="176" t="str" cm="1">
+      <c r="BS6" s="166"/>
+      <c r="BT6" s="166"/>
+      <c r="BU6" s="166"/>
+      <c r="BV6" s="167"/>
+      <c r="BY6" s="165" t="str" cm="1">
         <f t="array" ref="BY6">INDEX(T,5,lang)</f>
         <v>Quarterfinals</v>
       </c>
-      <c r="BZ6" s="177"/>
-      <c r="CA6" s="177"/>
-      <c r="CB6" s="177"/>
-      <c r="CC6" s="178"/>
-      <c r="CF6" s="176" t="str" cm="1">
+      <c r="BZ6" s="166"/>
+      <c r="CA6" s="166"/>
+      <c r="CB6" s="166"/>
+      <c r="CC6" s="167"/>
+      <c r="CF6" s="165" t="str" cm="1">
         <f t="array" ref="CF6">INDEX(T,6,lang)</f>
         <v>Semi-Finals</v>
       </c>
-      <c r="CG6" s="177"/>
-      <c r="CH6" s="177"/>
-      <c r="CI6" s="177"/>
-      <c r="CJ6" s="178"/>
+      <c r="CG6" s="166"/>
+      <c r="CH6" s="166"/>
+      <c r="CI6" s="166"/>
+      <c r="CJ6" s="167"/>
     </row>
     <row r="7" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="11">
@@ -41304,26 +41304,26 @@
         <v>1</v>
       </c>
       <c r="AY7" s="126"/>
-      <c r="BK7" s="179"/>
-      <c r="BL7" s="180"/>
-      <c r="BM7" s="180"/>
-      <c r="BN7" s="180"/>
-      <c r="BO7" s="181"/>
-      <c r="BR7" s="179"/>
-      <c r="BS7" s="180"/>
-      <c r="BT7" s="180"/>
-      <c r="BU7" s="180"/>
-      <c r="BV7" s="181"/>
-      <c r="BY7" s="179"/>
-      <c r="BZ7" s="180"/>
-      <c r="CA7" s="180"/>
-      <c r="CB7" s="180"/>
-      <c r="CC7" s="181"/>
-      <c r="CF7" s="179"/>
-      <c r="CG7" s="180"/>
-      <c r="CH7" s="180"/>
-      <c r="CI7" s="180"/>
-      <c r="CJ7" s="181"/>
+      <c r="BK7" s="168"/>
+      <c r="BL7" s="169"/>
+      <c r="BM7" s="169"/>
+      <c r="BN7" s="169"/>
+      <c r="BO7" s="170"/>
+      <c r="BR7" s="168"/>
+      <c r="BS7" s="169"/>
+      <c r="BT7" s="169"/>
+      <c r="BU7" s="169"/>
+      <c r="BV7" s="170"/>
+      <c r="BY7" s="168"/>
+      <c r="BZ7" s="169"/>
+      <c r="CA7" s="169"/>
+      <c r="CB7" s="169"/>
+      <c r="CC7" s="170"/>
+      <c r="CF7" s="168"/>
+      <c r="CG7" s="169"/>
+      <c r="CH7" s="169"/>
+      <c r="CI7" s="169"/>
+      <c r="CJ7" s="170"/>
     </row>
     <row r="8" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A8" s="16">
@@ -41437,7 +41437,7 @@
       </c>
       <c r="AF8" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE8 &amp; "_win")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG8" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE8 &amp; "_draw")</f>
@@ -41449,7 +41449,7 @@
       </c>
       <c r="AI8" s="123">
         <f>SUMIF($E$7:$E$78,$AE8,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE8,$G$7:$G$78)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AJ8" s="123">
         <f>SUMIF($E$7:$E$78,$AE8,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE8,$F$7:$F$78)</f>
@@ -41457,23 +41457,23 @@
       </c>
       <c r="AL8" s="123">
         <f>AI8-AJ8</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AM8" s="123">
         <f>AL8-AL12</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AN8" s="123">
         <f>AF8*3+AG8</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AO8" s="123">
         <f>AN8/AN12*10+BA8</f>
-        <v>8.5714285714285712</v>
+        <v>9</v>
       </c>
       <c r="AP8" s="123">
         <f>AO8*10000000+BI8*100+AM8/AM12*10+AI8/AI12*1++IF(AQ8=0,ROW(),AQ8)/2000000</f>
-        <v>85714294.79845956</v>
+        <v>90000009.948892459</v>
       </c>
       <c r="AQ8" s="126">
         <f>VLOOKUP(AE8,db_fifarank,2,FALSE)</f>
@@ -41481,11 +41481,11 @@
       </c>
       <c r="AR8" s="125">
         <f>AP8/AP12</f>
-        <v>0.9999999883333347</v>
+        <v>0.99999998888889019</v>
       </c>
       <c r="AS8" s="125" t="str">
         <f>IF(SUM(AF8:AH11)=12,J9,"1A")</f>
-        <v>1A</v>
+        <v>Mexico</v>
       </c>
       <c r="AT8" s="126" cm="1">
         <f t="array" ref="AT8">SUMPRODUCT(($S$7:$S$78=AE8&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE8&amp;"_win")*($U$7:$U$78))</f>
@@ -41608,11 +41608,11 @@
       </c>
       <c r="K9" s="31">
         <f>L9+M9+N9</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L9" s="31">
         <f>VLOOKUP(1,AD8:AN11,3,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M9" s="31">
         <f>VLOOKUP(1,AD8:AN11,4,FALSE)</f>
@@ -41624,11 +41624,11 @@
       </c>
       <c r="O9" s="31" t="str">
         <f>VLOOKUP(1,AD8:AN11,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD8:AN11,7,FALSE)</f>
-        <v>3 - 0</v>
+        <v>6 - 0</v>
       </c>
       <c r="P9" s="32">
         <f>L9*3+M9</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R9" s="123">
         <f>DATE(2026,6,12)+TIME(8,0,0)+gmt_delta</f>
@@ -41644,27 +41644,27 @@
       </c>
       <c r="U9" s="123">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="123">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" s="123">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9" s="123">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9" s="123">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z9" s="123">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA9" s="123">
         <f t="shared" si="5"/>
@@ -41676,7 +41676,7 @@
       </c>
       <c r="AD9" s="123">
         <f>COUNTIF(AR8:AR11,CONCATENATE("&gt;=",AR9))</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE9" s="124" t="str">
         <f>VLOOKUP("South Africa",T,lang,FALSE)</f>
@@ -41684,7 +41684,7 @@
       </c>
       <c r="AF9" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE9 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG9" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE9 &amp; "_draw")</f>
@@ -41696,7 +41696,7 @@
       </c>
       <c r="AI9" s="123">
         <f>SUMIF($E$7:$E$78,$AE9,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE9,$G$7:$G$78)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ9" s="123">
         <f>SUMIF($E$7:$E$78,$AE9,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE9,$F$7:$F$78)</f>
@@ -41704,23 +41704,23 @@
       </c>
       <c r="AL9" s="123">
         <f>AI9-AJ9</f>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AM9" s="123">
         <f>AL9-AL12</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN9" s="123">
         <f>AF9*3+AG9</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AO9" s="123">
         <f>AN9/AN12*10+BA9</f>
-        <v>2.409153952843273</v>
+        <v>4</v>
       </c>
       <c r="AP9" s="123">
         <f>AO9*10000000+BI9*100+AM9/AM12*10+AI9/AI12*1++IF(AQ9=0,ROW(),AQ9)/2000000</f>
-        <v>24091637.837400023</v>
+        <v>40000003.013701878</v>
       </c>
       <c r="AQ9" s="126">
         <f>VLOOKUP(AE9,db_fifarank,2,FALSE)</f>
@@ -41728,11 +41728,11 @@
       </c>
       <c r="AR9" s="125">
         <f>AP9/AP12</f>
-        <v>0.28106907503559042</v>
+        <v>0.44444442386141864</v>
       </c>
       <c r="AS9" s="125" t="str">
         <f>IF(SUM(AF8:AH11)=12,J10,"2A")</f>
-        <v>2A</v>
+        <v>South Africa</v>
       </c>
       <c r="AT9" s="126" cm="1">
         <f t="array" ref="AT9">SUMPRODUCT(($S$7:$S$78=AE9&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE9&amp;"_win")*($U$7:$U$78))</f>
@@ -41740,15 +41740,15 @@
       </c>
       <c r="AU9" s="126" cm="1">
         <f t="array" ref="AU9">SUMPRODUCT(($S$7:$S$78=AE9&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE9&amp;"_draw")*($U$7:$U$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV9" s="126" cm="1">
         <f t="array" ref="AV9">SUMPRODUCT(($E$7:$E$78=AE9)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE9)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW9" s="126" cm="1">
         <f t="array" ref="AW9">SUMPRODUCT(($E$7:$E$78=AE9)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE9)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX9" s="126">
         <f>AV9-AW9</f>
@@ -41760,11 +41760,11 @@
       </c>
       <c r="AZ9" s="126">
         <f>AT9/AT12*1000+AU9/AU12*100+AY9/AY12*10+AV9/AV12</f>
-        <v>50.5</v>
+        <v>0</v>
       </c>
       <c r="BA9" s="126">
         <f>AZ9/AZ12</f>
-        <v>0.98058252427184467</v>
+        <v>0</v>
       </c>
       <c r="BB9" s="126" cm="1">
         <f t="array" ref="BB9">SUMPRODUCT(($S$7:$S$78=AE9&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE9&amp;"_win")*($X$7:$X$78))</f>
@@ -41772,15 +41772,15 @@
       </c>
       <c r="BC9" s="126" cm="1">
         <f t="array" ref="BC9">SUMPRODUCT(($S$7:$S$78=AE9&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE9&amp;"_draw")*($X$7:$X$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD9" s="126" cm="1">
         <f t="array" ref="BD9">SUMPRODUCT(($E$7:$E$78=AE9)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE9)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE9" s="126" cm="1">
         <f t="array" ref="BE9">SUMPRODUCT(($E$7:$E$78=AE9)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE9)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF9" s="126">
         <f>BD9-BE9</f>
@@ -41792,11 +41792,11 @@
       </c>
       <c r="BH9" s="126">
         <f>BB9/BB12*1000+BC9/BC12*100+BG9/BG12*10+BD9/BD12</f>
-        <v>50.5</v>
+        <v>0</v>
       </c>
       <c r="BI9" s="126">
         <f>BH9/BH12</f>
-        <v>0.98058252427184467</v>
+        <v>0</v>
       </c>
       <c r="BK9" s="21" t="str" cm="1">
         <f t="array" ref="BK9">INDEX(T,24+MONTH(BP9),lang) &amp; " " &amp; DAY(BP9) &amp; ", " &amp; YEAR(BP9) &amp; "   " &amp; (IF(HOUR(BP9)&lt;10,0,"")&amp;HOUR(BP9)) &amp; ":" &amp;  (IF(MINUTE(BP9)&lt;10,0,"")&amp;MINUTE(BP9))</f>
@@ -41869,11 +41869,11 @@
       </c>
       <c r="J10" s="33" t="str">
         <f>VLOOKUP(2,AD8:AN11,2,FALSE)</f>
-        <v>Korea Republic</v>
+        <v>South Africa</v>
       </c>
       <c r="K10" s="23">
         <f>L10+M10+N10</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L10" s="23">
         <f>VLOOKUP(2,AD8:AN11,3,FALSE)</f>
@@ -41881,7 +41881,7 @@
       </c>
       <c r="M10" s="23">
         <f>VLOOKUP(2,AD8:AN11,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" s="23">
         <f>VLOOKUP(2,AD8:AN11,5,FALSE)</f>
@@ -41889,11 +41889,11 @@
       </c>
       <c r="O10" s="23" t="str">
         <f>VLOOKUP(2,AD8:AN11,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD8:AN11,7,FALSE)</f>
-        <v>2 - 2</v>
+        <v>2 - 3</v>
       </c>
       <c r="P10" s="34">
         <f>L10*3+M10</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R10" s="123">
         <f>DATE(2026,6,12)+TIME(14,0,0)+gmt_delta</f>
@@ -41941,7 +41941,7 @@
       </c>
       <c r="AD10" s="123">
         <f>COUNTIF(AR8:AR11,CONCATENATE("&gt;=",AR10))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE10" s="124" t="str">
         <f>VLOOKUP("Korea Republic",T,lang,FALSE)</f>
@@ -41957,7 +41957,7 @@
       </c>
       <c r="AH10" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE10 &amp; "_lose")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI10" s="123">
         <f>SUMIF($E$7:$E$78,$AE10,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE10,$G$7:$G$78)</f>
@@ -41965,15 +41965,15 @@
       </c>
       <c r="AJ10" s="123">
         <f>SUMIF($E$7:$E$78,$AE10,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE10,$F$7:$F$78)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL10" s="123">
         <f>AI10-AJ10</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM10" s="123">
         <f>AL10-AL12</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN10" s="123">
         <f>AF10*3+AG10</f>
@@ -41981,11 +41981,11 @@
       </c>
       <c r="AO10" s="123">
         <f>AN10/AN12*10+BA10</f>
-        <v>4.2857142857142856</v>
+        <v>3</v>
       </c>
       <c r="AP10" s="123">
         <f>AO10*10000000+BI10*100+AM10/AM12*10+AI10/AI12*1++IF(AQ10=0,ROW(),AQ10)/2000000</f>
-        <v>42857146.691270523</v>
+        <v>30000003.013781343</v>
       </c>
       <c r="AQ10" s="126">
         <f>VLOOKUP(AE10,db_fifarank,2,FALSE)</f>
@@ -41993,7 +41993,7 @@
       </c>
       <c r="AR10" s="125">
         <f>AP10/AP12</f>
-        <v>0.49999998590714367</v>
+        <v>0.33333332626834</v>
       </c>
       <c r="AT10" s="126" cm="1">
         <f t="array" ref="AT10">SUMPRODUCT(($S$7:$S$78=AE10&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE10&amp;"_win")*($U$7:$U$78))</f>
@@ -42059,12 +42059,12 @@
         <f>BH10/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK10" s="173">
+      <c r="BK10" s="163">
         <v>74</v>
       </c>
       <c r="BL10" s="24" t="str">
         <f>AS32</f>
-        <v>1E</v>
+        <v>Germany</v>
       </c>
       <c r="BM10" s="61"/>
       <c r="BN10" s="63"/>
@@ -42132,23 +42132,23 @@
       </c>
       <c r="J11" s="33" t="str">
         <f>VLOOKUP(3,AD8:AN11,2,FALSE)</f>
-        <v>Czech Republic</v>
+        <v>Korea Republic</v>
       </c>
       <c r="K11" s="23">
         <f>L11+M11+N11</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L11" s="23">
         <f>VLOOKUP(3,AD8:AN11,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="23">
         <f>VLOOKUP(3,AD8:AN11,4,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" s="23">
         <f>VLOOKUP(3,AD8:AN11,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O11" s="23" t="str">
         <f>VLOOKUP(3,AD8:AN11,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD8:AN11,7,FALSE)</f>
@@ -42156,7 +42156,7 @@
       </c>
       <c r="P11" s="34">
         <f>L11*3+M11</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R11" s="123">
         <f>DATE(2026,6,13)+TIME(14,0,0)+gmt_delta</f>
@@ -42204,7 +42204,7 @@
       </c>
       <c r="AD11" s="123">
         <f>COUNTIF(AR8:AR11,CONCATENATE("&gt;=",AR11))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE11" s="124" t="str">
         <f>VLOOKUP("Czech Republic",T,lang,FALSE)</f>
@@ -42220,7 +42220,7 @@
       </c>
       <c r="AH11" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE11 &amp; "_lose")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI11" s="123">
         <f>SUMIF($E$7:$E$78,$AE11,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE11,$G$7:$G$78)</f>
@@ -42228,15 +42228,15 @@
       </c>
       <c r="AJ11" s="123">
         <f>SUMIF($E$7:$E$78,$AE11,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE11,$F$7:$F$78)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AL11" s="123">
         <f>AI11-AJ11</f>
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="AM11" s="123">
         <f>AL11-AL12</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN11" s="123">
         <f>AF11*3+AG11</f>
@@ -42244,11 +42244,11 @@
       </c>
       <c r="AO11" s="123">
         <f>AN11/AN12*10+BA11</f>
-        <v>2.409153952843273</v>
+        <v>1</v>
       </c>
       <c r="AP11" s="123">
         <f>AO11*10000000+BI11*100+AM11/AM12*10+AI11/AI12*1++IF(AQ11=0,ROW(),AQ11)/2000000</f>
-        <v>24091639.754102517</v>
+        <v>10000000.286464976</v>
       </c>
       <c r="AQ11" s="126">
         <f>VLOOKUP(AE11,db_fifarank,2,FALSE)</f>
@@ -42256,7 +42256,7 @@
       </c>
       <c r="AR11" s="125">
         <f>AP11/AP12</f>
-        <v>0.28106909739711688</v>
+        <v>0.11111110077690536</v>
       </c>
       <c r="AT11" s="126" cm="1">
         <f t="array" ref="AT11">SUMPRODUCT(($S$7:$S$78=AE11&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE11&amp;"_win")*($U$7:$U$78))</f>
@@ -42264,15 +42264,15 @@
       </c>
       <c r="AU11" s="126" cm="1">
         <f t="array" ref="AU11">SUMPRODUCT(($S$7:$S$78=AE11&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE11&amp;"_draw")*($U$7:$U$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV11" s="126" cm="1">
         <f t="array" ref="AV11">SUMPRODUCT(($E$7:$E$78=AE11)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE11)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW11" s="126" cm="1">
         <f t="array" ref="AW11">SUMPRODUCT(($E$7:$E$78=AE11)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE11)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX11" s="126">
         <f>AV11-AW11</f>
@@ -42284,11 +42284,11 @@
       </c>
       <c r="AZ11" s="126">
         <f>AT11/AT12*1000+AU11/AU12*100+AY11/AY12*10+AV11/AV12</f>
-        <v>50.5</v>
+        <v>0</v>
       </c>
       <c r="BA11" s="126">
         <f>AZ11/AZ12</f>
-        <v>0.98058252427184467</v>
+        <v>0</v>
       </c>
       <c r="BB11" s="126" cm="1">
         <f t="array" ref="BB11">SUMPRODUCT(($S$7:$S$78=AE11&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE11&amp;"_win")*($X$7:$X$78))</f>
@@ -42296,15 +42296,15 @@
       </c>
       <c r="BC11" s="126" cm="1">
         <f t="array" ref="BC11">SUMPRODUCT(($S$7:$S$78=AE11&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE11&amp;"_draw")*($X$7:$X$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD11" s="126" cm="1">
         <f t="array" ref="BD11">SUMPRODUCT(($E$7:$E$78=AE11)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE11)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE11" s="126" cm="1">
         <f t="array" ref="BE11">SUMPRODUCT(($E$7:$E$78=AE11)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE11)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF11" s="126">
         <f>BD11-BE11</f>
@@ -42316,13 +42316,13 @@
       </c>
       <c r="BH11" s="126">
         <f>BB11/BB12*1000+BC11/BC12*100+BG11/BG12*10+BD11/BD12</f>
-        <v>50.5</v>
+        <v>0</v>
       </c>
       <c r="BI11" s="126">
         <f>BH11/BH12</f>
-        <v>0.98058252427184467</v>
-      </c>
-      <c r="BK11" s="174"/>
+        <v>0</v>
+      </c>
+      <c r="BK11" s="164"/>
       <c r="BL11" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!G3,AK80:AS91,9,FALSE),"3rd Group A/B/C/D/F")</f>
         <v>3rd Group A/B/C/D/F</v>
@@ -42399,11 +42399,11 @@
       </c>
       <c r="J12" s="35" t="str">
         <f>VLOOKUP(4,AD8:AN11,2,FALSE)</f>
-        <v>South Africa</v>
+        <v>Czech Republic</v>
       </c>
       <c r="K12" s="36">
         <f>L12+M12+N12</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L12" s="36">
         <f>VLOOKUP(4,AD8:AN11,3,FALSE)</f>
@@ -42415,11 +42415,11 @@
       </c>
       <c r="N12" s="36">
         <f>VLOOKUP(4,AD8:AN11,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O12" s="36" t="str">
         <f>VLOOKUP(4,AD8:AN11,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD8:AN11,7,FALSE)</f>
-        <v>1 - 3</v>
+        <v>2 - 6</v>
       </c>
       <c r="P12" s="37">
         <f>L12*3+M12</f>
@@ -42471,7 +42471,7 @@
       </c>
       <c r="AF12" s="123">
         <f t="shared" ref="AF12:AH12" si="12">MAX(AF8:AF11)-MIN(AF8:AF11)+1</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG12" s="123">
         <f t="shared" si="12"/>
@@ -42479,31 +42479,31 @@
       </c>
       <c r="AH12" s="123">
         <f t="shared" si="12"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI12" s="123">
         <f>MAX(AI8:AI11)+1</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AL12" s="123">
         <f>MIN(AL8:AL11)</f>
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="AM12" s="123">
         <f>MAX(AM8:AM11)+1</f>
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AN12" s="123">
         <f>MAX(AN8:AN11)+1</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AO12" s="123">
         <f>MAX(AO8:AO11)+1</f>
-        <v>9.5714285714285712</v>
+        <v>10</v>
       </c>
       <c r="AP12" s="123">
         <f>MAX(AP8:AP11)+1</f>
-        <v>85714295.79845956</v>
+        <v>90000010.948892459</v>
       </c>
       <c r="AT12" s="126">
         <f>MAX(AT8:AT11)-MIN(AT8:AT11)+1</f>
@@ -42511,15 +42511,15 @@
       </c>
       <c r="AU12" s="126">
         <f>MAX(AU8:AU11)-MIN(AU8:AU11)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV12" s="126">
         <f>MAX(AV8:AV11)-MIN(AV8:AV11)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW12" s="126">
         <f>MAX(AW8:AW11)-MIN(AW8:AW11)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY12" s="126">
         <f>MAX(AY8:AY11)-MIN(AY8:AY11)+1</f>
@@ -42527,7 +42527,7 @@
       </c>
       <c r="AZ12" s="126">
         <f>MAX(AZ8:AZ11)+1</f>
-        <v>51.5</v>
+        <v>1</v>
       </c>
       <c r="BB12" s="126">
         <f>MAX(BB8:BB11)-MIN(BB8:BB11)+1</f>
@@ -42535,15 +42535,15 @@
       </c>
       <c r="BC12" s="126">
         <f>MAX(BC8:BC11)-MIN(BC8:BC11)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BD12" s="126">
         <f>MAX(BD8:BD11)-MIN(BD8:BD11)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BE12" s="126">
         <f>MAX(BE8:BE11)-MIN(BE8:BE11)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BG12" s="126">
         <f>MAX(BG8:BG11)-MIN(BG8:BG11)+1</f>
@@ -42551,7 +42551,7 @@
       </c>
       <c r="BH12" s="126">
         <f>MAX(BH8:BH11)+1</f>
-        <v>51.5</v>
+        <v>1</v>
       </c>
       <c r="BK12" s="21"/>
       <c r="BL12" s="21"/>
@@ -42560,7 +42560,7 @@
       <c r="BO12" s="21"/>
       <c r="BP12" s="114"/>
       <c r="BQ12" s="112"/>
-      <c r="BR12" s="173">
+      <c r="BR12" s="163">
         <v>89</v>
       </c>
       <c r="BS12" s="24" t="str">
@@ -42681,7 +42681,7 @@
         <v>46203.875</v>
       </c>
       <c r="BQ13" s="115"/>
-      <c r="BR13" s="174"/>
+      <c r="BR13" s="164"/>
       <c r="BS13" s="26" t="str">
         <f>IF(BP14&gt;BP15,BL14,IF(BP14&lt;BP15,BL15,""))</f>
         <v/>
@@ -42817,7 +42817,7 @@
       </c>
       <c r="AD14" s="123">
         <f>COUNTIF(AR14:AR17,CONCATENATE("&gt;=",AR14))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE14" s="124" t="str">
         <f>VLOOKUP("Canada",T,lang,FALSE)</f>
@@ -42833,23 +42833,23 @@
       </c>
       <c r="AH14" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE14 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI14" s="123">
         <f>SUMIF($E$7:$E$78,$AE14,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE14,$G$7:$G$78)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ14" s="123">
         <f>SUMIF($E$7:$E$78,$AE14,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE14,$F$7:$F$78)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AL14" s="123">
         <f>AI14-AJ14</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM14" s="123">
         <f>AL14-AL18</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN14" s="123">
         <f>AF14*3+AG14</f>
@@ -42857,11 +42857,11 @@
       </c>
       <c r="AO14" s="123">
         <f>AN14/AN18*10+BA14</f>
-        <v>8</v>
+        <v>5.9805825242718447</v>
       </c>
       <c r="AP14" s="123">
         <f>AO14*10000000+BI14*100+AM14/AM18*10+AI14/AI18*1++IF(AQ14=0,ROW(),AQ14)/2000000</f>
-        <v>80000010.106547475</v>
+        <v>59805933.476352282</v>
       </c>
       <c r="AQ14" s="126">
         <f>VLOOKUP(AE14,db_fifarank,2,FALSE)</f>
@@ -42869,11 +42869,11 @@
       </c>
       <c r="AR14" s="125">
         <f>AP14/AP18</f>
-        <v>0.99999998750000174</v>
+        <v>0.68349630173879239</v>
       </c>
       <c r="AS14" s="125" t="str">
         <f>IF(SUM(AF14:AH17)=12,J15,"1B")</f>
-        <v>1B</v>
+        <v>Switzerland</v>
       </c>
       <c r="AT14" s="126" cm="1">
         <f t="array" ref="AT14">SUMPRODUCT(($S$7:$S$78=AE14&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE14&amp;"_win")*($U$7:$U$78))</f>
@@ -42881,15 +42881,15 @@
       </c>
       <c r="AU14" s="126" cm="1">
         <f t="array" ref="AU14">SUMPRODUCT(($S$7:$S$78=AE14&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE14&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV14" s="126" cm="1">
         <f t="array" ref="AV14">SUMPRODUCT(($E$7:$E$78=AE14)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE14)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW14" s="126" cm="1">
         <f t="array" ref="AW14">SUMPRODUCT(($E$7:$E$78=AE14)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE14)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX14" s="126">
         <f>AV14-AW14</f>
@@ -42901,11 +42901,11 @@
       </c>
       <c r="AZ14" s="126">
         <f>AT14/AT18*1000+AU14/AU18*100+AY14/AY18*10+AV14/AV18</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BA14" s="126">
         <f>AZ14/AZ18</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BB14" s="126" cm="1">
         <f t="array" ref="BB14">SUMPRODUCT(($S$7:$S$78=AE14&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE14&amp;"_win")*($X$7:$X$78))</f>
@@ -42913,15 +42913,15 @@
       </c>
       <c r="BC14" s="126" cm="1">
         <f t="array" ref="BC14">SUMPRODUCT(($S$7:$S$78=AE14&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE14&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD14" s="126" cm="1">
         <f t="array" ref="BD14">SUMPRODUCT(($E$7:$E$78=AE14)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE14)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE14" s="126" cm="1">
         <f t="array" ref="BE14">SUMPRODUCT(($E$7:$E$78=AE14)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE14)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF14" s="126">
         <f>BD14-BE14</f>
@@ -42933,18 +42933,18 @@
       </c>
       <c r="BH14" s="126">
         <f>BB14/BB18*1000+BC14/BC18*100+BG14/BG18*10+BD14/BD18</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BI14" s="126">
         <f>BH14/BH18</f>
-        <v>0</v>
-      </c>
-      <c r="BK14" s="173">
+        <v>0.98058252427184467</v>
+      </c>
+      <c r="BK14" s="163">
         <v>77</v>
       </c>
       <c r="BL14" s="24" t="str">
         <f>AS56</f>
-        <v>1I</v>
+        <v>France</v>
       </c>
       <c r="BM14" s="61"/>
       <c r="BN14" s="63"/>
@@ -43012,15 +43012,15 @@
       </c>
       <c r="J15" s="30" t="str">
         <f>VLOOKUP(1,AD14:AN17,2,FALSE)</f>
-        <v>Canada</v>
+        <v>Switzerland</v>
       </c>
       <c r="K15" s="31">
         <f>L15+M15+N15</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L15" s="31">
         <f>VLOOKUP(1,AD14:AN17,3,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M15" s="31">
         <f>VLOOKUP(1,AD14:AN17,4,FALSE)</f>
@@ -43032,11 +43032,11 @@
       </c>
       <c r="O15" s="31" t="str">
         <f>VLOOKUP(1,AD14:AN17,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD14:AN17,7,FALSE)</f>
-        <v>7 - 1</v>
+        <v>7 - 3</v>
       </c>
       <c r="P15" s="32">
         <f>L15*3+M15</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R15" s="123">
         <f>DATE(2026,6,14)+TIME(12,0,0)+gmt_delta</f>
@@ -43092,7 +43092,7 @@
       </c>
       <c r="AF15" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE15 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG15" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE15 &amp; "_draw")</f>
@@ -43104,31 +43104,31 @@
       </c>
       <c r="AI15" s="123">
         <f>SUMIF($E$7:$E$78,$AE15,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE15,$G$7:$G$78)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AJ15" s="123">
         <f>SUMIF($E$7:$E$78,$AE15,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE15,$F$7:$F$78)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL15" s="123">
         <f>AI15-AJ15</f>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="AM15" s="123">
         <f>AL15-AL18</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AN15" s="123">
         <f>AF15*3+AG15</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AO15" s="123">
         <f>AN15/AN18*10+BA15</f>
-        <v>2</v>
+        <v>5.9805825242718447</v>
       </c>
       <c r="AP15" s="123">
         <f>AO15*10000000+BI15*100+AM15/AM18*10+AI15/AI18*1++IF(AQ15=0,ROW(),AQ15)/2000000</f>
-        <v>20000002.558385227</v>
+        <v>59805928.857219338</v>
       </c>
       <c r="AQ15" s="126">
         <f>VLOOKUP(AE15,db_fifarank,2,FALSE)</f>
@@ -43136,11 +43136,11 @@
       </c>
       <c r="AR15" s="125">
         <f>AP15/AP18</f>
-        <v>0.24999999727185485</v>
+        <v>0.68349624894870786</v>
       </c>
       <c r="AS15" s="125" t="str">
         <f>IF(SUM(AF14:AH17)=12,J16,"2B")</f>
-        <v>2B</v>
+        <v>Canada</v>
       </c>
       <c r="AT15" s="126" cm="1">
         <f t="array" ref="AT15">SUMPRODUCT(($S$7:$S$78=AE15&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE15&amp;"_win")*($U$7:$U$78))</f>
@@ -43148,15 +43148,15 @@
       </c>
       <c r="AU15" s="126" cm="1">
         <f t="array" ref="AU15">SUMPRODUCT(($S$7:$S$78=AE15&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE15&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV15" s="126" cm="1">
         <f t="array" ref="AV15">SUMPRODUCT(($E$7:$E$78=AE15)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE15)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW15" s="126" cm="1">
         <f t="array" ref="AW15">SUMPRODUCT(($E$7:$E$78=AE15)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE15)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX15" s="126">
         <f>AV15-AW15</f>
@@ -43168,11 +43168,11 @@
       </c>
       <c r="AZ15" s="126">
         <f>AT15/AT18*1000+AU15/AU18*100+AY15/AY18*10+AV15/AV18</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BA15" s="126">
         <f>AZ15/AZ18</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BB15" s="126" cm="1">
         <f t="array" ref="BB15">SUMPRODUCT(($S$7:$S$78=AE15&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE15&amp;"_win")*($X$7:$X$78))</f>
@@ -43180,15 +43180,15 @@
       </c>
       <c r="BC15" s="126" cm="1">
         <f t="array" ref="BC15">SUMPRODUCT(($S$7:$S$78=AE15&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE15&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD15" s="126" cm="1">
         <f t="array" ref="BD15">SUMPRODUCT(($E$7:$E$78=AE15)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE15)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE15" s="126" cm="1">
         <f t="array" ref="BE15">SUMPRODUCT(($E$7:$E$78=AE15)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE15)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF15" s="126">
         <f>BD15-BE15</f>
@@ -43200,13 +43200,13 @@
       </c>
       <c r="BH15" s="126">
         <f>BB15/BB18*1000+BC15/BC18*100+BG15/BG18*10+BD15/BD18</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BI15" s="126">
         <f>BH15/BH18</f>
-        <v>0</v>
-      </c>
-      <c r="BK15" s="174"/>
+        <v>0.98058252427184467</v>
+      </c>
+      <c r="BK15" s="164"/>
       <c r="BL15" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!I3,AK80:AS91,9,FALSE),"3rd Group C/D/F/G/H")</f>
         <v>3rd Group C/D/F/G/H</v>
@@ -43276,11 +43276,11 @@
       </c>
       <c r="J16" s="33" t="str">
         <f>VLOOKUP(2,AD14:AN17,2,FALSE)</f>
-        <v>Switzerland</v>
+        <v>Canada</v>
       </c>
       <c r="K16" s="23">
         <f>L16+M16+N16</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L16" s="23">
         <f>VLOOKUP(2,AD14:AN17,3,FALSE)</f>
@@ -43292,11 +43292,11 @@
       </c>
       <c r="N16" s="23">
         <f>VLOOKUP(2,AD14:AN17,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" s="23" t="str">
         <f>VLOOKUP(2,AD14:AN17,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD14:AN17,7,FALSE)</f>
-        <v>5 - 2</v>
+        <v>8 - 3</v>
       </c>
       <c r="P16" s="34">
         <f>L16*3+M16</f>
@@ -43364,19 +43364,19 @@
       </c>
       <c r="AH16" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE16 &amp; "_lose")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI16" s="123">
         <f>SUMIF($E$7:$E$78,$AE16,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE16,$G$7:$G$78)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ16" s="123">
         <f>SUMIF($E$7:$E$78,$AE16,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE16,$F$7:$F$78)</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AL16" s="123">
         <f>AI16-AJ16</f>
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="AM16" s="123">
         <f>AL16-AL18</f>
@@ -43388,11 +43388,11 @@
       </c>
       <c r="AO16" s="123">
         <f>AN16/AN18*10+BA16</f>
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AP16" s="123">
         <f>AO16*10000000+BI16*100+AM16/AM18*10+AI16/AI18*1++IF(AQ16=0,ROW(),AQ16)/2000000</f>
-        <v>20000000.125727478</v>
+        <v>12500000.222949702</v>
       </c>
       <c r="AQ16" s="126">
         <f>VLOOKUP(AE16,db_fifarank,2,FALSE)</f>
@@ -43400,7 +43400,7 @@
       </c>
       <c r="AR16" s="125">
         <f>AP16/AP18</f>
-        <v>0.24999996686363724</v>
+        <v>0.14285712850713128</v>
       </c>
       <c r="AT16" s="126" cm="1">
         <f t="array" ref="AT16">SUMPRODUCT(($S$7:$S$78=AE16&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE16&amp;"_win")*($U$7:$U$78))</f>
@@ -43480,7 +43480,7 @@
       <c r="BV16" s="21"/>
       <c r="BW16" s="114"/>
       <c r="BX16" s="112"/>
-      <c r="BY16" s="173">
+      <c r="BY16" s="163">
         <v>97</v>
       </c>
       <c r="BZ16" s="24" t="str">
@@ -43536,11 +43536,11 @@
       </c>
       <c r="K17" s="23">
         <f>L17+M17+N17</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L17" s="23">
         <f>VLOOKUP(3,AD14:AN17,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="23">
         <f>VLOOKUP(3,AD14:AN17,4,FALSE)</f>
@@ -43552,11 +43552,11 @@
       </c>
       <c r="O17" s="23" t="str">
         <f>VLOOKUP(3,AD14:AN17,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD14:AN17,7,FALSE)</f>
-        <v>2 - 5</v>
+        <v>5 - 6</v>
       </c>
       <c r="P17" s="34">
         <f>L17*3+M17</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R17" s="123">
         <f>DATE(2026,6,14)+TIME(9,0,0)+gmt_delta</f>
@@ -43572,27 +43572,27 @@
       </c>
       <c r="U17" s="123">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="123">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W17" s="123">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X17" s="123">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y17" s="123">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z17" s="123">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA17" s="123">
         <f t="shared" si="5"/>
@@ -43604,7 +43604,7 @@
       </c>
       <c r="AD17" s="123">
         <f>COUNTIF(AR14:AR17,CONCATENATE("&gt;=",AR17))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE17" s="124" t="str">
         <f>VLOOKUP("Switzerland",T,lang,FALSE)</f>
@@ -43612,7 +43612,7 @@
       </c>
       <c r="AF17" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE17 &amp; "_win")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG17" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE17 &amp; "_draw")</f>
@@ -43624,31 +43624,31 @@
       </c>
       <c r="AI17" s="123">
         <f>SUMIF($E$7:$E$78,$AE17,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE17,$G$7:$G$78)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AJ17" s="123">
         <f>SUMIF($E$7:$E$78,$AE17,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE17,$F$7:$F$78)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL17" s="123">
         <f>AI17-AJ17</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM17" s="123">
         <f>AL17-AL18</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AN17" s="123">
         <f>AF17*3+AG17</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AO17" s="123">
         <f>AN17/AN18*10+BA17</f>
-        <v>8</v>
+        <v>8.75</v>
       </c>
       <c r="AP17" s="123">
         <f>AO17*10000000+BI17*100+AM17/AM18*10+AI17/AI18*1++IF(AQ17=0,ROW(),AQ17)/2000000</f>
-        <v>80000007.548901632</v>
+        <v>87500009.350031048</v>
       </c>
       <c r="AQ17" s="126">
         <f>VLOOKUP(AE17,db_fifarank,2,FALSE)</f>
@@ -43656,7 +43656,7 @@
       </c>
       <c r="AR17" s="125">
         <f>AP17/AP18</f>
-        <v>0.9999999555294331</v>
+        <v>0.99999998857142991</v>
       </c>
       <c r="AT17" s="126" cm="1">
         <f t="array" ref="AT17">SUMPRODUCT(($S$7:$S$78=AE17&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE17&amp;"_win")*($U$7:$U$78))</f>
@@ -43742,7 +43742,7 @@
       <c r="BV17" s="21"/>
       <c r="BW17" s="114"/>
       <c r="BX17" s="115"/>
-      <c r="BY17" s="174"/>
+      <c r="BY17" s="164"/>
       <c r="BZ17" s="26" t="str">
         <f>IF(BW20&gt;BW21,BS20,IF(BW20&lt;BW21,BS21,""))</f>
         <v/>
@@ -43796,7 +43796,7 @@
       </c>
       <c r="K18" s="36">
         <f>L18+M18+N18</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L18" s="36">
         <f>VLOOKUP(4,AD14:AN17,3,FALSE)</f>
@@ -43808,11 +43808,11 @@
       </c>
       <c r="N18" s="36">
         <f>VLOOKUP(4,AD14:AN17,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O18" s="36" t="str">
         <f>VLOOKUP(4,AD14:AN17,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD14:AN17,7,FALSE)</f>
-        <v>1 - 7</v>
+        <v>2 - 10</v>
       </c>
       <c r="P18" s="37">
         <f>L18*3+M18</f>
@@ -43864,7 +43864,7 @@
       </c>
       <c r="AF18" s="123">
         <f t="shared" ref="AF18:AH18" si="13">MAX(AF14:AF17)-MIN(AF14:AF17)+1</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG18" s="123">
         <f t="shared" si="13"/>
@@ -43872,31 +43872,31 @@
       </c>
       <c r="AH18" s="123">
         <f t="shared" si="13"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI18" s="123">
         <f>MAX(AI14:AI17)+1</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL18" s="123">
         <f>MIN(AL14:AL17)</f>
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="AM18" s="123">
         <f>MAX(AM14:AM17)+1</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AN18" s="123">
         <f>MAX(AN14:AN17)+1</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AO18" s="123">
         <f>MAX(AO14:AO17)+1</f>
-        <v>9</v>
+        <v>9.75</v>
       </c>
       <c r="AP18" s="123">
         <f>MAX(AP14:AP17)+1</f>
-        <v>80000011.106547475</v>
+        <v>87500010.350031048</v>
       </c>
       <c r="AT18" s="126">
         <f>MAX(AT14:AT17)-MIN(AT14:AT17)+1</f>
@@ -43904,15 +43904,15 @@
       </c>
       <c r="AU18" s="126">
         <f>MAX(AU14:AU17)-MIN(AU14:AU17)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV18" s="126">
         <f>MAX(AV14:AV17)-MIN(AV14:AV17)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW18" s="126">
         <f>MAX(AW14:AW17)-MIN(AW14:AW17)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY18" s="126">
         <f>MAX(AY14:AY17)-MIN(AY14:AY17)+1</f>
@@ -43920,7 +43920,7 @@
       </c>
       <c r="AZ18" s="126">
         <f>MAX(AZ14:AZ17)+1</f>
-        <v>1</v>
+        <v>51.5</v>
       </c>
       <c r="BB18" s="126">
         <f>MAX(BB14:BB17)-MIN(BB14:BB17)+1</f>
@@ -43928,15 +43928,15 @@
       </c>
       <c r="BC18" s="126">
         <f>MAX(BC14:BC17)-MIN(BC14:BC17)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD18" s="126">
         <f>MAX(BD14:BD17)-MIN(BD14:BD17)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BE18" s="126">
         <f>MAX(BE14:BE17)-MIN(BE14:BE17)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BG18" s="126">
         <f>MAX(BG14:BG17)-MIN(BG14:BG17)+1</f>
@@ -43944,14 +43944,14 @@
       </c>
       <c r="BH18" s="126">
         <f>MAX(BH14:BH17)+1</f>
-        <v>1</v>
-      </c>
-      <c r="BK18" s="173">
+        <v>51.5</v>
+      </c>
+      <c r="BK18" s="163">
         <v>73</v>
       </c>
       <c r="BL18" s="24" t="str">
         <f>AS9</f>
-        <v>2A</v>
+        <v>South Africa</v>
       </c>
       <c r="BM18" s="61"/>
       <c r="BN18" s="63"/>
@@ -44054,10 +44054,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BK19" s="174"/>
+      <c r="BK19" s="164"/>
       <c r="BL19" s="26" t="str">
         <f>AS15</f>
-        <v>2B</v>
+        <v>Canada</v>
       </c>
       <c r="BM19" s="62"/>
       <c r="BN19" s="64"/>
@@ -44211,7 +44211,7 @@
       </c>
       <c r="AF20" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE20 &amp; "_win")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG20" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE20 &amp; "_draw")</f>
@@ -44223,7 +44223,7 @@
       </c>
       <c r="AI20" s="123">
         <f>SUMIF($E$7:$E$78,$AE20,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE20,$G$7:$G$78)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AJ20" s="123">
         <f>SUMIF($E$7:$E$78,$AE20,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE20,$F$7:$F$78)</f>
@@ -44231,23 +44231,23 @@
       </c>
       <c r="AL20" s="123">
         <f>AI20-AJ20</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AM20" s="123">
         <f>AL20-AL24</f>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AN20" s="123">
         <f>AF20*3+AG20</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AO20" s="123">
         <f>AN20/AN24*10+BA20</f>
-        <v>8.9805825242718456</v>
+        <v>9.7305825242718456</v>
       </c>
       <c r="AP20" s="123">
         <f>AO20*10000000+BI20*100+AM20/AM24*10+AI20/AI24*1++IF(AQ20=0,ROW(),AQ20)/2000000</f>
-        <v>89805932.851851463</v>
+        <v>97305933.407620698</v>
       </c>
       <c r="AQ20" s="126">
         <f>VLOOKUP(AE20,db_fifarank,2,FALSE)</f>
@@ -44255,11 +44255,11 @@
       </c>
       <c r="AR20" s="125">
         <f>AP20/AP24</f>
-        <v>0.99999998886487829</v>
+        <v>0.99999998972313453</v>
       </c>
       <c r="AS20" s="125" t="str">
         <f>IF(SUM(AF20:AH23)=12,J21,"1C")</f>
-        <v>1C</v>
+        <v>Brazil</v>
       </c>
       <c r="AT20" s="126" cm="1">
         <f t="array" ref="AT20">SUMPRODUCT(($S$7:$S$78=AE20&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE20&amp;"_win")*($U$7:$U$78))</f>
@@ -44332,7 +44332,7 @@
       <c r="BO20" s="21"/>
       <c r="BP20" s="114"/>
       <c r="BQ20" s="112"/>
-      <c r="BR20" s="173">
+      <c r="BR20" s="163">
         <v>90</v>
       </c>
       <c r="BS20" s="24" t="str">
@@ -44402,11 +44402,11 @@
       </c>
       <c r="K21" s="31">
         <f>L21+M21+N21</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L21" s="31">
         <f>VLOOKUP(1,AD20:AN23,3,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M21" s="31">
         <f>VLOOKUP(1,AD20:AN23,4,FALSE)</f>
@@ -44418,11 +44418,11 @@
       </c>
       <c r="O21" s="31" t="str">
         <f>VLOOKUP(1,AD20:AN23,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD20:AN23,7,FALSE)</f>
-        <v>4 - 1</v>
+        <v>7 - 1</v>
       </c>
       <c r="P21" s="32">
         <f>L21*3+M21</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R21" s="123">
         <f>DATE(2026,6,15)+TIME(14,0,0)+gmt_delta</f>
@@ -44478,7 +44478,7 @@
       </c>
       <c r="AF21" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE21 &amp; "_win")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG21" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE21 &amp; "_draw")</f>
@@ -44490,31 +44490,31 @@
       </c>
       <c r="AI21" s="123">
         <f>SUMIF($E$7:$E$78,$AE21,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE21,$G$7:$G$78)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AJ21" s="123">
         <f>SUMIF($E$7:$E$78,$AE21,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE21,$F$7:$F$78)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AL21" s="123">
         <f>AI21-AJ21</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AM21" s="123">
         <f>AL21-AL24</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AN21" s="123">
         <f>AF21*3+AG21</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AO21" s="123">
         <f>AN21/AN24*10+BA21</f>
-        <v>8.9805825242718456</v>
+        <v>9.7305825242718456</v>
       </c>
       <c r="AP21" s="123">
         <f>AO21*10000000+BI21*100+AM21/AM24*10+AI21/AI24*1++IF(AQ21=0,ROW(),AQ21)/2000000</f>
-        <v>89805929.95184882</v>
+        <v>97305930.974925742</v>
       </c>
       <c r="AQ21" s="126">
         <f>VLOOKUP(AE21,db_fifarank,2,FALSE)</f>
@@ -44522,11 +44522,11 @@
       </c>
       <c r="AR21" s="125">
         <f>AP21/AP24</f>
-        <v>0.99999995657299601</v>
+        <v>0.99999996472265562</v>
       </c>
       <c r="AS21" s="125" t="str">
         <f>IF(SUM(AF20:AH23)=12,J22,"2C")</f>
-        <v>2C</v>
+        <v>Morocco</v>
       </c>
       <c r="AT21" s="126" cm="1">
         <f t="array" ref="AT21">SUMPRODUCT(($S$7:$S$78=AE21&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE21&amp;"_win")*($U$7:$U$78))</f>
@@ -44605,7 +44605,7 @@
         <v>46203.041666666672</v>
       </c>
       <c r="BQ21" s="115"/>
-      <c r="BR21" s="174"/>
+      <c r="BR21" s="164"/>
       <c r="BS21" s="26" t="str">
         <f>IF(BP22&gt;BP23,BL22,IF(BP22&lt;BP23,BL23,""))</f>
         <v/>
@@ -44673,11 +44673,11 @@
       </c>
       <c r="K22" s="23">
         <f>L22+M22+N22</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L22" s="23">
         <f>VLOOKUP(2,AD20:AN23,3,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M22" s="23">
         <f>VLOOKUP(2,AD20:AN23,4,FALSE)</f>
@@ -44689,11 +44689,11 @@
       </c>
       <c r="O22" s="23" t="str">
         <f>VLOOKUP(2,AD20:AN23,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD20:AN23,7,FALSE)</f>
-        <v>2 - 1</v>
+        <v>6 - 3</v>
       </c>
       <c r="P22" s="34">
         <f>L22*3+M22</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R22" s="123">
         <f>DATE(2026,6,15)+TIME(8,0,0)+gmt_delta</f>
@@ -44757,19 +44757,19 @@
       </c>
       <c r="AH22" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE22 &amp; "_lose")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI22" s="123">
         <f>SUMIF($E$7:$E$78,$AE22,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE22,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ22" s="123">
         <f>SUMIF($E$7:$E$78,$AE22,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE22,$F$7:$F$78)</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AL22" s="123">
         <f>AI22-AJ22</f>
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="AM22" s="123">
         <f>AL22-AL24</f>
@@ -44785,7 +44785,7 @@
       </c>
       <c r="AP22" s="123">
         <f>AO22*10000000+BI22*100+AM22/AM24*10+AI22/AI24*1++IF(AQ22=0,ROW(),AQ22)/2000000</f>
-        <v>6.4585499999999998E-4</v>
+        <v>0.25064585499999997</v>
       </c>
       <c r="AQ22" s="126">
         <f>VLOOKUP(AE22,db_fifarank,2,FALSE)</f>
@@ -44793,7 +44793,7 @@
       </c>
       <c r="AR22" s="125">
         <f>AP22/AP24</f>
-        <v>7.1916740052548863E-12</v>
+        <v>2.5758537393005105E-9</v>
       </c>
       <c r="AT22" s="126" cm="1">
         <f t="array" ref="AT22">SUMPRODUCT(($S$7:$S$78=AE22&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE22&amp;"_win")*($U$7:$U$78))</f>
@@ -44859,12 +44859,12 @@
         <f>BH22/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK22" s="173">
+      <c r="BK22" s="163">
         <v>75</v>
       </c>
       <c r="BL22" s="24" t="str">
         <f>AS38</f>
-        <v>1F</v>
+        <v>Netherlands</v>
       </c>
       <c r="BM22" s="61"/>
       <c r="BN22" s="63"/>
@@ -44937,7 +44937,7 @@
       </c>
       <c r="K23" s="23">
         <f>L23+M23+N23</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L23" s="23">
         <f>VLOOKUP(3,AD20:AN23,3,FALSE)</f>
@@ -44949,11 +44949,11 @@
       </c>
       <c r="N23" s="23">
         <f>VLOOKUP(3,AD20:AN23,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O23" s="23" t="str">
         <f>VLOOKUP(3,AD20:AN23,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD20:AN23,7,FALSE)</f>
-        <v>1 - 1</v>
+        <v>1 - 4</v>
       </c>
       <c r="P23" s="34">
         <f>L23*3+M23</f>
@@ -45021,7 +45021,7 @@
       </c>
       <c r="AH23" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE23 &amp; "_lose")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI23" s="123">
         <f>SUMIF($E$7:$E$78,$AE23,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE23,$G$7:$G$78)</f>
@@ -45029,15 +45029,15 @@
       </c>
       <c r="AJ23" s="123">
         <f>SUMIF($E$7:$E$78,$AE23,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE23,$F$7:$F$78)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AL23" s="123">
         <f>AI23-AJ23</f>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AM23" s="123">
         <f>AL23-AL24</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN23" s="123">
         <f>AF23*3+AG23</f>
@@ -45045,11 +45045,11 @@
       </c>
       <c r="AO23" s="123">
         <f>AN23/AN24*10+BA23</f>
-        <v>6</v>
+        <v>3.75</v>
       </c>
       <c r="AP23" s="123">
         <f>AO23*10000000+BI23*100+AM23/AM24*10+AI23/AI24*1++IF(AQ23=0,ROW(),AQ23)/2000000</f>
-        <v>60000005.200749181</v>
+        <v>37500002.433441482</v>
       </c>
       <c r="AQ23" s="126">
         <f>VLOOKUP(AE23,db_fifarank,2,FALSE)</f>
@@ -45057,7 +45057,7 @@
       </c>
       <c r="AR23" s="125">
         <f>AP23/AP24</f>
-        <v>0.66810735802523147</v>
+        <v>0.38538248115835982</v>
       </c>
       <c r="AT23" s="126" cm="1">
         <f t="array" ref="AT23">SUMPRODUCT(($S$7:$S$78=AE23&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE23&amp;"_win")*($U$7:$U$78))</f>
@@ -45123,10 +45123,10 @@
         <f>BH23/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK23" s="174"/>
+      <c r="BK23" s="164"/>
       <c r="BL23" s="26" t="str">
         <f>AS21</f>
-        <v>2C</v>
+        <v>Morocco</v>
       </c>
       <c r="BM23" s="62"/>
       <c r="BN23" s="64"/>
@@ -45150,7 +45150,7 @@
       <c r="CC23" s="21"/>
       <c r="CD23" s="114"/>
       <c r="CE23" s="112"/>
-      <c r="CF23" s="173">
+      <c r="CF23" s="163">
         <v>101</v>
       </c>
       <c r="CG23" s="24" t="str">
@@ -45201,7 +45201,7 @@
       </c>
       <c r="K24" s="36">
         <f>L24+M24+N24</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L24" s="36">
         <f>VLOOKUP(4,AD20:AN23,3,FALSE)</f>
@@ -45213,11 +45213,11 @@
       </c>
       <c r="N24" s="36">
         <f>VLOOKUP(4,AD20:AN23,5,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O24" s="36" t="str">
         <f>VLOOKUP(4,AD20:AN23,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD20:AN23,7,FALSE)</f>
-        <v>0 - 4</v>
+        <v>2 - 8</v>
       </c>
       <c r="P24" s="37">
         <f>L24*3+M24</f>
@@ -45269,7 +45269,7 @@
       </c>
       <c r="AF24" s="123">
         <f t="shared" ref="AF24:AH24" si="14">MAX(AF20:AF23)-MIN(AF20:AF23)+1</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG24" s="123">
         <f t="shared" si="14"/>
@@ -45277,31 +45277,31 @@
       </c>
       <c r="AH24" s="123">
         <f t="shared" si="14"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI24" s="123">
         <f>MAX(AI20:AI23)+1</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AL24" s="123">
         <f>MIN(AL20:AL23)</f>
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="AM24" s="123">
         <f>MAX(AM20:AM23)+1</f>
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AN24" s="123">
         <f>MAX(AN20:AN23)+1</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AO24" s="123">
         <f>MAX(AO20:AO23)+1</f>
-        <v>9.9805825242718456</v>
+        <v>10.730582524271846</v>
       </c>
       <c r="AP24" s="123">
         <f>MAX(AP20:AP23)+1</f>
-        <v>89805933.851851463</v>
+        <v>97305934.407620698</v>
       </c>
       <c r="AT24" s="126">
         <f>MAX(AT20:AT23)-MIN(AT20:AT23)+1</f>
@@ -45371,7 +45371,7 @@
       <c r="CC24" s="21"/>
       <c r="CD24" s="114"/>
       <c r="CE24" s="115"/>
-      <c r="CF24" s="174"/>
+      <c r="CF24" s="164"/>
       <c r="CG24" s="26" t="str">
         <f>IF(CD32&gt;CD33,BZ32,IF(CD32&lt;CD33,BZ33,""))</f>
         <v/>
@@ -45618,23 +45618,23 @@
       </c>
       <c r="AH26" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE26 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI26" s="123">
         <f>SUMIF($E$7:$E$78,$AE26,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE26,$G$7:$G$78)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AJ26" s="123">
         <f>SUMIF($E$7:$E$78,$AE26,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE26,$F$7:$F$78)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AL26" s="123">
         <f>AI26-AJ26</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM26" s="123">
         <f>AL26-AL30</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AN26" s="123">
         <f>AF26*3+AG26</f>
@@ -45646,7 +45646,7 @@
       </c>
       <c r="AP26" s="123">
         <f>AO26*10000000+BI26*100+AM26/AM30*10+AI26/AI30*1++IF(AQ26=0,ROW(),AQ26)/2000000</f>
-        <v>85714295.461154029</v>
+        <v>85714295.175439745</v>
       </c>
       <c r="AQ26" s="126">
         <f>VLOOKUP(AE26,db_fifarank,2,FALSE)</f>
@@ -45658,7 +45658,7 @@
       </c>
       <c r="AS26" s="125" t="str">
         <f>IF(SUM(AF26:AH29)=12,J27,"1D")</f>
-        <v>1D</v>
+        <v>United States</v>
       </c>
       <c r="AT26" s="126" cm="1">
         <f t="array" ref="AT26">SUMPRODUCT(($S$7:$S$78=AE26&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE26&amp;"_win")*($U$7:$U$78))</f>
@@ -45724,7 +45724,7 @@
         <f>BH26/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK26" s="173">
+      <c r="BK26" s="163">
         <v>83</v>
       </c>
       <c r="BL26" s="24" t="str">
@@ -45802,7 +45802,7 @@
       </c>
       <c r="K27" s="31">
         <f>L27+M27+N27</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L27" s="31">
         <f>VLOOKUP(1,AD26:AN29,3,FALSE)</f>
@@ -45814,11 +45814,11 @@
       </c>
       <c r="N27" s="31">
         <f>VLOOKUP(1,AD26:AN29,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27" s="31" t="str">
         <f>VLOOKUP(1,AD26:AN29,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD26:AN29,7,FALSE)</f>
-        <v>6 - 1</v>
+        <v>8 - 4</v>
       </c>
       <c r="P27" s="32">
         <f>L27*3+M27</f>
@@ -45882,7 +45882,7 @@
       </c>
       <c r="AG27" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE27 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH27" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE27 &amp; "_lose")</f>
@@ -45902,19 +45902,19 @@
       </c>
       <c r="AM27" s="123">
         <f>AL27-AL30</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN27" s="123">
         <f>AF27*3+AG27</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO27" s="123">
         <f>AN27/AN30*10+BA27</f>
-        <v>4.2857142857142856</v>
+        <v>6.6946778711484587</v>
       </c>
       <c r="AP27" s="123">
         <f>AO27*10000000+BI27*100+AM27/AM30*10+AI27/AI30*1++IF(AQ27=0,ROW(),AQ27)/2000000</f>
-        <v>42857144.254720002</v>
+        <v>66946876.973674245</v>
       </c>
       <c r="AQ27" s="126">
         <f>VLOOKUP(AE27,db_fifarank,2,FALSE)</f>
@@ -45922,11 +45922,11 @@
       </c>
       <c r="AR27" s="125">
         <f>AP27/AP30</f>
-        <v>0.49999995361500732</v>
+        <v>0.78104680270193894</v>
       </c>
       <c r="AS27" s="125" t="str">
         <f>IF(SUM(AF26:AH29)=12,J28,"2D")</f>
-        <v>2D</v>
+        <v>Australia</v>
       </c>
       <c r="AT27" s="126" cm="1">
         <f t="array" ref="AT27">SUMPRODUCT(($S$7:$S$78=AE27&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE27&amp;"_win")*($U$7:$U$78))</f>
@@ -45934,7 +45934,7 @@
       </c>
       <c r="AU27" s="126" cm="1">
         <f t="array" ref="AU27">SUMPRODUCT(($S$7:$S$78=AE27&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE27&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV27" s="126" cm="1">
         <f t="array" ref="AV27">SUMPRODUCT(($E$7:$E$78=AE27)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE27)*($U$7:$U$78)*($G$7:$G$78))</f>
@@ -45954,11 +45954,11 @@
       </c>
       <c r="AZ27" s="126">
         <f>AT27/AT30*1000+AU27/AU30*100+AY27/AY30*10+AV27/AV30</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BA27" s="126">
         <f>AZ27/AZ30</f>
-        <v>0</v>
+        <v>0.98039215686274506</v>
       </c>
       <c r="BB27" s="126" cm="1">
         <f t="array" ref="BB27">SUMPRODUCT(($S$7:$S$78=AE27&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE27&amp;"_win")*($X$7:$X$78))</f>
@@ -45966,7 +45966,7 @@
       </c>
       <c r="BC27" s="126" cm="1">
         <f t="array" ref="BC27">SUMPRODUCT(($S$7:$S$78=AE27&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE27&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD27" s="126" cm="1">
         <f t="array" ref="BD27">SUMPRODUCT(($E$7:$E$78=AE27)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE27)*($X$7:$X$78)*($G$7:$G$78))</f>
@@ -45986,13 +45986,13 @@
       </c>
       <c r="BH27" s="126">
         <f>BB27/BB30*1000+BC27/BC30*100+BG27/BG30*10+BD27/BD30</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BI27" s="126">
         <f>BH27/BH30</f>
-        <v>0</v>
-      </c>
-      <c r="BK27" s="174"/>
+        <v>0.98039215686274506</v>
+      </c>
+      <c r="BK27" s="164"/>
       <c r="BL27" s="26" t="str">
         <f>AS75</f>
         <v>2L</v>
@@ -46074,7 +46074,7 @@
       </c>
       <c r="K28" s="23">
         <f>L28+M28+N28</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L28" s="23">
         <f>VLOOKUP(2,AD26:AN29,3,FALSE)</f>
@@ -46082,7 +46082,7 @@
       </c>
       <c r="M28" s="23">
         <f>VLOOKUP(2,AD26:AN29,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N28" s="23">
         <f>VLOOKUP(2,AD26:AN29,5,FALSE)</f>
@@ -46094,7 +46094,7 @@
       </c>
       <c r="P28" s="34">
         <f>L28*3+M28</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R28" s="123">
         <f>DATE(2026,6,17)+TIME(9,0,0)+gmt_delta</f>
@@ -46154,7 +46154,7 @@
       </c>
       <c r="AG28" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE28 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH28" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE28 &amp; "_lose")</f>
@@ -46174,19 +46174,19 @@
       </c>
       <c r="AM28" s="123">
         <f>AL28-AL30</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN28" s="123">
         <f>AF28*3+AG28</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO28" s="123">
         <f>AN28/AN30*10+BA28</f>
-        <v>4.2857142857142856</v>
+        <v>6.6946778711484587</v>
       </c>
       <c r="AP28" s="123">
         <f>AO28*10000000+BI28*100+AM28/AM30*10+AI28/AI30*1++IF(AQ28=0,ROW(),AQ28)/2000000</f>
-        <v>42857146.476980813</v>
+        <v>66946879.83085569</v>
       </c>
       <c r="AQ28" s="126">
         <f>VLOOKUP(AE28,db_fifarank,2,FALSE)</f>
@@ -46194,7 +46194,7 @@
       </c>
       <c r="AR28" s="125">
         <f>AP28/AP30</f>
-        <v>0.4999999795413802</v>
+        <v>0.78104683603571834</v>
       </c>
       <c r="AT28" s="126" cm="1">
         <f t="array" ref="AT28">SUMPRODUCT(($S$7:$S$78=AE28&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE28&amp;"_win")*($U$7:$U$78))</f>
@@ -46202,7 +46202,7 @@
       </c>
       <c r="AU28" s="126" cm="1">
         <f t="array" ref="AU28">SUMPRODUCT(($S$7:$S$78=AE28&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE28&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV28" s="126" cm="1">
         <f t="array" ref="AV28">SUMPRODUCT(($E$7:$E$78=AE28)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE28)*($U$7:$U$78)*($G$7:$G$78))</f>
@@ -46222,11 +46222,11 @@
       </c>
       <c r="AZ28" s="126">
         <f>AT28/AT30*1000+AU28/AU30*100+AY28/AY30*10+AV28/AV30</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BA28" s="126">
         <f>AZ28/AZ30</f>
-        <v>0</v>
+        <v>0.98039215686274506</v>
       </c>
       <c r="BB28" s="126" cm="1">
         <f t="array" ref="BB28">SUMPRODUCT(($S$7:$S$78=AE28&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE28&amp;"_win")*($X$7:$X$78))</f>
@@ -46234,7 +46234,7 @@
       </c>
       <c r="BC28" s="126" cm="1">
         <f t="array" ref="BC28">SUMPRODUCT(($S$7:$S$78=AE28&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE28&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD28" s="126" cm="1">
         <f t="array" ref="BD28">SUMPRODUCT(($E$7:$E$78=AE28)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE28)*($X$7:$X$78)*($G$7:$G$78))</f>
@@ -46254,11 +46254,11 @@
       </c>
       <c r="BH28" s="126">
         <f>BB28/BB30*1000+BC28/BC30*100+BG28/BG30*10+BD28/BD30</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BI28" s="126">
         <f>BH28/BH30</f>
-        <v>0</v>
+        <v>0.98039215686274506</v>
       </c>
       <c r="BK28" s="21"/>
       <c r="BL28" s="21"/>
@@ -46267,7 +46267,7 @@
       <c r="BO28" s="21"/>
       <c r="BP28" s="114"/>
       <c r="BQ28" s="112"/>
-      <c r="BR28" s="173">
+      <c r="BR28" s="163">
         <v>93</v>
       </c>
       <c r="BS28" s="24" t="str">
@@ -46333,7 +46333,7 @@
       </c>
       <c r="K29" s="23">
         <f>L29+M29+N29</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L29" s="23">
         <f>VLOOKUP(3,AD26:AN29,3,FALSE)</f>
@@ -46341,7 +46341,7 @@
       </c>
       <c r="M29" s="23">
         <f>VLOOKUP(3,AD26:AN29,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N29" s="23">
         <f>VLOOKUP(3,AD26:AN29,5,FALSE)</f>
@@ -46353,7 +46353,7 @@
       </c>
       <c r="P29" s="34">
         <f>L29*3+M29</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R29" s="123">
         <f>DATE(2026,6,17)+TIME(6,0,0)+gmt_delta</f>
@@ -46409,7 +46409,7 @@
       </c>
       <c r="AF29" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE29 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG29" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE29 &amp; "_draw")</f>
@@ -46421,15 +46421,15 @@
       </c>
       <c r="AI29" s="123">
         <f>SUMIF($E$7:$E$78,$AE29,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE29,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AJ29" s="123">
         <f>SUMIF($E$7:$E$78,$AE29,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE29,$F$7:$F$78)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AL29" s="123">
         <f>AI29-AJ29</f>
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="AM29" s="123">
         <f>AL29-AL30</f>
@@ -46437,15 +46437,15 @@
       </c>
       <c r="AN29" s="123">
         <f>AF29*3+AG29</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO29" s="123">
         <f>AN29/AN30*10+BA29</f>
-        <v>0</v>
+        <v>4.2857142857142856</v>
       </c>
       <c r="AP29" s="123">
         <f>AO29*10000000+BI29*100+AM29/AM30*10+AI29/AI30*1++IF(AQ29=0,ROW(),AQ29)/2000000</f>
-        <v>7.9951999999999996E-4</v>
+        <v>42857143.191275716</v>
       </c>
       <c r="AQ29" s="126">
         <f>VLOOKUP(AE29,db_fifarank,2,FALSE)</f>
@@ -46453,7 +46453,7 @@
       </c>
       <c r="AR29" s="125">
         <f>AP29/AP30</f>
-        <v>9.3277321638210582E-12</v>
+        <v>0.49999994287482513</v>
       </c>
       <c r="AT29" s="126" cm="1">
         <f t="array" ref="AT29">SUMPRODUCT(($S$7:$S$78=AE29&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE29&amp;"_win")*($U$7:$U$78))</f>
@@ -46532,7 +46532,7 @@
         <v>46205.791666666672</v>
       </c>
       <c r="BQ29" s="115"/>
-      <c r="BR29" s="174"/>
+      <c r="BR29" s="164"/>
       <c r="BS29" s="26" t="str">
         <f>IF(BP30&gt;BP31,BL30,IF(BP30&lt;BP31,BL31,""))</f>
         <v/>
@@ -46596,11 +46596,11 @@
       </c>
       <c r="K30" s="36">
         <f>L30+M30+N30</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L30" s="36">
         <f>VLOOKUP(4,AD26:AN29,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="36">
         <f>VLOOKUP(4,AD26:AN29,4,FALSE)</f>
@@ -46612,11 +46612,11 @@
       </c>
       <c r="O30" s="36" t="str">
         <f>VLOOKUP(4,AD26:AN29,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD26:AN29,7,FALSE)</f>
-        <v>0 - 3</v>
+        <v>3 - 5</v>
       </c>
       <c r="P30" s="37">
         <f>L30*3+M30</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R30" s="123">
         <f>DATE(2026,6,17)+TIME(15,0,0)+gmt_delta</f>
@@ -46664,27 +46664,27 @@
       </c>
       <c r="AF30" s="123">
         <f t="shared" ref="AF30:AH30" si="15">MAX(AF26:AF29)-MIN(AF26:AF29)+1</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG30" s="123">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH30" s="123">
         <f t="shared" si="15"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI30" s="123">
         <f>MAX(AI26:AI29)+1</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AL30" s="123">
         <f>MIN(AL26:AL29)</f>
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="AM30" s="123">
         <f>MAX(AM26:AM29)+1</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AN30" s="123">
         <f>MAX(AN26:AN29)+1</f>
@@ -46696,7 +46696,7 @@
       </c>
       <c r="AP30" s="123">
         <f>MAX(AP26:AP29)+1</f>
-        <v>85714296.461154029</v>
+        <v>85714296.175439745</v>
       </c>
       <c r="AT30" s="126">
         <f>MAX(AT26:AT29)-MIN(AT26:AT29)+1</f>
@@ -46704,7 +46704,7 @@
       </c>
       <c r="AU30" s="126">
         <f>MAX(AU26:AU29)-MIN(AU26:AU29)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV30" s="126">
         <f>MAX(AV26:AV29)-MIN(AV26:AV29)+1</f>
@@ -46720,7 +46720,7 @@
       </c>
       <c r="AZ30" s="126">
         <f>MAX(AZ26:AZ29)+1</f>
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="BB30" s="126">
         <f>MAX(BB26:BB29)-MIN(BB26:BB29)+1</f>
@@ -46728,7 +46728,7 @@
       </c>
       <c r="BC30" s="126">
         <f>MAX(BC26:BC29)-MIN(BC26:BC29)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD30" s="126">
         <f>MAX(BD26:BD29)-MIN(BD26:BD29)+1</f>
@@ -46744,9 +46744,9 @@
       </c>
       <c r="BH30" s="126">
         <f>MAX(BH26:BH29)+1</f>
-        <v>1</v>
-      </c>
-      <c r="BK30" s="173">
+        <v>51</v>
+      </c>
+      <c r="BK30" s="163">
         <v>84</v>
       </c>
       <c r="BL30" s="24" t="str">
@@ -46827,27 +46827,27 @@
       </c>
       <c r="U31" s="123">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31" s="123">
         <f>U31*F31</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W31" s="123">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X31" s="123">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y31" s="123">
         <f>X31*F31</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z31" s="123">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA31" s="123">
         <f t="shared" si="5"/>
@@ -46857,7 +46857,7 @@
         <f>IF(OR(F31="",G31=""),"",IF(F31&gt;G31,1,IF(F31&lt;G31,-1,0)))</f>
         <v>0</v>
       </c>
-      <c r="BK31" s="174"/>
+      <c r="BK31" s="164"/>
       <c r="BL31" s="26" t="str">
         <f>AS63</f>
         <v>2J</v>
@@ -47013,23 +47013,23 @@
       </c>
       <c r="AH32" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE32 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI32" s="123">
         <f>SUMIF($E$7:$E$78,$AE32,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE32,$G$7:$G$78)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ32" s="123">
         <f>SUMIF($E$7:$E$78,$AE32,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE32,$F$7:$F$78)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AL32" s="123">
         <f>AI32-AJ32</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM32" s="123">
         <f>AL32-AL36</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AN32" s="123">
         <f>AF32*3+AG32</f>
@@ -47037,11 +47037,11 @@
       </c>
       <c r="AO32" s="123">
         <f>AN32/AN36*10+BA32</f>
-        <v>8.5714285714285712</v>
+        <v>9.5694613583138164</v>
       </c>
       <c r="AP32" s="123">
         <f>AO32*10000000+BI32*100+AM32/AM36*10+AI32/AI36*1++IF(AQ32=0,ROW(),AQ32)/2000000</f>
-        <v>85714295.900865197</v>
+        <v>95694623.826427594</v>
       </c>
       <c r="AQ32" s="126">
         <f>VLOOKUP(AE32,db_fifarank,2,FALSE)</f>
@@ -47049,15 +47049,15 @@
       </c>
       <c r="AR32" s="125">
         <f>AP32/AP36</f>
-        <v>0.99999998833333481</v>
+        <v>0.99999998955009228</v>
       </c>
       <c r="AS32" s="125" t="str">
         <f>IF(SUM(AF32:AH35)=12,J33,"1E")</f>
-        <v>1E</v>
+        <v>Germany</v>
       </c>
       <c r="AT32" s="126" cm="1">
         <f t="array" ref="AT32">SUMPRODUCT(($S$7:$S$78=AE32&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE32&amp;"_win")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU32" s="126" cm="1">
         <f t="array" ref="AU32">SUMPRODUCT(($S$7:$S$78=AE32&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE32&amp;"_draw")*($U$7:$U$78))</f>
@@ -47065,27 +47065,27 @@
       </c>
       <c r="AV32" s="126" cm="1">
         <f t="array" ref="AV32">SUMPRODUCT(($E$7:$E$78=AE32)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE32)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW32" s="126" cm="1">
         <f t="array" ref="AW32">SUMPRODUCT(($E$7:$E$78=AE32)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE32)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX32" s="126">
         <f>AV32-AW32</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY32" s="126">
         <f>AX32-MIN(AX32:AX35)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ32" s="126">
         <f>AT32/AT36*1000+AU32/AU36*100+AY32/AY36*10+AV32/AV36</f>
-        <v>0</v>
+        <v>507.33333333333337</v>
       </c>
       <c r="BA32" s="126">
         <f>AZ32/AZ36</f>
-        <v>0</v>
+        <v>0.99803278688524588</v>
       </c>
       <c r="BB32" s="126" cm="1">
         <f t="array" ref="BB32">SUMPRODUCT(($S$7:$S$78=AE32&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE32&amp;"_win")*($X$7:$X$78))</f>
@@ -47133,7 +47133,7 @@
       <c r="BV32" s="21"/>
       <c r="BW32" s="114"/>
       <c r="BX32" s="112"/>
-      <c r="BY32" s="173">
+      <c r="BY32" s="163">
         <v>98</v>
       </c>
       <c r="BZ32" s="24" t="str">
@@ -47187,7 +47187,7 @@
       </c>
       <c r="K33" s="31">
         <f>L33+M33+N33</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L33" s="31">
         <f>VLOOKUP(1,AD32:AN35,3,FALSE)</f>
@@ -47199,11 +47199,11 @@
       </c>
       <c r="N33" s="31">
         <f>VLOOKUP(1,AD32:AN35,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O33" s="31" t="str">
         <f>VLOOKUP(1,AD32:AN35,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD32:AN35,7,FALSE)</f>
-        <v>9 - 2</v>
+        <v>10 - 4</v>
       </c>
       <c r="P33" s="32">
         <f>L33*3+M33</f>
@@ -47271,7 +47271,7 @@
       </c>
       <c r="AH33" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE33 &amp; "_lose")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI33" s="123">
         <f>SUMIF($E$7:$E$78,$AE33,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE33,$G$7:$G$78)</f>
@@ -47279,11 +47279,11 @@
       </c>
       <c r="AJ33" s="123">
         <f>SUMIF($E$7:$E$78,$AE33,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE33,$F$7:$F$78)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AL33" s="123">
         <f>AI33-AJ33</f>
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="AM33" s="123">
         <f>AL33-AL36</f>
@@ -47295,11 +47295,11 @@
       </c>
       <c r="AO33" s="123">
         <f>AN33/AN36*10+BA33</f>
-        <v>2.4089635854341735</v>
+        <v>1.4351288056206086</v>
       </c>
       <c r="AP33" s="123">
         <f>AO33*10000000+BI33*100+AM33/AM36*10+AI33/AI36*1++IF(AQ33=0,ROW(),AQ33)/2000000</f>
-        <v>24089733.994204748</v>
+        <v>14351288.147762503</v>
       </c>
       <c r="AQ33" s="126">
         <f>VLOOKUP(AE33,db_fifarank,2,FALSE)</f>
@@ -47307,11 +47307,11 @@
       </c>
       <c r="AR33" s="125">
         <f>AP33/AP36</f>
-        <v>0.28104685991960332</v>
+        <v>0.14996963699678112</v>
       </c>
       <c r="AS33" s="125" t="str">
         <f>IF(SUM(AF32:AH35)=12,J34,"2E")</f>
-        <v>2E</v>
+        <v>Ivory Coast</v>
       </c>
       <c r="AT33" s="126" cm="1">
         <f t="array" ref="AT33">SUMPRODUCT(($S$7:$S$78=AE33&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE33&amp;"_win")*($U$7:$U$78))</f>
@@ -47319,7 +47319,7 @@
       </c>
       <c r="AU33" s="126" cm="1">
         <f t="array" ref="AU33">SUMPRODUCT(($S$7:$S$78=AE33&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE33&amp;"_draw")*($U$7:$U$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV33" s="126" cm="1">
         <f t="array" ref="AV33">SUMPRODUCT(($E$7:$E$78=AE33)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE33)*($U$7:$U$78)*($G$7:$G$78))</f>
@@ -47335,15 +47335,15 @@
       </c>
       <c r="AY33" s="126">
         <f>AX33-MIN(AX32:AX35)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ33" s="126">
         <f>AT33/AT36*1000+AU33/AU36*100+AY33/AY36*10+AV33/AV36</f>
-        <v>50</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="BA33" s="126">
         <f>AZ33/AZ36</f>
-        <v>0.98039215686274506</v>
+        <v>6.557377049180327E-3</v>
       </c>
       <c r="BB33" s="126" cm="1">
         <f t="array" ref="BB33">SUMPRODUCT(($S$7:$S$78=AE33&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE33&amp;"_win")*($X$7:$X$78))</f>
@@ -47351,7 +47351,7 @@
       </c>
       <c r="BC33" s="126" cm="1">
         <f t="array" ref="BC33">SUMPRODUCT(($S$7:$S$78=AE33&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE33&amp;"_draw")*($X$7:$X$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD33" s="126" cm="1">
         <f t="array" ref="BD33">SUMPRODUCT(($E$7:$E$78=AE33)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE33)*($X$7:$X$78)*($G$7:$G$78))</f>
@@ -47371,11 +47371,11 @@
       </c>
       <c r="BH33" s="126">
         <f>BB33/BB36*1000+BC33/BC36*100+BG33/BG36*10+BD33/BD36</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BI33" s="126">
         <f>BH33/BH36</f>
-        <v>0.98039215686274506</v>
+        <v>0</v>
       </c>
       <c r="BK33" s="21" t="str" cm="1">
         <f t="array" ref="BK33">INDEX(T,24+MONTH(BP33),lang) &amp; " " &amp; DAY(BP33) &amp; ", " &amp; YEAR(BP33) &amp; "   " &amp; (IF(HOUR(BP33)&lt;10,0,"")&amp;HOUR(BP33)) &amp; ":" &amp;  (IF(MINUTE(BP33)&lt;10,0,"")&amp;MINUTE(BP33))</f>
@@ -47397,7 +47397,7 @@
       <c r="BV33" s="21"/>
       <c r="BW33" s="114"/>
       <c r="BX33" s="115"/>
-      <c r="BY33" s="174"/>
+      <c r="BY33" s="164"/>
       <c r="BZ33" s="26" t="str">
         <f>IF(BW36&gt;BW37,BS36,IF(BW36&lt;BW37,BS37,""))</f>
         <v/>
@@ -47412,14 +47412,14 @@
       <c r="CE33" s="112"/>
       <c r="CK33" s="114"/>
       <c r="CL33" s="112"/>
-      <c r="CM33" s="176" t="str" cm="1">
+      <c r="CM33" s="165" t="str" cm="1">
         <f t="array" ref="CM33">INDEX(T,8,lang)</f>
         <v>Final</v>
       </c>
-      <c r="CN33" s="177"/>
-      <c r="CO33" s="177"/>
-      <c r="CP33" s="177"/>
-      <c r="CQ33" s="178"/>
+      <c r="CN33" s="166"/>
+      <c r="CO33" s="166"/>
+      <c r="CP33" s="166"/>
+      <c r="CQ33" s="167"/>
     </row>
     <row r="34" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A34" s="16">
@@ -47457,11 +47457,11 @@
       </c>
       <c r="K34" s="23">
         <f>L34+M34+N34</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L34" s="23">
         <f>VLOOKUP(2,AD32:AN35,3,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M34" s="23">
         <f>VLOOKUP(2,AD32:AN35,4,FALSE)</f>
@@ -47473,11 +47473,11 @@
       </c>
       <c r="O34" s="23" t="str">
         <f>VLOOKUP(2,AD32:AN35,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD32:AN35,7,FALSE)</f>
-        <v>2 - 2</v>
+        <v>4 - 2</v>
       </c>
       <c r="P34" s="34">
         <f>L34*3+M34</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R34" s="123">
         <f>DATE(2026,6,18)+TIME(14,0,0)+gmt_delta</f>
@@ -47533,7 +47533,7 @@
       </c>
       <c r="AF34" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE34 &amp; "_win")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG34" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE34 &amp; "_draw")</f>
@@ -47545,7 +47545,7 @@
       </c>
       <c r="AI34" s="123">
         <f>SUMIF($E$7:$E$78,$AE34,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE34,$G$7:$G$78)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AJ34" s="123">
         <f>SUMIF($E$7:$E$78,$AE34,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE34,$F$7:$F$78)</f>
@@ -47553,23 +47553,23 @@
       </c>
       <c r="AL34" s="123">
         <f>AI34-AJ34</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM34" s="123">
         <f>AL34-AL36</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AN34" s="123">
         <f>AF34*3+AG34</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AO34" s="123">
         <f>AN34/AN36*10+BA34</f>
-        <v>4.2857142857142856</v>
+        <v>8.5720843091334888</v>
       </c>
       <c r="AP34" s="123">
         <f>AO34*10000000+BI34*100+AM34/AM36*10+AI34/AI36*1++IF(AQ34=0,ROW(),AQ34)/2000000</f>
-        <v>42857147.343623638</v>
+        <v>85720850.122404411</v>
       </c>
       <c r="AQ34" s="126">
         <f>VLOOKUP(AE34,db_fifarank,2,FALSE)</f>
@@ -47577,7 +47577,7 @@
       </c>
       <c r="AR34" s="125">
         <f>AP34/AP36</f>
-        <v>0.49999998708723048</v>
+        <v>0.89577497459116673</v>
       </c>
       <c r="AT34" s="126" cm="1">
         <f t="array" ref="AT34">SUMPRODUCT(($S$7:$S$78=AE34&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE34&amp;"_win")*($U$7:$U$78))</f>
@@ -47589,15 +47589,15 @@
       </c>
       <c r="AV34" s="126" cm="1">
         <f t="array" ref="AV34">SUMPRODUCT(($E$7:$E$78=AE34)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE34)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW34" s="126" cm="1">
         <f t="array" ref="AW34">SUMPRODUCT(($E$7:$E$78=AE34)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE34)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX34" s="126">
         <f>AV34-AW34</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AY34" s="126">
         <f>AX34-MIN(AX32:AX35)</f>
@@ -47605,11 +47605,11 @@
       </c>
       <c r="AZ34" s="126">
         <f>AT34/AT36*1000+AU34/AU36*100+AY34/AY36*10+AV34/AV36</f>
-        <v>0</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="BA34" s="126">
         <f>AZ34/AZ36</f>
-        <v>0</v>
+        <v>6.5573770491803268E-4</v>
       </c>
       <c r="BB34" s="126" cm="1">
         <f t="array" ref="BB34">SUMPRODUCT(($S$7:$S$78=AE34&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE34&amp;"_win")*($X$7:$X$78))</f>
@@ -47643,12 +47643,12 @@
         <f>BH34/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK34" s="173">
+      <c r="BK34" s="163">
         <v>81</v>
       </c>
       <c r="BL34" s="24" t="str">
         <f>AS26</f>
-        <v>1D</v>
+        <v>United States</v>
       </c>
       <c r="BM34" s="61"/>
       <c r="BN34" s="63"/>
@@ -47674,11 +47674,11 @@
       <c r="CE34" s="112"/>
       <c r="CK34" s="114"/>
       <c r="CL34" s="112"/>
-      <c r="CM34" s="179"/>
-      <c r="CN34" s="180"/>
-      <c r="CO34" s="180"/>
-      <c r="CP34" s="180"/>
-      <c r="CQ34" s="181"/>
+      <c r="CM34" s="168"/>
+      <c r="CN34" s="169"/>
+      <c r="CO34" s="169"/>
+      <c r="CP34" s="169"/>
+      <c r="CQ34" s="170"/>
     </row>
     <row r="35" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A35" s="16">
@@ -47716,11 +47716,11 @@
       </c>
       <c r="K35" s="23">
         <f>L35+M35+N35</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L35" s="23">
         <f>VLOOKUP(3,AD32:AN35,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" s="23">
         <f>VLOOKUP(3,AD32:AN35,4,FALSE)</f>
@@ -47732,11 +47732,11 @@
       </c>
       <c r="O35" s="23" t="str">
         <f>VLOOKUP(3,AD32:AN35,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD32:AN35,7,FALSE)</f>
-        <v>0 - 1</v>
+        <v>2 - 2</v>
       </c>
       <c r="P35" s="34">
         <f>L35*3+M35</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R35" s="123">
         <f>DATE(2026,6,19)+TIME(13,30,0)+gmt_delta</f>
@@ -47792,7 +47792,7 @@
       </c>
       <c r="AF35" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE35 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG35" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE35 &amp; "_draw")</f>
@@ -47804,31 +47804,31 @@
       </c>
       <c r="AI35" s="123">
         <f>SUMIF($E$7:$E$78,$AE35,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE35,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ35" s="123">
         <f>SUMIF($E$7:$E$78,$AE35,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE35,$F$7:$F$78)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL35" s="123">
         <f>AI35-AJ35</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AM35" s="123">
         <f>AL35-AL36</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AN35" s="123">
         <f>AF35*3+AG35</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AO35" s="123">
         <f>AN35/AN36*10+BA35</f>
-        <v>2.4089635854341735</v>
+        <v>5.7208430913348938</v>
       </c>
       <c r="AP35" s="123">
         <f>AO35*10000000+BI35*100+AM35/AM36*10+AI35/AI36*1++IF(AQ35=0,ROW(),AQ35)/2000000</f>
-        <v>24089737.465783384</v>
+        <v>57208436.429297842</v>
       </c>
       <c r="AQ35" s="126">
         <f>VLOOKUP(AE35,db_fifarank,2,FALSE)</f>
@@ -47836,7 +47836,7 @@
       </c>
       <c r="AR35" s="125">
         <f>AP35/AP36</f>
-        <v>0.28104690042134878</v>
+        <v>0.59782288224718372</v>
       </c>
       <c r="AT35" s="126" cm="1">
         <f t="array" ref="AT35">SUMPRODUCT(($S$7:$S$78=AE35&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE35&amp;"_win")*($U$7:$U$78))</f>
@@ -47844,7 +47844,7 @@
       </c>
       <c r="AU35" s="126" cm="1">
         <f t="array" ref="AU35">SUMPRODUCT(($S$7:$S$78=AE35&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE35&amp;"_draw")*($U$7:$U$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV35" s="126" cm="1">
         <f t="array" ref="AV35">SUMPRODUCT(($E$7:$E$78=AE35)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE35)*($U$7:$U$78)*($G$7:$G$78))</f>
@@ -47860,15 +47860,15 @@
       </c>
       <c r="AY35" s="126">
         <f>AX35-MIN(AX32:AX35)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ35" s="126">
         <f>AT35/AT36*1000+AU35/AU36*100+AY35/AY36*10+AV35/AV36</f>
-        <v>50</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="BA35" s="126">
         <f>AZ35/AZ36</f>
-        <v>0.98039215686274506</v>
+        <v>6.557377049180327E-3</v>
       </c>
       <c r="BB35" s="126" cm="1">
         <f t="array" ref="BB35">SUMPRODUCT(($S$7:$S$78=AE35&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE35&amp;"_win")*($X$7:$X$78))</f>
@@ -47876,7 +47876,7 @@
       </c>
       <c r="BC35" s="126" cm="1">
         <f t="array" ref="BC35">SUMPRODUCT(($S$7:$S$78=AE35&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE35&amp;"_draw")*($X$7:$X$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD35" s="126" cm="1">
         <f t="array" ref="BD35">SUMPRODUCT(($E$7:$E$78=AE35)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE35)*($X$7:$X$78)*($G$7:$G$78))</f>
@@ -47896,13 +47896,13 @@
       </c>
       <c r="BH35" s="126">
         <f>BB35/BB36*1000+BC35/BC36*100+BG35/BG36*10+BD35/BD36</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BI35" s="126">
         <f>BH35/BH36</f>
-        <v>0.98039215686274506</v>
-      </c>
-      <c r="BK35" s="174"/>
+        <v>0</v>
+      </c>
+      <c r="BK35" s="164"/>
       <c r="BL35" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!F3,AK80:AS91,9,FALSE),"3rd Group B/E/F/I/J")</f>
         <v>3rd Group B/E/F/I/J</v>
@@ -47974,7 +47974,7 @@
       </c>
       <c r="K36" s="36">
         <f>L36+M36+N36</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L36" s="36">
         <f>VLOOKUP(4,AD32:AN35,3,FALSE)</f>
@@ -47986,11 +47986,11 @@
       </c>
       <c r="N36" s="36">
         <f>VLOOKUP(4,AD32:AN35,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O36" s="36" t="str">
         <f>VLOOKUP(4,AD32:AN35,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD32:AN35,7,FALSE)</f>
-        <v>1 - 7</v>
+        <v>1 - 9</v>
       </c>
       <c r="P36" s="37">
         <f>L36*3+M36</f>
@@ -48054,15 +48054,15 @@
       </c>
       <c r="AI36" s="123">
         <f>MAX(AI32:AI35)+1</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL36" s="123">
         <f>MIN(AL32:AL35)</f>
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="AM36" s="123">
         <f>MAX(AM32:AM35)+1</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AN36" s="123">
         <f>MAX(AN32:AN35)+1</f>
@@ -48070,35 +48070,35 @@
       </c>
       <c r="AO36" s="123">
         <f>MAX(AO32:AO35)+1</f>
-        <v>9.5714285714285712</v>
+        <v>10.569461358313816</v>
       </c>
       <c r="AP36" s="123">
         <f>MAX(AP32:AP35)+1</f>
-        <v>85714296.900865197</v>
+        <v>95694624.826427594</v>
       </c>
       <c r="AT36" s="126">
         <f>MAX(AT32:AT35)-MIN(AT32:AT35)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU36" s="126">
         <f>MAX(AU32:AU35)-MIN(AU32:AU35)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV36" s="126">
         <f>MAX(AV32:AV35)-MIN(AV32:AV35)+1</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW36" s="126">
         <f>MAX(AW32:AW35)-MIN(AW32:AW35)+1</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AY36" s="126">
         <f>MAX(AY32:AY35)-MIN(AY32:AY35)+1</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AZ36" s="126">
         <f>MAX(AZ32:AZ35)+1</f>
-        <v>51</v>
+        <v>508.33333333333337</v>
       </c>
       <c r="BB36" s="126">
         <f>MAX(BB32:BB35)-MIN(BB32:BB35)+1</f>
@@ -48106,7 +48106,7 @@
       </c>
       <c r="BC36" s="126">
         <f>MAX(BC32:BC35)-MIN(BC32:BC35)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BD36" s="126">
         <f>MAX(BD32:BD35)-MIN(BD32:BD35)+1</f>
@@ -48122,7 +48122,7 @@
       </c>
       <c r="BH36" s="126">
         <f>MAX(BH32:BH35)+1</f>
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="BK36" s="21"/>
       <c r="BL36" s="21"/>
@@ -48131,7 +48131,7 @@
       <c r="BO36" s="21"/>
       <c r="BP36" s="114"/>
       <c r="BQ36" s="112"/>
-      <c r="BR36" s="173">
+      <c r="BR36" s="163">
         <v>94</v>
       </c>
       <c r="BS36" s="24" t="str">
@@ -48255,7 +48255,7 @@
         <v>46204.833333333336</v>
       </c>
       <c r="BQ37" s="115"/>
-      <c r="BR37" s="174"/>
+      <c r="BR37" s="164"/>
       <c r="BS37" s="26" t="str">
         <f>IF(BP38&gt;BP39,BL38,IF(BP38&lt;BP39,BL39,""))</f>
         <v/>
@@ -48282,7 +48282,7 @@
       <c r="CJ37" s="21"/>
       <c r="CK37" s="114"/>
       <c r="CL37" s="112"/>
-      <c r="CM37" s="173">
+      <c r="CM37" s="163">
         <v>104</v>
       </c>
       <c r="CN37" s="24" t="str">
@@ -48409,7 +48409,7 @@
       </c>
       <c r="AF38" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE38 &amp; "_win")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG38" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE38 &amp; "_draw")</f>
@@ -48421,31 +48421,31 @@
       </c>
       <c r="AI38" s="123">
         <f>SUMIF($E$7:$E$78,$AE38,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE38,$G$7:$G$78)</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AJ38" s="123">
         <f>SUMIF($E$7:$E$78,$AE38,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE38,$F$7:$F$78)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL38" s="123">
         <f>AI38-AJ38</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AM38" s="123">
         <f>AL38-AL42</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AN38" s="123">
         <f>AF38*3+AG38</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AO38" s="123">
         <f>AN38/AN42*10+BA38</f>
-        <v>8.9806451612903224</v>
+        <v>8.75</v>
       </c>
       <c r="AP38" s="123">
         <f>AO38*10000000+BI38*100+AM38/AM42*10+AI38/AI42*1++IF(AQ38=0,ROW(),AQ38)/2000000</f>
-        <v>89806559.784067512</v>
+        <v>87500010.321734548</v>
       </c>
       <c r="AQ38" s="126">
         <f>VLOOKUP(AE38,db_fifarank,2,FALSE)</f>
@@ -48453,11 +48453,11 @@
       </c>
       <c r="AR38" s="125">
         <f>AP38/AP42</f>
-        <v>0.99999998886495611</v>
+        <v>0.99999998857143002</v>
       </c>
       <c r="AS38" s="125" t="str">
         <f>IF(SUM(AF38:AH41)=12,J39,"1F")</f>
-        <v>1F</v>
+        <v>Netherlands</v>
       </c>
       <c r="AT38" s="126" cm="1">
         <f t="array" ref="AT38">SUMPRODUCT(($S$7:$S$78=AE38&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE38&amp;"_win")*($U$7:$U$78))</f>
@@ -48465,15 +48465,15 @@
       </c>
       <c r="AU38" s="126" cm="1">
         <f t="array" ref="AU38">SUMPRODUCT(($S$7:$S$78=AE38&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE38&amp;"_draw")*($U$7:$U$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV38" s="126" cm="1">
         <f t="array" ref="AV38">SUMPRODUCT(($E$7:$E$78=AE38)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE38)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW38" s="126" cm="1">
         <f t="array" ref="AW38">SUMPRODUCT(($E$7:$E$78=AE38)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE38)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX38" s="126">
         <f>AV38-AW38</f>
@@ -48485,11 +48485,11 @@
       </c>
       <c r="AZ38" s="126">
         <f>AT38/AT42*1000+AU38/AU42*100+AY38/AY42*10+AV38/AV42</f>
-        <v>50.666666666666664</v>
+        <v>0</v>
       </c>
       <c r="BA38" s="126">
         <f>AZ38/AZ42</f>
-        <v>0.98064516129032253</v>
+        <v>0</v>
       </c>
       <c r="BB38" s="126" cm="1">
         <f t="array" ref="BB38">SUMPRODUCT(($S$7:$S$78=AE38&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE38&amp;"_win")*($X$7:$X$78))</f>
@@ -48497,15 +48497,15 @@
       </c>
       <c r="BC38" s="126" cm="1">
         <f t="array" ref="BC38">SUMPRODUCT(($S$7:$S$78=AE38&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE38&amp;"_draw")*($X$7:$X$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD38" s="126" cm="1">
         <f t="array" ref="BD38">SUMPRODUCT(($E$7:$E$78=AE38)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE38)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BE38" s="126" cm="1">
         <f t="array" ref="BE38">SUMPRODUCT(($E$7:$E$78=AE38)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE38)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF38" s="126">
         <f>BD38-BE38</f>
@@ -48517,13 +48517,13 @@
       </c>
       <c r="BH38" s="126">
         <f>BB38/BB42*1000+BC38/BC42*100+BG38/BG42*10+BD38/BD42</f>
-        <v>50.666666666666664</v>
+        <v>0</v>
       </c>
       <c r="BI38" s="126">
         <f>BH38/BH42</f>
-        <v>0.98064516129032253</v>
-      </c>
-      <c r="BK38" s="173">
+        <v>0</v>
+      </c>
+      <c r="BK38" s="163">
         <v>82</v>
       </c>
       <c r="BL38" s="24" t="str">
@@ -48553,7 +48553,7 @@
       <c r="CI38" s="21"/>
       <c r="CJ38" s="21"/>
       <c r="CL38" s="115"/>
-      <c r="CM38" s="174"/>
+      <c r="CM38" s="164"/>
       <c r="CN38" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG55,IF(CK55&lt;CK56,CG56,""))</f>
         <v/>
@@ -48602,11 +48602,11 @@
       </c>
       <c r="K39" s="31">
         <f>L39+M39+N39</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L39" s="31">
         <f>VLOOKUP(1,AD38:AN41,3,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M39" s="31">
         <f>VLOOKUP(1,AD38:AN41,4,FALSE)</f>
@@ -48618,11 +48618,11 @@
       </c>
       <c r="O39" s="31" t="str">
         <f>VLOOKUP(1,AD38:AN41,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD38:AN41,7,FALSE)</f>
-        <v>7 - 3</v>
+        <v>10 - 4</v>
       </c>
       <c r="P39" s="32">
         <f>L39*3+M39</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R39" s="123">
         <f>DATE(2026,6,20)+TIME(9,0,0)+gmt_delta</f>
@@ -48638,15 +48638,15 @@
       </c>
       <c r="U39" s="123">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V39" s="123">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W39" s="123">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X39" s="123">
         <f t="shared" si="9"/>
@@ -48682,7 +48682,7 @@
       </c>
       <c r="AG39" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE39 &amp; "_draw")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH39" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE39 &amp; "_lose")</f>
@@ -48690,11 +48690,11 @@
       </c>
       <c r="AI39" s="123">
         <f>SUMIF($E$7:$E$78,$AE39,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE39,$G$7:$G$78)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ39" s="123">
         <f>SUMIF($E$7:$E$78,$AE39,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE39,$F$7:$F$78)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL39" s="123">
         <f>AI39-AJ39</f>
@@ -48702,19 +48702,19 @@
       </c>
       <c r="AM39" s="123">
         <f>AL39-AL42</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AN39" s="123">
         <f>AF39*3+AG39</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO39" s="123">
         <f>AN39/AN42*10+BA39</f>
-        <v>8.9806451612903224</v>
+        <v>6.25</v>
       </c>
       <c r="AP39" s="123">
         <f>AO39*10000000+BI39*100+AM39/AM42*10+AI39/AI42*1++IF(AQ39=0,ROW(),AQ39)/2000000</f>
-        <v>89806559.6590188</v>
+        <v>62500008.87248797</v>
       </c>
       <c r="AQ39" s="126">
         <f>VLOOKUP(AE39,db_fifarank,2,FALSE)</f>
@@ -48722,11 +48722,11 @@
       </c>
       <c r="AR39" s="125">
         <f>AP39/AP42</f>
-        <v>0.99999998747253316</v>
+        <v>0.71428572326325279</v>
       </c>
       <c r="AS39" s="125" t="str">
         <f>IF(SUM(AF38:AH41)=12,J40,"2F")</f>
-        <v>2F</v>
+        <v>Japan</v>
       </c>
       <c r="AT39" s="126" cm="1">
         <f t="array" ref="AT39">SUMPRODUCT(($S$7:$S$78=AE39&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE39&amp;"_win")*($U$7:$U$78))</f>
@@ -48734,15 +48734,15 @@
       </c>
       <c r="AU39" s="126" cm="1">
         <f t="array" ref="AU39">SUMPRODUCT(($S$7:$S$78=AE39&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE39&amp;"_draw")*($U$7:$U$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV39" s="126" cm="1">
         <f t="array" ref="AV39">SUMPRODUCT(($E$7:$E$78=AE39)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE39)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW39" s="126" cm="1">
         <f t="array" ref="AW39">SUMPRODUCT(($E$7:$E$78=AE39)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE39)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX39" s="126">
         <f>AV39-AW39</f>
@@ -48754,11 +48754,11 @@
       </c>
       <c r="AZ39" s="126">
         <f>AT39/AT42*1000+AU39/AU42*100+AY39/AY42*10+AV39/AV42</f>
-        <v>50.666666666666664</v>
+        <v>0</v>
       </c>
       <c r="BA39" s="126">
         <f>AZ39/AZ42</f>
-        <v>0.98064516129032253</v>
+        <v>0</v>
       </c>
       <c r="BB39" s="126" cm="1">
         <f t="array" ref="BB39">SUMPRODUCT(($S$7:$S$78=AE39&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE39&amp;"_win")*($X$7:$X$78))</f>
@@ -48766,15 +48766,15 @@
       </c>
       <c r="BC39" s="126" cm="1">
         <f t="array" ref="BC39">SUMPRODUCT(($S$7:$S$78=AE39&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE39&amp;"_draw")*($X$7:$X$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD39" s="126" cm="1">
         <f t="array" ref="BD39">SUMPRODUCT(($E$7:$E$78=AE39)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE39)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BE39" s="126" cm="1">
         <f t="array" ref="BE39">SUMPRODUCT(($E$7:$E$78=AE39)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE39)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF39" s="126">
         <f>BD39-BE39</f>
@@ -48786,13 +48786,13 @@
       </c>
       <c r="BH39" s="126">
         <f>BB39/BB42*1000+BC39/BC42*100+BG39/BG42*10+BD39/BD42</f>
-        <v>50.666666666666664</v>
+        <v>0</v>
       </c>
       <c r="BI39" s="126">
         <f>BH39/BH42</f>
-        <v>0.98064516129032253</v>
-      </c>
-      <c r="BK39" s="174"/>
+        <v>0</v>
+      </c>
+      <c r="BK39" s="164"/>
       <c r="BL39" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!H3,AK80:AS91,9,FALSE),"3rd Group A/E/H/I/J")</f>
         <v>3rd Group A/E/H/I/J</v>
@@ -48861,7 +48861,7 @@
       </c>
       <c r="K40" s="23">
         <f>L40+M40+N40</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L40" s="23">
         <f>VLOOKUP(2,AD38:AN41,3,FALSE)</f>
@@ -48869,7 +48869,7 @@
       </c>
       <c r="M40" s="23">
         <f>VLOOKUP(2,AD38:AN41,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N40" s="23">
         <f>VLOOKUP(2,AD38:AN41,5,FALSE)</f>
@@ -48877,11 +48877,11 @@
       </c>
       <c r="O40" s="23" t="str">
         <f>VLOOKUP(2,AD38:AN41,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD38:AN41,7,FALSE)</f>
-        <v>6 - 2</v>
+        <v>7 - 3</v>
       </c>
       <c r="P40" s="34">
         <f>L40*3+M40</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R40" s="123">
         <f>DATE(2026,6,20)+TIME(13,0,0)+gmt_delta</f>
@@ -48897,7 +48897,7 @@
       </c>
       <c r="U40" s="123">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V40" s="123">
         <f t="shared" si="3"/>
@@ -48909,7 +48909,7 @@
       </c>
       <c r="X40" s="123">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y40" s="123">
         <f t="shared" si="10"/>
@@ -48941,7 +48941,7 @@
       </c>
       <c r="AG40" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE40 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH40" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE40 &amp; "_lose")</f>
@@ -48949,11 +48949,11 @@
       </c>
       <c r="AI40" s="123">
         <f>SUMIF($E$7:$E$78,$AE40,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE40,$G$7:$G$78)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ40" s="123">
         <f>SUMIF($E$7:$E$78,$AE40,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE40,$F$7:$F$78)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL40" s="123">
         <f>AI40-AJ40</f>
@@ -48961,19 +48961,19 @@
       </c>
       <c r="AM40" s="123">
         <f>AL40-AL42</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AN40" s="123">
         <f>AF40*3+AG40</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO40" s="123">
         <f>AN40/AN42*10+BA40</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP40" s="123">
         <f>AO40*10000000+BI40*100+AM40/AM42*10+AI40/AI42*1++IF(AQ40=0,ROW(),AQ40)/2000000</f>
-        <v>60000006.904603533</v>
+        <v>50000006.519473955</v>
       </c>
       <c r="AQ40" s="126">
         <f>VLOOKUP(AE40,db_fifarank,2,FALSE)</f>
@@ -48981,7 +48981,7 @@
       </c>
       <c r="AR40" s="125">
         <f>AP40/AP42</f>
-        <v>0.66810271299519663</v>
+        <v>0.57142857199898689</v>
       </c>
       <c r="AT40" s="126" cm="1">
         <f t="array" ref="AT40">SUMPRODUCT(($S$7:$S$78=AE40&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE40&amp;"_win")*($U$7:$U$78))</f>
@@ -49086,7 +49086,7 @@
       </c>
       <c r="K41" s="23">
         <f>L41+M41+N41</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L41" s="23">
         <f>VLOOKUP(3,AD38:AN41,3,FALSE)</f>
@@ -49094,7 +49094,7 @@
       </c>
       <c r="M41" s="23">
         <f>VLOOKUP(3,AD38:AN41,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N41" s="23">
         <f>VLOOKUP(3,AD38:AN41,5,FALSE)</f>
@@ -49102,11 +49102,11 @@
       </c>
       <c r="O41" s="23" t="str">
         <f>VLOOKUP(3,AD38:AN41,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD38:AN41,7,FALSE)</f>
-        <v>6 - 6</v>
+        <v>7 - 7</v>
       </c>
       <c r="P41" s="34">
         <f>L41*3+M41</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R41" s="123">
         <f>DATE(2026,6,20)+TIME(6,0,0)+gmt_delta</f>
@@ -49170,19 +49170,19 @@
       </c>
       <c r="AH41" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE41 &amp; "_lose")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI41" s="123">
         <f>SUMIF($E$7:$E$78,$AE41,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE41,$G$7:$G$78)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ41" s="123">
         <f>SUMIF($E$7:$E$78,$AE41,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE41,$F$7:$F$78)</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AL41" s="123">
         <f>AI41-AJ41</f>
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="AM41" s="123">
         <f>AL41-AL42</f>
@@ -49198,7 +49198,7 @@
       </c>
       <c r="AP41" s="123">
         <f>AO41*10000000+BI41*100+AM41/AM42*10+AI41/AI42*1++IF(AQ41=0,ROW(),AQ41)/2000000</f>
-        <v>0.12574152499999999</v>
+        <v>0.18255970681818182</v>
       </c>
       <c r="AQ41" s="126">
         <f>VLOOKUP(AE41,db_fifarank,2,FALSE)</f>
@@ -49206,7 +49206,7 @@
       </c>
       <c r="AR41" s="125">
         <f>AP41/AP42</f>
-        <v>1.4001374053543276E-9</v>
+        <v>2.0863963793892096E-9</v>
       </c>
       <c r="AT41" s="126" cm="1">
         <f t="array" ref="AT41">SUMPRODUCT(($S$7:$S$78=AE41&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE41&amp;"_win")*($U$7:$U$78))</f>
@@ -49330,7 +49330,7 @@
       </c>
       <c r="K42" s="36">
         <f>L42+M42+N42</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L42" s="36">
         <f>VLOOKUP(4,AD38:AN41,3,FALSE)</f>
@@ -49342,11 +49342,11 @@
       </c>
       <c r="N42" s="36">
         <f>VLOOKUP(4,AD38:AN41,5,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O42" s="36" t="str">
         <f>VLOOKUP(4,AD38:AN41,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD38:AN41,7,FALSE)</f>
-        <v>1 - 9</v>
+        <v>2 - 12</v>
       </c>
       <c r="P42" s="37">
         <f>L42*3+M42</f>
@@ -49398,39 +49398,39 @@
       </c>
       <c r="AF42" s="123">
         <f t="shared" ref="AF42:AH42" si="18">MAX(AF38:AF41)-MIN(AF38:AF41)+1</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG42" s="123">
         <f t="shared" si="18"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH42" s="123">
         <f t="shared" si="18"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI42" s="123">
         <f>MAX(AI38:AI41)+1</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AL42" s="123">
         <f>MIN(AL38:AL41)</f>
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="AM42" s="123">
         <f>MAX(AM38:AM41)+1</f>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AN42" s="123">
         <f>MAX(AN38:AN41)+1</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AO42" s="123">
         <f>MAX(AO38:AO41)+1</f>
-        <v>9.9806451612903224</v>
+        <v>9.75</v>
       </c>
       <c r="AP42" s="123">
         <f>MAX(AP38:AP41)+1</f>
-        <v>89806560.784067512</v>
+        <v>87500011.321734548</v>
       </c>
       <c r="AT42" s="126">
         <f>MAX(AT38:AT41)-MIN(AT38:AT41)+1</f>
@@ -49438,15 +49438,15 @@
       </c>
       <c r="AU42" s="126">
         <f>MAX(AU38:AU41)-MIN(AU38:AU41)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV42" s="126">
         <f>MAX(AV38:AV41)-MIN(AV38:AV41)+1</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AW42" s="126">
         <f>MAX(AW38:AW41)-MIN(AW38:AW41)+1</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY42" s="126">
         <f>MAX(AY38:AY41)-MIN(AY38:AY41)+1</f>
@@ -49454,7 +49454,7 @@
       </c>
       <c r="AZ42" s="126">
         <f>MAX(AZ38:AZ41)+1</f>
-        <v>51.666666666666664</v>
+        <v>1</v>
       </c>
       <c r="BB42" s="126">
         <f>MAX(BB38:BB41)-MIN(BB38:BB41)+1</f>
@@ -49462,15 +49462,15 @@
       </c>
       <c r="BC42" s="126">
         <f>MAX(BC38:BC41)-MIN(BC38:BC41)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BD42" s="126">
         <f>MAX(BD38:BD41)-MIN(BD38:BD41)+1</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BE42" s="126">
         <f>MAX(BE38:BE41)-MIN(BE38:BE41)+1</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BG42" s="126">
         <f>MAX(BG38:BG41)-MIN(BG38:BG41)+1</f>
@@ -49478,14 +49478,14 @@
       </c>
       <c r="BH42" s="126">
         <f>MAX(BH38:BH41)+1</f>
-        <v>51.666666666666664</v>
-      </c>
-      <c r="BK42" s="173">
+        <v>1</v>
+      </c>
+      <c r="BK42" s="163">
         <v>76</v>
       </c>
       <c r="BL42" s="24" t="str">
         <f>AS20</f>
-        <v>1C</v>
+        <v>Brazil</v>
       </c>
       <c r="BM42" s="61"/>
       <c r="BN42" s="63"/>
@@ -49577,10 +49577,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BK43" s="174"/>
+      <c r="BK43" s="164"/>
       <c r="BL43" s="26" t="str">
         <f>AS39</f>
-        <v>2F</v>
+        <v>Japan</v>
       </c>
       <c r="BM43" s="62"/>
       <c r="BN43" s="64"/>
@@ -49837,7 +49837,7 @@
       <c r="BO44" s="21"/>
       <c r="BP44" s="114"/>
       <c r="BQ44" s="112"/>
-      <c r="BR44" s="173">
+      <c r="BR44" s="163">
         <v>91</v>
       </c>
       <c r="BS44" s="24" t="str">
@@ -49852,14 +49852,14 @@
         <v/>
       </c>
       <c r="CK44" s="114"/>
-      <c r="CM44" s="176" t="str" cm="1">
+      <c r="CM44" s="165" t="str" cm="1">
         <f t="array" ref="CM44">INDEX(T,7,lang)</f>
         <v>Third-Place Play-Off</v>
       </c>
-      <c r="CN44" s="177"/>
-      <c r="CO44" s="177"/>
-      <c r="CP44" s="177"/>
-      <c r="CQ44" s="178"/>
+      <c r="CN44" s="166"/>
+      <c r="CO44" s="166"/>
+      <c r="CP44" s="166"/>
+      <c r="CQ44" s="167"/>
     </row>
     <row r="45" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="16">
@@ -50100,7 +50100,7 @@
         <v>46203.708333333336</v>
       </c>
       <c r="BQ45" s="115"/>
-      <c r="BR45" s="174"/>
+      <c r="BR45" s="164"/>
       <c r="BS45" s="26" t="str">
         <f>IF(BP46&gt;BP47,BL46,IF(BP46&lt;BP47,BL47,""))</f>
         <v/>
@@ -50113,11 +50113,11 @@
         <v/>
       </c>
       <c r="CK45" s="114"/>
-      <c r="CM45" s="179"/>
-      <c r="CN45" s="180"/>
-      <c r="CO45" s="180"/>
-      <c r="CP45" s="180"/>
-      <c r="CQ45" s="181"/>
+      <c r="CM45" s="168"/>
+      <c r="CN45" s="169"/>
+      <c r="CO45" s="169"/>
+      <c r="CP45" s="169"/>
+      <c r="CQ45" s="170"/>
     </row>
     <row r="46" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A46" s="16">
@@ -50341,12 +50341,12 @@
         <f>BH46/BH48</f>
         <v>0.98039215686274506</v>
       </c>
-      <c r="BK46" s="173">
+      <c r="BK46" s="163">
         <v>78</v>
       </c>
       <c r="BL46" s="24" t="str">
         <f>AS33</f>
-        <v>2E</v>
+        <v>Ivory Coast</v>
       </c>
       <c r="BM46" s="61"/>
       <c r="BN46" s="63"/>
@@ -50587,10 +50587,10 @@
         <f>BH47/BH48</f>
         <v>0</v>
       </c>
-      <c r="BK47" s="174"/>
+      <c r="BK47" s="164"/>
       <c r="BL47" s="26" t="str">
         <f>AS57</f>
-        <v>2I</v>
+        <v>Norway</v>
       </c>
       <c r="BM47" s="62"/>
       <c r="BN47" s="64"/>
@@ -50834,7 +50834,7 @@
       <c r="BV48" s="21"/>
       <c r="BW48" s="114"/>
       <c r="BX48" s="112"/>
-      <c r="BY48" s="173">
+      <c r="BY48" s="163">
         <v>99</v>
       </c>
       <c r="BZ48" s="24" t="str">
@@ -50850,7 +50850,7 @@
       </c>
       <c r="CK48" s="114"/>
       <c r="CL48" s="112"/>
-      <c r="CM48" s="173">
+      <c r="CM48" s="163">
         <v>103</v>
       </c>
       <c r="CN48" s="24" t="str">
@@ -50959,7 +50959,7 @@
       <c r="BV49" s="21"/>
       <c r="BW49" s="114"/>
       <c r="BX49" s="115"/>
-      <c r="BY49" s="174"/>
+      <c r="BY49" s="164"/>
       <c r="BZ49" s="26" t="str">
         <f>IF(BW52&gt;BW53,BS52,IF(BW52&lt;BW53,BS53,""))</f>
         <v/>
@@ -50973,7 +50973,7 @@
       </c>
       <c r="CK49" s="114"/>
       <c r="CL49" s="115"/>
-      <c r="CM49" s="174"/>
+      <c r="CM49" s="164"/>
       <c r="CN49" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG56,IF(CK55&lt;CK56,CG55,""))</f>
         <v/>
@@ -51212,12 +51212,12 @@
         <f>BH50/BH54</f>
         <v>0</v>
       </c>
-      <c r="BK50" s="173">
+      <c r="BK50" s="163">
         <v>79</v>
       </c>
       <c r="BL50" s="24" t="str">
         <f>AS8</f>
-        <v>1A</v>
+        <v>Mexico</v>
       </c>
       <c r="BM50" s="61"/>
       <c r="BN50" s="63"/>
@@ -51469,7 +51469,7 @@
         <f>BH51/BH54</f>
         <v>0.98064516129032253</v>
       </c>
-      <c r="BK51" s="174"/>
+      <c r="BK51" s="164"/>
       <c r="BL51" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!D3,AK80:AS91,9,FALSE),"3rd Group C/E/F/H/I")</f>
         <v>3rd Group C/E/F/H/I</v>
@@ -51733,7 +51733,7 @@
       <c r="BO52" s="21"/>
       <c r="BP52" s="114"/>
       <c r="BQ52" s="112"/>
-      <c r="BR52" s="173">
+      <c r="BR52" s="163">
         <v>92</v>
       </c>
       <c r="BS52" s="24" t="str">
@@ -51992,7 +51992,7 @@
         <v>46204.666666666672</v>
       </c>
       <c r="BQ53" s="115"/>
-      <c r="BR53" s="174"/>
+      <c r="BR53" s="164"/>
       <c r="BS53" s="26" t="str">
         <f>IF(BP54&gt;BP55,BL54,IF(BP54&lt;BP55,BL55,""))</f>
         <v/>
@@ -52200,7 +52200,7 @@
         <f>MAX(BH50:BH53)+1</f>
         <v>51.666666666666664</v>
       </c>
-      <c r="BK54" s="173">
+      <c r="BK54" s="163">
         <v>80</v>
       </c>
       <c r="BL54" s="24" t="str">
@@ -52263,8 +52263,12 @@
         <f>AE23</f>
         <v>Scotland</v>
       </c>
-      <c r="F55" s="19"/>
-      <c r="G55" s="20"/>
+      <c r="F55" s="19">
+        <v>0</v>
+      </c>
+      <c r="G55" s="20">
+        <v>3</v>
+      </c>
       <c r="H55" s="80" t="str">
         <f>AE20</f>
         <v>Brazil</v>
@@ -52283,11 +52287,11 @@
       </c>
       <c r="S55" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Scotland_lose</v>
       </c>
       <c r="T55" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Brazil_win</v>
       </c>
       <c r="U55" s="123">
         <f t="shared" si="8"/>
@@ -52317,11 +52321,11 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB55" s="123" t="str">
+      <c r="AB55" s="123">
         <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="BK55" s="174"/>
+        <v>-1</v>
+      </c>
+      <c r="BK55" s="164"/>
       <c r="BL55" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!K3,AK80:AS91,9,FALSE),"3rd Group E/H/I/J/K")</f>
         <v>3rd Group E/H/I/J/K</v>
@@ -52348,7 +52352,7 @@
       <c r="CC55" s="21"/>
       <c r="CD55" s="114"/>
       <c r="CE55" s="112"/>
-      <c r="CF55" s="173">
+      <c r="CF55" s="163">
         <v>102</v>
       </c>
       <c r="CG55" s="24" t="str">
@@ -52384,8 +52388,12 @@
         <f>AE21</f>
         <v>Morocco</v>
       </c>
-      <c r="F56" s="19"/>
-      <c r="G56" s="20"/>
+      <c r="F56" s="19">
+        <v>4</v>
+      </c>
+      <c r="G56" s="20">
+        <v>2</v>
+      </c>
       <c r="H56" s="80" t="str">
         <f>AE22</f>
         <v>Haiti</v>
@@ -52425,11 +52433,11 @@
       </c>
       <c r="S56" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Morocco_win</v>
       </c>
       <c r="T56" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Haiti_lose</v>
       </c>
       <c r="U56" s="123">
         <f t="shared" si="8"/>
@@ -52459,9 +52467,9 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB56" s="123" t="str">
+      <c r="AB56" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD56" s="123">
         <f>COUNTIF(AR56:AR59,CONCATENATE("&gt;=",AR56))</f>
@@ -52473,7 +52481,7 @@
       </c>
       <c r="AF56" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE56 &amp; "_win")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG56" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE56 &amp; "_draw")</f>
@@ -52485,31 +52493,31 @@
       </c>
       <c r="AI56" s="123">
         <f>SUMIF($E$7:$E$78,$AE56,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE56,$G$7:$G$78)</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AJ56" s="123">
         <f>SUMIF($E$7:$E$78,$AE56,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE56,$F$7:$F$78)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL56" s="123">
         <f>AI56-AJ56</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AM56" s="123">
         <f>AL56-AL60</f>
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="AN56" s="123">
         <f>AF56*3+AG56</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AO56" s="123">
         <f>AN56/AN60*10+BA56</f>
-        <v>8.5714285714285712</v>
+        <v>9</v>
       </c>
       <c r="AP56" s="123">
         <f>AO56*10000000+BI56*100+AM56/AM60*10+AI56/AI60*1++IF(AQ56=0,ROW(),AQ56)/2000000</f>
-        <v>85714295.631891042</v>
+        <v>90000010.41002956</v>
       </c>
       <c r="AQ56" s="126">
         <f>VLOOKUP(AE56,db_fifarank,2,FALSE)</f>
@@ -52517,11 +52525,11 @@
       </c>
       <c r="AR56" s="125">
         <f>AP56/AP60</f>
-        <v>0.99999998833333481</v>
+        <v>0.9999999888888903</v>
       </c>
       <c r="AS56" s="125" t="str">
         <f>IF(SUM(AF56:AH59)=12,J57,"1I")</f>
-        <v>1I</v>
+        <v>France</v>
       </c>
       <c r="AT56" s="126" cm="1">
         <f t="array" ref="AT56">SUMPRODUCT(($S$7:$S$78=AE56&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE56&amp;"_win")*($U$7:$U$78))</f>
@@ -52607,7 +52615,7 @@
       <c r="CC56" s="21"/>
       <c r="CD56" s="114"/>
       <c r="CE56" s="115"/>
-      <c r="CF56" s="174"/>
+      <c r="CF56" s="164"/>
       <c r="CG56" s="26" t="str">
         <f>IF(CD64&gt;CD65,BZ64,IF(CD64&lt;CD65,BZ65,""))</f>
         <v/>
@@ -52641,8 +52649,12 @@
         <f>AE17</f>
         <v>Switzerland</v>
       </c>
-      <c r="F57" s="19"/>
-      <c r="G57" s="20"/>
+      <c r="F57" s="19">
+        <v>2</v>
+      </c>
+      <c r="G57" s="20">
+        <v>1</v>
+      </c>
       <c r="H57" s="80" t="str">
         <f>AE14</f>
         <v>Canada</v>
@@ -52654,11 +52666,11 @@
       </c>
       <c r="K57" s="31">
         <f>L57+M57+N57</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L57" s="31">
         <f>VLOOKUP(1,AD56:AN59,3,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M57" s="31">
         <f>VLOOKUP(1,AD56:AN59,4,FALSE)</f>
@@ -52670,11 +52682,11 @@
       </c>
       <c r="O57" s="31" t="str">
         <f>VLOOKUP(1,AD56:AN59,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD56:AN59,7,FALSE)</f>
-        <v>6 - 1</v>
+        <v>10 - 2</v>
       </c>
       <c r="P57" s="32">
         <f>L57*3+M57</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R57" s="123">
         <f>DATE(2026,6,24)+TIME(8,0,0)+gmt_delta</f>
@@ -52682,11 +52694,11 @@
       </c>
       <c r="S57" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Switzerland_win</v>
       </c>
       <c r="T57" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Canada_lose</v>
       </c>
       <c r="U57" s="123">
         <f t="shared" si="8"/>
@@ -52716,9 +52728,9 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB57" s="123" t="str">
+      <c r="AB57" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD57" s="123">
         <f>COUNTIF(AR56:AR59,CONCATENATE("&gt;=",AR57))</f>
@@ -52730,7 +52742,7 @@
       </c>
       <c r="AF57" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE57 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG57" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE57 &amp; "_draw")</f>
@@ -52742,7 +52754,7 @@
       </c>
       <c r="AI57" s="123">
         <f>SUMIF($E$7:$E$78,$AE57,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE57,$G$7:$G$78)</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AJ57" s="123">
         <f>SUMIF($E$7:$E$78,$AE57,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE57,$F$7:$F$78)</f>
@@ -52750,23 +52762,23 @@
       </c>
       <c r="AL57" s="123">
         <f>AI57-AJ57</f>
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="AM57" s="123">
         <f>AL57-AL60</f>
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AN57" s="123">
         <f>AF57*3+AG57</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO57" s="123">
         <f>AN57/AN60*10+BA57</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP57" s="123">
         <f>AO57*10000000+BI57*100+AM57/AM60*10+AI57/AI60*1++IF(AQ57=0,ROW(),AQ57)/2000000</f>
-        <v>2.8758444949999999</v>
+        <v>30000007.22811722</v>
       </c>
       <c r="AQ57" s="126">
         <f>VLOOKUP(AE57,db_fifarank,2,FALSE)</f>
@@ -52774,11 +52786,11 @@
       </c>
       <c r="AR57" s="125">
         <f>AP57/AP60</f>
-        <v>3.35515148348077E-8</v>
+        <v>0.33333337138637331</v>
       </c>
       <c r="AS57" s="125" t="str">
         <f>IF(SUM(AF56:AH59)=12,J58,"2I")</f>
-        <v>2I</v>
+        <v>Norway</v>
       </c>
       <c r="AT57" s="126" cm="1">
         <f t="array" ref="AT57">SUMPRODUCT(($S$7:$S$78=AE57&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE57&amp;"_win")*($U$7:$U$78))</f>
@@ -52891,8 +52903,12 @@
         <f>AE15</f>
         <v>Bosnia and Herzegovina</v>
       </c>
-      <c r="F58" s="19"/>
-      <c r="G58" s="20"/>
+      <c r="F58" s="19">
+        <v>3</v>
+      </c>
+      <c r="G58" s="20">
+        <v>1</v>
+      </c>
       <c r="H58" s="80" t="str">
         <f>AE16</f>
         <v>Qatar</v>
@@ -52904,7 +52920,7 @@
       </c>
       <c r="K58" s="23">
         <f>L58+M58+N58</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L58" s="23">
         <f>VLOOKUP(2,AD56:AN59,3,FALSE)</f>
@@ -52916,11 +52932,11 @@
       </c>
       <c r="N58" s="23">
         <f>VLOOKUP(2,AD56:AN59,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O58" s="23" t="str">
         <f>VLOOKUP(2,AD56:AN59,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD56:AN59,7,FALSE)</f>
-        <v>7 - 3</v>
+        <v>8 - 7</v>
       </c>
       <c r="P58" s="34">
         <f>L58*3+M58</f>
@@ -52932,11 +52948,11 @@
       </c>
       <c r="S58" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Bosnia and Herzegovina_win</v>
       </c>
       <c r="T58" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Qatar_lose</v>
       </c>
       <c r="U58" s="123">
         <f t="shared" si="8"/>
@@ -52966,9 +52982,9 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB58" s="123" t="str">
+      <c r="AB58" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD58" s="123">
         <f>COUNTIF(AR56:AR59,CONCATENATE("&gt;=",AR58))</f>
@@ -52988,7 +53004,7 @@
       </c>
       <c r="AH58" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE58 &amp; "_lose")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI58" s="123">
         <f>SUMIF($E$7:$E$78,$AE58,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE58,$G$7:$G$78)</f>
@@ -52996,11 +53012,11 @@
       </c>
       <c r="AJ58" s="123">
         <f>SUMIF($E$7:$E$78,$AE58,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE58,$F$7:$F$78)</f>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AL58" s="123">
         <f>AI58-AJ58</f>
-        <v>-6</v>
+        <v>-11</v>
       </c>
       <c r="AM58" s="123">
         <f>AL58-AL60</f>
@@ -53016,7 +53032,7 @@
       </c>
       <c r="AP58" s="123">
         <f>AO58*10000000+BI58*100+AM58/AM60*10+AI58/AI60*1++IF(AQ58=0,ROW(),AQ58)/2000000</f>
-        <v>0.12572357000000001</v>
+        <v>9.1632660909090918E-2</v>
       </c>
       <c r="AQ58" s="126">
         <f>VLOOKUP(AE58,db_fifarank,2,FALSE)</f>
@@ -53024,7 +53040,7 @@
       </c>
       <c r="AR58" s="125">
         <f>AP58/AP60</f>
-        <v>1.466774796507203E-9</v>
+        <v>1.0181405476897463E-9</v>
       </c>
       <c r="AT58" s="126" cm="1">
         <f t="array" ref="AT58">SUMPRODUCT(($S$7:$S$78=AE58&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE58&amp;"_win")*($U$7:$U$78))</f>
@@ -53090,7 +53106,7 @@
         <f>BH58/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK58" s="173">
+      <c r="BK58" s="163">
         <v>86</v>
       </c>
       <c r="BL58" s="24" t="str">
@@ -53139,8 +53155,12 @@
         <f>AE11</f>
         <v>Czech Republic</v>
       </c>
-      <c r="F59" s="19"/>
-      <c r="G59" s="20"/>
+      <c r="F59" s="19">
+        <v>0</v>
+      </c>
+      <c r="G59" s="20">
+        <v>3</v>
+      </c>
       <c r="H59" s="80" t="str">
         <f>AE8</f>
         <v>Mexico</v>
@@ -53152,11 +53172,11 @@
       </c>
       <c r="K59" s="23">
         <f>L59+M59+N59</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L59" s="23">
         <f>VLOOKUP(3,AD56:AN59,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" s="23">
         <f>VLOOKUP(3,AD56:AN59,4,FALSE)</f>
@@ -53168,11 +53188,11 @@
       </c>
       <c r="O59" s="23" t="str">
         <f>VLOOKUP(3,AD56:AN59,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD56:AN59,7,FALSE)</f>
-        <v>3 - 6</v>
+        <v>8 - 6</v>
       </c>
       <c r="P59" s="34">
         <f>L59*3+M59</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R59" s="123">
         <f>DATE(2026,6,24)+TIME(14,0,0)+gmt_delta</f>
@@ -53180,11 +53200,11 @@
       </c>
       <c r="S59" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Czech Republic_lose</v>
       </c>
       <c r="T59" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Mexico_win</v>
       </c>
       <c r="U59" s="123">
         <f t="shared" si="8"/>
@@ -53214,9 +53234,9 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB59" s="123" t="str">
+      <c r="AB59" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>-1</v>
       </c>
       <c r="AD59" s="123">
         <f>COUNTIF(AR56:AR59,CONCATENATE("&gt;=",AR59))</f>
@@ -53236,23 +53256,23 @@
       </c>
       <c r="AH59" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE59 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI59" s="123">
         <f>SUMIF($E$7:$E$78,$AE59,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE59,$G$7:$G$78)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ59" s="123">
         <f>SUMIF($E$7:$E$78,$AE59,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE59,$F$7:$F$78)</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AL59" s="123">
         <f>AI59-AJ59</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AM59" s="123">
         <f>AL59-AL60</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AN59" s="123">
         <f>AF59*3+AG59</f>
@@ -53260,11 +53280,11 @@
       </c>
       <c r="AO59" s="123">
         <f>AN59/AN60*10+BA59</f>
-        <v>8.5714285714285712</v>
+        <v>6</v>
       </c>
       <c r="AP59" s="123">
         <f>AO59*10000000+BI59*100+AM59/AM60*10+AI59/AI60*1++IF(AQ59=0,ROW(),AQ59)/2000000</f>
-        <v>85714294.923394516</v>
+        <v>60000006.728048198</v>
       </c>
       <c r="AQ59" s="126">
         <f>VLOOKUP(AE59,db_fifarank,2,FALSE)</f>
@@ -53272,7 +53292,7 @@
       </c>
       <c r="AR59" s="125">
         <f>AP59/AP60</f>
-        <v>0.99999998006754309</v>
+        <v>0.66666665690402149</v>
       </c>
       <c r="AT59" s="126" cm="1">
         <f t="array" ref="AT59">SUMPRODUCT(($S$7:$S$78=AE59&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE59&amp;"_win")*($U$7:$U$78))</f>
@@ -53338,7 +53358,7 @@
         <f>BH59/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK59" s="174"/>
+      <c r="BK59" s="164"/>
       <c r="BL59" s="26" t="str">
         <f>AS51</f>
         <v>2H</v>
@@ -53391,8 +53411,12 @@
         <f>AE9</f>
         <v>South Africa</v>
       </c>
-      <c r="F60" s="19"/>
-      <c r="G60" s="20"/>
+      <c r="F60" s="19">
+        <v>1</v>
+      </c>
+      <c r="G60" s="20">
+        <v>0</v>
+      </c>
       <c r="H60" s="80" t="str">
         <f>AE10</f>
         <v>Korea Republic</v>
@@ -53404,7 +53428,7 @@
       </c>
       <c r="K60" s="36">
         <f>L60+M60+N60</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L60" s="36">
         <f>VLOOKUP(4,AD56:AN59,3,FALSE)</f>
@@ -53416,11 +53440,11 @@
       </c>
       <c r="N60" s="36">
         <f>VLOOKUP(4,AD56:AN59,5,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O60" s="36" t="str">
         <f>VLOOKUP(4,AD56:AN59,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD56:AN59,7,FALSE)</f>
-        <v>1 - 7</v>
+        <v>1 - 12</v>
       </c>
       <c r="P60" s="37">
         <f>L60*3+M60</f>
@@ -53432,11 +53456,11 @@
       </c>
       <c r="S60" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>South Africa_win</v>
       </c>
       <c r="T60" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Korea Republic_lose</v>
       </c>
       <c r="U60" s="123">
         <f t="shared" si="8"/>
@@ -53466,13 +53490,13 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB60" s="123" t="str">
+      <c r="AB60" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AF60" s="123">
         <f t="shared" ref="AF60:AH60" si="27">MAX(AF56:AF59)-MIN(AF56:AF59)+1</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG60" s="123">
         <f t="shared" si="27"/>
@@ -53480,31 +53504,31 @@
       </c>
       <c r="AH60" s="123">
         <f t="shared" si="27"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI60" s="123">
         <f>MAX(AI56:AI59)+1</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AL60" s="123">
         <f>MIN(AL56:AL59)</f>
-        <v>-6</v>
+        <v>-11</v>
       </c>
       <c r="AM60" s="123">
         <f>MAX(AM56:AM59)+1</f>
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AN60" s="123">
         <f>MAX(AN56:AN59)+1</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AO60" s="123">
         <f>MAX(AO56:AO59)+1</f>
-        <v>9.5714285714285712</v>
+        <v>10</v>
       </c>
       <c r="AP60" s="123">
         <f>MAX(AP56:AP59)+1</f>
-        <v>85714296.631891042</v>
+        <v>90000011.41002956</v>
       </c>
       <c r="AT60" s="126">
         <f>MAX(AT56:AT59)-MIN(AT56:AT59)+1</f>
@@ -53561,7 +53585,7 @@
       <c r="BO60" s="21"/>
       <c r="BP60" s="114"/>
       <c r="BQ60" s="112"/>
-      <c r="BR60" s="173">
+      <c r="BR60" s="163">
         <v>95</v>
       </c>
       <c r="BS60" s="24" t="str">
@@ -53603,8 +53627,12 @@
         <f>AE33</f>
         <v>Curaçao</v>
       </c>
-      <c r="F61" s="19"/>
-      <c r="G61" s="20"/>
+      <c r="F61" s="19">
+        <v>0</v>
+      </c>
+      <c r="G61" s="20">
+        <v>2</v>
+      </c>
       <c r="H61" s="80" t="str">
         <f>AE34</f>
         <v>Ivory Coast</v>
@@ -53623,11 +53651,11 @@
       </c>
       <c r="S61" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Curaçao_lose</v>
       </c>
       <c r="T61" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Ivory Coast_win</v>
       </c>
       <c r="U61" s="123">
         <f t="shared" si="8"/>
@@ -53657,9 +53685,9 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB61" s="123" t="str">
+      <c r="AB61" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>-1</v>
       </c>
       <c r="BK61" s="21" t="str" cm="1">
         <f t="array" ref="BK61">INDEX(T,24+MONTH(BP61),lang) &amp; " " &amp; DAY(BP61) &amp; ", " &amp; YEAR(BP61) &amp; "   " &amp; (IF(HOUR(BP61)&lt;10,0,"")&amp;HOUR(BP61)) &amp; ":" &amp;  (IF(MINUTE(BP61)&lt;10,0,"")&amp;MINUTE(BP61))</f>
@@ -53674,7 +53702,7 @@
         <v>46206.75</v>
       </c>
       <c r="BQ61" s="115"/>
-      <c r="BR61" s="174"/>
+      <c r="BR61" s="164"/>
       <c r="BS61" s="26" t="str">
         <f>IF(BP62&gt;BP63,BL62,IF(BP62&lt;BP63,BL63,""))</f>
         <v/>
@@ -53714,8 +53742,12 @@
         <f>AE35</f>
         <v>Ecuador</v>
       </c>
-      <c r="F62" s="19"/>
-      <c r="G62" s="20"/>
+      <c r="F62" s="19">
+        <v>2</v>
+      </c>
+      <c r="G62" s="20">
+        <v>1</v>
+      </c>
       <c r="H62" s="80" t="str">
         <f>AE32</f>
         <v>Germany</v>
@@ -53755,11 +53787,11 @@
       </c>
       <c r="S62" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Ecuador_win</v>
       </c>
       <c r="T62" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Germany_lose</v>
       </c>
       <c r="U62" s="123">
         <f t="shared" si="8"/>
@@ -53789,9 +53821,9 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB62" s="123" t="str">
+      <c r="AB62" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD62" s="123">
         <f>COUNTIF(AR62:AR65,CONCATENATE("&gt;=",AR62))</f>
@@ -53917,12 +53949,12 @@
         <f>BH62/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK62" s="173">
+      <c r="BK62" s="163">
         <v>88</v>
       </c>
       <c r="BL62" s="24" t="str">
         <f>AS27</f>
-        <v>2D</v>
+        <v>Australia</v>
       </c>
       <c r="BM62" s="61"/>
       <c r="BN62" s="63"/>
@@ -53966,8 +53998,12 @@
         <f>AE39</f>
         <v>Japan</v>
       </c>
-      <c r="F63" s="19"/>
-      <c r="G63" s="20"/>
+      <c r="F63" s="19">
+        <v>1</v>
+      </c>
+      <c r="G63" s="20">
+        <v>1</v>
+      </c>
       <c r="H63" s="80" t="str">
         <f>AE40</f>
         <v>Sweden</v>
@@ -54007,11 +54043,11 @@
       </c>
       <c r="S63" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Japan_draw</v>
       </c>
       <c r="T63" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Sweden_draw</v>
       </c>
       <c r="U63" s="123">
         <f t="shared" si="8"/>
@@ -54041,9 +54077,9 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB63" s="123" t="str">
+      <c r="AB63" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AD63" s="123">
         <f>COUNTIF(AR62:AR65,CONCATENATE("&gt;=",AR63))</f>
@@ -54169,7 +54205,7 @@
         <f>BH63/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK63" s="174"/>
+      <c r="BK63" s="164"/>
       <c r="BL63" s="26" t="str">
         <f>AS45</f>
         <v>2G</v>
@@ -54222,8 +54258,12 @@
         <f>AE41</f>
         <v>Tunisia</v>
       </c>
-      <c r="F64" s="19"/>
-      <c r="G64" s="20"/>
+      <c r="F64" s="19">
+        <v>1</v>
+      </c>
+      <c r="G64" s="20">
+        <v>3</v>
+      </c>
       <c r="H64" s="80" t="str">
         <f>AE38</f>
         <v>Netherlands</v>
@@ -54263,11 +54303,11 @@
       </c>
       <c r="S64" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Tunisia_lose</v>
       </c>
       <c r="T64" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Netherlands_win</v>
       </c>
       <c r="U64" s="123">
         <f t="shared" si="8"/>
@@ -54297,9 +54337,9 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB64" s="123" t="str">
+      <c r="AB64" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>-1</v>
       </c>
       <c r="AD64" s="123">
         <f>COUNTIF(AR62:AR65,CONCATENATE("&gt;=",AR64))</f>
@@ -54435,7 +54475,7 @@
       <c r="BV64" s="21"/>
       <c r="BW64" s="114"/>
       <c r="BX64" s="112"/>
-      <c r="BY64" s="173">
+      <c r="BY64" s="163">
         <v>100</v>
       </c>
       <c r="BZ64" s="24" t="str">
@@ -54470,8 +54510,12 @@
         <f>AE29</f>
         <v>Turkey</v>
       </c>
-      <c r="F65" s="19"/>
-      <c r="G65" s="20"/>
+      <c r="F65" s="19">
+        <v>3</v>
+      </c>
+      <c r="G65" s="20">
+        <v>2</v>
+      </c>
       <c r="H65" s="80" t="str">
         <f>AE26</f>
         <v>United States</v>
@@ -54511,11 +54555,11 @@
       </c>
       <c r="S65" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Turkey_win</v>
       </c>
       <c r="T65" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>United States_lose</v>
       </c>
       <c r="U65" s="123">
         <f t="shared" si="8"/>
@@ -54545,9 +54589,9 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB65" s="123" t="str">
+      <c r="AB65" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD65" s="123">
         <f>COUNTIF(AR62:AR65,CONCATENATE("&gt;=",AR65))</f>
@@ -54689,7 +54733,7 @@
       <c r="BV65" s="21"/>
       <c r="BW65" s="114"/>
       <c r="BX65" s="115"/>
-      <c r="BY65" s="174"/>
+      <c r="BY65" s="164"/>
       <c r="BZ65" s="26" t="str">
         <f>IF(BW68&gt;BW69,BS68,IF(BW68&lt;BW69,BS69,""))</f>
         <v/>
@@ -54722,8 +54766,12 @@
         <f>AE27</f>
         <v>Paraguay</v>
       </c>
-      <c r="F66" s="19"/>
-      <c r="G66" s="20"/>
+      <c r="F66" s="19">
+        <v>0</v>
+      </c>
+      <c r="G66" s="20">
+        <v>0</v>
+      </c>
       <c r="H66" s="80" t="str">
         <f>AE28</f>
         <v>Australia</v>
@@ -54763,15 +54811,15 @@
       </c>
       <c r="S66" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Paraguay_draw</v>
       </c>
       <c r="T66" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Australia_draw</v>
       </c>
       <c r="U66" s="123">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V66" s="123">
         <f t="shared" si="21"/>
@@ -54783,7 +54831,7 @@
       </c>
       <c r="X66" s="123">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y66" s="123">
         <f t="shared" si="10"/>
@@ -54797,9 +54845,9 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB66" s="123" t="str">
+      <c r="AB66" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF66" s="123">
         <f t="shared" ref="AF66:AH66" si="28">MAX(AF62:AF65)-MIN(AF62:AF65)+1</f>
@@ -54885,12 +54933,12 @@
         <f>MAX(BH62:BH65)+1</f>
         <v>1</v>
       </c>
-      <c r="BK66" s="173">
+      <c r="BK66" s="163">
         <v>85</v>
       </c>
       <c r="BL66" s="24" t="str">
         <f>AS14</f>
-        <v>1B</v>
+        <v>Switzerland</v>
       </c>
       <c r="BM66" s="61"/>
       <c r="BN66" s="63"/>
@@ -54927,8 +54975,12 @@
         <f>AE59</f>
         <v>Norway</v>
       </c>
-      <c r="F67" s="19"/>
-      <c r="G67" s="20"/>
+      <c r="F67" s="19">
+        <v>1</v>
+      </c>
+      <c r="G67" s="20">
+        <v>4</v>
+      </c>
       <c r="H67" s="80" t="str">
         <f>AE56</f>
         <v>France</v>
@@ -54947,11 +54999,11 @@
       </c>
       <c r="S67" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Norway_lose</v>
       </c>
       <c r="T67" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>France_win</v>
       </c>
       <c r="U67" s="123">
         <f t="shared" si="8"/>
@@ -54981,11 +55033,11 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB67" s="123" t="str">
+      <c r="AB67" s="123">
         <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="BK67" s="174"/>
+        <v>-1</v>
+      </c>
+      <c r="BK67" s="164"/>
       <c r="BL67" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!E3,AK80:AS91,9,FALSE),"3rd Group E/F/G/I/J")</f>
         <v>3rd Group E/F/G/I/J</v>
@@ -55031,8 +55083,12 @@
         <f>AE57</f>
         <v>Senegal</v>
       </c>
-      <c r="F68" s="19"/>
-      <c r="G68" s="20"/>
+      <c r="F68" s="19">
+        <v>5</v>
+      </c>
+      <c r="G68" s="20">
+        <v>0</v>
+      </c>
       <c r="H68" s="80" t="str">
         <f>AE58</f>
         <v>Iraq</v>
@@ -55072,11 +55128,11 @@
       </c>
       <c r="S68" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Senegal_win</v>
       </c>
       <c r="T68" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Iraq_lose</v>
       </c>
       <c r="U68" s="123">
         <f t="shared" si="8"/>
@@ -55106,9 +55162,9 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB68" s="123" t="str">
+      <c r="AB68" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD68" s="123">
         <f>COUNTIF(AR68:AR71,CONCATENATE("&gt;=",AR68))</f>
@@ -55241,7 +55297,7 @@
       <c r="BO68" s="21"/>
       <c r="BP68" s="114"/>
       <c r="BQ68" s="112"/>
-      <c r="BR68" s="173">
+      <c r="BR68" s="163">
         <v>96</v>
       </c>
       <c r="BS68" s="24" t="str">
@@ -55255,25 +55311,25 @@
         <f>IF(OR(BT68="",BT69="",AND(BU68="",BU69&lt;&gt;""),AND(BU69="",BU68&lt;&gt;""),AND(BV68="",BV69&lt;&gt;""),AND(BV69="",BV68&lt;&gt;"")),"",BT68*1000+BU68*10+BV68)</f>
         <v/>
       </c>
-      <c r="CE68" s="175" t="str">
+      <c r="CE68" s="195" t="str">
         <f>INDEX(T,144,lang)</f>
         <v>World Champion 2026</v>
       </c>
-      <c r="CF68" s="175"/>
-      <c r="CG68" s="175"/>
-      <c r="CH68" s="175"/>
-      <c r="CI68" s="175"/>
-      <c r="CJ68" s="175"/>
-      <c r="CK68" s="163" t="str">
+      <c r="CF68" s="195"/>
+      <c r="CG68" s="195"/>
+      <c r="CH68" s="195"/>
+      <c r="CI68" s="195"/>
+      <c r="CJ68" s="195"/>
+      <c r="CK68" s="185" t="str">
         <f>IF(CR37&gt;CR38,CN37,IF(CR37&lt;CR38,CN38,""))</f>
         <v/>
       </c>
-      <c r="CL68" s="163"/>
-      <c r="CM68" s="163"/>
-      <c r="CN68" s="163"/>
-      <c r="CO68" s="163"/>
-      <c r="CP68" s="163"/>
-      <c r="CQ68" s="163"/>
+      <c r="CL68" s="185"/>
+      <c r="CM68" s="185"/>
+      <c r="CN68" s="185"/>
+      <c r="CO68" s="185"/>
+      <c r="CP68" s="185"/>
+      <c r="CQ68" s="185"/>
     </row>
     <row r="69" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A69" s="16">
@@ -55511,7 +55567,7 @@
         <v>46207.0625</v>
       </c>
       <c r="BQ69" s="115"/>
-      <c r="BR69" s="174"/>
+      <c r="BR69" s="164"/>
       <c r="BS69" s="26" t="str">
         <f>IF(BP70&gt;BP71,BL70,IF(BP70&lt;BP71,BL71,""))</f>
         <v/>
@@ -55523,19 +55579,19 @@
         <f>IF(BW68="","",BT69*1000+BU69*10+BV69)</f>
         <v/>
       </c>
-      <c r="CE69" s="175"/>
-      <c r="CF69" s="175"/>
-      <c r="CG69" s="175"/>
-      <c r="CH69" s="175"/>
-      <c r="CI69" s="175"/>
-      <c r="CJ69" s="175"/>
-      <c r="CK69" s="163"/>
-      <c r="CL69" s="163"/>
-      <c r="CM69" s="163"/>
-      <c r="CN69" s="163"/>
-      <c r="CO69" s="163"/>
-      <c r="CP69" s="163"/>
-      <c r="CQ69" s="163"/>
+      <c r="CE69" s="195"/>
+      <c r="CF69" s="195"/>
+      <c r="CG69" s="195"/>
+      <c r="CH69" s="195"/>
+      <c r="CI69" s="195"/>
+      <c r="CJ69" s="195"/>
+      <c r="CK69" s="185"/>
+      <c r="CL69" s="185"/>
+      <c r="CM69" s="185"/>
+      <c r="CN69" s="185"/>
+      <c r="CO69" s="185"/>
+      <c r="CP69" s="185"/>
+      <c r="CQ69" s="185"/>
     </row>
     <row r="70" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A70" s="16">
@@ -55756,7 +55812,7 @@
         <f>BH70/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK70" s="173">
+      <c r="BK70" s="163">
         <v>87</v>
       </c>
       <c r="BL70" s="24" t="str">
@@ -55992,7 +56048,7 @@
         <f>BH71/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK71" s="174"/>
+      <c r="BK71" s="164"/>
       <c r="BL71" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!J3,AK80:AS91,9,FALSE),"3rd Group D/E/I/J/L")</f>
         <v>3rd Group D/E/I/J/L</v>
@@ -57399,23 +57455,23 @@
       </c>
       <c r="AD80" s="123">
         <f>COUNTIF($AP$80:$AP$91,CONCATENATE("&gt;=",AP80))</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE80" s="124" t="str">
         <f>J11</f>
-        <v>Czech Republic</v>
+        <v>Korea Republic</v>
       </c>
       <c r="AF80" s="123">
         <f>VLOOKUP($AE80,$AE$8:$AQ$78,2,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG80" s="123">
         <f>VLOOKUP($AE80,$AE$8:$AQ$78,3,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH80" s="123">
         <f>VLOOKUP($AE80,$AE$8:$AQ$78,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI80" s="123">
         <f>VLOOKUP($AE80,$AE$8:$AQ$78,5,FALSE)</f>
@@ -57438,15 +57494,15 @@
       </c>
       <c r="AN80" s="123">
         <f>VLOOKUP($AE80,$AE$8:$AQ$78,10,FALSE)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AP80" s="123">
         <f>AN80/AN92*10000+AM80/AM92*1000+AI80/AI92*100+IF(AQ80=0,ROW(),AQ80)/2000000</f>
-        <v>3028.5721792614286</v>
+        <v>6355.5563498855554</v>
       </c>
       <c r="AQ80" s="126">
         <f t="shared" ref="AQ80:AQ91" si="37">VLOOKUP($AE80,$AE$8:$AQ$78,13,FALSE)</f>
-        <v>1501.38</v>
+        <v>1588.66</v>
       </c>
       <c r="AR80" s="125" t="str">
         <f>IF(AD80&lt;=8,RIGHT(AK80,1),"")</f>
@@ -57454,11 +57510,11 @@
       </c>
       <c r="AS80" s="129" t="str">
         <f>IF(AD80&lt;=8,AE80,"")</f>
-        <v>Czech Republic</v>
+        <v>Korea Republic</v>
       </c>
       <c r="AT80" s="130" t="str">
         <f>"Ⓐ "&amp;AE80</f>
-        <v>Ⓐ Czech Republic</v>
+        <v>Ⓐ Korea Republic</v>
       </c>
     </row>
     <row r="81" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -57477,7 +57533,7 @@
       </c>
       <c r="K81" s="97">
         <f>L81+M81+N81</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L81" s="97">
         <f>VLOOKUP(1,$AD$80:$AN$91,3,FALSE)</f>
@@ -57485,7 +57541,7 @@
       </c>
       <c r="M81" s="97">
         <f>VLOOKUP(1,$AD$80:$AN$91,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N81" s="97">
         <f>VLOOKUP(1,$AD$80:$AN$91,5,FALSE)</f>
@@ -57493,15 +57549,15 @@
       </c>
       <c r="O81" s="97" t="str">
         <f>VLOOKUP(1,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(1,$AD$80:$AN$91,7,FALSE)</f>
-        <v>6 - 6</v>
+        <v>7 - 7</v>
       </c>
       <c r="P81" s="98">
         <f>L81*3+M81</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD81" s="123">
         <f t="shared" ref="AD81:AD91" si="38">COUNTIF($AP$80:$AP$91,CONCATENATE("&gt;=",AP81))</f>
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AE81" s="124" t="str">
         <f>J17</f>
@@ -57509,7 +57565,7 @@
       </c>
       <c r="AF81" s="123">
         <f t="shared" ref="AF81:AF91" si="39">VLOOKUP($AE81,$AE$8:$AQ$78,2,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG81" s="123">
         <f>VLOOKUP($AE81,$AE$8:$AQ$78,3,FALSE)</f>
@@ -57521,30 +57577,30 @@
       </c>
       <c r="AI81" s="123">
         <f t="shared" ref="AI81:AI90" si="41">VLOOKUP($AE81,$AE$8:$AQ$78,5,FALSE)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AJ81" s="123">
         <f t="shared" ref="AJ81:AJ90" si="42">VLOOKUP($AE81,$AE$8:$AQ$78,6,FALSE)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK81" s="123" t="s">
         <v>3181</v>
       </c>
       <c r="AL81" s="123">
         <f t="shared" ref="AL81:AL90" si="43">VLOOKUP($AE81,$AE$8:$AQ$78,8,FALSE)</f>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="AM81" s="123">
         <f t="shared" ref="AM81:AM91" si="44">AL81-$AL$92</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN81" s="123">
         <f t="shared" ref="AN81:AN90" si="45">VLOOKUP($AE81,$AE$8:$AQ$78,10,FALSE)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AP81" s="123">
         <f>AN81/AN92*10000+AM81/AM92*1000+AI81/AI92*100+IF(AQ81=0,ROW(),AQ81)/2000000</f>
-        <v>2528.5721214914283</v>
+        <v>8388.8895818088895</v>
       </c>
       <c r="AQ81" s="126">
         <f t="shared" si="37"/>
@@ -57552,11 +57608,11 @@
       </c>
       <c r="AR81" s="125" t="str">
         <f>AR80&amp;IF(AD81&lt;=8,RIGHT(AK81,1),"")</f>
-        <v>A</v>
+        <v>AB</v>
       </c>
       <c r="AS81" s="129" t="str">
         <f t="shared" ref="AS81:AS91" si="46">IF(AD81&lt;=8,AE81,"")</f>
-        <v/>
+        <v>Bosnia and Herzegovina</v>
       </c>
       <c r="AT81" s="130" t="str">
         <f>"Ⓑ "&amp;AE81</f>
@@ -57575,11 +57631,11 @@
       <c r="I82" s="69"/>
       <c r="J82" s="99" t="str">
         <f>VLOOKUP(2,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓒ Scotland</v>
+        <v>Ⓔ Ecuador</v>
       </c>
       <c r="K82" s="100">
         <f t="shared" ref="K82:K92" si="47">L82+M82+N82</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L82" s="100">
         <f>VLOOKUP(2,$AD$80:$AN$91,3,FALSE)</f>
@@ -57587,7 +57643,7 @@
       </c>
       <c r="M82" s="100">
         <f>VLOOKUP(2,$AD$80:$AN$91,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N82" s="100">
         <f>VLOOKUP(2,$AD$80:$AN$91,5,FALSE)</f>
@@ -57595,15 +57651,15 @@
       </c>
       <c r="O82" s="100" t="str">
         <f>VLOOKUP(2,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(2,$AD$80:$AN$91,7,FALSE)</f>
-        <v>1 - 1</v>
+        <v>2 - 2</v>
       </c>
       <c r="P82" s="101">
         <f t="shared" ref="P82:P92" si="48">L82*3+M82</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD82" s="123">
         <f t="shared" si="38"/>
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AE82" s="124" t="str">
         <f>J23</f>
@@ -57619,7 +57675,7 @@
       </c>
       <c r="AH82" s="123">
         <f t="shared" si="40"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI82" s="123">
         <f t="shared" si="41"/>
@@ -57627,18 +57683,18 @@
       </c>
       <c r="AJ82" s="123">
         <f t="shared" si="42"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AK82" s="123" t="s">
         <v>3182</v>
       </c>
       <c r="AL82" s="123">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AM82" s="123">
         <f t="shared" si="44"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AN82" s="123">
         <f t="shared" si="45"/>
@@ -57646,7 +57702,7 @@
       </c>
       <c r="AP82" s="123">
         <f>AN82/AN92*10000+AM82/AM92*1000+AI82/AI92*100+IF(AQ82=0,ROW(),AQ82)/2000000</f>
-        <v>8264.286463460714</v>
+        <v>6011.1118602861116</v>
       </c>
       <c r="AQ82" s="126">
         <f t="shared" si="37"/>
@@ -57654,11 +57710,11 @@
       </c>
       <c r="AR82" s="125" t="str">
         <f t="shared" ref="AR82:AR91" si="50">AR81&amp;IF(AD82&lt;=8,RIGHT(AK82,1),"")</f>
-        <v>AC</v>
+        <v>AB</v>
       </c>
       <c r="AS82" s="129" t="str">
         <f t="shared" si="46"/>
-        <v>Scotland</v>
+        <v/>
       </c>
       <c r="AT82" s="130" t="str">
         <f>"Ⓒ "&amp;AE82</f>
@@ -57668,22 +57724,22 @@
     <row r="83" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="73"/>
       <c r="B83" s="73"/>
-      <c r="C83" s="164" t="s">
+      <c r="C83" s="186" t="s">
         <v>3183</v>
       </c>
-      <c r="D83" s="165"/>
-      <c r="E83" s="165"/>
-      <c r="F83" s="165"/>
-      <c r="G83" s="166"/>
+      <c r="D83" s="187"/>
+      <c r="E83" s="187"/>
+      <c r="F83" s="187"/>
+      <c r="G83" s="188"/>
       <c r="H83" s="75"/>
       <c r="I83" s="69"/>
       <c r="J83" s="99" t="str">
         <f>VLOOKUP(3,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓛ Croatia</v>
+        <v>Ⓑ Bosnia and Herzegovina</v>
       </c>
       <c r="K83" s="100">
         <f t="shared" si="47"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L83" s="100">
         <f>VLOOKUP(3,$AD$80:$AN$91,3,FALSE)</f>
@@ -57691,7 +57747,7 @@
       </c>
       <c r="M83" s="100">
         <f>VLOOKUP(3,$AD$80:$AN$91,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N83" s="100">
         <f>VLOOKUP(3,$AD$80:$AN$91,5,FALSE)</f>
@@ -57699,15 +57755,15 @@
       </c>
       <c r="O83" s="100" t="str">
         <f>VLOOKUP(3,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(3,$AD$80:$AN$91,7,FALSE)</f>
-        <v>3 - 4</v>
+        <v>5 - 6</v>
       </c>
       <c r="P83" s="101">
         <f t="shared" si="48"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD83" s="123">
         <f t="shared" si="38"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE83" s="124" t="str">
         <f>J29</f>
@@ -57719,7 +57775,7 @@
       </c>
       <c r="AG83" s="123">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH83" s="123">
         <f t="shared" si="40"/>
@@ -57746,11 +57802,11 @@
       </c>
       <c r="AN83" s="123">
         <f t="shared" si="45"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP83" s="123">
         <f>AN83/AN92*10000+AM83/AM92*1000+AI83/AI92*100+IF(AQ83=0,ROW(),AQ83)/2000000</f>
-        <v>7778.5721803214283</v>
+        <v>8188.8896406388894</v>
       </c>
       <c r="AQ83" s="126">
         <f t="shared" si="37"/>
@@ -57758,7 +57814,7 @@
       </c>
       <c r="AR83" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ACD</v>
+        <v>ABD</v>
       </c>
       <c r="AS83" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57772,20 +57828,20 @@
     <row r="84" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="73"/>
       <c r="B84" s="73"/>
-      <c r="C84" s="167"/>
-      <c r="D84" s="168"/>
-      <c r="E84" s="168"/>
-      <c r="F84" s="168"/>
-      <c r="G84" s="169"/>
+      <c r="C84" s="189"/>
+      <c r="D84" s="190"/>
+      <c r="E84" s="190"/>
+      <c r="F84" s="190"/>
+      <c r="G84" s="191"/>
       <c r="H84" s="75"/>
       <c r="I84" s="69"/>
       <c r="J84" s="99" t="str">
         <f>VLOOKUP(4,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓙ Algeria</v>
+        <v>Ⓓ Paraguay</v>
       </c>
       <c r="K84" s="100">
         <f t="shared" si="47"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L84" s="100">
         <f>VLOOKUP(4,$AD$80:$AN$91,3,FALSE)</f>
@@ -57793,7 +57849,7 @@
       </c>
       <c r="M84" s="100">
         <f>VLOOKUP(4,$AD$80:$AN$91,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N84" s="100">
         <f>VLOOKUP(4,$AD$80:$AN$91,5,FALSE)</f>
@@ -57805,7 +57861,7 @@
       </c>
       <c r="P84" s="101">
         <f t="shared" si="48"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R84" s="123">
         <f>DATE(2026,12,3)+TIME(4,0,0)+gmt_delta</f>
@@ -57821,7 +57877,7 @@
       </c>
       <c r="AD84" s="123">
         <f t="shared" si="38"/>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AE84" s="124" t="str">
         <f>J35</f>
@@ -57829,7 +57885,7 @@
       </c>
       <c r="AF84" s="123">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG84" s="123">
         <f t="shared" si="49"/>
@@ -57841,30 +57897,30 @@
       </c>
       <c r="AI84" s="123">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ84" s="123">
         <f t="shared" si="42"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK84" s="123" t="s">
         <v>3185</v>
       </c>
       <c r="AL84" s="123">
         <f t="shared" si="43"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AM84" s="123">
         <f t="shared" si="44"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN84" s="123">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AP84" s="123">
         <f>AN84/AN92*10000+AM84/AM92*1000+AI84/AI92*100+IF(AQ84=0,ROW(),AQ84)/2000000</f>
-        <v>3000.0007973900001</v>
+        <v>8522.2230196122218</v>
       </c>
       <c r="AQ84" s="126">
         <f t="shared" si="37"/>
@@ -57872,11 +57928,11 @@
       </c>
       <c r="AR84" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ACD</v>
+        <v>ABDE</v>
       </c>
       <c r="AS84" s="129" t="str">
         <f t="shared" si="46"/>
-        <v/>
+        <v>Ecuador</v>
       </c>
       <c r="AT84" s="130" t="str">
         <f>"Ⓔ "&amp;AE84</f>
@@ -57886,20 +57942,20 @@
     <row r="85" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="73"/>
       <c r="B85" s="73"/>
-      <c r="C85" s="167"/>
-      <c r="D85" s="168"/>
-      <c r="E85" s="168"/>
-      <c r="F85" s="168"/>
-      <c r="G85" s="169"/>
+      <c r="C85" s="189"/>
+      <c r="D85" s="190"/>
+      <c r="E85" s="190"/>
+      <c r="F85" s="190"/>
+      <c r="G85" s="191"/>
       <c r="H85" s="75"/>
       <c r="I85" s="69"/>
       <c r="J85" s="99" t="str">
         <f>VLOOKUP(5,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓓ Paraguay</v>
+        <v>Ⓘ Senegal</v>
       </c>
       <c r="K85" s="100">
         <f t="shared" si="47"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L85" s="100">
         <f>VLOOKUP(5,$AD$80:$AN$91,3,FALSE)</f>
@@ -57911,11 +57967,11 @@
       </c>
       <c r="N85" s="100">
         <f>VLOOKUP(5,$AD$80:$AN$91,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O85" s="100" t="str">
         <f>VLOOKUP(5,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(5,$AD$80:$AN$91,7,FALSE)</f>
-        <v>2 - 4</v>
+        <v>8 - 6</v>
       </c>
       <c r="P85" s="101">
         <f t="shared" si="48"/>
@@ -57947,7 +58003,7 @@
       </c>
       <c r="AG85" s="123">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH85" s="123">
         <f t="shared" si="40"/>
@@ -57955,11 +58011,11 @@
       </c>
       <c r="AI85" s="123">
         <f t="shared" si="41"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ85" s="123">
         <f t="shared" si="42"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK85" s="123" t="s">
         <v>3186</v>
@@ -57974,11 +58030,11 @@
       </c>
       <c r="AN85" s="123">
         <f t="shared" si="45"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP85" s="123">
         <f>AN85/AN92*10000+AM85/AM92*1000+AI85/AI92*100+IF(AQ85=0,ROW(),AQ85)/2000000</f>
-        <v>8335.715043099286</v>
+        <v>8577.7785351627772</v>
       </c>
       <c r="AQ85" s="126">
         <f t="shared" si="37"/>
@@ -57986,7 +58042,7 @@
       </c>
       <c r="AR85" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ACDF</v>
+        <v>ABDEF</v>
       </c>
       <c r="AS85" s="129" t="str">
         <f t="shared" si="46"/>
@@ -58000,16 +58056,16 @@
     <row r="86" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="73"/>
       <c r="B86" s="73"/>
-      <c r="C86" s="167"/>
-      <c r="D86" s="168"/>
-      <c r="E86" s="168"/>
-      <c r="F86" s="168"/>
-      <c r="G86" s="169"/>
+      <c r="C86" s="189"/>
+      <c r="D86" s="190"/>
+      <c r="E86" s="190"/>
+      <c r="F86" s="190"/>
+      <c r="G86" s="191"/>
       <c r="H86" s="75"/>
       <c r="I86" s="69"/>
       <c r="J86" s="99" t="str">
         <f>VLOOKUP(6,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓗ Cape Verde</v>
+        <v>Ⓛ Croatia</v>
       </c>
       <c r="K86" s="100">
         <f t="shared" si="47"/>
@@ -58017,23 +58073,23 @@
       </c>
       <c r="L86" s="100">
         <f>VLOOKUP(6,$AD$80:$AN$91,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86" s="100">
         <f>VLOOKUP(6,$AD$80:$AN$91,4,FALSE)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N86" s="100">
         <f>VLOOKUP(6,$AD$80:$AN$91,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O86" s="100" t="str">
         <f>VLOOKUP(6,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(6,$AD$80:$AN$91,7,FALSE)</f>
-        <v>2 - 2</v>
+        <v>3 - 4</v>
       </c>
       <c r="P86" s="101">
         <f t="shared" si="48"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R86" s="123">
         <f>DATE(2026,12,4)+TIME(8,0,0)+gmt_delta</f>
@@ -58049,7 +58105,7 @@
       </c>
       <c r="AD86" s="123">
         <f t="shared" si="38"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE86" s="124" t="str">
         <f>J47</f>
@@ -58092,7 +58148,7 @@
       </c>
       <c r="AP86" s="123">
         <f>AN86/AN92*10000+AM86/AM92*1000+AI86/AI92*100+IF(AQ86=0,ROW(),AQ86)/2000000</f>
-        <v>5764.2865816407148</v>
+        <v>4511.1119784661114</v>
       </c>
       <c r="AQ86" s="126">
         <f t="shared" si="37"/>
@@ -58100,11 +58156,11 @@
       </c>
       <c r="AR86" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ACDFG</v>
+        <v>ABDEF</v>
       </c>
       <c r="AS86" s="129" t="str">
         <f t="shared" si="46"/>
-        <v>Belgium</v>
+        <v/>
       </c>
       <c r="AT86" s="130" t="str">
         <f>"Ⓖ "&amp;AE86</f>
@@ -58114,40 +58170,40 @@
     <row r="87" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="73"/>
       <c r="B87" s="73"/>
-      <c r="C87" s="167"/>
-      <c r="D87" s="168"/>
-      <c r="E87" s="168"/>
-      <c r="F87" s="168"/>
-      <c r="G87" s="169"/>
+      <c r="C87" s="189"/>
+      <c r="D87" s="190"/>
+      <c r="E87" s="190"/>
+      <c r="F87" s="190"/>
+      <c r="G87" s="191"/>
       <c r="H87" s="75"/>
       <c r="I87" s="69"/>
       <c r="J87" s="99" t="str">
         <f>VLOOKUP(7,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓖ Belgium</v>
+        <v>Ⓐ Korea Republic</v>
       </c>
       <c r="K87" s="100">
         <f t="shared" si="47"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L87" s="100">
         <f>VLOOKUP(7,$AD$80:$AN$91,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M87" s="100">
         <f>VLOOKUP(7,$AD$80:$AN$91,4,FALSE)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N87" s="100">
         <f>VLOOKUP(7,$AD$80:$AN$91,5,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O87" s="100" t="str">
         <f>VLOOKUP(7,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(7,$AD$80:$AN$91,7,FALSE)</f>
-        <v>1 - 1</v>
+        <v>2 - 3</v>
       </c>
       <c r="P87" s="101">
         <f t="shared" si="48"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R87" s="123">
         <f>DATE(2026,12,4)+TIME(4,0,0)+gmt_delta</f>
@@ -58163,7 +58219,7 @@
       </c>
       <c r="AD87" s="123">
         <f t="shared" si="38"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE87" s="124" t="str">
         <f>J53</f>
@@ -58206,7 +58262,7 @@
       </c>
       <c r="AP87" s="123">
         <f>AN87/AN92*10000+AM87/AM92*1000+AI87/AI92*100+IF(AQ87=0,ROW(),AQ87)/2000000</f>
-        <v>5778.5721116364284</v>
+        <v>4522.2229052872226</v>
       </c>
       <c r="AQ87" s="126">
         <f t="shared" si="37"/>
@@ -58214,11 +58270,11 @@
       </c>
       <c r="AR87" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ACDFGH</v>
+        <v>ABDEF</v>
       </c>
       <c r="AS87" s="129" t="str">
         <f t="shared" si="46"/>
-        <v>Cape Verde</v>
+        <v/>
       </c>
       <c r="AT87" s="130" t="str">
         <f>"Ⓗ "&amp;AE87</f>
@@ -58228,16 +58284,16 @@
     <row r="88" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="73"/>
       <c r="B88" s="73"/>
-      <c r="C88" s="170"/>
-      <c r="D88" s="171"/>
-      <c r="E88" s="171"/>
-      <c r="F88" s="171"/>
-      <c r="G88" s="172"/>
+      <c r="C88" s="192"/>
+      <c r="D88" s="193"/>
+      <c r="E88" s="193"/>
+      <c r="F88" s="193"/>
+      <c r="G88" s="194"/>
       <c r="H88" s="75"/>
       <c r="I88" s="69"/>
       <c r="J88" s="99" t="str">
         <f>VLOOKUP(8,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓐ Czech Republic</v>
+        <v>Ⓙ Algeria</v>
       </c>
       <c r="K88" s="100">
         <f t="shared" si="47"/>
@@ -58245,11 +58301,11 @@
       </c>
       <c r="L88" s="100">
         <f>VLOOKUP(8,$AD$80:$AN$91,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" s="100">
         <f>VLOOKUP(8,$AD$80:$AN$91,4,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N88" s="100">
         <f>VLOOKUP(8,$AD$80:$AN$91,5,FALSE)</f>
@@ -58257,11 +58313,11 @@
       </c>
       <c r="O88" s="100" t="str">
         <f>VLOOKUP(8,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(8,$AD$80:$AN$91,7,FALSE)</f>
-        <v>2 - 3</v>
+        <v>2 - 4</v>
       </c>
       <c r="P88" s="101">
         <f t="shared" si="48"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R88" s="123">
         <f>DATE(2026,12,5)+TIME(4,0,0)+gmt_delta</f>
@@ -58277,7 +58333,7 @@
       </c>
       <c r="AD88" s="123">
         <f t="shared" si="38"/>
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AE88" s="124" t="str">
         <f>J59</f>
@@ -58285,7 +58341,7 @@
       </c>
       <c r="AF88" s="123">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG88" s="123">
         <f t="shared" si="49"/>
@@ -58297,7 +58353,7 @@
       </c>
       <c r="AI88" s="123">
         <f t="shared" si="41"/>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AJ88" s="123">
         <f t="shared" si="42"/>
@@ -58308,19 +58364,19 @@
       </c>
       <c r="AL88" s="123">
         <f t="shared" si="43"/>
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="AM88" s="123">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AN88" s="123">
         <f t="shared" si="45"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP88" s="123">
         <f>AN88/AN92*10000+AM88/AM92*1000+AI88/AI92*100+IF(AQ88=0,ROW(),AQ88)/2000000</f>
-        <v>42.857987352142857</v>
+        <v>6922.2230667172216</v>
       </c>
       <c r="AQ88" s="126">
         <f t="shared" si="37"/>
@@ -58328,11 +58384,11 @@
       </c>
       <c r="AR88" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ACDFGH</v>
+        <v>ABDEFI</v>
       </c>
       <c r="AS88" s="129" t="str">
         <f t="shared" si="46"/>
-        <v/>
+        <v>Senegal</v>
       </c>
       <c r="AT88" s="130" t="str">
         <f>"Ⓘ "&amp;AE88</f>
@@ -58351,31 +58407,31 @@
       <c r="I89" s="69"/>
       <c r="J89" s="102" t="str">
         <f>VLOOKUP(9,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓚ DR Congo</v>
+        <v>Ⓒ Scotland</v>
       </c>
       <c r="K89" s="103">
         <f t="shared" si="47"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L89" s="103">
         <f>VLOOKUP(9,$AD$80:$AN$91,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M89" s="103">
         <f>VLOOKUP(9,$AD$80:$AN$91,4,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N89" s="103">
         <f>VLOOKUP(9,$AD$80:$AN$91,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O89" s="103" t="str">
         <f>VLOOKUP(9,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(9,$AD$80:$AN$91,7,FALSE)</f>
-        <v>1 - 2</v>
+        <v>1 - 4</v>
       </c>
       <c r="P89" s="104">
         <f t="shared" si="48"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R89" s="123">
         <f>DATE(2026,12,5)+TIME(8,0,0)+gmt_delta</f>
@@ -58391,7 +58447,7 @@
       </c>
       <c r="AD89" s="123">
         <f t="shared" si="38"/>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE89" s="124" t="str">
         <f>J65</f>
@@ -58434,7 +58490,7 @@
       </c>
       <c r="AP89" s="123">
         <f>AN89/AN92*10000+AM89/AM92*1000+AI89/AI92*100+IF(AQ89=0,ROW(),AQ89)/2000000</f>
-        <v>7778.572210701428</v>
+        <v>6188.8896710188892</v>
       </c>
       <c r="AQ89" s="126">
         <f t="shared" si="37"/>
@@ -58442,7 +58498,7 @@
       </c>
       <c r="AR89" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ACDFGHJ</v>
+        <v>ABDEFIJ</v>
       </c>
       <c r="AS89" s="129" t="str">
         <f t="shared" si="46"/>
@@ -58465,7 +58521,7 @@
       <c r="I90" s="69"/>
       <c r="J90" s="102" t="str">
         <f>VLOOKUP(10,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓔ Ecuador</v>
+        <v>Ⓗ Cape Verde</v>
       </c>
       <c r="K90" s="103">
         <f t="shared" si="47"/>
@@ -58477,19 +58533,19 @@
       </c>
       <c r="M90" s="103">
         <f>VLOOKUP(10,$AD$80:$AN$91,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N90" s="103">
         <f>VLOOKUP(10,$AD$80:$AN$91,5,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O90" s="103" t="str">
         <f>VLOOKUP(10,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(10,$AD$80:$AN$91,7,FALSE)</f>
-        <v>0 - 1</v>
+        <v>2 - 2</v>
       </c>
       <c r="P90" s="104">
         <f t="shared" si="48"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R90" s="123">
         <f>DATE(2026,12,6)+TIME(4,0,0)+gmt_delta</f>
@@ -58505,7 +58561,7 @@
       </c>
       <c r="AD90" s="123">
         <f t="shared" si="38"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AE90" s="124" t="str">
         <f>J71</f>
@@ -58548,7 +58604,7 @@
       </c>
       <c r="AP90" s="123">
         <f>AN90/AN92*10000+AM90/AM92*1000+AI90/AI92*100+IF(AQ90=0,ROW(),AQ90)/2000000</f>
-        <v>3014.2864534607143</v>
+        <v>2344.4451836194448</v>
       </c>
       <c r="AQ90" s="126">
         <f t="shared" si="37"/>
@@ -58556,7 +58612,7 @@
       </c>
       <c r="AR90" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ACDFGHJ</v>
+        <v>ABDEFIJ</v>
       </c>
       <c r="AS90" s="129" t="str">
         <f t="shared" si="46"/>
@@ -58579,7 +58635,7 @@
       <c r="I91" s="69"/>
       <c r="J91" s="102" t="str">
         <f>VLOOKUP(11,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓑ Bosnia and Herzegovina</v>
+        <v>Ⓖ Belgium</v>
       </c>
       <c r="K91" s="103">
         <f t="shared" si="47"/>
@@ -58591,19 +58647,19 @@
       </c>
       <c r="M91" s="103">
         <f>VLOOKUP(11,$AD$80:$AN$91,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N91" s="103">
         <f>VLOOKUP(11,$AD$80:$AN$91,5,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O91" s="103" t="str">
         <f>VLOOKUP(11,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(11,$AD$80:$AN$91,7,FALSE)</f>
-        <v>2 - 5</v>
+        <v>1 - 1</v>
       </c>
       <c r="P91" s="104">
         <f t="shared" si="48"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R91" s="123">
         <f>DATE(2026,12,6)+TIME(8,0,0)+gmt_delta</f>
@@ -58619,7 +58675,7 @@
       </c>
       <c r="AD91" s="123">
         <f t="shared" si="38"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE91" s="124" t="str">
         <f>J77</f>
@@ -58662,7 +58718,7 @@
       </c>
       <c r="AP91" s="123">
         <f>AN91/AN92*10000+AM91/AM92*1000+AI91/AI92*100+IF(AQ91=0,ROW(),AQ91)/2000000</f>
-        <v>8042.8580013921428</v>
+        <v>6366.6675252016657</v>
       </c>
       <c r="AQ91" s="126">
         <f t="shared" si="37"/>
@@ -58670,7 +58726,7 @@
       </c>
       <c r="AR91" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ACDFGHJL</v>
+        <v>ABDEFIJL</v>
       </c>
       <c r="AS91" s="129" t="str">
         <f t="shared" si="46"/>
@@ -58693,7 +58749,7 @@
       <c r="I92" s="69"/>
       <c r="J92" s="105" t="str">
         <f>VLOOKUP(12,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓘ Senegal</v>
+        <v>Ⓚ DR Congo</v>
       </c>
       <c r="K92" s="106">
         <f t="shared" si="47"/>
@@ -58705,19 +58761,19 @@
       </c>
       <c r="M92" s="106">
         <f>VLOOKUP(12,$AD$80:$AN$91,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N92" s="106">
         <f>VLOOKUP(12,$AD$80:$AN$91,5,FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O92" s="106" t="str">
         <f>VLOOKUP(12,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(12,$AD$80:$AN$91,7,FALSE)</f>
-        <v>3 - 6</v>
+        <v>1 - 2</v>
       </c>
       <c r="P92" s="107">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF92" s="123">
         <f>MAX(AF80:AF91)+1</f>
@@ -58733,11 +58789,11 @@
       </c>
       <c r="AI92" s="123">
         <f>MAX(AI80:AI91)+1</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AJ92" s="123">
         <f>MAX(AJ80:AJ91)+1</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL92" s="123">
         <f>MIN(AL80:AL91)</f>
@@ -58745,11 +58801,11 @@
       </c>
       <c r="AM92" s="123">
         <f>MAX(AM80:AM91)+1</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AN92" s="123">
         <f>MAX(AN80:AN91)+1</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AS92" s="126" t="b">
         <f>SUM(K9:K78)=144</f>
@@ -58910,11 +58966,31 @@
   <sheetProtection algorithmName="SHA-512" hashValue="7nWuIQAsd0NKRlhwUK3tOeNHpTch5B5FULy2gxNNaIdJM5RfhFSMzPcx55y+pmM3d73guUy+p5Y+SvIjJZQRaA==" saltValue="Uw23KnM8csnTioq5H8upCA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <dataConsolidate/>
   <mergeCells count="45">
-    <mergeCell ref="BK14:BK15"/>
-    <mergeCell ref="BY16:BY17"/>
-    <mergeCell ref="BK26:BK27"/>
-    <mergeCell ref="BR28:BR29"/>
-    <mergeCell ref="BK22:BK23"/>
+    <mergeCell ref="CK68:CQ69"/>
+    <mergeCell ref="C83:G88"/>
+    <mergeCell ref="BK70:BK71"/>
+    <mergeCell ref="BY48:BY49"/>
+    <mergeCell ref="BY64:BY65"/>
+    <mergeCell ref="CF55:CF56"/>
+    <mergeCell ref="BK58:BK59"/>
+    <mergeCell ref="BR60:BR61"/>
+    <mergeCell ref="BK62:BK63"/>
+    <mergeCell ref="BK66:BK67"/>
+    <mergeCell ref="BR68:BR69"/>
+    <mergeCell ref="BK50:BK51"/>
+    <mergeCell ref="BR52:BR53"/>
+    <mergeCell ref="BK54:BK55"/>
+    <mergeCell ref="CE68:CJ69"/>
+    <mergeCell ref="CF6:CJ7"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="A5:H6"/>
+    <mergeCell ref="J5:P6"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="BR12:BR13"/>
+    <mergeCell ref="BK6:BO7"/>
+    <mergeCell ref="BR6:BV7"/>
+    <mergeCell ref="BY6:CC7"/>
     <mergeCell ref="CF23:CF24"/>
     <mergeCell ref="BK18:BK19"/>
     <mergeCell ref="BR20:BR21"/>
@@ -58930,31 +59006,11 @@
     <mergeCell ref="BK42:BK43"/>
     <mergeCell ref="CM33:CQ34"/>
     <mergeCell ref="CM37:CM38"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="BR12:BR13"/>
-    <mergeCell ref="BK6:BO7"/>
-    <mergeCell ref="BR6:BV7"/>
-    <mergeCell ref="BY6:CC7"/>
-    <mergeCell ref="CF6:CJ7"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="A5:H6"/>
-    <mergeCell ref="J5:P6"/>
-    <mergeCell ref="CK68:CQ69"/>
-    <mergeCell ref="C83:G88"/>
-    <mergeCell ref="BK70:BK71"/>
-    <mergeCell ref="BY48:BY49"/>
-    <mergeCell ref="BY64:BY65"/>
-    <mergeCell ref="CF55:CF56"/>
-    <mergeCell ref="BK58:BK59"/>
-    <mergeCell ref="BR60:BR61"/>
-    <mergeCell ref="BK62:BK63"/>
-    <mergeCell ref="BK66:BK67"/>
-    <mergeCell ref="BR68:BR69"/>
-    <mergeCell ref="BK50:BK51"/>
-    <mergeCell ref="BR52:BR53"/>
-    <mergeCell ref="BK54:BK55"/>
-    <mergeCell ref="CE68:CJ69"/>
+    <mergeCell ref="BK14:BK15"/>
+    <mergeCell ref="BY16:BY17"/>
+    <mergeCell ref="BK26:BK27"/>
+    <mergeCell ref="BR28:BR29"/>
+    <mergeCell ref="BK22:BK23"/>
   </mergeCells>
   <conditionalFormatting sqref="A7:E78">
     <cfRule type="expression" dxfId="228" priority="339">
@@ -60251,23 +60307,23 @@
     <row r="3" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B3" s="109">
         <f>MATCH(C3,C6:C500,0)</f>
-        <v>246</v>
+        <v>352</v>
       </c>
       <c r="C3" s="121" t="str">
         <f>'2026 World Cup'!AR91</f>
-        <v>ACDFGHJL</v>
+        <v>ABDEFIJL</v>
       </c>
       <c r="D3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,2,FALSE)</f>
-        <v>3C</v>
+        <v>3E</v>
       </c>
       <c r="E3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,3,FALSE)</f>
-        <v>3G</v>
+        <v>3J</v>
       </c>
       <c r="F3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,4,FALSE)</f>
-        <v>3J</v>
+        <v>3B</v>
       </c>
       <c r="G3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,5,FALSE)</f>
@@ -60287,7 +60343,7 @@
       </c>
       <c r="K3" s="122" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,9,FALSE)</f>
-        <v>3H</v>
+        <v>3I</v>
       </c>
     </row>
     <row r="5" spans="2:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">

--- a/public/worldcup.xlsx
+++ b/public/worldcup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rylanpaul/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{890E4366-911D-7E45-82FF-2F002A696F7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BD2E748-0087-A84D-9509-98B9D3790692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T" sheetId="1" state="hidden" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9891" uniqueCount="3715">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9893" uniqueCount="3715">
   <si>
     <t>English</t>
   </si>
@@ -13305,12 +13305,56 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -13391,50 +13435,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -38846,6 +38846,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(J4,Rounds!I$2:I$25,Rounds!L$2:L$25), _xlfn.XLOOKUP(J4,Rounds!L$2:L$25,Rounds!I$2:I$25))</f>
         <v>Haiti</v>
       </c>
+      <c r="N4" s="148" t="s">
+        <v>1148</v>
+      </c>
       <c r="O4" s="146" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(N4,Rounds!M$2:M$17,Rounds!N$2:N$17), _xlfn.XLOOKUP(N4,Rounds!P$2:P$17,Rounds!O$2:O$17))</f>
         <v>#N/A</v>
@@ -38854,9 +38857,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(N4,Rounds!M$2:M$17,Rounds!O$2:O$17), _xlfn.XLOOKUP(N4,Rounds!P$2:P$17,Rounds!N$2:N$17))</f>
         <v>#N/A</v>
       </c>
-      <c r="Q4" s="147" t="e">
+      <c r="Q4" s="147" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(N4,Rounds!M$2:M$17,Rounds!P$2:P$17), _xlfn.XLOOKUP(N4,Rounds!P$2:P$17,Rounds!M$2:M$17))</f>
-        <v>#N/A</v>
+        <v>DR Congo</v>
       </c>
       <c r="S4" s="146" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(R4,Rounds!Q$2:Q$9,Rounds!R$2:R$9), _xlfn.XLOOKUP(R4,Rounds!T$2:T$9,Rounds!S$2:S$9))</f>
@@ -39286,7 +39289,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(J8,Rounds!I$2:I$25,Rounds!L$2:L$25), _xlfn.XLOOKUP(J8,Rounds!L$2:L$25,Rounds!I$2:I$25))</f>
         <v>Haiti</v>
       </c>
-      <c r="N8" s="152"/>
+      <c r="N8" s="152" t="s">
+        <v>1662</v>
+      </c>
       <c r="O8" s="150" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(N8,Rounds!M$2:M$17,Rounds!N$2:N$17), _xlfn.XLOOKUP(N8,Rounds!P$2:P$17,Rounds!O$2:O$17))</f>
         <v>#N/A</v>
@@ -39295,9 +39300,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(N8,Rounds!M$2:M$17,Rounds!O$2:O$17), _xlfn.XLOOKUP(N8,Rounds!P$2:P$17,Rounds!N$2:N$17))</f>
         <v>#N/A</v>
       </c>
-      <c r="Q8" s="151" t="e">
+      <c r="Q8" s="151" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(N8,Rounds!M$2:M$17,Rounds!P$2:P$17), _xlfn.XLOOKUP(N8,Rounds!P$2:P$17,Rounds!M$2:M$17))</f>
-        <v>#N/A</v>
+        <v>South Africa</v>
       </c>
       <c r="R8" s="152"/>
       <c r="S8" s="150" t="e">
@@ -39527,7 +39532,7 @@
       </c>
       <c r="P2" s="134" t="str">
         <f>'2026 World Cup'!BL11</f>
-        <v>3rd Group A/B/C/D/F</v>
+        <v>Paraguay</v>
       </c>
       <c r="Q2" s="132" t="str">
         <f>'2026 World Cup'!BS12</f>
@@ -39645,7 +39650,7 @@
       </c>
       <c r="P3" s="134" t="str">
         <f>'2026 World Cup'!BL15</f>
-        <v>3rd Group C/D/F/G/H</v>
+        <v>Sweden</v>
       </c>
       <c r="Q3" s="132" t="str">
         <f>'2026 World Cup'!BS20</f>
@@ -39907,7 +39912,7 @@
       </c>
       <c r="M6" s="132" t="str">
         <f>'2026 World Cup'!BL26</f>
-        <v>2K</v>
+        <v>Portugal</v>
       </c>
       <c r="N6" s="81" t="e">
         <f>IF('2026 World Cup'!$BM26="",NA(),'2026 World Cup'!$BM26)</f>
@@ -39919,7 +39924,7 @@
       </c>
       <c r="P6" s="134" t="str">
         <f>'2026 World Cup'!BL27</f>
-        <v>2L</v>
+        <v>Croatia</v>
       </c>
       <c r="Q6" s="132" t="str">
         <f>'2026 World Cup'!BS44</f>
@@ -39977,7 +39982,7 @@
       </c>
       <c r="M7" s="132" t="str">
         <f>'2026 World Cup'!BL30</f>
-        <v>1H</v>
+        <v>Spain</v>
       </c>
       <c r="N7" s="81" t="e">
         <f>IF('2026 World Cup'!$BM30="",NA(),'2026 World Cup'!$BM30)</f>
@@ -39989,7 +39994,7 @@
       </c>
       <c r="P7" s="134" t="str">
         <f>'2026 World Cup'!BL31</f>
-        <v>2J</v>
+        <v>Austria</v>
       </c>
       <c r="Q7" s="132" t="str">
         <f>'2026 World Cup'!BS52</f>
@@ -40059,7 +40064,7 @@
       </c>
       <c r="P8" s="134" t="str">
         <f>'2026 World Cup'!BL35</f>
-        <v>3rd Group B/E/F/I/J</v>
+        <v>Bosnia and Herzegovina</v>
       </c>
       <c r="Q8" s="132" t="str">
         <f>'2026 World Cup'!BS60</f>
@@ -40117,7 +40122,7 @@
       </c>
       <c r="M9" s="132" t="str">
         <f>'2026 World Cup'!BL38</f>
-        <v>1G</v>
+        <v>Belgium</v>
       </c>
       <c r="N9" s="81" t="e">
         <f>IF('2026 World Cup'!$BM38="",NA(),'2026 World Cup'!$BM38)</f>
@@ -40129,7 +40134,7 @@
       </c>
       <c r="P9" s="134" t="str">
         <f>'2026 World Cup'!BL39</f>
-        <v>3rd Group A/E/H/I/J</v>
+        <v>Senegal</v>
       </c>
       <c r="Q9" s="135" t="str">
         <f>'2026 World Cup'!BS68</f>
@@ -40307,7 +40312,7 @@
       </c>
       <c r="P12" s="134" t="str">
         <f>'2026 World Cup'!BL51</f>
-        <v>3rd Group C/E/F/H/I</v>
+        <v>Ecuador</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.2">
@@ -40349,7 +40354,7 @@
       </c>
       <c r="M13" s="132" t="str">
         <f>'2026 World Cup'!BL54</f>
-        <v>1L</v>
+        <v>England</v>
       </c>
       <c r="N13" s="81" t="e">
         <f>IF('2026 World Cup'!$BM54="",NA(),'2026 World Cup'!$BM54)</f>
@@ -40361,7 +40366,7 @@
       </c>
       <c r="P13" s="134" t="str">
         <f>'2026 World Cup'!BL55</f>
-        <v>3rd Group E/H/I/J/K</v>
+        <v>DR Congo</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.2">
@@ -40403,7 +40408,7 @@
       </c>
       <c r="M14" s="132" t="str">
         <f>'2026 World Cup'!BL58</f>
-        <v>1J</v>
+        <v>Argentina</v>
       </c>
       <c r="N14" s="81" t="e">
         <f>IF('2026 World Cup'!$BM58="",NA(),'2026 World Cup'!$BM58)</f>
@@ -40415,7 +40420,7 @@
       </c>
       <c r="P14" s="134" t="str">
         <f>'2026 World Cup'!BL59</f>
-        <v>2H</v>
+        <v>Cape Verde</v>
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.2">
@@ -40469,7 +40474,7 @@
       </c>
       <c r="P15" s="134" t="str">
         <f>'2026 World Cup'!BL63</f>
-        <v>2G</v>
+        <v>Egypt</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.2">
@@ -40500,11 +40505,11 @@
       <c r="I16" s="132" t="str">
         <v>Egypt</v>
       </c>
-      <c r="J16" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K16" s="81" t="e">
-        <v>#N/A</v>
+      <c r="J16" s="81">
+        <v>1</v>
+      </c>
+      <c r="K16" s="81">
+        <v>1</v>
       </c>
       <c r="L16" s="134" t="str">
         <v>Iran</v>
@@ -40523,7 +40528,7 @@
       </c>
       <c r="P16" s="134" t="str">
         <f>'2026 World Cup'!BL67</f>
-        <v>3rd Group E/F/G/I/J</v>
+        <v>Algeria</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.2">
@@ -40554,18 +40559,18 @@
       <c r="I17" s="132" t="str">
         <v>New Zealand</v>
       </c>
-      <c r="J17" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K17" s="81" t="e">
-        <v>#N/A</v>
+      <c r="J17" s="81">
+        <v>1</v>
+      </c>
+      <c r="K17" s="81">
+        <v>5</v>
       </c>
       <c r="L17" s="134" t="str">
         <v>Belgium</v>
       </c>
       <c r="M17" s="135" t="str">
         <f>'2026 World Cup'!BL70</f>
-        <v>1K</v>
+        <v>Colombia</v>
       </c>
       <c r="N17" s="153" t="e">
         <f>IF('2026 World Cup'!$BM70="",NA(),'2026 World Cup'!$BM70)</f>
@@ -40577,7 +40582,7 @@
       </c>
       <c r="P17" s="136" t="str">
         <f>'2026 World Cup'!BL71</f>
-        <v>3rd Group D/E/I/J/L</v>
+        <v>Ghana</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.2">
@@ -40608,11 +40613,11 @@
       <c r="I18" s="132" t="str">
         <v>Cape Verde</v>
       </c>
-      <c r="J18" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K18" s="81" t="e">
-        <v>#N/A</v>
+      <c r="J18" s="81">
+        <v>0</v>
+      </c>
+      <c r="K18" s="81">
+        <v>0</v>
       </c>
       <c r="L18" s="134" t="str">
         <v>Saudi Arabia</v>
@@ -40646,11 +40651,11 @@
       <c r="I19" s="132" t="str">
         <v>Uruguay</v>
       </c>
-      <c r="J19" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K19" s="81" t="e">
-        <v>#N/A</v>
+      <c r="J19" s="81">
+        <v>0</v>
+      </c>
+      <c r="K19" s="81">
+        <v>1</v>
       </c>
       <c r="L19" s="134" t="str">
         <v>Spain</v>
@@ -40684,11 +40689,11 @@
       <c r="I20" s="132" t="str">
         <v>Panama</v>
       </c>
-      <c r="J20" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K20" s="81" t="e">
-        <v>#N/A</v>
+      <c r="J20" s="81">
+        <v>0</v>
+      </c>
+      <c r="K20" s="81">
+        <v>2</v>
       </c>
       <c r="L20" s="134" t="str">
         <v>England</v>
@@ -40722,11 +40727,11 @@
       <c r="I21" s="132" t="str">
         <v>Croatia</v>
       </c>
-      <c r="J21" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K21" s="81" t="e">
-        <v>#N/A</v>
+      <c r="J21" s="81">
+        <v>2</v>
+      </c>
+      <c r="K21" s="81">
+        <v>1</v>
       </c>
       <c r="L21" s="134" t="str">
         <v>Ghana</v>
@@ -40760,11 +40765,11 @@
       <c r="I22" s="132" t="str">
         <v>Algeria</v>
       </c>
-      <c r="J22" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K22" s="81" t="e">
-        <v>#N/A</v>
+      <c r="J22" s="81">
+        <v>3</v>
+      </c>
+      <c r="K22" s="81">
+        <v>3</v>
       </c>
       <c r="L22" s="134" t="str">
         <v>Austria</v>
@@ -40798,11 +40803,11 @@
       <c r="I23" s="132" t="str">
         <v>Jordan</v>
       </c>
-      <c r="J23" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K23" s="81" t="e">
-        <v>#N/A</v>
+      <c r="J23" s="81">
+        <v>1</v>
+      </c>
+      <c r="K23" s="81">
+        <v>3</v>
       </c>
       <c r="L23" s="134" t="str">
         <v>Argentina</v>
@@ -40836,11 +40841,11 @@
       <c r="I24" s="132" t="str">
         <v>Colombia</v>
       </c>
-      <c r="J24" s="81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K24" s="81" t="e">
-        <v>#N/A</v>
+      <c r="J24" s="81">
+        <v>0</v>
+      </c>
+      <c r="K24" s="81">
+        <v>0</v>
       </c>
       <c r="L24" s="134" t="str">
         <v>Portugal</v>
@@ -40874,11 +40879,11 @@
       <c r="I25" s="135" t="str">
         <v>DR Congo</v>
       </c>
-      <c r="J25" s="153" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K25" s="153" t="e">
-        <v>#N/A</v>
+      <c r="J25" s="153">
+        <v>3</v>
+      </c>
+      <c r="K25" s="153">
+        <v>1</v>
       </c>
       <c r="L25" s="136" t="str">
         <v>Uzbekistan</v>
@@ -40964,25 +40969,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:95" ht="47" x14ac:dyDescent="0.2">
-      <c r="A1" s="171" t="str" cm="1">
+      <c r="A1" s="182" t="str" cm="1">
         <f t="array" ref="A1">INDEX(T,2,lang)</f>
         <v>2026 World Cup Final Tournament Schedule</v>
       </c>
-      <c r="B1" s="171"/>
-      <c r="C1" s="171"/>
-      <c r="D1" s="171"/>
-      <c r="E1" s="171"/>
-      <c r="F1" s="171"/>
-      <c r="G1" s="171"/>
-      <c r="H1" s="171"/>
-      <c r="I1" s="171"/>
-      <c r="J1" s="171"/>
-      <c r="K1" s="171"/>
-      <c r="L1" s="171"/>
-      <c r="M1" s="171"/>
-      <c r="N1" s="171"/>
-      <c r="O1" s="171"/>
-      <c r="P1" s="171"/>
+      <c r="B1" s="182"/>
+      <c r="C1" s="182"/>
+      <c r="D1" s="182"/>
+      <c r="E1" s="182"/>
+      <c r="F1" s="182"/>
+      <c r="G1" s="182"/>
+      <c r="H1" s="182"/>
+      <c r="I1" s="182"/>
+      <c r="J1" s="182"/>
+      <c r="K1" s="182"/>
+      <c r="L1" s="182"/>
+      <c r="M1" s="182"/>
+      <c r="N1" s="182"/>
+      <c r="O1" s="182"/>
+      <c r="P1" s="182"/>
       <c r="S1" s="123"/>
       <c r="T1" s="123"/>
       <c r="AC1" s="123"/>
@@ -41029,11 +41034,11 @@
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
-      <c r="O3" s="172" t="str">
+      <c r="O3" s="183" t="str">
         <f>"Language: " &amp; Settings!C4</f>
         <v>Language: English</v>
       </c>
-      <c r="P3" s="172"/>
+      <c r="P3" s="183"/>
       <c r="S3" s="123"/>
       <c r="T3" s="123"/>
       <c r="AC3" s="123"/>
@@ -41051,43 +41056,43 @@
     </row>
     <row r="4" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:95" x14ac:dyDescent="0.2">
-      <c r="A5" s="173" t="str" cm="1">
+      <c r="A5" s="184" t="str" cm="1">
         <f t="array" ref="A5">INDEX(T,3,lang)</f>
         <v>Group Stage</v>
       </c>
-      <c r="B5" s="174"/>
-      <c r="C5" s="174"/>
-      <c r="D5" s="174"/>
-      <c r="E5" s="174"/>
-      <c r="F5" s="174"/>
-      <c r="G5" s="174"/>
-      <c r="H5" s="175"/>
-      <c r="J5" s="179" t="s">
+      <c r="B5" s="185"/>
+      <c r="C5" s="185"/>
+      <c r="D5" s="185"/>
+      <c r="E5" s="185"/>
+      <c r="F5" s="185"/>
+      <c r="G5" s="185"/>
+      <c r="H5" s="186"/>
+      <c r="J5" s="190" t="s">
         <v>3166</v>
       </c>
-      <c r="K5" s="180"/>
-      <c r="L5" s="180"/>
-      <c r="M5" s="180"/>
-      <c r="N5" s="180"/>
-      <c r="O5" s="180"/>
-      <c r="P5" s="181"/>
+      <c r="K5" s="191"/>
+      <c r="L5" s="191"/>
+      <c r="M5" s="191"/>
+      <c r="N5" s="191"/>
+      <c r="O5" s="191"/>
+      <c r="P5" s="192"/>
     </row>
     <row r="6" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="176"/>
-      <c r="B6" s="177"/>
-      <c r="C6" s="177"/>
-      <c r="D6" s="177"/>
-      <c r="E6" s="177"/>
-      <c r="F6" s="177"/>
-      <c r="G6" s="177"/>
-      <c r="H6" s="178"/>
-      <c r="J6" s="182"/>
-      <c r="K6" s="183"/>
-      <c r="L6" s="183"/>
-      <c r="M6" s="183"/>
-      <c r="N6" s="183"/>
-      <c r="O6" s="183"/>
-      <c r="P6" s="184"/>
+      <c r="A6" s="187"/>
+      <c r="B6" s="188"/>
+      <c r="C6" s="188"/>
+      <c r="D6" s="188"/>
+      <c r="E6" s="188"/>
+      <c r="F6" s="188"/>
+      <c r="G6" s="188"/>
+      <c r="H6" s="189"/>
+      <c r="J6" s="193"/>
+      <c r="K6" s="194"/>
+      <c r="L6" s="194"/>
+      <c r="M6" s="194"/>
+      <c r="N6" s="194"/>
+      <c r="O6" s="194"/>
+      <c r="P6" s="195"/>
       <c r="R6" s="123" t="s">
         <v>3167</v>
       </c>
@@ -41197,37 +41202,37 @@
       <c r="BI6" s="128" t="s">
         <v>3178</v>
       </c>
-      <c r="BK6" s="165" t="s">
+      <c r="BK6" s="176" t="s">
         <v>3179</v>
       </c>
-      <c r="BL6" s="166"/>
-      <c r="BM6" s="166"/>
-      <c r="BN6" s="166"/>
-      <c r="BO6" s="167"/>
-      <c r="BR6" s="165" t="str" cm="1">
+      <c r="BL6" s="177"/>
+      <c r="BM6" s="177"/>
+      <c r="BN6" s="177"/>
+      <c r="BO6" s="178"/>
+      <c r="BR6" s="176" t="str" cm="1">
         <f t="array" ref="BR6">INDEX(T,4,lang)</f>
         <v>Round of 16</v>
       </c>
-      <c r="BS6" s="166"/>
-      <c r="BT6" s="166"/>
-      <c r="BU6" s="166"/>
-      <c r="BV6" s="167"/>
-      <c r="BY6" s="165" t="str" cm="1">
+      <c r="BS6" s="177"/>
+      <c r="BT6" s="177"/>
+      <c r="BU6" s="177"/>
+      <c r="BV6" s="178"/>
+      <c r="BY6" s="176" t="str" cm="1">
         <f t="array" ref="BY6">INDEX(T,5,lang)</f>
         <v>Quarterfinals</v>
       </c>
-      <c r="BZ6" s="166"/>
-      <c r="CA6" s="166"/>
-      <c r="CB6" s="166"/>
-      <c r="CC6" s="167"/>
-      <c r="CF6" s="165" t="str" cm="1">
+      <c r="BZ6" s="177"/>
+      <c r="CA6" s="177"/>
+      <c r="CB6" s="177"/>
+      <c r="CC6" s="178"/>
+      <c r="CF6" s="176" t="str" cm="1">
         <f t="array" ref="CF6">INDEX(T,6,lang)</f>
         <v>Semi-Finals</v>
       </c>
-      <c r="CG6" s="166"/>
-      <c r="CH6" s="166"/>
-      <c r="CI6" s="166"/>
-      <c r="CJ6" s="167"/>
+      <c r="CG6" s="177"/>
+      <c r="CH6" s="177"/>
+      <c r="CI6" s="177"/>
+      <c r="CJ6" s="178"/>
     </row>
     <row r="7" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="11">
@@ -41304,26 +41309,26 @@
         <v>1</v>
       </c>
       <c r="AY7" s="126"/>
-      <c r="BK7" s="168"/>
-      <c r="BL7" s="169"/>
-      <c r="BM7" s="169"/>
-      <c r="BN7" s="169"/>
-      <c r="BO7" s="170"/>
-      <c r="BR7" s="168"/>
-      <c r="BS7" s="169"/>
-      <c r="BT7" s="169"/>
-      <c r="BU7" s="169"/>
-      <c r="BV7" s="170"/>
-      <c r="BY7" s="168"/>
-      <c r="BZ7" s="169"/>
-      <c r="CA7" s="169"/>
-      <c r="CB7" s="169"/>
-      <c r="CC7" s="170"/>
-      <c r="CF7" s="168"/>
-      <c r="CG7" s="169"/>
-      <c r="CH7" s="169"/>
-      <c r="CI7" s="169"/>
-      <c r="CJ7" s="170"/>
+      <c r="BK7" s="179"/>
+      <c r="BL7" s="180"/>
+      <c r="BM7" s="180"/>
+      <c r="BN7" s="180"/>
+      <c r="BO7" s="181"/>
+      <c r="BR7" s="179"/>
+      <c r="BS7" s="180"/>
+      <c r="BT7" s="180"/>
+      <c r="BU7" s="180"/>
+      <c r="BV7" s="181"/>
+      <c r="BY7" s="179"/>
+      <c r="BZ7" s="180"/>
+      <c r="CA7" s="180"/>
+      <c r="CB7" s="180"/>
+      <c r="CC7" s="181"/>
+      <c r="CF7" s="179"/>
+      <c r="CG7" s="180"/>
+      <c r="CH7" s="180"/>
+      <c r="CI7" s="180"/>
+      <c r="CJ7" s="181"/>
     </row>
     <row r="8" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A8" s="16">
@@ -42059,7 +42064,7 @@
         <f>BH10/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK10" s="163">
+      <c r="BK10" s="173">
         <v>74</v>
       </c>
       <c r="BL10" s="24" t="str">
@@ -42322,10 +42327,10 @@
         <f>BH11/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK11" s="164"/>
+      <c r="BK11" s="174"/>
       <c r="BL11" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!G3,AK80:AS91,9,FALSE),"3rd Group A/B/C/D/F")</f>
-        <v>3rd Group A/B/C/D/F</v>
+        <v>Paraguay</v>
       </c>
       <c r="BM11" s="62"/>
       <c r="BN11" s="64"/>
@@ -42560,7 +42565,7 @@
       <c r="BO12" s="21"/>
       <c r="BP12" s="114"/>
       <c r="BQ12" s="112"/>
-      <c r="BR12" s="163">
+      <c r="BR12" s="173">
         <v>89</v>
       </c>
       <c r="BS12" s="24" t="str">
@@ -42681,7 +42686,7 @@
         <v>46203.875</v>
       </c>
       <c r="BQ13" s="115"/>
-      <c r="BR13" s="164"/>
+      <c r="BR13" s="174"/>
       <c r="BS13" s="26" t="str">
         <f>IF(BP14&gt;BP15,BL14,IF(BP14&lt;BP15,BL15,""))</f>
         <v/>
@@ -42939,7 +42944,7 @@
         <f>BH14/BH18</f>
         <v>0.98058252427184467</v>
       </c>
-      <c r="BK14" s="163">
+      <c r="BK14" s="173">
         <v>77</v>
       </c>
       <c r="BL14" s="24" t="str">
@@ -43206,10 +43211,10 @@
         <f>BH15/BH18</f>
         <v>0.98058252427184467</v>
       </c>
-      <c r="BK15" s="164"/>
+      <c r="BK15" s="174"/>
       <c r="BL15" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!I3,AK80:AS91,9,FALSE),"3rd Group C/D/F/G/H")</f>
-        <v>3rd Group C/D/F/G/H</v>
+        <v>Sweden</v>
       </c>
       <c r="BM15" s="62"/>
       <c r="BN15" s="64"/>
@@ -43480,7 +43485,7 @@
       <c r="BV16" s="21"/>
       <c r="BW16" s="114"/>
       <c r="BX16" s="112"/>
-      <c r="BY16" s="163">
+      <c r="BY16" s="173">
         <v>97</v>
       </c>
       <c r="BZ16" s="24" t="str">
@@ -43742,7 +43747,7 @@
       <c r="BV17" s="21"/>
       <c r="BW17" s="114"/>
       <c r="BX17" s="115"/>
-      <c r="BY17" s="164"/>
+      <c r="BY17" s="174"/>
       <c r="BZ17" s="26" t="str">
         <f>IF(BW20&gt;BW21,BS20,IF(BW20&lt;BW21,BS21,""))</f>
         <v/>
@@ -43946,7 +43951,7 @@
         <f>MAX(BH14:BH17)+1</f>
         <v>51.5</v>
       </c>
-      <c r="BK18" s="163">
+      <c r="BK18" s="173">
         <v>73</v>
       </c>
       <c r="BL18" s="24" t="str">
@@ -44024,27 +44029,27 @@
       </c>
       <c r="U19" s="123">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="123">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19" s="123">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" s="123">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19" s="123">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z19" s="123">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA19" s="123">
         <f t="shared" si="5"/>
@@ -44054,7 +44059,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BK19" s="164"/>
+      <c r="BK19" s="174"/>
       <c r="BL19" s="26" t="str">
         <f>AS15</f>
         <v>Canada</v>
@@ -44332,7 +44337,7 @@
       <c r="BO20" s="21"/>
       <c r="BP20" s="114"/>
       <c r="BQ20" s="112"/>
-      <c r="BR20" s="163">
+      <c r="BR20" s="173">
         <v>90</v>
       </c>
       <c r="BS20" s="24" t="str">
@@ -44605,7 +44610,7 @@
         <v>46203.041666666672</v>
       </c>
       <c r="BQ21" s="115"/>
-      <c r="BR21" s="164"/>
+      <c r="BR21" s="174"/>
       <c r="BS21" s="26" t="str">
         <f>IF(BP22&gt;BP23,BL22,IF(BP22&lt;BP23,BL23,""))</f>
         <v/>
@@ -44709,27 +44714,27 @@
       </c>
       <c r="U22" s="123">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="123">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W22" s="123">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22" s="123">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y22" s="123">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z22" s="123">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA22" s="123">
         <f t="shared" si="5"/>
@@ -44859,7 +44864,7 @@
         <f>BH22/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK22" s="163">
+      <c r="BK22" s="173">
         <v>75</v>
       </c>
       <c r="BL22" s="24" t="str">
@@ -45123,7 +45128,7 @@
         <f>BH23/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK23" s="164"/>
+      <c r="BK23" s="174"/>
       <c r="BL23" s="26" t="str">
         <f>AS21</f>
         <v>Morocco</v>
@@ -45150,7 +45155,7 @@
       <c r="CC23" s="21"/>
       <c r="CD23" s="114"/>
       <c r="CE23" s="112"/>
-      <c r="CF23" s="163">
+      <c r="CF23" s="173">
         <v>101</v>
       </c>
       <c r="CG23" s="24" t="str">
@@ -45371,7 +45376,7 @@
       <c r="CC24" s="21"/>
       <c r="CD24" s="114"/>
       <c r="CE24" s="115"/>
-      <c r="CF24" s="164"/>
+      <c r="CF24" s="174"/>
       <c r="CG24" s="26" t="str">
         <f>IF(CD32&gt;CD33,BZ32,IF(CD32&lt;CD33,BZ33,""))</f>
         <v/>
@@ -45724,12 +45729,12 @@
         <f>BH26/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK26" s="163">
+      <c r="BK26" s="173">
         <v>83</v>
       </c>
       <c r="BL26" s="24" t="str">
         <f>AS69</f>
-        <v>2K</v>
+        <v>Portugal</v>
       </c>
       <c r="BM26" s="61"/>
       <c r="BN26" s="63"/>
@@ -45992,10 +45997,10 @@
         <f>BH27/BH30</f>
         <v>0.98039215686274506</v>
       </c>
-      <c r="BK27" s="164"/>
+      <c r="BK27" s="174"/>
       <c r="BL27" s="26" t="str">
         <f>AS75</f>
-        <v>2L</v>
+        <v>Croatia</v>
       </c>
       <c r="BM27" s="62"/>
       <c r="BN27" s="64"/>
@@ -46267,7 +46272,7 @@
       <c r="BO28" s="21"/>
       <c r="BP28" s="114"/>
       <c r="BQ28" s="112"/>
-      <c r="BR28" s="163">
+      <c r="BR28" s="173">
         <v>93</v>
       </c>
       <c r="BS28" s="24" t="str">
@@ -46532,7 +46537,7 @@
         <v>46205.791666666672</v>
       </c>
       <c r="BQ29" s="115"/>
-      <c r="BR29" s="164"/>
+      <c r="BR29" s="174"/>
       <c r="BS29" s="26" t="str">
         <f>IF(BP30&gt;BP31,BL30,IF(BP30&lt;BP31,BL31,""))</f>
         <v/>
@@ -46746,12 +46751,12 @@
         <f>MAX(BH26:BH29)+1</f>
         <v>51</v>
       </c>
-      <c r="BK30" s="163">
+      <c r="BK30" s="173">
         <v>84</v>
       </c>
       <c r="BL30" s="24" t="str">
         <f>AS50</f>
-        <v>1H</v>
+        <v>Spain</v>
       </c>
       <c r="BM30" s="61"/>
       <c r="BN30" s="63"/>
@@ -46857,10 +46862,10 @@
         <f>IF(OR(F31="",G31=""),"",IF(F31&gt;G31,1,IF(F31&lt;G31,-1,0)))</f>
         <v>0</v>
       </c>
-      <c r="BK31" s="164"/>
+      <c r="BK31" s="174"/>
       <c r="BL31" s="26" t="str">
         <f>AS63</f>
-        <v>2J</v>
+        <v>Austria</v>
       </c>
       <c r="BM31" s="62"/>
       <c r="BN31" s="64"/>
@@ -47133,7 +47138,7 @@
       <c r="BV32" s="21"/>
       <c r="BW32" s="114"/>
       <c r="BX32" s="112"/>
-      <c r="BY32" s="163">
+      <c r="BY32" s="173">
         <v>98</v>
       </c>
       <c r="BZ32" s="24" t="str">
@@ -47397,7 +47402,7 @@
       <c r="BV33" s="21"/>
       <c r="BW33" s="114"/>
       <c r="BX33" s="115"/>
-      <c r="BY33" s="164"/>
+      <c r="BY33" s="174"/>
       <c r="BZ33" s="26" t="str">
         <f>IF(BW36&gt;BW37,BS36,IF(BW36&lt;BW37,BS37,""))</f>
         <v/>
@@ -47412,14 +47417,14 @@
       <c r="CE33" s="112"/>
       <c r="CK33" s="114"/>
       <c r="CL33" s="112"/>
-      <c r="CM33" s="165" t="str" cm="1">
+      <c r="CM33" s="176" t="str" cm="1">
         <f t="array" ref="CM33">INDEX(T,8,lang)</f>
         <v>Final</v>
       </c>
-      <c r="CN33" s="166"/>
-      <c r="CO33" s="166"/>
-      <c r="CP33" s="166"/>
-      <c r="CQ33" s="167"/>
+      <c r="CN33" s="177"/>
+      <c r="CO33" s="177"/>
+      <c r="CP33" s="177"/>
+      <c r="CQ33" s="178"/>
     </row>
     <row r="34" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A34" s="16">
@@ -47643,7 +47648,7 @@
         <f>BH34/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK34" s="163">
+      <c r="BK34" s="173">
         <v>81</v>
       </c>
       <c r="BL34" s="24" t="str">
@@ -47674,11 +47679,11 @@
       <c r="CE34" s="112"/>
       <c r="CK34" s="114"/>
       <c r="CL34" s="112"/>
-      <c r="CM34" s="168"/>
-      <c r="CN34" s="169"/>
-      <c r="CO34" s="169"/>
-      <c r="CP34" s="169"/>
-      <c r="CQ34" s="170"/>
+      <c r="CM34" s="179"/>
+      <c r="CN34" s="180"/>
+      <c r="CO34" s="180"/>
+      <c r="CP34" s="180"/>
+      <c r="CQ34" s="181"/>
     </row>
     <row r="35" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A35" s="16">
@@ -47902,10 +47907,10 @@
         <f>BH35/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK35" s="164"/>
+      <c r="BK35" s="174"/>
       <c r="BL35" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!F3,AK80:AS91,9,FALSE),"3rd Group B/E/F/I/J")</f>
-        <v>3rd Group B/E/F/I/J</v>
+        <v>Bosnia and Herzegovina</v>
       </c>
       <c r="BM35" s="62"/>
       <c r="BN35" s="64"/>
@@ -48131,7 +48136,7 @@
       <c r="BO36" s="21"/>
       <c r="BP36" s="114"/>
       <c r="BQ36" s="112"/>
-      <c r="BR36" s="163">
+      <c r="BR36" s="173">
         <v>94</v>
       </c>
       <c r="BS36" s="24" t="str">
@@ -48255,7 +48260,7 @@
         <v>46204.833333333336</v>
       </c>
       <c r="BQ37" s="115"/>
-      <c r="BR37" s="164"/>
+      <c r="BR37" s="174"/>
       <c r="BS37" s="26" t="str">
         <f>IF(BP38&gt;BP39,BL38,IF(BP38&lt;BP39,BL39,""))</f>
         <v/>
@@ -48282,7 +48287,7 @@
       <c r="CJ37" s="21"/>
       <c r="CK37" s="114"/>
       <c r="CL37" s="112"/>
-      <c r="CM37" s="163">
+      <c r="CM37" s="173">
         <v>104</v>
       </c>
       <c r="CN37" s="24" t="str">
@@ -48523,12 +48528,12 @@
         <f>BH38/BH42</f>
         <v>0</v>
       </c>
-      <c r="BK38" s="163">
+      <c r="BK38" s="173">
         <v>82</v>
       </c>
       <c r="BL38" s="24" t="str">
         <f>AS44</f>
-        <v>1G</v>
+        <v>Belgium</v>
       </c>
       <c r="BM38" s="61"/>
       <c r="BN38" s="63"/>
@@ -48553,7 +48558,7 @@
       <c r="CI38" s="21"/>
       <c r="CJ38" s="21"/>
       <c r="CL38" s="115"/>
-      <c r="CM38" s="164"/>
+      <c r="CM38" s="174"/>
       <c r="CN38" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG55,IF(CK55&lt;CK56,CG56,""))</f>
         <v/>
@@ -48792,10 +48797,10 @@
         <f>BH39/BH42</f>
         <v>0</v>
       </c>
-      <c r="BK39" s="164"/>
+      <c r="BK39" s="174"/>
       <c r="BL39" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!H3,AK80:AS91,9,FALSE),"3rd Group A/E/H/I/J")</f>
-        <v>3rd Group A/E/H/I/J</v>
+        <v>Senegal</v>
       </c>
       <c r="BM39" s="62"/>
       <c r="BN39" s="64"/>
@@ -49480,7 +49485,7 @@
         <f>MAX(BH38:BH41)+1</f>
         <v>1</v>
       </c>
-      <c r="BK42" s="163">
+      <c r="BK42" s="173">
         <v>76</v>
       </c>
       <c r="BL42" s="24" t="str">
@@ -49547,27 +49552,27 @@
       </c>
       <c r="U43" s="123">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V43" s="123">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W43" s="123">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X43" s="123">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y43" s="123">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z43" s="123">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA43" s="123">
         <f t="shared" si="17"/>
@@ -49577,7 +49582,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BK43" s="164"/>
+      <c r="BK43" s="174"/>
       <c r="BL43" s="26" t="str">
         <f>AS39</f>
         <v>Japan</v>
@@ -49708,7 +49713,7 @@
       </c>
       <c r="AD44" s="123">
         <f>COUNTIF(AR44:AR47,CONCATENATE("&gt;=",AR44))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE44" s="124" t="str">
         <f>VLOOKUP("Belgium",T,lang,FALSE)</f>
@@ -49716,7 +49721,7 @@
       </c>
       <c r="AF44" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE44 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG44" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE44 &amp; "_draw")</f>
@@ -49728,31 +49733,31 @@
       </c>
       <c r="AI44" s="123">
         <f>SUMIF($E$7:$E$78,$AE44,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE44,$G$7:$G$78)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AJ44" s="123">
         <f>SUMIF($E$7:$E$78,$AE44,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE44,$F$7:$F$78)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL44" s="123">
         <f>AI44-AJ44</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AM44" s="123">
         <f>AL44-AL48</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AN44" s="123">
         <f>AF44*3+AG44</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AO44" s="123">
         <f>AN44/AN48*10+BA44</f>
-        <v>4.9803921568627452</v>
+        <v>9.3139158576051777</v>
       </c>
       <c r="AP44" s="123">
         <f>AO44*10000000+BI44*100+AM44/AM48*10+AI44/AI48*1++IF(AQ44=0,ROW(),AQ44)/2000000</f>
-        <v>49804023.808710493</v>
+        <v>93139266.583223492</v>
       </c>
       <c r="AQ44" s="126">
         <f>VLOOKUP(AE44,db_fifarank,2,FALSE)</f>
@@ -49760,11 +49765,11 @@
       </c>
       <c r="AR44" s="125">
         <f>AP44/AP48</f>
-        <v>0.62255022134039661</v>
+        <v>0.99999998926338995</v>
       </c>
       <c r="AS44" s="125" t="str">
         <f>IF(SUM(AF44:AH47)=12,J45,"1G")</f>
-        <v>1G</v>
+        <v>Belgium</v>
       </c>
       <c r="AT44" s="126" cm="1">
         <f t="array" ref="AT44">SUMPRODUCT(($S$7:$S$78=AE44&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE44&amp;"_win")*($U$7:$U$78))</f>
@@ -49776,11 +49781,11 @@
       </c>
       <c r="AV44" s="126" cm="1">
         <f t="array" ref="AV44">SUMPRODUCT(($E$7:$E$78=AE44)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE44)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW44" s="126" cm="1">
         <f t="array" ref="AW44">SUMPRODUCT(($E$7:$E$78=AE44)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE44)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX44" s="126">
         <f>AV44-AW44</f>
@@ -49792,11 +49797,11 @@
       </c>
       <c r="AZ44" s="126">
         <f>AT44/AT48*1000+AU44/AU48*100+AY44/AY48*10+AV44/AV48</f>
-        <v>50</v>
+        <v>50.5</v>
       </c>
       <c r="BA44" s="126">
         <f>AZ44/AZ48</f>
-        <v>0.98039215686274506</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BB44" s="126" cm="1">
         <f t="array" ref="BB44">SUMPRODUCT(($S$7:$S$78=AE44&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE44&amp;"_win")*($X$7:$X$78))</f>
@@ -49808,11 +49813,11 @@
       </c>
       <c r="BD44" s="126" cm="1">
         <f t="array" ref="BD44">SUMPRODUCT(($E$7:$E$78=AE44)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE44)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE44" s="126" cm="1">
         <f t="array" ref="BE44">SUMPRODUCT(($E$7:$E$78=AE44)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE44)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF44" s="126">
         <f>BD44-BE44</f>
@@ -49824,11 +49829,11 @@
       </c>
       <c r="BH44" s="126">
         <f>BB44/BB48*1000+BC44/BC48*100+BG44/BG48*10+BD44/BD48</f>
-        <v>50</v>
+        <v>50.5</v>
       </c>
       <c r="BI44" s="126">
         <f>BH44/BH48</f>
-        <v>0.98039215686274506</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BK44" s="21"/>
       <c r="BL44" s="21"/>
@@ -49837,7 +49842,7 @@
       <c r="BO44" s="21"/>
       <c r="BP44" s="114"/>
       <c r="BQ44" s="112"/>
-      <c r="BR44" s="163">
+      <c r="BR44" s="173">
         <v>91</v>
       </c>
       <c r="BS44" s="24" t="str">
@@ -49852,14 +49857,14 @@
         <v/>
       </c>
       <c r="CK44" s="114"/>
-      <c r="CM44" s="165" t="str" cm="1">
+      <c r="CM44" s="176" t="str" cm="1">
         <f t="array" ref="CM44">INDEX(T,7,lang)</f>
         <v>Third-Place Play-Off</v>
       </c>
-      <c r="CN44" s="166"/>
-      <c r="CO44" s="166"/>
-      <c r="CP44" s="166"/>
-      <c r="CQ44" s="167"/>
+      <c r="CN44" s="177"/>
+      <c r="CO44" s="177"/>
+      <c r="CP44" s="177"/>
+      <c r="CQ44" s="178"/>
     </row>
     <row r="45" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="16">
@@ -49893,11 +49898,11 @@
       </c>
       <c r="J45" s="30" t="str">
         <f>VLOOKUP(1,AD44:AN47,2,FALSE)</f>
-        <v>Egypt</v>
+        <v>Belgium</v>
       </c>
       <c r="K45" s="31">
         <f>L45+M45+N45</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L45" s="31">
         <f>VLOOKUP(1,AD44:AN47,3,FALSE)</f>
@@ -49905,7 +49910,7 @@
       </c>
       <c r="M45" s="31">
         <f>VLOOKUP(1,AD44:AN47,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N45" s="31">
         <f>VLOOKUP(1,AD44:AN47,5,FALSE)</f>
@@ -49913,11 +49918,11 @@
       </c>
       <c r="O45" s="31" t="str">
         <f>VLOOKUP(1,AD44:AN47,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD44:AN47,7,FALSE)</f>
-        <v>4 - 2</v>
+        <v>6 - 2</v>
       </c>
       <c r="P45" s="32">
         <f>L45*3+M45</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R45" s="123">
         <f>DATE(2026,6,21)+TIME(8,0,0)+gmt_delta</f>
@@ -49933,7 +49938,7 @@
       </c>
       <c r="U45" s="123">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V45" s="123">
         <f t="shared" si="3"/>
@@ -49945,7 +49950,7 @@
       </c>
       <c r="X45" s="123">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y45" s="123">
         <f t="shared" si="10"/>
@@ -49965,7 +49970,7 @@
       </c>
       <c r="AD45" s="123">
         <f>COUNTIF(AR44:AR47,CONCATENATE("&gt;=",AR45))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE45" s="124" t="str">
         <f>VLOOKUP("Egypt",T,lang,FALSE)</f>
@@ -49977,7 +49982,7 @@
       </c>
       <c r="AG45" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE45 &amp; "_draw")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH45" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE45 &amp; "_lose")</f>
@@ -49985,11 +49990,11 @@
       </c>
       <c r="AI45" s="123">
         <f>SUMIF($E$7:$E$78,$AE45,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE45,$G$7:$G$78)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ45" s="123">
         <f>SUMIF($E$7:$E$78,$AE45,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE45,$F$7:$F$78)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL45" s="123">
         <f>AI45-AJ45</f>
@@ -49997,19 +50002,19 @@
       </c>
       <c r="AM45" s="123">
         <f>AL45-AL48</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AN45" s="123">
         <f>AF45*3+AG45</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO45" s="123">
         <f>AN45/AN48*10+BA45</f>
-        <v>8</v>
+        <v>9.3139158576051777</v>
       </c>
       <c r="AP45" s="123">
         <f>AO45*10000000+BI45*100+AM45/AM48*10+AI45/AI48*1++IF(AQ45=0,ROW(),AQ45)/2000000</f>
-        <v>80000008.800781623</v>
+        <v>93139264.622098804</v>
       </c>
       <c r="AQ45" s="126">
         <f>VLOOKUP(AE45,db_fifarank,2,FALSE)</f>
@@ -50017,11 +50022,11 @@
       </c>
       <c r="AR45" s="125">
         <f>AP45/AP48</f>
-        <v>0.99999998750000152</v>
+        <v>0.99999996820755876</v>
       </c>
       <c r="AS45" s="125" t="str">
         <f>IF(SUM(AF44:AH47)=12,J46,"2G")</f>
-        <v>2G</v>
+        <v>Egypt</v>
       </c>
       <c r="AT45" s="126" cm="1">
         <f t="array" ref="AT45">SUMPRODUCT(($S$7:$S$78=AE45&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE45&amp;"_win")*($U$7:$U$78))</f>
@@ -50029,15 +50034,15 @@
       </c>
       <c r="AU45" s="126" cm="1">
         <f t="array" ref="AU45">SUMPRODUCT(($S$7:$S$78=AE45&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE45&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV45" s="126" cm="1">
         <f t="array" ref="AV45">SUMPRODUCT(($E$7:$E$78=AE45)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE45)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW45" s="126" cm="1">
         <f t="array" ref="AW45">SUMPRODUCT(($E$7:$E$78=AE45)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE45)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX45" s="126">
         <f>AV45-AW45</f>
@@ -50049,11 +50054,11 @@
       </c>
       <c r="AZ45" s="126">
         <f>AT45/AT48*1000+AU45/AU48*100+AY45/AY48*10+AV45/AV48</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BA45" s="126">
         <f>AZ45/AZ48</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BB45" s="126" cm="1">
         <f t="array" ref="BB45">SUMPRODUCT(($S$7:$S$78=AE45&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE45&amp;"_win")*($X$7:$X$78))</f>
@@ -50061,15 +50066,15 @@
       </c>
       <c r="BC45" s="126" cm="1">
         <f t="array" ref="BC45">SUMPRODUCT(($S$7:$S$78=AE45&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE45&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD45" s="126" cm="1">
         <f t="array" ref="BD45">SUMPRODUCT(($E$7:$E$78=AE45)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE45)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE45" s="126" cm="1">
         <f t="array" ref="BE45">SUMPRODUCT(($E$7:$E$78=AE45)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE45)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF45" s="126">
         <f>BD45-BE45</f>
@@ -50081,11 +50086,11 @@
       </c>
       <c r="BH45" s="126">
         <f>BB45/BB48*1000+BC45/BC48*100+BG45/BG48*10+BD45/BD48</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BI45" s="126">
         <f>BH45/BH48</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BK45" s="21" t="str" cm="1">
         <f t="array" ref="BK45">INDEX(T,24+MONTH(BP45),lang) &amp; " " &amp; DAY(BP45) &amp; ", " &amp; YEAR(BP45) &amp; "   " &amp; (IF(HOUR(BP45)&lt;10,0,"")&amp;HOUR(BP45)) &amp; ":" &amp;  (IF(MINUTE(BP45)&lt;10,0,"")&amp;MINUTE(BP45))</f>
@@ -50100,7 +50105,7 @@
         <v>46203.708333333336</v>
       </c>
       <c r="BQ45" s="115"/>
-      <c r="BR45" s="164"/>
+      <c r="BR45" s="174"/>
       <c r="BS45" s="26" t="str">
         <f>IF(BP46&gt;BP47,BL46,IF(BP46&lt;BP47,BL47,""))</f>
         <v/>
@@ -50113,11 +50118,11 @@
         <v/>
       </c>
       <c r="CK45" s="114"/>
-      <c r="CM45" s="168"/>
-      <c r="CN45" s="169"/>
-      <c r="CO45" s="169"/>
-      <c r="CP45" s="169"/>
-      <c r="CQ45" s="170"/>
+      <c r="CM45" s="179"/>
+      <c r="CN45" s="180"/>
+      <c r="CO45" s="180"/>
+      <c r="CP45" s="180"/>
+      <c r="CQ45" s="181"/>
     </row>
     <row r="46" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A46" s="16">
@@ -50151,15 +50156,15 @@
       </c>
       <c r="J46" s="33" t="str">
         <f>VLOOKUP(2,AD44:AN47,2,FALSE)</f>
-        <v>Iran</v>
+        <v>Egypt</v>
       </c>
       <c r="K46" s="23">
         <f>L46+M46+N46</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L46" s="23">
         <f>VLOOKUP(2,AD44:AN47,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" s="23">
         <f>VLOOKUP(2,AD44:AN47,4,FALSE)</f>
@@ -50171,11 +50176,11 @@
       </c>
       <c r="O46" s="23" t="str">
         <f>VLOOKUP(2,AD44:AN47,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD44:AN47,7,FALSE)</f>
-        <v>2 - 2</v>
+        <v>5 - 3</v>
       </c>
       <c r="P46" s="34">
         <f>L46*3+M46</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R46" s="123">
         <f>DATE(2026,6,21)+TIME(14,0,0)+gmt_delta</f>
@@ -50223,7 +50228,7 @@
       </c>
       <c r="AD46" s="123">
         <f>COUNTIF(AR44:AR47,CONCATENATE("&gt;=",AR46))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE46" s="124" t="str">
         <f>VLOOKUP("Iran",T,lang,FALSE)</f>
@@ -50235,7 +50240,7 @@
       </c>
       <c r="AG46" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE46 &amp; "_draw")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH46" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE46 &amp; "_lose")</f>
@@ -50243,11 +50248,11 @@
       </c>
       <c r="AI46" s="123">
         <f>SUMIF($E$7:$E$78,$AE46,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE46,$G$7:$G$78)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ46" s="123">
         <f>SUMIF($E$7:$E$78,$AE46,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE46,$F$7:$F$78)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL46" s="123">
         <f>AI46-AJ46</f>
@@ -50255,19 +50260,19 @@
       </c>
       <c r="AM46" s="123">
         <f>AL46-AL48</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AN46" s="123">
         <f>AF46*3+AG46</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO46" s="123">
         <f>AN46/AN48*10+BA46</f>
-        <v>4.9803921568627452</v>
+        <v>5</v>
       </c>
       <c r="AP46" s="123">
         <f>AO46*10000000+BI46*100+AM46/AM48*10+AI46/AI48*1++IF(AQ46=0,ROW(),AQ46)/2000000</f>
-        <v>49804024.008650787</v>
+        <v>50000005.883924529</v>
       </c>
       <c r="AQ46" s="126">
         <f>VLOOKUP(AE46,db_fifarank,2,FALSE)</f>
@@ -50275,7 +50280,7 @@
       </c>
       <c r="AR46" s="125">
         <f>AP46/AP48</f>
-        <v>0.62255022383964997</v>
+        <v>0.53683056761475623</v>
       </c>
       <c r="AT46" s="126" cm="1">
         <f t="array" ref="AT46">SUMPRODUCT(($S$7:$S$78=AE46&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE46&amp;"_win")*($U$7:$U$78))</f>
@@ -50283,7 +50288,7 @@
       </c>
       <c r="AU46" s="126" cm="1">
         <f t="array" ref="AU46">SUMPRODUCT(($S$7:$S$78=AE46&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE46&amp;"_draw")*($U$7:$U$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV46" s="126" cm="1">
         <f t="array" ref="AV46">SUMPRODUCT(($E$7:$E$78=AE46)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE46)*($U$7:$U$78)*($G$7:$G$78))</f>
@@ -50303,11 +50308,11 @@
       </c>
       <c r="AZ46" s="126">
         <f>AT46/AT48*1000+AU46/AU48*100+AY46/AY48*10+AV46/AV48</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BA46" s="126">
         <f>AZ46/AZ48</f>
-        <v>0.98039215686274506</v>
+        <v>0</v>
       </c>
       <c r="BB46" s="126" cm="1">
         <f t="array" ref="BB46">SUMPRODUCT(($S$7:$S$78=AE46&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE46&amp;"_win")*($X$7:$X$78))</f>
@@ -50315,7 +50320,7 @@
       </c>
       <c r="BC46" s="126" cm="1">
         <f t="array" ref="BC46">SUMPRODUCT(($S$7:$S$78=AE46&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE46&amp;"_draw")*($X$7:$X$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD46" s="126" cm="1">
         <f t="array" ref="BD46">SUMPRODUCT(($E$7:$E$78=AE46)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE46)*($X$7:$X$78)*($G$7:$G$78))</f>
@@ -50335,13 +50340,13 @@
       </c>
       <c r="BH46" s="126">
         <f>BB46/BB48*1000+BC46/BC48*100+BG46/BG48*10+BD46/BD48</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BI46" s="126">
         <f>BH46/BH48</f>
-        <v>0.98039215686274506</v>
-      </c>
-      <c r="BK46" s="163">
+        <v>0</v>
+      </c>
+      <c r="BK46" s="173">
         <v>78</v>
       </c>
       <c r="BL46" s="24" t="str">
@@ -50397,11 +50402,11 @@
       </c>
       <c r="J47" s="33" t="str">
         <f>VLOOKUP(3,AD44:AN47,2,FALSE)</f>
-        <v>Belgium</v>
+        <v>Iran</v>
       </c>
       <c r="K47" s="23">
         <f>L47+M47+N47</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L47" s="23">
         <f>VLOOKUP(3,AD44:AN47,3,FALSE)</f>
@@ -50409,7 +50414,7 @@
       </c>
       <c r="M47" s="23">
         <f>VLOOKUP(3,AD44:AN47,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N47" s="23">
         <f>VLOOKUP(3,AD44:AN47,5,FALSE)</f>
@@ -50417,11 +50422,11 @@
       </c>
       <c r="O47" s="23" t="str">
         <f>VLOOKUP(3,AD44:AN47,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD44:AN47,7,FALSE)</f>
-        <v>1 - 1</v>
+        <v>3 - 3</v>
       </c>
       <c r="P47" s="34">
         <f>L47*3+M47</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R47" s="123">
         <f>DATE(2026,6,22)+TIME(13,0,0)+gmt_delta</f>
@@ -50485,19 +50490,19 @@
       </c>
       <c r="AH47" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE47 &amp; "_lose")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI47" s="123">
         <f>SUMIF($E$7:$E$78,$AE47,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE47,$G$7:$G$78)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ47" s="123">
         <f>SUMIF($E$7:$E$78,$AE47,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE47,$F$7:$F$78)</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AL47" s="123">
         <f>AI47-AJ47</f>
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="AM47" s="123">
         <f>AL47-AL48</f>
@@ -50509,11 +50514,11 @@
       </c>
       <c r="AO47" s="123">
         <f>AN47/AN48*10+BA47</f>
-        <v>2</v>
+        <v>1.6666666666666665</v>
       </c>
       <c r="AP47" s="123">
         <f>AO47*10000000+BI47*100+AM47/AM48*10+AI47/AI48*1++IF(AQ47=0,ROW(),AQ47)/2000000</f>
-        <v>20000000.600640785</v>
+        <v>16666667.238736022</v>
       </c>
       <c r="AQ47" s="126">
         <f>VLOOKUP(AE47,db_fifarank,2,FALSE)</f>
@@ -50521,7 +50526,7 @@
       </c>
       <c r="AR47" s="125">
         <f>AP47/AP48</f>
-        <v>0.24999997688057007</v>
+        <v>0.17894350762253652</v>
       </c>
       <c r="AT47" s="126" cm="1">
         <f t="array" ref="AT47">SUMPRODUCT(($S$7:$S$78=AE47&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE47&amp;"_win")*($U$7:$U$78))</f>
@@ -50587,7 +50592,7 @@
         <f>BH47/BH48</f>
         <v>0</v>
       </c>
-      <c r="BK47" s="164"/>
+      <c r="BK47" s="174"/>
       <c r="BL47" s="26" t="str">
         <f>AS57</f>
         <v>Norway</v>
@@ -50670,7 +50675,7 @@
       </c>
       <c r="K48" s="36">
         <f>L48+M48+N48</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L48" s="36">
         <f>VLOOKUP(4,AD44:AN47,3,FALSE)</f>
@@ -50682,11 +50687,11 @@
       </c>
       <c r="N48" s="36">
         <f>VLOOKUP(4,AD44:AN47,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O48" s="36" t="str">
         <f>VLOOKUP(4,AD44:AN47,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD44:AN47,7,FALSE)</f>
-        <v>3 - 5</v>
+        <v>4 - 10</v>
       </c>
       <c r="P48" s="37">
         <f>L48*3+M48</f>
@@ -50742,35 +50747,35 @@
       </c>
       <c r="AG48" s="123">
         <f t="shared" si="24"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH48" s="123">
         <f t="shared" si="24"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI48" s="123">
         <f>MAX(AI44:AI47)+1</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AL48" s="123">
         <f>MIN(AL44:AL47)</f>
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="AM48" s="123">
         <f>MAX(AM44:AM47)+1</f>
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AN48" s="123">
         <f>MAX(AN44:AN47)+1</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO48" s="123">
         <f>MAX(AO44:AO47)+1</f>
-        <v>9</v>
+        <v>10.313915857605178</v>
       </c>
       <c r="AP48" s="123">
         <f>MAX(AP44:AP47)+1</f>
-        <v>80000009.800781623</v>
+        <v>93139267.583223492</v>
       </c>
       <c r="AT48" s="126">
         <f>MAX(AT44:AT47)-MIN(AT44:AT47)+1</f>
@@ -50782,11 +50787,11 @@
       </c>
       <c r="AV48" s="126">
         <f>MAX(AV44:AV47)-MIN(AV44:AV47)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW48" s="126">
         <f>MAX(AW44:AW47)-MIN(AW44:AW47)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY48" s="126">
         <f>MAX(AY44:AY47)-MIN(AY44:AY47)+1</f>
@@ -50794,7 +50799,7 @@
       </c>
       <c r="AZ48" s="126">
         <f>MAX(AZ44:AZ47)+1</f>
-        <v>51</v>
+        <v>51.5</v>
       </c>
       <c r="BB48" s="126">
         <f>MAX(BB44:BB47)-MIN(BB44:BB47)+1</f>
@@ -50806,11 +50811,11 @@
       </c>
       <c r="BD48" s="126">
         <f>MAX(BD44:BD47)-MIN(BD44:BD47)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BE48" s="126">
         <f>MAX(BE44:BE47)-MIN(BE44:BE47)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BG48" s="126">
         <f>MAX(BG44:BG47)-MIN(BG44:BG47)+1</f>
@@ -50818,7 +50823,7 @@
       </c>
       <c r="BH48" s="126">
         <f>MAX(BH44:BH47)+1</f>
-        <v>51</v>
+        <v>51.5</v>
       </c>
       <c r="BK48" s="21"/>
       <c r="BL48" s="21"/>
@@ -50834,7 +50839,7 @@
       <c r="BV48" s="21"/>
       <c r="BW48" s="114"/>
       <c r="BX48" s="112"/>
-      <c r="BY48" s="163">
+      <c r="BY48" s="173">
         <v>99</v>
       </c>
       <c r="BZ48" s="24" t="str">
@@ -50850,7 +50855,7 @@
       </c>
       <c r="CK48" s="114"/>
       <c r="CL48" s="112"/>
-      <c r="CM48" s="163">
+      <c r="CM48" s="173">
         <v>103</v>
       </c>
       <c r="CN48" s="24" t="str">
@@ -50959,7 +50964,7 @@
       <c r="BV49" s="21"/>
       <c r="BW49" s="114"/>
       <c r="BX49" s="115"/>
-      <c r="BY49" s="164"/>
+      <c r="BY49" s="174"/>
       <c r="BZ49" s="26" t="str">
         <f>IF(BW52&gt;BW53,BS52,IF(BW52&lt;BW53,BS53,""))</f>
         <v/>
@@ -50973,7 +50978,7 @@
       </c>
       <c r="CK49" s="114"/>
       <c r="CL49" s="115"/>
-      <c r="CM49" s="164"/>
+      <c r="CM49" s="174"/>
       <c r="CN49" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG56,IF(CK55&lt;CK56,CG55,""))</f>
         <v/>
@@ -51098,7 +51103,7 @@
       </c>
       <c r="AF50" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE50 &amp; "_win")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG50" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE50 &amp; "_draw")</f>
@@ -51110,7 +51115,7 @@
       </c>
       <c r="AI50" s="123">
         <f>SUMIF($E$7:$E$78,$AE50,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE50,$G$7:$G$78)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ50" s="123">
         <f>SUMIF($E$7:$E$78,$AE50,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE50,$F$7:$F$78)</f>
@@ -51118,23 +51123,23 @@
       </c>
       <c r="AL50" s="123">
         <f>AI50-AJ50</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM50" s="123">
         <f>AL50-AL54</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AN50" s="123">
         <f>AF50*3+AG50</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AO50" s="123">
         <f>AN50/AN54*10+BA50</f>
-        <v>8</v>
+        <v>8.75</v>
       </c>
       <c r="AP50" s="123">
         <f>AO50*10000000+BI50*100+AM50/AM54*10+AI50/AI54*1++IF(AQ50=0,ROW(),AQ50)/2000000</f>
-        <v>80000009.689827099</v>
+        <v>87500009.834271535</v>
       </c>
       <c r="AQ50" s="126">
         <f>VLOOKUP(AE50,db_fifarank,2,FALSE)</f>
@@ -51142,11 +51147,11 @@
       </c>
       <c r="AR50" s="125">
         <f>AP50/AP54</f>
-        <v>0.99999998750000163</v>
+        <v>0.99999998857143002</v>
       </c>
       <c r="AS50" s="125" t="str">
         <f>IF(SUM(AF50:AH53)=12,J51,"1H")</f>
-        <v>1H</v>
+        <v>Spain</v>
       </c>
       <c r="AT50" s="126" cm="1">
         <f t="array" ref="AT50">SUMPRODUCT(($S$7:$S$78=AE50&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE50&amp;"_win")*($U$7:$U$78))</f>
@@ -51212,7 +51217,7 @@
         <f>BH50/BH54</f>
         <v>0</v>
       </c>
-      <c r="BK50" s="163">
+      <c r="BK50" s="173">
         <v>79</v>
       </c>
       <c r="BL50" s="24" t="str">
@@ -51279,11 +51284,11 @@
       </c>
       <c r="K51" s="31">
         <f>L51+M51+N51</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L51" s="31">
         <f>VLOOKUP(1,AD50:AN53,3,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M51" s="31">
         <f>VLOOKUP(1,AD50:AN53,4,FALSE)</f>
@@ -51295,11 +51300,11 @@
       </c>
       <c r="O51" s="31" t="str">
         <f>VLOOKUP(1,AD50:AN53,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD50:AN53,7,FALSE)</f>
-        <v>4 - 0</v>
+        <v>5 - 0</v>
       </c>
       <c r="P51" s="32">
         <f>L51*3+M51</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R51" s="123">
         <f>DATE(2026,6,23)+TIME(9,0,0)+gmt_delta</f>
@@ -51315,7 +51320,7 @@
       </c>
       <c r="U51" s="123">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V51" s="123">
         <f t="shared" si="21"/>
@@ -51327,7 +51332,7 @@
       </c>
       <c r="X51" s="123">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y51" s="123">
         <f t="shared" si="10"/>
@@ -51347,7 +51352,7 @@
       </c>
       <c r="AD51" s="123">
         <f>COUNTIF(AR50:AR53,CONCATENATE("&gt;=",AR51))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE51" s="124" t="str">
         <f>VLOOKUP("Cape Verde",T,lang,FALSE)</f>
@@ -51359,7 +51364,7 @@
       </c>
       <c r="AG51" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE51 &amp; "_draw")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH51" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE51 &amp; "_lose")</f>
@@ -51383,15 +51388,15 @@
       </c>
       <c r="AN51" s="123">
         <f>AF51*3+AG51</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO51" s="123">
         <f>AN51/AN54*10+BA51</f>
-        <v>4.9806451612903224</v>
+        <v>3.75</v>
       </c>
       <c r="AP51" s="123">
         <f>AO51*10000000+BI51*100+AM51/AM54*10+AI51/AI54*1++IF(AQ51=0,ROW(),AQ51)/2000000</f>
-        <v>49806554.522546858</v>
+        <v>37500004.334016398</v>
       </c>
       <c r="AQ51" s="126">
         <f>VLOOKUP(AE51,db_fifarank,2,FALSE)</f>
@@ -51399,11 +51404,11 @@
       </c>
       <c r="AR51" s="125">
         <f>AP51/AP54</f>
-        <v>0.62258184834068175</v>
+        <v>0.42857142503722523</v>
       </c>
       <c r="AS51" s="125" t="str">
         <f>IF(SUM(AF50:AH53)=12,J52,"2H")</f>
-        <v>2H</v>
+        <v>Cape Verde</v>
       </c>
       <c r="AT51" s="126" cm="1">
         <f t="array" ref="AT51">SUMPRODUCT(($S$7:$S$78=AE51&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE51&amp;"_win")*($U$7:$U$78))</f>
@@ -51411,15 +51416,15 @@
       </c>
       <c r="AU51" s="126" cm="1">
         <f t="array" ref="AU51">SUMPRODUCT(($S$7:$S$78=AE51&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE51&amp;"_draw")*($U$7:$U$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV51" s="126" cm="1">
         <f t="array" ref="AV51">SUMPRODUCT(($E$7:$E$78=AE51)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE51)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW51" s="126" cm="1">
         <f t="array" ref="AW51">SUMPRODUCT(($E$7:$E$78=AE51)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE51)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX51" s="126">
         <f>AV51-AW51</f>
@@ -51431,11 +51436,11 @@
       </c>
       <c r="AZ51" s="126">
         <f>AT51/AT54*1000+AU51/AU54*100+AY51/AY54*10+AV51/AV54</f>
-        <v>50.666666666666664</v>
+        <v>0</v>
       </c>
       <c r="BA51" s="126">
         <f>AZ51/AZ54</f>
-        <v>0.98064516129032253</v>
+        <v>0</v>
       </c>
       <c r="BB51" s="126" cm="1">
         <f t="array" ref="BB51">SUMPRODUCT(($S$7:$S$78=AE51&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE51&amp;"_win")*($X$7:$X$78))</f>
@@ -51443,15 +51448,15 @@
       </c>
       <c r="BC51" s="126" cm="1">
         <f t="array" ref="BC51">SUMPRODUCT(($S$7:$S$78=AE51&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE51&amp;"_draw")*($X$7:$X$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD51" s="126" cm="1">
         <f t="array" ref="BD51">SUMPRODUCT(($E$7:$E$78=AE51)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE51)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BE51" s="126" cm="1">
         <f t="array" ref="BE51">SUMPRODUCT(($E$7:$E$78=AE51)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE51)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF51" s="126">
         <f>BD51-BE51</f>
@@ -51463,16 +51468,16 @@
       </c>
       <c r="BH51" s="126">
         <f>BB51/BB54*1000+BC51/BC54*100+BG51/BG54*10+BD51/BD54</f>
-        <v>50.666666666666664</v>
+        <v>0</v>
       </c>
       <c r="BI51" s="126">
         <f>BH51/BH54</f>
-        <v>0.98064516129032253</v>
-      </c>
-      <c r="BK51" s="164"/>
+        <v>0</v>
+      </c>
+      <c r="BK51" s="174"/>
       <c r="BL51" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!D3,AK80:AS91,9,FALSE),"3rd Group C/E/F/H/I")</f>
-        <v>3rd Group C/E/F/H/I</v>
+        <v>Ecuador</v>
       </c>
       <c r="BM51" s="62"/>
       <c r="BN51" s="64"/>
@@ -51536,11 +51541,11 @@
       </c>
       <c r="J52" s="33" t="str">
         <f>VLOOKUP(2,AD50:AN53,2,FALSE)</f>
-        <v>Uruguay</v>
+        <v>Cape Verde</v>
       </c>
       <c r="K52" s="23">
         <f>L52+M52+N52</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L52" s="23">
         <f>VLOOKUP(2,AD50:AN53,3,FALSE)</f>
@@ -51548,7 +51553,7 @@
       </c>
       <c r="M52" s="23">
         <f>VLOOKUP(2,AD50:AN53,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N52" s="23">
         <f>VLOOKUP(2,AD50:AN53,5,FALSE)</f>
@@ -51556,11 +51561,11 @@
       </c>
       <c r="O52" s="23" t="str">
         <f>VLOOKUP(2,AD50:AN53,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD50:AN53,7,FALSE)</f>
-        <v>3 - 3</v>
+        <v>2 - 2</v>
       </c>
       <c r="P52" s="34">
         <f>L52*3+M52</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R52" s="123">
         <f>DATE(2026,6,23)+TIME(12,0,0)+gmt_delta</f>
@@ -51620,7 +51625,7 @@
       </c>
       <c r="AG52" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE52 &amp; "_draw")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH52" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE52 &amp; "_lose")</f>
@@ -51644,15 +51649,15 @@
       </c>
       <c r="AN52" s="123">
         <f>AF52*3+AG52</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO52" s="123">
         <f>AN52/AN54*10+BA52</f>
-        <v>2</v>
+        <v>3.4805825242718447</v>
       </c>
       <c r="AP52" s="123">
         <f>AO52*10000000+BI52*100+AM52/AM54*10+AI52/AI54*1++IF(AQ52=0,ROW(),AQ52)/2000000</f>
-        <v>20000000.200710714</v>
+        <v>34805923.46834825</v>
       </c>
       <c r="AQ52" s="126">
         <f>VLOOKUP(AE52,db_fifarank,2,FALSE)</f>
@@ -51660,7 +51665,7 @@
       </c>
       <c r="AR52" s="125">
         <f>AP52/AP54</f>
-        <v>0.24999996910317837</v>
+        <v>0.39778193324195171</v>
       </c>
       <c r="AT52" s="126" cm="1">
         <f t="array" ref="AT52">SUMPRODUCT(($S$7:$S$78=AE52&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE52&amp;"_win")*($U$7:$U$78))</f>
@@ -51668,15 +51673,15 @@
       </c>
       <c r="AU52" s="126" cm="1">
         <f t="array" ref="AU52">SUMPRODUCT(($S$7:$S$78=AE52&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE52&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV52" s="126" cm="1">
         <f t="array" ref="AV52">SUMPRODUCT(($E$7:$E$78=AE52)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE52)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW52" s="126" cm="1">
         <f t="array" ref="AW52">SUMPRODUCT(($E$7:$E$78=AE52)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE52)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX52" s="126">
         <f>AV52-AW52</f>
@@ -51688,11 +51693,11 @@
       </c>
       <c r="AZ52" s="126">
         <f>AT52/AT54*1000+AU52/AU54*100+AY52/AY54*10+AV52/AV54</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BA52" s="126">
         <f>AZ52/AZ54</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BB52" s="126" cm="1">
         <f t="array" ref="BB52">SUMPRODUCT(($S$7:$S$78=AE52&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE52&amp;"_win")*($X$7:$X$78))</f>
@@ -51700,15 +51705,15 @@
       </c>
       <c r="BC52" s="126" cm="1">
         <f t="array" ref="BC52">SUMPRODUCT(($S$7:$S$78=AE52&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE52&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD52" s="126" cm="1">
         <f t="array" ref="BD52">SUMPRODUCT(($E$7:$E$78=AE52)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE52)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE52" s="126" cm="1">
         <f t="array" ref="BE52">SUMPRODUCT(($E$7:$E$78=AE52)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE52)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF52" s="126">
         <f>BD52-BE52</f>
@@ -51720,11 +51725,11 @@
       </c>
       <c r="BH52" s="126">
         <f>BB52/BB54*1000+BC52/BC54*100+BG52/BG54*10+BD52/BD54</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BI52" s="126">
         <f>BH52/BH54</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BK52" s="21"/>
       <c r="BL52" s="21"/>
@@ -51733,7 +51738,7 @@
       <c r="BO52" s="21"/>
       <c r="BP52" s="114"/>
       <c r="BQ52" s="112"/>
-      <c r="BR52" s="163">
+      <c r="BR52" s="173">
         <v>92</v>
       </c>
       <c r="BS52" s="24" t="str">
@@ -51789,11 +51794,11 @@
       </c>
       <c r="J53" s="33" t="str">
         <f>VLOOKUP(3,AD50:AN53,2,FALSE)</f>
-        <v>Cape Verde</v>
+        <v>Uruguay</v>
       </c>
       <c r="K53" s="23">
         <f>L53+M53+N53</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L53" s="23">
         <f>VLOOKUP(3,AD50:AN53,3,FALSE)</f>
@@ -51805,11 +51810,11 @@
       </c>
       <c r="N53" s="23">
         <f>VLOOKUP(3,AD50:AN53,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O53" s="23" t="str">
         <f>VLOOKUP(3,AD50:AN53,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD50:AN53,7,FALSE)</f>
-        <v>2 - 2</v>
+        <v>3 - 4</v>
       </c>
       <c r="P53" s="34">
         <f>L53*3+M53</f>
@@ -51861,7 +51866,7 @@
       </c>
       <c r="AD53" s="123">
         <f>COUNTIF(AR50:AR53,CONCATENATE("&gt;=",AR53))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE53" s="124" t="str">
         <f>VLOOKUP("Uruguay",T,lang,FALSE)</f>
@@ -51877,7 +51882,7 @@
       </c>
       <c r="AH53" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE53 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI53" s="123">
         <f>SUMIF($E$7:$E$78,$AE53,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE53,$G$7:$G$78)</f>
@@ -51885,15 +51890,15 @@
       </c>
       <c r="AJ53" s="123">
         <f>SUMIF($E$7:$E$78,$AE53,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE53,$F$7:$F$78)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL53" s="123">
         <f>AI53-AJ53</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM53" s="123">
         <f>AL53-AL54</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN53" s="123">
         <f>AF53*3+AG53</f>
@@ -51901,11 +51906,11 @@
       </c>
       <c r="AO53" s="123">
         <f>AN53/AN54*10+BA53</f>
-        <v>4.9806451612903224</v>
+        <v>3.4805825242718447</v>
       </c>
       <c r="AP53" s="123">
         <f>AO53*10000000+BI53*100+AM53/AM54*10+AI53/AI54*1++IF(AQ53=0,ROW(),AQ53)/2000000</f>
-        <v>49806554.722700335</v>
+        <v>34805926.801807404</v>
       </c>
       <c r="AQ53" s="126">
         <f>VLOOKUP(AE53,db_fifarank,2,FALSE)</f>
@@ -51913,7 +51918,7 @@
       </c>
       <c r="AR53" s="125">
         <f>AP53/AP54</f>
-        <v>0.62258185084259998</v>
+        <v>0.39778197133862303</v>
       </c>
       <c r="AT53" s="126" cm="1">
         <f t="array" ref="AT53">SUMPRODUCT(($S$7:$S$78=AE53&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE53&amp;"_win")*($U$7:$U$78))</f>
@@ -51925,11 +51930,11 @@
       </c>
       <c r="AV53" s="126" cm="1">
         <f t="array" ref="AV53">SUMPRODUCT(($E$7:$E$78=AE53)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE53)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW53" s="126" cm="1">
         <f t="array" ref="AW53">SUMPRODUCT(($E$7:$E$78=AE53)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE53)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX53" s="126">
         <f>AV53-AW53</f>
@@ -51941,11 +51946,11 @@
       </c>
       <c r="AZ53" s="126">
         <f>AT53/AT54*1000+AU53/AU54*100+AY53/AY54*10+AV53/AV54</f>
-        <v>50.666666666666664</v>
+        <v>50.5</v>
       </c>
       <c r="BA53" s="126">
         <f>AZ53/AZ54</f>
-        <v>0.98064516129032253</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BB53" s="126" cm="1">
         <f t="array" ref="BB53">SUMPRODUCT(($S$7:$S$78=AE53&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE53&amp;"_win")*($X$7:$X$78))</f>
@@ -51957,11 +51962,11 @@
       </c>
       <c r="BD53" s="126" cm="1">
         <f t="array" ref="BD53">SUMPRODUCT(($E$7:$E$78=AE53)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE53)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BE53" s="126" cm="1">
         <f t="array" ref="BE53">SUMPRODUCT(($E$7:$E$78=AE53)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE53)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BF53" s="126">
         <f>BD53-BE53</f>
@@ -51973,11 +51978,11 @@
       </c>
       <c r="BH53" s="126">
         <f>BB53/BB54*1000+BC53/BC54*100+BG53/BG54*10+BD53/BD54</f>
-        <v>50.666666666666664</v>
+        <v>50.5</v>
       </c>
       <c r="BI53" s="126">
         <f>BH53/BH54</f>
-        <v>0.98064516129032253</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BK53" s="21" t="str" cm="1">
         <f t="array" ref="BK53">INDEX(T,24+MONTH(BP53),lang) &amp; " " &amp; DAY(BP53) &amp; ", " &amp; YEAR(BP53) &amp; "   " &amp; (IF(HOUR(BP53)&lt;10,0,"")&amp;HOUR(BP53)) &amp; ":" &amp;  (IF(MINUTE(BP53)&lt;10,0,"")&amp;MINUTE(BP53))</f>
@@ -51992,7 +51997,7 @@
         <v>46204.666666666672</v>
       </c>
       <c r="BQ53" s="115"/>
-      <c r="BR53" s="164"/>
+      <c r="BR53" s="174"/>
       <c r="BS53" s="26" t="str">
         <f>IF(BP54&gt;BP55,BL54,IF(BP54&lt;BP55,BL55,""))</f>
         <v/>
@@ -52050,7 +52055,7 @@
       </c>
       <c r="K54" s="36">
         <f>L54+M54+N54</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L54" s="36">
         <f>VLOOKUP(4,AD50:AN53,3,FALSE)</f>
@@ -52058,7 +52063,7 @@
       </c>
       <c r="M54" s="36">
         <f>VLOOKUP(4,AD50:AN53,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N54" s="36">
         <f>VLOOKUP(4,AD50:AN53,5,FALSE)</f>
@@ -52070,7 +52075,7 @@
       </c>
       <c r="P54" s="37">
         <f>L54*3+M54</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R54" s="123">
         <f>DATE(2026,6,23)+TIME(15,0,0)+gmt_delta</f>
@@ -52118,11 +52123,11 @@
       </c>
       <c r="AF54" s="123">
         <f t="shared" ref="AF54:AH54" si="25">MAX(AF50:AF53)-MIN(AF50:AF53)+1</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG54" s="123">
         <f t="shared" si="25"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH54" s="123">
         <f t="shared" si="25"/>
@@ -52130,7 +52135,7 @@
       </c>
       <c r="AI54" s="123">
         <f>MAX(AI50:AI53)+1</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL54" s="123">
         <f>MIN(AL50:AL53)</f>
@@ -52138,19 +52143,19 @@
       </c>
       <c r="AM54" s="123">
         <f>MAX(AM50:AM53)+1</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AN54" s="123">
         <f>MAX(AN50:AN53)+1</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AO54" s="123">
         <f>MAX(AO50:AO53)+1</f>
-        <v>9</v>
+        <v>9.75</v>
       </c>
       <c r="AP54" s="123">
         <f>MAX(AP50:AP53)+1</f>
-        <v>80000010.689827099</v>
+        <v>87500010.834271535</v>
       </c>
       <c r="AT54" s="126">
         <f>MAX(AT50:AT53)-MIN(AT50:AT53)+1</f>
@@ -52162,11 +52167,11 @@
       </c>
       <c r="AV54" s="126">
         <f>MAX(AV50:AV53)-MIN(AV50:AV53)+1</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW54" s="126">
         <f>MAX(AW50:AW53)-MIN(AW50:AW53)+1</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY54" s="126">
         <f>MAX(AY50:AY53)-MIN(AY50:AY53)+1</f>
@@ -52174,7 +52179,7 @@
       </c>
       <c r="AZ54" s="126">
         <f>MAX(AZ50:AZ53)+1</f>
-        <v>51.666666666666664</v>
+        <v>51.5</v>
       </c>
       <c r="BB54" s="126">
         <f>MAX(BB50:BB53)-MIN(BB50:BB53)+1</f>
@@ -52186,11 +52191,11 @@
       </c>
       <c r="BD54" s="126">
         <f>MAX(BD50:BD53)-MIN(BD50:BD53)+1</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BE54" s="126">
         <f>MAX(BE50:BE53)-MIN(BE50:BE53)+1</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BG54" s="126">
         <f>MAX(BG50:BG53)-MIN(BG50:BG53)+1</f>
@@ -52198,14 +52203,14 @@
       </c>
       <c r="BH54" s="126">
         <f>MAX(BH50:BH53)+1</f>
-        <v>51.666666666666664</v>
-      </c>
-      <c r="BK54" s="163">
+        <v>51.5</v>
+      </c>
+      <c r="BK54" s="173">
         <v>80</v>
       </c>
       <c r="BL54" s="24" t="str">
         <f>AS74</f>
-        <v>1L</v>
+        <v>England</v>
       </c>
       <c r="BM54" s="61"/>
       <c r="BN54" s="63"/>
@@ -52325,10 +52330,10 @@
         <f t="shared" si="23"/>
         <v>-1</v>
       </c>
-      <c r="BK55" s="164"/>
+      <c r="BK55" s="174"/>
       <c r="BL55" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!K3,AK80:AS91,9,FALSE),"3rd Group E/H/I/J/K")</f>
-        <v>3rd Group E/H/I/J/K</v>
+        <v>DR Congo</v>
       </c>
       <c r="BM55" s="62"/>
       <c r="BN55" s="64"/>
@@ -52352,7 +52357,7 @@
       <c r="CC55" s="21"/>
       <c r="CD55" s="114"/>
       <c r="CE55" s="112"/>
-      <c r="CF55" s="163">
+      <c r="CF55" s="173">
         <v>102</v>
       </c>
       <c r="CG55" s="24" t="str">
@@ -52615,7 +52620,7 @@
       <c r="CC56" s="21"/>
       <c r="CD56" s="114"/>
       <c r="CE56" s="115"/>
-      <c r="CF56" s="164"/>
+      <c r="CF56" s="174"/>
       <c r="CG56" s="26" t="str">
         <f>IF(CD64&gt;CD65,BZ64,IF(CD64&lt;CD65,BZ65,""))</f>
         <v/>
@@ -53106,12 +53111,12 @@
         <f>BH58/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK58" s="163">
+      <c r="BK58" s="173">
         <v>86</v>
       </c>
       <c r="BL58" s="24" t="str">
         <f>AS62</f>
-        <v>1J</v>
+        <v>Argentina</v>
       </c>
       <c r="BM58" s="61"/>
       <c r="BN58" s="63"/>
@@ -53358,10 +53363,10 @@
         <f>BH59/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK59" s="164"/>
+      <c r="BK59" s="174"/>
       <c r="BL59" s="26" t="str">
         <f>AS51</f>
-        <v>2H</v>
+        <v>Cape Verde</v>
       </c>
       <c r="BM59" s="62"/>
       <c r="BN59" s="64"/>
@@ -53585,7 +53590,7 @@
       <c r="BO60" s="21"/>
       <c r="BP60" s="114"/>
       <c r="BQ60" s="112"/>
-      <c r="BR60" s="163">
+      <c r="BR60" s="173">
         <v>95</v>
       </c>
       <c r="BS60" s="24" t="str">
@@ -53702,7 +53707,7 @@
         <v>46206.75</v>
       </c>
       <c r="BQ61" s="115"/>
-      <c r="BR61" s="164"/>
+      <c r="BR61" s="174"/>
       <c r="BS61" s="26" t="str">
         <f>IF(BP62&gt;BP63,BL62,IF(BP62&lt;BP63,BL63,""))</f>
         <v/>
@@ -53835,7 +53840,7 @@
       </c>
       <c r="AF62" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE62 &amp; "_win")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG62" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE62 &amp; "_draw")</f>
@@ -53847,31 +53852,31 @@
       </c>
       <c r="AI62" s="123">
         <f>SUMIF($E$7:$E$78,$AE62,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE62,$G$7:$G$78)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AJ62" s="123">
         <f>SUMIF($E$7:$E$78,$AE62,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE62,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL62" s="123">
         <f>AI62-AJ62</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AM62" s="123">
         <f>AL62-AL66</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AN62" s="123">
         <f>AF62*3+AG62</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AO62" s="123">
         <f>AN62/AN66*10+BA62</f>
-        <v>8.5714285714285712</v>
+        <v>9</v>
       </c>
       <c r="AP62" s="123">
         <f>AO62*10000000+BI62*100+AM62/AM66*10+AI62/AI66*1++IF(AQ62=0,ROW(),AQ62)/2000000</f>
-        <v>85714295.437445357</v>
+        <v>90000010.120595545</v>
       </c>
       <c r="AQ62" s="126">
         <f>VLOOKUP(AE62,db_fifarank,2,FALSE)</f>
@@ -53879,11 +53884,11 @@
       </c>
       <c r="AR62" s="125">
         <f>AP62/AP66</f>
-        <v>0.99999998833333481</v>
+        <v>0.9999999888888903</v>
       </c>
       <c r="AS62" s="125" t="str">
         <f>IF(SUM(AF62:AH65)=12,J63,"1J")</f>
-        <v>1J</v>
+        <v>Argentina</v>
       </c>
       <c r="AT62" s="126" cm="1">
         <f t="array" ref="AT62">SUMPRODUCT(($S$7:$S$78=AE62&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE62&amp;"_win")*($U$7:$U$78))</f>
@@ -53949,7 +53954,7 @@
         <f>BH62/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK62" s="163">
+      <c r="BK62" s="173">
         <v>88</v>
       </c>
       <c r="BL62" s="24" t="str">
@@ -54015,11 +54020,11 @@
       </c>
       <c r="K63" s="31">
         <f>L63+M63+N63</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L63" s="31">
         <f>VLOOKUP(1,AD62:AN65,3,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M63" s="31">
         <f>VLOOKUP(1,AD62:AN65,4,FALSE)</f>
@@ -54031,11 +54036,11 @@
       </c>
       <c r="O63" s="31" t="str">
         <f>VLOOKUP(1,AD62:AN65,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD62:AN65,7,FALSE)</f>
-        <v>5 - 0</v>
+        <v>8 - 1</v>
       </c>
       <c r="P63" s="32">
         <f>L63*3+M63</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R63" s="123">
         <f>DATE(2026,6,25)+TIME(12,0,0)+gmt_delta</f>
@@ -54095,7 +54100,7 @@
       </c>
       <c r="AG63" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE63 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH63" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE63 &amp; "_lose")</f>
@@ -54103,11 +54108,11 @@
       </c>
       <c r="AI63" s="123">
         <f>SUMIF($E$7:$E$78,$AE63,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE63,$G$7:$G$78)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AJ63" s="123">
         <f>SUMIF($E$7:$E$78,$AE63,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE63,$F$7:$F$78)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AL63" s="123">
         <f>AI63-AJ63</f>
@@ -54115,19 +54120,19 @@
       </c>
       <c r="AM63" s="123">
         <f>AL63-AL66</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AN63" s="123">
         <f>AF63*3+AG63</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO63" s="123">
         <f>AN63/AN66*10+BA63</f>
-        <v>4.2857142857142856</v>
+        <v>4.9806763285024154</v>
       </c>
       <c r="AP63" s="123">
         <f>AO63*10000000+BI63*100+AM63/AM66*10+AI63/AI66*1++IF(AQ63=0,ROW(),AQ63)/2000000</f>
-        <v>42857144.302369438</v>
+        <v>49806864.216686986</v>
       </c>
       <c r="AQ63" s="126">
         <f>VLOOKUP(AE63,db_fifarank,2,FALSE)</f>
@@ -54135,11 +54140,11 @@
       </c>
       <c r="AR63" s="125">
         <f>AP63/AP66</f>
-        <v>0.4999999543092179</v>
+        <v>0.55340953402714876</v>
       </c>
       <c r="AS63" s="125" t="str">
         <f>IF(SUM(AF62:AH65)=12,J64,"2J")</f>
-        <v>2J</v>
+        <v>Austria</v>
       </c>
       <c r="AT63" s="126" cm="1">
         <f t="array" ref="AT63">SUMPRODUCT(($S$7:$S$78=AE63&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE63&amp;"_win")*($U$7:$U$78))</f>
@@ -54147,15 +54152,15 @@
       </c>
       <c r="AU63" s="126" cm="1">
         <f t="array" ref="AU63">SUMPRODUCT(($S$7:$S$78=AE63&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE63&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV63" s="126" cm="1">
         <f t="array" ref="AV63">SUMPRODUCT(($E$7:$E$78=AE63)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE63)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW63" s="126" cm="1">
         <f t="array" ref="AW63">SUMPRODUCT(($E$7:$E$78=AE63)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE63)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AX63" s="126">
         <f>AV63-AW63</f>
@@ -54167,11 +54172,11 @@
       </c>
       <c r="AZ63" s="126">
         <f>AT63/AT66*1000+AU63/AU66*100+AY63/AY66*10+AV63/AV66</f>
-        <v>0</v>
+        <v>50.75</v>
       </c>
       <c r="BA63" s="126">
         <f>AZ63/AZ66</f>
-        <v>0</v>
+        <v>0.98067632850241548</v>
       </c>
       <c r="BB63" s="126" cm="1">
         <f t="array" ref="BB63">SUMPRODUCT(($S$7:$S$78=AE63&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE63&amp;"_win")*($X$7:$X$78))</f>
@@ -54179,15 +54184,15 @@
       </c>
       <c r="BC63" s="126" cm="1">
         <f t="array" ref="BC63">SUMPRODUCT(($S$7:$S$78=AE63&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE63&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD63" s="126" cm="1">
         <f t="array" ref="BD63">SUMPRODUCT(($E$7:$E$78=AE63)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE63)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BE63" s="126" cm="1">
         <f t="array" ref="BE63">SUMPRODUCT(($E$7:$E$78=AE63)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE63)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BF63" s="126">
         <f>BD63-BE63</f>
@@ -54199,16 +54204,16 @@
       </c>
       <c r="BH63" s="126">
         <f>BB63/BB66*1000+BC63/BC66*100+BG63/BG66*10+BD63/BD66</f>
-        <v>0</v>
+        <v>50.75</v>
       </c>
       <c r="BI63" s="126">
         <f>BH63/BH66</f>
-        <v>0</v>
-      </c>
-      <c r="BK63" s="164"/>
+        <v>0.98067632850241548</v>
+      </c>
+      <c r="BK63" s="174"/>
       <c r="BL63" s="26" t="str">
         <f>AS45</f>
-        <v>2G</v>
+        <v>Egypt</v>
       </c>
       <c r="BM63" s="62"/>
       <c r="BN63" s="64"/>
@@ -54275,7 +54280,7 @@
       </c>
       <c r="K64" s="23">
         <f>L64+M64+N64</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L64" s="23">
         <f>VLOOKUP(2,AD62:AN65,3,FALSE)</f>
@@ -54283,7 +54288,7 @@
       </c>
       <c r="M64" s="23">
         <f>VLOOKUP(2,AD62:AN65,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N64" s="23">
         <f>VLOOKUP(2,AD62:AN65,5,FALSE)</f>
@@ -54291,11 +54296,11 @@
       </c>
       <c r="O64" s="23" t="str">
         <f>VLOOKUP(2,AD62:AN65,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD62:AN65,7,FALSE)</f>
-        <v>3 - 3</v>
+        <v>6 - 6</v>
       </c>
       <c r="P64" s="34">
         <f>L64*3+M64</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R64" s="123">
         <f>DATE(2026,6,25)+TIME(12,0,0)+gmt_delta</f>
@@ -54355,7 +54360,7 @@
       </c>
       <c r="AG64" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE64 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH64" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE64 &amp; "_lose")</f>
@@ -54363,11 +54368,11 @@
       </c>
       <c r="AI64" s="123">
         <f>SUMIF($E$7:$E$78,$AE64,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE64,$G$7:$G$78)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AJ64" s="123">
         <f>SUMIF($E$7:$E$78,$AE64,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE64,$F$7:$F$78)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AL64" s="123">
         <f>AI64-AJ64</f>
@@ -54375,19 +54380,19 @@
       </c>
       <c r="AM64" s="123">
         <f>AL64-AL66</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AN64" s="123">
         <f>AF64*3+AG64</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO64" s="123">
         <f>AN64/AN66*10+BA64</f>
-        <v>4.2857142857142856</v>
+        <v>4.9806763285024154</v>
       </c>
       <c r="AP64" s="123">
         <f>AO64*10000000+BI64*100+AM64/AM66*10+AI64/AI66*1++IF(AQ64=0,ROW(),AQ64)/2000000</f>
-        <v>42857146.691272922</v>
+        <v>49806865.866274238</v>
       </c>
       <c r="AQ64" s="126">
         <f>VLOOKUP(AE64,db_fifarank,2,FALSE)</f>
@@ -54395,7 +54400,7 @@
       </c>
       <c r="AR64" s="125">
         <f>AP64/AP66</f>
-        <v>0.49999998217975505</v>
+        <v>0.55340955235589373</v>
       </c>
       <c r="AT64" s="126" cm="1">
         <f t="array" ref="AT64">SUMPRODUCT(($S$7:$S$78=AE64&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE64&amp;"_win")*($U$7:$U$78))</f>
@@ -54403,15 +54408,15 @@
       </c>
       <c r="AU64" s="126" cm="1">
         <f t="array" ref="AU64">SUMPRODUCT(($S$7:$S$78=AE64&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE64&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV64" s="126" cm="1">
         <f t="array" ref="AV64">SUMPRODUCT(($E$7:$E$78=AE64)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE64)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW64" s="126" cm="1">
         <f t="array" ref="AW64">SUMPRODUCT(($E$7:$E$78=AE64)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE64)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AX64" s="126">
         <f>AV64-AW64</f>
@@ -54423,11 +54428,11 @@
       </c>
       <c r="AZ64" s="126">
         <f>AT64/AT66*1000+AU64/AU66*100+AY64/AY66*10+AV64/AV66</f>
-        <v>0</v>
+        <v>50.75</v>
       </c>
       <c r="BA64" s="126">
         <f>AZ64/AZ66</f>
-        <v>0</v>
+        <v>0.98067632850241548</v>
       </c>
       <c r="BB64" s="126" cm="1">
         <f t="array" ref="BB64">SUMPRODUCT(($S$7:$S$78=AE64&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE64&amp;"_win")*($X$7:$X$78))</f>
@@ -54435,15 +54440,15 @@
       </c>
       <c r="BC64" s="126" cm="1">
         <f t="array" ref="BC64">SUMPRODUCT(($S$7:$S$78=AE64&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE64&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD64" s="126" cm="1">
         <f t="array" ref="BD64">SUMPRODUCT(($E$7:$E$78=AE64)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE64)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BE64" s="126" cm="1">
         <f t="array" ref="BE64">SUMPRODUCT(($E$7:$E$78=AE64)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE64)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BF64" s="126">
         <f>BD64-BE64</f>
@@ -54455,11 +54460,11 @@
       </c>
       <c r="BH64" s="126">
         <f>BB64/BB66*1000+BC64/BC66*100+BG64/BG66*10+BD64/BD66</f>
-        <v>0</v>
+        <v>50.75</v>
       </c>
       <c r="BI64" s="126">
         <f>BH64/BH66</f>
-        <v>0</v>
+        <v>0.98067632850241548</v>
       </c>
       <c r="BK64" s="21"/>
       <c r="BL64" s="21"/>
@@ -54475,7 +54480,7 @@
       <c r="BV64" s="21"/>
       <c r="BW64" s="114"/>
       <c r="BX64" s="112"/>
-      <c r="BY64" s="163">
+      <c r="BY64" s="173">
         <v>100</v>
       </c>
       <c r="BZ64" s="24" t="str">
@@ -54527,7 +54532,7 @@
       </c>
       <c r="K65" s="23">
         <f>L65+M65+N65</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L65" s="23">
         <f>VLOOKUP(3,AD62:AN65,3,FALSE)</f>
@@ -54535,7 +54540,7 @@
       </c>
       <c r="M65" s="23">
         <f>VLOOKUP(3,AD62:AN65,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N65" s="23">
         <f>VLOOKUP(3,AD62:AN65,5,FALSE)</f>
@@ -54543,11 +54548,11 @@
       </c>
       <c r="O65" s="23" t="str">
         <f>VLOOKUP(3,AD62:AN65,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD62:AN65,7,FALSE)</f>
-        <v>2 - 4</v>
+        <v>5 - 7</v>
       </c>
       <c r="P65" s="34">
         <f>L65*3+M65</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R65" s="123">
         <f>DATE(2026,6,25)+TIME(15,0,0)+gmt_delta</f>
@@ -54611,19 +54616,19 @@
       </c>
       <c r="AH65" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE65 &amp; "_lose")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI65" s="123">
         <f>SUMIF($E$7:$E$78,$AE65,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE65,$G$7:$G$78)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ65" s="123">
         <f>SUMIF($E$7:$E$78,$AE65,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE65,$F$7:$F$78)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AL65" s="123">
         <f>AI65-AJ65</f>
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="AM65" s="123">
         <f>AL65-AL66</f>
@@ -54647,7 +54652,7 @@
       </c>
       <c r="AR65" s="125">
         <f>AP65/AP66</f>
-        <v>3.8970051930264523E-9</v>
+        <v>3.7114335228886911E-9</v>
       </c>
       <c r="AT65" s="126" cm="1">
         <f t="array" ref="AT65">SUMPRODUCT(($S$7:$S$78=AE65&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE65&amp;"_win")*($U$7:$U$78))</f>
@@ -54733,7 +54738,7 @@
       <c r="BV65" s="21"/>
       <c r="BW65" s="114"/>
       <c r="BX65" s="115"/>
-      <c r="BY65" s="164"/>
+      <c r="BY65" s="174"/>
       <c r="BZ65" s="26" t="str">
         <f>IF(BW68&gt;BW69,BS68,IF(BW68&lt;BW69,BS69,""))</f>
         <v/>
@@ -54783,7 +54788,7 @@
       </c>
       <c r="K66" s="36">
         <f>L66+M66+N66</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L66" s="36">
         <f>VLOOKUP(4,AD62:AN65,3,FALSE)</f>
@@ -54795,11 +54800,11 @@
       </c>
       <c r="N66" s="36">
         <f>VLOOKUP(4,AD62:AN65,5,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O66" s="36" t="str">
         <f>VLOOKUP(4,AD62:AN65,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD62:AN65,7,FALSE)</f>
-        <v>2 - 5</v>
+        <v>3 - 8</v>
       </c>
       <c r="P66" s="37">
         <f>L66*3+M66</f>
@@ -54851,39 +54856,39 @@
       </c>
       <c r="AF66" s="123">
         <f t="shared" ref="AF66:AH66" si="28">MAX(AF62:AF65)-MIN(AF62:AF65)+1</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG66" s="123">
         <f t="shared" si="28"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH66" s="123">
         <f t="shared" si="28"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI66" s="123">
         <f>MAX(AI62:AI65)+1</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AL66" s="123">
         <f>MIN(AL62:AL65)</f>
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="AM66" s="123">
         <f>MAX(AM62:AM65)+1</f>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AN66" s="123">
         <f>MAX(AN62:AN65)+1</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AO66" s="123">
         <f>MAX(AO62:AO65)+1</f>
-        <v>9.5714285714285712</v>
+        <v>10</v>
       </c>
       <c r="AP66" s="123">
         <f>MAX(AP62:AP65)+1</f>
-        <v>85714296.437445357</v>
+        <v>90000011.120595545</v>
       </c>
       <c r="AT66" s="126">
         <f>MAX(AT62:AT65)-MIN(AT62:AT65)+1</f>
@@ -54891,15 +54896,15 @@
       </c>
       <c r="AU66" s="126">
         <f>MAX(AU62:AU65)-MIN(AU62:AU65)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV66" s="126">
         <f>MAX(AV62:AV65)-MIN(AV62:AV65)+1</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AW66" s="126">
         <f>MAX(AW62:AW65)-MIN(AW62:AW65)+1</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AY66" s="126">
         <f>MAX(AY62:AY65)-MIN(AY62:AY65)+1</f>
@@ -54907,7 +54912,7 @@
       </c>
       <c r="AZ66" s="126">
         <f>MAX(AZ62:AZ65)+1</f>
-        <v>1</v>
+        <v>51.75</v>
       </c>
       <c r="BB66" s="126">
         <f>MAX(BB62:BB65)-MIN(BB62:BB65)+1</f>
@@ -54915,15 +54920,15 @@
       </c>
       <c r="BC66" s="126">
         <f>MAX(BC62:BC65)-MIN(BC62:BC65)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD66" s="126">
         <f>MAX(BD62:BD65)-MIN(BD62:BD65)+1</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BE66" s="126">
         <f>MAX(BE62:BE65)-MIN(BE62:BE65)+1</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BG66" s="126">
         <f>MAX(BG62:BG65)-MIN(BG62:BG65)+1</f>
@@ -54931,9 +54936,9 @@
       </c>
       <c r="BH66" s="126">
         <f>MAX(BH62:BH65)+1</f>
-        <v>1</v>
-      </c>
-      <c r="BK66" s="163">
+        <v>51.75</v>
+      </c>
+      <c r="BK66" s="173">
         <v>85</v>
       </c>
       <c r="BL66" s="24" t="str">
@@ -55037,10 +55042,10 @@
         <f t="shared" si="23"/>
         <v>-1</v>
       </c>
-      <c r="BK67" s="164"/>
+      <c r="BK67" s="174"/>
       <c r="BL67" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!E3,AK80:AS91,9,FALSE),"3rd Group E/F/G/I/J")</f>
-        <v>3rd Group E/F/G/I/J</v>
+        <v>Algeria</v>
       </c>
       <c r="BM67" s="62"/>
       <c r="BN67" s="64"/>
@@ -55180,7 +55185,7 @@
       </c>
       <c r="AG68" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE68 &amp; "_draw")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH68" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE68 &amp; "_lose")</f>
@@ -55200,19 +55205,19 @@
       </c>
       <c r="AM68" s="123">
         <f>AL68-AL72</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AN68" s="123">
         <f>AF68*3+AG68</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO68" s="123">
         <f>AN68/AN72*10+BA68</f>
-        <v>5.7142857142857135</v>
+        <v>6.25</v>
       </c>
       <c r="AP68" s="123">
         <f>AO68*10000000+BI68*100+AM68/AM72*10+AI68/AI72*1++IF(AQ68=0,ROW(),AQ68)/2000000</f>
-        <v>57142867.231651142</v>
+        <v>62500010.191358112</v>
       </c>
       <c r="AQ68" s="126">
         <f>VLOOKUP(AE68,db_fifarank,2,FALSE)</f>
@@ -55220,11 +55225,11 @@
       </c>
       <c r="AR68" s="125">
         <f>AP68/AP72</f>
-        <v>0.66666671231139207</v>
+        <v>0.71428575261735283</v>
       </c>
       <c r="AS68" s="125" t="str">
         <f>IF(SUM(AF68:AH71)=12,J69,"1K")</f>
-        <v>1K</v>
+        <v>Colombia</v>
       </c>
       <c r="AT68" s="126" cm="1">
         <f t="array" ref="AT68">SUMPRODUCT(($S$7:$S$78=AE68&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE68&amp;"_win")*($U$7:$U$78))</f>
@@ -55297,7 +55302,7 @@
       <c r="BO68" s="21"/>
       <c r="BP68" s="114"/>
       <c r="BQ68" s="112"/>
-      <c r="BR68" s="163">
+      <c r="BR68" s="173">
         <v>96</v>
       </c>
       <c r="BS68" s="24" t="str">
@@ -55311,25 +55316,25 @@
         <f>IF(OR(BT68="",BT69="",AND(BU68="",BU69&lt;&gt;""),AND(BU69="",BU68&lt;&gt;""),AND(BV68="",BV69&lt;&gt;""),AND(BV69="",BV68&lt;&gt;"")),"",BT68*1000+BU68*10+BV68)</f>
         <v/>
       </c>
-      <c r="CE68" s="195" t="str">
+      <c r="CE68" s="175" t="str">
         <f>INDEX(T,144,lang)</f>
         <v>World Champion 2026</v>
       </c>
-      <c r="CF68" s="195"/>
-      <c r="CG68" s="195"/>
-      <c r="CH68" s="195"/>
-      <c r="CI68" s="195"/>
-      <c r="CJ68" s="195"/>
-      <c r="CK68" s="185" t="str">
+      <c r="CF68" s="175"/>
+      <c r="CG68" s="175"/>
+      <c r="CH68" s="175"/>
+      <c r="CI68" s="175"/>
+      <c r="CJ68" s="175"/>
+      <c r="CK68" s="163" t="str">
         <f>IF(CR37&gt;CR38,CN37,IF(CR37&lt;CR38,CN38,""))</f>
         <v/>
       </c>
-      <c r="CL68" s="185"/>
-      <c r="CM68" s="185"/>
-      <c r="CN68" s="185"/>
-      <c r="CO68" s="185"/>
-      <c r="CP68" s="185"/>
-      <c r="CQ68" s="185"/>
+      <c r="CL68" s="163"/>
+      <c r="CM68" s="163"/>
+      <c r="CN68" s="163"/>
+      <c r="CO68" s="163"/>
+      <c r="CP68" s="163"/>
+      <c r="CQ68" s="163"/>
     </row>
     <row r="69" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A69" s="16">
@@ -55351,8 +55356,12 @@
         <f>AE45</f>
         <v>Egypt</v>
       </c>
-      <c r="F69" s="19"/>
-      <c r="G69" s="20"/>
+      <c r="F69" s="19">
+        <v>1</v>
+      </c>
+      <c r="G69" s="20">
+        <v>1</v>
+      </c>
       <c r="H69" s="80" t="str">
         <f>AE46</f>
         <v>Iran</v>
@@ -55364,7 +55373,7 @@
       </c>
       <c r="K69" s="31">
         <f>L69+M69+N69</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L69" s="31">
         <f>VLOOKUP(1,AD68:AN71,3,FALSE)</f>
@@ -55372,7 +55381,7 @@
       </c>
       <c r="M69" s="31">
         <f>VLOOKUP(1,AD68:AN71,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N69" s="31">
         <f>VLOOKUP(1,AD68:AN71,5,FALSE)</f>
@@ -55384,7 +55393,7 @@
       </c>
       <c r="P69" s="32">
         <f>L69*3+M69</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R69" s="123">
         <f>DATE(2026,6,26)+TIME(16,0,0)+gmt_delta</f>
@@ -55392,11 +55401,11 @@
       </c>
       <c r="S69" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Egypt_draw</v>
       </c>
       <c r="T69" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Iran_draw</v>
       </c>
       <c r="U69" s="123">
         <f t="shared" si="8"/>
@@ -55426,9 +55435,9 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB69" s="123" t="str">
+      <c r="AB69" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AD69" s="123">
         <f>COUNTIF(AR68:AR71,CONCATENATE("&gt;=",AR69))</f>
@@ -55440,7 +55449,7 @@
       </c>
       <c r="AF69" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE69 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG69" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE69 &amp; "_draw")</f>
@@ -55452,31 +55461,31 @@
       </c>
       <c r="AI69" s="123">
         <f>SUMIF($E$7:$E$78,$AE69,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE69,$G$7:$G$78)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AJ69" s="123">
         <f>SUMIF($E$7:$E$78,$AE69,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE69,$F$7:$F$78)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL69" s="123">
         <f>AI69-AJ69</f>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AM69" s="123">
         <f>AL69-AL72</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AN69" s="123">
         <f>AF69*3+AG69</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AO69" s="123">
         <f>AN69/AN72*10+BA69</f>
-        <v>1.4285714285714284</v>
+        <v>5</v>
       </c>
       <c r="AP69" s="123">
         <f>AO69*10000000+BI69*100+AM69/AM72*10+AI69/AI72*1++IF(AQ69=0,ROW(),AQ69)/2000000</f>
-        <v>14285719.044695219</v>
+        <v>50000007.238834411</v>
       </c>
       <c r="AQ69" s="126">
         <f>VLOOKUP(AE69,db_fifarank,2,FALSE)</f>
@@ -55484,11 +55493,11 @@
       </c>
       <c r="AR69" s="125">
         <f>AP69/AP72</f>
-        <v>0.16666670417364024</v>
+        <v>0.57142859164528825</v>
       </c>
       <c r="AS69" s="125" t="str">
         <f>IF(SUM(AF68:AH71)=12,J70,"2K")</f>
-        <v>2K</v>
+        <v>Portugal</v>
       </c>
       <c r="AT69" s="126" cm="1">
         <f t="array" ref="AT69">SUMPRODUCT(($S$7:$S$78=AE69&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE69&amp;"_win")*($U$7:$U$78))</f>
@@ -55567,7 +55576,7 @@
         <v>46207.0625</v>
       </c>
       <c r="BQ69" s="115"/>
-      <c r="BR69" s="164"/>
+      <c r="BR69" s="174"/>
       <c r="BS69" s="26" t="str">
         <f>IF(BP70&gt;BP71,BL70,IF(BP70&lt;BP71,BL71,""))</f>
         <v/>
@@ -55579,19 +55588,19 @@
         <f>IF(BW68="","",BT69*1000+BU69*10+BV69)</f>
         <v/>
       </c>
-      <c r="CE69" s="195"/>
-      <c r="CF69" s="195"/>
-      <c r="CG69" s="195"/>
-      <c r="CH69" s="195"/>
-      <c r="CI69" s="195"/>
-      <c r="CJ69" s="195"/>
-      <c r="CK69" s="185"/>
-      <c r="CL69" s="185"/>
-      <c r="CM69" s="185"/>
-      <c r="CN69" s="185"/>
-      <c r="CO69" s="185"/>
-      <c r="CP69" s="185"/>
-      <c r="CQ69" s="185"/>
+      <c r="CE69" s="175"/>
+      <c r="CF69" s="175"/>
+      <c r="CG69" s="175"/>
+      <c r="CH69" s="175"/>
+      <c r="CI69" s="175"/>
+      <c r="CJ69" s="175"/>
+      <c r="CK69" s="163"/>
+      <c r="CL69" s="163"/>
+      <c r="CM69" s="163"/>
+      <c r="CN69" s="163"/>
+      <c r="CO69" s="163"/>
+      <c r="CP69" s="163"/>
+      <c r="CQ69" s="163"/>
     </row>
     <row r="70" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A70" s="16">
@@ -55613,8 +55622,12 @@
         <f>AE47</f>
         <v>New Zealand</v>
       </c>
-      <c r="F70" s="19"/>
-      <c r="G70" s="20"/>
+      <c r="F70" s="19">
+        <v>1</v>
+      </c>
+      <c r="G70" s="20">
+        <v>5</v>
+      </c>
       <c r="H70" s="80" t="str">
         <f>AE44</f>
         <v>Belgium</v>
@@ -55626,7 +55639,7 @@
       </c>
       <c r="K70" s="23">
         <f>L70+M70+N70</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L70" s="23">
         <f>VLOOKUP(2,AD68:AN71,3,FALSE)</f>
@@ -55634,7 +55647,7 @@
       </c>
       <c r="M70" s="23">
         <f>VLOOKUP(2,AD68:AN71,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N70" s="23">
         <f>VLOOKUP(2,AD68:AN71,5,FALSE)</f>
@@ -55646,7 +55659,7 @@
       </c>
       <c r="P70" s="34">
         <f>L70*3+M70</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R70" s="123">
         <f>DATE(2026,6,26)+TIME(16,0,0)+gmt_delta</f>
@@ -55654,11 +55667,11 @@
       </c>
       <c r="S70" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>New Zealand_lose</v>
       </c>
       <c r="T70" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Belgium_win</v>
       </c>
       <c r="U70" s="123">
         <f t="shared" si="8"/>
@@ -55688,9 +55701,9 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB70" s="123" t="str">
+      <c r="AB70" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>-1</v>
       </c>
       <c r="AD70" s="123">
         <f>COUNTIF(AR68:AR71,CONCATENATE("&gt;=",AR70))</f>
@@ -55710,19 +55723,19 @@
       </c>
       <c r="AH70" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE70 &amp; "_lose")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI70" s="123">
         <f>SUMIF($E$7:$E$78,$AE70,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE70,$G$7:$G$78)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ70" s="123">
         <f>SUMIF($E$7:$E$78,$AE70,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE70,$F$7:$F$78)</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AL70" s="123">
         <f>AI70-AJ70</f>
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="AM70" s="123">
         <f>AL70-AL72</f>
@@ -55738,7 +55751,7 @@
       </c>
       <c r="AP70" s="123">
         <f>AO70*10000000+BI70*100+AM70/AM72*10+AI70/AI72*1++IF(AQ70=0,ROW(),AQ70)/2000000</f>
-        <v>0.14358981285714284</v>
+        <v>0.28644695571428569</v>
       </c>
       <c r="AQ70" s="126">
         <f>VLOOKUP(AE70,db_fifarank,2,FALSE)</f>
@@ -55746,7 +55759,7 @@
       </c>
       <c r="AR70" s="125">
         <f>AP70/AP72</f>
-        <v>1.6752143022647808E-9</v>
+        <v>3.2736791357454669E-9</v>
       </c>
       <c r="AT70" s="126" cm="1">
         <f t="array" ref="AT70">SUMPRODUCT(($S$7:$S$78=AE70&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE70&amp;"_win")*($U$7:$U$78))</f>
@@ -55812,12 +55825,12 @@
         <f>BH70/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK70" s="163">
+      <c r="BK70" s="173">
         <v>87</v>
       </c>
       <c r="BL70" s="24" t="str">
         <f>AS68</f>
-        <v>1K</v>
+        <v>Colombia</v>
       </c>
       <c r="BM70" s="61"/>
       <c r="BN70" s="63"/>
@@ -55849,8 +55862,12 @@
         <f>AE51</f>
         <v>Cape Verde</v>
       </c>
-      <c r="F71" s="19"/>
-      <c r="G71" s="20"/>
+      <c r="F71" s="19">
+        <v>0</v>
+      </c>
+      <c r="G71" s="20">
+        <v>0</v>
+      </c>
       <c r="H71" s="80" t="str">
         <f>AE52</f>
         <v>Saudi Arabia</v>
@@ -55862,11 +55879,11 @@
       </c>
       <c r="K71" s="23">
         <f>L71+M71+N71</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L71" s="23">
         <f>VLOOKUP(3,AD68:AN71,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M71" s="23">
         <f>VLOOKUP(3,AD68:AN71,4,FALSE)</f>
@@ -55878,11 +55895,11 @@
       </c>
       <c r="O71" s="23" t="str">
         <f>VLOOKUP(3,AD68:AN71,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD68:AN71,7,FALSE)</f>
-        <v>1 - 2</v>
+        <v>4 - 3</v>
       </c>
       <c r="P71" s="34">
         <f>L71*3+M71</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R71" s="123">
         <f>DATE(2026,6,26)+TIME(13,0,0)+gmt_delta</f>
@@ -55890,11 +55907,11 @@
       </c>
       <c r="S71" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Cape Verde_draw</v>
       </c>
       <c r="T71" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Saudi Arabia_draw</v>
       </c>
       <c r="U71" s="123">
         <f t="shared" si="8"/>
@@ -55924,9 +55941,9 @@
         <f t="shared" ref="AA71:AA78" si="29">IF(OR(E71=my_team,H71=my_team),1,IF(INT(MATCH(E71,$AE$8:$AE$78,0)/6)=$AA$6,1,0))</f>
         <v>0</v>
       </c>
-      <c r="AB71" s="123" t="str">
+      <c r="AB71" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AD71" s="123">
         <f>COUNTIF(AR68:AR71,CONCATENATE("&gt;=",AR71))</f>
@@ -55942,7 +55959,7 @@
       </c>
       <c r="AG71" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE71 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH71" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE71 &amp; "_lose")</f>
@@ -55962,19 +55979,19 @@
       </c>
       <c r="AM71" s="123">
         <f>AL71-AL72</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AN71" s="123">
         <f>AF71*3+AG71</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO71" s="123">
         <f>AN71/AN72*10+BA71</f>
-        <v>8.5714285714285712</v>
+        <v>8.75</v>
       </c>
       <c r="AP71" s="123">
         <f>AO71*10000000+BI71*100+AM71/AM72*10+AI71/AI72*1++IF(AQ71=0,ROW(),AQ71)/2000000</f>
-        <v>85714293.978868529</v>
+        <v>87500008.572275117</v>
       </c>
       <c r="AQ71" s="126">
         <f>VLOOKUP(AE71,db_fifarank,2,FALSE)</f>
@@ -55982,7 +55999,7 @@
       </c>
       <c r="AR71" s="125">
         <f>AP71/AP72</f>
-        <v>0.99999998833333459</v>
+        <v>0.9999999885714298</v>
       </c>
       <c r="AT71" s="126" cm="1">
         <f t="array" ref="AT71">SUMPRODUCT(($S$7:$S$78=AE71&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE71&amp;"_win")*($U$7:$U$78))</f>
@@ -56048,10 +56065,10 @@
         <f>BH71/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK71" s="164"/>
+      <c r="BK71" s="174"/>
       <c r="BL71" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!J3,AK80:AS91,9,FALSE),"3rd Group D/E/I/J/L")</f>
-        <v>3rd Group D/E/I/J/L</v>
+        <v>Ghana</v>
       </c>
       <c r="BM71" s="62"/>
       <c r="BN71" s="64"/>
@@ -56082,8 +56099,12 @@
         <f>AE53</f>
         <v>Uruguay</v>
       </c>
-      <c r="F72" s="19"/>
-      <c r="G72" s="20"/>
+      <c r="F72" s="19">
+        <v>0</v>
+      </c>
+      <c r="G72" s="20">
+        <v>1</v>
+      </c>
       <c r="H72" s="80" t="str">
         <f>AE50</f>
         <v>Spain</v>
@@ -56095,7 +56116,7 @@
       </c>
       <c r="K72" s="36">
         <f>L72+M72+N72</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L72" s="36">
         <f>VLOOKUP(4,AD68:AN71,3,FALSE)</f>
@@ -56107,11 +56128,11 @@
       </c>
       <c r="N72" s="36">
         <f>VLOOKUP(4,AD68:AN71,5,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O72" s="36" t="str">
         <f>VLOOKUP(4,AD68:AN71,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD68:AN71,7,FALSE)</f>
-        <v>1 - 8</v>
+        <v>2 - 11</v>
       </c>
       <c r="P72" s="37">
         <f>L72*3+M72</f>
@@ -56123,11 +56144,11 @@
       </c>
       <c r="S72" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Uruguay_lose</v>
       </c>
       <c r="T72" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Spain_win</v>
       </c>
       <c r="U72" s="123">
         <f t="shared" ref="U72:U78" si="31">IF(S72="",0,IF(VLOOKUP(E72,$AE$8:$AN$77,10,FALSE)=VLOOKUP(H72,$AE$8:$AN$77,10,FALSE),1,0))</f>
@@ -56157,9 +56178,9 @@
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="AB72" s="123" t="str">
+      <c r="AB72" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>-1</v>
       </c>
       <c r="AF72" s="123">
         <f t="shared" ref="AF72:AH72" si="35">MAX(AF68:AF71)-MIN(AF68:AF71)+1</f>
@@ -56167,11 +56188,11 @@
       </c>
       <c r="AG72" s="123">
         <f t="shared" si="35"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH72" s="123">
         <f t="shared" si="35"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI72" s="123">
         <f>MAX(AI68:AI71)+1</f>
@@ -56179,23 +56200,23 @@
       </c>
       <c r="AL72" s="123">
         <f>MIN(AL68:AL71)</f>
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="AM72" s="123">
         <f>MAX(AM68:AM71)+1</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AN72" s="123">
         <f>MAX(AN68:AN71)+1</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO72" s="123">
         <f>MAX(AO68:AO71)+1</f>
-        <v>9.5714285714285712</v>
+        <v>9.75</v>
       </c>
       <c r="AP72" s="123">
         <f>MAX(AP68:AP71)+1</f>
-        <v>85714294.978868529</v>
+        <v>87500009.572275117</v>
       </c>
       <c r="AT72" s="126">
         <f>MAX(AT68:AT71)-MIN(AT68:AT71)+1</f>
@@ -56266,8 +56287,12 @@
         <f>AE77</f>
         <v>Panama</v>
       </c>
-      <c r="F73" s="19"/>
-      <c r="G73" s="20"/>
+      <c r="F73" s="19">
+        <v>0</v>
+      </c>
+      <c r="G73" s="20">
+        <v>2</v>
+      </c>
       <c r="H73" s="80" t="str">
         <f>AE74</f>
         <v>England</v>
@@ -56286,11 +56311,11 @@
       </c>
       <c r="S73" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Panama_lose</v>
       </c>
       <c r="T73" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>England_win</v>
       </c>
       <c r="U73" s="123">
         <f t="shared" si="31"/>
@@ -56320,9 +56345,9 @@
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="AB73" s="123" t="str">
+      <c r="AB73" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>-1</v>
       </c>
     </row>
     <row r="74" spans="1:95" x14ac:dyDescent="0.2">
@@ -56345,8 +56370,12 @@
         <f>AE75</f>
         <v>Croatia</v>
       </c>
-      <c r="F74" s="19"/>
-      <c r="G74" s="20"/>
+      <c r="F74" s="19">
+        <v>2</v>
+      </c>
+      <c r="G74" s="20">
+        <v>1</v>
+      </c>
       <c r="H74" s="80" t="str">
         <f>AE76</f>
         <v>Ghana</v>
@@ -56386,11 +56415,11 @@
       </c>
       <c r="S74" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Croatia_win</v>
       </c>
       <c r="T74" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Ghana_lose</v>
       </c>
       <c r="U74" s="123">
         <f t="shared" si="31"/>
@@ -56420,9 +56449,9 @@
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="AB74" s="123" t="str">
+      <c r="AB74" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD74" s="123">
         <f>COUNTIF(AR74:AR77,CONCATENATE("&gt;=",AR74))</f>
@@ -56434,7 +56463,7 @@
       </c>
       <c r="AF74" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE74 &amp; "_win")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG74" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE74 &amp; "_draw")</f>
@@ -56446,7 +56475,7 @@
       </c>
       <c r="AI74" s="123">
         <f>SUMIF($E$7:$E$78,$AE74,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE74,$G$7:$G$78)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AJ74" s="123">
         <f>SUMIF($E$7:$E$78,$AE74,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE74,$F$7:$F$78)</f>
@@ -56454,23 +56483,23 @@
       </c>
       <c r="AL74" s="123">
         <f>AI74-AJ74</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AM74" s="123">
         <f>AL74-AL78</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AN74" s="123">
         <f>AF74*3+AG74</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AO74" s="123">
         <f>AN74/AN78*10+BA74</f>
-        <v>8.9803921568627452</v>
+        <v>8.75</v>
       </c>
       <c r="AP74" s="123">
         <f>AO74*10000000+BI74*100+AM74/AM78*10+AI74/AI78*1++IF(AQ74=0,ROW(),AQ74)/2000000</f>
-        <v>89804028.408756107</v>
+        <v>87500009.746944726</v>
       </c>
       <c r="AQ74" s="126">
         <f>VLOOKUP(AE74,db_fifarank,2,FALSE)</f>
@@ -56478,11 +56507,11 @@
       </c>
       <c r="AR74" s="125">
         <f>AP74/AP78</f>
-        <v>0.99999998886464214</v>
+        <v>0.99999998857143002</v>
       </c>
       <c r="AS74" s="125" t="str">
         <f>IF(SUM(AF74:AH77)=12,J75,"1L")</f>
-        <v>1L</v>
+        <v>England</v>
       </c>
       <c r="AT74" s="126" cm="1">
         <f t="array" ref="AT74">SUMPRODUCT(($S$7:$S$78=AE74&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE74&amp;"_win")*($U$7:$U$78))</f>
@@ -56490,7 +56519,7 @@
       </c>
       <c r="AU74" s="126" cm="1">
         <f t="array" ref="AU74">SUMPRODUCT(($S$7:$S$78=AE74&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE74&amp;"_draw")*($U$7:$U$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV74" s="126" cm="1">
         <f t="array" ref="AV74">SUMPRODUCT(($E$7:$E$78=AE74)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE74)*($U$7:$U$78)*($G$7:$G$78))</f>
@@ -56510,11 +56539,11 @@
       </c>
       <c r="AZ74" s="126">
         <f>AT74/AT78*1000+AU74/AU78*100+AY74/AY78*10+AV74/AV78</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BA74" s="126">
         <f>AZ74/AZ78</f>
-        <v>0.98039215686274506</v>
+        <v>0</v>
       </c>
       <c r="BB74" s="126" cm="1">
         <f t="array" ref="BB74">SUMPRODUCT(($S$7:$S$78=AE74&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE74&amp;"_win")*($X$7:$X$78))</f>
@@ -56522,7 +56551,7 @@
       </c>
       <c r="BC74" s="126" cm="1">
         <f t="array" ref="BC74">SUMPRODUCT(($S$7:$S$78=AE74&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE74&amp;"_draw")*($X$7:$X$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD74" s="126" cm="1">
         <f t="array" ref="BD74">SUMPRODUCT(($E$7:$E$78=AE74)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE74)*($X$7:$X$78)*($G$7:$G$78))</f>
@@ -56542,11 +56571,11 @@
       </c>
       <c r="BH74" s="126">
         <f>BB74/BB78*1000+BC74/BC78*100+BG74/BG78*10+BD74/BD78</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BI74" s="126">
         <f>BH74/BH78</f>
-        <v>0.98039215686274506</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:95" x14ac:dyDescent="0.2">
@@ -56569,8 +56598,12 @@
         <f>AE63</f>
         <v>Algeria</v>
       </c>
-      <c r="F75" s="19"/>
-      <c r="G75" s="20"/>
+      <c r="F75" s="19">
+        <v>3</v>
+      </c>
+      <c r="G75" s="20">
+        <v>3</v>
+      </c>
       <c r="H75" s="80" t="str">
         <f>AE64</f>
         <v>Austria</v>
@@ -56582,11 +56615,11 @@
       </c>
       <c r="K75" s="31">
         <f>L75+M75+N75</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L75" s="31">
         <f>VLOOKUP(1,AD74:AN77,3,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M75" s="31">
         <f>VLOOKUP(1,AD74:AN77,4,FALSE)</f>
@@ -56598,11 +56631,11 @@
       </c>
       <c r="O75" s="31" t="str">
         <f>VLOOKUP(1,AD74:AN77,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD74:AN77,7,FALSE)</f>
-        <v>4 - 2</v>
+        <v>6 - 2</v>
       </c>
       <c r="P75" s="32">
         <f>L75*3+M75</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R75" s="123">
         <f>DATE(2026,6,27)+TIME(15,0,0)+gmt_delta</f>
@@ -56610,47 +56643,47 @@
       </c>
       <c r="S75" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Algeria_draw</v>
       </c>
       <c r="T75" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Austria_draw</v>
       </c>
       <c r="U75" s="123">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V75" s="123">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W75" s="123">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X75" s="123">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y75" s="123">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z75" s="123">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA75" s="123">
         <f t="shared" si="29"/>
         <v>1</v>
       </c>
-      <c r="AB75" s="123" t="str">
+      <c r="AB75" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AD75" s="123">
         <f>COUNTIF(AR74:AR77,CONCATENATE("&gt;=",AR75))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE75" s="124" t="str">
         <f>VLOOKUP("Croatia",T,lang,FALSE)</f>
@@ -56658,7 +56691,7 @@
       </c>
       <c r="AF75" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE75 &amp; "_win")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG75" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE75 &amp; "_draw")</f>
@@ -56670,31 +56703,31 @@
       </c>
       <c r="AI75" s="123">
         <f>SUMIF($E$7:$E$78,$AE75,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE75,$G$7:$G$78)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AJ75" s="123">
         <f>SUMIF($E$7:$E$78,$AE75,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE75,$F$7:$F$78)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL75" s="123">
         <f>AI75-AJ75</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AM75" s="123">
         <f>AL75-AL78</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AN75" s="123">
         <f>AF75*3+AG75</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AO75" s="123">
         <f>AN75/AN78*10+BA75</f>
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="AP75" s="123">
         <f>AO75*10000000+BI75*100+AM75/AM78*10+AI75/AI78*1++IF(AQ75=0,ROW(),AQ75)/2000000</f>
-        <v>60000002.600858539</v>
+        <v>75000005.159588695</v>
       </c>
       <c r="AQ75" s="126">
         <f>VLOOKUP(AE75,db_fifarank,2,FALSE)</f>
@@ -56702,11 +56735,11 @@
       </c>
       <c r="AR75" s="125">
         <f>AP75/AP78</f>
-        <v>0.66812149739695748</v>
+        <v>0.85714281083339749</v>
       </c>
       <c r="AS75" s="125" t="str">
         <f>IF(SUM(AF74:AH77)=12,J76,"2L")</f>
-        <v>2L</v>
+        <v>Croatia</v>
       </c>
       <c r="AT75" s="126" cm="1">
         <f t="array" ref="AT75">SUMPRODUCT(($S$7:$S$78=AE75&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE75&amp;"_win")*($U$7:$U$78))</f>
@@ -56793,8 +56826,12 @@
         <f>AE65</f>
         <v>Jordan</v>
       </c>
-      <c r="F76" s="19"/>
-      <c r="G76" s="20"/>
+      <c r="F76" s="19">
+        <v>1</v>
+      </c>
+      <c r="G76" s="20">
+        <v>3</v>
+      </c>
       <c r="H76" s="80" t="str">
         <f>AE62</f>
         <v>Argentina</v>
@@ -56802,31 +56839,31 @@
       <c r="I76" s="69"/>
       <c r="J76" s="33" t="str">
         <f>VLOOKUP(2,AD74:AN77,2,FALSE)</f>
-        <v>Ghana</v>
+        <v>Croatia</v>
       </c>
       <c r="K76" s="23">
         <f>L76+M76+N76</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L76" s="23">
         <f>VLOOKUP(2,AD74:AN77,3,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M76" s="23">
         <f>VLOOKUP(2,AD74:AN77,4,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N76" s="23">
         <f>VLOOKUP(2,AD74:AN77,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O76" s="23" t="str">
         <f>VLOOKUP(2,AD74:AN77,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD74:AN77,7,FALSE)</f>
-        <v>1 - 0</v>
+        <v>5 - 5</v>
       </c>
       <c r="P76" s="34">
         <f>L76*3+M76</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R76" s="123">
         <f>DATE(2026,6,27)+TIME(15,0,0)+gmt_delta</f>
@@ -56834,11 +56871,11 @@
       </c>
       <c r="S76" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Jordan_lose</v>
       </c>
       <c r="T76" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Argentina_win</v>
       </c>
       <c r="U76" s="123">
         <f t="shared" si="31"/>
@@ -56868,13 +56905,13 @@
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="AB76" s="123" t="str">
+      <c r="AB76" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>-1</v>
       </c>
       <c r="AD76" s="123">
         <f>COUNTIF(AR74:AR77,CONCATENATE("&gt;=",AR76))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE76" s="124" t="str">
         <f>VLOOKUP("Ghana",T,lang,FALSE)</f>
@@ -56890,23 +56927,23 @@
       </c>
       <c r="AH76" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE76 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI76" s="123">
         <f>SUMIF($E$7:$E$78,$AE76,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE76,$G$7:$G$78)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ76" s="123">
         <f>SUMIF($E$7:$E$78,$AE76,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE76,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL76" s="123">
         <f>AI76-AJ76</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM76" s="123">
         <f>AL76-AL78</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN76" s="123">
         <f>AF76*3+AG76</f>
@@ -56914,11 +56951,11 @@
       </c>
       <c r="AO76" s="123">
         <f>AN76/AN78*10+BA76</f>
-        <v>8.9803921568627452</v>
+        <v>5</v>
       </c>
       <c r="AP76" s="123">
         <f>AO76*10000000+BI76*100+AM76/AM78*10+AI76/AI78*1++IF(AQ76=0,ROW(),AQ76)/2000000</f>
-        <v>89804025.808516294</v>
+        <v>50000004.730831884</v>
       </c>
       <c r="AQ76" s="126">
         <f>VLOOKUP(AE76,db_fifarank,2,FALSE)</f>
@@ -56926,7 +56963,7 @@
       </c>
       <c r="AR76" s="125">
         <f>AP76/AP78</f>
-        <v>0.99999995991004154</v>
+        <v>0.57142855531109471</v>
       </c>
       <c r="AT76" s="126" cm="1">
         <f t="array" ref="AT76">SUMPRODUCT(($S$7:$S$78=AE76&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE76&amp;"_win")*($U$7:$U$78))</f>
@@ -56934,7 +56971,7 @@
       </c>
       <c r="AU76" s="126" cm="1">
         <f t="array" ref="AU76">SUMPRODUCT(($S$7:$S$78=AE76&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE76&amp;"_draw")*($U$7:$U$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV76" s="126" cm="1">
         <f t="array" ref="AV76">SUMPRODUCT(($E$7:$E$78=AE76)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE76)*($U$7:$U$78)*($G$7:$G$78))</f>
@@ -56954,11 +56991,11 @@
       </c>
       <c r="AZ76" s="126">
         <f>AT76/AT78*1000+AU76/AU78*100+AY76/AY78*10+AV76/AV78</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BA76" s="126">
         <f>AZ76/AZ78</f>
-        <v>0.98039215686274506</v>
+        <v>0</v>
       </c>
       <c r="BB76" s="126" cm="1">
         <f t="array" ref="BB76">SUMPRODUCT(($S$7:$S$78=AE76&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE76&amp;"_win")*($X$7:$X$78))</f>
@@ -56966,7 +57003,7 @@
       </c>
       <c r="BC76" s="126" cm="1">
         <f t="array" ref="BC76">SUMPRODUCT(($S$7:$S$78=AE76&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE76&amp;"_draw")*($X$7:$X$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD76" s="126" cm="1">
         <f t="array" ref="BD76">SUMPRODUCT(($E$7:$E$78=AE76)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE76)*($X$7:$X$78)*($G$7:$G$78))</f>
@@ -56986,11 +57023,11 @@
       </c>
       <c r="BH76" s="126">
         <f>BB76/BB78*1000+BC76/BC78*100+BG76/BG78*10+BD76/BD78</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BI76" s="126">
         <f>BH76/BH78</f>
-        <v>0.98039215686274506</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:95" x14ac:dyDescent="0.2">
@@ -57013,8 +57050,12 @@
         <f>AE71</f>
         <v>Colombia</v>
       </c>
-      <c r="F77" s="19"/>
-      <c r="G77" s="20"/>
+      <c r="F77" s="19">
+        <v>0</v>
+      </c>
+      <c r="G77" s="20">
+        <v>0</v>
+      </c>
       <c r="H77" s="80" t="str">
         <f>AE68</f>
         <v>Portugal</v>
@@ -57022,11 +57063,11 @@
       <c r="I77" s="69"/>
       <c r="J77" s="33" t="str">
         <f>VLOOKUP(3,AD74:AN77,2,FALSE)</f>
-        <v>Croatia</v>
+        <v>Ghana</v>
       </c>
       <c r="K77" s="23">
         <f>L77+M77+N77</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L77" s="23">
         <f>VLOOKUP(3,AD74:AN77,3,FALSE)</f>
@@ -57034,7 +57075,7 @@
       </c>
       <c r="M77" s="23">
         <f>VLOOKUP(3,AD74:AN77,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N77" s="23">
         <f>VLOOKUP(3,AD74:AN77,5,FALSE)</f>
@@ -57042,11 +57083,11 @@
       </c>
       <c r="O77" s="23" t="str">
         <f>VLOOKUP(3,AD74:AN77,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD74:AN77,7,FALSE)</f>
-        <v>3 - 4</v>
+        <v>2 - 2</v>
       </c>
       <c r="P77" s="34">
         <f>L77*3+M77</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R77" s="123">
         <f>DATE(2026,6,27)+TIME(12,30,0)+gmt_delta</f>
@@ -57054,11 +57095,11 @@
       </c>
       <c r="S77" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Colombia_draw</v>
       </c>
       <c r="T77" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Portugal_draw</v>
       </c>
       <c r="U77" s="123">
         <f t="shared" si="31"/>
@@ -57088,9 +57129,9 @@
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="AB77" s="123" t="str">
+      <c r="AB77" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AD77" s="123">
         <f>COUNTIF(AR74:AR77,CONCATENATE("&gt;=",AR77))</f>
@@ -57110,7 +57151,7 @@
       </c>
       <c r="AH77" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE77 &amp; "_lose")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI77" s="123">
         <f>SUMIF($E$7:$E$78,$AE77,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE77,$G$7:$G$78)</f>
@@ -57118,11 +57159,11 @@
       </c>
       <c r="AJ77" s="123">
         <f>SUMIF($E$7:$E$78,$AE77,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE77,$F$7:$F$78)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AL77" s="123">
         <f>AI77-AJ77</f>
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="AM77" s="123">
         <f>AL77-AL78</f>
@@ -57146,7 +57187,7 @@
       </c>
       <c r="AR77" s="125">
         <f>AP77/AP78</f>
-        <v>8.5777888260868168E-12</v>
+        <v>8.8036560615725139E-12</v>
       </c>
       <c r="AT77" s="126" cm="1">
         <f t="array" ref="AT77">SUMPRODUCT(($S$7:$S$78=AE77&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE77&amp;"_win")*($U$7:$U$78))</f>
@@ -57233,8 +57274,12 @@
         <f>AE69</f>
         <v>DR Congo</v>
       </c>
-      <c r="F78" s="19"/>
-      <c r="G78" s="20"/>
+      <c r="F78" s="19">
+        <v>3</v>
+      </c>
+      <c r="G78" s="20">
+        <v>1</v>
+      </c>
       <c r="H78" s="80" t="str">
         <f>AE70</f>
         <v>Uzbekistan</v>
@@ -57246,7 +57291,7 @@
       </c>
       <c r="K78" s="36">
         <f>L78+M78+N78</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L78" s="36">
         <f>VLOOKUP(4,AD74:AN77,3,FALSE)</f>
@@ -57258,11 +57303,11 @@
       </c>
       <c r="N78" s="36">
         <f>VLOOKUP(4,AD74:AN77,5,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O78" s="36" t="str">
         <f>VLOOKUP(4,AD74:AN77,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD74:AN77,7,FALSE)</f>
-        <v>0 - 2</v>
+        <v>0 - 4</v>
       </c>
       <c r="P78" s="37">
         <f>L78*3+M78</f>
@@ -57274,11 +57319,11 @@
       </c>
       <c r="S78" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>DR Congo_win</v>
       </c>
       <c r="T78" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Uzbekistan_lose</v>
       </c>
       <c r="U78" s="123">
         <f t="shared" si="31"/>
@@ -57308,13 +57353,13 @@
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="AB78" s="123" t="str">
+      <c r="AB78" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AF78" s="123">
         <f t="shared" ref="AF78:AH78" si="36">MAX(AF74:AF77)-MIN(AF74:AF77)+1</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG78" s="123">
         <f t="shared" si="36"/>
@@ -57322,31 +57367,31 @@
       </c>
       <c r="AH78" s="123">
         <f t="shared" si="36"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI78" s="123">
         <f>MAX(AI74:AI77)+1</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AL78" s="123">
         <f>MIN(AL74:AL77)</f>
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="AM78" s="123">
         <f>MAX(AM74:AM77)+1</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AN78" s="123">
         <f>MAX(AN74:AN77)+1</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AO78" s="123">
         <f>MAX(AO74:AO77)+1</f>
-        <v>9.9803921568627452</v>
+        <v>9.75</v>
       </c>
       <c r="AP78" s="123">
         <f>MAX(AP74:AP77)+1</f>
-        <v>89804029.408756107</v>
+        <v>87500010.746944726</v>
       </c>
       <c r="AT78" s="126">
         <f>MAX(AT74:AT77)-MIN(AT74:AT77)+1</f>
@@ -57354,7 +57399,7 @@
       </c>
       <c r="AU78" s="126">
         <f>MAX(AU74:AU77)-MIN(AU74:AU77)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV78" s="126">
         <f>MAX(AV74:AV77)-MIN(AV74:AV77)+1</f>
@@ -57370,7 +57415,7 @@
       </c>
       <c r="AZ78" s="126">
         <f>MAX(AZ74:AZ77)+1</f>
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="BB78" s="126">
         <f>MAX(BB74:BB77)-MIN(BB74:BB77)+1</f>
@@ -57378,7 +57423,7 @@
       </c>
       <c r="BC78" s="126">
         <f>MAX(BC74:BC77)-MIN(BC74:BC77)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BD78" s="126">
         <f>MAX(BD74:BD77)-MIN(BD74:BD77)+1</f>
@@ -57394,7 +57439,7 @@
       </c>
       <c r="BH78" s="126">
         <f>MAX(BH74:BH77)+1</f>
-        <v>51</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:95" x14ac:dyDescent="0.2">
@@ -57455,7 +57500,7 @@
       </c>
       <c r="AD80" s="123">
         <f>COUNTIF($AP$80:$AP$91,CONCATENATE("&gt;=",AP80))</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE80" s="124" t="str">
         <f>J11</f>
@@ -57506,11 +57551,11 @@
       </c>
       <c r="AR80" s="125" t="str">
         <f>IF(AD80&lt;=8,RIGHT(AK80,1),"")</f>
-        <v>A</v>
+        <v/>
       </c>
       <c r="AS80" s="129" t="str">
         <f>IF(AD80&lt;=8,AE80,"")</f>
-        <v>Korea Republic</v>
+        <v/>
       </c>
       <c r="AT80" s="130" t="str">
         <f>"Ⓐ "&amp;AE80</f>
@@ -57529,7 +57574,7 @@
       <c r="I81" s="69"/>
       <c r="J81" s="96" t="str">
         <f>VLOOKUP(1,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓕ Sweden</v>
+        <v>Ⓚ DR Congo</v>
       </c>
       <c r="K81" s="97">
         <f>L81+M81+N81</f>
@@ -57549,7 +57594,7 @@
       </c>
       <c r="O81" s="97" t="str">
         <f>VLOOKUP(1,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(1,$AD$80:$AN$91,7,FALSE)</f>
-        <v>7 - 7</v>
+        <v>4 - 3</v>
       </c>
       <c r="P81" s="98">
         <f>L81*3+M81</f>
@@ -57557,7 +57602,7 @@
       </c>
       <c r="AD81" s="123">
         <f t="shared" ref="AD81:AD91" si="38">COUNTIF($AP$80:$AP$91,CONCATENATE("&gt;=",AP81))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE81" s="124" t="str">
         <f>J17</f>
@@ -57608,7 +57653,7 @@
       </c>
       <c r="AR81" s="125" t="str">
         <f>AR80&amp;IF(AD81&lt;=8,RIGHT(AK81,1),"")</f>
-        <v>AB</v>
+        <v>B</v>
       </c>
       <c r="AS81" s="129" t="str">
         <f t="shared" ref="AS81:AS91" si="46">IF(AD81&lt;=8,AE81,"")</f>
@@ -57631,7 +57676,7 @@
       <c r="I82" s="69"/>
       <c r="J82" s="99" t="str">
         <f>VLOOKUP(2,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓔ Ecuador</v>
+        <v>Ⓕ Sweden</v>
       </c>
       <c r="K82" s="100">
         <f t="shared" ref="K82:K92" si="47">L82+M82+N82</f>
@@ -57651,7 +57696,7 @@
       </c>
       <c r="O82" s="100" t="str">
         <f>VLOOKUP(2,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(2,$AD$80:$AN$91,7,FALSE)</f>
-        <v>2 - 2</v>
+        <v>7 - 7</v>
       </c>
       <c r="P82" s="101">
         <f t="shared" ref="P82:P92" si="48">L82*3+M82</f>
@@ -57659,7 +57704,7 @@
       </c>
       <c r="AD82" s="123">
         <f t="shared" si="38"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE82" s="124" t="str">
         <f>J23</f>
@@ -57710,7 +57755,7 @@
       </c>
       <c r="AR82" s="125" t="str">
         <f t="shared" ref="AR82:AR91" si="50">AR81&amp;IF(AD82&lt;=8,RIGHT(AK82,1),"")</f>
-        <v>AB</v>
+        <v>B</v>
       </c>
       <c r="AS82" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57724,18 +57769,18 @@
     <row r="83" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="73"/>
       <c r="B83" s="73"/>
-      <c r="C83" s="186" t="s">
+      <c r="C83" s="164" t="s">
         <v>3183</v>
       </c>
-      <c r="D83" s="187"/>
-      <c r="E83" s="187"/>
-      <c r="F83" s="187"/>
-      <c r="G83" s="188"/>
+      <c r="D83" s="165"/>
+      <c r="E83" s="165"/>
+      <c r="F83" s="165"/>
+      <c r="G83" s="166"/>
       <c r="H83" s="75"/>
       <c r="I83" s="69"/>
       <c r="J83" s="99" t="str">
         <f>VLOOKUP(3,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓑ Bosnia and Herzegovina</v>
+        <v>Ⓔ Ecuador</v>
       </c>
       <c r="K83" s="100">
         <f t="shared" si="47"/>
@@ -57755,7 +57800,7 @@
       </c>
       <c r="O83" s="100" t="str">
         <f>VLOOKUP(3,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(3,$AD$80:$AN$91,7,FALSE)</f>
-        <v>5 - 6</v>
+        <v>2 - 2</v>
       </c>
       <c r="P83" s="101">
         <f t="shared" si="48"/>
@@ -57763,7 +57808,7 @@
       </c>
       <c r="AD83" s="123">
         <f t="shared" si="38"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE83" s="124" t="str">
         <f>J29</f>
@@ -57814,7 +57859,7 @@
       </c>
       <c r="AR83" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABD</v>
+        <v>BD</v>
       </c>
       <c r="AS83" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57828,16 +57873,16 @@
     <row r="84" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="73"/>
       <c r="B84" s="73"/>
-      <c r="C84" s="189"/>
-      <c r="D84" s="190"/>
-      <c r="E84" s="190"/>
-      <c r="F84" s="190"/>
-      <c r="G84" s="191"/>
+      <c r="C84" s="167"/>
+      <c r="D84" s="168"/>
+      <c r="E84" s="168"/>
+      <c r="F84" s="168"/>
+      <c r="G84" s="169"/>
       <c r="H84" s="75"/>
       <c r="I84" s="69"/>
       <c r="J84" s="99" t="str">
         <f>VLOOKUP(4,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓓ Paraguay</v>
+        <v>Ⓛ Ghana</v>
       </c>
       <c r="K84" s="100">
         <f t="shared" si="47"/>
@@ -57857,7 +57902,7 @@
       </c>
       <c r="O84" s="100" t="str">
         <f>VLOOKUP(4,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(4,$AD$80:$AN$91,7,FALSE)</f>
-        <v>2 - 4</v>
+        <v>2 - 2</v>
       </c>
       <c r="P84" s="101">
         <f t="shared" si="48"/>
@@ -57877,7 +57922,7 @@
       </c>
       <c r="AD84" s="123">
         <f t="shared" si="38"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE84" s="124" t="str">
         <f>J35</f>
@@ -57928,7 +57973,7 @@
       </c>
       <c r="AR84" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABDE</v>
+        <v>BDE</v>
       </c>
       <c r="AS84" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57942,16 +57987,16 @@
     <row r="85" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="73"/>
       <c r="B85" s="73"/>
-      <c r="C85" s="189"/>
-      <c r="D85" s="190"/>
-      <c r="E85" s="190"/>
-      <c r="F85" s="190"/>
-      <c r="G85" s="191"/>
+      <c r="C85" s="167"/>
+      <c r="D85" s="168"/>
+      <c r="E85" s="168"/>
+      <c r="F85" s="168"/>
+      <c r="G85" s="169"/>
       <c r="H85" s="75"/>
       <c r="I85" s="69"/>
       <c r="J85" s="99" t="str">
         <f>VLOOKUP(5,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓘ Senegal</v>
+        <v>Ⓑ Bosnia and Herzegovina</v>
       </c>
       <c r="K85" s="100">
         <f t="shared" si="47"/>
@@ -57963,19 +58008,19 @@
       </c>
       <c r="M85" s="100">
         <f>VLOOKUP(5,$AD$80:$AN$91,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N85" s="100">
         <f>VLOOKUP(5,$AD$80:$AN$91,5,FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O85" s="100" t="str">
         <f>VLOOKUP(5,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(5,$AD$80:$AN$91,7,FALSE)</f>
-        <v>8 - 6</v>
+        <v>5 - 6</v>
       </c>
       <c r="P85" s="101">
         <f t="shared" si="48"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R85" s="123">
         <f>DATE(2026,12,3)+TIME(8,0,0)+gmt_delta</f>
@@ -57991,7 +58036,7 @@
       </c>
       <c r="AD85" s="123">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE85" s="124" t="str">
         <f>J41</f>
@@ -58042,7 +58087,7 @@
       </c>
       <c r="AR85" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABDEF</v>
+        <v>BDEF</v>
       </c>
       <c r="AS85" s="129" t="str">
         <f t="shared" si="46"/>
@@ -58056,20 +58101,20 @@
     <row r="86" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="73"/>
       <c r="B86" s="73"/>
-      <c r="C86" s="189"/>
-      <c r="D86" s="190"/>
-      <c r="E86" s="190"/>
-      <c r="F86" s="190"/>
-      <c r="G86" s="191"/>
+      <c r="C86" s="167"/>
+      <c r="D86" s="168"/>
+      <c r="E86" s="168"/>
+      <c r="F86" s="168"/>
+      <c r="G86" s="169"/>
       <c r="H86" s="75"/>
       <c r="I86" s="69"/>
       <c r="J86" s="99" t="str">
         <f>VLOOKUP(6,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓛ Croatia</v>
+        <v>Ⓙ Algeria</v>
       </c>
       <c r="K86" s="100">
         <f t="shared" si="47"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L86" s="100">
         <f>VLOOKUP(6,$AD$80:$AN$91,3,FALSE)</f>
@@ -58077,7 +58122,7 @@
       </c>
       <c r="M86" s="100">
         <f>VLOOKUP(6,$AD$80:$AN$91,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N86" s="100">
         <f>VLOOKUP(6,$AD$80:$AN$91,5,FALSE)</f>
@@ -58085,11 +58130,11 @@
       </c>
       <c r="O86" s="100" t="str">
         <f>VLOOKUP(6,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(6,$AD$80:$AN$91,7,FALSE)</f>
-        <v>3 - 4</v>
+        <v>5 - 7</v>
       </c>
       <c r="P86" s="101">
         <f t="shared" si="48"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R86" s="123">
         <f>DATE(2026,12,4)+TIME(8,0,0)+gmt_delta</f>
@@ -58105,11 +58150,11 @@
       </c>
       <c r="AD86" s="123">
         <f t="shared" si="38"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE86" s="124" t="str">
         <f>J47</f>
-        <v>Belgium</v>
+        <v>Iran</v>
       </c>
       <c r="AF86" s="123">
         <f t="shared" si="39"/>
@@ -58117,7 +58162,7 @@
       </c>
       <c r="AG86" s="123">
         <f t="shared" si="49"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH86" s="123">
         <f t="shared" si="40"/>
@@ -58125,11 +58170,11 @@
       </c>
       <c r="AI86" s="123">
         <f t="shared" si="41"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AJ86" s="123">
         <f t="shared" si="42"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AK86" s="123" t="s">
         <v>3187</v>
@@ -58144,19 +58189,19 @@
       </c>
       <c r="AN86" s="123">
         <f t="shared" si="45"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP86" s="123">
         <f>AN86/AN92*10000+AM86/AM92*1000+AI86/AI92*100+IF(AQ86=0,ROW(),AQ86)/2000000</f>
-        <v>4511.1119784661114</v>
+        <v>6533.3341409833329</v>
       </c>
       <c r="AQ86" s="126">
         <f t="shared" si="37"/>
-        <v>1734.71</v>
+        <v>1615.3</v>
       </c>
       <c r="AR86" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABDEF</v>
+        <v>BDEF</v>
       </c>
       <c r="AS86" s="129" t="str">
         <f t="shared" si="46"/>
@@ -58164,22 +58209,22 @@
       </c>
       <c r="AT86" s="130" t="str">
         <f>"Ⓖ "&amp;AE86</f>
-        <v>Ⓖ Belgium</v>
+        <v>Ⓖ Iran</v>
       </c>
     </row>
     <row r="87" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="73"/>
       <c r="B87" s="73"/>
-      <c r="C87" s="189"/>
-      <c r="D87" s="190"/>
-      <c r="E87" s="190"/>
-      <c r="F87" s="190"/>
-      <c r="G87" s="191"/>
+      <c r="C87" s="167"/>
+      <c r="D87" s="168"/>
+      <c r="E87" s="168"/>
+      <c r="F87" s="168"/>
+      <c r="G87" s="169"/>
       <c r="H87" s="75"/>
       <c r="I87" s="69"/>
       <c r="J87" s="99" t="str">
         <f>VLOOKUP(7,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓐ Korea Republic</v>
+        <v>Ⓓ Paraguay</v>
       </c>
       <c r="K87" s="100">
         <f t="shared" si="47"/>
@@ -58191,19 +58236,19 @@
       </c>
       <c r="M87" s="100">
         <f>VLOOKUP(7,$AD$80:$AN$91,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N87" s="100">
         <f>VLOOKUP(7,$AD$80:$AN$91,5,FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O87" s="100" t="str">
         <f>VLOOKUP(7,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(7,$AD$80:$AN$91,7,FALSE)</f>
-        <v>2 - 3</v>
+        <v>2 - 4</v>
       </c>
       <c r="P87" s="101">
         <f t="shared" si="48"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R87" s="123">
         <f>DATE(2026,12,4)+TIME(4,0,0)+gmt_delta</f>
@@ -58219,11 +58264,11 @@
       </c>
       <c r="AD87" s="123">
         <f t="shared" si="38"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AE87" s="124" t="str">
         <f>J53</f>
-        <v>Cape Verde</v>
+        <v>Uruguay</v>
       </c>
       <c r="AF87" s="123">
         <f t="shared" si="39"/>
@@ -58235,26 +58280,26 @@
       </c>
       <c r="AH87" s="123">
         <f t="shared" si="40"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI87" s="123">
         <f t="shared" si="41"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ87" s="123">
         <f t="shared" si="42"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AK87" s="123" t="s">
         <v>3188</v>
       </c>
       <c r="AL87" s="123">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM87" s="123">
         <f t="shared" si="44"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN87" s="123">
         <f t="shared" si="45"/>
@@ -58262,15 +58307,15 @@
       </c>
       <c r="AP87" s="123">
         <f>AN87/AN92*10000+AM87/AM92*1000+AI87/AI92*100+IF(AQ87=0,ROW(),AQ87)/2000000</f>
-        <v>4522.2229052872226</v>
+        <v>4366.6675032016665</v>
       </c>
       <c r="AQ87" s="126">
         <f t="shared" si="37"/>
-        <v>1366.13</v>
+        <v>1673.07</v>
       </c>
       <c r="AR87" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABDEF</v>
+        <v>BDEF</v>
       </c>
       <c r="AS87" s="129" t="str">
         <f t="shared" si="46"/>
@@ -58278,26 +58323,26 @@
       </c>
       <c r="AT87" s="130" t="str">
         <f>"Ⓗ "&amp;AE87</f>
-        <v>Ⓗ Cape Verde</v>
+        <v>Ⓗ Uruguay</v>
       </c>
     </row>
     <row r="88" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="73"/>
       <c r="B88" s="73"/>
-      <c r="C88" s="192"/>
-      <c r="D88" s="193"/>
-      <c r="E88" s="193"/>
-      <c r="F88" s="193"/>
-      <c r="G88" s="194"/>
+      <c r="C88" s="170"/>
+      <c r="D88" s="171"/>
+      <c r="E88" s="171"/>
+      <c r="F88" s="171"/>
+      <c r="G88" s="172"/>
       <c r="H88" s="75"/>
       <c r="I88" s="69"/>
       <c r="J88" s="99" t="str">
         <f>VLOOKUP(8,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓙ Algeria</v>
+        <v>Ⓘ Senegal</v>
       </c>
       <c r="K88" s="100">
         <f t="shared" si="47"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L88" s="100">
         <f>VLOOKUP(8,$AD$80:$AN$91,3,FALSE)</f>
@@ -58309,11 +58354,11 @@
       </c>
       <c r="N88" s="100">
         <f>VLOOKUP(8,$AD$80:$AN$91,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O88" s="100" t="str">
         <f>VLOOKUP(8,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(8,$AD$80:$AN$91,7,FALSE)</f>
-        <v>2 - 4</v>
+        <v>8 - 6</v>
       </c>
       <c r="P88" s="101">
         <f t="shared" si="48"/>
@@ -58333,7 +58378,7 @@
       </c>
       <c r="AD88" s="123">
         <f t="shared" si="38"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AE88" s="124" t="str">
         <f>J59</f>
@@ -58384,7 +58429,7 @@
       </c>
       <c r="AR88" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABDEFI</v>
+        <v>BDEFI</v>
       </c>
       <c r="AS88" s="129" t="str">
         <f t="shared" si="46"/>
@@ -58407,7 +58452,7 @@
       <c r="I89" s="69"/>
       <c r="J89" s="102" t="str">
         <f>VLOOKUP(9,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓒ Scotland</v>
+        <v>Ⓖ Iran</v>
       </c>
       <c r="K89" s="103">
         <f t="shared" si="47"/>
@@ -58415,19 +58460,19 @@
       </c>
       <c r="L89" s="103">
         <f>VLOOKUP(9,$AD$80:$AN$91,3,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M89" s="103">
         <f>VLOOKUP(9,$AD$80:$AN$91,4,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N89" s="103">
         <f>VLOOKUP(9,$AD$80:$AN$91,5,FALSE)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O89" s="103" t="str">
         <f>VLOOKUP(9,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(9,$AD$80:$AN$91,7,FALSE)</f>
-        <v>1 - 4</v>
+        <v>3 - 3</v>
       </c>
       <c r="P89" s="104">
         <f t="shared" si="48"/>
@@ -58447,7 +58492,7 @@
       </c>
       <c r="AD89" s="123">
         <f t="shared" si="38"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE89" s="124" t="str">
         <f>J65</f>
@@ -58459,7 +58504,7 @@
       </c>
       <c r="AG89" s="123">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH89" s="123">
         <f t="shared" si="40"/>
@@ -58467,11 +58512,11 @@
       </c>
       <c r="AI89" s="123">
         <f t="shared" si="41"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AJ89" s="123">
         <f t="shared" si="42"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AK89" s="123" t="s">
         <v>3190</v>
@@ -58486,11 +58531,11 @@
       </c>
       <c r="AN89" s="123">
         <f t="shared" si="45"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP89" s="123">
         <f>AN89/AN92*10000+AM89/AM92*1000+AI89/AI92*100+IF(AQ89=0,ROW(),AQ89)/2000000</f>
-        <v>6188.8896710188892</v>
+        <v>8222.2230043522231</v>
       </c>
       <c r="AQ89" s="126">
         <f t="shared" si="37"/>
@@ -58498,7 +58543,7 @@
       </c>
       <c r="AR89" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABDEFIJ</v>
+        <v>BDEFIJ</v>
       </c>
       <c r="AS89" s="129" t="str">
         <f t="shared" si="46"/>
@@ -58521,31 +58566,31 @@
       <c r="I90" s="69"/>
       <c r="J90" s="102" t="str">
         <f>VLOOKUP(10,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓗ Cape Verde</v>
+        <v>Ⓐ Korea Republic</v>
       </c>
       <c r="K90" s="103">
         <f t="shared" si="47"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L90" s="103">
         <f>VLOOKUP(10,$AD$80:$AN$91,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" s="103">
         <f>VLOOKUP(10,$AD$80:$AN$91,4,FALSE)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N90" s="103">
         <f>VLOOKUP(10,$AD$80:$AN$91,5,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O90" s="103" t="str">
         <f>VLOOKUP(10,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(10,$AD$80:$AN$91,7,FALSE)</f>
-        <v>2 - 2</v>
+        <v>2 - 3</v>
       </c>
       <c r="P90" s="104">
         <f t="shared" si="48"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R90" s="123">
         <f>DATE(2026,12,6)+TIME(4,0,0)+gmt_delta</f>
@@ -58561,7 +58606,7 @@
       </c>
       <c r="AD90" s="123">
         <f t="shared" si="38"/>
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AE90" s="124" t="str">
         <f>J71</f>
@@ -58569,7 +58614,7 @@
       </c>
       <c r="AF90" s="123">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG90" s="123">
         <f t="shared" si="49"/>
@@ -58581,30 +58626,30 @@
       </c>
       <c r="AI90" s="123">
         <f t="shared" si="41"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AJ90" s="123">
         <f t="shared" si="42"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK90" s="123" t="s">
         <v>3191</v>
       </c>
       <c r="AL90" s="123">
         <f t="shared" si="43"/>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AM90" s="123">
         <f t="shared" si="44"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AN90" s="123">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AP90" s="123">
         <f>AN90/AN92*10000+AM90/AM92*1000+AI90/AI92*100+IF(AQ90=0,ROW(),AQ90)/2000000</f>
-        <v>2344.4451836194448</v>
+        <v>8711.1118502861118</v>
       </c>
       <c r="AQ90" s="126">
         <f t="shared" si="37"/>
@@ -58612,11 +58657,11 @@
       </c>
       <c r="AR90" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABDEFIJ</v>
+        <v>BDEFIJK</v>
       </c>
       <c r="AS90" s="129" t="str">
         <f t="shared" si="46"/>
-        <v/>
+        <v>DR Congo</v>
       </c>
       <c r="AT90" s="130" t="str">
         <f>"Ⓚ "&amp;AE90</f>
@@ -58635,31 +58680,31 @@
       <c r="I91" s="69"/>
       <c r="J91" s="102" t="str">
         <f>VLOOKUP(11,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓖ Belgium</v>
+        <v>Ⓒ Scotland</v>
       </c>
       <c r="K91" s="103">
         <f t="shared" si="47"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L91" s="103">
         <f>VLOOKUP(11,$AD$80:$AN$91,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M91" s="103">
         <f>VLOOKUP(11,$AD$80:$AN$91,4,FALSE)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N91" s="103">
         <f>VLOOKUP(11,$AD$80:$AN$91,5,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O91" s="103" t="str">
         <f>VLOOKUP(11,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(11,$AD$80:$AN$91,7,FALSE)</f>
-        <v>1 - 1</v>
+        <v>1 - 4</v>
       </c>
       <c r="P91" s="104">
         <f t="shared" si="48"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R91" s="123">
         <f>DATE(2026,12,6)+TIME(8,0,0)+gmt_delta</f>
@@ -58675,11 +58720,11 @@
       </c>
       <c r="AD91" s="123">
         <f t="shared" si="38"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE91" s="124" t="str">
         <f>J77</f>
-        <v>Croatia</v>
+        <v>Ghana</v>
       </c>
       <c r="AF91" s="123">
         <f t="shared" si="39"/>
@@ -58687,7 +58732,7 @@
       </c>
       <c r="AG91" s="123">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH91" s="123">
         <f>VLOOKUP($AE91,$AE$8:$AQ$78,4,FALSE)</f>
@@ -58695,46 +58740,46 @@
       </c>
       <c r="AI91" s="123">
         <f>VLOOKUP($AE91,$AE$8:$AQ$78,5,FALSE)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ91" s="123">
         <f>VLOOKUP($AE91,$AE$8:$AQ$78,6,FALSE)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AK91" s="123" t="s">
         <v>3192</v>
       </c>
       <c r="AL91" s="123">
         <f>VLOOKUP($AE91,$AE$8:$AQ$78,8,FALSE)</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AM91" s="123">
         <f t="shared" si="44"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN91" s="123">
         <f>VLOOKUP($AE91,$AE$8:$AQ$78,10,FALSE)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP91" s="123">
         <f>AN91/AN92*10000+AM91/AM92*1000+AI91/AI92*100+IF(AQ91=0,ROW(),AQ91)/2000000</f>
-        <v>6366.6675252016657</v>
+        <v>8522.2228953772228</v>
       </c>
       <c r="AQ91" s="126">
         <f t="shared" si="37"/>
-        <v>1717.07</v>
+        <v>1346.31</v>
       </c>
       <c r="AR91" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>ABDEFIJL</v>
+        <v>BDEFIJKL</v>
       </c>
       <c r="AS91" s="129" t="str">
         <f t="shared" si="46"/>
-        <v>Croatia</v>
+        <v>Ghana</v>
       </c>
       <c r="AT91" s="130" t="str">
         <f>"Ⓛ "&amp;AE91</f>
-        <v>Ⓛ Croatia</v>
+        <v>Ⓛ Ghana</v>
       </c>
     </row>
     <row r="92" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -58749,11 +58794,11 @@
       <c r="I92" s="69"/>
       <c r="J92" s="105" t="str">
         <f>VLOOKUP(12,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓚ DR Congo</v>
+        <v>Ⓗ Uruguay</v>
       </c>
       <c r="K92" s="106">
         <f t="shared" si="47"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L92" s="106">
         <f>VLOOKUP(12,$AD$80:$AN$91,3,FALSE)</f>
@@ -58761,7 +58806,7 @@
       </c>
       <c r="M92" s="106">
         <f>VLOOKUP(12,$AD$80:$AN$91,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N92" s="106">
         <f>VLOOKUP(12,$AD$80:$AN$91,5,FALSE)</f>
@@ -58769,11 +58814,11 @@
       </c>
       <c r="O92" s="106" t="str">
         <f>VLOOKUP(12,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(12,$AD$80:$AN$91,7,FALSE)</f>
-        <v>1 - 2</v>
+        <v>3 - 4</v>
       </c>
       <c r="P92" s="107">
         <f t="shared" si="48"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF92" s="123">
         <f>MAX(AF80:AF91)+1</f>
@@ -58781,7 +58826,7 @@
       </c>
       <c r="AG92" s="123">
         <f>MAX(AG80:AG91)+1</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH92" s="123">
         <f>MAX(AH80:AH91)+1</f>
@@ -58809,7 +58854,7 @@
       </c>
       <c r="AS92" s="126" t="b">
         <f>SUM(K9:K78)=144</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:46" x14ac:dyDescent="0.2">
@@ -58966,6 +59011,36 @@
   <sheetProtection algorithmName="SHA-512" hashValue="7nWuIQAsd0NKRlhwUK3tOeNHpTch5B5FULy2gxNNaIdJM5RfhFSMzPcx55y+pmM3d73guUy+p5Y+SvIjJZQRaA==" saltValue="Uw23KnM8csnTioq5H8upCA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <dataConsolidate/>
   <mergeCells count="45">
+    <mergeCell ref="BK14:BK15"/>
+    <mergeCell ref="BY16:BY17"/>
+    <mergeCell ref="BK26:BK27"/>
+    <mergeCell ref="BR28:BR29"/>
+    <mergeCell ref="BK22:BK23"/>
+    <mergeCell ref="CF23:CF24"/>
+    <mergeCell ref="BK18:BK19"/>
+    <mergeCell ref="BR20:BR21"/>
+    <mergeCell ref="CM48:CM49"/>
+    <mergeCell ref="BR44:BR45"/>
+    <mergeCell ref="BK46:BK47"/>
+    <mergeCell ref="BK30:BK31"/>
+    <mergeCell ref="CM44:CQ45"/>
+    <mergeCell ref="BY32:BY33"/>
+    <mergeCell ref="BK38:BK39"/>
+    <mergeCell ref="BK34:BK35"/>
+    <mergeCell ref="BR36:BR37"/>
+    <mergeCell ref="BK42:BK43"/>
+    <mergeCell ref="CM33:CQ34"/>
+    <mergeCell ref="CM37:CM38"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="BR12:BR13"/>
+    <mergeCell ref="BK6:BO7"/>
+    <mergeCell ref="BR6:BV7"/>
+    <mergeCell ref="BY6:CC7"/>
+    <mergeCell ref="CF6:CJ7"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="A5:H6"/>
+    <mergeCell ref="J5:P6"/>
     <mergeCell ref="CK68:CQ69"/>
     <mergeCell ref="C83:G88"/>
     <mergeCell ref="BK70:BK71"/>
@@ -58981,36 +59056,6 @@
     <mergeCell ref="BR52:BR53"/>
     <mergeCell ref="BK54:BK55"/>
     <mergeCell ref="CE68:CJ69"/>
-    <mergeCell ref="CF6:CJ7"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="A5:H6"/>
-    <mergeCell ref="J5:P6"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="BR12:BR13"/>
-    <mergeCell ref="BK6:BO7"/>
-    <mergeCell ref="BR6:BV7"/>
-    <mergeCell ref="BY6:CC7"/>
-    <mergeCell ref="CF23:CF24"/>
-    <mergeCell ref="BK18:BK19"/>
-    <mergeCell ref="BR20:BR21"/>
-    <mergeCell ref="CM48:CM49"/>
-    <mergeCell ref="BR44:BR45"/>
-    <mergeCell ref="BK46:BK47"/>
-    <mergeCell ref="BK30:BK31"/>
-    <mergeCell ref="CM44:CQ45"/>
-    <mergeCell ref="BY32:BY33"/>
-    <mergeCell ref="BK38:BK39"/>
-    <mergeCell ref="BK34:BK35"/>
-    <mergeCell ref="BR36:BR37"/>
-    <mergeCell ref="BK42:BK43"/>
-    <mergeCell ref="CM33:CQ34"/>
-    <mergeCell ref="CM37:CM38"/>
-    <mergeCell ref="BK14:BK15"/>
-    <mergeCell ref="BY16:BY17"/>
-    <mergeCell ref="BK26:BK27"/>
-    <mergeCell ref="BR28:BR29"/>
-    <mergeCell ref="BK22:BK23"/>
   </mergeCells>
   <conditionalFormatting sqref="A7:E78">
     <cfRule type="expression" dxfId="228" priority="339">
@@ -60307,11 +60352,11 @@
     <row r="3" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B3" s="109">
         <f>MATCH(C3,C6:C500,0)</f>
-        <v>352</v>
+        <v>67</v>
       </c>
       <c r="C3" s="121" t="str">
         <f>'2026 World Cup'!AR91</f>
-        <v>ABDEFIJL</v>
+        <v>BDEFIJKL</v>
       </c>
       <c r="D3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,2,FALSE)</f>
@@ -60331,7 +60376,7 @@
       </c>
       <c r="H3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,6,FALSE)</f>
-        <v>3A</v>
+        <v>3I</v>
       </c>
       <c r="I3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,7,FALSE)</f>
@@ -60343,7 +60388,7 @@
       </c>
       <c r="K3" s="122" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,9,FALSE)</f>
-        <v>3I</v>
+        <v>3K</v>
       </c>
     </row>
     <row r="5" spans="2:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">

--- a/public/worldcup.xlsx
+++ b/public/worldcup.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rylanpaul/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BD2E748-0087-A84D-9509-98B9D3790692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E535AAA6-96E1-FC4B-973D-D85F321980CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9893" uniqueCount="3715">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9896" uniqueCount="3715">
   <si>
     <t>English</t>
   </si>
@@ -38736,6 +38736,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(J3,Rounds!I$2:I$25,Rounds!L$2:L$25), _xlfn.XLOOKUP(J3,Rounds!L$2:L$25,Rounds!I$2:I$25))</f>
         <v>Curaçao</v>
       </c>
+      <c r="N3" t="s">
+        <v>1739</v>
+      </c>
       <c r="O3" s="142" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(N3,Rounds!M$2:M$17,Rounds!N$2:N$17), _xlfn.XLOOKUP(N3,Rounds!P$2:P$17,Rounds!O$2:O$17))</f>
         <v>#N/A</v>
@@ -38744,9 +38747,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(N3,Rounds!M$2:M$17,Rounds!O$2:O$17), _xlfn.XLOOKUP(N3,Rounds!P$2:P$17,Rounds!N$2:N$17))</f>
         <v>#N/A</v>
       </c>
-      <c r="Q3" s="140" t="e">
+      <c r="Q3" s="140" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(N3,Rounds!M$2:M$17,Rounds!P$2:P$17), _xlfn.XLOOKUP(N3,Rounds!P$2:P$17,Rounds!M$2:M$17))</f>
-        <v>#N/A</v>
+        <v>Japan</v>
       </c>
       <c r="S3" s="142" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(R3,Rounds!Q$2:Q$9,Rounds!R$2:R$9), _xlfn.XLOOKUP(R3,Rounds!T$2:T$9,Rounds!S$2:S$9))</f>
@@ -38959,6 +38962,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(J5,Rounds!I$2:I$25,Rounds!L$2:L$25), _xlfn.XLOOKUP(J5,Rounds!L$2:L$25,Rounds!I$2:I$25))</f>
         <v>Czech Republic</v>
       </c>
+      <c r="N5" t="s">
+        <v>1633</v>
+      </c>
       <c r="O5" s="82" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(N5,Rounds!M$2:M$17,Rounds!N$2:N$17), _xlfn.XLOOKUP(N5,Rounds!P$2:P$17,Rounds!O$2:O$17))</f>
         <v>#N/A</v>
@@ -38967,9 +38973,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(N5,Rounds!M$2:M$17,Rounds!O$2:O$17), _xlfn.XLOOKUP(N5,Rounds!P$2:P$17,Rounds!N$2:N$17))</f>
         <v>#N/A</v>
       </c>
-      <c r="Q5" s="134" t="e">
+      <c r="Q5" s="134" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(N5,Rounds!M$2:M$17,Rounds!P$2:P$17), _xlfn.XLOOKUP(N5,Rounds!P$2:P$17,Rounds!M$2:M$17))</f>
-        <v>#N/A</v>
+        <v>Senegal</v>
       </c>
       <c r="S5" s="82" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(R5,Rounds!Q$2:Q$9,Rounds!R$2:R$9), _xlfn.XLOOKUP(R5,Rounds!T$2:T$9,Rounds!S$2:S$9))</f>
@@ -39179,6 +39185,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(J7,Rounds!I$2:I$25,Rounds!L$2:L$25), _xlfn.XLOOKUP(J7,Rounds!L$2:L$25,Rounds!I$2:I$25))</f>
         <v>Qatar</v>
       </c>
+      <c r="N7" t="s">
+        <v>1633</v>
+      </c>
       <c r="O7" s="82" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(N7,Rounds!M$2:M$17,Rounds!N$2:N$17), _xlfn.XLOOKUP(N7,Rounds!P$2:P$17,Rounds!O$2:O$17))</f>
         <v>#N/A</v>
@@ -39187,9 +39196,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(N7,Rounds!M$2:M$17,Rounds!O$2:O$17), _xlfn.XLOOKUP(N7,Rounds!P$2:P$17,Rounds!N$2:N$17))</f>
         <v>#N/A</v>
       </c>
-      <c r="Q7" s="134" t="e">
+      <c r="Q7" s="134" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(N7,Rounds!M$2:M$17,Rounds!P$2:P$17), _xlfn.XLOOKUP(N7,Rounds!P$2:P$17,Rounds!M$2:M$17))</f>
-        <v>#N/A</v>
+        <v>Senegal</v>
       </c>
       <c r="S7" s="82" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(R7,Rounds!Q$2:Q$9,Rounds!R$2:R$9), _xlfn.XLOOKUP(R7,Rounds!T$2:T$9,Rounds!S$2:S$9))</f>

--- a/public/worldcup.xlsx
+++ b/public/worldcup.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rylanpaul/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E535AAA6-96E1-FC4B-973D-D85F321980CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8AEC348-EFE2-354E-BBED-C00DCFA821B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9896" uniqueCount="3715">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9897" uniqueCount="3715">
   <si>
     <t>English</t>
   </si>
@@ -13305,56 +13305,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -13435,6 +13391,50 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -39075,6 +39075,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(J6,Rounds!I$2:I$25,Rounds!L$2:L$25), _xlfn.XLOOKUP(J6,Rounds!L$2:L$25,Rounds!I$2:I$25))</f>
         <v>Curaçao</v>
       </c>
+      <c r="N6" s="148" t="s">
+        <v>1565</v>
+      </c>
       <c r="O6" s="146" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(N6,Rounds!M$2:M$17,Rounds!N$2:N$17), _xlfn.XLOOKUP(N6,Rounds!P$2:P$17,Rounds!O$2:O$17))</f>
         <v>#N/A</v>
@@ -39083,9 +39086,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(N6,Rounds!M$2:M$17,Rounds!O$2:O$17), _xlfn.XLOOKUP(N6,Rounds!P$2:P$17,Rounds!N$2:N$17))</f>
         <v>#N/A</v>
       </c>
-      <c r="Q6" s="147" t="e">
+      <c r="Q6" s="147" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(N6,Rounds!M$2:M$17,Rounds!P$2:P$17), _xlfn.XLOOKUP(N6,Rounds!P$2:P$17,Rounds!M$2:M$17))</f>
-        <v>#N/A</v>
+        <v>Paraguay</v>
       </c>
       <c r="S6" s="146" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(R6,Rounds!Q$2:Q$9,Rounds!R$2:R$9), _xlfn.XLOOKUP(R6,Rounds!T$2:T$9,Rounds!S$2:S$9))</f>
@@ -40978,25 +40981,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:95" ht="47" x14ac:dyDescent="0.2">
-      <c r="A1" s="182" t="str" cm="1">
+      <c r="A1" s="171" t="str" cm="1">
         <f t="array" ref="A1">INDEX(T,2,lang)</f>
         <v>2026 World Cup Final Tournament Schedule</v>
       </c>
-      <c r="B1" s="182"/>
-      <c r="C1" s="182"/>
-      <c r="D1" s="182"/>
-      <c r="E1" s="182"/>
-      <c r="F1" s="182"/>
-      <c r="G1" s="182"/>
-      <c r="H1" s="182"/>
-      <c r="I1" s="182"/>
-      <c r="J1" s="182"/>
-      <c r="K1" s="182"/>
-      <c r="L1" s="182"/>
-      <c r="M1" s="182"/>
-      <c r="N1" s="182"/>
-      <c r="O1" s="182"/>
-      <c r="P1" s="182"/>
+      <c r="B1" s="171"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="171"/>
+      <c r="F1" s="171"/>
+      <c r="G1" s="171"/>
+      <c r="H1" s="171"/>
+      <c r="I1" s="171"/>
+      <c r="J1" s="171"/>
+      <c r="K1" s="171"/>
+      <c r="L1" s="171"/>
+      <c r="M1" s="171"/>
+      <c r="N1" s="171"/>
+      <c r="O1" s="171"/>
+      <c r="P1" s="171"/>
       <c r="S1" s="123"/>
       <c r="T1" s="123"/>
       <c r="AC1" s="123"/>
@@ -41043,11 +41046,11 @@
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
-      <c r="O3" s="183" t="str">
+      <c r="O3" s="172" t="str">
         <f>"Language: " &amp; Settings!C4</f>
         <v>Language: English</v>
       </c>
-      <c r="P3" s="183"/>
+      <c r="P3" s="172"/>
       <c r="S3" s="123"/>
       <c r="T3" s="123"/>
       <c r="AC3" s="123"/>
@@ -41065,43 +41068,43 @@
     </row>
     <row r="4" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:95" x14ac:dyDescent="0.2">
-      <c r="A5" s="184" t="str" cm="1">
+      <c r="A5" s="173" t="str" cm="1">
         <f t="array" ref="A5">INDEX(T,3,lang)</f>
         <v>Group Stage</v>
       </c>
-      <c r="B5" s="185"/>
-      <c r="C5" s="185"/>
-      <c r="D5" s="185"/>
-      <c r="E5" s="185"/>
-      <c r="F5" s="185"/>
-      <c r="G5" s="185"/>
-      <c r="H5" s="186"/>
-      <c r="J5" s="190" t="s">
+      <c r="B5" s="174"/>
+      <c r="C5" s="174"/>
+      <c r="D5" s="174"/>
+      <c r="E5" s="174"/>
+      <c r="F5" s="174"/>
+      <c r="G5" s="174"/>
+      <c r="H5" s="175"/>
+      <c r="J5" s="179" t="s">
         <v>3166</v>
       </c>
-      <c r="K5" s="191"/>
-      <c r="L5" s="191"/>
-      <c r="M5" s="191"/>
-      <c r="N5" s="191"/>
-      <c r="O5" s="191"/>
-      <c r="P5" s="192"/>
+      <c r="K5" s="180"/>
+      <c r="L5" s="180"/>
+      <c r="M5" s="180"/>
+      <c r="N5" s="180"/>
+      <c r="O5" s="180"/>
+      <c r="P5" s="181"/>
     </row>
     <row r="6" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="187"/>
-      <c r="B6" s="188"/>
-      <c r="C6" s="188"/>
-      <c r="D6" s="188"/>
-      <c r="E6" s="188"/>
-      <c r="F6" s="188"/>
-      <c r="G6" s="188"/>
-      <c r="H6" s="189"/>
-      <c r="J6" s="193"/>
-      <c r="K6" s="194"/>
-      <c r="L6" s="194"/>
-      <c r="M6" s="194"/>
-      <c r="N6" s="194"/>
-      <c r="O6" s="194"/>
-      <c r="P6" s="195"/>
+      <c r="A6" s="176"/>
+      <c r="B6" s="177"/>
+      <c r="C6" s="177"/>
+      <c r="D6" s="177"/>
+      <c r="E6" s="177"/>
+      <c r="F6" s="177"/>
+      <c r="G6" s="177"/>
+      <c r="H6" s="178"/>
+      <c r="J6" s="182"/>
+      <c r="K6" s="183"/>
+      <c r="L6" s="183"/>
+      <c r="M6" s="183"/>
+      <c r="N6" s="183"/>
+      <c r="O6" s="183"/>
+      <c r="P6" s="184"/>
       <c r="R6" s="123" t="s">
         <v>3167</v>
       </c>
@@ -41211,37 +41214,37 @@
       <c r="BI6" s="128" t="s">
         <v>3178</v>
       </c>
-      <c r="BK6" s="176" t="s">
+      <c r="BK6" s="165" t="s">
         <v>3179</v>
       </c>
-      <c r="BL6" s="177"/>
-      <c r="BM6" s="177"/>
-      <c r="BN6" s="177"/>
-      <c r="BO6" s="178"/>
-      <c r="BR6" s="176" t="str" cm="1">
+      <c r="BL6" s="166"/>
+      <c r="BM6" s="166"/>
+      <c r="BN6" s="166"/>
+      <c r="BO6" s="167"/>
+      <c r="BR6" s="165" t="str" cm="1">
         <f t="array" ref="BR6">INDEX(T,4,lang)</f>
         <v>Round of 16</v>
       </c>
-      <c r="BS6" s="177"/>
-      <c r="BT6" s="177"/>
-      <c r="BU6" s="177"/>
-      <c r="BV6" s="178"/>
-      <c r="BY6" s="176" t="str" cm="1">
+      <c r="BS6" s="166"/>
+      <c r="BT6" s="166"/>
+      <c r="BU6" s="166"/>
+      <c r="BV6" s="167"/>
+      <c r="BY6" s="165" t="str" cm="1">
         <f t="array" ref="BY6">INDEX(T,5,lang)</f>
         <v>Quarterfinals</v>
       </c>
-      <c r="BZ6" s="177"/>
-      <c r="CA6" s="177"/>
-      <c r="CB6" s="177"/>
-      <c r="CC6" s="178"/>
-      <c r="CF6" s="176" t="str" cm="1">
+      <c r="BZ6" s="166"/>
+      <c r="CA6" s="166"/>
+      <c r="CB6" s="166"/>
+      <c r="CC6" s="167"/>
+      <c r="CF6" s="165" t="str" cm="1">
         <f t="array" ref="CF6">INDEX(T,6,lang)</f>
         <v>Semi-Finals</v>
       </c>
-      <c r="CG6" s="177"/>
-      <c r="CH6" s="177"/>
-      <c r="CI6" s="177"/>
-      <c r="CJ6" s="178"/>
+      <c r="CG6" s="166"/>
+      <c r="CH6" s="166"/>
+      <c r="CI6" s="166"/>
+      <c r="CJ6" s="167"/>
     </row>
     <row r="7" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="11">
@@ -41318,26 +41321,26 @@
         <v>1</v>
       </c>
       <c r="AY7" s="126"/>
-      <c r="BK7" s="179"/>
-      <c r="BL7" s="180"/>
-      <c r="BM7" s="180"/>
-      <c r="BN7" s="180"/>
-      <c r="BO7" s="181"/>
-      <c r="BR7" s="179"/>
-      <c r="BS7" s="180"/>
-      <c r="BT7" s="180"/>
-      <c r="BU7" s="180"/>
-      <c r="BV7" s="181"/>
-      <c r="BY7" s="179"/>
-      <c r="BZ7" s="180"/>
-      <c r="CA7" s="180"/>
-      <c r="CB7" s="180"/>
-      <c r="CC7" s="181"/>
-      <c r="CF7" s="179"/>
-      <c r="CG7" s="180"/>
-      <c r="CH7" s="180"/>
-      <c r="CI7" s="180"/>
-      <c r="CJ7" s="181"/>
+      <c r="BK7" s="168"/>
+      <c r="BL7" s="169"/>
+      <c r="BM7" s="169"/>
+      <c r="BN7" s="169"/>
+      <c r="BO7" s="170"/>
+      <c r="BR7" s="168"/>
+      <c r="BS7" s="169"/>
+      <c r="BT7" s="169"/>
+      <c r="BU7" s="169"/>
+      <c r="BV7" s="170"/>
+      <c r="BY7" s="168"/>
+      <c r="BZ7" s="169"/>
+      <c r="CA7" s="169"/>
+      <c r="CB7" s="169"/>
+      <c r="CC7" s="170"/>
+      <c r="CF7" s="168"/>
+      <c r="CG7" s="169"/>
+      <c r="CH7" s="169"/>
+      <c r="CI7" s="169"/>
+      <c r="CJ7" s="170"/>
     </row>
     <row r="8" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A8" s="16">
@@ -42073,7 +42076,7 @@
         <f>BH10/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK10" s="173">
+      <c r="BK10" s="163">
         <v>74</v>
       </c>
       <c r="BL10" s="24" t="str">
@@ -42336,7 +42339,7 @@
         <f>BH11/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK11" s="174"/>
+      <c r="BK11" s="164"/>
       <c r="BL11" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!G3,AK80:AS91,9,FALSE),"3rd Group A/B/C/D/F")</f>
         <v>Paraguay</v>
@@ -42574,7 +42577,7 @@
       <c r="BO12" s="21"/>
       <c r="BP12" s="114"/>
       <c r="BQ12" s="112"/>
-      <c r="BR12" s="173">
+      <c r="BR12" s="163">
         <v>89</v>
       </c>
       <c r="BS12" s="24" t="str">
@@ -42695,7 +42698,7 @@
         <v>46203.875</v>
       </c>
       <c r="BQ13" s="115"/>
-      <c r="BR13" s="174"/>
+      <c r="BR13" s="164"/>
       <c r="BS13" s="26" t="str">
         <f>IF(BP14&gt;BP15,BL14,IF(BP14&lt;BP15,BL15,""))</f>
         <v/>
@@ -42953,7 +42956,7 @@
         <f>BH14/BH18</f>
         <v>0.98058252427184467</v>
       </c>
-      <c r="BK14" s="173">
+      <c r="BK14" s="163">
         <v>77</v>
       </c>
       <c r="BL14" s="24" t="str">
@@ -43220,7 +43223,7 @@
         <f>BH15/BH18</f>
         <v>0.98058252427184467</v>
       </c>
-      <c r="BK15" s="174"/>
+      <c r="BK15" s="164"/>
       <c r="BL15" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!I3,AK80:AS91,9,FALSE),"3rd Group C/D/F/G/H")</f>
         <v>Sweden</v>
@@ -43494,7 +43497,7 @@
       <c r="BV16" s="21"/>
       <c r="BW16" s="114"/>
       <c r="BX16" s="112"/>
-      <c r="BY16" s="173">
+      <c r="BY16" s="163">
         <v>97</v>
       </c>
       <c r="BZ16" s="24" t="str">
@@ -43756,7 +43759,7 @@
       <c r="BV17" s="21"/>
       <c r="BW17" s="114"/>
       <c r="BX17" s="115"/>
-      <c r="BY17" s="174"/>
+      <c r="BY17" s="164"/>
       <c r="BZ17" s="26" t="str">
         <f>IF(BW20&gt;BW21,BS20,IF(BW20&lt;BW21,BS21,""))</f>
         <v/>
@@ -43960,7 +43963,7 @@
         <f>MAX(BH14:BH17)+1</f>
         <v>51.5</v>
       </c>
-      <c r="BK18" s="173">
+      <c r="BK18" s="163">
         <v>73</v>
       </c>
       <c r="BL18" s="24" t="str">
@@ -44068,7 +44071,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BK19" s="174"/>
+      <c r="BK19" s="164"/>
       <c r="BL19" s="26" t="str">
         <f>AS15</f>
         <v>Canada</v>
@@ -44346,7 +44349,7 @@
       <c r="BO20" s="21"/>
       <c r="BP20" s="114"/>
       <c r="BQ20" s="112"/>
-      <c r="BR20" s="173">
+      <c r="BR20" s="163">
         <v>90</v>
       </c>
       <c r="BS20" s="24" t="str">
@@ -44619,7 +44622,7 @@
         <v>46203.041666666672</v>
       </c>
       <c r="BQ21" s="115"/>
-      <c r="BR21" s="174"/>
+      <c r="BR21" s="164"/>
       <c r="BS21" s="26" t="str">
         <f>IF(BP22&gt;BP23,BL22,IF(BP22&lt;BP23,BL23,""))</f>
         <v/>
@@ -44873,7 +44876,7 @@
         <f>BH22/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK22" s="173">
+      <c r="BK22" s="163">
         <v>75</v>
       </c>
       <c r="BL22" s="24" t="str">
@@ -45137,7 +45140,7 @@
         <f>BH23/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK23" s="174"/>
+      <c r="BK23" s="164"/>
       <c r="BL23" s="26" t="str">
         <f>AS21</f>
         <v>Morocco</v>
@@ -45164,7 +45167,7 @@
       <c r="CC23" s="21"/>
       <c r="CD23" s="114"/>
       <c r="CE23" s="112"/>
-      <c r="CF23" s="173">
+      <c r="CF23" s="163">
         <v>101</v>
       </c>
       <c r="CG23" s="24" t="str">
@@ -45385,7 +45388,7 @@
       <c r="CC24" s="21"/>
       <c r="CD24" s="114"/>
       <c r="CE24" s="115"/>
-      <c r="CF24" s="174"/>
+      <c r="CF24" s="164"/>
       <c r="CG24" s="26" t="str">
         <f>IF(CD32&gt;CD33,BZ32,IF(CD32&lt;CD33,BZ33,""))</f>
         <v/>
@@ -45738,7 +45741,7 @@
         <f>BH26/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK26" s="173">
+      <c r="BK26" s="163">
         <v>83</v>
       </c>
       <c r="BL26" s="24" t="str">
@@ -46006,7 +46009,7 @@
         <f>BH27/BH30</f>
         <v>0.98039215686274506</v>
       </c>
-      <c r="BK27" s="174"/>
+      <c r="BK27" s="164"/>
       <c r="BL27" s="26" t="str">
         <f>AS75</f>
         <v>Croatia</v>
@@ -46281,7 +46284,7 @@
       <c r="BO28" s="21"/>
       <c r="BP28" s="114"/>
       <c r="BQ28" s="112"/>
-      <c r="BR28" s="173">
+      <c r="BR28" s="163">
         <v>93</v>
       </c>
       <c r="BS28" s="24" t="str">
@@ -46546,7 +46549,7 @@
         <v>46205.791666666672</v>
       </c>
       <c r="BQ29" s="115"/>
-      <c r="BR29" s="174"/>
+      <c r="BR29" s="164"/>
       <c r="BS29" s="26" t="str">
         <f>IF(BP30&gt;BP31,BL30,IF(BP30&lt;BP31,BL31,""))</f>
         <v/>
@@ -46760,7 +46763,7 @@
         <f>MAX(BH26:BH29)+1</f>
         <v>51</v>
       </c>
-      <c r="BK30" s="173">
+      <c r="BK30" s="163">
         <v>84</v>
       </c>
       <c r="BL30" s="24" t="str">
@@ -46871,7 +46874,7 @@
         <f>IF(OR(F31="",G31=""),"",IF(F31&gt;G31,1,IF(F31&lt;G31,-1,0)))</f>
         <v>0</v>
       </c>
-      <c r="BK31" s="174"/>
+      <c r="BK31" s="164"/>
       <c r="BL31" s="26" t="str">
         <f>AS63</f>
         <v>Austria</v>
@@ -47147,7 +47150,7 @@
       <c r="BV32" s="21"/>
       <c r="BW32" s="114"/>
       <c r="BX32" s="112"/>
-      <c r="BY32" s="173">
+      <c r="BY32" s="163">
         <v>98</v>
       </c>
       <c r="BZ32" s="24" t="str">
@@ -47411,7 +47414,7 @@
       <c r="BV33" s="21"/>
       <c r="BW33" s="114"/>
       <c r="BX33" s="115"/>
-      <c r="BY33" s="174"/>
+      <c r="BY33" s="164"/>
       <c r="BZ33" s="26" t="str">
         <f>IF(BW36&gt;BW37,BS36,IF(BW36&lt;BW37,BS37,""))</f>
         <v/>
@@ -47426,14 +47429,14 @@
       <c r="CE33" s="112"/>
       <c r="CK33" s="114"/>
       <c r="CL33" s="112"/>
-      <c r="CM33" s="176" t="str" cm="1">
+      <c r="CM33" s="165" t="str" cm="1">
         <f t="array" ref="CM33">INDEX(T,8,lang)</f>
         <v>Final</v>
       </c>
-      <c r="CN33" s="177"/>
-      <c r="CO33" s="177"/>
-      <c r="CP33" s="177"/>
-      <c r="CQ33" s="178"/>
+      <c r="CN33" s="166"/>
+      <c r="CO33" s="166"/>
+      <c r="CP33" s="166"/>
+      <c r="CQ33" s="167"/>
     </row>
     <row r="34" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A34" s="16">
@@ -47657,7 +47660,7 @@
         <f>BH34/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK34" s="173">
+      <c r="BK34" s="163">
         <v>81</v>
       </c>
       <c r="BL34" s="24" t="str">
@@ -47688,11 +47691,11 @@
       <c r="CE34" s="112"/>
       <c r="CK34" s="114"/>
       <c r="CL34" s="112"/>
-      <c r="CM34" s="179"/>
-      <c r="CN34" s="180"/>
-      <c r="CO34" s="180"/>
-      <c r="CP34" s="180"/>
-      <c r="CQ34" s="181"/>
+      <c r="CM34" s="168"/>
+      <c r="CN34" s="169"/>
+      <c r="CO34" s="169"/>
+      <c r="CP34" s="169"/>
+      <c r="CQ34" s="170"/>
     </row>
     <row r="35" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A35" s="16">
@@ -47916,7 +47919,7 @@
         <f>BH35/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK35" s="174"/>
+      <c r="BK35" s="164"/>
       <c r="BL35" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!F3,AK80:AS91,9,FALSE),"3rd Group B/E/F/I/J")</f>
         <v>Bosnia and Herzegovina</v>
@@ -48145,7 +48148,7 @@
       <c r="BO36" s="21"/>
       <c r="BP36" s="114"/>
       <c r="BQ36" s="112"/>
-      <c r="BR36" s="173">
+      <c r="BR36" s="163">
         <v>94</v>
       </c>
       <c r="BS36" s="24" t="str">
@@ -48269,7 +48272,7 @@
         <v>46204.833333333336</v>
       </c>
       <c r="BQ37" s="115"/>
-      <c r="BR37" s="174"/>
+      <c r="BR37" s="164"/>
       <c r="BS37" s="26" t="str">
         <f>IF(BP38&gt;BP39,BL38,IF(BP38&lt;BP39,BL39,""))</f>
         <v/>
@@ -48296,7 +48299,7 @@
       <c r="CJ37" s="21"/>
       <c r="CK37" s="114"/>
       <c r="CL37" s="112"/>
-      <c r="CM37" s="173">
+      <c r="CM37" s="163">
         <v>104</v>
       </c>
       <c r="CN37" s="24" t="str">
@@ -48537,7 +48540,7 @@
         <f>BH38/BH42</f>
         <v>0</v>
       </c>
-      <c r="BK38" s="173">
+      <c r="BK38" s="163">
         <v>82</v>
       </c>
       <c r="BL38" s="24" t="str">
@@ -48567,7 +48570,7 @@
       <c r="CI38" s="21"/>
       <c r="CJ38" s="21"/>
       <c r="CL38" s="115"/>
-      <c r="CM38" s="174"/>
+      <c r="CM38" s="164"/>
       <c r="CN38" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG55,IF(CK55&lt;CK56,CG56,""))</f>
         <v/>
@@ -48806,7 +48809,7 @@
         <f>BH39/BH42</f>
         <v>0</v>
       </c>
-      <c r="BK39" s="174"/>
+      <c r="BK39" s="164"/>
       <c r="BL39" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!H3,AK80:AS91,9,FALSE),"3rd Group A/E/H/I/J")</f>
         <v>Senegal</v>
@@ -49494,7 +49497,7 @@
         <f>MAX(BH38:BH41)+1</f>
         <v>1</v>
       </c>
-      <c r="BK42" s="173">
+      <c r="BK42" s="163">
         <v>76</v>
       </c>
       <c r="BL42" s="24" t="str">
@@ -49591,7 +49594,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BK43" s="174"/>
+      <c r="BK43" s="164"/>
       <c r="BL43" s="26" t="str">
         <f>AS39</f>
         <v>Japan</v>
@@ -49851,7 +49854,7 @@
       <c r="BO44" s="21"/>
       <c r="BP44" s="114"/>
       <c r="BQ44" s="112"/>
-      <c r="BR44" s="173">
+      <c r="BR44" s="163">
         <v>91</v>
       </c>
       <c r="BS44" s="24" t="str">
@@ -49866,14 +49869,14 @@
         <v/>
       </c>
       <c r="CK44" s="114"/>
-      <c r="CM44" s="176" t="str" cm="1">
+      <c r="CM44" s="165" t="str" cm="1">
         <f t="array" ref="CM44">INDEX(T,7,lang)</f>
         <v>Third-Place Play-Off</v>
       </c>
-      <c r="CN44" s="177"/>
-      <c r="CO44" s="177"/>
-      <c r="CP44" s="177"/>
-      <c r="CQ44" s="178"/>
+      <c r="CN44" s="166"/>
+      <c r="CO44" s="166"/>
+      <c r="CP44" s="166"/>
+      <c r="CQ44" s="167"/>
     </row>
     <row r="45" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="16">
@@ -50114,7 +50117,7 @@
         <v>46203.708333333336</v>
       </c>
       <c r="BQ45" s="115"/>
-      <c r="BR45" s="174"/>
+      <c r="BR45" s="164"/>
       <c r="BS45" s="26" t="str">
         <f>IF(BP46&gt;BP47,BL46,IF(BP46&lt;BP47,BL47,""))</f>
         <v/>
@@ -50127,11 +50130,11 @@
         <v/>
       </c>
       <c r="CK45" s="114"/>
-      <c r="CM45" s="179"/>
-      <c r="CN45" s="180"/>
-      <c r="CO45" s="180"/>
-      <c r="CP45" s="180"/>
-      <c r="CQ45" s="181"/>
+      <c r="CM45" s="168"/>
+      <c r="CN45" s="169"/>
+      <c r="CO45" s="169"/>
+      <c r="CP45" s="169"/>
+      <c r="CQ45" s="170"/>
     </row>
     <row r="46" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A46" s="16">
@@ -50355,7 +50358,7 @@
         <f>BH46/BH48</f>
         <v>0</v>
       </c>
-      <c r="BK46" s="173">
+      <c r="BK46" s="163">
         <v>78</v>
       </c>
       <c r="BL46" s="24" t="str">
@@ -50601,7 +50604,7 @@
         <f>BH47/BH48</f>
         <v>0</v>
       </c>
-      <c r="BK47" s="174"/>
+      <c r="BK47" s="164"/>
       <c r="BL47" s="26" t="str">
         <f>AS57</f>
         <v>Norway</v>
@@ -50848,7 +50851,7 @@
       <c r="BV48" s="21"/>
       <c r="BW48" s="114"/>
       <c r="BX48" s="112"/>
-      <c r="BY48" s="173">
+      <c r="BY48" s="163">
         <v>99</v>
       </c>
       <c r="BZ48" s="24" t="str">
@@ -50864,7 +50867,7 @@
       </c>
       <c r="CK48" s="114"/>
       <c r="CL48" s="112"/>
-      <c r="CM48" s="173">
+      <c r="CM48" s="163">
         <v>103</v>
       </c>
       <c r="CN48" s="24" t="str">
@@ -50973,7 +50976,7 @@
       <c r="BV49" s="21"/>
       <c r="BW49" s="114"/>
       <c r="BX49" s="115"/>
-      <c r="BY49" s="174"/>
+      <c r="BY49" s="164"/>
       <c r="BZ49" s="26" t="str">
         <f>IF(BW52&gt;BW53,BS52,IF(BW52&lt;BW53,BS53,""))</f>
         <v/>
@@ -50987,7 +50990,7 @@
       </c>
       <c r="CK49" s="114"/>
       <c r="CL49" s="115"/>
-      <c r="CM49" s="174"/>
+      <c r="CM49" s="164"/>
       <c r="CN49" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG56,IF(CK55&lt;CK56,CG55,""))</f>
         <v/>
@@ -51226,7 +51229,7 @@
         <f>BH50/BH54</f>
         <v>0</v>
       </c>
-      <c r="BK50" s="173">
+      <c r="BK50" s="163">
         <v>79</v>
       </c>
       <c r="BL50" s="24" t="str">
@@ -51483,7 +51486,7 @@
         <f>BH51/BH54</f>
         <v>0</v>
       </c>
-      <c r="BK51" s="174"/>
+      <c r="BK51" s="164"/>
       <c r="BL51" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!D3,AK80:AS91,9,FALSE),"3rd Group C/E/F/H/I")</f>
         <v>Ecuador</v>
@@ -51747,7 +51750,7 @@
       <c r="BO52" s="21"/>
       <c r="BP52" s="114"/>
       <c r="BQ52" s="112"/>
-      <c r="BR52" s="173">
+      <c r="BR52" s="163">
         <v>92</v>
       </c>
       <c r="BS52" s="24" t="str">
@@ -52006,7 +52009,7 @@
         <v>46204.666666666672</v>
       </c>
       <c r="BQ53" s="115"/>
-      <c r="BR53" s="174"/>
+      <c r="BR53" s="164"/>
       <c r="BS53" s="26" t="str">
         <f>IF(BP54&gt;BP55,BL54,IF(BP54&lt;BP55,BL55,""))</f>
         <v/>
@@ -52214,7 +52217,7 @@
         <f>MAX(BH50:BH53)+1</f>
         <v>51.5</v>
       </c>
-      <c r="BK54" s="173">
+      <c r="BK54" s="163">
         <v>80</v>
       </c>
       <c r="BL54" s="24" t="str">
@@ -52339,7 +52342,7 @@
         <f t="shared" si="23"/>
         <v>-1</v>
       </c>
-      <c r="BK55" s="174"/>
+      <c r="BK55" s="164"/>
       <c r="BL55" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!K3,AK80:AS91,9,FALSE),"3rd Group E/H/I/J/K")</f>
         <v>DR Congo</v>
@@ -52366,7 +52369,7 @@
       <c r="CC55" s="21"/>
       <c r="CD55" s="114"/>
       <c r="CE55" s="112"/>
-      <c r="CF55" s="173">
+      <c r="CF55" s="163">
         <v>102</v>
       </c>
       <c r="CG55" s="24" t="str">
@@ -52629,7 +52632,7 @@
       <c r="CC56" s="21"/>
       <c r="CD56" s="114"/>
       <c r="CE56" s="115"/>
-      <c r="CF56" s="174"/>
+      <c r="CF56" s="164"/>
       <c r="CG56" s="26" t="str">
         <f>IF(CD64&gt;CD65,BZ64,IF(CD64&lt;CD65,BZ65,""))</f>
         <v/>
@@ -53120,7 +53123,7 @@
         <f>BH58/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK58" s="173">
+      <c r="BK58" s="163">
         <v>86</v>
       </c>
       <c r="BL58" s="24" t="str">
@@ -53372,7 +53375,7 @@
         <f>BH59/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK59" s="174"/>
+      <c r="BK59" s="164"/>
       <c r="BL59" s="26" t="str">
         <f>AS51</f>
         <v>Cape Verde</v>
@@ -53599,7 +53602,7 @@
       <c r="BO60" s="21"/>
       <c r="BP60" s="114"/>
       <c r="BQ60" s="112"/>
-      <c r="BR60" s="173">
+      <c r="BR60" s="163">
         <v>95</v>
       </c>
       <c r="BS60" s="24" t="str">
@@ -53716,7 +53719,7 @@
         <v>46206.75</v>
       </c>
       <c r="BQ61" s="115"/>
-      <c r="BR61" s="174"/>
+      <c r="BR61" s="164"/>
       <c r="BS61" s="26" t="str">
         <f>IF(BP62&gt;BP63,BL62,IF(BP62&lt;BP63,BL63,""))</f>
         <v/>
@@ -53963,7 +53966,7 @@
         <f>BH62/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK62" s="173">
+      <c r="BK62" s="163">
         <v>88</v>
       </c>
       <c r="BL62" s="24" t="str">
@@ -54219,7 +54222,7 @@
         <f>BH63/BH66</f>
         <v>0.98067632850241548</v>
       </c>
-      <c r="BK63" s="174"/>
+      <c r="BK63" s="164"/>
       <c r="BL63" s="26" t="str">
         <f>AS45</f>
         <v>Egypt</v>
@@ -54489,7 +54492,7 @@
       <c r="BV64" s="21"/>
       <c r="BW64" s="114"/>
       <c r="BX64" s="112"/>
-      <c r="BY64" s="173">
+      <c r="BY64" s="163">
         <v>100</v>
       </c>
       <c r="BZ64" s="24" t="str">
@@ -54747,7 +54750,7 @@
       <c r="BV65" s="21"/>
       <c r="BW65" s="114"/>
       <c r="BX65" s="115"/>
-      <c r="BY65" s="174"/>
+      <c r="BY65" s="164"/>
       <c r="BZ65" s="26" t="str">
         <f>IF(BW68&gt;BW69,BS68,IF(BW68&lt;BW69,BS69,""))</f>
         <v/>
@@ -54947,7 +54950,7 @@
         <f>MAX(BH62:BH65)+1</f>
         <v>51.75</v>
       </c>
-      <c r="BK66" s="173">
+      <c r="BK66" s="163">
         <v>85</v>
       </c>
       <c r="BL66" s="24" t="str">
@@ -55051,7 +55054,7 @@
         <f t="shared" si="23"/>
         <v>-1</v>
       </c>
-      <c r="BK67" s="174"/>
+      <c r="BK67" s="164"/>
       <c r="BL67" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!E3,AK80:AS91,9,FALSE),"3rd Group E/F/G/I/J")</f>
         <v>Algeria</v>
@@ -55311,7 +55314,7 @@
       <c r="BO68" s="21"/>
       <c r="BP68" s="114"/>
       <c r="BQ68" s="112"/>
-      <c r="BR68" s="173">
+      <c r="BR68" s="163">
         <v>96</v>
       </c>
       <c r="BS68" s="24" t="str">
@@ -55325,25 +55328,25 @@
         <f>IF(OR(BT68="",BT69="",AND(BU68="",BU69&lt;&gt;""),AND(BU69="",BU68&lt;&gt;""),AND(BV68="",BV69&lt;&gt;""),AND(BV69="",BV68&lt;&gt;"")),"",BT68*1000+BU68*10+BV68)</f>
         <v/>
       </c>
-      <c r="CE68" s="175" t="str">
+      <c r="CE68" s="195" t="str">
         <f>INDEX(T,144,lang)</f>
         <v>World Champion 2026</v>
       </c>
-      <c r="CF68" s="175"/>
-      <c r="CG68" s="175"/>
-      <c r="CH68" s="175"/>
-      <c r="CI68" s="175"/>
-      <c r="CJ68" s="175"/>
-      <c r="CK68" s="163" t="str">
+      <c r="CF68" s="195"/>
+      <c r="CG68" s="195"/>
+      <c r="CH68" s="195"/>
+      <c r="CI68" s="195"/>
+      <c r="CJ68" s="195"/>
+      <c r="CK68" s="185" t="str">
         <f>IF(CR37&gt;CR38,CN37,IF(CR37&lt;CR38,CN38,""))</f>
         <v/>
       </c>
-      <c r="CL68" s="163"/>
-      <c r="CM68" s="163"/>
-      <c r="CN68" s="163"/>
-      <c r="CO68" s="163"/>
-      <c r="CP68" s="163"/>
-      <c r="CQ68" s="163"/>
+      <c r="CL68" s="185"/>
+      <c r="CM68" s="185"/>
+      <c r="CN68" s="185"/>
+      <c r="CO68" s="185"/>
+      <c r="CP68" s="185"/>
+      <c r="CQ68" s="185"/>
     </row>
     <row r="69" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A69" s="16">
@@ -55585,7 +55588,7 @@
         <v>46207.0625</v>
       </c>
       <c r="BQ69" s="115"/>
-      <c r="BR69" s="174"/>
+      <c r="BR69" s="164"/>
       <c r="BS69" s="26" t="str">
         <f>IF(BP70&gt;BP71,BL70,IF(BP70&lt;BP71,BL71,""))</f>
         <v/>
@@ -55597,19 +55600,19 @@
         <f>IF(BW68="","",BT69*1000+BU69*10+BV69)</f>
         <v/>
       </c>
-      <c r="CE69" s="175"/>
-      <c r="CF69" s="175"/>
-      <c r="CG69" s="175"/>
-      <c r="CH69" s="175"/>
-      <c r="CI69" s="175"/>
-      <c r="CJ69" s="175"/>
-      <c r="CK69" s="163"/>
-      <c r="CL69" s="163"/>
-      <c r="CM69" s="163"/>
-      <c r="CN69" s="163"/>
-      <c r="CO69" s="163"/>
-      <c r="CP69" s="163"/>
-      <c r="CQ69" s="163"/>
+      <c r="CE69" s="195"/>
+      <c r="CF69" s="195"/>
+      <c r="CG69" s="195"/>
+      <c r="CH69" s="195"/>
+      <c r="CI69" s="195"/>
+      <c r="CJ69" s="195"/>
+      <c r="CK69" s="185"/>
+      <c r="CL69" s="185"/>
+      <c r="CM69" s="185"/>
+      <c r="CN69" s="185"/>
+      <c r="CO69" s="185"/>
+      <c r="CP69" s="185"/>
+      <c r="CQ69" s="185"/>
     </row>
     <row r="70" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A70" s="16">
@@ -55834,7 +55837,7 @@
         <f>BH70/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK70" s="173">
+      <c r="BK70" s="163">
         <v>87</v>
       </c>
       <c r="BL70" s="24" t="str">
@@ -56074,7 +56077,7 @@
         <f>BH71/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK71" s="174"/>
+      <c r="BK71" s="164"/>
       <c r="BL71" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!J3,AK80:AS91,9,FALSE),"3rd Group D/E/I/J/L")</f>
         <v>Ghana</v>
@@ -57778,13 +57781,13 @@
     <row r="83" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="73"/>
       <c r="B83" s="73"/>
-      <c r="C83" s="164" t="s">
+      <c r="C83" s="186" t="s">
         <v>3183</v>
       </c>
-      <c r="D83" s="165"/>
-      <c r="E83" s="165"/>
-      <c r="F83" s="165"/>
-      <c r="G83" s="166"/>
+      <c r="D83" s="187"/>
+      <c r="E83" s="187"/>
+      <c r="F83" s="187"/>
+      <c r="G83" s="188"/>
       <c r="H83" s="75"/>
       <c r="I83" s="69"/>
       <c r="J83" s="99" t="str">
@@ -57882,11 +57885,11 @@
     <row r="84" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="73"/>
       <c r="B84" s="73"/>
-      <c r="C84" s="167"/>
-      <c r="D84" s="168"/>
-      <c r="E84" s="168"/>
-      <c r="F84" s="168"/>
-      <c r="G84" s="169"/>
+      <c r="C84" s="189"/>
+      <c r="D84" s="190"/>
+      <c r="E84" s="190"/>
+      <c r="F84" s="190"/>
+      <c r="G84" s="191"/>
       <c r="H84" s="75"/>
       <c r="I84" s="69"/>
       <c r="J84" s="99" t="str">
@@ -57996,11 +57999,11 @@
     <row r="85" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="73"/>
       <c r="B85" s="73"/>
-      <c r="C85" s="167"/>
-      <c r="D85" s="168"/>
-      <c r="E85" s="168"/>
-      <c r="F85" s="168"/>
-      <c r="G85" s="169"/>
+      <c r="C85" s="189"/>
+      <c r="D85" s="190"/>
+      <c r="E85" s="190"/>
+      <c r="F85" s="190"/>
+      <c r="G85" s="191"/>
       <c r="H85" s="75"/>
       <c r="I85" s="69"/>
       <c r="J85" s="99" t="str">
@@ -58110,11 +58113,11 @@
     <row r="86" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="73"/>
       <c r="B86" s="73"/>
-      <c r="C86" s="167"/>
-      <c r="D86" s="168"/>
-      <c r="E86" s="168"/>
-      <c r="F86" s="168"/>
-      <c r="G86" s="169"/>
+      <c r="C86" s="189"/>
+      <c r="D86" s="190"/>
+      <c r="E86" s="190"/>
+      <c r="F86" s="190"/>
+      <c r="G86" s="191"/>
       <c r="H86" s="75"/>
       <c r="I86" s="69"/>
       <c r="J86" s="99" t="str">
@@ -58224,11 +58227,11 @@
     <row r="87" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="73"/>
       <c r="B87" s="73"/>
-      <c r="C87" s="167"/>
-      <c r="D87" s="168"/>
-      <c r="E87" s="168"/>
-      <c r="F87" s="168"/>
-      <c r="G87" s="169"/>
+      <c r="C87" s="189"/>
+      <c r="D87" s="190"/>
+      <c r="E87" s="190"/>
+      <c r="F87" s="190"/>
+      <c r="G87" s="191"/>
       <c r="H87" s="75"/>
       <c r="I87" s="69"/>
       <c r="J87" s="99" t="str">
@@ -58338,11 +58341,11 @@
     <row r="88" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="73"/>
       <c r="B88" s="73"/>
-      <c r="C88" s="170"/>
-      <c r="D88" s="171"/>
-      <c r="E88" s="171"/>
-      <c r="F88" s="171"/>
-      <c r="G88" s="172"/>
+      <c r="C88" s="192"/>
+      <c r="D88" s="193"/>
+      <c r="E88" s="193"/>
+      <c r="F88" s="193"/>
+      <c r="G88" s="194"/>
       <c r="H88" s="75"/>
       <c r="I88" s="69"/>
       <c r="J88" s="99" t="str">
@@ -59020,11 +59023,31 @@
   <sheetProtection algorithmName="SHA-512" hashValue="7nWuIQAsd0NKRlhwUK3tOeNHpTch5B5FULy2gxNNaIdJM5RfhFSMzPcx55y+pmM3d73guUy+p5Y+SvIjJZQRaA==" saltValue="Uw23KnM8csnTioq5H8upCA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <dataConsolidate/>
   <mergeCells count="45">
-    <mergeCell ref="BK14:BK15"/>
-    <mergeCell ref="BY16:BY17"/>
-    <mergeCell ref="BK26:BK27"/>
-    <mergeCell ref="BR28:BR29"/>
-    <mergeCell ref="BK22:BK23"/>
+    <mergeCell ref="CK68:CQ69"/>
+    <mergeCell ref="C83:G88"/>
+    <mergeCell ref="BK70:BK71"/>
+    <mergeCell ref="BY48:BY49"/>
+    <mergeCell ref="BY64:BY65"/>
+    <mergeCell ref="CF55:CF56"/>
+    <mergeCell ref="BK58:BK59"/>
+    <mergeCell ref="BR60:BR61"/>
+    <mergeCell ref="BK62:BK63"/>
+    <mergeCell ref="BK66:BK67"/>
+    <mergeCell ref="BR68:BR69"/>
+    <mergeCell ref="BK50:BK51"/>
+    <mergeCell ref="BR52:BR53"/>
+    <mergeCell ref="BK54:BK55"/>
+    <mergeCell ref="CE68:CJ69"/>
+    <mergeCell ref="CF6:CJ7"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="A5:H6"/>
+    <mergeCell ref="J5:P6"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="BR12:BR13"/>
+    <mergeCell ref="BK6:BO7"/>
+    <mergeCell ref="BR6:BV7"/>
+    <mergeCell ref="BY6:CC7"/>
     <mergeCell ref="CF23:CF24"/>
     <mergeCell ref="BK18:BK19"/>
     <mergeCell ref="BR20:BR21"/>
@@ -59040,31 +59063,11 @@
     <mergeCell ref="BK42:BK43"/>
     <mergeCell ref="CM33:CQ34"/>
     <mergeCell ref="CM37:CM38"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="BR12:BR13"/>
-    <mergeCell ref="BK6:BO7"/>
-    <mergeCell ref="BR6:BV7"/>
-    <mergeCell ref="BY6:CC7"/>
-    <mergeCell ref="CF6:CJ7"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="A5:H6"/>
-    <mergeCell ref="J5:P6"/>
-    <mergeCell ref="CK68:CQ69"/>
-    <mergeCell ref="C83:G88"/>
-    <mergeCell ref="BK70:BK71"/>
-    <mergeCell ref="BY48:BY49"/>
-    <mergeCell ref="BY64:BY65"/>
-    <mergeCell ref="CF55:CF56"/>
-    <mergeCell ref="BK58:BK59"/>
-    <mergeCell ref="BR60:BR61"/>
-    <mergeCell ref="BK62:BK63"/>
-    <mergeCell ref="BK66:BK67"/>
-    <mergeCell ref="BR68:BR69"/>
-    <mergeCell ref="BK50:BK51"/>
-    <mergeCell ref="BR52:BR53"/>
-    <mergeCell ref="BK54:BK55"/>
-    <mergeCell ref="CE68:CJ69"/>
+    <mergeCell ref="BK14:BK15"/>
+    <mergeCell ref="BY16:BY17"/>
+    <mergeCell ref="BK26:BK27"/>
+    <mergeCell ref="BR28:BR29"/>
+    <mergeCell ref="BK22:BK23"/>
   </mergeCells>
   <conditionalFormatting sqref="A7:E78">
     <cfRule type="expression" dxfId="228" priority="339">

--- a/public/worldcup.xlsx
+++ b/public/worldcup.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rylanpaul/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8AEC348-EFE2-354E-BBED-C00DCFA821B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{084BA5B0-AE20-1E46-8C61-7F54D515ED5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9897" uniqueCount="3715">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9903" uniqueCount="3715">
   <si>
     <t>English</t>
   </si>
@@ -13305,12 +13305,56 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -13391,50 +13435,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -38739,18 +38739,21 @@
       <c r="N3" t="s">
         <v>1739</v>
       </c>
-      <c r="O3" s="142" t="e">
+      <c r="O3" s="142">
         <f>IFERROR(_xlfn.XLOOKUP(N3,Rounds!M$2:M$17,Rounds!N$2:N$17), _xlfn.XLOOKUP(N3,Rounds!P$2:P$17,Rounds!O$2:O$17))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="P3" s="142" t="e">
+        <v>2</v>
+      </c>
+      <c r="P3" s="142">
         <f>IFERROR(_xlfn.XLOOKUP(N3,Rounds!M$2:M$17,Rounds!O$2:O$17), _xlfn.XLOOKUP(N3,Rounds!P$2:P$17,Rounds!N$2:N$17))</f>
-        <v>#N/A</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="140" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(N3,Rounds!M$2:M$17,Rounds!P$2:P$17), _xlfn.XLOOKUP(N3,Rounds!P$2:P$17,Rounds!M$2:M$17))</f>
         <v>Japan</v>
       </c>
+      <c r="R3" t="s">
+        <v>1323</v>
+      </c>
       <c r="S3" s="142" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(R3,Rounds!Q$2:Q$9,Rounds!R$2:R$9), _xlfn.XLOOKUP(R3,Rounds!T$2:T$9,Rounds!S$2:S$9))</f>
         <v>#N/A</v>
@@ -38759,9 +38762,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(R3,Rounds!Q$2:Q$9,Rounds!S$2:S$9), _xlfn.XLOOKUP(R3,Rounds!T$2:T$9,Rounds!R$2:R$9))</f>
         <v>#N/A</v>
       </c>
-      <c r="U3" s="140" t="e">
+      <c r="U3" s="140" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(R3,Rounds!Q$2:Q$9,Rounds!T$2:T$9), _xlfn.XLOOKUP(R3,Rounds!T$2:T$9,Rounds!Q$2:Q$9))</f>
-        <v>#N/A</v>
+        <v>England</v>
       </c>
       <c r="W3" s="142" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(V3,Rounds!U$2:U$5,Rounds!V$2:V$5), _xlfn.XLOOKUP(V3,Rounds!X$2:X$5,Rounds!W$2:W$5))</f>
@@ -38852,18 +38855,21 @@
       <c r="N4" s="148" t="s">
         <v>1148</v>
       </c>
-      <c r="O4" s="146" t="e">
+      <c r="O4" s="146">
         <f>IFERROR(_xlfn.XLOOKUP(N4,Rounds!M$2:M$17,Rounds!N$2:N$17), _xlfn.XLOOKUP(N4,Rounds!P$2:P$17,Rounds!O$2:O$17))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="P4" s="146" t="e">
+        <v>2</v>
+      </c>
+      <c r="P4" s="146">
         <f>IFERROR(_xlfn.XLOOKUP(N4,Rounds!M$2:M$17,Rounds!O$2:O$17), _xlfn.XLOOKUP(N4,Rounds!P$2:P$17,Rounds!N$2:N$17))</f>
-        <v>#N/A</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="147" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(N4,Rounds!M$2:M$17,Rounds!P$2:P$17), _xlfn.XLOOKUP(N4,Rounds!P$2:P$17,Rounds!M$2:M$17))</f>
         <v>DR Congo</v>
       </c>
+      <c r="R4" s="148" t="s">
+        <v>1323</v>
+      </c>
       <c r="S4" s="146" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(R4,Rounds!Q$2:Q$9,Rounds!R$2:R$9), _xlfn.XLOOKUP(R4,Rounds!T$2:T$9,Rounds!S$2:S$9))</f>
         <v>#N/A</v>
@@ -38872,9 +38878,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(R4,Rounds!Q$2:Q$9,Rounds!S$2:S$9), _xlfn.XLOOKUP(R4,Rounds!T$2:T$9,Rounds!R$2:R$9))</f>
         <v>#N/A</v>
       </c>
-      <c r="U4" s="147" t="e">
+      <c r="U4" s="147" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(R4,Rounds!Q$2:Q$9,Rounds!T$2:T$9), _xlfn.XLOOKUP(R4,Rounds!T$2:T$9,Rounds!Q$2:Q$9))</f>
-        <v>#N/A</v>
+        <v>England</v>
       </c>
       <c r="W4" s="146" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(V4,Rounds!U$2:U$5,Rounds!V$2:V$5), _xlfn.XLOOKUP(V4,Rounds!X$2:X$5,Rounds!W$2:W$5))</f>
@@ -38965,18 +38971,21 @@
       <c r="N5" t="s">
         <v>1633</v>
       </c>
-      <c r="O5" s="82" t="e">
+      <c r="O5" s="82">
         <f>IFERROR(_xlfn.XLOOKUP(N5,Rounds!M$2:M$17,Rounds!N$2:N$17), _xlfn.XLOOKUP(N5,Rounds!P$2:P$17,Rounds!O$2:O$17))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="P5" s="82" t="e">
+        <v>3</v>
+      </c>
+      <c r="P5" s="82">
         <f>IFERROR(_xlfn.XLOOKUP(N5,Rounds!M$2:M$17,Rounds!O$2:O$17), _xlfn.XLOOKUP(N5,Rounds!P$2:P$17,Rounds!N$2:N$17))</f>
-        <v>#N/A</v>
+        <v>2</v>
       </c>
       <c r="Q5" s="134" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(N5,Rounds!M$2:M$17,Rounds!P$2:P$17), _xlfn.XLOOKUP(N5,Rounds!P$2:P$17,Rounds!M$2:M$17))</f>
         <v>Senegal</v>
       </c>
+      <c r="R5" t="s">
+        <v>1677</v>
+      </c>
       <c r="S5" s="82" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(R5,Rounds!Q$2:Q$9,Rounds!R$2:R$9), _xlfn.XLOOKUP(R5,Rounds!T$2:T$9,Rounds!S$2:S$9))</f>
         <v>#N/A</v>
@@ -38985,9 +38994,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(R5,Rounds!Q$2:Q$9,Rounds!S$2:S$9), _xlfn.XLOOKUP(R5,Rounds!T$2:T$9,Rounds!R$2:R$9))</f>
         <v>#N/A</v>
       </c>
-      <c r="U5" s="134" t="e">
+      <c r="U5" s="134" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(R5,Rounds!Q$2:Q$9,Rounds!T$2:T$9), _xlfn.XLOOKUP(R5,Rounds!T$2:T$9,Rounds!Q$2:Q$9))</f>
-        <v>#N/A</v>
+        <v>Canada</v>
       </c>
       <c r="W5" s="82" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(V5,Rounds!U$2:U$5,Rounds!V$2:V$5), _xlfn.XLOOKUP(V5,Rounds!X$2:X$5,Rounds!W$2:W$5))</f>
@@ -39078,18 +39087,21 @@
       <c r="N6" s="148" t="s">
         <v>1565</v>
       </c>
-      <c r="O6" s="146" t="e">
+      <c r="O6" s="146">
         <f>IFERROR(_xlfn.XLOOKUP(N6,Rounds!M$2:M$17,Rounds!N$2:N$17), _xlfn.XLOOKUP(N6,Rounds!P$2:P$17,Rounds!O$2:O$17))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="P6" s="146" t="e">
+        <v>1</v>
+      </c>
+      <c r="P6" s="146">
         <f>IFERROR(_xlfn.XLOOKUP(N6,Rounds!M$2:M$17,Rounds!O$2:O$17), _xlfn.XLOOKUP(N6,Rounds!P$2:P$17,Rounds!N$2:N$17))</f>
-        <v>#N/A</v>
+        <v>2</v>
       </c>
       <c r="Q6" s="147" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(N6,Rounds!M$2:M$17,Rounds!P$2:P$17), _xlfn.XLOOKUP(N6,Rounds!P$2:P$17,Rounds!M$2:M$17))</f>
         <v>Paraguay</v>
       </c>
+      <c r="R6" s="148" t="s">
+        <v>1323</v>
+      </c>
       <c r="S6" s="146" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(R6,Rounds!Q$2:Q$9,Rounds!R$2:R$9), _xlfn.XLOOKUP(R6,Rounds!T$2:T$9,Rounds!S$2:S$9))</f>
         <v>#N/A</v>
@@ -39098,9 +39110,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(R6,Rounds!Q$2:Q$9,Rounds!S$2:S$9), _xlfn.XLOOKUP(R6,Rounds!T$2:T$9,Rounds!R$2:R$9))</f>
         <v>#N/A</v>
       </c>
-      <c r="U6" s="147" t="e">
+      <c r="U6" s="147" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(R6,Rounds!Q$2:Q$9,Rounds!T$2:T$9), _xlfn.XLOOKUP(R6,Rounds!T$2:T$9,Rounds!Q$2:Q$9))</f>
-        <v>#N/A</v>
+        <v>England</v>
       </c>
       <c r="W6" s="146" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(V6,Rounds!U$2:U$5,Rounds!V$2:V$5), _xlfn.XLOOKUP(V6,Rounds!X$2:X$5,Rounds!W$2:W$5))</f>
@@ -39191,18 +39203,21 @@
       <c r="N7" t="s">
         <v>1633</v>
       </c>
-      <c r="O7" s="82" t="e">
+      <c r="O7" s="82">
         <f>IFERROR(_xlfn.XLOOKUP(N7,Rounds!M$2:M$17,Rounds!N$2:N$17), _xlfn.XLOOKUP(N7,Rounds!P$2:P$17,Rounds!O$2:O$17))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="P7" s="82" t="e">
+        <v>3</v>
+      </c>
+      <c r="P7" s="82">
         <f>IFERROR(_xlfn.XLOOKUP(N7,Rounds!M$2:M$17,Rounds!O$2:O$17), _xlfn.XLOOKUP(N7,Rounds!P$2:P$17,Rounds!N$2:N$17))</f>
-        <v>#N/A</v>
+        <v>2</v>
       </c>
       <c r="Q7" s="134" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(N7,Rounds!M$2:M$17,Rounds!P$2:P$17), _xlfn.XLOOKUP(N7,Rounds!P$2:P$17,Rounds!M$2:M$17))</f>
         <v>Senegal</v>
       </c>
+      <c r="R7" t="s">
+        <v>1508</v>
+      </c>
       <c r="S7" s="82" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(R7,Rounds!Q$2:Q$9,Rounds!R$2:R$9), _xlfn.XLOOKUP(R7,Rounds!T$2:T$9,Rounds!S$2:S$9))</f>
         <v>#N/A</v>
@@ -39211,9 +39226,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(R7,Rounds!Q$2:Q$9,Rounds!S$2:S$9), _xlfn.XLOOKUP(R7,Rounds!T$2:T$9,Rounds!R$2:R$9))</f>
         <v>#N/A</v>
       </c>
-      <c r="U7" s="134" t="e">
+      <c r="U7" s="134" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(R7,Rounds!Q$2:Q$9,Rounds!T$2:T$9), _xlfn.XLOOKUP(R7,Rounds!T$2:T$9,Rounds!Q$2:Q$9))</f>
-        <v>#N/A</v>
+        <v>Portugal</v>
       </c>
       <c r="W7" s="82" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(V7,Rounds!U$2:U$5,Rounds!V$2:V$5), _xlfn.XLOOKUP(V7,Rounds!X$2:X$5,Rounds!W$2:W$5))</f>
@@ -39304,19 +39319,21 @@
       <c r="N8" s="152" t="s">
         <v>1662</v>
       </c>
-      <c r="O8" s="150" t="e">
+      <c r="O8" s="150">
         <f>IFERROR(_xlfn.XLOOKUP(N8,Rounds!M$2:M$17,Rounds!N$2:N$17), _xlfn.XLOOKUP(N8,Rounds!P$2:P$17,Rounds!O$2:O$17))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="P8" s="150" t="e">
+        <v>1</v>
+      </c>
+      <c r="P8" s="150">
         <f>IFERROR(_xlfn.XLOOKUP(N8,Rounds!M$2:M$17,Rounds!O$2:O$17), _xlfn.XLOOKUP(N8,Rounds!P$2:P$17,Rounds!N$2:N$17))</f>
-        <v>#N/A</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="151" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(N8,Rounds!M$2:M$17,Rounds!P$2:P$17), _xlfn.XLOOKUP(N8,Rounds!P$2:P$17,Rounds!M$2:M$17))</f>
         <v>South Africa</v>
       </c>
-      <c r="R8" s="152"/>
+      <c r="R8" s="152" t="s">
+        <v>1148</v>
+      </c>
       <c r="S8" s="150" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(R8,Rounds!Q$2:Q$9,Rounds!R$2:R$9), _xlfn.XLOOKUP(R8,Rounds!T$2:T$9,Rounds!S$2:S$9))</f>
         <v>#N/A</v>
@@ -39325,9 +39342,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(R8,Rounds!Q$2:Q$9,Rounds!S$2:S$9), _xlfn.XLOOKUP(R8,Rounds!T$2:T$9,Rounds!R$2:R$9))</f>
         <v>#N/A</v>
       </c>
-      <c r="U8" s="151" t="e">
+      <c r="U8" s="151" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(R8,Rounds!Q$2:Q$9,Rounds!T$2:T$9), _xlfn.XLOOKUP(R8,Rounds!T$2:T$9,Rounds!Q$2:Q$9))</f>
-        <v>#N/A</v>
+        <v>Mexico</v>
       </c>
       <c r="V8" s="152"/>
       <c r="W8" s="150" t="e">
@@ -39534,13 +39551,13 @@
         <f>IF('2026 World Cup'!BL10="",NA(),'2026 World Cup'!BL10)</f>
         <v>Germany</v>
       </c>
-      <c r="N2" s="81" t="e">
+      <c r="N2" s="81">
         <f>IF('2026 World Cup'!$BM10="",NA(),'2026 World Cup'!$BM10)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="O2" s="81" t="e">
+        <v>1</v>
+      </c>
+      <c r="O2" s="81">
         <f>IF('2026 World Cup'!$BM11="",NA(),'2026 World Cup'!$BM11)</f>
-        <v>#N/A</v>
+        <v>2</v>
       </c>
       <c r="P2" s="134" t="str">
         <f>'2026 World Cup'!BL11</f>
@@ -39548,7 +39565,7 @@
       </c>
       <c r="Q2" s="132" t="str">
         <f>'2026 World Cup'!BS12</f>
-        <v/>
+        <v>Paraguay</v>
       </c>
       <c r="R2" s="81" t="e">
         <f>IF('2026 World Cup'!$BT12="",NA(),'2026 World Cup'!$BT12)</f>
@@ -39560,7 +39577,7 @@
       </c>
       <c r="T2" s="134" t="str">
         <f>'2026 World Cup'!BS13</f>
-        <v/>
+        <v>France</v>
       </c>
       <c r="U2" s="132" t="str">
         <f>'2026 World Cup'!BZ16</f>
@@ -39652,13 +39669,13 @@
         <f>'2026 World Cup'!BL14</f>
         <v>France</v>
       </c>
-      <c r="N3" s="81" t="e">
+      <c r="N3" s="81">
         <f>IF('2026 World Cup'!$BM14="",NA(),'2026 World Cup'!$BM14)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="O3" s="81" t="e">
+        <v>3</v>
+      </c>
+      <c r="O3" s="81">
         <f>IF('2026 World Cup'!$BM15="",NA(),'2026 World Cup'!$BM15)</f>
-        <v>#N/A</v>
+        <v>0</v>
       </c>
       <c r="P3" s="134" t="str">
         <f>'2026 World Cup'!BL15</f>
@@ -39666,7 +39683,7 @@
       </c>
       <c r="Q3" s="132" t="str">
         <f>'2026 World Cup'!BS20</f>
-        <v/>
+        <v>Canada</v>
       </c>
       <c r="R3" s="81" t="e">
         <f>IF('2026 World Cup'!$BT20="",NA(),'2026 World Cup'!$BT20)</f>
@@ -39678,7 +39695,7 @@
       </c>
       <c r="T3" s="134" t="str">
         <f>'2026 World Cup'!BS21</f>
-        <v/>
+        <v>Morocco</v>
       </c>
       <c r="U3" s="132" t="str">
         <f>'2026 World Cup'!BZ32</f>
@@ -39754,13 +39771,13 @@
         <f>'2026 World Cup'!BL18</f>
         <v>South Africa</v>
       </c>
-      <c r="N4" s="81" t="e">
+      <c r="N4" s="81">
         <f>IF('2026 World Cup'!$BM18="",NA(),'2026 World Cup'!$BM18)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="O4" s="81" t="e">
+        <v>0</v>
+      </c>
+      <c r="O4" s="81">
         <f>IF('2026 World Cup'!$BM19="",NA(),'2026 World Cup'!$BM19)</f>
-        <v>#N/A</v>
+        <v>1</v>
       </c>
       <c r="P4" s="134" t="str">
         <f>'2026 World Cup'!BL19</f>
@@ -39768,7 +39785,7 @@
       </c>
       <c r="Q4" s="132" t="str">
         <f>'2026 World Cup'!BS28</f>
-        <v/>
+        <v>Portugal</v>
       </c>
       <c r="R4" s="81" t="e">
         <f>IF('2026 World Cup'!$BT28="",NA(),'2026 World Cup'!$BT28)</f>
@@ -39780,7 +39797,7 @@
       </c>
       <c r="T4" s="134" t="str">
         <f>'2026 World Cup'!BS29</f>
-        <v/>
+        <v>Spain</v>
       </c>
       <c r="U4" s="132" t="str">
         <f>'2026 World Cup'!BZ48</f>
@@ -39840,13 +39857,13 @@
         <f>'2026 World Cup'!BL22</f>
         <v>Netherlands</v>
       </c>
-      <c r="N5" s="81" t="e">
+      <c r="N5" s="81">
         <f>IF('2026 World Cup'!$BM22="",NA(),'2026 World Cup'!$BM22)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="O5" s="81" t="e">
+        <v>1</v>
+      </c>
+      <c r="O5" s="81">
         <f>IF('2026 World Cup'!$BM23="",NA(),'2026 World Cup'!$BM23)</f>
-        <v>#N/A</v>
+        <v>2</v>
       </c>
       <c r="P5" s="134" t="str">
         <f>'2026 World Cup'!BL23</f>
@@ -39854,7 +39871,7 @@
       </c>
       <c r="Q5" s="132" t="str">
         <f>'2026 World Cup'!BS36</f>
-        <v/>
+        <v>United States</v>
       </c>
       <c r="R5" s="81" t="e">
         <f>IF('2026 World Cup'!$BT36="",NA(),'2026 World Cup'!$BT36)</f>
@@ -39866,7 +39883,7 @@
       </c>
       <c r="T5" s="134" t="str">
         <f>'2026 World Cup'!BS37</f>
-        <v/>
+        <v>Belgium</v>
       </c>
       <c r="U5" s="135" t="str">
         <f>'2026 World Cup'!BZ64</f>
@@ -39926,13 +39943,13 @@
         <f>'2026 World Cup'!BL26</f>
         <v>Portugal</v>
       </c>
-      <c r="N6" s="81" t="e">
+      <c r="N6" s="81">
         <f>IF('2026 World Cup'!$BM26="",NA(),'2026 World Cup'!$BM26)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="O6" s="81" t="e">
+        <v>2</v>
+      </c>
+      <c r="O6" s="81">
         <f>IF('2026 World Cup'!$BM27="",NA(),'2026 World Cup'!$BM27)</f>
-        <v>#N/A</v>
+        <v>1</v>
       </c>
       <c r="P6" s="134" t="str">
         <f>'2026 World Cup'!BL27</f>
@@ -39940,7 +39957,7 @@
       </c>
       <c r="Q6" s="132" t="str">
         <f>'2026 World Cup'!BS44</f>
-        <v/>
+        <v>Brazil</v>
       </c>
       <c r="R6" s="81" t="e">
         <f>IF('2026 World Cup'!$BT44="",NA(),'2026 World Cup'!$BT44)</f>
@@ -39952,7 +39969,7 @@
       </c>
       <c r="T6" s="134" t="str">
         <f>'2026 World Cup'!BS45</f>
-        <v/>
+        <v>Norway</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.2">
@@ -39996,13 +40013,13 @@
         <f>'2026 World Cup'!BL30</f>
         <v>Spain</v>
       </c>
-      <c r="N7" s="81" t="e">
+      <c r="N7" s="81">
         <f>IF('2026 World Cup'!$BM30="",NA(),'2026 World Cup'!$BM30)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="O7" s="81" t="e">
+        <v>3</v>
+      </c>
+      <c r="O7" s="81">
         <f>IF('2026 World Cup'!$BM31="",NA(),'2026 World Cup'!$BM31)</f>
-        <v>#N/A</v>
+        <v>0</v>
       </c>
       <c r="P7" s="134" t="str">
         <f>'2026 World Cup'!BL31</f>
@@ -40010,7 +40027,7 @@
       </c>
       <c r="Q7" s="132" t="str">
         <f>'2026 World Cup'!BS52</f>
-        <v/>
+        <v>Mexico</v>
       </c>
       <c r="R7" s="81" t="e">
         <f>IF('2026 World Cup'!$BT52="",NA(),'2026 World Cup'!$BT52)</f>
@@ -40022,7 +40039,7 @@
       </c>
       <c r="T7" s="134" t="str">
         <f>'2026 World Cup'!BS53</f>
-        <v/>
+        <v>England</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.2">
@@ -40066,13 +40083,13 @@
         <f>'2026 World Cup'!BL34</f>
         <v>United States</v>
       </c>
-      <c r="N8" s="81" t="e">
+      <c r="N8" s="81">
         <f>IF('2026 World Cup'!$BM34="",NA(),'2026 World Cup'!$BM34)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="O8" s="81" t="e">
+        <v>2</v>
+      </c>
+      <c r="O8" s="81">
         <f>IF('2026 World Cup'!$BM35="",NA(),'2026 World Cup'!$BM35)</f>
-        <v>#N/A</v>
+        <v>0</v>
       </c>
       <c r="P8" s="134" t="str">
         <f>'2026 World Cup'!BL35</f>
@@ -40080,7 +40097,7 @@
       </c>
       <c r="Q8" s="132" t="str">
         <f>'2026 World Cup'!BS60</f>
-        <v/>
+        <v>Argentina</v>
       </c>
       <c r="R8" s="81" t="e">
         <f>IF('2026 World Cup'!$BT60="",NA(),'2026 World Cup'!$BT60)</f>
@@ -40092,7 +40109,7 @@
       </c>
       <c r="T8" s="134" t="str">
         <f>'2026 World Cup'!BS61</f>
-        <v/>
+        <v>Egypt</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.2">
@@ -40136,13 +40153,13 @@
         <f>'2026 World Cup'!BL38</f>
         <v>Belgium</v>
       </c>
-      <c r="N9" s="81" t="e">
+      <c r="N9" s="81">
         <f>IF('2026 World Cup'!$BM38="",NA(),'2026 World Cup'!$BM38)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="O9" s="81" t="e">
+        <v>3</v>
+      </c>
+      <c r="O9" s="81">
         <f>IF('2026 World Cup'!$BM39="",NA(),'2026 World Cup'!$BM39)</f>
-        <v>#N/A</v>
+        <v>2</v>
       </c>
       <c r="P9" s="134" t="str">
         <f>'2026 World Cup'!BL39</f>
@@ -40150,7 +40167,7 @@
       </c>
       <c r="Q9" s="135" t="str">
         <f>'2026 World Cup'!BS68</f>
-        <v/>
+        <v>Switzerland</v>
       </c>
       <c r="R9" s="153" t="e">
         <f>IF('2026 World Cup'!$BT68="",NA(),'2026 World Cup'!$BT68)</f>
@@ -40206,13 +40223,13 @@
         <f>'2026 World Cup'!BL42</f>
         <v>Brazil</v>
       </c>
-      <c r="N10" s="81" t="e">
+      <c r="N10" s="81">
         <f>IF('2026 World Cup'!$BM42="",NA(),'2026 World Cup'!$BM42)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="O10" s="81" t="e">
+        <v>2</v>
+      </c>
+      <c r="O10" s="81">
         <f>IF('2026 World Cup'!$BM43="",NA(),'2026 World Cup'!$BM43)</f>
-        <v>#N/A</v>
+        <v>1</v>
       </c>
       <c r="P10" s="134" t="str">
         <f>'2026 World Cup'!BL43</f>
@@ -40260,13 +40277,13 @@
         <f>'2026 World Cup'!BL46</f>
         <v>Ivory Coast</v>
       </c>
-      <c r="N11" s="81" t="e">
+      <c r="N11" s="81">
         <f>IF('2026 World Cup'!$BM46="",NA(),'2026 World Cup'!$BM46)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="O11" s="81" t="e">
+        <v>1</v>
+      </c>
+      <c r="O11" s="81">
         <f>IF('2026 World Cup'!$BM47="",NA(),'2026 World Cup'!$BM47)</f>
-        <v>#N/A</v>
+        <v>2</v>
       </c>
       <c r="P11" s="134" t="str">
         <f>'2026 World Cup'!BL47</f>
@@ -40314,13 +40331,13 @@
         <f>'2026 World Cup'!BL50</f>
         <v>Mexico</v>
       </c>
-      <c r="N12" s="81" t="e">
-        <f>IF('2026 World Cup'!$BM40="",NA(),'2026 World Cup'!$BM40)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="O12" s="81" t="e">
-        <f>IF('2026 World Cup'!$BM41="",NA(),'2026 World Cup'!$BM41)</f>
-        <v>#N/A</v>
+      <c r="N12" s="81">
+        <f>IF('2026 World Cup'!$BM50="",NA(),'2026 World Cup'!$BM50)</f>
+        <v>2</v>
+      </c>
+      <c r="O12" s="81">
+        <f>IF('2026 World Cup'!$BM51="",NA(),'2026 World Cup'!$BM51)</f>
+        <v>0</v>
       </c>
       <c r="P12" s="134" t="str">
         <f>'2026 World Cup'!BL51</f>
@@ -40368,13 +40385,13 @@
         <f>'2026 World Cup'!BL54</f>
         <v>England</v>
       </c>
-      <c r="N13" s="81" t="e">
+      <c r="N13" s="81">
         <f>IF('2026 World Cup'!$BM54="",NA(),'2026 World Cup'!$BM54)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="O13" s="81" t="e">
+        <v>2</v>
+      </c>
+      <c r="O13" s="81">
         <f>IF('2026 World Cup'!$BM55="",NA(),'2026 World Cup'!$BM55)</f>
-        <v>#N/A</v>
+        <v>1</v>
       </c>
       <c r="P13" s="134" t="str">
         <f>'2026 World Cup'!BL55</f>
@@ -40422,13 +40439,13 @@
         <f>'2026 World Cup'!BL58</f>
         <v>Argentina</v>
       </c>
-      <c r="N14" s="81" t="e">
+      <c r="N14" s="81">
         <f>IF('2026 World Cup'!$BM58="",NA(),'2026 World Cup'!$BM58)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="O14" s="81" t="e">
+        <v>3</v>
+      </c>
+      <c r="O14" s="81">
         <f>IF('2026 World Cup'!$BM59="",NA(),'2026 World Cup'!$BM59)</f>
-        <v>#N/A</v>
+        <v>2</v>
       </c>
       <c r="P14" s="134" t="str">
         <f>'2026 World Cup'!BL59</f>
@@ -40476,13 +40493,13 @@
         <f>'2026 World Cup'!BL62</f>
         <v>Australia</v>
       </c>
-      <c r="N15" s="81" t="e">
+      <c r="N15" s="81">
         <f>IF('2026 World Cup'!$BM62="",NA(),'2026 World Cup'!$BM62)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="O15" s="81" t="e">
+        <v>1</v>
+      </c>
+      <c r="O15" s="81">
         <f>IF('2026 World Cup'!$BM63="",NA(),'2026 World Cup'!$BM63)</f>
-        <v>#N/A</v>
+        <v>2</v>
       </c>
       <c r="P15" s="134" t="str">
         <f>'2026 World Cup'!BL63</f>
@@ -40530,13 +40547,13 @@
         <f>'2026 World Cup'!BL66</f>
         <v>Switzerland</v>
       </c>
-      <c r="N16" s="81" t="e">
+      <c r="N16" s="81">
         <f>IF('2026 World Cup'!$BM66="",NA(),'2026 World Cup'!$BM66)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="O16" s="81" t="e">
+        <v>2</v>
+      </c>
+      <c r="O16" s="81">
         <f>IF('2026 World Cup'!$BM67="",NA(),'2026 World Cup'!$BM67)</f>
-        <v>#N/A</v>
+        <v>0</v>
       </c>
       <c r="P16" s="134" t="str">
         <f>'2026 World Cup'!BL67</f>
@@ -40981,25 +40998,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:95" ht="47" x14ac:dyDescent="0.2">
-      <c r="A1" s="171" t="str" cm="1">
+      <c r="A1" s="182" t="str" cm="1">
         <f t="array" ref="A1">INDEX(T,2,lang)</f>
         <v>2026 World Cup Final Tournament Schedule</v>
       </c>
-      <c r="B1" s="171"/>
-      <c r="C1" s="171"/>
-      <c r="D1" s="171"/>
-      <c r="E1" s="171"/>
-      <c r="F1" s="171"/>
-      <c r="G1" s="171"/>
-      <c r="H1" s="171"/>
-      <c r="I1" s="171"/>
-      <c r="J1" s="171"/>
-      <c r="K1" s="171"/>
-      <c r="L1" s="171"/>
-      <c r="M1" s="171"/>
-      <c r="N1" s="171"/>
-      <c r="O1" s="171"/>
-      <c r="P1" s="171"/>
+      <c r="B1" s="182"/>
+      <c r="C1" s="182"/>
+      <c r="D1" s="182"/>
+      <c r="E1" s="182"/>
+      <c r="F1" s="182"/>
+      <c r="G1" s="182"/>
+      <c r="H1" s="182"/>
+      <c r="I1" s="182"/>
+      <c r="J1" s="182"/>
+      <c r="K1" s="182"/>
+      <c r="L1" s="182"/>
+      <c r="M1" s="182"/>
+      <c r="N1" s="182"/>
+      <c r="O1" s="182"/>
+      <c r="P1" s="182"/>
       <c r="S1" s="123"/>
       <c r="T1" s="123"/>
       <c r="AC1" s="123"/>
@@ -41046,11 +41063,11 @@
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
-      <c r="O3" s="172" t="str">
+      <c r="O3" s="183" t="str">
         <f>"Language: " &amp; Settings!C4</f>
         <v>Language: English</v>
       </c>
-      <c r="P3" s="172"/>
+      <c r="P3" s="183"/>
       <c r="S3" s="123"/>
       <c r="T3" s="123"/>
       <c r="AC3" s="123"/>
@@ -41068,43 +41085,43 @@
     </row>
     <row r="4" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:95" x14ac:dyDescent="0.2">
-      <c r="A5" s="173" t="str" cm="1">
+      <c r="A5" s="184" t="str" cm="1">
         <f t="array" ref="A5">INDEX(T,3,lang)</f>
         <v>Group Stage</v>
       </c>
-      <c r="B5" s="174"/>
-      <c r="C5" s="174"/>
-      <c r="D5" s="174"/>
-      <c r="E5" s="174"/>
-      <c r="F5" s="174"/>
-      <c r="G5" s="174"/>
-      <c r="H5" s="175"/>
-      <c r="J5" s="179" t="s">
+      <c r="B5" s="185"/>
+      <c r="C5" s="185"/>
+      <c r="D5" s="185"/>
+      <c r="E5" s="185"/>
+      <c r="F5" s="185"/>
+      <c r="G5" s="185"/>
+      <c r="H5" s="186"/>
+      <c r="J5" s="190" t="s">
         <v>3166</v>
       </c>
-      <c r="K5" s="180"/>
-      <c r="L5" s="180"/>
-      <c r="M5" s="180"/>
-      <c r="N5" s="180"/>
-      <c r="O5" s="180"/>
-      <c r="P5" s="181"/>
+      <c r="K5" s="191"/>
+      <c r="L5" s="191"/>
+      <c r="M5" s="191"/>
+      <c r="N5" s="191"/>
+      <c r="O5" s="191"/>
+      <c r="P5" s="192"/>
     </row>
     <row r="6" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="176"/>
-      <c r="B6" s="177"/>
-      <c r="C6" s="177"/>
-      <c r="D6" s="177"/>
-      <c r="E6" s="177"/>
-      <c r="F6" s="177"/>
-      <c r="G6" s="177"/>
-      <c r="H6" s="178"/>
-      <c r="J6" s="182"/>
-      <c r="K6" s="183"/>
-      <c r="L6" s="183"/>
-      <c r="M6" s="183"/>
-      <c r="N6" s="183"/>
-      <c r="O6" s="183"/>
-      <c r="P6" s="184"/>
+      <c r="A6" s="187"/>
+      <c r="B6" s="188"/>
+      <c r="C6" s="188"/>
+      <c r="D6" s="188"/>
+      <c r="E6" s="188"/>
+      <c r="F6" s="188"/>
+      <c r="G6" s="188"/>
+      <c r="H6" s="189"/>
+      <c r="J6" s="193"/>
+      <c r="K6" s="194"/>
+      <c r="L6" s="194"/>
+      <c r="M6" s="194"/>
+      <c r="N6" s="194"/>
+      <c r="O6" s="194"/>
+      <c r="P6" s="195"/>
       <c r="R6" s="123" t="s">
         <v>3167</v>
       </c>
@@ -41214,37 +41231,37 @@
       <c r="BI6" s="128" t="s">
         <v>3178</v>
       </c>
-      <c r="BK6" s="165" t="s">
+      <c r="BK6" s="176" t="s">
         <v>3179</v>
       </c>
-      <c r="BL6" s="166"/>
-      <c r="BM6" s="166"/>
-      <c r="BN6" s="166"/>
-      <c r="BO6" s="167"/>
-      <c r="BR6" s="165" t="str" cm="1">
+      <c r="BL6" s="177"/>
+      <c r="BM6" s="177"/>
+      <c r="BN6" s="177"/>
+      <c r="BO6" s="178"/>
+      <c r="BR6" s="176" t="str" cm="1">
         <f t="array" ref="BR6">INDEX(T,4,lang)</f>
         <v>Round of 16</v>
       </c>
-      <c r="BS6" s="166"/>
-      <c r="BT6" s="166"/>
-      <c r="BU6" s="166"/>
-      <c r="BV6" s="167"/>
-      <c r="BY6" s="165" t="str" cm="1">
+      <c r="BS6" s="177"/>
+      <c r="BT6" s="177"/>
+      <c r="BU6" s="177"/>
+      <c r="BV6" s="178"/>
+      <c r="BY6" s="176" t="str" cm="1">
         <f t="array" ref="BY6">INDEX(T,5,lang)</f>
         <v>Quarterfinals</v>
       </c>
-      <c r="BZ6" s="166"/>
-      <c r="CA6" s="166"/>
-      <c r="CB6" s="166"/>
-      <c r="CC6" s="167"/>
-      <c r="CF6" s="165" t="str" cm="1">
+      <c r="BZ6" s="177"/>
+      <c r="CA6" s="177"/>
+      <c r="CB6" s="177"/>
+      <c r="CC6" s="178"/>
+      <c r="CF6" s="176" t="str" cm="1">
         <f t="array" ref="CF6">INDEX(T,6,lang)</f>
         <v>Semi-Finals</v>
       </c>
-      <c r="CG6" s="166"/>
-      <c r="CH6" s="166"/>
-      <c r="CI6" s="166"/>
-      <c r="CJ6" s="167"/>
+      <c r="CG6" s="177"/>
+      <c r="CH6" s="177"/>
+      <c r="CI6" s="177"/>
+      <c r="CJ6" s="178"/>
     </row>
     <row r="7" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="11">
@@ -41321,26 +41338,26 @@
         <v>1</v>
       </c>
       <c r="AY7" s="126"/>
-      <c r="BK7" s="168"/>
-      <c r="BL7" s="169"/>
-      <c r="BM7" s="169"/>
-      <c r="BN7" s="169"/>
-      <c r="BO7" s="170"/>
-      <c r="BR7" s="168"/>
-      <c r="BS7" s="169"/>
-      <c r="BT7" s="169"/>
-      <c r="BU7" s="169"/>
-      <c r="BV7" s="170"/>
-      <c r="BY7" s="168"/>
-      <c r="BZ7" s="169"/>
-      <c r="CA7" s="169"/>
-      <c r="CB7" s="169"/>
-      <c r="CC7" s="170"/>
-      <c r="CF7" s="168"/>
-      <c r="CG7" s="169"/>
-      <c r="CH7" s="169"/>
-      <c r="CI7" s="169"/>
-      <c r="CJ7" s="170"/>
+      <c r="BK7" s="179"/>
+      <c r="BL7" s="180"/>
+      <c r="BM7" s="180"/>
+      <c r="BN7" s="180"/>
+      <c r="BO7" s="181"/>
+      <c r="BR7" s="179"/>
+      <c r="BS7" s="180"/>
+      <c r="BT7" s="180"/>
+      <c r="BU7" s="180"/>
+      <c r="BV7" s="181"/>
+      <c r="BY7" s="179"/>
+      <c r="BZ7" s="180"/>
+      <c r="CA7" s="180"/>
+      <c r="CB7" s="180"/>
+      <c r="CC7" s="181"/>
+      <c r="CF7" s="179"/>
+      <c r="CG7" s="180"/>
+      <c r="CH7" s="180"/>
+      <c r="CI7" s="180"/>
+      <c r="CJ7" s="181"/>
     </row>
     <row r="8" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A8" s="16">
@@ -42076,19 +42093,21 @@
         <f>BH10/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK10" s="163">
+      <c r="BK10" s="173">
         <v>74</v>
       </c>
       <c r="BL10" s="24" t="str">
         <f>AS32</f>
         <v>Germany</v>
       </c>
-      <c r="BM10" s="61"/>
+      <c r="BM10" s="61">
+        <v>1</v>
+      </c>
       <c r="BN10" s="63"/>
       <c r="BO10" s="25"/>
-      <c r="BP10" s="112" t="str">
+      <c r="BP10" s="112">
         <f>IF(OR(BM10="",BM11="",AND(BN10="",BN11&lt;&gt;""),AND(BN11="",BN10&lt;&gt;""),AND(BO10="",BO11&lt;&gt;""),AND(BO11="",BO10&lt;&gt;"")),"",BM10*1000+BN10*10+BO10)</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="BQ10" s="112"/>
       <c r="BR10" s="21"/>
@@ -42339,17 +42358,19 @@
         <f>BH11/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK11" s="164"/>
+      <c r="BK11" s="174"/>
       <c r="BL11" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!G3,AK80:AS91,9,FALSE),"3rd Group A/B/C/D/F")</f>
         <v>Paraguay</v>
       </c>
-      <c r="BM11" s="62"/>
+      <c r="BM11" s="62">
+        <v>2</v>
+      </c>
       <c r="BN11" s="64"/>
       <c r="BO11" s="27"/>
-      <c r="BP11" s="113" t="str">
+      <c r="BP11" s="113">
         <f>IF(BP10="","",BM11*1000+BN11*10+BO11)</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="BQ11" s="112"/>
       <c r="BR11" s="21" t="str" cm="1">
@@ -42577,12 +42598,12 @@
       <c r="BO12" s="21"/>
       <c r="BP12" s="114"/>
       <c r="BQ12" s="112"/>
-      <c r="BR12" s="163">
+      <c r="BR12" s="173">
         <v>89</v>
       </c>
       <c r="BS12" s="24" t="str">
         <f>IF(BP10&gt;BP11,BL10,IF(BP10&lt;BP11,BL11,""))</f>
-        <v/>
+        <v>Paraguay</v>
       </c>
       <c r="BT12" s="61"/>
       <c r="BU12" s="63"/>
@@ -42698,10 +42719,10 @@
         <v>46203.875</v>
       </c>
       <c r="BQ13" s="115"/>
-      <c r="BR13" s="164"/>
+      <c r="BR13" s="174"/>
       <c r="BS13" s="26" t="str">
         <f>IF(BP14&gt;BP15,BL14,IF(BP14&lt;BP15,BL15,""))</f>
-        <v/>
+        <v>France</v>
       </c>
       <c r="BT13" s="62"/>
       <c r="BU13" s="64"/>
@@ -42956,19 +42977,21 @@
         <f>BH14/BH18</f>
         <v>0.98058252427184467</v>
       </c>
-      <c r="BK14" s="163">
+      <c r="BK14" s="173">
         <v>77</v>
       </c>
       <c r="BL14" s="24" t="str">
         <f>AS56</f>
         <v>France</v>
       </c>
-      <c r="BM14" s="61"/>
+      <c r="BM14" s="61">
+        <v>3</v>
+      </c>
       <c r="BN14" s="63"/>
       <c r="BO14" s="25"/>
-      <c r="BP14" s="116" t="str">
+      <c r="BP14" s="116">
         <f>IF(OR(BM14="",BM15="",AND(BN14="",BN15&lt;&gt;""),AND(BN15="",BN14&lt;&gt;""),AND(BO14="",BO15&lt;&gt;""),AND(BO15="",BO14&lt;&gt;"")),"",BM14*1000+BN14*10+BO14)</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="BQ14" s="112"/>
       <c r="BR14" s="21"/>
@@ -43223,17 +43246,19 @@
         <f>BH15/BH18</f>
         <v>0.98058252427184467</v>
       </c>
-      <c r="BK15" s="164"/>
+      <c r="BK15" s="174"/>
       <c r="BL15" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!I3,AK80:AS91,9,FALSE),"3rd Group C/D/F/G/H")</f>
         <v>Sweden</v>
       </c>
-      <c r="BM15" s="62"/>
+      <c r="BM15" s="62">
+        <v>0</v>
+      </c>
       <c r="BN15" s="64"/>
       <c r="BO15" s="27"/>
-      <c r="BP15" s="112" t="str">
+      <c r="BP15" s="112">
         <f>IF(BP14="","",BM15*1000+BN15*10+BO15)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BQ15" s="112"/>
       <c r="BR15" s="21"/>
@@ -43497,7 +43522,7 @@
       <c r="BV16" s="21"/>
       <c r="BW16" s="114"/>
       <c r="BX16" s="112"/>
-      <c r="BY16" s="163">
+      <c r="BY16" s="173">
         <v>97</v>
       </c>
       <c r="BZ16" s="24" t="str">
@@ -43759,7 +43784,7 @@
       <c r="BV17" s="21"/>
       <c r="BW17" s="114"/>
       <c r="BX17" s="115"/>
-      <c r="BY17" s="164"/>
+      <c r="BY17" s="174"/>
       <c r="BZ17" s="26" t="str">
         <f>IF(BW20&gt;BW21,BS20,IF(BW20&lt;BW21,BS21,""))</f>
         <v/>
@@ -43963,19 +43988,21 @@
         <f>MAX(BH14:BH17)+1</f>
         <v>51.5</v>
       </c>
-      <c r="BK18" s="163">
+      <c r="BK18" s="173">
         <v>73</v>
       </c>
       <c r="BL18" s="24" t="str">
         <f>AS9</f>
         <v>South Africa</v>
       </c>
-      <c r="BM18" s="61"/>
+      <c r="BM18" s="61">
+        <v>0</v>
+      </c>
       <c r="BN18" s="63"/>
       <c r="BO18" s="25"/>
-      <c r="BP18" s="112" t="str">
+      <c r="BP18" s="112">
         <f>IF(OR(BM18="",BM19="",AND(BN18="",BN19&lt;&gt;""),AND(BN19="",BN18&lt;&gt;""),AND(BO18="",BO19&lt;&gt;""),AND(BO19="",BO18&lt;&gt;"")),"",BM18*1000+BN18*10+BO18)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BQ18" s="112"/>
       <c r="BR18" s="21"/>
@@ -44071,17 +44098,19 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BK19" s="164"/>
+      <c r="BK19" s="174"/>
       <c r="BL19" s="26" t="str">
         <f>AS15</f>
         <v>Canada</v>
       </c>
-      <c r="BM19" s="62"/>
+      <c r="BM19" s="62">
+        <v>1</v>
+      </c>
       <c r="BN19" s="64"/>
       <c r="BO19" s="27"/>
-      <c r="BP19" s="113" t="str">
+      <c r="BP19" s="113">
         <f>IF(BP18="","",BM19*1000+BN19*10+BO19)</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="BQ19" s="112"/>
       <c r="BR19" s="21" t="str" cm="1">
@@ -44349,12 +44378,12 @@
       <c r="BO20" s="21"/>
       <c r="BP20" s="114"/>
       <c r="BQ20" s="112"/>
-      <c r="BR20" s="163">
+      <c r="BR20" s="173">
         <v>90</v>
       </c>
       <c r="BS20" s="24" t="str">
         <f>IF(BP18&gt;BP19,BL18,IF(BP18&lt;BP19,BL19,""))</f>
-        <v/>
+        <v>Canada</v>
       </c>
       <c r="BT20" s="61"/>
       <c r="BU20" s="63"/>
@@ -44622,10 +44651,10 @@
         <v>46203.041666666672</v>
       </c>
       <c r="BQ21" s="115"/>
-      <c r="BR21" s="164"/>
+      <c r="BR21" s="174"/>
       <c r="BS21" s="26" t="str">
         <f>IF(BP22&gt;BP23,BL22,IF(BP22&lt;BP23,BL23,""))</f>
-        <v/>
+        <v>Morocco</v>
       </c>
       <c r="BT21" s="62"/>
       <c r="BU21" s="64"/>
@@ -44876,19 +44905,21 @@
         <f>BH22/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK22" s="163">
+      <c r="BK22" s="173">
         <v>75</v>
       </c>
       <c r="BL22" s="24" t="str">
         <f>AS38</f>
         <v>Netherlands</v>
       </c>
-      <c r="BM22" s="61"/>
+      <c r="BM22" s="61">
+        <v>1</v>
+      </c>
       <c r="BN22" s="63"/>
       <c r="BO22" s="25"/>
-      <c r="BP22" s="116" t="str">
+      <c r="BP22" s="116">
         <f>IF(OR(BM22="",BM23="",AND(BN22="",BN23&lt;&gt;""),AND(BN23="",BN22&lt;&gt;""),AND(BO22="",BO23&lt;&gt;""),AND(BO23="",BO22&lt;&gt;"")),"",BM22*1000+BN22*10+BO22)</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="BQ22" s="112"/>
       <c r="BR22" s="21"/>
@@ -45140,17 +45171,19 @@
         <f>BH23/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK23" s="164"/>
+      <c r="BK23" s="174"/>
       <c r="BL23" s="26" t="str">
         <f>AS21</f>
         <v>Morocco</v>
       </c>
-      <c r="BM23" s="62"/>
+      <c r="BM23" s="62">
+        <v>2</v>
+      </c>
       <c r="BN23" s="64"/>
       <c r="BO23" s="27"/>
-      <c r="BP23" s="112" t="str">
+      <c r="BP23" s="112">
         <f>IF(BP22="","",BM23*1000+BN23*10+BO23)</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="BQ23" s="112"/>
       <c r="BR23" s="21"/>
@@ -45167,7 +45200,7 @@
       <c r="CC23" s="21"/>
       <c r="CD23" s="114"/>
       <c r="CE23" s="112"/>
-      <c r="CF23" s="163">
+      <c r="CF23" s="173">
         <v>101</v>
       </c>
       <c r="CG23" s="24" t="str">
@@ -45388,7 +45421,7 @@
       <c r="CC24" s="21"/>
       <c r="CD24" s="114"/>
       <c r="CE24" s="115"/>
-      <c r="CF24" s="164"/>
+      <c r="CF24" s="174"/>
       <c r="CG24" s="26" t="str">
         <f>IF(CD32&gt;CD33,BZ32,IF(CD32&lt;CD33,BZ33,""))</f>
         <v/>
@@ -45741,19 +45774,21 @@
         <f>BH26/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK26" s="163">
+      <c r="BK26" s="173">
         <v>83</v>
       </c>
       <c r="BL26" s="24" t="str">
         <f>AS69</f>
         <v>Portugal</v>
       </c>
-      <c r="BM26" s="61"/>
+      <c r="BM26" s="61">
+        <v>2</v>
+      </c>
       <c r="BN26" s="63"/>
       <c r="BO26" s="25"/>
-      <c r="BP26" s="112" t="str">
+      <c r="BP26" s="112">
         <f>IF(OR(BM26="",BM27="",AND(BN26="",BN27&lt;&gt;""),AND(BN27="",BN26&lt;&gt;""),AND(BO26="",BO27&lt;&gt;""),AND(BO27="",BO26&lt;&gt;"")),"",BM26*1000+BN26*10+BO26)</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="BQ26" s="112"/>
       <c r="BR26" s="21"/>
@@ -46009,17 +46044,19 @@
         <f>BH27/BH30</f>
         <v>0.98039215686274506</v>
       </c>
-      <c r="BK27" s="164"/>
+      <c r="BK27" s="174"/>
       <c r="BL27" s="26" t="str">
         <f>AS75</f>
         <v>Croatia</v>
       </c>
-      <c r="BM27" s="62"/>
+      <c r="BM27" s="62">
+        <v>1</v>
+      </c>
       <c r="BN27" s="64"/>
       <c r="BO27" s="27"/>
-      <c r="BP27" s="113" t="str">
+      <c r="BP27" s="113">
         <f>IF(BP26="","",BM27*1000+BN27*10+BO27)</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="BQ27" s="112"/>
       <c r="BR27" s="21" t="str" cm="1">
@@ -46284,12 +46321,12 @@
       <c r="BO28" s="21"/>
       <c r="BP28" s="114"/>
       <c r="BQ28" s="112"/>
-      <c r="BR28" s="163">
+      <c r="BR28" s="173">
         <v>93</v>
       </c>
       <c r="BS28" s="24" t="str">
         <f>IF(BP26&gt;BP27,BL26,IF(BP26&lt;BP27,BL27,""))</f>
-        <v/>
+        <v>Portugal</v>
       </c>
       <c r="BT28" s="61"/>
       <c r="BU28" s="63"/>
@@ -46549,10 +46586,10 @@
         <v>46205.791666666672</v>
       </c>
       <c r="BQ29" s="115"/>
-      <c r="BR29" s="164"/>
+      <c r="BR29" s="174"/>
       <c r="BS29" s="26" t="str">
         <f>IF(BP30&gt;BP31,BL30,IF(BP30&lt;BP31,BL31,""))</f>
-        <v/>
+        <v>Spain</v>
       </c>
       <c r="BT29" s="62"/>
       <c r="BU29" s="64"/>
@@ -46763,19 +46800,21 @@
         <f>MAX(BH26:BH29)+1</f>
         <v>51</v>
       </c>
-      <c r="BK30" s="163">
+      <c r="BK30" s="173">
         <v>84</v>
       </c>
       <c r="BL30" s="24" t="str">
         <f>AS50</f>
         <v>Spain</v>
       </c>
-      <c r="BM30" s="61"/>
+      <c r="BM30" s="61">
+        <v>3</v>
+      </c>
       <c r="BN30" s="63"/>
       <c r="BO30" s="25"/>
-      <c r="BP30" s="116" t="str">
+      <c r="BP30" s="116">
         <f>IF(OR(BM30="",BM31="",AND(BN30="",BN31&lt;&gt;""),AND(BN31="",BN30&lt;&gt;""),AND(BO30="",BO31&lt;&gt;""),AND(BO31="",BO30&lt;&gt;"")),"",BM30*1000+BN30*10+BO30)</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="BQ30" s="112"/>
       <c r="BR30" s="21"/>
@@ -46874,17 +46913,19 @@
         <f>IF(OR(F31="",G31=""),"",IF(F31&gt;G31,1,IF(F31&lt;G31,-1,0)))</f>
         <v>0</v>
       </c>
-      <c r="BK31" s="164"/>
+      <c r="BK31" s="174"/>
       <c r="BL31" s="26" t="str">
         <f>AS63</f>
         <v>Austria</v>
       </c>
-      <c r="BM31" s="62"/>
+      <c r="BM31" s="62">
+        <v>0</v>
+      </c>
       <c r="BN31" s="64"/>
       <c r="BO31" s="27"/>
-      <c r="BP31" s="112" t="str">
+      <c r="BP31" s="112">
         <f>IF(BP30="","",BM31*1000+BN31*10+BO31)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BQ31" s="112"/>
       <c r="BR31" s="21"/>
@@ -47150,7 +47191,7 @@
       <c r="BV32" s="21"/>
       <c r="BW32" s="114"/>
       <c r="BX32" s="112"/>
-      <c r="BY32" s="163">
+      <c r="BY32" s="173">
         <v>98</v>
       </c>
       <c r="BZ32" s="24" t="str">
@@ -47414,7 +47455,7 @@
       <c r="BV33" s="21"/>
       <c r="BW33" s="114"/>
       <c r="BX33" s="115"/>
-      <c r="BY33" s="164"/>
+      <c r="BY33" s="174"/>
       <c r="BZ33" s="26" t="str">
         <f>IF(BW36&gt;BW37,BS36,IF(BW36&lt;BW37,BS37,""))</f>
         <v/>
@@ -47429,14 +47470,14 @@
       <c r="CE33" s="112"/>
       <c r="CK33" s="114"/>
       <c r="CL33" s="112"/>
-      <c r="CM33" s="165" t="str" cm="1">
+      <c r="CM33" s="176" t="str" cm="1">
         <f t="array" ref="CM33">INDEX(T,8,lang)</f>
         <v>Final</v>
       </c>
-      <c r="CN33" s="166"/>
-      <c r="CO33" s="166"/>
-      <c r="CP33" s="166"/>
-      <c r="CQ33" s="167"/>
+      <c r="CN33" s="177"/>
+      <c r="CO33" s="177"/>
+      <c r="CP33" s="177"/>
+      <c r="CQ33" s="178"/>
     </row>
     <row r="34" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A34" s="16">
@@ -47660,19 +47701,21 @@
         <f>BH34/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK34" s="163">
+      <c r="BK34" s="173">
         <v>81</v>
       </c>
       <c r="BL34" s="24" t="str">
         <f>AS26</f>
         <v>United States</v>
       </c>
-      <c r="BM34" s="61"/>
+      <c r="BM34" s="61">
+        <v>2</v>
+      </c>
       <c r="BN34" s="63"/>
       <c r="BO34" s="25"/>
-      <c r="BP34" s="112" t="str">
+      <c r="BP34" s="112">
         <f>IF(OR(BM34="",BM35="",AND(BN34="",BN35&lt;&gt;""),AND(BN35="",BN34&lt;&gt;""),AND(BO34="",BO35&lt;&gt;""),AND(BO35="",BO34&lt;&gt;"")),"",BM34*1000+BN34*10+BO34)</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="BQ34" s="112"/>
       <c r="BR34" s="21"/>
@@ -47691,11 +47734,11 @@
       <c r="CE34" s="112"/>
       <c r="CK34" s="114"/>
       <c r="CL34" s="112"/>
-      <c r="CM34" s="168"/>
-      <c r="CN34" s="169"/>
-      <c r="CO34" s="169"/>
-      <c r="CP34" s="169"/>
-      <c r="CQ34" s="170"/>
+      <c r="CM34" s="179"/>
+      <c r="CN34" s="180"/>
+      <c r="CO34" s="180"/>
+      <c r="CP34" s="180"/>
+      <c r="CQ34" s="181"/>
     </row>
     <row r="35" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A35" s="16">
@@ -47919,17 +47962,19 @@
         <f>BH35/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK35" s="164"/>
+      <c r="BK35" s="174"/>
       <c r="BL35" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!F3,AK80:AS91,9,FALSE),"3rd Group B/E/F/I/J")</f>
         <v>Bosnia and Herzegovina</v>
       </c>
-      <c r="BM35" s="62"/>
+      <c r="BM35" s="62">
+        <v>0</v>
+      </c>
       <c r="BN35" s="64"/>
       <c r="BO35" s="27"/>
-      <c r="BP35" s="113" t="str">
+      <c r="BP35" s="113">
         <f>IF(BP34="","",BM35*1000+BN35*10+BO35)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BQ35" s="112"/>
       <c r="BR35" s="21" t="str" cm="1">
@@ -48148,12 +48193,12 @@
       <c r="BO36" s="21"/>
       <c r="BP36" s="114"/>
       <c r="BQ36" s="112"/>
-      <c r="BR36" s="163">
+      <c r="BR36" s="173">
         <v>94</v>
       </c>
       <c r="BS36" s="24" t="str">
         <f>IF(BP34&gt;BP35,BL34,IF(BP34&lt;BP35,BL35,""))</f>
-        <v/>
+        <v>United States</v>
       </c>
       <c r="BT36" s="61"/>
       <c r="BU36" s="63"/>
@@ -48272,10 +48317,10 @@
         <v>46204.833333333336</v>
       </c>
       <c r="BQ37" s="115"/>
-      <c r="BR37" s="164"/>
+      <c r="BR37" s="174"/>
       <c r="BS37" s="26" t="str">
         <f>IF(BP38&gt;BP39,BL38,IF(BP38&lt;BP39,BL39,""))</f>
-        <v/>
+        <v>Belgium</v>
       </c>
       <c r="BT37" s="62"/>
       <c r="BU37" s="64"/>
@@ -48299,7 +48344,7 @@
       <c r="CJ37" s="21"/>
       <c r="CK37" s="114"/>
       <c r="CL37" s="112"/>
-      <c r="CM37" s="163">
+      <c r="CM37" s="173">
         <v>104</v>
       </c>
       <c r="CN37" s="24" t="str">
@@ -48540,19 +48585,21 @@
         <f>BH38/BH42</f>
         <v>0</v>
       </c>
-      <c r="BK38" s="163">
+      <c r="BK38" s="173">
         <v>82</v>
       </c>
       <c r="BL38" s="24" t="str">
         <f>AS44</f>
         <v>Belgium</v>
       </c>
-      <c r="BM38" s="61"/>
+      <c r="BM38" s="61">
+        <v>3</v>
+      </c>
       <c r="BN38" s="63"/>
       <c r="BO38" s="25"/>
-      <c r="BP38" s="116" t="str">
+      <c r="BP38" s="116">
         <f>IF(OR(BM38="",BM39="",AND(BN38="",BN39&lt;&gt;""),AND(BN39="",BN38&lt;&gt;""),AND(BO38="",BO39&lt;&gt;""),AND(BO39="",BO38&lt;&gt;"")),"",BM38*1000+BN38*10+BO38)</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="BQ38" s="112"/>
       <c r="BW38" s="112"/>
@@ -48570,7 +48617,7 @@
       <c r="CI38" s="21"/>
       <c r="CJ38" s="21"/>
       <c r="CL38" s="115"/>
-      <c r="CM38" s="164"/>
+      <c r="CM38" s="174"/>
       <c r="CN38" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG55,IF(CK55&lt;CK56,CG56,""))</f>
         <v/>
@@ -48809,17 +48856,19 @@
         <f>BH39/BH42</f>
         <v>0</v>
       </c>
-      <c r="BK39" s="164"/>
+      <c r="BK39" s="174"/>
       <c r="BL39" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!H3,AK80:AS91,9,FALSE),"3rd Group A/E/H/I/J")</f>
         <v>Senegal</v>
       </c>
-      <c r="BM39" s="62"/>
+      <c r="BM39" s="62">
+        <v>2</v>
+      </c>
       <c r="BN39" s="64"/>
       <c r="BO39" s="27"/>
-      <c r="BP39" s="112" t="str">
+      <c r="BP39" s="112">
         <f>IF(BP38="","",BM39*1000+BN39*10+BO39)</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="BQ39" s="112"/>
       <c r="BY39" s="21"/>
@@ -49497,19 +49546,21 @@
         <f>MAX(BH38:BH41)+1</f>
         <v>1</v>
       </c>
-      <c r="BK42" s="163">
+      <c r="BK42" s="173">
         <v>76</v>
       </c>
       <c r="BL42" s="24" t="str">
         <f>AS20</f>
         <v>Brazil</v>
       </c>
-      <c r="BM42" s="61"/>
+      <c r="BM42" s="61">
+        <v>2</v>
+      </c>
       <c r="BN42" s="63"/>
       <c r="BO42" s="25"/>
-      <c r="BP42" s="112" t="str">
+      <c r="BP42" s="112">
         <f>IF(OR(BM42="",BM43="",AND(BN42="",BN43&lt;&gt;""),AND(BN43="",BN42&lt;&gt;""),AND(BO42="",BO43&lt;&gt;""),AND(BO43="",BO42&lt;&gt;"")),"",BM42*1000+BN42*10+BO42)</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="BQ42" s="112"/>
       <c r="BR42" s="21"/>
@@ -49594,17 +49645,19 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BK43" s="164"/>
+      <c r="BK43" s="174"/>
       <c r="BL43" s="26" t="str">
         <f>AS39</f>
         <v>Japan</v>
       </c>
-      <c r="BM43" s="62"/>
+      <c r="BM43" s="62">
+        <v>1</v>
+      </c>
       <c r="BN43" s="64"/>
       <c r="BO43" s="27"/>
-      <c r="BP43" s="113" t="str">
+      <c r="BP43" s="113">
         <f>IF(BP42="","",BM43*1000+BN43*10+BO43)</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="BQ43" s="112"/>
       <c r="BR43" s="21" t="str" cm="1">
@@ -49854,12 +49907,12 @@
       <c r="BO44" s="21"/>
       <c r="BP44" s="114"/>
       <c r="BQ44" s="112"/>
-      <c r="BR44" s="163">
+      <c r="BR44" s="173">
         <v>91</v>
       </c>
       <c r="BS44" s="24" t="str">
         <f>IF(BP42&gt;BP43,BL42,IF(BP42&lt;BP43,BL43,""))</f>
-        <v/>
+        <v>Brazil</v>
       </c>
       <c r="BT44" s="61"/>
       <c r="BU44" s="63"/>
@@ -49869,14 +49922,14 @@
         <v/>
       </c>
       <c r="CK44" s="114"/>
-      <c r="CM44" s="165" t="str" cm="1">
+      <c r="CM44" s="176" t="str" cm="1">
         <f t="array" ref="CM44">INDEX(T,7,lang)</f>
         <v>Third-Place Play-Off</v>
       </c>
-      <c r="CN44" s="166"/>
-      <c r="CO44" s="166"/>
-      <c r="CP44" s="166"/>
-      <c r="CQ44" s="167"/>
+      <c r="CN44" s="177"/>
+      <c r="CO44" s="177"/>
+      <c r="CP44" s="177"/>
+      <c r="CQ44" s="178"/>
     </row>
     <row r="45" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="16">
@@ -50117,10 +50170,10 @@
         <v>46203.708333333336</v>
       </c>
       <c r="BQ45" s="115"/>
-      <c r="BR45" s="164"/>
+      <c r="BR45" s="174"/>
       <c r="BS45" s="26" t="str">
         <f>IF(BP46&gt;BP47,BL46,IF(BP46&lt;BP47,BL47,""))</f>
-        <v/>
+        <v>Norway</v>
       </c>
       <c r="BT45" s="62"/>
       <c r="BU45" s="64"/>
@@ -50130,11 +50183,11 @@
         <v/>
       </c>
       <c r="CK45" s="114"/>
-      <c r="CM45" s="168"/>
-      <c r="CN45" s="169"/>
-      <c r="CO45" s="169"/>
-      <c r="CP45" s="169"/>
-      <c r="CQ45" s="170"/>
+      <c r="CM45" s="179"/>
+      <c r="CN45" s="180"/>
+      <c r="CO45" s="180"/>
+      <c r="CP45" s="180"/>
+      <c r="CQ45" s="181"/>
     </row>
     <row r="46" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A46" s="16">
@@ -50358,19 +50411,21 @@
         <f>BH46/BH48</f>
         <v>0</v>
       </c>
-      <c r="BK46" s="163">
+      <c r="BK46" s="173">
         <v>78</v>
       </c>
       <c r="BL46" s="24" t="str">
         <f>AS33</f>
         <v>Ivory Coast</v>
       </c>
-      <c r="BM46" s="61"/>
+      <c r="BM46" s="61">
+        <v>1</v>
+      </c>
       <c r="BN46" s="63"/>
       <c r="BO46" s="25"/>
-      <c r="BP46" s="116" t="str">
+      <c r="BP46" s="116">
         <f>IF(OR(BM46="",BM47="",AND(BN46="",BN47&lt;&gt;""),AND(BN47="",BN46&lt;&gt;""),AND(BO46="",BO47&lt;&gt;""),AND(BO47="",BO46&lt;&gt;"")),"",BM46*1000+BN46*10+BO46)</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="BQ46" s="112"/>
       <c r="BR46" s="21"/>
@@ -50604,17 +50659,19 @@
         <f>BH47/BH48</f>
         <v>0</v>
       </c>
-      <c r="BK47" s="164"/>
+      <c r="BK47" s="174"/>
       <c r="BL47" s="26" t="str">
         <f>AS57</f>
         <v>Norway</v>
       </c>
-      <c r="BM47" s="62"/>
+      <c r="BM47" s="62">
+        <v>2</v>
+      </c>
       <c r="BN47" s="64"/>
       <c r="BO47" s="27"/>
-      <c r="BP47" s="112" t="str">
+      <c r="BP47" s="112">
         <f>IF(BP46="","",BM47*1000+BN47*10+BO47)</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="BQ47" s="112"/>
       <c r="BR47" s="21"/>
@@ -50851,7 +50908,7 @@
       <c r="BV48" s="21"/>
       <c r="BW48" s="114"/>
       <c r="BX48" s="112"/>
-      <c r="BY48" s="163">
+      <c r="BY48" s="173">
         <v>99</v>
       </c>
       <c r="BZ48" s="24" t="str">
@@ -50867,7 +50924,7 @@
       </c>
       <c r="CK48" s="114"/>
       <c r="CL48" s="112"/>
-      <c r="CM48" s="163">
+      <c r="CM48" s="173">
         <v>103</v>
       </c>
       <c r="CN48" s="24" t="str">
@@ -50976,7 +51033,7 @@
       <c r="BV49" s="21"/>
       <c r="BW49" s="114"/>
       <c r="BX49" s="115"/>
-      <c r="BY49" s="164"/>
+      <c r="BY49" s="174"/>
       <c r="BZ49" s="26" t="str">
         <f>IF(BW52&gt;BW53,BS52,IF(BW52&lt;BW53,BS53,""))</f>
         <v/>
@@ -50990,7 +51047,7 @@
       </c>
       <c r="CK49" s="114"/>
       <c r="CL49" s="115"/>
-      <c r="CM49" s="164"/>
+      <c r="CM49" s="174"/>
       <c r="CN49" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG56,IF(CK55&lt;CK56,CG55,""))</f>
         <v/>
@@ -51229,19 +51286,21 @@
         <f>BH50/BH54</f>
         <v>0</v>
       </c>
-      <c r="BK50" s="163">
+      <c r="BK50" s="173">
         <v>79</v>
       </c>
       <c r="BL50" s="24" t="str">
         <f>AS8</f>
         <v>Mexico</v>
       </c>
-      <c r="BM50" s="61"/>
+      <c r="BM50" s="61">
+        <v>2</v>
+      </c>
       <c r="BN50" s="63"/>
       <c r="BO50" s="25"/>
-      <c r="BP50" s="112" t="str">
+      <c r="BP50" s="112">
         <f>IF(OR(BM50="",BM51="",AND(BN50="",BN51&lt;&gt;""),AND(BN51="",BN50&lt;&gt;""),AND(BO50="",BO51&lt;&gt;""),AND(BO51="",BO50&lt;&gt;"")),"",BM50*1000+BN50*10+BO50)</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="BQ50" s="112"/>
       <c r="BR50" s="21"/>
@@ -51486,17 +51545,19 @@
         <f>BH51/BH54</f>
         <v>0</v>
       </c>
-      <c r="BK51" s="164"/>
+      <c r="BK51" s="174"/>
       <c r="BL51" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!D3,AK80:AS91,9,FALSE),"3rd Group C/E/F/H/I")</f>
         <v>Ecuador</v>
       </c>
-      <c r="BM51" s="62"/>
+      <c r="BM51" s="62">
+        <v>0</v>
+      </c>
       <c r="BN51" s="64"/>
       <c r="BO51" s="27"/>
-      <c r="BP51" s="113" t="str">
+      <c r="BP51" s="113">
         <f>IF(BP50="","",BM51*1000+BN51*10+BO51)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BQ51" s="112"/>
       <c r="BR51" s="21" t="str" cm="1">
@@ -51750,12 +51811,12 @@
       <c r="BO52" s="21"/>
       <c r="BP52" s="114"/>
       <c r="BQ52" s="112"/>
-      <c r="BR52" s="163">
+      <c r="BR52" s="173">
         <v>92</v>
       </c>
       <c r="BS52" s="24" t="str">
         <f>IF(BP50&gt;BP51,BL50,IF(BP50&lt;BP51,BL51,""))</f>
-        <v/>
+        <v>Mexico</v>
       </c>
       <c r="BT52" s="61"/>
       <c r="BU52" s="63"/>
@@ -52009,10 +52070,10 @@
         <v>46204.666666666672</v>
       </c>
       <c r="BQ53" s="115"/>
-      <c r="BR53" s="164"/>
+      <c r="BR53" s="174"/>
       <c r="BS53" s="26" t="str">
         <f>IF(BP54&gt;BP55,BL54,IF(BP54&lt;BP55,BL55,""))</f>
-        <v/>
+        <v>England</v>
       </c>
       <c r="BT53" s="62"/>
       <c r="BU53" s="64"/>
@@ -52217,19 +52278,21 @@
         <f>MAX(BH50:BH53)+1</f>
         <v>51.5</v>
       </c>
-      <c r="BK54" s="163">
+      <c r="BK54" s="173">
         <v>80</v>
       </c>
       <c r="BL54" s="24" t="str">
         <f>AS74</f>
         <v>England</v>
       </c>
-      <c r="BM54" s="61"/>
+      <c r="BM54" s="61">
+        <v>2</v>
+      </c>
       <c r="BN54" s="63"/>
       <c r="BO54" s="25"/>
-      <c r="BP54" s="116" t="str">
+      <c r="BP54" s="116">
         <f>IF(OR(BM54="",BM55="",AND(BN54="",BN55&lt;&gt;""),AND(BN55="",BN54&lt;&gt;""),AND(BO54="",BO55&lt;&gt;""),AND(BO55="",BO54&lt;&gt;"")),"",BM54*1000+BN54*10+BO54)</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="BQ54" s="112"/>
       <c r="BR54" s="21"/>
@@ -52342,17 +52405,19 @@
         <f t="shared" si="23"/>
         <v>-1</v>
       </c>
-      <c r="BK55" s="164"/>
+      <c r="BK55" s="174"/>
       <c r="BL55" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!K3,AK80:AS91,9,FALSE),"3rd Group E/H/I/J/K")</f>
         <v>DR Congo</v>
       </c>
-      <c r="BM55" s="62"/>
+      <c r="BM55" s="62">
+        <v>1</v>
+      </c>
       <c r="BN55" s="64"/>
       <c r="BO55" s="27"/>
-      <c r="BP55" s="112" t="str">
+      <c r="BP55" s="112">
         <f>IF(BP54="","",BM55*1000+BN55*10+BO55)</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="BQ55" s="112"/>
       <c r="BR55" s="21"/>
@@ -52369,7 +52434,7 @@
       <c r="CC55" s="21"/>
       <c r="CD55" s="114"/>
       <c r="CE55" s="112"/>
-      <c r="CF55" s="163">
+      <c r="CF55" s="173">
         <v>102</v>
       </c>
       <c r="CG55" s="24" t="str">
@@ -52632,7 +52697,7 @@
       <c r="CC56" s="21"/>
       <c r="CD56" s="114"/>
       <c r="CE56" s="115"/>
-      <c r="CF56" s="164"/>
+      <c r="CF56" s="174"/>
       <c r="CG56" s="26" t="str">
         <f>IF(CD64&gt;CD65,BZ64,IF(CD64&lt;CD65,BZ65,""))</f>
         <v/>
@@ -53123,19 +53188,21 @@
         <f>BH58/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK58" s="163">
+      <c r="BK58" s="173">
         <v>86</v>
       </c>
       <c r="BL58" s="24" t="str">
         <f>AS62</f>
         <v>Argentina</v>
       </c>
-      <c r="BM58" s="61"/>
+      <c r="BM58" s="61">
+        <v>3</v>
+      </c>
       <c r="BN58" s="63"/>
       <c r="BO58" s="25"/>
-      <c r="BP58" s="112" t="str">
+      <c r="BP58" s="112">
         <f>IF(OR(BM58="",BM59="",AND(BN58="",BN59&lt;&gt;""),AND(BN59="",BN58&lt;&gt;""),AND(BO58="",BO59&lt;&gt;""),AND(BO59="",BO58&lt;&gt;"")),"",BM58*1000+BN58*10+BO58)</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="BQ58" s="112"/>
       <c r="BR58" s="21"/>
@@ -53375,17 +53442,19 @@
         <f>BH59/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK59" s="164"/>
+      <c r="BK59" s="174"/>
       <c r="BL59" s="26" t="str">
         <f>AS51</f>
         <v>Cape Verde</v>
       </c>
-      <c r="BM59" s="62"/>
+      <c r="BM59" s="62">
+        <v>2</v>
+      </c>
       <c r="BN59" s="64"/>
       <c r="BO59" s="27"/>
-      <c r="BP59" s="113" t="str">
+      <c r="BP59" s="113">
         <f>IF(BP58="","",BM59*1000+BN59*10+BO59)</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="BQ59" s="112"/>
       <c r="BR59" s="21" t="str" cm="1">
@@ -53602,12 +53671,12 @@
       <c r="BO60" s="21"/>
       <c r="BP60" s="114"/>
       <c r="BQ60" s="112"/>
-      <c r="BR60" s="163">
+      <c r="BR60" s="173">
         <v>95</v>
       </c>
       <c r="BS60" s="24" t="str">
         <f>IF(BP58&gt;BP59,BL58,IF(BP58&lt;BP59,BL59,""))</f>
-        <v/>
+        <v>Argentina</v>
       </c>
       <c r="BT60" s="61"/>
       <c r="BU60" s="63"/>
@@ -53719,10 +53788,10 @@
         <v>46206.75</v>
       </c>
       <c r="BQ61" s="115"/>
-      <c r="BR61" s="164"/>
+      <c r="BR61" s="174"/>
       <c r="BS61" s="26" t="str">
         <f>IF(BP62&gt;BP63,BL62,IF(BP62&lt;BP63,BL63,""))</f>
-        <v/>
+        <v>Egypt</v>
       </c>
       <c r="BT61" s="62"/>
       <c r="BU61" s="64"/>
@@ -53966,19 +54035,21 @@
         <f>BH62/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK62" s="163">
+      <c r="BK62" s="173">
         <v>88</v>
       </c>
       <c r="BL62" s="24" t="str">
         <f>AS27</f>
         <v>Australia</v>
       </c>
-      <c r="BM62" s="61"/>
+      <c r="BM62" s="61">
+        <v>1</v>
+      </c>
       <c r="BN62" s="63"/>
       <c r="BO62" s="25"/>
-      <c r="BP62" s="116" t="str">
+      <c r="BP62" s="116">
         <f>IF(OR(BM62="",BM63="",AND(BN62="",BN63&lt;&gt;""),AND(BN63="",BN62&lt;&gt;""),AND(BO62="",BO63&lt;&gt;""),AND(BO63="",BO62&lt;&gt;"")),"",BM62*1000+BN62*10+BO62)</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="BQ62" s="112"/>
       <c r="BR62" s="21"/>
@@ -54222,17 +54293,19 @@
         <f>BH63/BH66</f>
         <v>0.98067632850241548</v>
       </c>
-      <c r="BK63" s="164"/>
+      <c r="BK63" s="174"/>
       <c r="BL63" s="26" t="str">
         <f>AS45</f>
         <v>Egypt</v>
       </c>
-      <c r="BM63" s="62"/>
+      <c r="BM63" s="62">
+        <v>2</v>
+      </c>
       <c r="BN63" s="64"/>
       <c r="BO63" s="27"/>
-      <c r="BP63" s="112" t="str">
+      <c r="BP63" s="112">
         <f>IF(BP62="","",BM63*1000+BN63*10+BO63)</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="BQ63" s="112"/>
       <c r="BR63" s="21"/>
@@ -54492,7 +54565,7 @@
       <c r="BV64" s="21"/>
       <c r="BW64" s="114"/>
       <c r="BX64" s="112"/>
-      <c r="BY64" s="163">
+      <c r="BY64" s="173">
         <v>100</v>
       </c>
       <c r="BZ64" s="24" t="str">
@@ -54750,7 +54823,7 @@
       <c r="BV65" s="21"/>
       <c r="BW65" s="114"/>
       <c r="BX65" s="115"/>
-      <c r="BY65" s="164"/>
+      <c r="BY65" s="174"/>
       <c r="BZ65" s="26" t="str">
         <f>IF(BW68&gt;BW69,BS68,IF(BW68&lt;BW69,BS69,""))</f>
         <v/>
@@ -54950,19 +55023,21 @@
         <f>MAX(BH62:BH65)+1</f>
         <v>51.75</v>
       </c>
-      <c r="BK66" s="163">
+      <c r="BK66" s="173">
         <v>85</v>
       </c>
       <c r="BL66" s="24" t="str">
         <f>AS14</f>
         <v>Switzerland</v>
       </c>
-      <c r="BM66" s="61"/>
+      <c r="BM66" s="61">
+        <v>2</v>
+      </c>
       <c r="BN66" s="63"/>
       <c r="BO66" s="25"/>
-      <c r="BP66" s="112" t="str">
+      <c r="BP66" s="112">
         <f>IF(OR(BM66="",BM67="",AND(BN66="",BN67&lt;&gt;""),AND(BN67="",BN66&lt;&gt;""),AND(BO66="",BO67&lt;&gt;""),AND(BO67="",BO66&lt;&gt;"")),"",BM66*1000+BN66*10+BO66)</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="BQ66" s="112"/>
       <c r="BR66" s="21"/>
@@ -55054,17 +55129,19 @@
         <f t="shared" si="23"/>
         <v>-1</v>
       </c>
-      <c r="BK67" s="164"/>
+      <c r="BK67" s="174"/>
       <c r="BL67" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!E3,AK80:AS91,9,FALSE),"3rd Group E/F/G/I/J")</f>
         <v>Algeria</v>
       </c>
-      <c r="BM67" s="62"/>
+      <c r="BM67" s="62">
+        <v>0</v>
+      </c>
       <c r="BN67" s="64"/>
       <c r="BO67" s="27"/>
-      <c r="BP67" s="113" t="str">
+      <c r="BP67" s="113">
         <f>IF(BP66="","",BM67*1000+BN67*10+BO67)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BQ67" s="112"/>
       <c r="BR67" s="21" t="str" cm="1">
@@ -55314,12 +55391,12 @@
       <c r="BO68" s="21"/>
       <c r="BP68" s="114"/>
       <c r="BQ68" s="112"/>
-      <c r="BR68" s="163">
+      <c r="BR68" s="173">
         <v>96</v>
       </c>
       <c r="BS68" s="24" t="str">
         <f>IF(BP66&gt;BP67,BL66,IF(BP66&lt;BP67,BL67,""))</f>
-        <v/>
+        <v>Switzerland</v>
       </c>
       <c r="BT68" s="61"/>
       <c r="BU68" s="63"/>
@@ -55328,25 +55405,25 @@
         <f>IF(OR(BT68="",BT69="",AND(BU68="",BU69&lt;&gt;""),AND(BU69="",BU68&lt;&gt;""),AND(BV68="",BV69&lt;&gt;""),AND(BV69="",BV68&lt;&gt;"")),"",BT68*1000+BU68*10+BV68)</f>
         <v/>
       </c>
-      <c r="CE68" s="195" t="str">
+      <c r="CE68" s="175" t="str">
         <f>INDEX(T,144,lang)</f>
         <v>World Champion 2026</v>
       </c>
-      <c r="CF68" s="195"/>
-      <c r="CG68" s="195"/>
-      <c r="CH68" s="195"/>
-      <c r="CI68" s="195"/>
-      <c r="CJ68" s="195"/>
-      <c r="CK68" s="185" t="str">
+      <c r="CF68" s="175"/>
+      <c r="CG68" s="175"/>
+      <c r="CH68" s="175"/>
+      <c r="CI68" s="175"/>
+      <c r="CJ68" s="175"/>
+      <c r="CK68" s="163" t="str">
         <f>IF(CR37&gt;CR38,CN37,IF(CR37&lt;CR38,CN38,""))</f>
         <v/>
       </c>
-      <c r="CL68" s="185"/>
-      <c r="CM68" s="185"/>
-      <c r="CN68" s="185"/>
-      <c r="CO68" s="185"/>
-      <c r="CP68" s="185"/>
-      <c r="CQ68" s="185"/>
+      <c r="CL68" s="163"/>
+      <c r="CM68" s="163"/>
+      <c r="CN68" s="163"/>
+      <c r="CO68" s="163"/>
+      <c r="CP68" s="163"/>
+      <c r="CQ68" s="163"/>
     </row>
     <row r="69" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A69" s="16">
@@ -55588,7 +55665,7 @@
         <v>46207.0625</v>
       </c>
       <c r="BQ69" s="115"/>
-      <c r="BR69" s="164"/>
+      <c r="BR69" s="174"/>
       <c r="BS69" s="26" t="str">
         <f>IF(BP70&gt;BP71,BL70,IF(BP70&lt;BP71,BL71,""))</f>
         <v/>
@@ -55600,19 +55677,19 @@
         <f>IF(BW68="","",BT69*1000+BU69*10+BV69)</f>
         <v/>
       </c>
-      <c r="CE69" s="195"/>
-      <c r="CF69" s="195"/>
-      <c r="CG69" s="195"/>
-      <c r="CH69" s="195"/>
-      <c r="CI69" s="195"/>
-      <c r="CJ69" s="195"/>
-      <c r="CK69" s="185"/>
-      <c r="CL69" s="185"/>
-      <c r="CM69" s="185"/>
-      <c r="CN69" s="185"/>
-      <c r="CO69" s="185"/>
-      <c r="CP69" s="185"/>
-      <c r="CQ69" s="185"/>
+      <c r="CE69" s="175"/>
+      <c r="CF69" s="175"/>
+      <c r="CG69" s="175"/>
+      <c r="CH69" s="175"/>
+      <c r="CI69" s="175"/>
+      <c r="CJ69" s="175"/>
+      <c r="CK69" s="163"/>
+      <c r="CL69" s="163"/>
+      <c r="CM69" s="163"/>
+      <c r="CN69" s="163"/>
+      <c r="CO69" s="163"/>
+      <c r="CP69" s="163"/>
+      <c r="CQ69" s="163"/>
     </row>
     <row r="70" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A70" s="16">
@@ -55837,7 +55914,7 @@
         <f>BH70/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK70" s="163">
+      <c r="BK70" s="173">
         <v>87</v>
       </c>
       <c r="BL70" s="24" t="str">
@@ -56077,7 +56154,7 @@
         <f>BH71/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK71" s="164"/>
+      <c r="BK71" s="174"/>
       <c r="BL71" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!J3,AK80:AS91,9,FALSE),"3rd Group D/E/I/J/L")</f>
         <v>Ghana</v>
@@ -57781,13 +57858,13 @@
     <row r="83" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="73"/>
       <c r="B83" s="73"/>
-      <c r="C83" s="186" t="s">
+      <c r="C83" s="164" t="s">
         <v>3183</v>
       </c>
-      <c r="D83" s="187"/>
-      <c r="E83" s="187"/>
-      <c r="F83" s="187"/>
-      <c r="G83" s="188"/>
+      <c r="D83" s="165"/>
+      <c r="E83" s="165"/>
+      <c r="F83" s="165"/>
+      <c r="G83" s="166"/>
       <c r="H83" s="75"/>
       <c r="I83" s="69"/>
       <c r="J83" s="99" t="str">
@@ -57885,11 +57962,11 @@
     <row r="84" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="73"/>
       <c r="B84" s="73"/>
-      <c r="C84" s="189"/>
-      <c r="D84" s="190"/>
-      <c r="E84" s="190"/>
-      <c r="F84" s="190"/>
-      <c r="G84" s="191"/>
+      <c r="C84" s="167"/>
+      <c r="D84" s="168"/>
+      <c r="E84" s="168"/>
+      <c r="F84" s="168"/>
+      <c r="G84" s="169"/>
       <c r="H84" s="75"/>
       <c r="I84" s="69"/>
       <c r="J84" s="99" t="str">
@@ -57926,11 +58003,11 @@
       </c>
       <c r="S84" s="127" t="str">
         <f>IF(OR(BM10="",BM11=""),"",IF(BM10&gt;BM11,BL10,IF(BM10&lt;BM11,BL11,IF(OR(BN10="",BN11=""),"draw",IF(BN10&gt;BN11,BL10,IF(BN10&lt;BN11,BL11,IF(OR(BO10="",BO11=""),"draw",IF(BO10&gt;BO11,BL10,IF(BO10&lt;BO11,BL11,"draw")))))))))</f>
-        <v/>
+        <v>Paraguay</v>
       </c>
       <c r="T84" s="127" t="str" cm="1">
         <f t="array" ref="T84">IF(OR(S84="",S84="draw"),INDEX(T,86,lang),S84)</f>
-        <v>Austria</v>
+        <v>Paraguay</v>
       </c>
       <c r="AD84" s="123">
         <f t="shared" si="38"/>
@@ -57999,11 +58076,11 @@
     <row r="85" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="73"/>
       <c r="B85" s="73"/>
-      <c r="C85" s="189"/>
-      <c r="D85" s="190"/>
-      <c r="E85" s="190"/>
-      <c r="F85" s="190"/>
-      <c r="G85" s="191"/>
+      <c r="C85" s="167"/>
+      <c r="D85" s="168"/>
+      <c r="E85" s="168"/>
+      <c r="F85" s="168"/>
+      <c r="G85" s="169"/>
       <c r="H85" s="75"/>
       <c r="I85" s="69"/>
       <c r="J85" s="99" t="str">
@@ -58040,11 +58117,11 @@
       </c>
       <c r="S85" s="127" t="str">
         <f>IF(OR(BM14="",BM15=""),"",IF(BM14&gt;BM15,BL14,IF(BM14&lt;BM15,BL15,IF(OR(BN14="",BN15=""),"draw",IF(BN14&gt;BN15,BL14,IF(BN14&lt;BN15,BL15,IF(OR(BO14="",BO15=""),"draw",IF(BO14&gt;BO15,BL14,IF(BO14&lt;BO15,BL15,"draw")))))))))</f>
-        <v/>
+        <v>France</v>
       </c>
       <c r="T85" s="127" t="str" cm="1">
         <f t="array" ref="T85">IF(OR(S85="",S85="draw"),INDEX(T,87,lang),S85)</f>
-        <v>Jordan</v>
+        <v>France</v>
       </c>
       <c r="AD85" s="123">
         <f t="shared" si="38"/>
@@ -58113,11 +58190,11 @@
     <row r="86" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="73"/>
       <c r="B86" s="73"/>
-      <c r="C86" s="189"/>
-      <c r="D86" s="190"/>
-      <c r="E86" s="190"/>
-      <c r="F86" s="190"/>
-      <c r="G86" s="191"/>
+      <c r="C86" s="167"/>
+      <c r="D86" s="168"/>
+      <c r="E86" s="168"/>
+      <c r="F86" s="168"/>
+      <c r="G86" s="169"/>
       <c r="H86" s="75"/>
       <c r="I86" s="69"/>
       <c r="J86" s="99" t="str">
@@ -58154,11 +58231,11 @@
       </c>
       <c r="S86" s="127" t="str">
         <f>IF(OR(BM26="",BM27=""),"",IF(BM26&gt;BM27,BL26,IF(BM26&lt;BM27,BL27,IF(OR(BN26="",BN27=""),"draw",IF(BN26&gt;BN27,BL26,IF(BN26&lt;BN27,BL27,IF(OR(BO26="",BO27=""),"draw",IF(BO26&gt;BO27,BL26,IF(BO26&lt;BO27,BL27,"draw")))))))))</f>
-        <v/>
+        <v>Portugal</v>
       </c>
       <c r="T86" s="127" t="str" cm="1">
         <f t="array" ref="T86">IF(OR(S86="",S86="draw"),INDEX(T,88,lang),S86)</f>
-        <v>DR Congo</v>
+        <v>Portugal</v>
       </c>
       <c r="AD86" s="123">
         <f t="shared" si="38"/>
@@ -58227,11 +58304,11 @@
     <row r="87" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="73"/>
       <c r="B87" s="73"/>
-      <c r="C87" s="189"/>
-      <c r="D87" s="190"/>
-      <c r="E87" s="190"/>
-      <c r="F87" s="190"/>
-      <c r="G87" s="191"/>
+      <c r="C87" s="167"/>
+      <c r="D87" s="168"/>
+      <c r="E87" s="168"/>
+      <c r="F87" s="168"/>
+      <c r="G87" s="169"/>
       <c r="H87" s="75"/>
       <c r="I87" s="69"/>
       <c r="J87" s="99" t="str">
@@ -58268,11 +58345,11 @@
       </c>
       <c r="S87" s="127" t="str">
         <f>IF(OR(BM30="",BM31=""),"",IF(BM30&gt;BM31,BL30,IF(BM30&lt;BM31,BL31,IF(OR(BN30="",BN31=""),"draw",IF(BN30&gt;BN31,BL30,IF(BN30&lt;BN31,BL31,IF(OR(BO30="",BO31=""),"draw",IF(BO30&gt;BO31,BL30,IF(BO30&lt;BO31,BL31,"draw")))))))))</f>
-        <v/>
+        <v>Spain</v>
       </c>
       <c r="T87" s="127" t="str" cm="1">
         <f t="array" ref="T87">IF(OR(S87="",S87="draw"),INDEX(T,89,lang),S87)</f>
-        <v>Uzbekistan</v>
+        <v>Spain</v>
       </c>
       <c r="AD87" s="123">
         <f t="shared" si="38"/>
@@ -58341,11 +58418,11 @@
     <row r="88" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="73"/>
       <c r="B88" s="73"/>
-      <c r="C88" s="192"/>
-      <c r="D88" s="193"/>
-      <c r="E88" s="193"/>
-      <c r="F88" s="193"/>
-      <c r="G88" s="194"/>
+      <c r="C88" s="170"/>
+      <c r="D88" s="171"/>
+      <c r="E88" s="171"/>
+      <c r="F88" s="171"/>
+      <c r="G88" s="172"/>
       <c r="H88" s="75"/>
       <c r="I88" s="69"/>
       <c r="J88" s="99" t="str">
@@ -58382,11 +58459,11 @@
       </c>
       <c r="S88" s="127" t="str">
         <f>IF(OR(BM18="",BM19=""),"",IF(BM18&gt;BM19,BL18,IF(BM18&lt;BM19,BL19,IF(OR(BN18="",BN19=""),"draw",IF(BN18&gt;BN19,BL18,IF(BN18&lt;BN19,BL19,IF(OR(BO18="",BO19=""),"draw",IF(BO18&gt;BO19,BL18,IF(BO18&lt;BO19,BL19,"draw")))))))))</f>
-        <v/>
+        <v>Canada</v>
       </c>
       <c r="T88" s="127" t="str" cm="1">
         <f t="array" ref="T88">IF(OR(S88="",S88="draw"),INDEX(T,90,lang),S88)</f>
-        <v>Colombia</v>
+        <v>Canada</v>
       </c>
       <c r="AD88" s="123">
         <f t="shared" si="38"/>
@@ -58496,11 +58573,11 @@
       </c>
       <c r="S89" s="127" t="str">
         <f>IF(OR(BM22="",BM23=""),"",IF(BM22&gt;BM23,BL22,IF(BM22&lt;BM23,BL23,IF(OR(BN22="",BN23=""),"draw",IF(BN22&gt;BN23,BL22,IF(BN22&lt;BN23,BL23,IF(OR(BO22="",BO23=""),"draw",IF(BO22&gt;BO23,BL22,IF(BO22&lt;BO23,BL23,"draw")))))))))</f>
-        <v/>
+        <v>Morocco</v>
       </c>
       <c r="T89" s="127" t="str" cm="1">
         <f t="array" ref="T89">IF(OR(S89="",S89="draw"),INDEX(T,91,lang),S89)</f>
-        <v>Panama</v>
+        <v>Morocco</v>
       </c>
       <c r="AD89" s="123">
         <f t="shared" si="38"/>
@@ -58610,11 +58687,11 @@
       </c>
       <c r="S90" s="127" t="str">
         <f>IF(OR(BM34="",BM35=""),"",IF(BM34&gt;BM35,BL34,IF(BM34&lt;BM35,BL35,IF(OR(BN34="",BN35=""),"draw",IF(BN34&gt;BN35,BL34,IF(BN34&lt;BN35,BL35,IF(OR(BO34="",BO35=""),"draw",IF(BO34&gt;BO35,BL34,IF(BO34&lt;BO35,BL35,"draw")))))))))</f>
-        <v/>
-      </c>
-      <c r="T90" s="127" cm="1">
+        <v>United States</v>
+      </c>
+      <c r="T90" s="127" t="str" cm="1">
         <f t="array" ref="T90">IF(OR(S90="",S90="draw"),INDEX(T,92,lang),S90)</f>
-        <v>0</v>
+        <v>United States</v>
       </c>
       <c r="AD90" s="123">
         <f t="shared" si="38"/>
@@ -58724,11 +58801,11 @@
       </c>
       <c r="S91" s="127" t="str">
         <f>IF(OR(BM38="",BM39=""),"",IF(BM38&gt;BM39,BL38,IF(BM38&lt;BM39,BL39,IF(OR(BN38="",BN39=""),"draw",IF(BN38&gt;BN39,BL38,IF(BN38&lt;BN39,BL39,IF(OR(BO38="",BO39=""),"draw",IF(BO38&gt;BO39,BL38,IF(BO38&lt;BO39,BL39,"draw")))))))))</f>
-        <v/>
-      </c>
-      <c r="T91" s="127" cm="1">
+        <v>Belgium</v>
+      </c>
+      <c r="T91" s="127" t="str" cm="1">
         <f t="array" ref="T91">IF(OR(S91="",S91="draw"),INDEX(T,93,lang),S91)</f>
-        <v>0</v>
+        <v>Belgium</v>
       </c>
       <c r="AD91" s="123">
         <f t="shared" si="38"/>
@@ -59023,6 +59100,36 @@
   <sheetProtection algorithmName="SHA-512" hashValue="7nWuIQAsd0NKRlhwUK3tOeNHpTch5B5FULy2gxNNaIdJM5RfhFSMzPcx55y+pmM3d73guUy+p5Y+SvIjJZQRaA==" saltValue="Uw23KnM8csnTioq5H8upCA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <dataConsolidate/>
   <mergeCells count="45">
+    <mergeCell ref="BK14:BK15"/>
+    <mergeCell ref="BY16:BY17"/>
+    <mergeCell ref="BK26:BK27"/>
+    <mergeCell ref="BR28:BR29"/>
+    <mergeCell ref="BK22:BK23"/>
+    <mergeCell ref="CF23:CF24"/>
+    <mergeCell ref="BK18:BK19"/>
+    <mergeCell ref="BR20:BR21"/>
+    <mergeCell ref="CM48:CM49"/>
+    <mergeCell ref="BR44:BR45"/>
+    <mergeCell ref="BK46:BK47"/>
+    <mergeCell ref="BK30:BK31"/>
+    <mergeCell ref="CM44:CQ45"/>
+    <mergeCell ref="BY32:BY33"/>
+    <mergeCell ref="BK38:BK39"/>
+    <mergeCell ref="BK34:BK35"/>
+    <mergeCell ref="BR36:BR37"/>
+    <mergeCell ref="BK42:BK43"/>
+    <mergeCell ref="CM33:CQ34"/>
+    <mergeCell ref="CM37:CM38"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="BR12:BR13"/>
+    <mergeCell ref="BK6:BO7"/>
+    <mergeCell ref="BR6:BV7"/>
+    <mergeCell ref="BY6:CC7"/>
+    <mergeCell ref="CF6:CJ7"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="A5:H6"/>
+    <mergeCell ref="J5:P6"/>
     <mergeCell ref="CK68:CQ69"/>
     <mergeCell ref="C83:G88"/>
     <mergeCell ref="BK70:BK71"/>
@@ -59038,36 +59145,6 @@
     <mergeCell ref="BR52:BR53"/>
     <mergeCell ref="BK54:BK55"/>
     <mergeCell ref="CE68:CJ69"/>
-    <mergeCell ref="CF6:CJ7"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="A5:H6"/>
-    <mergeCell ref="J5:P6"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="BR12:BR13"/>
-    <mergeCell ref="BK6:BO7"/>
-    <mergeCell ref="BR6:BV7"/>
-    <mergeCell ref="BY6:CC7"/>
-    <mergeCell ref="CF23:CF24"/>
-    <mergeCell ref="BK18:BK19"/>
-    <mergeCell ref="BR20:BR21"/>
-    <mergeCell ref="CM48:CM49"/>
-    <mergeCell ref="BR44:BR45"/>
-    <mergeCell ref="BK46:BK47"/>
-    <mergeCell ref="BK30:BK31"/>
-    <mergeCell ref="CM44:CQ45"/>
-    <mergeCell ref="BY32:BY33"/>
-    <mergeCell ref="BK38:BK39"/>
-    <mergeCell ref="BK34:BK35"/>
-    <mergeCell ref="BR36:BR37"/>
-    <mergeCell ref="BK42:BK43"/>
-    <mergeCell ref="CM33:CQ34"/>
-    <mergeCell ref="CM37:CM38"/>
-    <mergeCell ref="BK14:BK15"/>
-    <mergeCell ref="BY16:BY17"/>
-    <mergeCell ref="BK26:BK27"/>
-    <mergeCell ref="BR28:BR29"/>
-    <mergeCell ref="BK22:BK23"/>
   </mergeCells>
   <conditionalFormatting sqref="A7:E78">
     <cfRule type="expression" dxfId="228" priority="339">

--- a/public/worldcup.xlsx
+++ b/public/worldcup.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rylanpaul/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{084BA5B0-AE20-1E46-8C61-7F54D515ED5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58F04A70-91A6-6A44-B439-C7F671E73D71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13305,56 +13305,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -13435,6 +13391,50 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -38754,13 +38754,13 @@
       <c r="R3" t="s">
         <v>1323</v>
       </c>
-      <c r="S3" s="142" t="e">
+      <c r="S3" s="142">
         <f>IFERROR(_xlfn.XLOOKUP(R3,Rounds!Q$2:Q$9,Rounds!R$2:R$9), _xlfn.XLOOKUP(R3,Rounds!T$2:T$9,Rounds!S$2:S$9))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="T3" s="142" t="e">
+        <v>2</v>
+      </c>
+      <c r="T3" s="142">
         <f>IFERROR(_xlfn.XLOOKUP(R3,Rounds!Q$2:Q$9,Rounds!S$2:S$9), _xlfn.XLOOKUP(R3,Rounds!T$2:T$9,Rounds!R$2:R$9))</f>
-        <v>#N/A</v>
+        <v>3</v>
       </c>
       <c r="U3" s="140" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(R3,Rounds!Q$2:Q$9,Rounds!T$2:T$9), _xlfn.XLOOKUP(R3,Rounds!T$2:T$9,Rounds!Q$2:Q$9))</f>
@@ -38870,13 +38870,13 @@
       <c r="R4" s="148" t="s">
         <v>1323</v>
       </c>
-      <c r="S4" s="146" t="e">
+      <c r="S4" s="146">
         <f>IFERROR(_xlfn.XLOOKUP(R4,Rounds!Q$2:Q$9,Rounds!R$2:R$9), _xlfn.XLOOKUP(R4,Rounds!T$2:T$9,Rounds!S$2:S$9))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="T4" s="146" t="e">
+        <v>2</v>
+      </c>
+      <c r="T4" s="146">
         <f>IFERROR(_xlfn.XLOOKUP(R4,Rounds!Q$2:Q$9,Rounds!S$2:S$9), _xlfn.XLOOKUP(R4,Rounds!T$2:T$9,Rounds!R$2:R$9))</f>
-        <v>#N/A</v>
+        <v>3</v>
       </c>
       <c r="U4" s="147" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(R4,Rounds!Q$2:Q$9,Rounds!T$2:T$9), _xlfn.XLOOKUP(R4,Rounds!T$2:T$9,Rounds!Q$2:Q$9))</f>
@@ -38986,13 +38986,13 @@
       <c r="R5" t="s">
         <v>1677</v>
       </c>
-      <c r="S5" s="82" t="e">
+      <c r="S5" s="82">
         <f>IFERROR(_xlfn.XLOOKUP(R5,Rounds!Q$2:Q$9,Rounds!R$2:R$9), _xlfn.XLOOKUP(R5,Rounds!T$2:T$9,Rounds!S$2:S$9))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="T5" s="82" t="e">
+        <v>3</v>
+      </c>
+      <c r="T5" s="82">
         <f>IFERROR(_xlfn.XLOOKUP(R5,Rounds!Q$2:Q$9,Rounds!S$2:S$9), _xlfn.XLOOKUP(R5,Rounds!T$2:T$9,Rounds!R$2:R$9))</f>
-        <v>#N/A</v>
+        <v>0</v>
       </c>
       <c r="U5" s="134" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(R5,Rounds!Q$2:Q$9,Rounds!T$2:T$9), _xlfn.XLOOKUP(R5,Rounds!T$2:T$9,Rounds!Q$2:Q$9))</f>
@@ -39102,13 +39102,13 @@
       <c r="R6" s="148" t="s">
         <v>1323</v>
       </c>
-      <c r="S6" s="146" t="e">
+      <c r="S6" s="146">
         <f>IFERROR(_xlfn.XLOOKUP(R6,Rounds!Q$2:Q$9,Rounds!R$2:R$9), _xlfn.XLOOKUP(R6,Rounds!T$2:T$9,Rounds!S$2:S$9))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="T6" s="146" t="e">
+        <v>2</v>
+      </c>
+      <c r="T6" s="146">
         <f>IFERROR(_xlfn.XLOOKUP(R6,Rounds!Q$2:Q$9,Rounds!S$2:S$9), _xlfn.XLOOKUP(R6,Rounds!T$2:T$9,Rounds!R$2:R$9))</f>
-        <v>#N/A</v>
+        <v>3</v>
       </c>
       <c r="U6" s="147" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(R6,Rounds!Q$2:Q$9,Rounds!T$2:T$9), _xlfn.XLOOKUP(R6,Rounds!T$2:T$9,Rounds!Q$2:Q$9))</f>
@@ -39218,13 +39218,13 @@
       <c r="R7" t="s">
         <v>1508</v>
       </c>
-      <c r="S7" s="82" t="e">
+      <c r="S7" s="82">
         <f>IFERROR(_xlfn.XLOOKUP(R7,Rounds!Q$2:Q$9,Rounds!R$2:R$9), _xlfn.XLOOKUP(R7,Rounds!T$2:T$9,Rounds!S$2:S$9))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="T7" s="82" t="e">
+        <v>1</v>
+      </c>
+      <c r="T7" s="82">
         <f>IFERROR(_xlfn.XLOOKUP(R7,Rounds!Q$2:Q$9,Rounds!S$2:S$9), _xlfn.XLOOKUP(R7,Rounds!T$2:T$9,Rounds!R$2:R$9))</f>
-        <v>#N/A</v>
+        <v>0</v>
       </c>
       <c r="U7" s="134" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(R7,Rounds!Q$2:Q$9,Rounds!T$2:T$9), _xlfn.XLOOKUP(R7,Rounds!T$2:T$9,Rounds!Q$2:Q$9))</f>
@@ -39334,13 +39334,13 @@
       <c r="R8" s="152" t="s">
         <v>1148</v>
       </c>
-      <c r="S8" s="150" t="e">
+      <c r="S8" s="150">
         <f>IFERROR(_xlfn.XLOOKUP(R8,Rounds!Q$2:Q$9,Rounds!R$2:R$9), _xlfn.XLOOKUP(R8,Rounds!T$2:T$9,Rounds!S$2:S$9))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="T8" s="150" t="e">
+        <v>3</v>
+      </c>
+      <c r="T8" s="150">
         <f>IFERROR(_xlfn.XLOOKUP(R8,Rounds!Q$2:Q$9,Rounds!S$2:S$9), _xlfn.XLOOKUP(R8,Rounds!T$2:T$9,Rounds!R$2:R$9))</f>
-        <v>#N/A</v>
+        <v>2</v>
       </c>
       <c r="U8" s="151" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(R8,Rounds!Q$2:Q$9,Rounds!T$2:T$9), _xlfn.XLOOKUP(R8,Rounds!T$2:T$9,Rounds!Q$2:Q$9))</f>
@@ -39567,13 +39567,13 @@
         <f>'2026 World Cup'!BS12</f>
         <v>Paraguay</v>
       </c>
-      <c r="R2" s="81" t="e">
+      <c r="R2" s="81">
         <f>IF('2026 World Cup'!$BT12="",NA(),'2026 World Cup'!$BT12)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="S2" s="81" t="e">
+        <v>0</v>
+      </c>
+      <c r="S2" s="81">
         <f>IF('2026 World Cup'!$BT13="",NA(),'2026 World Cup'!$BT13)</f>
-        <v>#N/A</v>
+        <v>1</v>
       </c>
       <c r="T2" s="134" t="str">
         <f>'2026 World Cup'!BS13</f>
@@ -39581,7 +39581,7 @@
       </c>
       <c r="U2" s="132" t="str">
         <f>'2026 World Cup'!BZ16</f>
-        <v/>
+        <v>France</v>
       </c>
       <c r="V2" s="81" t="e">
         <f>IF('2026 World Cup'!$CA16="",NA(),'2026 World Cup'!$CA16)</f>
@@ -39593,7 +39593,7 @@
       </c>
       <c r="X2" s="134" t="str">
         <f>'2026 World Cup'!BZ17</f>
-        <v/>
+        <v>Morocco</v>
       </c>
       <c r="Y2" s="132" t="str">
         <f>'2026 World Cup'!CG23</f>
@@ -39685,13 +39685,13 @@
         <f>'2026 World Cup'!BS20</f>
         <v>Canada</v>
       </c>
-      <c r="R3" s="81" t="e">
+      <c r="R3" s="81">
         <f>IF('2026 World Cup'!$BT20="",NA(),'2026 World Cup'!$BT20)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="S3" s="81" t="e">
+        <v>0</v>
+      </c>
+      <c r="S3" s="81">
         <f>IF('2026 World Cup'!$BT21="",NA(),'2026 World Cup'!$BT21)</f>
-        <v>#N/A</v>
+        <v>3</v>
       </c>
       <c r="T3" s="134" t="str">
         <f>'2026 World Cup'!BS21</f>
@@ -39699,7 +39699,7 @@
       </c>
       <c r="U3" s="132" t="str">
         <f>'2026 World Cup'!BZ32</f>
-        <v/>
+        <v>Spain</v>
       </c>
       <c r="V3" s="81" t="e">
         <f>IF('2026 World Cup'!$CA32="",NA(),'2026 World Cup'!$CA32)</f>
@@ -39787,13 +39787,13 @@
         <f>'2026 World Cup'!BS28</f>
         <v>Portugal</v>
       </c>
-      <c r="R4" s="81" t="e">
+      <c r="R4" s="81">
         <f>IF('2026 World Cup'!$BT28="",NA(),'2026 World Cup'!$BT28)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="S4" s="81" t="e">
+        <v>0</v>
+      </c>
+      <c r="S4" s="81">
         <f>IF('2026 World Cup'!$BT29="",NA(),'2026 World Cup'!$BT29)</f>
-        <v>#N/A</v>
+        <v>1</v>
       </c>
       <c r="T4" s="134" t="str">
         <f>'2026 World Cup'!BS29</f>
@@ -39801,7 +39801,7 @@
       </c>
       <c r="U4" s="132" t="str">
         <f>'2026 World Cup'!BZ48</f>
-        <v/>
+        <v>Norway</v>
       </c>
       <c r="V4" s="81" t="e">
         <f>IF('2026 World Cup'!$CA48="",NA(),'2026 World Cup'!$CA48)</f>
@@ -39813,7 +39813,7 @@
       </c>
       <c r="X4" s="134" t="str">
         <f>'2026 World Cup'!BZ49</f>
-        <v/>
+        <v>England</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.2">
@@ -39959,13 +39959,13 @@
         <f>'2026 World Cup'!BS44</f>
         <v>Brazil</v>
       </c>
-      <c r="R6" s="81" t="e">
+      <c r="R6" s="81">
         <f>IF('2026 World Cup'!$BT44="",NA(),'2026 World Cup'!$BT44)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="S6" s="81" t="e">
+        <v>1</v>
+      </c>
+      <c r="S6" s="81">
         <f>IF('2026 World Cup'!$BT45="",NA(),'2026 World Cup'!$BT45)</f>
-        <v>#N/A</v>
+        <v>2</v>
       </c>
       <c r="T6" s="134" t="str">
         <f>'2026 World Cup'!BS45</f>
@@ -40029,13 +40029,13 @@
         <f>'2026 World Cup'!BS52</f>
         <v>Mexico</v>
       </c>
-      <c r="R7" s="81" t="e">
+      <c r="R7" s="81">
         <f>IF('2026 World Cup'!$BT52="",NA(),'2026 World Cup'!$BT52)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="S7" s="81" t="e">
+        <v>2</v>
+      </c>
+      <c r="S7" s="81">
         <f>IF('2026 World Cup'!$BT53="",NA(),'2026 World Cup'!$BT53)</f>
-        <v>#N/A</v>
+        <v>3</v>
       </c>
       <c r="T7" s="134" t="str">
         <f>'2026 World Cup'!BS53</f>
@@ -40179,7 +40179,7 @@
       </c>
       <c r="T9" s="136" t="str">
         <f>'2026 World Cup'!BS69</f>
-        <v/>
+        <v>Colombia</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.2">
@@ -40601,13 +40601,13 @@
         <f>'2026 World Cup'!BL70</f>
         <v>Colombia</v>
       </c>
-      <c r="N17" s="153" t="e">
+      <c r="N17" s="153">
         <f>IF('2026 World Cup'!$BM70="",NA(),'2026 World Cup'!$BM70)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="O17" s="153" t="e">
+        <v>1</v>
+      </c>
+      <c r="O17" s="153">
         <f>IF('2026 World Cup'!$BM71="",NA(),'2026 World Cup'!$BM71)</f>
-        <v>#N/A</v>
+        <v>0</v>
       </c>
       <c r="P17" s="136" t="str">
         <f>'2026 World Cup'!BL71</f>
@@ -40998,25 +40998,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:95" ht="47" x14ac:dyDescent="0.2">
-      <c r="A1" s="182" t="str" cm="1">
+      <c r="A1" s="171" t="str" cm="1">
         <f t="array" ref="A1">INDEX(T,2,lang)</f>
         <v>2026 World Cup Final Tournament Schedule</v>
       </c>
-      <c r="B1" s="182"/>
-      <c r="C1" s="182"/>
-      <c r="D1" s="182"/>
-      <c r="E1" s="182"/>
-      <c r="F1" s="182"/>
-      <c r="G1" s="182"/>
-      <c r="H1" s="182"/>
-      <c r="I1" s="182"/>
-      <c r="J1" s="182"/>
-      <c r="K1" s="182"/>
-      <c r="L1" s="182"/>
-      <c r="M1" s="182"/>
-      <c r="N1" s="182"/>
-      <c r="O1" s="182"/>
-      <c r="P1" s="182"/>
+      <c r="B1" s="171"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="171"/>
+      <c r="F1" s="171"/>
+      <c r="G1" s="171"/>
+      <c r="H1" s="171"/>
+      <c r="I1" s="171"/>
+      <c r="J1" s="171"/>
+      <c r="K1" s="171"/>
+      <c r="L1" s="171"/>
+      <c r="M1" s="171"/>
+      <c r="N1" s="171"/>
+      <c r="O1" s="171"/>
+      <c r="P1" s="171"/>
       <c r="S1" s="123"/>
       <c r="T1" s="123"/>
       <c r="AC1" s="123"/>
@@ -41063,11 +41063,11 @@
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
-      <c r="O3" s="183" t="str">
+      <c r="O3" s="172" t="str">
         <f>"Language: " &amp; Settings!C4</f>
         <v>Language: English</v>
       </c>
-      <c r="P3" s="183"/>
+      <c r="P3" s="172"/>
       <c r="S3" s="123"/>
       <c r="T3" s="123"/>
       <c r="AC3" s="123"/>
@@ -41085,43 +41085,43 @@
     </row>
     <row r="4" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:95" x14ac:dyDescent="0.2">
-      <c r="A5" s="184" t="str" cm="1">
+      <c r="A5" s="173" t="str" cm="1">
         <f t="array" ref="A5">INDEX(T,3,lang)</f>
         <v>Group Stage</v>
       </c>
-      <c r="B5" s="185"/>
-      <c r="C5" s="185"/>
-      <c r="D5" s="185"/>
-      <c r="E5" s="185"/>
-      <c r="F5" s="185"/>
-      <c r="G5" s="185"/>
-      <c r="H5" s="186"/>
-      <c r="J5" s="190" t="s">
+      <c r="B5" s="174"/>
+      <c r="C5" s="174"/>
+      <c r="D5" s="174"/>
+      <c r="E5" s="174"/>
+      <c r="F5" s="174"/>
+      <c r="G5" s="174"/>
+      <c r="H5" s="175"/>
+      <c r="J5" s="179" t="s">
         <v>3166</v>
       </c>
-      <c r="K5" s="191"/>
-      <c r="L5" s="191"/>
-      <c r="M5" s="191"/>
-      <c r="N5" s="191"/>
-      <c r="O5" s="191"/>
-      <c r="P5" s="192"/>
+      <c r="K5" s="180"/>
+      <c r="L5" s="180"/>
+      <c r="M5" s="180"/>
+      <c r="N5" s="180"/>
+      <c r="O5" s="180"/>
+      <c r="P5" s="181"/>
     </row>
     <row r="6" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="187"/>
-      <c r="B6" s="188"/>
-      <c r="C6" s="188"/>
-      <c r="D6" s="188"/>
-      <c r="E6" s="188"/>
-      <c r="F6" s="188"/>
-      <c r="G6" s="188"/>
-      <c r="H6" s="189"/>
-      <c r="J6" s="193"/>
-      <c r="K6" s="194"/>
-      <c r="L6" s="194"/>
-      <c r="M6" s="194"/>
-      <c r="N6" s="194"/>
-      <c r="O6" s="194"/>
-      <c r="P6" s="195"/>
+      <c r="A6" s="176"/>
+      <c r="B6" s="177"/>
+      <c r="C6" s="177"/>
+      <c r="D6" s="177"/>
+      <c r="E6" s="177"/>
+      <c r="F6" s="177"/>
+      <c r="G6" s="177"/>
+      <c r="H6" s="178"/>
+      <c r="J6" s="182"/>
+      <c r="K6" s="183"/>
+      <c r="L6" s="183"/>
+      <c r="M6" s="183"/>
+      <c r="N6" s="183"/>
+      <c r="O6" s="183"/>
+      <c r="P6" s="184"/>
       <c r="R6" s="123" t="s">
         <v>3167</v>
       </c>
@@ -41231,37 +41231,37 @@
       <c r="BI6" s="128" t="s">
         <v>3178</v>
       </c>
-      <c r="BK6" s="176" t="s">
+      <c r="BK6" s="165" t="s">
         <v>3179</v>
       </c>
-      <c r="BL6" s="177"/>
-      <c r="BM6" s="177"/>
-      <c r="BN6" s="177"/>
-      <c r="BO6" s="178"/>
-      <c r="BR6" s="176" t="str" cm="1">
+      <c r="BL6" s="166"/>
+      <c r="BM6" s="166"/>
+      <c r="BN6" s="166"/>
+      <c r="BO6" s="167"/>
+      <c r="BR6" s="165" t="str" cm="1">
         <f t="array" ref="BR6">INDEX(T,4,lang)</f>
         <v>Round of 16</v>
       </c>
-      <c r="BS6" s="177"/>
-      <c r="BT6" s="177"/>
-      <c r="BU6" s="177"/>
-      <c r="BV6" s="178"/>
-      <c r="BY6" s="176" t="str" cm="1">
+      <c r="BS6" s="166"/>
+      <c r="BT6" s="166"/>
+      <c r="BU6" s="166"/>
+      <c r="BV6" s="167"/>
+      <c r="BY6" s="165" t="str" cm="1">
         <f t="array" ref="BY6">INDEX(T,5,lang)</f>
         <v>Quarterfinals</v>
       </c>
-      <c r="BZ6" s="177"/>
-      <c r="CA6" s="177"/>
-      <c r="CB6" s="177"/>
-      <c r="CC6" s="178"/>
-      <c r="CF6" s="176" t="str" cm="1">
+      <c r="BZ6" s="166"/>
+      <c r="CA6" s="166"/>
+      <c r="CB6" s="166"/>
+      <c r="CC6" s="167"/>
+      <c r="CF6" s="165" t="str" cm="1">
         <f t="array" ref="CF6">INDEX(T,6,lang)</f>
         <v>Semi-Finals</v>
       </c>
-      <c r="CG6" s="177"/>
-      <c r="CH6" s="177"/>
-      <c r="CI6" s="177"/>
-      <c r="CJ6" s="178"/>
+      <c r="CG6" s="166"/>
+      <c r="CH6" s="166"/>
+      <c r="CI6" s="166"/>
+      <c r="CJ6" s="167"/>
     </row>
     <row r="7" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="11">
@@ -41338,26 +41338,26 @@
         <v>1</v>
       </c>
       <c r="AY7" s="126"/>
-      <c r="BK7" s="179"/>
-      <c r="BL7" s="180"/>
-      <c r="BM7" s="180"/>
-      <c r="BN7" s="180"/>
-      <c r="BO7" s="181"/>
-      <c r="BR7" s="179"/>
-      <c r="BS7" s="180"/>
-      <c r="BT7" s="180"/>
-      <c r="BU7" s="180"/>
-      <c r="BV7" s="181"/>
-      <c r="BY7" s="179"/>
-      <c r="BZ7" s="180"/>
-      <c r="CA7" s="180"/>
-      <c r="CB7" s="180"/>
-      <c r="CC7" s="181"/>
-      <c r="CF7" s="179"/>
-      <c r="CG7" s="180"/>
-      <c r="CH7" s="180"/>
-      <c r="CI7" s="180"/>
-      <c r="CJ7" s="181"/>
+      <c r="BK7" s="168"/>
+      <c r="BL7" s="169"/>
+      <c r="BM7" s="169"/>
+      <c r="BN7" s="169"/>
+      <c r="BO7" s="170"/>
+      <c r="BR7" s="168"/>
+      <c r="BS7" s="169"/>
+      <c r="BT7" s="169"/>
+      <c r="BU7" s="169"/>
+      <c r="BV7" s="170"/>
+      <c r="BY7" s="168"/>
+      <c r="BZ7" s="169"/>
+      <c r="CA7" s="169"/>
+      <c r="CB7" s="169"/>
+      <c r="CC7" s="170"/>
+      <c r="CF7" s="168"/>
+      <c r="CG7" s="169"/>
+      <c r="CH7" s="169"/>
+      <c r="CI7" s="169"/>
+      <c r="CJ7" s="170"/>
     </row>
     <row r="8" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A8" s="16">
@@ -42093,7 +42093,7 @@
         <f>BH10/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK10" s="173">
+      <c r="BK10" s="163">
         <v>74</v>
       </c>
       <c r="BL10" s="24" t="str">
@@ -42358,7 +42358,7 @@
         <f>BH11/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK11" s="174"/>
+      <c r="BK11" s="164"/>
       <c r="BL11" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!G3,AK80:AS91,9,FALSE),"3rd Group A/B/C/D/F")</f>
         <v>Paraguay</v>
@@ -42598,19 +42598,21 @@
       <c r="BO12" s="21"/>
       <c r="BP12" s="114"/>
       <c r="BQ12" s="112"/>
-      <c r="BR12" s="173">
+      <c r="BR12" s="163">
         <v>89</v>
       </c>
       <c r="BS12" s="24" t="str">
         <f>IF(BP10&gt;BP11,BL10,IF(BP10&lt;BP11,BL11,""))</f>
         <v>Paraguay</v>
       </c>
-      <c r="BT12" s="61"/>
+      <c r="BT12" s="61">
+        <v>0</v>
+      </c>
       <c r="BU12" s="63"/>
       <c r="BV12" s="25"/>
-      <c r="BW12" s="112" t="str">
+      <c r="BW12" s="112">
         <f>IF(OR(BT12="",BT13="",AND(BU12="",BU13&lt;&gt;""),AND(BU13="",BU12&lt;&gt;""),AND(BV12="",BV13&lt;&gt;""),AND(BV13="",BV12&lt;&gt;"")),"",BT12*1000+BU12*10+BV12)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BX12" s="112"/>
       <c r="BY12" s="21"/>
@@ -42719,17 +42721,19 @@
         <v>46203.875</v>
       </c>
       <c r="BQ13" s="115"/>
-      <c r="BR13" s="174"/>
+      <c r="BR13" s="164"/>
       <c r="BS13" s="26" t="str">
         <f>IF(BP14&gt;BP15,BL14,IF(BP14&lt;BP15,BL15,""))</f>
         <v>France</v>
       </c>
-      <c r="BT13" s="62"/>
+      <c r="BT13" s="62">
+        <v>1</v>
+      </c>
       <c r="BU13" s="64"/>
       <c r="BV13" s="27"/>
-      <c r="BW13" s="113" t="str">
+      <c r="BW13" s="113">
         <f>IF(BW12="","",BT13*1000+BU13*10+BV13)</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="BX13" s="112"/>
       <c r="BY13" s="21"/>
@@ -42977,7 +42981,7 @@
         <f>BH14/BH18</f>
         <v>0.98058252427184467</v>
       </c>
-      <c r="BK14" s="173">
+      <c r="BK14" s="163">
         <v>77</v>
       </c>
       <c r="BL14" s="24" t="str">
@@ -43246,7 +43250,7 @@
         <f>BH15/BH18</f>
         <v>0.98058252427184467</v>
       </c>
-      <c r="BK15" s="174"/>
+      <c r="BK15" s="164"/>
       <c r="BL15" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!I3,AK80:AS91,9,FALSE),"3rd Group C/D/F/G/H")</f>
         <v>Sweden</v>
@@ -43522,12 +43526,12 @@
       <c r="BV16" s="21"/>
       <c r="BW16" s="114"/>
       <c r="BX16" s="112"/>
-      <c r="BY16" s="173">
+      <c r="BY16" s="163">
         <v>97</v>
       </c>
       <c r="BZ16" s="24" t="str">
         <f>IF(BW12&gt;BW13,BS12,IF(BW12&lt;BW13,BS13,""))</f>
-        <v/>
+        <v>France</v>
       </c>
       <c r="CA16" s="61"/>
       <c r="CB16" s="63"/>
@@ -43784,10 +43788,10 @@
       <c r="BV17" s="21"/>
       <c r="BW17" s="114"/>
       <c r="BX17" s="115"/>
-      <c r="BY17" s="174"/>
+      <c r="BY17" s="164"/>
       <c r="BZ17" s="26" t="str">
         <f>IF(BW20&gt;BW21,BS20,IF(BW20&lt;BW21,BS21,""))</f>
-        <v/>
+        <v>Morocco</v>
       </c>
       <c r="CA17" s="62"/>
       <c r="CB17" s="64"/>
@@ -43988,7 +43992,7 @@
         <f>MAX(BH14:BH17)+1</f>
         <v>51.5</v>
       </c>
-      <c r="BK18" s="173">
+      <c r="BK18" s="163">
         <v>73</v>
       </c>
       <c r="BL18" s="24" t="str">
@@ -44098,7 +44102,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BK19" s="174"/>
+      <c r="BK19" s="164"/>
       <c r="BL19" s="26" t="str">
         <f>AS15</f>
         <v>Canada</v>
@@ -44378,19 +44382,21 @@
       <c r="BO20" s="21"/>
       <c r="BP20" s="114"/>
       <c r="BQ20" s="112"/>
-      <c r="BR20" s="173">
+      <c r="BR20" s="163">
         <v>90</v>
       </c>
       <c r="BS20" s="24" t="str">
         <f>IF(BP18&gt;BP19,BL18,IF(BP18&lt;BP19,BL19,""))</f>
         <v>Canada</v>
       </c>
-      <c r="BT20" s="61"/>
+      <c r="BT20" s="61">
+        <v>0</v>
+      </c>
       <c r="BU20" s="63"/>
       <c r="BV20" s="25"/>
-      <c r="BW20" s="116" t="str">
+      <c r="BW20" s="116">
         <f>IF(OR(BT20="",BT21="",AND(BU20="",BU21&lt;&gt;""),AND(BU21="",BU20&lt;&gt;""),AND(BV20="",BV21&lt;&gt;""),AND(BV21="",BV20&lt;&gt;"")),"",BT20*1000+BU20*10+BV20)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BX20" s="112"/>
       <c r="BY20" s="21"/>
@@ -44651,17 +44657,19 @@
         <v>46203.041666666672</v>
       </c>
       <c r="BQ21" s="115"/>
-      <c r="BR21" s="174"/>
+      <c r="BR21" s="164"/>
       <c r="BS21" s="26" t="str">
         <f>IF(BP22&gt;BP23,BL22,IF(BP22&lt;BP23,BL23,""))</f>
         <v>Morocco</v>
       </c>
-      <c r="BT21" s="62"/>
+      <c r="BT21" s="62">
+        <v>3</v>
+      </c>
       <c r="BU21" s="64"/>
       <c r="BV21" s="27"/>
-      <c r="BW21" s="112" t="str">
+      <c r="BW21" s="112">
         <f>IF(BW20="","",BT21*1000+BU21*10+BV21)</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="BX21" s="112"/>
       <c r="BY21" s="21"/>
@@ -44905,7 +44913,7 @@
         <f>BH22/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK22" s="173">
+      <c r="BK22" s="163">
         <v>75</v>
       </c>
       <c r="BL22" s="24" t="str">
@@ -45171,7 +45179,7 @@
         <f>BH23/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK23" s="174"/>
+      <c r="BK23" s="164"/>
       <c r="BL23" s="26" t="str">
         <f>AS21</f>
         <v>Morocco</v>
@@ -45200,7 +45208,7 @@
       <c r="CC23" s="21"/>
       <c r="CD23" s="114"/>
       <c r="CE23" s="112"/>
-      <c r="CF23" s="173">
+      <c r="CF23" s="163">
         <v>101</v>
       </c>
       <c r="CG23" s="24" t="str">
@@ -45421,7 +45429,7 @@
       <c r="CC24" s="21"/>
       <c r="CD24" s="114"/>
       <c r="CE24" s="115"/>
-      <c r="CF24" s="174"/>
+      <c r="CF24" s="164"/>
       <c r="CG24" s="26" t="str">
         <f>IF(CD32&gt;CD33,BZ32,IF(CD32&lt;CD33,BZ33,""))</f>
         <v/>
@@ -45774,7 +45782,7 @@
         <f>BH26/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK26" s="173">
+      <c r="BK26" s="163">
         <v>83</v>
       </c>
       <c r="BL26" s="24" t="str">
@@ -46044,7 +46052,7 @@
         <f>BH27/BH30</f>
         <v>0.98039215686274506</v>
       </c>
-      <c r="BK27" s="174"/>
+      <c r="BK27" s="164"/>
       <c r="BL27" s="26" t="str">
         <f>AS75</f>
         <v>Croatia</v>
@@ -46321,19 +46329,21 @@
       <c r="BO28" s="21"/>
       <c r="BP28" s="114"/>
       <c r="BQ28" s="112"/>
-      <c r="BR28" s="173">
+      <c r="BR28" s="163">
         <v>93</v>
       </c>
       <c r="BS28" s="24" t="str">
         <f>IF(BP26&gt;BP27,BL26,IF(BP26&lt;BP27,BL27,""))</f>
         <v>Portugal</v>
       </c>
-      <c r="BT28" s="61"/>
+      <c r="BT28" s="61">
+        <v>0</v>
+      </c>
       <c r="BU28" s="63"/>
       <c r="BV28" s="25"/>
-      <c r="BW28" s="112" t="str">
+      <c r="BW28" s="112">
         <f>IF(OR(BT28="",BT29="",AND(BU28="",BU29&lt;&gt;""),AND(BU29="",BU28&lt;&gt;""),AND(BV28="",BV29&lt;&gt;""),AND(BV29="",BV28&lt;&gt;"")),"",BT28*1000+BU28*10+BV28)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BX28" s="112"/>
       <c r="BY28" s="21"/>
@@ -46586,17 +46596,19 @@
         <v>46205.791666666672</v>
       </c>
       <c r="BQ29" s="115"/>
-      <c r="BR29" s="174"/>
+      <c r="BR29" s="164"/>
       <c r="BS29" s="26" t="str">
         <f>IF(BP30&gt;BP31,BL30,IF(BP30&lt;BP31,BL31,""))</f>
         <v>Spain</v>
       </c>
-      <c r="BT29" s="62"/>
+      <c r="BT29" s="62">
+        <v>1</v>
+      </c>
       <c r="BU29" s="64"/>
       <c r="BV29" s="27"/>
-      <c r="BW29" s="113" t="str">
+      <c r="BW29" s="113">
         <f>IF(BW28="","",BT29*1000+BU29*10+BV29)</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="BX29" s="112"/>
       <c r="BY29" s="21"/>
@@ -46800,7 +46812,7 @@
         <f>MAX(BH26:BH29)+1</f>
         <v>51</v>
       </c>
-      <c r="BK30" s="173">
+      <c r="BK30" s="163">
         <v>84</v>
       </c>
       <c r="BL30" s="24" t="str">
@@ -46913,7 +46925,7 @@
         <f>IF(OR(F31="",G31=""),"",IF(F31&gt;G31,1,IF(F31&lt;G31,-1,0)))</f>
         <v>0</v>
       </c>
-      <c r="BK31" s="174"/>
+      <c r="BK31" s="164"/>
       <c r="BL31" s="26" t="str">
         <f>AS63</f>
         <v>Austria</v>
@@ -47191,12 +47203,12 @@
       <c r="BV32" s="21"/>
       <c r="BW32" s="114"/>
       <c r="BX32" s="112"/>
-      <c r="BY32" s="173">
+      <c r="BY32" s="163">
         <v>98</v>
       </c>
       <c r="BZ32" s="24" t="str">
         <f>IF(BW28&gt;BW29,BS28,IF(BW28&lt;BW29,BS29,""))</f>
-        <v/>
+        <v>Spain</v>
       </c>
       <c r="CA32" s="61"/>
       <c r="CB32" s="63"/>
@@ -47455,7 +47467,7 @@
       <c r="BV33" s="21"/>
       <c r="BW33" s="114"/>
       <c r="BX33" s="115"/>
-      <c r="BY33" s="174"/>
+      <c r="BY33" s="164"/>
       <c r="BZ33" s="26" t="str">
         <f>IF(BW36&gt;BW37,BS36,IF(BW36&lt;BW37,BS37,""))</f>
         <v/>
@@ -47470,14 +47482,14 @@
       <c r="CE33" s="112"/>
       <c r="CK33" s="114"/>
       <c r="CL33" s="112"/>
-      <c r="CM33" s="176" t="str" cm="1">
+      <c r="CM33" s="165" t="str" cm="1">
         <f t="array" ref="CM33">INDEX(T,8,lang)</f>
         <v>Final</v>
       </c>
-      <c r="CN33" s="177"/>
-      <c r="CO33" s="177"/>
-      <c r="CP33" s="177"/>
-      <c r="CQ33" s="178"/>
+      <c r="CN33" s="166"/>
+      <c r="CO33" s="166"/>
+      <c r="CP33" s="166"/>
+      <c r="CQ33" s="167"/>
     </row>
     <row r="34" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A34" s="16">
@@ -47701,7 +47713,7 @@
         <f>BH34/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK34" s="173">
+      <c r="BK34" s="163">
         <v>81</v>
       </c>
       <c r="BL34" s="24" t="str">
@@ -47734,11 +47746,11 @@
       <c r="CE34" s="112"/>
       <c r="CK34" s="114"/>
       <c r="CL34" s="112"/>
-      <c r="CM34" s="179"/>
-      <c r="CN34" s="180"/>
-      <c r="CO34" s="180"/>
-      <c r="CP34" s="180"/>
-      <c r="CQ34" s="181"/>
+      <c r="CM34" s="168"/>
+      <c r="CN34" s="169"/>
+      <c r="CO34" s="169"/>
+      <c r="CP34" s="169"/>
+      <c r="CQ34" s="170"/>
     </row>
     <row r="35" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A35" s="16">
@@ -47962,7 +47974,7 @@
         <f>BH35/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK35" s="174"/>
+      <c r="BK35" s="164"/>
       <c r="BL35" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!F3,AK80:AS91,9,FALSE),"3rd Group B/E/F/I/J")</f>
         <v>Bosnia and Herzegovina</v>
@@ -48193,7 +48205,7 @@
       <c r="BO36" s="21"/>
       <c r="BP36" s="114"/>
       <c r="BQ36" s="112"/>
-      <c r="BR36" s="173">
+      <c r="BR36" s="163">
         <v>94</v>
       </c>
       <c r="BS36" s="24" t="str">
@@ -48317,7 +48329,7 @@
         <v>46204.833333333336</v>
       </c>
       <c r="BQ37" s="115"/>
-      <c r="BR37" s="174"/>
+      <c r="BR37" s="164"/>
       <c r="BS37" s="26" t="str">
         <f>IF(BP38&gt;BP39,BL38,IF(BP38&lt;BP39,BL39,""))</f>
         <v>Belgium</v>
@@ -48344,7 +48356,7 @@
       <c r="CJ37" s="21"/>
       <c r="CK37" s="114"/>
       <c r="CL37" s="112"/>
-      <c r="CM37" s="173">
+      <c r="CM37" s="163">
         <v>104</v>
       </c>
       <c r="CN37" s="24" t="str">
@@ -48585,7 +48597,7 @@
         <f>BH38/BH42</f>
         <v>0</v>
       </c>
-      <c r="BK38" s="173">
+      <c r="BK38" s="163">
         <v>82</v>
       </c>
       <c r="BL38" s="24" t="str">
@@ -48617,7 +48629,7 @@
       <c r="CI38" s="21"/>
       <c r="CJ38" s="21"/>
       <c r="CL38" s="115"/>
-      <c r="CM38" s="174"/>
+      <c r="CM38" s="164"/>
       <c r="CN38" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG55,IF(CK55&lt;CK56,CG56,""))</f>
         <v/>
@@ -48856,7 +48868,7 @@
         <f>BH39/BH42</f>
         <v>0</v>
       </c>
-      <c r="BK39" s="174"/>
+      <c r="BK39" s="164"/>
       <c r="BL39" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!H3,AK80:AS91,9,FALSE),"3rd Group A/E/H/I/J")</f>
         <v>Senegal</v>
@@ -49546,7 +49558,7 @@
         <f>MAX(BH38:BH41)+1</f>
         <v>1</v>
       </c>
-      <c r="BK42" s="173">
+      <c r="BK42" s="163">
         <v>76</v>
       </c>
       <c r="BL42" s="24" t="str">
@@ -49645,7 +49657,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BK43" s="174"/>
+      <c r="BK43" s="164"/>
       <c r="BL43" s="26" t="str">
         <f>AS39</f>
         <v>Japan</v>
@@ -49907,29 +49919,31 @@
       <c r="BO44" s="21"/>
       <c r="BP44" s="114"/>
       <c r="BQ44" s="112"/>
-      <c r="BR44" s="173">
+      <c r="BR44" s="163">
         <v>91</v>
       </c>
       <c r="BS44" s="24" t="str">
         <f>IF(BP42&gt;BP43,BL42,IF(BP42&lt;BP43,BL43,""))</f>
         <v>Brazil</v>
       </c>
-      <c r="BT44" s="61"/>
+      <c r="BT44" s="61">
+        <v>1</v>
+      </c>
       <c r="BU44" s="63"/>
       <c r="BV44" s="25"/>
-      <c r="BW44" s="112" t="str">
+      <c r="BW44" s="112">
         <f>IF(OR(BT44="",BT45="",AND(BU44="",BU45&lt;&gt;""),AND(BU45="",BU44&lt;&gt;""),AND(BV44="",BV45&lt;&gt;""),AND(BV45="",BV44&lt;&gt;"")),"",BT44*1000+BU44*10+BV44)</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="CK44" s="114"/>
-      <c r="CM44" s="176" t="str" cm="1">
+      <c r="CM44" s="165" t="str" cm="1">
         <f t="array" ref="CM44">INDEX(T,7,lang)</f>
         <v>Third-Place Play-Off</v>
       </c>
-      <c r="CN44" s="177"/>
-      <c r="CO44" s="177"/>
-      <c r="CP44" s="177"/>
-      <c r="CQ44" s="178"/>
+      <c r="CN44" s="166"/>
+      <c r="CO44" s="166"/>
+      <c r="CP44" s="166"/>
+      <c r="CQ44" s="167"/>
     </row>
     <row r="45" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="16">
@@ -50170,24 +50184,26 @@
         <v>46203.708333333336</v>
       </c>
       <c r="BQ45" s="115"/>
-      <c r="BR45" s="174"/>
+      <c r="BR45" s="164"/>
       <c r="BS45" s="26" t="str">
         <f>IF(BP46&gt;BP47,BL46,IF(BP46&lt;BP47,BL47,""))</f>
         <v>Norway</v>
       </c>
-      <c r="BT45" s="62"/>
+      <c r="BT45" s="62">
+        <v>2</v>
+      </c>
       <c r="BU45" s="64"/>
       <c r="BV45" s="27"/>
-      <c r="BW45" s="113" t="str">
+      <c r="BW45" s="113">
         <f>IF(BW44="","",BT45*1000+BU45*10+BV45)</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="CK45" s="114"/>
-      <c r="CM45" s="179"/>
-      <c r="CN45" s="180"/>
-      <c r="CO45" s="180"/>
-      <c r="CP45" s="180"/>
-      <c r="CQ45" s="181"/>
+      <c r="CM45" s="168"/>
+      <c r="CN45" s="169"/>
+      <c r="CO45" s="169"/>
+      <c r="CP45" s="169"/>
+      <c r="CQ45" s="170"/>
     </row>
     <row r="46" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A46" s="16">
@@ -50411,7 +50427,7 @@
         <f>BH46/BH48</f>
         <v>0</v>
       </c>
-      <c r="BK46" s="173">
+      <c r="BK46" s="163">
         <v>78</v>
       </c>
       <c r="BL46" s="24" t="str">
@@ -50659,7 +50675,7 @@
         <f>BH47/BH48</f>
         <v>0</v>
       </c>
-      <c r="BK47" s="174"/>
+      <c r="BK47" s="164"/>
       <c r="BL47" s="26" t="str">
         <f>AS57</f>
         <v>Norway</v>
@@ -50908,12 +50924,12 @@
       <c r="BV48" s="21"/>
       <c r="BW48" s="114"/>
       <c r="BX48" s="112"/>
-      <c r="BY48" s="173">
+      <c r="BY48" s="163">
         <v>99</v>
       </c>
       <c r="BZ48" s="24" t="str">
         <f>IF(BW44&gt;BW45,BS44,IF(BW44&lt;BW45,BS45,""))</f>
-        <v/>
+        <v>Norway</v>
       </c>
       <c r="CA48" s="61"/>
       <c r="CB48" s="63"/>
@@ -50924,7 +50940,7 @@
       </c>
       <c r="CK48" s="114"/>
       <c r="CL48" s="112"/>
-      <c r="CM48" s="173">
+      <c r="CM48" s="163">
         <v>103</v>
       </c>
       <c r="CN48" s="24" t="str">
@@ -51033,10 +51049,10 @@
       <c r="BV49" s="21"/>
       <c r="BW49" s="114"/>
       <c r="BX49" s="115"/>
-      <c r="BY49" s="174"/>
+      <c r="BY49" s="164"/>
       <c r="BZ49" s="26" t="str">
         <f>IF(BW52&gt;BW53,BS52,IF(BW52&lt;BW53,BS53,""))</f>
-        <v/>
+        <v>England</v>
       </c>
       <c r="CA49" s="62"/>
       <c r="CB49" s="64"/>
@@ -51047,7 +51063,7 @@
       </c>
       <c r="CK49" s="114"/>
       <c r="CL49" s="115"/>
-      <c r="CM49" s="174"/>
+      <c r="CM49" s="164"/>
       <c r="CN49" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG56,IF(CK55&lt;CK56,CG55,""))</f>
         <v/>
@@ -51286,7 +51302,7 @@
         <f>BH50/BH54</f>
         <v>0</v>
       </c>
-      <c r="BK50" s="173">
+      <c r="BK50" s="163">
         <v>79</v>
       </c>
       <c r="BL50" s="24" t="str">
@@ -51545,7 +51561,7 @@
         <f>BH51/BH54</f>
         <v>0</v>
       </c>
-      <c r="BK51" s="174"/>
+      <c r="BK51" s="164"/>
       <c r="BL51" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!D3,AK80:AS91,9,FALSE),"3rd Group C/E/F/H/I")</f>
         <v>Ecuador</v>
@@ -51811,19 +51827,21 @@
       <c r="BO52" s="21"/>
       <c r="BP52" s="114"/>
       <c r="BQ52" s="112"/>
-      <c r="BR52" s="173">
+      <c r="BR52" s="163">
         <v>92</v>
       </c>
       <c r="BS52" s="24" t="str">
         <f>IF(BP50&gt;BP51,BL50,IF(BP50&lt;BP51,BL51,""))</f>
         <v>Mexico</v>
       </c>
-      <c r="BT52" s="61"/>
+      <c r="BT52" s="61">
+        <v>2</v>
+      </c>
       <c r="BU52" s="63"/>
       <c r="BV52" s="25"/>
-      <c r="BW52" s="116" t="str">
+      <c r="BW52" s="116">
         <f>IF(OR(BT52="",BT53="",AND(BU52="",BU53&lt;&gt;""),AND(BU53="",BU52&lt;&gt;""),AND(BV52="",BV53&lt;&gt;""),AND(BV53="",BV52&lt;&gt;"")),"",BT52*1000+BU52*10+BV52)</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="BX52" s="112"/>
       <c r="BY52" s="21"/>
@@ -52070,17 +52088,19 @@
         <v>46204.666666666672</v>
       </c>
       <c r="BQ53" s="115"/>
-      <c r="BR53" s="174"/>
+      <c r="BR53" s="164"/>
       <c r="BS53" s="26" t="str">
         <f>IF(BP54&gt;BP55,BL54,IF(BP54&lt;BP55,BL55,""))</f>
         <v>England</v>
       </c>
-      <c r="BT53" s="62"/>
+      <c r="BT53" s="62">
+        <v>3</v>
+      </c>
       <c r="BU53" s="64"/>
       <c r="BV53" s="27"/>
-      <c r="BW53" s="112" t="str">
+      <c r="BW53" s="112">
         <f>IF(BW52="","",BT53*1000+BU53*10+BV53)</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="BX53" s="112"/>
       <c r="BY53" s="21"/>
@@ -52278,7 +52298,7 @@
         <f>MAX(BH50:BH53)+1</f>
         <v>51.5</v>
       </c>
-      <c r="BK54" s="173">
+      <c r="BK54" s="163">
         <v>80</v>
       </c>
       <c r="BL54" s="24" t="str">
@@ -52405,7 +52425,7 @@
         <f t="shared" si="23"/>
         <v>-1</v>
       </c>
-      <c r="BK55" s="174"/>
+      <c r="BK55" s="164"/>
       <c r="BL55" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!K3,AK80:AS91,9,FALSE),"3rd Group E/H/I/J/K")</f>
         <v>DR Congo</v>
@@ -52434,7 +52454,7 @@
       <c r="CC55" s="21"/>
       <c r="CD55" s="114"/>
       <c r="CE55" s="112"/>
-      <c r="CF55" s="173">
+      <c r="CF55" s="163">
         <v>102</v>
       </c>
       <c r="CG55" s="24" t="str">
@@ -52697,7 +52717,7 @@
       <c r="CC56" s="21"/>
       <c r="CD56" s="114"/>
       <c r="CE56" s="115"/>
-      <c r="CF56" s="174"/>
+      <c r="CF56" s="164"/>
       <c r="CG56" s="26" t="str">
         <f>IF(CD64&gt;CD65,BZ64,IF(CD64&lt;CD65,BZ65,""))</f>
         <v/>
@@ -53188,7 +53208,7 @@
         <f>BH58/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK58" s="173">
+      <c r="BK58" s="163">
         <v>86</v>
       </c>
       <c r="BL58" s="24" t="str">
@@ -53442,7 +53462,7 @@
         <f>BH59/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK59" s="174"/>
+      <c r="BK59" s="164"/>
       <c r="BL59" s="26" t="str">
         <f>AS51</f>
         <v>Cape Verde</v>
@@ -53671,7 +53691,7 @@
       <c r="BO60" s="21"/>
       <c r="BP60" s="114"/>
       <c r="BQ60" s="112"/>
-      <c r="BR60" s="173">
+      <c r="BR60" s="163">
         <v>95</v>
       </c>
       <c r="BS60" s="24" t="str">
@@ -53788,7 +53808,7 @@
         <v>46206.75</v>
       </c>
       <c r="BQ61" s="115"/>
-      <c r="BR61" s="174"/>
+      <c r="BR61" s="164"/>
       <c r="BS61" s="26" t="str">
         <f>IF(BP62&gt;BP63,BL62,IF(BP62&lt;BP63,BL63,""))</f>
         <v>Egypt</v>
@@ -54035,7 +54055,7 @@
         <f>BH62/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK62" s="173">
+      <c r="BK62" s="163">
         <v>88</v>
       </c>
       <c r="BL62" s="24" t="str">
@@ -54293,7 +54313,7 @@
         <f>BH63/BH66</f>
         <v>0.98067632850241548</v>
       </c>
-      <c r="BK63" s="174"/>
+      <c r="BK63" s="164"/>
       <c r="BL63" s="26" t="str">
         <f>AS45</f>
         <v>Egypt</v>
@@ -54565,7 +54585,7 @@
       <c r="BV64" s="21"/>
       <c r="BW64" s="114"/>
       <c r="BX64" s="112"/>
-      <c r="BY64" s="173">
+      <c r="BY64" s="163">
         <v>100</v>
       </c>
       <c r="BZ64" s="24" t="str">
@@ -54823,7 +54843,7 @@
       <c r="BV65" s="21"/>
       <c r="BW65" s="114"/>
       <c r="BX65" s="115"/>
-      <c r="BY65" s="174"/>
+      <c r="BY65" s="164"/>
       <c r="BZ65" s="26" t="str">
         <f>IF(BW68&gt;BW69,BS68,IF(BW68&lt;BW69,BS69,""))</f>
         <v/>
@@ -55023,7 +55043,7 @@
         <f>MAX(BH62:BH65)+1</f>
         <v>51.75</v>
       </c>
-      <c r="BK66" s="173">
+      <c r="BK66" s="163">
         <v>85</v>
       </c>
       <c r="BL66" s="24" t="str">
@@ -55129,7 +55149,7 @@
         <f t="shared" si="23"/>
         <v>-1</v>
       </c>
-      <c r="BK67" s="174"/>
+      <c r="BK67" s="164"/>
       <c r="BL67" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!E3,AK80:AS91,9,FALSE),"3rd Group E/F/G/I/J")</f>
         <v>Algeria</v>
@@ -55391,7 +55411,7 @@
       <c r="BO68" s="21"/>
       <c r="BP68" s="114"/>
       <c r="BQ68" s="112"/>
-      <c r="BR68" s="173">
+      <c r="BR68" s="163">
         <v>96</v>
       </c>
       <c r="BS68" s="24" t="str">
@@ -55405,25 +55425,25 @@
         <f>IF(OR(BT68="",BT69="",AND(BU68="",BU69&lt;&gt;""),AND(BU69="",BU68&lt;&gt;""),AND(BV68="",BV69&lt;&gt;""),AND(BV69="",BV68&lt;&gt;"")),"",BT68*1000+BU68*10+BV68)</f>
         <v/>
       </c>
-      <c r="CE68" s="175" t="str">
+      <c r="CE68" s="195" t="str">
         <f>INDEX(T,144,lang)</f>
         <v>World Champion 2026</v>
       </c>
-      <c r="CF68" s="175"/>
-      <c r="CG68" s="175"/>
-      <c r="CH68" s="175"/>
-      <c r="CI68" s="175"/>
-      <c r="CJ68" s="175"/>
-      <c r="CK68" s="163" t="str">
+      <c r="CF68" s="195"/>
+      <c r="CG68" s="195"/>
+      <c r="CH68" s="195"/>
+      <c r="CI68" s="195"/>
+      <c r="CJ68" s="195"/>
+      <c r="CK68" s="185" t="str">
         <f>IF(CR37&gt;CR38,CN37,IF(CR37&lt;CR38,CN38,""))</f>
         <v/>
       </c>
-      <c r="CL68" s="163"/>
-      <c r="CM68" s="163"/>
-      <c r="CN68" s="163"/>
-      <c r="CO68" s="163"/>
-      <c r="CP68" s="163"/>
-      <c r="CQ68" s="163"/>
+      <c r="CL68" s="185"/>
+      <c r="CM68" s="185"/>
+      <c r="CN68" s="185"/>
+      <c r="CO68" s="185"/>
+      <c r="CP68" s="185"/>
+      <c r="CQ68" s="185"/>
     </row>
     <row r="69" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A69" s="16">
@@ -55665,10 +55685,10 @@
         <v>46207.0625</v>
       </c>
       <c r="BQ69" s="115"/>
-      <c r="BR69" s="174"/>
+      <c r="BR69" s="164"/>
       <c r="BS69" s="26" t="str">
         <f>IF(BP70&gt;BP71,BL70,IF(BP70&lt;BP71,BL71,""))</f>
-        <v/>
+        <v>Colombia</v>
       </c>
       <c r="BT69" s="62"/>
       <c r="BU69" s="64"/>
@@ -55677,19 +55697,19 @@
         <f>IF(BW68="","",BT69*1000+BU69*10+BV69)</f>
         <v/>
       </c>
-      <c r="CE69" s="175"/>
-      <c r="CF69" s="175"/>
-      <c r="CG69" s="175"/>
-      <c r="CH69" s="175"/>
-      <c r="CI69" s="175"/>
-      <c r="CJ69" s="175"/>
-      <c r="CK69" s="163"/>
-      <c r="CL69" s="163"/>
-      <c r="CM69" s="163"/>
-      <c r="CN69" s="163"/>
-      <c r="CO69" s="163"/>
-      <c r="CP69" s="163"/>
-      <c r="CQ69" s="163"/>
+      <c r="CE69" s="195"/>
+      <c r="CF69" s="195"/>
+      <c r="CG69" s="195"/>
+      <c r="CH69" s="195"/>
+      <c r="CI69" s="195"/>
+      <c r="CJ69" s="195"/>
+      <c r="CK69" s="185"/>
+      <c r="CL69" s="185"/>
+      <c r="CM69" s="185"/>
+      <c r="CN69" s="185"/>
+      <c r="CO69" s="185"/>
+      <c r="CP69" s="185"/>
+      <c r="CQ69" s="185"/>
     </row>
     <row r="70" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A70" s="16">
@@ -55914,19 +55934,21 @@
         <f>BH70/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK70" s="173">
+      <c r="BK70" s="163">
         <v>87</v>
       </c>
       <c r="BL70" s="24" t="str">
         <f>AS68</f>
         <v>Colombia</v>
       </c>
-      <c r="BM70" s="61"/>
+      <c r="BM70" s="61">
+        <v>1</v>
+      </c>
       <c r="BN70" s="63"/>
       <c r="BO70" s="25"/>
-      <c r="BP70" s="116" t="str">
+      <c r="BP70" s="116">
         <f>IF(OR(BM70="",BM71="",AND(BN70="",BN71&lt;&gt;""),AND(BN71="",BN70&lt;&gt;""),AND(BO70="",BO71&lt;&gt;""),AND(BO71="",BO70&lt;&gt;"")),"",BM70*1000+BN70*10+BO70)</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="BQ70" s="112"/>
       <c r="BW70" s="112"/>
@@ -56154,17 +56176,19 @@
         <f>BH71/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK71" s="174"/>
+      <c r="BK71" s="164"/>
       <c r="BL71" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!J3,AK80:AS91,9,FALSE),"3rd Group D/E/I/J/L")</f>
         <v>Ghana</v>
       </c>
-      <c r="BM71" s="62"/>
+      <c r="BM71" s="62">
+        <v>0</v>
+      </c>
       <c r="BN71" s="64"/>
       <c r="BO71" s="27"/>
-      <c r="BP71" s="112" t="str">
+      <c r="BP71" s="112">
         <f>IF(BP70="","",BM71*1000+BN71*10+BO71)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BQ71" s="112"/>
     </row>
@@ -57858,13 +57882,13 @@
     <row r="83" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="73"/>
       <c r="B83" s="73"/>
-      <c r="C83" s="164" t="s">
+      <c r="C83" s="186" t="s">
         <v>3183</v>
       </c>
-      <c r="D83" s="165"/>
-      <c r="E83" s="165"/>
-      <c r="F83" s="165"/>
-      <c r="G83" s="166"/>
+      <c r="D83" s="187"/>
+      <c r="E83" s="187"/>
+      <c r="F83" s="187"/>
+      <c r="G83" s="188"/>
       <c r="H83" s="75"/>
       <c r="I83" s="69"/>
       <c r="J83" s="99" t="str">
@@ -57962,11 +57986,11 @@
     <row r="84" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="73"/>
       <c r="B84" s="73"/>
-      <c r="C84" s="167"/>
-      <c r="D84" s="168"/>
-      <c r="E84" s="168"/>
-      <c r="F84" s="168"/>
-      <c r="G84" s="169"/>
+      <c r="C84" s="189"/>
+      <c r="D84" s="190"/>
+      <c r="E84" s="190"/>
+      <c r="F84" s="190"/>
+      <c r="G84" s="191"/>
       <c r="H84" s="75"/>
       <c r="I84" s="69"/>
       <c r="J84" s="99" t="str">
@@ -58076,11 +58100,11 @@
     <row r="85" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="73"/>
       <c r="B85" s="73"/>
-      <c r="C85" s="167"/>
-      <c r="D85" s="168"/>
-      <c r="E85" s="168"/>
-      <c r="F85" s="168"/>
-      <c r="G85" s="169"/>
+      <c r="C85" s="189"/>
+      <c r="D85" s="190"/>
+      <c r="E85" s="190"/>
+      <c r="F85" s="190"/>
+      <c r="G85" s="191"/>
       <c r="H85" s="75"/>
       <c r="I85" s="69"/>
       <c r="J85" s="99" t="str">
@@ -58190,11 +58214,11 @@
     <row r="86" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="73"/>
       <c r="B86" s="73"/>
-      <c r="C86" s="167"/>
-      <c r="D86" s="168"/>
-      <c r="E86" s="168"/>
-      <c r="F86" s="168"/>
-      <c r="G86" s="169"/>
+      <c r="C86" s="189"/>
+      <c r="D86" s="190"/>
+      <c r="E86" s="190"/>
+      <c r="F86" s="190"/>
+      <c r="G86" s="191"/>
       <c r="H86" s="75"/>
       <c r="I86" s="69"/>
       <c r="J86" s="99" t="str">
@@ -58304,11 +58328,11 @@
     <row r="87" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="73"/>
       <c r="B87" s="73"/>
-      <c r="C87" s="167"/>
-      <c r="D87" s="168"/>
-      <c r="E87" s="168"/>
-      <c r="F87" s="168"/>
-      <c r="G87" s="169"/>
+      <c r="C87" s="189"/>
+      <c r="D87" s="190"/>
+      <c r="E87" s="190"/>
+      <c r="F87" s="190"/>
+      <c r="G87" s="191"/>
       <c r="H87" s="75"/>
       <c r="I87" s="69"/>
       <c r="J87" s="99" t="str">
@@ -58418,11 +58442,11 @@
     <row r="88" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="73"/>
       <c r="B88" s="73"/>
-      <c r="C88" s="170"/>
-      <c r="D88" s="171"/>
-      <c r="E88" s="171"/>
-      <c r="F88" s="171"/>
-      <c r="G88" s="172"/>
+      <c r="C88" s="192"/>
+      <c r="D88" s="193"/>
+      <c r="E88" s="193"/>
+      <c r="F88" s="193"/>
+      <c r="G88" s="194"/>
       <c r="H88" s="75"/>
       <c r="I88" s="69"/>
       <c r="J88" s="99" t="str">
@@ -58971,11 +58995,11 @@
       </c>
       <c r="S95" s="127" t="str">
         <f>IF(OR(BT12="",BT13=""),"",IF(BT12&gt;BT13,BS12,IF(BT12&lt;BT13,BS13,IF(OR(BU12="",BU13=""),"draw",IF(BU12&gt;BU13,BS12,IF(BU12&lt;BU13,BS13,IF(OR(BV12="",BV13=""),"draw",IF(BV12&gt;BV13,BS12,IF(BV12&lt;BV13,BS13,"draw")))))))))</f>
-        <v/>
-      </c>
-      <c r="T95" s="127" cm="1">
+        <v>France</v>
+      </c>
+      <c r="T95" s="127" t="str" cm="1">
         <f t="array" ref="T95">IF(OR(S95="",S95="draw"),INDEX(T,94,lang),S95)</f>
-        <v>0</v>
+        <v>France</v>
       </c>
     </row>
     <row r="96" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58985,11 +59009,11 @@
       </c>
       <c r="S96" s="127" t="str">
         <f>IF(OR(BT20="",BT21=""),"",IF(BT20&gt;BT21,BS20,IF(BT20&lt;BT21,BS21,IF(OR(BU20="",BU21=""),"draw",IF(BU20&gt;BU21,BS20,IF(BU20&lt;BU21,BS21,IF(OR(BV20="",BV21=""),"draw",IF(BV20&gt;BV21,BS20,IF(BV20&lt;BV21,BS21,"draw")))))))))</f>
-        <v/>
-      </c>
-      <c r="T96" s="127" cm="1">
+        <v>Morocco</v>
+      </c>
+      <c r="T96" s="127" t="str" cm="1">
         <f t="array" ref="T96">IF(OR(S96="",S96="draw"),INDEX(T,95,lang),S96)</f>
-        <v>0</v>
+        <v>Morocco</v>
       </c>
     </row>
     <row r="97" spans="18:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58999,11 +59023,11 @@
       </c>
       <c r="S97" s="127" t="str">
         <f>IF(OR(BT28="",BT29=""),"",IF(BT28&gt;BT29,BS28,IF(BT28&lt;BT29,BS29,IF(OR(BU28="",BU29=""),"draw",IF(BU28&gt;BU29,BS28,IF(BU28&lt;BU29,BS29,IF(OR(BV28="",BV29=""),"draw",IF(BV28&gt;BV29,BS28,IF(BV28&lt;BV29,BS29,"draw")))))))))</f>
-        <v/>
-      </c>
-      <c r="T97" s="127" cm="1">
+        <v>Spain</v>
+      </c>
+      <c r="T97" s="127" t="str" cm="1">
         <f t="array" ref="T97">IF(OR(S97="",S97="draw"),INDEX(T,96,lang),S97)</f>
-        <v>0</v>
+        <v>Spain</v>
       </c>
     </row>
     <row r="98" spans="18:29" x14ac:dyDescent="0.2">
@@ -59100,11 +59124,31 @@
   <sheetProtection algorithmName="SHA-512" hashValue="7nWuIQAsd0NKRlhwUK3tOeNHpTch5B5FULy2gxNNaIdJM5RfhFSMzPcx55y+pmM3d73guUy+p5Y+SvIjJZQRaA==" saltValue="Uw23KnM8csnTioq5H8upCA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <dataConsolidate/>
   <mergeCells count="45">
-    <mergeCell ref="BK14:BK15"/>
-    <mergeCell ref="BY16:BY17"/>
-    <mergeCell ref="BK26:BK27"/>
-    <mergeCell ref="BR28:BR29"/>
-    <mergeCell ref="BK22:BK23"/>
+    <mergeCell ref="CK68:CQ69"/>
+    <mergeCell ref="C83:G88"/>
+    <mergeCell ref="BK70:BK71"/>
+    <mergeCell ref="BY48:BY49"/>
+    <mergeCell ref="BY64:BY65"/>
+    <mergeCell ref="CF55:CF56"/>
+    <mergeCell ref="BK58:BK59"/>
+    <mergeCell ref="BR60:BR61"/>
+    <mergeCell ref="BK62:BK63"/>
+    <mergeCell ref="BK66:BK67"/>
+    <mergeCell ref="BR68:BR69"/>
+    <mergeCell ref="BK50:BK51"/>
+    <mergeCell ref="BR52:BR53"/>
+    <mergeCell ref="BK54:BK55"/>
+    <mergeCell ref="CE68:CJ69"/>
+    <mergeCell ref="CF6:CJ7"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="A5:H6"/>
+    <mergeCell ref="J5:P6"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="BR12:BR13"/>
+    <mergeCell ref="BK6:BO7"/>
+    <mergeCell ref="BR6:BV7"/>
+    <mergeCell ref="BY6:CC7"/>
     <mergeCell ref="CF23:CF24"/>
     <mergeCell ref="BK18:BK19"/>
     <mergeCell ref="BR20:BR21"/>
@@ -59120,31 +59164,11 @@
     <mergeCell ref="BK42:BK43"/>
     <mergeCell ref="CM33:CQ34"/>
     <mergeCell ref="CM37:CM38"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="BR12:BR13"/>
-    <mergeCell ref="BK6:BO7"/>
-    <mergeCell ref="BR6:BV7"/>
-    <mergeCell ref="BY6:CC7"/>
-    <mergeCell ref="CF6:CJ7"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="A5:H6"/>
-    <mergeCell ref="J5:P6"/>
-    <mergeCell ref="CK68:CQ69"/>
-    <mergeCell ref="C83:G88"/>
-    <mergeCell ref="BK70:BK71"/>
-    <mergeCell ref="BY48:BY49"/>
-    <mergeCell ref="BY64:BY65"/>
-    <mergeCell ref="CF55:CF56"/>
-    <mergeCell ref="BK58:BK59"/>
-    <mergeCell ref="BR60:BR61"/>
-    <mergeCell ref="BK62:BK63"/>
-    <mergeCell ref="BK66:BK67"/>
-    <mergeCell ref="BR68:BR69"/>
-    <mergeCell ref="BK50:BK51"/>
-    <mergeCell ref="BR52:BR53"/>
-    <mergeCell ref="BK54:BK55"/>
-    <mergeCell ref="CE68:CJ69"/>
+    <mergeCell ref="BK14:BK15"/>
+    <mergeCell ref="BY16:BY17"/>
+    <mergeCell ref="BK26:BK27"/>
+    <mergeCell ref="BR28:BR29"/>
+    <mergeCell ref="BK22:BK23"/>
   </mergeCells>
   <conditionalFormatting sqref="A7:E78">
     <cfRule type="expression" dxfId="228" priority="339">

--- a/public/worldcup.xlsx
+++ b/public/worldcup.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rylanpaul/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58F04A70-91A6-6A44-B439-C7F671E73D71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DB22C1C-201B-AE4B-AAC8-4D762A6904D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9903" uniqueCount="3715">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9910" uniqueCount="3716">
   <si>
     <t>English</t>
   </si>
@@ -11249,6 +11249,9 @@
   </si>
   <si>
     <t>Opponent</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -13305,12 +13308,56 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -13391,50 +13438,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -38544,7 +38547,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FBEBCC1-8E24-6D45-9806-292128B12084}">
-  <dimension ref="A1:AG8"/>
+  <dimension ref="A1:AG18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.1640625" bestFit="1" customWidth="1"/>
@@ -38766,6 +38769,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(R3,Rounds!Q$2:Q$9,Rounds!T$2:T$9), _xlfn.XLOOKUP(R3,Rounds!T$2:T$9,Rounds!Q$2:Q$9))</f>
         <v>England</v>
       </c>
+      <c r="V3" t="s">
+        <v>1633</v>
+      </c>
       <c r="W3" s="142" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(V3,Rounds!U$2:U$5,Rounds!V$2:V$5), _xlfn.XLOOKUP(V3,Rounds!X$2:X$5,Rounds!W$2:W$5))</f>
         <v>#N/A</v>
@@ -38774,9 +38780,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(V3,Rounds!U$2:U$5,Rounds!W$2:W$5), _xlfn.XLOOKUP(V3,Rounds!X$2:X$5,Rounds!V$2:V$5))</f>
         <v>#N/A</v>
       </c>
-      <c r="Y3" s="140" t="e">
+      <c r="Y3" s="140" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(V3,Rounds!U$2:U$5,Rounds!X$2:X$5), _xlfn.XLOOKUP(V3,Rounds!X$2:X$5,Rounds!U$2:U$5))</f>
-        <v>#N/A</v>
+        <v>Spain</v>
       </c>
       <c r="AA3" s="142" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(Z3,Rounds!Y$2:Y$3,Rounds!Z$2:Z$3), _xlfn.XLOOKUP(Z3,Rounds!AB$2:AB$3,Rounds!AA$2:AA$3))</f>
@@ -38882,6 +38888,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(R4,Rounds!Q$2:Q$9,Rounds!T$2:T$9), _xlfn.XLOOKUP(R4,Rounds!T$2:T$9,Rounds!Q$2:Q$9))</f>
         <v>England</v>
       </c>
+      <c r="V4" s="148" t="s">
+        <v>2395</v>
+      </c>
       <c r="W4" s="146" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(V4,Rounds!U$2:U$5,Rounds!V$2:V$5), _xlfn.XLOOKUP(V4,Rounds!X$2:X$5,Rounds!W$2:W$5))</f>
         <v>#N/A</v>
@@ -38890,9 +38899,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(V4,Rounds!U$2:U$5,Rounds!W$2:W$5), _xlfn.XLOOKUP(V4,Rounds!X$2:X$5,Rounds!V$2:V$5))</f>
         <v>#N/A</v>
       </c>
-      <c r="Y4" s="147" t="e">
+      <c r="Y4" s="147" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(V4,Rounds!U$2:U$5,Rounds!X$2:X$5), _xlfn.XLOOKUP(V4,Rounds!X$2:X$5,Rounds!U$2:U$5))</f>
-        <v>#N/A</v>
+        <v>England</v>
       </c>
       <c r="AA4" s="146" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(Z4,Rounds!Y$2:Y$3,Rounds!Z$2:Z$3), _xlfn.XLOOKUP(Z4,Rounds!AB$2:AB$3,Rounds!AA$2:AA$3))</f>
@@ -38998,6 +39007,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(R5,Rounds!Q$2:Q$9,Rounds!T$2:T$9), _xlfn.XLOOKUP(R5,Rounds!T$2:T$9,Rounds!Q$2:Q$9))</f>
         <v>Canada</v>
       </c>
+      <c r="V5" t="s">
+        <v>1264</v>
+      </c>
       <c r="W5" s="82" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(V5,Rounds!U$2:U$5,Rounds!V$2:V$5), _xlfn.XLOOKUP(V5,Rounds!X$2:X$5,Rounds!W$2:W$5))</f>
         <v>#N/A</v>
@@ -39006,9 +39018,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(V5,Rounds!U$2:U$5,Rounds!W$2:W$5), _xlfn.XLOOKUP(V5,Rounds!X$2:X$5,Rounds!V$2:V$5))</f>
         <v>#N/A</v>
       </c>
-      <c r="Y5" s="134" t="e">
+      <c r="Y5" s="134" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(V5,Rounds!U$2:U$5,Rounds!X$2:X$5), _xlfn.XLOOKUP(V5,Rounds!X$2:X$5,Rounds!U$2:U$5))</f>
-        <v>#N/A</v>
+        <v>Switzerland</v>
       </c>
       <c r="AA5" s="82" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(Z5,Rounds!Y$2:Y$3,Rounds!Z$2:Z$3), _xlfn.XLOOKUP(Z5,Rounds!AB$2:AB$3,Rounds!AA$2:AA$3))</f>
@@ -39114,6 +39126,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(R6,Rounds!Q$2:Q$9,Rounds!T$2:T$9), _xlfn.XLOOKUP(R6,Rounds!T$2:T$9,Rounds!Q$2:Q$9))</f>
         <v>England</v>
       </c>
+      <c r="V6" s="148" t="s">
+        <v>1508</v>
+      </c>
       <c r="W6" s="146" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(V6,Rounds!U$2:U$5,Rounds!V$2:V$5), _xlfn.XLOOKUP(V6,Rounds!X$2:X$5,Rounds!W$2:W$5))</f>
         <v>#N/A</v>
@@ -39122,9 +39137,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(V6,Rounds!U$2:U$5,Rounds!W$2:W$5), _xlfn.XLOOKUP(V6,Rounds!X$2:X$5,Rounds!V$2:V$5))</f>
         <v>#N/A</v>
       </c>
-      <c r="Y6" s="147" t="e">
+      <c r="Y6" s="147" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(V6,Rounds!U$2:U$5,Rounds!X$2:X$5), _xlfn.XLOOKUP(V6,Rounds!X$2:X$5,Rounds!U$2:U$5))</f>
-        <v>#N/A</v>
+        <v>Belgium</v>
       </c>
       <c r="AA6" s="146" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(Z6,Rounds!Y$2:Y$3,Rounds!Z$2:Z$3), _xlfn.XLOOKUP(Z6,Rounds!AB$2:AB$3,Rounds!AA$2:AA$3))</f>
@@ -39230,6 +39245,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(R7,Rounds!Q$2:Q$9,Rounds!T$2:T$9), _xlfn.XLOOKUP(R7,Rounds!T$2:T$9,Rounds!Q$2:Q$9))</f>
         <v>Portugal</v>
       </c>
+      <c r="V7" t="s">
+        <v>1264</v>
+      </c>
       <c r="W7" s="82" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(V7,Rounds!U$2:U$5,Rounds!V$2:V$5), _xlfn.XLOOKUP(V7,Rounds!X$2:X$5,Rounds!W$2:W$5))</f>
         <v>#N/A</v>
@@ -39238,9 +39256,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(V7,Rounds!U$2:U$5,Rounds!W$2:W$5), _xlfn.XLOOKUP(V7,Rounds!X$2:X$5,Rounds!V$2:V$5))</f>
         <v>#N/A</v>
       </c>
-      <c r="Y7" s="134" t="e">
+      <c r="Y7" s="134" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(V7,Rounds!U$2:U$5,Rounds!X$2:X$5), _xlfn.XLOOKUP(V7,Rounds!X$2:X$5,Rounds!U$2:U$5))</f>
-        <v>#N/A</v>
+        <v>Switzerland</v>
       </c>
       <c r="AA7" s="82" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(Z7,Rounds!Y$2:Y$3,Rounds!Z$2:Z$3), _xlfn.XLOOKUP(Z7,Rounds!AB$2:AB$3,Rounds!AA$2:AA$3))</f>
@@ -39346,7 +39364,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(R8,Rounds!Q$2:Q$9,Rounds!T$2:T$9), _xlfn.XLOOKUP(R8,Rounds!T$2:T$9,Rounds!Q$2:Q$9))</f>
         <v>Mexico</v>
       </c>
-      <c r="V8" s="152"/>
+      <c r="V8" s="152" t="s">
+        <v>2395</v>
+      </c>
       <c r="W8" s="150" t="e">
         <f>IFERROR(_xlfn.XLOOKUP(V8,Rounds!U$2:U$5,Rounds!V$2:V$5), _xlfn.XLOOKUP(V8,Rounds!X$2:X$5,Rounds!W$2:W$5))</f>
         <v>#N/A</v>
@@ -39355,9 +39375,9 @@
         <f>IFERROR(_xlfn.XLOOKUP(V8,Rounds!U$2:U$5,Rounds!W$2:W$5), _xlfn.XLOOKUP(V8,Rounds!X$2:X$5,Rounds!V$2:V$5))</f>
         <v>#N/A</v>
       </c>
-      <c r="Y8" s="151" t="e">
+      <c r="Y8" s="151" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(V8,Rounds!U$2:U$5,Rounds!X$2:X$5), _xlfn.XLOOKUP(V8,Rounds!X$2:X$5,Rounds!U$2:U$5))</f>
-        <v>#N/A</v>
+        <v>England</v>
       </c>
       <c r="Z8" s="152"/>
       <c r="AA8" s="150" t="e">
@@ -39384,6 +39404,11 @@
       <c r="AG8" s="151" t="e" cm="1">
         <f t="array" ref="AG8">IFERROR(_xlfn.XLOOKUP(AD8,Rounds!AC$2:AC$2,Rounds!AF$2:AF$2), _xlfn.XLOOKUP(AD8,Rounds!AF$2:AF$2,Rounds!AC$2:AC$2))</f>
         <v>#N/A</v>
+      </c>
+    </row>
+    <row r="18" spans="14:14" x14ac:dyDescent="0.2">
+      <c r="N18" t="s">
+        <v>3715</v>
       </c>
     </row>
   </sheetData>
@@ -39711,7 +39736,7 @@
       </c>
       <c r="X3" s="134" t="str">
         <f>'2026 World Cup'!BZ33</f>
-        <v/>
+        <v>Belgium</v>
       </c>
       <c r="Y3" s="135" t="str">
         <f>'2026 World Cup'!CG55</f>
@@ -39873,13 +39898,13 @@
         <f>'2026 World Cup'!BS36</f>
         <v>United States</v>
       </c>
-      <c r="R5" s="81" t="e">
+      <c r="R5" s="81">
         <f>IF('2026 World Cup'!$BT36="",NA(),'2026 World Cup'!$BT36)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="S5" s="81" t="e">
+        <v>1</v>
+      </c>
+      <c r="S5" s="81">
         <f>IF('2026 World Cup'!$BT37="",NA(),'2026 World Cup'!$BT37)</f>
-        <v>#N/A</v>
+        <v>4</v>
       </c>
       <c r="T5" s="134" t="str">
         <f>'2026 World Cup'!BS37</f>
@@ -39887,7 +39912,7 @@
       </c>
       <c r="U5" s="135" t="str">
         <f>'2026 World Cup'!BZ64</f>
-        <v/>
+        <v>Argentina</v>
       </c>
       <c r="V5" s="153" t="e">
         <f>IF('2026 World Cup'!$CA64="",NA(),'2026 World Cup'!$CA64)</f>
@@ -39899,7 +39924,7 @@
       </c>
       <c r="X5" s="136" t="str">
         <f>'2026 World Cup'!BZ65</f>
-        <v/>
+        <v>Switzerland</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.2">
@@ -40099,13 +40124,13 @@
         <f>'2026 World Cup'!BS60</f>
         <v>Argentina</v>
       </c>
-      <c r="R8" s="81" t="e">
+      <c r="R8" s="81">
         <f>IF('2026 World Cup'!$BT60="",NA(),'2026 World Cup'!$BT60)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="S8" s="81" t="e">
+        <v>3</v>
+      </c>
+      <c r="S8" s="81">
         <f>IF('2026 World Cup'!$BT61="",NA(),'2026 World Cup'!$BT61)</f>
-        <v>#N/A</v>
+        <v>2</v>
       </c>
       <c r="T8" s="134" t="str">
         <f>'2026 World Cup'!BS61</f>
@@ -40169,13 +40194,13 @@
         <f>'2026 World Cup'!BS68</f>
         <v>Switzerland</v>
       </c>
-      <c r="R9" s="153" t="e">
+      <c r="R9" s="153">
         <f>IF('2026 World Cup'!$BT68="",NA(),'2026 World Cup'!$BT68)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="S9" s="153" t="e">
+        <v>1</v>
+      </c>
+      <c r="S9" s="153">
         <f>IF('2026 World Cup'!$BT69="",NA(),'2026 World Cup'!$BT69)</f>
-        <v>#N/A</v>
+        <v>0</v>
       </c>
       <c r="T9" s="136" t="str">
         <f>'2026 World Cup'!BS69</f>
@@ -40998,25 +41023,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:95" ht="47" x14ac:dyDescent="0.2">
-      <c r="A1" s="171" t="str" cm="1">
+      <c r="A1" s="182" t="str" cm="1">
         <f t="array" ref="A1">INDEX(T,2,lang)</f>
         <v>2026 World Cup Final Tournament Schedule</v>
       </c>
-      <c r="B1" s="171"/>
-      <c r="C1" s="171"/>
-      <c r="D1" s="171"/>
-      <c r="E1" s="171"/>
-      <c r="F1" s="171"/>
-      <c r="G1" s="171"/>
-      <c r="H1" s="171"/>
-      <c r="I1" s="171"/>
-      <c r="J1" s="171"/>
-      <c r="K1" s="171"/>
-      <c r="L1" s="171"/>
-      <c r="M1" s="171"/>
-      <c r="N1" s="171"/>
-      <c r="O1" s="171"/>
-      <c r="P1" s="171"/>
+      <c r="B1" s="182"/>
+      <c r="C1" s="182"/>
+      <c r="D1" s="182"/>
+      <c r="E1" s="182"/>
+      <c r="F1" s="182"/>
+      <c r="G1" s="182"/>
+      <c r="H1" s="182"/>
+      <c r="I1" s="182"/>
+      <c r="J1" s="182"/>
+      <c r="K1" s="182"/>
+      <c r="L1" s="182"/>
+      <c r="M1" s="182"/>
+      <c r="N1" s="182"/>
+      <c r="O1" s="182"/>
+      <c r="P1" s="182"/>
       <c r="S1" s="123"/>
       <c r="T1" s="123"/>
       <c r="AC1" s="123"/>
@@ -41063,11 +41088,11 @@
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
-      <c r="O3" s="172" t="str">
+      <c r="O3" s="183" t="str">
         <f>"Language: " &amp; Settings!C4</f>
         <v>Language: English</v>
       </c>
-      <c r="P3" s="172"/>
+      <c r="P3" s="183"/>
       <c r="S3" s="123"/>
       <c r="T3" s="123"/>
       <c r="AC3" s="123"/>
@@ -41085,43 +41110,43 @@
     </row>
     <row r="4" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:95" x14ac:dyDescent="0.2">
-      <c r="A5" s="173" t="str" cm="1">
+      <c r="A5" s="184" t="str" cm="1">
         <f t="array" ref="A5">INDEX(T,3,lang)</f>
         <v>Group Stage</v>
       </c>
-      <c r="B5" s="174"/>
-      <c r="C5" s="174"/>
-      <c r="D5" s="174"/>
-      <c r="E5" s="174"/>
-      <c r="F5" s="174"/>
-      <c r="G5" s="174"/>
-      <c r="H5" s="175"/>
-      <c r="J5" s="179" t="s">
+      <c r="B5" s="185"/>
+      <c r="C5" s="185"/>
+      <c r="D5" s="185"/>
+      <c r="E5" s="185"/>
+      <c r="F5" s="185"/>
+      <c r="G5" s="185"/>
+      <c r="H5" s="186"/>
+      <c r="J5" s="190" t="s">
         <v>3166</v>
       </c>
-      <c r="K5" s="180"/>
-      <c r="L5" s="180"/>
-      <c r="M5" s="180"/>
-      <c r="N5" s="180"/>
-      <c r="O5" s="180"/>
-      <c r="P5" s="181"/>
+      <c r="K5" s="191"/>
+      <c r="L5" s="191"/>
+      <c r="M5" s="191"/>
+      <c r="N5" s="191"/>
+      <c r="O5" s="191"/>
+      <c r="P5" s="192"/>
     </row>
     <row r="6" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="176"/>
-      <c r="B6" s="177"/>
-      <c r="C6" s="177"/>
-      <c r="D6" s="177"/>
-      <c r="E6" s="177"/>
-      <c r="F6" s="177"/>
-      <c r="G6" s="177"/>
-      <c r="H6" s="178"/>
-      <c r="J6" s="182"/>
-      <c r="K6" s="183"/>
-      <c r="L6" s="183"/>
-      <c r="M6" s="183"/>
-      <c r="N6" s="183"/>
-      <c r="O6" s="183"/>
-      <c r="P6" s="184"/>
+      <c r="A6" s="187"/>
+      <c r="B6" s="188"/>
+      <c r="C6" s="188"/>
+      <c r="D6" s="188"/>
+      <c r="E6" s="188"/>
+      <c r="F6" s="188"/>
+      <c r="G6" s="188"/>
+      <c r="H6" s="189"/>
+      <c r="J6" s="193"/>
+      <c r="K6" s="194"/>
+      <c r="L6" s="194"/>
+      <c r="M6" s="194"/>
+      <c r="N6" s="194"/>
+      <c r="O6" s="194"/>
+      <c r="P6" s="195"/>
       <c r="R6" s="123" t="s">
         <v>3167</v>
       </c>
@@ -41231,37 +41256,37 @@
       <c r="BI6" s="128" t="s">
         <v>3178</v>
       </c>
-      <c r="BK6" s="165" t="s">
+      <c r="BK6" s="176" t="s">
         <v>3179</v>
       </c>
-      <c r="BL6" s="166"/>
-      <c r="BM6" s="166"/>
-      <c r="BN6" s="166"/>
-      <c r="BO6" s="167"/>
-      <c r="BR6" s="165" t="str" cm="1">
+      <c r="BL6" s="177"/>
+      <c r="BM6" s="177"/>
+      <c r="BN6" s="177"/>
+      <c r="BO6" s="178"/>
+      <c r="BR6" s="176" t="str" cm="1">
         <f t="array" ref="BR6">INDEX(T,4,lang)</f>
         <v>Round of 16</v>
       </c>
-      <c r="BS6" s="166"/>
-      <c r="BT6" s="166"/>
-      <c r="BU6" s="166"/>
-      <c r="BV6" s="167"/>
-      <c r="BY6" s="165" t="str" cm="1">
+      <c r="BS6" s="177"/>
+      <c r="BT6" s="177"/>
+      <c r="BU6" s="177"/>
+      <c r="BV6" s="178"/>
+      <c r="BY6" s="176" t="str" cm="1">
         <f t="array" ref="BY6">INDEX(T,5,lang)</f>
         <v>Quarterfinals</v>
       </c>
-      <c r="BZ6" s="166"/>
-      <c r="CA6" s="166"/>
-      <c r="CB6" s="166"/>
-      <c r="CC6" s="167"/>
-      <c r="CF6" s="165" t="str" cm="1">
+      <c r="BZ6" s="177"/>
+      <c r="CA6" s="177"/>
+      <c r="CB6" s="177"/>
+      <c r="CC6" s="178"/>
+      <c r="CF6" s="176" t="str" cm="1">
         <f t="array" ref="CF6">INDEX(T,6,lang)</f>
         <v>Semi-Finals</v>
       </c>
-      <c r="CG6" s="166"/>
-      <c r="CH6" s="166"/>
-      <c r="CI6" s="166"/>
-      <c r="CJ6" s="167"/>
+      <c r="CG6" s="177"/>
+      <c r="CH6" s="177"/>
+      <c r="CI6" s="177"/>
+      <c r="CJ6" s="178"/>
     </row>
     <row r="7" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="11">
@@ -41338,26 +41363,26 @@
         <v>1</v>
       </c>
       <c r="AY7" s="126"/>
-      <c r="BK7" s="168"/>
-      <c r="BL7" s="169"/>
-      <c r="BM7" s="169"/>
-      <c r="BN7" s="169"/>
-      <c r="BO7" s="170"/>
-      <c r="BR7" s="168"/>
-      <c r="BS7" s="169"/>
-      <c r="BT7" s="169"/>
-      <c r="BU7" s="169"/>
-      <c r="BV7" s="170"/>
-      <c r="BY7" s="168"/>
-      <c r="BZ7" s="169"/>
-      <c r="CA7" s="169"/>
-      <c r="CB7" s="169"/>
-      <c r="CC7" s="170"/>
-      <c r="CF7" s="168"/>
-      <c r="CG7" s="169"/>
-      <c r="CH7" s="169"/>
-      <c r="CI7" s="169"/>
-      <c r="CJ7" s="170"/>
+      <c r="BK7" s="179"/>
+      <c r="BL7" s="180"/>
+      <c r="BM7" s="180"/>
+      <c r="BN7" s="180"/>
+      <c r="BO7" s="181"/>
+      <c r="BR7" s="179"/>
+      <c r="BS7" s="180"/>
+      <c r="BT7" s="180"/>
+      <c r="BU7" s="180"/>
+      <c r="BV7" s="181"/>
+      <c r="BY7" s="179"/>
+      <c r="BZ7" s="180"/>
+      <c r="CA7" s="180"/>
+      <c r="CB7" s="180"/>
+      <c r="CC7" s="181"/>
+      <c r="CF7" s="179"/>
+      <c r="CG7" s="180"/>
+      <c r="CH7" s="180"/>
+      <c r="CI7" s="180"/>
+      <c r="CJ7" s="181"/>
     </row>
     <row r="8" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A8" s="16">
@@ -42093,7 +42118,7 @@
         <f>BH10/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK10" s="163">
+      <c r="BK10" s="173">
         <v>74</v>
       </c>
       <c r="BL10" s="24" t="str">
@@ -42358,7 +42383,7 @@
         <f>BH11/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK11" s="164"/>
+      <c r="BK11" s="174"/>
       <c r="BL11" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!G3,AK80:AS91,9,FALSE),"3rd Group A/B/C/D/F")</f>
         <v>Paraguay</v>
@@ -42598,7 +42623,7 @@
       <c r="BO12" s="21"/>
       <c r="BP12" s="114"/>
       <c r="BQ12" s="112"/>
-      <c r="BR12" s="163">
+      <c r="BR12" s="173">
         <v>89</v>
       </c>
       <c r="BS12" s="24" t="str">
@@ -42721,7 +42746,7 @@
         <v>46203.875</v>
       </c>
       <c r="BQ13" s="115"/>
-      <c r="BR13" s="164"/>
+      <c r="BR13" s="174"/>
       <c r="BS13" s="26" t="str">
         <f>IF(BP14&gt;BP15,BL14,IF(BP14&lt;BP15,BL15,""))</f>
         <v>France</v>
@@ -42981,7 +43006,7 @@
         <f>BH14/BH18</f>
         <v>0.98058252427184467</v>
       </c>
-      <c r="BK14" s="163">
+      <c r="BK14" s="173">
         <v>77</v>
       </c>
       <c r="BL14" s="24" t="str">
@@ -43250,7 +43275,7 @@
         <f>BH15/BH18</f>
         <v>0.98058252427184467</v>
       </c>
-      <c r="BK15" s="164"/>
+      <c r="BK15" s="174"/>
       <c r="BL15" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!I3,AK80:AS91,9,FALSE),"3rd Group C/D/F/G/H")</f>
         <v>Sweden</v>
@@ -43526,7 +43551,7 @@
       <c r="BV16" s="21"/>
       <c r="BW16" s="114"/>
       <c r="BX16" s="112"/>
-      <c r="BY16" s="163">
+      <c r="BY16" s="173">
         <v>97</v>
       </c>
       <c r="BZ16" s="24" t="str">
@@ -43788,7 +43813,7 @@
       <c r="BV17" s="21"/>
       <c r="BW17" s="114"/>
       <c r="BX17" s="115"/>
-      <c r="BY17" s="164"/>
+      <c r="BY17" s="174"/>
       <c r="BZ17" s="26" t="str">
         <f>IF(BW20&gt;BW21,BS20,IF(BW20&lt;BW21,BS21,""))</f>
         <v>Morocco</v>
@@ -43992,7 +44017,7 @@
         <f>MAX(BH14:BH17)+1</f>
         <v>51.5</v>
       </c>
-      <c r="BK18" s="163">
+      <c r="BK18" s="173">
         <v>73</v>
       </c>
       <c r="BL18" s="24" t="str">
@@ -44102,7 +44127,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BK19" s="164"/>
+      <c r="BK19" s="174"/>
       <c r="BL19" s="26" t="str">
         <f>AS15</f>
         <v>Canada</v>
@@ -44382,7 +44407,7 @@
       <c r="BO20" s="21"/>
       <c r="BP20" s="114"/>
       <c r="BQ20" s="112"/>
-      <c r="BR20" s="163">
+      <c r="BR20" s="173">
         <v>90</v>
       </c>
       <c r="BS20" s="24" t="str">
@@ -44657,7 +44682,7 @@
         <v>46203.041666666672</v>
       </c>
       <c r="BQ21" s="115"/>
-      <c r="BR21" s="164"/>
+      <c r="BR21" s="174"/>
       <c r="BS21" s="26" t="str">
         <f>IF(BP22&gt;BP23,BL22,IF(BP22&lt;BP23,BL23,""))</f>
         <v>Morocco</v>
@@ -44913,7 +44938,7 @@
         <f>BH22/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK22" s="163">
+      <c r="BK22" s="173">
         <v>75</v>
       </c>
       <c r="BL22" s="24" t="str">
@@ -45179,7 +45204,7 @@
         <f>BH23/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK23" s="164"/>
+      <c r="BK23" s="174"/>
       <c r="BL23" s="26" t="str">
         <f>AS21</f>
         <v>Morocco</v>
@@ -45208,7 +45233,7 @@
       <c r="CC23" s="21"/>
       <c r="CD23" s="114"/>
       <c r="CE23" s="112"/>
-      <c r="CF23" s="163">
+      <c r="CF23" s="173">
         <v>101</v>
       </c>
       <c r="CG23" s="24" t="str">
@@ -45429,7 +45454,7 @@
       <c r="CC24" s="21"/>
       <c r="CD24" s="114"/>
       <c r="CE24" s="115"/>
-      <c r="CF24" s="164"/>
+      <c r="CF24" s="174"/>
       <c r="CG24" s="26" t="str">
         <f>IF(CD32&gt;CD33,BZ32,IF(CD32&lt;CD33,BZ33,""))</f>
         <v/>
@@ -45782,7 +45807,7 @@
         <f>BH26/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK26" s="163">
+      <c r="BK26" s="173">
         <v>83</v>
       </c>
       <c r="BL26" s="24" t="str">
@@ -46052,7 +46077,7 @@
         <f>BH27/BH30</f>
         <v>0.98039215686274506</v>
       </c>
-      <c r="BK27" s="164"/>
+      <c r="BK27" s="174"/>
       <c r="BL27" s="26" t="str">
         <f>AS75</f>
         <v>Croatia</v>
@@ -46329,7 +46354,7 @@
       <c r="BO28" s="21"/>
       <c r="BP28" s="114"/>
       <c r="BQ28" s="112"/>
-      <c r="BR28" s="163">
+      <c r="BR28" s="173">
         <v>93</v>
       </c>
       <c r="BS28" s="24" t="str">
@@ -46596,7 +46621,7 @@
         <v>46205.791666666672</v>
       </c>
       <c r="BQ29" s="115"/>
-      <c r="BR29" s="164"/>
+      <c r="BR29" s="174"/>
       <c r="BS29" s="26" t="str">
         <f>IF(BP30&gt;BP31,BL30,IF(BP30&lt;BP31,BL31,""))</f>
         <v>Spain</v>
@@ -46812,7 +46837,7 @@
         <f>MAX(BH26:BH29)+1</f>
         <v>51</v>
       </c>
-      <c r="BK30" s="163">
+      <c r="BK30" s="173">
         <v>84</v>
       </c>
       <c r="BL30" s="24" t="str">
@@ -46925,7 +46950,7 @@
         <f>IF(OR(F31="",G31=""),"",IF(F31&gt;G31,1,IF(F31&lt;G31,-1,0)))</f>
         <v>0</v>
       </c>
-      <c r="BK31" s="164"/>
+      <c r="BK31" s="174"/>
       <c r="BL31" s="26" t="str">
         <f>AS63</f>
         <v>Austria</v>
@@ -47203,7 +47228,7 @@
       <c r="BV32" s="21"/>
       <c r="BW32" s="114"/>
       <c r="BX32" s="112"/>
-      <c r="BY32" s="163">
+      <c r="BY32" s="173">
         <v>98</v>
       </c>
       <c r="BZ32" s="24" t="str">
@@ -47467,10 +47492,10 @@
       <c r="BV33" s="21"/>
       <c r="BW33" s="114"/>
       <c r="BX33" s="115"/>
-      <c r="BY33" s="164"/>
+      <c r="BY33" s="174"/>
       <c r="BZ33" s="26" t="str">
         <f>IF(BW36&gt;BW37,BS36,IF(BW36&lt;BW37,BS37,""))</f>
-        <v/>
+        <v>Belgium</v>
       </c>
       <c r="CA33" s="62"/>
       <c r="CB33" s="64"/>
@@ -47482,14 +47507,14 @@
       <c r="CE33" s="112"/>
       <c r="CK33" s="114"/>
       <c r="CL33" s="112"/>
-      <c r="CM33" s="165" t="str" cm="1">
+      <c r="CM33" s="176" t="str" cm="1">
         <f t="array" ref="CM33">INDEX(T,8,lang)</f>
         <v>Final</v>
       </c>
-      <c r="CN33" s="166"/>
-      <c r="CO33" s="166"/>
-      <c r="CP33" s="166"/>
-      <c r="CQ33" s="167"/>
+      <c r="CN33" s="177"/>
+      <c r="CO33" s="177"/>
+      <c r="CP33" s="177"/>
+      <c r="CQ33" s="178"/>
     </row>
     <row r="34" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A34" s="16">
@@ -47713,7 +47738,7 @@
         <f>BH34/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK34" s="163">
+      <c r="BK34" s="173">
         <v>81</v>
       </c>
       <c r="BL34" s="24" t="str">
@@ -47746,11 +47771,11 @@
       <c r="CE34" s="112"/>
       <c r="CK34" s="114"/>
       <c r="CL34" s="112"/>
-      <c r="CM34" s="168"/>
-      <c r="CN34" s="169"/>
-      <c r="CO34" s="169"/>
-      <c r="CP34" s="169"/>
-      <c r="CQ34" s="170"/>
+      <c r="CM34" s="179"/>
+      <c r="CN34" s="180"/>
+      <c r="CO34" s="180"/>
+      <c r="CP34" s="180"/>
+      <c r="CQ34" s="181"/>
     </row>
     <row r="35" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A35" s="16">
@@ -47974,7 +47999,7 @@
         <f>BH35/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK35" s="164"/>
+      <c r="BK35" s="174"/>
       <c r="BL35" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!F3,AK80:AS91,9,FALSE),"3rd Group B/E/F/I/J")</f>
         <v>Bosnia and Herzegovina</v>
@@ -48205,19 +48230,21 @@
       <c r="BO36" s="21"/>
       <c r="BP36" s="114"/>
       <c r="BQ36" s="112"/>
-      <c r="BR36" s="163">
+      <c r="BR36" s="173">
         <v>94</v>
       </c>
       <c r="BS36" s="24" t="str">
         <f>IF(BP34&gt;BP35,BL34,IF(BP34&lt;BP35,BL35,""))</f>
         <v>United States</v>
       </c>
-      <c r="BT36" s="61"/>
+      <c r="BT36" s="61">
+        <v>1</v>
+      </c>
       <c r="BU36" s="63"/>
       <c r="BV36" s="25"/>
-      <c r="BW36" s="116" t="str">
+      <c r="BW36" s="116">
         <f>IF(OR(BT36="",BT37="",AND(BU36="",BU37&lt;&gt;""),AND(BU37="",BU36&lt;&gt;""),AND(BV36="",BV37&lt;&gt;""),AND(BV37="",BV36&lt;&gt;"")),"",BT36*1000+BU36*10+BV36)</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="BX36" s="112"/>
       <c r="BY36" s="21"/>
@@ -48329,17 +48356,19 @@
         <v>46204.833333333336</v>
       </c>
       <c r="BQ37" s="115"/>
-      <c r="BR37" s="164"/>
+      <c r="BR37" s="174"/>
       <c r="BS37" s="26" t="str">
         <f>IF(BP38&gt;BP39,BL38,IF(BP38&lt;BP39,BL39,""))</f>
         <v>Belgium</v>
       </c>
-      <c r="BT37" s="62"/>
+      <c r="BT37" s="62">
+        <v>4</v>
+      </c>
       <c r="BU37" s="64"/>
       <c r="BV37" s="27"/>
-      <c r="BW37" s="112" t="str">
+      <c r="BW37" s="112">
         <f>IF(BW36="","",BT37*1000+BU37*10+BV37)</f>
-        <v/>
+        <v>4000</v>
       </c>
       <c r="BX37" s="112"/>
       <c r="BY37" s="21"/>
@@ -48356,7 +48385,7 @@
       <c r="CJ37" s="21"/>
       <c r="CK37" s="114"/>
       <c r="CL37" s="112"/>
-      <c r="CM37" s="163">
+      <c r="CM37" s="173">
         <v>104</v>
       </c>
       <c r="CN37" s="24" t="str">
@@ -48597,7 +48626,7 @@
         <f>BH38/BH42</f>
         <v>0</v>
       </c>
-      <c r="BK38" s="163">
+      <c r="BK38" s="173">
         <v>82</v>
       </c>
       <c r="BL38" s="24" t="str">
@@ -48629,7 +48658,7 @@
       <c r="CI38" s="21"/>
       <c r="CJ38" s="21"/>
       <c r="CL38" s="115"/>
-      <c r="CM38" s="164"/>
+      <c r="CM38" s="174"/>
       <c r="CN38" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG55,IF(CK55&lt;CK56,CG56,""))</f>
         <v/>
@@ -48868,7 +48897,7 @@
         <f>BH39/BH42</f>
         <v>0</v>
       </c>
-      <c r="BK39" s="164"/>
+      <c r="BK39" s="174"/>
       <c r="BL39" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!H3,AK80:AS91,9,FALSE),"3rd Group A/E/H/I/J")</f>
         <v>Senegal</v>
@@ -49558,7 +49587,7 @@
         <f>MAX(BH38:BH41)+1</f>
         <v>1</v>
       </c>
-      <c r="BK42" s="163">
+      <c r="BK42" s="173">
         <v>76</v>
       </c>
       <c r="BL42" s="24" t="str">
@@ -49657,7 +49686,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BK43" s="164"/>
+      <c r="BK43" s="174"/>
       <c r="BL43" s="26" t="str">
         <f>AS39</f>
         <v>Japan</v>
@@ -49919,7 +49948,7 @@
       <c r="BO44" s="21"/>
       <c r="BP44" s="114"/>
       <c r="BQ44" s="112"/>
-      <c r="BR44" s="163">
+      <c r="BR44" s="173">
         <v>91</v>
       </c>
       <c r="BS44" s="24" t="str">
@@ -49936,14 +49965,14 @@
         <v>1000</v>
       </c>
       <c r="CK44" s="114"/>
-      <c r="CM44" s="165" t="str" cm="1">
+      <c r="CM44" s="176" t="str" cm="1">
         <f t="array" ref="CM44">INDEX(T,7,lang)</f>
         <v>Third-Place Play-Off</v>
       </c>
-      <c r="CN44" s="166"/>
-      <c r="CO44" s="166"/>
-      <c r="CP44" s="166"/>
-      <c r="CQ44" s="167"/>
+      <c r="CN44" s="177"/>
+      <c r="CO44" s="177"/>
+      <c r="CP44" s="177"/>
+      <c r="CQ44" s="178"/>
     </row>
     <row r="45" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="16">
@@ -50184,7 +50213,7 @@
         <v>46203.708333333336</v>
       </c>
       <c r="BQ45" s="115"/>
-      <c r="BR45" s="164"/>
+      <c r="BR45" s="174"/>
       <c r="BS45" s="26" t="str">
         <f>IF(BP46&gt;BP47,BL46,IF(BP46&lt;BP47,BL47,""))</f>
         <v>Norway</v>
@@ -50199,11 +50228,11 @@
         <v>2000</v>
       </c>
       <c r="CK45" s="114"/>
-      <c r="CM45" s="168"/>
-      <c r="CN45" s="169"/>
-      <c r="CO45" s="169"/>
-      <c r="CP45" s="169"/>
-      <c r="CQ45" s="170"/>
+      <c r="CM45" s="179"/>
+      <c r="CN45" s="180"/>
+      <c r="CO45" s="180"/>
+      <c r="CP45" s="180"/>
+      <c r="CQ45" s="181"/>
     </row>
     <row r="46" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A46" s="16">
@@ -50427,7 +50456,7 @@
         <f>BH46/BH48</f>
         <v>0</v>
       </c>
-      <c r="BK46" s="163">
+      <c r="BK46" s="173">
         <v>78</v>
       </c>
       <c r="BL46" s="24" t="str">
@@ -50675,7 +50704,7 @@
         <f>BH47/BH48</f>
         <v>0</v>
       </c>
-      <c r="BK47" s="164"/>
+      <c r="BK47" s="174"/>
       <c r="BL47" s="26" t="str">
         <f>AS57</f>
         <v>Norway</v>
@@ -50924,7 +50953,7 @@
       <c r="BV48" s="21"/>
       <c r="BW48" s="114"/>
       <c r="BX48" s="112"/>
-      <c r="BY48" s="163">
+      <c r="BY48" s="173">
         <v>99</v>
       </c>
       <c r="BZ48" s="24" t="str">
@@ -50940,7 +50969,7 @@
       </c>
       <c r="CK48" s="114"/>
       <c r="CL48" s="112"/>
-      <c r="CM48" s="163">
+      <c r="CM48" s="173">
         <v>103</v>
       </c>
       <c r="CN48" s="24" t="str">
@@ -51049,7 +51078,7 @@
       <c r="BV49" s="21"/>
       <c r="BW49" s="114"/>
       <c r="BX49" s="115"/>
-      <c r="BY49" s="164"/>
+      <c r="BY49" s="174"/>
       <c r="BZ49" s="26" t="str">
         <f>IF(BW52&gt;BW53,BS52,IF(BW52&lt;BW53,BS53,""))</f>
         <v>England</v>
@@ -51063,7 +51092,7 @@
       </c>
       <c r="CK49" s="114"/>
       <c r="CL49" s="115"/>
-      <c r="CM49" s="164"/>
+      <c r="CM49" s="174"/>
       <c r="CN49" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG56,IF(CK55&lt;CK56,CG55,""))</f>
         <v/>
@@ -51302,7 +51331,7 @@
         <f>BH50/BH54</f>
         <v>0</v>
       </c>
-      <c r="BK50" s="163">
+      <c r="BK50" s="173">
         <v>79</v>
       </c>
       <c r="BL50" s="24" t="str">
@@ -51561,7 +51590,7 @@
         <f>BH51/BH54</f>
         <v>0</v>
       </c>
-      <c r="BK51" s="164"/>
+      <c r="BK51" s="174"/>
       <c r="BL51" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!D3,AK80:AS91,9,FALSE),"3rd Group C/E/F/H/I")</f>
         <v>Ecuador</v>
@@ -51827,7 +51856,7 @@
       <c r="BO52" s="21"/>
       <c r="BP52" s="114"/>
       <c r="BQ52" s="112"/>
-      <c r="BR52" s="163">
+      <c r="BR52" s="173">
         <v>92</v>
       </c>
       <c r="BS52" s="24" t="str">
@@ -52088,7 +52117,7 @@
         <v>46204.666666666672</v>
       </c>
       <c r="BQ53" s="115"/>
-      <c r="BR53" s="164"/>
+      <c r="BR53" s="174"/>
       <c r="BS53" s="26" t="str">
         <f>IF(BP54&gt;BP55,BL54,IF(BP54&lt;BP55,BL55,""))</f>
         <v>England</v>
@@ -52298,7 +52327,7 @@
         <f>MAX(BH50:BH53)+1</f>
         <v>51.5</v>
       </c>
-      <c r="BK54" s="163">
+      <c r="BK54" s="173">
         <v>80</v>
       </c>
       <c r="BL54" s="24" t="str">
@@ -52425,7 +52454,7 @@
         <f t="shared" si="23"/>
         <v>-1</v>
       </c>
-      <c r="BK55" s="164"/>
+      <c r="BK55" s="174"/>
       <c r="BL55" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!K3,AK80:AS91,9,FALSE),"3rd Group E/H/I/J/K")</f>
         <v>DR Congo</v>
@@ -52454,7 +52483,7 @@
       <c r="CC55" s="21"/>
       <c r="CD55" s="114"/>
       <c r="CE55" s="112"/>
-      <c r="CF55" s="163">
+      <c r="CF55" s="173">
         <v>102</v>
       </c>
       <c r="CG55" s="24" t="str">
@@ -52717,7 +52746,7 @@
       <c r="CC56" s="21"/>
       <c r="CD56" s="114"/>
       <c r="CE56" s="115"/>
-      <c r="CF56" s="164"/>
+      <c r="CF56" s="174"/>
       <c r="CG56" s="26" t="str">
         <f>IF(CD64&gt;CD65,BZ64,IF(CD64&lt;CD65,BZ65,""))</f>
         <v/>
@@ -53208,7 +53237,7 @@
         <f>BH58/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK58" s="163">
+      <c r="BK58" s="173">
         <v>86</v>
       </c>
       <c r="BL58" s="24" t="str">
@@ -53462,7 +53491,7 @@
         <f>BH59/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK59" s="164"/>
+      <c r="BK59" s="174"/>
       <c r="BL59" s="26" t="str">
         <f>AS51</f>
         <v>Cape Verde</v>
@@ -53691,19 +53720,21 @@
       <c r="BO60" s="21"/>
       <c r="BP60" s="114"/>
       <c r="BQ60" s="112"/>
-      <c r="BR60" s="163">
+      <c r="BR60" s="173">
         <v>95</v>
       </c>
       <c r="BS60" s="24" t="str">
         <f>IF(BP58&gt;BP59,BL58,IF(BP58&lt;BP59,BL59,""))</f>
         <v>Argentina</v>
       </c>
-      <c r="BT60" s="61"/>
+      <c r="BT60" s="61">
+        <v>3</v>
+      </c>
       <c r="BU60" s="63"/>
       <c r="BV60" s="25"/>
-      <c r="BW60" s="112" t="str">
+      <c r="BW60" s="112">
         <f>IF(OR(BT60="",BT61="",AND(BU60="",BU61&lt;&gt;""),AND(BU61="",BU60&lt;&gt;""),AND(BV60="",BV61&lt;&gt;""),AND(BV61="",BV60&lt;&gt;"")),"",BT60*1000+BU60*10+BV60)</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="BX60" s="112"/>
       <c r="BY60" s="21"/>
@@ -53808,17 +53839,19 @@
         <v>46206.75</v>
       </c>
       <c r="BQ61" s="115"/>
-      <c r="BR61" s="164"/>
+      <c r="BR61" s="174"/>
       <c r="BS61" s="26" t="str">
         <f>IF(BP62&gt;BP63,BL62,IF(BP62&lt;BP63,BL63,""))</f>
         <v>Egypt</v>
       </c>
-      <c r="BT61" s="62"/>
+      <c r="BT61" s="62">
+        <v>2</v>
+      </c>
       <c r="BU61" s="64"/>
       <c r="BV61" s="27"/>
-      <c r="BW61" s="113" t="str">
+      <c r="BW61" s="113">
         <f>IF(BW60="","",BT61*1000+BU61*10+BV61)</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="BX61" s="112"/>
       <c r="BY61" s="21"/>
@@ -54055,7 +54088,7 @@
         <f>BH62/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK62" s="163">
+      <c r="BK62" s="173">
         <v>88</v>
       </c>
       <c r="BL62" s="24" t="str">
@@ -54313,7 +54346,7 @@
         <f>BH63/BH66</f>
         <v>0.98067632850241548</v>
       </c>
-      <c r="BK63" s="164"/>
+      <c r="BK63" s="174"/>
       <c r="BL63" s="26" t="str">
         <f>AS45</f>
         <v>Egypt</v>
@@ -54585,12 +54618,12 @@
       <c r="BV64" s="21"/>
       <c r="BW64" s="114"/>
       <c r="BX64" s="112"/>
-      <c r="BY64" s="163">
+      <c r="BY64" s="173">
         <v>100</v>
       </c>
       <c r="BZ64" s="24" t="str">
         <f>IF(BW60&gt;BW61,BS60,IF(BW60&lt;BW61,BS61,""))</f>
-        <v/>
+        <v>Argentina</v>
       </c>
       <c r="CA64" s="61"/>
       <c r="CB64" s="63"/>
@@ -54843,10 +54876,10 @@
       <c r="BV65" s="21"/>
       <c r="BW65" s="114"/>
       <c r="BX65" s="115"/>
-      <c r="BY65" s="164"/>
+      <c r="BY65" s="174"/>
       <c r="BZ65" s="26" t="str">
         <f>IF(BW68&gt;BW69,BS68,IF(BW68&lt;BW69,BS69,""))</f>
-        <v/>
+        <v>Switzerland</v>
       </c>
       <c r="CA65" s="62"/>
       <c r="CB65" s="64"/>
@@ -55043,7 +55076,7 @@
         <f>MAX(BH62:BH65)+1</f>
         <v>51.75</v>
       </c>
-      <c r="BK66" s="163">
+      <c r="BK66" s="173">
         <v>85</v>
       </c>
       <c r="BL66" s="24" t="str">
@@ -55149,7 +55182,7 @@
         <f t="shared" si="23"/>
         <v>-1</v>
       </c>
-      <c r="BK67" s="164"/>
+      <c r="BK67" s="174"/>
       <c r="BL67" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!E3,AK80:AS91,9,FALSE),"3rd Group E/F/G/I/J")</f>
         <v>Algeria</v>
@@ -55411,39 +55444,41 @@
       <c r="BO68" s="21"/>
       <c r="BP68" s="114"/>
       <c r="BQ68" s="112"/>
-      <c r="BR68" s="163">
+      <c r="BR68" s="173">
         <v>96</v>
       </c>
       <c r="BS68" s="24" t="str">
         <f>IF(BP66&gt;BP67,BL66,IF(BP66&lt;BP67,BL67,""))</f>
         <v>Switzerland</v>
       </c>
-      <c r="BT68" s="61"/>
+      <c r="BT68" s="61">
+        <v>1</v>
+      </c>
       <c r="BU68" s="63"/>
       <c r="BV68" s="25"/>
-      <c r="BW68" s="116" t="str">
+      <c r="BW68" s="116">
         <f>IF(OR(BT68="",BT69="",AND(BU68="",BU69&lt;&gt;""),AND(BU69="",BU68&lt;&gt;""),AND(BV68="",BV69&lt;&gt;""),AND(BV69="",BV68&lt;&gt;"")),"",BT68*1000+BU68*10+BV68)</f>
-        <v/>
-      </c>
-      <c r="CE68" s="195" t="str">
+        <v>1000</v>
+      </c>
+      <c r="CE68" s="175" t="str">
         <f>INDEX(T,144,lang)</f>
         <v>World Champion 2026</v>
       </c>
-      <c r="CF68" s="195"/>
-      <c r="CG68" s="195"/>
-      <c r="CH68" s="195"/>
-      <c r="CI68" s="195"/>
-      <c r="CJ68" s="195"/>
-      <c r="CK68" s="185" t="str">
+      <c r="CF68" s="175"/>
+      <c r="CG68" s="175"/>
+      <c r="CH68" s="175"/>
+      <c r="CI68" s="175"/>
+      <c r="CJ68" s="175"/>
+      <c r="CK68" s="163" t="str">
         <f>IF(CR37&gt;CR38,CN37,IF(CR37&lt;CR38,CN38,""))</f>
         <v/>
       </c>
-      <c r="CL68" s="185"/>
-      <c r="CM68" s="185"/>
-      <c r="CN68" s="185"/>
-      <c r="CO68" s="185"/>
-      <c r="CP68" s="185"/>
-      <c r="CQ68" s="185"/>
+      <c r="CL68" s="163"/>
+      <c r="CM68" s="163"/>
+      <c r="CN68" s="163"/>
+      <c r="CO68" s="163"/>
+      <c r="CP68" s="163"/>
+      <c r="CQ68" s="163"/>
     </row>
     <row r="69" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A69" s="16">
@@ -55685,31 +55720,33 @@
         <v>46207.0625</v>
       </c>
       <c r="BQ69" s="115"/>
-      <c r="BR69" s="164"/>
+      <c r="BR69" s="174"/>
       <c r="BS69" s="26" t="str">
         <f>IF(BP70&gt;BP71,BL70,IF(BP70&lt;BP71,BL71,""))</f>
         <v>Colombia</v>
       </c>
-      <c r="BT69" s="62"/>
+      <c r="BT69" s="62">
+        <v>0</v>
+      </c>
       <c r="BU69" s="64"/>
       <c r="BV69" s="27"/>
-      <c r="BW69" s="112" t="str">
+      <c r="BW69" s="112">
         <f>IF(BW68="","",BT69*1000+BU69*10+BV69)</f>
-        <v/>
-      </c>
-      <c r="CE69" s="195"/>
-      <c r="CF69" s="195"/>
-      <c r="CG69" s="195"/>
-      <c r="CH69" s="195"/>
-      <c r="CI69" s="195"/>
-      <c r="CJ69" s="195"/>
-      <c r="CK69" s="185"/>
-      <c r="CL69" s="185"/>
-      <c r="CM69" s="185"/>
-      <c r="CN69" s="185"/>
-      <c r="CO69" s="185"/>
-      <c r="CP69" s="185"/>
-      <c r="CQ69" s="185"/>
+        <v>0</v>
+      </c>
+      <c r="CE69" s="175"/>
+      <c r="CF69" s="175"/>
+      <c r="CG69" s="175"/>
+      <c r="CH69" s="175"/>
+      <c r="CI69" s="175"/>
+      <c r="CJ69" s="175"/>
+      <c r="CK69" s="163"/>
+      <c r="CL69" s="163"/>
+      <c r="CM69" s="163"/>
+      <c r="CN69" s="163"/>
+      <c r="CO69" s="163"/>
+      <c r="CP69" s="163"/>
+      <c r="CQ69" s="163"/>
     </row>
     <row r="70" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A70" s="16">
@@ -55934,7 +55971,7 @@
         <f>BH70/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK70" s="163">
+      <c r="BK70" s="173">
         <v>87</v>
       </c>
       <c r="BL70" s="24" t="str">
@@ -56176,7 +56213,7 @@
         <f>BH71/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK71" s="164"/>
+      <c r="BK71" s="174"/>
       <c r="BL71" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!J3,AK80:AS91,9,FALSE),"3rd Group D/E/I/J/L")</f>
         <v>Ghana</v>
@@ -57882,13 +57919,13 @@
     <row r="83" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="73"/>
       <c r="B83" s="73"/>
-      <c r="C83" s="186" t="s">
+      <c r="C83" s="164" t="s">
         <v>3183</v>
       </c>
-      <c r="D83" s="187"/>
-      <c r="E83" s="187"/>
-      <c r="F83" s="187"/>
-      <c r="G83" s="188"/>
+      <c r="D83" s="165"/>
+      <c r="E83" s="165"/>
+      <c r="F83" s="165"/>
+      <c r="G83" s="166"/>
       <c r="H83" s="75"/>
       <c r="I83" s="69"/>
       <c r="J83" s="99" t="str">
@@ -57986,11 +58023,11 @@
     <row r="84" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="73"/>
       <c r="B84" s="73"/>
-      <c r="C84" s="189"/>
-      <c r="D84" s="190"/>
-      <c r="E84" s="190"/>
-      <c r="F84" s="190"/>
-      <c r="G84" s="191"/>
+      <c r="C84" s="167"/>
+      <c r="D84" s="168"/>
+      <c r="E84" s="168"/>
+      <c r="F84" s="168"/>
+      <c r="G84" s="169"/>
       <c r="H84" s="75"/>
       <c r="I84" s="69"/>
       <c r="J84" s="99" t="str">
@@ -58100,11 +58137,11 @@
     <row r="85" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="73"/>
       <c r="B85" s="73"/>
-      <c r="C85" s="189"/>
-      <c r="D85" s="190"/>
-      <c r="E85" s="190"/>
-      <c r="F85" s="190"/>
-      <c r="G85" s="191"/>
+      <c r="C85" s="167"/>
+      <c r="D85" s="168"/>
+      <c r="E85" s="168"/>
+      <c r="F85" s="168"/>
+      <c r="G85" s="169"/>
       <c r="H85" s="75"/>
       <c r="I85" s="69"/>
       <c r="J85" s="99" t="str">
@@ -58214,11 +58251,11 @@
     <row r="86" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="73"/>
       <c r="B86" s="73"/>
-      <c r="C86" s="189"/>
-      <c r="D86" s="190"/>
-      <c r="E86" s="190"/>
-      <c r="F86" s="190"/>
-      <c r="G86" s="191"/>
+      <c r="C86" s="167"/>
+      <c r="D86" s="168"/>
+      <c r="E86" s="168"/>
+      <c r="F86" s="168"/>
+      <c r="G86" s="169"/>
       <c r="H86" s="75"/>
       <c r="I86" s="69"/>
       <c r="J86" s="99" t="str">
@@ -58328,11 +58365,11 @@
     <row r="87" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="73"/>
       <c r="B87" s="73"/>
-      <c r="C87" s="189"/>
-      <c r="D87" s="190"/>
-      <c r="E87" s="190"/>
-      <c r="F87" s="190"/>
-      <c r="G87" s="191"/>
+      <c r="C87" s="167"/>
+      <c r="D87" s="168"/>
+      <c r="E87" s="168"/>
+      <c r="F87" s="168"/>
+      <c r="G87" s="169"/>
       <c r="H87" s="75"/>
       <c r="I87" s="69"/>
       <c r="J87" s="99" t="str">
@@ -58442,11 +58479,11 @@
     <row r="88" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="73"/>
       <c r="B88" s="73"/>
-      <c r="C88" s="192"/>
-      <c r="D88" s="193"/>
-      <c r="E88" s="193"/>
-      <c r="F88" s="193"/>
-      <c r="G88" s="194"/>
+      <c r="C88" s="170"/>
+      <c r="D88" s="171"/>
+      <c r="E88" s="171"/>
+      <c r="F88" s="171"/>
+      <c r="G88" s="172"/>
       <c r="H88" s="75"/>
       <c r="I88" s="69"/>
       <c r="J88" s="99" t="str">
@@ -59037,11 +59074,11 @@
       </c>
       <c r="S98" s="127" t="str">
         <f>IF(OR(BT36="",BT37=""),"",IF(BT36&gt;BT37,BS36,IF(BT36&lt;BT37,BS37,IF(OR(BU36="",BU37=""),"draw",IF(BU36&gt;BU37,BS36,IF(BU36&lt;BU37,BS37,IF(OR(BV36="",BV37=""),"draw",IF(BV36&gt;BV37,BS36,IF(BV36&lt;BV37,BS37,"draw")))))))))</f>
-        <v/>
-      </c>
-      <c r="T98" s="127" cm="1">
+        <v>Belgium</v>
+      </c>
+      <c r="T98" s="127" t="str" cm="1">
         <f t="array" ref="T98">IF(OR(S98="",S98="draw"),INDEX(T,97,lang),S98)</f>
-        <v>0</v>
+        <v>Belgium</v>
       </c>
     </row>
     <row r="102" spans="18:29" x14ac:dyDescent="0.2">
@@ -59124,6 +59161,36 @@
   <sheetProtection algorithmName="SHA-512" hashValue="7nWuIQAsd0NKRlhwUK3tOeNHpTch5B5FULy2gxNNaIdJM5RfhFSMzPcx55y+pmM3d73guUy+p5Y+SvIjJZQRaA==" saltValue="Uw23KnM8csnTioq5H8upCA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <dataConsolidate/>
   <mergeCells count="45">
+    <mergeCell ref="BK14:BK15"/>
+    <mergeCell ref="BY16:BY17"/>
+    <mergeCell ref="BK26:BK27"/>
+    <mergeCell ref="BR28:BR29"/>
+    <mergeCell ref="BK22:BK23"/>
+    <mergeCell ref="CF23:CF24"/>
+    <mergeCell ref="BK18:BK19"/>
+    <mergeCell ref="BR20:BR21"/>
+    <mergeCell ref="CM48:CM49"/>
+    <mergeCell ref="BR44:BR45"/>
+    <mergeCell ref="BK46:BK47"/>
+    <mergeCell ref="BK30:BK31"/>
+    <mergeCell ref="CM44:CQ45"/>
+    <mergeCell ref="BY32:BY33"/>
+    <mergeCell ref="BK38:BK39"/>
+    <mergeCell ref="BK34:BK35"/>
+    <mergeCell ref="BR36:BR37"/>
+    <mergeCell ref="BK42:BK43"/>
+    <mergeCell ref="CM33:CQ34"/>
+    <mergeCell ref="CM37:CM38"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="BR12:BR13"/>
+    <mergeCell ref="BK6:BO7"/>
+    <mergeCell ref="BR6:BV7"/>
+    <mergeCell ref="BY6:CC7"/>
+    <mergeCell ref="CF6:CJ7"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="A5:H6"/>
+    <mergeCell ref="J5:P6"/>
     <mergeCell ref="CK68:CQ69"/>
     <mergeCell ref="C83:G88"/>
     <mergeCell ref="BK70:BK71"/>
@@ -59139,36 +59206,6 @@
     <mergeCell ref="BR52:BR53"/>
     <mergeCell ref="BK54:BK55"/>
     <mergeCell ref="CE68:CJ69"/>
-    <mergeCell ref="CF6:CJ7"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="A5:H6"/>
-    <mergeCell ref="J5:P6"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="BR12:BR13"/>
-    <mergeCell ref="BK6:BO7"/>
-    <mergeCell ref="BR6:BV7"/>
-    <mergeCell ref="BY6:CC7"/>
-    <mergeCell ref="CF23:CF24"/>
-    <mergeCell ref="BK18:BK19"/>
-    <mergeCell ref="BR20:BR21"/>
-    <mergeCell ref="CM48:CM49"/>
-    <mergeCell ref="BR44:BR45"/>
-    <mergeCell ref="BK46:BK47"/>
-    <mergeCell ref="BK30:BK31"/>
-    <mergeCell ref="CM44:CQ45"/>
-    <mergeCell ref="BY32:BY33"/>
-    <mergeCell ref="BK38:BK39"/>
-    <mergeCell ref="BK34:BK35"/>
-    <mergeCell ref="BR36:BR37"/>
-    <mergeCell ref="BK42:BK43"/>
-    <mergeCell ref="CM33:CQ34"/>
-    <mergeCell ref="CM37:CM38"/>
-    <mergeCell ref="BK14:BK15"/>
-    <mergeCell ref="BY16:BY17"/>
-    <mergeCell ref="BK26:BK27"/>
-    <mergeCell ref="BR28:BR29"/>
-    <mergeCell ref="BK22:BK23"/>
   </mergeCells>
   <conditionalFormatting sqref="A7:E78">
     <cfRule type="expression" dxfId="228" priority="339">

--- a/public/worldcup.xlsx
+++ b/public/worldcup.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rylanpaul/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DB22C1C-201B-AE4B-AAC8-4D762A6904D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B7DA1BF-E6BC-294B-A658-997E9685B5DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9910" uniqueCount="3716">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9921" uniqueCount="3716">
   <si>
     <t>English</t>
   </si>
@@ -13308,56 +13308,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -13438,6 +13394,50 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -38772,29 +38772,35 @@
       <c r="V3" t="s">
         <v>1633</v>
       </c>
-      <c r="W3" s="142" t="e">
+      <c r="W3" s="142">
         <f>IFERROR(_xlfn.XLOOKUP(V3,Rounds!U$2:U$5,Rounds!V$2:V$5), _xlfn.XLOOKUP(V3,Rounds!X$2:X$5,Rounds!W$2:W$5))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="X3" s="142" t="e">
+        <v>1</v>
+      </c>
+      <c r="X3" s="142">
         <f>IFERROR(_xlfn.XLOOKUP(V3,Rounds!U$2:U$5,Rounds!W$2:W$5), _xlfn.XLOOKUP(V3,Rounds!X$2:X$5,Rounds!V$2:V$5))</f>
-        <v>#N/A</v>
+        <v>2</v>
       </c>
       <c r="Y3" s="140" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(V3,Rounds!U$2:U$5,Rounds!X$2:X$5), _xlfn.XLOOKUP(V3,Rounds!X$2:X$5,Rounds!U$2:U$5))</f>
         <v>Spain</v>
       </c>
-      <c r="AA3" s="142" t="e">
+      <c r="Z3" t="s">
+        <v>1384</v>
+      </c>
+      <c r="AA3" s="142">
         <f>IFERROR(_xlfn.XLOOKUP(Z3,Rounds!Y$2:Y$3,Rounds!Z$2:Z$3), _xlfn.XLOOKUP(Z3,Rounds!AB$2:AB$3,Rounds!AA$2:AA$3))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AB3" s="142" t="e">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="142">
         <f>IFERROR(_xlfn.XLOOKUP(Z3,Rounds!Y$2:Y$3,Rounds!AA$2:AA$3), _xlfn.XLOOKUP(Z3,Rounds!AB$2:AB$3,Rounds!Z$2:Z$3))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AC3" s="140" t="e">
+        <v>2</v>
+      </c>
+      <c r="AC3" s="140" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(Z3,Rounds!Y$2:Y$3,Rounds!AB$2:AB$3), _xlfn.XLOOKUP(Z3,Rounds!AB$2:AB$3,Rounds!Y$2:Y$3))</f>
-        <v>#N/A</v>
+        <v>Spain</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>1264</v>
       </c>
       <c r="AE3" s="142" t="e" cm="1">
         <f t="array" ref="AE3">IFERROR(_xlfn.XLOOKUP(AD3,Rounds!AC$2:AC$2,Rounds!AD$2:AD$2), _xlfn.XLOOKUP(AD3,Rounds!AF$2:AF$2,Rounds!AE$2:AE$2))</f>
@@ -38804,9 +38810,9 @@
         <f t="array" ref="AF3">IFERROR(_xlfn.XLOOKUP(AD3,Rounds!AC$2:AC$2,Rounds!AE$2:AE$2), _xlfn.XLOOKUP(AD3,Rounds!AF$2:AF$2,Rounds!AD$2:AD$2))</f>
         <v>#N/A</v>
       </c>
-      <c r="AG3" s="140" t="e" cm="1">
+      <c r="AG3" s="140" t="str" cm="1">
         <f t="array" ref="AG3">IFERROR(_xlfn.XLOOKUP(AD3,Rounds!AC$2:AC$2,Rounds!AF$2:AF$2), _xlfn.XLOOKUP(AD3,Rounds!AF$2:AF$2,Rounds!AC$2:AC$2))</f>
-        <v>#N/A</v>
+        <v>Spain</v>
       </c>
     </row>
     <row r="4" spans="1:33" s="148" customFormat="1" x14ac:dyDescent="0.2">
@@ -38891,29 +38897,35 @@
       <c r="V4" s="148" t="s">
         <v>2395</v>
       </c>
-      <c r="W4" s="146" t="e">
+      <c r="W4" s="146">
         <f>IFERROR(_xlfn.XLOOKUP(V4,Rounds!U$2:U$5,Rounds!V$2:V$5), _xlfn.XLOOKUP(V4,Rounds!X$2:X$5,Rounds!W$2:W$5))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="X4" s="146" t="e">
+        <v>1</v>
+      </c>
+      <c r="X4" s="146">
         <f>IFERROR(_xlfn.XLOOKUP(V4,Rounds!U$2:U$5,Rounds!W$2:W$5), _xlfn.XLOOKUP(V4,Rounds!X$2:X$5,Rounds!V$2:V$5))</f>
-        <v>#N/A</v>
+        <v>2</v>
       </c>
       <c r="Y4" s="147" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(V4,Rounds!U$2:U$5,Rounds!X$2:X$5), _xlfn.XLOOKUP(V4,Rounds!X$2:X$5,Rounds!U$2:U$5))</f>
         <v>England</v>
       </c>
-      <c r="AA4" s="146" t="e">
+      <c r="Z4" s="148" t="s">
+        <v>1264</v>
+      </c>
+      <c r="AA4" s="146">
         <f>IFERROR(_xlfn.XLOOKUP(Z4,Rounds!Y$2:Y$3,Rounds!Z$2:Z$3), _xlfn.XLOOKUP(Z4,Rounds!AB$2:AB$3,Rounds!AA$2:AA$3))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AB4" s="146" t="e">
+        <v>2</v>
+      </c>
+      <c r="AB4" s="146">
         <f>IFERROR(_xlfn.XLOOKUP(Z4,Rounds!Y$2:Y$3,Rounds!AA$2:AA$3), _xlfn.XLOOKUP(Z4,Rounds!AB$2:AB$3,Rounds!Z$2:Z$3))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AC4" s="147" t="e">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="147" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(Z4,Rounds!Y$2:Y$3,Rounds!AB$2:AB$3), _xlfn.XLOOKUP(Z4,Rounds!AB$2:AB$3,Rounds!Y$2:Y$3))</f>
-        <v>#N/A</v>
+        <v>England</v>
+      </c>
+      <c r="AD4" s="148" t="s">
+        <v>1508</v>
       </c>
       <c r="AE4" s="146" t="e" cm="1">
         <f t="array" ref="AE4">IFERROR(_xlfn.XLOOKUP(AD4,Rounds!AC$2:AC$2,Rounds!AD$2:AD$2), _xlfn.XLOOKUP(AD4,Rounds!AF$2:AF$2,Rounds!AE$2:AE$2))</f>
@@ -38923,9 +38935,9 @@
         <f t="array" ref="AF4">IFERROR(_xlfn.XLOOKUP(AD4,Rounds!AC$2:AC$2,Rounds!AE$2:AE$2), _xlfn.XLOOKUP(AD4,Rounds!AF$2:AF$2,Rounds!AD$2:AD$2))</f>
         <v>#N/A</v>
       </c>
-      <c r="AG4" s="147" t="e" cm="1">
+      <c r="AG4" s="147" t="str" cm="1">
         <f t="array" ref="AG4">IFERROR(_xlfn.XLOOKUP(AD4,Rounds!AC$2:AC$2,Rounds!AF$2:AF$2), _xlfn.XLOOKUP(AD4,Rounds!AF$2:AF$2,Rounds!AC$2:AC$2))</f>
-        <v>#N/A</v>
+        <v>Argentina</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.2">
@@ -39010,29 +39022,35 @@
       <c r="V5" t="s">
         <v>1264</v>
       </c>
-      <c r="W5" s="82" t="e">
+      <c r="W5" s="82">
         <f>IFERROR(_xlfn.XLOOKUP(V5,Rounds!U$2:U$5,Rounds!V$2:V$5), _xlfn.XLOOKUP(V5,Rounds!X$2:X$5,Rounds!W$2:W$5))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="X5" s="82" t="e">
+        <v>3</v>
+      </c>
+      <c r="X5" s="82">
         <f>IFERROR(_xlfn.XLOOKUP(V5,Rounds!U$2:U$5,Rounds!W$2:W$5), _xlfn.XLOOKUP(V5,Rounds!X$2:X$5,Rounds!V$2:V$5))</f>
-        <v>#N/A</v>
+        <v>1</v>
       </c>
       <c r="Y5" s="134" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(V5,Rounds!U$2:U$5,Rounds!X$2:X$5), _xlfn.XLOOKUP(V5,Rounds!X$2:X$5,Rounds!U$2:U$5))</f>
         <v>Switzerland</v>
       </c>
-      <c r="AA5" s="82" t="e">
+      <c r="Z5" t="s">
+        <v>1148</v>
+      </c>
+      <c r="AA5" s="82">
         <f>IFERROR(_xlfn.XLOOKUP(Z5,Rounds!Y$2:Y$3,Rounds!Z$2:Z$3), _xlfn.XLOOKUP(Z5,Rounds!AB$2:AB$3,Rounds!AA$2:AA$3))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AB5" s="82" t="e">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="82">
         <f>IFERROR(_xlfn.XLOOKUP(Z5,Rounds!Y$2:Y$3,Rounds!AA$2:AA$3), _xlfn.XLOOKUP(Z5,Rounds!AB$2:AB$3,Rounds!Z$2:Z$3))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AC5" s="134" t="e">
+        <v>2</v>
+      </c>
+      <c r="AC5" s="134" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(Z5,Rounds!Y$2:Y$3,Rounds!AB$2:AB$3), _xlfn.XLOOKUP(Z5,Rounds!AB$2:AB$3,Rounds!Y$2:Y$3))</f>
-        <v>#N/A</v>
+        <v>Argentina</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>1508</v>
       </c>
       <c r="AE5" s="82" t="e" cm="1">
         <f t="array" ref="AE5">IFERROR(_xlfn.XLOOKUP(AD5,Rounds!AC$2:AC$2,Rounds!AD$2:AD$2), _xlfn.XLOOKUP(AD5,Rounds!AF$2:AF$2,Rounds!AE$2:AE$2))</f>
@@ -39042,9 +39060,9 @@
         <f t="array" ref="AF5">IFERROR(_xlfn.XLOOKUP(AD5,Rounds!AC$2:AC$2,Rounds!AE$2:AE$2), _xlfn.XLOOKUP(AD5,Rounds!AF$2:AF$2,Rounds!AD$2:AD$2))</f>
         <v>#N/A</v>
       </c>
-      <c r="AG5" s="134" t="e" cm="1">
+      <c r="AG5" s="134" t="str" cm="1">
         <f t="array" ref="AG5">IFERROR(_xlfn.XLOOKUP(AD5,Rounds!AC$2:AC$2,Rounds!AF$2:AF$2), _xlfn.XLOOKUP(AD5,Rounds!AF$2:AF$2,Rounds!AC$2:AC$2))</f>
-        <v>#N/A</v>
+        <v>Argentina</v>
       </c>
     </row>
     <row r="6" spans="1:33" s="148" customFormat="1" x14ac:dyDescent="0.2">
@@ -39129,29 +39147,35 @@
       <c r="V6" s="148" t="s">
         <v>1508</v>
       </c>
-      <c r="W6" s="146" t="e">
+      <c r="W6" s="146">
         <f>IFERROR(_xlfn.XLOOKUP(V6,Rounds!U$2:U$5,Rounds!V$2:V$5), _xlfn.XLOOKUP(V6,Rounds!X$2:X$5,Rounds!W$2:W$5))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="X6" s="146" t="e">
+        <v>2</v>
+      </c>
+      <c r="X6" s="146">
         <f>IFERROR(_xlfn.XLOOKUP(V6,Rounds!U$2:U$5,Rounds!W$2:W$5), _xlfn.XLOOKUP(V6,Rounds!X$2:X$5,Rounds!V$2:V$5))</f>
-        <v>#N/A</v>
+        <v>1</v>
       </c>
       <c r="Y6" s="147" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(V6,Rounds!U$2:U$5,Rounds!X$2:X$5), _xlfn.XLOOKUP(V6,Rounds!X$2:X$5,Rounds!U$2:U$5))</f>
         <v>Belgium</v>
       </c>
-      <c r="AA6" s="146" t="e">
+      <c r="Z6" s="148" t="s">
+        <v>1148</v>
+      </c>
+      <c r="AA6" s="146">
         <f>IFERROR(_xlfn.XLOOKUP(Z6,Rounds!Y$2:Y$3,Rounds!Z$2:Z$3), _xlfn.XLOOKUP(Z6,Rounds!AB$2:AB$3,Rounds!AA$2:AA$3))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AB6" s="146" t="e">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="146">
         <f>IFERROR(_xlfn.XLOOKUP(Z6,Rounds!Y$2:Y$3,Rounds!AA$2:AA$3), _xlfn.XLOOKUP(Z6,Rounds!AB$2:AB$3,Rounds!Z$2:Z$3))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AC6" s="147" t="e">
+        <v>2</v>
+      </c>
+      <c r="AC6" s="147" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(Z6,Rounds!Y$2:Y$3,Rounds!AB$2:AB$3), _xlfn.XLOOKUP(Z6,Rounds!AB$2:AB$3,Rounds!Y$2:Y$3))</f>
-        <v>#N/A</v>
+        <v>Argentina</v>
+      </c>
+      <c r="AD6" s="148" t="s">
+        <v>1264</v>
       </c>
       <c r="AE6" s="146" t="e" cm="1">
         <f t="array" ref="AE6">IFERROR(_xlfn.XLOOKUP(AD6,Rounds!AC$2:AC$2,Rounds!AD$2:AD$2), _xlfn.XLOOKUP(AD6,Rounds!AF$2:AF$2,Rounds!AE$2:AE$2))</f>
@@ -39161,9 +39185,9 @@
         <f t="array" ref="AF6">IFERROR(_xlfn.XLOOKUP(AD6,Rounds!AC$2:AC$2,Rounds!AE$2:AE$2), _xlfn.XLOOKUP(AD6,Rounds!AF$2:AF$2,Rounds!AD$2:AD$2))</f>
         <v>#N/A</v>
       </c>
-      <c r="AG6" s="147" t="e" cm="1">
+      <c r="AG6" s="147" t="str" cm="1">
         <f t="array" ref="AG6">IFERROR(_xlfn.XLOOKUP(AD6,Rounds!AC$2:AC$2,Rounds!AF$2:AF$2), _xlfn.XLOOKUP(AD6,Rounds!AF$2:AF$2,Rounds!AC$2:AC$2))</f>
-        <v>#N/A</v>
+        <v>Spain</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.2">
@@ -39248,29 +39272,32 @@
       <c r="V7" t="s">
         <v>1264</v>
       </c>
-      <c r="W7" s="82" t="e">
+      <c r="W7" s="82">
         <f>IFERROR(_xlfn.XLOOKUP(V7,Rounds!U$2:U$5,Rounds!V$2:V$5), _xlfn.XLOOKUP(V7,Rounds!X$2:X$5,Rounds!W$2:W$5))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="X7" s="82" t="e">
+        <v>3</v>
+      </c>
+      <c r="X7" s="82">
         <f>IFERROR(_xlfn.XLOOKUP(V7,Rounds!U$2:U$5,Rounds!W$2:W$5), _xlfn.XLOOKUP(V7,Rounds!X$2:X$5,Rounds!V$2:V$5))</f>
-        <v>#N/A</v>
+        <v>1</v>
       </c>
       <c r="Y7" s="134" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(V7,Rounds!U$2:U$5,Rounds!X$2:X$5), _xlfn.XLOOKUP(V7,Rounds!X$2:X$5,Rounds!U$2:U$5))</f>
         <v>Switzerland</v>
       </c>
-      <c r="AA7" s="82" t="e">
+      <c r="Z7" t="s">
+        <v>1384</v>
+      </c>
+      <c r="AA7" s="82">
         <f>IFERROR(_xlfn.XLOOKUP(Z7,Rounds!Y$2:Y$3,Rounds!Z$2:Z$3), _xlfn.XLOOKUP(Z7,Rounds!AB$2:AB$3,Rounds!AA$2:AA$3))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AB7" s="82" t="e">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="82">
         <f>IFERROR(_xlfn.XLOOKUP(Z7,Rounds!Y$2:Y$3,Rounds!AA$2:AA$3), _xlfn.XLOOKUP(Z7,Rounds!AB$2:AB$3,Rounds!Z$2:Z$3))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AC7" s="134" t="e">
+        <v>2</v>
+      </c>
+      <c r="AC7" s="134" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(Z7,Rounds!Y$2:Y$3,Rounds!AB$2:AB$3), _xlfn.XLOOKUP(Z7,Rounds!AB$2:AB$3,Rounds!Y$2:Y$3))</f>
-        <v>#N/A</v>
+        <v>Spain</v>
       </c>
       <c r="AE7" s="82" t="e" cm="1">
         <f t="array" ref="AE7">IFERROR(_xlfn.XLOOKUP(AD7,Rounds!AC$2:AC$2,Rounds!AD$2:AD$2), _xlfn.XLOOKUP(AD7,Rounds!AF$2:AF$2,Rounds!AE$2:AE$2))</f>
@@ -39367,32 +39394,36 @@
       <c r="V8" s="152" t="s">
         <v>2395</v>
       </c>
-      <c r="W8" s="150" t="e">
+      <c r="W8" s="150">
         <f>IFERROR(_xlfn.XLOOKUP(V8,Rounds!U$2:U$5,Rounds!V$2:V$5), _xlfn.XLOOKUP(V8,Rounds!X$2:X$5,Rounds!W$2:W$5))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="X8" s="150" t="e">
+        <v>1</v>
+      </c>
+      <c r="X8" s="150">
         <f>IFERROR(_xlfn.XLOOKUP(V8,Rounds!U$2:U$5,Rounds!W$2:W$5), _xlfn.XLOOKUP(V8,Rounds!X$2:X$5,Rounds!V$2:V$5))</f>
-        <v>#N/A</v>
+        <v>2</v>
       </c>
       <c r="Y8" s="151" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(V8,Rounds!U$2:U$5,Rounds!X$2:X$5), _xlfn.XLOOKUP(V8,Rounds!X$2:X$5,Rounds!U$2:U$5))</f>
         <v>England</v>
       </c>
-      <c r="Z8" s="152"/>
-      <c r="AA8" s="150" t="e">
+      <c r="Z8" s="152" t="s">
+        <v>1508</v>
+      </c>
+      <c r="AA8" s="150">
         <f>IFERROR(_xlfn.XLOOKUP(Z8,Rounds!Y$2:Y$3,Rounds!Z$2:Z$3), _xlfn.XLOOKUP(Z8,Rounds!AB$2:AB$3,Rounds!AA$2:AA$3))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AB8" s="150" t="e">
+        <v>2</v>
+      </c>
+      <c r="AB8" s="150">
         <f>IFERROR(_xlfn.XLOOKUP(Z8,Rounds!Y$2:Y$3,Rounds!AA$2:AA$3), _xlfn.XLOOKUP(Z8,Rounds!AB$2:AB$3,Rounds!Z$2:Z$3))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AC8" s="151" t="e">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="151" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(Z8,Rounds!Y$2:Y$3,Rounds!AB$2:AB$3), _xlfn.XLOOKUP(Z8,Rounds!AB$2:AB$3,Rounds!Y$2:Y$3))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AD8" s="152"/>
+        <v>France</v>
+      </c>
+      <c r="AD8" s="152" t="s">
+        <v>1264</v>
+      </c>
       <c r="AE8" s="150" t="e" cm="1">
         <f t="array" ref="AE8">IFERROR(_xlfn.XLOOKUP(AD8,Rounds!AC$2:AC$2,Rounds!AD$2:AD$2), _xlfn.XLOOKUP(AD8,Rounds!AF$2:AF$2,Rounds!AE$2:AE$2))</f>
         <v>#N/A</v>
@@ -39401,9 +39432,9 @@
         <f t="array" ref="AF8">IFERROR(_xlfn.XLOOKUP(AD8,Rounds!AC$2:AC$2,Rounds!AE$2:AE$2), _xlfn.XLOOKUP(AD8,Rounds!AF$2:AF$2,Rounds!AD$2:AD$2))</f>
         <v>#N/A</v>
       </c>
-      <c r="AG8" s="151" t="e" cm="1">
+      <c r="AG8" s="151" t="str" cm="1">
         <f t="array" ref="AG8">IFERROR(_xlfn.XLOOKUP(AD8,Rounds!AC$2:AC$2,Rounds!AF$2:AF$2), _xlfn.XLOOKUP(AD8,Rounds!AF$2:AF$2,Rounds!AC$2:AC$2))</f>
-        <v>#N/A</v>
+        <v>Spain</v>
       </c>
     </row>
     <row r="18" spans="14:14" x14ac:dyDescent="0.2">
@@ -39608,13 +39639,13 @@
         <f>'2026 World Cup'!BZ16</f>
         <v>France</v>
       </c>
-      <c r="V2" s="81" t="e">
+      <c r="V2" s="81">
         <f>IF('2026 World Cup'!$CA16="",NA(),'2026 World Cup'!$CA16)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W2" s="81" t="e">
+        <v>2</v>
+      </c>
+      <c r="W2" s="81">
         <f>IF('2026 World Cup'!$CA17="",NA(),'2026 World Cup'!$CA17)</f>
-        <v>#N/A</v>
+        <v>0</v>
       </c>
       <c r="X2" s="134" t="str">
         <f>'2026 World Cup'!BZ17</f>
@@ -39622,23 +39653,23 @@
       </c>
       <c r="Y2" s="132" t="str">
         <f>'2026 World Cup'!CG23</f>
-        <v/>
-      </c>
-      <c r="Z2" s="81" t="e">
+        <v>France</v>
+      </c>
+      <c r="Z2" s="81">
         <f>IF('2026 World Cup'!$CH23="",NA(),'2026 World Cup'!$CH23)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AA2" s="81" t="e">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="81">
         <f>IF('2026 World Cup'!$CH24="",NA(),'2026 World Cup'!$CH24)</f>
-        <v>#N/A</v>
+        <v>2</v>
       </c>
       <c r="AB2" s="134" t="str">
         <f>'2026 World Cup'!CG24</f>
-        <v/>
+        <v>Spain</v>
       </c>
       <c r="AC2" s="135" t="str">
         <f>'2026 World Cup'!CN37</f>
-        <v/>
+        <v>Spain</v>
       </c>
       <c r="AD2" s="153" t="e">
         <f>IF('2026 World Cup'!$CO37="",NA(),'2026 World Cup'!$CO37)</f>
@@ -39650,7 +39681,7 @@
       </c>
       <c r="AF2" s="136" t="str">
         <f>'2026 World Cup'!CN38</f>
-        <v/>
+        <v>Argentina</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.2">
@@ -39726,13 +39757,13 @@
         <f>'2026 World Cup'!BZ32</f>
         <v>Spain</v>
       </c>
-      <c r="V3" s="81" t="e">
+      <c r="V3" s="81">
         <f>IF('2026 World Cup'!$CA32="",NA(),'2026 World Cup'!$CA32)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W3" s="81" t="e">
+        <v>2</v>
+      </c>
+      <c r="W3" s="81">
         <f>IF('2026 World Cup'!$CA33="",NA(),'2026 World Cup'!$CA33)</f>
-        <v>#N/A</v>
+        <v>1</v>
       </c>
       <c r="X3" s="134" t="str">
         <f>'2026 World Cup'!BZ33</f>
@@ -39740,19 +39771,19 @@
       </c>
       <c r="Y3" s="135" t="str">
         <f>'2026 World Cup'!CG55</f>
-        <v/>
-      </c>
-      <c r="Z3" s="153" t="e">
+        <v>England</v>
+      </c>
+      <c r="Z3" s="153">
         <f>IF('2026 World Cup'!$CH55="",NA(),'2026 World Cup'!$CH55)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AA3" s="153" t="e">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="153">
         <f>IF('2026 World Cup'!$CH56="",NA(),'2026 World Cup'!$CH56)</f>
-        <v>#N/A</v>
+        <v>2</v>
       </c>
       <c r="AB3" s="136" t="str">
         <f>'2026 World Cup'!CG56</f>
-        <v/>
+        <v>Argentina</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.2">
@@ -39828,13 +39859,13 @@
         <f>'2026 World Cup'!BZ48</f>
         <v>Norway</v>
       </c>
-      <c r="V4" s="81" t="e">
+      <c r="V4" s="81">
         <f>IF('2026 World Cup'!$CA48="",NA(),'2026 World Cup'!$CA48)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W4" s="81" t="e">
+        <v>1</v>
+      </c>
+      <c r="W4" s="81">
         <f>IF('2026 World Cup'!$CA49="",NA(),'2026 World Cup'!$CA49)</f>
-        <v>#N/A</v>
+        <v>2</v>
       </c>
       <c r="X4" s="134" t="str">
         <f>'2026 World Cup'!BZ49</f>
@@ -39914,13 +39945,13 @@
         <f>'2026 World Cup'!BZ64</f>
         <v>Argentina</v>
       </c>
-      <c r="V5" s="153" t="e">
+      <c r="V5" s="153">
         <f>IF('2026 World Cup'!$CA64="",NA(),'2026 World Cup'!$CA64)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W5" s="153" t="e">
+        <v>3</v>
+      </c>
+      <c r="W5" s="153">
         <f>IF('2026 World Cup'!$CA65="",NA(),'2026 World Cup'!$CA65)</f>
-        <v>#N/A</v>
+        <v>1</v>
       </c>
       <c r="X5" s="136" t="str">
         <f>'2026 World Cup'!BZ65</f>
@@ -41023,25 +41054,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:95" ht="47" x14ac:dyDescent="0.2">
-      <c r="A1" s="182" t="str" cm="1">
+      <c r="A1" s="171" t="str" cm="1">
         <f t="array" ref="A1">INDEX(T,2,lang)</f>
         <v>2026 World Cup Final Tournament Schedule</v>
       </c>
-      <c r="B1" s="182"/>
-      <c r="C1" s="182"/>
-      <c r="D1" s="182"/>
-      <c r="E1" s="182"/>
-      <c r="F1" s="182"/>
-      <c r="G1" s="182"/>
-      <c r="H1" s="182"/>
-      <c r="I1" s="182"/>
-      <c r="J1" s="182"/>
-      <c r="K1" s="182"/>
-      <c r="L1" s="182"/>
-      <c r="M1" s="182"/>
-      <c r="N1" s="182"/>
-      <c r="O1" s="182"/>
-      <c r="P1" s="182"/>
+      <c r="B1" s="171"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="171"/>
+      <c r="F1" s="171"/>
+      <c r="G1" s="171"/>
+      <c r="H1" s="171"/>
+      <c r="I1" s="171"/>
+      <c r="J1" s="171"/>
+      <c r="K1" s="171"/>
+      <c r="L1" s="171"/>
+      <c r="M1" s="171"/>
+      <c r="N1" s="171"/>
+      <c r="O1" s="171"/>
+      <c r="P1" s="171"/>
       <c r="S1" s="123"/>
       <c r="T1" s="123"/>
       <c r="AC1" s="123"/>
@@ -41088,11 +41119,11 @@
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
-      <c r="O3" s="183" t="str">
+      <c r="O3" s="172" t="str">
         <f>"Language: " &amp; Settings!C4</f>
         <v>Language: English</v>
       </c>
-      <c r="P3" s="183"/>
+      <c r="P3" s="172"/>
       <c r="S3" s="123"/>
       <c r="T3" s="123"/>
       <c r="AC3" s="123"/>
@@ -41110,43 +41141,43 @@
     </row>
     <row r="4" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:95" x14ac:dyDescent="0.2">
-      <c r="A5" s="184" t="str" cm="1">
+      <c r="A5" s="173" t="str" cm="1">
         <f t="array" ref="A5">INDEX(T,3,lang)</f>
         <v>Group Stage</v>
       </c>
-      <c r="B5" s="185"/>
-      <c r="C5" s="185"/>
-      <c r="D5" s="185"/>
-      <c r="E5" s="185"/>
-      <c r="F5" s="185"/>
-      <c r="G5" s="185"/>
-      <c r="H5" s="186"/>
-      <c r="J5" s="190" t="s">
+      <c r="B5" s="174"/>
+      <c r="C5" s="174"/>
+      <c r="D5" s="174"/>
+      <c r="E5" s="174"/>
+      <c r="F5" s="174"/>
+      <c r="G5" s="174"/>
+      <c r="H5" s="175"/>
+      <c r="J5" s="179" t="s">
         <v>3166</v>
       </c>
-      <c r="K5" s="191"/>
-      <c r="L5" s="191"/>
-      <c r="M5" s="191"/>
-      <c r="N5" s="191"/>
-      <c r="O5" s="191"/>
-      <c r="P5" s="192"/>
+      <c r="K5" s="180"/>
+      <c r="L5" s="180"/>
+      <c r="M5" s="180"/>
+      <c r="N5" s="180"/>
+      <c r="O5" s="180"/>
+      <c r="P5" s="181"/>
     </row>
     <row r="6" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="187"/>
-      <c r="B6" s="188"/>
-      <c r="C6" s="188"/>
-      <c r="D6" s="188"/>
-      <c r="E6" s="188"/>
-      <c r="F6" s="188"/>
-      <c r="G6" s="188"/>
-      <c r="H6" s="189"/>
-      <c r="J6" s="193"/>
-      <c r="K6" s="194"/>
-      <c r="L6" s="194"/>
-      <c r="M6" s="194"/>
-      <c r="N6" s="194"/>
-      <c r="O6" s="194"/>
-      <c r="P6" s="195"/>
+      <c r="A6" s="176"/>
+      <c r="B6" s="177"/>
+      <c r="C6" s="177"/>
+      <c r="D6" s="177"/>
+      <c r="E6" s="177"/>
+      <c r="F6" s="177"/>
+      <c r="G6" s="177"/>
+      <c r="H6" s="178"/>
+      <c r="J6" s="182"/>
+      <c r="K6" s="183"/>
+      <c r="L6" s="183"/>
+      <c r="M6" s="183"/>
+      <c r="N6" s="183"/>
+      <c r="O6" s="183"/>
+      <c r="P6" s="184"/>
       <c r="R6" s="123" t="s">
         <v>3167</v>
       </c>
@@ -41256,37 +41287,37 @@
       <c r="BI6" s="128" t="s">
         <v>3178</v>
       </c>
-      <c r="BK6" s="176" t="s">
+      <c r="BK6" s="165" t="s">
         <v>3179</v>
       </c>
-      <c r="BL6" s="177"/>
-      <c r="BM6" s="177"/>
-      <c r="BN6" s="177"/>
-      <c r="BO6" s="178"/>
-      <c r="BR6" s="176" t="str" cm="1">
+      <c r="BL6" s="166"/>
+      <c r="BM6" s="166"/>
+      <c r="BN6" s="166"/>
+      <c r="BO6" s="167"/>
+      <c r="BR6" s="165" t="str" cm="1">
         <f t="array" ref="BR6">INDEX(T,4,lang)</f>
         <v>Round of 16</v>
       </c>
-      <c r="BS6" s="177"/>
-      <c r="BT6" s="177"/>
-      <c r="BU6" s="177"/>
-      <c r="BV6" s="178"/>
-      <c r="BY6" s="176" t="str" cm="1">
+      <c r="BS6" s="166"/>
+      <c r="BT6" s="166"/>
+      <c r="BU6" s="166"/>
+      <c r="BV6" s="167"/>
+      <c r="BY6" s="165" t="str" cm="1">
         <f t="array" ref="BY6">INDEX(T,5,lang)</f>
         <v>Quarterfinals</v>
       </c>
-      <c r="BZ6" s="177"/>
-      <c r="CA6" s="177"/>
-      <c r="CB6" s="177"/>
-      <c r="CC6" s="178"/>
-      <c r="CF6" s="176" t="str" cm="1">
+      <c r="BZ6" s="166"/>
+      <c r="CA6" s="166"/>
+      <c r="CB6" s="166"/>
+      <c r="CC6" s="167"/>
+      <c r="CF6" s="165" t="str" cm="1">
         <f t="array" ref="CF6">INDEX(T,6,lang)</f>
         <v>Semi-Finals</v>
       </c>
-      <c r="CG6" s="177"/>
-      <c r="CH6" s="177"/>
-      <c r="CI6" s="177"/>
-      <c r="CJ6" s="178"/>
+      <c r="CG6" s="166"/>
+      <c r="CH6" s="166"/>
+      <c r="CI6" s="166"/>
+      <c r="CJ6" s="167"/>
     </row>
     <row r="7" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="11">
@@ -41363,26 +41394,26 @@
         <v>1</v>
       </c>
       <c r="AY7" s="126"/>
-      <c r="BK7" s="179"/>
-      <c r="BL7" s="180"/>
-      <c r="BM7" s="180"/>
-      <c r="BN7" s="180"/>
-      <c r="BO7" s="181"/>
-      <c r="BR7" s="179"/>
-      <c r="BS7" s="180"/>
-      <c r="BT7" s="180"/>
-      <c r="BU7" s="180"/>
-      <c r="BV7" s="181"/>
-      <c r="BY7" s="179"/>
-      <c r="BZ7" s="180"/>
-      <c r="CA7" s="180"/>
-      <c r="CB7" s="180"/>
-      <c r="CC7" s="181"/>
-      <c r="CF7" s="179"/>
-      <c r="CG7" s="180"/>
-      <c r="CH7" s="180"/>
-      <c r="CI7" s="180"/>
-      <c r="CJ7" s="181"/>
+      <c r="BK7" s="168"/>
+      <c r="BL7" s="169"/>
+      <c r="BM7" s="169"/>
+      <c r="BN7" s="169"/>
+      <c r="BO7" s="170"/>
+      <c r="BR7" s="168"/>
+      <c r="BS7" s="169"/>
+      <c r="BT7" s="169"/>
+      <c r="BU7" s="169"/>
+      <c r="BV7" s="170"/>
+      <c r="BY7" s="168"/>
+      <c r="BZ7" s="169"/>
+      <c r="CA7" s="169"/>
+      <c r="CB7" s="169"/>
+      <c r="CC7" s="170"/>
+      <c r="CF7" s="168"/>
+      <c r="CG7" s="169"/>
+      <c r="CH7" s="169"/>
+      <c r="CI7" s="169"/>
+      <c r="CJ7" s="170"/>
     </row>
     <row r="8" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A8" s="16">
@@ -42118,7 +42149,7 @@
         <f>BH10/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK10" s="173">
+      <c r="BK10" s="163">
         <v>74</v>
       </c>
       <c r="BL10" s="24" t="str">
@@ -42383,7 +42414,7 @@
         <f>BH11/BH12</f>
         <v>0</v>
       </c>
-      <c r="BK11" s="174"/>
+      <c r="BK11" s="164"/>
       <c r="BL11" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!G3,AK80:AS91,9,FALSE),"3rd Group A/B/C/D/F")</f>
         <v>Paraguay</v>
@@ -42623,7 +42654,7 @@
       <c r="BO12" s="21"/>
       <c r="BP12" s="114"/>
       <c r="BQ12" s="112"/>
-      <c r="BR12" s="173">
+      <c r="BR12" s="163">
         <v>89</v>
       </c>
       <c r="BS12" s="24" t="str">
@@ -42746,7 +42777,7 @@
         <v>46203.875</v>
       </c>
       <c r="BQ13" s="115"/>
-      <c r="BR13" s="174"/>
+      <c r="BR13" s="164"/>
       <c r="BS13" s="26" t="str">
         <f>IF(BP14&gt;BP15,BL14,IF(BP14&lt;BP15,BL15,""))</f>
         <v>France</v>
@@ -43006,7 +43037,7 @@
         <f>BH14/BH18</f>
         <v>0.98058252427184467</v>
       </c>
-      <c r="BK14" s="173">
+      <c r="BK14" s="163">
         <v>77</v>
       </c>
       <c r="BL14" s="24" t="str">
@@ -43275,7 +43306,7 @@
         <f>BH15/BH18</f>
         <v>0.98058252427184467</v>
       </c>
-      <c r="BK15" s="174"/>
+      <c r="BK15" s="164"/>
       <c r="BL15" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!I3,AK80:AS91,9,FALSE),"3rd Group C/D/F/G/H")</f>
         <v>Sweden</v>
@@ -43551,19 +43582,21 @@
       <c r="BV16" s="21"/>
       <c r="BW16" s="114"/>
       <c r="BX16" s="112"/>
-      <c r="BY16" s="173">
+      <c r="BY16" s="163">
         <v>97</v>
       </c>
       <c r="BZ16" s="24" t="str">
         <f>IF(BW12&gt;BW13,BS12,IF(BW12&lt;BW13,BS13,""))</f>
         <v>France</v>
       </c>
-      <c r="CA16" s="61"/>
+      <c r="CA16" s="61">
+        <v>2</v>
+      </c>
       <c r="CB16" s="63"/>
       <c r="CC16" s="25"/>
-      <c r="CD16" s="112" t="str">
+      <c r="CD16" s="112">
         <f>IF(OR(CA16="",CA17="",AND(CB16="",CB17&lt;&gt;""),AND(CB17="",CB16&lt;&gt;""),AND(CC16="",CC17&lt;&gt;""),AND(CC17="",CC16&lt;&gt;"")),"",CA16*1000+CB16*10+CC16)</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="CE16" s="112"/>
       <c r="CF16" s="21"/>
@@ -43813,17 +43846,19 @@
       <c r="BV17" s="21"/>
       <c r="BW17" s="114"/>
       <c r="BX17" s="115"/>
-      <c r="BY17" s="174"/>
+      <c r="BY17" s="164"/>
       <c r="BZ17" s="26" t="str">
         <f>IF(BW20&gt;BW21,BS20,IF(BW20&lt;BW21,BS21,""))</f>
         <v>Morocco</v>
       </c>
-      <c r="CA17" s="62"/>
+      <c r="CA17" s="62">
+        <v>0</v>
+      </c>
       <c r="CB17" s="64"/>
       <c r="CC17" s="27"/>
-      <c r="CD17" s="113" t="str">
+      <c r="CD17" s="113">
         <f>IF(CD16="","",CA17*1000+CB17*10+CC17)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CE17" s="117"/>
       <c r="CF17" s="21"/>
@@ -44017,7 +44052,7 @@
         <f>MAX(BH14:BH17)+1</f>
         <v>51.5</v>
       </c>
-      <c r="BK18" s="173">
+      <c r="BK18" s="163">
         <v>73</v>
       </c>
       <c r="BL18" s="24" t="str">
@@ -44127,7 +44162,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BK19" s="174"/>
+      <c r="BK19" s="164"/>
       <c r="BL19" s="26" t="str">
         <f>AS15</f>
         <v>Canada</v>
@@ -44407,7 +44442,7 @@
       <c r="BO20" s="21"/>
       <c r="BP20" s="114"/>
       <c r="BQ20" s="112"/>
-      <c r="BR20" s="173">
+      <c r="BR20" s="163">
         <v>90</v>
       </c>
       <c r="BS20" s="24" t="str">
@@ -44682,7 +44717,7 @@
         <v>46203.041666666672</v>
       </c>
       <c r="BQ21" s="115"/>
-      <c r="BR21" s="174"/>
+      <c r="BR21" s="164"/>
       <c r="BS21" s="26" t="str">
         <f>IF(BP22&gt;BP23,BL22,IF(BP22&lt;BP23,BL23,""))</f>
         <v>Morocco</v>
@@ -44938,7 +44973,7 @@
         <f>BH22/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK22" s="173">
+      <c r="BK22" s="163">
         <v>75</v>
       </c>
       <c r="BL22" s="24" t="str">
@@ -45204,7 +45239,7 @@
         <f>BH23/BH24</f>
         <v>0</v>
       </c>
-      <c r="BK23" s="174"/>
+      <c r="BK23" s="164"/>
       <c r="BL23" s="26" t="str">
         <f>AS21</f>
         <v>Morocco</v>
@@ -45233,19 +45268,21 @@
       <c r="CC23" s="21"/>
       <c r="CD23" s="114"/>
       <c r="CE23" s="112"/>
-      <c r="CF23" s="173">
+      <c r="CF23" s="163">
         <v>101</v>
       </c>
       <c r="CG23" s="24" t="str">
         <f>IF(CD16&gt;CD17,BZ16,IF(CD16&lt;CD17,BZ17,""))</f>
-        <v/>
-      </c>
-      <c r="CH23" s="61"/>
+        <v>France</v>
+      </c>
+      <c r="CH23" s="61">
+        <v>0</v>
+      </c>
       <c r="CI23" s="63"/>
       <c r="CJ23" s="25"/>
-      <c r="CK23" s="112" t="str">
+      <c r="CK23" s="112">
         <f>IF(OR(CH23="",CH24="",AND(CI23="",CI24&lt;&gt;""),AND(CI24="",CI23&lt;&gt;""),AND(CJ23="",CJ24&lt;&gt;""),AND(CJ24="",CJ23&lt;&gt;"")),"",CH23*1000+CI23*10+CJ23)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:95" x14ac:dyDescent="0.2">
@@ -45454,17 +45491,19 @@
       <c r="CC24" s="21"/>
       <c r="CD24" s="114"/>
       <c r="CE24" s="115"/>
-      <c r="CF24" s="174"/>
+      <c r="CF24" s="164"/>
       <c r="CG24" s="26" t="str">
         <f>IF(CD32&gt;CD33,BZ32,IF(CD32&lt;CD33,BZ33,""))</f>
-        <v/>
-      </c>
-      <c r="CH24" s="62"/>
+        <v>Spain</v>
+      </c>
+      <c r="CH24" s="62">
+        <v>2</v>
+      </c>
       <c r="CI24" s="64"/>
       <c r="CJ24" s="27"/>
-      <c r="CK24" s="113" t="str">
+      <c r="CK24" s="113">
         <f>IF(CK23="","",CH24*1000+CI24*10+CJ24)</f>
-        <v/>
+        <v>2000</v>
       </c>
     </row>
     <row r="25" spans="1:95" x14ac:dyDescent="0.2">
@@ -45807,7 +45846,7 @@
         <f>BH26/BH30</f>
         <v>0</v>
       </c>
-      <c r="BK26" s="173">
+      <c r="BK26" s="163">
         <v>83</v>
       </c>
       <c r="BL26" s="24" t="str">
@@ -46077,7 +46116,7 @@
         <f>BH27/BH30</f>
         <v>0.98039215686274506</v>
       </c>
-      <c r="BK27" s="174"/>
+      <c r="BK27" s="164"/>
       <c r="BL27" s="26" t="str">
         <f>AS75</f>
         <v>Croatia</v>
@@ -46354,7 +46393,7 @@
       <c r="BO28" s="21"/>
       <c r="BP28" s="114"/>
       <c r="BQ28" s="112"/>
-      <c r="BR28" s="173">
+      <c r="BR28" s="163">
         <v>93</v>
       </c>
       <c r="BS28" s="24" t="str">
@@ -46621,7 +46660,7 @@
         <v>46205.791666666672</v>
       </c>
       <c r="BQ29" s="115"/>
-      <c r="BR29" s="174"/>
+      <c r="BR29" s="164"/>
       <c r="BS29" s="26" t="str">
         <f>IF(BP30&gt;BP31,BL30,IF(BP30&lt;BP31,BL31,""))</f>
         <v>Spain</v>
@@ -46837,7 +46876,7 @@
         <f>MAX(BH26:BH29)+1</f>
         <v>51</v>
       </c>
-      <c r="BK30" s="173">
+      <c r="BK30" s="163">
         <v>84</v>
       </c>
       <c r="BL30" s="24" t="str">
@@ -46950,7 +46989,7 @@
         <f>IF(OR(F31="",G31=""),"",IF(F31&gt;G31,1,IF(F31&lt;G31,-1,0)))</f>
         <v>0</v>
       </c>
-      <c r="BK31" s="174"/>
+      <c r="BK31" s="164"/>
       <c r="BL31" s="26" t="str">
         <f>AS63</f>
         <v>Austria</v>
@@ -47228,19 +47267,21 @@
       <c r="BV32" s="21"/>
       <c r="BW32" s="114"/>
       <c r="BX32" s="112"/>
-      <c r="BY32" s="173">
+      <c r="BY32" s="163">
         <v>98</v>
       </c>
       <c r="BZ32" s="24" t="str">
         <f>IF(BW28&gt;BW29,BS28,IF(BW28&lt;BW29,BS29,""))</f>
         <v>Spain</v>
       </c>
-      <c r="CA32" s="61"/>
+      <c r="CA32" s="61">
+        <v>2</v>
+      </c>
       <c r="CB32" s="63"/>
       <c r="CC32" s="25"/>
-      <c r="CD32" s="116" t="str">
+      <c r="CD32" s="116">
         <f>IF(OR(CA32="",CA33="",AND(CB32="",CB33&lt;&gt;""),AND(CB33="",CB32&lt;&gt;""),AND(CC32="",CC33&lt;&gt;""),AND(CC33="",CC32&lt;&gt;"")),"",CA32*1000+CB32*10+CC32)</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="CE32" s="112"/>
       <c r="CK32" s="114"/>
@@ -47492,29 +47533,31 @@
       <c r="BV33" s="21"/>
       <c r="BW33" s="114"/>
       <c r="BX33" s="115"/>
-      <c r="BY33" s="174"/>
+      <c r="BY33" s="164"/>
       <c r="BZ33" s="26" t="str">
         <f>IF(BW36&gt;BW37,BS36,IF(BW36&lt;BW37,BS37,""))</f>
         <v>Belgium</v>
       </c>
-      <c r="CA33" s="62"/>
+      <c r="CA33" s="62">
+        <v>1</v>
+      </c>
       <c r="CB33" s="64"/>
       <c r="CC33" s="27"/>
-      <c r="CD33" s="112" t="str">
+      <c r="CD33" s="112">
         <f>IF(CD32="","",CA33*1000+CB33*10+CC33)</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="CE33" s="112"/>
       <c r="CK33" s="114"/>
       <c r="CL33" s="112"/>
-      <c r="CM33" s="176" t="str" cm="1">
+      <c r="CM33" s="165" t="str" cm="1">
         <f t="array" ref="CM33">INDEX(T,8,lang)</f>
         <v>Final</v>
       </c>
-      <c r="CN33" s="177"/>
-      <c r="CO33" s="177"/>
-      <c r="CP33" s="177"/>
-      <c r="CQ33" s="178"/>
+      <c r="CN33" s="166"/>
+      <c r="CO33" s="166"/>
+      <c r="CP33" s="166"/>
+      <c r="CQ33" s="167"/>
     </row>
     <row r="34" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A34" s="16">
@@ -47738,7 +47781,7 @@
         <f>BH34/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK34" s="173">
+      <c r="BK34" s="163">
         <v>81</v>
       </c>
       <c r="BL34" s="24" t="str">
@@ -47771,11 +47814,11 @@
       <c r="CE34" s="112"/>
       <c r="CK34" s="114"/>
       <c r="CL34" s="112"/>
-      <c r="CM34" s="179"/>
-      <c r="CN34" s="180"/>
-      <c r="CO34" s="180"/>
-      <c r="CP34" s="180"/>
-      <c r="CQ34" s="181"/>
+      <c r="CM34" s="168"/>
+      <c r="CN34" s="169"/>
+      <c r="CO34" s="169"/>
+      <c r="CP34" s="169"/>
+      <c r="CQ34" s="170"/>
     </row>
     <row r="35" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A35" s="16">
@@ -47999,7 +48042,7 @@
         <f>BH35/BH36</f>
         <v>0</v>
       </c>
-      <c r="BK35" s="174"/>
+      <c r="BK35" s="164"/>
       <c r="BL35" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!F3,AK80:AS91,9,FALSE),"3rd Group B/E/F/I/J")</f>
         <v>Bosnia and Herzegovina</v>
@@ -48230,7 +48273,7 @@
       <c r="BO36" s="21"/>
       <c r="BP36" s="114"/>
       <c r="BQ36" s="112"/>
-      <c r="BR36" s="173">
+      <c r="BR36" s="163">
         <v>94</v>
       </c>
       <c r="BS36" s="24" t="str">
@@ -48356,7 +48399,7 @@
         <v>46204.833333333336</v>
       </c>
       <c r="BQ37" s="115"/>
-      <c r="BR37" s="174"/>
+      <c r="BR37" s="164"/>
       <c r="BS37" s="26" t="str">
         <f>IF(BP38&gt;BP39,BL38,IF(BP38&lt;BP39,BL39,""))</f>
         <v>Belgium</v>
@@ -48385,12 +48428,12 @@
       <c r="CJ37" s="21"/>
       <c r="CK37" s="114"/>
       <c r="CL37" s="112"/>
-      <c r="CM37" s="173">
+      <c r="CM37" s="163">
         <v>104</v>
       </c>
       <c r="CN37" s="24" t="str">
         <f>IF(CK23&gt;CK24,CG23,IF(CK23&lt;CK24,CG24,""))</f>
-        <v/>
+        <v>Spain</v>
       </c>
       <c r="CO37" s="61"/>
       <c r="CP37" s="63"/>
@@ -48626,7 +48669,7 @@
         <f>BH38/BH42</f>
         <v>0</v>
       </c>
-      <c r="BK38" s="173">
+      <c r="BK38" s="163">
         <v>82</v>
       </c>
       <c r="BL38" s="24" t="str">
@@ -48658,10 +48701,10 @@
       <c r="CI38" s="21"/>
       <c r="CJ38" s="21"/>
       <c r="CL38" s="115"/>
-      <c r="CM38" s="174"/>
+      <c r="CM38" s="164"/>
       <c r="CN38" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG55,IF(CK55&lt;CK56,CG56,""))</f>
-        <v/>
+        <v>Argentina</v>
       </c>
       <c r="CO38" s="62"/>
       <c r="CP38" s="64"/>
@@ -48897,7 +48940,7 @@
         <f>BH39/BH42</f>
         <v>0</v>
       </c>
-      <c r="BK39" s="174"/>
+      <c r="BK39" s="164"/>
       <c r="BL39" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!H3,AK80:AS91,9,FALSE),"3rd Group A/E/H/I/J")</f>
         <v>Senegal</v>
@@ -49587,7 +49630,7 @@
         <f>MAX(BH38:BH41)+1</f>
         <v>1</v>
       </c>
-      <c r="BK42" s="173">
+      <c r="BK42" s="163">
         <v>76</v>
       </c>
       <c r="BL42" s="24" t="str">
@@ -49686,7 +49729,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BK43" s="174"/>
+      <c r="BK43" s="164"/>
       <c r="BL43" s="26" t="str">
         <f>AS39</f>
         <v>Japan</v>
@@ -49948,7 +49991,7 @@
       <c r="BO44" s="21"/>
       <c r="BP44" s="114"/>
       <c r="BQ44" s="112"/>
-      <c r="BR44" s="173">
+      <c r="BR44" s="163">
         <v>91</v>
       </c>
       <c r="BS44" s="24" t="str">
@@ -49965,14 +50008,14 @@
         <v>1000</v>
       </c>
       <c r="CK44" s="114"/>
-      <c r="CM44" s="176" t="str" cm="1">
+      <c r="CM44" s="165" t="str" cm="1">
         <f t="array" ref="CM44">INDEX(T,7,lang)</f>
         <v>Third-Place Play-Off</v>
       </c>
-      <c r="CN44" s="177"/>
-      <c r="CO44" s="177"/>
-      <c r="CP44" s="177"/>
-      <c r="CQ44" s="178"/>
+      <c r="CN44" s="166"/>
+      <c r="CO44" s="166"/>
+      <c r="CP44" s="166"/>
+      <c r="CQ44" s="167"/>
     </row>
     <row r="45" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="16">
@@ -50213,7 +50256,7 @@
         <v>46203.708333333336</v>
       </c>
       <c r="BQ45" s="115"/>
-      <c r="BR45" s="174"/>
+      <c r="BR45" s="164"/>
       <c r="BS45" s="26" t="str">
         <f>IF(BP46&gt;BP47,BL46,IF(BP46&lt;BP47,BL47,""))</f>
         <v>Norway</v>
@@ -50228,11 +50271,11 @@
         <v>2000</v>
       </c>
       <c r="CK45" s="114"/>
-      <c r="CM45" s="179"/>
-      <c r="CN45" s="180"/>
-      <c r="CO45" s="180"/>
-      <c r="CP45" s="180"/>
-      <c r="CQ45" s="181"/>
+      <c r="CM45" s="168"/>
+      <c r="CN45" s="169"/>
+      <c r="CO45" s="169"/>
+      <c r="CP45" s="169"/>
+      <c r="CQ45" s="170"/>
     </row>
     <row r="46" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A46" s="16">
@@ -50456,7 +50499,7 @@
         <f>BH46/BH48</f>
         <v>0</v>
       </c>
-      <c r="BK46" s="173">
+      <c r="BK46" s="163">
         <v>78</v>
       </c>
       <c r="BL46" s="24" t="str">
@@ -50704,7 +50747,7 @@
         <f>BH47/BH48</f>
         <v>0</v>
       </c>
-      <c r="BK47" s="174"/>
+      <c r="BK47" s="164"/>
       <c r="BL47" s="26" t="str">
         <f>AS57</f>
         <v>Norway</v>
@@ -50953,28 +50996,30 @@
       <c r="BV48" s="21"/>
       <c r="BW48" s="114"/>
       <c r="BX48" s="112"/>
-      <c r="BY48" s="173">
+      <c r="BY48" s="163">
         <v>99</v>
       </c>
       <c r="BZ48" s="24" t="str">
         <f>IF(BW44&gt;BW45,BS44,IF(BW44&lt;BW45,BS45,""))</f>
         <v>Norway</v>
       </c>
-      <c r="CA48" s="61"/>
+      <c r="CA48" s="61">
+        <v>1</v>
+      </c>
       <c r="CB48" s="63"/>
       <c r="CC48" s="25"/>
-      <c r="CD48" s="112" t="str">
+      <c r="CD48" s="112">
         <f>IF(OR(CA48="",CA49="",AND(CB48="",CB49&lt;&gt;""),AND(CB49="",CB48&lt;&gt;""),AND(CC48="",CC49&lt;&gt;""),AND(CC49="",CC48&lt;&gt;"")),"",CA48*1000+CB48*10+CC48)</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="CK48" s="114"/>
       <c r="CL48" s="112"/>
-      <c r="CM48" s="173">
+      <c r="CM48" s="163">
         <v>103</v>
       </c>
       <c r="CN48" s="24" t="str">
         <f>IF(CK23&gt;CK24,CG24,IF(CK23&lt;CK24,CG23,""))</f>
-        <v/>
+        <v>France</v>
       </c>
       <c r="CO48" s="61"/>
       <c r="CP48" s="63"/>
@@ -51078,24 +51123,26 @@
       <c r="BV49" s="21"/>
       <c r="BW49" s="114"/>
       <c r="BX49" s="115"/>
-      <c r="BY49" s="174"/>
+      <c r="BY49" s="164"/>
       <c r="BZ49" s="26" t="str">
         <f>IF(BW52&gt;BW53,BS52,IF(BW52&lt;BW53,BS53,""))</f>
         <v>England</v>
       </c>
-      <c r="CA49" s="62"/>
+      <c r="CA49" s="62">
+        <v>2</v>
+      </c>
       <c r="CB49" s="64"/>
       <c r="CC49" s="27"/>
-      <c r="CD49" s="113" t="str">
+      <c r="CD49" s="113">
         <f>IF(CD48="","",CA49*1000+CB49*10+CC49)</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="CK49" s="114"/>
       <c r="CL49" s="115"/>
-      <c r="CM49" s="174"/>
+      <c r="CM49" s="164"/>
       <c r="CN49" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG56,IF(CK55&lt;CK56,CG55,""))</f>
-        <v/>
+        <v>England</v>
       </c>
       <c r="CO49" s="62"/>
       <c r="CP49" s="64"/>
@@ -51331,7 +51378,7 @@
         <f>BH50/BH54</f>
         <v>0</v>
       </c>
-      <c r="BK50" s="173">
+      <c r="BK50" s="163">
         <v>79</v>
       </c>
       <c r="BL50" s="24" t="str">
@@ -51590,7 +51637,7 @@
         <f>BH51/BH54</f>
         <v>0</v>
       </c>
-      <c r="BK51" s="174"/>
+      <c r="BK51" s="164"/>
       <c r="BL51" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!D3,AK80:AS91,9,FALSE),"3rd Group C/E/F/H/I")</f>
         <v>Ecuador</v>
@@ -51856,7 +51903,7 @@
       <c r="BO52" s="21"/>
       <c r="BP52" s="114"/>
       <c r="BQ52" s="112"/>
-      <c r="BR52" s="173">
+      <c r="BR52" s="163">
         <v>92</v>
       </c>
       <c r="BS52" s="24" t="str">
@@ -52117,7 +52164,7 @@
         <v>46204.666666666672</v>
       </c>
       <c r="BQ53" s="115"/>
-      <c r="BR53" s="174"/>
+      <c r="BR53" s="164"/>
       <c r="BS53" s="26" t="str">
         <f>IF(BP54&gt;BP55,BL54,IF(BP54&lt;BP55,BL55,""))</f>
         <v>England</v>
@@ -52327,7 +52374,7 @@
         <f>MAX(BH50:BH53)+1</f>
         <v>51.5</v>
       </c>
-      <c r="BK54" s="173">
+      <c r="BK54" s="163">
         <v>80</v>
       </c>
       <c r="BL54" s="24" t="str">
@@ -52454,7 +52501,7 @@
         <f t="shared" si="23"/>
         <v>-1</v>
       </c>
-      <c r="BK55" s="174"/>
+      <c r="BK55" s="164"/>
       <c r="BL55" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!K3,AK80:AS91,9,FALSE),"3rd Group E/H/I/J/K")</f>
         <v>DR Congo</v>
@@ -52483,19 +52530,21 @@
       <c r="CC55" s="21"/>
       <c r="CD55" s="114"/>
       <c r="CE55" s="112"/>
-      <c r="CF55" s="173">
+      <c r="CF55" s="163">
         <v>102</v>
       </c>
       <c r="CG55" s="24" t="str">
         <f>IF(CD48&gt;CD49,BZ48,IF(CD48&lt;CD49,BZ49,""))</f>
-        <v/>
-      </c>
-      <c r="CH55" s="61"/>
+        <v>England</v>
+      </c>
+      <c r="CH55" s="61">
+        <v>1</v>
+      </c>
       <c r="CI55" s="63"/>
       <c r="CJ55" s="25"/>
-      <c r="CK55" s="116" t="str">
+      <c r="CK55" s="116">
         <f>IF(OR(CH55="",CH56="",AND(CI55="",CI56&lt;&gt;""),AND(CI56="",CI55&lt;&gt;""),AND(CJ55="",CJ56&lt;&gt;""),AND(CJ56="",CJ55&lt;&gt;"")),"",CH55*1000+CI55*10+CJ55)</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="CL55" s="112"/>
     </row>
@@ -52746,17 +52795,19 @@
       <c r="CC56" s="21"/>
       <c r="CD56" s="114"/>
       <c r="CE56" s="115"/>
-      <c r="CF56" s="174"/>
+      <c r="CF56" s="164"/>
       <c r="CG56" s="26" t="str">
         <f>IF(CD64&gt;CD65,BZ64,IF(CD64&lt;CD65,BZ65,""))</f>
-        <v/>
-      </c>
-      <c r="CH56" s="62"/>
+        <v>Argentina</v>
+      </c>
+      <c r="CH56" s="62">
+        <v>2</v>
+      </c>
       <c r="CI56" s="64"/>
       <c r="CJ56" s="27"/>
-      <c r="CK56" s="112" t="str">
+      <c r="CK56" s="112">
         <f>IF(CK55="","",CH56*1000+CI56*10+CJ56)</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="CL56" s="112"/>
     </row>
@@ -53237,7 +53288,7 @@
         <f>BH58/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK58" s="173">
+      <c r="BK58" s="163">
         <v>86</v>
       </c>
       <c r="BL58" s="24" t="str">
@@ -53491,7 +53542,7 @@
         <f>BH59/BH60</f>
         <v>0</v>
       </c>
-      <c r="BK59" s="174"/>
+      <c r="BK59" s="164"/>
       <c r="BL59" s="26" t="str">
         <f>AS51</f>
         <v>Cape Verde</v>
@@ -53720,7 +53771,7 @@
       <c r="BO60" s="21"/>
       <c r="BP60" s="114"/>
       <c r="BQ60" s="112"/>
-      <c r="BR60" s="173">
+      <c r="BR60" s="163">
         <v>95</v>
       </c>
       <c r="BS60" s="24" t="str">
@@ -53839,7 +53890,7 @@
         <v>46206.75</v>
       </c>
       <c r="BQ61" s="115"/>
-      <c r="BR61" s="174"/>
+      <c r="BR61" s="164"/>
       <c r="BS61" s="26" t="str">
         <f>IF(BP62&gt;BP63,BL62,IF(BP62&lt;BP63,BL63,""))</f>
         <v>Egypt</v>
@@ -54088,7 +54139,7 @@
         <f>BH62/BH66</f>
         <v>0</v>
       </c>
-      <c r="BK62" s="173">
+      <c r="BK62" s="163">
         <v>88</v>
       </c>
       <c r="BL62" s="24" t="str">
@@ -54346,7 +54397,7 @@
         <f>BH63/BH66</f>
         <v>0.98067632850241548</v>
       </c>
-      <c r="BK63" s="174"/>
+      <c r="BK63" s="164"/>
       <c r="BL63" s="26" t="str">
         <f>AS45</f>
         <v>Egypt</v>
@@ -54618,19 +54669,21 @@
       <c r="BV64" s="21"/>
       <c r="BW64" s="114"/>
       <c r="BX64" s="112"/>
-      <c r="BY64" s="173">
+      <c r="BY64" s="163">
         <v>100</v>
       </c>
       <c r="BZ64" s="24" t="str">
         <f>IF(BW60&gt;BW61,BS60,IF(BW60&lt;BW61,BS61,""))</f>
         <v>Argentina</v>
       </c>
-      <c r="CA64" s="61"/>
+      <c r="CA64" s="61">
+        <v>3</v>
+      </c>
       <c r="CB64" s="63"/>
       <c r="CC64" s="25"/>
-      <c r="CD64" s="116" t="str">
+      <c r="CD64" s="116">
         <f>IF(OR(CA64="",CA65="",AND(CB64="",CB65&lt;&gt;""),AND(CB65="",CB64&lt;&gt;""),AND(CC64="",CC65&lt;&gt;""),AND(CC65="",CC64&lt;&gt;"")),"",CA64*1000+CB64*10+CC64)</f>
-        <v/>
+        <v>3000</v>
       </c>
     </row>
     <row r="65" spans="1:95" x14ac:dyDescent="0.2">
@@ -54876,17 +54929,19 @@
       <c r="BV65" s="21"/>
       <c r="BW65" s="114"/>
       <c r="BX65" s="115"/>
-      <c r="BY65" s="174"/>
+      <c r="BY65" s="164"/>
       <c r="BZ65" s="26" t="str">
         <f>IF(BW68&gt;BW69,BS68,IF(BW68&lt;BW69,BS69,""))</f>
         <v>Switzerland</v>
       </c>
-      <c r="CA65" s="62"/>
+      <c r="CA65" s="62">
+        <v>1</v>
+      </c>
       <c r="CB65" s="64"/>
       <c r="CC65" s="27"/>
-      <c r="CD65" s="112" t="str">
+      <c r="CD65" s="112">
         <f>IF(CD64="","",CA65*1000+CB65*10+CC65)</f>
-        <v/>
+        <v>1000</v>
       </c>
     </row>
     <row r="66" spans="1:95" x14ac:dyDescent="0.2">
@@ -55076,7 +55131,7 @@
         <f>MAX(BH62:BH65)+1</f>
         <v>51.75</v>
       </c>
-      <c r="BK66" s="173">
+      <c r="BK66" s="163">
         <v>85</v>
       </c>
       <c r="BL66" s="24" t="str">
@@ -55182,7 +55237,7 @@
         <f t="shared" si="23"/>
         <v>-1</v>
       </c>
-      <c r="BK67" s="174"/>
+      <c r="BK67" s="164"/>
       <c r="BL67" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!E3,AK80:AS91,9,FALSE),"3rd Group E/F/G/I/J")</f>
         <v>Algeria</v>
@@ -55444,7 +55499,7 @@
       <c r="BO68" s="21"/>
       <c r="BP68" s="114"/>
       <c r="BQ68" s="112"/>
-      <c r="BR68" s="173">
+      <c r="BR68" s="163">
         <v>96</v>
       </c>
       <c r="BS68" s="24" t="str">
@@ -55460,25 +55515,25 @@
         <f>IF(OR(BT68="",BT69="",AND(BU68="",BU69&lt;&gt;""),AND(BU69="",BU68&lt;&gt;""),AND(BV68="",BV69&lt;&gt;""),AND(BV69="",BV68&lt;&gt;"")),"",BT68*1000+BU68*10+BV68)</f>
         <v>1000</v>
       </c>
-      <c r="CE68" s="175" t="str">
+      <c r="CE68" s="195" t="str">
         <f>INDEX(T,144,lang)</f>
         <v>World Champion 2026</v>
       </c>
-      <c r="CF68" s="175"/>
-      <c r="CG68" s="175"/>
-      <c r="CH68" s="175"/>
-      <c r="CI68" s="175"/>
-      <c r="CJ68" s="175"/>
-      <c r="CK68" s="163" t="str">
+      <c r="CF68" s="195"/>
+      <c r="CG68" s="195"/>
+      <c r="CH68" s="195"/>
+      <c r="CI68" s="195"/>
+      <c r="CJ68" s="195"/>
+      <c r="CK68" s="185" t="str">
         <f>IF(CR37&gt;CR38,CN37,IF(CR37&lt;CR38,CN38,""))</f>
         <v/>
       </c>
-      <c r="CL68" s="163"/>
-      <c r="CM68" s="163"/>
-      <c r="CN68" s="163"/>
-      <c r="CO68" s="163"/>
-      <c r="CP68" s="163"/>
-      <c r="CQ68" s="163"/>
+      <c r="CL68" s="185"/>
+      <c r="CM68" s="185"/>
+      <c r="CN68" s="185"/>
+      <c r="CO68" s="185"/>
+      <c r="CP68" s="185"/>
+      <c r="CQ68" s="185"/>
     </row>
     <row r="69" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A69" s="16">
@@ -55720,7 +55775,7 @@
         <v>46207.0625</v>
       </c>
       <c r="BQ69" s="115"/>
-      <c r="BR69" s="174"/>
+      <c r="BR69" s="164"/>
       <c r="BS69" s="26" t="str">
         <f>IF(BP70&gt;BP71,BL70,IF(BP70&lt;BP71,BL71,""))</f>
         <v>Colombia</v>
@@ -55734,19 +55789,19 @@
         <f>IF(BW68="","",BT69*1000+BU69*10+BV69)</f>
         <v>0</v>
       </c>
-      <c r="CE69" s="175"/>
-      <c r="CF69" s="175"/>
-      <c r="CG69" s="175"/>
-      <c r="CH69" s="175"/>
-      <c r="CI69" s="175"/>
-      <c r="CJ69" s="175"/>
-      <c r="CK69" s="163"/>
-      <c r="CL69" s="163"/>
-      <c r="CM69" s="163"/>
-      <c r="CN69" s="163"/>
-      <c r="CO69" s="163"/>
-      <c r="CP69" s="163"/>
-      <c r="CQ69" s="163"/>
+      <c r="CE69" s="195"/>
+      <c r="CF69" s="195"/>
+      <c r="CG69" s="195"/>
+      <c r="CH69" s="195"/>
+      <c r="CI69" s="195"/>
+      <c r="CJ69" s="195"/>
+      <c r="CK69" s="185"/>
+      <c r="CL69" s="185"/>
+      <c r="CM69" s="185"/>
+      <c r="CN69" s="185"/>
+      <c r="CO69" s="185"/>
+      <c r="CP69" s="185"/>
+      <c r="CQ69" s="185"/>
     </row>
     <row r="70" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A70" s="16">
@@ -55971,7 +56026,7 @@
         <f>BH70/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK70" s="173">
+      <c r="BK70" s="163">
         <v>87</v>
       </c>
       <c r="BL70" s="24" t="str">
@@ -56213,7 +56268,7 @@
         <f>BH71/BH72</f>
         <v>0</v>
       </c>
-      <c r="BK71" s="174"/>
+      <c r="BK71" s="164"/>
       <c r="BL71" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!J3,AK80:AS91,9,FALSE),"3rd Group D/E/I/J/L")</f>
         <v>Ghana</v>
@@ -57919,13 +57974,13 @@
     <row r="83" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="73"/>
       <c r="B83" s="73"/>
-      <c r="C83" s="164" t="s">
+      <c r="C83" s="186" t="s">
         <v>3183</v>
       </c>
-      <c r="D83" s="165"/>
-      <c r="E83" s="165"/>
-      <c r="F83" s="165"/>
-      <c r="G83" s="166"/>
+      <c r="D83" s="187"/>
+      <c r="E83" s="187"/>
+      <c r="F83" s="187"/>
+      <c r="G83" s="188"/>
       <c r="H83" s="75"/>
       <c r="I83" s="69"/>
       <c r="J83" s="99" t="str">
@@ -58023,11 +58078,11 @@
     <row r="84" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="73"/>
       <c r="B84" s="73"/>
-      <c r="C84" s="167"/>
-      <c r="D84" s="168"/>
-      <c r="E84" s="168"/>
-      <c r="F84" s="168"/>
-      <c r="G84" s="169"/>
+      <c r="C84" s="189"/>
+      <c r="D84" s="190"/>
+      <c r="E84" s="190"/>
+      <c r="F84" s="190"/>
+      <c r="G84" s="191"/>
       <c r="H84" s="75"/>
       <c r="I84" s="69"/>
       <c r="J84" s="99" t="str">
@@ -58137,11 +58192,11 @@
     <row r="85" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="73"/>
       <c r="B85" s="73"/>
-      <c r="C85" s="167"/>
-      <c r="D85" s="168"/>
-      <c r="E85" s="168"/>
-      <c r="F85" s="168"/>
-      <c r="G85" s="169"/>
+      <c r="C85" s="189"/>
+      <c r="D85" s="190"/>
+      <c r="E85" s="190"/>
+      <c r="F85" s="190"/>
+      <c r="G85" s="191"/>
       <c r="H85" s="75"/>
       <c r="I85" s="69"/>
       <c r="J85" s="99" t="str">
@@ -58251,11 +58306,11 @@
     <row r="86" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="73"/>
       <c r="B86" s="73"/>
-      <c r="C86" s="167"/>
-      <c r="D86" s="168"/>
-      <c r="E86" s="168"/>
-      <c r="F86" s="168"/>
-      <c r="G86" s="169"/>
+      <c r="C86" s="189"/>
+      <c r="D86" s="190"/>
+      <c r="E86" s="190"/>
+      <c r="F86" s="190"/>
+      <c r="G86" s="191"/>
       <c r="H86" s="75"/>
       <c r="I86" s="69"/>
       <c r="J86" s="99" t="str">
@@ -58365,11 +58420,11 @@
     <row r="87" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="73"/>
       <c r="B87" s="73"/>
-      <c r="C87" s="167"/>
-      <c r="D87" s="168"/>
-      <c r="E87" s="168"/>
-      <c r="F87" s="168"/>
-      <c r="G87" s="169"/>
+      <c r="C87" s="189"/>
+      <c r="D87" s="190"/>
+      <c r="E87" s="190"/>
+      <c r="F87" s="190"/>
+      <c r="G87" s="191"/>
       <c r="H87" s="75"/>
       <c r="I87" s="69"/>
       <c r="J87" s="99" t="str">
@@ -58479,11 +58534,11 @@
     <row r="88" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="73"/>
       <c r="B88" s="73"/>
-      <c r="C88" s="170"/>
-      <c r="D88" s="171"/>
-      <c r="E88" s="171"/>
-      <c r="F88" s="171"/>
-      <c r="G88" s="172"/>
+      <c r="C88" s="192"/>
+      <c r="D88" s="193"/>
+      <c r="E88" s="193"/>
+      <c r="F88" s="193"/>
+      <c r="G88" s="194"/>
       <c r="H88" s="75"/>
       <c r="I88" s="69"/>
       <c r="J88" s="99" t="str">
@@ -59088,23 +59143,23 @@
       </c>
       <c r="S102" s="127" t="str">
         <f>IF(OR(CA16="",CA17=""),"",IF(CA16&gt;CA17,BZ16,IF(CA16&lt;CA17,BZ17,IF(OR(CB16="",CB17=""),"draw",IF(CB16&gt;CB17,BZ16,IF(CB16&lt;CB17,BZ17,IF(OR(CC16="",CC17=""),"draw",IF(CC16&gt;CC17,BZ16,IF(CC16&lt;CC17,BZ17,"draw")))))))))</f>
-        <v/>
-      </c>
-      <c r="T102" s="127" cm="1">
+        <v>France</v>
+      </c>
+      <c r="T102" s="127" t="str" cm="1">
         <f t="array" ref="T102">IF(OR(S102="",S102="draw"),INDEX(T,98,lang),S102)</f>
-        <v>0</v>
+        <v>France</v>
       </c>
       <c r="U102" s="123" t="str">
         <f>IF(OR(CA16="",CA17=""),"",IF(CA16&lt;CA17,BZ16,IF(CA16&gt;CA17,BZ17,IF(OR(CB16="",CB17=""),"draw",IF(CB16&lt;CB17,BZ16,IF(CB16&gt;CB17,BZ17,IF(OR(CC16="",CC17=""),"draw",IF(CC16&lt;CC17,BZ16,IF(CC16&gt;CC17,BZ17,"draw")))))))))</f>
-        <v/>
+        <v>Morocco</v>
       </c>
       <c r="X102" s="123" t="str">
         <f>IF(OR(CM16="",CM17=""),"",IF(CM16&lt;CM17,CL16,IF(CM16&gt;CM17,CL17,IF(OR(CN16="",CN17=""),"draw",IF(CN16&lt;CN17,CL16,IF(CN16&gt;CN17,CL17,IF(OR(CO16="",CO17=""),"draw",IF(CO16&lt;CO17,CL16,IF(CO16&gt;CO17,CL17,"draw")))))))))</f>
         <v/>
       </c>
-      <c r="AC102" s="127" cm="1">
+      <c r="AC102" s="127" t="str" cm="1">
         <f t="array" ref="AC102">IF(OR(U102="",U102="draw"),INDEX(T,100,lang),U102)</f>
-        <v>0</v>
+        <v>Morocco</v>
       </c>
     </row>
     <row r="103" spans="18:29" x14ac:dyDescent="0.2">
@@ -59114,23 +59169,23 @@
       </c>
       <c r="S103" s="127" t="str">
         <f>IF(OR(CA32="",CA33=""),"",IF(CA32&gt;CA33,BZ32,IF(CA32&lt;CA33,BZ33,IF(OR(CB32="",CB33=""),"draw",IF(CB32&gt;CB33,BZ32,IF(CB32&lt;CB33,BZ33,IF(OR(CC32="",CC33=""),"draw",IF(CC32&gt;CC33,BZ32,IF(CC32&lt;CC33,BZ33,"draw")))))))))</f>
-        <v/>
-      </c>
-      <c r="T103" s="127" cm="1">
+        <v>Spain</v>
+      </c>
+      <c r="T103" s="127" t="str" cm="1">
         <f t="array" ref="T103">IF(OR(S103="",S103="draw"),INDEX(T,99,lang),S103)</f>
-        <v>0</v>
+        <v>Spain</v>
       </c>
       <c r="U103" s="123" t="str">
         <f>IF(OR(CA32="",CA33=""),"",IF(CA32&lt;CA33,BZ32,IF(CA32&gt;CA33,BZ33,IF(OR(CB32="",CB33=""),"draw",IF(CB32&lt;CB33,BZ32,IF(CB32&gt;CB33,BZ33,IF(OR(CC32="",CC33=""),"draw",IF(CC32&lt;CC33,BZ32,IF(CC32&gt;CC33,BZ33,"draw")))))))))</f>
-        <v/>
+        <v>Belgium</v>
       </c>
       <c r="X103" s="123" t="str">
         <f>IF(OR(CM32="",CM33=""),"",IF(CM32&lt;CM33,CL32,IF(CM32&gt;CM33,CL33,IF(OR(CN32="",CN33=""),"draw",IF(CN32&lt;CN33,CL32,IF(CN32&gt;CN33,CL33,IF(OR(CO32="",CO33=""),"draw",IF(CO32&lt;CO33,CL32,IF(CO32&gt;CO33,CL33,"draw")))))))))</f>
         <v/>
       </c>
-      <c r="AC103" s="127" cm="1">
+      <c r="AC103" s="127" t="str" cm="1">
         <f t="array" ref="AC103">IF(OR(U103="",U103="draw"),INDEX(T,101,lang),U103)</f>
-        <v>0</v>
+        <v>Belgium</v>
       </c>
     </row>
     <row r="107" spans="18:29" x14ac:dyDescent="0.2">
@@ -59150,22 +59205,42 @@
       </c>
       <c r="S111" s="127" t="str">
         <f>IF(OR(CH23="",CH24=""),"",IF(CH23&gt;CH24,CG23,IF(CH23&lt;CH24,CG24,IF(OR(CI23="",CI24=""),"",IF(CI23&gt;CI24,CG23,IF(CI23&lt;CI24,CG24,IF(OR(CJ23="",CJ24=""),"",IF(CJ23&gt;CJ24,CG23,IF(CJ23&lt;CJ24,CG24,"")))))))))</f>
-        <v/>
+        <v>Spain</v>
       </c>
       <c r="T111" s="127" t="str">
         <f>S111</f>
-        <v/>
+        <v>Spain</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="7nWuIQAsd0NKRlhwUK3tOeNHpTch5B5FULy2gxNNaIdJM5RfhFSMzPcx55y+pmM3d73guUy+p5Y+SvIjJZQRaA==" saltValue="Uw23KnM8csnTioq5H8upCA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <dataConsolidate/>
   <mergeCells count="45">
-    <mergeCell ref="BK14:BK15"/>
-    <mergeCell ref="BY16:BY17"/>
-    <mergeCell ref="BK26:BK27"/>
-    <mergeCell ref="BR28:BR29"/>
-    <mergeCell ref="BK22:BK23"/>
+    <mergeCell ref="CK68:CQ69"/>
+    <mergeCell ref="C83:G88"/>
+    <mergeCell ref="BK70:BK71"/>
+    <mergeCell ref="BY48:BY49"/>
+    <mergeCell ref="BY64:BY65"/>
+    <mergeCell ref="CF55:CF56"/>
+    <mergeCell ref="BK58:BK59"/>
+    <mergeCell ref="BR60:BR61"/>
+    <mergeCell ref="BK62:BK63"/>
+    <mergeCell ref="BK66:BK67"/>
+    <mergeCell ref="BR68:BR69"/>
+    <mergeCell ref="BK50:BK51"/>
+    <mergeCell ref="BR52:BR53"/>
+    <mergeCell ref="BK54:BK55"/>
+    <mergeCell ref="CE68:CJ69"/>
+    <mergeCell ref="CF6:CJ7"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="A5:H6"/>
+    <mergeCell ref="J5:P6"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="BR12:BR13"/>
+    <mergeCell ref="BK6:BO7"/>
+    <mergeCell ref="BR6:BV7"/>
+    <mergeCell ref="BY6:CC7"/>
     <mergeCell ref="CF23:CF24"/>
     <mergeCell ref="BK18:BK19"/>
     <mergeCell ref="BR20:BR21"/>
@@ -59181,31 +59256,11 @@
     <mergeCell ref="BK42:BK43"/>
     <mergeCell ref="CM33:CQ34"/>
     <mergeCell ref="CM37:CM38"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="BR12:BR13"/>
-    <mergeCell ref="BK6:BO7"/>
-    <mergeCell ref="BR6:BV7"/>
-    <mergeCell ref="BY6:CC7"/>
-    <mergeCell ref="CF6:CJ7"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="A5:H6"/>
-    <mergeCell ref="J5:P6"/>
-    <mergeCell ref="CK68:CQ69"/>
-    <mergeCell ref="C83:G88"/>
-    <mergeCell ref="BK70:BK71"/>
-    <mergeCell ref="BY48:BY49"/>
-    <mergeCell ref="BY64:BY65"/>
-    <mergeCell ref="CF55:CF56"/>
-    <mergeCell ref="BK58:BK59"/>
-    <mergeCell ref="BR60:BR61"/>
-    <mergeCell ref="BK62:BK63"/>
-    <mergeCell ref="BK66:BK67"/>
-    <mergeCell ref="BR68:BR69"/>
-    <mergeCell ref="BK50:BK51"/>
-    <mergeCell ref="BR52:BR53"/>
-    <mergeCell ref="BK54:BK55"/>
-    <mergeCell ref="CE68:CJ69"/>
+    <mergeCell ref="BK14:BK15"/>
+    <mergeCell ref="BY16:BY17"/>
+    <mergeCell ref="BK26:BK27"/>
+    <mergeCell ref="BR28:BR29"/>
+    <mergeCell ref="BK22:BK23"/>
   </mergeCells>
   <conditionalFormatting sqref="A7:E78">
     <cfRule type="expression" dxfId="228" priority="339">
